--- a/export_dati/06_Step6_Simulazione_Massiva_100.xlsx
+++ b/export_dati/06_Step6_Simulazione_Massiva_100.xlsx
@@ -539,68 +539,68 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>950.3205056459032</v>
+        <v>1030.583435716369</v>
       </c>
       <c r="D2" t="n">
-        <v>17.56403062197292</v>
+        <v>8.757435997200295</v>
       </c>
       <c r="E2" t="n">
-        <v>199.2324098723727</v>
+        <v>190.0120312499433</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8591651916503906</v>
+        <v>0.6508126258850098</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004665159154683352</v>
+        <v>0.007977633737027645</v>
       </c>
       <c r="H2" t="n">
-        <v>950.3205056537798</v>
+        <v>965.6040331780204</v>
       </c>
       <c r="I2" t="n">
-        <v>199.2324098723727</v>
+        <v>190.0120312499433</v>
       </c>
       <c r="J2" t="n">
-        <v>11.77729472285762</v>
+        <v>9.00005786666981</v>
       </c>
       <c r="K2" t="n">
-        <v>7.876678864704445e-09</v>
+        <v>64.97940253834884</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>5.786735899115302</v>
+        <v>0.2426218694695148</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9999641819642425</v>
+        <v>0.956171780136097</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003120962916625834</v>
+        <v>0.0004810095281391377</v>
       </c>
       <c r="Q2" t="n">
-        <v>800.0000005378503</v>
+        <v>955.4964160289745</v>
       </c>
       <c r="R2" t="n">
-        <v>200.4474890987788</v>
+        <v>190.2442073593656</v>
       </c>
       <c r="S2" t="n">
-        <v>14.99994212761442</v>
+        <v>9.000057868482628</v>
       </c>
       <c r="T2" t="n">
-        <v>150.3205051080529</v>
+        <v>75.08701968739467</v>
       </c>
       <c r="U2" t="n">
-        <v>1.21507922640609</v>
+        <v>0.2321761094222836</v>
       </c>
       <c r="V2" t="n">
-        <v>2.564088494358497</v>
+        <v>0.2426218712823331</v>
       </c>
       <c r="W2" t="b">
         <v>1</v>
@@ -612,68 +612,68 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>895.4593418075916</v>
+        <v>958.7264733934807</v>
       </c>
       <c r="D3" t="n">
-        <v>6.562413134269457</v>
+        <v>11.59811089575176</v>
       </c>
       <c r="E3" t="n">
-        <v>211.7112977550989</v>
+        <v>131.5485056501628</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8435835242271423</v>
+        <v>0.7905983924865723</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.01447403151541948</v>
       </c>
       <c r="H3" t="n">
-        <v>928.8432674866848</v>
+        <v>958.7264733942761</v>
       </c>
       <c r="I3" t="n">
-        <v>211.7112977550988</v>
+        <v>176.1525536259194</v>
       </c>
       <c r="J3" t="n">
-        <v>9.0000578674693</v>
+        <v>11.59811089573376</v>
       </c>
       <c r="K3" t="n">
-        <v>33.38392567909318</v>
+        <v>7.954668035381474e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4210854715202e-13</v>
+        <v>44.60404797575669</v>
       </c>
       <c r="M3" t="n">
-        <v>2.437644733199843</v>
+        <v>1.799982385364274e-11</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8620260407793787</v>
+        <v>0.9997066634307018</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0005142472827184365</v>
+        <v>0.001985356215246104</v>
       </c>
       <c r="Q3" t="n">
-        <v>948.1993003050451</v>
+        <v>804.6688490286708</v>
       </c>
       <c r="R3" t="n">
-        <v>210.3905323211192</v>
+        <v>150.0000472862362</v>
       </c>
       <c r="S3" t="n">
-        <v>9.000057839475856</v>
+        <v>11.5068767280431</v>
       </c>
       <c r="T3" t="n">
-        <v>52.73995849745347</v>
+        <v>154.0576243648098</v>
       </c>
       <c r="U3" t="n">
-        <v>1.320765433979744</v>
+        <v>18.45154163607347</v>
       </c>
       <c r="V3" t="n">
-        <v>2.437644705206399</v>
+        <v>0.09123416770866299</v>
       </c>
       <c r="W3" t="b">
         <v>1</v>
@@ -685,68 +685,68 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>971.0630570666581</v>
+        <v>889.7896881509041</v>
       </c>
       <c r="D4" t="n">
-        <v>9.721880135633667</v>
+        <v>7.199121975290029</v>
       </c>
       <c r="E4" t="n">
-        <v>246.5661183841028</v>
+        <v>192.8925602011192</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6636186242103577</v>
+        <v>0.7487070560455322</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00312661100178957</v>
+        <v>0.0107807656750083</v>
       </c>
       <c r="H4" t="n">
-        <v>972.5939420799651</v>
+        <v>928.8432674690713</v>
       </c>
       <c r="I4" t="n">
-        <v>222.3567121550116</v>
+        <v>192.8925602011192</v>
       </c>
       <c r="J4" t="n">
-        <v>9.732523961104201</v>
+        <v>9.000057868187181</v>
       </c>
       <c r="K4" t="n">
-        <v>1.530885013307056</v>
+        <v>39.05357931816718</v>
       </c>
       <c r="L4" t="n">
-        <v>24.2094062290912</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01064382547053455</v>
+        <v>1.800935892897152</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9752882041840766</v>
+        <v>0.9119186050945739</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00145628616486667</v>
+        <v>0.0005032440915117498</v>
       </c>
       <c r="Q4" t="n">
-        <v>846.9423118980399</v>
+        <v>943.9718546444117</v>
       </c>
       <c r="R4" t="n">
-        <v>226.2668238192292</v>
+        <v>192.7318937691159</v>
       </c>
       <c r="S4" t="n">
-        <v>9.677938548165491</v>
+        <v>9.000057868898709</v>
       </c>
       <c r="T4" t="n">
-        <v>124.1207451686182</v>
+        <v>54.18216649350757</v>
       </c>
       <c r="U4" t="n">
-        <v>20.29929456487358</v>
+        <v>0.1606664320032962</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04394158746817567</v>
+        <v>1.80093589360868</v>
       </c>
       <c r="W4" t="b">
         <v>1</v>
@@ -758,68 +758,68 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stains</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>879.0387028373722</v>
+        <v>947.4096550627312</v>
       </c>
       <c r="D5" t="n">
-        <v>9.646879819997553</v>
+        <v>10.09912579247616</v>
       </c>
       <c r="E5" t="n">
-        <v>206.2583865753571</v>
+        <v>154.8411189826099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6068803071975708</v>
+        <v>0.7905983924865723</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0032845763489604</v>
+        <v>0.01447403151541948</v>
       </c>
       <c r="H5" t="n">
-        <v>922.9741913766268</v>
+        <v>947.4096239677104</v>
       </c>
       <c r="I5" t="n">
-        <v>206.2583865753571</v>
+        <v>176.1525977521421</v>
       </c>
       <c r="J5" t="n">
-        <v>9.646879819997549</v>
+        <v>10.02799875499174</v>
       </c>
       <c r="K5" t="n">
-        <v>43.93548853925461</v>
+        <v>3.10950207449423e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>21.31147876953219</v>
       </c>
       <c r="M5" t="n">
-        <v>3.552713678800501e-15</v>
+        <v>0.07112703748441973</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4660404635555797</v>
+        <v>0.968609665537531</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0004958690725527312</v>
+        <v>0.00142754828692048</v>
       </c>
       <c r="Q5" t="n">
-        <v>937.2480469120045</v>
+        <v>829.4624329574276</v>
       </c>
       <c r="R5" t="n">
-        <v>205.5922209695499</v>
+        <v>161.2327367623647</v>
       </c>
       <c r="S5" t="n">
-        <v>9.635460415218885</v>
+        <v>10.04411720692117</v>
       </c>
       <c r="T5" t="n">
-        <v>58.20934407463233</v>
+        <v>117.9472221053036</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6661656058071799</v>
+        <v>6.391617779754853</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01141940477866754</v>
+        <v>0.055008585554992</v>
       </c>
       <c r="W5" t="b">
         <v>1</v>
@@ -831,68 +831,68 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>901.0507251457127</v>
+        <v>918.6608125766529</v>
       </c>
       <c r="D6" t="n">
-        <v>8.594140314134535</v>
+        <v>9.891146119267299</v>
       </c>
       <c r="E6" t="n">
-        <v>204.0188466312755</v>
+        <v>137.2264260381309</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6105899214744568</v>
+        <v>0.7801960110664368</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.01369568612426519</v>
       </c>
       <c r="H6" t="n">
-        <v>928.8432674809297</v>
+        <v>910.503660416069</v>
       </c>
       <c r="I6" t="n">
-        <v>204.0188466312755</v>
+        <v>176.1525536435829</v>
       </c>
       <c r="J6" t="n">
-        <v>9.000057868418914</v>
+        <v>9.896847925488609</v>
       </c>
       <c r="K6" t="n">
-        <v>27.79254233521704</v>
+        <v>8.157152160583905</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>38.92612760545202</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4059175542843789</v>
+        <v>0.005701806221310335</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3679098579149766</v>
+        <v>0.997740922229679</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0004274206376175458</v>
+        <v>0.001539844554627996</v>
       </c>
       <c r="Q6" t="n">
-        <v>947.007585339293</v>
+        <v>808.7030814424336</v>
       </c>
       <c r="R6" t="n">
-        <v>203.3353542261918</v>
+        <v>150.0000472875976</v>
       </c>
       <c r="S6" t="n">
-        <v>9.000057864342002</v>
+        <v>9.830873787286583</v>
       </c>
       <c r="T6" t="n">
-        <v>45.95686019358027</v>
+        <v>109.9577311342193</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6834924050836833</v>
+        <v>12.77362124946677</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4059175502074677</v>
+        <v>0.06027233198071613</v>
       </c>
       <c r="W6" t="b">
         <v>1</v>
@@ -904,68 +904,68 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>899.2379399366217</v>
+        <v>973.2947870891435</v>
       </c>
       <c r="D7" t="n">
-        <v>8.347434856276402</v>
+        <v>5.472803755358099</v>
       </c>
       <c r="E7" t="n">
-        <v>171.5362568367319</v>
+        <v>203.862115546625</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6025736331939697</v>
+        <v>0.6932011246681213</v>
       </c>
       <c r="G7" t="n">
-        <v>0.005945156328380108</v>
+        <v>0.005476452875882387</v>
       </c>
       <c r="H7" t="n">
-        <v>939.3061064294326</v>
+        <v>973.294787089135</v>
       </c>
       <c r="I7" t="n">
-        <v>179.2302637006003</v>
+        <v>203.8621155466249</v>
       </c>
       <c r="J7" t="n">
-        <v>9.000057868988554</v>
+        <v>9.000057869254071</v>
       </c>
       <c r="K7" t="n">
-        <v>40.06816649281086</v>
+        <v>8.526512829121202e-12</v>
       </c>
       <c r="L7" t="n">
-        <v>7.694006863868424</v>
+        <v>1.4210854715202e-13</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6526230127121515</v>
+        <v>3.527254113895973</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3191499188619872</v>
+        <v>0.9728707555440302</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0004679139301025962</v>
+        <v>0.001355710254997826</v>
       </c>
       <c r="Q7" t="n">
-        <v>945.1095730393612</v>
+        <v>956.2203661744913</v>
       </c>
       <c r="R7" t="n">
-        <v>171.0634274666846</v>
+        <v>201.6542691298841</v>
       </c>
       <c r="S7" t="n">
-        <v>9.000057866139418</v>
+        <v>9.000057869254071</v>
       </c>
       <c r="T7" t="n">
-        <v>45.87163310273945</v>
+        <v>17.07442091465214</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4728293700472648</v>
+        <v>2.207846416740949</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6526230098630155</v>
+        <v>3.527254113895973</v>
       </c>
       <c r="W7" t="b">
         <v>1</v>
@@ -977,68 +977,68 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1017.531123512318</v>
+        <v>891.692935376087</v>
       </c>
       <c r="D8" t="n">
-        <v>9.27034211770588</v>
+        <v>6.529474736408524</v>
       </c>
       <c r="E8" t="n">
-        <v>180.3857959086696</v>
+        <v>213.6274082699896</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6901307106018066</v>
+        <v>0.7614838480949402</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00438471557572484</v>
+        <v>0.0107807656750083</v>
       </c>
       <c r="H8" t="n">
-        <v>965.6040331646064</v>
+        <v>928.843267464791</v>
       </c>
       <c r="I8" t="n">
-        <v>180.3857959086696</v>
+        <v>213.6274082699897</v>
       </c>
       <c r="J8" t="n">
-        <v>9.270342117705878</v>
+        <v>9.000057867726536</v>
       </c>
       <c r="K8" t="n">
-        <v>51.92709034771121</v>
+        <v>37.15033208870398</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="M8" t="n">
-        <v>1.77635683940025e-15</v>
+        <v>2.470583131318012</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7697438663348006</v>
+        <v>0.9000178739341447</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00043917985805562</v>
+        <v>0.0005614290808879055</v>
       </c>
       <c r="Q8" t="n">
-        <v>953.6758713339957</v>
+        <v>948.2918192091475</v>
       </c>
       <c r="R8" t="n">
-        <v>180.8479916512672</v>
+        <v>212.06565140531</v>
       </c>
       <c r="S8" t="n">
-        <v>9.275692175528107</v>
+        <v>9.000057826406119</v>
       </c>
       <c r="T8" t="n">
-        <v>63.85525217832196</v>
+        <v>56.59888383306054</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4621957425975722</v>
+        <v>1.561756864679637</v>
       </c>
       <c r="V8" t="n">
-        <v>0.005350057822226972</v>
+        <v>2.470583089997595</v>
       </c>
       <c r="W8" t="b">
         <v>1</v>
@@ -1050,68 +1050,68 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>933.7519530212516</v>
+        <v>962.7980591430417</v>
       </c>
       <c r="D9" t="n">
-        <v>4.806874043301769</v>
+        <v>9.921830063864206</v>
       </c>
       <c r="E9" t="n">
-        <v>202.1435220827699</v>
+        <v>168.4091198645476</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8376048803329468</v>
+        <v>0.6174015402793884</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00305266329087317</v>
+        <v>0.0120297921821475</v>
       </c>
       <c r="H9" t="n">
-        <v>933.7519530212513</v>
+        <v>920.4421048968439</v>
       </c>
       <c r="I9" t="n">
-        <v>202.1435220827701</v>
+        <v>181.79132652353</v>
       </c>
       <c r="J9" t="n">
-        <v>9.000057869254071</v>
+        <v>9.627733510352812</v>
       </c>
       <c r="K9" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>42.35595424619771</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4210854715202e-13</v>
+        <v>13.3822066589824</v>
       </c>
       <c r="M9" t="n">
-        <v>4.193183825952302</v>
+        <v>0.2940965535113946</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9860555345557273</v>
+        <v>0.517431071606103</v>
       </c>
       <c r="P9" t="n">
-        <v>0.00117907258180053</v>
+        <v>0.001140668589984197</v>
       </c>
       <c r="Q9" t="n">
-        <v>937.5172664531447</v>
+        <v>856.9509284845999</v>
       </c>
       <c r="R9" t="n">
-        <v>200.3719567850134</v>
+        <v>175.3155423370213</v>
       </c>
       <c r="S9" t="n">
-        <v>9.000057869254071</v>
+        <v>9.877351462356494</v>
       </c>
       <c r="T9" t="n">
-        <v>3.765313431893105</v>
+        <v>105.8471306584418</v>
       </c>
       <c r="U9" t="n">
-        <v>1.771565297756553</v>
+        <v>6.906422472473736</v>
       </c>
       <c r="V9" t="n">
-        <v>4.193183825952302</v>
+        <v>0.04447860150771277</v>
       </c>
       <c r="W9" t="b">
         <v>1</v>
@@ -1123,68 +1123,68 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>941.9755905622833</v>
+        <v>948.0164827244123</v>
       </c>
       <c r="D10" t="n">
-        <v>10.64579764160371</v>
+        <v>9.65283851758155</v>
       </c>
       <c r="E10" t="n">
-        <v>269.4561757745847</v>
+        <v>119.4428441979827</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8176361322402954</v>
+        <v>0.7905983924865723</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003891526954248548</v>
+        <v>0.01428452972322702</v>
       </c>
       <c r="H10" t="n">
-        <v>941.9755905988666</v>
+        <v>948.995939460207</v>
       </c>
       <c r="I10" t="n">
-        <v>224.7375904853779</v>
+        <v>176.1525536257258</v>
       </c>
       <c r="J10" t="n">
-        <v>10.6457976405479</v>
+        <v>11.95381848092063</v>
       </c>
       <c r="K10" t="n">
-        <v>3.658328751043882e-08</v>
+        <v>0.9794567357946562</v>
       </c>
       <c r="L10" t="n">
-        <v>44.71858528920677</v>
+        <v>56.70970942774312</v>
       </c>
       <c r="M10" t="n">
-        <v>1.055813214634327e-09</v>
+        <v>2.300979963339083</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9997896917485788</v>
+        <v>0.9999054812485227</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001892551588458877</v>
+        <v>0.001749433898562091</v>
       </c>
       <c r="Q10" t="n">
-        <v>808.3099193192879</v>
+        <v>811.3979239211729</v>
       </c>
       <c r="R10" t="n">
-        <v>242.1620726549985</v>
+        <v>150.0000472865753</v>
       </c>
       <c r="S10" t="n">
-        <v>10.66285017360076</v>
+        <v>9.582298760453645</v>
       </c>
       <c r="T10" t="n">
-        <v>133.6656712429954</v>
+        <v>136.6185588032394</v>
       </c>
       <c r="U10" t="n">
-        <v>27.2941031195862</v>
+        <v>30.55720308859259</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01705253199704515</v>
+        <v>0.07053975712790539</v>
       </c>
       <c r="W10" t="b">
         <v>1</v>
@@ -1200,64 +1200,64 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>839.9028766404572</v>
+        <v>865.5234941240955</v>
       </c>
       <c r="D11" t="n">
-        <v>7.404855949979647</v>
+        <v>5.794056617050133</v>
       </c>
       <c r="E11" t="n">
-        <v>174.8116904508182</v>
+        <v>185.7493322485568</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8417344093322754</v>
+        <v>0.755632221698761</v>
       </c>
       <c r="G11" t="n">
-        <v>0.005945156328380108</v>
+        <v>0.0107807656750083</v>
       </c>
       <c r="H11" t="n">
-        <v>928.8459410537204</v>
+        <v>928.843267497137</v>
       </c>
       <c r="I11" t="n">
-        <v>179.2302637021997</v>
+        <v>185.7493322485568</v>
       </c>
       <c r="J11" t="n">
-        <v>9.000057869252819</v>
+        <v>9.000057868141909</v>
       </c>
       <c r="K11" t="n">
-        <v>88.94306441326319</v>
+        <v>63.31977337304158</v>
       </c>
       <c r="L11" t="n">
-        <v>4.418573251381559</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="M11" t="n">
-        <v>1.595201919273172</v>
+        <v>3.206001251091775</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8934762826924519</v>
+        <v>0.9781872632768009</v>
       </c>
       <c r="P11" t="n">
-        <v>0.001096416413131947</v>
+        <v>0.0007436002217320406</v>
       </c>
       <c r="Q11" t="n">
-        <v>938.7414325940305</v>
+        <v>941.0553301147726</v>
       </c>
       <c r="R11" t="n">
-        <v>174.6860315755196</v>
+        <v>185.8904182960312</v>
       </c>
       <c r="S11" t="n">
-        <v>9.000057869447067</v>
+        <v>9.000057869709417</v>
       </c>
       <c r="T11" t="n">
-        <v>98.83855595357329</v>
+        <v>75.53183599067711</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1256588752985408</v>
+        <v>0.1410860474744311</v>
       </c>
       <c r="V11" t="n">
-        <v>1.59520191946742</v>
+        <v>3.206001252659284</v>
       </c>
       <c r="W11" t="b">
         <v>1</v>
@@ -1269,68 +1269,68 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1045.066055964013</v>
+        <v>953.1618975173362</v>
       </c>
       <c r="D12" t="n">
-        <v>11.97257990444693</v>
+        <v>9.743266196519947</v>
       </c>
       <c r="E12" t="n">
-        <v>208.7342481994733</v>
+        <v>146.1562239411741</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7812808156013489</v>
+        <v>0.7905983924865723</v>
       </c>
       <c r="G12" t="n">
-        <v>0.004256739746779203</v>
+        <v>0.06394846737384796</v>
       </c>
       <c r="H12" t="n">
-        <v>965.6040331738346</v>
+        <v>963.478800228988</v>
       </c>
       <c r="I12" t="n">
-        <v>208.7342481994733</v>
+        <v>176.0443521145514</v>
       </c>
       <c r="J12" t="n">
-        <v>11.97257990444693</v>
+        <v>9.780498845503187</v>
       </c>
       <c r="K12" t="n">
-        <v>79.46202279017882</v>
+        <v>10.31690271165178</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>29.88812817337725</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>0.03723264898323997</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0.9950720585205197</v>
+        <v>0.995237948122055</v>
       </c>
       <c r="P12" t="n">
-        <v>0.000593527111646464</v>
+        <v>0.001712255582205869</v>
       </c>
       <c r="Q12" t="n">
-        <v>950.5107694693806</v>
+        <v>815.7502598479576</v>
       </c>
       <c r="R12" t="n">
-        <v>207.8478735970994</v>
+        <v>152.5542326571138</v>
       </c>
       <c r="S12" t="n">
-        <v>11.9195044307956</v>
+        <v>9.67417422161274</v>
       </c>
       <c r="T12" t="n">
-        <v>94.55528649463281</v>
+        <v>137.4116376693786</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8863746023739054</v>
+        <v>6.398008715939682</v>
       </c>
       <c r="V12" t="n">
-        <v>0.05307547365133303</v>
+        <v>0.06909197490720764</v>
       </c>
       <c r="W12" t="b">
         <v>1</v>
@@ -1346,64 +1346,64 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>930.1721530108739</v>
+        <v>945.2210390626718</v>
       </c>
       <c r="D13" t="n">
-        <v>13.33665518770309</v>
+        <v>14.14363612664931</v>
       </c>
       <c r="E13" t="n">
-        <v>194.8518033760263</v>
+        <v>209.4304064156104</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5193063020706177</v>
+        <v>0.7234267592430115</v>
       </c>
       <c r="G13" t="n">
-        <v>0.004665159154683352</v>
+        <v>0.008424116298556328</v>
       </c>
       <c r="H13" t="n">
-        <v>930.1721530300504</v>
+        <v>945.2210390363817</v>
       </c>
       <c r="I13" t="n">
-        <v>194.8518033760263</v>
+        <v>209.4304064156104</v>
       </c>
       <c r="J13" t="n">
-        <v>11.77729472323463</v>
+        <v>11.77729472198164</v>
       </c>
       <c r="K13" t="n">
-        <v>1.917646841320675e-08</v>
+        <v>2.629008122312371e-08</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.559360464468469</v>
+        <v>2.366341404667674</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7659099894406031</v>
+        <v>0.97331245967028</v>
       </c>
       <c r="P13" t="n">
-        <v>0.001203839357997257</v>
+        <v>0.001639342335084964</v>
       </c>
       <c r="Q13" t="n">
-        <v>840.0934042995856</v>
+        <v>829.9207677380336</v>
       </c>
       <c r="R13" t="n">
-        <v>195.6339899104131</v>
+        <v>209.4720892544866</v>
       </c>
       <c r="S13" t="n">
-        <v>12.88256798795882</v>
+        <v>13.49981776422353</v>
       </c>
       <c r="T13" t="n">
-        <v>90.07874871128831</v>
+        <v>115.3002713246382</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7821865343868808</v>
+        <v>0.04168283887622692</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4540871997442704</v>
+        <v>0.6438183624257761</v>
       </c>
       <c r="W13" t="b">
         <v>1</v>
@@ -1415,68 +1415,68 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Dirtiness</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>863.2686540011719</v>
+        <v>971.0630570666581</v>
       </c>
       <c r="D14" t="n">
-        <v>8.076778154806025</v>
+        <v>9.721880135633667</v>
       </c>
       <c r="E14" t="n">
-        <v>209.6583164685813</v>
+        <v>246.5661183841028</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7448315024375916</v>
+        <v>0.5874079465866089</v>
       </c>
       <c r="G14" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.005473046097904444</v>
       </c>
       <c r="H14" t="n">
-        <v>928.8432674712028</v>
+        <v>971.0630570665044</v>
       </c>
       <c r="I14" t="n">
-        <v>209.6583164685813</v>
+        <v>222.3568452515523</v>
       </c>
       <c r="J14" t="n">
-        <v>9.000057867773577</v>
+        <v>9.72188013563261</v>
       </c>
       <c r="K14" t="n">
-        <v>65.57461347003095</v>
+        <v>1.537046045996249e-10</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>24.20927313255052</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9232797129675525</v>
+        <v>1.056932319443149e-12</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8994251749909906</v>
+        <v>0.9752882041840766</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0008071948381660771</v>
+        <v>0.00145628616486667</v>
       </c>
       <c r="Q14" t="n">
-        <v>943.752605684126</v>
+        <v>846.9423118980399</v>
       </c>
       <c r="R14" t="n">
-        <v>207.9249701539842</v>
+        <v>226.2668238192292</v>
       </c>
       <c r="S14" t="n">
-        <v>9.000057847221081</v>
+        <v>9.677938548165491</v>
       </c>
       <c r="T14" t="n">
-        <v>80.48395168295417</v>
+        <v>124.1207451686182</v>
       </c>
       <c r="U14" t="n">
-        <v>1.733346314597043</v>
+        <v>20.29929456487358</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9232796924150559</v>
+        <v>0.04394158746817567</v>
       </c>
       <c r="W14" t="b">
         <v>1</v>
@@ -1488,68 +1488,68 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Dirtiness</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>900.8959811410301</v>
+        <v>917.8748642319608</v>
       </c>
       <c r="D15" t="n">
-        <v>8.136767061841049</v>
+        <v>10.70379588375082</v>
       </c>
       <c r="E15" t="n">
-        <v>198.5182959524577</v>
+        <v>276.5087578943281</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5882257223129272</v>
+        <v>0.6587895154953003</v>
       </c>
       <c r="G15" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.00655886298045516</v>
       </c>
       <c r="H15" t="n">
-        <v>928.8432674616064</v>
+        <v>916.5766038447071</v>
       </c>
       <c r="I15" t="n">
-        <v>198.5182959524577</v>
+        <v>224.7359055555619</v>
       </c>
       <c r="J15" t="n">
-        <v>9.000057868981713</v>
+        <v>10.70379588375083</v>
       </c>
       <c r="K15" t="n">
-        <v>27.94728632057627</v>
+        <v>1.298260387253777</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>51.7728523387662</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8632908071406646</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5378189860014168</v>
+        <v>0.9998597021223778</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0004140191717354265</v>
+        <v>0.002039819975799758</v>
       </c>
       <c r="Q15" t="n">
-        <v>946.0438293606871</v>
+        <v>800.0004553692589</v>
       </c>
       <c r="R15" t="n">
-        <v>198.1376614420037</v>
+        <v>245.8032933292593</v>
       </c>
       <c r="S15" t="n">
-        <v>9.000057868002671</v>
+        <v>10.73301244679471</v>
       </c>
       <c r="T15" t="n">
-        <v>45.14784821965702</v>
+        <v>117.8744088627019</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3806345104540299</v>
+        <v>30.70546456506884</v>
       </c>
       <c r="V15" t="n">
-        <v>0.863290806161622</v>
+        <v>0.02921656304389231</v>
       </c>
       <c r="W15" t="b">
         <v>1</v>
@@ -1565,64 +1565,64 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>921.8656113488089</v>
+        <v>984.3808122568364</v>
       </c>
       <c r="D16" t="n">
-        <v>11.67602145875993</v>
+        <v>8.386098544521008</v>
       </c>
       <c r="E16" t="n">
-        <v>125.3512267441674</v>
+        <v>137.8953690543283</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8908511400222778</v>
+        <v>0.7846513390541077</v>
       </c>
       <c r="G16" t="n">
-        <v>0.008997319266200066</v>
+        <v>0.01447403151541948</v>
       </c>
       <c r="H16" t="n">
-        <v>916.5765297237408</v>
+        <v>962.4140068377019</v>
       </c>
       <c r="I16" t="n">
-        <v>176.1525536306098</v>
+        <v>176.1526609190746</v>
       </c>
       <c r="J16" t="n">
-        <v>11.67602012874108</v>
+        <v>9.000000000962551</v>
       </c>
       <c r="K16" t="n">
-        <v>5.289081625068093</v>
+        <v>21.96680541913452</v>
       </c>
       <c r="L16" t="n">
-        <v>50.80132688644237</v>
+        <v>38.25729186474635</v>
       </c>
       <c r="M16" t="n">
-        <v>1.330018847056635e-06</v>
+        <v>0.6139014564415426</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9997152013578873</v>
+        <v>0.9986370695432607</v>
       </c>
       <c r="P16" t="n">
-        <v>0.001700377577687855</v>
+        <v>0.001930335722960556</v>
       </c>
       <c r="Q16" t="n">
-        <v>802.4439190175113</v>
+        <v>815.6503322721229</v>
       </c>
       <c r="R16" t="n">
-        <v>150.000047286532</v>
+        <v>150.0000472898313</v>
       </c>
       <c r="S16" t="n">
-        <v>11.59772975259802</v>
+        <v>9.000057868752561</v>
       </c>
       <c r="T16" t="n">
-        <v>119.4216923312975</v>
+        <v>168.7304799847135</v>
       </c>
       <c r="U16" t="n">
-        <v>24.64882054236459</v>
+        <v>12.10467823550306</v>
       </c>
       <c r="V16" t="n">
-        <v>0.07829170616191128</v>
+        <v>0.6139593242315531</v>
       </c>
       <c r="W16" t="b">
         <v>1</v>
@@ -1638,64 +1638,64 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>845.752179518036</v>
+        <v>870.079368107545</v>
       </c>
       <c r="D17" t="n">
-        <v>8.415496322103532</v>
+        <v>8.048918860873499</v>
       </c>
       <c r="E17" t="n">
-        <v>208.9341595668933</v>
+        <v>220.1393003038982</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7534701228141785</v>
+        <v>0.6696656942367554</v>
       </c>
       <c r="G17" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.01023163553327322</v>
       </c>
       <c r="H17" t="n">
-        <v>928.8432674686393</v>
+        <v>928.8443838783247</v>
       </c>
       <c r="I17" t="n">
-        <v>208.9341595668933</v>
+        <v>224.7375905032283</v>
       </c>
       <c r="J17" t="n">
-        <v>9.000057868998081</v>
+        <v>9.000057869092633</v>
       </c>
       <c r="K17" t="n">
-        <v>83.09108795060331</v>
+        <v>58.76501577077977</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4.598290199330194</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5845615468945482</v>
+        <v>0.9511390082191333</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8353195622094174</v>
+        <v>0.9076591737209158</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0009884609320466658</v>
+        <v>0.0008344577848599164</v>
       </c>
       <c r="Q17" t="n">
-        <v>941.9156611028426</v>
+        <v>947.9049189646879</v>
       </c>
       <c r="R17" t="n">
-        <v>206.970246678447</v>
+        <v>217.3530367296672</v>
       </c>
       <c r="S17" t="n">
-        <v>9.000057848205834</v>
+        <v>9.000057855392345</v>
       </c>
       <c r="T17" t="n">
-        <v>96.16348158480662</v>
+        <v>77.82555085714296</v>
       </c>
       <c r="U17" t="n">
-        <v>1.963912888446373</v>
+        <v>2.786263574230958</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5845615261023021</v>
+        <v>0.9511389945188462</v>
       </c>
       <c r="W17" t="b">
         <v>1</v>
@@ -1707,68 +1707,68 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>870.4442152957413</v>
+        <v>970.4327042765522</v>
       </c>
       <c r="D18" t="n">
-        <v>7.146853061409382</v>
+        <v>9.425206772784684</v>
       </c>
       <c r="E18" t="n">
-        <v>206.0551292023584</v>
+        <v>162.002639941599</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8869392275810242</v>
+        <v>0.6157383918762207</v>
       </c>
       <c r="G18" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.02453009411692619</v>
       </c>
       <c r="H18" t="n">
-        <v>928.8432674830061</v>
+        <v>880.49912995189</v>
       </c>
       <c r="I18" t="n">
-        <v>206.0551292023576</v>
+        <v>181.1730609959959</v>
       </c>
       <c r="J18" t="n">
-        <v>9.000057868708511</v>
+        <v>9.215485615879814</v>
       </c>
       <c r="K18" t="n">
-        <v>58.39905218726483</v>
+        <v>89.93357432466212</v>
       </c>
       <c r="L18" t="n">
-        <v>7.673861546209082e-13</v>
+        <v>19.17042105439688</v>
       </c>
       <c r="M18" t="n">
-        <v>1.85320480729913</v>
+        <v>0.2097211569048696</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9660853385354029</v>
+        <v>0.8532851020548059</v>
       </c>
       <c r="P18" t="n">
-        <v>0.0007130841185590223</v>
+        <v>0.001314022520981928</v>
       </c>
       <c r="Q18" t="n">
-        <v>943.6274714752439</v>
+        <v>847.6279854591171</v>
       </c>
       <c r="R18" t="n">
-        <v>204.8091472651537</v>
+        <v>169.0386082606258</v>
       </c>
       <c r="S18" t="n">
-        <v>9.000057858546738</v>
+        <v>9.364004924983192</v>
       </c>
       <c r="T18" t="n">
-        <v>73.18325617950256</v>
+        <v>122.8047188174351</v>
       </c>
       <c r="U18" t="n">
-        <v>1.245981937204704</v>
+        <v>7.035968319026836</v>
       </c>
       <c r="V18" t="n">
-        <v>1.853204797137356</v>
+        <v>0.06120184780149174</v>
       </c>
       <c r="W18" t="b">
         <v>1</v>
@@ -1780,68 +1780,68 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>937.8547717182784</v>
+        <v>963.908049491006</v>
       </c>
       <c r="D19" t="n">
-        <v>11.88981390389384</v>
+        <v>13.18657491181106</v>
       </c>
       <c r="E19" t="n">
-        <v>122.2507101207577</v>
+        <v>221.27004538893</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8925431370735168</v>
+        <v>0.6125883460044861</v>
       </c>
       <c r="G19" t="n">
-        <v>0.009124549105763435</v>
+        <v>0.007990965619683266</v>
       </c>
       <c r="H19" t="n">
-        <v>944.2578179317488</v>
+        <v>963.908049491009</v>
       </c>
       <c r="I19" t="n">
-        <v>176.1525536424485</v>
+        <v>224.7375914651388</v>
       </c>
       <c r="J19" t="n">
-        <v>11.88981390485472</v>
+        <v>11.77725334223896</v>
       </c>
       <c r="K19" t="n">
-        <v>6.403046213470475</v>
+        <v>3.069544618483633e-12</v>
       </c>
       <c r="L19" t="n">
-        <v>53.90184352169078</v>
+        <v>3.467546076208833</v>
       </c>
       <c r="M19" t="n">
-        <v>9.608740469957411e-10</v>
+        <v>1.409321569572093</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9998694038253124</v>
+        <v>0.7036991484062372</v>
       </c>
       <c r="P19" t="n">
-        <v>0.001845785697256699</v>
+        <v>0.001507485916176177</v>
       </c>
       <c r="Q19" t="n">
-        <v>802.6011019310831</v>
+        <v>848.7005209729417</v>
       </c>
       <c r="R19" t="n">
-        <v>150.0000472859354</v>
+        <v>220.4450357726695</v>
       </c>
       <c r="S19" t="n">
-        <v>11.80047724369028</v>
+        <v>12.66377058813266</v>
       </c>
       <c r="T19" t="n">
-        <v>135.2536697871952</v>
+        <v>115.2075285180642</v>
       </c>
       <c r="U19" t="n">
-        <v>27.74933716517765</v>
+        <v>0.8250096162605018</v>
       </c>
       <c r="V19" t="n">
-        <v>0.08933666020356235</v>
+        <v>0.522804323678395</v>
       </c>
       <c r="W19" t="b">
         <v>1</v>
@@ -1853,68 +1853,68 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>939.8207274858501</v>
+        <v>858.5954104313548</v>
       </c>
       <c r="D20" t="n">
-        <v>7.663930394978737</v>
+        <v>8.830731426677334</v>
       </c>
       <c r="E20" t="n">
-        <v>140.2610688388082</v>
+        <v>202.2892740270275</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8761634826660156</v>
+        <v>0.5621231198310852</v>
       </c>
       <c r="G20" t="n">
-        <v>0.009280012920498848</v>
+        <v>0.0107807656750083</v>
       </c>
       <c r="H20" t="n">
-        <v>939.820727483637</v>
+        <v>928.8432674714578</v>
       </c>
       <c r="I20" t="n">
-        <v>176.1525536267266</v>
+        <v>202.2892740270275</v>
       </c>
       <c r="J20" t="n">
-        <v>9.037361074601694</v>
+        <v>9.000057868668559</v>
       </c>
       <c r="K20" t="n">
-        <v>2.213027983088978e-09</v>
+        <v>70.24785704010299</v>
       </c>
       <c r="L20" t="n">
-        <v>35.89148478791844</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.373430679622958</v>
+        <v>0.1693264419912257</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9958406734596411</v>
+        <v>0.7140772021470611</v>
       </c>
       <c r="P20" t="n">
-        <v>0.001619762032843942</v>
+        <v>0.0008139230819724353</v>
       </c>
       <c r="Q20" t="n">
-        <v>813.6835696549635</v>
+        <v>941.7204884230094</v>
       </c>
       <c r="R20" t="n">
-        <v>150.0000472903498</v>
+        <v>201.2469894517664</v>
       </c>
       <c r="S20" t="n">
-        <v>9.000057869387012</v>
+        <v>9.000057866320244</v>
       </c>
       <c r="T20" t="n">
-        <v>126.1371578308865</v>
+        <v>83.12507799165462</v>
       </c>
       <c r="U20" t="n">
-        <v>9.738978451541612</v>
+        <v>1.042284575261107</v>
       </c>
       <c r="V20" t="n">
-        <v>1.336127474408276</v>
+        <v>0.1693264396429104</v>
       </c>
       <c r="W20" t="b">
         <v>1</v>
@@ -1926,68 +1926,68 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>957.8376252449117</v>
+        <v>935.5686183531994</v>
       </c>
       <c r="D21" t="n">
-        <v>4.773685431185793</v>
+        <v>8.680828042167876</v>
       </c>
       <c r="E21" t="n">
-        <v>214.2996118678968</v>
+        <v>140.8990356917723</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8445577621459961</v>
+        <v>0.7905983924865723</v>
       </c>
       <c r="G21" t="n">
-        <v>0.00305266329087317</v>
+        <v>0.01447403151541948</v>
       </c>
       <c r="H21" t="n">
-        <v>957.8376252449134</v>
+        <v>935.5713868675405</v>
       </c>
       <c r="I21" t="n">
-        <v>214.2996118678946</v>
+        <v>176.1527661758182</v>
       </c>
       <c r="J21" t="n">
-        <v>9.000057869254071</v>
+        <v>9.000000000220888</v>
       </c>
       <c r="K21" t="n">
-        <v>1.70530256582424e-12</v>
+        <v>0.002768514341028094</v>
       </c>
       <c r="L21" t="n">
-        <v>2.188471626141109e-12</v>
+        <v>35.25373048404597</v>
       </c>
       <c r="M21" t="n">
-        <v>4.226372438068278</v>
+        <v>0.3191719580530119</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9943567243610213</v>
+        <v>0.9964912973813387</v>
       </c>
       <c r="P21" t="n">
-        <v>0.001836897731187797</v>
+        <v>0.001586709028044793</v>
       </c>
       <c r="Q21" t="n">
-        <v>948.252364805199</v>
+        <v>813.4494220728872</v>
       </c>
       <c r="R21" t="n">
-        <v>209.409893383728</v>
+        <v>150.0000472903582</v>
       </c>
       <c r="S21" t="n">
-        <v>9.000057869254071</v>
+        <v>9.000057869397292</v>
       </c>
       <c r="T21" t="n">
-        <v>9.58526043971267</v>
+        <v>122.1191962803123</v>
       </c>
       <c r="U21" t="n">
-        <v>4.88971848416881</v>
+        <v>9.101011598585927</v>
       </c>
       <c r="V21" t="n">
-        <v>4.226372438068278</v>
+        <v>0.3192298272294156</v>
       </c>
       <c r="W21" t="b">
         <v>1</v>
@@ -2003,64 +2003,64 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>936.9679930478836</v>
+        <v>930.9536723852241</v>
       </c>
       <c r="D22" t="n">
-        <v>8.895974366527614</v>
+        <v>10.74705882782412</v>
       </c>
       <c r="E22" t="n">
-        <v>168.0073535478782</v>
+        <v>158.3215284092236</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6710121035575867</v>
+        <v>0.7905983924865723</v>
       </c>
       <c r="G22" t="n">
-        <v>0.009456926956772804</v>
+        <v>0.01447403151541948</v>
       </c>
       <c r="H22" t="n">
-        <v>887.2637180096368</v>
+        <v>930.953666496808</v>
       </c>
       <c r="I22" t="n">
-        <v>181.7913058722669</v>
+        <v>176.1526435262443</v>
       </c>
       <c r="J22" t="n">
-        <v>12.0017456633329</v>
+        <v>10.74706391390919</v>
       </c>
       <c r="K22" t="n">
-        <v>49.70427503824681</v>
+        <v>5.888416126254015e-06</v>
       </c>
       <c r="L22" t="n">
-        <v>13.78395232438868</v>
+        <v>17.83111511702069</v>
       </c>
       <c r="M22" t="n">
-        <v>3.105771296805283</v>
+        <v>5.086085065997281e-06</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3829937445952233</v>
+        <v>0.9103170189198628</v>
       </c>
       <c r="P22" t="n">
-        <v>0.0009268985206447032</v>
+        <v>0.001248655968202007</v>
       </c>
       <c r="Q22" t="n">
-        <v>855.6736953823283</v>
+        <v>831.8409425958835</v>
       </c>
       <c r="R22" t="n">
-        <v>173.5520232431114</v>
+        <v>164.2946129922157</v>
       </c>
       <c r="S22" t="n">
-        <v>9.000057869280491</v>
+        <v>10.70147628368998</v>
       </c>
       <c r="T22" t="n">
-        <v>81.29429766555529</v>
+        <v>99.11272978934062</v>
       </c>
       <c r="U22" t="n">
-        <v>5.544669695233182</v>
+        <v>5.973084582992129</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1040835027528768</v>
+        <v>0.04558254413414176</v>
       </c>
       <c r="W22" t="b">
         <v>1</v>
@@ -2072,68 +2072,68 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1049.124142340863</v>
+        <v>839.9028766404572</v>
       </c>
       <c r="D23" t="n">
-        <v>11.75337519872432</v>
+        <v>7.404855949979647</v>
       </c>
       <c r="E23" t="n">
-        <v>211.0593546195771</v>
+        <v>174.8116904508182</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7933045029640198</v>
+        <v>0.7361236810684204</v>
       </c>
       <c r="G23" t="n">
-        <v>0.004426439292728901</v>
+        <v>0.01076846290379763</v>
       </c>
       <c r="H23" t="n">
-        <v>965.604033165695</v>
+        <v>928.8454565611487</v>
       </c>
       <c r="I23" t="n">
-        <v>211.0593546195771</v>
+        <v>179.2302637048722</v>
       </c>
       <c r="J23" t="n">
-        <v>11.75337519872431</v>
+        <v>9.000057869034933</v>
       </c>
       <c r="K23" t="n">
-        <v>83.52010917516827</v>
+        <v>88.94257992069151</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>4.418573254054053</v>
       </c>
       <c r="M23" t="n">
-        <v>5.329070518200751e-15</v>
+        <v>1.595201919055286</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9972250939783822</v>
+        <v>0.8934762826924519</v>
       </c>
       <c r="P23" t="n">
-        <v>0.0006026320311088798</v>
+        <v>0.001096416413131947</v>
       </c>
       <c r="Q23" t="n">
-        <v>951.0095199379525</v>
+        <v>938.7414325940305</v>
       </c>
       <c r="R23" t="n">
-        <v>209.9861005424163</v>
+        <v>174.6860315755196</v>
       </c>
       <c r="S23" t="n">
-        <v>11.70126231848585</v>
+        <v>9.000057869447067</v>
       </c>
       <c r="T23" t="n">
-        <v>98.11462240291075</v>
+        <v>98.83855595357329</v>
       </c>
       <c r="U23" t="n">
-        <v>1.073254077160755</v>
+        <v>0.1256588752985408</v>
       </c>
       <c r="V23" t="n">
-        <v>0.05211288023846983</v>
+        <v>1.59520191946742</v>
       </c>
       <c r="W23" t="b">
         <v>1</v>
@@ -2145,68 +2145,68 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>984.3808122568364</v>
+        <v>872.951276388834</v>
       </c>
       <c r="D24" t="n">
-        <v>8.386098544521008</v>
+        <v>6.647864709753142</v>
       </c>
       <c r="E24" t="n">
-        <v>137.8953690543283</v>
+        <v>226.429104826243</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8913341760635376</v>
+        <v>0.7425936460494995</v>
       </c>
       <c r="G24" t="n">
-        <v>0.008119345642626286</v>
+        <v>0.006254705600440502</v>
       </c>
       <c r="H24" t="n">
-        <v>959.1994420138102</v>
+        <v>928.8444742296232</v>
       </c>
       <c r="I24" t="n">
-        <v>180.9081690435765</v>
+        <v>231.3668592757028</v>
       </c>
       <c r="J24" t="n">
-        <v>9.037337042138022</v>
+        <v>9.000057868632235</v>
       </c>
       <c r="K24" t="n">
-        <v>25.18137024302621</v>
+        <v>55.89319784078918</v>
       </c>
       <c r="L24" t="n">
-        <v>43.01279998924824</v>
+        <v>4.93775444945976</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6512384976170136</v>
+        <v>2.352193158879093</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9986370695432607</v>
+        <v>0.9699037175754671</v>
       </c>
       <c r="P24" t="n">
-        <v>0.001930335722960556</v>
+        <v>0.0008896991599113631</v>
       </c>
       <c r="Q24" t="n">
-        <v>815.6503322721229</v>
+        <v>950.9732542094079</v>
       </c>
       <c r="R24" t="n">
-        <v>150.0000472898313</v>
+        <v>223.616543468521</v>
       </c>
       <c r="S24" t="n">
-        <v>9.000057868752561</v>
+        <v>9.000057788147537</v>
       </c>
       <c r="T24" t="n">
-        <v>168.7304799847135</v>
+        <v>78.02197782057385</v>
       </c>
       <c r="U24" t="n">
-        <v>12.10467823550306</v>
+        <v>2.812561357722046</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6139593242315531</v>
+        <v>2.352193078394395</v>
       </c>
       <c r="W24" t="b">
         <v>1</v>
@@ -2222,64 +2222,64 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>893.3534815003172</v>
+        <v>961.7411506918908</v>
       </c>
       <c r="D25" t="n">
-        <v>9.416439452103926</v>
+        <v>9.501535917459156</v>
       </c>
       <c r="E25" t="n">
-        <v>158.2854949154974</v>
+        <v>134.8005772645463</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7847743630409241</v>
+        <v>0.7905983924865723</v>
       </c>
       <c r="G25" t="n">
-        <v>0.009788251481950283</v>
+        <v>0.01447403151541948</v>
       </c>
       <c r="H25" t="n">
-        <v>838.7952449546607</v>
+        <v>961.7411530323932</v>
       </c>
       <c r="I25" t="n">
-        <v>181.7912777187019</v>
+        <v>176.152553649176</v>
       </c>
       <c r="J25" t="n">
-        <v>9.457426730276001</v>
+        <v>9.501534934356345</v>
       </c>
       <c r="K25" t="n">
-        <v>54.55823654565654</v>
+        <v>2.340502419428958e-06</v>
       </c>
       <c r="L25" t="n">
-        <v>23.50578280320454</v>
+        <v>41.35197638462969</v>
       </c>
       <c r="M25" t="n">
-        <v>0.04098727817207504</v>
+        <v>9.831028116025209e-07</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6433456988015656</v>
+        <v>0.9993959460682591</v>
       </c>
       <c r="P25" t="n">
-        <v>0.0008910089391130349</v>
+        <v>0.00183165309562486</v>
       </c>
       <c r="Q25" t="n">
-        <v>829.7853258096021</v>
+        <v>812.7167930930882</v>
       </c>
       <c r="R25" t="n">
-        <v>162.3990143355159</v>
+        <v>150.0000472868396</v>
       </c>
       <c r="S25" t="n">
-        <v>9.3779689675568</v>
+        <v>9.426201575276425</v>
       </c>
       <c r="T25" t="n">
-        <v>63.56815569071512</v>
+        <v>149.0243575988026</v>
       </c>
       <c r="U25" t="n">
-        <v>4.113519420018491</v>
+        <v>15.19947002229327</v>
       </c>
       <c r="V25" t="n">
-        <v>0.0384704845471262</v>
+        <v>0.07533434218273172</v>
       </c>
       <c r="W25" t="b">
         <v>1</v>
@@ -2291,68 +2291,68 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1020.033583378828</v>
+        <v>953.8876860315468</v>
       </c>
       <c r="D26" t="n">
-        <v>10.24048764946776</v>
+        <v>10.26697578312756</v>
       </c>
       <c r="E26" t="n">
-        <v>211.5070327466673</v>
+        <v>133.9082043343228</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7582332491874695</v>
+        <v>0.7905983924865723</v>
       </c>
       <c r="G26" t="n">
-        <v>0.004426439292728901</v>
+        <v>0.01447403151541948</v>
       </c>
       <c r="H26" t="n">
-        <v>965.604033125925</v>
+        <v>953.8876859460212</v>
       </c>
       <c r="I26" t="n">
-        <v>211.5070327466673</v>
+        <v>176.1525536608956</v>
       </c>
       <c r="J26" t="n">
-        <v>10.24048764946776</v>
+        <v>10.26697578655412</v>
       </c>
       <c r="K26" t="n">
-        <v>54.42955025290269</v>
+        <v>8.552558483643224e-08</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>42.2443493265728</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.426556816066295e-09</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.9367601131308548</v>
+        <v>0.9995206905356393</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0004202932762567698</v>
+        <v>0.001851875149642966</v>
       </c>
       <c r="Q26" t="n">
-        <v>952.8965109324828</v>
+        <v>809.2262114316984</v>
       </c>
       <c r="R26" t="n">
-        <v>210.6771856885919</v>
+        <v>150.0000472882507</v>
       </c>
       <c r="S26" t="n">
-        <v>10.23073022006116</v>
+        <v>10.19446579512171</v>
       </c>
       <c r="T26" t="n">
-        <v>67.13707244634486</v>
+        <v>144.6614745998484</v>
       </c>
       <c r="U26" t="n">
-        <v>0.8298470580753303</v>
+        <v>16.09184295392791</v>
       </c>
       <c r="V26" t="n">
-        <v>0.009757429406599627</v>
+        <v>0.07250998800584973</v>
       </c>
       <c r="W26" t="b">
         <v>1</v>
@@ -2368,64 +2368,64 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>870.2300452285227</v>
+        <v>879.0387028373722</v>
       </c>
       <c r="D27" t="n">
-        <v>9.844937955301521</v>
+        <v>9.646879819997553</v>
       </c>
       <c r="E27" t="n">
-        <v>198.4091333563139</v>
+        <v>206.2583865753571</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5666285753250122</v>
+        <v>0.510233461856842</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0032845763489604</v>
+        <v>0.005909173749387264</v>
       </c>
       <c r="H27" t="n">
-        <v>922.9741913348181</v>
+        <v>922.9741913766268</v>
       </c>
       <c r="I27" t="n">
-        <v>198.4091333563139</v>
+        <v>206.2583865753573</v>
       </c>
       <c r="J27" t="n">
-        <v>9.844937955301527</v>
+        <v>9.646879819997551</v>
       </c>
       <c r="K27" t="n">
-        <v>52.74414610629537</v>
+        <v>43.93548853925461</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.989519660128281e-13</v>
       </c>
       <c r="M27" t="n">
-        <v>5.329070518200751e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>0.6181286588469306</v>
+        <v>0.4660404635555797</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0005617096395349768</v>
+        <v>0.0004958690725527312</v>
       </c>
       <c r="Q27" t="n">
-        <v>935.7617956187471</v>
+        <v>937.2480469120045</v>
       </c>
       <c r="R27" t="n">
-        <v>198.170656997013</v>
+        <v>205.5922209695499</v>
       </c>
       <c r="S27" t="n">
-        <v>9.828530664204326</v>
+        <v>9.635460415218885</v>
       </c>
       <c r="T27" t="n">
-        <v>65.53175039022437</v>
+        <v>58.20934407463233</v>
       </c>
       <c r="U27" t="n">
-        <v>0.2384763593008756</v>
+        <v>0.6661656058071799</v>
       </c>
       <c r="V27" t="n">
-        <v>0.0164072910971953</v>
+        <v>0.01141940477866754</v>
       </c>
       <c r="W27" t="b">
         <v>1</v>
@@ -2437,68 +2437,68 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>925.044336360703</v>
+        <v>954.7027059873237</v>
       </c>
       <c r="D28" t="n">
-        <v>10.40073725369161</v>
+        <v>4.543839976282341</v>
       </c>
       <c r="E28" t="n">
-        <v>126.1285687916081</v>
+        <v>212.3278427213668</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8979030251502991</v>
+        <v>0.6949941515922546</v>
       </c>
       <c r="G28" t="n">
-        <v>0.009216854348778725</v>
+        <v>0.005485068075358868</v>
       </c>
       <c r="H28" t="n">
-        <v>925.0443378907651</v>
+        <v>954.7027059873394</v>
       </c>
       <c r="I28" t="n">
-        <v>176.1525536301022</v>
+        <v>212.3278427213669</v>
       </c>
       <c r="J28" t="n">
-        <v>10.40073581339373</v>
+        <v>9.000057869254071</v>
       </c>
       <c r="K28" t="n">
-        <v>1.530062036181334e-06</v>
+        <v>1.568878360558301e-11</v>
       </c>
       <c r="L28" t="n">
-        <v>50.0239848384941</v>
+        <v>1.4210854715202e-13</v>
       </c>
       <c r="M28" t="n">
-        <v>1.440297884514052e-06</v>
+        <v>4.45621789297173</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>0.9996893952114001</v>
+        <v>0.9959965380304859</v>
       </c>
       <c r="P28" t="n">
-        <v>0.001638070726307181</v>
+        <v>0.001696458335149723</v>
       </c>
       <c r="Q28" t="n">
-        <v>807.1690593181947</v>
+        <v>947.1872232457737</v>
       </c>
       <c r="R28" t="n">
-        <v>150.0000472886534</v>
+        <v>208.1041258682009</v>
       </c>
       <c r="S28" t="n">
-        <v>10.33706676241117</v>
+        <v>9.000057869254071</v>
       </c>
       <c r="T28" t="n">
-        <v>117.8752770425083</v>
+        <v>7.515482741550045</v>
       </c>
       <c r="U28" t="n">
-        <v>23.8714784970453</v>
+        <v>4.223716853165911</v>
       </c>
       <c r="V28" t="n">
-        <v>0.063670491280444</v>
+        <v>4.45621789297173</v>
       </c>
       <c r="W28" t="b">
         <v>1</v>
@@ -2510,68 +2510,68 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Stains</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>914.8358224668913</v>
+        <v>845.1568631320561</v>
       </c>
       <c r="D29" t="n">
-        <v>11.97373344273585</v>
+        <v>10.74761024527205</v>
       </c>
       <c r="E29" t="n">
-        <v>149.2592673909325</v>
+        <v>194.9539987835122</v>
       </c>
       <c r="F29" t="n">
-        <v>0.878510057926178</v>
+        <v>0.5990298390388489</v>
       </c>
       <c r="G29" t="n">
-        <v>0.008714379742741585</v>
+        <v>0.005909173749387264</v>
       </c>
       <c r="H29" t="n">
-        <v>910.5037030115836</v>
+        <v>922.974191339715</v>
       </c>
       <c r="I29" t="n">
-        <v>176.1525536520595</v>
+        <v>194.9539987835122</v>
       </c>
       <c r="J29" t="n">
-        <v>11.9799845204373</v>
+        <v>10.74761024527205</v>
       </c>
       <c r="K29" t="n">
-        <v>4.332119455307634</v>
+        <v>77.81732820765899</v>
       </c>
       <c r="L29" t="n">
-        <v>26.893286261127</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.00625107770145128</v>
+        <v>0</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0.9801049057492081</v>
+        <v>0.8845784340001017</v>
       </c>
       <c r="P29" t="n">
-        <v>0.001478191253097526</v>
+        <v>0.0008550181598568042</v>
       </c>
       <c r="Q29" t="n">
-        <v>810.1509126759144</v>
+        <v>935.3876622886237</v>
       </c>
       <c r="R29" t="n">
-        <v>155.1044662849172</v>
+        <v>194.8438176612062</v>
       </c>
       <c r="S29" t="n">
-        <v>11.90264590875902</v>
+        <v>10.68937165559022</v>
       </c>
       <c r="T29" t="n">
-        <v>104.6849097909769</v>
+        <v>90.23079915656763</v>
       </c>
       <c r="U29" t="n">
-        <v>5.845198893984701</v>
+        <v>0.1101811223060167</v>
       </c>
       <c r="V29" t="n">
-        <v>0.07108753397682932</v>
+        <v>0.0582385896818316</v>
       </c>
       <c r="W29" t="b">
         <v>1</v>
@@ -2583,68 +2583,68 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1022.486271537985</v>
+        <v>954.9778793826652</v>
       </c>
       <c r="D30" t="n">
-        <v>11.29375315586596</v>
+        <v>14.60216899569308</v>
       </c>
       <c r="E30" t="n">
-        <v>203.849709813197</v>
+        <v>208.6719112576131</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7933045029640198</v>
+        <v>0.7234267592430115</v>
       </c>
       <c r="G30" t="n">
-        <v>0.004426439292728901</v>
+        <v>0.008424116298556328</v>
       </c>
       <c r="H30" t="n">
-        <v>965.6040331375054</v>
+        <v>954.9778793142917</v>
       </c>
       <c r="I30" t="n">
-        <v>203.849709813197</v>
+        <v>208.6719112576131</v>
       </c>
       <c r="J30" t="n">
-        <v>11.29375315586596</v>
+        <v>11.77729471953397</v>
       </c>
       <c r="K30" t="n">
-        <v>56.88223840047908</v>
+        <v>6.837342425569659e-08</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.77635683940025e-15</v>
+        <v>2.824874276159109</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>0.9548880642525903</v>
+        <v>0.9924333779233867</v>
       </c>
       <c r="P30" t="n">
-        <v>0.00043785800655081</v>
+        <v>0.001881050998491252</v>
       </c>
       <c r="Q30" t="n">
-        <v>952.0940995115631</v>
+        <v>823.4120515472366</v>
       </c>
       <c r="R30" t="n">
-        <v>203.4080078628873</v>
+        <v>208.8093206535109</v>
       </c>
       <c r="S30" t="n">
-        <v>11.26174605519906</v>
+        <v>13.83037558604234</v>
       </c>
       <c r="T30" t="n">
-        <v>70.39217202642146</v>
+        <v>131.5658278354285</v>
       </c>
       <c r="U30" t="n">
-        <v>0.4417019503096924</v>
+        <v>0.1374093958977483</v>
       </c>
       <c r="V30" t="n">
-        <v>0.03200710066690071</v>
+        <v>0.7717934096507388</v>
       </c>
       <c r="W30" t="b">
         <v>1</v>
@@ -2656,68 +2656,68 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>962.108090095255</v>
+        <v>877.9207487981846</v>
       </c>
       <c r="D31" t="n">
-        <v>14.50709433844091</v>
+        <v>8.772368688660679</v>
       </c>
       <c r="E31" t="n">
-        <v>223.2306932722092</v>
+        <v>189.5768976731275</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8617438077926636</v>
+        <v>0.6287869811058044</v>
       </c>
       <c r="G31" t="n">
-        <v>0.00442391075193882</v>
+        <v>0.0107807656750083</v>
       </c>
       <c r="H31" t="n">
-        <v>962.1082910972634</v>
+        <v>928.8432674775141</v>
       </c>
       <c r="I31" t="n">
-        <v>224.7375905016691</v>
+        <v>189.5768976731275</v>
       </c>
       <c r="J31" t="n">
-        <v>11.77719603065156</v>
+        <v>9.000057867504813</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0002010020084526332</v>
+        <v>50.92251867932953</v>
       </c>
       <c r="L31" t="n">
-        <v>1.506897229459952</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.72989830778935</v>
+        <v>0.227689178844134</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0.98674404300751</v>
+        <v>0.6619208421077007</v>
       </c>
       <c r="P31" t="n">
-        <v>0.002006932175816133</v>
+        <v>0.0006130186329304304</v>
       </c>
       <c r="Q31" t="n">
-        <v>825.8112881556253</v>
+        <v>942.4119440116023</v>
       </c>
       <c r="R31" t="n">
-        <v>222.2248420113521</v>
+        <v>189.5486254949676</v>
       </c>
       <c r="S31" t="n">
-        <v>13.73726563645751</v>
+        <v>9.000057869204142</v>
       </c>
       <c r="T31" t="n">
-        <v>136.2968019396296</v>
+        <v>64.49119521341765</v>
       </c>
       <c r="U31" t="n">
-        <v>1.005851260857099</v>
+        <v>0.02827217815990934</v>
       </c>
       <c r="V31" t="n">
-        <v>0.7698287019834034</v>
+        <v>0.2276891805434627</v>
       </c>
       <c r="W31" t="b">
         <v>1</v>
@@ -2729,68 +2729,68 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>949.4156718829203</v>
+        <v>931.2681598751271</v>
       </c>
       <c r="D32" t="n">
-        <v>6.692100047502612</v>
+        <v>15.24260180471171</v>
       </c>
       <c r="E32" t="n">
-        <v>198.2751311582606</v>
+        <v>204.7887497005245</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5351364016532898</v>
+        <v>0.7234267592430115</v>
       </c>
       <c r="G32" t="n">
-        <v>0.00305266329087317</v>
+        <v>0.01341769751161337</v>
       </c>
       <c r="H32" t="n">
-        <v>949.4156718829212</v>
+        <v>935.3031883591335</v>
       </c>
       <c r="I32" t="n">
-        <v>198.2751311582607</v>
+        <v>203.005318621267</v>
       </c>
       <c r="J32" t="n">
-        <v>9.000057869254071</v>
+        <v>11.97994325185223</v>
       </c>
       <c r="K32" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>4.035028484006375</v>
       </c>
       <c r="L32" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>1.783431079257582</v>
       </c>
       <c r="M32" t="n">
-        <v>2.30795782175146</v>
+        <v>3.262658552859483</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>0.6380169732061</v>
+        <v>0.9978983705744172</v>
       </c>
       <c r="P32" t="n">
-        <v>0.001060194274178123</v>
+        <v>0.00194906253253848</v>
       </c>
       <c r="Q32" t="n">
-        <v>945.6740233949744</v>
+        <v>809.196578494232</v>
       </c>
       <c r="R32" t="n">
-        <v>197.095394552684</v>
+        <v>205.17306135039</v>
       </c>
       <c r="S32" t="n">
-        <v>9.000057869254071</v>
+        <v>14.40282371194543</v>
       </c>
       <c r="T32" t="n">
-        <v>3.741648487945895</v>
+        <v>122.0715813808952</v>
       </c>
       <c r="U32" t="n">
-        <v>1.179736605576636</v>
+        <v>0.384311649865424</v>
       </c>
       <c r="V32" t="n">
-        <v>2.30795782175146</v>
+        <v>0.8397780927662843</v>
       </c>
       <c r="W32" t="b">
         <v>1</v>
@@ -2806,64 +2806,64 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>935.5686183531994</v>
+        <v>962.0729147792148</v>
       </c>
       <c r="D33" t="n">
-        <v>8.680828042167876</v>
+        <v>8.903987952128947</v>
       </c>
       <c r="E33" t="n">
-        <v>140.8990356917723</v>
+        <v>132.5915889980326</v>
       </c>
       <c r="F33" t="n">
-        <v>0.898436963558197</v>
+        <v>0.7905983924865723</v>
       </c>
       <c r="G33" t="n">
-        <v>0.009168993681669235</v>
+        <v>0.01447403151541948</v>
       </c>
       <c r="H33" t="n">
-        <v>928.8432674575631</v>
+        <v>961.3176773596946</v>
       </c>
       <c r="I33" t="n">
-        <v>176.152769605321</v>
+        <v>176.1526135343724</v>
       </c>
       <c r="J33" t="n">
-        <v>9.037405175530365</v>
+        <v>9.000000000116428</v>
       </c>
       <c r="K33" t="n">
-        <v>6.725350895636325</v>
+        <v>0.7552374195201992</v>
       </c>
       <c r="L33" t="n">
-        <v>35.25373391354876</v>
+        <v>43.5610245363398</v>
       </c>
       <c r="M33" t="n">
-        <v>0.3565771333624888</v>
+        <v>0.09601204798748064</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>0.9964912973813387</v>
+        <v>0.9994829773662345</v>
       </c>
       <c r="P33" t="n">
-        <v>0.001586709028044793</v>
+        <v>0.001782489477256973</v>
       </c>
       <c r="Q33" t="n">
-        <v>813.4494220728872</v>
+        <v>814.7624771308967</v>
       </c>
       <c r="R33" t="n">
-        <v>150.0000472903582</v>
+        <v>150.0000472903334</v>
       </c>
       <c r="S33" t="n">
-        <v>9.000057869397292</v>
+        <v>9.000057869366948</v>
       </c>
       <c r="T33" t="n">
-        <v>122.1191962803123</v>
+        <v>147.310437648318</v>
       </c>
       <c r="U33" t="n">
-        <v>9.101011598585927</v>
+        <v>17.40845829230074</v>
       </c>
       <c r="V33" t="n">
-        <v>0.3192298272294156</v>
+        <v>0.09606991723800107</v>
       </c>
       <c r="W33" t="b">
         <v>1</v>
@@ -2875,68 +2875,68 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Stains</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>966.8356154956803</v>
+        <v>845.0183602460452</v>
       </c>
       <c r="D34" t="n">
-        <v>9.933041109684755</v>
+        <v>11.00615113464798</v>
       </c>
       <c r="E34" t="n">
-        <v>119.561572878882</v>
+        <v>200.3466143205719</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8972465991973877</v>
+        <v>0.5955662727355957</v>
       </c>
       <c r="G34" t="n">
-        <v>0.009224903769791126</v>
+        <v>0.005909173749387264</v>
       </c>
       <c r="H34" t="n">
-        <v>959.1994049448696</v>
+        <v>922.9741913282998</v>
       </c>
       <c r="I34" t="n">
-        <v>176.1525536289689</v>
+        <v>200.3466143205719</v>
       </c>
       <c r="J34" t="n">
-        <v>9.933041109867355</v>
+        <v>11.00615113464798</v>
       </c>
       <c r="K34" t="n">
-        <v>7.636210550810688</v>
+        <v>77.95583108225458</v>
       </c>
       <c r="L34" t="n">
-        <v>56.59098075008694</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.826006013061487e-10</v>
+        <v>0</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0.9999319174620483</v>
+        <v>0.9141702060444017</v>
       </c>
       <c r="P34" t="n">
-        <v>0.001912649810709316</v>
+        <v>0.0008779888867831621</v>
       </c>
       <c r="Q34" t="n">
-        <v>811.105270911317</v>
+        <v>936.5868307737594</v>
       </c>
       <c r="R34" t="n">
-        <v>150.0000472875812</v>
+        <v>199.7881294756043</v>
       </c>
       <c r="S34" t="n">
-        <v>9.857203060597669</v>
+        <v>10.93416933649186</v>
       </c>
       <c r="T34" t="n">
-        <v>155.7303445843633</v>
+        <v>91.56847052771423</v>
       </c>
       <c r="U34" t="n">
-        <v>30.43847440869916</v>
+        <v>0.5584848449675519</v>
       </c>
       <c r="V34" t="n">
-        <v>0.07583804908708558</v>
+        <v>0.07198179815612882</v>
       </c>
       <c r="W34" t="b">
         <v>1</v>
@@ -2952,64 +2952,64 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>948.7421226620029</v>
+        <v>929.9675998021016</v>
       </c>
       <c r="D35" t="n">
-        <v>10.20178510737095</v>
+        <v>8.687511309663687</v>
       </c>
       <c r="E35" t="n">
-        <v>149.931318772952</v>
+        <v>142.901458212072</v>
       </c>
       <c r="F35" t="n">
-        <v>0.898436963558197</v>
+        <v>0.7905983924865723</v>
       </c>
       <c r="G35" t="n">
-        <v>0.009224903769791126</v>
+        <v>0.01447403151541948</v>
       </c>
       <c r="H35" t="n">
-        <v>948.7421226678881</v>
+        <v>929.9533321541509</v>
       </c>
       <c r="I35" t="n">
-        <v>176.1525536325836</v>
+        <v>176.1529775677769</v>
       </c>
       <c r="J35" t="n">
-        <v>10.20178510714254</v>
+        <v>9.000004483504393</v>
       </c>
       <c r="K35" t="n">
-        <v>5.885226528334897e-09</v>
+        <v>0.01426764795075997</v>
       </c>
       <c r="L35" t="n">
-        <v>26.22123485963155</v>
+        <v>33.25151935570489</v>
       </c>
       <c r="M35" t="n">
-        <v>2.284146205511206e-10</v>
+        <v>0.3124931738407053</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>0.9899826675466773</v>
+        <v>0.9941723991944598</v>
       </c>
       <c r="P35" t="n">
-        <v>0.001596905751454016</v>
+        <v>0.001542324938981525</v>
       </c>
       <c r="Q35" t="n">
-        <v>820.4822393528982</v>
+        <v>813.1261581054529</v>
       </c>
       <c r="R35" t="n">
-        <v>156.3679026058684</v>
+        <v>150.0000472904414</v>
       </c>
       <c r="S35" t="n">
-        <v>10.14008394380013</v>
+        <v>9.00005786949913</v>
       </c>
       <c r="T35" t="n">
-        <v>128.2598833091047</v>
+        <v>116.8414416966488</v>
       </c>
       <c r="U35" t="n">
-        <v>6.436583832916426</v>
+        <v>7.098589078369372</v>
       </c>
       <c r="V35" t="n">
-        <v>0.06170116357082556</v>
+        <v>0.3125465598354431</v>
       </c>
       <c r="W35" t="b">
         <v>1</v>
@@ -3021,68 +3021,68 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>970.6477879625279</v>
+        <v>926.6016632857942</v>
       </c>
       <c r="D36" t="n">
-        <v>8.747588815514455</v>
+        <v>14.8366109436522</v>
       </c>
       <c r="E36" t="n">
-        <v>135.5376000465195</v>
+        <v>205.0478136091507</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8972465991973877</v>
+        <v>0.7228195667266846</v>
       </c>
       <c r="G36" t="n">
-        <v>0.009280012920498848</v>
+        <v>0.008416088297963142</v>
       </c>
       <c r="H36" t="n">
-        <v>959.1994420147337</v>
+        <v>926.6016656386225</v>
       </c>
       <c r="I36" t="n">
-        <v>176.1532942893909</v>
+        <v>205.0478124927263</v>
       </c>
       <c r="J36" t="n">
-        <v>9.03739908912322</v>
+        <v>11.77729314408565</v>
       </c>
       <c r="K36" t="n">
-        <v>11.44834594779422</v>
+        <v>2.352828346374736e-06</v>
       </c>
       <c r="L36" t="n">
-        <v>40.61569424287137</v>
+        <v>1.116424357405776e-06</v>
       </c>
       <c r="M36" t="n">
-        <v>0.2898102736087651</v>
+        <v>3.05931779956655</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>0.9991961687348909</v>
+        <v>0.994159039427843</v>
       </c>
       <c r="P36" t="n">
-        <v>0.001841065528967685</v>
+        <v>0.001748581905013277</v>
       </c>
       <c r="Q36" t="n">
-        <v>815.1238461161786</v>
+        <v>815.2810671527558</v>
       </c>
       <c r="R36" t="n">
-        <v>150.000047290153</v>
+        <v>205.3724066480493</v>
       </c>
       <c r="S36" t="n">
-        <v>9.000057869146211</v>
+        <v>14.10779377789854</v>
       </c>
       <c r="T36" t="n">
-        <v>155.5239418463493</v>
+        <v>111.3205961330384</v>
       </c>
       <c r="U36" t="n">
-        <v>14.46244724363351</v>
+        <v>0.3245930388985698</v>
       </c>
       <c r="V36" t="n">
-        <v>0.2524690536317564</v>
+        <v>0.7288171657536555</v>
       </c>
       <c r="W36" t="b">
         <v>1</v>
@@ -3094,68 +3094,68 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Dirtiness</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1061.06698498125</v>
+        <v>916.2393134960464</v>
       </c>
       <c r="D37" t="n">
-        <v>10.30017504928452</v>
+        <v>8.798787181106738</v>
       </c>
       <c r="E37" t="n">
-        <v>197.9360094255946</v>
+        <v>254.6949431029583</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7933045029640198</v>
+        <v>0.6544783711433411</v>
       </c>
       <c r="G37" t="n">
-        <v>0.004426439292728901</v>
+        <v>0.005939361173659563</v>
       </c>
       <c r="H37" t="n">
-        <v>965.6040331737881</v>
+        <v>910.5037043922475</v>
       </c>
       <c r="I37" t="n">
-        <v>197.9360094255946</v>
+        <v>224.7372300887073</v>
       </c>
       <c r="J37" t="n">
-        <v>10.30017504928452</v>
+        <v>9.296241856875497</v>
       </c>
       <c r="K37" t="n">
-        <v>95.46295180746233</v>
+        <v>5.735609103798879</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>29.95771301425094</v>
       </c>
       <c r="M37" t="n">
-        <v>1.77635683940025e-15</v>
+        <v>0.4974546757687595</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>0.9989702954171809</v>
+        <v>0.9933836959334901</v>
       </c>
       <c r="P37" t="n">
-        <v>0.0005774394166326632</v>
+        <v>0.001310920546242343</v>
       </c>
       <c r="Q37" t="n">
-        <v>956.9778042549267</v>
+        <v>823.8594318253088</v>
       </c>
       <c r="R37" t="n">
-        <v>197.7622066873408</v>
+        <v>236.3300221102418</v>
       </c>
       <c r="S37" t="n">
-        <v>10.28562462312191</v>
+        <v>9.000057869320822</v>
       </c>
       <c r="T37" t="n">
-        <v>104.0891807263238</v>
+        <v>92.37988167073763</v>
       </c>
       <c r="U37" t="n">
-        <v>0.1738027382538405</v>
+        <v>18.36492099271646</v>
       </c>
       <c r="V37" t="n">
-        <v>0.01455042616261437</v>
+        <v>0.201270688214084</v>
       </c>
       <c r="W37" t="b">
         <v>1</v>
@@ -3167,68 +3167,68 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>870.7513134103172</v>
+        <v>935.024004079599</v>
       </c>
       <c r="D38" t="n">
-        <v>7.884237696536948</v>
+        <v>9.493295823789762</v>
       </c>
       <c r="E38" t="n">
-        <v>194.6998869595861</v>
+        <v>139.1472518940553</v>
       </c>
       <c r="F38" t="n">
-        <v>0.78486567735672</v>
+        <v>0.7905983924865723</v>
       </c>
       <c r="G38" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.05868716537952423</v>
       </c>
       <c r="H38" t="n">
-        <v>928.8432675222045</v>
+        <v>871.1349564485747</v>
       </c>
       <c r="I38" t="n">
-        <v>194.6998869595861</v>
+        <v>176.1525533989211</v>
       </c>
       <c r="J38" t="n">
-        <v>9.00005786718839</v>
+        <v>9.304083774985546</v>
       </c>
       <c r="K38" t="n">
-        <v>58.09195411188739</v>
+        <v>63.88904763102425</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>37.00530150486583</v>
       </c>
       <c r="M38" t="n">
-        <v>1.115820170651443</v>
+        <v>0.1892120488042153</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>0.898104778270799</v>
+        <v>0.9979507900650925</v>
       </c>
       <c r="P38" t="n">
-        <v>0.0006777249728569186</v>
+        <v>0.001632754862902922</v>
       </c>
       <c r="Q38" t="n">
-        <v>941.934038856728</v>
+        <v>811.3976295487325</v>
       </c>
       <c r="R38" t="n">
-        <v>194.3588315252479</v>
+        <v>150.0000472861513</v>
       </c>
       <c r="S38" t="n">
-        <v>9.00005786936636</v>
+        <v>9.42662096835625</v>
       </c>
       <c r="T38" t="n">
-        <v>71.18272544641081</v>
+        <v>123.6263745308664</v>
       </c>
       <c r="U38" t="n">
-        <v>0.3410554343382728</v>
+        <v>10.85279539209603</v>
       </c>
       <c r="V38" t="n">
-        <v>1.115820172829412</v>
+        <v>0.06667485543351148</v>
       </c>
       <c r="W38" t="b">
         <v>1</v>
@@ -3240,68 +3240,68 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>929.4519289694798</v>
+        <v>867.9713275556323</v>
       </c>
       <c r="D39" t="n">
-        <v>13.38714653154957</v>
+        <v>8.492118626600817</v>
       </c>
       <c r="E39" t="n">
-        <v>214.1658382334469</v>
+        <v>218.6047635319229</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5151498913764954</v>
+        <v>0.6739748120307922</v>
       </c>
       <c r="G39" t="n">
-        <v>0.004665159154683352</v>
+        <v>0.0107807656750083</v>
       </c>
       <c r="H39" t="n">
-        <v>929.4519289835769</v>
+        <v>928.8432674873783</v>
       </c>
       <c r="I39" t="n">
-        <v>214.1658382334469</v>
+        <v>218.6047635319248</v>
       </c>
       <c r="J39" t="n">
-        <v>11.77729472227237</v>
+        <v>9.000057866508561</v>
       </c>
       <c r="K39" t="n">
-        <v>1.409705419064267e-08</v>
+        <v>60.87193993174594</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.875832822406664e-12</v>
       </c>
       <c r="M39" t="n">
-        <v>1.609851809277203</v>
+        <v>0.5079392399077438</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>0.7530527623107396</v>
+        <v>0.8369867081372276</v>
       </c>
       <c r="P39" t="n">
-        <v>0.001270902051980514</v>
+        <v>0.0008393569850330224</v>
       </c>
       <c r="Q39" t="n">
-        <v>840.7056616420263</v>
+        <v>947.0740579907208</v>
       </c>
       <c r="R39" t="n">
-        <v>213.8676355153164</v>
+        <v>215.923748095988</v>
       </c>
       <c r="S39" t="n">
-        <v>12.93203052042315</v>
+        <v>9.000057858025528</v>
       </c>
       <c r="T39" t="n">
-        <v>88.74626732745355</v>
+        <v>79.10273043508846</v>
       </c>
       <c r="U39" t="n">
-        <v>0.2982027181305114</v>
+        <v>2.681015435934967</v>
       </c>
       <c r="V39" t="n">
-        <v>0.4551160111264174</v>
+        <v>0.5079392314247109</v>
       </c>
       <c r="W39" t="b">
         <v>1</v>
@@ -3313,68 +3313,68 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>969.1507432655953</v>
+        <v>1017.531123512318</v>
       </c>
       <c r="D40" t="n">
-        <v>15.11779471417397</v>
+        <v>9.27034211770588</v>
       </c>
       <c r="E40" t="n">
-        <v>205.7625139202212</v>
+        <v>180.3857959086696</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8579153418540955</v>
+        <v>0.5890865921974182</v>
       </c>
       <c r="G40" t="n">
-        <v>0.004654219374060631</v>
+        <v>0.007904686033725739</v>
       </c>
       <c r="H40" t="n">
-        <v>969.1507432561755</v>
+        <v>965.6040331595926</v>
       </c>
       <c r="I40" t="n">
-        <v>205.7625139202211</v>
+        <v>180.3857959086696</v>
       </c>
       <c r="J40" t="n">
-        <v>11.77729472228142</v>
+        <v>9.270342117705876</v>
       </c>
       <c r="K40" t="n">
-        <v>9.419863999937661e-09</v>
+        <v>51.92709035272503</v>
       </c>
       <c r="L40" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M40" t="n">
-        <v>3.340499991892546</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0.9977736881314933</v>
+        <v>0.7697438663348006</v>
       </c>
       <c r="P40" t="n">
-        <v>0.002164460308084747</v>
+        <v>0.00043917985805562</v>
       </c>
       <c r="Q40" t="n">
-        <v>816.361870961309</v>
+        <v>953.6758713339957</v>
       </c>
       <c r="R40" t="n">
-        <v>206.1771441246076</v>
+        <v>180.8479916512672</v>
       </c>
       <c r="S40" t="n">
-        <v>14.17970498194673</v>
+        <v>9.275692175528107</v>
       </c>
       <c r="T40" t="n">
-        <v>152.7888723042863</v>
+        <v>63.85525217832196</v>
       </c>
       <c r="U40" t="n">
-        <v>0.4146302043864125</v>
+        <v>0.4621957425975722</v>
       </c>
       <c r="V40" t="n">
-        <v>0.9380897322272368</v>
+        <v>0.005350057822226972</v>
       </c>
       <c r="W40" t="b">
         <v>1</v>
@@ -3386,68 +3386,68 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>864.2514804699548</v>
+        <v>948.0282373543148</v>
       </c>
       <c r="D41" t="n">
-        <v>6.382136184215076</v>
+        <v>9.181997815258253</v>
       </c>
       <c r="E41" t="n">
-        <v>212.699534889551</v>
+        <v>117.599356467224</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9033607840538025</v>
+        <v>0.7905983924865723</v>
       </c>
       <c r="G41" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.01618981175124645</v>
       </c>
       <c r="H41" t="n">
-        <v>928.8432674698869</v>
+        <v>948.0282373582619</v>
       </c>
       <c r="I41" t="n">
-        <v>212.6995348895511</v>
+        <v>176.1525536277982</v>
       </c>
       <c r="J41" t="n">
-        <v>9.000057868380868</v>
+        <v>13.04806048730416</v>
       </c>
       <c r="K41" t="n">
-        <v>64.59178699993208</v>
+        <v>3.947093318856787e-09</v>
       </c>
       <c r="L41" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>58.5531971605742</v>
       </c>
       <c r="M41" t="n">
-        <v>2.617921684165792</v>
+        <v>3.866062672045908</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>0.9840933010517571</v>
+        <v>0.9999101521770775</v>
       </c>
       <c r="P41" t="n">
-        <v>0.0008211513041026012</v>
+        <v>0.001695329703914839</v>
       </c>
       <c r="Q41" t="n">
-        <v>944.6987375512529</v>
+        <v>813.5609134239396</v>
       </c>
       <c r="R41" t="n">
-        <v>210.6402144596041</v>
+        <v>150.0000472860426</v>
       </c>
       <c r="S41" t="n">
-        <v>9.000057829788277</v>
+        <v>9.109975438975489</v>
       </c>
       <c r="T41" t="n">
-        <v>80.44725708129806</v>
+        <v>134.4673239303752</v>
       </c>
       <c r="U41" t="n">
-        <v>2.059320429946922</v>
+        <v>32.40069081881862</v>
       </c>
       <c r="V41" t="n">
-        <v>2.617921645573201</v>
+        <v>0.07202237628276364</v>
       </c>
       <c r="W41" t="b">
         <v>1</v>
@@ -3459,68 +3459,68 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>945.8832028015731</v>
+        <v>959.8383834301301</v>
       </c>
       <c r="D42" t="n">
-        <v>4.000080069270404</v>
+        <v>14.76159296348758</v>
       </c>
       <c r="E42" t="n">
-        <v>199.2729243726371</v>
+        <v>184.2724959430851</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8448003530502319</v>
+        <v>0.7234267592430115</v>
       </c>
       <c r="G42" t="n">
-        <v>0.00305266329087317</v>
+        <v>0.008424116298556328</v>
       </c>
       <c r="H42" t="n">
-        <v>945.8832028015788</v>
+        <v>931.2030345055626</v>
       </c>
       <c r="I42" t="n">
-        <v>199.2729243726372</v>
+        <v>184.2724959430851</v>
       </c>
       <c r="J42" t="n">
-        <v>9.000057869254071</v>
+        <v>11.7772910843587</v>
       </c>
       <c r="K42" t="n">
-        <v>5.684341886080801e-12</v>
+        <v>28.63534892456744</v>
       </c>
       <c r="L42" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.999977799983667</v>
+        <v>2.984301879128886</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>0.9974606109936222</v>
+        <v>0.9952305758711408</v>
       </c>
       <c r="P42" t="n">
-        <v>0.001081372661017758</v>
+        <v>0.001911867524951935</v>
       </c>
       <c r="Q42" t="n">
-        <v>943.7956656803468</v>
+        <v>817.3428455243761</v>
       </c>
       <c r="R42" t="n">
-        <v>197.9593030747029</v>
+        <v>185.9504320651347</v>
       </c>
       <c r="S42" t="n">
-        <v>9.000057869254071</v>
+        <v>13.92626204698621</v>
       </c>
       <c r="T42" t="n">
-        <v>2.087537121226319</v>
+        <v>142.495537905754</v>
       </c>
       <c r="U42" t="n">
-        <v>1.313621297934247</v>
+        <v>1.67793612204963</v>
       </c>
       <c r="V42" t="n">
-        <v>4.999977799983667</v>
+        <v>0.8353309165013751</v>
       </c>
       <c r="W42" t="b">
         <v>1</v>
@@ -3532,68 +3532,68 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Stains</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>845.0183602460452</v>
+        <v>930.9861861316949</v>
       </c>
       <c r="D43" t="n">
-        <v>11.00615113464798</v>
+        <v>10.19477400562807</v>
       </c>
       <c r="E43" t="n">
-        <v>200.3466143205719</v>
+        <v>156.8152425913856</v>
       </c>
       <c r="F43" t="n">
-        <v>0.709333062171936</v>
+        <v>0.7905983924865723</v>
       </c>
       <c r="G43" t="n">
-        <v>0.003290718421339989</v>
+        <v>0.01447403151541948</v>
       </c>
       <c r="H43" t="n">
-        <v>922.9741913652521</v>
+        <v>930.9896552775257</v>
       </c>
       <c r="I43" t="n">
-        <v>200.3466143205719</v>
+        <v>176.1527446833997</v>
       </c>
       <c r="J43" t="n">
-        <v>11.00615113464798</v>
+        <v>10.14888182215203</v>
       </c>
       <c r="K43" t="n">
-        <v>77.95583111920689</v>
+        <v>0.003469145830763409</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>19.33750209201403</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>0.04589218347604174</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0.9141702060444017</v>
+        <v>0.9288649395605902</v>
       </c>
       <c r="P43" t="n">
-        <v>0.0008779888867831621</v>
+        <v>0.001265134556541037</v>
       </c>
       <c r="Q43" t="n">
-        <v>936.5868307737594</v>
+        <v>830.6202214179372</v>
       </c>
       <c r="R43" t="n">
-        <v>199.7881294756043</v>
+        <v>162.6499106517926</v>
       </c>
       <c r="S43" t="n">
-        <v>10.93416933649186</v>
+        <v>10.14717197528575</v>
       </c>
       <c r="T43" t="n">
-        <v>91.56847052771423</v>
+        <v>100.3659647137578</v>
       </c>
       <c r="U43" t="n">
-        <v>0.5584848449675519</v>
+        <v>5.834668060406983</v>
       </c>
       <c r="V43" t="n">
-        <v>0.07198179815612882</v>
+        <v>0.04760203034231836</v>
       </c>
       <c r="W43" t="b">
         <v>1</v>
@@ -3609,64 +3609,64 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>879.0897682029588</v>
+        <v>878.0453694497114</v>
       </c>
       <c r="D44" t="n">
-        <v>6.802501004329576</v>
+        <v>8.856200757471097</v>
       </c>
       <c r="E44" t="n">
-        <v>199.392593431129</v>
+        <v>208.6281755523033</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8870348930358887</v>
+        <v>0.5621231198310852</v>
       </c>
       <c r="G44" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.0107807656750083</v>
       </c>
       <c r="H44" t="n">
-        <v>928.8432675234773</v>
+        <v>928.8432675273689</v>
       </c>
       <c r="I44" t="n">
-        <v>199.392593431129</v>
+        <v>208.6281755523033</v>
       </c>
       <c r="J44" t="n">
-        <v>9.000057865899157</v>
+        <v>9.000057867329405</v>
       </c>
       <c r="K44" t="n">
-        <v>49.75349932051847</v>
+        <v>50.79789807765746</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2.197556861569581</v>
+        <v>0.1438571098583079</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0.9646910232842123</v>
+        <v>0.6911975537835221</v>
       </c>
       <c r="P44" t="n">
-        <v>0.0006059814839692356</v>
+        <v>0.0006543153484417812</v>
       </c>
       <c r="Q44" t="n">
-        <v>943.3564193997805</v>
+        <v>945.0847396805009</v>
       </c>
       <c r="R44" t="n">
-        <v>198.7900667580237</v>
+        <v>207.2602058182935</v>
       </c>
       <c r="S44" t="n">
-        <v>9.000057867752513</v>
+        <v>9.000057851877191</v>
       </c>
       <c r="T44" t="n">
-        <v>64.26665119682173</v>
+        <v>67.03937023078947</v>
       </c>
       <c r="U44" t="n">
-        <v>0.6025266731053307</v>
+        <v>1.367969734009847</v>
       </c>
       <c r="V44" t="n">
-        <v>2.197556863422937</v>
+        <v>0.1438570944060942</v>
       </c>
       <c r="W44" t="b">
         <v>1</v>
@@ -3678,68 +3678,68 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>907.5210483459867</v>
+        <v>834.8959959628713</v>
       </c>
       <c r="D45" t="n">
-        <v>14.47908425102576</v>
+        <v>7.016158992161908</v>
       </c>
       <c r="E45" t="n">
-        <v>215.0193854879847</v>
+        <v>186.8628065520684</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8253076672554016</v>
+        <v>0.7581575512886047</v>
       </c>
       <c r="G45" t="n">
-        <v>0.004446235951036215</v>
+        <v>0.0107807656750083</v>
       </c>
       <c r="H45" t="n">
-        <v>908.0128797806661</v>
+        <v>928.8432674756143</v>
       </c>
       <c r="I45" t="n">
-        <v>215.0193854879847</v>
+        <v>186.8628065520684</v>
       </c>
       <c r="J45" t="n">
-        <v>11.77729472288637</v>
+        <v>9.000057867796691</v>
       </c>
       <c r="K45" t="n">
-        <v>0.4918314346793977</v>
+        <v>93.94727151274299</v>
       </c>
       <c r="L45" t="n">
         <v>5.684341886080801e-14</v>
       </c>
       <c r="M45" t="n">
-        <v>2.701789528139384</v>
+        <v>1.983898875634783</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>0.964248395075688</v>
+        <v>0.9460786248053551</v>
       </c>
       <c r="P45" t="n">
-        <v>0.001503292210404655</v>
+        <v>0.001070384573441114</v>
       </c>
       <c r="Q45" t="n">
-        <v>818.5257614600431</v>
+        <v>938.3728845080026</v>
       </c>
       <c r="R45" t="n">
-        <v>214.6897995010518</v>
+        <v>186.9317176624866</v>
       </c>
       <c r="S45" t="n">
-        <v>13.89897201341323</v>
+        <v>9.000057869916374</v>
       </c>
       <c r="T45" t="n">
-        <v>88.99528688594364</v>
+        <v>103.4768885451313</v>
       </c>
       <c r="U45" t="n">
-        <v>0.329585986932841</v>
+        <v>0.06891111041821318</v>
       </c>
       <c r="V45" t="n">
-        <v>0.5801122376125303</v>
+        <v>1.983898877754465</v>
       </c>
       <c r="W45" t="b">
         <v>1</v>
@@ -3751,68 +3751,68 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>966.8459465402781</v>
+        <v>958.5923643826517</v>
       </c>
       <c r="D46" t="n">
-        <v>6.244284486169816</v>
+        <v>13.47709016575634</v>
       </c>
       <c r="E46" t="n">
-        <v>206.1158392578174</v>
+        <v>197.0407245979124</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8416843414306641</v>
+        <v>0.6135947108268738</v>
       </c>
       <c r="G46" t="n">
-        <v>0.003047461854293942</v>
+        <v>0.008424116298556328</v>
       </c>
       <c r="H46" t="n">
-        <v>966.8459465402855</v>
+        <v>958.5893134440868</v>
       </c>
       <c r="I46" t="n">
-        <v>206.1158392578177</v>
+        <v>197.0407245979124</v>
       </c>
       <c r="J46" t="n">
-        <v>9.000057869254071</v>
+        <v>11.77724993003268</v>
       </c>
       <c r="K46" t="n">
-        <v>7.389644451905042e-12</v>
+        <v>0.003050938564911121</v>
       </c>
       <c r="L46" t="n">
-        <v>3.126388037344441e-13</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2.755773383084255</v>
+        <v>1.699840235723666</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>0.8684485648217146</v>
+        <v>0.8796295315742628</v>
       </c>
       <c r="P46" t="n">
-        <v>0.001410246476517982</v>
+        <v>0.001452622566738687</v>
       </c>
       <c r="Q46" t="n">
-        <v>953.1369688631636</v>
+        <v>841.8496432852859</v>
       </c>
       <c r="R46" t="n">
-        <v>203.4812354644959</v>
+        <v>197.8759414472123</v>
       </c>
       <c r="S46" t="n">
-        <v>9.000057869254071</v>
+        <v>12.91593221380215</v>
       </c>
       <c r="T46" t="n">
-        <v>13.70897767711449</v>
+        <v>116.7427210973658</v>
       </c>
       <c r="U46" t="n">
-        <v>2.634603793321503</v>
+        <v>0.8352168492999681</v>
       </c>
       <c r="V46" t="n">
-        <v>2.755773383084255</v>
+        <v>0.5611579519541916</v>
       </c>
       <c r="W46" t="b">
         <v>1</v>
@@ -3824,68 +3824,68 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Dirtiness</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>928.3999478323574</v>
+        <v>956.1480713943938</v>
       </c>
       <c r="D47" t="n">
-        <v>4.983346624917393</v>
+        <v>10.47729600880942</v>
       </c>
       <c r="E47" t="n">
-        <v>214.3444516963449</v>
+        <v>234.7411873193184</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7518618106842041</v>
+        <v>0.6140981912612915</v>
       </c>
       <c r="G47" t="n">
-        <v>0.003003395861014724</v>
+        <v>0.005481656175106764</v>
       </c>
       <c r="H47" t="n">
-        <v>928.3999478325787</v>
+        <v>956.1480714109659</v>
       </c>
       <c r="I47" t="n">
-        <v>214.3444516963429</v>
+        <v>222.3568452404015</v>
       </c>
       <c r="J47" t="n">
-        <v>9.000057869254071</v>
+        <v>10.47729600891967</v>
       </c>
       <c r="K47" t="n">
-        <v>2.213482730439864e-10</v>
+        <v>1.657213033467997e-08</v>
       </c>
       <c r="L47" t="n">
-        <v>1.961097950697877e-12</v>
+        <v>12.38434207891686</v>
       </c>
       <c r="M47" t="n">
-        <v>4.016711244336678</v>
+        <v>1.102513635942159e-10</v>
       </c>
       <c r="N47" t="b">
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>0.9706963315591096</v>
+        <v>0.676259209640181</v>
       </c>
       <c r="P47" t="n">
-        <v>0.0007114460105238887</v>
+        <v>0.001161497825082428</v>
       </c>
       <c r="Q47" t="n">
-        <v>879.7545943628139</v>
+        <v>860.1313150301785</v>
       </c>
       <c r="R47" t="n">
-        <v>213.0064730246715</v>
+        <v>219.740945322078</v>
       </c>
       <c r="S47" t="n">
-        <v>9.000057869254071</v>
+        <v>10.48328932262805</v>
       </c>
       <c r="T47" t="n">
-        <v>48.64535346954347</v>
+        <v>96.01675636421533</v>
       </c>
       <c r="U47" t="n">
-        <v>1.337978671673397</v>
+        <v>15.00024199724038</v>
       </c>
       <c r="V47" t="n">
-        <v>4.016711244336678</v>
+        <v>0.005993313818624557</v>
       </c>
       <c r="W47" t="b">
         <v>1</v>
@@ -3897,68 +3897,68 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>874.6089997628396</v>
+        <v>1074.522531647945</v>
       </c>
       <c r="D48" t="n">
-        <v>8.393235415755681</v>
+        <v>7.270595615076266</v>
       </c>
       <c r="E48" t="n">
-        <v>180.8725179414861</v>
+        <v>200.626561449358</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6910176873207092</v>
+        <v>0.6431265473365784</v>
       </c>
       <c r="G48" t="n">
-        <v>0.005945156328380108</v>
+        <v>0.007977633737027645</v>
       </c>
       <c r="H48" t="n">
-        <v>928.8432674612978</v>
+        <v>965.6040331489128</v>
       </c>
       <c r="I48" t="n">
-        <v>180.8725179414864</v>
+        <v>200.626561449358</v>
       </c>
       <c r="J48" t="n">
-        <v>9.000057869244914</v>
+        <v>9.00005786727233</v>
       </c>
       <c r="K48" t="n">
-        <v>54.23426769845821</v>
+        <v>108.9184984990327</v>
       </c>
       <c r="L48" t="n">
-        <v>3.126388037344441e-13</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.606822453489233</v>
+        <v>1.729462252196065</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>0.752846972513842</v>
+        <v>0.9978547212377892</v>
       </c>
       <c r="P48" t="n">
-        <v>0.0006736926414182765</v>
+        <v>0.0006681420358284944</v>
       </c>
       <c r="Q48" t="n">
-        <v>942.1283737514706</v>
+        <v>957.7165529023971</v>
       </c>
       <c r="R48" t="n">
-        <v>181.1423017811665</v>
+        <v>200.2914651770552</v>
       </c>
       <c r="S48" t="n">
-        <v>9.000057869311426</v>
+        <v>9.00005786869111</v>
       </c>
       <c r="T48" t="n">
-        <v>67.51937398863095</v>
+        <v>116.8059787455484</v>
       </c>
       <c r="U48" t="n">
-        <v>0.2697838396804002</v>
+        <v>0.3350962723027919</v>
       </c>
       <c r="V48" t="n">
-        <v>0.6068224535557452</v>
+        <v>1.729462253614845</v>
       </c>
       <c r="W48" t="b">
         <v>1</v>
@@ -3970,68 +3970,68 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>Stains</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>916.2393134960464</v>
+        <v>864.3495133812861</v>
       </c>
       <c r="D49" t="n">
-        <v>8.798787181106738</v>
+        <v>10.08936073859624</v>
       </c>
       <c r="E49" t="n">
-        <v>254.6949431029583</v>
+        <v>183.4775643305902</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8057592511177063</v>
+        <v>0.5327199101448059</v>
       </c>
       <c r="G49" t="n">
-        <v>0.003143226960673928</v>
+        <v>0.005909173749387264</v>
       </c>
       <c r="H49" t="n">
-        <v>910.5035790805175</v>
+        <v>922.9741913766268</v>
       </c>
       <c r="I49" t="n">
-        <v>224.7366045534222</v>
+        <v>183.4775643305902</v>
       </c>
       <c r="J49" t="n">
-        <v>9.041596437084181</v>
+        <v>10.08936073859624</v>
       </c>
       <c r="K49" t="n">
-        <v>5.735734415528896</v>
+        <v>58.62467799534068</v>
       </c>
       <c r="L49" t="n">
-        <v>29.95833854953605</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.2428092559774431</v>
+        <v>0</v>
       </c>
       <c r="N49" t="b">
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>0.9933836959334901</v>
+        <v>0.7317755814384203</v>
       </c>
       <c r="P49" t="n">
-        <v>0.001310920546242343</v>
+        <v>0.000663159104119457</v>
       </c>
       <c r="Q49" t="n">
-        <v>823.8594318253088</v>
+        <v>935.7902123807238</v>
       </c>
       <c r="R49" t="n">
-        <v>236.3300221102418</v>
+        <v>183.9322719644943</v>
       </c>
       <c r="S49" t="n">
-        <v>9.000057869320822</v>
+        <v>10.06480901148663</v>
       </c>
       <c r="T49" t="n">
-        <v>92.37988167073763</v>
+        <v>71.4406989994377</v>
       </c>
       <c r="U49" t="n">
-        <v>18.36492099271646</v>
+        <v>0.4547076339040927</v>
       </c>
       <c r="V49" t="n">
-        <v>0.201270688214084</v>
+        <v>0.02455172710960696</v>
       </c>
       <c r="W49" t="b">
         <v>1</v>
@@ -4043,68 +4043,68 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Dirtiness</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>866.6469798302189</v>
+        <v>952.5275915909282</v>
       </c>
       <c r="D50" t="n">
-        <v>8.352002582573306</v>
+        <v>9.496836480953643</v>
       </c>
       <c r="E50" t="n">
-        <v>200.3207432755719</v>
+        <v>276.9861334429187</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7423422336578369</v>
+        <v>0.6614874005317688</v>
       </c>
       <c r="G50" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.006804721895605326</v>
       </c>
       <c r="H50" t="n">
-        <v>928.8432675015051</v>
+        <v>952.5275916104775</v>
       </c>
       <c r="I50" t="n">
-        <v>200.3207432755719</v>
+        <v>224.737590442474</v>
       </c>
       <c r="J50" t="n">
-        <v>9.000057867345458</v>
+        <v>9.49683648114731</v>
       </c>
       <c r="K50" t="n">
-        <v>62.1962876712862</v>
+        <v>1.954936124093365e-08</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>52.2485430004447</v>
       </c>
       <c r="M50" t="n">
-        <v>0.6480552847721519</v>
+        <v>1.936673044156123e-10</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>0.8340759480899332</v>
+        <v>0.9999185704371893</v>
       </c>
       <c r="P50" t="n">
-        <v>0.0007265959383227255</v>
+        <v>0.002586488068130616</v>
       </c>
       <c r="Q50" t="n">
-        <v>942.1804231281868</v>
+        <v>953.2697017965532</v>
       </c>
       <c r="R50" t="n">
-        <v>199.5367648590452</v>
+        <v>213.2387300333199</v>
       </c>
       <c r="S50" t="n">
-        <v>9.000057867298075</v>
+        <v>9.525692397766266</v>
       </c>
       <c r="T50" t="n">
-        <v>75.53344329796789</v>
+        <v>0.7421102056250675</v>
       </c>
       <c r="U50" t="n">
-        <v>0.7839784165266792</v>
+        <v>63.74740340959875</v>
       </c>
       <c r="V50" t="n">
-        <v>0.6480552847247694</v>
+        <v>0.02885591681262234</v>
       </c>
       <c r="W50" t="b">
         <v>1</v>
@@ -4116,68 +4116,68 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>944.0919717972195</v>
+        <v>850.9222712794735</v>
       </c>
       <c r="D51" t="n">
-        <v>9.309987400185415</v>
+        <v>7.209835753453065</v>
       </c>
       <c r="E51" t="n">
-        <v>232.6787413846192</v>
+        <v>200.2000321982746</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6677823066711426</v>
+        <v>0.7841600179672241</v>
       </c>
       <c r="G51" t="n">
-        <v>0.003891526954248548</v>
+        <v>0.0107807656750083</v>
       </c>
       <c r="H51" t="n">
-        <v>944.0947912973799</v>
+        <v>928.8432674721494</v>
       </c>
       <c r="I51" t="n">
-        <v>224.7375904956835</v>
+        <v>200.2000321982746</v>
       </c>
       <c r="J51" t="n">
-        <v>9.309835143384889</v>
+        <v>9.000057868991323</v>
       </c>
       <c r="K51" t="n">
-        <v>0.002819500160399002</v>
+        <v>77.92099619267583</v>
       </c>
       <c r="L51" t="n">
-        <v>7.941150888935766</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.000152256800525663</v>
+        <v>1.790222115538258</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>0.5462332029619766</v>
+        <v>0.9583416528171256</v>
       </c>
       <c r="P51" t="n">
-        <v>0.001006409582844446</v>
+        <v>0.0008866006028634679</v>
       </c>
       <c r="Q51" t="n">
-        <v>861.046482093859</v>
+        <v>940.7005596673206</v>
       </c>
       <c r="R51" t="n">
-        <v>219.8711815678608</v>
+        <v>199.2758436352991</v>
       </c>
       <c r="S51" t="n">
-        <v>9.264297069358657</v>
+        <v>9.000057867420534</v>
       </c>
       <c r="T51" t="n">
-        <v>83.04548970336043</v>
+        <v>89.77828838784706</v>
       </c>
       <c r="U51" t="n">
-        <v>12.80755981675847</v>
+        <v>0.9241885629755586</v>
       </c>
       <c r="V51" t="n">
-        <v>0.04569033082675844</v>
+        <v>1.790222113967468</v>
       </c>
       <c r="W51" t="b">
         <v>1</v>
@@ -4189,68 +4189,68 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>957.142251430235</v>
+        <v>874.1975775676389</v>
       </c>
       <c r="D52" t="n">
-        <v>8.69235741890656</v>
+        <v>8.330144978297355</v>
       </c>
       <c r="E52" t="n">
-        <v>241.1149309650345</v>
+        <v>207.9266506684008</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6677823066711426</v>
+        <v>0.6621172428131104</v>
       </c>
       <c r="G52" t="n">
-        <v>0.003891526954248548</v>
+        <v>0.0107807656750083</v>
       </c>
       <c r="H52" t="n">
-        <v>957.1422514365698</v>
+        <v>928.8432675261648</v>
       </c>
       <c r="I52" t="n">
-        <v>224.7375904850236</v>
+        <v>207.9266506684009</v>
       </c>
       <c r="J52" t="n">
-        <v>9.000057869254068</v>
+        <v>9.000057866516878</v>
       </c>
       <c r="K52" t="n">
-        <v>6.334857971523888e-09</v>
+        <v>54.64568995852596</v>
       </c>
       <c r="L52" t="n">
-        <v>16.3773404800109</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M52" t="n">
-        <v>0.3077004503475074</v>
+        <v>0.6699128882195229</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>0.913058609196467</v>
+        <v>0.8471564595625299</v>
       </c>
       <c r="P52" t="n">
-        <v>0.001233767894678567</v>
+        <v>0.0006870242246896139</v>
       </c>
       <c r="Q52" t="n">
-        <v>853.2008744156448</v>
+        <v>944.4718311621449</v>
       </c>
       <c r="R52" t="n">
-        <v>224.5238548111134</v>
+        <v>206.5607728354697</v>
       </c>
       <c r="S52" t="n">
-        <v>9.0000578694449</v>
+        <v>9.000057854730544</v>
       </c>
       <c r="T52" t="n">
-        <v>103.9413770145902</v>
+        <v>70.27425359450604</v>
       </c>
       <c r="U52" t="n">
-        <v>16.59107615392114</v>
+        <v>1.365877832931119</v>
       </c>
       <c r="V52" t="n">
-        <v>0.3077004505383396</v>
+        <v>0.6699128764331892</v>
       </c>
       <c r="W52" t="b">
         <v>1</v>
@@ -4262,68 +4262,68 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Dirtiness</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>938.1459435408578</v>
+        <v>980.0546865261117</v>
       </c>
       <c r="D53" t="n">
-        <v>5.745619797061272</v>
+        <v>11.22234525646797</v>
       </c>
       <c r="E53" t="n">
-        <v>191.8219120285565</v>
+        <v>274.3893932538601</v>
       </c>
       <c r="F53" t="n">
-        <v>0.841779351234436</v>
+        <v>0.6526216864585876</v>
       </c>
       <c r="G53" t="n">
-        <v>0.00305266329087317</v>
+        <v>0.006203936412930489</v>
       </c>
       <c r="H53" t="n">
-        <v>938.1459435408819</v>
+        <v>991.5080134160714</v>
       </c>
       <c r="I53" t="n">
-        <v>191.8219120285565</v>
+        <v>224.7359402359462</v>
       </c>
       <c r="J53" t="n">
-        <v>9.000057869254071</v>
+        <v>11.2223430071803</v>
       </c>
       <c r="K53" t="n">
-        <v>2.41016095969826e-11</v>
+        <v>11.45332688995973</v>
       </c>
       <c r="L53" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>49.65345301791385</v>
       </c>
       <c r="M53" t="n">
-        <v>3.2544380721928</v>
+        <v>2.24928767877941e-06</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0.9430288734295714</v>
+        <v>0.9998216593048536</v>
       </c>
       <c r="P53" t="n">
-        <v>0.0009309934670253035</v>
+        <v>0.002651848498518323</v>
       </c>
       <c r="Q53" t="n">
-        <v>939.4137983040019</v>
+        <v>960.6726882500265</v>
       </c>
       <c r="R53" t="n">
-        <v>191.3248356440719</v>
+        <v>212.9050482834675</v>
       </c>
       <c r="S53" t="n">
-        <v>9.000057869254071</v>
+        <v>11.14477895032718</v>
       </c>
       <c r="T53" t="n">
-        <v>1.267854763144101</v>
+        <v>19.38199827608526</v>
       </c>
       <c r="U53" t="n">
-        <v>0.4970763844845862</v>
+        <v>61.48434497039256</v>
       </c>
       <c r="V53" t="n">
-        <v>3.2544380721928</v>
+        <v>0.07756630614079363</v>
       </c>
       <c r="W53" t="b">
         <v>1</v>
@@ -4339,64 +4339,64 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>957.041107930286</v>
+        <v>947.7088114505497</v>
       </c>
       <c r="D54" t="n">
-        <v>16.64018067797121</v>
+        <v>15.04330896333172</v>
       </c>
       <c r="E54" t="n">
-        <v>200.0934717636573</v>
+        <v>203.2822033198099</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8591651916503906</v>
+        <v>0.7234267592430115</v>
       </c>
       <c r="G54" t="n">
-        <v>0.004665159154683352</v>
+        <v>0.008424116298556328</v>
       </c>
       <c r="H54" t="n">
-        <v>957.041107955317</v>
+        <v>947.7087833202827</v>
       </c>
       <c r="I54" t="n">
-        <v>200.0934717636573</v>
+        <v>203.2822136370266</v>
       </c>
       <c r="J54" t="n">
-        <v>11.77729471945922</v>
+        <v>11.77729058984163</v>
       </c>
       <c r="K54" t="n">
-        <v>2.503099949535681e-08</v>
+        <v>2.813026696912857e-05</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.031721677691166e-05</v>
       </c>
       <c r="M54" t="n">
-        <v>4.86288595851199</v>
+        <v>3.266018373490088</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>0.9998740219463007</v>
+        <v>0.9973670931728997</v>
       </c>
       <c r="P54" t="n">
-        <v>0.003097996831260259</v>
+        <v>0.001978279186394049</v>
       </c>
       <c r="Q54" t="n">
-        <v>800.0000006061211</v>
+        <v>814.6753526656346</v>
       </c>
       <c r="R54" t="n">
-        <v>201.2276890670141</v>
+        <v>203.8010938176184</v>
       </c>
       <c r="S54" t="n">
-        <v>14.99994212736794</v>
+        <v>14.1921751958092</v>
       </c>
       <c r="T54" t="n">
-        <v>157.0411073241648</v>
+        <v>133.0334587849151</v>
       </c>
       <c r="U54" t="n">
-        <v>1.13421730335682</v>
+        <v>0.5188904978085702</v>
       </c>
       <c r="V54" t="n">
-        <v>1.640238550603264</v>
+        <v>0.8511337675225228</v>
       </c>
       <c r="W54" t="b">
         <v>1</v>
@@ -4412,64 +4412,64 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>956.9535296707668</v>
+        <v>944.0919717972195</v>
       </c>
       <c r="D55" t="n">
-        <v>7.978997679123756</v>
+        <v>9.309987400185415</v>
       </c>
       <c r="E55" t="n">
-        <v>243.8252811055272</v>
+        <v>232.6787413846192</v>
       </c>
       <c r="F55" t="n">
-        <v>0.6496495604515076</v>
+        <v>0.5879876613616943</v>
       </c>
       <c r="G55" t="n">
-        <v>0.003891526954248548</v>
+        <v>0.005481656175106764</v>
       </c>
       <c r="H55" t="n">
-        <v>956.9535295774681</v>
+        <v>944.0992593563091</v>
       </c>
       <c r="I55" t="n">
-        <v>224.7375904805501</v>
+        <v>222.3550699320454</v>
       </c>
       <c r="J55" t="n">
-        <v>9.000057869254118</v>
+        <v>9.309987400185413</v>
       </c>
       <c r="K55" t="n">
-        <v>9.32986949919723e-08</v>
+        <v>0.007287559089604656</v>
       </c>
       <c r="L55" t="n">
-        <v>19.08769062497709</v>
+        <v>10.32367145257379</v>
       </c>
       <c r="M55" t="n">
-        <v>1.021060190130362</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>0.9346431973215277</v>
+        <v>0.5462332029619766</v>
       </c>
       <c r="P55" t="n">
-        <v>0.001289202305866142</v>
+        <v>0.001006409582844446</v>
       </c>
       <c r="Q55" t="n">
-        <v>849.3825463134793</v>
+        <v>861.046482093859</v>
       </c>
       <c r="R55" t="n">
-        <v>226.2314470854654</v>
+        <v>219.8711815678608</v>
       </c>
       <c r="S55" t="n">
-        <v>9.000057869661168</v>
+        <v>9.264297069358657</v>
       </c>
       <c r="T55" t="n">
-        <v>107.5709833572874</v>
+        <v>83.04548970336043</v>
       </c>
       <c r="U55" t="n">
-        <v>17.59383402006179</v>
+        <v>12.80755981675847</v>
       </c>
       <c r="V55" t="n">
-        <v>1.021060190537412</v>
+        <v>0.04569033082675844</v>
       </c>
       <c r="W55" t="b">
         <v>1</v>
@@ -4481,68 +4481,68 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>907.9083440246934</v>
+        <v>945.1483392742041</v>
       </c>
       <c r="D56" t="n">
-        <v>10.62947649711448</v>
+        <v>16.47453325099633</v>
       </c>
       <c r="E56" t="n">
-        <v>128.3441543429158</v>
+        <v>204.0138139078038</v>
       </c>
       <c r="F56" t="n">
-        <v>0.833095371723175</v>
+        <v>0.7234267592430115</v>
       </c>
       <c r="G56" t="n">
-        <v>0.008665982633829117</v>
+        <v>0.008424116298556328</v>
       </c>
       <c r="H56" t="n">
-        <v>908.0130066194835</v>
+        <v>945.1480789311051</v>
       </c>
       <c r="I56" t="n">
-        <v>176.1525616200267</v>
+        <v>204.0139101225869</v>
       </c>
       <c r="J56" t="n">
-        <v>10.31536429843633</v>
+        <v>11.77728359765431</v>
       </c>
       <c r="K56" t="n">
-        <v>0.1046625947900566</v>
+        <v>0.0002603430989438493</v>
       </c>
       <c r="L56" t="n">
-        <v>47.80840727711089</v>
+        <v>9.621478315580134e-05</v>
       </c>
       <c r="M56" t="n">
-        <v>0.314112198678151</v>
+        <v>4.697249653342029</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>0.9992326166729234</v>
+        <v>0.9998293157136278</v>
       </c>
       <c r="P56" t="n">
-        <v>0.001507563620875813</v>
+        <v>0.003014767551189289</v>
       </c>
       <c r="Q56" t="n">
-        <v>805.1864964063076</v>
+        <v>800.0000003429969</v>
       </c>
       <c r="R56" t="n">
-        <v>150.0000472887688</v>
+        <v>204.7873332373533</v>
       </c>
       <c r="S56" t="n">
-        <v>10.57059963391205</v>
+        <v>14.9999420403823</v>
       </c>
       <c r="T56" t="n">
-        <v>102.7218476183858</v>
+        <v>145.1483389312071</v>
       </c>
       <c r="U56" t="n">
-        <v>21.65589294585297</v>
+        <v>0.7735193295494867</v>
       </c>
       <c r="V56" t="n">
-        <v>0.05887686320242302</v>
+        <v>1.474591210614033</v>
       </c>
       <c r="W56" t="b">
         <v>1</v>
@@ -4554,68 +4554,68 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>970.6776210984842</v>
+        <v>952.5999645160319</v>
       </c>
       <c r="D57" t="n">
-        <v>8.276953970708769</v>
+        <v>4.619017120565551</v>
       </c>
       <c r="E57" t="n">
-        <v>285.6788027223245</v>
+        <v>204.7455476235796</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8148069381713867</v>
+        <v>0.6949941515922546</v>
       </c>
       <c r="G57" t="n">
-        <v>0.003883478464558721</v>
+        <v>0.005485068075358868</v>
       </c>
       <c r="H57" t="n">
-        <v>970.6776210728542</v>
+        <v>952.5999645160553</v>
       </c>
       <c r="I57" t="n">
-        <v>224.7375904774019</v>
+        <v>204.7455476235801</v>
       </c>
       <c r="J57" t="n">
-        <v>9.000057869254086</v>
+        <v>9.000057869254071</v>
       </c>
       <c r="K57" t="n">
-        <v>2.5630015443312e-08</v>
+        <v>2.330580173293129e-11</v>
       </c>
       <c r="L57" t="n">
-        <v>60.94121224492253</v>
+        <v>4.263256414560601e-13</v>
       </c>
       <c r="M57" t="n">
-        <v>0.7231038985453164</v>
+        <v>4.381040748688521</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>0.9999076436685418</v>
+        <v>0.9953407538462484</v>
       </c>
       <c r="P57" t="n">
-        <v>0.002862147847864263</v>
+        <v>0.001288184610508574</v>
       </c>
       <c r="Q57" t="n">
-        <v>962.2271336923334</v>
+        <v>946.9251142389905</v>
       </c>
       <c r="R57" t="n">
-        <v>213.265116005748</v>
+        <v>202.4803961183322</v>
       </c>
       <c r="S57" t="n">
-        <v>9.000057869235404</v>
+        <v>9.000057869254071</v>
       </c>
       <c r="T57" t="n">
-        <v>8.450487406150842</v>
+        <v>5.674850277041401</v>
       </c>
       <c r="U57" t="n">
-        <v>72.41368671657642</v>
+        <v>2.265151505247388</v>
       </c>
       <c r="V57" t="n">
-        <v>0.7231038985266345</v>
+        <v>4.381040748688521</v>
       </c>
       <c r="W57" t="b">
         <v>1</v>
@@ -4627,68 +4627,68 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Dirtiness</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>834.8959959628713</v>
+        <v>934.1516015800008</v>
       </c>
       <c r="D58" t="n">
-        <v>7.016158992161908</v>
+        <v>9.672204944122537</v>
       </c>
       <c r="E58" t="n">
-        <v>186.8628065520684</v>
+        <v>261.3919563361865</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8687505125999451</v>
+        <v>0.6614874005317688</v>
       </c>
       <c r="G58" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.06253347545862198</v>
       </c>
       <c r="H58" t="n">
-        <v>928.8432676219472</v>
+        <v>916.5765949595466</v>
       </c>
       <c r="I58" t="n">
-        <v>186.8628065520681</v>
+        <v>226.6297487372529</v>
       </c>
       <c r="J58" t="n">
-        <v>9.000057867462752</v>
+        <v>10.4736733246405</v>
       </c>
       <c r="K58" t="n">
-        <v>93.94727165907591</v>
+        <v>17.57500662045425</v>
       </c>
       <c r="L58" t="n">
-        <v>2.557953848736361e-13</v>
+        <v>34.7622075989336</v>
       </c>
       <c r="M58" t="n">
-        <v>1.983898875300844</v>
+        <v>0.8014683805179672</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>0.9460786248053551</v>
+        <v>0.9990510067272277</v>
       </c>
       <c r="P58" t="n">
-        <v>0.001070384573441114</v>
+        <v>0.001601802584027147</v>
       </c>
       <c r="Q58" t="n">
-        <v>938.3728845080026</v>
+        <v>818.0769121803255</v>
       </c>
       <c r="R58" t="n">
-        <v>186.9317176624866</v>
+        <v>238.1022239749218</v>
       </c>
       <c r="S58" t="n">
-        <v>9.000057869916374</v>
+        <v>9.620864224866009</v>
       </c>
       <c r="T58" t="n">
-        <v>103.4768885451313</v>
+        <v>116.0746893996753</v>
       </c>
       <c r="U58" t="n">
-        <v>0.06891111041821318</v>
+        <v>23.2897323612647</v>
       </c>
       <c r="V58" t="n">
-        <v>1.983898877754465</v>
+        <v>0.05134071925652783</v>
       </c>
       <c r="W58" t="b">
         <v>1</v>
@@ -4700,68 +4700,68 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>855.8840427817152</v>
+        <v>977.0407873194865</v>
       </c>
       <c r="D59" t="n">
-        <v>8.192331414542458</v>
+        <v>9.6400238264191</v>
       </c>
       <c r="E59" t="n">
-        <v>198.999589622694</v>
+        <v>131.4534776103323</v>
       </c>
       <c r="F59" t="n">
-        <v>0.7447089552879333</v>
+        <v>0.7780663967132568</v>
       </c>
       <c r="G59" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.01447403151541948</v>
       </c>
       <c r="H59" t="n">
-        <v>928.8432674659656</v>
+        <v>964.5525899945035</v>
       </c>
       <c r="I59" t="n">
-        <v>198.999589622694</v>
+        <v>176.153369464617</v>
       </c>
       <c r="J59" t="n">
-        <v>9.000057869021807</v>
+        <v>9.640194385009149</v>
       </c>
       <c r="K59" t="n">
-        <v>72.95922468425044</v>
+        <v>12.48819732498305</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>44.69989185428474</v>
       </c>
       <c r="M59" t="n">
-        <v>0.807726454479349</v>
+        <v>0.0001705585900495521</v>
       </c>
       <c r="N59" t="b">
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0.8582236933007159</v>
+        <v>0.9996751182502833</v>
       </c>
       <c r="P59" t="n">
-        <v>0.0008314436356054831</v>
+        <v>0.001950419708030513</v>
       </c>
       <c r="Q59" t="n">
-        <v>940.9754775277175</v>
+        <v>812.7475647186927</v>
       </c>
       <c r="R59" t="n">
-        <v>198.2309836708399</v>
+        <v>150.0000472868369</v>
       </c>
       <c r="S59" t="n">
-        <v>9.000057867129845</v>
+        <v>9.560659868653543</v>
       </c>
       <c r="T59" t="n">
-        <v>85.09143474600239</v>
+        <v>164.2932226007938</v>
       </c>
       <c r="U59" t="n">
-        <v>0.768605951854056</v>
+        <v>18.54656967650456</v>
       </c>
       <c r="V59" t="n">
-        <v>0.8077264525873868</v>
+        <v>0.07936395776555649</v>
       </c>
       <c r="W59" t="b">
         <v>1</v>
@@ -4773,68 +4773,68 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>949.6136339145633</v>
+        <v>913.8591721013637</v>
       </c>
       <c r="D60" t="n">
-        <v>14.47447169815221</v>
+        <v>9.230854720193383</v>
       </c>
       <c r="E60" t="n">
-        <v>186.5458632561667</v>
+        <v>121.510709542018</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8591651916503906</v>
+        <v>0.6958089470863342</v>
       </c>
       <c r="G60" t="n">
-        <v>0.004665159154683352</v>
+        <v>0.02752229943871498</v>
       </c>
       <c r="H60" t="n">
-        <v>949.6136339951472</v>
+        <v>871.1349397250013</v>
       </c>
       <c r="I60" t="n">
-        <v>186.5458632561671</v>
+        <v>176.1525898290093</v>
       </c>
       <c r="J60" t="n">
-        <v>11.77729472118987</v>
+        <v>9.233294125848257</v>
       </c>
       <c r="K60" t="n">
-        <v>8.058395906118676e-08</v>
+        <v>42.72423237636235</v>
       </c>
       <c r="L60" t="n">
-        <v>3.694822225952521e-13</v>
+        <v>54.64188028699132</v>
       </c>
       <c r="M60" t="n">
-        <v>2.697176976962345</v>
+        <v>0.002439405654873994</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>0.9903562080682629</v>
+        <v>0.9996615681809872</v>
       </c>
       <c r="P60" t="n">
-        <v>0.001737594168691558</v>
+        <v>0.001428954415346748</v>
       </c>
       <c r="Q60" t="n">
-        <v>821.4958110267258</v>
+        <v>811.2493626982476</v>
       </c>
       <c r="R60" t="n">
-        <v>188.0076462563096</v>
+        <v>150.0000472865586</v>
       </c>
       <c r="S60" t="n">
-        <v>13.73677527551606</v>
+        <v>9.171148520557409</v>
       </c>
       <c r="T60" t="n">
-        <v>128.1178228878374</v>
+        <v>102.6098094031161</v>
       </c>
       <c r="U60" t="n">
-        <v>1.461783000142901</v>
+        <v>28.48933774454056</v>
       </c>
       <c r="V60" t="n">
-        <v>0.7376964226361498</v>
+        <v>0.05970619963597379</v>
       </c>
       <c r="W60" t="b">
         <v>1</v>
@@ -4846,68 +4846,68 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>956.1480713943938</v>
+        <v>918.9392944432036</v>
       </c>
       <c r="D61" t="n">
-        <v>10.47729600880942</v>
+        <v>8.76813131186692</v>
       </c>
       <c r="E61" t="n">
-        <v>234.7411873193184</v>
+        <v>144.1376341282934</v>
       </c>
       <c r="F61" t="n">
-        <v>0.735504686832428</v>
+        <v>0.7776037454605103</v>
       </c>
       <c r="G61" t="n">
-        <v>0.6677823066711426</v>
+        <v>0.01262497249990702</v>
       </c>
       <c r="H61" t="n">
-        <v>956.2629680640516</v>
+        <v>910.503704730356</v>
       </c>
       <c r="I61" t="n">
-        <v>238.5692351026376</v>
+        <v>176.15396903449</v>
       </c>
       <c r="J61" t="n">
-        <v>10.25232714647424</v>
+        <v>9.000107894621815</v>
       </c>
       <c r="K61" t="n">
-        <v>0.11489666965781</v>
+        <v>8.435589712847559</v>
       </c>
       <c r="L61" t="n">
-        <v>3.828047783319192</v>
+        <v>32.01633490619662</v>
       </c>
       <c r="M61" t="n">
-        <v>0.2249688623351798</v>
+        <v>0.2319765827548945</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>0.676259209640181</v>
+        <v>0.9899008807706283</v>
       </c>
       <c r="P61" t="n">
-        <v>0.001161497825082428</v>
+        <v>0.001451701790644071</v>
       </c>
       <c r="Q61" t="n">
-        <v>860.1313150301785</v>
+        <v>812.432047238053</v>
       </c>
       <c r="R61" t="n">
-        <v>219.740945322078</v>
+        <v>150.0000472904324</v>
       </c>
       <c r="S61" t="n">
-        <v>10.48328932262805</v>
+        <v>9.000057869488069</v>
       </c>
       <c r="T61" t="n">
-        <v>96.01675636421533</v>
+        <v>106.5072472051506</v>
       </c>
       <c r="U61" t="n">
-        <v>15.00024199724038</v>
+        <v>5.862413162138978</v>
       </c>
       <c r="V61" t="n">
-        <v>0.005993313818624557</v>
+        <v>0.2319265576211489</v>
       </c>
       <c r="W61" t="b">
         <v>1</v>
@@ -4919,68 +4919,68 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Dirtiness</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>905.1906120174584</v>
+        <v>948.511331417999</v>
       </c>
       <c r="D62" t="n">
-        <v>7.56428685873548</v>
+        <v>10.38994559938344</v>
       </c>
       <c r="E62" t="n">
-        <v>197.4911582041763</v>
+        <v>271.9097831786312</v>
       </c>
       <c r="F62" t="n">
-        <v>0.5604537129402161</v>
+        <v>0.6614874005317688</v>
       </c>
       <c r="G62" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.006804721895605326</v>
       </c>
       <c r="H62" t="n">
-        <v>928.8432674637658</v>
+        <v>948.5113314184365</v>
       </c>
       <c r="I62" t="n">
-        <v>197.4911582041763</v>
+        <v>224.7375904915977</v>
       </c>
       <c r="J62" t="n">
-        <v>9.000057868674507</v>
+        <v>10.38994559938028</v>
       </c>
       <c r="K62" t="n">
-        <v>23.65265544630734</v>
+        <v>4.374669515527785e-10</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>47.17219268703349</v>
       </c>
       <c r="M62" t="n">
-        <v>1.435771009939026</v>
+        <v>3.154809746774845e-12</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>0.6046072520782534</v>
+        <v>0.9998599522950143</v>
       </c>
       <c r="P62" t="n">
-        <v>0.0003777425144149139</v>
+        <v>0.001961491137519355</v>
       </c>
       <c r="Q62" t="n">
-        <v>946.5720916233867</v>
+        <v>808.9166275780772</v>
       </c>
       <c r="R62" t="n">
-        <v>197.187884947419</v>
+        <v>242.0389090756035</v>
       </c>
       <c r="S62" t="n">
-        <v>9.000057868865936</v>
+        <v>10.39113440725969</v>
       </c>
       <c r="T62" t="n">
-        <v>41.38147960592823</v>
+        <v>139.5947038399219</v>
       </c>
       <c r="U62" t="n">
-        <v>0.3032732567573078</v>
+        <v>29.87087410302772</v>
       </c>
       <c r="V62" t="n">
-        <v>1.435771010130455</v>
+        <v>0.001188807876255638</v>
       </c>
       <c r="W62" t="b">
         <v>1</v>
@@ -4996,64 +4996,64 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>936.4333074132901</v>
+        <v>978.5461072857843</v>
       </c>
       <c r="D63" t="n">
-        <v>10.13074385901825</v>
+        <v>9.270427066779609</v>
       </c>
       <c r="E63" t="n">
-        <v>238.143767332355</v>
+        <v>288.9239529281692</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7452751994132996</v>
+        <v>0.6535143256187439</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003133095800876617</v>
+        <v>0.006656103301793337</v>
       </c>
       <c r="H63" t="n">
-        <v>936.4333074218969</v>
+        <v>978.5458854275453</v>
       </c>
       <c r="I63" t="n">
-        <v>222.3568452444926</v>
+        <v>224.737590480615</v>
       </c>
       <c r="J63" t="n">
-        <v>10.13074385911359</v>
+        <v>9.270427066779755</v>
       </c>
       <c r="K63" t="n">
-        <v>8.606775736552663e-09</v>
+        <v>0.000221858239001449</v>
       </c>
       <c r="L63" t="n">
-        <v>15.78692208786242</v>
+        <v>64.18636244755416</v>
       </c>
       <c r="M63" t="n">
-        <v>9.533884792745084e-11</v>
+        <v>1.456612608308205e-13</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0.8507400829563879</v>
+        <v>0.9999668975172847</v>
       </c>
       <c r="P63" t="n">
-        <v>0.001111625569653826</v>
+        <v>0.00289448256149877</v>
       </c>
       <c r="Q63" t="n">
-        <v>849.5355032540671</v>
+        <v>963.6116928119862</v>
       </c>
       <c r="R63" t="n">
-        <v>223.6864463042877</v>
+        <v>213.4223213521694</v>
       </c>
       <c r="S63" t="n">
-        <v>10.12025959005423</v>
+        <v>9.299901877687281</v>
       </c>
       <c r="T63" t="n">
-        <v>86.89780415922303</v>
+        <v>14.93441447379803</v>
       </c>
       <c r="U63" t="n">
-        <v>14.4573210280673</v>
+        <v>75.50163157599977</v>
       </c>
       <c r="V63" t="n">
-        <v>0.01048426896401722</v>
+        <v>0.02947481090767212</v>
       </c>
       <c r="W63" t="b">
         <v>1</v>
@@ -5065,68 +5065,68 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>926.6016632857942</v>
+        <v>948.7421226620029</v>
       </c>
       <c r="D64" t="n">
-        <v>14.8366109436522</v>
+        <v>10.20178510737095</v>
       </c>
       <c r="E64" t="n">
-        <v>205.0478136091507</v>
+        <v>149.931318772952</v>
       </c>
       <c r="F64" t="n">
-        <v>0.8587579727172852</v>
+        <v>0.7905983924865723</v>
       </c>
       <c r="G64" t="n">
-        <v>0.004661593120545149</v>
+        <v>0.01447403151541948</v>
       </c>
       <c r="H64" t="n">
-        <v>926.6016633016582</v>
+        <v>948.7421226589198</v>
       </c>
       <c r="I64" t="n">
-        <v>205.0478136091507</v>
+        <v>176.1525536296017</v>
       </c>
       <c r="J64" t="n">
-        <v>11.77729472279498</v>
+        <v>10.20178510750526</v>
       </c>
       <c r="K64" t="n">
-        <v>1.586397502251202e-08</v>
+        <v>3.083073352172505e-09</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>26.22123485664969</v>
       </c>
       <c r="M64" t="n">
-        <v>3.05931622085722</v>
+        <v>1.343067879133741e-10</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>0.994159039427843</v>
+        <v>0.9899826675466773</v>
       </c>
       <c r="P64" t="n">
-        <v>0.001748581905013277</v>
+        <v>0.001596905751454016</v>
       </c>
       <c r="Q64" t="n">
-        <v>815.2810671527558</v>
+        <v>820.4822393528982</v>
       </c>
       <c r="R64" t="n">
-        <v>205.3724066480493</v>
+        <v>156.3679026058684</v>
       </c>
       <c r="S64" t="n">
-        <v>14.10779377789854</v>
+        <v>10.14008394380013</v>
       </c>
       <c r="T64" t="n">
-        <v>111.3205961330384</v>
+        <v>128.2598833091047</v>
       </c>
       <c r="U64" t="n">
-        <v>0.3245930388985698</v>
+        <v>6.436583832916426</v>
       </c>
       <c r="V64" t="n">
-        <v>0.7288171657536555</v>
+        <v>0.06170116357082556</v>
       </c>
       <c r="W64" t="b">
         <v>1</v>
@@ -5138,68 +5138,68 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>878.2026739000856</v>
+        <v>959.5408165444625</v>
       </c>
       <c r="D65" t="n">
-        <v>6.944129728917112</v>
+        <v>4.920585130854247</v>
       </c>
       <c r="E65" t="n">
-        <v>202.3609729421508</v>
+        <v>224.2255557459594</v>
       </c>
       <c r="F65" t="n">
-        <v>0.884280264377594</v>
+        <v>0.6944717168807983</v>
       </c>
       <c r="G65" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.005241473205387592</v>
       </c>
       <c r="H65" t="n">
-        <v>928.8432674745022</v>
+        <v>959.5408165444643</v>
       </c>
       <c r="I65" t="n">
-        <v>202.3609729421508</v>
+        <v>224.7375904987678</v>
       </c>
       <c r="J65" t="n">
-        <v>9.000057868677425</v>
+        <v>9.000057867608652</v>
       </c>
       <c r="K65" t="n">
-        <v>50.64059357441658</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>0.5120347528083471</v>
       </c>
       <c r="M65" t="n">
-        <v>2.055928139760313</v>
+        <v>4.079472736754404</v>
       </c>
       <c r="N65" t="b">
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>0.964330485769023</v>
+        <v>0.9923315399961953</v>
       </c>
       <c r="P65" t="n">
-        <v>0.0006228643099622639</v>
+        <v>0.001122361159079843</v>
       </c>
       <c r="Q65" t="n">
-        <v>943.7319337235346</v>
+        <v>880.7002980573727</v>
       </c>
       <c r="R65" t="n">
-        <v>201.5310900930351</v>
+        <v>221.5548368377026</v>
       </c>
       <c r="S65" t="n">
-        <v>9.000057865901521</v>
+        <v>9.000057869254071</v>
       </c>
       <c r="T65" t="n">
-        <v>65.52925982344891</v>
+        <v>78.84051848708975</v>
       </c>
       <c r="U65" t="n">
-        <v>0.82988284911562</v>
+        <v>2.670718908256816</v>
       </c>
       <c r="V65" t="n">
-        <v>2.055928136984409</v>
+        <v>4.079472738399824</v>
       </c>
       <c r="W65" t="b">
         <v>1</v>
@@ -5211,68 +5211,68 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Dirtiness</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1019.087392367041</v>
+        <v>956.1226910620551</v>
       </c>
       <c r="D66" t="n">
-        <v>10.45740074279174</v>
+        <v>7.782716289746432</v>
       </c>
       <c r="E66" t="n">
-        <v>221.331260765201</v>
+        <v>277.6453165735577</v>
       </c>
       <c r="F66" t="n">
-        <v>0.770132839679718</v>
+        <v>0.6554653644561768</v>
       </c>
       <c r="G66" t="n">
-        <v>0.004426439292728901</v>
+        <v>0.006804721895605326</v>
       </c>
       <c r="H66" t="n">
-        <v>965.6040331720995</v>
+        <v>956.1226910698024</v>
       </c>
       <c r="I66" t="n">
-        <v>221.2331857893307</v>
+        <v>224.7375904723221</v>
       </c>
       <c r="J66" t="n">
-        <v>10.45740074279174</v>
+        <v>9.000057869254062</v>
       </c>
       <c r="K66" t="n">
-        <v>53.48335919494116</v>
+        <v>7.747303243377246e-09</v>
       </c>
       <c r="L66" t="n">
-        <v>0.09807497587036096</v>
+        <v>52.90772610123557</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>1.217341579507631</v>
       </c>
       <c r="N66" t="b">
         <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>0.9293832482187542</v>
+        <v>0.9996612454450711</v>
       </c>
       <c r="P66" t="n">
-        <v>0.0004641502011800133</v>
+        <v>0.00203315826163045</v>
       </c>
       <c r="Q66" t="n">
-        <v>949.8397876665732</v>
+        <v>806.242058205123</v>
       </c>
       <c r="R66" t="n">
-        <v>220.0032747323285</v>
+        <v>245.2617231039781</v>
       </c>
       <c r="S66" t="n">
-        <v>10.44275030799048</v>
+        <v>9.000057863069008</v>
       </c>
       <c r="T66" t="n">
-        <v>69.24760470046749</v>
+        <v>149.880632856932</v>
       </c>
       <c r="U66" t="n">
-        <v>1.327986032872559</v>
+        <v>32.38359346957964</v>
       </c>
       <c r="V66" t="n">
-        <v>0.0146504348012666</v>
+        <v>1.217341573322576</v>
       </c>
       <c r="W66" t="b">
         <v>1</v>
@@ -5288,64 +5288,64 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>872.951276388834</v>
+        <v>866.4777495445426</v>
       </c>
       <c r="D67" t="n">
-        <v>6.647864709753142</v>
+        <v>8.500222946410677</v>
       </c>
       <c r="E67" t="n">
-        <v>226.429104826243</v>
+        <v>196.1930257438338</v>
       </c>
       <c r="F67" t="n">
-        <v>0.8396716713905334</v>
+        <v>0.6621172428131104</v>
       </c>
       <c r="G67" t="n">
-        <v>0.002856495557352901</v>
+        <v>0.0107807656750083</v>
       </c>
       <c r="H67" t="n">
-        <v>928.8439474225394</v>
+        <v>928.8432674911214</v>
       </c>
       <c r="I67" t="n">
-        <v>231.3668592702861</v>
+        <v>196.1930257438338</v>
       </c>
       <c r="J67" t="n">
-        <v>9.0000578688262</v>
+        <v>9.00005786849632</v>
       </c>
       <c r="K67" t="n">
-        <v>55.89267103370537</v>
+        <v>62.36551794657885</v>
       </c>
       <c r="L67" t="n">
-        <v>4.937754444043094</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>2.352193159073058</v>
+        <v>0.4998349220856433</v>
       </c>
       <c r="N67" t="b">
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>0.9699037175754671</v>
+        <v>0.7881563935561191</v>
       </c>
       <c r="P67" t="n">
-        <v>0.0008896991599113631</v>
+        <v>0.0007201746865634971</v>
       </c>
       <c r="Q67" t="n">
-        <v>950.9732542094079</v>
+        <v>941.6446782573946</v>
       </c>
       <c r="R67" t="n">
-        <v>223.616543468521</v>
+        <v>195.7259787528989</v>
       </c>
       <c r="S67" t="n">
-        <v>9.000057788147537</v>
+        <v>9.000057869728865</v>
       </c>
       <c r="T67" t="n">
-        <v>78.02197782057385</v>
+        <v>75.16692871285204</v>
       </c>
       <c r="U67" t="n">
-        <v>2.812561357722046</v>
+        <v>0.4670469909348469</v>
       </c>
       <c r="V67" t="n">
-        <v>2.352193078394395</v>
+        <v>0.499834923318188</v>
       </c>
       <c r="W67" t="b">
         <v>1</v>
@@ -5357,68 +5357,68 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>928.4852670311677</v>
+        <v>1015.52584876243</v>
       </c>
       <c r="D68" t="n">
-        <v>9.994669426673875</v>
+        <v>8.112137762777651</v>
       </c>
       <c r="E68" t="n">
-        <v>139.84012418203</v>
+        <v>184.3591981108835</v>
       </c>
       <c r="F68" t="n">
-        <v>0.8965997695922852</v>
+        <v>0.5826367139816284</v>
       </c>
       <c r="G68" t="n">
-        <v>0.05808445438742638</v>
+        <v>0.007977633737027645</v>
       </c>
       <c r="H68" t="n">
-        <v>913.4548990979315</v>
+        <v>965.6040331503077</v>
       </c>
       <c r="I68" t="n">
-        <v>171.224862151858</v>
+        <v>184.3591981108835</v>
       </c>
       <c r="J68" t="n">
-        <v>13.58226972539386</v>
+        <v>9.000057867769048</v>
       </c>
       <c r="K68" t="n">
-        <v>15.03036793323622</v>
+        <v>49.92181561212215</v>
       </c>
       <c r="L68" t="n">
-        <v>31.384737969828</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.587600298719984</v>
+        <v>0.8879201049913963</v>
       </c>
       <c r="N68" t="b">
         <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>0.9975355363478511</v>
+        <v>0.6981251195672556</v>
       </c>
       <c r="P68" t="n">
-        <v>0.00163130432745098</v>
+        <v>0.0004219042398538178</v>
       </c>
       <c r="Q68" t="n">
-        <v>808.9165571241892</v>
+        <v>953.8229193647451</v>
       </c>
       <c r="R68" t="n">
-        <v>150.0000472879381</v>
+        <v>184.736719654626</v>
       </c>
       <c r="S68" t="n">
-        <v>9.930947474571092</v>
+        <v>9.000057868610762</v>
       </c>
       <c r="T68" t="n">
-        <v>119.5687099069785</v>
+        <v>61.70292939768478</v>
       </c>
       <c r="U68" t="n">
-        <v>10.15992310590804</v>
+        <v>0.3775215437425175</v>
       </c>
       <c r="V68" t="n">
-        <v>0.06372195210278342</v>
+        <v>0.8879201058331105</v>
       </c>
       <c r="W68" t="b">
         <v>1</v>
@@ -5430,68 +5430,68 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>949.2834884258707</v>
+        <v>927.8859066302813</v>
       </c>
       <c r="D69" t="n">
-        <v>6.488632830092022</v>
+        <v>17.64577591489981</v>
       </c>
       <c r="E69" t="n">
-        <v>205.1426559241486</v>
+        <v>203.6229680364656</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8445577621459961</v>
+        <v>0.7228195667266846</v>
       </c>
       <c r="G69" t="n">
-        <v>0.00305266329087317</v>
+        <v>0.01293464377522469</v>
       </c>
       <c r="H69" t="n">
-        <v>949.2834884258696</v>
+        <v>916.576561518555</v>
       </c>
       <c r="I69" t="n">
-        <v>205.1426559241485</v>
+        <v>203.6229680364666</v>
       </c>
       <c r="J69" t="n">
-        <v>9.000057869254071</v>
+        <v>11.97988253465197</v>
       </c>
       <c r="K69" t="n">
-        <v>1.13686837721616e-12</v>
+        <v>11.30934511172632</v>
       </c>
       <c r="L69" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>1.023181539494544e-12</v>
       </c>
       <c r="M69" t="n">
-        <v>2.51142503916205</v>
+        <v>5.665893380247834</v>
       </c>
       <c r="N69" t="b">
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>0.7826959113381116</v>
+        <v>0.9999571352671371</v>
       </c>
       <c r="P69" t="n">
-        <v>0.00129747453087709</v>
+        <v>0.00302150296796179</v>
       </c>
       <c r="Q69" t="n">
-        <v>945.3278715151563</v>
+        <v>800.0000004972368</v>
       </c>
       <c r="R69" t="n">
-        <v>202.8051406401836</v>
+        <v>204.4349670969896</v>
       </c>
       <c r="S69" t="n">
-        <v>9.000057869254071</v>
+        <v>14.99994212734213</v>
       </c>
       <c r="T69" t="n">
-        <v>3.955616910714411</v>
+        <v>127.8859061330445</v>
       </c>
       <c r="U69" t="n">
-        <v>2.337515283965018</v>
+        <v>0.811999060524073</v>
       </c>
       <c r="V69" t="n">
-        <v>2.51142503916205</v>
+        <v>2.645833787557677</v>
       </c>
       <c r="W69" t="b">
         <v>1</v>
@@ -5503,68 +5503,68 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>947.7088114505497</v>
+        <v>957.8376252449117</v>
       </c>
       <c r="D70" t="n">
-        <v>15.04330896333172</v>
+        <v>4.773685431185793</v>
       </c>
       <c r="E70" t="n">
-        <v>203.2822033198099</v>
+        <v>214.2996118678968</v>
       </c>
       <c r="F70" t="n">
-        <v>0.8591651916503906</v>
+        <v>0.6949941515922546</v>
       </c>
       <c r="G70" t="n">
-        <v>0.004665159154683352</v>
+        <v>0.005485068075358868</v>
       </c>
       <c r="H70" t="n">
-        <v>947.7088114642545</v>
+        <v>957.8376252449157</v>
       </c>
       <c r="I70" t="n">
-        <v>203.2822033196692</v>
+        <v>214.2996118678969</v>
       </c>
       <c r="J70" t="n">
-        <v>11.77729472124748</v>
+        <v>9.000057869254071</v>
       </c>
       <c r="K70" t="n">
-        <v>1.370483460050309e-08</v>
+        <v>3.979039320256561e-12</v>
       </c>
       <c r="L70" t="n">
-        <v>1.406590399710694e-10</v>
+        <v>1.70530256582424e-13</v>
       </c>
       <c r="M70" t="n">
-        <v>3.266014242084241</v>
+        <v>4.226372438068278</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>0.9973670931728997</v>
+        <v>0.9943567243610213</v>
       </c>
       <c r="P70" t="n">
-        <v>0.001978279186394049</v>
+        <v>0.001836897731187797</v>
       </c>
       <c r="Q70" t="n">
-        <v>814.6753526656346</v>
+        <v>948.252364805199</v>
       </c>
       <c r="R70" t="n">
-        <v>203.8010938176184</v>
+        <v>209.409893383728</v>
       </c>
       <c r="S70" t="n">
-        <v>14.1921751958092</v>
+        <v>9.000057869254071</v>
       </c>
       <c r="T70" t="n">
-        <v>133.0334587849151</v>
+        <v>9.58526043971267</v>
       </c>
       <c r="U70" t="n">
-        <v>0.5188904978085702</v>
+        <v>4.88971848416881</v>
       </c>
       <c r="V70" t="n">
-        <v>0.8511337675225228</v>
+        <v>4.226372438068278</v>
       </c>
       <c r="W70" t="b">
         <v>1</v>
@@ -5576,68 +5576,68 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>945.4280016931996</v>
+        <v>833.9256956383012</v>
       </c>
       <c r="D71" t="n">
-        <v>10.16969315797128</v>
+        <v>8.289100872085879</v>
       </c>
       <c r="E71" t="n">
-        <v>123.6167408783263</v>
+        <v>188.1754205275467</v>
       </c>
       <c r="F71" t="n">
-        <v>0.898436963558197</v>
+        <v>0.6337262392044067</v>
       </c>
       <c r="G71" t="n">
-        <v>0.009224903769791126</v>
+        <v>0.0107807656750083</v>
       </c>
       <c r="H71" t="n">
-        <v>945.4280017285848</v>
+        <v>928.8432674797829</v>
       </c>
       <c r="I71" t="n">
-        <v>176.1525536340899</v>
+        <v>188.1754205275467</v>
       </c>
       <c r="J71" t="n">
-        <v>10.16969315653008</v>
+        <v>9.000057867156455</v>
       </c>
       <c r="K71" t="n">
-        <v>3.538525561452843e-08</v>
+        <v>94.91757184148162</v>
       </c>
       <c r="L71" t="n">
-        <v>52.53581275576369</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>1.441202712726408e-09</v>
+        <v>0.7109569950705765</v>
       </c>
       <c r="N71" t="b">
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>0.9998597096722134</v>
+        <v>0.788050207572062</v>
       </c>
       <c r="P71" t="n">
-        <v>0.001780382639228377</v>
+        <v>0.00107619670292462</v>
       </c>
       <c r="Q71" t="n">
-        <v>809.1792368572565</v>
+        <v>938.3277722701279</v>
       </c>
       <c r="R71" t="n">
-        <v>150.0000472872834</v>
+        <v>188.157550104991</v>
       </c>
       <c r="S71" t="n">
-        <v>10.10016308556093</v>
+        <v>9.000057869318903</v>
       </c>
       <c r="T71" t="n">
-        <v>136.2487648359431</v>
+        <v>104.4020766318266</v>
       </c>
       <c r="U71" t="n">
-        <v>26.38330640895711</v>
+        <v>0.01787042255563165</v>
       </c>
       <c r="V71" t="n">
-        <v>0.06953007241035358</v>
+        <v>0.7109569972330245</v>
       </c>
       <c r="W71" t="b">
         <v>1</v>
@@ -5649,68 +5649,68 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1008.363471101202</v>
+        <v>932.9300903987731</v>
       </c>
       <c r="D72" t="n">
-        <v>10.89307743456569</v>
+        <v>14.58085842659227</v>
       </c>
       <c r="E72" t="n">
-        <v>194.4090542789506</v>
+        <v>221.2210945723355</v>
       </c>
       <c r="F72" t="n">
-        <v>0.51530921459198</v>
+        <v>0.7234267592430115</v>
       </c>
       <c r="G72" t="n">
-        <v>0.004426439292728901</v>
+        <v>0.007928796112537384</v>
       </c>
       <c r="H72" t="n">
-        <v>965.6040331629179</v>
+        <v>932.9301221148419</v>
       </c>
       <c r="I72" t="n">
-        <v>194.4090542789506</v>
+        <v>224.7375904988753</v>
       </c>
       <c r="J72" t="n">
-        <v>10.89307743456569</v>
+        <v>11.77716114675325</v>
       </c>
       <c r="K72" t="n">
-        <v>42.75943793828401</v>
+        <v>3.17160687473006e-05</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>3.516495926539847</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>2.803697279839023</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
       </c>
       <c r="O72" t="n">
-        <v>0.7004579829434877</v>
+        <v>0.9863341127292515</v>
       </c>
       <c r="P72" t="n">
-        <v>0.0003538563279151808</v>
+        <v>0.001800858667026563</v>
       </c>
       <c r="Q72" t="n">
-        <v>952.6418704766083</v>
+        <v>820.7373439814994</v>
       </c>
       <c r="R72" t="n">
-        <v>194.4499066696577</v>
+        <v>220.4437630328117</v>
       </c>
       <c r="S72" t="n">
-        <v>10.87414254924984</v>
+        <v>13.88949516356204</v>
       </c>
       <c r="T72" t="n">
-        <v>55.72160062459352</v>
+        <v>112.1927464172737</v>
       </c>
       <c r="U72" t="n">
-        <v>0.04085239070710145</v>
+        <v>0.7773315395238285</v>
       </c>
       <c r="V72" t="n">
-        <v>0.01893488531585064</v>
+        <v>0.6913632630302331</v>
       </c>
       <c r="W72" t="b">
         <v>1</v>
@@ -5722,68 +5722,68 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>939.634595634527</v>
+        <v>949.6175564029259</v>
       </c>
       <c r="D73" t="n">
-        <v>6.011481972499717</v>
+        <v>9.917669449982794</v>
       </c>
       <c r="E73" t="n">
-        <v>211.927690016471</v>
+        <v>144.5779808580052</v>
       </c>
       <c r="F73" t="n">
-        <v>0.8447094559669495</v>
+        <v>0.7905983924865723</v>
       </c>
       <c r="G73" t="n">
-        <v>0.00305266329087317</v>
+        <v>0.06394846737384796</v>
       </c>
       <c r="H73" t="n">
-        <v>939.6345956346626</v>
+        <v>963.6246559823973</v>
       </c>
       <c r="I73" t="n">
-        <v>211.9276900164707</v>
+        <v>175.7990059882059</v>
       </c>
       <c r="J73" t="n">
-        <v>9.000057869254071</v>
+        <v>9.963551746923205</v>
       </c>
       <c r="K73" t="n">
-        <v>1.355147105641663e-10</v>
+        <v>14.0070995794714</v>
       </c>
       <c r="L73" t="n">
-        <v>2.557953848736361e-13</v>
+        <v>31.22102513020076</v>
       </c>
       <c r="M73" t="n">
-        <v>2.988575896754354</v>
+        <v>0.04588229694041068</v>
       </c>
       <c r="N73" t="b">
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>0.9217876973475667</v>
+        <v>0.996459173492649</v>
       </c>
       <c r="P73" t="n">
-        <v>0.001655599113606738</v>
+        <v>0.001762343385386861</v>
       </c>
       <c r="Q73" t="n">
-        <v>940.5689860030224</v>
+        <v>811.721593985368</v>
       </c>
       <c r="R73" t="n">
-        <v>207.9129092736274</v>
+        <v>150.7709461458721</v>
       </c>
       <c r="S73" t="n">
-        <v>9.000057829742349</v>
+        <v>9.849555942680613</v>
       </c>
       <c r="T73" t="n">
-        <v>0.9343903684953148</v>
+        <v>137.8959624175578</v>
       </c>
       <c r="U73" t="n">
-        <v>4.014780742843556</v>
+        <v>6.19296528786694</v>
       </c>
       <c r="V73" t="n">
-        <v>2.988575857242632</v>
+        <v>0.06811350730218102</v>
       </c>
       <c r="W73" t="b">
         <v>1</v>
@@ -5799,64 +5799,64 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>866.4777495445426</v>
+        <v>901.0507251457127</v>
       </c>
       <c r="D74" t="n">
-        <v>8.500222946410677</v>
+        <v>8.594140314134535</v>
       </c>
       <c r="E74" t="n">
-        <v>196.1930257438338</v>
+        <v>204.0188466312755</v>
       </c>
       <c r="F74" t="n">
-        <v>0.7496830821037292</v>
+        <v>0.5476883053779602</v>
       </c>
       <c r="G74" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.0107807656750083</v>
       </c>
       <c r="H74" t="n">
-        <v>928.8432674742278</v>
+        <v>928.843267476436</v>
       </c>
       <c r="I74" t="n">
-        <v>196.1930257438338</v>
+        <v>204.0188466312755</v>
       </c>
       <c r="J74" t="n">
-        <v>9.000057868496304</v>
+        <v>9.000057868418905</v>
       </c>
       <c r="K74" t="n">
-        <v>62.36551792968521</v>
+        <v>27.79254233072334</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>0.4998349220856273</v>
+        <v>0.40591755428437</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0.7881563935561191</v>
+        <v>0.3679098579149766</v>
       </c>
       <c r="P74" t="n">
-        <v>0.0007201746865634971</v>
+        <v>0.0004274206376175458</v>
       </c>
       <c r="Q74" t="n">
-        <v>941.6446782573946</v>
+        <v>947.007585339293</v>
       </c>
       <c r="R74" t="n">
-        <v>195.7259787528989</v>
+        <v>203.3353542261918</v>
       </c>
       <c r="S74" t="n">
-        <v>9.000057869728865</v>
+        <v>9.000057864342002</v>
       </c>
       <c r="T74" t="n">
-        <v>75.16692871285204</v>
+        <v>45.95686019358027</v>
       </c>
       <c r="U74" t="n">
-        <v>0.4670469909348469</v>
+        <v>0.6834924050836833</v>
       </c>
       <c r="V74" t="n">
-        <v>0.499834923318188</v>
+        <v>0.4059175502074677</v>
       </c>
       <c r="W74" t="b">
         <v>1</v>
@@ -5868,68 +5868,68 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>976.3519507121592</v>
+        <v>989.0621439654515</v>
       </c>
       <c r="D75" t="n">
-        <v>11.0925378336083</v>
+        <v>15.52164038629858</v>
       </c>
       <c r="E75" t="n">
-        <v>153.1915328858273</v>
+        <v>211.9652678668288</v>
       </c>
       <c r="F75" t="n">
-        <v>0.8849048018455505</v>
+        <v>0.6981363892555237</v>
       </c>
       <c r="G75" t="n">
-        <v>0.009224903769791126</v>
+        <v>0.007554174400866032</v>
       </c>
       <c r="H75" t="n">
-        <v>959.1994328805602</v>
+        <v>991.5080415387845</v>
       </c>
       <c r="I75" t="n">
-        <v>176.1531872957831</v>
+        <v>211.9652678668273</v>
       </c>
       <c r="J75" t="n">
-        <v>11.09253742559404</v>
+        <v>11.77729472229702</v>
       </c>
       <c r="K75" t="n">
-        <v>17.15251783159908</v>
+        <v>2.445897573333013</v>
       </c>
       <c r="L75" t="n">
-        <v>22.96165440995574</v>
+        <v>1.534772309241816e-12</v>
       </c>
       <c r="M75" t="n">
-        <v>4.080142605999981e-07</v>
+        <v>3.744345664001555</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>0.9860155183520621</v>
+        <v>0.9982928998632259</v>
       </c>
       <c r="P75" t="n">
-        <v>0.001709713397138161</v>
+        <v>0.002499602621814765</v>
       </c>
       <c r="Q75" t="n">
-        <v>826.8429546106154</v>
+        <v>812.3518565656884</v>
       </c>
       <c r="R75" t="n">
-        <v>160.76774668764</v>
+        <v>211.9612790027144</v>
       </c>
       <c r="S75" t="n">
-        <v>11.02474024133094</v>
+        <v>14.42256403795143</v>
       </c>
       <c r="T75" t="n">
-        <v>149.5089961015439</v>
+        <v>176.710287399763</v>
       </c>
       <c r="U75" t="n">
-        <v>7.576213801812656</v>
+        <v>0.003988864114432999</v>
       </c>
       <c r="V75" t="n">
-        <v>0.06779759227736726</v>
+        <v>1.099076348347147</v>
       </c>
       <c r="W75" t="b">
         <v>1</v>
@@ -5941,68 +5941,68 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Stains</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>868.5815029465992</v>
+        <v>853.8620208630202</v>
       </c>
       <c r="D76" t="n">
-        <v>7.635551753367551</v>
+        <v>11.02488643276593</v>
       </c>
       <c r="E76" t="n">
-        <v>220.2487860932945</v>
+        <v>195.7072577712682</v>
       </c>
       <c r="F76" t="n">
-        <v>0.9011951088905334</v>
+        <v>0.5955662727355957</v>
       </c>
       <c r="G76" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.005909173749387264</v>
       </c>
       <c r="H76" t="n">
-        <v>928.8432674767054</v>
+        <v>922.9741913974954</v>
       </c>
       <c r="I76" t="n">
-        <v>220.2487860932943</v>
+        <v>195.7072577712682</v>
       </c>
       <c r="J76" t="n">
-        <v>9.000057868760697</v>
+        <v>11.02488643276593</v>
       </c>
       <c r="K76" t="n">
-        <v>60.26176453010612</v>
+        <v>69.11217053447513</v>
       </c>
       <c r="L76" t="n">
-        <v>1.4210854715202e-13</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>1.364506115393146</v>
+        <v>0</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>0.9468243835735063</v>
+        <v>0.9116697077839033</v>
       </c>
       <c r="P76" t="n">
-        <v>0.0008519538770306365</v>
+        <v>0.0007905151706244139</v>
       </c>
       <c r="Q76" t="n">
-        <v>947.7890870890958</v>
+        <v>937.1240040995773</v>
       </c>
       <c r="R76" t="n">
-        <v>217.4468672639432</v>
+        <v>195.5592389153184</v>
       </c>
       <c r="S76" t="n">
-        <v>9.000057765192453</v>
+        <v>10.95898308319927</v>
       </c>
       <c r="T76" t="n">
-        <v>79.20758414249656</v>
+        <v>83.26198323655706</v>
       </c>
       <c r="U76" t="n">
-        <v>2.801918829351223</v>
+        <v>0.1480188559498288</v>
       </c>
       <c r="V76" t="n">
-        <v>1.364506011824902</v>
+        <v>0.06590334956665878</v>
       </c>
       <c r="W76" t="b">
         <v>1</v>
@@ -6018,64 +6018,64 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>962.9439187940549</v>
+        <v>956.481679387896</v>
       </c>
       <c r="D77" t="n">
-        <v>10.99056682744279</v>
+        <v>8.228103317753556</v>
       </c>
       <c r="E77" t="n">
-        <v>133.1457093690507</v>
+        <v>129.7853208763004</v>
       </c>
       <c r="F77" t="n">
-        <v>0.898436963558197</v>
+        <v>0.7905983924865723</v>
       </c>
       <c r="G77" t="n">
-        <v>0.009224903769791126</v>
+        <v>0.01447403151541948</v>
       </c>
       <c r="H77" t="n">
-        <v>959.1994418563565</v>
+        <v>956.4867033702712</v>
       </c>
       <c r="I77" t="n">
-        <v>176.1530046699244</v>
+        <v>176.1526712278782</v>
       </c>
       <c r="J77" t="n">
-        <v>10.99066324780564</v>
+        <v>9.000000000342993</v>
       </c>
       <c r="K77" t="n">
-        <v>3.744476937698323</v>
+        <v>0.00502398237529178</v>
       </c>
       <c r="L77" t="n">
-        <v>43.00729530087369</v>
+        <v>46.36735035157781</v>
       </c>
       <c r="M77" t="n">
-        <v>9.642036285306688e-05</v>
+        <v>0.7718966825894373</v>
       </c>
       <c r="N77" t="b">
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0.9996521210001176</v>
+        <v>0.9995228290527134</v>
       </c>
       <c r="P77" t="n">
-        <v>0.001973901120047933</v>
+        <v>0.001743116500829386</v>
       </c>
       <c r="Q77" t="n">
-        <v>807.0116829925142</v>
+        <v>814.511952807126</v>
       </c>
       <c r="R77" t="n">
-        <v>150.0000472873784</v>
+        <v>150.0000472901694</v>
       </c>
       <c r="S77" t="n">
-        <v>10.9086816394455</v>
+        <v>9.000057869166337</v>
       </c>
       <c r="T77" t="n">
-        <v>155.9322358015406</v>
+        <v>141.9697265807699</v>
       </c>
       <c r="U77" t="n">
-        <v>16.85433791832767</v>
+        <v>20.21472641386902</v>
       </c>
       <c r="V77" t="n">
-        <v>0.08188518799728506</v>
+        <v>0.7719545514127812</v>
       </c>
       <c r="W77" t="b">
         <v>1</v>
@@ -6087,68 +6087,68 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>944.6222261889034</v>
+        <v>977.1837898832805</v>
       </c>
       <c r="D78" t="n">
-        <v>9.61241910874443</v>
+        <v>16.1801220378143</v>
       </c>
       <c r="E78" t="n">
-        <v>263.0470290970871</v>
+        <v>182.7243896236366</v>
       </c>
       <c r="F78" t="n">
-        <v>0.8176361322402954</v>
+        <v>0.7118963003158569</v>
       </c>
       <c r="G78" t="n">
-        <v>0.003891526954248548</v>
+        <v>0.008424116298556328</v>
       </c>
       <c r="H78" t="n">
-        <v>944.6222261877898</v>
+        <v>951.5961433977041</v>
       </c>
       <c r="I78" t="n">
-        <v>224.7375904674323</v>
+        <v>182.7244096056963</v>
       </c>
       <c r="J78" t="n">
-        <v>9.612419108736342</v>
+        <v>11.77729185434857</v>
       </c>
       <c r="K78" t="n">
-        <v>1.113562575483229e-09</v>
+        <v>25.58764648557644</v>
       </c>
       <c r="L78" t="n">
-        <v>38.30943862965478</v>
+        <v>1.998205965492161e-05</v>
       </c>
       <c r="M78" t="n">
-        <v>8.08775268978934e-12</v>
+        <v>4.40283018346573</v>
       </c>
       <c r="N78" t="b">
         <v>1</v>
       </c>
       <c r="O78" t="n">
-        <v>0.9993531415271683</v>
+        <v>0.9996234350014528</v>
       </c>
       <c r="P78" t="n">
-        <v>0.001687135502335879</v>
+        <v>0.002776573757838296</v>
       </c>
       <c r="Q78" t="n">
-        <v>818.9382887977189</v>
+        <v>800.0000000000251</v>
       </c>
       <c r="R78" t="n">
-        <v>238.1247089198715</v>
+        <v>184.9089674601588</v>
       </c>
       <c r="S78" t="n">
-        <v>9.553691560535309</v>
+        <v>14.80018846437015</v>
       </c>
       <c r="T78" t="n">
-        <v>125.6839373911845</v>
+        <v>177.1837898832554</v>
       </c>
       <c r="U78" t="n">
-        <v>24.92232017721557</v>
+        <v>2.18457783652218</v>
       </c>
       <c r="V78" t="n">
-        <v>0.05872754820912007</v>
+        <v>1.379933573444145</v>
       </c>
       <c r="W78" t="b">
         <v>1</v>
@@ -6160,68 +6160,68 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>880.3904114497318</v>
+        <v>945.4280016931996</v>
       </c>
       <c r="D79" t="n">
-        <v>8.673565172692003</v>
+        <v>10.16969315797128</v>
       </c>
       <c r="E79" t="n">
-        <v>190.6505216253202</v>
+        <v>123.6167408783263</v>
       </c>
       <c r="F79" t="n">
-        <v>0.7148687243461609</v>
+        <v>0.7905983924865723</v>
       </c>
       <c r="G79" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.01447403151541948</v>
       </c>
       <c r="H79" t="n">
-        <v>928.8432675104241</v>
+        <v>945.4280010337602</v>
       </c>
       <c r="I79" t="n">
-        <v>190.6505216253202</v>
+        <v>176.1525536468137</v>
       </c>
       <c r="J79" t="n">
-        <v>9.000057867285298</v>
+        <v>10.16969315797128</v>
       </c>
       <c r="K79" t="n">
-        <v>48.45285606069228</v>
+        <v>6.594393653358566e-07</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>52.53581276848746</v>
       </c>
       <c r="M79" t="n">
-        <v>0.3264926945932949</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>0.685584385543634</v>
+        <v>0.9998597096722134</v>
       </c>
       <c r="P79" t="n">
-        <v>0.0005886648928861205</v>
+        <v>0.001780382639228377</v>
       </c>
       <c r="Q79" t="n">
-        <v>942.7269140815517</v>
+        <v>809.1792368572565</v>
       </c>
       <c r="R79" t="n">
-        <v>190.574195442033</v>
+        <v>150.0000472872834</v>
       </c>
       <c r="S79" t="n">
-        <v>9.000057869835084</v>
+        <v>10.10016308556093</v>
       </c>
       <c r="T79" t="n">
-        <v>62.33650263181994</v>
+        <v>136.2487648359431</v>
       </c>
       <c r="U79" t="n">
-        <v>0.07632618328722174</v>
+        <v>26.38330640895711</v>
       </c>
       <c r="V79" t="n">
-        <v>0.326492697143081</v>
+        <v>0.06953007241035358</v>
       </c>
       <c r="W79" t="b">
         <v>1</v>
@@ -6233,68 +6233,68 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1020.590107503704</v>
+        <v>879.6778683555364</v>
       </c>
       <c r="D80" t="n">
-        <v>9.120983731049549</v>
+        <v>8.409181496956737</v>
       </c>
       <c r="E80" t="n">
-        <v>193.5922472591342</v>
+        <v>192.244665557246</v>
       </c>
       <c r="F80" t="n">
-        <v>0.7933045029640198</v>
+        <v>0.6287869811058044</v>
       </c>
       <c r="G80" t="n">
-        <v>0.004426439292728901</v>
+        <v>0.0107807656750083</v>
       </c>
       <c r="H80" t="n">
-        <v>965.6040331554768</v>
+        <v>928.8432674868275</v>
       </c>
       <c r="I80" t="n">
-        <v>193.5922472591342</v>
+        <v>192.244665557246</v>
       </c>
       <c r="J80" t="n">
-        <v>9.120983731049558</v>
+        <v>9.000057868106214</v>
       </c>
       <c r="K80" t="n">
-        <v>54.98607434822679</v>
+        <v>49.16539913129111</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>8.881784197001252e-15</v>
+        <v>0.5908763711494771</v>
       </c>
       <c r="N80" t="b">
         <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>0.8891471293741059</v>
+        <v>0.7748990773582409</v>
       </c>
       <c r="P80" t="n">
-        <v>0.0004203312276753548</v>
+        <v>0.0005939363444627738</v>
       </c>
       <c r="Q80" t="n">
-        <v>955.0164289101614</v>
+        <v>942.7215469300116</v>
       </c>
       <c r="R80" t="n">
-        <v>193.672478615373</v>
+        <v>192.0846387696111</v>
       </c>
       <c r="S80" t="n">
-        <v>9.128910428474168</v>
+        <v>9.000057869911943</v>
       </c>
       <c r="T80" t="n">
-        <v>65.57367859354224</v>
+        <v>63.04367857447528</v>
       </c>
       <c r="U80" t="n">
-        <v>0.08023135623884059</v>
+        <v>0.1600267876349051</v>
       </c>
       <c r="V80" t="n">
-        <v>0.007926697424618823</v>
+        <v>0.590876372955206</v>
       </c>
       <c r="W80" t="b">
         <v>1</v>
@@ -6310,64 +6310,64 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>895.0537988063985</v>
+        <v>870.7513134103172</v>
       </c>
       <c r="D81" t="n">
-        <v>7.534486523059265</v>
+        <v>7.884237696536948</v>
       </c>
       <c r="E81" t="n">
-        <v>205.8930180594417</v>
+        <v>194.6998869595861</v>
       </c>
       <c r="F81" t="n">
-        <v>0.7825547456741333</v>
+        <v>0.6866244077682495</v>
       </c>
       <c r="G81" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.0107807656750083</v>
       </c>
       <c r="H81" t="n">
-        <v>928.8432674671133</v>
+        <v>928.8432674700963</v>
       </c>
       <c r="I81" t="n">
-        <v>205.8930180594395</v>
+        <v>194.6998869595861</v>
       </c>
       <c r="J81" t="n">
-        <v>9.00005786891621</v>
+        <v>9.000057866218208</v>
       </c>
       <c r="K81" t="n">
-        <v>33.78946866071476</v>
+        <v>58.09195405977914</v>
       </c>
       <c r="L81" t="n">
-        <v>2.188471626141109e-12</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>1.465571345856945</v>
+        <v>1.11582016968126</v>
       </c>
       <c r="N81" t="b">
         <v>1</v>
       </c>
       <c r="O81" t="n">
-        <v>0.8439084600283216</v>
+        <v>0.898104778270799</v>
       </c>
       <c r="P81" t="n">
-        <v>0.0004858185597145025</v>
+        <v>0.0006777249728569186</v>
       </c>
       <c r="Q81" t="n">
-        <v>946.5551923324931</v>
+        <v>941.934038856728</v>
       </c>
       <c r="R81" t="n">
-        <v>205.0095719266471</v>
+        <v>194.3588315252479</v>
       </c>
       <c r="S81" t="n">
-        <v>9.000057861073191</v>
+        <v>9.00005786936636</v>
       </c>
       <c r="T81" t="n">
-        <v>51.5013935260946</v>
+        <v>71.18272544641081</v>
       </c>
       <c r="U81" t="n">
-        <v>0.8834461327946315</v>
+        <v>0.3410554343382728</v>
       </c>
       <c r="V81" t="n">
-        <v>1.465571338013926</v>
+        <v>1.115820172829412</v>
       </c>
       <c r="W81" t="b">
         <v>1</v>
@@ -6383,64 +6383,64 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>865.5234941240955</v>
+        <v>858.1779506520814</v>
       </c>
       <c r="D82" t="n">
-        <v>5.794056617050133</v>
+        <v>8.307110321367631</v>
       </c>
       <c r="E82" t="n">
-        <v>185.7493322485568</v>
+        <v>202.7281673227784</v>
       </c>
       <c r="F82" t="n">
-        <v>0.8575201034545898</v>
+        <v>0.6621172428131104</v>
       </c>
       <c r="G82" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.0107807656750083</v>
       </c>
       <c r="H82" t="n">
-        <v>928.8432674646418</v>
+        <v>928.8432674781424</v>
       </c>
       <c r="I82" t="n">
-        <v>185.7493322485567</v>
+        <v>202.7281673227784</v>
       </c>
       <c r="J82" t="n">
-        <v>9.000057868433272</v>
+        <v>9.000057868484312</v>
       </c>
       <c r="K82" t="n">
-        <v>63.31977334054636</v>
+        <v>70.66531682606092</v>
       </c>
       <c r="L82" t="n">
         <v>2.842170943040401e-14</v>
       </c>
       <c r="M82" t="n">
-        <v>3.206001251383139</v>
+        <v>0.6929475471166811</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
       </c>
       <c r="O82" t="n">
-        <v>0.9781872632768009</v>
+        <v>0.8477183436844844</v>
       </c>
       <c r="P82" t="n">
-        <v>0.0007436002217320406</v>
+        <v>0.0008200011890188441</v>
       </c>
       <c r="Q82" t="n">
-        <v>941.0553301147726</v>
+        <v>941.7568608463895</v>
       </c>
       <c r="R82" t="n">
-        <v>185.8904182960312</v>
+        <v>201.6389954079011</v>
       </c>
       <c r="S82" t="n">
-        <v>9.000057869709417</v>
+        <v>9.000057865826527</v>
       </c>
       <c r="T82" t="n">
-        <v>75.53183599067711</v>
+        <v>83.57891019430804</v>
       </c>
       <c r="U82" t="n">
-        <v>0.1410860474744311</v>
+        <v>1.08917191487734</v>
       </c>
       <c r="V82" t="n">
-        <v>3.206001252659284</v>
+        <v>0.6929475444588959</v>
       </c>
       <c r="W82" t="b">
         <v>1</v>
@@ -6452,68 +6452,68 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>889.7896881509041</v>
+        <v>907.5210483459867</v>
       </c>
       <c r="D83" t="n">
-        <v>7.199121975290029</v>
+        <v>14.47908425102576</v>
       </c>
       <c r="E83" t="n">
-        <v>192.8925602011192</v>
+        <v>215.0193854879847</v>
       </c>
       <c r="F83" t="n">
-        <v>0.8525000214576721</v>
+        <v>0.6851028800010681</v>
       </c>
       <c r="G83" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.008092132396996021</v>
       </c>
       <c r="H83" t="n">
-        <v>928.8432674739572</v>
+        <v>908.0128723511148</v>
       </c>
       <c r="I83" t="n">
-        <v>192.8925602011192</v>
+        <v>215.0193854899296</v>
       </c>
       <c r="J83" t="n">
-        <v>9.000057868187188</v>
+        <v>11.77729472234742</v>
       </c>
       <c r="K83" t="n">
-        <v>39.0535793230531</v>
+        <v>0.4918240051280236</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.944982841450837e-09</v>
       </c>
       <c r="M83" t="n">
-        <v>1.800935892897159</v>
+        <v>2.701789528678336</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
       </c>
       <c r="O83" t="n">
-        <v>0.9119186050945739</v>
+        <v>0.964248395075688</v>
       </c>
       <c r="P83" t="n">
-        <v>0.0005032440915117498</v>
+        <v>0.001503292210404655</v>
       </c>
       <c r="Q83" t="n">
-        <v>943.9718546444117</v>
+        <v>818.5257614600431</v>
       </c>
       <c r="R83" t="n">
-        <v>192.7318937691159</v>
+        <v>214.6897995010518</v>
       </c>
       <c r="S83" t="n">
-        <v>9.000057868898709</v>
+        <v>13.89897201341323</v>
       </c>
       <c r="T83" t="n">
-        <v>54.18216649350757</v>
+        <v>88.99528688594364</v>
       </c>
       <c r="U83" t="n">
-        <v>0.1606664320032962</v>
+        <v>0.329585986932841</v>
       </c>
       <c r="V83" t="n">
-        <v>1.80093589360868</v>
+        <v>0.5801122376125303</v>
       </c>
       <c r="W83" t="b">
         <v>1</v>
@@ -6525,68 +6525,68 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>932.8511514090557</v>
+        <v>1045.066055964013</v>
       </c>
       <c r="D84" t="n">
-        <v>14.30651280429054</v>
+        <v>11.97257990444693</v>
       </c>
       <c r="E84" t="n">
-        <v>195.5242282111045</v>
+        <v>208.7342481994733</v>
       </c>
       <c r="F84" t="n">
-        <v>0.8591651916503906</v>
+        <v>0.6389009356498718</v>
       </c>
       <c r="G84" t="n">
-        <v>0.004665159154683352</v>
+        <v>0.007744077127426863</v>
       </c>
       <c r="H84" t="n">
-        <v>932.8511512989573</v>
+        <v>965.6040331806454</v>
       </c>
       <c r="I84" t="n">
-        <v>195.5242282111045</v>
+        <v>208.7342481994732</v>
       </c>
       <c r="J84" t="n">
-        <v>11.77729471588324</v>
+        <v>11.97257990444694</v>
       </c>
       <c r="K84" t="n">
-        <v>1.100983126889332e-07</v>
+        <v>79.46202278336807</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M84" t="n">
-        <v>2.529218088407294</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>0.9819903249735874</v>
+        <v>0.9950720585205197</v>
       </c>
       <c r="P84" t="n">
-        <v>0.001561483086341692</v>
+        <v>0.000593527111646464</v>
       </c>
       <c r="Q84" t="n">
-        <v>823.9699411554446</v>
+        <v>950.5107694693806</v>
       </c>
       <c r="R84" t="n">
-        <v>196.3850664225823</v>
+        <v>207.8478735970994</v>
       </c>
       <c r="S84" t="n">
-        <v>13.664556506826</v>
+        <v>11.9195044307956</v>
       </c>
       <c r="T84" t="n">
-        <v>108.881210253611</v>
+        <v>94.55528649463281</v>
       </c>
       <c r="U84" t="n">
-        <v>0.8608382114778124</v>
+        <v>0.8863746023739054</v>
       </c>
       <c r="V84" t="n">
-        <v>0.6419562974645316</v>
+        <v>0.05307547365133303</v>
       </c>
       <c r="W84" t="b">
         <v>1</v>
@@ -6598,68 +6598,68 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Stains</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>880.0576694243047</v>
+        <v>958.1627182555671</v>
       </c>
       <c r="D85" t="n">
-        <v>9.81859396528281</v>
+        <v>5.668629819570818</v>
       </c>
       <c r="E85" t="n">
-        <v>198.9086141515425</v>
+        <v>210.4580345136799</v>
       </c>
       <c r="F85" t="n">
-        <v>0.6293198466300964</v>
+        <v>0.6949941515922546</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0032845763489604</v>
+        <v>0.005485068075358868</v>
       </c>
       <c r="H85" t="n">
-        <v>922.9741913766268</v>
+        <v>958.1627182555648</v>
       </c>
       <c r="I85" t="n">
-        <v>198.9086141515425</v>
+        <v>210.4580345136799</v>
       </c>
       <c r="J85" t="n">
-        <v>9.818593965282792</v>
+        <v>9.000057869254071</v>
       </c>
       <c r="K85" t="n">
-        <v>42.91652195232211</v>
+        <v>2.387423592153937e-12</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M85" t="n">
-        <v>1.77635683940025e-14</v>
+        <v>3.331428049683254</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>0.5192035784168804</v>
+        <v>0.9670661206681781</v>
       </c>
       <c r="P85" t="n">
-        <v>0.0004776136350669723</v>
+        <v>0.001594391717383161</v>
       </c>
       <c r="Q85" t="n">
-        <v>936.8083969716043</v>
+        <v>948.8598730155405</v>
       </c>
       <c r="R85" t="n">
-        <v>198.6795136720016</v>
+        <v>206.7744196915362</v>
       </c>
       <c r="S85" t="n">
-        <v>9.804851928388286</v>
+        <v>9.000057869254071</v>
       </c>
       <c r="T85" t="n">
-        <v>56.75072754729968</v>
+        <v>9.302845240026613</v>
       </c>
       <c r="U85" t="n">
-        <v>0.2291004795408185</v>
+        <v>3.68361482214371</v>
       </c>
       <c r="V85" t="n">
-        <v>0.01374203689452358</v>
+        <v>3.331428049683254</v>
       </c>
       <c r="W85" t="b">
         <v>1</v>
@@ -6671,68 +6671,68 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>949.6175564029259</v>
+        <v>963.6665798562213</v>
       </c>
       <c r="D86" t="n">
-        <v>9.917669449982794</v>
+        <v>6.165623509601247</v>
       </c>
       <c r="E86" t="n">
-        <v>144.5779808580052</v>
+        <v>194.8996182548566</v>
       </c>
       <c r="F86" t="n">
-        <v>0.898436963558197</v>
+        <v>0.6949941515922546</v>
       </c>
       <c r="G86" t="n">
-        <v>0.009224903769791126</v>
+        <v>0.005485068075358868</v>
       </c>
       <c r="H86" t="n">
-        <v>949.6187981197262</v>
+        <v>963.6665798562193</v>
       </c>
       <c r="I86" t="n">
-        <v>176.1525536265771</v>
+        <v>194.8996182548567</v>
       </c>
       <c r="J86" t="n">
-        <v>9.917316085073059</v>
+        <v>9.000057869254071</v>
       </c>
       <c r="K86" t="n">
-        <v>0.00124171680033669</v>
+        <v>2.046363078989089e-12</v>
       </c>
       <c r="L86" t="n">
-        <v>31.57457276857187</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M86" t="n">
-        <v>0.0003533649097349212</v>
+        <v>2.834434359652825</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>0.996459173492649</v>
+        <v>0.8637625687507785</v>
       </c>
       <c r="P86" t="n">
-        <v>0.001762343385386861</v>
+        <v>0.001041549576820156</v>
       </c>
       <c r="Q86" t="n">
-        <v>811.721593985368</v>
+        <v>953.1245536945784</v>
       </c>
       <c r="R86" t="n">
-        <v>150.7709461458721</v>
+        <v>194.0887758847322</v>
       </c>
       <c r="S86" t="n">
-        <v>9.849555942680613</v>
+        <v>9.000057869254071</v>
       </c>
       <c r="T86" t="n">
-        <v>137.8959624175578</v>
+        <v>10.54202616164298</v>
       </c>
       <c r="U86" t="n">
-        <v>6.19296528786694</v>
+        <v>0.810842370124476</v>
       </c>
       <c r="V86" t="n">
-        <v>0.06811350730218102</v>
+        <v>2.834434359652825</v>
       </c>
       <c r="W86" t="b">
         <v>1</v>
@@ -6744,68 +6744,68 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>938.8656420428567</v>
+        <v>895.8137950481108</v>
       </c>
       <c r="D87" t="n">
-        <v>9.711022741733842</v>
+        <v>8.598473644703342</v>
       </c>
       <c r="E87" t="n">
-        <v>145.5722215619359</v>
+        <v>206.6625854025031</v>
       </c>
       <c r="F87" t="n">
-        <v>0.898436963558197</v>
+        <v>0.620580792427063</v>
       </c>
       <c r="G87" t="n">
-        <v>0.06757150590419769</v>
+        <v>0.0107807656750083</v>
       </c>
       <c r="H87" t="n">
-        <v>945.4104302390047</v>
+        <v>928.8432674808973</v>
       </c>
       <c r="I87" t="n">
-        <v>175.8531626773831</v>
+        <v>206.6625854025031</v>
       </c>
       <c r="J87" t="n">
-        <v>9.813463800305046</v>
+        <v>9.000057868423067</v>
       </c>
       <c r="K87" t="n">
-        <v>6.54478819614792</v>
+        <v>33.02947243278652</v>
       </c>
       <c r="L87" t="n">
-        <v>30.28094111544715</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M87" t="n">
-        <v>0.1024410585712037</v>
+        <v>0.4015842237197251</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
       </c>
       <c r="O87" t="n">
-        <v>0.9942782075798909</v>
+        <v>0.519092130117935</v>
       </c>
       <c r="P87" t="n">
-        <v>0.001634614792615171</v>
+        <v>0.0004826176356546388</v>
       </c>
       <c r="Q87" t="n">
-        <v>813.3790922147751</v>
+        <v>946.8470346543037</v>
       </c>
       <c r="R87" t="n">
-        <v>151.553913441716</v>
+        <v>205.73566202997</v>
       </c>
       <c r="S87" t="n">
-        <v>9.645312417759607</v>
+        <v>9.000057859463142</v>
       </c>
       <c r="T87" t="n">
-        <v>125.4865498280816</v>
+        <v>51.03323960619286</v>
       </c>
       <c r="U87" t="n">
-        <v>5.981691879780072</v>
+        <v>0.9269233725330537</v>
       </c>
       <c r="V87" t="n">
-        <v>0.06571032397423515</v>
+        <v>0.4015842147598008</v>
       </c>
       <c r="W87" t="b">
         <v>1</v>
@@ -6817,68 +6817,68 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Dirtiness</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>989.0621439654515</v>
+        <v>944.6222261889034</v>
       </c>
       <c r="D88" t="n">
-        <v>15.52164038629858</v>
+        <v>9.61241910874443</v>
       </c>
       <c r="E88" t="n">
-        <v>211.9652678668288</v>
+        <v>263.0470290970871</v>
       </c>
       <c r="F88" t="n">
-        <v>0.8318169116973877</v>
+        <v>0.6614874005317688</v>
       </c>
       <c r="G88" t="n">
-        <v>0.004271036013960838</v>
+        <v>0.006804721895605326</v>
       </c>
       <c r="H88" t="n">
-        <v>990.4518202496184</v>
+        <v>944.2251868308263</v>
       </c>
       <c r="I88" t="n">
-        <v>211.9652678668296</v>
+        <v>222.3777147431355</v>
       </c>
       <c r="J88" t="n">
-        <v>11.7772947223313</v>
+        <v>9.743181577476669</v>
       </c>
       <c r="K88" t="n">
-        <v>1.389676284166967</v>
+        <v>0.3970393580771088</v>
       </c>
       <c r="L88" t="n">
-        <v>7.958078640513122e-13</v>
+        <v>40.66931435395162</v>
       </c>
       <c r="M88" t="n">
-        <v>3.744345663967277</v>
+        <v>0.1307624687322395</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
       </c>
       <c r="O88" t="n">
-        <v>0.9982928998632259</v>
+        <v>0.9993531415271683</v>
       </c>
       <c r="P88" t="n">
-        <v>0.002499602621814765</v>
+        <v>0.001687135502335879</v>
       </c>
       <c r="Q88" t="n">
-        <v>812.3518565656884</v>
+        <v>818.9382887977189</v>
       </c>
       <c r="R88" t="n">
-        <v>211.9612790027144</v>
+        <v>238.1247089198715</v>
       </c>
       <c r="S88" t="n">
-        <v>14.42256403795143</v>
+        <v>9.553691560535309</v>
       </c>
       <c r="T88" t="n">
-        <v>176.710287399763</v>
+        <v>125.6839373911845</v>
       </c>
       <c r="U88" t="n">
-        <v>0.003988864114432999</v>
+        <v>24.92232017721557</v>
       </c>
       <c r="V88" t="n">
-        <v>1.099076348347147</v>
+        <v>0.05872754820912007</v>
       </c>
       <c r="W88" t="b">
         <v>1</v>
@@ -6890,68 +6890,68 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>953.8876860315468</v>
+        <v>863.1668720727778</v>
       </c>
       <c r="D89" t="n">
-        <v>10.26697578312756</v>
+        <v>8.257379855576692</v>
       </c>
       <c r="E89" t="n">
-        <v>133.9082043343228</v>
+        <v>202.4578501738119</v>
       </c>
       <c r="F89" t="n">
-        <v>0.898436963558197</v>
+        <v>0.6621172428131104</v>
       </c>
       <c r="G89" t="n">
-        <v>0.009224903769791126</v>
+        <v>0.0107807656750083</v>
       </c>
       <c r="H89" t="n">
-        <v>953.887686053728</v>
+        <v>928.8432675179702</v>
       </c>
       <c r="I89" t="n">
-        <v>176.1525536307083</v>
+        <v>202.4578501738119</v>
       </c>
       <c r="J89" t="n">
-        <v>10.26697578233031</v>
+        <v>9.000057866603507</v>
       </c>
       <c r="K89" t="n">
-        <v>2.218121153418906e-08</v>
+        <v>65.67639544519238</v>
       </c>
       <c r="L89" t="n">
-        <v>42.24434929638554</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>7.97253818518584e-10</v>
+        <v>0.7426780110268147</v>
       </c>
       <c r="N89" t="b">
         <v>1</v>
       </c>
       <c r="O89" t="n">
-        <v>0.9995206905356393</v>
+        <v>0.8577642243197116</v>
       </c>
       <c r="P89" t="n">
-        <v>0.001851875149642966</v>
+        <v>0.0007683347517901382</v>
       </c>
       <c r="Q89" t="n">
-        <v>809.2262114316984</v>
+        <v>942.1841852943093</v>
       </c>
       <c r="R89" t="n">
-        <v>150.0000472882507</v>
+        <v>201.451960927629</v>
       </c>
       <c r="S89" t="n">
-        <v>10.19446579512171</v>
+        <v>9.00005786540785</v>
       </c>
       <c r="T89" t="n">
-        <v>144.6614745998484</v>
+        <v>79.01731322153148</v>
       </c>
       <c r="U89" t="n">
-        <v>16.09184295392791</v>
+        <v>1.005889246182875</v>
       </c>
       <c r="V89" t="n">
-        <v>0.07250998800584973</v>
+        <v>0.7426780098311578</v>
       </c>
       <c r="W89" t="b">
         <v>1</v>
@@ -6963,68 +6963,68 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>935.4399411754173</v>
+        <v>983.901020808615</v>
       </c>
       <c r="D90" t="n">
-        <v>9.87950258610064</v>
+        <v>13.76898907605516</v>
       </c>
       <c r="E90" t="n">
-        <v>133.1145117025978</v>
+        <v>198.4880261430288</v>
       </c>
       <c r="F90" t="n">
-        <v>0.898436963558197</v>
+        <v>0.7168129682540894</v>
       </c>
       <c r="G90" t="n">
-        <v>0.009224903769791126</v>
+        <v>0.007583793252706528</v>
       </c>
       <c r="H90" t="n">
-        <v>935.4399414219187</v>
+        <v>991.5080620940015</v>
       </c>
       <c r="I90" t="n">
-        <v>176.152553690535</v>
+        <v>198.4880261430283</v>
       </c>
       <c r="J90" t="n">
-        <v>9.87950240139522</v>
+        <v>11.77729472265093</v>
       </c>
       <c r="K90" t="n">
-        <v>2.465013722030562e-07</v>
+        <v>7.607041285386458</v>
       </c>
       <c r="L90" t="n">
-        <v>43.03804198793722</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="M90" t="n">
-        <v>1.847054207360088e-07</v>
+        <v>1.991694353404233</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
       </c>
       <c r="O90" t="n">
-        <v>0.9993111828502101</v>
+        <v>0.9473558225655059</v>
       </c>
       <c r="P90" t="n">
-        <v>0.001676154356337248</v>
+        <v>0.001713693887865423</v>
       </c>
       <c r="Q90" t="n">
-        <v>809.7816434419815</v>
+        <v>839.8954072031228</v>
       </c>
       <c r="R90" t="n">
-        <v>150.0000472874704</v>
+        <v>199.3711627963716</v>
       </c>
       <c r="S90" t="n">
-        <v>9.813439815044669</v>
+        <v>13.08424536513067</v>
       </c>
       <c r="T90" t="n">
-        <v>125.6582977334358</v>
+        <v>144.0056136054923</v>
       </c>
       <c r="U90" t="n">
-        <v>16.88553558487266</v>
+        <v>0.883136653342774</v>
       </c>
       <c r="V90" t="n">
-        <v>0.06606277105597158</v>
+        <v>0.6847437109244918</v>
       </c>
       <c r="W90" t="b">
         <v>1</v>
@@ -7036,68 +7036,68 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Dirtiness</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>930.9536723852241</v>
+        <v>944.194509116227</v>
       </c>
       <c r="D91" t="n">
-        <v>10.74705882782412</v>
+        <v>9.530270203510403</v>
       </c>
       <c r="E91" t="n">
-        <v>158.3215284092236</v>
+        <v>248.7612646314657</v>
       </c>
       <c r="F91" t="n">
-        <v>0.898436963558197</v>
+        <v>0.6614874005317688</v>
       </c>
       <c r="G91" t="n">
-        <v>0.009224903769791126</v>
+        <v>0.006804721895605326</v>
       </c>
       <c r="H91" t="n">
-        <v>930.9474355298083</v>
+        <v>943.970686717293</v>
       </c>
       <c r="I91" t="n">
-        <v>176.1525854224256</v>
+        <v>222.3804919422276</v>
       </c>
       <c r="J91" t="n">
-        <v>10.54506804822702</v>
+        <v>9.623047244604891</v>
       </c>
       <c r="K91" t="n">
-        <v>0.006236855415750142</v>
+        <v>0.2238223989339758</v>
       </c>
       <c r="L91" t="n">
-        <v>17.83105701320198</v>
+        <v>26.38077268923811</v>
       </c>
       <c r="M91" t="n">
-        <v>0.2019907795971001</v>
+        <v>0.0927770410944877</v>
       </c>
       <c r="N91" t="b">
         <v>1</v>
       </c>
       <c r="O91" t="n">
-        <v>0.9103170189198628</v>
+        <v>0.9882337561435889</v>
       </c>
       <c r="P91" t="n">
-        <v>0.001248655968202007</v>
+        <v>0.00135852531626458</v>
       </c>
       <c r="Q91" t="n">
-        <v>831.8409425958835</v>
+        <v>837.698140265108</v>
       </c>
       <c r="R91" t="n">
-        <v>164.2946129922157</v>
+        <v>229.9290947021141</v>
       </c>
       <c r="S91" t="n">
-        <v>10.70147628368998</v>
+        <v>9.477537641904293</v>
       </c>
       <c r="T91" t="n">
-        <v>99.11272978934062</v>
+        <v>106.496368851119</v>
       </c>
       <c r="U91" t="n">
-        <v>5.973084582992129</v>
+        <v>18.83216992935155</v>
       </c>
       <c r="V91" t="n">
-        <v>0.04558254413414176</v>
+        <v>0.05273256160610984</v>
       </c>
       <c r="W91" t="b">
         <v>1</v>
@@ -7109,68 +7109,68 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Stains</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>937.8043419136123</v>
+        <v>876.3504279631637</v>
       </c>
       <c r="D92" t="n">
-        <v>9.875451520313577</v>
+        <v>11.34587500317772</v>
       </c>
       <c r="E92" t="n">
-        <v>125.1384266710015</v>
+        <v>209.9489333488838</v>
       </c>
       <c r="F92" t="n">
-        <v>0.898436963558197</v>
+        <v>0.6125013828277588</v>
       </c>
       <c r="G92" t="n">
-        <v>0.009224903769791126</v>
+        <v>0.005909173749387264</v>
       </c>
       <c r="H92" t="n">
-        <v>937.8043448712422</v>
+        <v>922.9741913766268</v>
       </c>
       <c r="I92" t="n">
-        <v>176.152553626836</v>
+        <v>209.9489333488838</v>
       </c>
       <c r="J92" t="n">
-        <v>9.875449119361987</v>
+        <v>11.34587500317772</v>
       </c>
       <c r="K92" t="n">
-        <v>2.957629817501584e-06</v>
+        <v>46.62376341346305</v>
       </c>
       <c r="L92" t="n">
-        <v>51.01412695583457</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>2.400951590431077e-06</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>0.9997839501156084</v>
+        <v>0.8153352059091716</v>
       </c>
       <c r="P92" t="n">
-        <v>0.001694320168954188</v>
+        <v>0.0006264322143201939</v>
       </c>
       <c r="Q92" t="n">
-        <v>809.9301782237127</v>
+        <v>942.5488295184717</v>
       </c>
       <c r="R92" t="n">
-        <v>150.0000472874291</v>
+        <v>208.8502911972969</v>
       </c>
       <c r="S92" t="n">
-        <v>9.808602380887409</v>
+        <v>11.2826747603838</v>
       </c>
       <c r="T92" t="n">
-        <v>127.8741636898997</v>
+        <v>66.19840155530801</v>
       </c>
       <c r="U92" t="n">
-        <v>24.86162061642767</v>
+        <v>1.098642151586915</v>
       </c>
       <c r="V92" t="n">
-        <v>0.06684913942616788</v>
+        <v>0.0632002427939149</v>
       </c>
       <c r="W92" t="b">
         <v>1</v>
@@ -7182,68 +7182,68 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>952.468583634073</v>
+        <v>1060.809240086009</v>
       </c>
       <c r="D93" t="n">
-        <v>10.13941515934641</v>
+        <v>9.631116897062975</v>
       </c>
       <c r="E93" t="n">
-        <v>137.1269399592908</v>
+        <v>200.2362060241465</v>
       </c>
       <c r="F93" t="n">
-        <v>0.898436963558197</v>
+        <v>0.6508126258850098</v>
       </c>
       <c r="G93" t="n">
-        <v>0.009224903769791126</v>
+        <v>0.007977633737027645</v>
       </c>
       <c r="H93" t="n">
-        <v>952.4685836501495</v>
+        <v>965.6040331730386</v>
       </c>
       <c r="I93" t="n">
-        <v>176.1525536515622</v>
+        <v>200.2362060241465</v>
       </c>
       <c r="J93" t="n">
-        <v>10.13941515873681</v>
+        <v>9.631116897062974</v>
       </c>
       <c r="K93" t="n">
-        <v>1.607656940905144e-08</v>
+        <v>95.20520691297054</v>
       </c>
       <c r="L93" t="n">
-        <v>39.02561369227132</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>6.095994820043416e-10</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="N93" t="b">
         <v>1</v>
       </c>
       <c r="O93" t="n">
-        <v>0.9991588937702729</v>
+        <v>0.9989035357889861</v>
       </c>
       <c r="P93" t="n">
-        <v>0.001830166654516844</v>
+        <v>0.0005829023441392633</v>
       </c>
       <c r="Q93" t="n">
-        <v>809.6439681234634</v>
+        <v>957.3671172764099</v>
       </c>
       <c r="R93" t="n">
-        <v>150.000047287171</v>
+        <v>199.9317826026219</v>
       </c>
       <c r="S93" t="n">
-        <v>10.06775259558112</v>
+        <v>9.631534542727458</v>
       </c>
       <c r="T93" t="n">
-        <v>142.8246155106095</v>
+        <v>103.4421228095993</v>
       </c>
       <c r="U93" t="n">
-        <v>12.87310732788012</v>
+        <v>0.3044234215245751</v>
       </c>
       <c r="V93" t="n">
-        <v>0.07166256376529034</v>
+        <v>0.0004176456644824356</v>
       </c>
       <c r="W93" t="b">
         <v>1</v>
@@ -7255,68 +7255,68 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>879.6778683555364</v>
+        <v>973.0469727792386</v>
       </c>
       <c r="D94" t="n">
-        <v>8.409181496956737</v>
+        <v>10.47787893609605</v>
       </c>
       <c r="E94" t="n">
-        <v>192.244665557246</v>
+        <v>124.6665701044529</v>
       </c>
       <c r="F94" t="n">
-        <v>0.7148687243461609</v>
+        <v>0.7892021536827087</v>
       </c>
       <c r="G94" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.01447403151541948</v>
       </c>
       <c r="H94" t="n">
-        <v>928.8432674923583</v>
+        <v>964.5525899915925</v>
       </c>
       <c r="I94" t="n">
-        <v>192.244665557246</v>
+        <v>176.1529501388631</v>
       </c>
       <c r="J94" t="n">
-        <v>9.000057868032547</v>
+        <v>10.47795226877035</v>
       </c>
       <c r="K94" t="n">
-        <v>49.16539913682197</v>
+        <v>8.494382787646032</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>51.48638003441025</v>
       </c>
       <c r="M94" t="n">
-        <v>0.5908763710758098</v>
+        <v>7.33326743027618e-05</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
       </c>
       <c r="O94" t="n">
-        <v>0.7748990773582409</v>
+        <v>0.9998900281081606</v>
       </c>
       <c r="P94" t="n">
-        <v>0.0005939363444627738</v>
+        <v>0.002004033270910592</v>
       </c>
       <c r="Q94" t="n">
-        <v>942.7215469300116</v>
+        <v>809.2758483455329</v>
       </c>
       <c r="R94" t="n">
-        <v>192.0846387696111</v>
+        <v>150.0000472877422</v>
       </c>
       <c r="S94" t="n">
-        <v>9.000057869911943</v>
+        <v>10.39853357254134</v>
       </c>
       <c r="T94" t="n">
-        <v>63.04367857447528</v>
+        <v>163.7711244337056</v>
       </c>
       <c r="U94" t="n">
-        <v>0.1600267876349051</v>
+        <v>25.33347718328932</v>
       </c>
       <c r="V94" t="n">
-        <v>0.590876372955206</v>
+        <v>0.07934536355471522</v>
       </c>
       <c r="W94" t="b">
         <v>1</v>
@@ -7332,64 +7332,64 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>966.5423085713154</v>
+        <v>962.0516053595668</v>
       </c>
       <c r="D95" t="n">
-        <v>13.14042291010224</v>
+        <v>16.09234396975411</v>
       </c>
       <c r="E95" t="n">
-        <v>197.7657652725835</v>
+        <v>204.3244311042431</v>
       </c>
       <c r="F95" t="n">
-        <v>0.7118276357650757</v>
+        <v>0.7234267592430115</v>
       </c>
       <c r="G95" t="n">
-        <v>0.007323441095650196</v>
+        <v>0.008424116298556328</v>
       </c>
       <c r="H95" t="n">
-        <v>871.1349584469542</v>
+        <v>962.0517409419034</v>
       </c>
       <c r="I95" t="n">
-        <v>197.7657652725856</v>
+        <v>204.3243907763482</v>
       </c>
       <c r="J95" t="n">
-        <v>11.77727926677925</v>
+        <v>11.77729107542714</v>
       </c>
       <c r="K95" t="n">
-        <v>95.40735012436119</v>
+        <v>0.0001355823366111508</v>
       </c>
       <c r="L95" t="n">
-        <v>2.160049916710705e-12</v>
+        <v>4.03278949079322e-05</v>
       </c>
       <c r="M95" t="n">
-        <v>1.363143643322987</v>
+        <v>4.315052894326975</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
       </c>
       <c r="O95" t="n">
-        <v>0.7431482893248885</v>
+        <v>0.9996780981033778</v>
       </c>
       <c r="P95" t="n">
-        <v>0.001396832028235451</v>
+        <v>0.002547836813188511</v>
       </c>
       <c r="Q95" t="n">
-        <v>848.7743500185034</v>
+        <v>800.0000005995885</v>
       </c>
       <c r="R95" t="n">
-        <v>198.5664792161159</v>
+        <v>204.904125831805</v>
       </c>
       <c r="S95" t="n">
-        <v>12.61624143528335</v>
+        <v>14.9066245559576</v>
       </c>
       <c r="T95" t="n">
-        <v>117.767958552812</v>
+        <v>162.0516047599783</v>
       </c>
       <c r="U95" t="n">
-        <v>0.8007139435324007</v>
+        <v>0.5796947275619004</v>
       </c>
       <c r="V95" t="n">
-        <v>0.5241814748188833</v>
+        <v>1.185719413796509</v>
       </c>
       <c r="W95" t="b">
         <v>1</v>
@@ -7401,68 +7401,68 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>863.3433651598725</v>
+        <v>929.2738150525246</v>
       </c>
       <c r="D96" t="n">
-        <v>8.958113067522632</v>
+        <v>9.284455580241472</v>
       </c>
       <c r="E96" t="n">
-        <v>223.8194498341562</v>
+        <v>124.5817455398897</v>
       </c>
       <c r="F96" t="n">
-        <v>0.5720645189285278</v>
+        <v>0.7905983924865723</v>
       </c>
       <c r="G96" t="n">
-        <v>0.005645568948239088</v>
+        <v>0.01444620545953512</v>
       </c>
       <c r="H96" t="n">
-        <v>928.845293794911</v>
+        <v>928.8432674281495</v>
       </c>
       <c r="I96" t="n">
-        <v>224.7375904982351</v>
+        <v>176.1525536328066</v>
       </c>
       <c r="J96" t="n">
-        <v>9.000057869022088</v>
+        <v>9.284250544240875</v>
       </c>
       <c r="K96" t="n">
-        <v>65.50192863503844</v>
+        <v>0.4305476243750945</v>
       </c>
       <c r="L96" t="n">
-        <v>0.9181406640788055</v>
+        <v>51.57080809291691</v>
       </c>
       <c r="M96" t="n">
-        <v>0.04194480149945612</v>
+        <v>0.0002050360005974028</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
       </c>
       <c r="O96" t="n">
-        <v>0.7246998841238931</v>
+        <v>0.9997003099067855</v>
       </c>
       <c r="P96" t="n">
-        <v>0.0009405126676312138</v>
+        <v>0.001563233690525028</v>
       </c>
       <c r="Q96" t="n">
-        <v>947.723662001242</v>
+        <v>812.0174921107624</v>
       </c>
       <c r="R96" t="n">
-        <v>220.5640906715748</v>
+        <v>150.0000472864174</v>
       </c>
       <c r="S96" t="n">
-        <v>9.077678127524736</v>
+        <v>9.219186697060195</v>
       </c>
       <c r="T96" t="n">
-        <v>84.3802968413695</v>
+        <v>117.2563229417622</v>
       </c>
       <c r="U96" t="n">
-        <v>3.255359162581442</v>
+        <v>25.41830174652767</v>
       </c>
       <c r="V96" t="n">
-        <v>0.1195650600021043</v>
+        <v>0.0652688831812771</v>
       </c>
       <c r="W96" t="b">
         <v>1</v>
@@ -7474,68 +7474,68 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>912.9631453685068</v>
+        <v>1022.429663133332</v>
       </c>
       <c r="D97" t="n">
-        <v>9.112037063398379</v>
+        <v>11.11643074878221</v>
       </c>
       <c r="E97" t="n">
-        <v>139.0988209939565</v>
+        <v>213.6935336757777</v>
       </c>
       <c r="F97" t="n">
-        <v>0.8184100985527039</v>
+        <v>0.6508126258850098</v>
       </c>
       <c r="G97" t="n">
-        <v>0.00783149991184473</v>
+        <v>0.007977633737027645</v>
       </c>
       <c r="H97" t="n">
-        <v>910.5034539054226</v>
+        <v>965.6040331587085</v>
       </c>
       <c r="I97" t="n">
-        <v>176.1525536255858</v>
+        <v>213.6935336757777</v>
       </c>
       <c r="J97" t="n">
-        <v>9.110678135520715</v>
+        <v>11.11643074878221</v>
       </c>
       <c r="K97" t="n">
-        <v>2.459691463084255</v>
+        <v>56.82562997462378</v>
       </c>
       <c r="L97" t="n">
-        <v>37.05373263162926</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>0.001358927877664229</v>
+        <v>0</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
       </c>
       <c r="O97" t="n">
-        <v>0.9953384087124076</v>
+        <v>0.9606179555357727</v>
       </c>
       <c r="P97" t="n">
-        <v>0.001407117645958143</v>
+        <v>0.0004566143107414854</v>
       </c>
       <c r="Q97" t="n">
-        <v>811.760004387709</v>
+        <v>950.7338272738875</v>
       </c>
       <c r="R97" t="n">
-        <v>150.000047286275</v>
+        <v>212.6779086444871</v>
       </c>
       <c r="S97" t="n">
-        <v>9.052479068377888</v>
+        <v>11.08782501383651</v>
       </c>
       <c r="T97" t="n">
-        <v>101.2031409807978</v>
+        <v>71.69583585944474</v>
       </c>
       <c r="U97" t="n">
-        <v>10.90122629231846</v>
+        <v>1.015625031290597</v>
       </c>
       <c r="V97" t="n">
-        <v>0.05955799502049075</v>
+        <v>0.02860573494569607</v>
       </c>
       <c r="W97" t="b">
         <v>1</v>
@@ -7547,68 +7547,68 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>863.6979788580384</v>
+        <v>907.9083440246934</v>
       </c>
       <c r="D98" t="n">
-        <v>6.827761165334765</v>
+        <v>10.62947649711448</v>
       </c>
       <c r="E98" t="n">
-        <v>187.5563751585021</v>
+        <v>128.3441543429158</v>
       </c>
       <c r="F98" t="n">
-        <v>0.8753654360771179</v>
+        <v>0.6891825199127197</v>
       </c>
       <c r="G98" t="n">
-        <v>0.005963578354567289</v>
+        <v>0.01369568612426519</v>
       </c>
       <c r="H98" t="n">
-        <v>928.8432674983528</v>
+        <v>908.0129273449041</v>
       </c>
       <c r="I98" t="n">
-        <v>187.5563751585021</v>
+        <v>176.1525834652572</v>
       </c>
       <c r="J98" t="n">
-        <v>9.000057867786236</v>
+        <v>10.31533469854956</v>
       </c>
       <c r="K98" t="n">
-        <v>65.14528864031445</v>
+        <v>0.104583320210736</v>
       </c>
       <c r="L98" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>47.80842912234141</v>
       </c>
       <c r="M98" t="n">
-        <v>2.172296702451471</v>
+        <v>0.3141417985649149</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>0.9650910960063801</v>
+        <v>0.9992326166729234</v>
       </c>
       <c r="P98" t="n">
-        <v>0.000755873576752319</v>
+        <v>0.001507563620875813</v>
       </c>
       <c r="Q98" t="n">
-        <v>940.8867899053899</v>
+        <v>805.1864964063076</v>
       </c>
       <c r="R98" t="n">
-        <v>187.6124485687417</v>
+        <v>150.0000472887688</v>
       </c>
       <c r="S98" t="n">
-        <v>9.000057869185591</v>
+        <v>10.57059963391205</v>
       </c>
       <c r="T98" t="n">
-        <v>77.18881104735158</v>
+        <v>102.7218476183858</v>
       </c>
       <c r="U98" t="n">
-        <v>0.05607341023954859</v>
+        <v>21.65589294585297</v>
       </c>
       <c r="V98" t="n">
-        <v>2.172296703850826</v>
+        <v>0.05887686320242302</v>
       </c>
       <c r="W98" t="b">
         <v>1</v>
@@ -7620,68 +7620,68 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Stains</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>952.731947911775</v>
+        <v>868.4370442567305</v>
       </c>
       <c r="D99" t="n">
-        <v>10.25947882308648</v>
+        <v>11.02975816430903</v>
       </c>
       <c r="E99" t="n">
-        <v>109.9704251528463</v>
+        <v>213.1212320917566</v>
       </c>
       <c r="F99" t="n">
-        <v>0.898436963558197</v>
+        <v>0.5927297472953796</v>
       </c>
       <c r="G99" t="n">
-        <v>0.04618793725967407</v>
+        <v>0.005909173749387264</v>
       </c>
       <c r="H99" t="n">
-        <v>886.5914798097971</v>
+        <v>922.9741913807004</v>
       </c>
       <c r="I99" t="n">
-        <v>169.79456248342</v>
+        <v>213.1212320917566</v>
       </c>
       <c r="J99" t="n">
-        <v>13.58228088953019</v>
+        <v>11.02975816430903</v>
       </c>
       <c r="K99" t="n">
-        <v>66.14046810197794</v>
+        <v>54.53714712396993</v>
       </c>
       <c r="L99" t="n">
-        <v>59.82413733057372</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M99" t="n">
-        <v>3.322802066443717</v>
+        <v>0</v>
       </c>
       <c r="N99" t="b">
         <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>0.9999703457428308</v>
+        <v>0.8558815783183614</v>
       </c>
       <c r="P99" t="n">
-        <v>0.001842767007610021</v>
+        <v>0.0006911895152332209</v>
       </c>
       <c r="Q99" t="n">
-        <v>809.1995894073517</v>
+        <v>941.0594335434713</v>
       </c>
       <c r="R99" t="n">
-        <v>150.0000472883041</v>
+        <v>211.6327696334628</v>
       </c>
       <c r="S99" t="n">
-        <v>10.18735266177704</v>
+        <v>10.97200158742111</v>
       </c>
       <c r="T99" t="n">
-        <v>143.5323585044233</v>
+        <v>72.62238928674083</v>
       </c>
       <c r="U99" t="n">
-        <v>40.02962213545781</v>
+        <v>1.488462458293782</v>
       </c>
       <c r="V99" t="n">
-        <v>0.07212616130943239</v>
+        <v>0.05775657688791647</v>
       </c>
       <c r="W99" t="b">
         <v>1</v>
@@ -7693,68 +7693,68 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>946.7441418785542</v>
+        <v>969.1507432655953</v>
       </c>
       <c r="D100" t="n">
-        <v>10.76339307958197</v>
+        <v>15.11779471417397</v>
       </c>
       <c r="E100" t="n">
-        <v>157.9451574629643</v>
+        <v>205.7625139202212</v>
       </c>
       <c r="F100" t="n">
-        <v>0.898436963558197</v>
+        <v>0.7224258780479431</v>
       </c>
       <c r="G100" t="n">
-        <v>0.004876246210187674</v>
+        <v>0.008410884998738766</v>
       </c>
       <c r="H100" t="n">
-        <v>910.5852869727195</v>
+        <v>969.1506879267129</v>
       </c>
       <c r="I100" t="n">
-        <v>179.2303424768062</v>
+        <v>205.7625283762321</v>
       </c>
       <c r="J100" t="n">
-        <v>14.04003495027137</v>
+        <v>11.77728774237585</v>
       </c>
       <c r="K100" t="n">
-        <v>36.15885490583469</v>
+        <v>5.533888247555296e-05</v>
       </c>
       <c r="L100" t="n">
-        <v>21.28518501384193</v>
+        <v>1.445601091631943e-05</v>
       </c>
       <c r="M100" t="n">
-        <v>3.276641870689403</v>
+        <v>3.340506971798114</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>0.9433857230399106</v>
+        <v>0.9977736881314933</v>
       </c>
       <c r="P100" t="n">
-        <v>0.001365727128748474</v>
+        <v>0.002164460308084747</v>
       </c>
       <c r="Q100" t="n">
-        <v>833.2154425500859</v>
+        <v>816.361870961309</v>
       </c>
       <c r="R100" t="n">
-        <v>164.5073351852222</v>
+        <v>206.1771441246076</v>
       </c>
       <c r="S100" t="n">
-        <v>10.71326165807914</v>
+        <v>14.17970498194673</v>
       </c>
       <c r="T100" t="n">
-        <v>113.5286993284683</v>
+        <v>152.7888723042863</v>
       </c>
       <c r="U100" t="n">
-        <v>6.562177722257928</v>
+        <v>0.4146302043864125</v>
       </c>
       <c r="V100" t="n">
-        <v>0.05013142150282768</v>
+        <v>0.9380897322272368</v>
       </c>
       <c r="W100" t="b">
         <v>1</v>
@@ -7766,68 +7766,68 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>917.8748642319608</v>
+        <v>964.50191573696</v>
       </c>
       <c r="D101" t="n">
-        <v>10.70379588375082</v>
+        <v>10.0773637302841</v>
       </c>
       <c r="E101" t="n">
-        <v>276.5087578943281</v>
+        <v>133.3308696860855</v>
       </c>
       <c r="F101" t="n">
-        <v>0.8160291314125061</v>
+        <v>0.7905983924865723</v>
       </c>
       <c r="G101" t="n">
-        <v>0.003728296607732773</v>
+        <v>0.01447403151541948</v>
       </c>
       <c r="H101" t="n">
-        <v>916.5766037826769</v>
+        <v>964.5019160363886</v>
       </c>
       <c r="I101" t="n">
-        <v>224.7360514776903</v>
+        <v>176.1525536347904</v>
       </c>
       <c r="J101" t="n">
-        <v>10.70385752861269</v>
+        <v>10.07736324053892</v>
       </c>
       <c r="K101" t="n">
-        <v>1.29826044928393</v>
+        <v>2.994286205648677e-07</v>
       </c>
       <c r="L101" t="n">
-        <v>51.77270641663782</v>
+        <v>42.8216839487049</v>
       </c>
       <c r="M101" t="n">
-        <v>6.164486187287821e-05</v>
+        <v>4.897451741925352e-07</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>0.9998597021223778</v>
+        <v>0.9995946372735726</v>
       </c>
       <c r="P101" t="n">
-        <v>0.002039819975799758</v>
+        <v>0.001910393958052752</v>
       </c>
       <c r="Q101" t="n">
-        <v>800.0004553692589</v>
+        <v>810.4329883279124</v>
       </c>
       <c r="R101" t="n">
-        <v>245.8032933292593</v>
+        <v>150.0000472877453</v>
       </c>
       <c r="S101" t="n">
-        <v>10.73301244679471</v>
+        <v>10.00214042873084</v>
       </c>
       <c r="T101" t="n">
-        <v>117.8744088627019</v>
+        <v>154.0689274090475</v>
       </c>
       <c r="U101" t="n">
-        <v>30.70546456506884</v>
+        <v>16.66917760165975</v>
       </c>
       <c r="V101" t="n">
-        <v>0.02921656304389231</v>
+        <v>0.07522330155325818</v>
       </c>
       <c r="W101" t="b">
         <v>1</v>

--- a/export_dati/06_Step6_Simulazione_Massiva_100.xlsx
+++ b/export_dati/06_Step6_Simulazione_Massiva_100.xlsx
@@ -579,28 +579,28 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.956171780136097</v>
+        <v>0.9269339875444544</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0004810095281391377</v>
+        <v>0.000571814265090467</v>
       </c>
       <c r="Q2" t="n">
-        <v>955.4964160289745</v>
+        <v>953.4739960882771</v>
       </c>
       <c r="R2" t="n">
-        <v>190.2442073593656</v>
+        <v>190.3160917381414</v>
       </c>
       <c r="S2" t="n">
-        <v>9.000057868482628</v>
+        <v>9.000057869985689</v>
       </c>
       <c r="T2" t="n">
-        <v>75.08701968739467</v>
+        <v>77.1094396280921</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2321761094222836</v>
+        <v>0.3040604881981608</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2426218712823331</v>
+        <v>0.2426218727853939</v>
       </c>
       <c r="W2" t="b">
         <v>1</v>
@@ -652,28 +652,28 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9997066634307018</v>
+        <v>0.9995815054235507</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001985356215246104</v>
+        <v>0.002070304312487993</v>
       </c>
       <c r="Q3" t="n">
-        <v>804.6688490286708</v>
+        <v>805.1042191866012</v>
       </c>
       <c r="R3" t="n">
-        <v>150.0000472862362</v>
+        <v>150.0000472891128</v>
       </c>
       <c r="S3" t="n">
-        <v>11.5068767280431</v>
+        <v>11.53170340464211</v>
       </c>
       <c r="T3" t="n">
-        <v>154.0576243648098</v>
+        <v>153.6222542068795</v>
       </c>
       <c r="U3" t="n">
-        <v>18.45154163607347</v>
+        <v>18.45154163895003</v>
       </c>
       <c r="V3" t="n">
-        <v>0.09123416770866299</v>
+        <v>0.06640749110964705</v>
       </c>
       <c r="W3" t="b">
         <v>1</v>
@@ -725,28 +725,28 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9119186050945739</v>
+        <v>0.9262714254362029</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0005032440915117498</v>
+        <v>0.0005536665631668084</v>
       </c>
       <c r="Q4" t="n">
-        <v>943.9718546444117</v>
+        <v>947.7381755119324</v>
       </c>
       <c r="R4" t="n">
-        <v>192.7318937691159</v>
+        <v>192.8577935277279</v>
       </c>
       <c r="S4" t="n">
-        <v>9.000057868898709</v>
+        <v>9.000057869167906</v>
       </c>
       <c r="T4" t="n">
-        <v>54.18216649350757</v>
+        <v>57.94848736102824</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1606664320032962</v>
+        <v>0.0347666733912888</v>
       </c>
       <c r="V4" t="n">
-        <v>1.80093589360868</v>
+        <v>1.800935893877877</v>
       </c>
       <c r="W4" t="b">
         <v>1</v>
@@ -798,28 +798,28 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.968609665537531</v>
+        <v>0.9672264356887684</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00142754828692048</v>
+        <v>0.001513710548740302</v>
       </c>
       <c r="Q5" t="n">
-        <v>829.4624329574276</v>
+        <v>828.7038736334952</v>
       </c>
       <c r="R5" t="n">
-        <v>161.2327367623647</v>
+        <v>161.248687507975</v>
       </c>
       <c r="S5" t="n">
-        <v>10.04411720692117</v>
+        <v>10.05310231141007</v>
       </c>
       <c r="T5" t="n">
-        <v>117.9472221053036</v>
+        <v>118.705781429236</v>
       </c>
       <c r="U5" t="n">
-        <v>6.391617779754853</v>
+        <v>6.40756852536515</v>
       </c>
       <c r="V5" t="n">
-        <v>0.055008585554992</v>
+        <v>0.04602348106608645</v>
       </c>
       <c r="W5" t="b">
         <v>1</v>
@@ -871,28 +871,28 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.997740922229679</v>
+        <v>0.9980126380382254</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001539844554627996</v>
+        <v>0.001634785038524356</v>
       </c>
       <c r="Q6" t="n">
-        <v>808.7030814424336</v>
+        <v>807.8401037577198</v>
       </c>
       <c r="R6" t="n">
-        <v>150.0000472875976</v>
+        <v>150.000047288629</v>
       </c>
       <c r="S6" t="n">
-        <v>9.830873787286583</v>
+        <v>9.836657571320121</v>
       </c>
       <c r="T6" t="n">
-        <v>109.9577311342193</v>
+        <v>110.8207088189331</v>
       </c>
       <c r="U6" t="n">
-        <v>12.77362124946677</v>
+        <v>12.77362125049811</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06027233198071613</v>
+        <v>0.05448854794717839</v>
       </c>
       <c r="W6" t="b">
         <v>1</v>
@@ -944,25 +944,25 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9728707555440302</v>
+        <v>0.9623213690697382</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001355710254997826</v>
+        <v>0.001502235201471605</v>
       </c>
       <c r="Q7" t="n">
-        <v>956.2203661744913</v>
+        <v>961.6812693999583</v>
       </c>
       <c r="R7" t="n">
-        <v>201.6542691298841</v>
+        <v>201.9872809663549</v>
       </c>
       <c r="S7" t="n">
         <v>9.000057869254071</v>
       </c>
       <c r="T7" t="n">
-        <v>17.07442091465214</v>
+        <v>11.61351768918519</v>
       </c>
       <c r="U7" t="n">
-        <v>2.207846416740949</v>
+        <v>1.874834580270175</v>
       </c>
       <c r="V7" t="n">
         <v>3.527254113895973</v>
@@ -1017,28 +1017,28 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9000178739341447</v>
+        <v>0.9182172922384561</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0005614290808879055</v>
+        <v>0.0006013376516738945</v>
       </c>
       <c r="Q8" t="n">
-        <v>948.2918192091475</v>
+        <v>951.2388149432117</v>
       </c>
       <c r="R8" t="n">
-        <v>212.06565140531</v>
+        <v>212.1911934077939</v>
       </c>
       <c r="S8" t="n">
-        <v>9.000057826406119</v>
+        <v>9.000057843535902</v>
       </c>
       <c r="T8" t="n">
-        <v>56.59888383306054</v>
+        <v>59.54587956712464</v>
       </c>
       <c r="U8" t="n">
-        <v>1.561756864679637</v>
+        <v>1.436214862195669</v>
       </c>
       <c r="V8" t="n">
-        <v>2.470583089997595</v>
+        <v>2.470583107127378</v>
       </c>
       <c r="W8" t="b">
         <v>1</v>
@@ -1090,28 +1090,28 @@
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.517431071606103</v>
+        <v>0.5041579765801472</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001140668589984197</v>
+        <v>0.001215904094541128</v>
       </c>
       <c r="Q9" t="n">
-        <v>856.9509284845999</v>
+        <v>855.4096393258563</v>
       </c>
       <c r="R9" t="n">
-        <v>175.3155423370213</v>
+        <v>175.2284062726977</v>
       </c>
       <c r="S9" t="n">
-        <v>9.877351462356494</v>
+        <v>9.884756168044577</v>
       </c>
       <c r="T9" t="n">
-        <v>105.8471306584418</v>
+        <v>107.3884198171853</v>
       </c>
       <c r="U9" t="n">
-        <v>6.906422472473736</v>
+        <v>6.819286408150163</v>
       </c>
       <c r="V9" t="n">
-        <v>0.04447860150771277</v>
+        <v>0.0370738958196295</v>
       </c>
       <c r="W9" t="b">
         <v>1</v>
@@ -1163,28 +1163,28 @@
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9999054812485227</v>
+        <v>0.9999295997973171</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001749433898562091</v>
+        <v>0.001853967366114005</v>
       </c>
       <c r="Q10" t="n">
-        <v>811.3979239211729</v>
+        <v>810.4950795130085</v>
       </c>
       <c r="R10" t="n">
-        <v>150.0000472865753</v>
+        <v>150.0000472884115</v>
       </c>
       <c r="S10" t="n">
-        <v>9.582298760453645</v>
+        <v>9.586667418640062</v>
       </c>
       <c r="T10" t="n">
-        <v>136.6185588032394</v>
+        <v>137.5214032114038</v>
       </c>
       <c r="U10" t="n">
-        <v>30.55720308859259</v>
+        <v>30.55720309042886</v>
       </c>
       <c r="V10" t="n">
-        <v>0.07053975712790539</v>
+        <v>0.06617109894148854</v>
       </c>
       <c r="W10" t="b">
         <v>1</v>
@@ -1236,28 +1236,28 @@
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9781872632768009</v>
+        <v>0.9797486231851009</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0007436002217320406</v>
+        <v>0.0008077019984873753</v>
       </c>
       <c r="Q11" t="n">
-        <v>941.0553301147726</v>
+        <v>945.1905645476064</v>
       </c>
       <c r="R11" t="n">
-        <v>185.8904182960312</v>
+        <v>186.1041766319713</v>
       </c>
       <c r="S11" t="n">
-        <v>9.000057869709417</v>
+        <v>9.000057869339136</v>
       </c>
       <c r="T11" t="n">
-        <v>75.53183599067711</v>
+        <v>79.66707042351095</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1410860474744311</v>
+        <v>0.3548443834145871</v>
       </c>
       <c r="V11" t="n">
-        <v>3.206001252659284</v>
+        <v>3.206001252289003</v>
       </c>
       <c r="W11" t="b">
         <v>1</v>
@@ -1309,28 +1309,28 @@
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0.995237948122055</v>
+        <v>0.995183737798693</v>
       </c>
       <c r="P12" t="n">
-        <v>0.001712255582205869</v>
+        <v>0.001812900675894847</v>
       </c>
       <c r="Q12" t="n">
-        <v>815.7502598479576</v>
+        <v>814.9601914464938</v>
       </c>
       <c r="R12" t="n">
-        <v>152.5542326571138</v>
+        <v>152.6025294723253</v>
       </c>
       <c r="S12" t="n">
-        <v>9.67417422161274</v>
+        <v>9.680022241534479</v>
       </c>
       <c r="T12" t="n">
-        <v>137.4116376693786</v>
+        <v>138.2017060708424</v>
       </c>
       <c r="U12" t="n">
-        <v>6.398008715939682</v>
+        <v>6.446305531151211</v>
       </c>
       <c r="V12" t="n">
-        <v>0.06909197490720764</v>
+        <v>0.06324395498546842</v>
       </c>
       <c r="W12" t="b">
         <v>1</v>
@@ -1382,28 +1382,28 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.97331245967028</v>
+        <v>0.9655222473680127</v>
       </c>
       <c r="P13" t="n">
-        <v>0.001639342335084964</v>
+        <v>0.001636339556408885</v>
       </c>
       <c r="Q13" t="n">
-        <v>829.9207677380336</v>
+        <v>830.5841640560996</v>
       </c>
       <c r="R13" t="n">
-        <v>209.4720892544866</v>
+        <v>209.465373291986</v>
       </c>
       <c r="S13" t="n">
-        <v>13.49981776422353</v>
+        <v>13.53743906050636</v>
       </c>
       <c r="T13" t="n">
-        <v>115.3002713246382</v>
+        <v>114.6368750065723</v>
       </c>
       <c r="U13" t="n">
-        <v>0.04168283887622692</v>
+        <v>0.03496687637556306</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6438183624257761</v>
+        <v>0.6061970661429488</v>
       </c>
       <c r="W13" t="b">
         <v>1</v>
@@ -1455,28 +1455,28 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9752882041840766</v>
+        <v>0.9445556656479172</v>
       </c>
       <c r="P14" t="n">
-        <v>0.00145628616486667</v>
+        <v>0.00155615750935175</v>
       </c>
       <c r="Q14" t="n">
-        <v>846.9423118980399</v>
+        <v>845.1653073815638</v>
       </c>
       <c r="R14" t="n">
-        <v>226.2668238192292</v>
+        <v>226.8936099544382</v>
       </c>
       <c r="S14" t="n">
-        <v>9.677938548165491</v>
+        <v>9.673316028752401</v>
       </c>
       <c r="T14" t="n">
-        <v>124.1207451686182</v>
+        <v>125.8977496850943</v>
       </c>
       <c r="U14" t="n">
-        <v>20.29929456487358</v>
+        <v>19.67250842966456</v>
       </c>
       <c r="V14" t="n">
-        <v>0.04394158746817567</v>
+        <v>0.04856410688126545</v>
       </c>
       <c r="W14" t="b">
         <v>1</v>
@@ -1528,28 +1528,28 @@
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9998597021223778</v>
+        <v>0.9997107748479873</v>
       </c>
       <c r="P15" t="n">
-        <v>0.002039819975799758</v>
+        <v>0.002140514699298466</v>
       </c>
       <c r="Q15" t="n">
         <v>800.0004553692589</v>
       </c>
       <c r="R15" t="n">
-        <v>245.8032933292593</v>
+        <v>246.5507300037852</v>
       </c>
       <c r="S15" t="n">
-        <v>10.73301244679471</v>
+        <v>10.7298153553938</v>
       </c>
       <c r="T15" t="n">
         <v>117.8744088627019</v>
       </c>
       <c r="U15" t="n">
-        <v>30.70546456506884</v>
+        <v>29.95802789054292</v>
       </c>
       <c r="V15" t="n">
-        <v>0.02921656304389231</v>
+        <v>0.02601947164297869</v>
       </c>
       <c r="W15" t="b">
         <v>1</v>
@@ -1601,28 +1601,28 @@
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9986370695432607</v>
+        <v>0.9987290286610602</v>
       </c>
       <c r="P16" t="n">
-        <v>0.001930335722960556</v>
+        <v>0.002039156083297489</v>
       </c>
       <c r="Q16" t="n">
-        <v>815.6503322721229</v>
+        <v>814.7044667649247</v>
       </c>
       <c r="R16" t="n">
-        <v>150.0000472898313</v>
+        <v>150.0000472905103</v>
       </c>
       <c r="S16" t="n">
-        <v>9.000057868752561</v>
+        <v>9.000057869583411</v>
       </c>
       <c r="T16" t="n">
-        <v>168.7304799847135</v>
+        <v>169.6763454919117</v>
       </c>
       <c r="U16" t="n">
-        <v>12.10467823550306</v>
+        <v>12.10467823618202</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6139593242315531</v>
+        <v>0.6139593250624031</v>
       </c>
       <c r="W16" t="b">
         <v>1</v>
@@ -1674,28 +1674,28 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9076591737209158</v>
+        <v>0.9065675541941576</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0008344577848599164</v>
+        <v>0.0008785978085595368</v>
       </c>
       <c r="Q17" t="n">
-        <v>947.9049189646879</v>
+        <v>950.6607647402244</v>
       </c>
       <c r="R17" t="n">
-        <v>217.3530367296672</v>
+        <v>217.6032788711231</v>
       </c>
       <c r="S17" t="n">
-        <v>9.000057855392345</v>
+        <v>9.000057803562907</v>
       </c>
       <c r="T17" t="n">
-        <v>77.82555085714296</v>
+        <v>80.58139663267946</v>
       </c>
       <c r="U17" t="n">
-        <v>2.786263574230958</v>
+        <v>2.536021432775016</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9511389945188462</v>
+        <v>0.9511389426894077</v>
       </c>
       <c r="W17" t="b">
         <v>1</v>
@@ -1747,28 +1747,28 @@
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8532851020548059</v>
+        <v>0.8438579327110084</v>
       </c>
       <c r="P18" t="n">
-        <v>0.001314022520981928</v>
+        <v>0.001401562631860155</v>
       </c>
       <c r="Q18" t="n">
-        <v>847.6279854591171</v>
+        <v>846.2614605511525</v>
       </c>
       <c r="R18" t="n">
-        <v>169.0386082606258</v>
+        <v>169.0030238183578</v>
       </c>
       <c r="S18" t="n">
-        <v>9.364004924983192</v>
+        <v>9.368175873444359</v>
       </c>
       <c r="T18" t="n">
-        <v>122.8047188174351</v>
+        <v>124.1712437253997</v>
       </c>
       <c r="U18" t="n">
-        <v>7.035968319026836</v>
+        <v>7.000383876758832</v>
       </c>
       <c r="V18" t="n">
-        <v>0.06120184780149174</v>
+        <v>0.05703089934032413</v>
       </c>
       <c r="W18" t="b">
         <v>1</v>
@@ -1820,28 +1820,28 @@
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7036991484062372</v>
+        <v>0.6238866850540444</v>
       </c>
       <c r="P19" t="n">
-        <v>0.001507485916176177</v>
+        <v>0.001518533829946619</v>
       </c>
       <c r="Q19" t="n">
-        <v>848.7005209729417</v>
+        <v>848.3648785256021</v>
       </c>
       <c r="R19" t="n">
-        <v>220.4450357726695</v>
+        <v>220.2906712587289</v>
       </c>
       <c r="S19" t="n">
-        <v>12.66377058813266</v>
+        <v>12.69451968361827</v>
       </c>
       <c r="T19" t="n">
-        <v>115.2075285180642</v>
+        <v>115.5431709654039</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8250096162605018</v>
+        <v>0.9793741302010233</v>
       </c>
       <c r="V19" t="n">
-        <v>0.522804323678395</v>
+        <v>0.4920552281927897</v>
       </c>
       <c r="W19" t="b">
         <v>1</v>
@@ -1893,28 +1893,28 @@
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7140772021470611</v>
+        <v>0.6985852681374433</v>
       </c>
       <c r="P20" t="n">
-        <v>0.0008139230819724353</v>
+        <v>0.0008680252345416306</v>
       </c>
       <c r="Q20" t="n">
-        <v>941.7204884230094</v>
+        <v>945.2299071716528</v>
       </c>
       <c r="R20" t="n">
-        <v>201.2469894517664</v>
+        <v>201.4248419267716</v>
       </c>
       <c r="S20" t="n">
-        <v>9.000057866320244</v>
+        <v>9.000057867527333</v>
       </c>
       <c r="T20" t="n">
-        <v>83.12507799165462</v>
+        <v>86.634496740298</v>
       </c>
       <c r="U20" t="n">
-        <v>1.042284575261107</v>
+        <v>0.8644321002558968</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1693264396429104</v>
+        <v>0.1693264408499999</v>
       </c>
       <c r="W20" t="b">
         <v>1</v>
@@ -1966,28 +1966,28 @@
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9964912973813387</v>
+        <v>0.9969749901955914</v>
       </c>
       <c r="P21" t="n">
-        <v>0.001586709028044793</v>
+        <v>0.001680591176466929</v>
       </c>
       <c r="Q21" t="n">
-        <v>813.4494220728872</v>
+        <v>812.4237439117898</v>
       </c>
       <c r="R21" t="n">
-        <v>150.0000472903582</v>
+        <v>150.0000472902463</v>
       </c>
       <c r="S21" t="n">
-        <v>9.000057869397292</v>
+        <v>9.000057869260331</v>
       </c>
       <c r="T21" t="n">
-        <v>122.1191962803123</v>
+        <v>123.1448744414097</v>
       </c>
       <c r="U21" t="n">
-        <v>9.101011598585927</v>
+        <v>9.101011598474003</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3192298272294156</v>
+        <v>0.319229827092455</v>
       </c>
       <c r="W21" t="b">
         <v>1</v>
@@ -2039,28 +2039,28 @@
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9103170189198628</v>
+        <v>0.9121806772260779</v>
       </c>
       <c r="P22" t="n">
-        <v>0.001248655968202007</v>
+        <v>0.00132024284695085</v>
       </c>
       <c r="Q22" t="n">
-        <v>831.8409425958835</v>
+        <v>831.4027298434457</v>
       </c>
       <c r="R22" t="n">
-        <v>164.2946129922157</v>
+        <v>164.2830393731329</v>
       </c>
       <c r="S22" t="n">
-        <v>10.70147628368998</v>
+        <v>10.71289817887899</v>
       </c>
       <c r="T22" t="n">
-        <v>99.11272978934062</v>
+        <v>99.55094254177834</v>
       </c>
       <c r="U22" t="n">
-        <v>5.973084582992129</v>
+        <v>5.961510963909262</v>
       </c>
       <c r="V22" t="n">
-        <v>0.04558254413414176</v>
+        <v>0.03416064894513049</v>
       </c>
       <c r="W22" t="b">
         <v>1</v>
@@ -2112,28 +2112,28 @@
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8934762826924519</v>
+        <v>0.8955804872098443</v>
       </c>
       <c r="P23" t="n">
-        <v>0.001096416413131947</v>
+        <v>0.001188780437316197</v>
       </c>
       <c r="Q23" t="n">
-        <v>938.7414325940305</v>
+        <v>943.457495505261</v>
       </c>
       <c r="R23" t="n">
-        <v>174.6860315755196</v>
+        <v>174.9044418097916</v>
       </c>
       <c r="S23" t="n">
-        <v>9.000057869447067</v>
+        <v>9.000057869520404</v>
       </c>
       <c r="T23" t="n">
-        <v>98.83855595357329</v>
+        <v>103.5546188648038</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1256588752985408</v>
+        <v>0.09275135897345876</v>
       </c>
       <c r="V23" t="n">
-        <v>1.59520191946742</v>
+        <v>1.595201919540757</v>
       </c>
       <c r="W23" t="b">
         <v>1</v>
@@ -2185,28 +2185,28 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9699037175754671</v>
+        <v>0.9735310436294481</v>
       </c>
       <c r="P24" t="n">
-        <v>0.0008896991599113631</v>
+        <v>0.0009317527878463582</v>
       </c>
       <c r="Q24" t="n">
-        <v>950.9732542094079</v>
+        <v>953.3226362059706</v>
       </c>
       <c r="R24" t="n">
-        <v>223.616543468521</v>
+        <v>223.6717468361445</v>
       </c>
       <c r="S24" t="n">
-        <v>9.000057788147537</v>
+        <v>9.000057805709503</v>
       </c>
       <c r="T24" t="n">
-        <v>78.02197782057385</v>
+        <v>80.37135981713664</v>
       </c>
       <c r="U24" t="n">
-        <v>2.812561357722046</v>
+        <v>2.757357990098569</v>
       </c>
       <c r="V24" t="n">
-        <v>2.352193078394395</v>
+        <v>2.352193095956361</v>
       </c>
       <c r="W24" t="b">
         <v>1</v>
@@ -2258,28 +2258,28 @@
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9993959460682591</v>
+        <v>0.9994425789695852</v>
       </c>
       <c r="P25" t="n">
-        <v>0.00183165309562486</v>
+        <v>0.001939396499236482</v>
       </c>
       <c r="Q25" t="n">
-        <v>812.7167930930882</v>
+        <v>811.7917865849433</v>
       </c>
       <c r="R25" t="n">
-        <v>150.0000472868396</v>
+        <v>150.0000472878515</v>
       </c>
       <c r="S25" t="n">
-        <v>9.426201575276425</v>
+        <v>9.429234185915144</v>
       </c>
       <c r="T25" t="n">
-        <v>149.0243575988026</v>
+        <v>149.9493641069474</v>
       </c>
       <c r="U25" t="n">
-        <v>15.19947002229327</v>
+        <v>15.1994700233052</v>
       </c>
       <c r="V25" t="n">
-        <v>0.07533434218273172</v>
+        <v>0.07230173154401243</v>
       </c>
       <c r="W25" t="b">
         <v>1</v>
@@ -2331,28 +2331,28 @@
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.9995206905356393</v>
+        <v>0.9995206438039369</v>
       </c>
       <c r="P26" t="n">
-        <v>0.001851875149642966</v>
+        <v>0.001958679987557739</v>
       </c>
       <c r="Q26" t="n">
-        <v>809.2262114316984</v>
+        <v>808.6255391234719</v>
       </c>
       <c r="R26" t="n">
-        <v>150.0000472882507</v>
+        <v>150.0000472896715</v>
       </c>
       <c r="S26" t="n">
-        <v>10.19446579512171</v>
+        <v>10.2056190620028</v>
       </c>
       <c r="T26" t="n">
-        <v>144.6614745998484</v>
+        <v>145.2621469080749</v>
       </c>
       <c r="U26" t="n">
-        <v>16.09184295392791</v>
+        <v>16.09184295534871</v>
       </c>
       <c r="V26" t="n">
-        <v>0.07250998800584973</v>
+        <v>0.06135672112475987</v>
       </c>
       <c r="W26" t="b">
         <v>1</v>
@@ -2404,28 +2404,28 @@
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>0.4660404635555797</v>
+        <v>0.5207946968687837</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0004958690725527312</v>
+        <v>0.0005391750645429849</v>
       </c>
       <c r="Q27" t="n">
-        <v>937.2480469120045</v>
+        <v>940.8367047258195</v>
       </c>
       <c r="R27" t="n">
-        <v>205.5922209695499</v>
+        <v>205.6986441614883</v>
       </c>
       <c r="S27" t="n">
-        <v>9.635460415218885</v>
+        <v>9.63648382118469</v>
       </c>
       <c r="T27" t="n">
-        <v>58.20934407463233</v>
+        <v>61.79800188844729</v>
       </c>
       <c r="U27" t="n">
-        <v>0.6661656058071799</v>
+        <v>0.5597424138687472</v>
       </c>
       <c r="V27" t="n">
-        <v>0.01141940477866754</v>
+        <v>0.01039599881286257</v>
       </c>
       <c r="W27" t="b">
         <v>1</v>
@@ -2477,25 +2477,25 @@
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>0.9959965380304859</v>
+        <v>0.9944839731230863</v>
       </c>
       <c r="P28" t="n">
-        <v>0.001696458335149723</v>
+        <v>0.001860325997298282</v>
       </c>
       <c r="Q28" t="n">
-        <v>947.1872232457737</v>
+        <v>953.7968869359587</v>
       </c>
       <c r="R28" t="n">
-        <v>208.1041258682009</v>
+        <v>208.4638778792243</v>
       </c>
       <c r="S28" t="n">
         <v>9.000057869254071</v>
       </c>
       <c r="T28" t="n">
-        <v>7.515482741550045</v>
+        <v>0.9058190513650288</v>
       </c>
       <c r="U28" t="n">
-        <v>4.223716853165911</v>
+        <v>3.863964842142508</v>
       </c>
       <c r="V28" t="n">
         <v>4.45621789297173</v>
@@ -2550,28 +2550,28 @@
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8845784340001017</v>
+        <v>0.8977436780447999</v>
       </c>
       <c r="P29" t="n">
-        <v>0.0008550181598568042</v>
+        <v>0.0009180601509068569</v>
       </c>
       <c r="Q29" t="n">
-        <v>935.3876622886237</v>
+        <v>939.452313146076</v>
       </c>
       <c r="R29" t="n">
-        <v>194.8438176612062</v>
+        <v>195.1565499196259</v>
       </c>
       <c r="S29" t="n">
-        <v>10.68937165559022</v>
+        <v>10.6852278685776</v>
       </c>
       <c r="T29" t="n">
-        <v>90.23079915656763</v>
+        <v>94.29545001401993</v>
       </c>
       <c r="U29" t="n">
-        <v>0.1101811223060167</v>
+        <v>0.2025511361136694</v>
       </c>
       <c r="V29" t="n">
-        <v>0.0582385896818316</v>
+        <v>0.06238237669444935</v>
       </c>
       <c r="W29" t="b">
         <v>1</v>
@@ -2623,28 +2623,28 @@
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>0.9924333779233867</v>
+        <v>0.9898295967989218</v>
       </c>
       <c r="P30" t="n">
-        <v>0.001881050998491252</v>
+        <v>0.001872209900798662</v>
       </c>
       <c r="Q30" t="n">
-        <v>823.4120515472366</v>
+        <v>824.2807290463936</v>
       </c>
       <c r="R30" t="n">
-        <v>208.8093206535109</v>
+        <v>208.812053473411</v>
       </c>
       <c r="S30" t="n">
-        <v>13.83037558604234</v>
+        <v>13.87657798915766</v>
       </c>
       <c r="T30" t="n">
-        <v>131.5658278354285</v>
+        <v>130.6971503362715</v>
       </c>
       <c r="U30" t="n">
-        <v>0.1374093958977483</v>
+        <v>0.1401422157978232</v>
       </c>
       <c r="V30" t="n">
-        <v>0.7717934096507388</v>
+        <v>0.7255910065354207</v>
       </c>
       <c r="W30" t="b">
         <v>1</v>
@@ -2696,28 +2696,28 @@
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0.6619208421077007</v>
+        <v>0.672209379656895</v>
       </c>
       <c r="P31" t="n">
-        <v>0.0006130186329304304</v>
+        <v>0.0006696179529128564</v>
       </c>
       <c r="Q31" t="n">
-        <v>942.4119440116023</v>
+        <v>946.352413746896</v>
       </c>
       <c r="R31" t="n">
-        <v>189.5486254949676</v>
+        <v>189.7135700591255</v>
       </c>
       <c r="S31" t="n">
-        <v>9.000057869204142</v>
+        <v>9.000057869411549</v>
       </c>
       <c r="T31" t="n">
-        <v>64.49119521341765</v>
+        <v>68.43166494871139</v>
       </c>
       <c r="U31" t="n">
-        <v>0.02827217815990934</v>
+        <v>0.1366723859980254</v>
       </c>
       <c r="V31" t="n">
-        <v>0.2276891805434627</v>
+        <v>0.2276891807508701</v>
       </c>
       <c r="W31" t="b">
         <v>1</v>
@@ -2769,28 +2769,28 @@
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>0.9978983705744172</v>
+        <v>0.9972387862937727</v>
       </c>
       <c r="P32" t="n">
-        <v>0.00194906253253848</v>
+        <v>0.001926654321043025</v>
       </c>
       <c r="Q32" t="n">
-        <v>809.196578494232</v>
+        <v>810.5218297833327</v>
       </c>
       <c r="R32" t="n">
-        <v>205.17306135039</v>
+        <v>205.1960549879077</v>
       </c>
       <c r="S32" t="n">
-        <v>14.40282371194543</v>
+        <v>14.45904671983305</v>
       </c>
       <c r="T32" t="n">
-        <v>122.0715813808952</v>
+        <v>120.7463300917944</v>
       </c>
       <c r="U32" t="n">
-        <v>0.384311649865424</v>
+        <v>0.4073052873831955</v>
       </c>
       <c r="V32" t="n">
-        <v>0.8397780927662843</v>
+        <v>0.7835550848786639</v>
       </c>
       <c r="W32" t="b">
         <v>1</v>
@@ -2842,28 +2842,28 @@
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>0.9994829773662345</v>
+        <v>0.9995680016057145</v>
       </c>
       <c r="P33" t="n">
-        <v>0.001782489477256973</v>
+        <v>0.00188484686738011</v>
       </c>
       <c r="Q33" t="n">
-        <v>814.7624771308967</v>
+        <v>813.7834354726926</v>
       </c>
       <c r="R33" t="n">
-        <v>150.0000472903334</v>
+        <v>150.0000472903855</v>
       </c>
       <c r="S33" t="n">
-        <v>9.000057869366948</v>
+        <v>9.000057869430696</v>
       </c>
       <c r="T33" t="n">
-        <v>147.310437648318</v>
+        <v>148.2894793065221</v>
       </c>
       <c r="U33" t="n">
-        <v>17.40845829230074</v>
+        <v>17.40845829235283</v>
       </c>
       <c r="V33" t="n">
-        <v>0.09606991723800107</v>
+        <v>0.09606991730174919</v>
       </c>
       <c r="W33" t="b">
         <v>1</v>
@@ -2915,28 +2915,28 @@
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0.9141702060444017</v>
+        <v>0.9241481659238815</v>
       </c>
       <c r="P34" t="n">
-        <v>0.0008779888867831621</v>
+        <v>0.0009399021841554903</v>
       </c>
       <c r="Q34" t="n">
-        <v>936.5868307737594</v>
+        <v>940.3732479495258</v>
       </c>
       <c r="R34" t="n">
-        <v>199.7881294756043</v>
+        <v>200.1092821753496</v>
       </c>
       <c r="S34" t="n">
-        <v>10.93416933649186</v>
+        <v>10.93037211948388</v>
       </c>
       <c r="T34" t="n">
-        <v>91.56847052771423</v>
+        <v>95.35488770348059</v>
       </c>
       <c r="U34" t="n">
-        <v>0.5584848449675519</v>
+        <v>0.2373321452222683</v>
       </c>
       <c r="V34" t="n">
-        <v>0.07198179815612882</v>
+        <v>0.07577901516410002</v>
       </c>
       <c r="W34" t="b">
         <v>1</v>
@@ -2988,28 +2988,28 @@
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>0.9941723991944598</v>
+        <v>0.9949327079780264</v>
       </c>
       <c r="P35" t="n">
-        <v>0.001542324938981525</v>
+        <v>0.001634300686191376</v>
       </c>
       <c r="Q35" t="n">
-        <v>813.1261581054529</v>
+        <v>812.0894811465266</v>
       </c>
       <c r="R35" t="n">
-        <v>150.0000472904414</v>
+        <v>150.0000472902792</v>
       </c>
       <c r="S35" t="n">
-        <v>9.00005786949913</v>
+        <v>9.000057869300663</v>
       </c>
       <c r="T35" t="n">
-        <v>116.8414416966488</v>
+        <v>117.878118655575</v>
       </c>
       <c r="U35" t="n">
-        <v>7.098589078369372</v>
+        <v>7.098589078207198</v>
       </c>
       <c r="V35" t="n">
-        <v>0.3125465598354431</v>
+        <v>0.3125465596369761</v>
       </c>
       <c r="W35" t="b">
         <v>1</v>
@@ -3061,28 +3061,28 @@
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>0.994159039427843</v>
+        <v>0.9924663958655049</v>
       </c>
       <c r="P36" t="n">
-        <v>0.001748581905013277</v>
+        <v>0.00173306087152696</v>
       </c>
       <c r="Q36" t="n">
-        <v>815.2810671527558</v>
+        <v>816.4402722783584</v>
       </c>
       <c r="R36" t="n">
-        <v>205.3724066480493</v>
+        <v>205.3958570917621</v>
       </c>
       <c r="S36" t="n">
-        <v>14.10779377789854</v>
+        <v>14.15496831013463</v>
       </c>
       <c r="T36" t="n">
-        <v>111.3205961330384</v>
+        <v>110.1613910074358</v>
       </c>
       <c r="U36" t="n">
-        <v>0.3245930388985698</v>
+        <v>0.3480434826114447</v>
       </c>
       <c r="V36" t="n">
-        <v>0.7288171657536555</v>
+        <v>0.6816426335175692</v>
       </c>
       <c r="W36" t="b">
         <v>1</v>
@@ -3134,28 +3134,28 @@
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>0.9933836959334901</v>
+        <v>0.9893205482746081</v>
       </c>
       <c r="P37" t="n">
-        <v>0.001310920546242343</v>
+        <v>0.001389402878035869</v>
       </c>
       <c r="Q37" t="n">
-        <v>823.8594318253088</v>
+        <v>823.1360210248589</v>
       </c>
       <c r="R37" t="n">
-        <v>236.3300221102418</v>
+        <v>237.0869377249136</v>
       </c>
       <c r="S37" t="n">
-        <v>9.000057869320822</v>
+        <v>9.000057869280431</v>
       </c>
       <c r="T37" t="n">
-        <v>92.37988167073763</v>
+        <v>93.1032924711875</v>
       </c>
       <c r="U37" t="n">
-        <v>18.36492099271646</v>
+        <v>17.60800537804465</v>
       </c>
       <c r="V37" t="n">
-        <v>0.201270688214084</v>
+        <v>0.2012706881736932</v>
       </c>
       <c r="W37" t="b">
         <v>1</v>
@@ -3207,28 +3207,28 @@
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>0.9979507900650925</v>
+        <v>0.9981931466980017</v>
       </c>
       <c r="P38" t="n">
-        <v>0.001632754862902922</v>
+        <v>0.001731622010935966</v>
       </c>
       <c r="Q38" t="n">
-        <v>811.3976295487325</v>
+        <v>810.4264262414273</v>
       </c>
       <c r="R38" t="n">
-        <v>150.0000472861513</v>
+        <v>150.0000472874946</v>
       </c>
       <c r="S38" t="n">
-        <v>9.42662096835625</v>
+        <v>9.429072252051789</v>
       </c>
       <c r="T38" t="n">
-        <v>123.6263745308664</v>
+        <v>124.5975778381717</v>
       </c>
       <c r="U38" t="n">
-        <v>10.85279539209603</v>
+        <v>10.85279539343929</v>
       </c>
       <c r="V38" t="n">
-        <v>0.06667485543351148</v>
+        <v>0.06422357173797266</v>
       </c>
       <c r="W38" t="b">
         <v>1</v>
@@ -3280,28 +3280,28 @@
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>0.8369867081372276</v>
+        <v>0.8316781602869349</v>
       </c>
       <c r="P39" t="n">
-        <v>0.0008393569850330224</v>
+        <v>0.0008844104172125199</v>
       </c>
       <c r="Q39" t="n">
-        <v>947.0740579907208</v>
+        <v>949.9119619833524</v>
       </c>
       <c r="R39" t="n">
-        <v>215.923748095988</v>
+        <v>216.1714923946195</v>
       </c>
       <c r="S39" t="n">
-        <v>9.000057858025528</v>
+        <v>9.000057813049315</v>
       </c>
       <c r="T39" t="n">
-        <v>79.10273043508846</v>
+        <v>81.94063442772006</v>
       </c>
       <c r="U39" t="n">
-        <v>2.681015435934967</v>
+        <v>2.433271137303393</v>
       </c>
       <c r="V39" t="n">
-        <v>0.5079392314247109</v>
+        <v>0.5079391864484979</v>
       </c>
       <c r="W39" t="b">
         <v>1</v>
@@ -3353,28 +3353,28 @@
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0.7697438663348006</v>
+        <v>0.7067508044231408</v>
       </c>
       <c r="P40" t="n">
-        <v>0.00043917985805562</v>
+        <v>0.0005227293178559609</v>
       </c>
       <c r="Q40" t="n">
-        <v>953.6758713339957</v>
+        <v>951.2597773477098</v>
       </c>
       <c r="R40" t="n">
-        <v>180.8479916512672</v>
+        <v>180.9632582563371</v>
       </c>
       <c r="S40" t="n">
-        <v>9.275692175528107</v>
+        <v>9.275598885438304</v>
       </c>
       <c r="T40" t="n">
-        <v>63.85525217832196</v>
+        <v>66.27134616460785</v>
       </c>
       <c r="U40" t="n">
-        <v>0.4621957425975722</v>
+        <v>0.577462347667506</v>
       </c>
       <c r="V40" t="n">
-        <v>0.005350057822226972</v>
+        <v>0.00525676773242445</v>
       </c>
       <c r="W40" t="b">
         <v>1</v>
@@ -3426,28 +3426,28 @@
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>0.9999101521770775</v>
+        <v>0.9999389029456597</v>
       </c>
       <c r="P41" t="n">
-        <v>0.001695329703914839</v>
+        <v>0.001794812865684754</v>
       </c>
       <c r="Q41" t="n">
-        <v>813.5609134239396</v>
+        <v>812.5666353847927</v>
       </c>
       <c r="R41" t="n">
-        <v>150.0000472860426</v>
+        <v>150.0000472857825</v>
       </c>
       <c r="S41" t="n">
-        <v>9.109975438975489</v>
+        <v>9.10957895556057</v>
       </c>
       <c r="T41" t="n">
-        <v>134.4673239303752</v>
+        <v>135.4616019695221</v>
       </c>
       <c r="U41" t="n">
-        <v>32.40069081881862</v>
+        <v>32.4006908185585</v>
       </c>
       <c r="V41" t="n">
-        <v>0.07202237628276364</v>
+        <v>0.07241885969768269</v>
       </c>
       <c r="W41" t="b">
         <v>1</v>
@@ -3499,28 +3499,28 @@
         <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>0.9952305758711408</v>
+        <v>0.9939638524351613</v>
       </c>
       <c r="P42" t="n">
-        <v>0.001911867524951935</v>
+        <v>0.001930103868454727</v>
       </c>
       <c r="Q42" t="n">
-        <v>817.3428455243761</v>
+        <v>818.2456352873575</v>
       </c>
       <c r="R42" t="n">
-        <v>185.9504320651347</v>
+        <v>186.0483426757007</v>
       </c>
       <c r="S42" t="n">
-        <v>13.92626204698621</v>
+        <v>13.97487492473567</v>
       </c>
       <c r="T42" t="n">
-        <v>142.495537905754</v>
+        <v>141.5927481427726</v>
       </c>
       <c r="U42" t="n">
-        <v>1.67793612204963</v>
+        <v>1.775846732615605</v>
       </c>
       <c r="V42" t="n">
-        <v>0.8353309165013751</v>
+        <v>0.7867180387519177</v>
       </c>
       <c r="W42" t="b">
         <v>1</v>
@@ -3572,28 +3572,28 @@
         <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0.9288649395605902</v>
+        <v>0.9328819787915791</v>
       </c>
       <c r="P43" t="n">
-        <v>0.001265134556541037</v>
+        <v>0.001343040213317007</v>
       </c>
       <c r="Q43" t="n">
-        <v>830.6202214179372</v>
+        <v>829.8647205309549</v>
       </c>
       <c r="R43" t="n">
-        <v>162.6499106517926</v>
+        <v>162.6648085865374</v>
       </c>
       <c r="S43" t="n">
-        <v>10.14717197528575</v>
+        <v>10.15575183071282</v>
       </c>
       <c r="T43" t="n">
-        <v>100.3659647137578</v>
+        <v>101.1214656007401</v>
       </c>
       <c r="U43" t="n">
-        <v>5.834668060406983</v>
+        <v>5.849565995151778</v>
       </c>
       <c r="V43" t="n">
-        <v>0.04760203034231836</v>
+        <v>0.03902217491524773</v>
       </c>
       <c r="W43" t="b">
         <v>1</v>
@@ -3645,28 +3645,28 @@
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0.6911975537835221</v>
+        <v>0.6980136554101417</v>
       </c>
       <c r="P44" t="n">
-        <v>0.0006543153484417812</v>
+        <v>0.0006999133048971682</v>
       </c>
       <c r="Q44" t="n">
-        <v>945.0847396805009</v>
+        <v>948.301946711998</v>
       </c>
       <c r="R44" t="n">
-        <v>207.2602058182935</v>
+        <v>207.4041622400812</v>
       </c>
       <c r="S44" t="n">
-        <v>9.000057851877191</v>
+        <v>9.000057859847047</v>
       </c>
       <c r="T44" t="n">
-        <v>67.03937023078947</v>
+        <v>70.25657726228656</v>
       </c>
       <c r="U44" t="n">
-        <v>1.367969734009847</v>
+        <v>1.224013312222155</v>
       </c>
       <c r="V44" t="n">
-        <v>0.1438570944060942</v>
+        <v>0.1438571023759501</v>
       </c>
       <c r="W44" t="b">
         <v>1</v>
@@ -3718,28 +3718,28 @@
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>0.9460786248053551</v>
+        <v>0.9464873892555224</v>
       </c>
       <c r="P45" t="n">
-        <v>0.001070384573441114</v>
+        <v>0.00114329585597964</v>
       </c>
       <c r="Q45" t="n">
-        <v>938.3728845080026</v>
+        <v>942.4958063823801</v>
       </c>
       <c r="R45" t="n">
-        <v>186.9317176624866</v>
+        <v>187.217653905461</v>
       </c>
       <c r="S45" t="n">
-        <v>9.000057869916374</v>
+        <v>9.000057869790005</v>
       </c>
       <c r="T45" t="n">
-        <v>103.4768885451313</v>
+        <v>107.5998104195088</v>
       </c>
       <c r="U45" t="n">
-        <v>0.06891111041821318</v>
+        <v>0.354847353392671</v>
       </c>
       <c r="V45" t="n">
-        <v>1.983898877754465</v>
+        <v>1.983898877628097</v>
       </c>
       <c r="W45" t="b">
         <v>1</v>
@@ -3791,28 +3791,28 @@
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>0.8796295315742628</v>
+        <v>0.8558049334060781</v>
       </c>
       <c r="P46" t="n">
-        <v>0.001452622566738687</v>
+        <v>0.001476038402235606</v>
       </c>
       <c r="Q46" t="n">
-        <v>841.8496432852859</v>
+        <v>842.1911799205358</v>
       </c>
       <c r="R46" t="n">
-        <v>197.8759414472123</v>
+        <v>197.9024398213539</v>
       </c>
       <c r="S46" t="n">
-        <v>12.91593221380215</v>
+        <v>12.94399703122344</v>
       </c>
       <c r="T46" t="n">
-        <v>116.7427210973658</v>
+        <v>116.4011844621159</v>
       </c>
       <c r="U46" t="n">
-        <v>0.8352168492999681</v>
+        <v>0.8617152234415073</v>
       </c>
       <c r="V46" t="n">
-        <v>0.5611579519541916</v>
+        <v>0.5330931345328995</v>
       </c>
       <c r="W46" t="b">
         <v>1</v>
@@ -3864,28 +3864,28 @@
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>0.676259209640181</v>
+        <v>0.5181408766353688</v>
       </c>
       <c r="P47" t="n">
-        <v>0.001161497825082428</v>
+        <v>0.001242224925512452</v>
       </c>
       <c r="Q47" t="n">
-        <v>860.1313150301785</v>
+        <v>857.8482053852759</v>
       </c>
       <c r="R47" t="n">
-        <v>219.740945322078</v>
+        <v>220.157224609334</v>
       </c>
       <c r="S47" t="n">
-        <v>10.48328932262805</v>
+        <v>10.48245554368248</v>
       </c>
       <c r="T47" t="n">
-        <v>96.01675636421533</v>
+        <v>98.29986600911786</v>
       </c>
       <c r="U47" t="n">
-        <v>15.00024199724038</v>
+        <v>14.58396270998443</v>
       </c>
       <c r="V47" t="n">
-        <v>0.005993313818624557</v>
+        <v>0.005159534873055094</v>
       </c>
       <c r="W47" t="b">
         <v>1</v>
@@ -3937,28 +3937,28 @@
         <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>0.9978547212377892</v>
+        <v>0.9967246122004051</v>
       </c>
       <c r="P48" t="n">
-        <v>0.0006681420358284944</v>
+        <v>0.0007880797886469035</v>
       </c>
       <c r="Q48" t="n">
-        <v>957.7165529023971</v>
+        <v>956.1272860425254</v>
       </c>
       <c r="R48" t="n">
-        <v>200.2914651770552</v>
+        <v>200.2987295186366</v>
       </c>
       <c r="S48" t="n">
-        <v>9.00005786869111</v>
+        <v>9.000057868713494</v>
       </c>
       <c r="T48" t="n">
-        <v>116.8059787455484</v>
+        <v>118.3952456054201</v>
       </c>
       <c r="U48" t="n">
-        <v>0.3350962723027919</v>
+        <v>0.3278319307213735</v>
       </c>
       <c r="V48" t="n">
-        <v>1.729462253614845</v>
+        <v>1.729462253637228</v>
       </c>
       <c r="W48" t="b">
         <v>1</v>
@@ -4010,28 +4010,28 @@
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>0.7317755814384203</v>
+        <v>0.7637864077416848</v>
       </c>
       <c r="P49" t="n">
-        <v>0.000663159104119457</v>
+        <v>0.0007266981009792432</v>
       </c>
       <c r="Q49" t="n">
-        <v>935.7902123807238</v>
+        <v>940.3654230155698</v>
       </c>
       <c r="R49" t="n">
-        <v>183.9322719644943</v>
+        <v>184.1890997594415</v>
       </c>
       <c r="S49" t="n">
-        <v>10.06480901148663</v>
+        <v>10.06056936382245</v>
       </c>
       <c r="T49" t="n">
-        <v>71.4406989994377</v>
+        <v>76.01590963428373</v>
       </c>
       <c r="U49" t="n">
-        <v>0.4547076339040927</v>
+        <v>0.7115354288513061</v>
       </c>
       <c r="V49" t="n">
-        <v>0.02455172710960696</v>
+        <v>0.02879137477379423</v>
       </c>
       <c r="W49" t="b">
         <v>1</v>
@@ -4083,28 +4083,28 @@
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>0.9999185704371893</v>
+        <v>0.9998253570475214</v>
       </c>
       <c r="P50" t="n">
-        <v>0.002586488068130616</v>
+        <v>0.002136359137945608</v>
       </c>
       <c r="Q50" t="n">
-        <v>953.2697017965532</v>
+        <v>803.1086002218975</v>
       </c>
       <c r="R50" t="n">
-        <v>213.2387300333199</v>
+        <v>246.3725355033174</v>
       </c>
       <c r="S50" t="n">
-        <v>9.525692397766266</v>
+        <v>9.411007309424141</v>
       </c>
       <c r="T50" t="n">
-        <v>0.7421102056250675</v>
+        <v>149.4189913690307</v>
       </c>
       <c r="U50" t="n">
-        <v>63.74740340959875</v>
+        <v>30.61359793960128</v>
       </c>
       <c r="V50" t="n">
-        <v>0.02885591681262234</v>
+        <v>0.08582917152950209</v>
       </c>
       <c r="W50" t="b">
         <v>1</v>
@@ -4156,28 +4156,28 @@
         <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>0.9583416528171256</v>
+        <v>0.9567267158619907</v>
       </c>
       <c r="P51" t="n">
-        <v>0.0008866006028634679</v>
+        <v>0.0009441125689977485</v>
       </c>
       <c r="Q51" t="n">
-        <v>940.7005596673206</v>
+        <v>944.2990112798274</v>
       </c>
       <c r="R51" t="n">
-        <v>199.2758436352991</v>
+        <v>199.4707916317523</v>
       </c>
       <c r="S51" t="n">
-        <v>9.000057867420534</v>
+        <v>9.000057868763989</v>
       </c>
       <c r="T51" t="n">
-        <v>89.77828838784706</v>
+        <v>93.37674000035383</v>
       </c>
       <c r="U51" t="n">
-        <v>0.9241885629755586</v>
+        <v>0.7292405665223498</v>
       </c>
       <c r="V51" t="n">
-        <v>1.790222113967468</v>
+        <v>1.790222115310923</v>
       </c>
       <c r="W51" t="b">
         <v>1</v>
@@ -4229,28 +4229,28 @@
         <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>0.8471564595625299</v>
+        <v>0.8471175566978565</v>
       </c>
       <c r="P52" t="n">
-        <v>0.0006870242246896139</v>
+        <v>0.0007339885546241874</v>
       </c>
       <c r="Q52" t="n">
-        <v>944.4718311621449</v>
+        <v>947.7300935326629</v>
       </c>
       <c r="R52" t="n">
-        <v>206.5607728354697</v>
+        <v>206.7123237122713</v>
       </c>
       <c r="S52" t="n">
-        <v>9.000057854730544</v>
+        <v>9.000057861247972</v>
       </c>
       <c r="T52" t="n">
-        <v>70.27425359450604</v>
+        <v>73.532515965024</v>
       </c>
       <c r="U52" t="n">
-        <v>1.365877832931119</v>
+        <v>1.214326956129582</v>
       </c>
       <c r="V52" t="n">
-        <v>0.6699128764331892</v>
+        <v>0.6699128829506176</v>
       </c>
       <c r="W52" t="b">
         <v>1</v>
@@ -4302,28 +4302,28 @@
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0.9998216593048536</v>
+        <v>0.9994660785611302</v>
       </c>
       <c r="P53" t="n">
-        <v>0.002651848498518323</v>
+        <v>0.003580138358393574</v>
       </c>
       <c r="Q53" t="n">
-        <v>960.6726882500265</v>
+        <v>869.4102979292102</v>
       </c>
       <c r="R53" t="n">
-        <v>212.9050482834675</v>
+        <v>220.703676588334</v>
       </c>
       <c r="S53" t="n">
-        <v>11.14477895032718</v>
+        <v>11.23141282950746</v>
       </c>
       <c r="T53" t="n">
-        <v>19.38199827608526</v>
+        <v>110.6443885969015</v>
       </c>
       <c r="U53" t="n">
-        <v>61.48434497039256</v>
+        <v>53.68571666552603</v>
       </c>
       <c r="V53" t="n">
-        <v>0.07756630614079363</v>
+        <v>0.009067573039487797</v>
       </c>
       <c r="W53" t="b">
         <v>1</v>
@@ -4375,28 +4375,28 @@
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>0.9973670931728997</v>
+        <v>0.9965709863549486</v>
       </c>
       <c r="P54" t="n">
-        <v>0.001978279186394049</v>
+        <v>0.001965538752900588</v>
       </c>
       <c r="Q54" t="n">
-        <v>814.6753526656346</v>
+        <v>815.8222118983308</v>
       </c>
       <c r="R54" t="n">
-        <v>203.8010938176184</v>
+        <v>203.8280908349716</v>
       </c>
       <c r="S54" t="n">
-        <v>14.1921751958092</v>
+        <v>14.24594930819829</v>
       </c>
       <c r="T54" t="n">
-        <v>133.0334587849151</v>
+        <v>131.8865995522189</v>
       </c>
       <c r="U54" t="n">
-        <v>0.5188904978085702</v>
+        <v>0.5458875151617519</v>
       </c>
       <c r="V54" t="n">
-        <v>0.8511337675225228</v>
+        <v>0.7973596551334285</v>
       </c>
       <c r="W54" t="b">
         <v>1</v>
@@ -4448,28 +4448,28 @@
         <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>0.5462332029619766</v>
+        <v>0.4461637882758212</v>
       </c>
       <c r="P55" t="n">
-        <v>0.001006409582844446</v>
+        <v>0.001086510063284846</v>
       </c>
       <c r="Q55" t="n">
-        <v>861.046482093859</v>
+        <v>859.2310404720315</v>
       </c>
       <c r="R55" t="n">
-        <v>219.8711815678608</v>
+        <v>220.2345236624318</v>
       </c>
       <c r="S55" t="n">
-        <v>9.264297069358657</v>
+        <v>9.258760151791563</v>
       </c>
       <c r="T55" t="n">
-        <v>83.04548970336043</v>
+        <v>84.86093132518795</v>
       </c>
       <c r="U55" t="n">
-        <v>12.80755981675847</v>
+        <v>12.44421772218746</v>
       </c>
       <c r="V55" t="n">
-        <v>0.04569033082675844</v>
+        <v>0.05122724839385207</v>
       </c>
       <c r="W55" t="b">
         <v>1</v>
@@ -4521,28 +4521,28 @@
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>0.9998293157136278</v>
+        <v>0.9997623754067174</v>
       </c>
       <c r="P56" t="n">
-        <v>0.003014767551189289</v>
+        <v>0.00233883799185668</v>
       </c>
       <c r="Q56" t="n">
-        <v>800.0000003429969</v>
+        <v>800.0831077242001</v>
       </c>
       <c r="R56" t="n">
-        <v>204.7873332373533</v>
+        <v>204.5650172311876</v>
       </c>
       <c r="S56" t="n">
-        <v>14.9999420403823</v>
+        <v>14.99994213049567</v>
       </c>
       <c r="T56" t="n">
-        <v>145.1483389312071</v>
+        <v>145.065231550004</v>
       </c>
       <c r="U56" t="n">
-        <v>0.7735193295494867</v>
+        <v>0.5512033233838167</v>
       </c>
       <c r="V56" t="n">
-        <v>1.474591210614033</v>
+        <v>1.47459112050066</v>
       </c>
       <c r="W56" t="b">
         <v>1</v>
@@ -4594,25 +4594,25 @@
         <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>0.9953407538462484</v>
+        <v>0.9933757675078213</v>
       </c>
       <c r="P57" t="n">
-        <v>0.001288184610508574</v>
+        <v>0.00147800297715752</v>
       </c>
       <c r="Q57" t="n">
-        <v>946.9251142389905</v>
+        <v>952.4585131517812</v>
       </c>
       <c r="R57" t="n">
-        <v>202.4803961183322</v>
+        <v>202.6902629812823</v>
       </c>
       <c r="S57" t="n">
         <v>9.000057869254071</v>
       </c>
       <c r="T57" t="n">
-        <v>5.674850277041401</v>
+        <v>0.14145136425077</v>
       </c>
       <c r="U57" t="n">
-        <v>2.265151505247388</v>
+        <v>2.055284642297323</v>
       </c>
       <c r="V57" t="n">
         <v>4.381040748688521</v>
@@ -4667,28 +4667,28 @@
         <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>0.9990510067272277</v>
+        <v>0.9980933374103921</v>
       </c>
       <c r="P58" t="n">
-        <v>0.001601802584027147</v>
+        <v>0.001688844871491204</v>
       </c>
       <c r="Q58" t="n">
-        <v>818.0769121803255</v>
+        <v>816.8741060158883</v>
       </c>
       <c r="R58" t="n">
-        <v>238.1022239749218</v>
+        <v>239.0331049298636</v>
       </c>
       <c r="S58" t="n">
-        <v>9.620864224866009</v>
+        <v>9.61606148525966</v>
       </c>
       <c r="T58" t="n">
-        <v>116.0746893996753</v>
+        <v>117.2774955641125</v>
       </c>
       <c r="U58" t="n">
-        <v>23.2897323612647</v>
+        <v>22.35885140632283</v>
       </c>
       <c r="V58" t="n">
-        <v>0.05134071925652783</v>
+        <v>0.05614345886287708</v>
       </c>
       <c r="W58" t="b">
         <v>1</v>
@@ -4740,28 +4740,28 @@
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0.9996751182502833</v>
+        <v>0.9996734282358312</v>
       </c>
       <c r="P59" t="n">
-        <v>0.001950419708030513</v>
+        <v>0.00206399954321481</v>
       </c>
       <c r="Q59" t="n">
-        <v>812.7475647186927</v>
+        <v>811.8830990232789</v>
       </c>
       <c r="R59" t="n">
-        <v>150.0000472868369</v>
+        <v>150.0000472880309</v>
       </c>
       <c r="S59" t="n">
-        <v>9.560659868653543</v>
+        <v>9.565582334464697</v>
       </c>
       <c r="T59" t="n">
-        <v>164.2932226007938</v>
+        <v>165.1576882962077</v>
       </c>
       <c r="U59" t="n">
-        <v>18.54656967650456</v>
+        <v>18.54656967769861</v>
       </c>
       <c r="V59" t="n">
-        <v>0.07936395776555649</v>
+        <v>0.07444149195440275</v>
       </c>
       <c r="W59" t="b">
         <v>1</v>
@@ -4813,28 +4813,28 @@
         <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>0.9996615681809872</v>
+        <v>0.999732702636326</v>
       </c>
       <c r="P60" t="n">
-        <v>0.001428954415346748</v>
+        <v>0.00151739854940814</v>
       </c>
       <c r="Q60" t="n">
-        <v>811.2493626982476</v>
+        <v>810.1919859690605</v>
       </c>
       <c r="R60" t="n">
-        <v>150.0000472865586</v>
+        <v>150.0000472868454</v>
       </c>
       <c r="S60" t="n">
-        <v>9.171148520557409</v>
+        <v>9.17096803743228</v>
       </c>
       <c r="T60" t="n">
-        <v>102.6098094031161</v>
+        <v>103.6671861323032</v>
       </c>
       <c r="U60" t="n">
-        <v>28.48933774454056</v>
+        <v>28.48933774482742</v>
       </c>
       <c r="V60" t="n">
-        <v>0.05970619963597379</v>
+        <v>0.05988668276110332</v>
       </c>
       <c r="W60" t="b">
         <v>1</v>
@@ -4886,28 +4886,28 @@
         <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>0.9899008807706283</v>
+        <v>0.9912042705973496</v>
       </c>
       <c r="P61" t="n">
-        <v>0.001451701790644071</v>
+        <v>0.001539803939746313</v>
       </c>
       <c r="Q61" t="n">
-        <v>812.432047238053</v>
+        <v>811.3724448540579</v>
       </c>
       <c r="R61" t="n">
-        <v>150.0000472904324</v>
+        <v>150.000047290349</v>
       </c>
       <c r="S61" t="n">
-        <v>9.000057869488069</v>
+        <v>9.000057869386046</v>
       </c>
       <c r="T61" t="n">
-        <v>106.5072472051506</v>
+        <v>107.5668495891457</v>
       </c>
       <c r="U61" t="n">
-        <v>5.862413162138978</v>
+        <v>5.862413162055617</v>
       </c>
       <c r="V61" t="n">
-        <v>0.2319265576211489</v>
+        <v>0.2319265575191256</v>
       </c>
       <c r="W61" t="b">
         <v>1</v>
@@ -4959,28 +4959,28 @@
         <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>0.9998599522950143</v>
+        <v>0.9996600609875907</v>
       </c>
       <c r="P62" t="n">
-        <v>0.001961491137519355</v>
+        <v>0.00204533229717532</v>
       </c>
       <c r="Q62" t="n">
-        <v>808.9166275780772</v>
+        <v>807.9012421769005</v>
       </c>
       <c r="R62" t="n">
-        <v>242.0389090756035</v>
+        <v>242.9948709400781</v>
       </c>
       <c r="S62" t="n">
-        <v>10.39113440725969</v>
+        <v>10.38796975448151</v>
       </c>
       <c r="T62" t="n">
-        <v>139.5947038399219</v>
+        <v>140.6100892410985</v>
       </c>
       <c r="U62" t="n">
-        <v>29.87087410302772</v>
+        <v>28.91491223855306</v>
       </c>
       <c r="V62" t="n">
-        <v>0.001188807876255638</v>
+        <v>0.001975844901922486</v>
       </c>
       <c r="W62" t="b">
         <v>1</v>
@@ -5032,28 +5032,28 @@
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0.9999668975172847</v>
+        <v>0.9999321359261277</v>
       </c>
       <c r="P63" t="n">
-        <v>0.00289448256149877</v>
+        <v>0.003744064627176985</v>
       </c>
       <c r="Q63" t="n">
-        <v>963.6116928119862</v>
+        <v>874.5920183431525</v>
       </c>
       <c r="R63" t="n">
-        <v>213.4223213521694</v>
+        <v>219.6298758743239</v>
       </c>
       <c r="S63" t="n">
-        <v>9.299901877687281</v>
+        <v>9.216062369296679</v>
       </c>
       <c r="T63" t="n">
-        <v>14.93441447379803</v>
+        <v>103.9540889426318</v>
       </c>
       <c r="U63" t="n">
-        <v>75.50163157599977</v>
+        <v>69.29407705384523</v>
       </c>
       <c r="V63" t="n">
-        <v>0.02947481090767212</v>
+        <v>0.05436469748292971</v>
       </c>
       <c r="W63" t="b">
         <v>1</v>
@@ -5105,28 +5105,28 @@
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>0.9899826675466773</v>
+        <v>0.9893628723263816</v>
       </c>
       <c r="P64" t="n">
-        <v>0.001596905751454016</v>
+        <v>0.001689572613974221</v>
       </c>
       <c r="Q64" t="n">
-        <v>820.4822393528982</v>
+        <v>819.8824783628796</v>
       </c>
       <c r="R64" t="n">
-        <v>156.3679026058684</v>
+        <v>156.4046498153921</v>
       </c>
       <c r="S64" t="n">
-        <v>10.14008394380013</v>
+        <v>10.15023425213265</v>
       </c>
       <c r="T64" t="n">
-        <v>128.2598833091047</v>
+        <v>128.8596442991233</v>
       </c>
       <c r="U64" t="n">
-        <v>6.436583832916426</v>
+        <v>6.473331042440122</v>
       </c>
       <c r="V64" t="n">
-        <v>0.06170116357082556</v>
+        <v>0.05155085523830216</v>
       </c>
       <c r="W64" t="b">
         <v>1</v>
@@ -5178,25 +5178,25 @@
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>0.9923315399961953</v>
+        <v>0.9899559021365771</v>
       </c>
       <c r="P65" t="n">
-        <v>0.001122361159079843</v>
+        <v>0.001044677408278651</v>
       </c>
       <c r="Q65" t="n">
-        <v>880.7002980573727</v>
+        <v>878.9113316920636</v>
       </c>
       <c r="R65" t="n">
-        <v>221.5548368377026</v>
+        <v>221.9175230698593</v>
       </c>
       <c r="S65" t="n">
         <v>9.000057869254071</v>
       </c>
       <c r="T65" t="n">
-        <v>78.84051848708975</v>
+        <v>80.62948485239883</v>
       </c>
       <c r="U65" t="n">
-        <v>2.670718908256816</v>
+        <v>2.308032676100169</v>
       </c>
       <c r="V65" t="n">
         <v>4.079472738399824</v>
@@ -5251,28 +5251,28 @@
         <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>0.9996612454450711</v>
+        <v>0.9994980371719612</v>
       </c>
       <c r="P66" t="n">
-        <v>0.00203315826163045</v>
+        <v>0.002133885197722446</v>
       </c>
       <c r="Q66" t="n">
-        <v>806.242058205123</v>
+        <v>805.1519184106039</v>
       </c>
       <c r="R66" t="n">
-        <v>245.2617231039781</v>
+        <v>246.6905102208083</v>
       </c>
       <c r="S66" t="n">
-        <v>9.000057863069008</v>
+        <v>9.000057863520329</v>
       </c>
       <c r="T66" t="n">
-        <v>149.880632856932</v>
+        <v>150.9707726514512</v>
       </c>
       <c r="U66" t="n">
-        <v>32.38359346957964</v>
+        <v>30.95480635274939</v>
       </c>
       <c r="V66" t="n">
-        <v>1.217341573322576</v>
+        <v>1.217341573773897</v>
       </c>
       <c r="W66" t="b">
         <v>1</v>
@@ -5324,28 +5324,28 @@
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>0.7881563935561191</v>
+        <v>0.7811817072505802</v>
       </c>
       <c r="P67" t="n">
-        <v>0.0007201746865634971</v>
+        <v>0.0007754995256549815</v>
       </c>
       <c r="Q67" t="n">
-        <v>941.6446782573946</v>
+        <v>945.3569473906055</v>
       </c>
       <c r="R67" t="n">
-        <v>195.7259787528989</v>
+        <v>195.891201778279</v>
       </c>
       <c r="S67" t="n">
-        <v>9.000057869728865</v>
+        <v>9.000057869386268</v>
       </c>
       <c r="T67" t="n">
-        <v>75.16692871285204</v>
+        <v>78.87919784606288</v>
       </c>
       <c r="U67" t="n">
-        <v>0.4670469909348469</v>
+        <v>0.301823965554803</v>
       </c>
       <c r="V67" t="n">
-        <v>0.499834923318188</v>
+        <v>0.499834922975591</v>
       </c>
       <c r="W67" t="b">
         <v>1</v>
@@ -5397,28 +5397,28 @@
         <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>0.6981251195672556</v>
+        <v>0.6334919968180894</v>
       </c>
       <c r="P68" t="n">
-        <v>0.0004219042398538178</v>
+        <v>0.0005044970463841696</v>
       </c>
       <c r="Q68" t="n">
-        <v>953.8229193647451</v>
+        <v>951.5424514598917</v>
       </c>
       <c r="R68" t="n">
-        <v>184.736719654626</v>
+        <v>184.823650290297</v>
       </c>
       <c r="S68" t="n">
-        <v>9.000057868610762</v>
+        <v>9.000057868797599</v>
       </c>
       <c r="T68" t="n">
-        <v>61.70292939768478</v>
+        <v>63.98339730253815</v>
       </c>
       <c r="U68" t="n">
-        <v>0.3775215437425175</v>
+        <v>0.4644521794135414</v>
       </c>
       <c r="V68" t="n">
-        <v>0.8879201058331105</v>
+        <v>0.8879201060199478</v>
       </c>
       <c r="W68" t="b">
         <v>1</v>
@@ -5470,28 +5470,28 @@
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>0.9999571352671371</v>
+        <v>0.9999306642434019</v>
       </c>
       <c r="P69" t="n">
-        <v>0.00302150296796179</v>
+        <v>0.002330327710711407</v>
       </c>
       <c r="Q69" t="n">
-        <v>800.0000004972368</v>
+        <v>800.0000002330278</v>
       </c>
       <c r="R69" t="n">
-        <v>204.4349670969896</v>
+        <v>204.1987542548447</v>
       </c>
       <c r="S69" t="n">
-        <v>14.99994212734213</v>
+        <v>14.99994212757452</v>
       </c>
       <c r="T69" t="n">
-        <v>127.8859061330445</v>
+        <v>127.8859063972535</v>
       </c>
       <c r="U69" t="n">
-        <v>0.811999060524073</v>
+        <v>0.5757862183791644</v>
       </c>
       <c r="V69" t="n">
-        <v>2.645833787557677</v>
+        <v>2.645833787325286</v>
       </c>
       <c r="W69" t="b">
         <v>1</v>
@@ -5543,25 +5543,25 @@
         <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>0.9943567243610213</v>
+        <v>0.9925704560366325</v>
       </c>
       <c r="P70" t="n">
-        <v>0.001836897731187797</v>
+        <v>0.00198945663166214</v>
       </c>
       <c r="Q70" t="n">
-        <v>948.252364805199</v>
+        <v>955.2026121095096</v>
       </c>
       <c r="R70" t="n">
-        <v>209.409893383728</v>
+        <v>209.850142364516</v>
       </c>
       <c r="S70" t="n">
         <v>9.000057869254071</v>
       </c>
       <c r="T70" t="n">
-        <v>9.58526043971267</v>
+        <v>2.635013135402119</v>
       </c>
       <c r="U70" t="n">
-        <v>4.88971848416881</v>
+        <v>4.449469503380755</v>
       </c>
       <c r="V70" t="n">
         <v>4.226372438068278</v>
@@ -5616,28 +5616,28 @@
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>0.788050207572062</v>
+        <v>0.7767660368799064</v>
       </c>
       <c r="P71" t="n">
-        <v>0.00107619670292462</v>
+        <v>0.001148071187293484</v>
       </c>
       <c r="Q71" t="n">
-        <v>938.3277722701279</v>
+        <v>942.3959097614249</v>
       </c>
       <c r="R71" t="n">
-        <v>188.157550104991</v>
+        <v>188.4372351828872</v>
       </c>
       <c r="S71" t="n">
-        <v>9.000057869318903</v>
+        <v>9.000057869254974</v>
       </c>
       <c r="T71" t="n">
-        <v>104.4020766318266</v>
+        <v>108.4702141231237</v>
       </c>
       <c r="U71" t="n">
-        <v>0.01787042255563165</v>
+        <v>0.2618146553405722</v>
       </c>
       <c r="V71" t="n">
-        <v>0.7109569972330245</v>
+        <v>0.7109569971690952</v>
       </c>
       <c r="W71" t="b">
         <v>1</v>
@@ -5689,28 +5689,28 @@
         <v>1</v>
       </c>
       <c r="O72" t="n">
-        <v>0.9863341127292515</v>
+        <v>0.9805547719063622</v>
       </c>
       <c r="P72" t="n">
-        <v>0.001800858667026563</v>
+        <v>0.001774550646526203</v>
       </c>
       <c r="Q72" t="n">
-        <v>820.7373439814994</v>
+        <v>821.5555658109116</v>
       </c>
       <c r="R72" t="n">
-        <v>220.4437630328117</v>
+        <v>220.4062653062061</v>
       </c>
       <c r="S72" t="n">
-        <v>13.88949516356204</v>
+        <v>13.9342056221396</v>
       </c>
       <c r="T72" t="n">
-        <v>112.1927464172737</v>
+        <v>111.3745245878615</v>
       </c>
       <c r="U72" t="n">
-        <v>0.7773315395238285</v>
+        <v>0.8148292661293794</v>
       </c>
       <c r="V72" t="n">
-        <v>0.6913632630302331</v>
+        <v>0.6466528044526729</v>
       </c>
       <c r="W72" t="b">
         <v>1</v>
@@ -5762,28 +5762,28 @@
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>0.996459173492649</v>
+        <v>0.9964367712060401</v>
       </c>
       <c r="P73" t="n">
-        <v>0.001762343385386861</v>
+        <v>0.001864698908634125</v>
       </c>
       <c r="Q73" t="n">
-        <v>811.721593985368</v>
+        <v>811.0376113065032</v>
       </c>
       <c r="R73" t="n">
-        <v>150.7709461458721</v>
+        <v>150.8342806475491</v>
       </c>
       <c r="S73" t="n">
-        <v>9.849555942680613</v>
+        <v>9.856729712780513</v>
       </c>
       <c r="T73" t="n">
-        <v>137.8959624175578</v>
+        <v>138.5799450964226</v>
       </c>
       <c r="U73" t="n">
-        <v>6.19296528786694</v>
+        <v>6.256299789543931</v>
       </c>
       <c r="V73" t="n">
-        <v>0.06811350730218102</v>
+        <v>0.06093973720228085</v>
       </c>
       <c r="W73" t="b">
         <v>1</v>
@@ -5835,28 +5835,28 @@
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0.3679098579149766</v>
+        <v>0.470911561025959</v>
       </c>
       <c r="P74" t="n">
-        <v>0.0004274206376175458</v>
+        <v>0.0004686162051055615</v>
       </c>
       <c r="Q74" t="n">
-        <v>947.007585339293</v>
+        <v>950.2967706884758</v>
       </c>
       <c r="R74" t="n">
-        <v>203.3353542261918</v>
+        <v>203.4194637489505</v>
       </c>
       <c r="S74" t="n">
-        <v>9.000057864342002</v>
+        <v>9.00005786750633</v>
       </c>
       <c r="T74" t="n">
-        <v>45.95686019358027</v>
+        <v>49.24604554276311</v>
       </c>
       <c r="U74" t="n">
-        <v>0.6834924050836833</v>
+        <v>0.5993828823249885</v>
       </c>
       <c r="V74" t="n">
-        <v>0.4059175502074677</v>
+        <v>0.4059175533717951</v>
       </c>
       <c r="W74" t="b">
         <v>1</v>
@@ -5908,28 +5908,28 @@
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>0.9982928998632259</v>
+        <v>0.9974555323243089</v>
       </c>
       <c r="P75" t="n">
-        <v>0.002499602621814765</v>
+        <v>0.002474742833338809</v>
       </c>
       <c r="Q75" t="n">
-        <v>812.3518565656884</v>
+        <v>813.4360830307882</v>
       </c>
       <c r="R75" t="n">
-        <v>211.9612790027144</v>
+        <v>211.951497200641</v>
       </c>
       <c r="S75" t="n">
-        <v>14.42256403795143</v>
+        <v>14.49097995158031</v>
       </c>
       <c r="T75" t="n">
-        <v>176.710287399763</v>
+        <v>175.6260609346633</v>
       </c>
       <c r="U75" t="n">
-        <v>0.003988864114432999</v>
+        <v>0.01377066618786671</v>
       </c>
       <c r="V75" t="n">
-        <v>1.099076348347147</v>
+        <v>1.030660434718268</v>
       </c>
       <c r="W75" t="b">
         <v>1</v>
@@ -5981,28 +5981,28 @@
         <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>0.9116697077839033</v>
+        <v>0.9239158876633884</v>
       </c>
       <c r="P76" t="n">
-        <v>0.0007905151706244139</v>
+        <v>0.0008527657826972769</v>
       </c>
       <c r="Q76" t="n">
-        <v>937.1240040995773</v>
+        <v>941.1512166181586</v>
       </c>
       <c r="R76" t="n">
-        <v>195.5592389153184</v>
+        <v>195.8624588216715</v>
       </c>
       <c r="S76" t="n">
-        <v>10.95898308319927</v>
+        <v>10.95390150437082</v>
       </c>
       <c r="T76" t="n">
-        <v>83.26198323655706</v>
+        <v>87.28919575513839</v>
       </c>
       <c r="U76" t="n">
-        <v>0.1480188559498288</v>
+        <v>0.1552010504033206</v>
       </c>
       <c r="V76" t="n">
-        <v>0.06590334956665878</v>
+        <v>0.07098492839511472</v>
       </c>
       <c r="W76" t="b">
         <v>1</v>
@@ -6054,28 +6054,28 @@
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0.9995228290527134</v>
+        <v>0.9996358091387807</v>
       </c>
       <c r="P77" t="n">
-        <v>0.001743116500829386</v>
+        <v>0.001843761011184523</v>
       </c>
       <c r="Q77" t="n">
-        <v>814.511952807126</v>
+        <v>813.5237786304446</v>
       </c>
       <c r="R77" t="n">
-        <v>150.0000472901694</v>
+        <v>150.0000472904179</v>
       </c>
       <c r="S77" t="n">
-        <v>9.000057869166337</v>
+        <v>9.000057869470412</v>
       </c>
       <c r="T77" t="n">
-        <v>141.9697265807699</v>
+        <v>142.9579007574514</v>
       </c>
       <c r="U77" t="n">
-        <v>20.21472641386902</v>
+        <v>20.21472641411751</v>
       </c>
       <c r="V77" t="n">
-        <v>0.7719545514127812</v>
+        <v>0.7719545517168562</v>
       </c>
       <c r="W77" t="b">
         <v>1</v>
@@ -6127,28 +6127,28 @@
         <v>1</v>
       </c>
       <c r="O78" t="n">
-        <v>0.9996234350014528</v>
+        <v>0.9994469881392449</v>
       </c>
       <c r="P78" t="n">
-        <v>0.002776573757838296</v>
+        <v>0.002716686171042783</v>
       </c>
       <c r="Q78" t="n">
-        <v>800.0000000000251</v>
+        <v>800.0000000000211</v>
       </c>
       <c r="R78" t="n">
-        <v>184.9089674601588</v>
+        <v>184.9705219587475</v>
       </c>
       <c r="S78" t="n">
-        <v>14.80018846437015</v>
+        <v>14.92241746523769</v>
       </c>
       <c r="T78" t="n">
-        <v>177.1837898832554</v>
+        <v>177.1837898832594</v>
       </c>
       <c r="U78" t="n">
-        <v>2.18457783652218</v>
+        <v>2.246132335110872</v>
       </c>
       <c r="V78" t="n">
-        <v>1.379933573444145</v>
+        <v>1.257704572576605</v>
       </c>
       <c r="W78" t="b">
         <v>1</v>
@@ -6200,28 +6200,28 @@
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>0.9998597096722134</v>
+        <v>0.9998807250201307</v>
       </c>
       <c r="P79" t="n">
-        <v>0.001780382639228377</v>
+        <v>0.001884741211074473</v>
       </c>
       <c r="Q79" t="n">
-        <v>809.1792368572565</v>
+        <v>808.50818049264</v>
       </c>
       <c r="R79" t="n">
-        <v>150.0000472872834</v>
+        <v>150.0000472893526</v>
       </c>
       <c r="S79" t="n">
-        <v>10.10016308556093</v>
+        <v>10.10985451616791</v>
       </c>
       <c r="T79" t="n">
-        <v>136.2487648359431</v>
+        <v>136.9198212005596</v>
       </c>
       <c r="U79" t="n">
-        <v>26.38330640895711</v>
+        <v>26.38330641102635</v>
       </c>
       <c r="V79" t="n">
-        <v>0.06953007241035358</v>
+        <v>0.05983864180337939</v>
       </c>
       <c r="W79" t="b">
         <v>1</v>
@@ -6273,28 +6273,28 @@
         <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>0.7748990773582409</v>
+        <v>0.7860919123070932</v>
       </c>
       <c r="P80" t="n">
-        <v>0.0005939363444627738</v>
+        <v>0.0006479382174591173</v>
       </c>
       <c r="Q80" t="n">
-        <v>942.7215469300116</v>
+        <v>946.5494609654912</v>
       </c>
       <c r="R80" t="n">
-        <v>192.0846387696111</v>
+        <v>192.2341378348172</v>
       </c>
       <c r="S80" t="n">
-        <v>9.000057869911943</v>
+        <v>9.000057869116391</v>
       </c>
       <c r="T80" t="n">
-        <v>63.04367857447528</v>
+        <v>66.87159260995486</v>
       </c>
       <c r="U80" t="n">
-        <v>0.1600267876349051</v>
+        <v>0.01052772242874767</v>
       </c>
       <c r="V80" t="n">
-        <v>0.590876372955206</v>
+        <v>0.5908763721596539</v>
       </c>
       <c r="W80" t="b">
         <v>1</v>
@@ -6346,28 +6346,28 @@
         <v>1</v>
       </c>
       <c r="O81" t="n">
-        <v>0.898104778270799</v>
+        <v>0.8972688172538158</v>
       </c>
       <c r="P81" t="n">
-        <v>0.0006777249728569186</v>
+        <v>0.0007327426574986495</v>
       </c>
       <c r="Q81" t="n">
-        <v>941.934038856728</v>
+        <v>945.6919968923789</v>
       </c>
       <c r="R81" t="n">
-        <v>194.3588315252479</v>
+        <v>194.5188358052751</v>
       </c>
       <c r="S81" t="n">
-        <v>9.00005786936636</v>
+        <v>9.000057869271767</v>
       </c>
       <c r="T81" t="n">
-        <v>71.18272544641081</v>
+        <v>74.94068348206179</v>
       </c>
       <c r="U81" t="n">
-        <v>0.3410554343382728</v>
+        <v>0.1810511543110067</v>
       </c>
       <c r="V81" t="n">
-        <v>1.115820172829412</v>
+        <v>1.11582017273482</v>
       </c>
       <c r="W81" t="b">
         <v>1</v>
@@ -6419,28 +6419,28 @@
         <v>1</v>
       </c>
       <c r="O82" t="n">
-        <v>0.8477183436844844</v>
+        <v>0.8390944395826102</v>
       </c>
       <c r="P82" t="n">
-        <v>0.0008200011890188441</v>
+        <v>0.0008739934013113232</v>
       </c>
       <c r="Q82" t="n">
-        <v>941.7568608463895</v>
+        <v>945.2514970619076</v>
       </c>
       <c r="R82" t="n">
-        <v>201.6389954079011</v>
+        <v>201.8182569368012</v>
       </c>
       <c r="S82" t="n">
-        <v>9.000057865826527</v>
+        <v>9.000057867271094</v>
       </c>
       <c r="T82" t="n">
-        <v>83.57891019430804</v>
+        <v>87.07354640982612</v>
       </c>
       <c r="U82" t="n">
-        <v>1.08917191487734</v>
+        <v>0.9099103859772129</v>
       </c>
       <c r="V82" t="n">
-        <v>0.6929475444588959</v>
+        <v>0.6929475459034631</v>
       </c>
       <c r="W82" t="b">
         <v>1</v>
@@ -6492,28 +6492,28 @@
         <v>1</v>
       </c>
       <c r="O83" t="n">
-        <v>0.964248395075688</v>
+        <v>0.9493608401224272</v>
       </c>
       <c r="P83" t="n">
-        <v>0.001503292210404655</v>
+        <v>0.0014801647182863</v>
       </c>
       <c r="Q83" t="n">
-        <v>818.5257614600431</v>
+        <v>819.5266994189953</v>
       </c>
       <c r="R83" t="n">
-        <v>214.6897995010518</v>
+        <v>214.687373253186</v>
       </c>
       <c r="S83" t="n">
-        <v>13.89897201341323</v>
+        <v>13.93762867188919</v>
       </c>
       <c r="T83" t="n">
-        <v>88.99528688594364</v>
+        <v>87.99434892699139</v>
       </c>
       <c r="U83" t="n">
-        <v>0.329585986932841</v>
+        <v>0.3320122347986967</v>
       </c>
       <c r="V83" t="n">
-        <v>0.5801122376125303</v>
+        <v>0.5414555791365689</v>
       </c>
       <c r="W83" t="b">
         <v>1</v>
@@ -6565,28 +6565,28 @@
         <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>0.9950720585205197</v>
+        <v>0.9890397340445956</v>
       </c>
       <c r="P84" t="n">
-        <v>0.000593527111646464</v>
+        <v>0.0006905390835415546</v>
       </c>
       <c r="Q84" t="n">
-        <v>950.5107694693806</v>
+        <v>948.9991614246512</v>
       </c>
       <c r="R84" t="n">
-        <v>207.8478735970994</v>
+        <v>207.9996969756142</v>
       </c>
       <c r="S84" t="n">
-        <v>11.9195044307956</v>
+        <v>11.91038521163961</v>
       </c>
       <c r="T84" t="n">
-        <v>94.55528649463281</v>
+        <v>96.06689453936224</v>
       </c>
       <c r="U84" t="n">
-        <v>0.8863746023739054</v>
+        <v>0.7345512238590572</v>
       </c>
       <c r="V84" t="n">
-        <v>0.05307547365133303</v>
+        <v>0.06219469280732426</v>
       </c>
       <c r="W84" t="b">
         <v>1</v>
@@ -6638,25 +6638,25 @@
         <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>0.9670661206681781</v>
+        <v>0.9598608837460775</v>
       </c>
       <c r="P85" t="n">
-        <v>0.001594391717383161</v>
+        <v>0.001754821458701727</v>
       </c>
       <c r="Q85" t="n">
-        <v>948.8598730155405</v>
+        <v>955.1891963532011</v>
       </c>
       <c r="R85" t="n">
-        <v>206.7744196915362</v>
+        <v>207.1162165948828</v>
       </c>
       <c r="S85" t="n">
         <v>9.000057869254071</v>
       </c>
       <c r="T85" t="n">
-        <v>9.302845240026613</v>
+        <v>2.973521902366087</v>
       </c>
       <c r="U85" t="n">
-        <v>3.68361482214371</v>
+        <v>3.341817918797091</v>
       </c>
       <c r="V85" t="n">
         <v>3.331428049683254</v>
@@ -6711,25 +6711,25 @@
         <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>0.8637625687507785</v>
+        <v>0.8258206962233363</v>
       </c>
       <c r="P86" t="n">
-        <v>0.001041549576820156</v>
+        <v>0.001239928065953514</v>
       </c>
       <c r="Q86" t="n">
-        <v>953.1245536945784</v>
+        <v>957.3404950565476</v>
       </c>
       <c r="R86" t="n">
-        <v>194.0887758847322</v>
+        <v>194.3285072504098</v>
       </c>
       <c r="S86" t="n">
         <v>9.000057869254071</v>
       </c>
       <c r="T86" t="n">
-        <v>10.54202616164298</v>
+        <v>6.326084799673708</v>
       </c>
       <c r="U86" t="n">
-        <v>0.810842370124476</v>
+        <v>0.5711110044468626</v>
       </c>
       <c r="V86" t="n">
         <v>2.834434359652825</v>
@@ -6784,28 +6784,28 @@
         <v>1</v>
       </c>
       <c r="O87" t="n">
-        <v>0.519092130117935</v>
+        <v>0.6029070403352221</v>
       </c>
       <c r="P87" t="n">
-        <v>0.0004826176356546388</v>
+        <v>0.0005241619693778824</v>
       </c>
       <c r="Q87" t="n">
-        <v>946.8470346543037</v>
+        <v>950.0638055424195</v>
       </c>
       <c r="R87" t="n">
-        <v>205.73566202997</v>
+        <v>205.8332559239097</v>
       </c>
       <c r="S87" t="n">
-        <v>9.000057859463142</v>
+        <v>9.000057864021455</v>
       </c>
       <c r="T87" t="n">
-        <v>51.03323960619286</v>
+        <v>54.25001049430864</v>
       </c>
       <c r="U87" t="n">
-        <v>0.9269233725330537</v>
+        <v>0.8293294785933938</v>
       </c>
       <c r="V87" t="n">
-        <v>0.4015842147598008</v>
+        <v>0.4015842193181136</v>
       </c>
       <c r="W87" t="b">
         <v>1</v>
@@ -6857,28 +6857,28 @@
         <v>1</v>
       </c>
       <c r="O88" t="n">
-        <v>0.9993531415271683</v>
+        <v>0.9986307059018253</v>
       </c>
       <c r="P88" t="n">
-        <v>0.001687135502335879</v>
+        <v>0.001779694656980572</v>
       </c>
       <c r="Q88" t="n">
-        <v>818.9382887977189</v>
+        <v>817.6554609556013</v>
       </c>
       <c r="R88" t="n">
-        <v>238.1247089198715</v>
+        <v>239.1172318489688</v>
       </c>
       <c r="S88" t="n">
-        <v>9.553691560535309</v>
+        <v>9.547799124078217</v>
       </c>
       <c r="T88" t="n">
-        <v>125.6839373911845</v>
+        <v>126.9667652333021</v>
       </c>
       <c r="U88" t="n">
-        <v>24.92232017721557</v>
+        <v>23.92979724811832</v>
       </c>
       <c r="V88" t="n">
-        <v>0.05872754820912007</v>
+        <v>0.0646199846662121</v>
       </c>
       <c r="W88" t="b">
         <v>1</v>
@@ -6930,28 +6930,28 @@
         <v>1</v>
       </c>
       <c r="O89" t="n">
-        <v>0.8577642243197116</v>
+        <v>0.8511362929325419</v>
       </c>
       <c r="P89" t="n">
-        <v>0.0007683347517901382</v>
+        <v>0.0008210226646968817</v>
       </c>
       <c r="Q89" t="n">
-        <v>942.1841852943093</v>
+        <v>945.6772694944309</v>
       </c>
       <c r="R89" t="n">
-        <v>201.451960927629</v>
+        <v>201.6191501323349</v>
       </c>
       <c r="S89" t="n">
-        <v>9.00005786540785</v>
+        <v>9.000057867690298</v>
       </c>
       <c r="T89" t="n">
-        <v>79.01731322153148</v>
+        <v>82.51039742165312</v>
       </c>
       <c r="U89" t="n">
-        <v>1.005889246182875</v>
+        <v>0.8387000414770114</v>
       </c>
       <c r="V89" t="n">
-        <v>0.7426780098311578</v>
+        <v>0.7426780121136058</v>
       </c>
       <c r="W89" t="b">
         <v>1</v>
@@ -7003,28 +7003,28 @@
         <v>1</v>
       </c>
       <c r="O90" t="n">
-        <v>0.9473558225655059</v>
+        <v>0.9262151264979197</v>
       </c>
       <c r="P90" t="n">
-        <v>0.001713693887865423</v>
+        <v>0.001737298450509479</v>
       </c>
       <c r="Q90" t="n">
-        <v>839.8954072031228</v>
+        <v>840.2943356540662</v>
       </c>
       <c r="R90" t="n">
-        <v>199.3711627963716</v>
+        <v>199.3948084364884</v>
       </c>
       <c r="S90" t="n">
-        <v>13.08424536513067</v>
+        <v>13.11884733089248</v>
       </c>
       <c r="T90" t="n">
-        <v>144.0056136054923</v>
+        <v>143.6066851545488</v>
       </c>
       <c r="U90" t="n">
-        <v>0.883136653342774</v>
+        <v>0.9067822934595995</v>
       </c>
       <c r="V90" t="n">
-        <v>0.6847437109244918</v>
+        <v>0.6501417451626867</v>
       </c>
       <c r="W90" t="b">
         <v>1</v>
@@ -7076,28 +7076,28 @@
         <v>1</v>
       </c>
       <c r="O91" t="n">
-        <v>0.9882337561435889</v>
+        <v>0.9775344829919823</v>
       </c>
       <c r="P91" t="n">
-        <v>0.00135852531626458</v>
+        <v>0.001449320043861181</v>
       </c>
       <c r="Q91" t="n">
-        <v>837.698140265108</v>
+        <v>836.3444044785281</v>
       </c>
       <c r="R91" t="n">
-        <v>229.9290947021141</v>
+        <v>230.5622105687933</v>
       </c>
       <c r="S91" t="n">
-        <v>9.477537641904293</v>
+        <v>9.47193105192968</v>
       </c>
       <c r="T91" t="n">
-        <v>106.496368851119</v>
+        <v>107.8501046376989</v>
       </c>
       <c r="U91" t="n">
-        <v>18.83216992935155</v>
+        <v>18.19905406267233</v>
       </c>
       <c r="V91" t="n">
-        <v>0.05273256160610984</v>
+        <v>0.05833915158072323</v>
       </c>
       <c r="W91" t="b">
         <v>1</v>
@@ -7149,28 +7149,28 @@
         <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>0.8153352059091716</v>
+        <v>0.8599177692213379</v>
       </c>
       <c r="P92" t="n">
-        <v>0.0006264322143201939</v>
+        <v>0.0006763184669479458</v>
       </c>
       <c r="Q92" t="n">
-        <v>942.5488295184717</v>
+        <v>945.7285221442801</v>
       </c>
       <c r="R92" t="n">
-        <v>208.8502911972969</v>
+        <v>209.0856916349678</v>
       </c>
       <c r="S92" t="n">
-        <v>11.2826747603838</v>
+        <v>11.2794832144418</v>
       </c>
       <c r="T92" t="n">
-        <v>66.19840155530801</v>
+        <v>69.37809418111635</v>
       </c>
       <c r="U92" t="n">
-        <v>1.098642151586915</v>
+        <v>0.8632417139160395</v>
       </c>
       <c r="V92" t="n">
-        <v>0.0632002427939149</v>
+        <v>0.06639178873592044</v>
       </c>
       <c r="W92" t="b">
         <v>1</v>
@@ -7222,28 +7222,28 @@
         <v>1</v>
       </c>
       <c r="O93" t="n">
-        <v>0.9989035357889861</v>
+        <v>0.9971472325905434</v>
       </c>
       <c r="P93" t="n">
-        <v>0.0005829023441392633</v>
+        <v>0.0006864910528413771</v>
       </c>
       <c r="Q93" t="n">
-        <v>957.3671172764099</v>
+        <v>955.9335619967439</v>
       </c>
       <c r="R93" t="n">
-        <v>199.9317826026219</v>
+        <v>200.0043579965127</v>
       </c>
       <c r="S93" t="n">
-        <v>9.631534542727458</v>
+        <v>9.634533990032214</v>
       </c>
       <c r="T93" t="n">
-        <v>103.4421228095993</v>
+        <v>104.8756780892652</v>
       </c>
       <c r="U93" t="n">
-        <v>0.3044234215245751</v>
+        <v>0.2318480276338448</v>
       </c>
       <c r="V93" t="n">
-        <v>0.0004176456644824356</v>
+        <v>0.003417092969238311</v>
       </c>
       <c r="W93" t="b">
         <v>1</v>
@@ -7295,28 +7295,28 @@
         <v>1</v>
       </c>
       <c r="O94" t="n">
-        <v>0.9998900281081606</v>
+        <v>0.9998778420671173</v>
       </c>
       <c r="P94" t="n">
-        <v>0.002004033270910592</v>
+        <v>0.002115461938069771</v>
       </c>
       <c r="Q94" t="n">
-        <v>809.2758483455329</v>
+        <v>808.8370170697486</v>
       </c>
       <c r="R94" t="n">
-        <v>150.0000472877422</v>
+        <v>150.0000472886719</v>
       </c>
       <c r="S94" t="n">
-        <v>10.39853357254134</v>
+        <v>10.41300028484139</v>
       </c>
       <c r="T94" t="n">
-        <v>163.7711244337056</v>
+        <v>164.2099557094899</v>
       </c>
       <c r="U94" t="n">
-        <v>25.33347718328932</v>
+        <v>25.33347718421902</v>
       </c>
       <c r="V94" t="n">
-        <v>0.07934536355471522</v>
+        <v>0.0648786512546593</v>
       </c>
       <c r="W94" t="b">
         <v>1</v>
@@ -7368,28 +7368,28 @@
         <v>1</v>
       </c>
       <c r="O95" t="n">
-        <v>0.9996780981033778</v>
+        <v>0.9995460724268719</v>
       </c>
       <c r="P95" t="n">
-        <v>0.002547836813188511</v>
+        <v>0.002489114810205524</v>
       </c>
       <c r="Q95" t="n">
-        <v>800.0000005995885</v>
+        <v>801.0047840845582</v>
       </c>
       <c r="R95" t="n">
-        <v>204.904125831805</v>
+        <v>204.9086887932281</v>
       </c>
       <c r="S95" t="n">
-        <v>14.9066245559576</v>
+        <v>14.99994213185762</v>
       </c>
       <c r="T95" t="n">
-        <v>162.0516047599783</v>
+        <v>161.0468212750086</v>
       </c>
       <c r="U95" t="n">
-        <v>0.5796947275619004</v>
+        <v>0.5842576889849624</v>
       </c>
       <c r="V95" t="n">
-        <v>1.185719413796509</v>
+        <v>1.092401837896491</v>
       </c>
       <c r="W95" t="b">
         <v>1</v>
@@ -7441,28 +7441,28 @@
         <v>1</v>
       </c>
       <c r="O96" t="n">
-        <v>0.9997003099067855</v>
+        <v>0.9997724854317206</v>
       </c>
       <c r="P96" t="n">
-        <v>0.001563233690525028</v>
+        <v>0.001657856811156112</v>
       </c>
       <c r="Q96" t="n">
-        <v>812.0174921107624</v>
+        <v>810.9974287912703</v>
       </c>
       <c r="R96" t="n">
-        <v>150.0000472864174</v>
+        <v>150.0000472868553</v>
       </c>
       <c r="S96" t="n">
-        <v>9.219186697060195</v>
+        <v>9.219603389999154</v>
       </c>
       <c r="T96" t="n">
-        <v>117.2563229417622</v>
+        <v>118.2763862612543</v>
       </c>
       <c r="U96" t="n">
-        <v>25.41830174652767</v>
+        <v>25.4183017469656</v>
       </c>
       <c r="V96" t="n">
-        <v>0.0652688831812771</v>
+        <v>0.06485219024231803</v>
       </c>
       <c r="W96" t="b">
         <v>1</v>
@@ -7514,28 +7514,28 @@
         <v>1</v>
       </c>
       <c r="O97" t="n">
-        <v>0.9606179555357727</v>
+        <v>0.9128046873457122</v>
       </c>
       <c r="P97" t="n">
-        <v>0.0004566143107414854</v>
+        <v>0.0005380867177944855</v>
       </c>
       <c r="Q97" t="n">
-        <v>950.7338272738875</v>
+        <v>949.5141872923681</v>
       </c>
       <c r="R97" t="n">
-        <v>212.6779086444871</v>
+        <v>212.7202238743716</v>
       </c>
       <c r="S97" t="n">
-        <v>11.08782501383651</v>
+        <v>11.08650552326533</v>
       </c>
       <c r="T97" t="n">
-        <v>71.69583585944474</v>
+        <v>72.91547584096418</v>
       </c>
       <c r="U97" t="n">
-        <v>1.015625031290597</v>
+        <v>0.973309801406117</v>
       </c>
       <c r="V97" t="n">
-        <v>0.02860573494569607</v>
+        <v>0.02992522551687493</v>
       </c>
       <c r="W97" t="b">
         <v>1</v>
@@ -7587,28 +7587,28 @@
         <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>0.9992326166729234</v>
+        <v>0.999296996534649</v>
       </c>
       <c r="P98" t="n">
-        <v>0.001507563620875813</v>
+        <v>0.001594043117660707</v>
       </c>
       <c r="Q98" t="n">
-        <v>805.1864964063076</v>
+        <v>804.7393832002284</v>
       </c>
       <c r="R98" t="n">
-        <v>150.0000472887688</v>
+        <v>150.0000472900304</v>
       </c>
       <c r="S98" t="n">
-        <v>10.57059963391205</v>
+        <v>10.58237920855332</v>
       </c>
       <c r="T98" t="n">
-        <v>102.7218476183858</v>
+        <v>103.168960824465</v>
       </c>
       <c r="U98" t="n">
-        <v>21.65589294585297</v>
+        <v>21.65589294711461</v>
       </c>
       <c r="V98" t="n">
-        <v>0.05887686320242302</v>
+        <v>0.04709728856115447</v>
       </c>
       <c r="W98" t="b">
         <v>1</v>
@@ -7660,28 +7660,28 @@
         <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>0.8558815783183614</v>
+        <v>0.8824982214395597</v>
       </c>
       <c r="P99" t="n">
-        <v>0.0006911895152332209</v>
+        <v>0.0007395499293089758</v>
       </c>
       <c r="Q99" t="n">
-        <v>941.0594335434713</v>
+        <v>944.1241120697684</v>
       </c>
       <c r="R99" t="n">
-        <v>211.6327696334628</v>
+        <v>211.8757752146327</v>
       </c>
       <c r="S99" t="n">
-        <v>10.97200158742111</v>
+        <v>10.97105843762282</v>
       </c>
       <c r="T99" t="n">
-        <v>72.62238928674083</v>
+        <v>75.68706781303797</v>
       </c>
       <c r="U99" t="n">
-        <v>1.488462458293782</v>
+        <v>1.245456877123956</v>
       </c>
       <c r="V99" t="n">
-        <v>0.05775657688791647</v>
+        <v>0.0586997266862106</v>
       </c>
       <c r="W99" t="b">
         <v>1</v>
@@ -7733,28 +7733,28 @@
         <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>0.9977736881314933</v>
+        <v>0.9968660788395162</v>
       </c>
       <c r="P100" t="n">
-        <v>0.002164460308084747</v>
+        <v>0.002151857035013566</v>
       </c>
       <c r="Q100" t="n">
-        <v>816.361870961309</v>
+        <v>817.4198050524553</v>
       </c>
       <c r="R100" t="n">
-        <v>206.1771441246076</v>
+        <v>206.1928410189711</v>
       </c>
       <c r="S100" t="n">
-        <v>14.17970498194673</v>
+        <v>14.23725958088068</v>
       </c>
       <c r="T100" t="n">
-        <v>152.7888723042863</v>
+        <v>151.73093821314</v>
       </c>
       <c r="U100" t="n">
-        <v>0.4146302043864125</v>
+        <v>0.4303270987498991</v>
       </c>
       <c r="V100" t="n">
-        <v>0.9380897322272368</v>
+        <v>0.8805351332932911</v>
       </c>
       <c r="W100" t="b">
         <v>1</v>
@@ -7806,28 +7806,28 @@
         <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>0.9995946372735726</v>
+        <v>0.9995852359882401</v>
       </c>
       <c r="P101" t="n">
-        <v>0.001910393958052752</v>
+        <v>0.002021378079006431</v>
       </c>
       <c r="Q101" t="n">
-        <v>810.4329883279124</v>
+        <v>809.7399962441003</v>
       </c>
       <c r="R101" t="n">
-        <v>150.0000472877453</v>
+        <v>150.0000472891086</v>
       </c>
       <c r="S101" t="n">
-        <v>10.00214042873084</v>
+        <v>10.01172077475117</v>
       </c>
       <c r="T101" t="n">
-        <v>154.0689274090475</v>
+        <v>154.7619194928596</v>
       </c>
       <c r="U101" t="n">
-        <v>16.66917760165975</v>
+        <v>16.66917760302309</v>
       </c>
       <c r="V101" t="n">
-        <v>0.07522330155325818</v>
+        <v>0.06564295553292787</v>
       </c>
       <c r="W101" t="b">
         <v>1</v>

--- a/export_dati/06_Step6_Simulazione_Massiva_100.xlsx
+++ b/export_dati/06_Step6_Simulazione_Massiva_100.xlsx
@@ -489,47 +489,47 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Prob_Iniziale_MLP</t>
+          <t>Prob_Iniziale_TensorFlow</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Prob_Finale_MLP</t>
+          <t>Prob_Finale_TensorFlow</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Temp_Finale_MLP</t>
+          <t>Temp_Finale_TensorFlow</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Press_Finale_MLP</t>
+          <t>Press_Finale_TensorFlow</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Vel_Finale_MLP</t>
+          <t>Vel_Finale_TensorFlow</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Delta_Temp_MLP</t>
+          <t>Delta_Temp_TensorFlow</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Delta_Press_MLP</t>
+          <t>Delta_Press_TensorFlow</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Delta_Vel_MLP</t>
+          <t>Delta_Vel_TensorFlow</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Successo_MLP</t>
+          <t>Successo_TensorFlow</t>
         </is>
       </c>
     </row>
@@ -539,68 +539,68 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1030.583435716369</v>
+        <v>946.9778445568023</v>
       </c>
       <c r="D2" t="n">
-        <v>8.757435997200295</v>
+        <v>10.25061390415358</v>
       </c>
       <c r="E2" t="n">
-        <v>190.0120312499433</v>
+        <v>121.3394806969968</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6508126258850098</v>
+        <v>0.936724841594696</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007977633737027645</v>
+        <v>0.008770139887928963</v>
       </c>
       <c r="H2" t="n">
-        <v>965.6040331780204</v>
+        <v>961.9639154094285</v>
       </c>
       <c r="I2" t="n">
-        <v>190.0120312499433</v>
+        <v>164.2910916663061</v>
       </c>
       <c r="J2" t="n">
-        <v>9.00005786666981</v>
+        <v>10.2506139133091</v>
       </c>
       <c r="K2" t="n">
-        <v>64.97940253834884</v>
+        <v>14.9860708526262</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>42.95161096930933</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2426218694695148</v>
+        <v>9.15552256230967e-09</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9269339875444544</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0.000571814265090467</v>
+        <v>0.006659499369561672</v>
       </c>
       <c r="Q2" t="n">
-        <v>953.4739960882771</v>
+        <v>800.0000219124043</v>
       </c>
       <c r="R2" t="n">
-        <v>190.3160917381414</v>
+        <v>153.8185114094987</v>
       </c>
       <c r="S2" t="n">
-        <v>9.000057869985689</v>
+        <v>9.235524845135297</v>
       </c>
       <c r="T2" t="n">
-        <v>77.1094396280921</v>
+        <v>146.977822644398</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3040604881981608</v>
+        <v>32.47903071250188</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2426218727853939</v>
+        <v>1.015089059018282</v>
       </c>
       <c r="W2" t="b">
         <v>1</v>
@@ -616,64 +616,64 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>958.7264733934807</v>
+        <v>944.3042118096921</v>
       </c>
       <c r="D3" t="n">
-        <v>11.59811089575176</v>
+        <v>8.944074329837868</v>
       </c>
       <c r="E3" t="n">
-        <v>131.5485056501628</v>
+        <v>123.3414099489059</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7905983924865723</v>
+        <v>0.9283017516136169</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01447403151541948</v>
+        <v>0.01065392885357141</v>
       </c>
       <c r="H3" t="n">
-        <v>958.7264733942761</v>
+        <v>913.9203041578202</v>
       </c>
       <c r="I3" t="n">
-        <v>176.1525536259194</v>
+        <v>172.0412147838669</v>
       </c>
       <c r="J3" t="n">
-        <v>11.59811089573376</v>
+        <v>10.2133161481209</v>
       </c>
       <c r="K3" t="n">
-        <v>7.954668035381474e-10</v>
+        <v>30.38390765187194</v>
       </c>
       <c r="L3" t="n">
-        <v>44.60404797575669</v>
+        <v>48.69980483496101</v>
       </c>
       <c r="M3" t="n">
-        <v>1.799982385364274e-11</v>
+        <v>1.269241818283033</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9995815054235507</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002070304312487993</v>
+        <v>0.00610250374302268</v>
       </c>
       <c r="Q3" t="n">
-        <v>805.1042191866012</v>
+        <v>800.0000297768911</v>
       </c>
       <c r="R3" t="n">
-        <v>150.0000472891128</v>
+        <v>153.2155563052054</v>
       </c>
       <c r="S3" t="n">
-        <v>11.53170340464211</v>
+        <v>9.000642056348982</v>
       </c>
       <c r="T3" t="n">
-        <v>153.6222542068795</v>
+        <v>144.304182032801</v>
       </c>
       <c r="U3" t="n">
-        <v>18.45154163895003</v>
+        <v>29.87414635629949</v>
       </c>
       <c r="V3" t="n">
-        <v>0.06640749110964705</v>
+        <v>0.05656772651111375</v>
       </c>
       <c r="W3" t="b">
         <v>1</v>
@@ -685,68 +685,68 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>889.7896881509041</v>
+        <v>904.715095600088</v>
       </c>
       <c r="D4" t="n">
-        <v>7.199121975290029</v>
+        <v>6.107927575160065</v>
       </c>
       <c r="E4" t="n">
-        <v>192.8925602011192</v>
+        <v>187.2758413485633</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7487070560455322</v>
+        <v>0.5180330276489258</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0107807656750083</v>
+        <v>0.0006940661114640534</v>
       </c>
       <c r="H4" t="n">
-        <v>928.8432674690713</v>
+        <v>918.8325213643333</v>
       </c>
       <c r="I4" t="n">
-        <v>192.8925602011192</v>
+        <v>187.2757770889637</v>
       </c>
       <c r="J4" t="n">
-        <v>9.000057868187181</v>
+        <v>9.0006415701978</v>
       </c>
       <c r="K4" t="n">
-        <v>39.05357931816718</v>
+        <v>14.11742576424524</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>6.425959961120498e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.800935892897152</v>
+        <v>2.892713995037735</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9262714254362029</v>
+        <v>0.09352170675992966</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0005536665631668084</v>
+        <v>0.0001489813439548016</v>
       </c>
       <c r="Q4" t="n">
-        <v>947.7381755119324</v>
+        <v>905.5404680892183</v>
       </c>
       <c r="R4" t="n">
-        <v>192.8577935277279</v>
+        <v>187.4784567056928</v>
       </c>
       <c r="S4" t="n">
-        <v>9.000057869167906</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T4" t="n">
-        <v>57.94848736102824</v>
+        <v>0.8253724891302454</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0347666733912888</v>
+        <v>0.202615357129531</v>
       </c>
       <c r="V4" t="n">
-        <v>1.800935893877877</v>
+        <v>2.892714204702098</v>
       </c>
       <c r="W4" t="b">
         <v>1</v>
@@ -758,68 +758,68 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>947.4096550627312</v>
+        <v>873.427052571014</v>
       </c>
       <c r="D5" t="n">
-        <v>10.09912579247616</v>
+        <v>8.978020743857002</v>
       </c>
       <c r="E5" t="n">
-        <v>154.8411189826099</v>
+        <v>188.4813806348763</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7905983924865723</v>
+        <v>0.6949636340141296</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01447403151541948</v>
+        <v>0.001017419970594347</v>
       </c>
       <c r="H5" t="n">
-        <v>947.4096239677104</v>
+        <v>919.4282413549977</v>
       </c>
       <c r="I5" t="n">
-        <v>176.1525977521421</v>
+        <v>188.4813806348763</v>
       </c>
       <c r="J5" t="n">
-        <v>10.02799875499174</v>
+        <v>9.329040318616576</v>
       </c>
       <c r="K5" t="n">
-        <v>3.10950207449423e-05</v>
+        <v>46.00118878398371</v>
       </c>
       <c r="L5" t="n">
-        <v>21.31147876953219</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07112703748441973</v>
+        <v>0.3510195747595741</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9672264356887684</v>
+        <v>0.5460717678070068</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001513710548740302</v>
+        <v>0.0004996052011847496</v>
       </c>
       <c r="Q5" t="n">
-        <v>828.7038736334952</v>
+        <v>932.9256879424437</v>
       </c>
       <c r="R5" t="n">
-        <v>161.248687507975</v>
+        <v>189.1457888726968</v>
       </c>
       <c r="S5" t="n">
-        <v>10.05310231141007</v>
+        <v>9.055393497055434</v>
       </c>
       <c r="T5" t="n">
-        <v>118.705781429236</v>
+        <v>59.49863537142971</v>
       </c>
       <c r="U5" t="n">
-        <v>6.40756852536515</v>
+        <v>0.6644082378205098</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04602348106608645</v>
+        <v>0.07737275319843206</v>
       </c>
       <c r="W5" t="b">
         <v>1</v>
@@ -831,68 +831,68 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>918.6608125766529</v>
+        <v>862.8168537192801</v>
       </c>
       <c r="D6" t="n">
-        <v>9.891146119267299</v>
+        <v>9.055073258720897</v>
       </c>
       <c r="E6" t="n">
-        <v>137.2264260381309</v>
+        <v>186.3258914472227</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7801960110664368</v>
+        <v>0.6867222785949707</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01369568612426519</v>
+        <v>0.001256016083061695</v>
       </c>
       <c r="H6" t="n">
-        <v>910.503660416069</v>
+        <v>919.4282392833672</v>
       </c>
       <c r="I6" t="n">
-        <v>176.1525536435829</v>
+        <v>186.3258914472227</v>
       </c>
       <c r="J6" t="n">
-        <v>9.896847925488609</v>
+        <v>9.103639971063563</v>
       </c>
       <c r="K6" t="n">
-        <v>8.157152160583905</v>
+        <v>56.61138556408719</v>
       </c>
       <c r="L6" t="n">
-        <v>38.92612760545202</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.005701806221310335</v>
+        <v>0.04856671234266585</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9980126380382254</v>
+        <v>0.5865327715873718</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001634785038524356</v>
+        <v>0.0005892477347515523</v>
       </c>
       <c r="Q6" t="n">
-        <v>807.8401037577198</v>
+        <v>931.215072320197</v>
       </c>
       <c r="R6" t="n">
-        <v>150.000047288629</v>
+        <v>187.0908162274205</v>
       </c>
       <c r="S6" t="n">
-        <v>9.836657571320121</v>
+        <v>9.146899377497578</v>
       </c>
       <c r="T6" t="n">
-        <v>110.8207088189331</v>
+        <v>68.39821860091695</v>
       </c>
       <c r="U6" t="n">
-        <v>12.77362125049811</v>
+        <v>0.7649247801978163</v>
       </c>
       <c r="V6" t="n">
-        <v>0.05448854794717839</v>
+        <v>0.09182611877668023</v>
       </c>
       <c r="W6" t="b">
         <v>1</v>
@@ -904,68 +904,68 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>973.2947870891435</v>
+        <v>847.2631338004336</v>
       </c>
       <c r="D7" t="n">
-        <v>5.472803755358099</v>
+        <v>9.172488831188625</v>
       </c>
       <c r="E7" t="n">
-        <v>203.862115546625</v>
+        <v>189.3189149000324</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6932011246681213</v>
+        <v>0.7424965500831604</v>
       </c>
       <c r="G7" t="n">
-        <v>0.005476452875882387</v>
+        <v>0.001017419970594347</v>
       </c>
       <c r="H7" t="n">
-        <v>973.294787089135</v>
+        <v>919.4282395837976</v>
       </c>
       <c r="I7" t="n">
-        <v>203.8621155466249</v>
+        <v>189.3189149000324</v>
       </c>
       <c r="J7" t="n">
-        <v>9.000057869254071</v>
+        <v>9.328631572554473</v>
       </c>
       <c r="K7" t="n">
-        <v>8.526512829121202e-12</v>
+        <v>72.16510578336397</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4210854715202e-13</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.527254113895973</v>
+        <v>0.1561427413658478</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9623213690697382</v>
+        <v>0.6044442057609558</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001502235201471605</v>
+        <v>0.0007164647686295211</v>
       </c>
       <c r="Q7" t="n">
-        <v>961.6812693999583</v>
+        <v>927.4571806157584</v>
       </c>
       <c r="R7" t="n">
-        <v>201.9872809663549</v>
+        <v>190.2719624961</v>
       </c>
       <c r="S7" t="n">
-        <v>9.000057869254071</v>
+        <v>9.285528667324632</v>
       </c>
       <c r="T7" t="n">
-        <v>11.61351768918519</v>
+        <v>80.19404681532478</v>
       </c>
       <c r="U7" t="n">
-        <v>1.874834580270175</v>
+        <v>0.9530475960675631</v>
       </c>
       <c r="V7" t="n">
-        <v>3.527254113895973</v>
+        <v>0.1130398361360072</v>
       </c>
       <c r="W7" t="b">
         <v>1</v>
@@ -977,68 +977,68 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>891.692935376087</v>
+        <v>958.80278331025</v>
       </c>
       <c r="D8" t="n">
-        <v>6.529474736408524</v>
+        <v>10.28318524302703</v>
       </c>
       <c r="E8" t="n">
-        <v>213.6274082699896</v>
+        <v>160.5893325834675</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7614838480949402</v>
+        <v>0.9366707801818848</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0107807656750083</v>
+        <v>0.0004814271233044565</v>
       </c>
       <c r="H8" t="n">
-        <v>928.843267464791</v>
+        <v>958.8037626434731</v>
       </c>
       <c r="I8" t="n">
-        <v>213.6274082699897</v>
+        <v>176.1296281525858</v>
       </c>
       <c r="J8" t="n">
-        <v>9.000057867726536</v>
+        <v>10.28318697955493</v>
       </c>
       <c r="K8" t="n">
-        <v>37.15033208870398</v>
+        <v>0.0009793332230856322</v>
       </c>
       <c r="L8" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>15.54029556911834</v>
       </c>
       <c r="M8" t="n">
-        <v>2.470583131318012</v>
+        <v>1.736527895701556e-06</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9182172922384561</v>
+        <v>0.9719220995903015</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0006013376516738945</v>
+        <v>0.001231190282851458</v>
       </c>
       <c r="Q8" t="n">
-        <v>951.2388149432117</v>
+        <v>825.9301997375334</v>
       </c>
       <c r="R8" t="n">
-        <v>212.1911934077939</v>
+        <v>171.0947458983082</v>
       </c>
       <c r="S8" t="n">
-        <v>9.000057843535902</v>
+        <v>10.19636104480619</v>
       </c>
       <c r="T8" t="n">
-        <v>59.54587956712464</v>
+        <v>132.8725835727166</v>
       </c>
       <c r="U8" t="n">
-        <v>1.436214862195669</v>
+        <v>10.50541331484075</v>
       </c>
       <c r="V8" t="n">
-        <v>2.470583107127378</v>
+        <v>0.08682419822084064</v>
       </c>
       <c r="W8" t="b">
         <v>1</v>
@@ -1054,64 +1054,64 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>962.7980591430417</v>
+        <v>928.6179141766808</v>
       </c>
       <c r="D9" t="n">
-        <v>9.921830063864206</v>
+        <v>8.764360589699487</v>
       </c>
       <c r="E9" t="n">
-        <v>168.4091198645476</v>
+        <v>105.423870623254</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6174015402793884</v>
+        <v>0.931891918182373</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0120297921821475</v>
+        <v>0.005232266616076231</v>
       </c>
       <c r="H9" t="n">
-        <v>920.4421048968439</v>
+        <v>922.2378914997506</v>
       </c>
       <c r="I9" t="n">
-        <v>181.79132652353</v>
+        <v>173.6136106608438</v>
       </c>
       <c r="J9" t="n">
-        <v>9.627733510352812</v>
+        <v>9.886858219649927</v>
       </c>
       <c r="K9" t="n">
-        <v>42.35595424619771</v>
+        <v>6.380022676930139</v>
       </c>
       <c r="L9" t="n">
-        <v>13.3822066589824</v>
+        <v>68.1897400375898</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2940965535113946</v>
+        <v>1.122497629950439</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5041579765801472</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001215904094541128</v>
+        <v>0.01186289545148611</v>
       </c>
       <c r="Q9" t="n">
-        <v>855.4096393258563</v>
+        <v>800.0000277327417</v>
       </c>
       <c r="R9" t="n">
-        <v>175.2284062726977</v>
+        <v>151.17209527343</v>
       </c>
       <c r="S9" t="n">
-        <v>9.884756168044577</v>
+        <v>9.000642108477239</v>
       </c>
       <c r="T9" t="n">
-        <v>107.3884198171853</v>
+        <v>128.617886443939</v>
       </c>
       <c r="U9" t="n">
-        <v>6.819286408150163</v>
+        <v>45.74822465017603</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0370738958196295</v>
+        <v>0.2362815187777514</v>
       </c>
       <c r="W9" t="b">
         <v>1</v>
@@ -1123,68 +1123,68 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>948.0164827244123</v>
+        <v>960.6999207074333</v>
       </c>
       <c r="D10" t="n">
-        <v>9.65283851758155</v>
+        <v>13.60431810949872</v>
       </c>
       <c r="E10" t="n">
-        <v>119.4428441979827</v>
+        <v>210.2668897524188</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7905983924865723</v>
+        <v>0.9146213531494141</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01428452972322702</v>
+        <v>0.0002867737784981728</v>
       </c>
       <c r="H10" t="n">
-        <v>948.995939460207</v>
+        <v>928.0985965868126</v>
       </c>
       <c r="I10" t="n">
-        <v>176.1525536257258</v>
+        <v>209.7307690011954</v>
       </c>
       <c r="J10" t="n">
-        <v>11.95381848092063</v>
+        <v>11.82175029222345</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9794567357946562</v>
+        <v>32.60132412062069</v>
       </c>
       <c r="L10" t="n">
-        <v>56.70970942774312</v>
+        <v>0.5361207512234216</v>
       </c>
       <c r="M10" t="n">
-        <v>2.300979963339083</v>
+        <v>1.782567817275266</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9999295997973171</v>
+        <v>0.5614466667175293</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001853967366114005</v>
+        <v>0.001731006195768714</v>
       </c>
       <c r="Q10" t="n">
-        <v>810.4950795130085</v>
+        <v>816.8216669343834</v>
       </c>
       <c r="R10" t="n">
-        <v>150.0000472884115</v>
+        <v>210.6084233075179</v>
       </c>
       <c r="S10" t="n">
-        <v>9.586667418640062</v>
+        <v>12.7822833483868</v>
       </c>
       <c r="T10" t="n">
-        <v>137.5214032114038</v>
+        <v>143.8782537730499</v>
       </c>
       <c r="U10" t="n">
-        <v>30.55720309042886</v>
+        <v>0.3415335550990335</v>
       </c>
       <c r="V10" t="n">
-        <v>0.06617109894148854</v>
+        <v>0.8220347611119241</v>
       </c>
       <c r="W10" t="b">
         <v>1</v>
@@ -1200,64 +1200,64 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>865.5234941240955</v>
+        <v>850.8627711339921</v>
       </c>
       <c r="D11" t="n">
-        <v>5.794056617050133</v>
+        <v>7.301350401444483</v>
       </c>
       <c r="E11" t="n">
-        <v>185.7493322485568</v>
+        <v>213.6171334391107</v>
       </c>
       <c r="F11" t="n">
-        <v>0.755632221698761</v>
+        <v>0.8791069388389587</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0107807656750083</v>
+        <v>0.001712197670713067</v>
       </c>
       <c r="H11" t="n">
-        <v>928.843267497137</v>
+        <v>918.8490055847537</v>
       </c>
       <c r="I11" t="n">
-        <v>185.7493322485568</v>
+        <v>210.2246188077564</v>
       </c>
       <c r="J11" t="n">
-        <v>9.000057868141909</v>
+        <v>9.000641764210666</v>
       </c>
       <c r="K11" t="n">
-        <v>63.31977337304158</v>
+        <v>67.98623445076169</v>
       </c>
       <c r="L11" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>3.392514631354288</v>
       </c>
       <c r="M11" t="n">
-        <v>3.206001251091775</v>
+        <v>1.699291362766183</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9797486231851009</v>
+        <v>0.9576789736747742</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0008077019984873753</v>
+        <v>0.0007729309727437794</v>
       </c>
       <c r="Q11" t="n">
-        <v>945.1905645476064</v>
+        <v>929.039341052369</v>
       </c>
       <c r="R11" t="n">
-        <v>186.1041766319713</v>
+        <v>211.9593253659875</v>
       </c>
       <c r="S11" t="n">
-        <v>9.000057869339136</v>
+        <v>9.000641545307294</v>
       </c>
       <c r="T11" t="n">
-        <v>79.66707042351095</v>
+        <v>78.17656991837691</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3548443834145871</v>
+        <v>1.657808073123192</v>
       </c>
       <c r="V11" t="n">
-        <v>3.206001252289003</v>
+        <v>1.699291143862811</v>
       </c>
       <c r="W11" t="b">
         <v>1</v>
@@ -1269,68 +1269,68 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>953.1618975173362</v>
+        <v>873.9455507441398</v>
       </c>
       <c r="D12" t="n">
-        <v>9.743266196519947</v>
+        <v>9.760608195236596</v>
       </c>
       <c r="E12" t="n">
-        <v>146.1562239411741</v>
+        <v>210.7181823014149</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7905983924865723</v>
+        <v>0.700507640838623</v>
       </c>
       <c r="G12" t="n">
-        <v>0.06394846737384796</v>
+        <v>0.0009920429438352585</v>
       </c>
       <c r="H12" t="n">
-        <v>963.478800228988</v>
+        <v>919.4282410300033</v>
       </c>
       <c r="I12" t="n">
-        <v>176.0443521145514</v>
+        <v>210.7181830589438</v>
       </c>
       <c r="J12" t="n">
-        <v>9.780498845503187</v>
+        <v>9.760608195236605</v>
       </c>
       <c r="K12" t="n">
-        <v>10.31690271165178</v>
+        <v>45.48269028586344</v>
       </c>
       <c r="L12" t="n">
-        <v>29.88812817337725</v>
+        <v>7.575289089345461e-07</v>
       </c>
       <c r="M12" t="n">
-        <v>0.03723264898323997</v>
+        <v>8.881784197001252e-15</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0.995183737798693</v>
+        <v>0.292863667011261</v>
       </c>
       <c r="P12" t="n">
-        <v>0.001812900675894847</v>
+        <v>0.0004289619973860681</v>
       </c>
       <c r="Q12" t="n">
-        <v>814.9601914464938</v>
+        <v>924.195031144189</v>
       </c>
       <c r="R12" t="n">
-        <v>152.6025294723253</v>
+        <v>210.2009476065454</v>
       </c>
       <c r="S12" t="n">
-        <v>9.680022241534479</v>
+        <v>9.818198186311022</v>
       </c>
       <c r="T12" t="n">
-        <v>138.2017060708424</v>
+        <v>50.24948040004915</v>
       </c>
       <c r="U12" t="n">
-        <v>6.446305531151211</v>
+        <v>0.5172346948694724</v>
       </c>
       <c r="V12" t="n">
-        <v>0.06324395498546842</v>
+        <v>0.05758999107442619</v>
       </c>
       <c r="W12" t="b">
         <v>1</v>
@@ -1342,68 +1342,68 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>945.2210390626718</v>
+        <v>1009.225673939027</v>
       </c>
       <c r="D13" t="n">
-        <v>14.14363612664931</v>
+        <v>11.24199065836542</v>
       </c>
       <c r="E13" t="n">
-        <v>209.4304064156104</v>
+        <v>199.6806142356528</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7234267592430115</v>
+        <v>0.5538040995597839</v>
       </c>
       <c r="G13" t="n">
-        <v>0.008424116298556328</v>
+        <v>0.0002065182634396479</v>
       </c>
       <c r="H13" t="n">
-        <v>945.2210390363817</v>
+        <v>969.8951533578321</v>
       </c>
       <c r="I13" t="n">
-        <v>209.4304064156104</v>
+        <v>199.6806142356528</v>
       </c>
       <c r="J13" t="n">
-        <v>11.77729472198164</v>
+        <v>11.24199065836542</v>
       </c>
       <c r="K13" t="n">
-        <v>2.629008122312371e-08</v>
+        <v>39.33052058119495</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.366341404667674</v>
+        <v>0</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9655222473680127</v>
+        <v>0.2145334333181381</v>
       </c>
       <c r="P13" t="n">
-        <v>0.001636339556408885</v>
+        <v>0.0002808739664033055</v>
       </c>
       <c r="Q13" t="n">
-        <v>830.5841640560996</v>
+        <v>967.4213158193367</v>
       </c>
       <c r="R13" t="n">
-        <v>209.465373291986</v>
+        <v>199.4366567174505</v>
       </c>
       <c r="S13" t="n">
-        <v>13.53743906050636</v>
+        <v>11.20875769210023</v>
       </c>
       <c r="T13" t="n">
-        <v>114.6368750065723</v>
+        <v>41.80435811969039</v>
       </c>
       <c r="U13" t="n">
-        <v>0.03496687637556306</v>
+        <v>0.2439575182023646</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6061970661429488</v>
+        <v>0.03323296626518868</v>
       </c>
       <c r="W13" t="b">
         <v>1</v>
@@ -1415,68 +1415,68 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>971.0630570666581</v>
+        <v>1055.239264964649</v>
       </c>
       <c r="D14" t="n">
-        <v>9.721880135633667</v>
+        <v>10.47260622354199</v>
       </c>
       <c r="E14" t="n">
-        <v>246.5661183841028</v>
+        <v>201.2867700217913</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5874079465866089</v>
+        <v>0.5329121947288513</v>
       </c>
       <c r="G14" t="n">
-        <v>0.005473046097904444</v>
+        <v>0.0002065182634396479</v>
       </c>
       <c r="H14" t="n">
-        <v>971.0630570665044</v>
+        <v>969.8951533967315</v>
       </c>
       <c r="I14" t="n">
-        <v>222.3568452515523</v>
+        <v>201.2867700217913</v>
       </c>
       <c r="J14" t="n">
-        <v>9.72188013563261</v>
+        <v>10.47260622354199</v>
       </c>
       <c r="K14" t="n">
-        <v>1.537046045996249e-10</v>
+        <v>85.34411156791793</v>
       </c>
       <c r="L14" t="n">
-        <v>24.20927313255052</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.056932319443149e-12</v>
+        <v>0</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9445556656479172</v>
+        <v>0.9983097314834595</v>
       </c>
       <c r="P14" t="n">
-        <v>0.00155615750935175</v>
+        <v>0.0004108299617655575</v>
       </c>
       <c r="Q14" t="n">
-        <v>845.1653073815638</v>
+        <v>972.8587109486521</v>
       </c>
       <c r="R14" t="n">
-        <v>226.8936099544382</v>
+        <v>200.4282806604633</v>
       </c>
       <c r="S14" t="n">
-        <v>9.673316028752401</v>
+        <v>10.4479038330142</v>
       </c>
       <c r="T14" t="n">
-        <v>125.8977496850943</v>
+        <v>82.3805540159974</v>
       </c>
       <c r="U14" t="n">
-        <v>19.67250842966456</v>
+        <v>0.8584893613279689</v>
       </c>
       <c r="V14" t="n">
-        <v>0.04856410688126545</v>
+        <v>0.02470239052778389</v>
       </c>
       <c r="W14" t="b">
         <v>1</v>
@@ -1488,68 +1488,68 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>917.8748642319608</v>
+        <v>949.2196096124491</v>
       </c>
       <c r="D15" t="n">
-        <v>10.70379588375082</v>
+        <v>4.056588199894033</v>
       </c>
       <c r="E15" t="n">
-        <v>276.5087578943281</v>
+        <v>205.1094495850843</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6587895154953003</v>
+        <v>0.9323320388793945</v>
       </c>
       <c r="G15" t="n">
-        <v>0.00655886298045516</v>
+        <v>0.0005017773364670575</v>
       </c>
       <c r="H15" t="n">
-        <v>916.5766038447071</v>
+        <v>949.2196096116362</v>
       </c>
       <c r="I15" t="n">
-        <v>224.7359055555619</v>
+        <v>205.1094495850838</v>
       </c>
       <c r="J15" t="n">
-        <v>10.70379588375083</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K15" t="n">
-        <v>1.298260387253777</v>
+        <v>8.128608897095546e-10</v>
       </c>
       <c r="L15" t="n">
-        <v>51.7728523387662</v>
+        <v>5.115907697472721e-13</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06581410364015e-14</v>
+        <v>4.944053579968129</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9997107748479873</v>
+        <v>0.9959384202957153</v>
       </c>
       <c r="P15" t="n">
-        <v>0.002140514699298466</v>
+        <v>4.551598976831883e-05</v>
       </c>
       <c r="Q15" t="n">
-        <v>800.0004553692589</v>
+        <v>950.5099832745492</v>
       </c>
       <c r="R15" t="n">
-        <v>246.5507300037852</v>
+        <v>204.975883077593</v>
       </c>
       <c r="S15" t="n">
-        <v>10.7298153553938</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T15" t="n">
-        <v>117.8744088627019</v>
+        <v>1.290373662100137</v>
       </c>
       <c r="U15" t="n">
-        <v>29.95802789054292</v>
+        <v>0.1335665074912242</v>
       </c>
       <c r="V15" t="n">
-        <v>0.02601947164297869</v>
+        <v>4.944053579968129</v>
       </c>
       <c r="W15" t="b">
         <v>1</v>
@@ -1561,68 +1561,68 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>984.3808122568364</v>
+        <v>965.9137404024477</v>
       </c>
       <c r="D16" t="n">
-        <v>8.386098544521008</v>
+        <v>6.797941762263909</v>
       </c>
       <c r="E16" t="n">
-        <v>137.8953690543283</v>
+        <v>196.4419897894029</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7846513390541077</v>
+        <v>0.6720576882362366</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01447403151541948</v>
+        <v>0.0005017708754166961</v>
       </c>
       <c r="H16" t="n">
-        <v>962.4140068377019</v>
+        <v>965.913740406535</v>
       </c>
       <c r="I16" t="n">
-        <v>176.1526609190746</v>
+        <v>196.4419897894029</v>
       </c>
       <c r="J16" t="n">
-        <v>9.000000000962551</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K16" t="n">
-        <v>21.96680541913452</v>
+        <v>4.08726918976754e-09</v>
       </c>
       <c r="L16" t="n">
-        <v>38.25729186474635</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6139014564415426</v>
+        <v>2.202700017598254</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9987290286610602</v>
+        <v>0.1251122653484344</v>
       </c>
       <c r="P16" t="n">
-        <v>0.002039156083297489</v>
+        <v>5.469888128573075e-05</v>
       </c>
       <c r="Q16" t="n">
-        <v>814.7044667649247</v>
+        <v>964.9659651083233</v>
       </c>
       <c r="R16" t="n">
-        <v>150.0000472905103</v>
+        <v>196.5647414329569</v>
       </c>
       <c r="S16" t="n">
-        <v>9.000057869583411</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T16" t="n">
-        <v>169.6763454919117</v>
+        <v>0.9477752941244262</v>
       </c>
       <c r="U16" t="n">
-        <v>12.10467823618202</v>
+        <v>0.122751643554011</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6139593250624031</v>
+        <v>2.202700017598254</v>
       </c>
       <c r="W16" t="b">
         <v>1</v>
@@ -1638,64 +1638,64 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>870.079368107545</v>
+        <v>823.6010354296754</v>
       </c>
       <c r="D17" t="n">
-        <v>8.048918860873499</v>
+        <v>8.156698768960831</v>
       </c>
       <c r="E17" t="n">
-        <v>220.1393003038982</v>
+        <v>187.6051836674413</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6696656942367554</v>
+        <v>0.6394528746604919</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01023163553327322</v>
+        <v>0.001519713317975402</v>
       </c>
       <c r="H17" t="n">
-        <v>928.8443838783247</v>
+        <v>919.4282386951398</v>
       </c>
       <c r="I17" t="n">
-        <v>224.7375905032283</v>
+        <v>187.6051836674413</v>
       </c>
       <c r="J17" t="n">
-        <v>9.000057869092633</v>
+        <v>9.000382145855776</v>
       </c>
       <c r="K17" t="n">
-        <v>58.76501577077977</v>
+        <v>95.82720326546439</v>
       </c>
       <c r="L17" t="n">
-        <v>4.598290199330194</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9511390082191333</v>
+        <v>0.8436833768949441</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9065675541941576</v>
+        <v>0.8501085638999939</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0008785978085595368</v>
+        <v>0.0009994297288358212</v>
       </c>
       <c r="Q17" t="n">
-        <v>950.6607647402244</v>
+        <v>929.2178114924061</v>
       </c>
       <c r="R17" t="n">
-        <v>217.6032788711231</v>
+        <v>188.9226517882464</v>
       </c>
       <c r="S17" t="n">
-        <v>9.000057803562907</v>
+        <v>9.000641693830673</v>
       </c>
       <c r="T17" t="n">
-        <v>80.58139663267946</v>
+        <v>105.6167760627307</v>
       </c>
       <c r="U17" t="n">
-        <v>2.536021432775016</v>
+        <v>1.31746812080516</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9511389426894077</v>
+        <v>0.8439429248698413</v>
       </c>
       <c r="W17" t="b">
         <v>1</v>
@@ -1707,68 +1707,68 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>970.4327042765522</v>
+        <v>938.4531596858333</v>
       </c>
       <c r="D18" t="n">
-        <v>9.425206772784684</v>
+        <v>14.02077782303913</v>
       </c>
       <c r="E18" t="n">
-        <v>162.002639941599</v>
+        <v>202.7593789159424</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6157383918762207</v>
+        <v>0.9039955735206604</v>
       </c>
       <c r="G18" t="n">
-        <v>0.02453009411692619</v>
+        <v>0.0002902889100369066</v>
       </c>
       <c r="H18" t="n">
-        <v>880.49912995189</v>
+        <v>933.1538668597773</v>
       </c>
       <c r="I18" t="n">
-        <v>181.1730609959959</v>
+        <v>202.8114669493673</v>
       </c>
       <c r="J18" t="n">
-        <v>9.215485615879814</v>
+        <v>11.82162592400131</v>
       </c>
       <c r="K18" t="n">
-        <v>89.93357432466212</v>
+        <v>5.299292826055989</v>
       </c>
       <c r="L18" t="n">
-        <v>19.17042105439688</v>
+        <v>0.05208803342497959</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2097211569048696</v>
+        <v>2.199151899037819</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8438579327110084</v>
+        <v>0.9017627239227295</v>
       </c>
       <c r="P18" t="n">
-        <v>0.001401562631860155</v>
+        <v>0.001597243011929095</v>
       </c>
       <c r="Q18" t="n">
-        <v>846.2614605511525</v>
+        <v>806.469808496011</v>
       </c>
       <c r="R18" t="n">
-        <v>169.0030238183578</v>
+        <v>199.6358147095653</v>
       </c>
       <c r="S18" t="n">
-        <v>9.368175873444359</v>
+        <v>13.18033760210351</v>
       </c>
       <c r="T18" t="n">
-        <v>124.1712437253997</v>
+        <v>131.9833511898223</v>
       </c>
       <c r="U18" t="n">
-        <v>7.000383876758832</v>
+        <v>3.123564206377068</v>
       </c>
       <c r="V18" t="n">
-        <v>0.05703089934032413</v>
+        <v>0.8404402209356245</v>
       </c>
       <c r="W18" t="b">
         <v>1</v>
@@ -1780,68 +1780,68 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>963.908049491006</v>
+        <v>994.1156538949632</v>
       </c>
       <c r="D19" t="n">
-        <v>13.18657491181106</v>
+        <v>5.130632828330791</v>
       </c>
       <c r="E19" t="n">
-        <v>221.27004538893</v>
+        <v>204.8091508976131</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6125883460044861</v>
+        <v>0.9241881370544434</v>
       </c>
       <c r="G19" t="n">
-        <v>0.007990965619683266</v>
+        <v>0.0005015467177145183</v>
       </c>
       <c r="H19" t="n">
-        <v>963.908049491009</v>
+        <v>993.9623661134164</v>
       </c>
       <c r="I19" t="n">
-        <v>224.7375914651388</v>
+        <v>204.8090361473304</v>
       </c>
       <c r="J19" t="n">
-        <v>11.77725334223896</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K19" t="n">
-        <v>3.069544618483633e-12</v>
+        <v>0.153287781546851</v>
       </c>
       <c r="L19" t="n">
-        <v>3.467546076208833</v>
+        <v>0.0001147502826768232</v>
       </c>
       <c r="M19" t="n">
-        <v>1.409321569572093</v>
+        <v>3.870008951531371</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6238866850540444</v>
+        <v>0.8989121913909912</v>
       </c>
       <c r="P19" t="n">
-        <v>0.001518533829946619</v>
+        <v>4.492159860092215e-05</v>
       </c>
       <c r="Q19" t="n">
-        <v>848.3648785256021</v>
+        <v>994.2866780926453</v>
       </c>
       <c r="R19" t="n">
-        <v>220.2906712587289</v>
+        <v>204.904651792149</v>
       </c>
       <c r="S19" t="n">
-        <v>12.69451968361827</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T19" t="n">
-        <v>115.5431709654039</v>
+        <v>0.1710241976820726</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9793741302010233</v>
+        <v>0.09550089453597366</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4920552281927897</v>
+        <v>3.870008951531371</v>
       </c>
       <c r="W19" t="b">
         <v>1</v>
@@ -1853,68 +1853,68 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>858.5954104313548</v>
+        <v>956.7552063987063</v>
       </c>
       <c r="D20" t="n">
-        <v>8.830731426677334</v>
+        <v>6.091078583278835</v>
       </c>
       <c r="E20" t="n">
-        <v>202.2892740270275</v>
+        <v>182.764004648775</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5621231198310852</v>
+        <v>0.9294523596763611</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0107807656750083</v>
+        <v>0.0005016286741010845</v>
       </c>
       <c r="H20" t="n">
-        <v>928.8432674714578</v>
+        <v>956.7552063983394</v>
       </c>
       <c r="I20" t="n">
-        <v>202.2892740270275</v>
+        <v>182.7640046487469</v>
       </c>
       <c r="J20" t="n">
-        <v>9.000057868668559</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K20" t="n">
-        <v>70.24785704010299</v>
+        <v>3.668674253276549e-10</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.810907062666956e-11</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1693264419912257</v>
+        <v>2.909563196583328</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6985852681374433</v>
+        <v>0.7503392696380615</v>
       </c>
       <c r="P20" t="n">
-        <v>0.0008680252345416306</v>
+        <v>0.0001778428995748982</v>
       </c>
       <c r="Q20" t="n">
-        <v>945.2299071716528</v>
+        <v>958.1412743882329</v>
       </c>
       <c r="R20" t="n">
-        <v>201.4248419267716</v>
+        <v>183.3722727235086</v>
       </c>
       <c r="S20" t="n">
-        <v>9.000057867527333</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T20" t="n">
-        <v>86.634496740298</v>
+        <v>1.386067989526623</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8644321002558968</v>
+        <v>0.6082680747336155</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1693264408499999</v>
+        <v>2.909563196583328</v>
       </c>
       <c r="W20" t="b">
         <v>1</v>
@@ -1926,68 +1926,68 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>935.5686183531994</v>
+        <v>920.4477518616111</v>
       </c>
       <c r="D21" t="n">
-        <v>8.680828042167876</v>
+        <v>5.399449507428002</v>
       </c>
       <c r="E21" t="n">
-        <v>140.8990356917723</v>
+        <v>193.8694212945647</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7905983924865723</v>
+        <v>0.8345319032669067</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01447403151541948</v>
+        <v>0.0005017755320295691</v>
       </c>
       <c r="H21" t="n">
-        <v>935.5713868675405</v>
+        <v>935.6639036487664</v>
       </c>
       <c r="I21" t="n">
-        <v>176.1527661758182</v>
+        <v>193.8694212945647</v>
       </c>
       <c r="J21" t="n">
-        <v>9.000000000220888</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K21" t="n">
-        <v>0.002768514341028094</v>
+        <v>15.21615178715535</v>
       </c>
       <c r="L21" t="n">
-        <v>35.25373048404597</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3191719580530119</v>
+        <v>3.601192272434161</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9969749901955914</v>
+        <v>0.6869150400161743</v>
       </c>
       <c r="P21" t="n">
-        <v>0.001680591176466929</v>
+        <v>8.305979281431064e-05</v>
       </c>
       <c r="Q21" t="n">
-        <v>812.4237439117898</v>
+        <v>921.9938324262904</v>
       </c>
       <c r="R21" t="n">
-        <v>150.0000472902463</v>
+        <v>194.0030687154665</v>
       </c>
       <c r="S21" t="n">
-        <v>9.000057869260331</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T21" t="n">
-        <v>123.1448744414097</v>
+        <v>1.546080564679301</v>
       </c>
       <c r="U21" t="n">
-        <v>9.101011598474003</v>
+        <v>0.1336474209018093</v>
       </c>
       <c r="V21" t="n">
-        <v>0.319229827092455</v>
+        <v>3.601192272434161</v>
       </c>
       <c r="W21" t="b">
         <v>1</v>
@@ -1999,68 +1999,68 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>930.9536723852241</v>
+        <v>1008.545401849467</v>
       </c>
       <c r="D22" t="n">
-        <v>10.74705882782412</v>
+        <v>8.387579334556282</v>
       </c>
       <c r="E22" t="n">
-        <v>158.3215284092236</v>
+        <v>194.8371481599837</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7905983924865723</v>
+        <v>0.6021395921707153</v>
       </c>
       <c r="G22" t="n">
-        <v>0.01447403151541948</v>
+        <v>0.0003897787537425756</v>
       </c>
       <c r="H22" t="n">
-        <v>930.953666496808</v>
+        <v>986.6826889296826</v>
       </c>
       <c r="I22" t="n">
-        <v>176.1526435262443</v>
+        <v>194.8371481599838</v>
       </c>
       <c r="J22" t="n">
-        <v>10.74706391390919</v>
+        <v>9.000641725090741</v>
       </c>
       <c r="K22" t="n">
-        <v>5.888416126254015e-06</v>
+        <v>21.86271291978392</v>
       </c>
       <c r="L22" t="n">
-        <v>17.83111511702069</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="M22" t="n">
-        <v>5.086085065997281e-06</v>
+        <v>0.6130623905344592</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9121806772260779</v>
+        <v>0.1814334839582443</v>
       </c>
       <c r="P22" t="n">
-        <v>0.00132024284695085</v>
+        <v>0.0001901875220937654</v>
       </c>
       <c r="Q22" t="n">
-        <v>831.4027298434457</v>
+        <v>970.8512799528562</v>
       </c>
       <c r="R22" t="n">
-        <v>164.2830393731329</v>
+        <v>195.0313830168044</v>
       </c>
       <c r="S22" t="n">
-        <v>10.71289817887899</v>
+        <v>9.000641929974737</v>
       </c>
       <c r="T22" t="n">
-        <v>99.55094254177834</v>
+        <v>37.69412189661034</v>
       </c>
       <c r="U22" t="n">
-        <v>5.961510963909262</v>
+        <v>0.1942348568207422</v>
       </c>
       <c r="V22" t="n">
-        <v>0.03416064894513049</v>
+        <v>0.6130625954184552</v>
       </c>
       <c r="W22" t="b">
         <v>1</v>
@@ -2076,64 +2076,64 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>839.9028766404572</v>
+        <v>890.5470318060303</v>
       </c>
       <c r="D23" t="n">
-        <v>7.404855949979647</v>
+        <v>7.512650723820679</v>
       </c>
       <c r="E23" t="n">
-        <v>174.8116904508182</v>
+        <v>215.574397047935</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7361236810684204</v>
+        <v>0.8756701946258545</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01076846290379763</v>
+        <v>0.0008488548919558525</v>
       </c>
       <c r="H23" t="n">
-        <v>928.8454565611487</v>
+        <v>935.6635585384556</v>
       </c>
       <c r="I23" t="n">
-        <v>179.2302637048722</v>
+        <v>215.5743970479351</v>
       </c>
       <c r="J23" t="n">
-        <v>9.000057869034933</v>
+        <v>9.000641616426195</v>
       </c>
       <c r="K23" t="n">
-        <v>88.94257992069151</v>
+        <v>45.11652673242531</v>
       </c>
       <c r="L23" t="n">
-        <v>4.418573254054053</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="M23" t="n">
-        <v>1.595201919055286</v>
+        <v>1.487990892605517</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8955804872098443</v>
+        <v>0.7318476438522339</v>
       </c>
       <c r="P23" t="n">
-        <v>0.001188780437316197</v>
+        <v>0.0003999538312200457</v>
       </c>
       <c r="Q23" t="n">
-        <v>943.457495505261</v>
+        <v>934.6730939272626</v>
       </c>
       <c r="R23" t="n">
-        <v>174.9044418097916</v>
+        <v>214.6975377911914</v>
       </c>
       <c r="S23" t="n">
-        <v>9.000057869520404</v>
+        <v>9.000641611676619</v>
       </c>
       <c r="T23" t="n">
-        <v>103.5546188648038</v>
+        <v>44.12606212123228</v>
       </c>
       <c r="U23" t="n">
-        <v>0.09275135897345876</v>
+        <v>0.8768592567436144</v>
       </c>
       <c r="V23" t="n">
-        <v>1.595201919540757</v>
+        <v>1.48799088785594</v>
       </c>
       <c r="W23" t="b">
         <v>1</v>
@@ -2145,68 +2145,68 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>872.951276388834</v>
+        <v>933.5632513407731</v>
       </c>
       <c r="D24" t="n">
-        <v>6.647864709753142</v>
+        <v>9.495609619023877</v>
       </c>
       <c r="E24" t="n">
-        <v>226.429104826243</v>
+        <v>148.5271119319719</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7425936460494995</v>
+        <v>0.9296471476554871</v>
       </c>
       <c r="G24" t="n">
-        <v>0.006254705600440502</v>
+        <v>0.0004814165877178311</v>
       </c>
       <c r="H24" t="n">
-        <v>928.8444742296232</v>
+        <v>933.5632530583321</v>
       </c>
       <c r="I24" t="n">
-        <v>231.3668592757028</v>
+        <v>176.1296284718941</v>
       </c>
       <c r="J24" t="n">
-        <v>9.000057868632235</v>
+        <v>9.495609622360865</v>
       </c>
       <c r="K24" t="n">
-        <v>55.89319784078918</v>
+        <v>1.717558916425332e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>4.93775444945976</v>
+        <v>27.60251653992225</v>
       </c>
       <c r="M24" t="n">
-        <v>2.352193158879093</v>
+        <v>3.336987575153216e-09</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9735310436294481</v>
+        <v>0.9997897744178772</v>
       </c>
       <c r="P24" t="n">
-        <v>0.0009317527878463582</v>
+        <v>0.001465250737965107</v>
       </c>
       <c r="Q24" t="n">
-        <v>953.3226362059706</v>
+        <v>800.0002581692682</v>
       </c>
       <c r="R24" t="n">
-        <v>223.6717468361445</v>
+        <v>158.9344481770417</v>
       </c>
       <c r="S24" t="n">
-        <v>9.000057805709503</v>
+        <v>9.35127402927262</v>
       </c>
       <c r="T24" t="n">
-        <v>80.37135981713664</v>
+        <v>133.5629931715049</v>
       </c>
       <c r="U24" t="n">
-        <v>2.757357990098569</v>
+        <v>10.40733624506979</v>
       </c>
       <c r="V24" t="n">
-        <v>2.352193095956361</v>
+        <v>0.1443355897512575</v>
       </c>
       <c r="W24" t="b">
         <v>1</v>
@@ -2218,68 +2218,68 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>961.7411506918908</v>
+        <v>879.8503448575644</v>
       </c>
       <c r="D25" t="n">
-        <v>9.501535917459156</v>
+        <v>7.981785480275626</v>
       </c>
       <c r="E25" t="n">
-        <v>134.8005772645463</v>
+        <v>204.6400688540783</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7905983924865723</v>
+        <v>0.9106591939926147</v>
       </c>
       <c r="G25" t="n">
-        <v>0.01447403151541948</v>
+        <v>0.0009904649341478944</v>
       </c>
       <c r="H25" t="n">
-        <v>961.7411530323932</v>
+        <v>933.0453147958009</v>
       </c>
       <c r="I25" t="n">
-        <v>176.152553649176</v>
+        <v>204.6400688540841</v>
       </c>
       <c r="J25" t="n">
-        <v>9.501534934356345</v>
+        <v>9.000641773373468</v>
       </c>
       <c r="K25" t="n">
-        <v>2.340502419428958e-06</v>
+        <v>53.19496993823645</v>
       </c>
       <c r="L25" t="n">
-        <v>41.35197638462969</v>
+        <v>5.854872142663226e-12</v>
       </c>
       <c r="M25" t="n">
-        <v>9.831028116025209e-07</v>
+        <v>1.018856293097842</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9994425789695852</v>
+        <v>0.7956917881965637</v>
       </c>
       <c r="P25" t="n">
-        <v>0.001939396499236482</v>
+        <v>0.0004527805431280285</v>
       </c>
       <c r="Q25" t="n">
-        <v>811.7917865849433</v>
+        <v>932.1693009318664</v>
       </c>
       <c r="R25" t="n">
-        <v>150.0000472878515</v>
+        <v>204.7523039490771</v>
       </c>
       <c r="S25" t="n">
-        <v>9.429234185915144</v>
+        <v>9.000641755189859</v>
       </c>
       <c r="T25" t="n">
-        <v>149.9493641069474</v>
+        <v>52.31895607430192</v>
       </c>
       <c r="U25" t="n">
-        <v>15.1994700233052</v>
+        <v>0.1122350949988515</v>
       </c>
       <c r="V25" t="n">
-        <v>0.07230173154401243</v>
+        <v>1.018856274914233</v>
       </c>
       <c r="W25" t="b">
         <v>1</v>
@@ -2291,68 +2291,68 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>953.8876860315468</v>
+        <v>959.6756321662</v>
       </c>
       <c r="D26" t="n">
-        <v>10.26697578312756</v>
+        <v>5.831329231494768</v>
       </c>
       <c r="E26" t="n">
-        <v>133.9082043343228</v>
+        <v>194.6804051385997</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7905983924865723</v>
+        <v>0.9300639033317566</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01447403151541948</v>
+        <v>0.0005017708754166961</v>
       </c>
       <c r="H26" t="n">
-        <v>953.8876859460212</v>
+        <v>959.6756313174292</v>
       </c>
       <c r="I26" t="n">
-        <v>176.1525536608956</v>
+        <v>194.6804051385997</v>
       </c>
       <c r="J26" t="n">
-        <v>10.26697578655412</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K26" t="n">
-        <v>8.552558483643224e-08</v>
+        <v>8.487708100801683e-07</v>
       </c>
       <c r="L26" t="n">
-        <v>42.2443493265728</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.426556816066295e-09</v>
+        <v>3.169312548367394</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.9995206438039369</v>
+        <v>0.7936587333679199</v>
       </c>
       <c r="P26" t="n">
-        <v>0.001958679987557739</v>
+        <v>5.530041744350456e-05</v>
       </c>
       <c r="Q26" t="n">
-        <v>808.6255391234719</v>
+        <v>958.6961054480799</v>
       </c>
       <c r="R26" t="n">
-        <v>150.0000472896715</v>
+        <v>194.8446104328014</v>
       </c>
       <c r="S26" t="n">
-        <v>10.2056190620028</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T26" t="n">
-        <v>145.2621469080749</v>
+        <v>0.9795267181200416</v>
       </c>
       <c r="U26" t="n">
-        <v>16.09184295534871</v>
+        <v>0.1642052942017642</v>
       </c>
       <c r="V26" t="n">
-        <v>0.06135672112475987</v>
+        <v>3.169312548367394</v>
       </c>
       <c r="W26" t="b">
         <v>1</v>
@@ -2364,68 +2364,68 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Stains</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>879.0387028373722</v>
+        <v>840.864426422445</v>
       </c>
       <c r="D27" t="n">
-        <v>9.646879819997553</v>
+        <v>7.2688151502831</v>
       </c>
       <c r="E27" t="n">
-        <v>206.2583865753571</v>
+        <v>214.1732560514905</v>
       </c>
       <c r="F27" t="n">
-        <v>0.510233461856842</v>
+        <v>0.8751335740089417</v>
       </c>
       <c r="G27" t="n">
-        <v>0.005909173749387264</v>
+        <v>0.001493598334491253</v>
       </c>
       <c r="H27" t="n">
-        <v>922.9741913766268</v>
+        <v>918.8325210985497</v>
       </c>
       <c r="I27" t="n">
-        <v>206.2583865753573</v>
+        <v>217.7669380872254</v>
       </c>
       <c r="J27" t="n">
-        <v>9.646879819997551</v>
+        <v>9.000641759092115</v>
       </c>
       <c r="K27" t="n">
-        <v>43.93548853925461</v>
+        <v>77.96809467610467</v>
       </c>
       <c r="L27" t="n">
-        <v>1.989519660128281e-13</v>
+        <v>3.593682035734986</v>
       </c>
       <c r="M27" t="n">
-        <v>1.77635683940025e-15</v>
+        <v>1.731826608809016</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>0.5207946968687837</v>
+        <v>0.9579663872718811</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0005391750645429849</v>
+        <v>0.0008848594152368605</v>
       </c>
       <c r="Q27" t="n">
-        <v>940.8367047258195</v>
+        <v>928.1776765612262</v>
       </c>
       <c r="R27" t="n">
-        <v>205.6986441614883</v>
+        <v>212.2699504876935</v>
       </c>
       <c r="S27" t="n">
-        <v>9.63648382118469</v>
+        <v>9.000641338496399</v>
       </c>
       <c r="T27" t="n">
-        <v>61.79800188844729</v>
+        <v>87.3132501387812</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5597424138687472</v>
+        <v>1.903305563796977</v>
       </c>
       <c r="V27" t="n">
-        <v>0.01039599881286257</v>
+        <v>1.731826188213299</v>
       </c>
       <c r="W27" t="b">
         <v>1</v>
@@ -2441,64 +2441,64 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>954.7027059873237</v>
+        <v>911.3617056587202</v>
       </c>
       <c r="D28" t="n">
-        <v>4.543839976282341</v>
+        <v>5.844386886400764</v>
       </c>
       <c r="E28" t="n">
-        <v>212.3278427213668</v>
+        <v>201.7404262696538</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6949941515922546</v>
+        <v>0.6870334148406982</v>
       </c>
       <c r="G28" t="n">
-        <v>0.005485068075358868</v>
+        <v>0.0006761035765521228</v>
       </c>
       <c r="H28" t="n">
-        <v>954.7027059873394</v>
+        <v>918.8325209898146</v>
       </c>
       <c r="I28" t="n">
-        <v>212.3278427213669</v>
+        <v>201.740426269635</v>
       </c>
       <c r="J28" t="n">
-        <v>9.000057869254071</v>
+        <v>9.000641741814141</v>
       </c>
       <c r="K28" t="n">
-        <v>1.568878360558301e-11</v>
+        <v>7.4708153310944</v>
       </c>
       <c r="L28" t="n">
-        <v>1.4210854715202e-13</v>
+        <v>1.881517164292745e-11</v>
       </c>
       <c r="M28" t="n">
-        <v>4.45621789297173</v>
+        <v>3.156254855413377</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>0.9944839731230863</v>
+        <v>0.1848437339067459</v>
       </c>
       <c r="P28" t="n">
-        <v>0.001860325997298282</v>
+        <v>0.0001026247991831042</v>
       </c>
       <c r="Q28" t="n">
-        <v>953.7968869359587</v>
+        <v>913.4711181325252</v>
       </c>
       <c r="R28" t="n">
-        <v>208.4638778792243</v>
+        <v>201.5742021385845</v>
       </c>
       <c r="S28" t="n">
-        <v>9.000057869254071</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T28" t="n">
-        <v>0.9058190513650288</v>
+        <v>2.109412473805037</v>
       </c>
       <c r="U28" t="n">
-        <v>3.863964842142508</v>
+        <v>0.1662241310693275</v>
       </c>
       <c r="V28" t="n">
-        <v>4.45621789297173</v>
+        <v>3.156254893461399</v>
       </c>
       <c r="W28" t="b">
         <v>1</v>
@@ -2510,68 +2510,68 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Stains</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>845.1568631320561</v>
+        <v>915.1328945729765</v>
       </c>
       <c r="D29" t="n">
-        <v>10.74761024527205</v>
+        <v>6.059991622037932</v>
       </c>
       <c r="E29" t="n">
-        <v>194.9539987835122</v>
+        <v>210.4936769056666</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5990298390388489</v>
+        <v>0.5132704377174377</v>
       </c>
       <c r="G29" t="n">
-        <v>0.005909173749387264</v>
+        <v>0.0006742415716871619</v>
       </c>
       <c r="H29" t="n">
-        <v>922.974191339715</v>
+        <v>918.8325212429251</v>
       </c>
       <c r="I29" t="n">
-        <v>194.9539987835122</v>
+        <v>210.4936544229514</v>
       </c>
       <c r="J29" t="n">
-        <v>10.74761024527205</v>
+        <v>9.000641665751749</v>
       </c>
       <c r="K29" t="n">
-        <v>77.81732820765899</v>
+        <v>3.699626669948543</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.248271522375944e-05</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2.940650043713816</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8977436780447999</v>
+        <v>0.1295967251062393</v>
       </c>
       <c r="P29" t="n">
-        <v>0.0009180601509068569</v>
+        <v>0.00010634635691531</v>
       </c>
       <c r="Q29" t="n">
-        <v>939.452313146076</v>
+        <v>918.3621231351999</v>
       </c>
       <c r="R29" t="n">
-        <v>195.1565499196259</v>
+        <v>210.4376500123542</v>
       </c>
       <c r="S29" t="n">
-        <v>10.6852278685776</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T29" t="n">
-        <v>94.29545001401993</v>
+        <v>3.229228562223398</v>
       </c>
       <c r="U29" t="n">
-        <v>0.2025511361136694</v>
+        <v>0.05602689331243482</v>
       </c>
       <c r="V29" t="n">
-        <v>0.06238237669444935</v>
+        <v>2.94065015782423</v>
       </c>
       <c r="W29" t="b">
         <v>1</v>
@@ -2583,68 +2583,68 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>954.9778793826652</v>
+        <v>963.176555542808</v>
       </c>
       <c r="D30" t="n">
-        <v>14.60216899569308</v>
+        <v>4.610213383201334</v>
       </c>
       <c r="E30" t="n">
-        <v>208.6719112576131</v>
+        <v>216.9138812036659</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7234267592430115</v>
+        <v>0.9196237921714783</v>
       </c>
       <c r="G30" t="n">
-        <v>0.008424116298556328</v>
+        <v>0.0005017708754166961</v>
       </c>
       <c r="H30" t="n">
-        <v>954.9778793142917</v>
+        <v>963.1765985496064</v>
       </c>
       <c r="I30" t="n">
-        <v>208.6719112576131</v>
+        <v>216.9138812036652</v>
       </c>
       <c r="J30" t="n">
-        <v>11.77729471953397</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K30" t="n">
-        <v>6.837342425569659e-08</v>
+        <v>4.300679836433119e-05</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="M30" t="n">
-        <v>2.824874276159109</v>
+        <v>4.390428396660829</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>0.9898295967989218</v>
+        <v>0.9579758048057556</v>
       </c>
       <c r="P30" t="n">
-        <v>0.001872209900798662</v>
+        <v>6.45573454676196e-05</v>
       </c>
       <c r="Q30" t="n">
-        <v>824.2807290463936</v>
+        <v>964.9659656111527</v>
       </c>
       <c r="R30" t="n">
-        <v>208.812053473411</v>
+        <v>216.6780625403437</v>
       </c>
       <c r="S30" t="n">
-        <v>13.87657798915766</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T30" t="n">
-        <v>130.6971503362715</v>
+        <v>1.789410068344637</v>
       </c>
       <c r="U30" t="n">
-        <v>0.1401422157978232</v>
+        <v>0.2358186633221919</v>
       </c>
       <c r="V30" t="n">
-        <v>0.7255910065354207</v>
+        <v>4.390428396660829</v>
       </c>
       <c r="W30" t="b">
         <v>1</v>
@@ -2656,68 +2656,68 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>877.9207487981846</v>
+        <v>928.2851535806614</v>
       </c>
       <c r="D31" t="n">
-        <v>8.772368688660679</v>
+        <v>5.653746606050514</v>
       </c>
       <c r="E31" t="n">
-        <v>189.5768976731275</v>
+        <v>204.0727182995776</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6287869811058044</v>
+        <v>0.7720369696617126</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0107807656750083</v>
+        <v>0.0005017755320295691</v>
       </c>
       <c r="H31" t="n">
-        <v>928.8432674775141</v>
+        <v>935.66365058833</v>
       </c>
       <c r="I31" t="n">
-        <v>189.5768976731275</v>
+        <v>204.0727182995776</v>
       </c>
       <c r="J31" t="n">
-        <v>9.000057867504813</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K31" t="n">
-        <v>50.92251867932953</v>
+        <v>7.37849700766867</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M31" t="n">
-        <v>0.227689178844134</v>
+        <v>3.346895173811649</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0.672209379656895</v>
+        <v>0.6143945455551147</v>
       </c>
       <c r="P31" t="n">
-        <v>0.0006696179529128564</v>
+        <v>6.935622513992712e-05</v>
       </c>
       <c r="Q31" t="n">
-        <v>946.352413746896</v>
+        <v>929.6297667727787</v>
       </c>
       <c r="R31" t="n">
-        <v>189.7135700591255</v>
+        <v>203.9832749384079</v>
       </c>
       <c r="S31" t="n">
-        <v>9.000057869411549</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T31" t="n">
-        <v>68.43166494871139</v>
+        <v>1.344613192117322</v>
       </c>
       <c r="U31" t="n">
-        <v>0.1366723859980254</v>
+        <v>0.08944336116968543</v>
       </c>
       <c r="V31" t="n">
-        <v>0.2276891807508701</v>
+        <v>3.346895173811649</v>
       </c>
       <c r="W31" t="b">
         <v>1</v>
@@ -2733,64 +2733,64 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>931.2681598751271</v>
+        <v>941.0057360916854</v>
       </c>
       <c r="D32" t="n">
-        <v>15.24260180471171</v>
+        <v>16.20970598452344</v>
       </c>
       <c r="E32" t="n">
-        <v>204.7887497005245</v>
+        <v>200.3765036916771</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7234267592430115</v>
+        <v>0.8926043510437012</v>
       </c>
       <c r="G32" t="n">
-        <v>0.01341769751161337</v>
+        <v>0.0002902889100369066</v>
       </c>
       <c r="H32" t="n">
-        <v>935.3031883591335</v>
+        <v>941.0057263688439</v>
       </c>
       <c r="I32" t="n">
-        <v>203.005318621267</v>
+        <v>200.3765036916771</v>
       </c>
       <c r="J32" t="n">
-        <v>11.97994325185223</v>
+        <v>11.82181865973818</v>
       </c>
       <c r="K32" t="n">
-        <v>4.035028484006375</v>
+        <v>9.722841582515684e-06</v>
       </c>
       <c r="L32" t="n">
-        <v>1.783431079257582</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.262658552859483</v>
+        <v>4.387887324785257</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>0.9972387862937727</v>
+        <v>0.9998775720596313</v>
       </c>
       <c r="P32" t="n">
-        <v>0.001926654321043025</v>
+        <v>0.003183335298672318</v>
       </c>
       <c r="Q32" t="n">
-        <v>810.5218297833327</v>
+        <v>800.0000871831492</v>
       </c>
       <c r="R32" t="n">
-        <v>205.1960549879077</v>
+        <v>192.4862910914212</v>
       </c>
       <c r="S32" t="n">
-        <v>14.45904671983305</v>
+        <v>13.82570568898254</v>
       </c>
       <c r="T32" t="n">
-        <v>120.7463300917944</v>
+        <v>141.0056489085363</v>
       </c>
       <c r="U32" t="n">
-        <v>0.4073052873831955</v>
+        <v>7.890212600255921</v>
       </c>
       <c r="V32" t="n">
-        <v>0.7835550848786639</v>
+        <v>2.384000295540897</v>
       </c>
       <c r="W32" t="b">
         <v>1</v>
@@ -2806,64 +2806,64 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>962.0729147792148</v>
+        <v>930.7536861441955</v>
       </c>
       <c r="D33" t="n">
-        <v>8.903987952128947</v>
+        <v>8.927977431822347</v>
       </c>
       <c r="E33" t="n">
-        <v>132.5915889980326</v>
+        <v>122.6107519328073</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7905983924865723</v>
+        <v>0.9230289459228516</v>
       </c>
       <c r="G33" t="n">
-        <v>0.01447403151541948</v>
+        <v>0.006477588787674904</v>
       </c>
       <c r="H33" t="n">
-        <v>961.3176773596946</v>
+        <v>902.6500424418728</v>
       </c>
       <c r="I33" t="n">
-        <v>176.1526135343724</v>
+        <v>173.6141399233477</v>
       </c>
       <c r="J33" t="n">
-        <v>9.000000000116428</v>
+        <v>9.532468987427524</v>
       </c>
       <c r="K33" t="n">
-        <v>0.7552374195201992</v>
+        <v>28.10364370232276</v>
       </c>
       <c r="L33" t="n">
-        <v>43.5610245363398</v>
+        <v>51.00338799054042</v>
       </c>
       <c r="M33" t="n">
-        <v>0.09601204798748064</v>
+        <v>0.6044915556051773</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>0.9995680016057145</v>
+        <v>1</v>
       </c>
       <c r="P33" t="n">
-        <v>0.00188484686738011</v>
+        <v>0.006292601116001606</v>
       </c>
       <c r="Q33" t="n">
-        <v>813.7834354726926</v>
+        <v>800.000031837548</v>
       </c>
       <c r="R33" t="n">
-        <v>150.0000472903855</v>
+        <v>153.1194834201628</v>
       </c>
       <c r="S33" t="n">
-        <v>9.000057869430696</v>
+        <v>9.000642159913577</v>
       </c>
       <c r="T33" t="n">
-        <v>148.2894793065221</v>
+        <v>130.7536543066475</v>
       </c>
       <c r="U33" t="n">
-        <v>17.40845829235283</v>
+        <v>30.50873148735555</v>
       </c>
       <c r="V33" t="n">
-        <v>0.09606991730174919</v>
+        <v>0.07266472809122959</v>
       </c>
       <c r="W33" t="b">
         <v>1</v>
@@ -2875,35 +2875,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Stains</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>845.0183602460452</v>
+        <v>1012.064025522282</v>
       </c>
       <c r="D34" t="n">
-        <v>11.00615113464798</v>
+        <v>10.21826323818112</v>
       </c>
       <c r="E34" t="n">
-        <v>200.3466143205719</v>
+        <v>186.3622748836766</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5955662727355957</v>
+        <v>0.5391393303871155</v>
       </c>
       <c r="G34" t="n">
-        <v>0.005909173749387264</v>
+        <v>0.0003771110787056386</v>
       </c>
       <c r="H34" t="n">
-        <v>922.9741913282998</v>
+        <v>986.6826880845888</v>
       </c>
       <c r="I34" t="n">
-        <v>200.3466143205719</v>
+        <v>186.3622748836766</v>
       </c>
       <c r="J34" t="n">
-        <v>11.00615113464798</v>
+        <v>10.21826323818112</v>
       </c>
       <c r="K34" t="n">
-        <v>77.95583108225458</v>
+        <v>25.38133743769311</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2915,28 +2915,28 @@
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0.9241481659238815</v>
+        <v>0.2783395648002625</v>
       </c>
       <c r="P34" t="n">
-        <v>0.0009399021841554903</v>
+        <v>0.000243284142925404</v>
       </c>
       <c r="Q34" t="n">
-        <v>940.3732479495258</v>
+        <v>969.6457482330858</v>
       </c>
       <c r="R34" t="n">
-        <v>200.1092821753496</v>
+        <v>186.9235872563537</v>
       </c>
       <c r="S34" t="n">
-        <v>10.93037211948388</v>
+        <v>10.21285885123135</v>
       </c>
       <c r="T34" t="n">
-        <v>95.35488770348059</v>
+        <v>42.41827728919611</v>
       </c>
       <c r="U34" t="n">
-        <v>0.2373321452222683</v>
+        <v>0.5613123726770652</v>
       </c>
       <c r="V34" t="n">
-        <v>0.07577901516410002</v>
+        <v>0.005404386949775741</v>
       </c>
       <c r="W34" t="b">
         <v>1</v>
@@ -2948,68 +2948,68 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>929.9675998021016</v>
+        <v>935.6117250099762</v>
       </c>
       <c r="D35" t="n">
-        <v>8.687511309663687</v>
+        <v>6.976582088864133</v>
       </c>
       <c r="E35" t="n">
-        <v>142.901458212072</v>
+        <v>196.9071804633607</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7905983924865723</v>
+        <v>0.5775360465049744</v>
       </c>
       <c r="G35" t="n">
-        <v>0.01447403151541948</v>
+        <v>0.0005017755320295691</v>
       </c>
       <c r="H35" t="n">
-        <v>929.9533321541509</v>
+        <v>935.6635829324442</v>
       </c>
       <c r="I35" t="n">
-        <v>176.1529775677769</v>
+        <v>196.9071804633607</v>
       </c>
       <c r="J35" t="n">
-        <v>9.000004483504393</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K35" t="n">
-        <v>0.01426764795075997</v>
+        <v>0.05185792246800247</v>
       </c>
       <c r="L35" t="n">
-        <v>33.25151935570489</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.3124931738407053</v>
+        <v>2.024059690998029</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>0.9949327079780264</v>
+        <v>0.05048427730798721</v>
       </c>
       <c r="P35" t="n">
-        <v>0.001634300686191376</v>
+        <v>5.384787073126063e-05</v>
       </c>
       <c r="Q35" t="n">
-        <v>812.0894811465266</v>
+        <v>936.7085765330972</v>
       </c>
       <c r="R35" t="n">
-        <v>150.0000472902792</v>
+        <v>197.0358711118342</v>
       </c>
       <c r="S35" t="n">
-        <v>9.000057869300663</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T35" t="n">
-        <v>117.878118655575</v>
+        <v>1.096851523121018</v>
       </c>
       <c r="U35" t="n">
-        <v>7.098589078207198</v>
+        <v>0.1286906484735084</v>
       </c>
       <c r="V35" t="n">
-        <v>0.3125465596369761</v>
+        <v>2.024059690998029</v>
       </c>
       <c r="W35" t="b">
         <v>1</v>
@@ -3021,68 +3021,68 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>926.6016632857942</v>
+        <v>855.8055457652536</v>
       </c>
       <c r="D36" t="n">
-        <v>14.8366109436522</v>
+        <v>8.089133363160869</v>
       </c>
       <c r="E36" t="n">
-        <v>205.0478136091507</v>
+        <v>208.8341411339296</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7228195667266846</v>
+        <v>0.9102580547332764</v>
       </c>
       <c r="G36" t="n">
-        <v>0.008416088297963142</v>
+        <v>0.001780243474058807</v>
       </c>
       <c r="H36" t="n">
-        <v>926.6016656386225</v>
+        <v>919.4282405781895</v>
       </c>
       <c r="I36" t="n">
-        <v>205.0478124927263</v>
+        <v>208.83414113393</v>
       </c>
       <c r="J36" t="n">
-        <v>11.77729314408565</v>
+        <v>9.000427732128925</v>
       </c>
       <c r="K36" t="n">
-        <v>2.352828346374736e-06</v>
+        <v>63.62269481293595</v>
       </c>
       <c r="L36" t="n">
-        <v>1.116424357405776e-06</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="M36" t="n">
-        <v>3.05931779956655</v>
+        <v>0.9112943689680559</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>0.9924663958655049</v>
+        <v>0.856378972530365</v>
       </c>
       <c r="P36" t="n">
-        <v>0.00173306087152696</v>
+        <v>0.0007010294357314706</v>
       </c>
       <c r="Q36" t="n">
-        <v>816.4402722783584</v>
+        <v>929.3381058370564</v>
       </c>
       <c r="R36" t="n">
-        <v>205.3958570917621</v>
+        <v>208.5485245747717</v>
       </c>
       <c r="S36" t="n">
-        <v>14.15496831013463</v>
+        <v>9.000641717217011</v>
       </c>
       <c r="T36" t="n">
-        <v>110.1613910074358</v>
+        <v>73.53256007180289</v>
       </c>
       <c r="U36" t="n">
-        <v>0.3480434826114447</v>
+        <v>0.2856165591578872</v>
       </c>
       <c r="V36" t="n">
-        <v>0.6816426335175692</v>
+        <v>0.9115083540561422</v>
       </c>
       <c r="W36" t="b">
         <v>1</v>
@@ -3094,68 +3094,68 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>916.2393134960464</v>
+        <v>878.9000351868293</v>
       </c>
       <c r="D37" t="n">
-        <v>8.798787181106738</v>
+        <v>8.425764143923214</v>
       </c>
       <c r="E37" t="n">
-        <v>254.6949431029583</v>
+        <v>210.6415662798122</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6544783711433411</v>
+        <v>0.844025194644928</v>
       </c>
       <c r="G37" t="n">
-        <v>0.005939361173659563</v>
+        <v>0.0008488548919558525</v>
       </c>
       <c r="H37" t="n">
-        <v>910.5037043922475</v>
+        <v>935.663960287817</v>
       </c>
       <c r="I37" t="n">
-        <v>224.7372300887073</v>
+        <v>210.6415662798107</v>
       </c>
       <c r="J37" t="n">
-        <v>9.296241856875497</v>
+        <v>9.00067634306866</v>
       </c>
       <c r="K37" t="n">
-        <v>5.735609103798879</v>
+        <v>56.76392510098765</v>
       </c>
       <c r="L37" t="n">
-        <v>29.95771301425094</v>
+        <v>1.56319401867222e-12</v>
       </c>
       <c r="M37" t="n">
-        <v>0.4974546757687595</v>
+        <v>0.5749121991454462</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>0.9893205482746081</v>
+        <v>0.6453439593315125</v>
       </c>
       <c r="P37" t="n">
-        <v>0.001389402878035869</v>
+        <v>0.0004896446480415761</v>
       </c>
       <c r="Q37" t="n">
-        <v>823.1360210248589</v>
+        <v>931.9762502311136</v>
       </c>
       <c r="R37" t="n">
-        <v>237.0869377249136</v>
+        <v>210.2662434834862</v>
       </c>
       <c r="S37" t="n">
-        <v>9.000057869280431</v>
+        <v>9.000641889741685</v>
       </c>
       <c r="T37" t="n">
-        <v>93.1032924711875</v>
+        <v>53.07621504428425</v>
       </c>
       <c r="U37" t="n">
-        <v>17.60800537804465</v>
+        <v>0.3753227963259747</v>
       </c>
       <c r="V37" t="n">
-        <v>0.2012706881736932</v>
+        <v>0.5748777458184708</v>
       </c>
       <c r="W37" t="b">
         <v>1</v>
@@ -3167,68 +3167,68 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>935.024004079599</v>
+        <v>943.1920968656827</v>
       </c>
       <c r="D38" t="n">
-        <v>9.493295823789762</v>
+        <v>4.855755251113765</v>
       </c>
       <c r="E38" t="n">
-        <v>139.1472518940553</v>
+        <v>190.548390651031</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7905983924865723</v>
+        <v>0.9312343001365662</v>
       </c>
       <c r="G38" t="n">
-        <v>0.05868716537952423</v>
+        <v>0.0005017555085942149</v>
       </c>
       <c r="H38" t="n">
-        <v>871.1349564485747</v>
+        <v>943.1920968655592</v>
       </c>
       <c r="I38" t="n">
-        <v>176.1525533989211</v>
+        <v>190.548390651031</v>
       </c>
       <c r="J38" t="n">
-        <v>9.304083774985546</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K38" t="n">
-        <v>63.88904763102425</v>
+        <v>1.235775926033966e-10</v>
       </c>
       <c r="L38" t="n">
-        <v>37.00530150486583</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1892120488042153</v>
+        <v>4.144886528748398</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>0.9981931466980017</v>
+        <v>0.9858017563819885</v>
       </c>
       <c r="P38" t="n">
-        <v>0.001731622010935966</v>
+        <v>8.154602983267978e-05</v>
       </c>
       <c r="Q38" t="n">
-        <v>810.4264262414273</v>
+        <v>943.3279112994134</v>
       </c>
       <c r="R38" t="n">
-        <v>150.0000472874946</v>
+        <v>190.8846503836392</v>
       </c>
       <c r="S38" t="n">
-        <v>9.429072252051789</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T38" t="n">
-        <v>124.5975778381717</v>
+        <v>0.1358144337306157</v>
       </c>
       <c r="U38" t="n">
-        <v>10.85279539343929</v>
+        <v>0.3362597326081129</v>
       </c>
       <c r="V38" t="n">
-        <v>0.06422357173797266</v>
+        <v>4.144886528748398</v>
       </c>
       <c r="W38" t="b">
         <v>1</v>
@@ -3240,68 +3240,68 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>867.9713275556323</v>
+        <v>946.7151602993594</v>
       </c>
       <c r="D39" t="n">
-        <v>8.492118626600817</v>
+        <v>15.09768161441414</v>
       </c>
       <c r="E39" t="n">
-        <v>218.6047635319229</v>
+        <v>180.2590242190516</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6739748120307922</v>
+        <v>0.7820267677307129</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0107807656750083</v>
+        <v>0.001222321996465325</v>
       </c>
       <c r="H39" t="n">
-        <v>928.8432674873783</v>
+        <v>886.7991406513916</v>
       </c>
       <c r="I39" t="n">
-        <v>218.6047635319248</v>
+        <v>180.2590242190512</v>
       </c>
       <c r="J39" t="n">
-        <v>9.000057866508561</v>
+        <v>11.82181846190499</v>
       </c>
       <c r="K39" t="n">
-        <v>60.87193993174594</v>
+        <v>59.9160196479678</v>
       </c>
       <c r="L39" t="n">
-        <v>1.875832822406664e-12</v>
+        <v>3.694822225952521e-13</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5079392399077438</v>
+        <v>3.27586315250915</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>0.8316781602869349</v>
+        <v>0.9952612519264221</v>
       </c>
       <c r="P39" t="n">
-        <v>0.0008844104172125199</v>
+        <v>0.001771747833117843</v>
       </c>
       <c r="Q39" t="n">
-        <v>949.9119619833524</v>
+        <v>800.5288572796525</v>
       </c>
       <c r="R39" t="n">
-        <v>216.1714923946195</v>
+        <v>176.0436713347065</v>
       </c>
       <c r="S39" t="n">
-        <v>9.000057813049315</v>
+        <v>13.93894427568883</v>
       </c>
       <c r="T39" t="n">
-        <v>81.94063442772006</v>
+        <v>146.1863030197069</v>
       </c>
       <c r="U39" t="n">
-        <v>2.433271137303393</v>
+        <v>4.215352884345066</v>
       </c>
       <c r="V39" t="n">
-        <v>0.5079391864484979</v>
+        <v>1.158737338725304</v>
       </c>
       <c r="W39" t="b">
         <v>1</v>
@@ -3313,68 +3313,68 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1017.531123512318</v>
+        <v>962.4134419510135</v>
       </c>
       <c r="D40" t="n">
-        <v>9.27034211770588</v>
+        <v>3.933248002329482</v>
       </c>
       <c r="E40" t="n">
-        <v>180.3857959086696</v>
+        <v>196.8357926842313</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5890865921974182</v>
+        <v>0.9322754740715027</v>
       </c>
       <c r="G40" t="n">
-        <v>0.007904686033725739</v>
+        <v>0.0005017708754166961</v>
       </c>
       <c r="H40" t="n">
-        <v>965.6040331595926</v>
+        <v>962.4134582398787</v>
       </c>
       <c r="I40" t="n">
-        <v>180.3857959086696</v>
+        <v>196.8357926842312</v>
       </c>
       <c r="J40" t="n">
-        <v>9.270342117705876</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K40" t="n">
-        <v>51.92709035272503</v>
+        <v>1.628886514026817e-05</v>
       </c>
       <c r="L40" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="M40" t="n">
-        <v>3.552713678800501e-15</v>
+        <v>5.06739377753268</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0.7067508044231408</v>
+        <v>0.9990611672401428</v>
       </c>
       <c r="P40" t="n">
-        <v>0.0005227293178559609</v>
+        <v>5.014624548493885e-05</v>
       </c>
       <c r="Q40" t="n">
-        <v>951.2597773477098</v>
+        <v>961.5070079064665</v>
       </c>
       <c r="R40" t="n">
-        <v>180.9632582563371</v>
+        <v>196.9322381642739</v>
       </c>
       <c r="S40" t="n">
-        <v>9.275598885438304</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T40" t="n">
-        <v>66.27134616460785</v>
+        <v>0.9064340445470407</v>
       </c>
       <c r="U40" t="n">
-        <v>0.577462347667506</v>
+        <v>0.09644548004263243</v>
       </c>
       <c r="V40" t="n">
-        <v>0.00525676773242445</v>
+        <v>5.06739377753268</v>
       </c>
       <c r="W40" t="b">
         <v>1</v>
@@ -3390,64 +3390,64 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>948.0282373543148</v>
+        <v>925.5264205940191</v>
       </c>
       <c r="D41" t="n">
-        <v>9.181997815258253</v>
+        <v>9.240641298553927</v>
       </c>
       <c r="E41" t="n">
-        <v>117.599356467224</v>
+        <v>121.6092848320675</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7905983924865723</v>
+        <v>0.9222081303596497</v>
       </c>
       <c r="G41" t="n">
-        <v>0.01618981175124645</v>
+        <v>0.00293063884600997</v>
       </c>
       <c r="H41" t="n">
-        <v>948.0282373582619</v>
+        <v>945.8155635373156</v>
       </c>
       <c r="I41" t="n">
-        <v>176.1525536277982</v>
+        <v>173.6136086170593</v>
       </c>
       <c r="J41" t="n">
-        <v>13.04806048730416</v>
+        <v>9.240570266520603</v>
       </c>
       <c r="K41" t="n">
-        <v>3.947093318856787e-09</v>
+        <v>20.2891429432965</v>
       </c>
       <c r="L41" t="n">
-        <v>58.5531971605742</v>
+        <v>52.00432378499181</v>
       </c>
       <c r="M41" t="n">
-        <v>3.866062672045908</v>
+        <v>7.103203332370356e-05</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>0.9999389029456597</v>
+        <v>1</v>
       </c>
       <c r="P41" t="n">
-        <v>0.001794812865684754</v>
+        <v>0.00659690098837018</v>
       </c>
       <c r="Q41" t="n">
-        <v>812.5666353847927</v>
+        <v>800.0000287052792</v>
       </c>
       <c r="R41" t="n">
-        <v>150.0000472857825</v>
+        <v>152.9710540771775</v>
       </c>
       <c r="S41" t="n">
-        <v>9.10957895556057</v>
+        <v>9.000521147785134</v>
       </c>
       <c r="T41" t="n">
-        <v>135.4616019695221</v>
+        <v>125.5263918887399</v>
       </c>
       <c r="U41" t="n">
-        <v>32.4006908185585</v>
+        <v>31.36176924511</v>
       </c>
       <c r="V41" t="n">
-        <v>0.07241885969768269</v>
+        <v>0.2401201507687922</v>
       </c>
       <c r="W41" t="b">
         <v>1</v>
@@ -3459,68 +3459,68 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>959.8383834301301</v>
+        <v>874.0821187064782</v>
       </c>
       <c r="D42" t="n">
-        <v>14.76159296348758</v>
+        <v>7.767320450652663</v>
       </c>
       <c r="E42" t="n">
-        <v>184.2724959430851</v>
+        <v>206.1137005176345</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7234267592430115</v>
+        <v>0.9018924236297607</v>
       </c>
       <c r="G42" t="n">
-        <v>0.008424116298556328</v>
+        <v>0.001779327751137316</v>
       </c>
       <c r="H42" t="n">
-        <v>931.2030345055626</v>
+        <v>919.428358468431</v>
       </c>
       <c r="I42" t="n">
-        <v>184.2724959430851</v>
+        <v>206.1137005176378</v>
       </c>
       <c r="J42" t="n">
-        <v>11.7772910843587</v>
+        <v>9.000556221005253</v>
       </c>
       <c r="K42" t="n">
-        <v>28.63534892456744</v>
+        <v>45.3462397619528</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>3.268496584496461e-12</v>
       </c>
       <c r="M42" t="n">
-        <v>2.984301879128886</v>
+        <v>1.233235770352589</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>0.9939638524351613</v>
+        <v>0.8891984820365906</v>
       </c>
       <c r="P42" t="n">
-        <v>0.001930103868454727</v>
+        <v>0.0005225249915383756</v>
       </c>
       <c r="Q42" t="n">
-        <v>818.2456352873575</v>
+        <v>931.2143001768042</v>
       </c>
       <c r="R42" t="n">
-        <v>186.0483426757007</v>
+        <v>205.9051783415973</v>
       </c>
       <c r="S42" t="n">
-        <v>13.97487492473567</v>
+        <v>9.000641815342336</v>
       </c>
       <c r="T42" t="n">
-        <v>141.5927481427726</v>
+        <v>57.13218147032592</v>
       </c>
       <c r="U42" t="n">
-        <v>1.775846732615605</v>
+        <v>0.2085221760372349</v>
       </c>
       <c r="V42" t="n">
-        <v>0.7867180387519177</v>
+        <v>1.233321364689672</v>
       </c>
       <c r="W42" t="b">
         <v>1</v>
@@ -3536,64 +3536,64 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>930.9861861316949</v>
+        <v>930.9026183683185</v>
       </c>
       <c r="D43" t="n">
-        <v>10.19477400562807</v>
+        <v>9.525206097560066</v>
       </c>
       <c r="E43" t="n">
-        <v>156.8152425913856</v>
+        <v>125.4374594005599</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7905983924865723</v>
+        <v>0.9357817769050598</v>
       </c>
       <c r="G43" t="n">
-        <v>0.01447403151541948</v>
+        <v>0.0006120777106843889</v>
       </c>
       <c r="H43" t="n">
-        <v>930.9896552775257</v>
+        <v>917.7907176321553</v>
       </c>
       <c r="I43" t="n">
-        <v>176.1527446833997</v>
+        <v>176.1296287130706</v>
       </c>
       <c r="J43" t="n">
-        <v>10.14888182215203</v>
+        <v>10.13573355234474</v>
       </c>
       <c r="K43" t="n">
-        <v>0.003469145830763409</v>
+        <v>13.11190073616319</v>
       </c>
       <c r="L43" t="n">
-        <v>19.33750209201403</v>
+        <v>50.69216931251074</v>
       </c>
       <c r="M43" t="n">
-        <v>0.04589218347604174</v>
+        <v>0.6105274547846768</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0.9328819787915791</v>
+        <v>1</v>
       </c>
       <c r="P43" t="n">
-        <v>0.001343040213317007</v>
+        <v>0.005546124652028084</v>
       </c>
       <c r="Q43" t="n">
-        <v>829.8647205309549</v>
+        <v>800.0000336898173</v>
       </c>
       <c r="R43" t="n">
-        <v>162.6648085865374</v>
+        <v>153.514054838844</v>
       </c>
       <c r="S43" t="n">
-        <v>10.15575183071282</v>
+        <v>9.000431717953688</v>
       </c>
       <c r="T43" t="n">
-        <v>101.1214656007401</v>
+        <v>130.9025846785012</v>
       </c>
       <c r="U43" t="n">
-        <v>5.849565995151778</v>
+        <v>28.07659543828416</v>
       </c>
       <c r="V43" t="n">
-        <v>0.03902217491524773</v>
+        <v>0.5247743796063773</v>
       </c>
       <c r="W43" t="b">
         <v>1</v>
@@ -3605,68 +3605,68 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>878.0453694497114</v>
+        <v>934.5079730422938</v>
       </c>
       <c r="D44" t="n">
-        <v>8.856200757471097</v>
+        <v>11.10399410569217</v>
       </c>
       <c r="E44" t="n">
-        <v>208.6281755523033</v>
+        <v>123.3863151689311</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5621231198310852</v>
+        <v>0.9367098808288574</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0107807656750083</v>
+        <v>0.009299690835177898</v>
       </c>
       <c r="H44" t="n">
-        <v>928.8432675273689</v>
+        <v>949.4787530746802</v>
       </c>
       <c r="I44" t="n">
-        <v>208.6281755523033</v>
+        <v>164.2917033976996</v>
       </c>
       <c r="J44" t="n">
-        <v>9.000057867329405</v>
+        <v>11.10398611585794</v>
       </c>
       <c r="K44" t="n">
-        <v>50.79789807765746</v>
+        <v>14.97078003238641</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>40.90538822876854</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1438571098583079</v>
+        <v>7.989834232446924e-06</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0.6980136554101417</v>
+        <v>1</v>
       </c>
       <c r="P44" t="n">
-        <v>0.0006999133048971682</v>
+        <v>0.006058187689632177</v>
       </c>
       <c r="Q44" t="n">
-        <v>948.301946711998</v>
+        <v>800.0000168814817</v>
       </c>
       <c r="R44" t="n">
-        <v>207.4041622400812</v>
+        <v>155.903664336477</v>
       </c>
       <c r="S44" t="n">
-        <v>9.000057859847047</v>
+        <v>9.787412548957926</v>
       </c>
       <c r="T44" t="n">
-        <v>70.25657726228656</v>
+        <v>134.5079561608121</v>
       </c>
       <c r="U44" t="n">
-        <v>1.224013312222155</v>
+        <v>32.51734916754589</v>
       </c>
       <c r="V44" t="n">
-        <v>0.1438571023759501</v>
+        <v>1.316581556734244</v>
       </c>
       <c r="W44" t="b">
         <v>1</v>
@@ -3678,68 +3678,68 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>834.8959959628713</v>
+        <v>915.971295548182</v>
       </c>
       <c r="D45" t="n">
-        <v>7.016158992161908</v>
+        <v>8.433968397484772</v>
       </c>
       <c r="E45" t="n">
-        <v>186.8628065520684</v>
+        <v>116.6329714024075</v>
       </c>
       <c r="F45" t="n">
-        <v>0.7581575512886047</v>
+        <v>0.8985404372215271</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0107807656750083</v>
+        <v>0.7366998791694641</v>
       </c>
       <c r="H45" t="n">
-        <v>928.8432674756143</v>
+        <v>928.0996907866038</v>
       </c>
       <c r="I45" t="n">
-        <v>186.8628065520684</v>
+        <v>155.4679670918317</v>
       </c>
       <c r="J45" t="n">
-        <v>9.000057867796691</v>
+        <v>10.70182571703081</v>
       </c>
       <c r="K45" t="n">
-        <v>93.94727151274299</v>
+        <v>12.12839523842183</v>
       </c>
       <c r="L45" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>38.83499568942426</v>
       </c>
       <c r="M45" t="n">
-        <v>1.983898875634783</v>
+        <v>2.267857319546039</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>0.9464873892555224</v>
+        <v>1</v>
       </c>
       <c r="P45" t="n">
-        <v>0.00114329585597964</v>
+        <v>0.008150499314069748</v>
       </c>
       <c r="Q45" t="n">
-        <v>942.4958063823801</v>
+        <v>800.0000413639809</v>
       </c>
       <c r="R45" t="n">
-        <v>187.217653905461</v>
+        <v>152.3083530559339</v>
       </c>
       <c r="S45" t="n">
-        <v>9.000057869790005</v>
+        <v>9.00064218658547</v>
       </c>
       <c r="T45" t="n">
-        <v>107.5998104195088</v>
+        <v>115.971254184201</v>
       </c>
       <c r="U45" t="n">
-        <v>0.354847353392671</v>
+        <v>35.67538165352641</v>
       </c>
       <c r="V45" t="n">
-        <v>1.983898877628097</v>
+        <v>0.5666737891006974</v>
       </c>
       <c r="W45" t="b">
         <v>1</v>
@@ -3751,68 +3751,68 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>958.5923643826517</v>
+        <v>943.9422951240201</v>
       </c>
       <c r="D46" t="n">
-        <v>13.47709016575634</v>
+        <v>10.70997486905503</v>
       </c>
       <c r="E46" t="n">
-        <v>197.0407245979124</v>
+        <v>151.5073318488736</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6135947108268738</v>
+        <v>0.9365445375442505</v>
       </c>
       <c r="G46" t="n">
-        <v>0.008424116298556328</v>
+        <v>0.009299447759985924</v>
       </c>
       <c r="H46" t="n">
-        <v>958.5893134440868</v>
+        <v>961.9582331686189</v>
       </c>
       <c r="I46" t="n">
-        <v>197.0407245979124</v>
+        <v>164.2946055648584</v>
       </c>
       <c r="J46" t="n">
-        <v>11.77724993003268</v>
+        <v>10.7099535991266</v>
       </c>
       <c r="K46" t="n">
-        <v>0.003050938564911121</v>
+        <v>18.01593804459878</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>12.78727371598484</v>
       </c>
       <c r="M46" t="n">
-        <v>1.699840235723666</v>
+        <v>2.126992843187736e-05</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>0.8558049334060781</v>
+        <v>0.9993827342987061</v>
       </c>
       <c r="P46" t="n">
-        <v>0.001476038402235606</v>
+        <v>0.001424258691258729</v>
       </c>
       <c r="Q46" t="n">
-        <v>842.1911799205358</v>
+        <v>800.0021207589001</v>
       </c>
       <c r="R46" t="n">
-        <v>197.9024398213539</v>
+        <v>162.2341719230256</v>
       </c>
       <c r="S46" t="n">
-        <v>12.94399703122344</v>
+        <v>10.61504536185583</v>
       </c>
       <c r="T46" t="n">
-        <v>116.4011844621159</v>
+        <v>143.94017436512</v>
       </c>
       <c r="U46" t="n">
-        <v>0.8617152234415073</v>
+        <v>10.72684007415205</v>
       </c>
       <c r="V46" t="n">
-        <v>0.5330931345328995</v>
+        <v>0.09492950719920401</v>
       </c>
       <c r="W46" t="b">
         <v>1</v>
@@ -3824,68 +3824,68 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>956.1480713943938</v>
+        <v>943.1555501890516</v>
       </c>
       <c r="D47" t="n">
-        <v>10.47729600880942</v>
+        <v>4.136696116149537</v>
       </c>
       <c r="E47" t="n">
-        <v>234.7411873193184</v>
+        <v>189.8889599538231</v>
       </c>
       <c r="F47" t="n">
-        <v>0.6140981912612915</v>
+        <v>0.9312343001365662</v>
       </c>
       <c r="G47" t="n">
-        <v>0.005481656175106764</v>
+        <v>0.0005017555085942149</v>
       </c>
       <c r="H47" t="n">
-        <v>956.1480714109659</v>
+        <v>943.1555501892484</v>
       </c>
       <c r="I47" t="n">
-        <v>222.3568452404015</v>
+        <v>189.8889599538228</v>
       </c>
       <c r="J47" t="n">
-        <v>10.47729600891967</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K47" t="n">
-        <v>1.657213033467997e-08</v>
+        <v>1.967919160961173e-10</v>
       </c>
       <c r="L47" t="n">
-        <v>12.38434207891686</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="M47" t="n">
-        <v>1.102513635942159e-10</v>
+        <v>4.863945663712625</v>
       </c>
       <c r="N47" t="b">
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>0.5181408766353688</v>
+        <v>0.9973565340042114</v>
       </c>
       <c r="P47" t="n">
-        <v>0.001242224925512452</v>
+        <v>8.763681398704648e-05</v>
       </c>
       <c r="Q47" t="n">
-        <v>857.8482053852759</v>
+        <v>943.3095661882148</v>
       </c>
       <c r="R47" t="n">
-        <v>220.157224609334</v>
+        <v>190.2481437043452</v>
       </c>
       <c r="S47" t="n">
-        <v>10.48245554368248</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T47" t="n">
-        <v>98.29986600911786</v>
+        <v>0.1540159991632208</v>
       </c>
       <c r="U47" t="n">
-        <v>14.58396270998443</v>
+        <v>0.3591837505220496</v>
       </c>
       <c r="V47" t="n">
-        <v>0.005159534873055094</v>
+        <v>4.863945663712625</v>
       </c>
       <c r="W47" t="b">
         <v>1</v>
@@ -3897,68 +3897,68 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1074.522531647945</v>
+        <v>844.5788138547135</v>
       </c>
       <c r="D48" t="n">
-        <v>7.270595615076266</v>
+        <v>7.59415139233557</v>
       </c>
       <c r="E48" t="n">
-        <v>200.626561449358</v>
+        <v>226.8746747136299</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6431265473365784</v>
+        <v>0.9086915850639343</v>
       </c>
       <c r="G48" t="n">
-        <v>0.007977633737027645</v>
+        <v>0.001532252877950668</v>
       </c>
       <c r="H48" t="n">
-        <v>965.6040331489128</v>
+        <v>918.8530573661448</v>
       </c>
       <c r="I48" t="n">
-        <v>200.626561449358</v>
+        <v>224.8621573092537</v>
       </c>
       <c r="J48" t="n">
-        <v>9.00005786727233</v>
+        <v>9.000641664911376</v>
       </c>
       <c r="K48" t="n">
-        <v>108.9184984990327</v>
+        <v>74.27424351143122</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.012517404376212</v>
       </c>
       <c r="M48" t="n">
-        <v>1.729462252196065</v>
+        <v>1.406490272575805</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>0.9967246122004051</v>
+        <v>0.935052752494812</v>
       </c>
       <c r="P48" t="n">
-        <v>0.0007880797886469035</v>
+        <v>0.0008573738159611821</v>
       </c>
       <c r="Q48" t="n">
-        <v>956.1272860425254</v>
+        <v>931.5109106147402</v>
       </c>
       <c r="R48" t="n">
-        <v>200.2987295186366</v>
+        <v>226.1500806240446</v>
       </c>
       <c r="S48" t="n">
-        <v>9.000057868713494</v>
+        <v>9.000641819438632</v>
       </c>
       <c r="T48" t="n">
-        <v>118.3952456054201</v>
+        <v>86.93209676002664</v>
       </c>
       <c r="U48" t="n">
-        <v>0.3278319307213735</v>
+        <v>0.7245940895852527</v>
       </c>
       <c r="V48" t="n">
-        <v>1.729462253637228</v>
+        <v>1.406490427103062</v>
       </c>
       <c r="W48" t="b">
         <v>1</v>
@@ -3970,68 +3970,68 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Stains</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>864.3495133812861</v>
+        <v>837.7732934689444</v>
       </c>
       <c r="D49" t="n">
-        <v>10.08936073859624</v>
+        <v>6.753432575528466</v>
       </c>
       <c r="E49" t="n">
-        <v>183.4775643305902</v>
+        <v>190.2151386067326</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5327199101448059</v>
+        <v>0.9365894198417664</v>
       </c>
       <c r="G49" t="n">
-        <v>0.005909173749387264</v>
+        <v>0.001716198050417006</v>
       </c>
       <c r="H49" t="n">
-        <v>922.9741913766268</v>
+        <v>919.4282431361685</v>
       </c>
       <c r="I49" t="n">
-        <v>183.4775643305902</v>
+        <v>190.2151386067326</v>
       </c>
       <c r="J49" t="n">
-        <v>10.08936073859624</v>
+        <v>9.000641583549386</v>
       </c>
       <c r="K49" t="n">
-        <v>58.62467799534068</v>
+        <v>81.65494966722406</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>2.247209008020921</v>
       </c>
       <c r="N49" t="b">
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>0.7637864077416848</v>
+        <v>0.980803906917572</v>
       </c>
       <c r="P49" t="n">
-        <v>0.0007266981009792432</v>
+        <v>0.0008952956413850188</v>
       </c>
       <c r="Q49" t="n">
-        <v>940.3654230155698</v>
+        <v>929.2538290430722</v>
       </c>
       <c r="R49" t="n">
-        <v>184.1890997594415</v>
+        <v>191.4382316943292</v>
       </c>
       <c r="S49" t="n">
-        <v>10.06056936382245</v>
+        <v>9.000641568676816</v>
       </c>
       <c r="T49" t="n">
-        <v>76.01590963428373</v>
+        <v>91.48053557412777</v>
       </c>
       <c r="U49" t="n">
-        <v>0.7115354288513061</v>
+        <v>1.223093087596538</v>
       </c>
       <c r="V49" t="n">
-        <v>0.02879137477379423</v>
+        <v>2.24720899314835</v>
       </c>
       <c r="W49" t="b">
         <v>1</v>
@@ -4043,68 +4043,68 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>952.5275915909282</v>
+        <v>942.8290100072318</v>
       </c>
       <c r="D50" t="n">
-        <v>9.496836480953643</v>
+        <v>6.400376626811989</v>
       </c>
       <c r="E50" t="n">
-        <v>276.9861334429187</v>
+        <v>188.1906254437854</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6614874005317688</v>
+        <v>0.8688167333602905</v>
       </c>
       <c r="G50" t="n">
-        <v>0.006804721895605326</v>
+        <v>0.0005017622606828809</v>
       </c>
       <c r="H50" t="n">
-        <v>952.5275916104775</v>
+        <v>942.8290100062374</v>
       </c>
       <c r="I50" t="n">
-        <v>224.737590442474</v>
+        <v>188.1906254437855</v>
       </c>
       <c r="J50" t="n">
-        <v>9.49683648114731</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K50" t="n">
-        <v>1.954936124093365e-08</v>
+        <v>9.944187695509754e-10</v>
       </c>
       <c r="L50" t="n">
-        <v>52.2485430004447</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="M50" t="n">
-        <v>1.936673044156123e-10</v>
+        <v>2.600265153050173</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>0.9998253570475214</v>
+        <v>0.3870470523834229</v>
       </c>
       <c r="P50" t="n">
-        <v>0.002136359137945608</v>
+        <v>0.0001054359672707506</v>
       </c>
       <c r="Q50" t="n">
-        <v>803.1086002218975</v>
+        <v>942.9872770622436</v>
       </c>
       <c r="R50" t="n">
-        <v>246.3725355033174</v>
+        <v>188.6078339197368</v>
       </c>
       <c r="S50" t="n">
-        <v>9.411007309424141</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T50" t="n">
-        <v>149.4189913690307</v>
+        <v>0.1582670550118337</v>
       </c>
       <c r="U50" t="n">
-        <v>30.61359793960128</v>
+        <v>0.4172084759514121</v>
       </c>
       <c r="V50" t="n">
-        <v>0.08582917152950209</v>
+        <v>2.600265153050173</v>
       </c>
       <c r="W50" t="b">
         <v>1</v>
@@ -4116,68 +4116,68 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>850.9222712794735</v>
+        <v>952.2244666968172</v>
       </c>
       <c r="D51" t="n">
-        <v>7.209835753453065</v>
+        <v>9.374842474547272</v>
       </c>
       <c r="E51" t="n">
-        <v>200.2000321982746</v>
+        <v>143.7893713723858</v>
       </c>
       <c r="F51" t="n">
-        <v>0.7841600179672241</v>
+        <v>0.9364324808120728</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0107807656750083</v>
+        <v>0.0004814165877178311</v>
       </c>
       <c r="H51" t="n">
-        <v>928.8432674721494</v>
+        <v>941.8996676143486</v>
       </c>
       <c r="I51" t="n">
-        <v>200.2000321982746</v>
+        <v>176.1296282510185</v>
       </c>
       <c r="J51" t="n">
-        <v>9.000057868991323</v>
+        <v>9.413359194205254</v>
       </c>
       <c r="K51" t="n">
-        <v>77.92099619267583</v>
+        <v>10.32479908246864</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>32.34025687863266</v>
       </c>
       <c r="M51" t="n">
-        <v>1.790222115538258</v>
+        <v>0.03851671965798253</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>0.9567267158619907</v>
+        <v>0.9999693632125854</v>
       </c>
       <c r="P51" t="n">
-        <v>0.0009441125689977485</v>
+        <v>0.002009839517995715</v>
       </c>
       <c r="Q51" t="n">
-        <v>944.2990112798274</v>
+        <v>800.0000477177562</v>
       </c>
       <c r="R51" t="n">
-        <v>199.4707916317523</v>
+        <v>157.2553292145766</v>
       </c>
       <c r="S51" t="n">
-        <v>9.000057868763989</v>
+        <v>9.153376617899209</v>
       </c>
       <c r="T51" t="n">
-        <v>93.37674000035383</v>
+        <v>152.2244189790611</v>
       </c>
       <c r="U51" t="n">
-        <v>0.7292405665223498</v>
+        <v>13.46595784219082</v>
       </c>
       <c r="V51" t="n">
-        <v>1.790222115310923</v>
+        <v>0.221465856648063</v>
       </c>
       <c r="W51" t="b">
         <v>1</v>
@@ -4189,68 +4189,68 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>874.1975775676389</v>
+        <v>949.4125772685856</v>
       </c>
       <c r="D52" t="n">
-        <v>8.330144978297355</v>
+        <v>9.419741467999932</v>
       </c>
       <c r="E52" t="n">
-        <v>207.9266506684008</v>
+        <v>151.2707874231109</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6621172428131104</v>
+        <v>0.9364324808120728</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0107807656750083</v>
+        <v>0.0004813938576262444</v>
       </c>
       <c r="H52" t="n">
-        <v>928.8432675261648</v>
+        <v>943.0041329358821</v>
       </c>
       <c r="I52" t="n">
-        <v>207.9266506684009</v>
+        <v>176.1296323000503</v>
       </c>
       <c r="J52" t="n">
-        <v>9.000057866516878</v>
+        <v>9.419741454718308</v>
       </c>
       <c r="K52" t="n">
-        <v>54.64568995852596</v>
+        <v>6.408444332703425</v>
       </c>
       <c r="L52" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>24.85884487693946</v>
       </c>
       <c r="M52" t="n">
-        <v>0.6699128882195229</v>
+        <v>1.328162468894334e-08</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>0.8471175566978565</v>
+        <v>0.9994656443595886</v>
       </c>
       <c r="P52" t="n">
-        <v>0.0007339885546241874</v>
+        <v>0.001347462879493833</v>
       </c>
       <c r="Q52" t="n">
-        <v>947.7300935326629</v>
+        <v>804.781662546915</v>
       </c>
       <c r="R52" t="n">
-        <v>206.7123237122713</v>
+        <v>160.8312442361627</v>
       </c>
       <c r="S52" t="n">
-        <v>9.000057861247972</v>
+        <v>9.320841841179172</v>
       </c>
       <c r="T52" t="n">
-        <v>73.532515965024</v>
+        <v>144.6309147216706</v>
       </c>
       <c r="U52" t="n">
-        <v>1.214326956129582</v>
+        <v>9.560456813051871</v>
       </c>
       <c r="V52" t="n">
-        <v>0.6699128829506176</v>
+        <v>0.09889962682076003</v>
       </c>
       <c r="W52" t="b">
         <v>1</v>
@@ -4262,68 +4262,68 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>980.0546865261117</v>
+        <v>845.8345604713478</v>
       </c>
       <c r="D53" t="n">
-        <v>11.22234525646797</v>
+        <v>7.121444438263866</v>
       </c>
       <c r="E53" t="n">
-        <v>274.3893932538601</v>
+        <v>187.936628615325</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6526216864585876</v>
+        <v>0.8870140314102173</v>
       </c>
       <c r="G53" t="n">
-        <v>0.006203936412930489</v>
+        <v>0.001519713317975402</v>
       </c>
       <c r="H53" t="n">
-        <v>991.5080134160714</v>
+        <v>919.4282428039663</v>
       </c>
       <c r="I53" t="n">
-        <v>224.7359402359462</v>
+        <v>187.7720126067777</v>
       </c>
       <c r="J53" t="n">
-        <v>11.2223430071803</v>
+        <v>9.000641642332553</v>
       </c>
       <c r="K53" t="n">
-        <v>11.45332688995973</v>
+        <v>73.59368233261853</v>
       </c>
       <c r="L53" t="n">
-        <v>49.65345301791385</v>
+        <v>0.1646160085473696</v>
       </c>
       <c r="M53" t="n">
-        <v>2.24928767877941e-06</v>
+        <v>1.879197204068687</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0.9994660785611302</v>
+        <v>0.9661648273468018</v>
       </c>
       <c r="P53" t="n">
-        <v>0.003580138358393574</v>
+        <v>0.0007653642096556723</v>
       </c>
       <c r="Q53" t="n">
-        <v>869.4102979292102</v>
+        <v>930.924148335347</v>
       </c>
       <c r="R53" t="n">
-        <v>220.703676588334</v>
+        <v>188.946509587826</v>
       </c>
       <c r="S53" t="n">
-        <v>11.23141282950746</v>
+        <v>9.000641600240087</v>
       </c>
       <c r="T53" t="n">
-        <v>110.6443885969015</v>
+        <v>85.08958786399921</v>
       </c>
       <c r="U53" t="n">
-        <v>53.68571666552603</v>
+        <v>1.009880972500952</v>
       </c>
       <c r="V53" t="n">
-        <v>0.009067573039487797</v>
+        <v>1.87919716197622</v>
       </c>
       <c r="W53" t="b">
         <v>1</v>
@@ -4339,64 +4339,64 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>947.7088114505497</v>
+        <v>945.7356325434033</v>
       </c>
       <c r="D54" t="n">
-        <v>15.04330896333172</v>
+        <v>14.97427748487189</v>
       </c>
       <c r="E54" t="n">
-        <v>203.2822033198099</v>
+        <v>213.3456914558439</v>
       </c>
       <c r="F54" t="n">
-        <v>0.7234267592430115</v>
+        <v>0.9109001755714417</v>
       </c>
       <c r="G54" t="n">
-        <v>0.008424116298556328</v>
+        <v>0.006548034492880106</v>
       </c>
       <c r="H54" t="n">
-        <v>947.7087833202827</v>
+        <v>951.4455763065425</v>
       </c>
       <c r="I54" t="n">
-        <v>203.2822136370266</v>
+        <v>214.5108091988581</v>
       </c>
       <c r="J54" t="n">
-        <v>11.77729058984163</v>
+        <v>12.63059754492861</v>
       </c>
       <c r="K54" t="n">
-        <v>2.813026696912857e-05</v>
+        <v>5.709943763139222</v>
       </c>
       <c r="L54" t="n">
-        <v>1.031721677691166e-05</v>
+        <v>1.165117743014235</v>
       </c>
       <c r="M54" t="n">
-        <v>3.266018373490088</v>
+        <v>2.343679939943279</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>0.9965709863549486</v>
+        <v>0.9926930665969849</v>
       </c>
       <c r="P54" t="n">
-        <v>0.001965538752900588</v>
+        <v>0.002502325922250748</v>
       </c>
       <c r="Q54" t="n">
-        <v>815.8222118983308</v>
+        <v>800.0000481799771</v>
       </c>
       <c r="R54" t="n">
-        <v>203.8280908349716</v>
+        <v>213.8192697118915</v>
       </c>
       <c r="S54" t="n">
-        <v>14.24594930819829</v>
+        <v>13.52464736754915</v>
       </c>
       <c r="T54" t="n">
-        <v>131.8865995522189</v>
+        <v>145.7355843634263</v>
       </c>
       <c r="U54" t="n">
-        <v>0.5458875151617519</v>
+        <v>0.4735782560476025</v>
       </c>
       <c r="V54" t="n">
-        <v>0.7973596551334285</v>
+        <v>1.449630117322741</v>
       </c>
       <c r="W54" t="b">
         <v>1</v>
@@ -4408,68 +4408,68 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>944.0919717972195</v>
+        <v>922.8358850593218</v>
       </c>
       <c r="D55" t="n">
-        <v>9.309987400185415</v>
+        <v>9.435939006210385</v>
       </c>
       <c r="E55" t="n">
-        <v>232.6787413846192</v>
+        <v>137.6584224652683</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5879876613616943</v>
+        <v>0.9230242967605591</v>
       </c>
       <c r="G55" t="n">
-        <v>0.005481656175106764</v>
+        <v>0.000481406576000154</v>
       </c>
       <c r="H55" t="n">
-        <v>944.0992593563091</v>
+        <v>928.4785359230387</v>
       </c>
       <c r="I55" t="n">
-        <v>222.3550699320454</v>
+        <v>176.12962837029</v>
       </c>
       <c r="J55" t="n">
-        <v>9.309987400185413</v>
+        <v>9.435939007490056</v>
       </c>
       <c r="K55" t="n">
-        <v>0.007287559089604656</v>
+        <v>5.642650863716995</v>
       </c>
       <c r="L55" t="n">
-        <v>10.32367145257379</v>
+        <v>38.47120590502166</v>
       </c>
       <c r="M55" t="n">
-        <v>1.77635683940025e-15</v>
+        <v>1.279671479892386e-09</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>0.4461637882758212</v>
+        <v>0.9999954700469971</v>
       </c>
       <c r="P55" t="n">
-        <v>0.001086510063284846</v>
+        <v>0.003018099348992109</v>
       </c>
       <c r="Q55" t="n">
-        <v>859.2310404720315</v>
+        <v>800.0000000315933</v>
       </c>
       <c r="R55" t="n">
-        <v>220.2345236624318</v>
+        <v>155.8001768353091</v>
       </c>
       <c r="S55" t="n">
-        <v>9.258760151791563</v>
+        <v>9.102167624133051</v>
       </c>
       <c r="T55" t="n">
-        <v>84.86093132518795</v>
+        <v>122.8358850277284</v>
       </c>
       <c r="U55" t="n">
-        <v>12.44421772218746</v>
+        <v>18.14175437004073</v>
       </c>
       <c r="V55" t="n">
-        <v>0.05122724839385207</v>
+        <v>0.3337713820773338</v>
       </c>
       <c r="W55" t="b">
         <v>1</v>
@@ -4481,68 +4481,68 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>945.1483392742041</v>
+        <v>891.0512054522358</v>
       </c>
       <c r="D56" t="n">
-        <v>16.47453325099633</v>
+        <v>8.14885781102695</v>
       </c>
       <c r="E56" t="n">
-        <v>204.0138139078038</v>
+        <v>208.040866618594</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7234267592430115</v>
+        <v>0.5500662326812744</v>
       </c>
       <c r="G56" t="n">
-        <v>0.008424116298556328</v>
+        <v>0.0009904649341478944</v>
       </c>
       <c r="H56" t="n">
-        <v>945.1480789311051</v>
+        <v>933.045360532583</v>
       </c>
       <c r="I56" t="n">
-        <v>204.0139101225869</v>
+        <v>208.040866618594</v>
       </c>
       <c r="J56" t="n">
-        <v>11.77728359765431</v>
+        <v>9.0006014916427</v>
       </c>
       <c r="K56" t="n">
-        <v>0.0002603430989438493</v>
+        <v>41.99415508034724</v>
       </c>
       <c r="L56" t="n">
-        <v>9.621478315580134e-05</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>4.697249653342029</v>
+        <v>0.8517436806157495</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>0.9997623754067174</v>
+        <v>0.4739420711994171</v>
       </c>
       <c r="P56" t="n">
-        <v>0.00233883799185668</v>
+        <v>0.0003752864140551537</v>
       </c>
       <c r="Q56" t="n">
-        <v>800.0831077242001</v>
+        <v>933.6513723873582</v>
       </c>
       <c r="R56" t="n">
-        <v>204.5650172311876</v>
+        <v>207.8869740492335</v>
       </c>
       <c r="S56" t="n">
-        <v>14.99994213049567</v>
+        <v>9.00064159569663</v>
       </c>
       <c r="T56" t="n">
-        <v>145.065231550004</v>
+        <v>42.60016693512239</v>
       </c>
       <c r="U56" t="n">
-        <v>0.5512033233838167</v>
+        <v>0.1538925693605222</v>
       </c>
       <c r="V56" t="n">
-        <v>1.47459112050066</v>
+        <v>0.8517837846696796</v>
       </c>
       <c r="W56" t="b">
         <v>1</v>
@@ -4554,68 +4554,68 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>952.5999645160319</v>
+        <v>862.4995334483451</v>
       </c>
       <c r="D57" t="n">
-        <v>4.619017120565551</v>
+        <v>9.063402892415709</v>
       </c>
       <c r="E57" t="n">
-        <v>204.7455476235796</v>
+        <v>198.8624436728534</v>
       </c>
       <c r="F57" t="n">
-        <v>0.6949941515922546</v>
+        <v>0.7983468770980835</v>
       </c>
       <c r="G57" t="n">
-        <v>0.005485068075358868</v>
+        <v>0.0009909978834912181</v>
       </c>
       <c r="H57" t="n">
-        <v>952.5999645160553</v>
+        <v>919.4282420387069</v>
       </c>
       <c r="I57" t="n">
-        <v>204.7455476235801</v>
+        <v>198.8624436728549</v>
       </c>
       <c r="J57" t="n">
-        <v>9.000057869254071</v>
+        <v>9.328972722858682</v>
       </c>
       <c r="K57" t="n">
-        <v>2.330580173293129e-11</v>
+        <v>56.92870859036179</v>
       </c>
       <c r="L57" t="n">
-        <v>4.263256414560601e-13</v>
+        <v>1.4210854715202e-12</v>
       </c>
       <c r="M57" t="n">
-        <v>4.381040748688521</v>
+        <v>0.2655698304429723</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>0.9933757675078213</v>
+        <v>0.6215916275978088</v>
       </c>
       <c r="P57" t="n">
-        <v>0.00147800297715752</v>
+        <v>0.0005747005343437195</v>
       </c>
       <c r="Q57" t="n">
-        <v>952.4585131517812</v>
+        <v>929.3043873945442</v>
       </c>
       <c r="R57" t="n">
-        <v>202.6902629812823</v>
+        <v>199.1364279502518</v>
       </c>
       <c r="S57" t="n">
-        <v>9.000057869254071</v>
+        <v>9.1368074679358</v>
       </c>
       <c r="T57" t="n">
-        <v>0.14145136425077</v>
+        <v>66.80485394619905</v>
       </c>
       <c r="U57" t="n">
-        <v>2.055284642297323</v>
+        <v>0.2739842773983412</v>
       </c>
       <c r="V57" t="n">
-        <v>4.381040748688521</v>
+        <v>0.07340457552009028</v>
       </c>
       <c r="W57" t="b">
         <v>1</v>
@@ -4627,68 +4627,68 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>934.1516015800008</v>
+        <v>861.319520664121</v>
       </c>
       <c r="D58" t="n">
-        <v>9.672204944122537</v>
+        <v>9.051488789697419</v>
       </c>
       <c r="E58" t="n">
-        <v>261.3919563361865</v>
+        <v>213.8252113029648</v>
       </c>
       <c r="F58" t="n">
-        <v>0.6614874005317688</v>
+        <v>0.6722577214241028</v>
       </c>
       <c r="G58" t="n">
-        <v>0.06253347545862198</v>
+        <v>0.001411959761753678</v>
       </c>
       <c r="H58" t="n">
-        <v>916.5765949595466</v>
+        <v>918.8325220646911</v>
       </c>
       <c r="I58" t="n">
-        <v>226.6297487372529</v>
+        <v>213.8252113029648</v>
       </c>
       <c r="J58" t="n">
-        <v>10.4736733246405</v>
+        <v>9.103706540268195</v>
       </c>
       <c r="K58" t="n">
-        <v>17.57500662045425</v>
+        <v>57.51300140057015</v>
       </c>
       <c r="L58" t="n">
-        <v>34.7622075989336</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="M58" t="n">
-        <v>0.8014683805179672</v>
+        <v>0.05221775057077593</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>0.9980933374103921</v>
+        <v>0.6172221302986145</v>
       </c>
       <c r="P58" t="n">
-        <v>0.001688844871491204</v>
+        <v>0.000645729131065309</v>
       </c>
       <c r="Q58" t="n">
-        <v>816.8741060158883</v>
+        <v>928.4044117379327</v>
       </c>
       <c r="R58" t="n">
-        <v>239.0331049298636</v>
+        <v>212.4457103726802</v>
       </c>
       <c r="S58" t="n">
-        <v>9.61606148525966</v>
+        <v>9.150504956925413</v>
       </c>
       <c r="T58" t="n">
-        <v>117.2774955641125</v>
+        <v>67.08489107381172</v>
       </c>
       <c r="U58" t="n">
-        <v>22.35885140632283</v>
+        <v>1.379500930284678</v>
       </c>
       <c r="V58" t="n">
-        <v>0.05614345886287708</v>
+        <v>0.09901616722799389</v>
       </c>
       <c r="W58" t="b">
         <v>1</v>
@@ -4700,68 +4700,68 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>977.0407873194865</v>
+        <v>856.4722890513826</v>
       </c>
       <c r="D59" t="n">
-        <v>9.6400238264191</v>
+        <v>8.618206508851333</v>
       </c>
       <c r="E59" t="n">
-        <v>131.4534776103323</v>
+        <v>193.3351615894211</v>
       </c>
       <c r="F59" t="n">
-        <v>0.7780663967132568</v>
+        <v>0.9211325645446777</v>
       </c>
       <c r="G59" t="n">
-        <v>0.01447403151541948</v>
+        <v>0.001672132988460362</v>
       </c>
       <c r="H59" t="n">
-        <v>964.5525899945035</v>
+        <v>919.4282417771147</v>
       </c>
       <c r="I59" t="n">
-        <v>176.153369464617</v>
+        <v>193.3351615894247</v>
       </c>
       <c r="J59" t="n">
-        <v>9.640194385009149</v>
+        <v>9.000337529229164</v>
       </c>
       <c r="K59" t="n">
-        <v>12.48819732498305</v>
+        <v>62.95595272573212</v>
       </c>
       <c r="L59" t="n">
-        <v>44.69989185428474</v>
+        <v>3.609557097661309e-12</v>
       </c>
       <c r="M59" t="n">
-        <v>0.0001705585900495521</v>
+        <v>0.3821310203778303</v>
       </c>
       <c r="N59" t="b">
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0.9996734282358312</v>
+        <v>0.7454203963279724</v>
       </c>
       <c r="P59" t="n">
-        <v>0.00206399954321481</v>
+        <v>0.0006990937399677932</v>
       </c>
       <c r="Q59" t="n">
-        <v>811.8830990232789</v>
+        <v>930.329712043601</v>
       </c>
       <c r="R59" t="n">
-        <v>150.0000472880309</v>
+        <v>194.4189437576046</v>
       </c>
       <c r="S59" t="n">
-        <v>9.565582334464697</v>
+        <v>9.000641741783939</v>
       </c>
       <c r="T59" t="n">
-        <v>165.1576882962077</v>
+        <v>73.8574229922184</v>
       </c>
       <c r="U59" t="n">
-        <v>18.54656967769861</v>
+        <v>1.083782168183461</v>
       </c>
       <c r="V59" t="n">
-        <v>0.07444149195440275</v>
+        <v>0.3824352329326057</v>
       </c>
       <c r="W59" t="b">
         <v>1</v>
@@ -4777,64 +4777,64 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>913.8591721013637</v>
+        <v>952.2225875059303</v>
       </c>
       <c r="D60" t="n">
-        <v>9.230854720193383</v>
+        <v>8.982060962729719</v>
       </c>
       <c r="E60" t="n">
-        <v>121.510709542018</v>
+        <v>134.8889820198774</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6958089470863342</v>
+        <v>0.9365533590316772</v>
       </c>
       <c r="G60" t="n">
-        <v>0.02752229943871498</v>
+        <v>0.007413487415760756</v>
       </c>
       <c r="H60" t="n">
-        <v>871.1349397250013</v>
+        <v>929.2633953515734</v>
       </c>
       <c r="I60" t="n">
-        <v>176.1525898290093</v>
+        <v>173.6136086230761</v>
       </c>
       <c r="J60" t="n">
-        <v>9.233294125848257</v>
+        <v>9.232344420629534</v>
       </c>
       <c r="K60" t="n">
-        <v>42.72423237636235</v>
+        <v>22.95919215435686</v>
       </c>
       <c r="L60" t="n">
-        <v>54.64188028699132</v>
+        <v>38.72462660319871</v>
       </c>
       <c r="M60" t="n">
-        <v>0.002439405654873994</v>
+        <v>0.2502834578998154</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>0.999732702636326</v>
+        <v>0.9999988079071045</v>
       </c>
       <c r="P60" t="n">
-        <v>0.00151739854940814</v>
+        <v>0.003431547898799181</v>
       </c>
       <c r="Q60" t="n">
-        <v>810.1919859690605</v>
+        <v>800.0000288101971</v>
       </c>
       <c r="R60" t="n">
-        <v>150.0000472868454</v>
+        <v>155.0156379021303</v>
       </c>
       <c r="S60" t="n">
-        <v>9.17096803743228</v>
+        <v>9.000641998095166</v>
       </c>
       <c r="T60" t="n">
-        <v>103.6671861323032</v>
+        <v>152.2225586957331</v>
       </c>
       <c r="U60" t="n">
-        <v>28.48933774482742</v>
+        <v>20.12665588225289</v>
       </c>
       <c r="V60" t="n">
-        <v>0.05988668276110332</v>
+        <v>0.01858103536544675</v>
       </c>
       <c r="W60" t="b">
         <v>1</v>
@@ -4850,64 +4850,64 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>918.9392944432036</v>
+        <v>921.8809467282865</v>
       </c>
       <c r="D61" t="n">
-        <v>8.76813131186692</v>
+        <v>10.09601292276444</v>
       </c>
       <c r="E61" t="n">
-        <v>144.1376341282934</v>
+        <v>132.0277192594506</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7776037454605103</v>
+        <v>0.9341587424278259</v>
       </c>
       <c r="G61" t="n">
-        <v>0.01262497249990702</v>
+        <v>0.009299690835177898</v>
       </c>
       <c r="H61" t="n">
-        <v>910.503704730356</v>
+        <v>949.4790683064618</v>
       </c>
       <c r="I61" t="n">
-        <v>176.15396903449</v>
+        <v>164.2910901515149</v>
       </c>
       <c r="J61" t="n">
-        <v>9.000107894621815</v>
+        <v>10.21318288643995</v>
       </c>
       <c r="K61" t="n">
-        <v>8.435589712847559</v>
+        <v>27.59812157817532</v>
       </c>
       <c r="L61" t="n">
-        <v>32.01633490619662</v>
+        <v>32.26337089206436</v>
       </c>
       <c r="M61" t="n">
-        <v>0.2319765827548945</v>
+        <v>0.1171699636755061</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>0.9912042705973496</v>
+        <v>0.9999994039535522</v>
       </c>
       <c r="P61" t="n">
-        <v>0.001539803939746313</v>
+        <v>0.004358210135251284</v>
       </c>
       <c r="Q61" t="n">
-        <v>811.3724448540579</v>
+        <v>800.0000263267774</v>
       </c>
       <c r="R61" t="n">
-        <v>150.000047290349</v>
+        <v>156.5498345696142</v>
       </c>
       <c r="S61" t="n">
-        <v>9.000057869386046</v>
+        <v>9.660706272486324</v>
       </c>
       <c r="T61" t="n">
-        <v>107.5668495891457</v>
+        <v>121.8809204015091</v>
       </c>
       <c r="U61" t="n">
-        <v>5.862413162055617</v>
+        <v>24.5221153101636</v>
       </c>
       <c r="V61" t="n">
-        <v>0.2319265575191256</v>
+        <v>0.4353066502781147</v>
       </c>
       <c r="W61" t="b">
         <v>1</v>
@@ -4919,68 +4919,68 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>948.511331417999</v>
+        <v>936.5075895128662</v>
       </c>
       <c r="D62" t="n">
-        <v>10.38994559938344</v>
+        <v>10.61556857993143</v>
       </c>
       <c r="E62" t="n">
-        <v>271.9097831786312</v>
+        <v>123.2569631234545</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6614874005317688</v>
+        <v>0.9367098808288574</v>
       </c>
       <c r="G62" t="n">
-        <v>0.006804721895605326</v>
+        <v>0.008770139887928963</v>
       </c>
       <c r="H62" t="n">
-        <v>948.5113314184365</v>
+        <v>961.9642386131758</v>
       </c>
       <c r="I62" t="n">
-        <v>224.7375904915977</v>
+        <v>164.2946796752816</v>
       </c>
       <c r="J62" t="n">
-        <v>10.38994559938028</v>
+        <v>10.61556946151251</v>
       </c>
       <c r="K62" t="n">
-        <v>4.374669515527785e-10</v>
+        <v>25.45664910030962</v>
       </c>
       <c r="L62" t="n">
-        <v>47.17219268703349</v>
+        <v>41.03771655182712</v>
       </c>
       <c r="M62" t="n">
-        <v>3.154809746774845e-12</v>
+        <v>8.815810748075137e-07</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>0.9996600609875907</v>
+        <v>1</v>
       </c>
       <c r="P62" t="n">
-        <v>0.00204533229717532</v>
+        <v>0.006687334273010492</v>
       </c>
       <c r="Q62" t="n">
-        <v>807.9012421769005</v>
+        <v>800.0000371340137</v>
       </c>
       <c r="R62" t="n">
-        <v>242.9948709400781</v>
+        <v>156.1514644887971</v>
       </c>
       <c r="S62" t="n">
-        <v>10.38796975448151</v>
+        <v>9.989012907460575</v>
       </c>
       <c r="T62" t="n">
-        <v>140.6100892410985</v>
+        <v>136.5075523788524</v>
       </c>
       <c r="U62" t="n">
-        <v>28.91491223855306</v>
+        <v>32.89450136534256</v>
       </c>
       <c r="V62" t="n">
-        <v>0.001975844901922486</v>
+        <v>0.6265556724708556</v>
       </c>
       <c r="W62" t="b">
         <v>1</v>
@@ -4992,68 +4992,68 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>978.5461072857843</v>
+        <v>937.1020828271132</v>
       </c>
       <c r="D63" t="n">
-        <v>9.270427066779609</v>
+        <v>9.457147352903927</v>
       </c>
       <c r="E63" t="n">
-        <v>288.9239529281692</v>
+        <v>133.4013110152258</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6535143256187439</v>
+        <v>0.9357374310493469</v>
       </c>
       <c r="G63" t="n">
-        <v>0.006656103301793337</v>
+        <v>0.006667737383395433</v>
       </c>
       <c r="H63" t="n">
-        <v>978.5458854275453</v>
+        <v>922.3136985527285</v>
       </c>
       <c r="I63" t="n">
-        <v>224.737590480615</v>
+        <v>173.6136088670399</v>
       </c>
       <c r="J63" t="n">
-        <v>9.270427066779755</v>
+        <v>10.17656754540036</v>
       </c>
       <c r="K63" t="n">
-        <v>0.000221858239001449</v>
+        <v>14.78838427438473</v>
       </c>
       <c r="L63" t="n">
-        <v>64.18636244755416</v>
+        <v>40.21229785181416</v>
       </c>
       <c r="M63" t="n">
-        <v>1.456612608308205e-13</v>
+        <v>0.719420192496429</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0.9999321359261277</v>
+        <v>0.9999992847442627</v>
       </c>
       <c r="P63" t="n">
-        <v>0.003744064627176985</v>
+        <v>0.00386183662340045</v>
       </c>
       <c r="Q63" t="n">
-        <v>874.5920183431525</v>
+        <v>800.0000441129705</v>
       </c>
       <c r="R63" t="n">
-        <v>219.6298758743239</v>
+        <v>154.7658806082032</v>
       </c>
       <c r="S63" t="n">
-        <v>9.216062369296679</v>
+        <v>9.031790010078778</v>
       </c>
       <c r="T63" t="n">
-        <v>103.9540889426318</v>
+        <v>137.1020387141427</v>
       </c>
       <c r="U63" t="n">
-        <v>69.29407705384523</v>
+        <v>21.3645695929774</v>
       </c>
       <c r="V63" t="n">
-        <v>0.05436469748292971</v>
+        <v>0.4253573428251496</v>
       </c>
       <c r="W63" t="b">
         <v>1</v>
@@ -5069,64 +5069,64 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>948.7421226620029</v>
+        <v>938.1528808869589</v>
       </c>
       <c r="D64" t="n">
-        <v>10.20178510737095</v>
+        <v>9.522277446844168</v>
       </c>
       <c r="E64" t="n">
-        <v>149.931318772952</v>
+        <v>153.3143187245932</v>
       </c>
       <c r="F64" t="n">
-        <v>0.7905983924865723</v>
+        <v>0.9361411333084106</v>
       </c>
       <c r="G64" t="n">
-        <v>0.01447403151541948</v>
+        <v>0.0004814314306713641</v>
       </c>
       <c r="H64" t="n">
-        <v>948.7421226589198</v>
+        <v>938.1543951074055</v>
       </c>
       <c r="I64" t="n">
-        <v>176.1525536296017</v>
+        <v>176.1296280903845</v>
       </c>
       <c r="J64" t="n">
-        <v>10.20178510750526</v>
+        <v>9.522277446844166</v>
       </c>
       <c r="K64" t="n">
-        <v>3.083073352172505e-09</v>
+        <v>0.001514220446665604</v>
       </c>
       <c r="L64" t="n">
-        <v>26.22123485664969</v>
+        <v>22.81530936579125</v>
       </c>
       <c r="M64" t="n">
-        <v>1.343067879133741e-10</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>0.9893628723263816</v>
+        <v>0.9987419247627258</v>
       </c>
       <c r="P64" t="n">
-        <v>0.001689572613974221</v>
+        <v>0.001245645340532064</v>
       </c>
       <c r="Q64" t="n">
-        <v>819.8824783628796</v>
+        <v>807.6659300832602</v>
       </c>
       <c r="R64" t="n">
-        <v>156.4046498153921</v>
+        <v>162.4883681177157</v>
       </c>
       <c r="S64" t="n">
-        <v>10.15023425213265</v>
+        <v>9.430640501271011</v>
       </c>
       <c r="T64" t="n">
-        <v>128.8596442991233</v>
+        <v>130.4869508036987</v>
       </c>
       <c r="U64" t="n">
-        <v>6.473331042440122</v>
+        <v>9.174049393122431</v>
       </c>
       <c r="V64" t="n">
-        <v>0.05155085523830216</v>
+        <v>0.09163694557315694</v>
       </c>
       <c r="W64" t="b">
         <v>1</v>
@@ -5138,68 +5138,68 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>959.5408165444625</v>
+        <v>952.731947911775</v>
       </c>
       <c r="D65" t="n">
-        <v>4.920585130854247</v>
+        <v>10.24171237566759</v>
       </c>
       <c r="E65" t="n">
-        <v>224.2255557459594</v>
+        <v>133.4683090236713</v>
       </c>
       <c r="F65" t="n">
-        <v>0.6944717168807983</v>
+        <v>0.936724841594696</v>
       </c>
       <c r="G65" t="n">
-        <v>0.005241473205387592</v>
+        <v>0.007099774666130543</v>
       </c>
       <c r="H65" t="n">
-        <v>959.5408165444643</v>
+        <v>909.4379273278954</v>
       </c>
       <c r="I65" t="n">
-        <v>224.7375904987678</v>
+        <v>165.346713547775</v>
       </c>
       <c r="J65" t="n">
-        <v>9.000057867608652</v>
+        <v>10.61256887190718</v>
       </c>
       <c r="K65" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>43.29402058387961</v>
       </c>
       <c r="L65" t="n">
-        <v>0.5120347528083471</v>
+        <v>31.87840452410364</v>
       </c>
       <c r="M65" t="n">
-        <v>4.079472736754404</v>
+        <v>0.3708564962395879</v>
       </c>
       <c r="N65" t="b">
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>0.9899559021365771</v>
+        <v>0.9999992847442627</v>
       </c>
       <c r="P65" t="n">
-        <v>0.001044677408278651</v>
+        <v>0.004129878710955381</v>
       </c>
       <c r="Q65" t="n">
-        <v>878.9113316920636</v>
+        <v>800.0000313160459</v>
       </c>
       <c r="R65" t="n">
-        <v>221.9175230698593</v>
+        <v>157.2709049961554</v>
       </c>
       <c r="S65" t="n">
-        <v>9.000057869254071</v>
+        <v>9.851394610548327</v>
       </c>
       <c r="T65" t="n">
-        <v>80.62948485239883</v>
+        <v>152.7319165957291</v>
       </c>
       <c r="U65" t="n">
-        <v>2.308032676100169</v>
+        <v>23.80259597248406</v>
       </c>
       <c r="V65" t="n">
-        <v>4.079472738399824</v>
+        <v>0.3903177651192653</v>
       </c>
       <c r="W65" t="b">
         <v>1</v>
@@ -5211,68 +5211,68 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>956.1226910620551</v>
+        <v>848.8662607676159</v>
       </c>
       <c r="D66" t="n">
-        <v>7.782716289746432</v>
+        <v>9.303277940532087</v>
       </c>
       <c r="E66" t="n">
-        <v>277.6453165735577</v>
+        <v>205.1944430344406</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6554653644561768</v>
+        <v>0.8402423858642578</v>
       </c>
       <c r="G66" t="n">
-        <v>0.006804721895605326</v>
+        <v>0.0008212371612899005</v>
       </c>
       <c r="H66" t="n">
-        <v>956.1226910698024</v>
+        <v>933.0453214022597</v>
       </c>
       <c r="I66" t="n">
-        <v>224.7375904723221</v>
+        <v>205.1944430344406</v>
       </c>
       <c r="J66" t="n">
-        <v>9.000057869254062</v>
+        <v>9.303277940532084</v>
       </c>
       <c r="K66" t="n">
-        <v>7.747303243377246e-09</v>
+        <v>84.17906063464375</v>
       </c>
       <c r="L66" t="n">
-        <v>52.90772610123557</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>1.217341579507631</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="N66" t="b">
         <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>0.9994980371719612</v>
+        <v>0.5697894096374512</v>
       </c>
       <c r="P66" t="n">
-        <v>0.002133885197722446</v>
+        <v>0.000677684205584228</v>
       </c>
       <c r="Q66" t="n">
-        <v>805.1519184106039</v>
+        <v>925.1630750318811</v>
       </c>
       <c r="R66" t="n">
-        <v>246.6905102208083</v>
+        <v>205.5374799478248</v>
       </c>
       <c r="S66" t="n">
-        <v>9.000057863520329</v>
+        <v>9.393854690845984</v>
       </c>
       <c r="T66" t="n">
-        <v>150.9707726514512</v>
+        <v>76.29681426426521</v>
       </c>
       <c r="U66" t="n">
-        <v>30.95480635274939</v>
+        <v>0.3430369133842817</v>
       </c>
       <c r="V66" t="n">
-        <v>1.217341573773897</v>
+        <v>0.09057675031389678</v>
       </c>
       <c r="W66" t="b">
         <v>1</v>
@@ -5284,68 +5284,68 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>866.4777495445426</v>
+        <v>957.2734529567797</v>
       </c>
       <c r="D67" t="n">
-        <v>8.500222946410677</v>
+        <v>4.155185467070856</v>
       </c>
       <c r="E67" t="n">
-        <v>196.1930257438338</v>
+        <v>200.7057822251266</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6621172428131104</v>
+        <v>0.9316644668579102</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0107807656750083</v>
+        <v>0.0005017013754695654</v>
       </c>
       <c r="H67" t="n">
-        <v>928.8432674911214</v>
+        <v>957.2734529568208</v>
       </c>
       <c r="I67" t="n">
-        <v>196.1930257438338</v>
+        <v>200.7057822251264</v>
       </c>
       <c r="J67" t="n">
-        <v>9.00005786849632</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K67" t="n">
-        <v>62.36551794657885</v>
+        <v>4.1154635255225e-11</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.989519660128281e-13</v>
       </c>
       <c r="M67" t="n">
-        <v>0.4998349220856433</v>
+        <v>4.845456312791306</v>
       </c>
       <c r="N67" t="b">
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>0.7811817072505802</v>
+        <v>0.9973123073577881</v>
       </c>
       <c r="P67" t="n">
-        <v>0.0007754995256549815</v>
+        <v>3.975718573201448e-05</v>
       </c>
       <c r="Q67" t="n">
-        <v>945.3569473906055</v>
+        <v>956.7213574636606</v>
       </c>
       <c r="R67" t="n">
-        <v>195.891201778279</v>
+        <v>200.7704591606353</v>
       </c>
       <c r="S67" t="n">
-        <v>9.000057869386268</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T67" t="n">
-        <v>78.87919784606288</v>
+        <v>0.5520954931190545</v>
       </c>
       <c r="U67" t="n">
-        <v>0.301823965554803</v>
+        <v>0.06467693550871445</v>
       </c>
       <c r="V67" t="n">
-        <v>0.499834922975591</v>
+        <v>4.845456312791306</v>
       </c>
       <c r="W67" t="b">
         <v>1</v>
@@ -5357,68 +5357,68 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1015.52584876243</v>
+        <v>878.5936264077441</v>
       </c>
       <c r="D68" t="n">
-        <v>8.112137762777651</v>
+        <v>8.921512208203685</v>
       </c>
       <c r="E68" t="n">
-        <v>184.3591981108835</v>
+        <v>211.4861040096172</v>
       </c>
       <c r="F68" t="n">
-        <v>0.5826367139816284</v>
+        <v>0.6340576410293579</v>
       </c>
       <c r="G68" t="n">
-        <v>0.007977633737027645</v>
+        <v>0.0009918330470100045</v>
       </c>
       <c r="H68" t="n">
-        <v>965.6040331503077</v>
+        <v>919.4282414150917</v>
       </c>
       <c r="I68" t="n">
-        <v>184.3591981108835</v>
+        <v>211.4861033783361</v>
       </c>
       <c r="J68" t="n">
-        <v>9.000057867769048</v>
+        <v>9.328733482464639</v>
       </c>
       <c r="K68" t="n">
-        <v>49.92181561212215</v>
+        <v>40.83461500734768</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>6.312811819952913e-07</v>
       </c>
       <c r="M68" t="n">
-        <v>0.8879201049913963</v>
+        <v>0.4072212742609533</v>
       </c>
       <c r="N68" t="b">
         <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>0.6334919968180894</v>
+        <v>0.4796126186847687</v>
       </c>
       <c r="P68" t="n">
-        <v>0.0005044970463841696</v>
+        <v>0.0004923328524455428</v>
       </c>
       <c r="Q68" t="n">
-        <v>951.5424514598917</v>
+        <v>931.9918298244547</v>
       </c>
       <c r="R68" t="n">
-        <v>184.823650290297</v>
+        <v>211.1082232637067</v>
       </c>
       <c r="S68" t="n">
-        <v>9.000057868797599</v>
+        <v>9.003863754075047</v>
       </c>
       <c r="T68" t="n">
-        <v>63.98339730253815</v>
+        <v>53.39820341671066</v>
       </c>
       <c r="U68" t="n">
-        <v>0.4644521794135414</v>
+        <v>0.3778807459105735</v>
       </c>
       <c r="V68" t="n">
-        <v>0.8879201060199478</v>
+        <v>0.08235154587136151</v>
       </c>
       <c r="W68" t="b">
         <v>1</v>
@@ -5430,68 +5430,68 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>927.8859066302813</v>
+        <v>960.3160877562763</v>
       </c>
       <c r="D69" t="n">
-        <v>17.64577591489981</v>
+        <v>11.53288740219859</v>
       </c>
       <c r="E69" t="n">
-        <v>203.6229680364656</v>
+        <v>127.4000134727045</v>
       </c>
       <c r="F69" t="n">
-        <v>0.7228195667266846</v>
+        <v>0.9366707801818848</v>
       </c>
       <c r="G69" t="n">
-        <v>0.01293464377522469</v>
+        <v>0.008770139887928963</v>
       </c>
       <c r="H69" t="n">
-        <v>916.576561518555</v>
+        <v>961.9634948669038</v>
       </c>
       <c r="I69" t="n">
-        <v>203.6229680364666</v>
+        <v>164.2914193736947</v>
       </c>
       <c r="J69" t="n">
-        <v>11.97988253465197</v>
+        <v>11.53288740219861</v>
       </c>
       <c r="K69" t="n">
-        <v>11.30934511172632</v>
+        <v>1.647407110627569</v>
       </c>
       <c r="L69" t="n">
-        <v>1.023181539494544e-12</v>
+        <v>36.89140590099012</v>
       </c>
       <c r="M69" t="n">
-        <v>5.665893380247834</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="N69" t="b">
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>0.9999306642434019</v>
+        <v>0.9999998807907104</v>
       </c>
       <c r="P69" t="n">
-        <v>0.002330327710711407</v>
+        <v>0.00587997492402792</v>
       </c>
       <c r="Q69" t="n">
-        <v>800.0000002330278</v>
+        <v>800.0000564158436</v>
       </c>
       <c r="R69" t="n">
-        <v>204.1987542548447</v>
+        <v>158.8016989772121</v>
       </c>
       <c r="S69" t="n">
-        <v>14.99994212757452</v>
+        <v>11.18470988119274</v>
       </c>
       <c r="T69" t="n">
-        <v>127.8859063972535</v>
+        <v>160.3160313404327</v>
       </c>
       <c r="U69" t="n">
-        <v>0.5757862183791644</v>
+        <v>31.40168550450761</v>
       </c>
       <c r="V69" t="n">
-        <v>2.645833787325286</v>
+        <v>0.3481775210058551</v>
       </c>
       <c r="W69" t="b">
         <v>1</v>
@@ -5503,68 +5503,68 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>957.8376252449117</v>
+        <v>975.3332250639683</v>
       </c>
       <c r="D70" t="n">
-        <v>4.773685431185793</v>
+        <v>15.61534603848897</v>
       </c>
       <c r="E70" t="n">
-        <v>214.2996118678968</v>
+        <v>210.7024584419487</v>
       </c>
       <c r="F70" t="n">
-        <v>0.6949941515922546</v>
+        <v>0.9138248562812805</v>
       </c>
       <c r="G70" t="n">
-        <v>0.005485068075358868</v>
+        <v>0.0008986954926513135</v>
       </c>
       <c r="H70" t="n">
-        <v>957.8376252449157</v>
+        <v>951.442885646785</v>
       </c>
       <c r="I70" t="n">
-        <v>214.2996118678969</v>
+        <v>210.7023761633751</v>
       </c>
       <c r="J70" t="n">
-        <v>9.000057869254071</v>
+        <v>12.18355467952391</v>
       </c>
       <c r="K70" t="n">
-        <v>3.979039320256561e-12</v>
+        <v>23.89033941718321</v>
       </c>
       <c r="L70" t="n">
-        <v>1.70530256582424e-13</v>
+        <v>8.227857367160141e-05</v>
       </c>
       <c r="M70" t="n">
-        <v>4.226372438068278</v>
+        <v>3.431791358965063</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>0.9925704560366325</v>
+        <v>0.9992037415504456</v>
       </c>
       <c r="P70" t="n">
-        <v>0.00198945663166214</v>
+        <v>0.003223470412194729</v>
       </c>
       <c r="Q70" t="n">
-        <v>955.2026121095096</v>
+        <v>800.0000360733081</v>
       </c>
       <c r="R70" t="n">
-        <v>209.850142364516</v>
+        <v>209.805788225996</v>
       </c>
       <c r="S70" t="n">
-        <v>9.000057869254071</v>
+        <v>13.6250882361084</v>
       </c>
       <c r="T70" t="n">
-        <v>2.635013135402119</v>
+        <v>175.3331889906601</v>
       </c>
       <c r="U70" t="n">
-        <v>4.449469503380755</v>
+        <v>0.8966702159527529</v>
       </c>
       <c r="V70" t="n">
-        <v>4.226372438068278</v>
+        <v>1.990257802380572</v>
       </c>
       <c r="W70" t="b">
         <v>1</v>
@@ -5576,68 +5576,68 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>833.9256956383012</v>
+        <v>949.7831932054952</v>
       </c>
       <c r="D71" t="n">
-        <v>8.289100872085879</v>
+        <v>5.360848171565396</v>
       </c>
       <c r="E71" t="n">
-        <v>188.1754205275467</v>
+        <v>199.3387355217609</v>
       </c>
       <c r="F71" t="n">
-        <v>0.6337262392044067</v>
+        <v>0.9301205277442932</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0107807656750083</v>
+        <v>0.0005017773364670575</v>
       </c>
       <c r="H71" t="n">
-        <v>928.8432674797829</v>
+        <v>949.783193205518</v>
       </c>
       <c r="I71" t="n">
-        <v>188.1754205275467</v>
+        <v>199.3387355217609</v>
       </c>
       <c r="J71" t="n">
-        <v>9.000057867156455</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K71" t="n">
-        <v>94.91757184148162</v>
+        <v>2.285105438204482e-11</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M71" t="n">
-        <v>0.7109569950705765</v>
+        <v>3.639793608296766</v>
       </c>
       <c r="N71" t="b">
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>0.7767660368799064</v>
+        <v>0.9113386273384094</v>
       </c>
       <c r="P71" t="n">
-        <v>0.001148071187293484</v>
+        <v>3.956037471652962e-05</v>
       </c>
       <c r="Q71" t="n">
-        <v>942.3959097614249</v>
+        <v>949.9166917557488</v>
       </c>
       <c r="R71" t="n">
-        <v>188.4372351828872</v>
+        <v>199.3476842624615</v>
       </c>
       <c r="S71" t="n">
-        <v>9.000057869254974</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T71" t="n">
-        <v>108.4702141231237</v>
+        <v>0.1334985502536483</v>
       </c>
       <c r="U71" t="n">
-        <v>0.2618146553405722</v>
+        <v>0.008948740700617464</v>
       </c>
       <c r="V71" t="n">
-        <v>0.7109569971690952</v>
+        <v>3.639793608296766</v>
       </c>
       <c r="W71" t="b">
         <v>1</v>
@@ -5649,68 +5649,68 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>932.9300903987731</v>
+        <v>859.049721060047</v>
       </c>
       <c r="D72" t="n">
-        <v>14.58085842659227</v>
+        <v>9.20155298729558</v>
       </c>
       <c r="E72" t="n">
-        <v>221.2210945723355</v>
+        <v>189.0584905356224</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7234267592430115</v>
+        <v>0.7010003924369812</v>
       </c>
       <c r="G72" t="n">
-        <v>0.007928796112537384</v>
+        <v>0.001017419970594347</v>
       </c>
       <c r="H72" t="n">
-        <v>932.9301221148419</v>
+        <v>919.4282385861036</v>
       </c>
       <c r="I72" t="n">
-        <v>224.7375904988753</v>
+        <v>189.0584905356224</v>
       </c>
       <c r="J72" t="n">
-        <v>11.77716114675325</v>
+        <v>9.32888373758998</v>
       </c>
       <c r="K72" t="n">
-        <v>3.17160687473006e-05</v>
+        <v>60.37851752605661</v>
       </c>
       <c r="L72" t="n">
-        <v>3.516495926539847</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>2.803697279839023</v>
+        <v>0.1273307502943997</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
       </c>
       <c r="O72" t="n">
-        <v>0.9805547719063622</v>
+        <v>0.5660150647163391</v>
       </c>
       <c r="P72" t="n">
-        <v>0.001774550646526203</v>
+        <v>0.0006031086086295545</v>
       </c>
       <c r="Q72" t="n">
-        <v>821.5555658109116</v>
+        <v>928.4998907770305</v>
       </c>
       <c r="R72" t="n">
-        <v>220.4062653062061</v>
+        <v>189.8645660831946</v>
       </c>
       <c r="S72" t="n">
-        <v>13.9342056221396</v>
+        <v>9.298330737299311</v>
       </c>
       <c r="T72" t="n">
-        <v>111.3745245878615</v>
+        <v>69.45016971698351</v>
       </c>
       <c r="U72" t="n">
-        <v>0.8148292661293794</v>
+        <v>0.8060755475721919</v>
       </c>
       <c r="V72" t="n">
-        <v>0.6466528044526729</v>
+        <v>0.09677775000373146</v>
       </c>
       <c r="W72" t="b">
         <v>1</v>
@@ -5722,68 +5722,68 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>949.6175564029259</v>
+        <v>871.376215413518</v>
       </c>
       <c r="D73" t="n">
-        <v>9.917669449982794</v>
+        <v>7.926433919294807</v>
       </c>
       <c r="E73" t="n">
-        <v>144.5779808580052</v>
+        <v>179.6327752373482</v>
       </c>
       <c r="F73" t="n">
-        <v>0.7905983924865723</v>
+        <v>0.7732902765274048</v>
       </c>
       <c r="G73" t="n">
-        <v>0.06394846737384796</v>
+        <v>0.001843692734837532</v>
       </c>
       <c r="H73" t="n">
-        <v>963.6246559823973</v>
+        <v>918.8325215337015</v>
       </c>
       <c r="I73" t="n">
-        <v>175.7990059882059</v>
+        <v>179.6327676548619</v>
       </c>
       <c r="J73" t="n">
-        <v>9.963551746923205</v>
+        <v>9.000615219003098</v>
       </c>
       <c r="K73" t="n">
-        <v>14.0070995794714</v>
+        <v>47.45630612018351</v>
       </c>
       <c r="L73" t="n">
-        <v>31.22102513020076</v>
+        <v>7.582486233559393e-06</v>
       </c>
       <c r="M73" t="n">
-        <v>0.04588229694041068</v>
+        <v>1.074181299708291</v>
       </c>
       <c r="N73" t="b">
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>0.9964367712060401</v>
+        <v>0.8805047273635864</v>
       </c>
       <c r="P73" t="n">
-        <v>0.001864698908634125</v>
+        <v>0.0006936352583579719</v>
       </c>
       <c r="Q73" t="n">
-        <v>811.0376113065032</v>
+        <v>933.1540303255215</v>
       </c>
       <c r="R73" t="n">
-        <v>150.8342806475491</v>
+        <v>181.2461943694394</v>
       </c>
       <c r="S73" t="n">
-        <v>9.856729712780513</v>
+        <v>9.000640905190261</v>
       </c>
       <c r="T73" t="n">
-        <v>138.5799450964226</v>
+        <v>61.77781491200346</v>
       </c>
       <c r="U73" t="n">
-        <v>6.256299789543931</v>
+        <v>1.613419132091252</v>
       </c>
       <c r="V73" t="n">
-        <v>0.06093973720228085</v>
+        <v>1.074206985895454</v>
       </c>
       <c r="W73" t="b">
         <v>1</v>
@@ -5795,68 +5795,68 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>901.0507251457127</v>
+        <v>931.4457141543127</v>
       </c>
       <c r="D74" t="n">
-        <v>8.594140314134535</v>
+        <v>5.966615046177687</v>
       </c>
       <c r="E74" t="n">
-        <v>204.0188466312755</v>
+        <v>195.8168760577822</v>
       </c>
       <c r="F74" t="n">
-        <v>0.5476883053779602</v>
+        <v>0.9244334697723389</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0107807656750083</v>
+        <v>0.0005017755320295691</v>
       </c>
       <c r="H74" t="n">
-        <v>928.843267476436</v>
+        <v>935.6639931132505</v>
       </c>
       <c r="I74" t="n">
-        <v>204.0188466312755</v>
+        <v>195.8168760577822</v>
       </c>
       <c r="J74" t="n">
-        <v>9.000057868418905</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K74" t="n">
-        <v>27.79254233072334</v>
+        <v>4.218278958937844</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>0.40591755428437</v>
+        <v>3.034026733684476</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0.470911561025959</v>
+        <v>0.560565173625946</v>
       </c>
       <c r="P74" t="n">
-        <v>0.0004686162051055615</v>
+        <v>6.196981848916039e-05</v>
       </c>
       <c r="Q74" t="n">
-        <v>950.2967706884758</v>
+        <v>931.4395549368886</v>
       </c>
       <c r="R74" t="n">
-        <v>203.4194637489505</v>
+        <v>195.9970530213007</v>
       </c>
       <c r="S74" t="n">
-        <v>9.00005786750633</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T74" t="n">
-        <v>49.24604554276311</v>
+        <v>0.006159217424055896</v>
       </c>
       <c r="U74" t="n">
-        <v>0.5993828823249885</v>
+        <v>0.1801769635185053</v>
       </c>
       <c r="V74" t="n">
-        <v>0.4059175533717951</v>
+        <v>3.034026733684476</v>
       </c>
       <c r="W74" t="b">
         <v>1</v>
@@ -5868,68 +5868,68 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>989.0621439654515</v>
+        <v>830.2144726175446</v>
       </c>
       <c r="D75" t="n">
-        <v>15.52164038629858</v>
+        <v>8.828976256445142</v>
       </c>
       <c r="E75" t="n">
-        <v>211.9652678668288</v>
+        <v>198.3914538010805</v>
       </c>
       <c r="F75" t="n">
-        <v>0.6981363892555237</v>
+        <v>0.8605555891990662</v>
       </c>
       <c r="G75" t="n">
-        <v>0.007554174400866032</v>
+        <v>0.0009911501547321677</v>
       </c>
       <c r="H75" t="n">
-        <v>991.5080415387845</v>
+        <v>919.4282408027589</v>
       </c>
       <c r="I75" t="n">
-        <v>211.9652678668273</v>
+        <v>198.3914538010775</v>
       </c>
       <c r="J75" t="n">
-        <v>11.77729472229702</v>
+        <v>9.328581997462527</v>
       </c>
       <c r="K75" t="n">
-        <v>2.445897573333013</v>
+        <v>89.21376818521424</v>
       </c>
       <c r="L75" t="n">
-        <v>1.534772309241816e-12</v>
+        <v>2.955857780762017e-12</v>
       </c>
       <c r="M75" t="n">
-        <v>3.744345664001555</v>
+        <v>0.4996057410173851</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>0.9974555323243089</v>
+        <v>0.7414771914482117</v>
       </c>
       <c r="P75" t="n">
-        <v>0.002474742833338809</v>
+        <v>0.0009387387544848025</v>
       </c>
       <c r="Q75" t="n">
-        <v>813.4360830307882</v>
+        <v>927.6206414360383</v>
       </c>
       <c r="R75" t="n">
-        <v>211.951497200641</v>
+        <v>199.0854529998045</v>
       </c>
       <c r="S75" t="n">
-        <v>14.49097995158031</v>
+        <v>9.000625542269841</v>
       </c>
       <c r="T75" t="n">
-        <v>175.6260609346633</v>
+        <v>97.40616881849371</v>
       </c>
       <c r="U75" t="n">
-        <v>0.01377066618786671</v>
+        <v>0.6939991987240148</v>
       </c>
       <c r="V75" t="n">
-        <v>1.030660434718268</v>
+        <v>0.1716492858246994</v>
       </c>
       <c r="W75" t="b">
         <v>1</v>
@@ -5941,68 +5941,68 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Stains</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>853.8620208630202</v>
+        <v>858.8247965039768</v>
       </c>
       <c r="D76" t="n">
-        <v>11.02488643276593</v>
+        <v>7.545357578691671</v>
       </c>
       <c r="E76" t="n">
-        <v>195.7072577712682</v>
+        <v>207.8025841162732</v>
       </c>
       <c r="F76" t="n">
-        <v>0.5955662727355957</v>
+        <v>0.9208168983459473</v>
       </c>
       <c r="G76" t="n">
-        <v>0.005909173749387264</v>
+        <v>0.0009904649341478944</v>
       </c>
       <c r="H76" t="n">
-        <v>922.9741913974954</v>
+        <v>933.0455648964845</v>
       </c>
       <c r="I76" t="n">
-        <v>195.7072577712682</v>
+        <v>207.802584116224</v>
       </c>
       <c r="J76" t="n">
-        <v>11.02488643276593</v>
+        <v>9.000792238411469</v>
       </c>
       <c r="K76" t="n">
-        <v>69.11217053447513</v>
+        <v>74.22076839250769</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>4.914113560516853e-11</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>1.455434659719798</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>0.9239158876633884</v>
+        <v>0.9375021457672119</v>
       </c>
       <c r="P76" t="n">
-        <v>0.0008527657826972769</v>
+        <v>0.0006701329839415848</v>
       </c>
       <c r="Q76" t="n">
-        <v>941.1512166181586</v>
+        <v>929.5857897239175</v>
       </c>
       <c r="R76" t="n">
-        <v>195.8624588216715</v>
+        <v>207.5299022253909</v>
       </c>
       <c r="S76" t="n">
-        <v>10.95390150437082</v>
+        <v>9.000641753803901</v>
       </c>
       <c r="T76" t="n">
-        <v>87.28919575513839</v>
+        <v>70.7609932199407</v>
       </c>
       <c r="U76" t="n">
-        <v>0.1552010504033206</v>
+        <v>0.2726818908822679</v>
       </c>
       <c r="V76" t="n">
-        <v>0.07098492839511472</v>
+        <v>1.45528417511223</v>
       </c>
       <c r="W76" t="b">
         <v>1</v>
@@ -6014,68 +6014,68 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>956.481679387896</v>
+        <v>1033.421152192183</v>
       </c>
       <c r="D77" t="n">
-        <v>8.228103317753556</v>
+        <v>9.659614894708168</v>
       </c>
       <c r="E77" t="n">
-        <v>129.7853208763004</v>
+        <v>187.7384288079069</v>
       </c>
       <c r="F77" t="n">
-        <v>0.7905983924865723</v>
+        <v>0.8256695866584778</v>
       </c>
       <c r="G77" t="n">
-        <v>0.01447403151541948</v>
+        <v>0.0003771110787056386</v>
       </c>
       <c r="H77" t="n">
-        <v>956.4867033702712</v>
+        <v>986.681296161195</v>
       </c>
       <c r="I77" t="n">
-        <v>176.1526712278782</v>
+        <v>187.7384288079069</v>
       </c>
       <c r="J77" t="n">
-        <v>9.000000000342993</v>
+        <v>9.659614862268491</v>
       </c>
       <c r="K77" t="n">
-        <v>0.00502398237529178</v>
+        <v>46.73985603098845</v>
       </c>
       <c r="L77" t="n">
-        <v>46.36735035157781</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>0.7718966825894373</v>
+        <v>3.243967761079602e-08</v>
       </c>
       <c r="N77" t="b">
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0.9996358091387807</v>
+        <v>0.9524146318435669</v>
       </c>
       <c r="P77" t="n">
-        <v>0.001843761011184523</v>
+        <v>0.0003148202667944133</v>
       </c>
       <c r="Q77" t="n">
-        <v>813.5237786304446</v>
+        <v>973.0624369005177</v>
       </c>
       <c r="R77" t="n">
-        <v>150.0000472904179</v>
+        <v>188.4506913878029</v>
       </c>
       <c r="S77" t="n">
-        <v>9.000057869470412</v>
+        <v>9.648103466181166</v>
       </c>
       <c r="T77" t="n">
-        <v>142.9579007574514</v>
+        <v>60.3587152916657</v>
       </c>
       <c r="U77" t="n">
-        <v>20.21472641411751</v>
+        <v>0.71226257989602</v>
       </c>
       <c r="V77" t="n">
-        <v>0.7719545517168562</v>
+        <v>0.01151142852700282</v>
       </c>
       <c r="W77" t="b">
         <v>1</v>
@@ -6087,68 +6087,68 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>977.1837898832805</v>
+        <v>955.8201925449489</v>
       </c>
       <c r="D78" t="n">
-        <v>16.1801220378143</v>
+        <v>9.394153645796282</v>
       </c>
       <c r="E78" t="n">
-        <v>182.7243896236366</v>
+        <v>147.706171563257</v>
       </c>
       <c r="F78" t="n">
-        <v>0.7118963003158569</v>
+        <v>0.9357934594154358</v>
       </c>
       <c r="G78" t="n">
-        <v>0.008424116298556328</v>
+        <v>0.0004813481937162578</v>
       </c>
       <c r="H78" t="n">
-        <v>951.5961433977041</v>
+        <v>955.8238816211176</v>
       </c>
       <c r="I78" t="n">
-        <v>182.7244096056963</v>
+        <v>176.1296297734542</v>
       </c>
       <c r="J78" t="n">
-        <v>11.77729185434857</v>
+        <v>9.394152686610232</v>
       </c>
       <c r="K78" t="n">
-        <v>25.58764648557644</v>
+        <v>0.003689076168711836</v>
       </c>
       <c r="L78" t="n">
-        <v>1.998205965492161e-05</v>
+        <v>28.42345821019714</v>
       </c>
       <c r="M78" t="n">
-        <v>4.40283018346573</v>
+        <v>9.591860496982463e-07</v>
       </c>
       <c r="N78" t="b">
         <v>1</v>
       </c>
       <c r="O78" t="n">
-        <v>0.9994469881392449</v>
+        <v>0.9998502731323242</v>
       </c>
       <c r="P78" t="n">
-        <v>0.002716686171042783</v>
+        <v>0.001525965635664761</v>
       </c>
       <c r="Q78" t="n">
-        <v>800.0000000000211</v>
+        <v>800.0005421327032</v>
       </c>
       <c r="R78" t="n">
-        <v>184.9705219587475</v>
+        <v>158.4272295515852</v>
       </c>
       <c r="S78" t="n">
-        <v>14.92241746523769</v>
+        <v>9.241181016988612</v>
       </c>
       <c r="T78" t="n">
-        <v>177.1837898832594</v>
+        <v>155.8196504122457</v>
       </c>
       <c r="U78" t="n">
-        <v>2.246132335110872</v>
+        <v>10.72105798832811</v>
       </c>
       <c r="V78" t="n">
-        <v>1.257704572576605</v>
+        <v>0.1529726288076692</v>
       </c>
       <c r="W78" t="b">
         <v>1</v>
@@ -6164,64 +6164,64 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>945.4280016931996</v>
+        <v>960.1629618523173</v>
       </c>
       <c r="D79" t="n">
-        <v>10.16969315797128</v>
+        <v>7.987831876099619</v>
       </c>
       <c r="E79" t="n">
-        <v>123.6167408783263</v>
+        <v>120.38691645617</v>
       </c>
       <c r="F79" t="n">
-        <v>0.7905983924865723</v>
+        <v>0.9136694073677063</v>
       </c>
       <c r="G79" t="n">
-        <v>0.01447403151541948</v>
+        <v>0.02702897414565086</v>
       </c>
       <c r="H79" t="n">
-        <v>945.4280010337602</v>
+        <v>925.8268142710091</v>
       </c>
       <c r="I79" t="n">
-        <v>176.1525536468137</v>
+        <v>165.8417338350223</v>
       </c>
       <c r="J79" t="n">
-        <v>10.16969315797128</v>
+        <v>9.88525554598826</v>
       </c>
       <c r="K79" t="n">
-        <v>6.594393653358566e-07</v>
+        <v>34.33614758130818</v>
       </c>
       <c r="L79" t="n">
-        <v>52.53581276848746</v>
+        <v>45.45481737885231</v>
       </c>
       <c r="M79" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>1.89742366988864</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>0.9998807250201307</v>
+        <v>1</v>
       </c>
       <c r="P79" t="n">
-        <v>0.001884741211074473</v>
+        <v>0.006979768630117178</v>
       </c>
       <c r="Q79" t="n">
-        <v>808.50818049264</v>
+        <v>800.0001992762569</v>
       </c>
       <c r="R79" t="n">
-        <v>150.0000472893526</v>
+        <v>152.7947715488496</v>
       </c>
       <c r="S79" t="n">
-        <v>10.10985451616791</v>
+        <v>9.000641934653842</v>
       </c>
       <c r="T79" t="n">
-        <v>136.9198212005596</v>
+        <v>160.1627625760603</v>
       </c>
       <c r="U79" t="n">
-        <v>26.38330641102635</v>
+        <v>32.40785509267954</v>
       </c>
       <c r="V79" t="n">
-        <v>0.05983864180337939</v>
+        <v>1.012810058554223</v>
       </c>
       <c r="W79" t="b">
         <v>1</v>
@@ -6233,68 +6233,68 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>879.6778683555364</v>
+        <v>1008.860966705372</v>
       </c>
       <c r="D80" t="n">
-        <v>8.409181496956737</v>
+        <v>11.75517422967491</v>
       </c>
       <c r="E80" t="n">
-        <v>192.244665557246</v>
+        <v>189.835374969951</v>
       </c>
       <c r="F80" t="n">
-        <v>0.6287869811058044</v>
+        <v>0.579925537109375</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0107807656750083</v>
+        <v>0.0002065182634396479</v>
       </c>
       <c r="H80" t="n">
-        <v>928.8432674868275</v>
+        <v>969.8951504520487</v>
       </c>
       <c r="I80" t="n">
-        <v>192.244665557246</v>
+        <v>189.835374969951</v>
       </c>
       <c r="J80" t="n">
-        <v>9.000057868106214</v>
+        <v>11.75517422967491</v>
       </c>
       <c r="K80" t="n">
-        <v>49.16539913129111</v>
+        <v>38.96581625332374</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>0.5908763711494771</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="N80" t="b">
         <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>0.7860919123070932</v>
+        <v>0.2208804935216904</v>
       </c>
       <c r="P80" t="n">
-        <v>0.0006479382174591173</v>
+        <v>0.0003166623646393418</v>
       </c>
       <c r="Q80" t="n">
-        <v>946.5494609654912</v>
+        <v>965.3488937046658</v>
       </c>
       <c r="R80" t="n">
-        <v>192.2341378348172</v>
+        <v>189.8714524856854</v>
       </c>
       <c r="S80" t="n">
-        <v>9.000057869116391</v>
+        <v>11.71480806099444</v>
       </c>
       <c r="T80" t="n">
-        <v>66.87159260995486</v>
+        <v>43.51207300070666</v>
       </c>
       <c r="U80" t="n">
-        <v>0.01052772242874767</v>
+        <v>0.03607751573431983</v>
       </c>
       <c r="V80" t="n">
-        <v>0.5908763721596539</v>
+        <v>0.04036616868046572</v>
       </c>
       <c r="W80" t="b">
         <v>1</v>
@@ -6310,64 +6310,64 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>870.7513134103172</v>
+        <v>872.5112835741422</v>
       </c>
       <c r="D81" t="n">
-        <v>7.884237696536948</v>
+        <v>8.030773748666871</v>
       </c>
       <c r="E81" t="n">
-        <v>194.6998869595861</v>
+        <v>206.1849114791996</v>
       </c>
       <c r="F81" t="n">
-        <v>0.6866244077682495</v>
+        <v>0.8621165752410889</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0107807656750083</v>
+        <v>0.0008488548919558525</v>
       </c>
       <c r="H81" t="n">
-        <v>928.8432674700963</v>
+        <v>935.6635631688569</v>
       </c>
       <c r="I81" t="n">
-        <v>194.6998869595861</v>
+        <v>206.1849114792007</v>
       </c>
       <c r="J81" t="n">
-        <v>9.000057866218208</v>
+        <v>9.000736857150294</v>
       </c>
       <c r="K81" t="n">
-        <v>58.09195405977914</v>
+        <v>63.15227959471463</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.080024958355352e-12</v>
       </c>
       <c r="M81" t="n">
-        <v>1.11582016968126</v>
+        <v>0.969963108483423</v>
       </c>
       <c r="N81" t="b">
         <v>1</v>
       </c>
       <c r="O81" t="n">
-        <v>0.8972688172538158</v>
+        <v>0.8429480791091919</v>
       </c>
       <c r="P81" t="n">
-        <v>0.0007327426574986495</v>
+        <v>0.0005371501320041716</v>
       </c>
       <c r="Q81" t="n">
-        <v>945.6919968923789</v>
+        <v>931.0261935682043</v>
       </c>
       <c r="R81" t="n">
-        <v>194.5188358052751</v>
+        <v>205.9717516595086</v>
       </c>
       <c r="S81" t="n">
-        <v>9.000057869271767</v>
+        <v>9.000641774204905</v>
       </c>
       <c r="T81" t="n">
-        <v>74.94068348206179</v>
+        <v>58.51490999406212</v>
       </c>
       <c r="U81" t="n">
-        <v>0.1810511543110067</v>
+        <v>0.2131598196909579</v>
       </c>
       <c r="V81" t="n">
-        <v>1.11582017273482</v>
+        <v>0.9698680255380339</v>
       </c>
       <c r="W81" t="b">
         <v>1</v>
@@ -6379,68 +6379,68 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>858.1779506520814</v>
+        <v>958.5182193420283</v>
       </c>
       <c r="D82" t="n">
-        <v>8.307110321367631</v>
+        <v>17.54506413723065</v>
       </c>
       <c r="E82" t="n">
-        <v>202.7281673227784</v>
+        <v>186.63028357336</v>
       </c>
       <c r="F82" t="n">
-        <v>0.6621172428131104</v>
+        <v>0.710898220539093</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0107807656750083</v>
+        <v>0.00131626904476434</v>
       </c>
       <c r="H82" t="n">
-        <v>928.8432674781424</v>
+        <v>969.3051348442323</v>
       </c>
       <c r="I82" t="n">
-        <v>202.7281673227784</v>
+        <v>187.8107180122819</v>
       </c>
       <c r="J82" t="n">
-        <v>9.000057868484312</v>
+        <v>12.18349667747283</v>
       </c>
       <c r="K82" t="n">
-        <v>70.66531682606092</v>
+        <v>10.78691550220401</v>
       </c>
       <c r="L82" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>1.180434438921878</v>
       </c>
       <c r="M82" t="n">
-        <v>0.6929475471166811</v>
+        <v>5.361567459757826</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
       </c>
       <c r="O82" t="n">
-        <v>0.8390944395826102</v>
+        <v>0.999996542930603</v>
       </c>
       <c r="P82" t="n">
-        <v>0.0008739934013113232</v>
+        <v>0.004110715351998806</v>
       </c>
       <c r="Q82" t="n">
-        <v>945.2514970619076</v>
+        <v>800.0000198014205</v>
       </c>
       <c r="R82" t="n">
-        <v>201.8182569368012</v>
+        <v>178.8236545071726</v>
       </c>
       <c r="S82" t="n">
-        <v>9.000057867271094</v>
+        <v>14.21433766679809</v>
       </c>
       <c r="T82" t="n">
-        <v>87.07354640982612</v>
+        <v>158.5181995406077</v>
       </c>
       <c r="U82" t="n">
-        <v>0.9099103859772129</v>
+        <v>7.806629066187412</v>
       </c>
       <c r="V82" t="n">
-        <v>0.6929475459034631</v>
+        <v>3.330726470432563</v>
       </c>
       <c r="W82" t="b">
         <v>1</v>
@@ -6452,68 +6452,68 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Stains</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>907.5210483459867</v>
+        <v>853.1068822635369</v>
       </c>
       <c r="D83" t="n">
-        <v>14.47908425102576</v>
+        <v>11.11190379454757</v>
       </c>
       <c r="E83" t="n">
-        <v>215.0193854879847</v>
+        <v>189.9561798748537</v>
       </c>
       <c r="F83" t="n">
-        <v>0.6851028800010681</v>
+        <v>0.5852022767066956</v>
       </c>
       <c r="G83" t="n">
-        <v>0.008092132396996021</v>
+        <v>0.0002988803607877344</v>
       </c>
       <c r="H83" t="n">
-        <v>908.0128723511148</v>
+        <v>907.8188165345761</v>
       </c>
       <c r="I83" t="n">
-        <v>215.0193854899296</v>
+        <v>189.9561798748533</v>
       </c>
       <c r="J83" t="n">
-        <v>11.77729472234742</v>
+        <v>11.11190379454756</v>
       </c>
       <c r="K83" t="n">
-        <v>0.4918240051280236</v>
+        <v>54.71193427103913</v>
       </c>
       <c r="L83" t="n">
-        <v>1.944982841450837e-09</v>
+        <v>3.694822225952521e-13</v>
       </c>
       <c r="M83" t="n">
-        <v>2.701789528678336</v>
+        <v>5.329070518200751e-15</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
       </c>
       <c r="O83" t="n">
-        <v>0.9493608401224272</v>
+        <v>0.7647218108177185</v>
       </c>
       <c r="P83" t="n">
-        <v>0.0014801647182863</v>
+        <v>0.0008331288117915392</v>
       </c>
       <c r="Q83" t="n">
-        <v>819.5266994189953</v>
+        <v>920.0810684273382</v>
       </c>
       <c r="R83" t="n">
-        <v>214.687373253186</v>
+        <v>191.9813636115171</v>
       </c>
       <c r="S83" t="n">
-        <v>13.93762867188919</v>
+        <v>11.07924406586887</v>
       </c>
       <c r="T83" t="n">
-        <v>87.99434892699139</v>
+        <v>66.97418616380128</v>
       </c>
       <c r="U83" t="n">
-        <v>0.3320122347986967</v>
+        <v>2.025183736663337</v>
       </c>
       <c r="V83" t="n">
-        <v>0.5414555791365689</v>
+        <v>0.03265972867869316</v>
       </c>
       <c r="W83" t="b">
         <v>1</v>
@@ -6525,68 +6525,68 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1045.066055964013</v>
+        <v>952.027795562598</v>
       </c>
       <c r="D84" t="n">
-        <v>11.97257990444693</v>
+        <v>4.656797091604268</v>
       </c>
       <c r="E84" t="n">
-        <v>208.7342481994733</v>
+        <v>186.1754126618551</v>
       </c>
       <c r="F84" t="n">
-        <v>0.6389009356498718</v>
+        <v>0.9323320388793945</v>
       </c>
       <c r="G84" t="n">
-        <v>0.007744077127426863</v>
+        <v>0.0005017773364670575</v>
       </c>
       <c r="H84" t="n">
-        <v>965.6040331806454</v>
+        <v>952.0278776577869</v>
       </c>
       <c r="I84" t="n">
-        <v>208.7342481994732</v>
+        <v>186.1754126618554</v>
       </c>
       <c r="J84" t="n">
-        <v>11.97257990444694</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K84" t="n">
-        <v>79.46202278336807</v>
+        <v>8.209518887269951e-05</v>
       </c>
       <c r="L84" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>2.842170943040401e-13</v>
       </c>
       <c r="M84" t="n">
-        <v>1.06581410364015e-14</v>
+        <v>4.343844688257894</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>0.9890397340445956</v>
+        <v>0.995408833026886</v>
       </c>
       <c r="P84" t="n">
-        <v>0.0006905390835415546</v>
+        <v>0.0001300808071391657</v>
       </c>
       <c r="Q84" t="n">
-        <v>948.9991614246512</v>
+        <v>951.5059737346145</v>
       </c>
       <c r="R84" t="n">
-        <v>207.9996969756142</v>
+        <v>186.6427205441336</v>
       </c>
       <c r="S84" t="n">
-        <v>11.91038521163961</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T84" t="n">
-        <v>96.06689453936224</v>
+        <v>0.5218218279835583</v>
       </c>
       <c r="U84" t="n">
-        <v>0.7345512238590572</v>
+        <v>0.4673078822784476</v>
       </c>
       <c r="V84" t="n">
-        <v>0.06219469280732426</v>
+        <v>4.343844688257894</v>
       </c>
       <c r="W84" t="b">
         <v>1</v>
@@ -6598,68 +6598,68 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>958.1627182555671</v>
+        <v>843.2242537188664</v>
       </c>
       <c r="D85" t="n">
-        <v>5.668629819570818</v>
+        <v>9.857427139480592</v>
       </c>
       <c r="E85" t="n">
-        <v>210.4580345136799</v>
+        <v>195.2329477018448</v>
       </c>
       <c r="F85" t="n">
-        <v>0.6949941515922546</v>
+        <v>0.8010148406028748</v>
       </c>
       <c r="G85" t="n">
-        <v>0.005485068075358868</v>
+        <v>0.0009919416625052691</v>
       </c>
       <c r="H85" t="n">
-        <v>958.1627182555648</v>
+        <v>919.4282448217766</v>
       </c>
       <c r="I85" t="n">
-        <v>210.4580345136799</v>
+        <v>195.2329477018454</v>
       </c>
       <c r="J85" t="n">
-        <v>9.000057869254071</v>
+        <v>9.857440020598014</v>
       </c>
       <c r="K85" t="n">
-        <v>2.387423592153937e-12</v>
+        <v>76.20399110291021</v>
       </c>
       <c r="L85" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>6.252776074688882e-13</v>
       </c>
       <c r="M85" t="n">
-        <v>3.331428049683254</v>
+        <v>1.288111742248077e-05</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>0.9598608837460775</v>
+        <v>0.4259612262248993</v>
       </c>
       <c r="P85" t="n">
-        <v>0.001754821458701727</v>
+        <v>0.0006472592940554023</v>
       </c>
       <c r="Q85" t="n">
-        <v>955.1891963532011</v>
+        <v>920.5291165008689</v>
       </c>
       <c r="R85" t="n">
-        <v>207.1162165948828</v>
+        <v>195.4909371048369</v>
       </c>
       <c r="S85" t="n">
-        <v>9.000057869254071</v>
+        <v>9.958908275007344</v>
       </c>
       <c r="T85" t="n">
-        <v>2.973521902366087</v>
+        <v>77.30486278200249</v>
       </c>
       <c r="U85" t="n">
-        <v>3.341817918797091</v>
+        <v>0.2579894029921093</v>
       </c>
       <c r="V85" t="n">
-        <v>3.331428049683254</v>
+        <v>0.1014811355267522</v>
       </c>
       <c r="W85" t="b">
         <v>1</v>
@@ -6671,68 +6671,68 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>963.6665798562213</v>
+        <v>944.6598326992513</v>
       </c>
       <c r="D86" t="n">
-        <v>6.165623509601247</v>
+        <v>8.686377349508932</v>
       </c>
       <c r="E86" t="n">
-        <v>194.8996182548566</v>
+        <v>129.8690795151252</v>
       </c>
       <c r="F86" t="n">
-        <v>0.6949941515922546</v>
+        <v>0.9353889226913452</v>
       </c>
       <c r="G86" t="n">
-        <v>0.005485068075358868</v>
+        <v>0.009299447759985924</v>
       </c>
       <c r="H86" t="n">
-        <v>963.6665798562193</v>
+        <v>961.9623342822939</v>
       </c>
       <c r="I86" t="n">
-        <v>194.8996182548567</v>
+        <v>167.3961728881269</v>
       </c>
       <c r="J86" t="n">
-        <v>9.000057869254071</v>
+        <v>10.21309702781242</v>
       </c>
       <c r="K86" t="n">
-        <v>2.046363078989089e-12</v>
+        <v>17.30250158304261</v>
       </c>
       <c r="L86" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>37.52709337300163</v>
       </c>
       <c r="M86" t="n">
-        <v>2.834434359652825</v>
+        <v>1.526719678303484</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>0.8258206962233363</v>
+        <v>0.9999997615814209</v>
       </c>
       <c r="P86" t="n">
-        <v>0.001239928065953514</v>
+        <v>0.004487267229706049</v>
       </c>
       <c r="Q86" t="n">
-        <v>957.3404950565476</v>
+        <v>800.0001890297845</v>
       </c>
       <c r="R86" t="n">
-        <v>194.3285072504098</v>
+        <v>154.1776123514343</v>
       </c>
       <c r="S86" t="n">
-        <v>9.000057869254071</v>
+        <v>9.000641919293081</v>
       </c>
       <c r="T86" t="n">
-        <v>6.326084799673708</v>
+        <v>144.6596436694668</v>
       </c>
       <c r="U86" t="n">
-        <v>0.5711110044468626</v>
+        <v>24.3085328363091</v>
       </c>
       <c r="V86" t="n">
-        <v>2.834434359652825</v>
+        <v>0.3142645697841484</v>
       </c>
       <c r="W86" t="b">
         <v>1</v>
@@ -6744,68 +6744,68 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>895.8137950481108</v>
+        <v>963.0088085381315</v>
       </c>
       <c r="D87" t="n">
-        <v>8.598473644703342</v>
+        <v>11.52744922557012</v>
       </c>
       <c r="E87" t="n">
-        <v>206.6625854025031</v>
+        <v>154.0011373358929</v>
       </c>
       <c r="F87" t="n">
-        <v>0.620580792427063</v>
+        <v>0.9366707801818848</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0107807656750083</v>
+        <v>0.008740254677832127</v>
       </c>
       <c r="H87" t="n">
-        <v>928.8432674808973</v>
+        <v>969.8968468191288</v>
       </c>
       <c r="I87" t="n">
-        <v>206.6625854025031</v>
+        <v>164.2921630999697</v>
       </c>
       <c r="J87" t="n">
-        <v>9.000057868423067</v>
+        <v>11.52741317986812</v>
       </c>
       <c r="K87" t="n">
-        <v>33.02947243278652</v>
+        <v>6.888038280997307</v>
       </c>
       <c r="L87" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>10.29102576407681</v>
       </c>
       <c r="M87" t="n">
-        <v>0.4015842237197251</v>
+        <v>3.604570200010926e-05</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
       </c>
       <c r="O87" t="n">
-        <v>0.6029070403352221</v>
+        <v>0.9963548183441162</v>
       </c>
       <c r="P87" t="n">
-        <v>0.0005241619693778824</v>
+        <v>0.001668425975367427</v>
       </c>
       <c r="Q87" t="n">
-        <v>950.0638055424195</v>
+        <v>802.4046981988903</v>
       </c>
       <c r="R87" t="n">
-        <v>205.8332559239097</v>
+        <v>164.1937758926997</v>
       </c>
       <c r="S87" t="n">
-        <v>9.000057864021455</v>
+        <v>11.35124755002548</v>
       </c>
       <c r="T87" t="n">
-        <v>54.25001049430864</v>
+        <v>160.6041103392412</v>
       </c>
       <c r="U87" t="n">
-        <v>0.8293294785933938</v>
+        <v>10.1926385568068</v>
       </c>
       <c r="V87" t="n">
-        <v>0.4015842193181136</v>
+        <v>0.1762016755446343</v>
       </c>
       <c r="W87" t="b">
         <v>1</v>
@@ -6817,68 +6817,68 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>944.6222261889034</v>
+        <v>892.491731029129</v>
       </c>
       <c r="D88" t="n">
-        <v>9.61241910874443</v>
+        <v>7.810111168776988</v>
       </c>
       <c r="E88" t="n">
-        <v>263.0470290970871</v>
+        <v>200.1966656998361</v>
       </c>
       <c r="F88" t="n">
-        <v>0.6614874005317688</v>
+        <v>0.8966370224952698</v>
       </c>
       <c r="G88" t="n">
-        <v>0.006804721895605326</v>
+        <v>0.0009936729911714792</v>
       </c>
       <c r="H88" t="n">
-        <v>944.2251868308263</v>
+        <v>933.0453150172963</v>
       </c>
       <c r="I88" t="n">
-        <v>222.3777147431355</v>
+        <v>200.1966656998328</v>
       </c>
       <c r="J88" t="n">
-        <v>9.743181577476669</v>
+        <v>9.000641767238305</v>
       </c>
       <c r="K88" t="n">
-        <v>0.3970393580771088</v>
+        <v>40.55358398816725</v>
       </c>
       <c r="L88" t="n">
-        <v>40.66931435395162</v>
+        <v>3.325340003357269e-12</v>
       </c>
       <c r="M88" t="n">
-        <v>0.1307624687322395</v>
+        <v>1.190530598461317</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
       </c>
       <c r="O88" t="n">
-        <v>0.9986307059018253</v>
+        <v>0.5854637622833252</v>
       </c>
       <c r="P88" t="n">
-        <v>0.001779694656980572</v>
+        <v>0.0003506072680465877</v>
       </c>
       <c r="Q88" t="n">
-        <v>817.6554609556013</v>
+        <v>934.1143449481981</v>
       </c>
       <c r="R88" t="n">
-        <v>239.1172318489688</v>
+        <v>200.3119122546795</v>
       </c>
       <c r="S88" t="n">
-        <v>9.547799124078217</v>
+        <v>9.000641838000544</v>
       </c>
       <c r="T88" t="n">
-        <v>126.9667652333021</v>
+        <v>41.62261391906907</v>
       </c>
       <c r="U88" t="n">
-        <v>23.92979724811832</v>
+        <v>0.1152465548434236</v>
       </c>
       <c r="V88" t="n">
-        <v>0.0646199846662121</v>
+        <v>1.190530669223556</v>
       </c>
       <c r="W88" t="b">
         <v>1</v>
@@ -6890,68 +6890,68 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>863.1668720727778</v>
+        <v>926.488107887503</v>
       </c>
       <c r="D89" t="n">
-        <v>8.257379855576692</v>
+        <v>2.529784239256371</v>
       </c>
       <c r="E89" t="n">
-        <v>202.4578501738119</v>
+        <v>204.8976295739575</v>
       </c>
       <c r="F89" t="n">
-        <v>0.6621172428131104</v>
+        <v>0.894043505191803</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0107807656750083</v>
+        <v>0.0005849990993738174</v>
       </c>
       <c r="H89" t="n">
-        <v>928.8432675179702</v>
+        <v>928.4781867933435</v>
       </c>
       <c r="I89" t="n">
-        <v>202.4578501738119</v>
+        <v>204.8976295852661</v>
       </c>
       <c r="J89" t="n">
-        <v>9.000057866603507</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K89" t="n">
-        <v>65.67639544519238</v>
+        <v>1.990078905840505</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.130860027842573e-08</v>
       </c>
       <c r="M89" t="n">
-        <v>0.7426780110268147</v>
+        <v>6.470857540605791</v>
       </c>
       <c r="N89" t="b">
         <v>1</v>
       </c>
       <c r="O89" t="n">
-        <v>0.8511362929325419</v>
+        <v>0.9933645725250244</v>
       </c>
       <c r="P89" t="n">
-        <v>0.0008210226646968817</v>
+        <v>7.393852138193324e-05</v>
       </c>
       <c r="Q89" t="n">
-        <v>945.6772694944309</v>
+        <v>927.9136192410906</v>
       </c>
       <c r="R89" t="n">
-        <v>201.6191501323349</v>
+        <v>204.800052155285</v>
       </c>
       <c r="S89" t="n">
-        <v>9.000057867690298</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T89" t="n">
-        <v>82.51039742165312</v>
+        <v>1.425511353587581</v>
       </c>
       <c r="U89" t="n">
-        <v>0.8387000414770114</v>
+        <v>0.09757741867250047</v>
       </c>
       <c r="V89" t="n">
-        <v>0.7426780121136058</v>
+        <v>6.470857540605791</v>
       </c>
       <c r="W89" t="b">
         <v>1</v>
@@ -6963,68 +6963,68 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>983.901020808615</v>
+        <v>972.9392573651033</v>
       </c>
       <c r="D90" t="n">
-        <v>13.76898907605516</v>
+        <v>6.22268352310375</v>
       </c>
       <c r="E90" t="n">
-        <v>198.4880261430288</v>
+        <v>197.3898722457993</v>
       </c>
       <c r="F90" t="n">
-        <v>0.7168129682540894</v>
+        <v>0.9299044013023376</v>
       </c>
       <c r="G90" t="n">
-        <v>0.007583793252706528</v>
+        <v>0.0005017528310418129</v>
       </c>
       <c r="H90" t="n">
-        <v>991.5080620940015</v>
+        <v>972.9392651459993</v>
       </c>
       <c r="I90" t="n">
-        <v>198.4880261430283</v>
+        <v>197.3898722457993</v>
       </c>
       <c r="J90" t="n">
-        <v>11.77729472265093</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K90" t="n">
-        <v>7.607041285386458</v>
+        <v>7.780895998621418e-06</v>
       </c>
       <c r="L90" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M90" t="n">
-        <v>1.991694353404233</v>
+        <v>2.777958256758413</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
       </c>
       <c r="O90" t="n">
-        <v>0.9262151264979197</v>
+        <v>0.4632772505283356</v>
       </c>
       <c r="P90" t="n">
-        <v>0.001737298450509479</v>
+        <v>5.905363286728971e-05</v>
       </c>
       <c r="Q90" t="n">
-        <v>840.2943356540662</v>
+        <v>971.9526968495683</v>
       </c>
       <c r="R90" t="n">
-        <v>199.3948084364884</v>
+        <v>197.4957337413712</v>
       </c>
       <c r="S90" t="n">
-        <v>13.11884733089248</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T90" t="n">
-        <v>143.6066851545488</v>
+        <v>0.986560515535075</v>
       </c>
       <c r="U90" t="n">
-        <v>0.9067822934595995</v>
+        <v>0.1058614955719008</v>
       </c>
       <c r="V90" t="n">
-        <v>0.6501417451626867</v>
+        <v>2.777958256758413</v>
       </c>
       <c r="W90" t="b">
         <v>1</v>
@@ -7036,68 +7036,68 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dirtiness</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>944.194509116227</v>
+        <v>961.4877270226775</v>
       </c>
       <c r="D91" t="n">
-        <v>9.530270203510403</v>
+        <v>5.656828570275804</v>
       </c>
       <c r="E91" t="n">
-        <v>248.7612646314657</v>
+        <v>203.1362182545766</v>
       </c>
       <c r="F91" t="n">
-        <v>0.6614874005317688</v>
+        <v>0.9300639033317566</v>
       </c>
       <c r="G91" t="n">
-        <v>0.006804721895605326</v>
+        <v>0.0005017708754166961</v>
       </c>
       <c r="H91" t="n">
-        <v>943.970686717293</v>
+        <v>961.4877679289691</v>
       </c>
       <c r="I91" t="n">
-        <v>222.3804919422276</v>
+        <v>203.1362182545766</v>
       </c>
       <c r="J91" t="n">
-        <v>9.623047244604891</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K91" t="n">
-        <v>0.2238223989339758</v>
+        <v>4.090629158781667e-05</v>
       </c>
       <c r="L91" t="n">
-        <v>26.38077268923811</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M91" t="n">
-        <v>0.0927770410944877</v>
+        <v>3.343813209586358</v>
       </c>
       <c r="N91" t="b">
         <v>1</v>
       </c>
       <c r="O91" t="n">
-        <v>0.9775344829919823</v>
+        <v>0.7523629069328308</v>
       </c>
       <c r="P91" t="n">
-        <v>0.001449320043861181</v>
+        <v>3.810009002336301e-05</v>
       </c>
       <c r="Q91" t="n">
-        <v>836.3444044785281</v>
+        <v>961.023793550907</v>
       </c>
       <c r="R91" t="n">
-        <v>230.5622105687933</v>
+        <v>203.208155845297</v>
       </c>
       <c r="S91" t="n">
-        <v>9.47193105192968</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T91" t="n">
-        <v>107.8501046376989</v>
+        <v>0.4639334717704742</v>
       </c>
       <c r="U91" t="n">
-        <v>18.19905406267233</v>
+        <v>0.07193759072038119</v>
       </c>
       <c r="V91" t="n">
-        <v>0.05833915158072323</v>
+        <v>3.343813209586358</v>
       </c>
       <c r="W91" t="b">
         <v>1</v>
@@ -7109,68 +7109,68 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Stains</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>876.3504279631637</v>
+        <v>1012.733720966446</v>
       </c>
       <c r="D92" t="n">
-        <v>11.34587500317772</v>
+        <v>11.10052158718142</v>
       </c>
       <c r="E92" t="n">
-        <v>209.9489333488838</v>
+        <v>194.5264532054536</v>
       </c>
       <c r="F92" t="n">
-        <v>0.6125013828277588</v>
+        <v>0.6780478954315186</v>
       </c>
       <c r="G92" t="n">
-        <v>0.005909173749387264</v>
+        <v>0.0002065182634396479</v>
       </c>
       <c r="H92" t="n">
-        <v>922.9741913766268</v>
+        <v>969.8951498482114</v>
       </c>
       <c r="I92" t="n">
-        <v>209.9489333488838</v>
+        <v>194.5264532054536</v>
       </c>
       <c r="J92" t="n">
-        <v>11.34587500317772</v>
+        <v>11.10052158718142</v>
       </c>
       <c r="K92" t="n">
-        <v>46.62376341346305</v>
+        <v>42.83857111823409</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>1.77635683940025e-15</v>
+        <v>0</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>0.8599177692213379</v>
+        <v>0.307061493396759</v>
       </c>
       <c r="P92" t="n">
-        <v>0.0006763184669479458</v>
+        <v>0.0002763189550023526</v>
       </c>
       <c r="Q92" t="n">
-        <v>945.7285221442801</v>
+        <v>968.5671410337684</v>
       </c>
       <c r="R92" t="n">
-        <v>209.0856916349678</v>
+        <v>194.4928325880919</v>
       </c>
       <c r="S92" t="n">
-        <v>11.2794832144418</v>
+        <v>11.07110038742804</v>
       </c>
       <c r="T92" t="n">
-        <v>69.37809418111635</v>
+        <v>44.16657993267711</v>
       </c>
       <c r="U92" t="n">
-        <v>0.8632417139160395</v>
+        <v>0.03362061736171995</v>
       </c>
       <c r="V92" t="n">
-        <v>0.06639178873592044</v>
+        <v>0.02942119975337754</v>
       </c>
       <c r="W92" t="b">
         <v>1</v>
@@ -7182,68 +7182,68 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1060.809240086009</v>
+        <v>942.9844485085017</v>
       </c>
       <c r="D93" t="n">
-        <v>9.631116897062975</v>
+        <v>10.54675837316494</v>
       </c>
       <c r="E93" t="n">
-        <v>200.2362060241465</v>
+        <v>125.2009240422635</v>
       </c>
       <c r="F93" t="n">
-        <v>0.6508126258850098</v>
+        <v>0.9365445375442505</v>
       </c>
       <c r="G93" t="n">
-        <v>0.007977633737027645</v>
+        <v>0.008770139887928963</v>
       </c>
       <c r="H93" t="n">
-        <v>965.6040331730386</v>
+        <v>961.965048199994</v>
       </c>
       <c r="I93" t="n">
-        <v>200.2362060241465</v>
+        <v>164.2936197249232</v>
       </c>
       <c r="J93" t="n">
-        <v>9.631116897062974</v>
+        <v>10.54675991027221</v>
       </c>
       <c r="K93" t="n">
-        <v>95.20520691297054</v>
+        <v>18.98059969149233</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>39.09269568265971</v>
       </c>
       <c r="M93" t="n">
-        <v>1.77635683940025e-15</v>
+        <v>1.537107275240146e-06</v>
       </c>
       <c r="N93" t="b">
         <v>1</v>
       </c>
       <c r="O93" t="n">
-        <v>0.9971472325905434</v>
+        <v>1</v>
       </c>
       <c r="P93" t="n">
-        <v>0.0006864910528413771</v>
+        <v>0.005425143521279097</v>
       </c>
       <c r="Q93" t="n">
-        <v>955.9335619967439</v>
+        <v>800.0000312533836</v>
       </c>
       <c r="R93" t="n">
-        <v>200.0043579965127</v>
+        <v>155.5913555596204</v>
       </c>
       <c r="S93" t="n">
-        <v>9.634533990032214</v>
+        <v>9.570740319814577</v>
       </c>
       <c r="T93" t="n">
-        <v>104.8756780892652</v>
+        <v>142.9844172551182</v>
       </c>
       <c r="U93" t="n">
-        <v>0.2318480276338448</v>
+        <v>30.39043151735687</v>
       </c>
       <c r="V93" t="n">
-        <v>0.003417092969238311</v>
+        <v>0.9760180533503622</v>
       </c>
       <c r="W93" t="b">
         <v>1</v>
@@ -7259,64 +7259,64 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>973.0469727792386</v>
+        <v>954.2639325647538</v>
       </c>
       <c r="D94" t="n">
-        <v>10.47787893609605</v>
+        <v>10.33724301374753</v>
       </c>
       <c r="E94" t="n">
-        <v>124.6665701044529</v>
+        <v>137.8400438434407</v>
       </c>
       <c r="F94" t="n">
-        <v>0.7892021536827087</v>
+        <v>0.936724841594696</v>
       </c>
       <c r="G94" t="n">
-        <v>0.01447403151541948</v>
+        <v>0.007099774666130543</v>
       </c>
       <c r="H94" t="n">
-        <v>964.5525899915925</v>
+        <v>909.5714153305253</v>
       </c>
       <c r="I94" t="n">
-        <v>176.1529501388631</v>
+        <v>164.293079444303</v>
       </c>
       <c r="J94" t="n">
-        <v>10.47795226877035</v>
+        <v>10.60853595284197</v>
       </c>
       <c r="K94" t="n">
-        <v>8.494382787646032</v>
+        <v>44.69251723422849</v>
       </c>
       <c r="L94" t="n">
-        <v>51.48638003441025</v>
+        <v>26.45303560086228</v>
       </c>
       <c r="M94" t="n">
-        <v>7.33326743027618e-05</v>
+        <v>0.2712929390944403</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
       </c>
       <c r="O94" t="n">
-        <v>0.9998778420671173</v>
+        <v>0.999996542930603</v>
       </c>
       <c r="P94" t="n">
-        <v>0.002115461938069771</v>
+        <v>0.003333923174068332</v>
       </c>
       <c r="Q94" t="n">
-        <v>808.8370170697486</v>
+        <v>800.0000439418317</v>
       </c>
       <c r="R94" t="n">
-        <v>150.0000472886719</v>
+        <v>158.4561967727692</v>
       </c>
       <c r="S94" t="n">
-        <v>10.41300028484139</v>
+        <v>10.05337013655258</v>
       </c>
       <c r="T94" t="n">
-        <v>164.2099557094899</v>
+        <v>154.2638886229221</v>
       </c>
       <c r="U94" t="n">
-        <v>25.33347718421902</v>
+        <v>20.61615292932851</v>
       </c>
       <c r="V94" t="n">
-        <v>0.0648786512546593</v>
+        <v>0.2838728771949448</v>
       </c>
       <c r="W94" t="b">
         <v>1</v>
@@ -7328,68 +7328,68 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>962.0516053595668</v>
+        <v>866.3135954672613</v>
       </c>
       <c r="D95" t="n">
-        <v>16.09234396975411</v>
+        <v>7.522699393143458</v>
       </c>
       <c r="E95" t="n">
-        <v>204.3244311042431</v>
+        <v>184.4397332854445</v>
       </c>
       <c r="F95" t="n">
-        <v>0.7234267592430115</v>
+        <v>0.9320161938667297</v>
       </c>
       <c r="G95" t="n">
-        <v>0.008424116298556328</v>
+        <v>0.001519713317975402</v>
       </c>
       <c r="H95" t="n">
-        <v>962.0517409419034</v>
+        <v>919.4282385708856</v>
       </c>
       <c r="I95" t="n">
-        <v>204.3243907763482</v>
+        <v>184.4397332854444</v>
       </c>
       <c r="J95" t="n">
-        <v>11.77729107542714</v>
+        <v>9.000641772860659</v>
       </c>
       <c r="K95" t="n">
-        <v>0.0001355823366111508</v>
+        <v>53.1146431036243</v>
       </c>
       <c r="L95" t="n">
-        <v>4.03278949079322e-05</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="M95" t="n">
-        <v>4.315052894326975</v>
+        <v>1.4779423797172</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
       </c>
       <c r="O95" t="n">
-        <v>0.9995460724268719</v>
+        <v>0.9412451982498169</v>
       </c>
       <c r="P95" t="n">
-        <v>0.002489114810205524</v>
+        <v>0.0005465617869049311</v>
       </c>
       <c r="Q95" t="n">
-        <v>801.0047840845582</v>
+        <v>933.9098903894704</v>
       </c>
       <c r="R95" t="n">
-        <v>204.9086887932281</v>
+        <v>184.9164873782845</v>
       </c>
       <c r="S95" t="n">
-        <v>14.99994213185762</v>
+        <v>9.000641822348175</v>
       </c>
       <c r="T95" t="n">
-        <v>161.0468212750086</v>
+        <v>67.59629492220915</v>
       </c>
       <c r="U95" t="n">
-        <v>0.5842576889849624</v>
+        <v>0.4767540928399967</v>
       </c>
       <c r="V95" t="n">
-        <v>1.092401837896491</v>
+        <v>1.477942429204717</v>
       </c>
       <c r="W95" t="b">
         <v>1</v>
@@ -7401,68 +7401,68 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>929.2738150525246</v>
+        <v>965.2935835087047</v>
       </c>
       <c r="D96" t="n">
-        <v>9.284455580241472</v>
+        <v>16.76683532917998</v>
       </c>
       <c r="E96" t="n">
-        <v>124.5817455398897</v>
+        <v>200.9176028663524</v>
       </c>
       <c r="F96" t="n">
-        <v>0.7905983924865723</v>
+        <v>0.9146213531494141</v>
       </c>
       <c r="G96" t="n">
-        <v>0.01444620545953512</v>
+        <v>0.0008162212907336652</v>
       </c>
       <c r="H96" t="n">
-        <v>928.8432674281495</v>
+        <v>951.4454618445599</v>
       </c>
       <c r="I96" t="n">
-        <v>176.1525536328066</v>
+        <v>202.6499990634966</v>
       </c>
       <c r="J96" t="n">
-        <v>9.284250544240875</v>
+        <v>12.18359449059338</v>
       </c>
       <c r="K96" t="n">
-        <v>0.4305476243750945</v>
+        <v>13.84812166414486</v>
       </c>
       <c r="L96" t="n">
-        <v>51.57080809291691</v>
+        <v>1.732396197144197</v>
       </c>
       <c r="M96" t="n">
-        <v>0.0002050360005974028</v>
+        <v>4.583240838586606</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
       </c>
       <c r="O96" t="n">
-        <v>0.9997724854317206</v>
+        <v>0.9999829530715942</v>
       </c>
       <c r="P96" t="n">
-        <v>0.001657856811156112</v>
+        <v>0.003629679558798671</v>
       </c>
       <c r="Q96" t="n">
-        <v>810.9974287912703</v>
+        <v>800.0000299899725</v>
       </c>
       <c r="R96" t="n">
-        <v>150.0000472868553</v>
+        <v>191.8273025892069</v>
       </c>
       <c r="S96" t="n">
-        <v>9.219603389999154</v>
+        <v>13.89003242424208</v>
       </c>
       <c r="T96" t="n">
-        <v>118.2763862612543</v>
+        <v>165.2935535187322</v>
       </c>
       <c r="U96" t="n">
-        <v>25.4183017469656</v>
+        <v>9.090300277145531</v>
       </c>
       <c r="V96" t="n">
-        <v>0.06485219024231803</v>
+        <v>2.8768029049379</v>
       </c>
       <c r="W96" t="b">
         <v>1</v>
@@ -7474,68 +7474,68 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1022.429663133332</v>
+        <v>968.2154140690368</v>
       </c>
       <c r="D97" t="n">
-        <v>11.11643074878221</v>
+        <v>8.848166911781199</v>
       </c>
       <c r="E97" t="n">
-        <v>213.6935336757777</v>
+        <v>152.2234677677183</v>
       </c>
       <c r="F97" t="n">
-        <v>0.6508126258850098</v>
+        <v>0.9364097118377686</v>
       </c>
       <c r="G97" t="n">
-        <v>0.007977633737027645</v>
+        <v>0.0004976012860424817</v>
       </c>
       <c r="H97" t="n">
-        <v>965.6040331587085</v>
+        <v>968.244809625298</v>
       </c>
       <c r="I97" t="n">
-        <v>213.6935336757777</v>
+        <v>176.1296280327352</v>
       </c>
       <c r="J97" t="n">
-        <v>11.11643074878221</v>
+        <v>9.000000101022215</v>
       </c>
       <c r="K97" t="n">
-        <v>56.82562997462378</v>
+        <v>0.02939555626119272</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>23.90616026501698</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>0.1518331892410156</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
       </c>
       <c r="O97" t="n">
-        <v>0.9128046873457122</v>
+        <v>0.9989148378372192</v>
       </c>
       <c r="P97" t="n">
-        <v>0.0005380867177944855</v>
+        <v>0.001407192670740187</v>
       </c>
       <c r="Q97" t="n">
-        <v>949.5141872923681</v>
+        <v>813.3892719110506</v>
       </c>
       <c r="R97" t="n">
-        <v>212.7202238743716</v>
+        <v>162.6894281831615</v>
       </c>
       <c r="S97" t="n">
-        <v>11.08650552326533</v>
+        <v>9.000447316348586</v>
       </c>
       <c r="T97" t="n">
-        <v>72.91547584096418</v>
+        <v>154.8261421579862</v>
       </c>
       <c r="U97" t="n">
-        <v>0.973309801406117</v>
+        <v>10.46596041544319</v>
       </c>
       <c r="V97" t="n">
-        <v>0.02992522551687493</v>
+        <v>0.1522804045673869</v>
       </c>
       <c r="W97" t="b">
         <v>1</v>
@@ -7551,64 +7551,64 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>907.9083440246934</v>
+        <v>953.4174705749397</v>
       </c>
       <c r="D98" t="n">
-        <v>10.62947649711448</v>
+        <v>11.46913598192008</v>
       </c>
       <c r="E98" t="n">
-        <v>128.3441543429158</v>
+        <v>128.7835388480846</v>
       </c>
       <c r="F98" t="n">
-        <v>0.6891825199127197</v>
+        <v>0.936724841594696</v>
       </c>
       <c r="G98" t="n">
-        <v>0.01369568612426519</v>
+        <v>0.04245391860604286</v>
       </c>
       <c r="H98" t="n">
-        <v>908.0129273449041</v>
+        <v>843.4070516182264</v>
       </c>
       <c r="I98" t="n">
-        <v>176.1525834652572</v>
+        <v>173.6136085934705</v>
       </c>
       <c r="J98" t="n">
-        <v>10.31533469854956</v>
+        <v>12.37031421688196</v>
       </c>
       <c r="K98" t="n">
-        <v>0.104583320210736</v>
+        <v>110.0104189567132</v>
       </c>
       <c r="L98" t="n">
-        <v>47.80842912234141</v>
+        <v>44.83006974538591</v>
       </c>
       <c r="M98" t="n">
-        <v>0.3141417985649149</v>
+        <v>0.9011782349618809</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>0.999296996534649</v>
+        <v>0.9999997615814209</v>
       </c>
       <c r="P98" t="n">
-        <v>0.001594043117660707</v>
+        <v>0.00549617875367403</v>
       </c>
       <c r="Q98" t="n">
-        <v>804.7393832002284</v>
+        <v>800.0000324218692</v>
       </c>
       <c r="R98" t="n">
-        <v>150.0000472900304</v>
+        <v>158.9430110284084</v>
       </c>
       <c r="S98" t="n">
-        <v>10.58237920855332</v>
+        <v>11.13789911145014</v>
       </c>
       <c r="T98" t="n">
-        <v>103.168960824465</v>
+        <v>153.4174381530705</v>
       </c>
       <c r="U98" t="n">
-        <v>21.65589294711461</v>
+        <v>30.15947218032389</v>
       </c>
       <c r="V98" t="n">
-        <v>0.04709728856115447</v>
+        <v>0.331236870469942</v>
       </c>
       <c r="W98" t="b">
         <v>1</v>
@@ -7620,68 +7620,68 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Stains</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>868.4370442567305</v>
+        <v>957.5527914357328</v>
       </c>
       <c r="D99" t="n">
-        <v>11.02975816430903</v>
+        <v>6.273858724981029</v>
       </c>
       <c r="E99" t="n">
-        <v>213.1212320917566</v>
+        <v>210.8378318806114</v>
       </c>
       <c r="F99" t="n">
-        <v>0.5927297472953796</v>
+        <v>0.9283376932144165</v>
       </c>
       <c r="G99" t="n">
-        <v>0.005909173749387264</v>
+        <v>0.0005017013754695654</v>
       </c>
       <c r="H99" t="n">
-        <v>922.9741913807004</v>
+        <v>957.5527914357391</v>
       </c>
       <c r="I99" t="n">
-        <v>213.1212320917566</v>
+        <v>210.8378318806112</v>
       </c>
       <c r="J99" t="n">
-        <v>11.02975816430903</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K99" t="n">
-        <v>54.53714712396993</v>
+        <v>6.252776074688882e-12</v>
       </c>
       <c r="L99" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>1.989519660128281e-13</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>2.726783054881134</v>
       </c>
       <c r="N99" t="b">
         <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>0.8824982214395597</v>
+        <v>0.1798679828643799</v>
       </c>
       <c r="P99" t="n">
-        <v>0.0007395499293089758</v>
+        <v>4.90026650368236e-05</v>
       </c>
       <c r="Q99" t="n">
-        <v>944.1241120697684</v>
+        <v>959.0235485976783</v>
       </c>
       <c r="R99" t="n">
-        <v>211.8757752146327</v>
+        <v>210.6703539728738</v>
       </c>
       <c r="S99" t="n">
-        <v>10.97105843762282</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T99" t="n">
-        <v>75.68706781303797</v>
+        <v>1.470757161945471</v>
       </c>
       <c r="U99" t="n">
-        <v>1.245456877123956</v>
+        <v>0.167477907737549</v>
       </c>
       <c r="V99" t="n">
-        <v>0.0586997266862106</v>
+        <v>2.726783054881134</v>
       </c>
       <c r="W99" t="b">
         <v>1</v>
@@ -7697,64 +7697,64 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>969.1507432655953</v>
+        <v>918.183082862826</v>
       </c>
       <c r="D100" t="n">
-        <v>15.11779471417397</v>
+        <v>15.8800637485525</v>
       </c>
       <c r="E100" t="n">
-        <v>205.7625139202212</v>
+        <v>182.155694562732</v>
       </c>
       <c r="F100" t="n">
-        <v>0.7224258780479431</v>
+        <v>0.7846332192420959</v>
       </c>
       <c r="G100" t="n">
-        <v>0.008410884998738766</v>
+        <v>0.001172919757664204</v>
       </c>
       <c r="H100" t="n">
-        <v>969.1506879267129</v>
+        <v>891.3488276612976</v>
       </c>
       <c r="I100" t="n">
-        <v>205.7625283762321</v>
+        <v>182.1556945627322</v>
       </c>
       <c r="J100" t="n">
-        <v>11.77728774237585</v>
+        <v>11.82175923198185</v>
       </c>
       <c r="K100" t="n">
-        <v>5.533888247555296e-05</v>
+        <v>26.83425520152844</v>
       </c>
       <c r="L100" t="n">
-        <v>1.445601091631943e-05</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="M100" t="n">
-        <v>3.340506971798114</v>
+        <v>4.058304516570646</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>0.9968660788395162</v>
+        <v>0.9989892840385437</v>
       </c>
       <c r="P100" t="n">
-        <v>0.002151857035013566</v>
+        <v>0.002657468430697918</v>
       </c>
       <c r="Q100" t="n">
-        <v>817.4198050524553</v>
+        <v>800.0000000797795</v>
       </c>
       <c r="R100" t="n">
-        <v>206.1928410189711</v>
+        <v>177.3612850526923</v>
       </c>
       <c r="S100" t="n">
-        <v>14.23725958088068</v>
+        <v>14.07866665159937</v>
       </c>
       <c r="T100" t="n">
-        <v>151.73093821314</v>
+        <v>118.1830827830465</v>
       </c>
       <c r="U100" t="n">
-        <v>0.4303270987498991</v>
+        <v>4.794409510039685</v>
       </c>
       <c r="V100" t="n">
-        <v>0.8805351332932911</v>
+        <v>1.801397096953126</v>
       </c>
       <c r="W100" t="b">
         <v>1</v>
@@ -7766,68 +7766,68 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>964.50191573696</v>
+        <v>952.5170560737424</v>
       </c>
       <c r="D101" t="n">
-        <v>10.0773637302841</v>
+        <v>4.006125349756688</v>
       </c>
       <c r="E101" t="n">
-        <v>133.3308696860855</v>
+        <v>183.7661784047959</v>
       </c>
       <c r="F101" t="n">
-        <v>0.7905983924865723</v>
+        <v>0.9323320388793945</v>
       </c>
       <c r="G101" t="n">
-        <v>0.01447403151541948</v>
+        <v>0.0005017046350985765</v>
       </c>
       <c r="H101" t="n">
-        <v>964.5019160363886</v>
+        <v>952.5170560737286</v>
       </c>
       <c r="I101" t="n">
-        <v>176.1525536347904</v>
+        <v>183.7661784047961</v>
       </c>
       <c r="J101" t="n">
-        <v>10.07736324053892</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K101" t="n">
-        <v>2.994286205648677e-07</v>
+        <v>1.386979420203716e-11</v>
       </c>
       <c r="L101" t="n">
-        <v>42.8216839487049</v>
+        <v>2.557953848736361e-13</v>
       </c>
       <c r="M101" t="n">
-        <v>4.897451741925352e-07</v>
+        <v>4.994516430105475</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>0.9995852359882401</v>
+        <v>0.9992189407348633</v>
       </c>
       <c r="P101" t="n">
-        <v>0.002021378079006431</v>
+        <v>0.0001652052305871621</v>
       </c>
       <c r="Q101" t="n">
-        <v>809.7399962441003</v>
+        <v>951.8445947940265</v>
       </c>
       <c r="R101" t="n">
-        <v>150.0000472891086</v>
+        <v>184.3411756244252</v>
       </c>
       <c r="S101" t="n">
-        <v>10.01172077475117</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T101" t="n">
-        <v>154.7619194928596</v>
+        <v>0.6724612797158898</v>
       </c>
       <c r="U101" t="n">
-        <v>16.66917760302309</v>
+        <v>0.5749972196293811</v>
       </c>
       <c r="V101" t="n">
-        <v>0.06564295553292787</v>
+        <v>4.994516430105475</v>
       </c>
       <c r="W101" t="b">
         <v>1</v>

--- a/export_dati/06_Step6_Simulazione_Massiva_100.xlsx
+++ b/export_dati/06_Step6_Simulazione_Massiva_100.xlsx
@@ -539,68 +539,68 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>946.9778445568023</v>
+        <v>956.7070005389429</v>
       </c>
       <c r="D2" t="n">
-        <v>10.25061390415358</v>
+        <v>2.960049688720861</v>
       </c>
       <c r="E2" t="n">
-        <v>121.3394806969968</v>
+        <v>216.8657265165326</v>
       </c>
       <c r="F2" t="n">
-        <v>0.936724841594696</v>
+        <v>0.8311465382575989</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008770139887928963</v>
+        <v>0.001009689178317785</v>
       </c>
       <c r="H2" t="n">
-        <v>961.9639154094285</v>
+        <v>956.7070125195878</v>
       </c>
       <c r="I2" t="n">
-        <v>164.2910916663061</v>
+        <v>216.8657265166484</v>
       </c>
       <c r="J2" t="n">
-        <v>10.2506139133091</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K2" t="n">
-        <v>14.9860708526262</v>
+        <v>1.198064489926765e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>42.95161096930933</v>
+        <v>1.157900442194659e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>9.15552256230967e-09</v>
+        <v>6.040592091141301</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0.9984650611877441</v>
       </c>
       <c r="P2" t="n">
-        <v>0.006659499369561672</v>
+        <v>0.0001277170667890459</v>
       </c>
       <c r="Q2" t="n">
-        <v>800.0000219124043</v>
+        <v>953.5419627940839</v>
       </c>
       <c r="R2" t="n">
-        <v>153.8185114094987</v>
+        <v>216.3614796664943</v>
       </c>
       <c r="S2" t="n">
-        <v>9.235524845135297</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T2" t="n">
-        <v>146.977822644398</v>
+        <v>3.165037744858978</v>
       </c>
       <c r="U2" t="n">
-        <v>32.47903071250188</v>
+        <v>0.5042468500382995</v>
       </c>
       <c r="V2" t="n">
-        <v>1.015089059018282</v>
+        <v>6.040592091141301</v>
       </c>
       <c r="W2" t="b">
         <v>1</v>
@@ -616,64 +616,64 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>944.3042118096921</v>
+        <v>963.0582695268022</v>
       </c>
       <c r="D3" t="n">
-        <v>8.944074329837868</v>
+        <v>9.031225337763633</v>
       </c>
       <c r="E3" t="n">
-        <v>123.3414099489059</v>
+        <v>139.5365085777432</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9283017516136169</v>
+        <v>0.9065932631492615</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01065392885357141</v>
+        <v>0.001030125422403216</v>
       </c>
       <c r="H3" t="n">
-        <v>913.9203041578202</v>
+        <v>962.9737328302404</v>
       </c>
       <c r="I3" t="n">
-        <v>172.0412147838669</v>
+        <v>176.1361461155139</v>
       </c>
       <c r="J3" t="n">
-        <v>10.2133161481209</v>
+        <v>9.032050357428021</v>
       </c>
       <c r="K3" t="n">
-        <v>30.38390765187194</v>
+        <v>0.08453669656182683</v>
       </c>
       <c r="L3" t="n">
-        <v>48.69980483496101</v>
+        <v>36.59963753777063</v>
       </c>
       <c r="M3" t="n">
-        <v>1.269241818283033</v>
+        <v>0.0008250196643881935</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0.9997538924217224</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00610250374302268</v>
+        <v>0.004132937174290419</v>
       </c>
       <c r="Q3" t="n">
-        <v>800.0000297768911</v>
+        <v>800.000046225852</v>
       </c>
       <c r="R3" t="n">
-        <v>153.2155563052054</v>
+        <v>152.9961138612727</v>
       </c>
       <c r="S3" t="n">
-        <v>9.000642056348982</v>
+        <v>9.000626972961413</v>
       </c>
       <c r="T3" t="n">
-        <v>144.304182032801</v>
+        <v>163.0582233009502</v>
       </c>
       <c r="U3" t="n">
-        <v>29.87414635629949</v>
+        <v>13.45960528352947</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05656772651111375</v>
+        <v>0.03059836480221989</v>
       </c>
       <c r="W3" t="b">
         <v>1</v>
@@ -685,68 +685,68 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>904.715095600088</v>
+        <v>887.7583948719523</v>
       </c>
       <c r="D4" t="n">
-        <v>6.107927575160065</v>
+        <v>7.910424121717402</v>
       </c>
       <c r="E4" t="n">
-        <v>187.2758413485633</v>
+        <v>189.7627174383277</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5180330276489258</v>
+        <v>0.8497275114059448</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006940661114640534</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H4" t="n">
-        <v>918.8325213643333</v>
+        <v>933.0453158671529</v>
       </c>
       <c r="I4" t="n">
-        <v>187.2757770889637</v>
+        <v>189.7627174383277</v>
       </c>
       <c r="J4" t="n">
-        <v>9.0006415701978</v>
+        <v>9.000641723067526</v>
       </c>
       <c r="K4" t="n">
-        <v>14.11742576424524</v>
+        <v>45.2869209952006</v>
       </c>
       <c r="L4" t="n">
-        <v>6.425959961120498e-05</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.892713995037735</v>
+        <v>1.090217601350123</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09352170675992966</v>
+        <v>0.7980248332023621</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0001489813439548016</v>
+        <v>0.0003900832962244749</v>
       </c>
       <c r="Q4" t="n">
-        <v>905.5404680892183</v>
+        <v>935.4339213799741</v>
       </c>
       <c r="R4" t="n">
-        <v>187.4784567056928</v>
+        <v>190.9073789144944</v>
       </c>
       <c r="S4" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641399869208</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8253724891302454</v>
+        <v>47.67552650802179</v>
       </c>
       <c r="U4" t="n">
-        <v>0.202615357129531</v>
+        <v>1.144661476166732</v>
       </c>
       <c r="V4" t="n">
-        <v>2.892714204702098</v>
+        <v>1.090217278151806</v>
       </c>
       <c r="W4" t="b">
         <v>1</v>
@@ -762,64 +762,64 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>873.427052571014</v>
+        <v>858.8247965039768</v>
       </c>
       <c r="D5" t="n">
-        <v>8.978020743857002</v>
+        <v>7.545357578691671</v>
       </c>
       <c r="E5" t="n">
-        <v>188.4813806348763</v>
+        <v>207.8025841162732</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6949636340141296</v>
+        <v>0.9223969578742981</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001017419970594347</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H5" t="n">
-        <v>919.4282413549977</v>
+        <v>933.0453163595322</v>
       </c>
       <c r="I5" t="n">
-        <v>188.4813806348763</v>
+        <v>207.8025841162733</v>
       </c>
       <c r="J5" t="n">
-        <v>9.329040318616576</v>
+        <v>9.000641635262166</v>
       </c>
       <c r="K5" t="n">
-        <v>46.00118878398371</v>
+        <v>74.22051985555538</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3510195747595741</v>
+        <v>1.455284056570496</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5460717678070068</v>
+        <v>0.9807637929916382</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0004996052011847496</v>
+        <v>0.000568950898014009</v>
       </c>
       <c r="Q5" t="n">
-        <v>932.9256879424437</v>
+        <v>930.1514210452157</v>
       </c>
       <c r="R5" t="n">
-        <v>189.1457888726968</v>
+        <v>207.4168434684353</v>
       </c>
       <c r="S5" t="n">
-        <v>9.055393497055434</v>
+        <v>9.000641886527552</v>
       </c>
       <c r="T5" t="n">
-        <v>59.49863537142971</v>
+        <v>71.32662454123886</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6644082378205098</v>
+        <v>0.3857406478378778</v>
       </c>
       <c r="V5" t="n">
-        <v>0.07737275319843206</v>
+        <v>1.455284307835881</v>
       </c>
       <c r="W5" t="b">
         <v>1</v>
@@ -835,64 +835,64 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>862.8168537192801</v>
+        <v>840.864426422445</v>
       </c>
       <c r="D6" t="n">
-        <v>9.055073258720897</v>
+        <v>7.2688151502831</v>
       </c>
       <c r="E6" t="n">
-        <v>186.3258914472227</v>
+        <v>214.1732560514905</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6867222785949707</v>
+        <v>0.9229809045791626</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001256016083061695</v>
+        <v>0.003427958348765969</v>
       </c>
       <c r="H6" t="n">
-        <v>919.4282392833672</v>
+        <v>919.4292614984873</v>
       </c>
       <c r="I6" t="n">
-        <v>186.3258914472227</v>
+        <v>214.1732853240142</v>
       </c>
       <c r="J6" t="n">
-        <v>9.103639971063563</v>
+        <v>9.000641620391105</v>
       </c>
       <c r="K6" t="n">
-        <v>56.61138556408719</v>
+        <v>78.5648350760423</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.92725237045488e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.04856671234266585</v>
+        <v>1.731826470108006</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5865327715873718</v>
+        <v>0.9851906895637512</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0005892477347515523</v>
+        <v>0.0007730433135293424</v>
       </c>
       <c r="Q6" t="n">
-        <v>931.215072320197</v>
+        <v>929.208491204292</v>
       </c>
       <c r="R6" t="n">
-        <v>187.0908162274205</v>
+        <v>212.796194392322</v>
       </c>
       <c r="S6" t="n">
-        <v>9.146899377497578</v>
+        <v>9.000641780042598</v>
       </c>
       <c r="T6" t="n">
-        <v>68.39821860091695</v>
+        <v>88.34406478184701</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7649247801978163</v>
+        <v>1.377061659168419</v>
       </c>
       <c r="V6" t="n">
-        <v>0.09182611877668023</v>
+        <v>1.731826629759498</v>
       </c>
       <c r="W6" t="b">
         <v>1</v>
@@ -908,64 +908,64 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>847.2631338004336</v>
+        <v>837.7732934689444</v>
       </c>
       <c r="D7" t="n">
-        <v>9.172488831188625</v>
+        <v>6.753432575528466</v>
       </c>
       <c r="E7" t="n">
-        <v>189.3189149000324</v>
+        <v>190.2151386067326</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7424965500831604</v>
+        <v>0.9318311810493469</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001017419970594347</v>
+        <v>0.00342625891789794</v>
       </c>
       <c r="H7" t="n">
-        <v>919.4282395837976</v>
+        <v>919.4285746978336</v>
       </c>
       <c r="I7" t="n">
-        <v>189.3189149000324</v>
+        <v>190.2152978630455</v>
       </c>
       <c r="J7" t="n">
-        <v>9.328631572554473</v>
+        <v>9.000641470395857</v>
       </c>
       <c r="K7" t="n">
-        <v>72.16510578336397</v>
+        <v>81.65528122888918</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.000159256312826983</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1561427413658478</v>
+        <v>2.247208894867391</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6044442057609558</v>
+        <v>0.9940164089202881</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0007164647686295211</v>
+        <v>0.0008019836386665702</v>
       </c>
       <c r="Q7" t="n">
-        <v>927.4571806157584</v>
+        <v>930.3887040062316</v>
       </c>
       <c r="R7" t="n">
-        <v>190.2719624961</v>
+        <v>192.1108243414958</v>
       </c>
       <c r="S7" t="n">
-        <v>9.285528667324632</v>
+        <v>9.000641542753687</v>
       </c>
       <c r="T7" t="n">
-        <v>80.19404681532478</v>
+        <v>92.61541053728718</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9530475960675631</v>
+        <v>1.895685734763134</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1130398361360072</v>
+        <v>2.247208967225221</v>
       </c>
       <c r="W7" t="b">
         <v>1</v>
@@ -981,64 +981,64 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>958.80278331025</v>
+        <v>925.5264205940191</v>
       </c>
       <c r="D8" t="n">
-        <v>10.28318524302703</v>
+        <v>9.240641298553927</v>
       </c>
       <c r="E8" t="n">
-        <v>160.5893325834675</v>
+        <v>121.6092848320675</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9366707801818848</v>
+        <v>0.9032833576202393</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0004814271233044565</v>
+        <v>0.01683678291738033</v>
       </c>
       <c r="H8" t="n">
-        <v>958.8037626434731</v>
+        <v>949.4830945243247</v>
       </c>
       <c r="I8" t="n">
-        <v>176.1296281525858</v>
+        <v>164.2954243232535</v>
       </c>
       <c r="J8" t="n">
-        <v>10.28318697955493</v>
+        <v>10.35900525829285</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0009793332230856322</v>
+        <v>23.95667393030556</v>
       </c>
       <c r="L8" t="n">
-        <v>15.54029556911834</v>
+        <v>42.68613949118594</v>
       </c>
       <c r="M8" t="n">
-        <v>1.736527895701556e-06</v>
+        <v>1.118363959738925</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9719220995903015</v>
+        <v>0.9999545812606812</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001231190282851458</v>
+        <v>0.00681344885379076</v>
       </c>
       <c r="Q8" t="n">
-        <v>825.9301997375334</v>
+        <v>800.0000219058935</v>
       </c>
       <c r="R8" t="n">
-        <v>171.0947458983082</v>
+        <v>150.0005528888143</v>
       </c>
       <c r="S8" t="n">
-        <v>10.19636104480619</v>
+        <v>9.000517302645695</v>
       </c>
       <c r="T8" t="n">
-        <v>132.8725835727166</v>
+        <v>125.5263986881256</v>
       </c>
       <c r="U8" t="n">
-        <v>10.50541331484075</v>
+        <v>28.39126805674678</v>
       </c>
       <c r="V8" t="n">
-        <v>0.08682419822084064</v>
+        <v>0.2401239959082311</v>
       </c>
       <c r="W8" t="b">
         <v>1</v>
@@ -1054,64 +1054,64 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>928.6179141766808</v>
+        <v>946.8480970394265</v>
       </c>
       <c r="D9" t="n">
-        <v>8.764360589699487</v>
+        <v>8.922389234586777</v>
       </c>
       <c r="E9" t="n">
-        <v>105.423870623254</v>
+        <v>138.1580572051397</v>
       </c>
       <c r="F9" t="n">
-        <v>0.931891918182373</v>
+        <v>0.9055460095405579</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005232266616076231</v>
+        <v>0.001030128798447549</v>
       </c>
       <c r="H9" t="n">
-        <v>922.2378914997506</v>
+        <v>946.8713463951168</v>
       </c>
       <c r="I9" t="n">
-        <v>173.6136106608438</v>
+        <v>176.1301709725823</v>
       </c>
       <c r="J9" t="n">
-        <v>9.886858219649927</v>
+        <v>9.000046829594119</v>
       </c>
       <c r="K9" t="n">
-        <v>6.380022676930139</v>
+        <v>0.0232493556902682</v>
       </c>
       <c r="L9" t="n">
-        <v>68.1897400375898</v>
+        <v>37.97211376744261</v>
       </c>
       <c r="M9" t="n">
-        <v>1.122497629950439</v>
+        <v>0.07765759500734148</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0.9997928738594055</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01186289545148611</v>
+        <v>0.004489098209887743</v>
       </c>
       <c r="Q9" t="n">
-        <v>800.0000277327417</v>
+        <v>800.0001164632197</v>
       </c>
       <c r="R9" t="n">
-        <v>151.17209527343</v>
+        <v>152.5000897651726</v>
       </c>
       <c r="S9" t="n">
-        <v>9.000642108477239</v>
+        <v>9.000642074482945</v>
       </c>
       <c r="T9" t="n">
-        <v>128.617886443939</v>
+        <v>146.8479805762069</v>
       </c>
       <c r="U9" t="n">
-        <v>45.74822465017603</v>
+        <v>14.34203256003286</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2362815187777514</v>
+        <v>0.07825283989616771</v>
       </c>
       <c r="W9" t="b">
         <v>1</v>
@@ -1123,68 +1123,68 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>960.6999207074333</v>
+        <v>930.9026183683185</v>
       </c>
       <c r="D10" t="n">
-        <v>13.60431810949872</v>
+        <v>9.525206097560066</v>
       </c>
       <c r="E10" t="n">
-        <v>210.2668897524188</v>
+        <v>125.4374594005599</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9146213531494141</v>
+        <v>0.9060201048851013</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0002867737784981728</v>
+        <v>0.3082052767276764</v>
       </c>
       <c r="H10" t="n">
-        <v>928.0985965868126</v>
+        <v>883.1735957798602</v>
       </c>
       <c r="I10" t="n">
-        <v>209.7307690011954</v>
+        <v>154.9694592328663</v>
       </c>
       <c r="J10" t="n">
-        <v>11.82175029222345</v>
+        <v>13.49511302625649</v>
       </c>
       <c r="K10" t="n">
-        <v>32.60132412062069</v>
+        <v>47.72902258845829</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5361207512234216</v>
+        <v>29.53199983230644</v>
       </c>
       <c r="M10" t="n">
-        <v>1.782567817275266</v>
+        <v>3.969906928696423</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5614466667175293</v>
+        <v>0.9999504089355469</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001731006195768714</v>
+        <v>0.006811983417719603</v>
       </c>
       <c r="Q10" t="n">
-        <v>816.8216669343834</v>
+        <v>800.0000324709177</v>
       </c>
       <c r="R10" t="n">
-        <v>210.6084233075179</v>
+        <v>150.0005529448622</v>
       </c>
       <c r="S10" t="n">
-        <v>12.7822833483868</v>
+        <v>9.000316507161397</v>
       </c>
       <c r="T10" t="n">
-        <v>143.8782537730499</v>
+        <v>130.9025858974007</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3415335550990335</v>
+        <v>24.56309354430238</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8220347611119241</v>
+        <v>0.5248895903986686</v>
       </c>
       <c r="W10" t="b">
         <v>1</v>
@@ -1200,64 +1200,64 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>850.8627711339921</v>
+        <v>845.8345604713478</v>
       </c>
       <c r="D11" t="n">
-        <v>7.301350401444483</v>
+        <v>7.121444438263866</v>
       </c>
       <c r="E11" t="n">
-        <v>213.6171334391107</v>
+        <v>187.936628615325</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8791069388389587</v>
+        <v>0.8864884376525879</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001712197670713067</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H11" t="n">
-        <v>918.8490055847537</v>
+        <v>933.0521472444783</v>
       </c>
       <c r="I11" t="n">
-        <v>210.2246188077564</v>
+        <v>187.9366286142111</v>
       </c>
       <c r="J11" t="n">
-        <v>9.000641764210666</v>
+        <v>9.000641774130662</v>
       </c>
       <c r="K11" t="n">
-        <v>67.98623445076169</v>
+        <v>87.21758677313051</v>
       </c>
       <c r="L11" t="n">
-        <v>3.392514631354288</v>
+        <v>1.113903635996394e-09</v>
       </c>
       <c r="M11" t="n">
-        <v>1.699291362766183</v>
+        <v>1.879197335866795</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9576789736747742</v>
+        <v>0.9909976720809937</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0007729309727437794</v>
+        <v>0.0007567066350020468</v>
       </c>
       <c r="Q11" t="n">
-        <v>929.039341052369</v>
+        <v>931.6791869949426</v>
       </c>
       <c r="R11" t="n">
-        <v>211.9593253659875</v>
+        <v>190.0194687992341</v>
       </c>
       <c r="S11" t="n">
-        <v>9.000641545307294</v>
+        <v>9.000641223484863</v>
       </c>
       <c r="T11" t="n">
-        <v>78.17656991837691</v>
+        <v>85.8446265235948</v>
       </c>
       <c r="U11" t="n">
-        <v>1.657808073123192</v>
+        <v>2.08284018390907</v>
       </c>
       <c r="V11" t="n">
-        <v>1.699291143862811</v>
+        <v>1.879196785220996</v>
       </c>
       <c r="W11" t="b">
         <v>1</v>
@@ -1269,68 +1269,68 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>873.9455507441398</v>
+        <v>926.488107887503</v>
       </c>
       <c r="D12" t="n">
-        <v>9.760608195236596</v>
+        <v>2.529784239256371</v>
       </c>
       <c r="E12" t="n">
-        <v>210.7181823014149</v>
+        <v>204.8976295739575</v>
       </c>
       <c r="F12" t="n">
-        <v>0.700507640838623</v>
+        <v>0.8486842513084412</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0009920429438352585</v>
+        <v>0.001007982064038515</v>
       </c>
       <c r="H12" t="n">
-        <v>919.4282410300033</v>
+        <v>926.4881078869265</v>
       </c>
       <c r="I12" t="n">
-        <v>210.7181830589438</v>
+        <v>204.8976295739571</v>
       </c>
       <c r="J12" t="n">
-        <v>9.760608195236605</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K12" t="n">
-        <v>45.48269028586344</v>
+        <v>5.765059540863149e-10</v>
       </c>
       <c r="L12" t="n">
-        <v>7.575289089345461e-07</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="M12" t="n">
-        <v>8.881784197001252e-15</v>
+        <v>6.470857540605791</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0.292863667011261</v>
+        <v>0.9948940277099609</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0004289619973860681</v>
+        <v>7.942881347844377e-05</v>
       </c>
       <c r="Q12" t="n">
-        <v>924.195031144189</v>
+        <v>928.8894039884373</v>
       </c>
       <c r="R12" t="n">
-        <v>210.2009476065454</v>
+        <v>204.8915238950187</v>
       </c>
       <c r="S12" t="n">
-        <v>9.818198186311022</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T12" t="n">
-        <v>50.24948040004915</v>
+        <v>2.401296100934246</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5172346948694724</v>
+        <v>0.006105678938865822</v>
       </c>
       <c r="V12" t="n">
-        <v>0.05758999107442619</v>
+        <v>6.470857540605791</v>
       </c>
       <c r="W12" t="b">
         <v>1</v>
@@ -1342,68 +1342,68 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1009.225673939027</v>
+        <v>952.027795562598</v>
       </c>
       <c r="D13" t="n">
-        <v>11.24199065836542</v>
+        <v>4.656797091604268</v>
       </c>
       <c r="E13" t="n">
-        <v>199.6806142356528</v>
+        <v>186.1754126618551</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5538040995597839</v>
+        <v>0.9024239182472229</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0002065182634396479</v>
+        <v>0.001009692437946796</v>
       </c>
       <c r="H13" t="n">
-        <v>969.8951533578321</v>
+        <v>952.027795562646</v>
       </c>
       <c r="I13" t="n">
-        <v>199.6806142356528</v>
+        <v>186.1754126618561</v>
       </c>
       <c r="J13" t="n">
-        <v>11.24199065836542</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K13" t="n">
-        <v>39.33052058119495</v>
+        <v>4.797584551852196e-11</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>9.379164112033322e-13</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.343844688257894</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2145334333181381</v>
+        <v>0.9948107004165649</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0002808739664033055</v>
+        <v>0.0001839407632360235</v>
       </c>
       <c r="Q13" t="n">
-        <v>967.4213158193367</v>
+        <v>950.1497964422522</v>
       </c>
       <c r="R13" t="n">
-        <v>199.4366567174505</v>
+        <v>186.9397681791904</v>
       </c>
       <c r="S13" t="n">
-        <v>11.20875769210023</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T13" t="n">
-        <v>41.80435811969039</v>
+        <v>1.877999120345862</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2439575182023646</v>
+        <v>0.7643555173353036</v>
       </c>
       <c r="V13" t="n">
-        <v>0.03323296626518868</v>
+        <v>4.343844688257894</v>
       </c>
       <c r="W13" t="b">
         <v>1</v>
@@ -1415,68 +1415,68 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1055.239264964649</v>
+        <v>893.0387236117929</v>
       </c>
       <c r="D14" t="n">
-        <v>10.47260622354199</v>
+        <v>8.073795114468973</v>
       </c>
       <c r="E14" t="n">
-        <v>201.2867700217913</v>
+        <v>215.2269604592039</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5329121947288513</v>
+        <v>0.8512338399887085</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0002065182634396479</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H14" t="n">
-        <v>969.8951533967315</v>
+        <v>933.0453223404814</v>
       </c>
       <c r="I14" t="n">
-        <v>201.2867700217913</v>
+        <v>215.2269604592034</v>
       </c>
       <c r="J14" t="n">
-        <v>10.47260622354199</v>
+        <v>9.00064138932148</v>
       </c>
       <c r="K14" t="n">
-        <v>85.34411156791793</v>
+        <v>40.00659872868857</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>0.9268462748525064</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9983097314834595</v>
+        <v>0.5668800473213196</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0004108299617655575</v>
+        <v>0.0003507932124193758</v>
       </c>
       <c r="Q14" t="n">
-        <v>972.8587109486521</v>
+        <v>934.7396900659435</v>
       </c>
       <c r="R14" t="n">
-        <v>200.4282806604633</v>
+        <v>214.2867320423746</v>
       </c>
       <c r="S14" t="n">
-        <v>10.4479038330142</v>
+        <v>9.000641719708399</v>
       </c>
       <c r="T14" t="n">
-        <v>82.3805540159974</v>
+        <v>41.7009664541506</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8584893613279689</v>
+        <v>0.9402284168292567</v>
       </c>
       <c r="V14" t="n">
-        <v>0.02470239052778389</v>
+        <v>0.926846605239426</v>
       </c>
       <c r="W14" t="b">
         <v>1</v>
@@ -1492,64 +1492,64 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>949.2196096124491</v>
+        <v>920.4477518616111</v>
       </c>
       <c r="D15" t="n">
-        <v>4.056588199894033</v>
+        <v>5.399449507428002</v>
       </c>
       <c r="E15" t="n">
-        <v>205.1094495850843</v>
+        <v>193.8694212945647</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9323320388793945</v>
+        <v>0.7920407652854919</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0005017773364670575</v>
+        <v>0.001006337930448353</v>
       </c>
       <c r="H15" t="n">
-        <v>949.2196096116362</v>
+        <v>920.4477518616443</v>
       </c>
       <c r="I15" t="n">
-        <v>205.1094495850838</v>
+        <v>193.8695360089797</v>
       </c>
       <c r="J15" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="K15" t="n">
-        <v>8.128608897095546e-10</v>
+        <v>3.319655661471188e-11</v>
       </c>
       <c r="L15" t="n">
-        <v>5.115907697472721e-13</v>
+        <v>0.0001147144149911128</v>
       </c>
       <c r="M15" t="n">
-        <v>4.944053579968129</v>
+        <v>3.601192272434161</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9959384202957153</v>
+        <v>0.8327110409736633</v>
       </c>
       <c r="P15" t="n">
-        <v>4.551598976831883e-05</v>
+        <v>0.0001308294740738347</v>
       </c>
       <c r="Q15" t="n">
-        <v>950.5099832745492</v>
+        <v>925.0065121095117</v>
       </c>
       <c r="R15" t="n">
-        <v>204.975883077593</v>
+        <v>194.1850604810351</v>
       </c>
       <c r="S15" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="T15" t="n">
-        <v>1.290373662100137</v>
+        <v>4.558760247900636</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1335665074912242</v>
+        <v>0.3156391864703778</v>
       </c>
       <c r="V15" t="n">
-        <v>4.944053579968129</v>
+        <v>3.601192272434161</v>
       </c>
       <c r="W15" t="b">
         <v>1</v>
@@ -1561,68 +1561,68 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>965.9137404024477</v>
+        <v>873.2174027771838</v>
       </c>
       <c r="D16" t="n">
-        <v>6.797941762263909</v>
+        <v>8.013912992634639</v>
       </c>
       <c r="E16" t="n">
-        <v>196.4419897894029</v>
+        <v>207.6909897806796</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6720576882362366</v>
+        <v>0.9079104661941528</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0005017708754166961</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H16" t="n">
-        <v>965.913740406535</v>
+        <v>933.0453168724518</v>
       </c>
       <c r="I16" t="n">
-        <v>196.4419897894029</v>
+        <v>207.6909897806796</v>
       </c>
       <c r="J16" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641731294142</v>
       </c>
       <c r="K16" t="n">
-        <v>4.08726918976754e-09</v>
+        <v>59.82791409526806</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.202700017598254</v>
+        <v>0.9867287386595027</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1251122653484344</v>
+        <v>0.9426078200340271</v>
       </c>
       <c r="P16" t="n">
-        <v>5.469888128573075e-05</v>
+        <v>0.0004555612686090171</v>
       </c>
       <c r="Q16" t="n">
-        <v>964.9659651083233</v>
+        <v>931.4591806257216</v>
       </c>
       <c r="R16" t="n">
-        <v>196.5647414329569</v>
+        <v>207.3560650221063</v>
       </c>
       <c r="S16" t="n">
-        <v>9.000641779862162</v>
+        <v>9.00064179623668</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9477752941244262</v>
+        <v>58.24177784853782</v>
       </c>
       <c r="U16" t="n">
-        <v>0.122751643554011</v>
+        <v>0.3349247585732655</v>
       </c>
       <c r="V16" t="n">
-        <v>2.202700017598254</v>
+        <v>0.9867288036020412</v>
       </c>
       <c r="W16" t="b">
         <v>1</v>
@@ -1638,64 +1638,64 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>823.6010354296754</v>
+        <v>870.0683359708542</v>
       </c>
       <c r="D17" t="n">
-        <v>8.156698768960831</v>
+        <v>7.967527244884925</v>
       </c>
       <c r="E17" t="n">
-        <v>187.6051836674413</v>
+        <v>218.8704895387035</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6394528746604919</v>
+        <v>0.8978111743927002</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001519713317975402</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H17" t="n">
-        <v>919.4282386951398</v>
+        <v>933.0453231485079</v>
       </c>
       <c r="I17" t="n">
-        <v>187.6051836674413</v>
+        <v>218.8704895387038</v>
       </c>
       <c r="J17" t="n">
-        <v>9.000382145855776</v>
+        <v>9.000641515419224</v>
       </c>
       <c r="K17" t="n">
-        <v>95.82720326546439</v>
+        <v>62.97698717765377</v>
       </c>
       <c r="L17" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>3.126388037344441e-13</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8436833768949441</v>
+        <v>1.033114270534298</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8501085638999939</v>
+        <v>0.9329906702041626</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0009994297288358212</v>
+        <v>0.0005669897072948515</v>
       </c>
       <c r="Q17" t="n">
-        <v>929.2178114924061</v>
+        <v>932.6745823948378</v>
       </c>
       <c r="R17" t="n">
-        <v>188.9226517882464</v>
+        <v>217.1156120884552</v>
       </c>
       <c r="S17" t="n">
-        <v>9.000641693830673</v>
+        <v>9.000641438366646</v>
       </c>
       <c r="T17" t="n">
-        <v>105.6167760627307</v>
+        <v>62.60624642398363</v>
       </c>
       <c r="U17" t="n">
-        <v>1.31746812080516</v>
+        <v>1.754877450248301</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8439429248698413</v>
+        <v>1.033114193481721</v>
       </c>
       <c r="W17" t="b">
         <v>1</v>
@@ -1711,64 +1711,64 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>938.4531596858333</v>
+        <v>928.336231066679</v>
       </c>
       <c r="D18" t="n">
-        <v>14.02077782303913</v>
+        <v>15.080408447795</v>
       </c>
       <c r="E18" t="n">
-        <v>202.7593789159424</v>
+        <v>206.9551153259485</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9039955735206604</v>
+        <v>0.808607816696167</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0002902889100369066</v>
+        <v>0.0006024915492162108</v>
       </c>
       <c r="H18" t="n">
-        <v>933.1538668597773</v>
+        <v>928.3360848535272</v>
       </c>
       <c r="I18" t="n">
-        <v>202.8114669493673</v>
+        <v>206.955115325948</v>
       </c>
       <c r="J18" t="n">
-        <v>11.82162592400131</v>
+        <v>11.82181869723987</v>
       </c>
       <c r="K18" t="n">
-        <v>5.299292826055989</v>
+        <v>0.0001462131518792376</v>
       </c>
       <c r="L18" t="n">
-        <v>0.05208803342497959</v>
+        <v>5.684341886080801e-13</v>
       </c>
       <c r="M18" t="n">
-        <v>2.199151899037819</v>
+        <v>3.258589750555128</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9017627239227295</v>
+        <v>0.992428719997406</v>
       </c>
       <c r="P18" t="n">
-        <v>0.001597243011929095</v>
+        <v>0.003744108136743307</v>
       </c>
       <c r="Q18" t="n">
-        <v>806.469808496011</v>
+        <v>800.0002067412524</v>
       </c>
       <c r="R18" t="n">
-        <v>199.6358147095653</v>
+        <v>209.4596136620074</v>
       </c>
       <c r="S18" t="n">
-        <v>13.18033760210351</v>
+        <v>13.82712360716748</v>
       </c>
       <c r="T18" t="n">
-        <v>131.9833511898223</v>
+        <v>128.3360243254266</v>
       </c>
       <c r="U18" t="n">
-        <v>3.123564206377068</v>
+        <v>2.504498336058873</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8404402209356245</v>
+        <v>1.25328484062752</v>
       </c>
       <c r="W18" t="b">
         <v>1</v>
@@ -1780,68 +1780,68 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>994.1156538949632</v>
+        <v>911.7671889869648</v>
       </c>
       <c r="D19" t="n">
-        <v>5.130632828330791</v>
+        <v>14.35672491529613</v>
       </c>
       <c r="E19" t="n">
-        <v>204.8091508976131</v>
+        <v>209.1110804489853</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9241881370544434</v>
+        <v>0.8073925971984863</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0005015467177145183</v>
+        <v>0.0006009557982906699</v>
       </c>
       <c r="H19" t="n">
-        <v>993.9623661134164</v>
+        <v>911.7671889876393</v>
       </c>
       <c r="I19" t="n">
-        <v>204.8090361473304</v>
+        <v>209.1110188661193</v>
       </c>
       <c r="J19" t="n">
-        <v>9.000641779862162</v>
+        <v>11.8218186837652</v>
       </c>
       <c r="K19" t="n">
-        <v>0.153287781546851</v>
+        <v>6.745040082023479e-10</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0001147502826768232</v>
+        <v>6.158286595336904e-05</v>
       </c>
       <c r="M19" t="n">
-        <v>3.870008951531371</v>
+        <v>2.534906231530936</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8989121913909912</v>
+        <v>0.9235931038856506</v>
       </c>
       <c r="P19" t="n">
-        <v>4.492159860092215e-05</v>
+        <v>0.002666007960215211</v>
       </c>
       <c r="Q19" t="n">
-        <v>994.2866780926453</v>
+        <v>800.8990815772046</v>
       </c>
       <c r="R19" t="n">
-        <v>204.904651792149</v>
+        <v>210.7943469705368</v>
       </c>
       <c r="S19" t="n">
-        <v>9.000641779862162</v>
+        <v>13.5760774326327</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1710241976820726</v>
+        <v>110.8681074097602</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09550089453597366</v>
+        <v>1.683266521551559</v>
       </c>
       <c r="V19" t="n">
-        <v>3.870008951531371</v>
+        <v>0.7806474826634329</v>
       </c>
       <c r="W19" t="b">
         <v>1</v>
@@ -1853,68 +1853,68 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>956.7552063987063</v>
+        <v>872.3088207217586</v>
       </c>
       <c r="D20" t="n">
-        <v>6.091078583278835</v>
+        <v>5.997991866309297</v>
       </c>
       <c r="E20" t="n">
-        <v>182.764004648775</v>
+        <v>194.5602717348846</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9294523596763611</v>
+        <v>0.9218559265136719</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0005016286741010845</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H20" t="n">
-        <v>956.7552063983394</v>
+        <v>933.0453188157161</v>
       </c>
       <c r="I20" t="n">
-        <v>182.7640046487469</v>
+        <v>194.5602717348846</v>
       </c>
       <c r="J20" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641460635768</v>
       </c>
       <c r="K20" t="n">
-        <v>3.668674253276549e-10</v>
+        <v>60.73649809395749</v>
       </c>
       <c r="L20" t="n">
-        <v>2.810907062666956e-11</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M20" t="n">
-        <v>2.909563196583328</v>
+        <v>3.002649594326471</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7503392696380615</v>
+        <v>0.983623206615448</v>
       </c>
       <c r="P20" t="n">
-        <v>0.0001778428995748982</v>
+        <v>0.0004763400938827544</v>
       </c>
       <c r="Q20" t="n">
-        <v>958.1412743882329</v>
+        <v>932.3340483433182</v>
       </c>
       <c r="R20" t="n">
-        <v>183.3722727235086</v>
+        <v>195.4742354627464</v>
       </c>
       <c r="S20" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641710559979</v>
       </c>
       <c r="T20" t="n">
-        <v>1.386067989526623</v>
+        <v>60.02522762155957</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6082680747336155</v>
+        <v>0.913963727861784</v>
       </c>
       <c r="V20" t="n">
-        <v>2.909563196583328</v>
+        <v>3.002649844250682</v>
       </c>
       <c r="W20" t="b">
         <v>1</v>
@@ -1926,68 +1926,68 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>920.4477518616111</v>
+        <v>862.4995334483451</v>
       </c>
       <c r="D21" t="n">
-        <v>5.399449507428002</v>
+        <v>9.063402892415709</v>
       </c>
       <c r="E21" t="n">
-        <v>193.8694212945647</v>
+        <v>198.8624436728534</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8345319032669067</v>
+        <v>0.6929391622543335</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0005017755320295691</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H21" t="n">
-        <v>935.6639036487664</v>
+        <v>933.045314793127</v>
       </c>
       <c r="I21" t="n">
-        <v>193.8694212945647</v>
+        <v>198.8624436728534</v>
       </c>
       <c r="J21" t="n">
-        <v>9.000641779862162</v>
+        <v>9.063484785375332</v>
       </c>
       <c r="K21" t="n">
-        <v>15.21615178715535</v>
+        <v>70.54578134478186</v>
       </c>
       <c r="L21" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.601192272434161</v>
+        <v>8.18929596224649e-05</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6869150400161743</v>
+        <v>0.8879396915435791</v>
       </c>
       <c r="P21" t="n">
-        <v>8.305979281431064e-05</v>
+        <v>0.0005059161339886487</v>
       </c>
       <c r="Q21" t="n">
-        <v>921.9938324262904</v>
+        <v>929.3283213572553</v>
       </c>
       <c r="R21" t="n">
-        <v>194.0030687154665</v>
+        <v>199.4055310231324</v>
       </c>
       <c r="S21" t="n">
-        <v>9.000641779862162</v>
+        <v>9.146813060403945</v>
       </c>
       <c r="T21" t="n">
-        <v>1.546080564679301</v>
+        <v>66.82878790891016</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1336474209018093</v>
+        <v>0.5430873502789382</v>
       </c>
       <c r="V21" t="n">
-        <v>3.601192272434161</v>
+        <v>0.08341016798823553</v>
       </c>
       <c r="W21" t="b">
         <v>1</v>
@@ -1999,68 +1999,68 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1008.545401849467</v>
+        <v>833.9053299675722</v>
       </c>
       <c r="D22" t="n">
-        <v>8.387579334556282</v>
+        <v>6.739674607954534</v>
       </c>
       <c r="E22" t="n">
-        <v>194.8371481599837</v>
+        <v>211.5352295757988</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6021395921707153</v>
+        <v>0.9285228848457336</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0003897787537425756</v>
+        <v>0.003427958348765969</v>
       </c>
       <c r="H22" t="n">
-        <v>986.6826889296826</v>
+        <v>919.4284671926684</v>
       </c>
       <c r="I22" t="n">
-        <v>194.8371481599838</v>
+        <v>211.5352295758159</v>
       </c>
       <c r="J22" t="n">
-        <v>9.000641725090741</v>
+        <v>9.00064149937015</v>
       </c>
       <c r="K22" t="n">
-        <v>21.86271291978392</v>
+        <v>85.52313722509621</v>
       </c>
       <c r="L22" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>1.710986907710321e-11</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6130623905344592</v>
+        <v>2.260966891415617</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1814334839582443</v>
+        <v>0.9919396042823792</v>
       </c>
       <c r="P22" t="n">
-        <v>0.0001901875220937654</v>
+        <v>0.0008126465254463255</v>
       </c>
       <c r="Q22" t="n">
-        <v>970.8512799528562</v>
+        <v>928.449079809769</v>
       </c>
       <c r="R22" t="n">
-        <v>195.0313830168044</v>
+        <v>210.5350275243712</v>
       </c>
       <c r="S22" t="n">
-        <v>9.000641929974737</v>
+        <v>9.000641794504519</v>
       </c>
       <c r="T22" t="n">
-        <v>37.69412189661034</v>
+        <v>94.5437498421968</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1942348568207422</v>
+        <v>1.000202051427635</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6130625954184552</v>
+        <v>2.260967186549985</v>
       </c>
       <c r="W22" t="b">
         <v>1</v>
@@ -2072,68 +2072,68 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>890.5470318060303</v>
+        <v>919.4196995117043</v>
       </c>
       <c r="D23" t="n">
-        <v>7.512650723820679</v>
+        <v>4.403121322198782</v>
       </c>
       <c r="E23" t="n">
-        <v>215.574397047935</v>
+        <v>191.226696989756</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8756701946258545</v>
+        <v>0.805339515209198</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0008488548919558525</v>
+        <v>0.001005758997052908</v>
       </c>
       <c r="H23" t="n">
-        <v>935.6635585384556</v>
+        <v>919.419699510728</v>
       </c>
       <c r="I23" t="n">
-        <v>215.5743970479351</v>
+        <v>191.2266667868728</v>
       </c>
       <c r="J23" t="n">
-        <v>9.000641616426195</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K23" t="n">
-        <v>45.11652673242531</v>
+        <v>9.762288755155168e-10</v>
       </c>
       <c r="L23" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>3.020288323796194e-05</v>
       </c>
       <c r="M23" t="n">
-        <v>1.487990892605517</v>
+        <v>4.59752045766338</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7318476438522339</v>
+        <v>0.9488726258277893</v>
       </c>
       <c r="P23" t="n">
-        <v>0.0003999538312200457</v>
+        <v>0.000158387643750757</v>
       </c>
       <c r="Q23" t="n">
-        <v>934.6730939272626</v>
+        <v>924.6552355079745</v>
       </c>
       <c r="R23" t="n">
-        <v>214.6975377911914</v>
+        <v>191.6740524889995</v>
       </c>
       <c r="S23" t="n">
-        <v>9.000641611676619</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T23" t="n">
-        <v>44.12606212123228</v>
+        <v>5.235535996270187</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8768592567436144</v>
+        <v>0.4473554992435425</v>
       </c>
       <c r="V23" t="n">
-        <v>1.48799088785594</v>
+        <v>4.59752045766338</v>
       </c>
       <c r="W23" t="b">
         <v>1</v>
@@ -2149,64 +2149,64 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>933.5632513407731</v>
+        <v>952.2244666968172</v>
       </c>
       <c r="D24" t="n">
-        <v>9.495609619023877</v>
+        <v>9.374842474547272</v>
       </c>
       <c r="E24" t="n">
-        <v>148.5271119319719</v>
+        <v>143.7893713723858</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9296471476554871</v>
+        <v>0.9065526127815247</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0004814165877178311</v>
+        <v>0.001030103303492069</v>
       </c>
       <c r="H24" t="n">
-        <v>933.5632530583321</v>
+        <v>952.2237433096756</v>
       </c>
       <c r="I24" t="n">
-        <v>176.1296284718941</v>
+        <v>176.1300422857316</v>
       </c>
       <c r="J24" t="n">
-        <v>9.495609622360865</v>
+        <v>9.374850103793611</v>
       </c>
       <c r="K24" t="n">
-        <v>1.717558916425332e-06</v>
+        <v>0.0007233871416474358</v>
       </c>
       <c r="L24" t="n">
-        <v>27.60251653992225</v>
+        <v>32.3406709133458</v>
       </c>
       <c r="M24" t="n">
-        <v>3.336987575153216e-09</v>
+        <v>7.629246338680673e-06</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9997897744178772</v>
+        <v>0.9995040893554688</v>
       </c>
       <c r="P24" t="n">
-        <v>0.001465250737965107</v>
+        <v>0.003259731689468026</v>
       </c>
       <c r="Q24" t="n">
-        <v>800.0002581692682</v>
+        <v>800.0005237085558</v>
       </c>
       <c r="R24" t="n">
-        <v>158.9344481770417</v>
+        <v>154.8642565598411</v>
       </c>
       <c r="S24" t="n">
-        <v>9.35127402927262</v>
+        <v>9.068700901537206</v>
       </c>
       <c r="T24" t="n">
-        <v>133.5629931715049</v>
+        <v>152.2239429882615</v>
       </c>
       <c r="U24" t="n">
-        <v>10.40733624506979</v>
+        <v>11.07488518745524</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1443355897512575</v>
+        <v>0.3061415730100663</v>
       </c>
       <c r="W24" t="b">
         <v>1</v>
@@ -2218,68 +2218,68 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>879.8503448575644</v>
+        <v>956.2277987539286</v>
       </c>
       <c r="D25" t="n">
-        <v>7.981785480275626</v>
+        <v>4.811217842338543</v>
       </c>
       <c r="E25" t="n">
-        <v>204.6400688540783</v>
+        <v>194.0256945301476</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9106591939926147</v>
+        <v>0.9024178981781006</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0009904649341478944</v>
+        <v>0.001009689178317785</v>
       </c>
       <c r="H25" t="n">
-        <v>933.0453147958009</v>
+        <v>956.2278164579523</v>
       </c>
       <c r="I25" t="n">
-        <v>204.6400688540841</v>
+        <v>194.0256945301476</v>
       </c>
       <c r="J25" t="n">
-        <v>9.000641773373468</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K25" t="n">
-        <v>53.19496993823645</v>
+        <v>1.770402366219059e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>5.854872142663226e-12</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M25" t="n">
-        <v>1.018856293097842</v>
+        <v>4.189423937523619</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0.7956917881965637</v>
+        <v>0.9954556226730347</v>
       </c>
       <c r="P25" t="n">
-        <v>0.0004527805431280285</v>
+        <v>9.789256000658497e-05</v>
       </c>
       <c r="Q25" t="n">
-        <v>932.1693009318664</v>
+        <v>954.0561715566727</v>
       </c>
       <c r="R25" t="n">
-        <v>204.7523039490771</v>
+        <v>194.2776007423727</v>
       </c>
       <c r="S25" t="n">
-        <v>9.000641755189859</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T25" t="n">
-        <v>52.31895607430192</v>
+        <v>2.17162719725593</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1122350949988515</v>
+        <v>0.2519062122250375</v>
       </c>
       <c r="V25" t="n">
-        <v>1.018856274914233</v>
+        <v>4.189423937523619</v>
       </c>
       <c r="W25" t="b">
         <v>1</v>
@@ -2295,64 +2295,64 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>959.6756321662</v>
+        <v>953.8523829517387</v>
       </c>
       <c r="D26" t="n">
-        <v>5.831329231494768</v>
+        <v>5.686118461029691</v>
       </c>
       <c r="E26" t="n">
-        <v>194.6804051385997</v>
+        <v>197.2173923656629</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9300639033317566</v>
+        <v>0.8952300548553467</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0005017708754166961</v>
+        <v>0.001009692437946796</v>
       </c>
       <c r="H26" t="n">
-        <v>959.6756313174292</v>
+        <v>953.8523829517435</v>
       </c>
       <c r="I26" t="n">
-        <v>194.6804051385997</v>
+        <v>197.2173923656629</v>
       </c>
       <c r="J26" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="K26" t="n">
-        <v>8.487708100801683e-07</v>
+        <v>4.774847184307873e-12</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M26" t="n">
-        <v>3.169312548367394</v>
+        <v>3.314523318832471</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7936587333679199</v>
+        <v>0.9684089422225952</v>
       </c>
       <c r="P26" t="n">
-        <v>5.530041744350456e-05</v>
+        <v>7.875309529481456e-05</v>
       </c>
       <c r="Q26" t="n">
-        <v>958.6961054480799</v>
+        <v>952.2779037561498</v>
       </c>
       <c r="R26" t="n">
-        <v>194.8446104328014</v>
+        <v>197.359555974358</v>
       </c>
       <c r="S26" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9795267181200416</v>
+        <v>1.574479195588879</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1642052942017642</v>
+        <v>0.1421636086951423</v>
       </c>
       <c r="V26" t="n">
-        <v>3.169312548367394</v>
+        <v>3.314523318832471</v>
       </c>
       <c r="W26" t="b">
         <v>1</v>
@@ -2368,64 +2368,64 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>840.864426422445</v>
+        <v>890.1597844686212</v>
       </c>
       <c r="D27" t="n">
-        <v>7.2688151502831</v>
+        <v>6.759569324867613</v>
       </c>
       <c r="E27" t="n">
-        <v>214.1732560514905</v>
+        <v>199.571267049108</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8751335740089417</v>
+        <v>0.8561516404151917</v>
       </c>
       <c r="G27" t="n">
-        <v>0.001493598334491253</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H27" t="n">
-        <v>918.8325210985497</v>
+        <v>933.0453194073473</v>
       </c>
       <c r="I27" t="n">
-        <v>217.7669380872254</v>
+        <v>199.571267049108</v>
       </c>
       <c r="J27" t="n">
-        <v>9.000641759092115</v>
+        <v>9.000641455569848</v>
       </c>
       <c r="K27" t="n">
-        <v>77.96809467610467</v>
+        <v>42.8855349387261</v>
       </c>
       <c r="L27" t="n">
-        <v>3.593682035734986</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.731826608809016</v>
+        <v>2.241072130702236</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>0.9579663872718811</v>
+        <v>0.9055102467536926</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0008848594152368605</v>
+        <v>0.0003290710155852139</v>
       </c>
       <c r="Q27" t="n">
-        <v>928.1776765612262</v>
+        <v>933.5256557902768</v>
       </c>
       <c r="R27" t="n">
-        <v>212.2699504876935</v>
+        <v>199.8990573379143</v>
       </c>
       <c r="S27" t="n">
-        <v>9.000641338496399</v>
+        <v>9.000641688101206</v>
       </c>
       <c r="T27" t="n">
-        <v>87.3132501387812</v>
+        <v>43.36587132165562</v>
       </c>
       <c r="U27" t="n">
-        <v>1.903305563796977</v>
+        <v>0.3277902888062556</v>
       </c>
       <c r="V27" t="n">
-        <v>1.731826188213299</v>
+        <v>2.241072363233593</v>
       </c>
       <c r="W27" t="b">
         <v>1</v>
@@ -2441,64 +2441,64 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>911.3617056587202</v>
+        <v>931.4457141543127</v>
       </c>
       <c r="D28" t="n">
-        <v>5.844386886400764</v>
+        <v>5.966615046177687</v>
       </c>
       <c r="E28" t="n">
-        <v>201.7404262696538</v>
+        <v>195.8168760577822</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6870334148406982</v>
+        <v>0.8818866610527039</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0006761035765521228</v>
+        <v>0.001008538878522813</v>
       </c>
       <c r="H28" t="n">
-        <v>918.8325209898146</v>
+        <v>931.4457141549879</v>
       </c>
       <c r="I28" t="n">
-        <v>201.740426269635</v>
+        <v>195.8168760577822</v>
       </c>
       <c r="J28" t="n">
-        <v>9.000641741814141</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K28" t="n">
-        <v>7.4708153310944</v>
+        <v>6.751861292286776e-10</v>
       </c>
       <c r="L28" t="n">
-        <v>1.881517164292745e-11</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.156254855413377</v>
+        <v>3.034026733684476</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>0.1848437339067459</v>
+        <v>0.8182072639465332</v>
       </c>
       <c r="P28" t="n">
-        <v>0.0001026247991831042</v>
+        <v>8.831613376969472e-05</v>
       </c>
       <c r="Q28" t="n">
-        <v>913.4711181325252</v>
+        <v>933.3959975134389</v>
       </c>
       <c r="R28" t="n">
-        <v>201.5742021385845</v>
+        <v>196.0145772467511</v>
       </c>
       <c r="S28" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="T28" t="n">
-        <v>2.109412473805037</v>
+        <v>1.950283359126274</v>
       </c>
       <c r="U28" t="n">
-        <v>0.1662241310693275</v>
+        <v>0.1977011889689493</v>
       </c>
       <c r="V28" t="n">
-        <v>3.156254893461399</v>
+        <v>3.034026733684476</v>
       </c>
       <c r="W28" t="b">
         <v>1</v>
@@ -2510,68 +2510,68 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>915.1328945729765</v>
+        <v>876.039542019205</v>
       </c>
       <c r="D29" t="n">
-        <v>6.059991622037932</v>
+        <v>7.762170518968503</v>
       </c>
       <c r="E29" t="n">
-        <v>210.4936769056666</v>
+        <v>199.3835674526191</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5132704377174377</v>
+        <v>0.8770247101783752</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0006742415716871619</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H29" t="n">
-        <v>918.8325212429251</v>
+        <v>933.0453165345622</v>
       </c>
       <c r="I29" t="n">
-        <v>210.4936544229514</v>
+        <v>199.3835674526191</v>
       </c>
       <c r="J29" t="n">
-        <v>9.000641665751749</v>
+        <v>9.000641444380859</v>
       </c>
       <c r="K29" t="n">
-        <v>3.699626669948543</v>
+        <v>57.00577451535719</v>
       </c>
       <c r="L29" t="n">
-        <v>2.248271522375944e-05</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.940650043713816</v>
+        <v>1.238470925412356</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0.1295967251062393</v>
+        <v>0.9504122138023376</v>
       </c>
       <c r="P29" t="n">
-        <v>0.00010634635691531</v>
+        <v>0.0004275877145119011</v>
       </c>
       <c r="Q29" t="n">
-        <v>918.3621231351999</v>
+        <v>931.9960616942669</v>
       </c>
       <c r="R29" t="n">
-        <v>210.4376500123542</v>
+        <v>199.8138056945083</v>
       </c>
       <c r="S29" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641713001917</v>
       </c>
       <c r="T29" t="n">
-        <v>3.229228562223398</v>
+        <v>55.95651967506194</v>
       </c>
       <c r="U29" t="n">
-        <v>0.05602689331243482</v>
+        <v>0.4302382418892137</v>
       </c>
       <c r="V29" t="n">
-        <v>2.94065015782423</v>
+        <v>1.238471194033414</v>
       </c>
       <c r="W29" t="b">
         <v>1</v>
@@ -2583,68 +2583,68 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>963.176555542808</v>
+        <v>943.9422951240201</v>
       </c>
       <c r="D30" t="n">
-        <v>4.610213383201334</v>
+        <v>10.70997486905503</v>
       </c>
       <c r="E30" t="n">
-        <v>216.9138812036659</v>
+        <v>151.5073318488736</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9196237921714783</v>
+        <v>0.9065549969673157</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0005017708754166961</v>
+        <v>0.001030104584060609</v>
       </c>
       <c r="H30" t="n">
-        <v>963.1765985496064</v>
+        <v>943.9423829455822</v>
       </c>
       <c r="I30" t="n">
-        <v>216.9138812036652</v>
+        <v>176.1300256938736</v>
       </c>
       <c r="J30" t="n">
-        <v>9.000641779862162</v>
+        <v>10.70997659428209</v>
       </c>
       <c r="K30" t="n">
-        <v>4.300679836433119e-05</v>
+        <v>8.782156203324121e-05</v>
       </c>
       <c r="L30" t="n">
-        <v>6.821210263296962e-13</v>
+        <v>24.62269384500007</v>
       </c>
       <c r="M30" t="n">
-        <v>4.390428396660829</v>
+        <v>1.725227058102519e-06</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>0.9579758048057556</v>
+        <v>0.9918924570083618</v>
       </c>
       <c r="P30" t="n">
-        <v>6.45573454676196e-05</v>
+        <v>0.003159148385748267</v>
       </c>
       <c r="Q30" t="n">
-        <v>964.9659656111527</v>
+        <v>801.2810062706731</v>
       </c>
       <c r="R30" t="n">
-        <v>216.6780625403437</v>
+        <v>163.3468738567666</v>
       </c>
       <c r="S30" t="n">
-        <v>9.000641779862162</v>
+        <v>10.40957077238443</v>
       </c>
       <c r="T30" t="n">
-        <v>1.789410068344637</v>
+        <v>142.6612888533471</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2358186633221919</v>
+        <v>11.83954200789299</v>
       </c>
       <c r="V30" t="n">
-        <v>4.390428396660829</v>
+        <v>0.3004040966706061</v>
       </c>
       <c r="W30" t="b">
         <v>1</v>
@@ -2656,68 +2656,68 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>928.2851535806614</v>
+        <v>892.491731029129</v>
       </c>
       <c r="D31" t="n">
-        <v>5.653746606050514</v>
+        <v>7.810111168776988</v>
       </c>
       <c r="E31" t="n">
-        <v>204.0727182995776</v>
+        <v>200.1966656998361</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7720369696617126</v>
+        <v>0.8543873429298401</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0005017755320295691</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H31" t="n">
-        <v>935.66365058833</v>
+        <v>933.0453213537381</v>
       </c>
       <c r="I31" t="n">
-        <v>204.0727182995776</v>
+        <v>200.1966656998361</v>
       </c>
       <c r="J31" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641440969263</v>
       </c>
       <c r="K31" t="n">
-        <v>7.37849700766867</v>
+        <v>40.5535903246091</v>
       </c>
       <c r="L31" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.346895173811649</v>
+        <v>1.190530272192275</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0.6143945455551147</v>
+        <v>0.7319111824035645</v>
       </c>
       <c r="P31" t="n">
-        <v>6.935622513992712e-05</v>
+        <v>0.0003101793117821217</v>
       </c>
       <c r="Q31" t="n">
-        <v>929.6297667727787</v>
+        <v>933.7979632503138</v>
       </c>
       <c r="R31" t="n">
-        <v>203.9832749384079</v>
+        <v>200.4673134555944</v>
       </c>
       <c r="S31" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641802103901</v>
       </c>
       <c r="T31" t="n">
-        <v>1.344613192117322</v>
+        <v>41.30623222118481</v>
       </c>
       <c r="U31" t="n">
-        <v>0.08944336116968543</v>
+        <v>0.2706477557583185</v>
       </c>
       <c r="V31" t="n">
-        <v>3.346895173811649</v>
+        <v>1.190530633326913</v>
       </c>
       <c r="W31" t="b">
         <v>1</v>
@@ -2729,68 +2729,68 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>941.0057360916854</v>
+        <v>929.2378602707793</v>
       </c>
       <c r="D32" t="n">
-        <v>16.20970598452344</v>
+        <v>10.46531685190464</v>
       </c>
       <c r="E32" t="n">
-        <v>200.3765036916771</v>
+        <v>126.3945203148254</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8926043510437012</v>
+        <v>0.906248927116394</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0002902889100369066</v>
+        <v>0.3009131848812103</v>
       </c>
       <c r="H32" t="n">
-        <v>941.0057263688439</v>
+        <v>889.923146978501</v>
       </c>
       <c r="I32" t="n">
-        <v>200.3765036916771</v>
+        <v>154.9673492026013</v>
       </c>
       <c r="J32" t="n">
-        <v>11.82181865973818</v>
+        <v>13.49511335001083</v>
       </c>
       <c r="K32" t="n">
-        <v>9.722841582515684e-06</v>
+        <v>39.31471329227827</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>28.57282888777593</v>
       </c>
       <c r="M32" t="n">
-        <v>4.387887324785257</v>
+        <v>3.029796498106192</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>0.9998775720596313</v>
+        <v>0.9999374151229858</v>
       </c>
       <c r="P32" t="n">
-        <v>0.003183335298672318</v>
+        <v>0.009384246543049812</v>
       </c>
       <c r="Q32" t="n">
-        <v>800.0000871831492</v>
+        <v>800.0000080722131</v>
       </c>
       <c r="R32" t="n">
-        <v>192.4862910914212</v>
+        <v>150.744039781876</v>
       </c>
       <c r="S32" t="n">
-        <v>13.82570568898254</v>
+        <v>9.42738008829091</v>
       </c>
       <c r="T32" t="n">
-        <v>141.0056489085363</v>
+        <v>129.2378521985662</v>
       </c>
       <c r="U32" t="n">
-        <v>7.890212600255921</v>
+        <v>24.34951946705064</v>
       </c>
       <c r="V32" t="n">
-        <v>2.384000295540897</v>
+        <v>1.037936763613731</v>
       </c>
       <c r="W32" t="b">
         <v>1</v>
@@ -2802,68 +2802,68 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>930.7536861441955</v>
+        <v>896.3065469305708</v>
       </c>
       <c r="D33" t="n">
-        <v>8.927977431822347</v>
+        <v>8.139929682304544</v>
       </c>
       <c r="E33" t="n">
-        <v>122.6107519328073</v>
+        <v>189.2080860494468</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9230289459228516</v>
+        <v>0.6450386643409729</v>
       </c>
       <c r="G33" t="n">
-        <v>0.006477588787674904</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H33" t="n">
-        <v>902.6500424418728</v>
+        <v>933.0453172379919</v>
       </c>
       <c r="I33" t="n">
-        <v>173.6141399233477</v>
+        <v>189.2080860494468</v>
       </c>
       <c r="J33" t="n">
-        <v>9.532468987427524</v>
+        <v>9.000641646512664</v>
       </c>
       <c r="K33" t="n">
-        <v>28.10364370232276</v>
+        <v>36.73877030742108</v>
       </c>
       <c r="L33" t="n">
-        <v>51.00338799054042</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.6044915556051773</v>
+        <v>0.8607119642081198</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>1</v>
+        <v>0.4835691750049591</v>
       </c>
       <c r="P33" t="n">
-        <v>0.006292601116001606</v>
+        <v>0.0003324900171719491</v>
       </c>
       <c r="Q33" t="n">
-        <v>800.000031837548</v>
+        <v>936.833944083687</v>
       </c>
       <c r="R33" t="n">
-        <v>153.1194834201628</v>
+        <v>190.2503562287347</v>
       </c>
       <c r="S33" t="n">
-        <v>9.000642159913577</v>
+        <v>9.000641406274427</v>
       </c>
       <c r="T33" t="n">
-        <v>130.7536543066475</v>
+        <v>40.52739715311623</v>
       </c>
       <c r="U33" t="n">
-        <v>30.50873148735555</v>
+        <v>1.042270179287897</v>
       </c>
       <c r="V33" t="n">
-        <v>0.07266472809122959</v>
+        <v>0.8607117239698834</v>
       </c>
       <c r="W33" t="b">
         <v>1</v>
@@ -2875,68 +2875,68 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1012.064025522282</v>
+        <v>915.1328945729765</v>
       </c>
       <c r="D34" t="n">
-        <v>10.21826323818112</v>
+        <v>6.059991622037932</v>
       </c>
       <c r="E34" t="n">
-        <v>186.3622748836766</v>
+        <v>210.4936769056666</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5391393303871155</v>
+        <v>0.6736760139465332</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0003771110787056386</v>
+        <v>0.000984171056188643</v>
       </c>
       <c r="H34" t="n">
-        <v>986.6826880845888</v>
+        <v>915.1328945729775</v>
       </c>
       <c r="I34" t="n">
-        <v>186.3622748836766</v>
+        <v>210.4936200339029</v>
       </c>
       <c r="J34" t="n">
-        <v>10.21826323818112</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K34" t="n">
-        <v>25.38133743769311</v>
+        <v>1.023181539494544e-12</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>5.687176368951441e-05</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>2.94065015782423</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0.2783395648002625</v>
+        <v>0.4378473460674286</v>
       </c>
       <c r="P34" t="n">
-        <v>0.000243284142925404</v>
+        <v>0.000124749043607153</v>
       </c>
       <c r="Q34" t="n">
-        <v>969.6457482330858</v>
+        <v>920.0335508665838</v>
       </c>
       <c r="R34" t="n">
-        <v>186.9235872563537</v>
+        <v>210.3537102698414</v>
       </c>
       <c r="S34" t="n">
-        <v>10.21285885123135</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T34" t="n">
-        <v>42.41827728919611</v>
+        <v>4.900656293607312</v>
       </c>
       <c r="U34" t="n">
-        <v>0.5613123726770652</v>
+        <v>0.1399666358252603</v>
       </c>
       <c r="V34" t="n">
-        <v>0.005404386949775741</v>
+        <v>2.94065015782423</v>
       </c>
       <c r="W34" t="b">
         <v>1</v>
@@ -2948,68 +2948,68 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>935.6117250099762</v>
+        <v>859.049721060047</v>
       </c>
       <c r="D35" t="n">
-        <v>6.976582088864133</v>
+        <v>9.20155298729558</v>
       </c>
       <c r="E35" t="n">
-        <v>196.9071804633607</v>
+        <v>189.0584905356224</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5775360465049744</v>
+        <v>0.6800032258033752</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0005017755320295691</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H35" t="n">
-        <v>935.6635829324442</v>
+        <v>933.0453175131333</v>
       </c>
       <c r="I35" t="n">
-        <v>196.9071804633607</v>
+        <v>189.0584905356224</v>
       </c>
       <c r="J35" t="n">
-        <v>9.000641779862162</v>
+        <v>9.201547175138938</v>
       </c>
       <c r="K35" t="n">
-        <v>0.05185792246800247</v>
+        <v>73.99559645308636</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.024059690998029</v>
+        <v>5.812156642193145e-06</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>0.05048427730798721</v>
+        <v>0.8762199878692627</v>
       </c>
       <c r="P35" t="n">
-        <v>5.384787073126063e-05</v>
+        <v>0.0005770547431893647</v>
       </c>
       <c r="Q35" t="n">
-        <v>936.7085765330972</v>
+        <v>929.5407158013484</v>
       </c>
       <c r="R35" t="n">
-        <v>197.0358711118342</v>
+        <v>190.6089707428995</v>
       </c>
       <c r="S35" t="n">
-        <v>9.000641779862162</v>
+        <v>9.291360846420563</v>
       </c>
       <c r="T35" t="n">
-        <v>1.096851523121018</v>
+        <v>70.49099474130139</v>
       </c>
       <c r="U35" t="n">
-        <v>0.1286906484735084</v>
+        <v>1.550480207277076</v>
       </c>
       <c r="V35" t="n">
-        <v>2.024059690998029</v>
+        <v>0.08980785912498312</v>
       </c>
       <c r="W35" t="b">
         <v>1</v>
@@ -3021,68 +3021,68 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>855.8055457652536</v>
+        <v>952.2225875059303</v>
       </c>
       <c r="D36" t="n">
-        <v>8.089133363160869</v>
+        <v>8.982060962729719</v>
       </c>
       <c r="E36" t="n">
-        <v>208.8341411339296</v>
+        <v>134.8889820198774</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9102580547332764</v>
+        <v>0.9065995812416077</v>
       </c>
       <c r="G36" t="n">
-        <v>0.001780243474058807</v>
+        <v>0.001030128798447549</v>
       </c>
       <c r="H36" t="n">
-        <v>919.4282405781895</v>
+        <v>952.2484980377182</v>
       </c>
       <c r="I36" t="n">
-        <v>208.83414113393</v>
+        <v>176.1328449451751</v>
       </c>
       <c r="J36" t="n">
-        <v>9.000427732128925</v>
+        <v>9.000377581460532</v>
       </c>
       <c r="K36" t="n">
-        <v>63.62269481293595</v>
+        <v>0.02591053178787206</v>
       </c>
       <c r="L36" t="n">
-        <v>3.410605131648481e-13</v>
+        <v>41.24386292529766</v>
       </c>
       <c r="M36" t="n">
-        <v>0.9112943689680559</v>
+        <v>0.01831661873081281</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>0.856378972530365</v>
+        <v>0.9998905658721924</v>
       </c>
       <c r="P36" t="n">
-        <v>0.0007010294357314706</v>
+        <v>0.005409229081124067</v>
       </c>
       <c r="Q36" t="n">
-        <v>929.3381058370564</v>
+        <v>800.0000415835403</v>
       </c>
       <c r="R36" t="n">
-        <v>208.5485245747717</v>
+        <v>151.3825738093049</v>
       </c>
       <c r="S36" t="n">
-        <v>9.000641717217011</v>
+        <v>9.000642091291407</v>
       </c>
       <c r="T36" t="n">
-        <v>73.53256007180289</v>
+        <v>152.2225459223899</v>
       </c>
       <c r="U36" t="n">
-        <v>0.2856165591578872</v>
+        <v>16.49359178942751</v>
       </c>
       <c r="V36" t="n">
-        <v>0.9115083540561422</v>
+        <v>0.01858112856168859</v>
       </c>
       <c r="W36" t="b">
         <v>1</v>
@@ -3094,68 +3094,68 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>878.9000351868293</v>
+        <v>957.2734529567797</v>
       </c>
       <c r="D37" t="n">
-        <v>8.425764143923214</v>
+        <v>4.155185467070856</v>
       </c>
       <c r="E37" t="n">
-        <v>210.6415662798122</v>
+        <v>200.7057822251266</v>
       </c>
       <c r="F37" t="n">
-        <v>0.844025194644928</v>
+        <v>0.9024178981781006</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0008488548919558525</v>
+        <v>0.001009689178317785</v>
       </c>
       <c r="H37" t="n">
-        <v>935.663960287817</v>
+        <v>957.2734629994419</v>
       </c>
       <c r="I37" t="n">
-        <v>210.6415662798107</v>
+        <v>200.7057822251265</v>
       </c>
       <c r="J37" t="n">
-        <v>9.00067634306866</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K37" t="n">
-        <v>56.76392510098765</v>
+        <v>1.004266221116268e-05</v>
       </c>
       <c r="L37" t="n">
-        <v>1.56319401867222e-12</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="M37" t="n">
-        <v>0.5749121991454462</v>
+        <v>4.845456312791306</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>0.6453439593315125</v>
+        <v>0.9979609251022339</v>
       </c>
       <c r="P37" t="n">
-        <v>0.0004896446480415761</v>
+        <v>7.600859680678695e-05</v>
       </c>
       <c r="Q37" t="n">
-        <v>931.9762502311136</v>
+        <v>955.138105480333</v>
       </c>
       <c r="R37" t="n">
-        <v>210.2662434834862</v>
+        <v>200.762489903932</v>
       </c>
       <c r="S37" t="n">
-        <v>9.000641889741685</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T37" t="n">
-        <v>53.07621504428425</v>
+        <v>2.135347476446668</v>
       </c>
       <c r="U37" t="n">
-        <v>0.3753227963259747</v>
+        <v>0.05670767880536687</v>
       </c>
       <c r="V37" t="n">
-        <v>0.5748777458184708</v>
+        <v>4.845456312791306</v>
       </c>
       <c r="W37" t="b">
         <v>1</v>
@@ -3171,64 +3171,64 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>943.1920968656827</v>
+        <v>926.3837436938231</v>
       </c>
       <c r="D38" t="n">
-        <v>4.855755251113765</v>
+        <v>4.098870829540688</v>
       </c>
       <c r="E38" t="n">
-        <v>190.548390651031</v>
+        <v>202.112192541617</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9312343001365662</v>
+        <v>0.8486842513084412</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0005017555085942149</v>
+        <v>0.001007982064038515</v>
       </c>
       <c r="H38" t="n">
-        <v>943.1920968655592</v>
+        <v>926.3837436926442</v>
       </c>
       <c r="I38" t="n">
-        <v>190.548390651031</v>
+        <v>202.1121925416174</v>
       </c>
       <c r="J38" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="K38" t="n">
-        <v>1.235775926033966e-10</v>
+        <v>1.178932507173158e-09</v>
       </c>
       <c r="L38" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="M38" t="n">
-        <v>4.144886528748398</v>
+        <v>4.901770950321474</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>0.9858017563819885</v>
+        <v>0.9823220372200012</v>
       </c>
       <c r="P38" t="n">
-        <v>8.154602983267978e-05</v>
+        <v>8.093146607279778e-05</v>
       </c>
       <c r="Q38" t="n">
-        <v>943.3279112994134</v>
+        <v>928.9055085139474</v>
       </c>
       <c r="R38" t="n">
-        <v>190.8846503836392</v>
+        <v>202.1654128272097</v>
       </c>
       <c r="S38" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="T38" t="n">
-        <v>0.1358144337306157</v>
+        <v>2.521764820124304</v>
       </c>
       <c r="U38" t="n">
-        <v>0.3362597326081129</v>
+        <v>0.0532202855927153</v>
       </c>
       <c r="V38" t="n">
-        <v>4.144886528748398</v>
+        <v>4.901770950321474</v>
       </c>
       <c r="W38" t="b">
         <v>1</v>
@@ -3240,68 +3240,68 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>946.7151602993594</v>
+        <v>946.9778445568023</v>
       </c>
       <c r="D39" t="n">
-        <v>15.09768161441414</v>
+        <v>10.25061390415358</v>
       </c>
       <c r="E39" t="n">
-        <v>180.2590242190516</v>
+        <v>121.3394806969968</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7820267677307129</v>
+        <v>0.906603217124939</v>
       </c>
       <c r="G39" t="n">
-        <v>0.001222321996465325</v>
+        <v>0.005423423834145069</v>
       </c>
       <c r="H39" t="n">
-        <v>886.7991406513916</v>
+        <v>946.9770546909749</v>
       </c>
       <c r="I39" t="n">
-        <v>180.2590242190512</v>
+        <v>173.6139250356486</v>
       </c>
       <c r="J39" t="n">
-        <v>11.82181846190499</v>
+        <v>10.25060663381155</v>
       </c>
       <c r="K39" t="n">
-        <v>59.9160196479678</v>
+        <v>0.00078986582741436</v>
       </c>
       <c r="L39" t="n">
-        <v>3.694822225952521e-13</v>
+        <v>52.27444433865183</v>
       </c>
       <c r="M39" t="n">
-        <v>3.27586315250915</v>
+        <v>7.270342027965171e-06</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>0.9952612519264221</v>
+        <v>0.9999711513519287</v>
       </c>
       <c r="P39" t="n">
-        <v>0.001771747833117843</v>
+        <v>0.00902106985449791</v>
       </c>
       <c r="Q39" t="n">
-        <v>800.5288572796525</v>
+        <v>800.0000355193972</v>
       </c>
       <c r="R39" t="n">
-        <v>176.0436713347065</v>
+        <v>150.0005529326348</v>
       </c>
       <c r="S39" t="n">
-        <v>13.93894427568883</v>
+        <v>9.267952934273886</v>
       </c>
       <c r="T39" t="n">
-        <v>146.1863030197069</v>
+        <v>146.9778090374051</v>
       </c>
       <c r="U39" t="n">
-        <v>4.215352884345066</v>
+        <v>28.66107223563803</v>
       </c>
       <c r="V39" t="n">
-        <v>1.158737338725304</v>
+        <v>0.9826609698796922</v>
       </c>
       <c r="W39" t="b">
         <v>1</v>
@@ -3317,64 +3317,64 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>962.4134419510135</v>
+        <v>958.1211224485617</v>
       </c>
       <c r="D40" t="n">
-        <v>3.933248002329482</v>
+        <v>5.021450956164415</v>
       </c>
       <c r="E40" t="n">
-        <v>196.8357926842313</v>
+        <v>220.5997899278971</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9322754740715027</v>
+        <v>0.8311465382575989</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0005017708754166961</v>
+        <v>0.001009689178317785</v>
       </c>
       <c r="H40" t="n">
-        <v>962.4134582398787</v>
+        <v>958.1211297509594</v>
       </c>
       <c r="I40" t="n">
-        <v>196.8357926842312</v>
+        <v>220.599789927901</v>
       </c>
       <c r="J40" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="K40" t="n">
-        <v>1.628886514026817e-05</v>
+        <v>7.302397762032342e-06</v>
       </c>
       <c r="L40" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>3.979039320256561e-12</v>
       </c>
       <c r="M40" t="n">
-        <v>5.06739377753268</v>
+        <v>3.979190823697747</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0.9990611672401428</v>
+        <v>0.9774666428565979</v>
       </c>
       <c r="P40" t="n">
-        <v>5.014624548493885e-05</v>
+        <v>0.0001757863064995036</v>
       </c>
       <c r="Q40" t="n">
-        <v>961.5070079064665</v>
+        <v>953.8902278592511</v>
       </c>
       <c r="R40" t="n">
-        <v>196.9322381642739</v>
+        <v>219.7635399870685</v>
       </c>
       <c r="S40" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="T40" t="n">
-        <v>0.9064340445470407</v>
+        <v>4.230894589310537</v>
       </c>
       <c r="U40" t="n">
-        <v>0.09644548004263243</v>
+        <v>0.8362499408285942</v>
       </c>
       <c r="V40" t="n">
-        <v>5.06739377753268</v>
+        <v>3.979190823697747</v>
       </c>
       <c r="W40" t="b">
         <v>1</v>
@@ -3386,68 +3386,68 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>925.5264205940191</v>
+        <v>954.3792783171195</v>
       </c>
       <c r="D41" t="n">
-        <v>9.240641298553927</v>
+        <v>5.779407977267885</v>
       </c>
       <c r="E41" t="n">
-        <v>121.6092848320675</v>
+        <v>200.2942369471083</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9222081303596497</v>
+        <v>0.8952300548553467</v>
       </c>
       <c r="G41" t="n">
-        <v>0.00293063884600997</v>
+        <v>0.001009692437946796</v>
       </c>
       <c r="H41" t="n">
-        <v>945.8155635373156</v>
+        <v>954.3792783171151</v>
       </c>
       <c r="I41" t="n">
-        <v>173.6136086170593</v>
+        <v>200.2942369471084</v>
       </c>
       <c r="J41" t="n">
-        <v>9.240570266520603</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K41" t="n">
-        <v>20.2891429432965</v>
+        <v>4.433786671143025e-12</v>
       </c>
       <c r="L41" t="n">
-        <v>52.00432378499181</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="M41" t="n">
-        <v>7.103203332370356e-05</v>
+        <v>3.221233802594277</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>1</v>
+        <v>0.9577566385269165</v>
       </c>
       <c r="P41" t="n">
-        <v>0.00659690098837018</v>
+        <v>7.182874105637893e-05</v>
       </c>
       <c r="Q41" t="n">
-        <v>800.0000287052792</v>
+        <v>952.7822106816167</v>
       </c>
       <c r="R41" t="n">
-        <v>152.9710540771775</v>
+        <v>200.3588301549985</v>
       </c>
       <c r="S41" t="n">
-        <v>9.000521147785134</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T41" t="n">
-        <v>125.5263918887399</v>
+        <v>1.597067635502867</v>
       </c>
       <c r="U41" t="n">
-        <v>31.36176924511</v>
+        <v>0.06459320789016942</v>
       </c>
       <c r="V41" t="n">
-        <v>0.2401201507687922</v>
+        <v>3.221233802594277</v>
       </c>
       <c r="W41" t="b">
         <v>1</v>
@@ -3463,64 +3463,64 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>874.0821187064782</v>
+        <v>875.0560704311393</v>
       </c>
       <c r="D42" t="n">
-        <v>7.767320450652663</v>
+        <v>8.044794669919384</v>
       </c>
       <c r="E42" t="n">
-        <v>206.1137005176345</v>
+        <v>196.1256248794963</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9018924236297607</v>
+        <v>0.9285256266593933</v>
       </c>
       <c r="G42" t="n">
-        <v>0.001779327751137316</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H42" t="n">
-        <v>919.428358468431</v>
+        <v>933.0453159927907</v>
       </c>
       <c r="I42" t="n">
-        <v>206.1137005176378</v>
+        <v>196.1256248794963</v>
       </c>
       <c r="J42" t="n">
-        <v>9.000556221005253</v>
+        <v>9.000641636420553</v>
       </c>
       <c r="K42" t="n">
-        <v>45.3462397619528</v>
+        <v>57.98924556165139</v>
       </c>
       <c r="L42" t="n">
-        <v>3.268496584496461e-12</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.233235770352589</v>
+        <v>0.95584696650117</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>0.8891984820365906</v>
+        <v>0.9370651245117188</v>
       </c>
       <c r="P42" t="n">
-        <v>0.0005225249915383756</v>
+        <v>0.0004446028033271432</v>
       </c>
       <c r="Q42" t="n">
-        <v>931.2143001768042</v>
+        <v>932.3591921618067</v>
       </c>
       <c r="R42" t="n">
-        <v>205.9051783415973</v>
+        <v>196.8563581366042</v>
       </c>
       <c r="S42" t="n">
-        <v>9.000641815342336</v>
+        <v>9.000641673276222</v>
       </c>
       <c r="T42" t="n">
-        <v>57.13218147032592</v>
+        <v>57.30312173066739</v>
       </c>
       <c r="U42" t="n">
-        <v>0.2085221760372349</v>
+        <v>0.7307332571079712</v>
       </c>
       <c r="V42" t="n">
-        <v>1.233321364689672</v>
+        <v>0.9558470033568387</v>
       </c>
       <c r="W42" t="b">
         <v>1</v>
@@ -3532,68 +3532,68 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>930.9026183683185</v>
+        <v>881.8095444567513</v>
       </c>
       <c r="D43" t="n">
-        <v>9.525206097560066</v>
+        <v>9.096120612402132</v>
       </c>
       <c r="E43" t="n">
-        <v>125.4374594005599</v>
+        <v>222.6158273769345</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9357817769050598</v>
+        <v>0.5667540431022644</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0006120777106843889</v>
+        <v>0.001727092894725502</v>
       </c>
       <c r="H43" t="n">
-        <v>917.7907176321553</v>
+        <v>933.045328905432</v>
       </c>
       <c r="I43" t="n">
-        <v>176.1296287130706</v>
+        <v>222.6158371179696</v>
       </c>
       <c r="J43" t="n">
-        <v>10.13573355234474</v>
+        <v>9.096080025806208</v>
       </c>
       <c r="K43" t="n">
-        <v>13.11190073616319</v>
+        <v>51.23578444868076</v>
       </c>
       <c r="L43" t="n">
-        <v>50.69216931251074</v>
+        <v>9.741035086108241e-06</v>
       </c>
       <c r="M43" t="n">
-        <v>0.6105274547846768</v>
+        <v>4.058659592409697e-05</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>1</v>
+        <v>0.5008395910263062</v>
       </c>
       <c r="P43" t="n">
-        <v>0.005546124652028084</v>
+        <v>0.0004888346302323043</v>
       </c>
       <c r="Q43" t="n">
-        <v>800.0000336898173</v>
+        <v>933.4359710505946</v>
       </c>
       <c r="R43" t="n">
-        <v>153.514054838844</v>
+        <v>220.625887798531</v>
       </c>
       <c r="S43" t="n">
-        <v>9.000431717953688</v>
+        <v>9.164699991109494</v>
       </c>
       <c r="T43" t="n">
-        <v>130.9025846785012</v>
+        <v>51.62642659384335</v>
       </c>
       <c r="U43" t="n">
-        <v>28.07659543828416</v>
+        <v>1.989939578403465</v>
       </c>
       <c r="V43" t="n">
-        <v>0.5247743796063773</v>
+        <v>0.06857937870736208</v>
       </c>
       <c r="W43" t="b">
         <v>1</v>
@@ -3605,68 +3605,68 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>934.5079730422938</v>
+        <v>933.5595659170884</v>
       </c>
       <c r="D44" t="n">
-        <v>11.10399410569217</v>
+        <v>3.566375687654564</v>
       </c>
       <c r="E44" t="n">
-        <v>123.3863151689311</v>
+        <v>200.6836171785196</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9367098808288574</v>
+        <v>0.902368426322937</v>
       </c>
       <c r="G44" t="n">
-        <v>0.009299690835177898</v>
+        <v>0.001009692437946796</v>
       </c>
       <c r="H44" t="n">
-        <v>949.4787530746802</v>
+        <v>933.559565917431</v>
       </c>
       <c r="I44" t="n">
-        <v>164.2917033976996</v>
+        <v>200.6836171785194</v>
       </c>
       <c r="J44" t="n">
-        <v>11.10398611585794</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K44" t="n">
-        <v>14.97078003238641</v>
+        <v>3.425384420552291e-10</v>
       </c>
       <c r="L44" t="n">
-        <v>40.90538822876854</v>
+        <v>1.70530256582424e-13</v>
       </c>
       <c r="M44" t="n">
-        <v>7.989834232446924e-06</v>
+        <v>5.434266092207598</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>1</v>
+        <v>0.9942396879196167</v>
       </c>
       <c r="P44" t="n">
-        <v>0.006058187689632177</v>
+        <v>6.981344631640241e-05</v>
       </c>
       <c r="Q44" t="n">
-        <v>800.0000168814817</v>
+        <v>934.9200161751213</v>
       </c>
       <c r="R44" t="n">
-        <v>155.903664336477</v>
+        <v>200.7534167666371</v>
       </c>
       <c r="S44" t="n">
-        <v>9.787412548957926</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T44" t="n">
-        <v>134.5079561608121</v>
+        <v>1.36045025803287</v>
       </c>
       <c r="U44" t="n">
-        <v>32.51734916754589</v>
+        <v>0.06979958811751885</v>
       </c>
       <c r="V44" t="n">
-        <v>1.316581556734244</v>
+        <v>5.434266092207598</v>
       </c>
       <c r="W44" t="b">
         <v>1</v>
@@ -3678,68 +3678,68 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>915.971295548182</v>
+        <v>897.3852576339389</v>
       </c>
       <c r="D45" t="n">
-        <v>8.433968397484772</v>
+        <v>6.78893341300639</v>
       </c>
       <c r="E45" t="n">
-        <v>116.6329714024075</v>
+        <v>193.4707971802883</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8985404372215271</v>
+        <v>0.7910519242286682</v>
       </c>
       <c r="G45" t="n">
-        <v>0.7366998791694641</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H45" t="n">
-        <v>928.0996907866038</v>
+        <v>933.0453150666568</v>
       </c>
       <c r="I45" t="n">
-        <v>155.4679670918317</v>
+        <v>193.4707971802883</v>
       </c>
       <c r="J45" t="n">
-        <v>10.70182571703081</v>
+        <v>9.000641658368027</v>
       </c>
       <c r="K45" t="n">
-        <v>12.12839523842183</v>
+        <v>35.66005743271796</v>
       </c>
       <c r="L45" t="n">
-        <v>38.83499568942426</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.267857319546039</v>
+        <v>2.211708245361637</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>0.793515145778656</v>
       </c>
       <c r="P45" t="n">
-        <v>0.008150499314069748</v>
+        <v>0.0003006612241733819</v>
       </c>
       <c r="Q45" t="n">
-        <v>800.0000413639809</v>
+        <v>935.5889220183041</v>
       </c>
       <c r="R45" t="n">
-        <v>152.3083530559339</v>
+        <v>194.1723296924535</v>
       </c>
       <c r="S45" t="n">
-        <v>9.00064218658547</v>
+        <v>9.000641650906047</v>
       </c>
       <c r="T45" t="n">
-        <v>115.971254184201</v>
+        <v>38.2036643843652</v>
       </c>
       <c r="U45" t="n">
-        <v>35.67538165352641</v>
+        <v>0.7015325121652438</v>
       </c>
       <c r="V45" t="n">
-        <v>0.5666737891006974</v>
+        <v>2.211708237899657</v>
       </c>
       <c r="W45" t="b">
         <v>1</v>
@@ -3751,68 +3751,68 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>943.9422951240201</v>
+        <v>895.9203767289504</v>
       </c>
       <c r="D46" t="n">
-        <v>10.70997486905503</v>
+        <v>5.067263974051466</v>
       </c>
       <c r="E46" t="n">
-        <v>151.5073318488736</v>
+        <v>196.2792330886438</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9365445375442505</v>
+        <v>0.8566992282867432</v>
       </c>
       <c r="G46" t="n">
-        <v>0.009299447759985924</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H46" t="n">
-        <v>961.9582331686189</v>
+        <v>933.0453168435243</v>
       </c>
       <c r="I46" t="n">
-        <v>164.2946055648584</v>
+        <v>196.2792330886437</v>
       </c>
       <c r="J46" t="n">
-        <v>10.7099535991266</v>
+        <v>9.000641671427948</v>
       </c>
       <c r="K46" t="n">
-        <v>18.01593804459878</v>
+        <v>37.12494011457397</v>
       </c>
       <c r="L46" t="n">
-        <v>12.78727371598484</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="M46" t="n">
-        <v>2.126992843187736e-05</v>
+        <v>3.933377697376482</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>0.9993827342987061</v>
+        <v>0.6922328472137451</v>
       </c>
       <c r="P46" t="n">
-        <v>0.001424258691258729</v>
+        <v>0.0003074153210036457</v>
       </c>
       <c r="Q46" t="n">
-        <v>800.0021207589001</v>
+        <v>934.582654289844</v>
       </c>
       <c r="R46" t="n">
-        <v>162.2341719230256</v>
+        <v>196.8077102173943</v>
       </c>
       <c r="S46" t="n">
-        <v>10.61504536185583</v>
+        <v>9.000641740151302</v>
       </c>
       <c r="T46" t="n">
-        <v>143.94017436512</v>
+        <v>38.66227756089359</v>
       </c>
       <c r="U46" t="n">
-        <v>10.72684007415205</v>
+        <v>0.5284771287505237</v>
       </c>
       <c r="V46" t="n">
-        <v>0.09492950719920401</v>
+        <v>3.933377766099836</v>
       </c>
       <c r="W46" t="b">
         <v>1</v>
@@ -3824,68 +3824,68 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>943.1555501890516</v>
+        <v>955.4729197493958</v>
       </c>
       <c r="D47" t="n">
-        <v>4.136696116149537</v>
+        <v>9.569674922845763</v>
       </c>
       <c r="E47" t="n">
-        <v>189.8889599538231</v>
+        <v>134.1891954710945</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9312343001365662</v>
+        <v>0.906603217124939</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0005017555085942149</v>
+        <v>0.01683678291738033</v>
       </c>
       <c r="H47" t="n">
-        <v>943.1555501892484</v>
+        <v>955.5017000687828</v>
       </c>
       <c r="I47" t="n">
-        <v>189.8889599538228</v>
+        <v>164.2913488507402</v>
       </c>
       <c r="J47" t="n">
-        <v>9.000641779862162</v>
+        <v>10.2130040540647</v>
       </c>
       <c r="K47" t="n">
-        <v>1.967919160961173e-10</v>
+        <v>0.02878031938701042</v>
       </c>
       <c r="L47" t="n">
-        <v>3.410605131648481e-13</v>
+        <v>30.1021533796457</v>
       </c>
       <c r="M47" t="n">
-        <v>4.863945663712625</v>
+        <v>0.643329131218934</v>
       </c>
       <c r="N47" t="b">
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>0.9973565340042114</v>
+        <v>0.9999130964279175</v>
       </c>
       <c r="P47" t="n">
-        <v>8.763681398704648e-05</v>
+        <v>0.005678033921867609</v>
       </c>
       <c r="Q47" t="n">
-        <v>943.3095661882148</v>
+        <v>800.0000298746668</v>
       </c>
       <c r="R47" t="n">
-        <v>190.2481437043452</v>
+        <v>151.157383265226</v>
       </c>
       <c r="S47" t="n">
-        <v>9.000641779862162</v>
+        <v>9.01081412252911</v>
       </c>
       <c r="T47" t="n">
-        <v>0.1540159991632208</v>
+        <v>155.472889874729</v>
       </c>
       <c r="U47" t="n">
-        <v>0.3591837505220496</v>
+        <v>16.96818779413147</v>
       </c>
       <c r="V47" t="n">
-        <v>4.863945663712625</v>
+        <v>0.5588608003166531</v>
       </c>
       <c r="W47" t="b">
         <v>1</v>
@@ -3901,64 +3901,64 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>844.5788138547135</v>
+        <v>888.8566881929055</v>
       </c>
       <c r="D48" t="n">
-        <v>7.59415139233557</v>
+        <v>7.723190453058736</v>
       </c>
       <c r="E48" t="n">
-        <v>226.8746747136299</v>
+        <v>200.0492671848147</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9086915850639343</v>
+        <v>0.8543873429298401</v>
       </c>
       <c r="G48" t="n">
-        <v>0.001532252877950668</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H48" t="n">
-        <v>918.8530573661448</v>
+        <v>933.0453179642307</v>
       </c>
       <c r="I48" t="n">
-        <v>224.8621573092537</v>
+        <v>200.0492671848147</v>
       </c>
       <c r="J48" t="n">
-        <v>9.000641664911376</v>
+        <v>9.000641509076948</v>
       </c>
       <c r="K48" t="n">
-        <v>74.27424351143122</v>
+        <v>44.18862977132517</v>
       </c>
       <c r="L48" t="n">
-        <v>2.012517404376212</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1.406490272575805</v>
+        <v>1.277451056018212</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>0.935052752494812</v>
+        <v>0.8312811851501465</v>
       </c>
       <c r="P48" t="n">
-        <v>0.0008573738159611821</v>
+        <v>0.00033524539321661</v>
       </c>
       <c r="Q48" t="n">
-        <v>931.5109106147402</v>
+        <v>933.3516624718369</v>
       </c>
       <c r="R48" t="n">
-        <v>226.1500806240446</v>
+        <v>200.3508451231407</v>
       </c>
       <c r="S48" t="n">
-        <v>9.000641819438632</v>
+        <v>9.000641918464289</v>
       </c>
       <c r="T48" t="n">
-        <v>86.93209676002664</v>
+        <v>44.49497427893141</v>
       </c>
       <c r="U48" t="n">
-        <v>0.7245940895852527</v>
+        <v>0.3015779383260053</v>
       </c>
       <c r="V48" t="n">
-        <v>1.406490427103062</v>
+        <v>1.277451465405553</v>
       </c>
       <c r="W48" t="b">
         <v>1</v>
@@ -3970,68 +3970,68 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>837.7732934689444</v>
+        <v>963.0088085381315</v>
       </c>
       <c r="D49" t="n">
-        <v>6.753432575528466</v>
+        <v>11.52744922557012</v>
       </c>
       <c r="E49" t="n">
-        <v>190.2151386067326</v>
+        <v>154.0011373358929</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9365894198417664</v>
+        <v>0.9065951704978943</v>
       </c>
       <c r="G49" t="n">
-        <v>0.001716198050417006</v>
+        <v>0.001030126353725791</v>
       </c>
       <c r="H49" t="n">
-        <v>919.4282431361685</v>
+        <v>963.0026827948595</v>
       </c>
       <c r="I49" t="n">
-        <v>190.2151386067326</v>
+        <v>176.1299395222404</v>
       </c>
       <c r="J49" t="n">
-        <v>9.000641583549386</v>
+        <v>11.52742682408505</v>
       </c>
       <c r="K49" t="n">
-        <v>81.65494966722406</v>
+        <v>0.006125743271923056</v>
       </c>
       <c r="L49" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>22.12880218634746</v>
       </c>
       <c r="M49" t="n">
-        <v>2.247209008020921</v>
+        <v>2.240148506693629e-05</v>
       </c>
       <c r="N49" t="b">
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>0.980803906917572</v>
+        <v>0.9454864263534546</v>
       </c>
       <c r="P49" t="n">
-        <v>0.0008952956413850188</v>
+        <v>0.003417638596147299</v>
       </c>
       <c r="Q49" t="n">
-        <v>929.2538290430722</v>
+        <v>802.7478830538647</v>
       </c>
       <c r="R49" t="n">
-        <v>191.4382316943292</v>
+        <v>166.9986867266815</v>
       </c>
       <c r="S49" t="n">
-        <v>9.000641568676816</v>
+        <v>11.27867430317689</v>
       </c>
       <c r="T49" t="n">
-        <v>91.48053557412777</v>
+        <v>160.2609254842667</v>
       </c>
       <c r="U49" t="n">
-        <v>1.223093087596538</v>
+        <v>12.99754939078858</v>
       </c>
       <c r="V49" t="n">
-        <v>2.24720899314835</v>
+        <v>0.2487749223932223</v>
       </c>
       <c r="W49" t="b">
         <v>1</v>
@@ -4047,64 +4047,64 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>942.8290100072318</v>
+        <v>963.176555542808</v>
       </c>
       <c r="D50" t="n">
-        <v>6.400376626811989</v>
+        <v>4.610213383201334</v>
       </c>
       <c r="E50" t="n">
-        <v>188.1906254437854</v>
+        <v>216.9138812036659</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8688167333602905</v>
+        <v>0.8311465382575989</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0005017622606828809</v>
+        <v>0.001009689178317785</v>
       </c>
       <c r="H50" t="n">
-        <v>942.8290100062374</v>
+        <v>963.1765581926694</v>
       </c>
       <c r="I50" t="n">
-        <v>188.1906254437855</v>
+        <v>216.9138812036777</v>
       </c>
       <c r="J50" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="K50" t="n">
-        <v>9.944187695509754e-10</v>
+        <v>2.649861357895134e-06</v>
       </c>
       <c r="L50" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>1.182343112304807e-11</v>
       </c>
       <c r="M50" t="n">
-        <v>2.600265153050173</v>
+        <v>4.390428396660829</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>0.3870470523834229</v>
+        <v>0.9931203126907349</v>
       </c>
       <c r="P50" t="n">
-        <v>0.0001054359672707506</v>
+        <v>0.0001475030148867518</v>
       </c>
       <c r="Q50" t="n">
-        <v>942.9872770622436</v>
+        <v>958.3165018710007</v>
       </c>
       <c r="R50" t="n">
-        <v>188.6078339197368</v>
+        <v>216.3539704999721</v>
       </c>
       <c r="S50" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="T50" t="n">
-        <v>0.1582670550118337</v>
+        <v>4.86005367180735</v>
       </c>
       <c r="U50" t="n">
-        <v>0.4172084759514121</v>
+        <v>0.5599107036938449</v>
       </c>
       <c r="V50" t="n">
-        <v>2.600265153050173</v>
+        <v>4.390428396660829</v>
       </c>
       <c r="W50" t="b">
         <v>1</v>
@@ -4116,68 +4116,68 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>952.2244666968172</v>
+        <v>844.5788138547135</v>
       </c>
       <c r="D51" t="n">
-        <v>9.374842474547272</v>
+        <v>7.59415139233557</v>
       </c>
       <c r="E51" t="n">
-        <v>143.7893713723858</v>
+        <v>226.8746747136299</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9364324808120728</v>
+        <v>0.9079260230064392</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0004814165877178311</v>
+        <v>0.001726252725347877</v>
       </c>
       <c r="H51" t="n">
-        <v>941.8996676143486</v>
+        <v>933.0554803850504</v>
       </c>
       <c r="I51" t="n">
-        <v>176.1296282510185</v>
+        <v>226.87467471363</v>
       </c>
       <c r="J51" t="n">
-        <v>9.413359194205254</v>
+        <v>9.000641712244377</v>
       </c>
       <c r="K51" t="n">
-        <v>10.32479908246864</v>
+        <v>88.47666653033684</v>
       </c>
       <c r="L51" t="n">
-        <v>32.34025687863266</v>
+        <v>1.70530256582424e-13</v>
       </c>
       <c r="M51" t="n">
-        <v>0.03851671965798253</v>
+        <v>1.406490319908807</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>0.9999693632125854</v>
+        <v>0.9656434059143066</v>
       </c>
       <c r="P51" t="n">
-        <v>0.002009839517995715</v>
+        <v>0.0009472327656112611</v>
       </c>
       <c r="Q51" t="n">
-        <v>800.0000477177562</v>
+        <v>932.1064155296973</v>
       </c>
       <c r="R51" t="n">
-        <v>157.2553292145766</v>
+        <v>223.0414237065359</v>
       </c>
       <c r="S51" t="n">
-        <v>9.153376617899209</v>
+        <v>9.000640444864356</v>
       </c>
       <c r="T51" t="n">
-        <v>152.2244189790611</v>
+        <v>87.52760167498377</v>
       </c>
       <c r="U51" t="n">
-        <v>13.46595784219082</v>
+        <v>3.833251007093935</v>
       </c>
       <c r="V51" t="n">
-        <v>0.221465856648063</v>
+        <v>1.406489052528785</v>
       </c>
       <c r="W51" t="b">
         <v>1</v>
@@ -4193,64 +4193,64 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>949.4125772685856</v>
+        <v>915.971295548182</v>
       </c>
       <c r="D52" t="n">
-        <v>9.419741467999932</v>
+        <v>8.433968397484772</v>
       </c>
       <c r="E52" t="n">
-        <v>151.2707874231109</v>
+        <v>116.6329714024075</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9364324808120728</v>
+        <v>0.8593701124191284</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0004813938576262444</v>
+        <v>0.001029878039844334</v>
       </c>
       <c r="H52" t="n">
-        <v>943.0041329358821</v>
+        <v>930.9479374974435</v>
       </c>
       <c r="I52" t="n">
-        <v>176.1296323000503</v>
+        <v>176.1296285244026</v>
       </c>
       <c r="J52" t="n">
-        <v>9.419741454718308</v>
+        <v>10.12701083913167</v>
       </c>
       <c r="K52" t="n">
-        <v>6.408444332703425</v>
+        <v>14.97664194926153</v>
       </c>
       <c r="L52" t="n">
-        <v>24.85884487693946</v>
+        <v>59.4966571219951</v>
       </c>
       <c r="M52" t="n">
-        <v>1.328162468894334e-08</v>
+        <v>1.693042441646893</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>0.9994656443595886</v>
+        <v>0.9999322891235352</v>
       </c>
       <c r="P52" t="n">
-        <v>0.001347462879493833</v>
+        <v>0.006814353633671999</v>
       </c>
       <c r="Q52" t="n">
-        <v>804.781662546915</v>
+        <v>800.0000254716435</v>
       </c>
       <c r="R52" t="n">
-        <v>160.8312442361627</v>
+        <v>150.0005529027002</v>
       </c>
       <c r="S52" t="n">
-        <v>9.320841841179172</v>
+        <v>9.000642128851966</v>
       </c>
       <c r="T52" t="n">
-        <v>144.6309147216706</v>
+        <v>115.9712700765384</v>
       </c>
       <c r="U52" t="n">
-        <v>9.560456813051871</v>
+        <v>33.36758150029272</v>
       </c>
       <c r="V52" t="n">
-        <v>0.09889962682076003</v>
+        <v>0.5666737313671941</v>
       </c>
       <c r="W52" t="b">
         <v>1</v>
@@ -4262,68 +4262,68 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>845.8345604713478</v>
+        <v>922.8358850593218</v>
       </c>
       <c r="D53" t="n">
-        <v>7.121444438263866</v>
+        <v>9.435939006210385</v>
       </c>
       <c r="E53" t="n">
-        <v>187.936628615325</v>
+        <v>137.6584224652683</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8870140314102173</v>
+        <v>0.9028918147087097</v>
       </c>
       <c r="G53" t="n">
-        <v>0.001519713317975402</v>
+        <v>0.006410556379705667</v>
       </c>
       <c r="H53" t="n">
-        <v>919.4282428039663</v>
+        <v>911.5480505174032</v>
       </c>
       <c r="I53" t="n">
-        <v>187.7720126067777</v>
+        <v>175.6483503656856</v>
       </c>
       <c r="J53" t="n">
-        <v>9.000641642332553</v>
+        <v>10.21300403347576</v>
       </c>
       <c r="K53" t="n">
-        <v>73.59368233261853</v>
+        <v>11.28783454191853</v>
       </c>
       <c r="L53" t="n">
-        <v>0.1646160085473696</v>
+        <v>37.98992790041726</v>
       </c>
       <c r="M53" t="n">
-        <v>1.879197204068687</v>
+        <v>0.7770650272653779</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0.9661648273468018</v>
+        <v>0.9995856881141663</v>
       </c>
       <c r="P53" t="n">
-        <v>0.0007653642096556723</v>
+        <v>0.00461842305958271</v>
       </c>
       <c r="Q53" t="n">
-        <v>930.924148335347</v>
+        <v>800.0000272562969</v>
       </c>
       <c r="R53" t="n">
-        <v>188.946509587826</v>
+        <v>152.3281931477131</v>
       </c>
       <c r="S53" t="n">
-        <v>9.000641600240087</v>
+        <v>9.000406356546192</v>
       </c>
       <c r="T53" t="n">
-        <v>85.08958786399921</v>
+        <v>122.8358578030249</v>
       </c>
       <c r="U53" t="n">
-        <v>1.009880972500952</v>
+        <v>14.66977068244481</v>
       </c>
       <c r="V53" t="n">
-        <v>1.87919716197622</v>
+        <v>0.4355326496641929</v>
       </c>
       <c r="W53" t="b">
         <v>1</v>
@@ -4339,64 +4339,64 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>945.7356325434033</v>
+        <v>931.1795459866725</v>
       </c>
       <c r="D54" t="n">
-        <v>14.97427748487189</v>
+        <v>15.01021031559371</v>
       </c>
       <c r="E54" t="n">
-        <v>213.3456914558439</v>
+        <v>196.3062034466771</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9109001755714417</v>
+        <v>0.8086524605751038</v>
       </c>
       <c r="G54" t="n">
-        <v>0.006548034492880106</v>
+        <v>0.0006024915492162108</v>
       </c>
       <c r="H54" t="n">
-        <v>951.4455763065425</v>
+        <v>931.1718345308351</v>
       </c>
       <c r="I54" t="n">
-        <v>214.5108091988581</v>
+        <v>196.3063189322034</v>
       </c>
       <c r="J54" t="n">
-        <v>12.63059754492861</v>
+        <v>11.82181856638964</v>
       </c>
       <c r="K54" t="n">
-        <v>5.709943763139222</v>
+        <v>0.007711455837352332</v>
       </c>
       <c r="L54" t="n">
-        <v>1.165117743014235</v>
+        <v>0.0001154855263223453</v>
       </c>
       <c r="M54" t="n">
-        <v>2.343679939943279</v>
+        <v>3.188391749204067</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>0.9926930665969849</v>
+        <v>0.9922215342521667</v>
       </c>
       <c r="P54" t="n">
-        <v>0.002502325922250748</v>
+        <v>0.003961622714996338</v>
       </c>
       <c r="Q54" t="n">
-        <v>800.0000481799771</v>
+        <v>800.0000435724913</v>
       </c>
       <c r="R54" t="n">
-        <v>213.8192697118915</v>
+        <v>200.2040577450566</v>
       </c>
       <c r="S54" t="n">
-        <v>13.52464736754915</v>
+        <v>13.72671710098872</v>
       </c>
       <c r="T54" t="n">
-        <v>145.7355843634263</v>
+        <v>131.1795024141811</v>
       </c>
       <c r="U54" t="n">
-        <v>0.4735782560476025</v>
+        <v>3.897854298379514</v>
       </c>
       <c r="V54" t="n">
-        <v>1.449630117322741</v>
+        <v>1.283493214604986</v>
       </c>
       <c r="W54" t="b">
         <v>1</v>
@@ -4408,68 +4408,68 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>922.8358850593218</v>
+        <v>871.376215413518</v>
       </c>
       <c r="D55" t="n">
-        <v>9.435939006210385</v>
+        <v>7.926433919294807</v>
       </c>
       <c r="E55" t="n">
-        <v>137.6584224652683</v>
+        <v>179.6327752373482</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9230242967605591</v>
+        <v>0.8652369379997253</v>
       </c>
       <c r="G55" t="n">
-        <v>0.000481406576000154</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H55" t="n">
-        <v>928.4785359230387</v>
+        <v>933.0453156546907</v>
       </c>
       <c r="I55" t="n">
-        <v>176.12962837029</v>
+        <v>179.6327752373482</v>
       </c>
       <c r="J55" t="n">
-        <v>9.435939007490056</v>
+        <v>9.000641751175976</v>
       </c>
       <c r="K55" t="n">
-        <v>5.642650863716995</v>
+        <v>61.66910024117271</v>
       </c>
       <c r="L55" t="n">
-        <v>38.47120590502166</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>1.279671479892386e-09</v>
+        <v>1.07420783188117</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>0.9999954700469971</v>
+        <v>0.9245845675468445</v>
       </c>
       <c r="P55" t="n">
-        <v>0.003018099348992109</v>
+        <v>0.0006644257227890193</v>
       </c>
       <c r="Q55" t="n">
-        <v>800.0000000315933</v>
+        <v>938.1207292980874</v>
       </c>
       <c r="R55" t="n">
-        <v>155.8001768353091</v>
+        <v>182.3052040854125</v>
       </c>
       <c r="S55" t="n">
-        <v>9.102167624133051</v>
+        <v>9.000638692968462</v>
       </c>
       <c r="T55" t="n">
-        <v>122.8358850277284</v>
+        <v>66.74451388456941</v>
       </c>
       <c r="U55" t="n">
-        <v>18.14175437004073</v>
+        <v>2.672428848064357</v>
       </c>
       <c r="V55" t="n">
-        <v>0.3337713820773338</v>
+        <v>1.074204773673655</v>
       </c>
       <c r="W55" t="b">
         <v>1</v>
@@ -4481,68 +4481,68 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>891.0512054522358</v>
+        <v>949.2196096124491</v>
       </c>
       <c r="D56" t="n">
-        <v>8.14885781102695</v>
+        <v>4.056588199894033</v>
       </c>
       <c r="E56" t="n">
-        <v>208.040866618594</v>
+        <v>205.1094495850843</v>
       </c>
       <c r="F56" t="n">
-        <v>0.5500662326812744</v>
+        <v>0.9024239182472229</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0009904649341478944</v>
+        <v>0.001009692437946796</v>
       </c>
       <c r="H56" t="n">
-        <v>933.045360532583</v>
+        <v>949.2196096124475</v>
       </c>
       <c r="I56" t="n">
-        <v>208.040866618594</v>
+        <v>205.1094495850839</v>
       </c>
       <c r="J56" t="n">
-        <v>9.0006014916427</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K56" t="n">
-        <v>41.99415508034724</v>
+        <v>1.591615728102624e-12</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="M56" t="n">
-        <v>0.8517436806157495</v>
+        <v>4.944053579968129</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>0.4739420711994171</v>
+        <v>0.9969459176063538</v>
       </c>
       <c r="P56" t="n">
-        <v>0.0003752864140551537</v>
+        <v>6.421738362405449e-05</v>
       </c>
       <c r="Q56" t="n">
-        <v>933.6513723873582</v>
+        <v>948.3804055264109</v>
       </c>
       <c r="R56" t="n">
-        <v>207.8869740492335</v>
+        <v>205.0775835163348</v>
       </c>
       <c r="S56" t="n">
-        <v>9.00064159569663</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T56" t="n">
-        <v>42.60016693512239</v>
+        <v>0.839204086038194</v>
       </c>
       <c r="U56" t="n">
-        <v>0.1538925693605222</v>
+        <v>0.03186606874945141</v>
       </c>
       <c r="V56" t="n">
-        <v>0.8517837846696796</v>
+        <v>4.944053579968129</v>
       </c>
       <c r="W56" t="b">
         <v>1</v>
@@ -4554,68 +4554,68 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>862.4995334483451</v>
+        <v>921.8809467282865</v>
       </c>
       <c r="D57" t="n">
-        <v>9.063402892415709</v>
+        <v>10.09601292276444</v>
       </c>
       <c r="E57" t="n">
-        <v>198.8624436728534</v>
+        <v>132.0277192594506</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7983468770980835</v>
+        <v>0.9047420620918274</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0009909978834912181</v>
+        <v>0.01683678291738033</v>
       </c>
       <c r="H57" t="n">
-        <v>919.4282420387069</v>
+        <v>949.4790620128981</v>
       </c>
       <c r="I57" t="n">
-        <v>198.8624436728549</v>
+        <v>164.2967489857195</v>
       </c>
       <c r="J57" t="n">
-        <v>9.328972722858682</v>
+        <v>10.21326267224778</v>
       </c>
       <c r="K57" t="n">
-        <v>56.92870859036179</v>
+        <v>27.59811528461159</v>
       </c>
       <c r="L57" t="n">
-        <v>1.4210854715202e-12</v>
+        <v>32.26902972626888</v>
       </c>
       <c r="M57" t="n">
-        <v>0.2655698304429723</v>
+        <v>0.1172497494833458</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>0.6215916275978088</v>
+        <v>0.9998440742492676</v>
       </c>
       <c r="P57" t="n">
-        <v>0.0005747005343437195</v>
+        <v>0.006838074885308743</v>
       </c>
       <c r="Q57" t="n">
-        <v>929.3043873945442</v>
+        <v>800.0000420441365</v>
       </c>
       <c r="R57" t="n">
-        <v>199.1364279502518</v>
+        <v>152.0401262919456</v>
       </c>
       <c r="S57" t="n">
-        <v>9.1368074679358</v>
+        <v>9.327410971660093</v>
       </c>
       <c r="T57" t="n">
-        <v>66.80485394619905</v>
+        <v>121.88090468415</v>
       </c>
       <c r="U57" t="n">
-        <v>0.2739842773983412</v>
+        <v>20.01240703249499</v>
       </c>
       <c r="V57" t="n">
-        <v>0.07340457552009028</v>
+        <v>0.7686019511043458</v>
       </c>
       <c r="W57" t="b">
         <v>1</v>
@@ -4631,64 +4631,64 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>861.319520664121</v>
+        <v>877.66740996343</v>
       </c>
       <c r="D58" t="n">
-        <v>9.051488789697419</v>
+        <v>8.192804608108121</v>
       </c>
       <c r="E58" t="n">
-        <v>213.8252113029648</v>
+        <v>200.1572790929328</v>
       </c>
       <c r="F58" t="n">
-        <v>0.6722577214241028</v>
+        <v>0.7510212659835815</v>
       </c>
       <c r="G58" t="n">
-        <v>0.001411959761753678</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H58" t="n">
-        <v>918.8325220646911</v>
+        <v>933.045316180193</v>
       </c>
       <c r="I58" t="n">
-        <v>213.8252113029648</v>
+        <v>200.1572790929328</v>
       </c>
       <c r="J58" t="n">
-        <v>9.103706540268195</v>
+        <v>9.000641730023091</v>
       </c>
       <c r="K58" t="n">
-        <v>57.51300140057015</v>
+        <v>55.37790621676299</v>
       </c>
       <c r="L58" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.05221775057077593</v>
+        <v>0.8078371219149698</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>0.6172221302986145</v>
+        <v>0.9104511141777039</v>
       </c>
       <c r="P58" t="n">
-        <v>0.000645729131065309</v>
+        <v>0.0004137116193305701</v>
       </c>
       <c r="Q58" t="n">
-        <v>928.4044117379327</v>
+        <v>932.0941669109948</v>
       </c>
       <c r="R58" t="n">
-        <v>212.4457103726802</v>
+        <v>200.5079936668576</v>
       </c>
       <c r="S58" t="n">
-        <v>9.150504956925413</v>
+        <v>9.000641699917967</v>
       </c>
       <c r="T58" t="n">
-        <v>67.08489107381172</v>
+        <v>54.42675694756474</v>
       </c>
       <c r="U58" t="n">
-        <v>1.379500930284678</v>
+        <v>0.3507145739247619</v>
       </c>
       <c r="V58" t="n">
-        <v>0.09901616722799389</v>
+        <v>0.8078370918098461</v>
       </c>
       <c r="W58" t="b">
         <v>1</v>
@@ -4704,64 +4704,64 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>856.4722890513826</v>
+        <v>857.4402903576622</v>
       </c>
       <c r="D59" t="n">
-        <v>8.618206508851333</v>
+        <v>10.0511729032616</v>
       </c>
       <c r="E59" t="n">
-        <v>193.3351615894211</v>
+        <v>193.6996328017243</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9211325645446777</v>
+        <v>0.516746461391449</v>
       </c>
       <c r="G59" t="n">
-        <v>0.001672132988460362</v>
+        <v>0.001971905818209052</v>
       </c>
       <c r="H59" t="n">
-        <v>919.4282417771147</v>
+        <v>919.4282401253752</v>
       </c>
       <c r="I59" t="n">
-        <v>193.3351615894247</v>
+        <v>193.6997658941246</v>
       </c>
       <c r="J59" t="n">
-        <v>9.000337529229164</v>
+        <v>10.0511729032616</v>
       </c>
       <c r="K59" t="n">
-        <v>62.95595272573212</v>
+        <v>61.98794976771296</v>
       </c>
       <c r="L59" t="n">
-        <v>3.609557097661309e-12</v>
+        <v>0.0001330924002331813</v>
       </c>
       <c r="M59" t="n">
-        <v>0.3821310203778303</v>
+        <v>0</v>
       </c>
       <c r="N59" t="b">
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0.7454203963279724</v>
+        <v>0.6959951519966125</v>
       </c>
       <c r="P59" t="n">
-        <v>0.0006990937399677932</v>
+        <v>0.0004828143573831767</v>
       </c>
       <c r="Q59" t="n">
-        <v>930.329712043601</v>
+        <v>921.3330311054875</v>
       </c>
       <c r="R59" t="n">
-        <v>194.4189437576046</v>
+        <v>194.4069102079444</v>
       </c>
       <c r="S59" t="n">
-        <v>9.000641741783939</v>
+        <v>10.12046928659891</v>
       </c>
       <c r="T59" t="n">
-        <v>73.8574229922184</v>
+        <v>63.89274074782531</v>
       </c>
       <c r="U59" t="n">
-        <v>1.083782168183461</v>
+        <v>0.7072774062200722</v>
       </c>
       <c r="V59" t="n">
-        <v>0.3824352329326057</v>
+        <v>0.06929638333731347</v>
       </c>
       <c r="W59" t="b">
         <v>1</v>
@@ -4777,64 +4777,64 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>952.2225875059303</v>
+        <v>971.5369628931536</v>
       </c>
       <c r="D60" t="n">
-        <v>8.982060962729719</v>
+        <v>10.58970799778279</v>
       </c>
       <c r="E60" t="n">
-        <v>134.8889820198774</v>
+        <v>137.7143366682456</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9365533590316772</v>
+        <v>0.9041826725006104</v>
       </c>
       <c r="G60" t="n">
-        <v>0.007413487415760756</v>
+        <v>0.0168119240552187</v>
       </c>
       <c r="H60" t="n">
-        <v>929.2633953515734</v>
+        <v>971.2633245673884</v>
       </c>
       <c r="I60" t="n">
-        <v>173.6136086230761</v>
+        <v>164.2913669007378</v>
       </c>
       <c r="J60" t="n">
-        <v>9.232344420629534</v>
+        <v>10.58885070916368</v>
       </c>
       <c r="K60" t="n">
-        <v>22.95919215435686</v>
+        <v>0.2736383257652051</v>
       </c>
       <c r="L60" t="n">
-        <v>38.72462660319871</v>
+        <v>26.57703023249229</v>
       </c>
       <c r="M60" t="n">
-        <v>0.2502834578998154</v>
+        <v>0.0008572886191160478</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>0.9999988079071045</v>
+        <v>0.9995449185371399</v>
       </c>
       <c r="P60" t="n">
-        <v>0.003431547898799181</v>
+        <v>0.005703567061573267</v>
       </c>
       <c r="Q60" t="n">
-        <v>800.0000288101971</v>
+        <v>800.0000849724677</v>
       </c>
       <c r="R60" t="n">
-        <v>155.0156379021303</v>
+        <v>156.2690226856972</v>
       </c>
       <c r="S60" t="n">
-        <v>9.000641998095166</v>
+        <v>9.846628373946597</v>
       </c>
       <c r="T60" t="n">
-        <v>152.2225586957331</v>
+        <v>171.5368779206859</v>
       </c>
       <c r="U60" t="n">
-        <v>20.12665588225289</v>
+        <v>18.55468601745162</v>
       </c>
       <c r="V60" t="n">
-        <v>0.01858103536544675</v>
+        <v>0.7430796238361967</v>
       </c>
       <c r="W60" t="b">
         <v>1</v>
@@ -4846,68 +4846,68 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>921.8809467282865</v>
+        <v>994.1156538949632</v>
       </c>
       <c r="D61" t="n">
-        <v>10.09601292276444</v>
+        <v>5.130632828330791</v>
       </c>
       <c r="E61" t="n">
-        <v>132.0277192594506</v>
+        <v>204.8091508976131</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9341587424278259</v>
+        <v>0.8883886337280273</v>
       </c>
       <c r="G61" t="n">
-        <v>0.009299690835177898</v>
+        <v>0.001002088305540383</v>
       </c>
       <c r="H61" t="n">
-        <v>949.4790683064618</v>
+        <v>994.115653893045</v>
       </c>
       <c r="I61" t="n">
-        <v>164.2910901515149</v>
+        <v>204.8091508975887</v>
       </c>
       <c r="J61" t="n">
-        <v>10.21318288643995</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K61" t="n">
-        <v>27.59812157817532</v>
+        <v>1.918238012876827e-09</v>
       </c>
       <c r="L61" t="n">
-        <v>32.26337089206436</v>
+        <v>2.438582669128664e-11</v>
       </c>
       <c r="M61" t="n">
-        <v>0.1171699636755061</v>
+        <v>3.870008951531371</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>0.9999994039535522</v>
+        <v>0.98008793592453</v>
       </c>
       <c r="P61" t="n">
-        <v>0.004358210135251284</v>
+        <v>0.0002450481115374714</v>
       </c>
       <c r="Q61" t="n">
-        <v>800.0000263267774</v>
+        <v>977.1921363602071</v>
       </c>
       <c r="R61" t="n">
-        <v>156.5498345696142</v>
+        <v>204.7237888816042</v>
       </c>
       <c r="S61" t="n">
-        <v>9.660706272486324</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T61" t="n">
-        <v>121.8809204015091</v>
+        <v>16.92351753475612</v>
       </c>
       <c r="U61" t="n">
-        <v>24.5221153101636</v>
+        <v>0.08536201600887239</v>
       </c>
       <c r="V61" t="n">
-        <v>0.4353066502781147</v>
+        <v>3.870008951531371</v>
       </c>
       <c r="W61" t="b">
         <v>1</v>
@@ -4919,68 +4919,68 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>936.5075895128662</v>
+        <v>843.2242537188664</v>
       </c>
       <c r="D62" t="n">
-        <v>10.61556857993143</v>
+        <v>9.857427139480592</v>
       </c>
       <c r="E62" t="n">
-        <v>123.2569631234545</v>
+        <v>195.2329477018448</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9367098808288574</v>
+        <v>0.5352276563644409</v>
       </c>
       <c r="G62" t="n">
-        <v>0.008770139887928963</v>
+        <v>0.002033084630966187</v>
       </c>
       <c r="H62" t="n">
-        <v>961.9642386131758</v>
+        <v>919.4282525630487</v>
       </c>
       <c r="I62" t="n">
-        <v>164.2946796752816</v>
+        <v>195.2329474754656</v>
       </c>
       <c r="J62" t="n">
-        <v>10.61556946151251</v>
+        <v>9.857427139480594</v>
       </c>
       <c r="K62" t="n">
-        <v>25.45664910030962</v>
+        <v>76.20399884418225</v>
       </c>
       <c r="L62" t="n">
-        <v>41.03771655182712</v>
+        <v>2.263791998302622e-07</v>
       </c>
       <c r="M62" t="n">
-        <v>8.815810748075137e-07</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>1</v>
+        <v>0.7889383435249329</v>
       </c>
       <c r="P62" t="n">
-        <v>0.006687334273010492</v>
+        <v>0.0005952381179668009</v>
       </c>
       <c r="Q62" t="n">
-        <v>800.0000371340137</v>
+        <v>921.3012915559344</v>
       </c>
       <c r="R62" t="n">
-        <v>156.1514644887971</v>
+        <v>195.9925667719498</v>
       </c>
       <c r="S62" t="n">
-        <v>9.989012907460575</v>
+        <v>9.944844047513044</v>
       </c>
       <c r="T62" t="n">
-        <v>136.5075523788524</v>
+        <v>78.07703783706802</v>
       </c>
       <c r="U62" t="n">
-        <v>32.89450136534256</v>
+        <v>0.7596190701049466</v>
       </c>
       <c r="V62" t="n">
-        <v>0.6265556724708556</v>
+        <v>0.08741690803245206</v>
       </c>
       <c r="W62" t="b">
         <v>1</v>
@@ -4992,68 +4992,68 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>937.1020828271132</v>
+        <v>876.8033910623137</v>
       </c>
       <c r="D63" t="n">
-        <v>9.457147352903927</v>
+        <v>8.170535320686376</v>
       </c>
       <c r="E63" t="n">
-        <v>133.4013110152258</v>
+        <v>209.1884006414471</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9357374310493469</v>
+        <v>0.7446001172065735</v>
       </c>
       <c r="G63" t="n">
-        <v>0.006667737383395433</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H63" t="n">
-        <v>922.3136985527285</v>
+        <v>933.0453149342344</v>
       </c>
       <c r="I63" t="n">
-        <v>173.6136088670399</v>
+        <v>209.1884006414472</v>
       </c>
       <c r="J63" t="n">
-        <v>10.17656754540036</v>
+        <v>9.000641749277776</v>
       </c>
       <c r="K63" t="n">
-        <v>14.78838427438473</v>
+        <v>56.24192387192068</v>
       </c>
       <c r="L63" t="n">
-        <v>40.21229785181416</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M63" t="n">
-        <v>0.719420192496429</v>
+        <v>0.8301064285913995</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0.9999992847442627</v>
+        <v>0.9081918001174927</v>
       </c>
       <c r="P63" t="n">
-        <v>0.00386183662340045</v>
+        <v>0.0004345132037997246</v>
       </c>
       <c r="Q63" t="n">
-        <v>800.0000441129705</v>
+        <v>931.913776584382</v>
       </c>
       <c r="R63" t="n">
-        <v>154.7658806082032</v>
+        <v>208.7142223390433</v>
       </c>
       <c r="S63" t="n">
-        <v>9.031790010078778</v>
+        <v>9.0006416738313</v>
       </c>
       <c r="T63" t="n">
-        <v>137.1020387141427</v>
+        <v>55.11038552206833</v>
       </c>
       <c r="U63" t="n">
-        <v>21.3645695929774</v>
+        <v>0.4741783024038853</v>
       </c>
       <c r="V63" t="n">
-        <v>0.4253573428251496</v>
+        <v>0.8301063531449238</v>
       </c>
       <c r="W63" t="b">
         <v>1</v>
@@ -5065,68 +5065,68 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>938.1528808869589</v>
+        <v>929.8197953783028</v>
       </c>
       <c r="D64" t="n">
-        <v>9.522277446844168</v>
+        <v>6.000780914534034</v>
       </c>
       <c r="E64" t="n">
-        <v>153.3143187245932</v>
+        <v>191.293101093024</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9361411333084106</v>
+        <v>0.8721053600311279</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0004814314306713641</v>
+        <v>0.001007982064038515</v>
       </c>
       <c r="H64" t="n">
-        <v>938.1543951074055</v>
+        <v>929.8197953794917</v>
       </c>
       <c r="I64" t="n">
-        <v>176.1296280903845</v>
+        <v>191.293101093024</v>
       </c>
       <c r="J64" t="n">
-        <v>9.522277446844166</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K64" t="n">
-        <v>0.001514220446665604</v>
+        <v>1.188823262054939e-09</v>
       </c>
       <c r="L64" t="n">
-        <v>22.81530936579125</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M64" t="n">
-        <v>1.77635683940025e-15</v>
+        <v>2.999860865328128</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>0.9987419247627258</v>
+        <v>0.7787668108940125</v>
       </c>
       <c r="P64" t="n">
-        <v>0.001245645340532064</v>
+        <v>0.0001237320830114186</v>
       </c>
       <c r="Q64" t="n">
-        <v>807.6659300832602</v>
+        <v>932.4721316810803</v>
       </c>
       <c r="R64" t="n">
-        <v>162.4883681177157</v>
+        <v>191.6845267373567</v>
       </c>
       <c r="S64" t="n">
-        <v>9.430640501271011</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T64" t="n">
-        <v>130.4869508036987</v>
+        <v>2.652336302777485</v>
       </c>
       <c r="U64" t="n">
-        <v>9.174049393122431</v>
+        <v>0.3914256443326849</v>
       </c>
       <c r="V64" t="n">
-        <v>0.09163694557315694</v>
+        <v>2.999860865328128</v>
       </c>
       <c r="W64" t="b">
         <v>1</v>
@@ -5142,64 +5142,64 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>952.731947911775</v>
+        <v>978.2805827112397</v>
       </c>
       <c r="D65" t="n">
-        <v>10.24171237566759</v>
+        <v>10.72423713873273</v>
       </c>
       <c r="E65" t="n">
-        <v>133.4683090236713</v>
+        <v>160.7661531054825</v>
       </c>
       <c r="F65" t="n">
-        <v>0.936724841594696</v>
+        <v>0.9041489362716675</v>
       </c>
       <c r="G65" t="n">
-        <v>0.007099774666130543</v>
+        <v>0.001028560451231897</v>
       </c>
       <c r="H65" t="n">
-        <v>909.4379273278954</v>
+        <v>978.286516615565</v>
       </c>
       <c r="I65" t="n">
-        <v>165.346713547775</v>
+        <v>176.130051055941</v>
       </c>
       <c r="J65" t="n">
-        <v>10.61256887190718</v>
+        <v>10.72426807302894</v>
       </c>
       <c r="K65" t="n">
-        <v>43.29402058387961</v>
+        <v>0.005933904325274852</v>
       </c>
       <c r="L65" t="n">
-        <v>31.87840452410364</v>
+        <v>15.36389795045844</v>
       </c>
       <c r="M65" t="n">
-        <v>0.3708564962395879</v>
+        <v>3.093429621614519e-05</v>
       </c>
       <c r="N65" t="b">
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>0.9999992847442627</v>
+        <v>0.7500676512718201</v>
       </c>
       <c r="P65" t="n">
-        <v>0.004129878710955381</v>
+        <v>0.002602088497951627</v>
       </c>
       <c r="Q65" t="n">
-        <v>800.0000313160459</v>
+        <v>831.2155293829998</v>
       </c>
       <c r="R65" t="n">
-        <v>157.2709049961554</v>
+        <v>173.906238417989</v>
       </c>
       <c r="S65" t="n">
-        <v>9.851394610548327</v>
+        <v>10.47967825555682</v>
       </c>
       <c r="T65" t="n">
-        <v>152.7319165957291</v>
+        <v>147.06505332824</v>
       </c>
       <c r="U65" t="n">
-        <v>23.80259597248406</v>
+        <v>13.14008531250641</v>
       </c>
       <c r="V65" t="n">
-        <v>0.3903177651192653</v>
+        <v>0.2445588831759054</v>
       </c>
       <c r="W65" t="b">
         <v>1</v>
@@ -5211,68 +5211,68 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>848.8662607676159</v>
+        <v>985.9822307898403</v>
       </c>
       <c r="D66" t="n">
-        <v>9.303277940532087</v>
+        <v>6.311976211576789</v>
       </c>
       <c r="E66" t="n">
-        <v>205.1944430344406</v>
+        <v>187.9596397528457</v>
       </c>
       <c r="F66" t="n">
-        <v>0.8402423858642578</v>
+        <v>0.89444899559021</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0008212371612899005</v>
+        <v>0.00100928673055023</v>
       </c>
       <c r="H66" t="n">
-        <v>933.0453214022597</v>
+        <v>985.9823009650738</v>
       </c>
       <c r="I66" t="n">
-        <v>205.1944430344406</v>
+        <v>187.9596259850493</v>
       </c>
       <c r="J66" t="n">
-        <v>9.303277940532084</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K66" t="n">
-        <v>84.17906063464375</v>
+        <v>7.017523353169963e-05</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.37677964175964e-05</v>
       </c>
       <c r="M66" t="n">
-        <v>3.552713678800501e-15</v>
+        <v>2.688665568285373</v>
       </c>
       <c r="N66" t="b">
         <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>0.5697894096374512</v>
+        <v>0.8084630966186523</v>
       </c>
       <c r="P66" t="n">
-        <v>0.000677684205584228</v>
+        <v>0.0002948164474219084</v>
       </c>
       <c r="Q66" t="n">
-        <v>925.1630750318811</v>
+        <v>971.8504073656826</v>
       </c>
       <c r="R66" t="n">
-        <v>205.5374799478248</v>
+        <v>188.7730732314516</v>
       </c>
       <c r="S66" t="n">
-        <v>9.393854690845984</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T66" t="n">
-        <v>76.29681426426521</v>
+        <v>14.13182342415769</v>
       </c>
       <c r="U66" t="n">
-        <v>0.3430369133842817</v>
+        <v>0.8134334786059014</v>
       </c>
       <c r="V66" t="n">
-        <v>0.09057675031389678</v>
+        <v>2.688665568285373</v>
       </c>
       <c r="W66" t="b">
         <v>1</v>
@@ -5284,68 +5284,68 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>957.2734529567797</v>
+        <v>960.6999207074333</v>
       </c>
       <c r="D67" t="n">
-        <v>4.155185467070856</v>
+        <v>13.60431810949872</v>
       </c>
       <c r="E67" t="n">
-        <v>200.7057822251266</v>
+        <v>210.2668897524188</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9316644668579102</v>
+        <v>0.808692991733551</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0005017013754695654</v>
+        <v>0.0006025993498042226</v>
       </c>
       <c r="H67" t="n">
-        <v>957.2734529568208</v>
+        <v>960.6999209343498</v>
       </c>
       <c r="I67" t="n">
-        <v>200.7057822251264</v>
+        <v>210.2668897524188</v>
       </c>
       <c r="J67" t="n">
-        <v>9.000641779862162</v>
+        <v>11.8218186911064</v>
       </c>
       <c r="K67" t="n">
-        <v>4.1154635255225e-11</v>
+        <v>2.269165406687534e-07</v>
       </c>
       <c r="L67" t="n">
-        <v>1.989519660128281e-13</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>4.845456312791306</v>
+        <v>1.782499418392316</v>
       </c>
       <c r="N67" t="b">
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>0.9973123073577881</v>
+        <v>0.6865601539611816</v>
       </c>
       <c r="P67" t="n">
-        <v>3.975718573201448e-05</v>
+        <v>0.002614962868392467</v>
       </c>
       <c r="Q67" t="n">
-        <v>956.7213574636606</v>
+        <v>823.3017663542978</v>
       </c>
       <c r="R67" t="n">
-        <v>200.7704591606353</v>
+        <v>211.1980452289216</v>
       </c>
       <c r="S67" t="n">
-        <v>9.000641779862162</v>
+        <v>12.79677363301607</v>
       </c>
       <c r="T67" t="n">
-        <v>0.5520954931190545</v>
+        <v>137.3981543531355</v>
       </c>
       <c r="U67" t="n">
-        <v>0.06467693550871445</v>
+        <v>0.9311554765027381</v>
       </c>
       <c r="V67" t="n">
-        <v>4.845456312791306</v>
+        <v>0.8075444764826507</v>
       </c>
       <c r="W67" t="b">
         <v>1</v>
@@ -5357,68 +5357,68 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>878.5936264077441</v>
+        <v>958.9557390280952</v>
       </c>
       <c r="D68" t="n">
-        <v>8.921512208203685</v>
+        <v>14.00468254643085</v>
       </c>
       <c r="E68" t="n">
-        <v>211.4861040096172</v>
+        <v>201.8530725115117</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6340576410293579</v>
+        <v>0.808692991733551</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0009918330470100045</v>
+        <v>0.0006025993498042226</v>
       </c>
       <c r="H68" t="n">
-        <v>919.4282414150917</v>
+        <v>958.955739282253</v>
       </c>
       <c r="I68" t="n">
-        <v>211.4861033783361</v>
+        <v>201.8530725115117</v>
       </c>
       <c r="J68" t="n">
-        <v>9.328733482464639</v>
+        <v>11.82181859823</v>
       </c>
       <c r="K68" t="n">
-        <v>40.83461500734768</v>
+        <v>2.541578396630939e-07</v>
       </c>
       <c r="L68" t="n">
-        <v>6.312811819952913e-07</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0.4072212742609533</v>
+        <v>2.182863948200851</v>
       </c>
       <c r="N68" t="b">
         <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>0.4796126186847687</v>
+        <v>0.9163044691085815</v>
       </c>
       <c r="P68" t="n">
-        <v>0.0004923328524455428</v>
+        <v>0.002945144427940249</v>
       </c>
       <c r="Q68" t="n">
-        <v>931.9918298244547</v>
+        <v>815.0120327863149</v>
       </c>
       <c r="R68" t="n">
-        <v>211.1082232637067</v>
+        <v>204.3746510337279</v>
       </c>
       <c r="S68" t="n">
-        <v>9.003863754075047</v>
+        <v>13.08705758989309</v>
       </c>
       <c r="T68" t="n">
-        <v>53.39820341671066</v>
+        <v>143.9437062417803</v>
       </c>
       <c r="U68" t="n">
-        <v>0.3778807459105735</v>
+        <v>2.521578522216174</v>
       </c>
       <c r="V68" t="n">
-        <v>0.08235154587136151</v>
+        <v>0.9176249565377681</v>
       </c>
       <c r="W68" t="b">
         <v>1</v>
@@ -5434,64 +5434,64 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>960.3160877562763</v>
+        <v>934.5079730422938</v>
       </c>
       <c r="D69" t="n">
-        <v>11.53288740219859</v>
+        <v>11.10399410569217</v>
       </c>
       <c r="E69" t="n">
-        <v>127.4000134727045</v>
+        <v>123.3863151689311</v>
       </c>
       <c r="F69" t="n">
-        <v>0.9366707801818848</v>
+        <v>0.9066013097763062</v>
       </c>
       <c r="G69" t="n">
-        <v>0.008770139887928963</v>
+        <v>0.005423417314887047</v>
       </c>
       <c r="H69" t="n">
-        <v>961.9634948669038</v>
+        <v>945.815868889224</v>
       </c>
       <c r="I69" t="n">
-        <v>164.2914193736947</v>
+        <v>173.6140089857064</v>
       </c>
       <c r="J69" t="n">
-        <v>11.53288740219861</v>
+        <v>11.10399430358096</v>
       </c>
       <c r="K69" t="n">
-        <v>1.647407110627569</v>
+        <v>11.30789584693025</v>
       </c>
       <c r="L69" t="n">
-        <v>36.89140590099012</v>
+        <v>50.22769381677537</v>
       </c>
       <c r="M69" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>1.978887862463807e-07</v>
       </c>
       <c r="N69" t="b">
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>0.9999998807907104</v>
+        <v>0.9999405145645142</v>
       </c>
       <c r="P69" t="n">
-        <v>0.00587997492402792</v>
+        <v>0.01122257206588984</v>
       </c>
       <c r="Q69" t="n">
-        <v>800.0000564158436</v>
+        <v>800.0000000759403</v>
       </c>
       <c r="R69" t="n">
-        <v>158.8016989772121</v>
+        <v>151.2606678279526</v>
       </c>
       <c r="S69" t="n">
-        <v>11.18470988119274</v>
+        <v>9.694884576499641</v>
       </c>
       <c r="T69" t="n">
-        <v>160.3160313404327</v>
+        <v>134.5079729663535</v>
       </c>
       <c r="U69" t="n">
-        <v>31.40168550450761</v>
+        <v>27.87435265902153</v>
       </c>
       <c r="V69" t="n">
-        <v>0.3481775210058551</v>
+        <v>1.409109529192529</v>
       </c>
       <c r="W69" t="b">
         <v>1</v>
@@ -5503,68 +5503,68 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>975.3332250639683</v>
+        <v>898.1808237942174</v>
       </c>
       <c r="D70" t="n">
-        <v>15.61534603848897</v>
+        <v>7.158907973127043</v>
       </c>
       <c r="E70" t="n">
-        <v>210.7024584419487</v>
+        <v>201.5385972936553</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9138248562812805</v>
+        <v>0.6930186748504639</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0008986954926513135</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H70" t="n">
-        <v>951.442885646785</v>
+        <v>933.0453176152432</v>
       </c>
       <c r="I70" t="n">
-        <v>210.7023761633751</v>
+        <v>201.5385972936552</v>
       </c>
       <c r="J70" t="n">
-        <v>12.18355467952391</v>
+        <v>9.000641564714643</v>
       </c>
       <c r="K70" t="n">
-        <v>23.89033941718321</v>
+        <v>34.8644938210258</v>
       </c>
       <c r="L70" t="n">
-        <v>8.227857367160141e-05</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M70" t="n">
-        <v>3.431791358965063</v>
+        <v>1.8417335915876</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>0.9992037415504456</v>
+        <v>0.7245321869850159</v>
       </c>
       <c r="P70" t="n">
-        <v>0.003223470412194729</v>
+        <v>0.0002733006549533457</v>
       </c>
       <c r="Q70" t="n">
-        <v>800.0000360733081</v>
+        <v>934.4237000770559</v>
       </c>
       <c r="R70" t="n">
-        <v>209.805788225996</v>
+        <v>201.6922972534761</v>
       </c>
       <c r="S70" t="n">
-        <v>13.6250882361084</v>
+        <v>9.000641812212503</v>
       </c>
       <c r="T70" t="n">
-        <v>175.3331889906601</v>
+        <v>36.24287628283844</v>
       </c>
       <c r="U70" t="n">
-        <v>0.8966702159527529</v>
+        <v>0.1536999598208411</v>
       </c>
       <c r="V70" t="n">
-        <v>1.990257802380572</v>
+        <v>1.84173383908546</v>
       </c>
       <c r="W70" t="b">
         <v>1</v>
@@ -5580,64 +5580,64 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>949.7831932054952</v>
+        <v>955.1753961048785</v>
       </c>
       <c r="D71" t="n">
-        <v>5.360848171565396</v>
+        <v>4.45135698723502</v>
       </c>
       <c r="E71" t="n">
-        <v>199.3387355217609</v>
+        <v>202.6339143433278</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9301205277442932</v>
+        <v>0.9024239182472229</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0005017773364670575</v>
+        <v>0.001009692437946796</v>
       </c>
       <c r="H71" t="n">
-        <v>949.783193205518</v>
+        <v>955.1753961048713</v>
       </c>
       <c r="I71" t="n">
-        <v>199.3387355217609</v>
+        <v>202.6339143433277</v>
       </c>
       <c r="J71" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="K71" t="n">
-        <v>2.285105438204482e-11</v>
+        <v>7.16227077646181e-12</v>
       </c>
       <c r="L71" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="M71" t="n">
-        <v>3.639793608296766</v>
+        <v>4.549284792627142</v>
       </c>
       <c r="N71" t="b">
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>0.9113386273384094</v>
+        <v>0.9968396425247192</v>
       </c>
       <c r="P71" t="n">
-        <v>3.956037471652962e-05</v>
+        <v>7.074128370732069e-05</v>
       </c>
       <c r="Q71" t="n">
-        <v>949.9166917557488</v>
+        <v>953.4234917160812</v>
       </c>
       <c r="R71" t="n">
-        <v>199.3476842624615</v>
+        <v>202.6491852020652</v>
       </c>
       <c r="S71" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="T71" t="n">
-        <v>0.1334985502536483</v>
+        <v>1.751904388797243</v>
       </c>
       <c r="U71" t="n">
-        <v>0.008948740700617464</v>
+        <v>0.01527085873738088</v>
       </c>
       <c r="V71" t="n">
-        <v>3.639793608296766</v>
+        <v>4.549284792627142</v>
       </c>
       <c r="W71" t="b">
         <v>1</v>
@@ -5649,68 +5649,68 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>859.049721060047</v>
+        <v>965.5247197696567</v>
       </c>
       <c r="D72" t="n">
-        <v>9.20155298729558</v>
+        <v>14.11893637093065</v>
       </c>
       <c r="E72" t="n">
-        <v>189.0584905356224</v>
+        <v>185.5322626065073</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7010003924369812</v>
+        <v>0.7510432004928589</v>
       </c>
       <c r="G72" t="n">
-        <v>0.001017419970594347</v>
+        <v>0.0006025993498042226</v>
       </c>
       <c r="H72" t="n">
-        <v>919.4282385861036</v>
+        <v>965.5243626629821</v>
       </c>
       <c r="I72" t="n">
-        <v>189.0584905356224</v>
+        <v>185.5322626065075</v>
       </c>
       <c r="J72" t="n">
-        <v>9.32888373758998</v>
+        <v>11.82181869298677</v>
       </c>
       <c r="K72" t="n">
-        <v>60.37851752605661</v>
+        <v>0.0003571066746417273</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.70530256582424e-13</v>
       </c>
       <c r="M72" t="n">
-        <v>0.1273307502943997</v>
+        <v>2.297117677943881</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
       </c>
       <c r="O72" t="n">
-        <v>0.5660150647163391</v>
+        <v>0.9097729921340942</v>
       </c>
       <c r="P72" t="n">
-        <v>0.0006031086086295545</v>
+        <v>0.003439165186136961</v>
       </c>
       <c r="Q72" t="n">
-        <v>928.4998907770305</v>
+        <v>810.1024239623029</v>
       </c>
       <c r="R72" t="n">
-        <v>189.8645660831946</v>
+        <v>189.8320510991121</v>
       </c>
       <c r="S72" t="n">
-        <v>9.298330737299311</v>
+        <v>13.07139598362592</v>
       </c>
       <c r="T72" t="n">
-        <v>69.45016971698351</v>
+        <v>155.4222958073539</v>
       </c>
       <c r="U72" t="n">
-        <v>0.8060755475721919</v>
+        <v>4.29978849260479</v>
       </c>
       <c r="V72" t="n">
-        <v>0.09677775000373146</v>
+        <v>1.047540387304728</v>
       </c>
       <c r="W72" t="b">
         <v>1</v>
@@ -5722,68 +5722,68 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>871.376215413518</v>
+        <v>938.0410907075174</v>
       </c>
       <c r="D73" t="n">
-        <v>7.926433919294807</v>
+        <v>6.182956613823269</v>
       </c>
       <c r="E73" t="n">
-        <v>179.6327752373482</v>
+        <v>210.3731746953267</v>
       </c>
       <c r="F73" t="n">
-        <v>0.7732902765274048</v>
+        <v>0.8901363015174866</v>
       </c>
       <c r="G73" t="n">
-        <v>0.001843692734837532</v>
+        <v>0.001009692437946796</v>
       </c>
       <c r="H73" t="n">
-        <v>918.8325215337015</v>
+        <v>938.0410907074877</v>
       </c>
       <c r="I73" t="n">
-        <v>179.6327676548619</v>
+        <v>210.3731746953268</v>
       </c>
       <c r="J73" t="n">
-        <v>9.000615219003098</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K73" t="n">
-        <v>47.45630612018351</v>
+        <v>2.967226464534178e-11</v>
       </c>
       <c r="L73" t="n">
-        <v>7.582486233559393e-06</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M73" t="n">
-        <v>1.074181299708291</v>
+        <v>2.817685166038894</v>
       </c>
       <c r="N73" t="b">
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>0.8805047273635864</v>
+        <v>0.7319839596748352</v>
       </c>
       <c r="P73" t="n">
-        <v>0.0006936352583579719</v>
+        <v>7.256054959725589e-05</v>
       </c>
       <c r="Q73" t="n">
-        <v>933.1540303255215</v>
+        <v>938.5659989505303</v>
       </c>
       <c r="R73" t="n">
-        <v>181.2461943694394</v>
+        <v>210.2305950568462</v>
       </c>
       <c r="S73" t="n">
-        <v>9.000640905190261</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T73" t="n">
-        <v>61.77781491200346</v>
+        <v>0.5249082430129874</v>
       </c>
       <c r="U73" t="n">
-        <v>1.613419132091252</v>
+        <v>0.1425796384804983</v>
       </c>
       <c r="V73" t="n">
-        <v>1.074206985895454</v>
+        <v>2.817685166038894</v>
       </c>
       <c r="W73" t="b">
         <v>1</v>
@@ -5795,68 +5795,68 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>931.4457141543127</v>
+        <v>919.2332883952536</v>
       </c>
       <c r="D74" t="n">
-        <v>5.966615046177687</v>
+        <v>8.409170461064056</v>
       </c>
       <c r="E74" t="n">
-        <v>195.8168760577822</v>
+        <v>152.3051255060128</v>
       </c>
       <c r="F74" t="n">
-        <v>0.9244334697723389</v>
+        <v>0.8928853869438171</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0005017755320295691</v>
+        <v>0.001026143436320126</v>
       </c>
       <c r="H74" t="n">
-        <v>935.6639931132505</v>
+        <v>919.2394190784231</v>
       </c>
       <c r="I74" t="n">
-        <v>195.8168760577822</v>
+        <v>176.1296280276241</v>
       </c>
       <c r="J74" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000260210710346</v>
       </c>
       <c r="K74" t="n">
-        <v>4.218278958937844</v>
+        <v>0.006130683169544682</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>23.82450252161132</v>
       </c>
       <c r="M74" t="n">
-        <v>3.034026733684476</v>
+        <v>0.5910897496462901</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0.560565173625946</v>
+        <v>0.9610162377357483</v>
       </c>
       <c r="P74" t="n">
-        <v>6.196981848916039e-05</v>
+        <v>0.002215735614299774</v>
       </c>
       <c r="Q74" t="n">
-        <v>931.4395549368886</v>
+        <v>814.0699568674833</v>
       </c>
       <c r="R74" t="n">
-        <v>195.9970530213007</v>
+        <v>161.2473461306475</v>
       </c>
       <c r="S74" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641810543284</v>
       </c>
       <c r="T74" t="n">
-        <v>0.006159217424055896</v>
+        <v>105.1633315277703</v>
       </c>
       <c r="U74" t="n">
-        <v>0.1801769635185053</v>
+        <v>8.942220624634757</v>
       </c>
       <c r="V74" t="n">
-        <v>3.034026733684476</v>
+        <v>0.5914713494792281</v>
       </c>
       <c r="W74" t="b">
         <v>1</v>
@@ -5868,68 +5868,68 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>830.2144726175446</v>
+        <v>959.1442612738502</v>
       </c>
       <c r="D75" t="n">
-        <v>8.828976256445142</v>
+        <v>12.04133438956063</v>
       </c>
       <c r="E75" t="n">
-        <v>198.3914538010805</v>
+        <v>127.0493257167431</v>
       </c>
       <c r="F75" t="n">
-        <v>0.8605555891990662</v>
+        <v>0.8992465734481812</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0009911501547321677</v>
+        <v>0.005398744251579046</v>
       </c>
       <c r="H75" t="n">
-        <v>919.4282408027589</v>
+        <v>959.1442612738585</v>
       </c>
       <c r="I75" t="n">
-        <v>198.3914538010775</v>
+        <v>173.6137580462745</v>
       </c>
       <c r="J75" t="n">
-        <v>9.328581997462527</v>
+        <v>12.04133438956064</v>
       </c>
       <c r="K75" t="n">
-        <v>89.21376818521424</v>
+        <v>8.29913915367797e-12</v>
       </c>
       <c r="L75" t="n">
-        <v>2.955857780762017e-12</v>
+        <v>46.56443232953136</v>
       </c>
       <c r="M75" t="n">
-        <v>0.4996057410173851</v>
+        <v>5.329070518200751e-15</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>0.7414771914482117</v>
+        <v>0.9996368885040283</v>
       </c>
       <c r="P75" t="n">
-        <v>0.0009387387544848025</v>
+        <v>0.01029244158416986</v>
       </c>
       <c r="Q75" t="n">
-        <v>927.6206414360383</v>
+        <v>800.0000197778818</v>
       </c>
       <c r="R75" t="n">
-        <v>199.0854529998045</v>
+        <v>155.444514288579</v>
       </c>
       <c r="S75" t="n">
-        <v>9.000625542269841</v>
+        <v>10.35308057308538</v>
       </c>
       <c r="T75" t="n">
-        <v>97.40616881849371</v>
+        <v>159.1442414959685</v>
       </c>
       <c r="U75" t="n">
-        <v>0.6939991987240148</v>
+        <v>28.39518857183587</v>
       </c>
       <c r="V75" t="n">
-        <v>0.1716492858246994</v>
+        <v>1.688253816475246</v>
       </c>
       <c r="W75" t="b">
         <v>1</v>
@@ -5945,64 +5945,64 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>858.8247965039768</v>
+        <v>850.3245848097874</v>
       </c>
       <c r="D76" t="n">
-        <v>7.545357578691671</v>
+        <v>6.753786323906015</v>
       </c>
       <c r="E76" t="n">
-        <v>207.8025841162732</v>
+        <v>178.6721191470512</v>
       </c>
       <c r="F76" t="n">
-        <v>0.9208168983459473</v>
+        <v>0.8777484893798828</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0009904649341478944</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H76" t="n">
-        <v>933.0455648964845</v>
+        <v>933.0453193863964</v>
       </c>
       <c r="I76" t="n">
-        <v>207.802584116224</v>
+        <v>178.6721191470512</v>
       </c>
       <c r="J76" t="n">
-        <v>9.000792238411469</v>
+        <v>9.000641529070483</v>
       </c>
       <c r="K76" t="n">
-        <v>74.22076839250769</v>
+        <v>82.72073457660895</v>
       </c>
       <c r="L76" t="n">
-        <v>4.914113560516853e-11</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M76" t="n">
-        <v>1.455434659719798</v>
+        <v>2.246855205164469</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>0.9375021457672119</v>
+        <v>0.9901487827301025</v>
       </c>
       <c r="P76" t="n">
-        <v>0.0006701329839415848</v>
+        <v>0.0008922269917093217</v>
       </c>
       <c r="Q76" t="n">
-        <v>929.5857897239175</v>
+        <v>936.1392340187068</v>
       </c>
       <c r="R76" t="n">
-        <v>207.5299022253909</v>
+        <v>182.0576574607934</v>
       </c>
       <c r="S76" t="n">
-        <v>9.000641753803901</v>
+        <v>9.000638657114816</v>
       </c>
       <c r="T76" t="n">
-        <v>70.7609932199407</v>
+        <v>85.81464920891938</v>
       </c>
       <c r="U76" t="n">
-        <v>0.2726818908822679</v>
+        <v>3.385538313742131</v>
       </c>
       <c r="V76" t="n">
-        <v>1.45528417511223</v>
+        <v>2.246852333208802</v>
       </c>
       <c r="W76" t="b">
         <v>1</v>
@@ -6014,68 +6014,68 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1033.421152192183</v>
+        <v>955.8201925449489</v>
       </c>
       <c r="D77" t="n">
-        <v>9.659614894708168</v>
+        <v>9.394153645796282</v>
       </c>
       <c r="E77" t="n">
-        <v>187.7384288079069</v>
+        <v>147.706171563257</v>
       </c>
       <c r="F77" t="n">
-        <v>0.8256695866584778</v>
+        <v>0.9065464735031128</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0003771110787056386</v>
+        <v>0.001030099927447736</v>
       </c>
       <c r="H77" t="n">
-        <v>986.681296161195</v>
+        <v>955.8194453666717</v>
       </c>
       <c r="I77" t="n">
-        <v>187.7384288079069</v>
+        <v>176.1300441983605</v>
       </c>
       <c r="J77" t="n">
-        <v>9.659614862268491</v>
+        <v>9.394163106950252</v>
       </c>
       <c r="K77" t="n">
-        <v>46.73985603098845</v>
+        <v>0.000747178277151761</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>28.42387263510344</v>
       </c>
       <c r="M77" t="n">
-        <v>3.243967761079602e-08</v>
+        <v>9.461153970491409e-06</v>
       </c>
       <c r="N77" t="b">
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0.9524146318435669</v>
+        <v>0.9986504912376404</v>
       </c>
       <c r="P77" t="n">
-        <v>0.0003148202667944133</v>
+        <v>0.002817480592057109</v>
       </c>
       <c r="Q77" t="n">
-        <v>973.0624369005177</v>
+        <v>807.3892955176485</v>
       </c>
       <c r="R77" t="n">
-        <v>188.4506913878029</v>
+        <v>158.5080442101335</v>
       </c>
       <c r="S77" t="n">
-        <v>9.648103466181166</v>
+        <v>9.129250964530206</v>
       </c>
       <c r="T77" t="n">
-        <v>60.3587152916657</v>
+        <v>148.4308970273004</v>
       </c>
       <c r="U77" t="n">
-        <v>0.71226257989602</v>
+        <v>10.80187264687649</v>
       </c>
       <c r="V77" t="n">
-        <v>0.01151142852700282</v>
+        <v>0.2649026812660757</v>
       </c>
       <c r="W77" t="b">
         <v>1</v>
@@ -6087,68 +6087,68 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>955.8201925449489</v>
+        <v>951.2473896040931</v>
       </c>
       <c r="D78" t="n">
-        <v>9.394153645796282</v>
+        <v>4.084940245326943</v>
       </c>
       <c r="E78" t="n">
-        <v>147.706171563257</v>
+        <v>197.0422059273024</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9357934594154358</v>
+        <v>0.9024239182472229</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0004813481937162578</v>
+        <v>0.001009692437946796</v>
       </c>
       <c r="H78" t="n">
-        <v>955.8238816211176</v>
+        <v>951.2473896040889</v>
       </c>
       <c r="I78" t="n">
-        <v>176.1296297734542</v>
+        <v>197.0422059273024</v>
       </c>
       <c r="J78" t="n">
-        <v>9.394152686610232</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K78" t="n">
-        <v>0.003689076168711836</v>
+        <v>4.206412995699793e-12</v>
       </c>
       <c r="L78" t="n">
-        <v>28.42345821019714</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M78" t="n">
-        <v>9.591860496982463e-07</v>
+        <v>4.915701534535219</v>
       </c>
       <c r="N78" t="b">
         <v>1</v>
       </c>
       <c r="O78" t="n">
-        <v>0.9998502731323242</v>
+        <v>0.9975175857543945</v>
       </c>
       <c r="P78" t="n">
-        <v>0.001525965635664761</v>
+        <v>7.62157142162323e-05</v>
       </c>
       <c r="Q78" t="n">
-        <v>800.0005421327032</v>
+        <v>950.1206732791601</v>
       </c>
       <c r="R78" t="n">
-        <v>158.4272295515852</v>
+        <v>197.1874498366921</v>
       </c>
       <c r="S78" t="n">
-        <v>9.241181016988612</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T78" t="n">
-        <v>155.8196504122457</v>
+        <v>1.126716324933</v>
       </c>
       <c r="U78" t="n">
-        <v>10.72105798832811</v>
+        <v>0.1452439093896203</v>
       </c>
       <c r="V78" t="n">
-        <v>0.1529726288076692</v>
+        <v>4.915701534535219</v>
       </c>
       <c r="W78" t="b">
         <v>1</v>
@@ -6160,68 +6160,68 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>960.1629618523173</v>
+        <v>925.1740145451809</v>
       </c>
       <c r="D79" t="n">
-        <v>7.987831876099619</v>
+        <v>16.94827947591534</v>
       </c>
       <c r="E79" t="n">
-        <v>120.38691645617</v>
+        <v>201.3815745203189</v>
       </c>
       <c r="F79" t="n">
-        <v>0.9136694073677063</v>
+        <v>0.8084505796432495</v>
       </c>
       <c r="G79" t="n">
-        <v>0.02702897414565086</v>
+        <v>0.0006022927118465304</v>
       </c>
       <c r="H79" t="n">
-        <v>925.8268142710091</v>
+        <v>925.174014693928</v>
       </c>
       <c r="I79" t="n">
-        <v>165.8417338350223</v>
+        <v>201.381697026613</v>
       </c>
       <c r="J79" t="n">
-        <v>9.88525554598826</v>
+        <v>11.821818590448</v>
       </c>
       <c r="K79" t="n">
-        <v>34.33614758130818</v>
+        <v>1.487471763539361e-07</v>
       </c>
       <c r="L79" t="n">
-        <v>45.45481737885231</v>
+        <v>0.0001225062940193311</v>
       </c>
       <c r="M79" t="n">
-        <v>1.89742366988864</v>
+        <v>5.126460885467337</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>1</v>
+        <v>0.9994738698005676</v>
       </c>
       <c r="P79" t="n">
-        <v>0.006979768630117178</v>
+        <v>0.006471996195614338</v>
       </c>
       <c r="Q79" t="n">
-        <v>800.0001992762569</v>
+        <v>800.0000156062938</v>
       </c>
       <c r="R79" t="n">
-        <v>152.7947715488496</v>
+        <v>206.3163229298266</v>
       </c>
       <c r="S79" t="n">
-        <v>9.000641934653842</v>
+        <v>14.15924514663618</v>
       </c>
       <c r="T79" t="n">
-        <v>160.1627625760603</v>
+        <v>125.1739989388871</v>
       </c>
       <c r="U79" t="n">
-        <v>32.40785509267954</v>
+        <v>4.934748409507648</v>
       </c>
       <c r="V79" t="n">
-        <v>1.012810058554223</v>
+        <v>2.789034329279161</v>
       </c>
       <c r="W79" t="b">
         <v>1</v>
@@ -6233,68 +6233,68 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1008.860966705372</v>
+        <v>922.0588995370605</v>
       </c>
       <c r="D80" t="n">
-        <v>11.75517422967491</v>
+        <v>10.47891849893005</v>
       </c>
       <c r="E80" t="n">
-        <v>189.835374969951</v>
+        <v>125.7251267695712</v>
       </c>
       <c r="F80" t="n">
-        <v>0.579925537109375</v>
+        <v>0.9052466154098511</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0002065182634396479</v>
+        <v>0.005423423834145069</v>
       </c>
       <c r="H80" t="n">
-        <v>969.8951504520487</v>
+        <v>949.4788151061367</v>
       </c>
       <c r="I80" t="n">
-        <v>189.835374969951</v>
+        <v>173.6136600186001</v>
       </c>
       <c r="J80" t="n">
-        <v>11.75517422967491</v>
+        <v>10.47887078902613</v>
       </c>
       <c r="K80" t="n">
-        <v>38.96581625332374</v>
+        <v>27.41991556907624</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>47.8885332490289</v>
       </c>
       <c r="M80" t="n">
-        <v>1.77635683940025e-15</v>
+        <v>4.770990392088947e-05</v>
       </c>
       <c r="N80" t="b">
         <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>0.2208804935216904</v>
+        <v>0.9999251365661621</v>
       </c>
       <c r="P80" t="n">
-        <v>0.0003166623646393418</v>
+        <v>0.009678383357822895</v>
       </c>
       <c r="Q80" t="n">
-        <v>965.3488937046658</v>
+        <v>800.0000456797455</v>
       </c>
       <c r="R80" t="n">
-        <v>189.8714524856854</v>
+        <v>150.3752637279571</v>
       </c>
       <c r="S80" t="n">
-        <v>11.71480806099444</v>
+        <v>9.397611148181095</v>
       </c>
       <c r="T80" t="n">
-        <v>43.51207300070666</v>
+        <v>122.0588538573149</v>
       </c>
       <c r="U80" t="n">
-        <v>0.03607751573431983</v>
+        <v>24.65013695838583</v>
       </c>
       <c r="V80" t="n">
-        <v>0.04036616868046572</v>
+        <v>1.081307350748959</v>
       </c>
       <c r="W80" t="b">
         <v>1</v>
@@ -6306,68 +6306,68 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>872.5112835741422</v>
+        <v>973.9269377632744</v>
       </c>
       <c r="D81" t="n">
-        <v>8.030773748666871</v>
+        <v>4.218786795303473</v>
       </c>
       <c r="E81" t="n">
-        <v>206.1849114791996</v>
+        <v>199.6085588066183</v>
       </c>
       <c r="F81" t="n">
-        <v>0.8621165752410889</v>
+        <v>0.9021573066711426</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0008488548919558525</v>
+        <v>0.001009549014270306</v>
       </c>
       <c r="H81" t="n">
-        <v>935.6635631688569</v>
+        <v>973.9269377634739</v>
       </c>
       <c r="I81" t="n">
-        <v>206.1849114792007</v>
+        <v>199.6085588066182</v>
       </c>
       <c r="J81" t="n">
-        <v>9.000736857150294</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K81" t="n">
-        <v>63.15227959471463</v>
+        <v>1.995204002014361e-10</v>
       </c>
       <c r="L81" t="n">
-        <v>1.080024958355352e-12</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="M81" t="n">
-        <v>0.969963108483423</v>
+        <v>4.78185498455869</v>
       </c>
       <c r="N81" t="b">
         <v>1</v>
       </c>
       <c r="O81" t="n">
-        <v>0.8429480791091919</v>
+        <v>0.998477041721344</v>
       </c>
       <c r="P81" t="n">
-        <v>0.0005371501320041716</v>
+        <v>0.0001305704936385155</v>
       </c>
       <c r="Q81" t="n">
-        <v>931.0261935682043</v>
+        <v>967.0214510986905</v>
       </c>
       <c r="R81" t="n">
-        <v>205.9717516595086</v>
+        <v>199.7114103307554</v>
       </c>
       <c r="S81" t="n">
-        <v>9.000641774204905</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T81" t="n">
-        <v>58.51490999406212</v>
+        <v>6.905486664583918</v>
       </c>
       <c r="U81" t="n">
-        <v>0.2131598196909579</v>
+        <v>0.102851524137094</v>
       </c>
       <c r="V81" t="n">
-        <v>0.9698680255380339</v>
+        <v>4.78185498455869</v>
       </c>
       <c r="W81" t="b">
         <v>1</v>
@@ -6383,64 +6383,64 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>958.5182193420283</v>
+        <v>941.0057360916854</v>
       </c>
       <c r="D82" t="n">
-        <v>17.54506413723065</v>
+        <v>16.20970598452344</v>
       </c>
       <c r="E82" t="n">
-        <v>186.63028357336</v>
+        <v>200.3765036916771</v>
       </c>
       <c r="F82" t="n">
-        <v>0.710898220539093</v>
+        <v>0.8086944818496704</v>
       </c>
       <c r="G82" t="n">
-        <v>0.00131626904476434</v>
+        <v>0.0006026012706570327</v>
       </c>
       <c r="H82" t="n">
-        <v>969.3051348442323</v>
+        <v>941.0057360331089</v>
       </c>
       <c r="I82" t="n">
-        <v>187.8107180122819</v>
+        <v>200.376503691677</v>
       </c>
       <c r="J82" t="n">
-        <v>12.18349667747283</v>
+        <v>11.82181869152873</v>
       </c>
       <c r="K82" t="n">
-        <v>10.78691550220401</v>
+        <v>5.857657470187405e-08</v>
       </c>
       <c r="L82" t="n">
-        <v>1.180434438921878</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="M82" t="n">
-        <v>5.361567459757826</v>
+        <v>4.387887292994707</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
       </c>
       <c r="O82" t="n">
-        <v>0.999996542930603</v>
+        <v>0.9989344477653503</v>
       </c>
       <c r="P82" t="n">
-        <v>0.004110715351998806</v>
+        <v>0.00557564664632082</v>
       </c>
       <c r="Q82" t="n">
-        <v>800.0000198014205</v>
+        <v>800.000002604693</v>
       </c>
       <c r="R82" t="n">
-        <v>178.8236545071726</v>
+        <v>205.0365738482125</v>
       </c>
       <c r="S82" t="n">
-        <v>14.21433766679809</v>
+        <v>14.04212724502304</v>
       </c>
       <c r="T82" t="n">
-        <v>158.5181995406077</v>
+        <v>141.0057334869924</v>
       </c>
       <c r="U82" t="n">
-        <v>7.806629066187412</v>
+        <v>4.660070156535426</v>
       </c>
       <c r="V82" t="n">
-        <v>3.330726470432563</v>
+        <v>2.167578739500398</v>
       </c>
       <c r="W82" t="b">
         <v>1</v>
@@ -6452,68 +6452,68 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Stains</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>853.1068822635369</v>
+        <v>952.4875224460186</v>
       </c>
       <c r="D83" t="n">
-        <v>11.11190379454757</v>
+        <v>15.55473009125146</v>
       </c>
       <c r="E83" t="n">
-        <v>189.9561798748537</v>
+        <v>224.1490198147962</v>
       </c>
       <c r="F83" t="n">
-        <v>0.5852022767066956</v>
+        <v>0.8086159825325012</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0002988803607877344</v>
+        <v>0.003117481712251902</v>
       </c>
       <c r="H83" t="n">
-        <v>907.8188165345761</v>
+        <v>952.487523118034</v>
       </c>
       <c r="I83" t="n">
-        <v>189.9561798748533</v>
+        <v>224.1490198147981</v>
       </c>
       <c r="J83" t="n">
-        <v>11.11190379454756</v>
+        <v>12.18382108846124</v>
       </c>
       <c r="K83" t="n">
-        <v>54.71193427103913</v>
+        <v>6.720154033246217e-07</v>
       </c>
       <c r="L83" t="n">
-        <v>3.694822225952521e-13</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="M83" t="n">
-        <v>5.329070518200751e-15</v>
+        <v>3.370909002790219</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
       </c>
       <c r="O83" t="n">
-        <v>0.7647218108177185</v>
+        <v>0.9905823469161987</v>
       </c>
       <c r="P83" t="n">
-        <v>0.0008331288117915392</v>
+        <v>0.004256206564605236</v>
       </c>
       <c r="Q83" t="n">
-        <v>920.0810684273382</v>
+        <v>800.0000516999291</v>
       </c>
       <c r="R83" t="n">
-        <v>191.9813636115171</v>
+        <v>222.7823365021821</v>
       </c>
       <c r="S83" t="n">
-        <v>11.07924406586887</v>
+        <v>13.95969768168954</v>
       </c>
       <c r="T83" t="n">
-        <v>66.97418616380128</v>
+        <v>152.4874707460895</v>
       </c>
       <c r="U83" t="n">
-        <v>2.025183736663337</v>
+        <v>1.366683312614157</v>
       </c>
       <c r="V83" t="n">
-        <v>0.03265972867869316</v>
+        <v>1.59503240956192</v>
       </c>
       <c r="W83" t="b">
         <v>1</v>
@@ -6525,68 +6525,68 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>952.027795562598</v>
+        <v>871.9166034954022</v>
       </c>
       <c r="D84" t="n">
-        <v>4.656797091604268</v>
+        <v>5.719503605443095</v>
       </c>
       <c r="E84" t="n">
-        <v>186.1754126618551</v>
+        <v>200.6776147264315</v>
       </c>
       <c r="F84" t="n">
-        <v>0.9323320388793945</v>
+        <v>0.922005295753479</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0005017773364670575</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H84" t="n">
-        <v>952.0278776577869</v>
+        <v>933.0453206329204</v>
       </c>
       <c r="I84" t="n">
-        <v>186.1754126618554</v>
+        <v>200.6776147264315</v>
       </c>
       <c r="J84" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641565762713</v>
       </c>
       <c r="K84" t="n">
-        <v>8.209518887269951e-05</v>
+        <v>61.12871713751815</v>
       </c>
       <c r="L84" t="n">
-        <v>2.842170943040401e-13</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M84" t="n">
-        <v>4.343844688257894</v>
+        <v>3.281137960319618</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>0.995408833026886</v>
+        <v>0.9836069345474243</v>
       </c>
       <c r="P84" t="n">
-        <v>0.0001300808071391657</v>
+        <v>0.0004600539396051317</v>
       </c>
       <c r="Q84" t="n">
-        <v>951.5059737346145</v>
+        <v>931.4172888466742</v>
       </c>
       <c r="R84" t="n">
-        <v>186.6427205441336</v>
+        <v>201.0166361276813</v>
       </c>
       <c r="S84" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641823443345</v>
       </c>
       <c r="T84" t="n">
-        <v>0.5218218279835583</v>
+        <v>59.50068535127195</v>
       </c>
       <c r="U84" t="n">
-        <v>0.4673078822784476</v>
+        <v>0.339021401249795</v>
       </c>
       <c r="V84" t="n">
-        <v>4.343844688257894</v>
+        <v>3.28113821800025</v>
       </c>
       <c r="W84" t="b">
         <v>1</v>
@@ -6598,68 +6598,68 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>843.2242537188664</v>
+        <v>954.3289701898689</v>
       </c>
       <c r="D85" t="n">
-        <v>9.857427139480592</v>
+        <v>15.88412626296671</v>
       </c>
       <c r="E85" t="n">
-        <v>195.2329477018448</v>
+        <v>194.513701431672</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8010148406028748</v>
+        <v>0.8066105842590332</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0009919416625052691</v>
+        <v>0.0006026012706570327</v>
       </c>
       <c r="H85" t="n">
-        <v>919.4282448217766</v>
+        <v>954.3289701894272</v>
       </c>
       <c r="I85" t="n">
-        <v>195.2329477018454</v>
+        <v>194.513701431672</v>
       </c>
       <c r="J85" t="n">
-        <v>9.857440020598014</v>
+        <v>11.82181868708977</v>
       </c>
       <c r="K85" t="n">
-        <v>76.20399110291021</v>
+        <v>4.416733645484783e-10</v>
       </c>
       <c r="L85" t="n">
-        <v>6.252776074688882e-13</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>1.288111742248077e-05</v>
+        <v>4.062307575876947</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>0.4259612262248993</v>
+        <v>0.9978845715522766</v>
       </c>
       <c r="P85" t="n">
-        <v>0.0006472592940554023</v>
+        <v>0.005341557785868645</v>
       </c>
       <c r="Q85" t="n">
-        <v>920.5291165008689</v>
+        <v>800.0000163811827</v>
       </c>
       <c r="R85" t="n">
-        <v>195.4909371048369</v>
+        <v>199.953679766063</v>
       </c>
       <c r="S85" t="n">
-        <v>9.958908275007344</v>
+        <v>13.92933069491104</v>
       </c>
       <c r="T85" t="n">
-        <v>77.30486278200249</v>
+        <v>154.3289538086862</v>
       </c>
       <c r="U85" t="n">
-        <v>0.2579894029921093</v>
+        <v>5.439978334390929</v>
       </c>
       <c r="V85" t="n">
-        <v>0.1014811355267522</v>
+        <v>1.954795568055673</v>
       </c>
       <c r="W85" t="b">
         <v>1</v>
@@ -6671,68 +6671,68 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>944.6598326992513</v>
+        <v>874.0821187064782</v>
       </c>
       <c r="D86" t="n">
-        <v>8.686377349508932</v>
+        <v>7.767320450652663</v>
       </c>
       <c r="E86" t="n">
-        <v>129.8690795151252</v>
+        <v>206.1137005176345</v>
       </c>
       <c r="F86" t="n">
-        <v>0.9353889226913452</v>
+        <v>0.9223952293395996</v>
       </c>
       <c r="G86" t="n">
-        <v>0.009299447759985924</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H86" t="n">
-        <v>961.9623342822939</v>
+        <v>933.045323442969</v>
       </c>
       <c r="I86" t="n">
-        <v>167.3961728881269</v>
+        <v>206.1137005176346</v>
       </c>
       <c r="J86" t="n">
-        <v>10.21309702781242</v>
+        <v>9.000641603026418</v>
       </c>
       <c r="K86" t="n">
-        <v>17.30250158304261</v>
+        <v>58.96320473649075</v>
       </c>
       <c r="L86" t="n">
-        <v>37.52709337300163</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="M86" t="n">
-        <v>1.526719678303484</v>
+        <v>1.233321152373755</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>0.9999997615814209</v>
+        <v>0.9544556736946106</v>
       </c>
       <c r="P86" t="n">
-        <v>0.004487267229706049</v>
+        <v>0.0004442452045623213</v>
       </c>
       <c r="Q86" t="n">
-        <v>800.0001890297845</v>
+        <v>931.4965765509721</v>
       </c>
       <c r="R86" t="n">
-        <v>154.1776123514343</v>
+        <v>205.9378992788192</v>
       </c>
       <c r="S86" t="n">
-        <v>9.000641919293081</v>
+        <v>9.000641769660129</v>
       </c>
       <c r="T86" t="n">
-        <v>144.6596436694668</v>
+        <v>57.41445784449388</v>
       </c>
       <c r="U86" t="n">
-        <v>24.3085328363091</v>
+        <v>0.1758012388153247</v>
       </c>
       <c r="V86" t="n">
-        <v>0.3142645697841484</v>
+        <v>1.233321319007466</v>
       </c>
       <c r="W86" t="b">
         <v>1</v>
@@ -6744,68 +6744,68 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>963.0088085381315</v>
+        <v>876.1126159340909</v>
       </c>
       <c r="D87" t="n">
-        <v>11.52744922557012</v>
+        <v>8.053275722005807</v>
       </c>
       <c r="E87" t="n">
-        <v>154.0011373358929</v>
+        <v>205.0024370668732</v>
       </c>
       <c r="F87" t="n">
-        <v>0.9366707801818848</v>
+        <v>0.873828649520874</v>
       </c>
       <c r="G87" t="n">
-        <v>0.008740254677832127</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H87" t="n">
-        <v>969.8968468191288</v>
+        <v>933.0453309638863</v>
       </c>
       <c r="I87" t="n">
-        <v>164.2921630999697</v>
+        <v>205.0024370668731</v>
       </c>
       <c r="J87" t="n">
-        <v>11.52741317986812</v>
+        <v>9.000641473388258</v>
       </c>
       <c r="K87" t="n">
-        <v>6.888038280997307</v>
+        <v>56.93271502979542</v>
       </c>
       <c r="L87" t="n">
-        <v>10.29102576407681</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M87" t="n">
-        <v>3.604570200010926e-05</v>
+        <v>0.9473657513824509</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
       </c>
       <c r="O87" t="n">
-        <v>0.9963548183441162</v>
+        <v>0.929789662361145</v>
       </c>
       <c r="P87" t="n">
-        <v>0.001668425975367427</v>
+        <v>0.0004262854345142841</v>
       </c>
       <c r="Q87" t="n">
-        <v>802.4046981988903</v>
+        <v>931.699289828486</v>
       </c>
       <c r="R87" t="n">
-        <v>164.1937758926997</v>
+        <v>204.9316780319158</v>
       </c>
       <c r="S87" t="n">
-        <v>11.35124755002548</v>
+        <v>9.000641724417703</v>
       </c>
       <c r="T87" t="n">
-        <v>160.6041103392412</v>
+        <v>55.58667389439518</v>
       </c>
       <c r="U87" t="n">
-        <v>10.1926385568068</v>
+        <v>0.07075903495740477</v>
       </c>
       <c r="V87" t="n">
-        <v>0.1762016755446343</v>
+        <v>0.9473660024118953</v>
       </c>
       <c r="W87" t="b">
         <v>1</v>
@@ -6821,64 +6821,64 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>892.491731029129</v>
+        <v>855.6371246689862</v>
       </c>
       <c r="D88" t="n">
-        <v>7.810111168776988</v>
+        <v>8.571125134918899</v>
       </c>
       <c r="E88" t="n">
-        <v>200.1966656998361</v>
+        <v>217.555696678885</v>
       </c>
       <c r="F88" t="n">
-        <v>0.8966370224952698</v>
+        <v>0.7911791801452637</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0009936729911714792</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H88" t="n">
-        <v>933.0453150172963</v>
+        <v>933.0453163395235</v>
       </c>
       <c r="I88" t="n">
-        <v>200.1966656998328</v>
+        <v>217.555696678885</v>
       </c>
       <c r="J88" t="n">
-        <v>9.000641767238305</v>
+        <v>9.000641740363921</v>
       </c>
       <c r="K88" t="n">
-        <v>40.55358398816725</v>
+        <v>77.40819167053735</v>
       </c>
       <c r="L88" t="n">
-        <v>3.325340003357269e-12</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M88" t="n">
-        <v>1.190530598461317</v>
+        <v>0.4295166054450217</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
       </c>
       <c r="O88" t="n">
-        <v>0.5854637622833252</v>
+        <v>0.9194717407226562</v>
       </c>
       <c r="P88" t="n">
-        <v>0.0003506072680465877</v>
+        <v>0.000676877039950341</v>
       </c>
       <c r="Q88" t="n">
-        <v>934.1143449481981</v>
+        <v>930.9534650858936</v>
       </c>
       <c r="R88" t="n">
-        <v>200.3119122546795</v>
+        <v>215.7931514023659</v>
       </c>
       <c r="S88" t="n">
-        <v>9.000641838000544</v>
+        <v>9.000641666766001</v>
       </c>
       <c r="T88" t="n">
-        <v>41.62261391906907</v>
+        <v>75.31634041690745</v>
       </c>
       <c r="U88" t="n">
-        <v>0.1152465548434236</v>
+        <v>1.762545276519063</v>
       </c>
       <c r="V88" t="n">
-        <v>1.190530669223556</v>
+        <v>0.429516531847101</v>
       </c>
       <c r="W88" t="b">
         <v>1</v>
@@ -6890,68 +6890,68 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>926.488107887503</v>
+        <v>835.123914281303</v>
       </c>
       <c r="D89" t="n">
-        <v>2.529784239256371</v>
+        <v>6.824300738939943</v>
       </c>
       <c r="E89" t="n">
-        <v>204.8976295739575</v>
+        <v>192.4932415837991</v>
       </c>
       <c r="F89" t="n">
-        <v>0.894043505191803</v>
+        <v>0.9318311810493469</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0005849990993738174</v>
+        <v>0.00342625891789794</v>
       </c>
       <c r="H89" t="n">
-        <v>928.4781867933435</v>
+        <v>919.4285358038763</v>
       </c>
       <c r="I89" t="n">
-        <v>204.8976295852661</v>
+        <v>192.4932371931276</v>
       </c>
       <c r="J89" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641776727523</v>
       </c>
       <c r="K89" t="n">
-        <v>1.990078905840505</v>
+        <v>84.30462152257337</v>
       </c>
       <c r="L89" t="n">
-        <v>1.130860027842573e-08</v>
+        <v>4.390671506371291e-06</v>
       </c>
       <c r="M89" t="n">
-        <v>6.470857540605791</v>
+        <v>2.17634103778758</v>
       </c>
       <c r="N89" t="b">
         <v>1</v>
       </c>
       <c r="O89" t="n">
-        <v>0.9933645725250244</v>
+        <v>0.993739128112793</v>
       </c>
       <c r="P89" t="n">
-        <v>7.393852138193324e-05</v>
+        <v>0.0008020448731258512</v>
       </c>
       <c r="Q89" t="n">
-        <v>927.9136192410906</v>
+        <v>929.6720784369048</v>
       </c>
       <c r="R89" t="n">
-        <v>204.800052155285</v>
+        <v>194.1052503352452</v>
       </c>
       <c r="S89" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641701703499</v>
       </c>
       <c r="T89" t="n">
-        <v>1.425511353587581</v>
+        <v>94.54816415560185</v>
       </c>
       <c r="U89" t="n">
-        <v>0.09757741867250047</v>
+        <v>1.612008751446098</v>
       </c>
       <c r="V89" t="n">
-        <v>6.470857540605791</v>
+        <v>2.176340962763556</v>
       </c>
       <c r="W89" t="b">
         <v>1</v>
@@ -6967,64 +6967,64 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>972.9392573651033</v>
+        <v>946.5757757630857</v>
       </c>
       <c r="D90" t="n">
-        <v>6.22268352310375</v>
+        <v>5.498200963589312</v>
       </c>
       <c r="E90" t="n">
-        <v>197.3898722457993</v>
+        <v>203.0338594278622</v>
       </c>
       <c r="F90" t="n">
-        <v>0.9299044013023376</v>
+        <v>0.8901962041854858</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0005017528310418129</v>
+        <v>0.001009692437946796</v>
       </c>
       <c r="H90" t="n">
-        <v>972.9392651459993</v>
+        <v>946.5757757630849</v>
       </c>
       <c r="I90" t="n">
-        <v>197.3898722457993</v>
+        <v>203.0338594278622</v>
       </c>
       <c r="J90" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="K90" t="n">
-        <v>7.780895998621418e-06</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="L90" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="M90" t="n">
-        <v>2.777958256758413</v>
+        <v>3.50244081627285</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
       </c>
       <c r="O90" t="n">
-        <v>0.4632772505283356</v>
+        <v>0.9716449379920959</v>
       </c>
       <c r="P90" t="n">
-        <v>5.905363286728971e-05</v>
+        <v>6.211008440004662e-05</v>
       </c>
       <c r="Q90" t="n">
-        <v>971.9526968495683</v>
+        <v>946.1353768581462</v>
       </c>
       <c r="R90" t="n">
-        <v>197.4957337413712</v>
+        <v>203.0442228055896</v>
       </c>
       <c r="S90" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="T90" t="n">
-        <v>0.986560515535075</v>
+        <v>0.4403989049395705</v>
       </c>
       <c r="U90" t="n">
-        <v>0.1058614955719008</v>
+        <v>0.01036337772742968</v>
       </c>
       <c r="V90" t="n">
-        <v>2.777958256758413</v>
+        <v>3.50244081627285</v>
       </c>
       <c r="W90" t="b">
         <v>1</v>
@@ -7036,68 +7036,68 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>961.4877270226775</v>
+        <v>887.5228913766166</v>
       </c>
       <c r="D91" t="n">
-        <v>5.656828570275804</v>
+        <v>7.649765801260644</v>
       </c>
       <c r="E91" t="n">
-        <v>203.1362182545766</v>
+        <v>209.333586015199</v>
       </c>
       <c r="F91" t="n">
-        <v>0.9300639033317566</v>
+        <v>0.8506448864936829</v>
       </c>
       <c r="G91" t="n">
-        <v>0.0005017708754166961</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H91" t="n">
-        <v>961.4877679289691</v>
+        <v>933.0453154075816</v>
       </c>
       <c r="I91" t="n">
-        <v>203.1362182545766</v>
+        <v>209.333586015199</v>
       </c>
       <c r="J91" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641608203027</v>
       </c>
       <c r="K91" t="n">
-        <v>4.090629158781667e-05</v>
+        <v>45.522424030965</v>
       </c>
       <c r="L91" t="n">
         <v>2.842170943040401e-14</v>
       </c>
       <c r="M91" t="n">
-        <v>3.343813209586358</v>
+        <v>1.350875806942383</v>
       </c>
       <c r="N91" t="b">
         <v>1</v>
       </c>
       <c r="O91" t="n">
-        <v>0.7523629069328308</v>
+        <v>0.8476199507713318</v>
       </c>
       <c r="P91" t="n">
-        <v>3.810009002336301e-05</v>
+        <v>0.0003574339498300105</v>
       </c>
       <c r="Q91" t="n">
-        <v>961.023793550907</v>
+        <v>933.1325387041923</v>
       </c>
       <c r="R91" t="n">
-        <v>203.208155845297</v>
+        <v>208.894945893669</v>
       </c>
       <c r="S91" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641775144661</v>
       </c>
       <c r="T91" t="n">
-        <v>0.4639334717704742</v>
+        <v>45.60964732757566</v>
       </c>
       <c r="U91" t="n">
-        <v>0.07193759072038119</v>
+        <v>0.4386401215299713</v>
       </c>
       <c r="V91" t="n">
-        <v>3.343813209586358</v>
+        <v>1.350875973884017</v>
       </c>
       <c r="W91" t="b">
         <v>1</v>
@@ -7109,68 +7109,68 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1012.733720966446</v>
+        <v>878.9000351868293</v>
       </c>
       <c r="D92" t="n">
-        <v>11.10052158718142</v>
+        <v>8.425764143923214</v>
       </c>
       <c r="E92" t="n">
-        <v>194.5264532054536</v>
+        <v>210.6415662798122</v>
       </c>
       <c r="F92" t="n">
-        <v>0.6780478954315186</v>
+        <v>0.7311365604400635</v>
       </c>
       <c r="G92" t="n">
-        <v>0.0002065182634396479</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H92" t="n">
-        <v>969.8951498482114</v>
+        <v>933.0453157089106</v>
       </c>
       <c r="I92" t="n">
-        <v>194.5264532054536</v>
+        <v>210.6415662798122</v>
       </c>
       <c r="J92" t="n">
-        <v>11.10052158718142</v>
+        <v>9.000641653985529</v>
       </c>
       <c r="K92" t="n">
-        <v>42.83857111823409</v>
+        <v>54.14528052208129</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>0.5748775100623149</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>0.307061493396759</v>
+        <v>0.8502494096755981</v>
       </c>
       <c r="P92" t="n">
-        <v>0.0002763189550023526</v>
+        <v>0.000425392878241837</v>
       </c>
       <c r="Q92" t="n">
-        <v>968.5671410337684</v>
+        <v>932.2726888561129</v>
       </c>
       <c r="R92" t="n">
-        <v>194.4928325880919</v>
+        <v>210.0301590263422</v>
       </c>
       <c r="S92" t="n">
-        <v>11.07110038742804</v>
+        <v>9.000641895492265</v>
       </c>
       <c r="T92" t="n">
-        <v>44.16657993267711</v>
+        <v>53.37265366928364</v>
       </c>
       <c r="U92" t="n">
-        <v>0.03362061736171995</v>
+        <v>0.6114072534700199</v>
       </c>
       <c r="V92" t="n">
-        <v>0.02942119975337754</v>
+        <v>0.5748777515690513</v>
       </c>
       <c r="W92" t="b">
         <v>1</v>
@@ -7182,68 +7182,68 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>942.9844485085017</v>
+        <v>878.3564058967878</v>
       </c>
       <c r="D93" t="n">
-        <v>10.54675837316494</v>
+        <v>8.799881216785067</v>
       </c>
       <c r="E93" t="n">
-        <v>125.2009240422635</v>
+        <v>202.7497246495558</v>
       </c>
       <c r="F93" t="n">
-        <v>0.9365445375442505</v>
+        <v>0.678946852684021</v>
       </c>
       <c r="G93" t="n">
-        <v>0.008770139887928963</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H93" t="n">
-        <v>961.965048199994</v>
+        <v>933.0453185661082</v>
       </c>
       <c r="I93" t="n">
-        <v>164.2936197249232</v>
+        <v>202.7497246495558</v>
       </c>
       <c r="J93" t="n">
-        <v>10.54675991027221</v>
+        <v>9.000641602739906</v>
       </c>
       <c r="K93" t="n">
-        <v>18.98059969149233</v>
+        <v>54.68891266932042</v>
       </c>
       <c r="L93" t="n">
-        <v>39.09269568265971</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>1.537107275240146e-06</v>
+        <v>0.2007603859548386</v>
       </c>
       <c r="N93" t="b">
         <v>1</v>
       </c>
       <c r="O93" t="n">
-        <v>1</v>
+        <v>0.8087602257728577</v>
       </c>
       <c r="P93" t="n">
-        <v>0.005425143521279097</v>
+        <v>0.0004069936112500727</v>
       </c>
       <c r="Q93" t="n">
-        <v>800.0000312533836</v>
+        <v>931.9908767333558</v>
       </c>
       <c r="R93" t="n">
-        <v>155.5913555596204</v>
+        <v>202.8749338543323</v>
       </c>
       <c r="S93" t="n">
-        <v>9.570740319814577</v>
+        <v>9.000641826765426</v>
       </c>
       <c r="T93" t="n">
-        <v>142.9844172551182</v>
+        <v>53.63447083656797</v>
       </c>
       <c r="U93" t="n">
-        <v>30.39043151735687</v>
+        <v>0.1252092047765814</v>
       </c>
       <c r="V93" t="n">
-        <v>0.9760180533503622</v>
+        <v>0.2007606099803585</v>
       </c>
       <c r="W93" t="b">
         <v>1</v>
@@ -7259,64 +7259,64 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>954.2639325647538</v>
+        <v>944.6598326992513</v>
       </c>
       <c r="D94" t="n">
-        <v>10.33724301374753</v>
+        <v>8.686377349508932</v>
       </c>
       <c r="E94" t="n">
-        <v>137.8400438434407</v>
+        <v>129.8690795151252</v>
       </c>
       <c r="F94" t="n">
-        <v>0.936724841594696</v>
+        <v>0.9054416418075562</v>
       </c>
       <c r="G94" t="n">
-        <v>0.007099774666130543</v>
+        <v>0.02525101602077484</v>
       </c>
       <c r="H94" t="n">
-        <v>909.5714153305253</v>
+        <v>960.0063177017861</v>
       </c>
       <c r="I94" t="n">
-        <v>164.293079444303</v>
+        <v>165.9408748827772</v>
       </c>
       <c r="J94" t="n">
-        <v>10.60853595284197</v>
+        <v>9.868906925182481</v>
       </c>
       <c r="K94" t="n">
-        <v>44.69251723422849</v>
+        <v>15.34648500253479</v>
       </c>
       <c r="L94" t="n">
-        <v>26.45303560086228</v>
+        <v>36.07179536765193</v>
       </c>
       <c r="M94" t="n">
-        <v>0.2712929390944403</v>
+        <v>1.182529575673549</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
       </c>
       <c r="O94" t="n">
-        <v>0.999996542930603</v>
+        <v>0.9999221563339233</v>
       </c>
       <c r="P94" t="n">
-        <v>0.003333923174068332</v>
+        <v>0.006814353633671999</v>
       </c>
       <c r="Q94" t="n">
-        <v>800.0000439418317</v>
+        <v>800.0000297204384</v>
       </c>
       <c r="R94" t="n">
-        <v>158.4561967727692</v>
+        <v>150.0005528529397</v>
       </c>
       <c r="S94" t="n">
-        <v>10.05337013655258</v>
+        <v>9.000642071061314</v>
       </c>
       <c r="T94" t="n">
-        <v>154.2638886229221</v>
+        <v>144.6598029788129</v>
       </c>
       <c r="U94" t="n">
-        <v>20.61615292932851</v>
+        <v>20.1314733378145</v>
       </c>
       <c r="V94" t="n">
-        <v>0.2838728771949448</v>
+        <v>0.3142647215523819</v>
       </c>
       <c r="W94" t="b">
         <v>1</v>
@@ -7328,68 +7328,68 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>866.3135954672613</v>
+        <v>967.3991853873271</v>
       </c>
       <c r="D95" t="n">
-        <v>7.522699393143458</v>
+        <v>2.956282732464466</v>
       </c>
       <c r="E95" t="n">
-        <v>184.4397332854445</v>
+        <v>187.3077628180434</v>
       </c>
       <c r="F95" t="n">
-        <v>0.9320161938667297</v>
+        <v>0.9024178981781006</v>
       </c>
       <c r="G95" t="n">
-        <v>0.001519713317975402</v>
+        <v>0.001009689178317785</v>
       </c>
       <c r="H95" t="n">
-        <v>919.4282385708856</v>
+        <v>967.3991853906026</v>
       </c>
       <c r="I95" t="n">
-        <v>184.4397332854444</v>
+        <v>187.3077628180489</v>
       </c>
       <c r="J95" t="n">
-        <v>9.000641772860659</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K95" t="n">
-        <v>53.1146431036243</v>
+        <v>3.275545168435201e-09</v>
       </c>
       <c r="L95" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>5.542233338928781e-12</v>
       </c>
       <c r="M95" t="n">
-        <v>1.4779423797172</v>
+        <v>6.044359047397696</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
       </c>
       <c r="O95" t="n">
-        <v>0.9412451982498169</v>
+        <v>0.9993027448654175</v>
       </c>
       <c r="P95" t="n">
-        <v>0.0005465617869049311</v>
+        <v>0.0002048588066827506</v>
       </c>
       <c r="Q95" t="n">
-        <v>933.9098903894704</v>
+        <v>961.1976297098331</v>
       </c>
       <c r="R95" t="n">
-        <v>184.9164873782845</v>
+        <v>188.0350796961787</v>
       </c>
       <c r="S95" t="n">
-        <v>9.000641822348175</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T95" t="n">
-        <v>67.59629492220915</v>
+        <v>6.201555677493957</v>
       </c>
       <c r="U95" t="n">
-        <v>0.4767540928399967</v>
+        <v>0.7273168781353831</v>
       </c>
       <c r="V95" t="n">
-        <v>1.477942429204717</v>
+        <v>6.044359047397696</v>
       </c>
       <c r="W95" t="b">
         <v>1</v>
@@ -7401,68 +7401,68 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>965.2935835087047</v>
+        <v>890.5470318060303</v>
       </c>
       <c r="D96" t="n">
-        <v>16.76683532917998</v>
+        <v>7.512650723820679</v>
       </c>
       <c r="E96" t="n">
-        <v>200.9176028663524</v>
+        <v>215.574397047935</v>
       </c>
       <c r="F96" t="n">
-        <v>0.9146213531494141</v>
+        <v>0.8500855565071106</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0008162212907336652</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H96" t="n">
-        <v>951.4454618445599</v>
+        <v>933.0453168076448</v>
       </c>
       <c r="I96" t="n">
-        <v>202.6499990634966</v>
+        <v>215.5743970479351</v>
       </c>
       <c r="J96" t="n">
-        <v>12.18359449059338</v>
+        <v>9.000641605434167</v>
       </c>
       <c r="K96" t="n">
-        <v>13.84812166414486</v>
+        <v>42.49828500161448</v>
       </c>
       <c r="L96" t="n">
-        <v>1.732396197144197</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M96" t="n">
-        <v>4.583240838586606</v>
+        <v>1.487990881613488</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
       </c>
       <c r="O96" t="n">
-        <v>0.9999829530715942</v>
+        <v>0.7874205112457275</v>
       </c>
       <c r="P96" t="n">
-        <v>0.003629679558798671</v>
+        <v>0.0003726465802174062</v>
       </c>
       <c r="Q96" t="n">
-        <v>800.0000299899725</v>
+        <v>934.4434799154654</v>
       </c>
       <c r="R96" t="n">
-        <v>191.8273025892069</v>
+        <v>214.56302936227</v>
       </c>
       <c r="S96" t="n">
-        <v>13.89003242424208</v>
+        <v>9.000641644686672</v>
       </c>
       <c r="T96" t="n">
-        <v>165.2935535187322</v>
+        <v>43.89644810943514</v>
       </c>
       <c r="U96" t="n">
-        <v>9.090300277145531</v>
+        <v>1.011367685665022</v>
       </c>
       <c r="V96" t="n">
-        <v>2.8768029049379</v>
+        <v>1.487990920865993</v>
       </c>
       <c r="W96" t="b">
         <v>1</v>
@@ -7474,68 +7474,68 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>968.2154140690368</v>
+        <v>833.7210060081408</v>
       </c>
       <c r="D97" t="n">
-        <v>8.848166911781199</v>
+        <v>5.895170445327111</v>
       </c>
       <c r="E97" t="n">
-        <v>152.2234677677183</v>
+        <v>194.1856708830898</v>
       </c>
       <c r="F97" t="n">
-        <v>0.9364097118377686</v>
+        <v>0.9218559265136719</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0004976012860424817</v>
+        <v>0.00342625891789794</v>
       </c>
       <c r="H97" t="n">
-        <v>968.244809625298</v>
+        <v>919.4290659766887</v>
       </c>
       <c r="I97" t="n">
-        <v>176.1296280327352</v>
+        <v>194.1856691650754</v>
       </c>
       <c r="J97" t="n">
-        <v>9.000000101022215</v>
+        <v>9.000641690081178</v>
       </c>
       <c r="K97" t="n">
-        <v>0.02939555626119272</v>
+        <v>85.7080599685479</v>
       </c>
       <c r="L97" t="n">
-        <v>23.90616026501698</v>
+        <v>1.718014431162374e-06</v>
       </c>
       <c r="M97" t="n">
-        <v>0.1518331892410156</v>
+        <v>3.105471244754067</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
       </c>
       <c r="O97" t="n">
-        <v>0.9989148378372192</v>
+        <v>0.9966822266578674</v>
       </c>
       <c r="P97" t="n">
-        <v>0.001407192670740187</v>
+        <v>0.0008018033113330603</v>
       </c>
       <c r="Q97" t="n">
-        <v>813.3892719110506</v>
+        <v>929.2366177875384</v>
       </c>
       <c r="R97" t="n">
-        <v>162.6894281831615</v>
+        <v>195.5874239900444</v>
       </c>
       <c r="S97" t="n">
-        <v>9.000447316348586</v>
+        <v>9.000641751428157</v>
       </c>
       <c r="T97" t="n">
-        <v>154.8261421579862</v>
+        <v>95.51561177939766</v>
       </c>
       <c r="U97" t="n">
-        <v>10.46596041544319</v>
+        <v>1.401753106954601</v>
       </c>
       <c r="V97" t="n">
-        <v>0.1522804045673869</v>
+        <v>3.105471306101046</v>
       </c>
       <c r="W97" t="b">
         <v>1</v>
@@ -7547,68 +7547,68 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>953.4174705749397</v>
+        <v>853.6665716226203</v>
       </c>
       <c r="D98" t="n">
-        <v>11.46913598192008</v>
+        <v>8.011088900073144</v>
       </c>
       <c r="E98" t="n">
-        <v>128.7835388480846</v>
+        <v>197.7691512671515</v>
       </c>
       <c r="F98" t="n">
-        <v>0.936724841594696</v>
+        <v>0.9254602789878845</v>
       </c>
       <c r="G98" t="n">
-        <v>0.04245391860604286</v>
+        <v>0.001727184862829745</v>
       </c>
       <c r="H98" t="n">
-        <v>843.4070516182264</v>
+        <v>933.0453153860811</v>
       </c>
       <c r="I98" t="n">
-        <v>173.6136085934705</v>
+        <v>197.7691512671515</v>
       </c>
       <c r="J98" t="n">
-        <v>12.37031421688196</v>
+        <v>9.000641633837835</v>
       </c>
       <c r="K98" t="n">
-        <v>110.0104189567132</v>
+        <v>79.37874376346088</v>
       </c>
       <c r="L98" t="n">
-        <v>44.83006974538591</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>0.9011782349618809</v>
+        <v>0.9895527337646914</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>0.9999997615814209</v>
+        <v>0.9749099612236023</v>
       </c>
       <c r="P98" t="n">
-        <v>0.00549617875367403</v>
+        <v>0.000605639535933733</v>
       </c>
       <c r="Q98" t="n">
-        <v>800.0000324218692</v>
+        <v>930.1923421324998</v>
       </c>
       <c r="R98" t="n">
-        <v>158.9430110284084</v>
+        <v>198.5222939748784</v>
       </c>
       <c r="S98" t="n">
-        <v>11.13789911145014</v>
+        <v>9.000641677059376</v>
       </c>
       <c r="T98" t="n">
-        <v>153.4174381530705</v>
+        <v>76.52577050987952</v>
       </c>
       <c r="U98" t="n">
-        <v>30.15947218032389</v>
+        <v>0.753142707726937</v>
       </c>
       <c r="V98" t="n">
-        <v>0.331236870469942</v>
+        <v>0.9895527769862316</v>
       </c>
       <c r="W98" t="b">
         <v>1</v>
@@ -7620,68 +7620,68 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>957.5527914357328</v>
+        <v>807.6692789674012</v>
       </c>
       <c r="D99" t="n">
-        <v>6.273858724981029</v>
+        <v>8.29204520892505</v>
       </c>
       <c r="E99" t="n">
-        <v>210.8378318806114</v>
+        <v>207.8843195352499</v>
       </c>
       <c r="F99" t="n">
-        <v>0.9283376932144165</v>
+        <v>0.8163442015647888</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0005017013754695654</v>
+        <v>0.004001171793788671</v>
       </c>
       <c r="H99" t="n">
-        <v>957.5527914357391</v>
+        <v>916.4024450851115</v>
       </c>
       <c r="I99" t="n">
-        <v>210.8378318806112</v>
+        <v>207.8843195352526</v>
       </c>
       <c r="J99" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000623852342402</v>
       </c>
       <c r="K99" t="n">
-        <v>6.252776074688882e-12</v>
+        <v>108.7331661177103</v>
       </c>
       <c r="L99" t="n">
-        <v>1.989519660128281e-13</v>
+        <v>2.756905814749189e-12</v>
       </c>
       <c r="M99" t="n">
-        <v>2.726783054881134</v>
+        <v>0.7085786434173524</v>
       </c>
       <c r="N99" t="b">
         <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>0.1798679828643799</v>
+        <v>0.9572621583938599</v>
       </c>
       <c r="P99" t="n">
-        <v>4.90026650368236e-05</v>
+        <v>0.001039233291521668</v>
       </c>
       <c r="Q99" t="n">
-        <v>959.0235485976783</v>
+        <v>926.6671077541839</v>
       </c>
       <c r="R99" t="n">
-        <v>210.6703539728738</v>
+        <v>207.3958812301202</v>
       </c>
       <c r="S99" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641698294629</v>
       </c>
       <c r="T99" t="n">
-        <v>1.470757161945471</v>
+        <v>118.9978287867827</v>
       </c>
       <c r="U99" t="n">
-        <v>0.167477907737549</v>
+        <v>0.4884383051296766</v>
       </c>
       <c r="V99" t="n">
-        <v>2.726783054881134</v>
+        <v>0.7085964893695795</v>
       </c>
       <c r="W99" t="b">
         <v>1</v>
@@ -7693,68 +7693,68 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>918.183082862826</v>
+        <v>943.8134301445141</v>
       </c>
       <c r="D100" t="n">
-        <v>15.8800637485525</v>
+        <v>10.5416950744846</v>
       </c>
       <c r="E100" t="n">
-        <v>182.155694562732</v>
+        <v>143.1611992120024</v>
       </c>
       <c r="F100" t="n">
-        <v>0.7846332192420959</v>
+        <v>0.9065549969673157</v>
       </c>
       <c r="G100" t="n">
-        <v>0.001172919757664204</v>
+        <v>0.001030104584060609</v>
       </c>
       <c r="H100" t="n">
-        <v>891.3488276612976</v>
+        <v>943.8137819908089</v>
       </c>
       <c r="I100" t="n">
-        <v>182.1556945627322</v>
+        <v>176.1299334757794</v>
       </c>
       <c r="J100" t="n">
-        <v>11.82175923198185</v>
+        <v>10.54169094731249</v>
       </c>
       <c r="K100" t="n">
-        <v>26.83425520152844</v>
+        <v>0.0003518462948477463</v>
       </c>
       <c r="L100" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>32.96873426377692</v>
       </c>
       <c r="M100" t="n">
-        <v>4.058304516570646</v>
+        <v>4.127172115175881e-06</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>0.9989892840385437</v>
+        <v>0.9992758631706238</v>
       </c>
       <c r="P100" t="n">
-        <v>0.002657468430697918</v>
+        <v>0.004649315495043993</v>
       </c>
       <c r="Q100" t="n">
-        <v>800.0000000797795</v>
+        <v>800.0002135690013</v>
       </c>
       <c r="R100" t="n">
-        <v>177.3612850526923</v>
+        <v>158.7902180698048</v>
       </c>
       <c r="S100" t="n">
-        <v>14.07866665159937</v>
+        <v>10.07105028681568</v>
       </c>
       <c r="T100" t="n">
-        <v>118.1830827830465</v>
+        <v>143.8132165755128</v>
       </c>
       <c r="U100" t="n">
-        <v>4.794409510039685</v>
+        <v>15.62901885780232</v>
       </c>
       <c r="V100" t="n">
-        <v>1.801397096953126</v>
+        <v>0.4706447876689204</v>
       </c>
       <c r="W100" t="b">
         <v>1</v>
@@ -7766,68 +7766,68 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>952.5170560737424</v>
+        <v>866.0466215846022</v>
       </c>
       <c r="D101" t="n">
-        <v>4.006125349756688</v>
+        <v>8.883345110211364</v>
       </c>
       <c r="E101" t="n">
-        <v>183.7661784047959</v>
+        <v>206.4366122184509</v>
       </c>
       <c r="F101" t="n">
-        <v>0.9323320388793945</v>
+        <v>0.7579154968261719</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0005017046350985765</v>
+        <v>0.002170027466490865</v>
       </c>
       <c r="H101" t="n">
-        <v>952.5170560737286</v>
+        <v>919.4300916867811</v>
       </c>
       <c r="I101" t="n">
-        <v>183.7661784047961</v>
+        <v>206.436563578844</v>
       </c>
       <c r="J101" t="n">
-        <v>9.000641779862162</v>
+        <v>9.328898478925602</v>
       </c>
       <c r="K101" t="n">
-        <v>1.386979420203716e-11</v>
+        <v>53.38347010217888</v>
       </c>
       <c r="L101" t="n">
-        <v>2.557953848736361e-13</v>
+        <v>4.863960694478919e-05</v>
       </c>
       <c r="M101" t="n">
-        <v>4.994516430105475</v>
+        <v>0.4455533687142381</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>0.9992189407348633</v>
+        <v>0.8912108540534973</v>
       </c>
       <c r="P101" t="n">
-        <v>0.0001652052305871621</v>
+        <v>0.0005053678178228438</v>
       </c>
       <c r="Q101" t="n">
-        <v>951.8445947940265</v>
+        <v>930.7552569684668</v>
       </c>
       <c r="R101" t="n">
-        <v>184.3411756244252</v>
+        <v>206.2174158124488</v>
       </c>
       <c r="S101" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641822762658</v>
       </c>
       <c r="T101" t="n">
-        <v>0.6724612797158898</v>
+        <v>64.70863538386459</v>
       </c>
       <c r="U101" t="n">
-        <v>0.5749972196293811</v>
+        <v>0.2191964060021121</v>
       </c>
       <c r="V101" t="n">
-        <v>4.994516430105475</v>
+        <v>0.117296712551294</v>
       </c>
       <c r="W101" t="b">
         <v>1</v>

--- a/export_dati/06_Step6_Simulazione_Massiva_100.xlsx
+++ b/export_dati/06_Step6_Simulazione_Massiva_100.xlsx
@@ -539,68 +539,68 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>956.7070005389429</v>
+        <v>846.35473260961</v>
       </c>
       <c r="D2" t="n">
-        <v>2.960049688720861</v>
+        <v>9.678010236705797</v>
       </c>
       <c r="E2" t="n">
-        <v>216.8657265165326</v>
+        <v>201.2301164142077</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8311465382575989</v>
+        <v>0.6594186425209045</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001009689178317785</v>
+        <v>0.0008911140612326562</v>
       </c>
       <c r="H2" t="n">
-        <v>956.7070125195878</v>
+        <v>920.0548507071468</v>
       </c>
       <c r="I2" t="n">
-        <v>216.8657265166484</v>
+        <v>201.2411827932042</v>
       </c>
       <c r="J2" t="n">
-        <v>9.000641779862162</v>
+        <v>9.711011639075149</v>
       </c>
       <c r="K2" t="n">
-        <v>1.198064489926765e-05</v>
+        <v>73.7001180975368</v>
       </c>
       <c r="L2" t="n">
-        <v>1.157900442194659e-10</v>
+        <v>0.01106637899650309</v>
       </c>
       <c r="M2" t="n">
-        <v>6.040592091141301</v>
+        <v>0.03300140236935256</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9984650611877441</v>
+        <v>0.7613406181335449</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0001277170667890459</v>
+        <v>0.0005433859187178314</v>
       </c>
       <c r="Q2" t="n">
-        <v>953.5419627940839</v>
+        <v>922.8714624173679</v>
       </c>
       <c r="R2" t="n">
-        <v>216.3614796664943</v>
+        <v>199.9695216718602</v>
       </c>
       <c r="S2" t="n">
-        <v>9.000641779862162</v>
+        <v>9.740446104148106</v>
       </c>
       <c r="T2" t="n">
-        <v>3.165037744858978</v>
+        <v>76.51672980775788</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5042468500382995</v>
+        <v>1.260594742347479</v>
       </c>
       <c r="V2" t="n">
-        <v>6.040592091141301</v>
+        <v>0.06243586744230889</v>
       </c>
       <c r="W2" t="b">
         <v>1</v>
@@ -612,68 +612,68 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>963.0582695268022</v>
+        <v>1039.581685020515</v>
       </c>
       <c r="D3" t="n">
-        <v>9.031225337763633</v>
+        <v>10.96782296594122</v>
       </c>
       <c r="E3" t="n">
-        <v>139.5365085777432</v>
+        <v>195.7838520794682</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9065932631492615</v>
+        <v>0.6184679865837097</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001030125422403216</v>
+        <v>9.742625115904957e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>962.9737328302404</v>
+        <v>985.8937770676032</v>
       </c>
       <c r="I3" t="n">
-        <v>176.1361461155139</v>
+        <v>195.7838875835934</v>
       </c>
       <c r="J3" t="n">
-        <v>9.032050357428021</v>
+        <v>10.96782296594122</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08453669656182683</v>
+        <v>53.68790795291193</v>
       </c>
       <c r="L3" t="n">
-        <v>36.59963753777063</v>
+        <v>3.55041252078081e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0008250196643881935</v>
+        <v>0</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9997538924217224</v>
+        <v>0.9861426949501038</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004132937174290419</v>
+        <v>0.0002667448716238141</v>
       </c>
       <c r="Q3" t="n">
-        <v>800.000046225852</v>
+        <v>975.3683586632568</v>
       </c>
       <c r="R3" t="n">
-        <v>152.9961138612727</v>
+        <v>195.3094626140189</v>
       </c>
       <c r="S3" t="n">
-        <v>9.000626972961413</v>
+        <v>10.967173305267</v>
       </c>
       <c r="T3" t="n">
-        <v>163.0582233009502</v>
+        <v>64.21332635725832</v>
       </c>
       <c r="U3" t="n">
-        <v>13.45960528352947</v>
+        <v>0.4743894654492919</v>
       </c>
       <c r="V3" t="n">
-        <v>0.03059836480221989</v>
+        <v>0.0006496606742132371</v>
       </c>
       <c r="W3" t="b">
         <v>1</v>
@@ -685,68 +685,68 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>887.7583948719523</v>
+        <v>966.3537262610911</v>
       </c>
       <c r="D4" t="n">
-        <v>7.910424121717402</v>
+        <v>5.389466018585829</v>
       </c>
       <c r="E4" t="n">
-        <v>189.7627174383277</v>
+        <v>191.0819217970761</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8497275114059448</v>
+        <v>0.9324119091033936</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.000253947131568566</v>
       </c>
       <c r="H4" t="n">
-        <v>933.0453158671529</v>
+        <v>966.3537262610907</v>
       </c>
       <c r="I4" t="n">
-        <v>189.7627174383277</v>
+        <v>191.0819217970763</v>
       </c>
       <c r="J4" t="n">
-        <v>9.000641723067526</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K4" t="n">
-        <v>45.2869209952006</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="M4" t="n">
-        <v>1.090217601350123</v>
+        <v>3.611175761276333</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7980248332023621</v>
+        <v>0.9593839645385742</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0003900832962244749</v>
+        <v>0.0001522877864772454</v>
       </c>
       <c r="Q4" t="n">
-        <v>935.4339213799741</v>
+        <v>957.9046369489666</v>
       </c>
       <c r="R4" t="n">
-        <v>190.9073789144944</v>
+        <v>191.5366588035811</v>
       </c>
       <c r="S4" t="n">
-        <v>9.000641399869208</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T4" t="n">
-        <v>47.67552650802179</v>
+        <v>8.449089312124443</v>
       </c>
       <c r="U4" t="n">
-        <v>1.144661476166732</v>
+        <v>0.45473700650507</v>
       </c>
       <c r="V4" t="n">
-        <v>1.090217278151806</v>
+        <v>3.611175761276333</v>
       </c>
       <c r="W4" t="b">
         <v>1</v>
@@ -758,68 +758,68 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>858.8247965039768</v>
+        <v>945.074197147824</v>
       </c>
       <c r="D5" t="n">
-        <v>7.545357578691671</v>
+        <v>10.31564330773237</v>
       </c>
       <c r="E5" t="n">
-        <v>207.8025841162732</v>
+        <v>108.2684665753791</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9223969578742981</v>
+        <v>0.9806832075119019</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.01705425418913364</v>
       </c>
       <c r="H5" t="n">
-        <v>933.0453163595322</v>
+        <v>970.2248744616279</v>
       </c>
       <c r="I5" t="n">
-        <v>207.8025841162733</v>
+        <v>166.3955239495973</v>
       </c>
       <c r="J5" t="n">
-        <v>9.000641635262166</v>
+        <v>10.2422937265863</v>
       </c>
       <c r="K5" t="n">
-        <v>74.22051985555538</v>
+        <v>25.15067731380395</v>
       </c>
       <c r="L5" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>58.12705737421825</v>
       </c>
       <c r="M5" t="n">
-        <v>1.455284056570496</v>
+        <v>0.07334958114606671</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9807637929916382</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>0.000568950898014009</v>
+        <v>0.001186170382425189</v>
       </c>
       <c r="Q5" t="n">
-        <v>930.1514210452157</v>
+        <v>801.5323704320843</v>
       </c>
       <c r="R5" t="n">
-        <v>207.4168434684353</v>
+        <v>150.0005523686477</v>
       </c>
       <c r="S5" t="n">
-        <v>9.000641886527552</v>
+        <v>10.19476330015607</v>
       </c>
       <c r="T5" t="n">
-        <v>71.32662454123886</v>
+        <v>143.5418267157396</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3857406478378778</v>
+        <v>41.73208579326865</v>
       </c>
       <c r="V5" t="n">
-        <v>1.455284307835881</v>
+        <v>0.1208800075763001</v>
       </c>
       <c r="W5" t="b">
         <v>1</v>
@@ -831,68 +831,68 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>840.864426422445</v>
+        <v>936.9104665539262</v>
       </c>
       <c r="D6" t="n">
-        <v>7.2688151502831</v>
+        <v>9.584612612311092</v>
       </c>
       <c r="E6" t="n">
-        <v>214.1732560514905</v>
+        <v>127.5048688562275</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9229809045791626</v>
+        <v>0.9835739135742188</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003427958348765969</v>
+        <v>0.001278240233659744</v>
       </c>
       <c r="H6" t="n">
-        <v>919.4292614984873</v>
+        <v>857.2976406733651</v>
       </c>
       <c r="I6" t="n">
-        <v>214.1732853240142</v>
+        <v>176.1732637380991</v>
       </c>
       <c r="J6" t="n">
-        <v>9.000641620391105</v>
+        <v>9.740868471732181</v>
       </c>
       <c r="K6" t="n">
-        <v>78.5648350760423</v>
+        <v>79.6128258805611</v>
       </c>
       <c r="L6" t="n">
-        <v>2.92725237045488e-05</v>
+        <v>48.66839488187156</v>
       </c>
       <c r="M6" t="n">
-        <v>1.731826470108006</v>
+        <v>0.1562558594210888</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9851906895637512</v>
+        <v>0.9999996423721313</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0007730433135293424</v>
+        <v>0.001099389512091875</v>
       </c>
       <c r="Q6" t="n">
-        <v>929.208491204292</v>
+        <v>806.1222020152608</v>
       </c>
       <c r="R6" t="n">
-        <v>212.796194392322</v>
+        <v>150.0005523521421</v>
       </c>
       <c r="S6" t="n">
-        <v>9.000641780042598</v>
+        <v>9.484521859520243</v>
       </c>
       <c r="T6" t="n">
-        <v>88.34406478184701</v>
+        <v>130.7882645386654</v>
       </c>
       <c r="U6" t="n">
-        <v>1.377061659168419</v>
+        <v>22.49568349591453</v>
       </c>
       <c r="V6" t="n">
-        <v>1.731826629759498</v>
+        <v>0.1000907527908499</v>
       </c>
       <c r="W6" t="b">
         <v>1</v>
@@ -908,64 +908,64 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>837.7732934689444</v>
+        <v>866.2846900080363</v>
       </c>
       <c r="D7" t="n">
-        <v>6.753432575528466</v>
+        <v>8.995260756589422</v>
       </c>
       <c r="E7" t="n">
-        <v>190.2151386067326</v>
+        <v>176.6771407193691</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9318311810493469</v>
+        <v>0.6979028582572937</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00342625891789794</v>
+        <v>0.001823191996663809</v>
       </c>
       <c r="H7" t="n">
-        <v>919.4285746978336</v>
+        <v>920.0234447258514</v>
       </c>
       <c r="I7" t="n">
-        <v>190.2152978630455</v>
+        <v>176.6771407193691</v>
       </c>
       <c r="J7" t="n">
-        <v>9.000641470395857</v>
+        <v>9.438119575974012</v>
       </c>
       <c r="K7" t="n">
-        <v>81.65528122888918</v>
+        <v>53.73875471781514</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000159256312826983</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M7" t="n">
-        <v>2.247208894867391</v>
+        <v>0.4428588193845897</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9940164089202881</v>
+        <v>0.9147205948829651</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0008019836386665702</v>
+        <v>0.0008118203841149807</v>
       </c>
       <c r="Q7" t="n">
-        <v>930.3887040062316</v>
+        <v>937.3181585469058</v>
       </c>
       <c r="R7" t="n">
-        <v>192.1108243414958</v>
+        <v>177.9227023451915</v>
       </c>
       <c r="S7" t="n">
-        <v>9.000641542753687</v>
+        <v>9.124220769798955</v>
       </c>
       <c r="T7" t="n">
-        <v>92.61541053728718</v>
+        <v>71.03346853886956</v>
       </c>
       <c r="U7" t="n">
-        <v>1.895685734763134</v>
+        <v>1.245561625822319</v>
       </c>
       <c r="V7" t="n">
-        <v>2.247208967225221</v>
+        <v>0.1289600132095323</v>
       </c>
       <c r="W7" t="b">
         <v>1</v>
@@ -977,68 +977,68 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>925.5264205940191</v>
+        <v>941.236377616053</v>
       </c>
       <c r="D8" t="n">
-        <v>9.240641298553927</v>
+        <v>5.830052991279411</v>
       </c>
       <c r="E8" t="n">
-        <v>121.6092848320675</v>
+        <v>206.5003175015056</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9032833576202393</v>
+        <v>0.9655842781066895</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01683678291738033</v>
+        <v>0.0002531284117139876</v>
       </c>
       <c r="H8" t="n">
-        <v>949.4830945243247</v>
+        <v>940.869883521915</v>
       </c>
       <c r="I8" t="n">
-        <v>164.2954243232535</v>
+        <v>206.5003175015104</v>
       </c>
       <c r="J8" t="n">
-        <v>10.35900525829285</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K8" t="n">
-        <v>23.95667393030556</v>
+        <v>0.3664940941380337</v>
       </c>
       <c r="L8" t="n">
-        <v>42.68613949118594</v>
+        <v>4.774847184307873e-12</v>
       </c>
       <c r="M8" t="n">
-        <v>1.118363959738925</v>
+        <v>3.170588788582752</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9999545812606812</v>
+        <v>0.8467274308204651</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00681344885379076</v>
+        <v>9.20423335628584e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>800.0000219058935</v>
+        <v>940.1738274090035</v>
       </c>
       <c r="R8" t="n">
-        <v>150.0005528888143</v>
+        <v>206.2006449566969</v>
       </c>
       <c r="S8" t="n">
-        <v>9.000517302645695</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T8" t="n">
-        <v>125.5263986881256</v>
+        <v>1.062550207049526</v>
       </c>
       <c r="U8" t="n">
-        <v>28.39126805674678</v>
+        <v>0.2996725448087147</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2401239959082311</v>
+        <v>3.170588788582752</v>
       </c>
       <c r="W8" t="b">
         <v>1</v>
@@ -1050,68 +1050,68 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>946.8480970394265</v>
+        <v>877.0934940793688</v>
       </c>
       <c r="D9" t="n">
-        <v>8.922389234586777</v>
+        <v>8.507304316587792</v>
       </c>
       <c r="E9" t="n">
-        <v>138.1580572051397</v>
+        <v>190.8029197760436</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9055460095405579</v>
+        <v>0.8222670555114746</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001030128798447549</v>
+        <v>0.001392161007970572</v>
       </c>
       <c r="H9" t="n">
-        <v>946.8713463951168</v>
+        <v>925.9037157961071</v>
       </c>
       <c r="I9" t="n">
-        <v>176.1301709725823</v>
+        <v>190.8029197760437</v>
       </c>
       <c r="J9" t="n">
-        <v>9.000046829594119</v>
+        <v>9.000540538610286</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0232493556902682</v>
+        <v>48.81022171673828</v>
       </c>
       <c r="L9" t="n">
-        <v>37.97211376744261</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M9" t="n">
-        <v>0.07765759500734148</v>
+        <v>0.4932362220224942</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9997928738594055</v>
+        <v>0.905357301235199</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004489098209887743</v>
+        <v>0.0004600656393449754</v>
       </c>
       <c r="Q9" t="n">
-        <v>800.0001164632197</v>
+        <v>937.4510330395266</v>
       </c>
       <c r="R9" t="n">
-        <v>152.5000897651726</v>
+        <v>191.4340264013696</v>
       </c>
       <c r="S9" t="n">
-        <v>9.000642074482945</v>
+        <v>9.000641659469542</v>
       </c>
       <c r="T9" t="n">
-        <v>146.8479805762069</v>
+        <v>60.35753896015774</v>
       </c>
       <c r="U9" t="n">
-        <v>14.34203256003286</v>
+        <v>0.6311066253259412</v>
       </c>
       <c r="V9" t="n">
-        <v>0.07825283989616771</v>
+        <v>0.49333734288175</v>
       </c>
       <c r="W9" t="b">
         <v>1</v>
@@ -1123,68 +1123,68 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>930.9026183683185</v>
+        <v>861.2941101957704</v>
       </c>
       <c r="D10" t="n">
-        <v>9.525206097560066</v>
+        <v>7.456844375297822</v>
       </c>
       <c r="E10" t="n">
-        <v>125.4374594005599</v>
+        <v>183.8016666056681</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9060201048851013</v>
+        <v>0.9792359471321106</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3082052767276764</v>
+        <v>0.0004074503376614302</v>
       </c>
       <c r="H10" t="n">
-        <v>883.1735957798602</v>
+        <v>940.8703895322254</v>
       </c>
       <c r="I10" t="n">
-        <v>154.9694592328663</v>
+        <v>183.8016390686678</v>
       </c>
       <c r="J10" t="n">
-        <v>13.49511302625649</v>
+        <v>9.00074240025527</v>
       </c>
       <c r="K10" t="n">
-        <v>47.72902258845829</v>
+        <v>79.57627933645506</v>
       </c>
       <c r="L10" t="n">
-        <v>29.53199983230644</v>
+        <v>2.75370003066655e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>3.969906928696423</v>
+        <v>1.543898024957448</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9999504089355469</v>
+        <v>0.9938086867332458</v>
       </c>
       <c r="P10" t="n">
-        <v>0.006811983417719603</v>
+        <v>0.0008139526471495628</v>
       </c>
       <c r="Q10" t="n">
-        <v>800.0000324709177</v>
+        <v>935.8644288209084</v>
       </c>
       <c r="R10" t="n">
-        <v>150.0005529448622</v>
+        <v>185.4695796277663</v>
       </c>
       <c r="S10" t="n">
-        <v>9.000316507161397</v>
+        <v>9.000641158624035</v>
       </c>
       <c r="T10" t="n">
-        <v>130.9025858974007</v>
+        <v>74.57031862513804</v>
       </c>
       <c r="U10" t="n">
-        <v>24.56309354430238</v>
+        <v>1.667913022098162</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5248895903986686</v>
+        <v>1.543796783326213</v>
       </c>
       <c r="W10" t="b">
         <v>1</v>
@@ -1200,64 +1200,64 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>845.8345604713478</v>
+        <v>843.8714565189717</v>
       </c>
       <c r="D11" t="n">
-        <v>7.121444438263866</v>
+        <v>8.913834110200215</v>
       </c>
       <c r="E11" t="n">
-        <v>187.936628615325</v>
+        <v>204.2353346863231</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8864884376525879</v>
+        <v>0.9629010558128357</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.001197295030578971</v>
       </c>
       <c r="H11" t="n">
-        <v>933.0521472444783</v>
+        <v>925.9037179955458</v>
       </c>
       <c r="I11" t="n">
-        <v>187.9366286142111</v>
+        <v>204.2353346863231</v>
       </c>
       <c r="J11" t="n">
-        <v>9.000641774130662</v>
+        <v>9.14054197930473</v>
       </c>
       <c r="K11" t="n">
-        <v>87.21758677313051</v>
+        <v>82.03226147657404</v>
       </c>
       <c r="L11" t="n">
-        <v>1.113903635996394e-09</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="M11" t="n">
-        <v>1.879197335866795</v>
+        <v>0.2267078691045157</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9909976720809937</v>
+        <v>0.9316202998161316</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0007567066350020468</v>
+        <v>0.0008104241569526494</v>
       </c>
       <c r="Q11" t="n">
-        <v>931.6791869949426</v>
+        <v>931.1274538887245</v>
       </c>
       <c r="R11" t="n">
-        <v>190.0194687992341</v>
+        <v>202.86571498608</v>
       </c>
       <c r="S11" t="n">
-        <v>9.000641223484863</v>
+        <v>9.057323664140805</v>
       </c>
       <c r="T11" t="n">
-        <v>85.8446265235948</v>
+        <v>87.25599736975278</v>
       </c>
       <c r="U11" t="n">
-        <v>2.08284018390907</v>
+        <v>1.369619700243135</v>
       </c>
       <c r="V11" t="n">
-        <v>1.879196785220996</v>
+        <v>0.14348955394059</v>
       </c>
       <c r="W11" t="b">
         <v>1</v>
@@ -1269,68 +1269,68 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>926.488107887503</v>
+        <v>956.1855677025339</v>
       </c>
       <c r="D12" t="n">
-        <v>2.529784239256371</v>
+        <v>9.609036295539731</v>
       </c>
       <c r="E12" t="n">
-        <v>204.8976295739575</v>
+        <v>120.7957395002968</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8486842513084412</v>
+        <v>0.9834682941436768</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001007982064038515</v>
+        <v>0.0002063950814772397</v>
       </c>
       <c r="H12" t="n">
-        <v>926.4881078869265</v>
+        <v>956.2139859828969</v>
       </c>
       <c r="I12" t="n">
-        <v>204.8976295739571</v>
+        <v>176.1732562784816</v>
       </c>
       <c r="J12" t="n">
-        <v>9.000641779862162</v>
+        <v>9.609087940925981</v>
       </c>
       <c r="K12" t="n">
-        <v>5.765059540863149e-10</v>
+        <v>0.02841828036298466</v>
       </c>
       <c r="L12" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>55.37751677818477</v>
       </c>
       <c r="M12" t="n">
-        <v>6.470857540605791</v>
+        <v>5.164538625024306e-05</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0.9948940277099609</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>7.942881347844377e-05</v>
+        <v>0.001205819193273783</v>
       </c>
       <c r="Q12" t="n">
-        <v>928.8894039884373</v>
+        <v>806.7000349875539</v>
       </c>
       <c r="R12" t="n">
-        <v>204.8915238950187</v>
+        <v>150.0005524239352</v>
       </c>
       <c r="S12" t="n">
-        <v>9.000641779862162</v>
+        <v>9.49864303421038</v>
       </c>
       <c r="T12" t="n">
-        <v>2.401296100934246</v>
+        <v>149.4855327149801</v>
       </c>
       <c r="U12" t="n">
-        <v>0.006105678938865822</v>
+        <v>29.20481292363843</v>
       </c>
       <c r="V12" t="n">
-        <v>6.470857540605791</v>
+        <v>0.1103932613293512</v>
       </c>
       <c r="W12" t="b">
         <v>1</v>
@@ -1342,68 +1342,68 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>952.027795562598</v>
+        <v>882.9238867430507</v>
       </c>
       <c r="D13" t="n">
-        <v>4.656797091604268</v>
+        <v>7.391527344970747</v>
       </c>
       <c r="E13" t="n">
-        <v>186.1754126618551</v>
+        <v>179.9914727762026</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9024239182472229</v>
+        <v>0.9216844439506531</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001009692437946796</v>
+        <v>0.00115188374184072</v>
       </c>
       <c r="H13" t="n">
-        <v>952.027795562646</v>
+        <v>925.903722391216</v>
       </c>
       <c r="I13" t="n">
-        <v>186.1754126618561</v>
+        <v>179.3816766502316</v>
       </c>
       <c r="J13" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641767919562</v>
       </c>
       <c r="K13" t="n">
-        <v>4.797584551852196e-11</v>
+        <v>42.97983564816525</v>
       </c>
       <c r="L13" t="n">
-        <v>9.379164112033322e-13</v>
+        <v>0.6097961259710019</v>
       </c>
       <c r="M13" t="n">
-        <v>4.343844688257894</v>
+        <v>1.609114422948815</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9948107004165649</v>
+        <v>0.9591795206069946</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0001839407632360235</v>
+        <v>0.0005985167226754129</v>
       </c>
       <c r="Q13" t="n">
-        <v>950.1497964422522</v>
+        <v>940.4709368943387</v>
       </c>
       <c r="R13" t="n">
-        <v>186.9397681791904</v>
+        <v>181.1667405124898</v>
       </c>
       <c r="S13" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641401718326</v>
       </c>
       <c r="T13" t="n">
-        <v>1.877999120345862</v>
+        <v>57.54705015128798</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7643555173353036</v>
+        <v>1.175267736287225</v>
       </c>
       <c r="V13" t="n">
-        <v>4.343844688257894</v>
+        <v>1.609114056747579</v>
       </c>
       <c r="W13" t="b">
         <v>1</v>
@@ -1419,64 +1419,64 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>893.0387236117929</v>
+        <v>848.7136186284401</v>
       </c>
       <c r="D14" t="n">
-        <v>8.073795114468973</v>
+        <v>9.977749373670072</v>
       </c>
       <c r="E14" t="n">
-        <v>215.2269604592039</v>
+        <v>198.2654474321201</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8512338399887085</v>
+        <v>0.6788570880889893</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.0009468119242228568</v>
       </c>
       <c r="H14" t="n">
-        <v>933.0453223404814</v>
+        <v>920.0548587821094</v>
       </c>
       <c r="I14" t="n">
-        <v>215.2269604592034</v>
+        <v>198.2654474321198</v>
       </c>
       <c r="J14" t="n">
-        <v>9.00064138932148</v>
+        <v>9.977749373670072</v>
       </c>
       <c r="K14" t="n">
-        <v>40.00659872868857</v>
+        <v>71.34124015366922</v>
       </c>
       <c r="L14" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>3.126388037344441e-13</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9268462748525064</v>
+        <v>0</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5668800473213196</v>
+        <v>0.6402310729026794</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0003507932124193758</v>
+        <v>0.0005777662736363709</v>
       </c>
       <c r="Q14" t="n">
-        <v>934.7396900659435</v>
+        <v>918.9948686969481</v>
       </c>
       <c r="R14" t="n">
-        <v>214.2867320423746</v>
+        <v>198.4618634645798</v>
       </c>
       <c r="S14" t="n">
-        <v>9.000641719708399</v>
+        <v>10.08806581593034</v>
       </c>
       <c r="T14" t="n">
-        <v>41.7009664541506</v>
+        <v>70.28125006850792</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9402284168292567</v>
+        <v>0.1964160324597231</v>
       </c>
       <c r="V14" t="n">
-        <v>0.926846605239426</v>
+        <v>0.110316442260272</v>
       </c>
       <c r="W14" t="b">
         <v>1</v>
@@ -1492,64 +1492,64 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>920.4477518616111</v>
+        <v>961.807244162299</v>
       </c>
       <c r="D15" t="n">
-        <v>5.399449507428002</v>
+        <v>5.776420331070021</v>
       </c>
       <c r="E15" t="n">
-        <v>193.8694212945647</v>
+        <v>202.8315364014022</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7920407652854919</v>
+        <v>0.7952963709831238</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001006337930448353</v>
+        <v>0.000253947131568566</v>
       </c>
       <c r="H15" t="n">
-        <v>920.4477518616443</v>
+        <v>961.8072441622284</v>
       </c>
       <c r="I15" t="n">
-        <v>193.8695360089797</v>
+        <v>202.8315364014029</v>
       </c>
       <c r="J15" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="K15" t="n">
-        <v>3.319655661471188e-11</v>
+        <v>7.059952622512355e-11</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0001147144149911128</v>
+        <v>7.105427357601002e-13</v>
       </c>
       <c r="M15" t="n">
-        <v>3.601192272434161</v>
+        <v>3.224221448792141</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8327110409736633</v>
+        <v>0.8996849656105042</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0001308294740738347</v>
+        <v>9.912327368510887e-05</v>
       </c>
       <c r="Q15" t="n">
-        <v>925.0065121095117</v>
+        <v>955.5901352049857</v>
       </c>
       <c r="R15" t="n">
-        <v>194.1850604810351</v>
+        <v>202.3649107996706</v>
       </c>
       <c r="S15" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="T15" t="n">
-        <v>4.558760247900636</v>
+        <v>6.217108957313258</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3156391864703778</v>
+        <v>0.4666256017315504</v>
       </c>
       <c r="V15" t="n">
-        <v>3.601192272434161</v>
+        <v>3.224221448792141</v>
       </c>
       <c r="W15" t="b">
         <v>1</v>
@@ -1565,64 +1565,64 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>873.2174027771838</v>
+        <v>820.2728574140868</v>
       </c>
       <c r="D16" t="n">
-        <v>8.013912992634639</v>
+        <v>7.327058662315346</v>
       </c>
       <c r="E16" t="n">
-        <v>207.6909897806796</v>
+        <v>220.7869893880287</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9079104661941528</v>
+        <v>0.9842979311943054</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.001060195965692401</v>
       </c>
       <c r="H16" t="n">
-        <v>933.0453168724518</v>
+        <v>937.9053910882772</v>
       </c>
       <c r="I16" t="n">
-        <v>207.6909897806796</v>
+        <v>220.1042600299626</v>
       </c>
       <c r="J16" t="n">
-        <v>9.000641731294142</v>
+        <v>9.000645620321198</v>
       </c>
       <c r="K16" t="n">
-        <v>59.82791409526806</v>
+        <v>117.6325336741903</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.6827293580660694</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9867287386595027</v>
+        <v>1.673586958005852</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9426078200340271</v>
+        <v>0.996921181678772</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0004555612686090171</v>
+        <v>0.001144251204095781</v>
       </c>
       <c r="Q16" t="n">
-        <v>931.4591806257216</v>
+        <v>934.1263414437773</v>
       </c>
       <c r="R16" t="n">
-        <v>207.3560650221063</v>
+        <v>218.1800748214364</v>
       </c>
       <c r="S16" t="n">
-        <v>9.00064179623668</v>
+        <v>9.00064143614474</v>
       </c>
       <c r="T16" t="n">
-        <v>58.24177784853782</v>
+        <v>113.8534840296904</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3349247585732655</v>
+        <v>2.606914566592252</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9867288036020412</v>
+        <v>1.673582773829394</v>
       </c>
       <c r="W16" t="b">
         <v>1</v>
@@ -1638,64 +1638,64 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>870.0683359708542</v>
+        <v>885.1661868745564</v>
       </c>
       <c r="D17" t="n">
-        <v>7.967527244884925</v>
+        <v>8.240226798135994</v>
       </c>
       <c r="E17" t="n">
-        <v>218.8704895387035</v>
+        <v>192.5125193001751</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8978111743927002</v>
+        <v>0.8579790592193604</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.0004035303718410432</v>
       </c>
       <c r="H17" t="n">
-        <v>933.0453231485079</v>
+        <v>940.8711338869272</v>
       </c>
       <c r="I17" t="n">
-        <v>218.8704895387038</v>
+        <v>192.5125193001732</v>
       </c>
       <c r="J17" t="n">
-        <v>9.000641515419224</v>
+        <v>9.000641706318349</v>
       </c>
       <c r="K17" t="n">
-        <v>62.97698717765377</v>
+        <v>55.70494701237078</v>
       </c>
       <c r="L17" t="n">
-        <v>3.126388037344441e-13</v>
+        <v>1.932676241267473e-12</v>
       </c>
       <c r="M17" t="n">
-        <v>1.033114270534298</v>
+        <v>0.760414908182355</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9329906702041626</v>
+        <v>0.8316174745559692</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0005669897072948515</v>
+        <v>0.0003955218999180943</v>
       </c>
       <c r="Q17" t="n">
-        <v>932.6745823948378</v>
+        <v>937.9754251215503</v>
       </c>
       <c r="R17" t="n">
-        <v>217.1156120884552</v>
+        <v>193.0669831017955</v>
       </c>
       <c r="S17" t="n">
-        <v>9.000641438366646</v>
+        <v>9.000641840584759</v>
       </c>
       <c r="T17" t="n">
-        <v>62.60624642398363</v>
+        <v>52.80923824699391</v>
       </c>
       <c r="U17" t="n">
-        <v>1.754877450248301</v>
+        <v>0.5544638016204146</v>
       </c>
       <c r="V17" t="n">
-        <v>1.033114193481721</v>
+        <v>0.7604150424487646</v>
       </c>
       <c r="W17" t="b">
         <v>1</v>
@@ -1707,68 +1707,68 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>928.336231066679</v>
+        <v>923.3756002298574</v>
       </c>
       <c r="D18" t="n">
-        <v>15.080408447795</v>
+        <v>6.591725410672975</v>
       </c>
       <c r="E18" t="n">
-        <v>206.9551153259485</v>
+        <v>210.8643918262847</v>
       </c>
       <c r="F18" t="n">
-        <v>0.808607816696167</v>
+        <v>0.6072345972061157</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0006024915492162108</v>
+        <v>0.00027896897518076</v>
       </c>
       <c r="H18" t="n">
-        <v>928.3360848535272</v>
+        <v>923.5689299805319</v>
       </c>
       <c r="I18" t="n">
-        <v>206.955115325948</v>
+        <v>210.8644338795117</v>
       </c>
       <c r="J18" t="n">
-        <v>11.82181869723987</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0001462131518792376</v>
+        <v>0.193329750674593</v>
       </c>
       <c r="L18" t="n">
-        <v>5.684341886080801e-13</v>
+        <v>4.205322696293479e-05</v>
       </c>
       <c r="M18" t="n">
-        <v>3.258589750555128</v>
+        <v>2.408916369189187</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0.992428719997406</v>
+        <v>0.2149681448936462</v>
       </c>
       <c r="P18" t="n">
-        <v>0.003744108136743307</v>
+        <v>0.0001078279528883286</v>
       </c>
       <c r="Q18" t="n">
-        <v>800.0002067412524</v>
+        <v>926.7729900152885</v>
       </c>
       <c r="R18" t="n">
-        <v>209.4596136620074</v>
+        <v>211.0144049665592</v>
       </c>
       <c r="S18" t="n">
-        <v>13.82712360716748</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T18" t="n">
-        <v>128.3360243254266</v>
+        <v>3.397389785431187</v>
       </c>
       <c r="U18" t="n">
-        <v>2.504498336058873</v>
+        <v>0.1500131402744671</v>
       </c>
       <c r="V18" t="n">
-        <v>1.25328484062752</v>
+        <v>2.408916369189187</v>
       </c>
       <c r="W18" t="b">
         <v>1</v>
@@ -1780,68 +1780,68 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>911.7671889869648</v>
+        <v>982.9256676716795</v>
       </c>
       <c r="D19" t="n">
-        <v>14.35672491529613</v>
+        <v>10.39192749632255</v>
       </c>
       <c r="E19" t="n">
-        <v>209.1110804489853</v>
+        <v>122.8959397398837</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8073925971984863</v>
+        <v>0.9723821878433228</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0006009557982906699</v>
+        <v>0.001777262426912785</v>
       </c>
       <c r="H19" t="n">
-        <v>911.7671889876393</v>
+        <v>980.6562466243272</v>
       </c>
       <c r="I19" t="n">
-        <v>209.1110188661193</v>
+        <v>173.8994571341418</v>
       </c>
       <c r="J19" t="n">
-        <v>11.8218186837652</v>
+        <v>10.39192679211197</v>
       </c>
       <c r="K19" t="n">
-        <v>6.745040082023479e-10</v>
+        <v>2.269421047352353</v>
       </c>
       <c r="L19" t="n">
-        <v>6.158286595336904e-05</v>
+        <v>51.00351739425815</v>
       </c>
       <c r="M19" t="n">
-        <v>2.534906231530936</v>
+        <v>7.042105814036859e-07</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9235931038856506</v>
+        <v>0.9999998807907104</v>
       </c>
       <c r="P19" t="n">
-        <v>0.002666007960215211</v>
+        <v>0.001379667315632105</v>
       </c>
       <c r="Q19" t="n">
-        <v>800.8990815772046</v>
+        <v>802.2463404644901</v>
       </c>
       <c r="R19" t="n">
-        <v>210.7943469705368</v>
+        <v>150.0005522524178</v>
       </c>
       <c r="S19" t="n">
-        <v>13.5760774326327</v>
+        <v>10.251242020522</v>
       </c>
       <c r="T19" t="n">
-        <v>110.8681074097602</v>
+        <v>180.6793272071894</v>
       </c>
       <c r="U19" t="n">
-        <v>1.683266521551559</v>
+        <v>27.10461251253409</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7806474826634329</v>
+        <v>0.1406854758005522</v>
       </c>
       <c r="W19" t="b">
         <v>1</v>
@@ -1853,68 +1853,68 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>872.3088207217586</v>
+        <v>928.7700471758762</v>
       </c>
       <c r="D20" t="n">
-        <v>5.997991866309297</v>
+        <v>4.990616426953078</v>
       </c>
       <c r="E20" t="n">
-        <v>194.5602717348846</v>
+        <v>206.8596956383927</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9218559265136719</v>
+        <v>0.9851580262184143</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.0002752725849859416</v>
       </c>
       <c r="H20" t="n">
-        <v>933.0453188157161</v>
+        <v>928.7700471761835</v>
       </c>
       <c r="I20" t="n">
-        <v>194.5602717348846</v>
+        <v>206.8596956383719</v>
       </c>
       <c r="J20" t="n">
-        <v>9.000641460635768</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K20" t="n">
-        <v>60.73649809395749</v>
+        <v>3.072955223615281e-10</v>
       </c>
       <c r="L20" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>2.080469130305573e-11</v>
       </c>
       <c r="M20" t="n">
-        <v>3.002649594326471</v>
+        <v>4.010025352909084</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0.983623206615448</v>
+        <v>0.9745203852653503</v>
       </c>
       <c r="P20" t="n">
-        <v>0.0004763400938827544</v>
+        <v>9.672575833974406e-05</v>
       </c>
       <c r="Q20" t="n">
-        <v>932.3340483433182</v>
+        <v>931.5014521472814</v>
       </c>
       <c r="R20" t="n">
-        <v>195.4742354627464</v>
+        <v>206.8819205344054</v>
       </c>
       <c r="S20" t="n">
-        <v>9.000641710559979</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T20" t="n">
-        <v>60.02522762155957</v>
+        <v>2.731404971405141</v>
       </c>
       <c r="U20" t="n">
-        <v>0.913963727861784</v>
+        <v>0.0222248960126592</v>
       </c>
       <c r="V20" t="n">
-        <v>3.002649844250682</v>
+        <v>4.010025352909084</v>
       </c>
       <c r="W20" t="b">
         <v>1</v>
@@ -1926,68 +1926,68 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>862.4995334483451</v>
+        <v>960.0499939225858</v>
       </c>
       <c r="D21" t="n">
-        <v>9.063402892415709</v>
+        <v>6.196926327266365</v>
       </c>
       <c r="E21" t="n">
-        <v>198.8624436728534</v>
+        <v>201.8401166993026</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6929391622543335</v>
+        <v>0.7952963709831238</v>
       </c>
       <c r="G21" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.0002481373958289623</v>
       </c>
       <c r="H21" t="n">
-        <v>933.045314793127</v>
+        <v>957.5953327879187</v>
       </c>
       <c r="I21" t="n">
-        <v>198.8624436728534</v>
+        <v>201.840116699303</v>
       </c>
       <c r="J21" t="n">
-        <v>9.063484785375332</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K21" t="n">
-        <v>70.54578134478186</v>
+        <v>2.454661134667163</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>4.263256414560601e-13</v>
       </c>
       <c r="M21" t="n">
-        <v>8.18929596224649e-05</v>
+        <v>2.803715452595798</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8879396915435791</v>
+        <v>0.7199969887733459</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0005059161339886487</v>
+        <v>9.093464177567512e-05</v>
       </c>
       <c r="Q21" t="n">
-        <v>929.3283213572553</v>
+        <v>955.6526061024898</v>
       </c>
       <c r="R21" t="n">
-        <v>199.4055310231324</v>
+        <v>201.5062186996885</v>
       </c>
       <c r="S21" t="n">
-        <v>9.146813060403945</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T21" t="n">
-        <v>66.82878790891016</v>
+        <v>4.397387820096014</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5430873502789382</v>
+        <v>0.3338979996140665</v>
       </c>
       <c r="V21" t="n">
-        <v>0.08341016798823553</v>
+        <v>2.803715452595798</v>
       </c>
       <c r="W21" t="b">
         <v>1</v>
@@ -2003,64 +2003,64 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>833.9053299675722</v>
+        <v>888.2055850320147</v>
       </c>
       <c r="D22" t="n">
-        <v>6.739674607954534</v>
+        <v>8.074739075875389</v>
       </c>
       <c r="E22" t="n">
-        <v>211.5352295757988</v>
+        <v>207.9615602408907</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9285228848457336</v>
+        <v>0.7019981145858765</v>
       </c>
       <c r="G22" t="n">
-        <v>0.003427958348765969</v>
+        <v>0.000411912944400683</v>
       </c>
       <c r="H22" t="n">
-        <v>919.4284671926684</v>
+        <v>940.8700915289151</v>
       </c>
       <c r="I22" t="n">
-        <v>211.5352295758159</v>
+        <v>207.9615602408907</v>
       </c>
       <c r="J22" t="n">
-        <v>9.00064149937015</v>
+        <v>9.000641655378949</v>
       </c>
       <c r="K22" t="n">
-        <v>85.52313722509621</v>
+        <v>52.66450649690034</v>
       </c>
       <c r="L22" t="n">
-        <v>1.710986907710321e-11</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.260966891415617</v>
+        <v>0.9259025795035605</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9919396042823792</v>
+        <v>0.7525087594985962</v>
       </c>
       <c r="P22" t="n">
-        <v>0.0008126465254463255</v>
+        <v>0.0003843112499453127</v>
       </c>
       <c r="Q22" t="n">
-        <v>928.449079809769</v>
+        <v>938.665155213009</v>
       </c>
       <c r="R22" t="n">
-        <v>210.5350275243712</v>
+        <v>206.93691963733</v>
       </c>
       <c r="S22" t="n">
-        <v>9.000641794504519</v>
+        <v>9.000641479829829</v>
       </c>
       <c r="T22" t="n">
-        <v>94.5437498421968</v>
+        <v>50.45957018099432</v>
       </c>
       <c r="U22" t="n">
-        <v>1.000202051427635</v>
+        <v>1.024640603560641</v>
       </c>
       <c r="V22" t="n">
-        <v>2.260967186549985</v>
+        <v>0.9259024039544403</v>
       </c>
       <c r="W22" t="b">
         <v>1</v>
@@ -2072,68 +2072,68 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>919.4196995117043</v>
+        <v>829.3002648931302</v>
       </c>
       <c r="D23" t="n">
-        <v>4.403121322198782</v>
+        <v>9.126064977223706</v>
       </c>
       <c r="E23" t="n">
-        <v>191.226696989756</v>
+        <v>198.6980166651521</v>
       </c>
       <c r="F23" t="n">
-        <v>0.805339515209198</v>
+        <v>0.9158090949058533</v>
       </c>
       <c r="G23" t="n">
-        <v>0.001005758997052908</v>
+        <v>0.001327915932051837</v>
       </c>
       <c r="H23" t="n">
-        <v>919.419699510728</v>
+        <v>925.9037229340205</v>
       </c>
       <c r="I23" t="n">
-        <v>191.2266667868728</v>
+        <v>198.6980166651561</v>
       </c>
       <c r="J23" t="n">
-        <v>9.000641779862162</v>
+        <v>9.140537946887919</v>
       </c>
       <c r="K23" t="n">
-        <v>9.762288755155168e-10</v>
+        <v>96.60345804089025</v>
       </c>
       <c r="L23" t="n">
-        <v>3.020288323796194e-05</v>
+        <v>4.007461029686965e-12</v>
       </c>
       <c r="M23" t="n">
-        <v>4.59752045766338</v>
+        <v>0.01447296966421341</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9488726258277893</v>
+        <v>0.9185240268707275</v>
       </c>
       <c r="P23" t="n">
-        <v>0.000158387643750757</v>
+        <v>0.0008830088190734386</v>
       </c>
       <c r="Q23" t="n">
-        <v>924.6552355079745</v>
+        <v>925.7961345245654</v>
       </c>
       <c r="R23" t="n">
-        <v>191.6740524889995</v>
+        <v>199.984272134458</v>
       </c>
       <c r="S23" t="n">
-        <v>9.000641779862162</v>
+        <v>9.328020855699309</v>
       </c>
       <c r="T23" t="n">
-        <v>5.235535996270187</v>
+        <v>96.4958696314352</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4473554992435425</v>
+        <v>1.286255469305871</v>
       </c>
       <c r="V23" t="n">
-        <v>4.59752045766338</v>
+        <v>0.2019558784756033</v>
       </c>
       <c r="W23" t="b">
         <v>1</v>
@@ -2145,68 +2145,68 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>952.2244666968172</v>
+        <v>962.1201990269128</v>
       </c>
       <c r="D24" t="n">
-        <v>9.374842474547272</v>
+        <v>6.589725558079908</v>
       </c>
       <c r="E24" t="n">
-        <v>143.7893713723858</v>
+        <v>202.6234247915652</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9065526127815247</v>
+        <v>0.578937828540802</v>
       </c>
       <c r="G24" t="n">
-        <v>0.001030103303492069</v>
+        <v>0.000253947131568566</v>
       </c>
       <c r="H24" t="n">
-        <v>952.2237433096756</v>
+        <v>962.1201990269394</v>
       </c>
       <c r="I24" t="n">
-        <v>176.1300422857316</v>
+        <v>202.6234247915654</v>
       </c>
       <c r="J24" t="n">
-        <v>9.374850103793611</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0007233871416474358</v>
+        <v>2.660272002685815e-11</v>
       </c>
       <c r="L24" t="n">
-        <v>32.3406709133458</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="M24" t="n">
-        <v>7.629246338680673e-06</v>
+        <v>2.410916221782254</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9995040893554688</v>
+        <v>0.384284108877182</v>
       </c>
       <c r="P24" t="n">
-        <v>0.003259731689468026</v>
+        <v>9.885372128337622e-05</v>
       </c>
       <c r="Q24" t="n">
-        <v>800.0005237085558</v>
+        <v>955.9111106197507</v>
       </c>
       <c r="R24" t="n">
-        <v>154.8642565598411</v>
+        <v>202.1605808544388</v>
       </c>
       <c r="S24" t="n">
-        <v>9.068700901537206</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T24" t="n">
-        <v>152.2239429882615</v>
+        <v>6.209088407162085</v>
       </c>
       <c r="U24" t="n">
-        <v>11.07488518745524</v>
+        <v>0.4628439371263937</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3061415730100663</v>
+        <v>2.410916221782254</v>
       </c>
       <c r="W24" t="b">
         <v>1</v>
@@ -2218,68 +2218,68 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>956.2277987539286</v>
+        <v>963.1849133686482</v>
       </c>
       <c r="D25" t="n">
-        <v>4.811217842338543</v>
+        <v>7.790920947512554</v>
       </c>
       <c r="E25" t="n">
-        <v>194.0256945301476</v>
+        <v>136.9652156072593</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9024178981781006</v>
+        <v>0.9558945894241333</v>
       </c>
       <c r="G25" t="n">
-        <v>0.001009689178317785</v>
+        <v>0.000221210895688273</v>
       </c>
       <c r="H25" t="n">
-        <v>956.2278164579523</v>
+        <v>963.1849133869182</v>
       </c>
       <c r="I25" t="n">
-        <v>194.0256945301476</v>
+        <v>176.1732576611711</v>
       </c>
       <c r="J25" t="n">
-        <v>9.000641779862162</v>
+        <v>9.00000171320859</v>
       </c>
       <c r="K25" t="n">
-        <v>1.770402366219059e-05</v>
+        <v>1.82700432560523e-08</v>
       </c>
       <c r="L25" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>39.20804205391184</v>
       </c>
       <c r="M25" t="n">
-        <v>4.189423937523619</v>
+        <v>1.209080765696037</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9954556226730347</v>
+        <v>0.9999759197235107</v>
       </c>
       <c r="P25" t="n">
-        <v>9.789256000658497e-05</v>
+        <v>0.001095251413062215</v>
       </c>
       <c r="Q25" t="n">
-        <v>954.0561715566727</v>
+        <v>809.9402019035333</v>
       </c>
       <c r="R25" t="n">
-        <v>194.2776007423727</v>
+        <v>150.0005525357284</v>
       </c>
       <c r="S25" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641702659145</v>
       </c>
       <c r="T25" t="n">
-        <v>2.17162719725593</v>
+        <v>153.2447114651148</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2519062122250375</v>
+        <v>13.03533692846915</v>
       </c>
       <c r="V25" t="n">
-        <v>4.189423937523619</v>
+        <v>1.209720755146591</v>
       </c>
       <c r="W25" t="b">
         <v>1</v>
@@ -2295,64 +2295,64 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>953.8523829517387</v>
+        <v>921.5473306157119</v>
       </c>
       <c r="D26" t="n">
-        <v>5.686118461029691</v>
+        <v>1.579754803432637</v>
       </c>
       <c r="E26" t="n">
-        <v>197.2173923656629</v>
+        <v>197.3268465800665</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8952300548553467</v>
+        <v>0.9593200087547302</v>
       </c>
       <c r="G26" t="n">
-        <v>0.001009692437946796</v>
+        <v>0.0002819020883180201</v>
       </c>
       <c r="H26" t="n">
-        <v>953.8523829517435</v>
+        <v>921.5473306165907</v>
       </c>
       <c r="I26" t="n">
-        <v>197.2173923656629</v>
+        <v>197.3268466222976</v>
       </c>
       <c r="J26" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="K26" t="n">
-        <v>4.774847184307873e-12</v>
+        <v>8.787992555880919e-10</v>
       </c>
       <c r="L26" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>4.223102223477326e-08</v>
       </c>
       <c r="M26" t="n">
-        <v>3.314523318832471</v>
+        <v>7.420886976429525</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.9684089422225952</v>
+        <v>0.999847412109375</v>
       </c>
       <c r="P26" t="n">
-        <v>7.875309529481456e-05</v>
+        <v>0.0001655499800108373</v>
       </c>
       <c r="Q26" t="n">
-        <v>952.2779037561498</v>
+        <v>929.307332401006</v>
       </c>
       <c r="R26" t="n">
-        <v>197.359555974358</v>
+        <v>197.8663378519999</v>
       </c>
       <c r="S26" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="T26" t="n">
-        <v>1.574479195588879</v>
+        <v>7.760001785294094</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1421636086951423</v>
+        <v>0.5394912719333433</v>
       </c>
       <c r="V26" t="n">
-        <v>3.314523318832471</v>
+        <v>7.420886976429525</v>
       </c>
       <c r="W26" t="b">
         <v>1</v>
@@ -2364,68 +2364,68 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>890.1597844686212</v>
+        <v>979.6651776971319</v>
       </c>
       <c r="D27" t="n">
-        <v>6.759569324867613</v>
+        <v>5.196853798040799</v>
       </c>
       <c r="E27" t="n">
-        <v>199.571267049108</v>
+        <v>191.5825472588185</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8561516404151917</v>
+        <v>0.9209200143814087</v>
       </c>
       <c r="G27" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.000253947131568566</v>
       </c>
       <c r="H27" t="n">
-        <v>933.0453194073473</v>
+        <v>979.6651776971187</v>
       </c>
       <c r="I27" t="n">
-        <v>199.571267049108</v>
+        <v>191.5825472588183</v>
       </c>
       <c r="J27" t="n">
-        <v>9.000641455569848</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K27" t="n">
-        <v>42.8855349387261</v>
+        <v>1.318767317570746e-11</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="M27" t="n">
-        <v>2.241072130702236</v>
+        <v>3.803787981821364</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>0.9055102467536926</v>
+        <v>0.9783687591552734</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0003290710155852139</v>
+        <v>0.0002305722155142576</v>
       </c>
       <c r="Q27" t="n">
-        <v>933.5256557902768</v>
+        <v>966.2149183878104</v>
       </c>
       <c r="R27" t="n">
-        <v>199.8990573379143</v>
+        <v>192.2770742262953</v>
       </c>
       <c r="S27" t="n">
-        <v>9.000641688101206</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T27" t="n">
-        <v>43.36587132165562</v>
+        <v>13.4502593093215</v>
       </c>
       <c r="U27" t="n">
-        <v>0.3277902888062556</v>
+        <v>0.6945269674767474</v>
       </c>
       <c r="V27" t="n">
-        <v>2.241072363233593</v>
+        <v>3.803787981821364</v>
       </c>
       <c r="W27" t="b">
         <v>1</v>
@@ -2437,68 +2437,68 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>931.4457141543127</v>
+        <v>1010.098879449908</v>
       </c>
       <c r="D28" t="n">
-        <v>5.966615046177687</v>
+        <v>9.458817302534468</v>
       </c>
       <c r="E28" t="n">
-        <v>195.8168760577822</v>
+        <v>195.5915518803773</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8818866610527039</v>
+        <v>0.7058996558189392</v>
       </c>
       <c r="G28" t="n">
-        <v>0.001008538878522813</v>
+        <v>0.0001050807259161957</v>
       </c>
       <c r="H28" t="n">
-        <v>931.4457141549879</v>
+        <v>985.8937780007902</v>
       </c>
       <c r="I28" t="n">
-        <v>195.8168760577822</v>
+        <v>195.5914779393746</v>
       </c>
       <c r="J28" t="n">
-        <v>9.000641779862162</v>
+        <v>9.458810875340344</v>
       </c>
       <c r="K28" t="n">
-        <v>6.751861292286776e-10</v>
+        <v>24.20510144911805</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>7.394100262558823e-05</v>
       </c>
       <c r="M28" t="n">
-        <v>3.034026733684476</v>
+        <v>6.427194124469793e-06</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>0.8182072639465332</v>
+        <v>0.2233198583126068</v>
       </c>
       <c r="P28" t="n">
-        <v>8.831613376969472e-05</v>
+        <v>0.0001602740812813863</v>
       </c>
       <c r="Q28" t="n">
-        <v>933.3959975134389</v>
+        <v>973.0537009867018</v>
       </c>
       <c r="R28" t="n">
-        <v>196.0145772467511</v>
+        <v>194.946216007718</v>
       </c>
       <c r="S28" t="n">
-        <v>9.000641779862162</v>
+        <v>9.458934504884526</v>
       </c>
       <c r="T28" t="n">
-        <v>1.950283359126274</v>
+        <v>37.04517846320653</v>
       </c>
       <c r="U28" t="n">
-        <v>0.1977011889689493</v>
+        <v>0.6453358726593024</v>
       </c>
       <c r="V28" t="n">
-        <v>3.034026733684476</v>
+        <v>0.0001172023500579655</v>
       </c>
       <c r="W28" t="b">
         <v>1</v>
@@ -2514,64 +2514,64 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>876.039542019205</v>
+        <v>880.7493568531423</v>
       </c>
       <c r="D29" t="n">
-        <v>7.762170518968503</v>
+        <v>8.683454608493577</v>
       </c>
       <c r="E29" t="n">
-        <v>199.3835674526191</v>
+        <v>188.591225330526</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8770247101783752</v>
+        <v>0.7772117853164673</v>
       </c>
       <c r="G29" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.001392161007970572</v>
       </c>
       <c r="H29" t="n">
-        <v>933.0453165345622</v>
+        <v>925.9044564923068</v>
       </c>
       <c r="I29" t="n">
-        <v>199.3835674526191</v>
+        <v>188.5912253305267</v>
       </c>
       <c r="J29" t="n">
-        <v>9.000641444380859</v>
+        <v>9.000458133074735</v>
       </c>
       <c r="K29" t="n">
-        <v>57.00577451535719</v>
+        <v>45.15509963916452</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>6.536993168992922e-13</v>
       </c>
       <c r="M29" t="n">
-        <v>1.238470925412356</v>
+        <v>0.3170035245811587</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0.9504122138023376</v>
+        <v>0.8484960794448853</v>
       </c>
       <c r="P29" t="n">
-        <v>0.0004275877145119011</v>
+        <v>0.0004724953614640981</v>
       </c>
       <c r="Q29" t="n">
-        <v>931.9960616942669</v>
+        <v>937.580897911713</v>
       </c>
       <c r="R29" t="n">
-        <v>199.8138056945083</v>
+        <v>190.1407925270615</v>
       </c>
       <c r="S29" t="n">
-        <v>9.000641713001917</v>
+        <v>9.000641777042683</v>
       </c>
       <c r="T29" t="n">
-        <v>55.95651967506194</v>
+        <v>56.83154105857068</v>
       </c>
       <c r="U29" t="n">
-        <v>0.4302382418892137</v>
+        <v>1.549567196535492</v>
       </c>
       <c r="V29" t="n">
-        <v>1.238471194033414</v>
+        <v>0.3171871685491059</v>
       </c>
       <c r="W29" t="b">
         <v>1</v>
@@ -2583,68 +2583,68 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>943.9422951240201</v>
+        <v>830.9241946101021</v>
       </c>
       <c r="D30" t="n">
-        <v>10.70997486905503</v>
+        <v>8.530552348971069</v>
       </c>
       <c r="E30" t="n">
-        <v>151.5073318488736</v>
+        <v>187.7586960367381</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9065549969673157</v>
+        <v>0.9804819226264954</v>
       </c>
       <c r="G30" t="n">
-        <v>0.001030104584060609</v>
+        <v>0.001278901007026434</v>
       </c>
       <c r="H30" t="n">
-        <v>943.9423829455822</v>
+        <v>920.066988000005</v>
       </c>
       <c r="I30" t="n">
-        <v>176.1300256938736</v>
+        <v>187.3611277202333</v>
       </c>
       <c r="J30" t="n">
-        <v>10.70997659428209</v>
+        <v>9.000398779892071</v>
       </c>
       <c r="K30" t="n">
-        <v>8.782156203324121e-05</v>
+        <v>89.14279338990298</v>
       </c>
       <c r="L30" t="n">
-        <v>24.62269384500007</v>
+        <v>0.3975683165048167</v>
       </c>
       <c r="M30" t="n">
-        <v>1.725227058102519e-06</v>
+        <v>0.4698464309210024</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>0.9918924570083618</v>
+        <v>0.9746896624565125</v>
       </c>
       <c r="P30" t="n">
-        <v>0.003159148385748267</v>
+        <v>0.0008967292378656566</v>
       </c>
       <c r="Q30" t="n">
-        <v>801.2810062706731</v>
+        <v>934.0741017748486</v>
       </c>
       <c r="R30" t="n">
-        <v>163.3468738567666</v>
+        <v>189.0181080717882</v>
       </c>
       <c r="S30" t="n">
-        <v>10.40957077238443</v>
+        <v>9.000641782501154</v>
       </c>
       <c r="T30" t="n">
-        <v>142.6612888533471</v>
+        <v>103.1499071647465</v>
       </c>
       <c r="U30" t="n">
-        <v>11.83954200789299</v>
+        <v>1.259412035050019</v>
       </c>
       <c r="V30" t="n">
-        <v>0.3004040966706061</v>
+        <v>0.4700894335300845</v>
       </c>
       <c r="W30" t="b">
         <v>1</v>
@@ -2656,68 +2656,68 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>892.491731029129</v>
+        <v>948.417099474584</v>
       </c>
       <c r="D31" t="n">
-        <v>7.810111168776988</v>
+        <v>6.315913495187232</v>
       </c>
       <c r="E31" t="n">
-        <v>200.1966656998361</v>
+        <v>189.5951259527816</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8543873429298401</v>
+        <v>0.9357121586799622</v>
       </c>
       <c r="G31" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.0002481373958289623</v>
       </c>
       <c r="H31" t="n">
-        <v>933.0453213537381</v>
+        <v>948.4170994745834</v>
       </c>
       <c r="I31" t="n">
-        <v>200.1966656998361</v>
+        <v>189.5951259527817</v>
       </c>
       <c r="J31" t="n">
-        <v>9.000641440969263</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K31" t="n">
-        <v>40.5535903246091</v>
+        <v>5.684341886080801e-13</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.4210854715202e-13</v>
       </c>
       <c r="M31" t="n">
-        <v>1.190530272192275</v>
+        <v>2.684728284674931</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0.7319111824035645</v>
+        <v>0.5973597168922424</v>
       </c>
       <c r="P31" t="n">
-        <v>0.0003101793117821217</v>
+        <v>0.000136012036819011</v>
       </c>
       <c r="Q31" t="n">
-        <v>933.7979632503138</v>
+        <v>949.1320697827482</v>
       </c>
       <c r="R31" t="n">
-        <v>200.4673134555944</v>
+        <v>190.3090014250181</v>
       </c>
       <c r="S31" t="n">
-        <v>9.000641802103901</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T31" t="n">
-        <v>41.30623222118481</v>
+        <v>0.7149703081641974</v>
       </c>
       <c r="U31" t="n">
-        <v>0.2706477557583185</v>
+        <v>0.7138754722365377</v>
       </c>
       <c r="V31" t="n">
-        <v>1.190530633326913</v>
+        <v>2.684728284674931</v>
       </c>
       <c r="W31" t="b">
         <v>1</v>
@@ -2733,64 +2733,64 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>929.2378602707793</v>
+        <v>933.002481497652</v>
       </c>
       <c r="D32" t="n">
-        <v>10.46531685190464</v>
+        <v>9.181170400494413</v>
       </c>
       <c r="E32" t="n">
-        <v>126.3945203148254</v>
+        <v>141.3157333632496</v>
       </c>
       <c r="F32" t="n">
-        <v>0.906248927116394</v>
+        <v>0.9438311457633972</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3009131848812103</v>
+        <v>0.0007830621325410903</v>
       </c>
       <c r="H32" t="n">
-        <v>889.923146978501</v>
+        <v>857.2842430817823</v>
       </c>
       <c r="I32" t="n">
-        <v>154.9673492026013</v>
+        <v>176.1732571575571</v>
       </c>
       <c r="J32" t="n">
-        <v>13.49511335001083</v>
+        <v>9.181216882346309</v>
       </c>
       <c r="K32" t="n">
-        <v>39.31471329227827</v>
+        <v>75.71823841586968</v>
       </c>
       <c r="L32" t="n">
-        <v>28.57282888777593</v>
+        <v>34.85752379430758</v>
       </c>
       <c r="M32" t="n">
-        <v>3.029796498106192</v>
+        <v>4.648185189637388e-05</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>0.9999374151229858</v>
+        <v>0.9999220371246338</v>
       </c>
       <c r="P32" t="n">
-        <v>0.009384246543049812</v>
+        <v>0.0009473156533204019</v>
       </c>
       <c r="Q32" t="n">
-        <v>800.0000080722131</v>
+        <v>808.3780025139052</v>
       </c>
       <c r="R32" t="n">
-        <v>150.744039781876</v>
+        <v>150.000552462468</v>
       </c>
       <c r="S32" t="n">
-        <v>9.42738008829091</v>
+        <v>9.060269515117977</v>
       </c>
       <c r="T32" t="n">
-        <v>129.2378521985662</v>
+        <v>124.6244789837467</v>
       </c>
       <c r="U32" t="n">
-        <v>24.34951946705064</v>
+        <v>8.684819099218458</v>
       </c>
       <c r="V32" t="n">
-        <v>1.037936763613731</v>
+        <v>0.120900885376436</v>
       </c>
       <c r="W32" t="b">
         <v>1</v>
@@ -2806,64 +2806,64 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>896.3065469305708</v>
+        <v>869.6138301375908</v>
       </c>
       <c r="D33" t="n">
-        <v>8.139929682304544</v>
+        <v>6.851638222058278</v>
       </c>
       <c r="E33" t="n">
-        <v>189.2080860494468</v>
+        <v>209.7582590983853</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6450386643409729</v>
+        <v>0.985556423664093</v>
       </c>
       <c r="G33" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.000411912944400683</v>
       </c>
       <c r="H33" t="n">
-        <v>933.0453172379919</v>
+        <v>940.8724259033206</v>
       </c>
       <c r="I33" t="n">
-        <v>189.2080860494468</v>
+        <v>209.7582135058447</v>
       </c>
       <c r="J33" t="n">
-        <v>9.000641646512664</v>
+        <v>9.000792066771698</v>
       </c>
       <c r="K33" t="n">
-        <v>36.73877030742108</v>
+        <v>71.25859576572986</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>4.559254057312501e-05</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8607119642081198</v>
+        <v>2.14915384471342</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>0.4835691750049591</v>
+        <v>0.9940339922904968</v>
       </c>
       <c r="P33" t="n">
-        <v>0.0003324900171719491</v>
+        <v>0.0005393409519456327</v>
       </c>
       <c r="Q33" t="n">
-        <v>936.833944083687</v>
+        <v>937.231212664414</v>
       </c>
       <c r="R33" t="n">
-        <v>190.2503562287347</v>
+        <v>209.3073512554583</v>
       </c>
       <c r="S33" t="n">
-        <v>9.000641406274427</v>
+        <v>9.000641839176451</v>
       </c>
       <c r="T33" t="n">
-        <v>40.52739715311623</v>
+        <v>67.61738252682323</v>
       </c>
       <c r="U33" t="n">
-        <v>1.042270179287897</v>
+        <v>0.450907842926938</v>
       </c>
       <c r="V33" t="n">
-        <v>0.8607117239698834</v>
+        <v>2.149003617118173</v>
       </c>
       <c r="W33" t="b">
         <v>1</v>
@@ -2875,68 +2875,68 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>915.1328945729765</v>
+        <v>910.0002687937941</v>
       </c>
       <c r="D34" t="n">
-        <v>6.059991622037932</v>
+        <v>6.509694684952102</v>
       </c>
       <c r="E34" t="n">
-        <v>210.4936769056666</v>
+        <v>195.4662529131482</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6736760139465332</v>
+        <v>0.6023518443107605</v>
       </c>
       <c r="G34" t="n">
-        <v>0.000984171056188643</v>
+        <v>0.0004035303718410432</v>
       </c>
       <c r="H34" t="n">
-        <v>915.1328945729775</v>
+        <v>940.8700877632323</v>
       </c>
       <c r="I34" t="n">
-        <v>210.4936200339029</v>
+        <v>195.4663604418713</v>
       </c>
       <c r="J34" t="n">
-        <v>9.000641779862162</v>
+        <v>9.00064169072197</v>
       </c>
       <c r="K34" t="n">
-        <v>1.023181539494544e-12</v>
+        <v>30.86981896943814</v>
       </c>
       <c r="L34" t="n">
-        <v>5.687176368951441e-05</v>
+        <v>0.0001075287231344646</v>
       </c>
       <c r="M34" t="n">
-        <v>2.94065015782423</v>
+        <v>2.490947005769868</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0.4378473460674286</v>
+        <v>0.7095156908035278</v>
       </c>
       <c r="P34" t="n">
-        <v>0.000124749043607153</v>
+        <v>0.0002230912650702521</v>
       </c>
       <c r="Q34" t="n">
-        <v>920.0335508665838</v>
+        <v>940.9225514289294</v>
       </c>
       <c r="R34" t="n">
-        <v>210.3537102698414</v>
+        <v>195.5942420968957</v>
       </c>
       <c r="S34" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641738451689</v>
       </c>
       <c r="T34" t="n">
-        <v>4.900656293607312</v>
+        <v>30.92228263513528</v>
       </c>
       <c r="U34" t="n">
-        <v>0.1399666358252603</v>
+        <v>0.1279891837475304</v>
       </c>
       <c r="V34" t="n">
-        <v>2.94065015782423</v>
+        <v>2.490947053499587</v>
       </c>
       <c r="W34" t="b">
         <v>1</v>
@@ -2948,68 +2948,68 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>859.049721060047</v>
+        <v>944.2477137625015</v>
       </c>
       <c r="D35" t="n">
-        <v>9.20155298729558</v>
+        <v>6.713790928942508</v>
       </c>
       <c r="E35" t="n">
-        <v>189.0584905356224</v>
+        <v>202.9110208185347</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6800032258033752</v>
+        <v>0.5389013886451721</v>
       </c>
       <c r="G35" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.000253292266279459</v>
       </c>
       <c r="H35" t="n">
-        <v>933.0453175131333</v>
+        <v>944.2477137625023</v>
       </c>
       <c r="I35" t="n">
-        <v>189.0584905356224</v>
+        <v>202.9110208185284</v>
       </c>
       <c r="J35" t="n">
-        <v>9.201547175138938</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K35" t="n">
-        <v>73.99559645308636</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>6.338041202980094e-12</v>
       </c>
       <c r="M35" t="n">
-        <v>5.812156642193145e-06</v>
+        <v>2.286850850919654</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>0.8762199878692627</v>
+        <v>0.2857986986637115</v>
       </c>
       <c r="P35" t="n">
-        <v>0.0005770547431893647</v>
+        <v>6.801854760851711e-05</v>
       </c>
       <c r="Q35" t="n">
-        <v>929.5407158013484</v>
+        <v>944.2045204081038</v>
       </c>
       <c r="R35" t="n">
-        <v>190.6089707428995</v>
+        <v>202.6210047121934</v>
       </c>
       <c r="S35" t="n">
-        <v>9.291360846420563</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T35" t="n">
-        <v>70.49099474130139</v>
+        <v>0.04319335439765837</v>
       </c>
       <c r="U35" t="n">
-        <v>1.550480207277076</v>
+        <v>0.2900161063413123</v>
       </c>
       <c r="V35" t="n">
-        <v>0.08980785912498312</v>
+        <v>2.286850850919654</v>
       </c>
       <c r="W35" t="b">
         <v>1</v>
@@ -3021,68 +3021,68 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>952.2225875059303</v>
+        <v>960.1745004645986</v>
       </c>
       <c r="D36" t="n">
-        <v>8.982060962729719</v>
+        <v>6.919401272826073</v>
       </c>
       <c r="E36" t="n">
-        <v>134.8889820198774</v>
+        <v>194.5526131976476</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9065995812416077</v>
+        <v>0.5939324498176575</v>
       </c>
       <c r="G36" t="n">
-        <v>0.001030128798447549</v>
+        <v>0.000253947131568566</v>
       </c>
       <c r="H36" t="n">
-        <v>952.2484980377182</v>
+        <v>960.7595512215461</v>
       </c>
       <c r="I36" t="n">
-        <v>176.1328449451751</v>
+        <v>194.5526131976409</v>
       </c>
       <c r="J36" t="n">
-        <v>9.000377581460532</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K36" t="n">
-        <v>0.02591053178787206</v>
+        <v>0.585050756947453</v>
       </c>
       <c r="L36" t="n">
-        <v>41.24386292529766</v>
+        <v>6.650680006714538e-12</v>
       </c>
       <c r="M36" t="n">
-        <v>0.01831661873081281</v>
+        <v>2.08124050703609</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>0.9998905658721924</v>
+        <v>0.2214724123477936</v>
       </c>
       <c r="P36" t="n">
-        <v>0.005409229081124067</v>
+        <v>9.755695646163076e-05</v>
       </c>
       <c r="Q36" t="n">
-        <v>800.0000415835403</v>
+        <v>954.8750935505767</v>
       </c>
       <c r="R36" t="n">
-        <v>151.3825738093049</v>
+        <v>194.8541510484343</v>
       </c>
       <c r="S36" t="n">
-        <v>9.000642091291407</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T36" t="n">
-        <v>152.2225459223899</v>
+        <v>5.299406914021915</v>
       </c>
       <c r="U36" t="n">
-        <v>16.49359178942751</v>
+        <v>0.3015378507867013</v>
       </c>
       <c r="V36" t="n">
-        <v>0.01858112856168859</v>
+        <v>2.08124050703609</v>
       </c>
       <c r="W36" t="b">
         <v>1</v>
@@ -3094,68 +3094,68 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>957.2734529567797</v>
+        <v>891.8415293788554</v>
       </c>
       <c r="D37" t="n">
-        <v>4.155185467070856</v>
+        <v>7.552619146637452</v>
       </c>
       <c r="E37" t="n">
-        <v>200.7057822251266</v>
+        <v>198.2877898279365</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9024178981781006</v>
+        <v>0.8210803866386414</v>
       </c>
       <c r="G37" t="n">
-        <v>0.001009689178317785</v>
+        <v>0.0004035303718410432</v>
       </c>
       <c r="H37" t="n">
-        <v>957.2734629994419</v>
+        <v>940.8700875246753</v>
       </c>
       <c r="I37" t="n">
-        <v>200.7057822251265</v>
+        <v>198.2877898279416</v>
       </c>
       <c r="J37" t="n">
-        <v>9.000641779862162</v>
+        <v>9.00064177013282</v>
       </c>
       <c r="K37" t="n">
-        <v>1.004266221116268e-05</v>
+        <v>49.02855814581994</v>
       </c>
       <c r="L37" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>5.115907697472721e-12</v>
       </c>
       <c r="M37" t="n">
-        <v>4.845456312791306</v>
+        <v>1.448022623495367</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>0.9979609251022339</v>
+        <v>0.8353708982467651</v>
       </c>
       <c r="P37" t="n">
-        <v>7.600859680678695e-05</v>
+        <v>0.0003396867250557989</v>
       </c>
       <c r="Q37" t="n">
-        <v>955.138105480333</v>
+        <v>938.2394138496758</v>
       </c>
       <c r="R37" t="n">
-        <v>200.762489903932</v>
+        <v>198.4891410057571</v>
       </c>
       <c r="S37" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641792512026</v>
       </c>
       <c r="T37" t="n">
-        <v>2.135347476446668</v>
+        <v>46.39788447082037</v>
       </c>
       <c r="U37" t="n">
-        <v>0.05670767880536687</v>
+        <v>0.2013511778206407</v>
       </c>
       <c r="V37" t="n">
-        <v>4.845456312791306</v>
+        <v>1.448022645874573</v>
       </c>
       <c r="W37" t="b">
         <v>1</v>
@@ -3167,68 +3167,68 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>926.3837436938231</v>
+        <v>870.5685418924138</v>
       </c>
       <c r="D38" t="n">
-        <v>4.098870829540688</v>
+        <v>8.972329951056187</v>
       </c>
       <c r="E38" t="n">
-        <v>202.112192541617</v>
+        <v>212.0850439335515</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8486842513084412</v>
+        <v>0.8523421287536621</v>
       </c>
       <c r="G38" t="n">
-        <v>0.001007982064038515</v>
+        <v>0.0009401811985298991</v>
       </c>
       <c r="H38" t="n">
-        <v>926.3837436926442</v>
+        <v>933.5317547573583</v>
       </c>
       <c r="I38" t="n">
-        <v>202.1121925416174</v>
+        <v>212.085043933552</v>
       </c>
       <c r="J38" t="n">
-        <v>9.000641779862162</v>
+        <v>9.140517219559058</v>
       </c>
       <c r="K38" t="n">
-        <v>1.178932507173158e-09</v>
+        <v>62.96321286494447</v>
       </c>
       <c r="L38" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>4.831690603168681e-13</v>
       </c>
       <c r="M38" t="n">
-        <v>4.901770950321474</v>
+        <v>0.1681872685028711</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>0.9823220372200012</v>
+        <v>0.8625028729438782</v>
       </c>
       <c r="P38" t="n">
-        <v>8.093146607279778e-05</v>
+        <v>0.0005280999466776848</v>
       </c>
       <c r="Q38" t="n">
-        <v>928.9055085139474</v>
+        <v>937.2163987752673</v>
       </c>
       <c r="R38" t="n">
-        <v>202.1654128272097</v>
+        <v>211.6371636356351</v>
       </c>
       <c r="S38" t="n">
-        <v>9.000641779862162</v>
+        <v>9.041741678188288</v>
       </c>
       <c r="T38" t="n">
-        <v>2.521764820124304</v>
+        <v>66.64785688285349</v>
       </c>
       <c r="U38" t="n">
-        <v>0.0532202855927153</v>
+        <v>0.4478802979164698</v>
       </c>
       <c r="V38" t="n">
-        <v>4.901770950321474</v>
+        <v>0.06941172713210086</v>
       </c>
       <c r="W38" t="b">
         <v>1</v>
@@ -3240,68 +3240,68 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>946.9778445568023</v>
+        <v>987.7612048249165</v>
       </c>
       <c r="D39" t="n">
-        <v>10.25061390415358</v>
+        <v>5.680238395149107</v>
       </c>
       <c r="E39" t="n">
-        <v>121.3394806969968</v>
+        <v>194.8632000754484</v>
       </c>
       <c r="F39" t="n">
-        <v>0.906603217124939</v>
+        <v>0.9430859684944153</v>
       </c>
       <c r="G39" t="n">
-        <v>0.005423423834145069</v>
+        <v>0.0002567658957559615</v>
       </c>
       <c r="H39" t="n">
-        <v>946.9770546909749</v>
+        <v>983.8468877335921</v>
       </c>
       <c r="I39" t="n">
-        <v>173.6139250356486</v>
+        <v>194.8632000756561</v>
       </c>
       <c r="J39" t="n">
-        <v>10.25060663381155</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K39" t="n">
-        <v>0.00078986582741436</v>
+        <v>3.914317091324392</v>
       </c>
       <c r="L39" t="n">
-        <v>52.27444433865183</v>
+        <v>2.077342742268229e-10</v>
       </c>
       <c r="M39" t="n">
-        <v>7.270342027965171e-06</v>
+        <v>3.320403384713055</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>0.9999711513519287</v>
+        <v>0.9402955770492554</v>
       </c>
       <c r="P39" t="n">
-        <v>0.00902106985449791</v>
+        <v>0.0002447155711706728</v>
       </c>
       <c r="Q39" t="n">
-        <v>800.0000355193972</v>
+        <v>970.4327363135158</v>
       </c>
       <c r="R39" t="n">
-        <v>150.0005529326348</v>
+        <v>195.4047599117028</v>
       </c>
       <c r="S39" t="n">
-        <v>9.267952934273886</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T39" t="n">
-        <v>146.9778090374051</v>
+        <v>17.32846851140073</v>
       </c>
       <c r="U39" t="n">
-        <v>28.66107223563803</v>
+        <v>0.5415598362544074</v>
       </c>
       <c r="V39" t="n">
-        <v>0.9826609698796922</v>
+        <v>3.320403384713055</v>
       </c>
       <c r="W39" t="b">
         <v>1</v>
@@ -3313,68 +3313,68 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>958.1211224485617</v>
+        <v>926.7751109503928</v>
       </c>
       <c r="D40" t="n">
-        <v>5.021450956164415</v>
+        <v>14.69975478021877</v>
       </c>
       <c r="E40" t="n">
-        <v>220.5997899278971</v>
+        <v>193.0143456688106</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8311465382575989</v>
+        <v>0.9287258982658386</v>
       </c>
       <c r="G40" t="n">
-        <v>0.001009689178317785</v>
+        <v>0.001690759556367993</v>
       </c>
       <c r="H40" t="n">
-        <v>958.1211297509594</v>
+        <v>944.2003722545508</v>
       </c>
       <c r="I40" t="n">
-        <v>220.599789927901</v>
+        <v>193.0366390264005</v>
       </c>
       <c r="J40" t="n">
-        <v>9.000641779862162</v>
+        <v>12.2293513262616</v>
       </c>
       <c r="K40" t="n">
-        <v>7.302397762032342e-06</v>
+        <v>17.42526130415797</v>
       </c>
       <c r="L40" t="n">
-        <v>3.979039320256561e-12</v>
+        <v>0.02229335758994466</v>
       </c>
       <c r="M40" t="n">
-        <v>3.979190823697747</v>
+        <v>2.47040345395717</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0.9774666428565979</v>
+        <v>0.9976328611373901</v>
       </c>
       <c r="P40" t="n">
-        <v>0.0001757863064995036</v>
+        <v>0.003201540093868971</v>
       </c>
       <c r="Q40" t="n">
-        <v>953.8902278592511</v>
+        <v>942.6131840930096</v>
       </c>
       <c r="R40" t="n">
-        <v>219.7635399870685</v>
+        <v>195.2798984007391</v>
       </c>
       <c r="S40" t="n">
-        <v>9.000641779862162</v>
+        <v>11.86594435661859</v>
       </c>
       <c r="T40" t="n">
-        <v>4.230894589310537</v>
+        <v>15.83807314261685</v>
       </c>
       <c r="U40" t="n">
-        <v>0.8362499408285942</v>
+        <v>2.265552731928551</v>
       </c>
       <c r="V40" t="n">
-        <v>3.979190823697747</v>
+        <v>2.833810423600179</v>
       </c>
       <c r="W40" t="b">
         <v>1</v>
@@ -3386,68 +3386,68 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>954.3792783171195</v>
+        <v>967.7238237716959</v>
       </c>
       <c r="D41" t="n">
-        <v>5.779407977267885</v>
+        <v>16.96676997577074</v>
       </c>
       <c r="E41" t="n">
-        <v>200.2942369471083</v>
+        <v>193.1431016470713</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8952300548553467</v>
+        <v>0.9571895003318787</v>
       </c>
       <c r="G41" t="n">
-        <v>0.001009692437946796</v>
+        <v>0.001836215727962554</v>
       </c>
       <c r="H41" t="n">
-        <v>954.3792783171151</v>
+        <v>957.5903888236588</v>
       </c>
       <c r="I41" t="n">
-        <v>200.2942369471084</v>
+        <v>193.1433285014407</v>
       </c>
       <c r="J41" t="n">
-        <v>9.000641779862162</v>
+        <v>12.60945375558594</v>
       </c>
       <c r="K41" t="n">
-        <v>4.433786671143025e-12</v>
+        <v>10.13343494803712</v>
       </c>
       <c r="L41" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>0.0002268543694015079</v>
       </c>
       <c r="M41" t="n">
-        <v>3.221233802594277</v>
+        <v>4.357316220184797</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>0.9577566385269165</v>
+        <v>0.9999992847442627</v>
       </c>
       <c r="P41" t="n">
-        <v>7.182874105637893e-05</v>
+        <v>0.006113273091614246</v>
       </c>
       <c r="Q41" t="n">
-        <v>952.7822106816167</v>
+        <v>997.6463614792851</v>
       </c>
       <c r="R41" t="n">
-        <v>200.3588301549985</v>
+        <v>202.3419907418982</v>
       </c>
       <c r="S41" t="n">
-        <v>9.000641779862162</v>
+        <v>12.39254106358857</v>
       </c>
       <c r="T41" t="n">
-        <v>1.597067635502867</v>
+        <v>29.92253770758919</v>
       </c>
       <c r="U41" t="n">
-        <v>0.06459320789016942</v>
+        <v>9.198889094826882</v>
       </c>
       <c r="V41" t="n">
-        <v>3.221233802594277</v>
+        <v>4.574228912182168</v>
       </c>
       <c r="W41" t="b">
         <v>1</v>
@@ -3463,64 +3463,64 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>875.0560704311393</v>
+        <v>871.1878645029764</v>
       </c>
       <c r="D42" t="n">
-        <v>8.044794669919384</v>
+        <v>9.221556844223011</v>
       </c>
       <c r="E42" t="n">
-        <v>196.1256248794963</v>
+        <v>201.2938789870475</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9285256266593933</v>
+        <v>0.8681793212890625</v>
       </c>
       <c r="G42" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.0009456591797061265</v>
       </c>
       <c r="H42" t="n">
-        <v>933.0453159927907</v>
+        <v>933.529305815971</v>
       </c>
       <c r="I42" t="n">
-        <v>196.1256248794963</v>
+        <v>201.2938789870477</v>
       </c>
       <c r="J42" t="n">
-        <v>9.000641636420553</v>
+        <v>9.221556844223198</v>
       </c>
       <c r="K42" t="n">
-        <v>57.98924556165139</v>
+        <v>62.34144131299468</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.4210854715202e-13</v>
       </c>
       <c r="M42" t="n">
-        <v>0.95584696650117</v>
+        <v>1.865174681370263e-13</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>0.9370651245117188</v>
+        <v>0.7932679653167725</v>
       </c>
       <c r="P42" t="n">
-        <v>0.0004446028033271432</v>
+        <v>0.000482002884382382</v>
       </c>
       <c r="Q42" t="n">
-        <v>932.3591921618067</v>
+        <v>929.4627165375941</v>
       </c>
       <c r="R42" t="n">
-        <v>196.8563581366042</v>
+        <v>201.2974331655836</v>
       </c>
       <c r="S42" t="n">
-        <v>9.000641673276222</v>
+        <v>9.3355220125991</v>
       </c>
       <c r="T42" t="n">
-        <v>57.30312173066739</v>
+        <v>58.27485203461777</v>
       </c>
       <c r="U42" t="n">
-        <v>0.7307332571079712</v>
+        <v>0.003554178536091968</v>
       </c>
       <c r="V42" t="n">
-        <v>0.9558470033568387</v>
+        <v>0.1139651683760885</v>
       </c>
       <c r="W42" t="b">
         <v>1</v>
@@ -3536,64 +3536,64 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>881.8095444567513</v>
+        <v>910.7474861665485</v>
       </c>
       <c r="D43" t="n">
-        <v>9.096120612402132</v>
+        <v>6.916535206831445</v>
       </c>
       <c r="E43" t="n">
-        <v>222.6158273769345</v>
+        <v>191.468689876302</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5667540431022644</v>
+        <v>0.5367275476455688</v>
       </c>
       <c r="G43" t="n">
-        <v>0.001727092894725502</v>
+        <v>0.0004035303718410432</v>
       </c>
       <c r="H43" t="n">
-        <v>933.045328905432</v>
+        <v>940.8700882102418</v>
       </c>
       <c r="I43" t="n">
-        <v>222.6158371179696</v>
+        <v>191.4686898763189</v>
       </c>
       <c r="J43" t="n">
-        <v>9.096080025806208</v>
+        <v>9.000641570011767</v>
       </c>
       <c r="K43" t="n">
-        <v>51.23578444868076</v>
+        <v>30.12260204369329</v>
       </c>
       <c r="L43" t="n">
-        <v>9.741035086108241e-06</v>
+        <v>1.688249540165998e-11</v>
       </c>
       <c r="M43" t="n">
-        <v>4.058659592409697e-05</v>
+        <v>2.084106363180322</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0.5008395910263062</v>
+        <v>0.6276092529296875</v>
       </c>
       <c r="P43" t="n">
-        <v>0.0004888346302323043</v>
+        <v>0.0002688669483177364</v>
       </c>
       <c r="Q43" t="n">
-        <v>933.4359710505946</v>
+        <v>940.7493143942288</v>
       </c>
       <c r="R43" t="n">
-        <v>220.625887798531</v>
+        <v>192.0537798779237</v>
       </c>
       <c r="S43" t="n">
-        <v>9.164699991109494</v>
+        <v>9.000641489598474</v>
       </c>
       <c r="T43" t="n">
-        <v>51.62642659384335</v>
+        <v>30.00182822768033</v>
       </c>
       <c r="U43" t="n">
-        <v>1.989939578403465</v>
+        <v>0.5850900016217224</v>
       </c>
       <c r="V43" t="n">
-        <v>0.06857937870736208</v>
+        <v>2.084106282767029</v>
       </c>
       <c r="W43" t="b">
         <v>1</v>
@@ -3605,68 +3605,68 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>933.5595659170884</v>
+        <v>894.680717095766</v>
       </c>
       <c r="D44" t="n">
-        <v>3.566375687654564</v>
+        <v>8.054306864091931</v>
       </c>
       <c r="E44" t="n">
-        <v>200.6836171785196</v>
+        <v>205.3223585507395</v>
       </c>
       <c r="F44" t="n">
-        <v>0.902368426322937</v>
+        <v>0.5986339449882507</v>
       </c>
       <c r="G44" t="n">
-        <v>0.001009692437946796</v>
+        <v>0.000411912944400683</v>
       </c>
       <c r="H44" t="n">
-        <v>933.559565917431</v>
+        <v>940.8700876071158</v>
       </c>
       <c r="I44" t="n">
-        <v>200.6836171785194</v>
+        <v>205.3223585507395</v>
       </c>
       <c r="J44" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641771151603</v>
       </c>
       <c r="K44" t="n">
-        <v>3.425384420552291e-10</v>
+        <v>46.18937051134981</v>
       </c>
       <c r="L44" t="n">
-        <v>1.70530256582424e-13</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M44" t="n">
-        <v>5.434266092207598</v>
+        <v>0.946334907059672</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0.9942396879196167</v>
+        <v>0.574456512928009</v>
       </c>
       <c r="P44" t="n">
-        <v>6.981344631640241e-05</v>
+        <v>0.0003302170371171087</v>
       </c>
       <c r="Q44" t="n">
-        <v>934.9200161751213</v>
+        <v>938.6620247693616</v>
       </c>
       <c r="R44" t="n">
-        <v>200.7534167666371</v>
+        <v>204.4655777312656</v>
       </c>
       <c r="S44" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641545257663</v>
       </c>
       <c r="T44" t="n">
-        <v>1.36045025803287</v>
+        <v>43.98130767359555</v>
       </c>
       <c r="U44" t="n">
-        <v>0.06979958811751885</v>
+        <v>0.8567808194738404</v>
       </c>
       <c r="V44" t="n">
-        <v>5.434266092207598</v>
+        <v>0.9463346811657321</v>
       </c>
       <c r="W44" t="b">
         <v>1</v>
@@ -3678,68 +3678,68 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>897.3852576339389</v>
+        <v>935.6105523132412</v>
       </c>
       <c r="D45" t="n">
-        <v>6.78893341300639</v>
+        <v>3.983120227922022</v>
       </c>
       <c r="E45" t="n">
-        <v>193.4707971802883</v>
+        <v>198.3576384098161</v>
       </c>
       <c r="F45" t="n">
-        <v>0.7910519242286682</v>
+        <v>0.9862354397773743</v>
       </c>
       <c r="G45" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.000275987054919824</v>
       </c>
       <c r="H45" t="n">
-        <v>933.0453150666568</v>
+        <v>935.8914960217039</v>
       </c>
       <c r="I45" t="n">
-        <v>193.4707971802883</v>
+        <v>198.357638409793</v>
       </c>
       <c r="J45" t="n">
-        <v>9.000641658368027</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K45" t="n">
-        <v>35.66005743271796</v>
+        <v>0.2809437084627007</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.310684976691846e-11</v>
       </c>
       <c r="M45" t="n">
-        <v>2.211708245361637</v>
+        <v>5.01752155194014</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>0.793515145778656</v>
+        <v>0.9986103773117065</v>
       </c>
       <c r="P45" t="n">
-        <v>0.0003006612241733819</v>
+        <v>8.306914241984487e-05</v>
       </c>
       <c r="Q45" t="n">
-        <v>935.5889220183041</v>
+        <v>940.1894910089754</v>
       </c>
       <c r="R45" t="n">
-        <v>194.1723296924535</v>
+        <v>198.5975637538426</v>
       </c>
       <c r="S45" t="n">
-        <v>9.000641650906047</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T45" t="n">
-        <v>38.2036643843652</v>
+        <v>4.578938695734223</v>
       </c>
       <c r="U45" t="n">
-        <v>0.7015325121652438</v>
+        <v>0.2399253440265454</v>
       </c>
       <c r="V45" t="n">
-        <v>2.211708237899657</v>
+        <v>5.01752155194014</v>
       </c>
       <c r="W45" t="b">
         <v>1</v>
@@ -3755,64 +3755,64 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>895.9203767289504</v>
+        <v>820.1509486704676</v>
       </c>
       <c r="D46" t="n">
-        <v>5.067263974051466</v>
+        <v>7.819756061424561</v>
       </c>
       <c r="E46" t="n">
-        <v>196.2792330886438</v>
+        <v>193.308108436903</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8566992282867432</v>
+        <v>0.9871838092803955</v>
       </c>
       <c r="G46" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.001659385743550956</v>
       </c>
       <c r="H46" t="n">
-        <v>933.0453168435243</v>
+        <v>925.9037138259948</v>
       </c>
       <c r="I46" t="n">
-        <v>196.2792330886437</v>
+        <v>193.3079578136815</v>
       </c>
       <c r="J46" t="n">
-        <v>9.000641671427948</v>
+        <v>9.000641664806555</v>
       </c>
       <c r="K46" t="n">
-        <v>37.12494011457397</v>
+        <v>105.7527651555272</v>
       </c>
       <c r="L46" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0.0001506232214865122</v>
       </c>
       <c r="M46" t="n">
-        <v>3.933377697376482</v>
+        <v>1.180885603381993</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>0.6922328472137451</v>
+        <v>0.9938814640045166</v>
       </c>
       <c r="P46" t="n">
-        <v>0.0003074153210036457</v>
+        <v>0.0009672881569713354</v>
       </c>
       <c r="Q46" t="n">
-        <v>934.582654289844</v>
+        <v>932.5852889144468</v>
       </c>
       <c r="R46" t="n">
-        <v>196.8077102173943</v>
+        <v>193.8467371367263</v>
       </c>
       <c r="S46" t="n">
-        <v>9.000641740151302</v>
+        <v>9.00064181636632</v>
       </c>
       <c r="T46" t="n">
-        <v>38.66227756089359</v>
+        <v>112.4343402439791</v>
       </c>
       <c r="U46" t="n">
-        <v>0.5284771287505237</v>
+        <v>0.5386286998232777</v>
       </c>
       <c r="V46" t="n">
-        <v>3.933377766099836</v>
+        <v>1.180885754941759</v>
       </c>
       <c r="W46" t="b">
         <v>1</v>
@@ -3824,68 +3824,68 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>955.4729197493958</v>
+        <v>881.4368294756746</v>
       </c>
       <c r="D47" t="n">
-        <v>9.569674922845763</v>
+        <v>8.683883718620109</v>
       </c>
       <c r="E47" t="n">
-        <v>134.1891954710945</v>
+        <v>210.5079349734594</v>
       </c>
       <c r="F47" t="n">
-        <v>0.906603217124939</v>
+        <v>0.7437790036201477</v>
       </c>
       <c r="G47" t="n">
-        <v>0.01683678291738033</v>
+        <v>0.000411912944400683</v>
       </c>
       <c r="H47" t="n">
-        <v>955.5017000687828</v>
+        <v>940.8726226535753</v>
       </c>
       <c r="I47" t="n">
-        <v>164.2913488507402</v>
+        <v>210.507934973459</v>
       </c>
       <c r="J47" t="n">
-        <v>10.2130040540647</v>
+        <v>9.000565823278913</v>
       </c>
       <c r="K47" t="n">
-        <v>0.02878031938701042</v>
+        <v>59.43579317790068</v>
       </c>
       <c r="L47" t="n">
-        <v>30.1021533796457</v>
+        <v>3.126388037344441e-13</v>
       </c>
       <c r="M47" t="n">
-        <v>0.643329131218934</v>
+        <v>0.3166821046588044</v>
       </c>
       <c r="N47" t="b">
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>0.9999130964279175</v>
+        <v>0.7713530659675598</v>
       </c>
       <c r="P47" t="n">
-        <v>0.005678033921867609</v>
+        <v>0.0004413022543303668</v>
       </c>
       <c r="Q47" t="n">
-        <v>800.0000298746668</v>
+        <v>938.5293567094973</v>
       </c>
       <c r="R47" t="n">
-        <v>151.157383265226</v>
+        <v>210.1331971044325</v>
       </c>
       <c r="S47" t="n">
-        <v>9.01081412252911</v>
+        <v>9.000641817535367</v>
       </c>
       <c r="T47" t="n">
-        <v>155.472889874729</v>
+        <v>57.09252723382269</v>
       </c>
       <c r="U47" t="n">
-        <v>16.96818779413147</v>
+        <v>0.374737869026859</v>
       </c>
       <c r="V47" t="n">
-        <v>0.5588608003166531</v>
+        <v>0.3167580989152583</v>
       </c>
       <c r="W47" t="b">
         <v>1</v>
@@ -3901,64 +3901,64 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>888.8566881929055</v>
+        <v>838.4958321264128</v>
       </c>
       <c r="D48" t="n">
-        <v>7.723190453058736</v>
+        <v>6.424566946963213</v>
       </c>
       <c r="E48" t="n">
-        <v>200.0492671848147</v>
+        <v>205.9056743663126</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8543873429298401</v>
+        <v>0.9884505271911621</v>
       </c>
       <c r="G48" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.001565012848004699</v>
       </c>
       <c r="H48" t="n">
-        <v>933.0453179642307</v>
+        <v>925.904175032681</v>
       </c>
       <c r="I48" t="n">
-        <v>200.0492671848147</v>
+        <v>206.4751248904578</v>
       </c>
       <c r="J48" t="n">
-        <v>9.000641509076948</v>
+        <v>9.000641775249187</v>
       </c>
       <c r="K48" t="n">
-        <v>44.18862977132517</v>
+        <v>87.40834290626822</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>0.5694505241451964</v>
       </c>
       <c r="M48" t="n">
-        <v>1.277451056018212</v>
+        <v>2.576074828285974</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>0.8312811851501465</v>
+        <v>0.9993426203727722</v>
       </c>
       <c r="P48" t="n">
-        <v>0.00033524539321661</v>
+        <v>0.0008612173842266202</v>
       </c>
       <c r="Q48" t="n">
-        <v>933.3516624718369</v>
+        <v>931.7496615487512</v>
       </c>
       <c r="R48" t="n">
-        <v>200.3508451231407</v>
+        <v>203.1123440504731</v>
       </c>
       <c r="S48" t="n">
-        <v>9.000641918464289</v>
+        <v>9.000641776003501</v>
       </c>
       <c r="T48" t="n">
-        <v>44.49497427893141</v>
+        <v>93.25382942233841</v>
       </c>
       <c r="U48" t="n">
-        <v>0.3015779383260053</v>
+        <v>2.793330315839455</v>
       </c>
       <c r="V48" t="n">
-        <v>1.277451465405553</v>
+        <v>2.576074829040288</v>
       </c>
       <c r="W48" t="b">
         <v>1</v>
@@ -3970,68 +3970,68 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>963.0088085381315</v>
+        <v>868.4852255114015</v>
       </c>
       <c r="D49" t="n">
-        <v>11.52744922557012</v>
+        <v>8.292692082730287</v>
       </c>
       <c r="E49" t="n">
-        <v>154.0011373358929</v>
+        <v>202.9592609694175</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9065951704978943</v>
+        <v>0.9624367356300354</v>
       </c>
       <c r="G49" t="n">
-        <v>0.001030126353725791</v>
+        <v>0.00113704486284405</v>
       </c>
       <c r="H49" t="n">
-        <v>963.0026827948595</v>
+        <v>933.5293046828175</v>
       </c>
       <c r="I49" t="n">
-        <v>176.1299395222404</v>
+        <v>202.0291270286342</v>
       </c>
       <c r="J49" t="n">
-        <v>11.52742682408505</v>
+        <v>9.000641646246294</v>
       </c>
       <c r="K49" t="n">
-        <v>0.006125743271923056</v>
+        <v>65.044079171416</v>
       </c>
       <c r="L49" t="n">
-        <v>22.12880218634746</v>
+        <v>0.9301339407832927</v>
       </c>
       <c r="M49" t="n">
-        <v>2.240148506693629e-05</v>
+        <v>0.7079495635160065</v>
       </c>
       <c r="N49" t="b">
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>0.9454864263534546</v>
+        <v>0.9565010666847229</v>
       </c>
       <c r="P49" t="n">
-        <v>0.003417638596147299</v>
+        <v>0.0005720136105082929</v>
       </c>
       <c r="Q49" t="n">
-        <v>802.7478830538647</v>
+        <v>934.3204597322963</v>
       </c>
       <c r="R49" t="n">
-        <v>166.9986867266815</v>
+        <v>202.8428408865294</v>
       </c>
       <c r="S49" t="n">
-        <v>11.27867430317689</v>
+        <v>9.000641793594395</v>
       </c>
       <c r="T49" t="n">
-        <v>160.2609254842667</v>
+        <v>65.83523422089479</v>
       </c>
       <c r="U49" t="n">
-        <v>12.99754939078858</v>
+        <v>0.116420082888169</v>
       </c>
       <c r="V49" t="n">
-        <v>0.2487749223932223</v>
+        <v>0.7079497108641082</v>
       </c>
       <c r="W49" t="b">
         <v>1</v>
@@ -4047,64 +4047,64 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>963.176555542808</v>
+        <v>979.1832198837739</v>
       </c>
       <c r="D50" t="n">
-        <v>4.610213383201334</v>
+        <v>6.04101607694327</v>
       </c>
       <c r="E50" t="n">
-        <v>216.9138812036659</v>
+        <v>209.9137319136483</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8311465382575989</v>
+        <v>0.9600974917411804</v>
       </c>
       <c r="G50" t="n">
-        <v>0.001009689178317785</v>
+        <v>0.000253947131568566</v>
       </c>
       <c r="H50" t="n">
-        <v>963.1765581926694</v>
+        <v>979.1832198837656</v>
       </c>
       <c r="I50" t="n">
-        <v>216.9138812036777</v>
+        <v>209.913731913648</v>
       </c>
       <c r="J50" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="K50" t="n">
-        <v>2.649861357895134e-06</v>
+        <v>8.29913915367797e-12</v>
       </c>
       <c r="L50" t="n">
-        <v>1.182343112304807e-11</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="M50" t="n">
-        <v>4.390428396660829</v>
+        <v>2.959625702918892</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>0.9931203126907349</v>
+        <v>0.6635180711746216</v>
       </c>
       <c r="P50" t="n">
-        <v>0.0001475030148867518</v>
+        <v>0.0002802814706228673</v>
       </c>
       <c r="Q50" t="n">
-        <v>958.3165018710007</v>
+        <v>962.2228492949848</v>
       </c>
       <c r="R50" t="n">
-        <v>216.3539704999721</v>
+        <v>209.0336145198863</v>
       </c>
       <c r="S50" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="T50" t="n">
-        <v>4.86005367180735</v>
+        <v>16.96037058878903</v>
       </c>
       <c r="U50" t="n">
-        <v>0.5599107036938449</v>
+        <v>0.8801173937620206</v>
       </c>
       <c r="V50" t="n">
-        <v>4.390428396660829</v>
+        <v>2.959625702918892</v>
       </c>
       <c r="W50" t="b">
         <v>1</v>
@@ -4116,68 +4116,68 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>844.5788138547135</v>
+        <v>976.2856368605904</v>
       </c>
       <c r="D51" t="n">
-        <v>7.59415139233557</v>
+        <v>3.608205604519258</v>
       </c>
       <c r="E51" t="n">
-        <v>226.8746747136299</v>
+        <v>200.1675935669597</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9079260230064392</v>
+        <v>0.9850831031799316</v>
       </c>
       <c r="G51" t="n">
-        <v>0.001726252725347877</v>
+        <v>0.000253947131568566</v>
       </c>
       <c r="H51" t="n">
-        <v>933.0554803850504</v>
+        <v>976.2856368605152</v>
       </c>
       <c r="I51" t="n">
-        <v>226.87467471363</v>
+        <v>200.1675935669443</v>
       </c>
       <c r="J51" t="n">
-        <v>9.000641712244377</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K51" t="n">
-        <v>88.47666653033684</v>
+        <v>7.526068657170981e-11</v>
       </c>
       <c r="L51" t="n">
-        <v>1.70530256582424e-13</v>
+        <v>1.534772309241816e-11</v>
       </c>
       <c r="M51" t="n">
-        <v>1.406490319908807</v>
+        <v>5.392436175342905</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>0.9656434059143066</v>
+        <v>0.9998348951339722</v>
       </c>
       <c r="P51" t="n">
-        <v>0.0009472327656112611</v>
+        <v>0.0001455066521884874</v>
       </c>
       <c r="Q51" t="n">
-        <v>932.1064155296973</v>
+        <v>966.6650389299334</v>
       </c>
       <c r="R51" t="n">
-        <v>223.0414237065359</v>
+        <v>199.5008290252252</v>
       </c>
       <c r="S51" t="n">
-        <v>9.000640444864356</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T51" t="n">
-        <v>87.52760167498377</v>
+        <v>9.620597930657027</v>
       </c>
       <c r="U51" t="n">
-        <v>3.833251007093935</v>
+        <v>0.6667645417344659</v>
       </c>
       <c r="V51" t="n">
-        <v>1.406489052528785</v>
+        <v>5.392436175342905</v>
       </c>
       <c r="W51" t="b">
         <v>1</v>
@@ -4189,68 +4189,68 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>915.971295548182</v>
+        <v>879.5698638782484</v>
       </c>
       <c r="D52" t="n">
-        <v>8.433968397484772</v>
+        <v>7.519056712967613</v>
       </c>
       <c r="E52" t="n">
-        <v>116.6329714024075</v>
+        <v>204.2154180932888</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8593701124191284</v>
+        <v>0.947009265422821</v>
       </c>
       <c r="G52" t="n">
-        <v>0.001029878039844334</v>
+        <v>0.000411912944400683</v>
       </c>
       <c r="H52" t="n">
-        <v>930.9479374974435</v>
+        <v>940.8731615347237</v>
       </c>
       <c r="I52" t="n">
-        <v>176.1296285244026</v>
+        <v>204.2154180932891</v>
       </c>
       <c r="J52" t="n">
-        <v>10.12701083913167</v>
+        <v>9.000819739421681</v>
       </c>
       <c r="K52" t="n">
-        <v>14.97664194926153</v>
+        <v>61.30329765647537</v>
       </c>
       <c r="L52" t="n">
-        <v>59.4966571219951</v>
+        <v>3.126388037344441e-13</v>
       </c>
       <c r="M52" t="n">
-        <v>1.693042441646893</v>
+        <v>1.481763026454068</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>0.9999322891235352</v>
+        <v>0.9585382342338562</v>
       </c>
       <c r="P52" t="n">
-        <v>0.006814353633671999</v>
+        <v>0.0004808686499018222</v>
       </c>
       <c r="Q52" t="n">
-        <v>800.0000254716435</v>
+        <v>935.4956827664361</v>
       </c>
       <c r="R52" t="n">
-        <v>150.0005529027002</v>
+        <v>202.8839473154934</v>
       </c>
       <c r="S52" t="n">
-        <v>9.000642128851966</v>
+        <v>9.000641085506452</v>
       </c>
       <c r="T52" t="n">
-        <v>115.9712700765384</v>
+        <v>55.92581888818768</v>
       </c>
       <c r="U52" t="n">
-        <v>33.36758150029272</v>
+        <v>1.331470777795431</v>
       </c>
       <c r="V52" t="n">
-        <v>0.5666737313671941</v>
+        <v>1.481584372538839</v>
       </c>
       <c r="W52" t="b">
         <v>1</v>
@@ -4262,68 +4262,68 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>922.8358850593218</v>
+        <v>845.2643484678721</v>
       </c>
       <c r="D53" t="n">
-        <v>9.435939006210385</v>
+        <v>6.481086831255346</v>
       </c>
       <c r="E53" t="n">
-        <v>137.6584224652683</v>
+        <v>201.3158137114366</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9028918147087097</v>
+        <v>0.9875456690788269</v>
       </c>
       <c r="G53" t="n">
-        <v>0.006410556379705667</v>
+        <v>0.001542833168059587</v>
       </c>
       <c r="H53" t="n">
-        <v>911.5480505174032</v>
+        <v>925.9037154494032</v>
       </c>
       <c r="I53" t="n">
-        <v>175.6483503656856</v>
+        <v>201.315813711462</v>
       </c>
       <c r="J53" t="n">
-        <v>10.21300403347576</v>
+        <v>9.000641710553122</v>
       </c>
       <c r="K53" t="n">
-        <v>11.28783454191853</v>
+        <v>80.63936698153111</v>
       </c>
       <c r="L53" t="n">
-        <v>37.98992790041726</v>
+        <v>2.543742994021159e-11</v>
       </c>
       <c r="M53" t="n">
-        <v>0.7770650272653779</v>
+        <v>2.519554879297776</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0.9995856881141663</v>
+        <v>0.9990785121917725</v>
       </c>
       <c r="P53" t="n">
-        <v>0.00461842305958271</v>
+        <v>0.0007722207228653133</v>
       </c>
       <c r="Q53" t="n">
-        <v>800.0000272562969</v>
+        <v>932.4366476622735</v>
       </c>
       <c r="R53" t="n">
-        <v>152.3281931477131</v>
+        <v>202.3069924400194</v>
       </c>
       <c r="S53" t="n">
-        <v>9.000406356546192</v>
+        <v>9.000641766265922</v>
       </c>
       <c r="T53" t="n">
-        <v>122.8358578030249</v>
+        <v>87.17229919440138</v>
       </c>
       <c r="U53" t="n">
-        <v>14.66977068244481</v>
+        <v>0.9911787285828098</v>
       </c>
       <c r="V53" t="n">
-        <v>0.4355326496641929</v>
+        <v>2.519554935010576</v>
       </c>
       <c r="W53" t="b">
         <v>1</v>
@@ -4335,68 +4335,68 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>931.1795459866725</v>
+        <v>869.2077288586329</v>
       </c>
       <c r="D54" t="n">
-        <v>15.01021031559371</v>
+        <v>8.156572598306287</v>
       </c>
       <c r="E54" t="n">
-        <v>196.3062034466771</v>
+        <v>211.0666041718146</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8086524605751038</v>
+        <v>0.9508481621742249</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0006024915492162108</v>
+        <v>0.000411912944400683</v>
       </c>
       <c r="H54" t="n">
-        <v>931.1718345308351</v>
+        <v>940.8711689760428</v>
       </c>
       <c r="I54" t="n">
-        <v>196.3063189322034</v>
+        <v>211.0666041718132</v>
       </c>
       <c r="J54" t="n">
-        <v>11.82181856638964</v>
+        <v>9.000790958495239</v>
       </c>
       <c r="K54" t="n">
-        <v>0.007711455837352332</v>
+        <v>71.66344011740989</v>
       </c>
       <c r="L54" t="n">
-        <v>0.0001154855263223453</v>
+        <v>1.392663762089796e-12</v>
       </c>
       <c r="M54" t="n">
-        <v>3.188391749204067</v>
+        <v>0.8442183601889521</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>0.9922215342521667</v>
+        <v>0.9606555700302124</v>
       </c>
       <c r="P54" t="n">
-        <v>0.003961622714996338</v>
+        <v>0.0005422459216788411</v>
       </c>
       <c r="Q54" t="n">
-        <v>800.0000435724913</v>
+        <v>937.3466056090383</v>
       </c>
       <c r="R54" t="n">
-        <v>200.2040577450566</v>
+        <v>210.6104757333097</v>
       </c>
       <c r="S54" t="n">
-        <v>13.72671710098872</v>
+        <v>9.000641828255763</v>
       </c>
       <c r="T54" t="n">
-        <v>131.1795024141811</v>
+        <v>68.13887675040542</v>
       </c>
       <c r="U54" t="n">
-        <v>3.897854298379514</v>
+        <v>0.4561284385048907</v>
       </c>
       <c r="V54" t="n">
-        <v>1.283493214604986</v>
+        <v>0.8440692299494756</v>
       </c>
       <c r="W54" t="b">
         <v>1</v>
@@ -4408,68 +4408,68 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>871.376215413518</v>
+        <v>954.0981077738504</v>
       </c>
       <c r="D55" t="n">
-        <v>7.926433919294807</v>
+        <v>13.61339723938121</v>
       </c>
       <c r="E55" t="n">
-        <v>179.6327752373482</v>
+        <v>207.3980148487064</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8652369379997253</v>
+        <v>0.9797565340995789</v>
       </c>
       <c r="G55" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.003873131237924099</v>
       </c>
       <c r="H55" t="n">
-        <v>933.0453156546907</v>
+        <v>934.2940845470123</v>
       </c>
       <c r="I55" t="n">
-        <v>179.6327752373482</v>
+        <v>207.3980148487063</v>
       </c>
       <c r="J55" t="n">
-        <v>9.000641751175976</v>
+        <v>12.60851163809747</v>
       </c>
       <c r="K55" t="n">
-        <v>61.66910024117271</v>
+        <v>19.80402322683813</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="M55" t="n">
-        <v>1.07420783188117</v>
+        <v>1.004885601283739</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>0.9245845675468445</v>
+        <v>0.7573673129081726</v>
       </c>
       <c r="P55" t="n">
-        <v>0.0006644257227890193</v>
+        <v>0.003130298340693116</v>
       </c>
       <c r="Q55" t="n">
-        <v>938.1207292980874</v>
+        <v>991.18655346703</v>
       </c>
       <c r="R55" t="n">
-        <v>182.3052040854125</v>
+        <v>211.8481165997178</v>
       </c>
       <c r="S55" t="n">
-        <v>9.000638692968462</v>
+        <v>12.27486805864158</v>
       </c>
       <c r="T55" t="n">
-        <v>66.74451388456941</v>
+        <v>37.08844569317955</v>
       </c>
       <c r="U55" t="n">
-        <v>2.672428848064357</v>
+        <v>4.450101751011402</v>
       </c>
       <c r="V55" t="n">
-        <v>1.074204773673655</v>
+        <v>1.338529180739631</v>
       </c>
       <c r="W55" t="b">
         <v>1</v>
@@ -4481,68 +4481,68 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>949.2196096124491</v>
+        <v>931.7308284073556</v>
       </c>
       <c r="D56" t="n">
-        <v>4.056588199894033</v>
+        <v>12.21795956652855</v>
       </c>
       <c r="E56" t="n">
-        <v>205.1094495850843</v>
+        <v>140.4789340981374</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9024239182472229</v>
+        <v>0.9017484784126282</v>
       </c>
       <c r="G56" t="n">
-        <v>0.001009692437946796</v>
+        <v>0.006988451816141605</v>
       </c>
       <c r="H56" t="n">
-        <v>949.2196096124475</v>
+        <v>963.2227555194617</v>
       </c>
       <c r="I56" t="n">
-        <v>205.1094495850839</v>
+        <v>168.5515212074577</v>
       </c>
       <c r="J56" t="n">
-        <v>9.000641779862162</v>
+        <v>12.31551705382621</v>
       </c>
       <c r="K56" t="n">
-        <v>1.591615728102624e-12</v>
+        <v>31.49192711210605</v>
       </c>
       <c r="L56" t="n">
-        <v>3.410605131648481e-13</v>
+        <v>28.0725871093203</v>
       </c>
       <c r="M56" t="n">
-        <v>4.944053579968129</v>
+        <v>0.09755748729765834</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>0.9969459176063538</v>
+        <v>0.9999312162399292</v>
       </c>
       <c r="P56" t="n">
-        <v>6.421738362405449e-05</v>
+        <v>0.001832844573073089</v>
       </c>
       <c r="Q56" t="n">
-        <v>948.3804055264109</v>
+        <v>800.0000091408048</v>
       </c>
       <c r="R56" t="n">
-        <v>205.0775835163348</v>
+        <v>152.9628440298373</v>
       </c>
       <c r="S56" t="n">
-        <v>9.000641779862162</v>
+        <v>11.98061332445481</v>
       </c>
       <c r="T56" t="n">
-        <v>0.839204086038194</v>
+        <v>131.7308192665508</v>
       </c>
       <c r="U56" t="n">
-        <v>0.03186606874945141</v>
+        <v>12.48390993169988</v>
       </c>
       <c r="V56" t="n">
-        <v>4.944053579968129</v>
+        <v>0.2373462420737376</v>
       </c>
       <c r="W56" t="b">
         <v>1</v>
@@ -4554,68 +4554,68 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>921.8809467282865</v>
+        <v>857.2994480480713</v>
       </c>
       <c r="D57" t="n">
-        <v>10.09601292276444</v>
+        <v>8.210698431009181</v>
       </c>
       <c r="E57" t="n">
-        <v>132.0277192594506</v>
+        <v>188.9520760400035</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9047420620918274</v>
+        <v>0.9745776653289795</v>
       </c>
       <c r="G57" t="n">
-        <v>0.01683678291738033</v>
+        <v>0.0004035303718410432</v>
       </c>
       <c r="H57" t="n">
-        <v>949.4790620128981</v>
+        <v>940.8751706479679</v>
       </c>
       <c r="I57" t="n">
-        <v>164.2967489857195</v>
+        <v>188.766031281211</v>
       </c>
       <c r="J57" t="n">
-        <v>10.21326267224778</v>
+        <v>9.000712603548521</v>
       </c>
       <c r="K57" t="n">
-        <v>27.59811528461159</v>
+        <v>83.57572259989661</v>
       </c>
       <c r="L57" t="n">
-        <v>32.26902972626888</v>
+        <v>0.1860447587924625</v>
       </c>
       <c r="M57" t="n">
-        <v>0.1172497494833458</v>
+        <v>0.7900141725393404</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>0.9998440742492676</v>
+        <v>0.9783176183700562</v>
       </c>
       <c r="P57" t="n">
-        <v>0.006838074885308743</v>
+        <v>0.0006282278918661177</v>
       </c>
       <c r="Q57" t="n">
-        <v>800.0000420441365</v>
+        <v>935.9869932756089</v>
       </c>
       <c r="R57" t="n">
-        <v>152.0401262919456</v>
+        <v>189.7997976671825</v>
       </c>
       <c r="S57" t="n">
-        <v>9.327410971660093</v>
+        <v>9.000641716806388</v>
       </c>
       <c r="T57" t="n">
-        <v>121.88090468415</v>
+        <v>78.68754522753761</v>
       </c>
       <c r="U57" t="n">
-        <v>20.01240703249499</v>
+        <v>0.8477216271789985</v>
       </c>
       <c r="V57" t="n">
-        <v>0.7686019511043458</v>
+        <v>0.7899432857972073</v>
       </c>
       <c r="W57" t="b">
         <v>1</v>
@@ -4627,68 +4627,68 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>877.66740996343</v>
+        <v>1010.27586565436</v>
       </c>
       <c r="D58" t="n">
-        <v>8.192804608108121</v>
+        <v>9.017888444486854</v>
       </c>
       <c r="E58" t="n">
-        <v>200.1572790929328</v>
+        <v>202.6109224616086</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7510212659835815</v>
+        <v>0.7210264205932617</v>
       </c>
       <c r="G58" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.0001128785734181292</v>
       </c>
       <c r="H58" t="n">
-        <v>933.045316180193</v>
+        <v>985.893777989925</v>
       </c>
       <c r="I58" t="n">
-        <v>200.1572790929328</v>
+        <v>202.610868033151</v>
       </c>
       <c r="J58" t="n">
-        <v>9.000641730023091</v>
+        <v>9.017888444486854</v>
       </c>
       <c r="K58" t="n">
-        <v>55.37790621676299</v>
+        <v>24.38208766443495</v>
       </c>
       <c r="L58" t="n">
+        <v>5.442845755965209e-05</v>
+      </c>
+      <c r="M58" t="n">
         <v>0</v>
       </c>
-      <c r="M58" t="n">
-        <v>0.8078371219149698</v>
-      </c>
       <c r="N58" t="b">
         <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>0.9104511141777039</v>
+        <v>0.2172415405511856</v>
       </c>
       <c r="P58" t="n">
-        <v>0.0004137116193305701</v>
+        <v>0.0001713034143904224</v>
       </c>
       <c r="Q58" t="n">
-        <v>932.0941669109948</v>
+        <v>970.7350899870861</v>
       </c>
       <c r="R58" t="n">
-        <v>200.5079936668576</v>
+        <v>202.0518413661979</v>
       </c>
       <c r="S58" t="n">
-        <v>9.000641699917967</v>
+        <v>9.016835065698935</v>
       </c>
       <c r="T58" t="n">
-        <v>54.42675694756474</v>
+        <v>39.54077566727381</v>
       </c>
       <c r="U58" t="n">
-        <v>0.3507145739247619</v>
+        <v>0.5590810954106757</v>
       </c>
       <c r="V58" t="n">
-        <v>0.8078370918098461</v>
+        <v>0.001053378787919002</v>
       </c>
       <c r="W58" t="b">
         <v>1</v>
@@ -4700,68 +4700,68 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>857.4402903576622</v>
+        <v>1007.368061113335</v>
       </c>
       <c r="D59" t="n">
-        <v>10.0511729032616</v>
+        <v>5.858454552670492</v>
       </c>
       <c r="E59" t="n">
-        <v>193.6996328017243</v>
+        <v>206.6120925773124</v>
       </c>
       <c r="F59" t="n">
-        <v>0.516746461391449</v>
+        <v>0.858593761920929</v>
       </c>
       <c r="G59" t="n">
-        <v>0.001971905818209052</v>
+        <v>0.0002920783299487084</v>
       </c>
       <c r="H59" t="n">
-        <v>919.4282401253752</v>
+        <v>992.206710447728</v>
       </c>
       <c r="I59" t="n">
-        <v>193.6997658941246</v>
+        <v>206.6120925773116</v>
       </c>
       <c r="J59" t="n">
-        <v>10.0511729032616</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K59" t="n">
-        <v>61.98794976771296</v>
+        <v>15.1613506656073</v>
       </c>
       <c r="L59" t="n">
-        <v>0.0001330924002331813</v>
+        <v>8.810729923425242e-13</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.142187227191671</v>
       </c>
       <c r="N59" t="b">
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0.6959951519966125</v>
+        <v>0.8841882944107056</v>
       </c>
       <c r="P59" t="n">
-        <v>0.0004828143573831767</v>
+        <v>0.000573034689296037</v>
       </c>
       <c r="Q59" t="n">
-        <v>921.3330311054875</v>
+        <v>980.9178434157742</v>
       </c>
       <c r="R59" t="n">
-        <v>194.4069102079444</v>
+        <v>204.8738046546223</v>
       </c>
       <c r="S59" t="n">
-        <v>10.12046928659891</v>
+        <v>9.000628038949028</v>
       </c>
       <c r="T59" t="n">
-        <v>63.89274074782531</v>
+        <v>26.45021769756113</v>
       </c>
       <c r="U59" t="n">
-        <v>0.7072774062200722</v>
+        <v>1.738287922690148</v>
       </c>
       <c r="V59" t="n">
-        <v>0.06929638333731347</v>
+        <v>3.142173486278536</v>
       </c>
       <c r="W59" t="b">
         <v>1</v>
@@ -4773,68 +4773,68 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>971.5369628931536</v>
+        <v>952.8683526136296</v>
       </c>
       <c r="D60" t="n">
-        <v>10.58970799778279</v>
+        <v>5.790407170797956</v>
       </c>
       <c r="E60" t="n">
-        <v>137.7143366682456</v>
+        <v>193.0425995540196</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9041826725006104</v>
+        <v>0.8984211683273315</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0168119240552187</v>
+        <v>0.0002481373958289623</v>
       </c>
       <c r="H60" t="n">
-        <v>971.2633245673884</v>
+        <v>952.8683526134881</v>
       </c>
       <c r="I60" t="n">
-        <v>164.2913669007378</v>
+        <v>193.0425995540116</v>
       </c>
       <c r="J60" t="n">
-        <v>10.58885070916368</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K60" t="n">
-        <v>0.2736383257652051</v>
+        <v>1.414264261256903e-10</v>
       </c>
       <c r="L60" t="n">
-        <v>26.57703023249229</v>
+        <v>7.986500349943526e-12</v>
       </c>
       <c r="M60" t="n">
-        <v>0.0008572886191160478</v>
+        <v>3.210234609064206</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>0.9995449185371399</v>
+        <v>0.8999966979026794</v>
       </c>
       <c r="P60" t="n">
-        <v>0.005703567061573267</v>
+        <v>9.054003749042749e-05</v>
       </c>
       <c r="Q60" t="n">
-        <v>800.0000849724677</v>
+        <v>951.3724997507622</v>
       </c>
       <c r="R60" t="n">
-        <v>156.2690226856972</v>
+        <v>193.3197302100868</v>
       </c>
       <c r="S60" t="n">
-        <v>9.846628373946597</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T60" t="n">
-        <v>171.5368779206859</v>
+        <v>1.495852862867309</v>
       </c>
       <c r="U60" t="n">
-        <v>18.55468601745162</v>
+        <v>0.2771306560672144</v>
       </c>
       <c r="V60" t="n">
-        <v>0.7430796238361967</v>
+        <v>3.210234609064206</v>
       </c>
       <c r="W60" t="b">
         <v>1</v>
@@ -4850,64 +4850,64 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>994.1156538949632</v>
+        <v>924.8299017864933</v>
       </c>
       <c r="D61" t="n">
-        <v>5.130632828330791</v>
+        <v>5.534396136471122</v>
       </c>
       <c r="E61" t="n">
-        <v>204.8091508976131</v>
+        <v>195.1662686173504</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8883886337280273</v>
+        <v>0.7833482623100281</v>
       </c>
       <c r="G61" t="n">
-        <v>0.001002088305540383</v>
+        <v>0.0002815423358697444</v>
       </c>
       <c r="H61" t="n">
-        <v>994.115653893045</v>
+        <v>924.8299017867786</v>
       </c>
       <c r="I61" t="n">
-        <v>204.8091508975887</v>
+        <v>195.1662686173202</v>
       </c>
       <c r="J61" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="K61" t="n">
-        <v>1.918238012876827e-09</v>
+        <v>2.852402758435346e-10</v>
       </c>
       <c r="L61" t="n">
-        <v>2.438582669128664e-11</v>
+        <v>3.021227712451946e-11</v>
       </c>
       <c r="M61" t="n">
-        <v>3.870008951531371</v>
+        <v>3.46624564339104</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>0.98008793592453</v>
+        <v>0.8357070088386536</v>
       </c>
       <c r="P61" t="n">
-        <v>0.0002450481115374714</v>
+        <v>0.0001572461769683287</v>
       </c>
       <c r="Q61" t="n">
-        <v>977.1921363602071</v>
+        <v>933.4096860014398</v>
       </c>
       <c r="R61" t="n">
-        <v>204.7237888816042</v>
+        <v>195.6067456782189</v>
       </c>
       <c r="S61" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="T61" t="n">
-        <v>16.92351753475612</v>
+        <v>8.579784214946471</v>
       </c>
       <c r="U61" t="n">
-        <v>0.08536201600887239</v>
+        <v>0.4404770608684885</v>
       </c>
       <c r="V61" t="n">
-        <v>3.870008951531371</v>
+        <v>3.46624564339104</v>
       </c>
       <c r="W61" t="b">
         <v>1</v>
@@ -4919,68 +4919,68 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>843.2242537188664</v>
+        <v>930.7910609203224</v>
       </c>
       <c r="D62" t="n">
-        <v>9.857427139480592</v>
+        <v>5.581461844348611</v>
       </c>
       <c r="E62" t="n">
-        <v>195.2329477018448</v>
+        <v>196.7342281172041</v>
       </c>
       <c r="F62" t="n">
-        <v>0.5352276563644409</v>
+        <v>0.8887342810630798</v>
       </c>
       <c r="G62" t="n">
-        <v>0.002033084630966187</v>
+        <v>0.0002782602678053081</v>
       </c>
       <c r="H62" t="n">
-        <v>919.4282525630487</v>
+        <v>930.7910609201529</v>
       </c>
       <c r="I62" t="n">
-        <v>195.2329474754656</v>
+        <v>196.7342250164554</v>
       </c>
       <c r="J62" t="n">
-        <v>9.857427139480594</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K62" t="n">
-        <v>76.20399884418225</v>
+        <v>1.695070750429295e-10</v>
       </c>
       <c r="L62" t="n">
-        <v>2.263791998302622e-07</v>
+        <v>3.100748699580436e-06</v>
       </c>
       <c r="M62" t="n">
-        <v>1.77635683940025e-15</v>
+        <v>3.419179935513551</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>0.7889383435249329</v>
+        <v>0.8975760936737061</v>
       </c>
       <c r="P62" t="n">
-        <v>0.0005952381179668009</v>
+        <v>0.0001132614415837452</v>
       </c>
       <c r="Q62" t="n">
-        <v>921.3012915559344</v>
+        <v>937.0014956331149</v>
       </c>
       <c r="R62" t="n">
-        <v>195.9925667719498</v>
+        <v>197.0572972587113</v>
       </c>
       <c r="S62" t="n">
-        <v>9.944844047513044</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T62" t="n">
-        <v>78.07703783706802</v>
+        <v>6.210434712792562</v>
       </c>
       <c r="U62" t="n">
-        <v>0.7596190701049466</v>
+        <v>0.323069141507176</v>
       </c>
       <c r="V62" t="n">
-        <v>0.08741690803245206</v>
+        <v>3.419179935513551</v>
       </c>
       <c r="W62" t="b">
         <v>1</v>
@@ -4996,64 +4996,64 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>876.8033910623137</v>
+        <v>861.5329745921342</v>
       </c>
       <c r="D63" t="n">
-        <v>8.170535320686376</v>
+        <v>7.210532926372144</v>
       </c>
       <c r="E63" t="n">
-        <v>209.1884006414471</v>
+        <v>191.7940433259565</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7446001172065735</v>
+        <v>0.9867919683456421</v>
       </c>
       <c r="G63" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.0004035303718410432</v>
       </c>
       <c r="H63" t="n">
-        <v>933.0453149342344</v>
+        <v>940.870088731476</v>
       </c>
       <c r="I63" t="n">
-        <v>209.1884006414472</v>
+        <v>191.7940433259601</v>
       </c>
       <c r="J63" t="n">
-        <v>9.000641749277776</v>
+        <v>9.000790976912986</v>
       </c>
       <c r="K63" t="n">
-        <v>56.24192387192068</v>
+        <v>79.33711413934179</v>
       </c>
       <c r="L63" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>3.581135388230905e-12</v>
       </c>
       <c r="M63" t="n">
-        <v>0.8301064285913995</v>
+        <v>1.790258050540842</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0.9081918001174927</v>
+        <v>0.9944410920143127</v>
       </c>
       <c r="P63" t="n">
-        <v>0.0004345132037997246</v>
+        <v>0.0005870770546607673</v>
       </c>
       <c r="Q63" t="n">
-        <v>931.913776584382</v>
+        <v>935.7631255584643</v>
       </c>
       <c r="R63" t="n">
-        <v>208.7142223390433</v>
+        <v>192.6067966181187</v>
       </c>
       <c r="S63" t="n">
-        <v>9.0006416738313</v>
+        <v>9.000641753231061</v>
       </c>
       <c r="T63" t="n">
-        <v>55.11038552206833</v>
+        <v>74.23015096633003</v>
       </c>
       <c r="U63" t="n">
-        <v>0.4741783024038853</v>
+        <v>0.8127532921621707</v>
       </c>
       <c r="V63" t="n">
-        <v>0.8301063531449238</v>
+        <v>1.790108826858917</v>
       </c>
       <c r="W63" t="b">
         <v>1</v>
@@ -5065,68 +5065,68 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>929.8197953783028</v>
+        <v>812.9298109768056</v>
       </c>
       <c r="D64" t="n">
-        <v>6.000780914534034</v>
+        <v>8.927339304654152</v>
       </c>
       <c r="E64" t="n">
-        <v>191.293101093024</v>
+        <v>199.9840388767094</v>
       </c>
       <c r="F64" t="n">
-        <v>0.8721053600311279</v>
+        <v>0.941252589225769</v>
       </c>
       <c r="G64" t="n">
-        <v>0.001007982064038515</v>
+        <v>0.001797718345187604</v>
       </c>
       <c r="H64" t="n">
-        <v>929.8197953794917</v>
+        <v>920.0676024229934</v>
       </c>
       <c r="I64" t="n">
-        <v>191.293101093024</v>
+        <v>199.9840388767092</v>
       </c>
       <c r="J64" t="n">
-        <v>9.000641779862162</v>
+        <v>9.438070172352452</v>
       </c>
       <c r="K64" t="n">
-        <v>1.188823262054939e-09</v>
+        <v>107.1377914461879</v>
       </c>
       <c r="L64" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>1.70530256582424e-13</v>
       </c>
       <c r="M64" t="n">
-        <v>2.999860865328128</v>
+        <v>0.5107308676982996</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>0.7787668108940125</v>
+        <v>0.951556921005249</v>
       </c>
       <c r="P64" t="n">
-        <v>0.0001237320830114186</v>
+        <v>0.001087722019292414</v>
       </c>
       <c r="Q64" t="n">
-        <v>932.4721316810803</v>
+        <v>927.3972624839309</v>
       </c>
       <c r="R64" t="n">
-        <v>191.6845267373567</v>
+        <v>200.88141034478</v>
       </c>
       <c r="S64" t="n">
-        <v>9.000641779862162</v>
+        <v>9.163684741342754</v>
       </c>
       <c r="T64" t="n">
-        <v>2.652336302777485</v>
+        <v>114.4674515071254</v>
       </c>
       <c r="U64" t="n">
-        <v>0.3914256443326849</v>
+        <v>0.8973714680705882</v>
       </c>
       <c r="V64" t="n">
-        <v>2.999860865328128</v>
+        <v>0.2363454366886018</v>
       </c>
       <c r="W64" t="b">
         <v>1</v>
@@ -5142,64 +5142,64 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>978.2805827112397</v>
+        <v>936.8009197370681</v>
       </c>
       <c r="D65" t="n">
-        <v>10.72423713873273</v>
+        <v>10.79800730495699</v>
       </c>
       <c r="E65" t="n">
-        <v>160.7661531054825</v>
+        <v>130.444792546047</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9041489362716675</v>
+        <v>0.9844457507133484</v>
       </c>
       <c r="G65" t="n">
-        <v>0.001028560451231897</v>
+        <v>0.0001908497797558084</v>
       </c>
       <c r="H65" t="n">
-        <v>978.286516615565</v>
+        <v>937.9052154350181</v>
       </c>
       <c r="I65" t="n">
-        <v>176.130051055941</v>
+        <v>176.1734342559908</v>
       </c>
       <c r="J65" t="n">
-        <v>10.72426807302894</v>
+        <v>10.79917135648461</v>
       </c>
       <c r="K65" t="n">
-        <v>0.005933904325274852</v>
+        <v>1.104295697950079</v>
       </c>
       <c r="L65" t="n">
-        <v>15.36389795045844</v>
+        <v>45.72864170994379</v>
       </c>
       <c r="M65" t="n">
-        <v>3.093429621614519e-05</v>
+        <v>0.001164051527615229</v>
       </c>
       <c r="N65" t="b">
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>0.7500676512718201</v>
+        <v>0.9999996423721313</v>
       </c>
       <c r="P65" t="n">
-        <v>0.002602088497951627</v>
+        <v>0.001466728397645056</v>
       </c>
       <c r="Q65" t="n">
-        <v>831.2155293829998</v>
+        <v>800.0001507079837</v>
       </c>
       <c r="R65" t="n">
-        <v>173.906238417989</v>
+        <v>150.000552917753</v>
       </c>
       <c r="S65" t="n">
-        <v>10.47967825555682</v>
+        <v>10.63746911898502</v>
       </c>
       <c r="T65" t="n">
-        <v>147.06505332824</v>
+        <v>136.8007690290843</v>
       </c>
       <c r="U65" t="n">
-        <v>13.14008531250641</v>
+        <v>19.55576037170599</v>
       </c>
       <c r="V65" t="n">
-        <v>0.2445588831759054</v>
+        <v>0.160538185971971</v>
       </c>
       <c r="W65" t="b">
         <v>1</v>
@@ -5211,68 +5211,68 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>985.9822307898403</v>
+        <v>864.1459023921725</v>
       </c>
       <c r="D66" t="n">
-        <v>6.311976211576789</v>
+        <v>7.215065843312352</v>
       </c>
       <c r="E66" t="n">
-        <v>187.9596397528457</v>
+        <v>181.8768456708378</v>
       </c>
       <c r="F66" t="n">
-        <v>0.89444899559021</v>
+        <v>0.9790980815887451</v>
       </c>
       <c r="G66" t="n">
-        <v>0.00100928673055023</v>
+        <v>0.0009753215708769858</v>
       </c>
       <c r="H66" t="n">
-        <v>985.9823009650738</v>
+        <v>933.5301576108425</v>
       </c>
       <c r="I66" t="n">
-        <v>187.9596259850493</v>
+        <v>180.7271785998349</v>
       </c>
       <c r="J66" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000678720989361</v>
       </c>
       <c r="K66" t="n">
-        <v>7.017523353169963e-05</v>
+        <v>69.38425521866998</v>
       </c>
       <c r="L66" t="n">
-        <v>1.37677964175964e-05</v>
+        <v>1.149667071002938</v>
       </c>
       <c r="M66" t="n">
-        <v>2.688665568285373</v>
+        <v>1.785612877677009</v>
       </c>
       <c r="N66" t="b">
         <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>0.8084630966186523</v>
+        <v>0.9942413568496704</v>
       </c>
       <c r="P66" t="n">
-        <v>0.0002948164474219084</v>
+        <v>0.000791300437413156</v>
       </c>
       <c r="Q66" t="n">
-        <v>971.8504073656826</v>
+        <v>937.0812140315644</v>
       </c>
       <c r="R66" t="n">
-        <v>188.7730732314516</v>
+        <v>183.4696252299289</v>
       </c>
       <c r="S66" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641277380145</v>
       </c>
       <c r="T66" t="n">
-        <v>14.13182342415769</v>
+        <v>72.9353116393919</v>
       </c>
       <c r="U66" t="n">
-        <v>0.8134334786059014</v>
+        <v>1.592779559091099</v>
       </c>
       <c r="V66" t="n">
-        <v>2.688665568285373</v>
+        <v>1.785575434067793</v>
       </c>
       <c r="W66" t="b">
         <v>1</v>
@@ -5284,68 +5284,68 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>960.6999207074333</v>
+        <v>1029.22856125831</v>
       </c>
       <c r="D67" t="n">
-        <v>13.60431810949872</v>
+        <v>10.83039286424729</v>
       </c>
       <c r="E67" t="n">
-        <v>210.2668897524188</v>
+        <v>212.6385535812693</v>
       </c>
       <c r="F67" t="n">
-        <v>0.808692991733551</v>
+        <v>0.7356811761856079</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0006025993498042226</v>
+        <v>9.742625115904957e-05</v>
       </c>
       <c r="H67" t="n">
-        <v>960.6999209343498</v>
+        <v>985.8937770003619</v>
       </c>
       <c r="I67" t="n">
-        <v>210.2668897524188</v>
+        <v>212.6385535812693</v>
       </c>
       <c r="J67" t="n">
-        <v>11.8218186911064</v>
+        <v>10.83054006389804</v>
       </c>
       <c r="K67" t="n">
-        <v>2.269165406687534e-07</v>
+        <v>43.33478425794772</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>1.782499418392316</v>
+        <v>0.0001471996507493856</v>
       </c>
       <c r="N67" t="b">
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>0.6865601539611816</v>
+        <v>0.923780620098114</v>
       </c>
       <c r="P67" t="n">
-        <v>0.002614962868392467</v>
+        <v>0.0002607010246720165</v>
       </c>
       <c r="Q67" t="n">
-        <v>823.3017663542978</v>
+        <v>971.1219136847757</v>
       </c>
       <c r="R67" t="n">
-        <v>211.1980452289216</v>
+        <v>212.1368848941592</v>
       </c>
       <c r="S67" t="n">
-        <v>12.79677363301607</v>
+        <v>10.82596850169796</v>
       </c>
       <c r="T67" t="n">
-        <v>137.3981543531355</v>
+        <v>58.10664757353391</v>
       </c>
       <c r="U67" t="n">
-        <v>0.9311554765027381</v>
+        <v>0.5016686871101683</v>
       </c>
       <c r="V67" t="n">
-        <v>0.8075444764826507</v>
+        <v>0.004424362549332983</v>
       </c>
       <c r="W67" t="b">
         <v>1</v>
@@ -5357,68 +5357,68 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>958.9557390280952</v>
+        <v>869.7865631882487</v>
       </c>
       <c r="D68" t="n">
-        <v>14.00468254643085</v>
+        <v>10.01016271697617</v>
       </c>
       <c r="E68" t="n">
-        <v>201.8530725115117</v>
+        <v>220.620048122057</v>
       </c>
       <c r="F68" t="n">
-        <v>0.808692991733551</v>
+        <v>0.7658896446228027</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0006025993498042226</v>
+        <v>0.0007880357443355024</v>
       </c>
       <c r="H68" t="n">
-        <v>958.955739282253</v>
+        <v>925.9052788979586</v>
       </c>
       <c r="I68" t="n">
-        <v>201.8530725115117</v>
+        <v>220.1083942025494</v>
       </c>
       <c r="J68" t="n">
-        <v>11.82181859823</v>
+        <v>10.01016271697617</v>
       </c>
       <c r="K68" t="n">
-        <v>2.541578396630939e-07</v>
+        <v>56.11871570970993</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>0.5116539195075518</v>
       </c>
       <c r="M68" t="n">
-        <v>2.182863948200851</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="N68" t="b">
         <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>0.9163044691085815</v>
+        <v>0.6383228898048401</v>
       </c>
       <c r="P68" t="n">
-        <v>0.002945144427940249</v>
+        <v>0.0004742451419588178</v>
       </c>
       <c r="Q68" t="n">
-        <v>815.0120327863149</v>
+        <v>929.3630438185602</v>
       </c>
       <c r="R68" t="n">
-        <v>204.3746510337279</v>
+        <v>218.7516846822802</v>
       </c>
       <c r="S68" t="n">
-        <v>13.08705758989309</v>
+        <v>10.04089007789262</v>
       </c>
       <c r="T68" t="n">
-        <v>143.9437062417803</v>
+        <v>59.57648063031149</v>
       </c>
       <c r="U68" t="n">
-        <v>2.521578522216174</v>
+        <v>1.868363439776772</v>
       </c>
       <c r="V68" t="n">
-        <v>0.9176249565377681</v>
+        <v>0.03072736091645822</v>
       </c>
       <c r="W68" t="b">
         <v>1</v>
@@ -5430,68 +5430,68 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>934.5079730422938</v>
+        <v>852.3877700309616</v>
       </c>
       <c r="D69" t="n">
-        <v>11.10399410569217</v>
+        <v>7.705590918851363</v>
       </c>
       <c r="E69" t="n">
-        <v>123.3863151689311</v>
+        <v>203.9794727730402</v>
       </c>
       <c r="F69" t="n">
-        <v>0.9066013097763062</v>
+        <v>0.9864906072616577</v>
       </c>
       <c r="G69" t="n">
-        <v>0.005423417314887047</v>
+        <v>0.001153156976215541</v>
       </c>
       <c r="H69" t="n">
-        <v>945.815868889224</v>
+        <v>933.5293079644696</v>
       </c>
       <c r="I69" t="n">
-        <v>173.6140089857064</v>
+        <v>203.9794727730373</v>
       </c>
       <c r="J69" t="n">
-        <v>11.10399430358096</v>
+        <v>9.000641612788701</v>
       </c>
       <c r="K69" t="n">
-        <v>11.30789584693025</v>
+        <v>81.14153793350795</v>
       </c>
       <c r="L69" t="n">
-        <v>50.22769381677537</v>
+        <v>2.870592652470805e-12</v>
       </c>
       <c r="M69" t="n">
-        <v>1.978887862463807e-07</v>
+        <v>1.295050693937339</v>
       </c>
       <c r="N69" t="b">
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>0.9999405145645142</v>
+        <v>0.9914131164550781</v>
       </c>
       <c r="P69" t="n">
-        <v>0.01122257206588984</v>
+        <v>0.0007015690789557993</v>
       </c>
       <c r="Q69" t="n">
-        <v>800.0000000759403</v>
+        <v>933.0378740011065</v>
       </c>
       <c r="R69" t="n">
-        <v>151.2606678279526</v>
+        <v>202.9771593752459</v>
       </c>
       <c r="S69" t="n">
-        <v>9.694884576499641</v>
+        <v>9.00064178893847</v>
       </c>
       <c r="T69" t="n">
-        <v>134.5079729663535</v>
+        <v>80.65010397014487</v>
       </c>
       <c r="U69" t="n">
-        <v>27.87435265902153</v>
+        <v>1.002313397794325</v>
       </c>
       <c r="V69" t="n">
-        <v>1.409109529192529</v>
+        <v>1.295050870087107</v>
       </c>
       <c r="W69" t="b">
         <v>1</v>
@@ -5507,64 +5507,64 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>898.1808237942174</v>
+        <v>875.1834060512713</v>
       </c>
       <c r="D70" t="n">
-        <v>7.158907973127043</v>
+        <v>6.442722668560213</v>
       </c>
       <c r="E70" t="n">
-        <v>201.5385972936553</v>
+        <v>189.6956515728362</v>
       </c>
       <c r="F70" t="n">
-        <v>0.6930186748504639</v>
+        <v>0.9526134133338928</v>
       </c>
       <c r="G70" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.001392161007970572</v>
       </c>
       <c r="H70" t="n">
-        <v>933.0453176152432</v>
+        <v>925.9037133508269</v>
       </c>
       <c r="I70" t="n">
-        <v>201.5385972936552</v>
+        <v>189.6956515728363</v>
       </c>
       <c r="J70" t="n">
-        <v>9.000641564714643</v>
+        <v>9.000641718221598</v>
       </c>
       <c r="K70" t="n">
-        <v>34.8644938210258</v>
+        <v>50.72030729955566</v>
       </c>
       <c r="L70" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>1.70530256582424e-13</v>
       </c>
       <c r="M70" t="n">
-        <v>1.8417335915876</v>
+        <v>2.557919049661384</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>0.7245321869850159</v>
+        <v>0.9910576343536377</v>
       </c>
       <c r="P70" t="n">
-        <v>0.0002733006549533457</v>
+        <v>0.000479795562569052</v>
       </c>
       <c r="Q70" t="n">
-        <v>934.4237000770559</v>
+        <v>937.4447875887574</v>
       </c>
       <c r="R70" t="n">
-        <v>201.6922972534761</v>
+        <v>190.3498873846831</v>
       </c>
       <c r="S70" t="n">
-        <v>9.000641812212503</v>
+        <v>9.000641991304178</v>
       </c>
       <c r="T70" t="n">
-        <v>36.24287628283844</v>
+        <v>62.26138153748616</v>
       </c>
       <c r="U70" t="n">
-        <v>0.1536999598208411</v>
+        <v>0.6542358118469167</v>
       </c>
       <c r="V70" t="n">
-        <v>1.84173383908546</v>
+        <v>2.557919322743965</v>
       </c>
       <c r="W70" t="b">
         <v>1</v>
@@ -5576,68 +5576,68 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>955.1753961048785</v>
+        <v>879.4980539994262</v>
       </c>
       <c r="D71" t="n">
-        <v>4.45135698723502</v>
+        <v>8.738906620407827</v>
       </c>
       <c r="E71" t="n">
-        <v>202.6339143433278</v>
+        <v>193.6028206897869</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9024239182472229</v>
+        <v>0.7990202307701111</v>
       </c>
       <c r="G71" t="n">
-        <v>0.001009692437946796</v>
+        <v>0.0004035303718410432</v>
       </c>
       <c r="H71" t="n">
-        <v>955.1753961048713</v>
+        <v>940.870098875969</v>
       </c>
       <c r="I71" t="n">
-        <v>202.6339143433277</v>
+        <v>193.6028206897864</v>
       </c>
       <c r="J71" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641549284468</v>
       </c>
       <c r="K71" t="n">
-        <v>7.16227077646181e-12</v>
+        <v>61.37204487654276</v>
       </c>
       <c r="L71" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>5.115907697472721e-13</v>
       </c>
       <c r="M71" t="n">
-        <v>4.549284792627142</v>
+        <v>0.261734928876642</v>
       </c>
       <c r="N71" t="b">
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>0.9968396425247192</v>
+        <v>0.8270676136016846</v>
       </c>
       <c r="P71" t="n">
-        <v>7.074128370732069e-05</v>
+        <v>0.000432800967246294</v>
       </c>
       <c r="Q71" t="n">
-        <v>953.4234917160812</v>
+        <v>937.2173254955171</v>
       </c>
       <c r="R71" t="n">
-        <v>202.6491852020652</v>
+        <v>194.1086399025454</v>
       </c>
       <c r="S71" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641752862078</v>
       </c>
       <c r="T71" t="n">
-        <v>1.751904388797243</v>
+        <v>57.71927149609087</v>
       </c>
       <c r="U71" t="n">
-        <v>0.01527085873738088</v>
+        <v>0.5058192127584391</v>
       </c>
       <c r="V71" t="n">
-        <v>4.549284792627142</v>
+        <v>0.2617351324542518</v>
       </c>
       <c r="W71" t="b">
         <v>1</v>
@@ -5653,64 +5653,64 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>965.5247197696567</v>
+        <v>948.0406853580649</v>
       </c>
       <c r="D72" t="n">
-        <v>14.11893637093065</v>
+        <v>13.75977046212345</v>
       </c>
       <c r="E72" t="n">
-        <v>185.5322626065073</v>
+        <v>204.1520155094046</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7510432004928589</v>
+        <v>0.9320546984672546</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0006025993498042226</v>
+        <v>0.001686847768723965</v>
       </c>
       <c r="H72" t="n">
-        <v>965.5243626629821</v>
+        <v>918.4376755048595</v>
       </c>
       <c r="I72" t="n">
-        <v>185.5322626065075</v>
+        <v>206.285132575113</v>
       </c>
       <c r="J72" t="n">
-        <v>11.82181869298677</v>
+        <v>12.22541010675307</v>
       </c>
       <c r="K72" t="n">
-        <v>0.0003571066746417273</v>
+        <v>29.60300985320544</v>
       </c>
       <c r="L72" t="n">
-        <v>1.70530256582424e-13</v>
+        <v>2.133117065708404</v>
       </c>
       <c r="M72" t="n">
-        <v>2.297117677943881</v>
+        <v>1.534360355370373</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
       </c>
       <c r="O72" t="n">
-        <v>0.9097729921340942</v>
+        <v>0.8628045916557312</v>
       </c>
       <c r="P72" t="n">
-        <v>0.003439165186136961</v>
+        <v>0.003511777613312006</v>
       </c>
       <c r="Q72" t="n">
-        <v>810.1024239623029</v>
+        <v>992.3112875783348</v>
       </c>
       <c r="R72" t="n">
-        <v>189.8320510991121</v>
+        <v>208.9912806387586</v>
       </c>
       <c r="S72" t="n">
-        <v>13.07139598362592</v>
+        <v>12.27949167529618</v>
       </c>
       <c r="T72" t="n">
-        <v>155.4222958073539</v>
+        <v>44.27060222026989</v>
       </c>
       <c r="U72" t="n">
-        <v>4.29978849260479</v>
+        <v>4.839265129353976</v>
       </c>
       <c r="V72" t="n">
-        <v>1.047540387304728</v>
+        <v>1.480278786827265</v>
       </c>
       <c r="W72" t="b">
         <v>1</v>
@@ -5722,68 +5722,68 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>938.0410907075174</v>
+        <v>966.4059674901793</v>
       </c>
       <c r="D73" t="n">
-        <v>6.182956613823269</v>
+        <v>15.17770026835904</v>
       </c>
       <c r="E73" t="n">
-        <v>210.3731746953267</v>
+        <v>211.3861979220888</v>
       </c>
       <c r="F73" t="n">
-        <v>0.8901363015174866</v>
+        <v>0.961039125919342</v>
       </c>
       <c r="G73" t="n">
-        <v>0.001009692437946796</v>
+        <v>0.0005593529785983264</v>
       </c>
       <c r="H73" t="n">
-        <v>938.0410907074877</v>
+        <v>944.1999543755353</v>
       </c>
       <c r="I73" t="n">
-        <v>210.3731746953268</v>
+        <v>211.3862036764079</v>
       </c>
       <c r="J73" t="n">
-        <v>9.000641779862162</v>
+        <v>12.24328301386874</v>
       </c>
       <c r="K73" t="n">
-        <v>2.967226464534178e-11</v>
+        <v>22.20601311464395</v>
       </c>
       <c r="L73" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>5.754319062134527e-06</v>
       </c>
       <c r="M73" t="n">
-        <v>2.817685166038894</v>
+        <v>2.934417254490297</v>
       </c>
       <c r="N73" t="b">
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>0.7319839596748352</v>
+        <v>0.999210000038147</v>
       </c>
       <c r="P73" t="n">
-        <v>7.256054959725589e-05</v>
+        <v>0.003619997529312968</v>
       </c>
       <c r="Q73" t="n">
-        <v>938.5659989505303</v>
+        <v>994.819259883107</v>
       </c>
       <c r="R73" t="n">
-        <v>210.2305950568462</v>
+        <v>223.6151777573764</v>
       </c>
       <c r="S73" t="n">
-        <v>9.000641779862162</v>
+        <v>12.56653644760171</v>
       </c>
       <c r="T73" t="n">
-        <v>0.5249082430129874</v>
+        <v>28.4132923929277</v>
       </c>
       <c r="U73" t="n">
-        <v>0.1425796384804983</v>
+        <v>12.22897983528759</v>
       </c>
       <c r="V73" t="n">
-        <v>2.817685166038894</v>
+        <v>2.611163820757326</v>
       </c>
       <c r="W73" t="b">
         <v>1</v>
@@ -5795,68 +5795,68 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>919.2332883952536</v>
+        <v>893.2486385287158</v>
       </c>
       <c r="D74" t="n">
-        <v>8.409170461064056</v>
+        <v>6.59528431853333</v>
       </c>
       <c r="E74" t="n">
-        <v>152.3051255060128</v>
+        <v>189.0610863136084</v>
       </c>
       <c r="F74" t="n">
-        <v>0.8928853869438171</v>
+        <v>0.8671261668205261</v>
       </c>
       <c r="G74" t="n">
-        <v>0.001026143436320126</v>
+        <v>0.0004035303718410432</v>
       </c>
       <c r="H74" t="n">
-        <v>919.2394190784231</v>
+        <v>940.871427355211</v>
       </c>
       <c r="I74" t="n">
-        <v>176.1296280276241</v>
+        <v>189.061086313599</v>
       </c>
       <c r="J74" t="n">
-        <v>9.000260210710346</v>
+        <v>9.000641667410143</v>
       </c>
       <c r="K74" t="n">
-        <v>0.006130683169544682</v>
+        <v>47.62278882649525</v>
       </c>
       <c r="L74" t="n">
-        <v>23.82450252161132</v>
+        <v>9.407585821463726e-12</v>
       </c>
       <c r="M74" t="n">
-        <v>0.5910897496462901</v>
+        <v>2.405357348876813</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0.9610162377357483</v>
+        <v>0.9443646669387817</v>
       </c>
       <c r="P74" t="n">
-        <v>0.002215735614299774</v>
+        <v>0.0004216879606246948</v>
       </c>
       <c r="Q74" t="n">
-        <v>814.0699568674833</v>
+        <v>938.221775418859</v>
       </c>
       <c r="R74" t="n">
-        <v>161.2473461306475</v>
+        <v>190.3461218253021</v>
       </c>
       <c r="S74" t="n">
-        <v>9.000641810543284</v>
+        <v>9.000641768627496</v>
       </c>
       <c r="T74" t="n">
-        <v>105.1633315277703</v>
+        <v>44.97313689014322</v>
       </c>
       <c r="U74" t="n">
-        <v>8.942220624634757</v>
+        <v>1.285035511693735</v>
       </c>
       <c r="V74" t="n">
-        <v>0.5914713494792281</v>
+        <v>2.405357450094166</v>
       </c>
       <c r="W74" t="b">
         <v>1</v>
@@ -5868,68 +5868,68 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>959.1442612738502</v>
+        <v>870.4140949772889</v>
       </c>
       <c r="D75" t="n">
-        <v>12.04133438956063</v>
+        <v>7.952992623630619</v>
       </c>
       <c r="E75" t="n">
-        <v>127.0493257167431</v>
+        <v>199.8737532158461</v>
       </c>
       <c r="F75" t="n">
-        <v>0.8992465734481812</v>
+        <v>0.974799633026123</v>
       </c>
       <c r="G75" t="n">
-        <v>0.005398744251579046</v>
+        <v>0.001176272286102176</v>
       </c>
       <c r="H75" t="n">
-        <v>959.1442612738585</v>
+        <v>933.5293019251812</v>
       </c>
       <c r="I75" t="n">
-        <v>173.6137580462745</v>
+        <v>199.8737532158483</v>
       </c>
       <c r="J75" t="n">
-        <v>12.04133438956064</v>
+        <v>9.000641734796444</v>
       </c>
       <c r="K75" t="n">
-        <v>8.29913915367797e-12</v>
+        <v>63.11520694789237</v>
       </c>
       <c r="L75" t="n">
-        <v>46.56443232953136</v>
+        <v>2.188471626141109e-12</v>
       </c>
       <c r="M75" t="n">
-        <v>5.329070518200751e-15</v>
+        <v>1.047649111165825</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>0.9996368885040283</v>
+        <v>0.9719758033752441</v>
       </c>
       <c r="P75" t="n">
-        <v>0.01029244158416986</v>
+        <v>0.0005613354151137173</v>
       </c>
       <c r="Q75" t="n">
-        <v>800.0000197778818</v>
+        <v>934.9361922073288</v>
       </c>
       <c r="R75" t="n">
-        <v>155.444514288579</v>
+        <v>200.7485020133153</v>
       </c>
       <c r="S75" t="n">
-        <v>10.35308057308538</v>
+        <v>9.000641471498632</v>
       </c>
       <c r="T75" t="n">
-        <v>159.1442414959685</v>
+        <v>64.52209723003989</v>
       </c>
       <c r="U75" t="n">
-        <v>28.39518857183587</v>
+        <v>0.8747487974692092</v>
       </c>
       <c r="V75" t="n">
-        <v>1.688253816475246</v>
+        <v>1.047648847868013</v>
       </c>
       <c r="W75" t="b">
         <v>1</v>
@@ -5941,68 +5941,68 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>850.3245848097874</v>
+        <v>955.1343834559148</v>
       </c>
       <c r="D76" t="n">
-        <v>6.753786323906015</v>
+        <v>8.977698358244938</v>
       </c>
       <c r="E76" t="n">
-        <v>178.6721191470512</v>
+        <v>149.4975831316712</v>
       </c>
       <c r="F76" t="n">
-        <v>0.8777484893798828</v>
+        <v>0.9152489304542542</v>
       </c>
       <c r="G76" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.0006277773063629866</v>
       </c>
       <c r="H76" t="n">
-        <v>933.0453193863964</v>
+        <v>857.2992001435658</v>
       </c>
       <c r="I76" t="n">
-        <v>178.6721191470512</v>
+        <v>176.1732571670742</v>
       </c>
       <c r="J76" t="n">
-        <v>9.000641529070483</v>
+        <v>9.000001070377479</v>
       </c>
       <c r="K76" t="n">
-        <v>82.72073457660895</v>
+        <v>97.83518331234893</v>
       </c>
       <c r="L76" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>26.67567403540298</v>
       </c>
       <c r="M76" t="n">
-        <v>2.246855205164469</v>
+        <v>0.0223027121325412</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>0.9901487827301025</v>
+        <v>0.9978660941123962</v>
       </c>
       <c r="P76" t="n">
-        <v>0.0008922269917093217</v>
+        <v>0.0009542824700474739</v>
       </c>
       <c r="Q76" t="n">
-        <v>936.1392340187068</v>
+        <v>825.7593186655516</v>
       </c>
       <c r="R76" t="n">
-        <v>182.0576574607934</v>
+        <v>156.9450891358731</v>
       </c>
       <c r="S76" t="n">
-        <v>9.000638657114816</v>
+        <v>9.000641898947027</v>
       </c>
       <c r="T76" t="n">
-        <v>85.81464920891938</v>
+        <v>129.3750647903631</v>
       </c>
       <c r="U76" t="n">
-        <v>3.385538313742131</v>
+        <v>7.447506004201841</v>
       </c>
       <c r="V76" t="n">
-        <v>2.246852333208802</v>
+        <v>0.02294354070208904</v>
       </c>
       <c r="W76" t="b">
         <v>1</v>
@@ -6014,68 +6014,68 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>955.8201925449489</v>
+        <v>851.5745269766401</v>
       </c>
       <c r="D77" t="n">
-        <v>9.394153645796282</v>
+        <v>7.449623063406067</v>
       </c>
       <c r="E77" t="n">
-        <v>147.706171563257</v>
+        <v>203.3669380432765</v>
       </c>
       <c r="F77" t="n">
-        <v>0.9065464735031128</v>
+        <v>0.9866198301315308</v>
       </c>
       <c r="G77" t="n">
-        <v>0.001030099927447736</v>
+        <v>0.002527530770748854</v>
       </c>
       <c r="H77" t="n">
-        <v>955.8194453666717</v>
+        <v>920.0590705958026</v>
       </c>
       <c r="I77" t="n">
-        <v>176.1300441983605</v>
+        <v>204.0722128093243</v>
       </c>
       <c r="J77" t="n">
-        <v>9.394163106950252</v>
+        <v>9.000595810886647</v>
       </c>
       <c r="K77" t="n">
-        <v>0.000747178277151761</v>
+        <v>68.48454361916254</v>
       </c>
       <c r="L77" t="n">
-        <v>28.42387263510344</v>
+        <v>0.7052747660477507</v>
       </c>
       <c r="M77" t="n">
-        <v>9.461153970491409e-06</v>
+        <v>1.55097274748058</v>
       </c>
       <c r="N77" t="b">
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0.9986504912376404</v>
+        <v>0.9947485327720642</v>
       </c>
       <c r="P77" t="n">
-        <v>0.002817480592057109</v>
+        <v>0.0007225964218378067</v>
       </c>
       <c r="Q77" t="n">
-        <v>807.3892955176485</v>
+        <v>932.8523372106046</v>
       </c>
       <c r="R77" t="n">
-        <v>158.5080442101335</v>
+        <v>202.9966871986997</v>
       </c>
       <c r="S77" t="n">
-        <v>9.129250964530206</v>
+        <v>9.000641779210863</v>
       </c>
       <c r="T77" t="n">
-        <v>148.4308970273004</v>
+        <v>81.27781023396449</v>
       </c>
       <c r="U77" t="n">
-        <v>10.80187264687649</v>
+        <v>0.370250844576816</v>
       </c>
       <c r="V77" t="n">
-        <v>0.2649026812660757</v>
+        <v>1.551018715804796</v>
       </c>
       <c r="W77" t="b">
         <v>1</v>
@@ -6087,68 +6087,68 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>951.2473896040931</v>
+        <v>983.9103163849971</v>
       </c>
       <c r="D78" t="n">
-        <v>4.084940245326943</v>
+        <v>10.80942127573965</v>
       </c>
       <c r="E78" t="n">
-        <v>197.0422059273024</v>
+        <v>157.6836892871747</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9024239182472229</v>
+        <v>0.7411229610443115</v>
       </c>
       <c r="G78" t="n">
-        <v>0.001009692437946796</v>
+        <v>0.001695083919912577</v>
       </c>
       <c r="H78" t="n">
-        <v>951.2473896040889</v>
+        <v>980.651521949164</v>
       </c>
       <c r="I78" t="n">
-        <v>197.0422059273024</v>
+        <v>173.9057564547762</v>
       </c>
       <c r="J78" t="n">
-        <v>9.000641779862162</v>
+        <v>10.90223005966835</v>
       </c>
       <c r="K78" t="n">
-        <v>4.206412995699793e-12</v>
+        <v>3.258794435833124</v>
       </c>
       <c r="L78" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>16.22206716760144</v>
       </c>
       <c r="M78" t="n">
-        <v>4.915701534535219</v>
+        <v>0.09280878392869596</v>
       </c>
       <c r="N78" t="b">
         <v>1</v>
       </c>
       <c r="O78" t="n">
-        <v>0.9975175857543945</v>
+        <v>0.8478268384933472</v>
       </c>
       <c r="P78" t="n">
-        <v>7.62157142162323e-05</v>
+        <v>0.001091392943635583</v>
       </c>
       <c r="Q78" t="n">
-        <v>950.1206732791601</v>
+        <v>838.1733811423935</v>
       </c>
       <c r="R78" t="n">
-        <v>197.1874498366921</v>
+        <v>166.8817318252682</v>
       </c>
       <c r="S78" t="n">
-        <v>9.000641779862162</v>
+        <v>10.70126787999254</v>
       </c>
       <c r="T78" t="n">
-        <v>1.126716324933</v>
+        <v>145.7369352426036</v>
       </c>
       <c r="U78" t="n">
-        <v>0.1452439093896203</v>
+        <v>9.198042538093432</v>
       </c>
       <c r="V78" t="n">
-        <v>4.915701534535219</v>
+        <v>0.1081533957471077</v>
       </c>
       <c r="W78" t="b">
         <v>1</v>
@@ -6160,68 +6160,68 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>925.1740145451809</v>
+        <v>993.8091125161995</v>
       </c>
       <c r="D79" t="n">
-        <v>16.94827947591534</v>
+        <v>10.42881588760178</v>
       </c>
       <c r="E79" t="n">
-        <v>201.3815745203189</v>
+        <v>126.4222581227791</v>
       </c>
       <c r="F79" t="n">
-        <v>0.8084505796432495</v>
+        <v>0.9748581051826477</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0006022927118465304</v>
+        <v>0.6460902690887451</v>
       </c>
       <c r="H79" t="n">
-        <v>925.174014693928</v>
+        <v>945.6722747289361</v>
       </c>
       <c r="I79" t="n">
-        <v>201.381697026613</v>
+        <v>158.2367514784902</v>
       </c>
       <c r="J79" t="n">
-        <v>11.821818590448</v>
+        <v>10.22185835107431</v>
       </c>
       <c r="K79" t="n">
-        <v>1.487471763539361e-07</v>
+        <v>48.1368377872634</v>
       </c>
       <c r="L79" t="n">
-        <v>0.0001225062940193311</v>
+        <v>31.81449335571106</v>
       </c>
       <c r="M79" t="n">
-        <v>5.126460885467337</v>
+        <v>0.2069575365274687</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>0.9994738698005676</v>
+        <v>0.9999992847442627</v>
       </c>
       <c r="P79" t="n">
-        <v>0.006471996195614338</v>
+        <v>0.001430986099876463</v>
       </c>
       <c r="Q79" t="n">
-        <v>800.0000156062938</v>
+        <v>802.3016053467004</v>
       </c>
       <c r="R79" t="n">
-        <v>206.3163229298266</v>
+        <v>150.000552308477</v>
       </c>
       <c r="S79" t="n">
-        <v>14.15924514663618</v>
+        <v>10.28149806424723</v>
       </c>
       <c r="T79" t="n">
-        <v>125.1739989388871</v>
+        <v>191.5075071694991</v>
       </c>
       <c r="U79" t="n">
-        <v>4.934748409507648</v>
+        <v>23.57829418569789</v>
       </c>
       <c r="V79" t="n">
-        <v>2.789034329279161</v>
+        <v>0.1473178233545536</v>
       </c>
       <c r="W79" t="b">
         <v>1</v>
@@ -6237,64 +6237,64 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>922.0588995370605</v>
+        <v>957.0963623635679</v>
       </c>
       <c r="D80" t="n">
-        <v>10.47891849893005</v>
+        <v>9.945535047873713</v>
       </c>
       <c r="E80" t="n">
-        <v>125.7251267695712</v>
+        <v>146.1438499325558</v>
       </c>
       <c r="F80" t="n">
-        <v>0.9052466154098511</v>
+        <v>0.8736257553100586</v>
       </c>
       <c r="G80" t="n">
-        <v>0.005423423834145069</v>
+        <v>0.0001908630947582424</v>
       </c>
       <c r="H80" t="n">
-        <v>949.4788151061367</v>
+        <v>957.0934828425404</v>
       </c>
       <c r="I80" t="n">
-        <v>173.6136600186001</v>
+        <v>176.173305591252</v>
       </c>
       <c r="J80" t="n">
-        <v>10.47887078902613</v>
+        <v>10.45735275974209</v>
       </c>
       <c r="K80" t="n">
-        <v>27.41991556907624</v>
+        <v>0.002879521027466581</v>
       </c>
       <c r="L80" t="n">
-        <v>47.8885332490289</v>
+        <v>30.02945565869624</v>
       </c>
       <c r="M80" t="n">
-        <v>4.770990392088947e-05</v>
+        <v>0.5118177118683747</v>
       </c>
       <c r="N80" t="b">
         <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>0.9999251365661621</v>
+        <v>0.9993975162506104</v>
       </c>
       <c r="P80" t="n">
-        <v>0.009678383357822895</v>
+        <v>0.001149837160483003</v>
       </c>
       <c r="Q80" t="n">
-        <v>800.0000456797455</v>
+        <v>813.6166645695683</v>
       </c>
       <c r="R80" t="n">
-        <v>150.3752637279571</v>
+        <v>154.0988370143027</v>
       </c>
       <c r="S80" t="n">
-        <v>9.397611148181095</v>
+        <v>9.835380076011546</v>
       </c>
       <c r="T80" t="n">
-        <v>122.0588538573149</v>
+        <v>143.4796977939995</v>
       </c>
       <c r="U80" t="n">
-        <v>24.65013695838583</v>
+        <v>7.954987081746964</v>
       </c>
       <c r="V80" t="n">
-        <v>1.081307350748959</v>
+        <v>0.1101549718621673</v>
       </c>
       <c r="W80" t="b">
         <v>1</v>
@@ -6306,68 +6306,68 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>973.9269377632744</v>
+        <v>960.9051696605223</v>
       </c>
       <c r="D81" t="n">
-        <v>4.218786795303473</v>
+        <v>8.837957497580597</v>
       </c>
       <c r="E81" t="n">
-        <v>199.6085588066183</v>
+        <v>130.4948925638571</v>
       </c>
       <c r="F81" t="n">
-        <v>0.9021573066711426</v>
+        <v>0.9823979735374451</v>
       </c>
       <c r="G81" t="n">
-        <v>0.001009549014270306</v>
+        <v>0.0006277773063629866</v>
       </c>
       <c r="H81" t="n">
-        <v>973.9269377634739</v>
+        <v>857.2856615298629</v>
       </c>
       <c r="I81" t="n">
-        <v>199.6085588066182</v>
+        <v>176.1732577477451</v>
       </c>
       <c r="J81" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000001253609373</v>
       </c>
       <c r="K81" t="n">
-        <v>1.995204002014361e-10</v>
+        <v>103.6195081306595</v>
       </c>
       <c r="L81" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>45.67836518388796</v>
       </c>
       <c r="M81" t="n">
-        <v>4.78185498455869</v>
+        <v>0.1620437560287762</v>
       </c>
       <c r="N81" t="b">
         <v>1</v>
       </c>
       <c r="O81" t="n">
-        <v>0.998477041721344</v>
+        <v>0.9999986886978149</v>
       </c>
       <c r="P81" t="n">
-        <v>0.0001305704936385155</v>
+        <v>0.001082598813809454</v>
       </c>
       <c r="Q81" t="n">
-        <v>967.0214510986905</v>
+        <v>809.8632596390128</v>
       </c>
       <c r="R81" t="n">
-        <v>199.7114103307554</v>
+        <v>150.0005525771487</v>
       </c>
       <c r="S81" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641750763702</v>
       </c>
       <c r="T81" t="n">
-        <v>6.905486664583918</v>
+        <v>151.0419100215096</v>
       </c>
       <c r="U81" t="n">
-        <v>0.102851524137094</v>
+        <v>19.50566001329153</v>
       </c>
       <c r="V81" t="n">
-        <v>4.78185498455869</v>
+        <v>0.1626842531831052</v>
       </c>
       <c r="W81" t="b">
         <v>1</v>
@@ -6379,68 +6379,68 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>941.0057360916854</v>
+        <v>955.4016882269552</v>
       </c>
       <c r="D82" t="n">
-        <v>16.20970598452344</v>
+        <v>9.689352730554308</v>
       </c>
       <c r="E82" t="n">
-        <v>200.3765036916771</v>
+        <v>123.1606314457139</v>
       </c>
       <c r="F82" t="n">
-        <v>0.8086944818496704</v>
+        <v>0.9816255569458008</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0006026012706570327</v>
+        <v>0.002671804977580905</v>
       </c>
       <c r="H82" t="n">
-        <v>941.0057360331089</v>
+        <v>963.2195815735341</v>
       </c>
       <c r="I82" t="n">
-        <v>200.376503691677</v>
+        <v>173.947135934415</v>
       </c>
       <c r="J82" t="n">
-        <v>11.82181869152873</v>
+        <v>10.51127185358748</v>
       </c>
       <c r="K82" t="n">
-        <v>5.857657470187405e-08</v>
+        <v>7.817893346578899</v>
       </c>
       <c r="L82" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>50.78650448870104</v>
       </c>
       <c r="M82" t="n">
-        <v>4.387887292994707</v>
+        <v>0.8219191230331671</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
       </c>
       <c r="O82" t="n">
-        <v>0.9989344477653503</v>
+        <v>0.9999998807907104</v>
       </c>
       <c r="P82" t="n">
-        <v>0.00557564664632082</v>
+        <v>0.001205563778057694</v>
       </c>
       <c r="Q82" t="n">
-        <v>800.000002604693</v>
+        <v>806.1187487135985</v>
       </c>
       <c r="R82" t="n">
-        <v>205.0365738482125</v>
+        <v>150.0005523809073</v>
       </c>
       <c r="S82" t="n">
-        <v>14.04212724502304</v>
+        <v>9.577554091634845</v>
       </c>
       <c r="T82" t="n">
-        <v>141.0057334869924</v>
+        <v>149.2829395133567</v>
       </c>
       <c r="U82" t="n">
-        <v>4.660070156535426</v>
+        <v>26.83992093519339</v>
       </c>
       <c r="V82" t="n">
-        <v>2.167578739500398</v>
+        <v>0.1117986389194634</v>
       </c>
       <c r="W82" t="b">
         <v>1</v>
@@ -6452,68 +6452,68 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>952.4875224460186</v>
+        <v>959.2619273148472</v>
       </c>
       <c r="D83" t="n">
-        <v>15.55473009125146</v>
+        <v>10.64543182167768</v>
       </c>
       <c r="E83" t="n">
-        <v>224.1490198147962</v>
+        <v>147.3925039561177</v>
       </c>
       <c r="F83" t="n">
-        <v>0.8086159825325012</v>
+        <v>0.8763126730918884</v>
       </c>
       <c r="G83" t="n">
-        <v>0.003117481712251902</v>
+        <v>0.0001908630947582424</v>
       </c>
       <c r="H83" t="n">
-        <v>952.487523118034</v>
+        <v>957.595351926822</v>
       </c>
       <c r="I83" t="n">
-        <v>224.1490198147981</v>
+        <v>176.1732562427629</v>
       </c>
       <c r="J83" t="n">
-        <v>12.18382108846124</v>
+        <v>10.6453756697237</v>
       </c>
       <c r="K83" t="n">
-        <v>6.720154033246217e-07</v>
+        <v>1.666575388025194</v>
       </c>
       <c r="L83" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>28.7807522866452</v>
       </c>
       <c r="M83" t="n">
-        <v>3.370909002790219</v>
+        <v>5.61519539825639e-05</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
       </c>
       <c r="O83" t="n">
-        <v>0.9905823469161987</v>
+        <v>0.9990686774253845</v>
       </c>
       <c r="P83" t="n">
-        <v>0.004256206564605236</v>
+        <v>0.00116412085480988</v>
       </c>
       <c r="Q83" t="n">
-        <v>800.0000516999291</v>
+        <v>812.8254762022008</v>
       </c>
       <c r="R83" t="n">
-        <v>222.7823365021821</v>
+        <v>155.7319196026767</v>
       </c>
       <c r="S83" t="n">
-        <v>13.95969768168954</v>
+        <v>10.52625283050107</v>
       </c>
       <c r="T83" t="n">
-        <v>152.4874707460895</v>
+        <v>146.4364511126464</v>
       </c>
       <c r="U83" t="n">
-        <v>1.366683312614157</v>
+        <v>8.339415646559019</v>
       </c>
       <c r="V83" t="n">
-        <v>1.59503240956192</v>
+        <v>0.1191789911766161</v>
       </c>
       <c r="W83" t="b">
         <v>1</v>
@@ -6529,64 +6529,64 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>871.9166034954022</v>
+        <v>844.1387241107644</v>
       </c>
       <c r="D84" t="n">
-        <v>5.719503605443095</v>
+        <v>8.359806894064747</v>
       </c>
       <c r="E84" t="n">
-        <v>200.6776147264315</v>
+        <v>202.8412666888779</v>
       </c>
       <c r="F84" t="n">
-        <v>0.922005295753479</v>
+        <v>0.9779818654060364</v>
       </c>
       <c r="G84" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.00139266811311245</v>
       </c>
       <c r="H84" t="n">
-        <v>933.0453206329204</v>
+        <v>925.9037221576409</v>
       </c>
       <c r="I84" t="n">
-        <v>200.6776147264315</v>
+        <v>191.0020853883559</v>
       </c>
       <c r="J84" t="n">
-        <v>9.000641565762713</v>
+        <v>9.000723577019036</v>
       </c>
       <c r="K84" t="n">
-        <v>61.12871713751815</v>
+        <v>81.76499804687649</v>
       </c>
       <c r="L84" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>11.83918130052203</v>
       </c>
       <c r="M84" t="n">
-        <v>3.281137960319618</v>
+        <v>0.6409166829542894</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>0.9836069345474243</v>
+        <v>0.9751982092857361</v>
       </c>
       <c r="P84" t="n">
-        <v>0.0004600539396051317</v>
+        <v>0.000778059649746865</v>
       </c>
       <c r="Q84" t="n">
-        <v>931.4172888466742</v>
+        <v>932.3881242143485</v>
       </c>
       <c r="R84" t="n">
-        <v>201.0166361276813</v>
+        <v>202.852877928763</v>
       </c>
       <c r="S84" t="n">
-        <v>9.000641823443345</v>
+        <v>9.000641815761385</v>
       </c>
       <c r="T84" t="n">
-        <v>59.50068535127195</v>
+        <v>88.24940010358409</v>
       </c>
       <c r="U84" t="n">
-        <v>0.339021401249795</v>
+        <v>0.01161123988509871</v>
       </c>
       <c r="V84" t="n">
-        <v>3.28113821800025</v>
+        <v>0.6408349216966389</v>
       </c>
       <c r="W84" t="b">
         <v>1</v>
@@ -6598,68 +6598,68 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>954.3289701898689</v>
+        <v>870.4646279587909</v>
       </c>
       <c r="D85" t="n">
-        <v>15.88412626296671</v>
+        <v>7.267081257983708</v>
       </c>
       <c r="E85" t="n">
-        <v>194.513701431672</v>
+        <v>183.9231629870082</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8066105842590332</v>
+        <v>0.9806914329528809</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0006026012706570327</v>
+        <v>0.0009205389069393277</v>
       </c>
       <c r="H85" t="n">
-        <v>954.3289701894272</v>
+        <v>933.5316326486537</v>
       </c>
       <c r="I85" t="n">
-        <v>194.513701431672</v>
+        <v>185.8717530899106</v>
       </c>
       <c r="J85" t="n">
-        <v>11.82181868708977</v>
+        <v>9.000778900824686</v>
       </c>
       <c r="K85" t="n">
-        <v>4.416733645484783e-10</v>
+        <v>63.06700468986287</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.948590102902415</v>
       </c>
       <c r="M85" t="n">
-        <v>4.062307575876947</v>
+        <v>1.733697642840978</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>0.9978845715522766</v>
+        <v>0.9893494844436646</v>
       </c>
       <c r="P85" t="n">
-        <v>0.005341557785868645</v>
+        <v>0.0007114786421880126</v>
       </c>
       <c r="Q85" t="n">
-        <v>800.0000163811827</v>
+        <v>936.9937504318341</v>
       </c>
       <c r="R85" t="n">
-        <v>199.953679766063</v>
+        <v>185.3831038268206</v>
       </c>
       <c r="S85" t="n">
-        <v>13.92933069491104</v>
+        <v>9.000641188679623</v>
       </c>
       <c r="T85" t="n">
-        <v>154.3289538086862</v>
+        <v>66.52912247304323</v>
       </c>
       <c r="U85" t="n">
-        <v>5.439978334390929</v>
+        <v>1.45994083981239</v>
       </c>
       <c r="V85" t="n">
-        <v>1.954795568055673</v>
+        <v>1.733559930695915</v>
       </c>
       <c r="W85" t="b">
         <v>1</v>
@@ -6675,64 +6675,64 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>874.0821187064782</v>
+        <v>851.3108041478846</v>
       </c>
       <c r="D86" t="n">
-        <v>7.767320450652663</v>
+        <v>9.465494845876609</v>
       </c>
       <c r="E86" t="n">
-        <v>206.1137005176345</v>
+        <v>192.9091882371535</v>
       </c>
       <c r="F86" t="n">
-        <v>0.9223952293395996</v>
+        <v>0.9742845892906189</v>
       </c>
       <c r="G86" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.0009308591834269464</v>
       </c>
       <c r="H86" t="n">
-        <v>933.045323442969</v>
+        <v>920.0548465954727</v>
       </c>
       <c r="I86" t="n">
-        <v>206.1137005176346</v>
+        <v>192.9091882371536</v>
       </c>
       <c r="J86" t="n">
-        <v>9.000641603026418</v>
+        <v>9.710948091122503</v>
       </c>
       <c r="K86" t="n">
-        <v>58.96320473649075</v>
+        <v>68.74404244758807</v>
       </c>
       <c r="L86" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="M86" t="n">
-        <v>1.233321152373755</v>
+        <v>0.2454532452458942</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>0.9544556736946106</v>
+        <v>0.8256574869155884</v>
       </c>
       <c r="P86" t="n">
-        <v>0.0004442452045623213</v>
+        <v>0.000521176727488637</v>
       </c>
       <c r="Q86" t="n">
-        <v>931.4965765509721</v>
+        <v>925.9549669497503</v>
       </c>
       <c r="R86" t="n">
-        <v>205.9378992788192</v>
+        <v>193.2005295497968</v>
       </c>
       <c r="S86" t="n">
-        <v>9.000641769660129</v>
+        <v>9.576079516169717</v>
       </c>
       <c r="T86" t="n">
-        <v>57.41445784449388</v>
+        <v>74.64416280186572</v>
       </c>
       <c r="U86" t="n">
-        <v>0.1758012388153247</v>
+        <v>0.2913413126433113</v>
       </c>
       <c r="V86" t="n">
-        <v>1.233321319007466</v>
+        <v>0.1105846702931075</v>
       </c>
       <c r="W86" t="b">
         <v>1</v>
@@ -6744,68 +6744,68 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>876.1126159340909</v>
+        <v>935.6117250099762</v>
       </c>
       <c r="D87" t="n">
-        <v>8.053275722005807</v>
+        <v>8.096975787254928</v>
       </c>
       <c r="E87" t="n">
-        <v>205.0024370668732</v>
+        <v>120.4668218901487</v>
       </c>
       <c r="F87" t="n">
-        <v>0.873828649520874</v>
+        <v>0.9742164015769958</v>
       </c>
       <c r="G87" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.002779936417937279</v>
       </c>
       <c r="H87" t="n">
-        <v>933.0453309638863</v>
+        <v>828.025278046671</v>
       </c>
       <c r="I87" t="n">
-        <v>205.0024370668731</v>
+        <v>176.1732562382385</v>
       </c>
       <c r="J87" t="n">
-        <v>9.000641473388258</v>
+        <v>10.52896040961697</v>
       </c>
       <c r="K87" t="n">
-        <v>56.93271502979542</v>
+        <v>107.5864469633052</v>
       </c>
       <c r="L87" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>55.70643434808989</v>
       </c>
       <c r="M87" t="n">
-        <v>0.9473657513824509</v>
+        <v>2.431984622362041</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
       </c>
       <c r="O87" t="n">
-        <v>0.929789662361145</v>
+        <v>1</v>
       </c>
       <c r="P87" t="n">
-        <v>0.0004262854345142841</v>
+        <v>0.0009585798834450543</v>
       </c>
       <c r="Q87" t="n">
-        <v>931.699289828486</v>
+        <v>809.0576498480506</v>
       </c>
       <c r="R87" t="n">
-        <v>204.9316780319158</v>
+        <v>150.0005526172212</v>
       </c>
       <c r="S87" t="n">
-        <v>9.000641724417703</v>
+        <v>9.000641797303111</v>
       </c>
       <c r="T87" t="n">
-        <v>55.58667389439518</v>
+        <v>126.5540751619257</v>
       </c>
       <c r="U87" t="n">
-        <v>0.07075903495740477</v>
+        <v>29.53373072707259</v>
       </c>
       <c r="V87" t="n">
-        <v>0.9473660024118953</v>
+        <v>0.9036660100481821</v>
       </c>
       <c r="W87" t="b">
         <v>1</v>
@@ -6817,68 +6817,68 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>855.6371246689862</v>
+        <v>941.4647434232286</v>
       </c>
       <c r="D88" t="n">
-        <v>8.571125134918899</v>
+        <v>5.690848243636317</v>
       </c>
       <c r="E88" t="n">
-        <v>217.555696678885</v>
+        <v>197.0383130866155</v>
       </c>
       <c r="F88" t="n">
-        <v>0.7911791801452637</v>
+        <v>0.966529905796051</v>
       </c>
       <c r="G88" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.0002481373958289623</v>
       </c>
       <c r="H88" t="n">
-        <v>933.0453163395235</v>
+        <v>941.4647434232262</v>
       </c>
       <c r="I88" t="n">
-        <v>217.555696678885</v>
+        <v>197.0383130866234</v>
       </c>
       <c r="J88" t="n">
-        <v>9.000641740363921</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K88" t="n">
-        <v>77.40819167053735</v>
+        <v>2.387423592153937e-12</v>
       </c>
       <c r="L88" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>7.986500349943526e-12</v>
       </c>
       <c r="M88" t="n">
-        <v>0.4295166054450217</v>
+        <v>3.309793536225845</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
       </c>
       <c r="O88" t="n">
-        <v>0.9194717407226562</v>
+        <v>0.9168035984039307</v>
       </c>
       <c r="P88" t="n">
-        <v>0.000676877039950341</v>
+        <v>7.379243470495567e-05</v>
       </c>
       <c r="Q88" t="n">
-        <v>930.9534650858936</v>
+        <v>944.1741116076072</v>
       </c>
       <c r="R88" t="n">
-        <v>215.7931514023659</v>
+        <v>197.2879143069717</v>
       </c>
       <c r="S88" t="n">
-        <v>9.000641666766001</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T88" t="n">
-        <v>75.31634041690745</v>
+        <v>2.709368184378604</v>
       </c>
       <c r="U88" t="n">
-        <v>1.762545276519063</v>
+        <v>0.2496012203562259</v>
       </c>
       <c r="V88" t="n">
-        <v>0.429516531847101</v>
+        <v>3.309793536225845</v>
       </c>
       <c r="W88" t="b">
         <v>1</v>
@@ -6890,68 +6890,68 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>835.123914281303</v>
+        <v>970.7952457920957</v>
       </c>
       <c r="D89" t="n">
-        <v>6.824300738939943</v>
+        <v>6.023239565209312</v>
       </c>
       <c r="E89" t="n">
-        <v>192.4932415837991</v>
+        <v>209.455973623258</v>
       </c>
       <c r="F89" t="n">
-        <v>0.9318311810493469</v>
+        <v>0.9555602073669434</v>
       </c>
       <c r="G89" t="n">
-        <v>0.00342625891789794</v>
+        <v>0.000253947131568566</v>
       </c>
       <c r="H89" t="n">
-        <v>919.4285358038763</v>
+        <v>970.7952457920951</v>
       </c>
       <c r="I89" t="n">
-        <v>192.4932371931276</v>
+        <v>209.4559736232624</v>
       </c>
       <c r="J89" t="n">
-        <v>9.000641776727523</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K89" t="n">
-        <v>84.30462152257337</v>
+        <v>5.684341886080801e-13</v>
       </c>
       <c r="L89" t="n">
-        <v>4.390671506371291e-06</v>
+        <v>4.405364961712621e-12</v>
       </c>
       <c r="M89" t="n">
-        <v>2.17634103778758</v>
+        <v>2.97740221465285</v>
       </c>
       <c r="N89" t="b">
         <v>1</v>
       </c>
       <c r="O89" t="n">
-        <v>0.993739128112793</v>
+        <v>0.6877107620239258</v>
       </c>
       <c r="P89" t="n">
-        <v>0.0008020448731258512</v>
+        <v>0.0002129104541381821</v>
       </c>
       <c r="Q89" t="n">
-        <v>929.6720784369048</v>
+        <v>958.1342269951343</v>
       </c>
       <c r="R89" t="n">
-        <v>194.1052503352452</v>
+        <v>208.7891453574638</v>
       </c>
       <c r="S89" t="n">
-        <v>9.000641701703499</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T89" t="n">
-        <v>94.54816415560185</v>
+        <v>12.66101879696134</v>
       </c>
       <c r="U89" t="n">
-        <v>1.612008751446098</v>
+        <v>0.6668282657941518</v>
       </c>
       <c r="V89" t="n">
-        <v>2.176340962763556</v>
+        <v>2.97740221465285</v>
       </c>
       <c r="W89" t="b">
         <v>1</v>
@@ -6963,68 +6963,68 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>946.5757757630857</v>
+        <v>893.2184268102915</v>
       </c>
       <c r="D90" t="n">
-        <v>5.498200963589312</v>
+        <v>9.616785371297654</v>
       </c>
       <c r="E90" t="n">
-        <v>203.0338594278622</v>
+        <v>209.1237870441858</v>
       </c>
       <c r="F90" t="n">
-        <v>0.8901962041854858</v>
+        <v>0.573319137096405</v>
       </c>
       <c r="G90" t="n">
-        <v>0.001009692437946796</v>
+        <v>0.0009827348403632641</v>
       </c>
       <c r="H90" t="n">
-        <v>946.5757757630849</v>
+        <v>920.0581520444725</v>
       </c>
       <c r="I90" t="n">
-        <v>203.0338594278622</v>
+        <v>209.1236725574585</v>
       </c>
       <c r="J90" t="n">
-        <v>9.000641779862162</v>
+        <v>9.697405842036328</v>
       </c>
       <c r="K90" t="n">
-        <v>7.958078640513122e-13</v>
+        <v>26.83972523418106</v>
       </c>
       <c r="L90" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0.0001144867273126238</v>
       </c>
       <c r="M90" t="n">
-        <v>3.50244081627285</v>
+        <v>0.0806204707386744</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
       </c>
       <c r="O90" t="n">
-        <v>0.9716449379920959</v>
+        <v>0.1592088490724564</v>
       </c>
       <c r="P90" t="n">
-        <v>6.211008440004662e-05</v>
+        <v>0.0003098166198469698</v>
       </c>
       <c r="Q90" t="n">
-        <v>946.1353768581462</v>
+        <v>930.5117822941343</v>
       </c>
       <c r="R90" t="n">
-        <v>203.0442228055896</v>
+        <v>208.030578759704</v>
       </c>
       <c r="S90" t="n">
-        <v>9.000641779862162</v>
+        <v>9.682177542113363</v>
       </c>
       <c r="T90" t="n">
-        <v>0.4403989049395705</v>
+        <v>37.29335548384279</v>
       </c>
       <c r="U90" t="n">
-        <v>0.01036337772742968</v>
+        <v>1.09320828448179</v>
       </c>
       <c r="V90" t="n">
-        <v>3.50244081627285</v>
+        <v>0.06539217081570925</v>
       </c>
       <c r="W90" t="b">
         <v>1</v>
@@ -7036,68 +7036,68 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>887.5228913766166</v>
+        <v>946.6736588014063</v>
       </c>
       <c r="D91" t="n">
-        <v>7.649765801260644</v>
+        <v>10.82030558818615</v>
       </c>
       <c r="E91" t="n">
-        <v>209.333586015199</v>
+        <v>130.0842806140458</v>
       </c>
       <c r="F91" t="n">
-        <v>0.8506448864936829</v>
+        <v>0.9806832075119019</v>
       </c>
       <c r="G91" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.0001908630947582424</v>
       </c>
       <c r="H91" t="n">
-        <v>933.0453154075816</v>
+        <v>946.6770800594492</v>
       </c>
       <c r="I91" t="n">
-        <v>209.333586015199</v>
+        <v>176.1732562382421</v>
       </c>
       <c r="J91" t="n">
-        <v>9.000641608203027</v>
+        <v>10.82079502788056</v>
       </c>
       <c r="K91" t="n">
-        <v>45.522424030965</v>
+        <v>0.003421258042862974</v>
       </c>
       <c r="L91" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>46.08897562419628</v>
       </c>
       <c r="M91" t="n">
-        <v>1.350875806942383</v>
+        <v>0.0004894396944052914</v>
       </c>
       <c r="N91" t="b">
         <v>1</v>
       </c>
       <c r="O91" t="n">
-        <v>0.8476199507713318</v>
+        <v>0.9999995231628418</v>
       </c>
       <c r="P91" t="n">
-        <v>0.0003574339498300105</v>
+        <v>0.001492185285314918</v>
       </c>
       <c r="Q91" t="n">
-        <v>933.1325387041923</v>
+        <v>800.0000772633028</v>
       </c>
       <c r="R91" t="n">
-        <v>208.894945893669</v>
+        <v>150.0005529414757</v>
       </c>
       <c r="S91" t="n">
-        <v>9.000641775144661</v>
+        <v>10.65599292394612</v>
       </c>
       <c r="T91" t="n">
-        <v>45.60964732757566</v>
+        <v>146.6735815381035</v>
       </c>
       <c r="U91" t="n">
-        <v>0.4386401215299713</v>
+        <v>19.91627232742982</v>
       </c>
       <c r="V91" t="n">
-        <v>1.350875973884017</v>
+        <v>0.1643126642400361</v>
       </c>
       <c r="W91" t="b">
         <v>1</v>
@@ -7109,68 +7109,68 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>878.9000351868293</v>
+        <v>985.1016721152307</v>
       </c>
       <c r="D92" t="n">
-        <v>8.425764143923214</v>
+        <v>14.32305064805296</v>
       </c>
       <c r="E92" t="n">
-        <v>210.6415662798122</v>
+        <v>195.2429895351666</v>
       </c>
       <c r="F92" t="n">
-        <v>0.7311365604400635</v>
+        <v>0.961887001991272</v>
       </c>
       <c r="G92" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.01351658906787634</v>
       </c>
       <c r="H92" t="n">
-        <v>933.0453157089106</v>
+        <v>952.7864045000421</v>
       </c>
       <c r="I92" t="n">
-        <v>210.6415662798122</v>
+        <v>196.3535407277273</v>
       </c>
       <c r="J92" t="n">
-        <v>9.000641653985529</v>
+        <v>12.67378394915221</v>
       </c>
       <c r="K92" t="n">
-        <v>54.14528052208129</v>
+        <v>32.31526761518865</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.110551192560678</v>
       </c>
       <c r="M92" t="n">
-        <v>0.5748775100623149</v>
+        <v>1.64926669890075</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>0.8502494096755981</v>
+        <v>0.978660523891449</v>
       </c>
       <c r="P92" t="n">
-        <v>0.000425392878241837</v>
+        <v>0.003753010649234056</v>
       </c>
       <c r="Q92" t="n">
-        <v>932.2726888561129</v>
+        <v>993.074366447731</v>
       </c>
       <c r="R92" t="n">
-        <v>210.0301590263422</v>
+        <v>202.397504154491</v>
       </c>
       <c r="S92" t="n">
-        <v>9.000641895492265</v>
+        <v>12.22133803359736</v>
       </c>
       <c r="T92" t="n">
-        <v>53.37265366928364</v>
+        <v>7.972694332500282</v>
       </c>
       <c r="U92" t="n">
-        <v>0.6114072534700199</v>
+        <v>7.154514619324431</v>
       </c>
       <c r="V92" t="n">
-        <v>0.5748777515690513</v>
+        <v>2.101712614455593</v>
       </c>
       <c r="W92" t="b">
         <v>1</v>
@@ -7182,68 +7182,68 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>878.3564058967878</v>
+        <v>919.8886962981079</v>
       </c>
       <c r="D93" t="n">
-        <v>8.799881216785067</v>
+        <v>3.25331237475298</v>
       </c>
       <c r="E93" t="n">
-        <v>202.7497246495558</v>
+        <v>201.6262289488754</v>
       </c>
       <c r="F93" t="n">
-        <v>0.678946852684021</v>
+        <v>0.920503556728363</v>
       </c>
       <c r="G93" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.0002785818069241941</v>
       </c>
       <c r="H93" t="n">
-        <v>933.0453185661082</v>
+        <v>920.0551572371252</v>
       </c>
       <c r="I93" t="n">
-        <v>202.7497246495558</v>
+        <v>201.6262289489925</v>
       </c>
       <c r="J93" t="n">
-        <v>9.000641602739906</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="K93" t="n">
-        <v>54.68891266932042</v>
+        <v>0.16646093901727</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.171542862721253e-10</v>
       </c>
       <c r="M93" t="n">
-        <v>0.2007603859548386</v>
+        <v>5.747329405109182</v>
       </c>
       <c r="N93" t="b">
         <v>1</v>
       </c>
       <c r="O93" t="n">
-        <v>0.8087602257728577</v>
+        <v>0.9969003200531006</v>
       </c>
       <c r="P93" t="n">
-        <v>0.0004069936112500727</v>
+        <v>0.0001354460546281189</v>
       </c>
       <c r="Q93" t="n">
-        <v>931.9908767333558</v>
+        <v>925.8859438848896</v>
       </c>
       <c r="R93" t="n">
-        <v>202.8749338543323</v>
+        <v>202.1825667962769</v>
       </c>
       <c r="S93" t="n">
-        <v>9.000641826765426</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="T93" t="n">
-        <v>53.63447083656797</v>
+        <v>5.997247586781668</v>
       </c>
       <c r="U93" t="n">
-        <v>0.1252092047765814</v>
+        <v>0.5563378474015224</v>
       </c>
       <c r="V93" t="n">
-        <v>0.2007606099803585</v>
+        <v>5.747329405109182</v>
       </c>
       <c r="W93" t="b">
         <v>1</v>
@@ -7259,64 +7259,64 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>944.6598326992513</v>
+        <v>965.9262016570707</v>
       </c>
       <c r="D94" t="n">
-        <v>8.686377349508932</v>
+        <v>11.12397579585559</v>
       </c>
       <c r="E94" t="n">
-        <v>129.8690795151252</v>
+        <v>134.9569477941156</v>
       </c>
       <c r="F94" t="n">
-        <v>0.9054416418075562</v>
+        <v>0.9808417558670044</v>
       </c>
       <c r="G94" t="n">
-        <v>0.02525101602077484</v>
+        <v>0.01346223335713148</v>
       </c>
       <c r="H94" t="n">
-        <v>960.0063177017861</v>
+        <v>983.8469288560883</v>
       </c>
       <c r="I94" t="n">
-        <v>165.9408748827772</v>
+        <v>169.4477859692686</v>
       </c>
       <c r="J94" t="n">
-        <v>9.868906925182481</v>
+        <v>10.73647508767043</v>
       </c>
       <c r="K94" t="n">
-        <v>15.34648500253479</v>
+        <v>17.92072719901762</v>
       </c>
       <c r="L94" t="n">
-        <v>36.07179536765193</v>
+        <v>34.49083817515299</v>
       </c>
       <c r="M94" t="n">
-        <v>1.182529575673549</v>
+        <v>0.3875007081851596</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
       </c>
       <c r="O94" t="n">
-        <v>0.9999221563339233</v>
+        <v>0.9999947547912598</v>
       </c>
       <c r="P94" t="n">
-        <v>0.006814353633671999</v>
+        <v>0.001884272904135287</v>
       </c>
       <c r="Q94" t="n">
-        <v>800.0000297204384</v>
+        <v>800.0000381085832</v>
       </c>
       <c r="R94" t="n">
-        <v>150.0005528529397</v>
+        <v>150.0005529163256</v>
       </c>
       <c r="S94" t="n">
-        <v>9.000642071061314</v>
+        <v>10.91074169056781</v>
       </c>
       <c r="T94" t="n">
-        <v>144.6598029788129</v>
+        <v>165.9261635484875</v>
       </c>
       <c r="U94" t="n">
-        <v>20.1314733378145</v>
+        <v>15.04360512220995</v>
       </c>
       <c r="V94" t="n">
-        <v>0.3142647215523819</v>
+        <v>0.2132341052877766</v>
       </c>
       <c r="W94" t="b">
         <v>1</v>
@@ -7328,68 +7328,68 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>967.3991853873271</v>
+        <v>1012.808458202045</v>
       </c>
       <c r="D95" t="n">
-        <v>2.956282732464466</v>
+        <v>9.980022214052862</v>
       </c>
       <c r="E95" t="n">
-        <v>187.3077628180434</v>
+        <v>201.8109792519376</v>
       </c>
       <c r="F95" t="n">
-        <v>0.9024178981781006</v>
+        <v>0.5065088272094727</v>
       </c>
       <c r="G95" t="n">
-        <v>0.001009689178317785</v>
+        <v>9.540664177620783e-05</v>
       </c>
       <c r="H95" t="n">
-        <v>967.3991853906026</v>
+        <v>985.8937768399126</v>
       </c>
       <c r="I95" t="n">
-        <v>187.3077628180489</v>
+        <v>201.8109792519376</v>
       </c>
       <c r="J95" t="n">
-        <v>9.000641779862162</v>
+        <v>9.980027350415719</v>
       </c>
       <c r="K95" t="n">
-        <v>3.275545168435201e-09</v>
+        <v>26.91468136213223</v>
       </c>
       <c r="L95" t="n">
-        <v>5.542233338928781e-12</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>6.044359047397696</v>
+        <v>5.136362856816845e-06</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
       </c>
       <c r="O95" t="n">
-        <v>0.9993027448654175</v>
+        <v>0.3398919999599457</v>
       </c>
       <c r="P95" t="n">
-        <v>0.0002048588066827506</v>
+        <v>0.0001813282287912443</v>
       </c>
       <c r="Q95" t="n">
-        <v>961.1976297098331</v>
+        <v>971.9395462658636</v>
       </c>
       <c r="R95" t="n">
-        <v>188.0350796961787</v>
+        <v>201.2533652131466</v>
       </c>
       <c r="S95" t="n">
-        <v>9.000641779862162</v>
+        <v>9.984604753091288</v>
       </c>
       <c r="T95" t="n">
-        <v>6.201555677493957</v>
+        <v>40.86891193618123</v>
       </c>
       <c r="U95" t="n">
-        <v>0.7273168781353831</v>
+        <v>0.5576140387909732</v>
       </c>
       <c r="V95" t="n">
-        <v>6.044359047397696</v>
+        <v>0.004582539038425537</v>
       </c>
       <c r="W95" t="b">
         <v>1</v>
@@ -7401,68 +7401,68 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>890.5470318060303</v>
+        <v>1008.578650305117</v>
       </c>
       <c r="D96" t="n">
-        <v>7.512650723820679</v>
+        <v>11.87591072259123</v>
       </c>
       <c r="E96" t="n">
-        <v>215.574397047935</v>
+        <v>213.22179032479</v>
       </c>
       <c r="F96" t="n">
-        <v>0.8500855565071106</v>
+        <v>0.7313722372055054</v>
       </c>
       <c r="G96" t="n">
-        <v>0.001727184862829745</v>
+        <v>9.798719838727266e-05</v>
       </c>
       <c r="H96" t="n">
-        <v>933.0453168076448</v>
+        <v>985.8937777479543</v>
       </c>
       <c r="I96" t="n">
-        <v>215.5743970479351</v>
+        <v>213.22179032479</v>
       </c>
       <c r="J96" t="n">
-        <v>9.000641605434167</v>
+        <v>11.87590853111443</v>
       </c>
       <c r="K96" t="n">
-        <v>42.49828500161448</v>
+        <v>22.68487255716286</v>
       </c>
       <c r="L96" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>1.487990881613488</v>
+        <v>2.191476799140446e-06</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
       </c>
       <c r="O96" t="n">
-        <v>0.7874205112457275</v>
+        <v>0.3155722618103027</v>
       </c>
       <c r="P96" t="n">
-        <v>0.0003726465802174062</v>
+        <v>0.0001751119416439906</v>
       </c>
       <c r="Q96" t="n">
-        <v>934.4434799154654</v>
+        <v>968.8324358270991</v>
       </c>
       <c r="R96" t="n">
-        <v>214.56302936227</v>
+        <v>212.8675182768862</v>
       </c>
       <c r="S96" t="n">
-        <v>9.000641644686672</v>
+        <v>11.88075236671716</v>
       </c>
       <c r="T96" t="n">
-        <v>43.89644810943514</v>
+        <v>39.74621447801815</v>
       </c>
       <c r="U96" t="n">
-        <v>1.011367685665022</v>
+        <v>0.3542720479038053</v>
       </c>
       <c r="V96" t="n">
-        <v>1.487990920865993</v>
+        <v>0.004841644125933797</v>
       </c>
       <c r="W96" t="b">
         <v>1</v>
@@ -7478,64 +7478,64 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>833.7210060081408</v>
+        <v>897.4090095422152</v>
       </c>
       <c r="D97" t="n">
-        <v>5.895170445327111</v>
+        <v>6.06450522840354</v>
       </c>
       <c r="E97" t="n">
-        <v>194.1856708830898</v>
+        <v>203.6379405791601</v>
       </c>
       <c r="F97" t="n">
-        <v>0.9218559265136719</v>
+        <v>0.8587307333946228</v>
       </c>
       <c r="G97" t="n">
-        <v>0.00342625891789794</v>
+        <v>0.000411912944400683</v>
       </c>
       <c r="H97" t="n">
-        <v>919.4290659766887</v>
+        <v>940.8700876040477</v>
       </c>
       <c r="I97" t="n">
-        <v>194.1856691650754</v>
+        <v>203.6379405791603</v>
       </c>
       <c r="J97" t="n">
-        <v>9.000641690081178</v>
+        <v>9.000641764910846</v>
       </c>
       <c r="K97" t="n">
-        <v>85.7080599685479</v>
+        <v>43.4610780618325</v>
       </c>
       <c r="L97" t="n">
-        <v>1.718014431162374e-06</v>
+        <v>1.989519660128281e-13</v>
       </c>
       <c r="M97" t="n">
-        <v>3.105471244754067</v>
+        <v>2.936136536507306</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
       </c>
       <c r="O97" t="n">
-        <v>0.9966822266578674</v>
+        <v>0.9261912107467651</v>
       </c>
       <c r="P97" t="n">
-        <v>0.0008018033113330603</v>
+        <v>0.0003565092920325696</v>
       </c>
       <c r="Q97" t="n">
-        <v>929.2366177875384</v>
+        <v>937.6236143402366</v>
       </c>
       <c r="R97" t="n">
-        <v>195.5874239900444</v>
+        <v>203.0320182731289</v>
       </c>
       <c r="S97" t="n">
-        <v>9.000641751428157</v>
+        <v>9.000635566424766</v>
       </c>
       <c r="T97" t="n">
-        <v>95.51561177939766</v>
+        <v>40.21460479802136</v>
       </c>
       <c r="U97" t="n">
-        <v>1.401753106954601</v>
+        <v>0.6059223060311751</v>
       </c>
       <c r="V97" t="n">
-        <v>3.105471306101046</v>
+        <v>2.936130338021226</v>
       </c>
       <c r="W97" t="b">
         <v>1</v>
@@ -7547,68 +7547,68 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>853.6665716226203</v>
+        <v>946.0759667984183</v>
       </c>
       <c r="D98" t="n">
-        <v>8.011088900073144</v>
+        <v>9.580764759021758</v>
       </c>
       <c r="E98" t="n">
-        <v>197.7691512671515</v>
+        <v>154.1075734706715</v>
       </c>
       <c r="F98" t="n">
-        <v>0.9254602789878845</v>
+        <v>0.8382338285446167</v>
       </c>
       <c r="G98" t="n">
-        <v>0.001727184862829745</v>
+        <v>0.0002063950814772397</v>
       </c>
       <c r="H98" t="n">
-        <v>933.0453153860811</v>
+        <v>946.0783613191138</v>
       </c>
       <c r="I98" t="n">
-        <v>197.7691512671515</v>
+        <v>176.1732562473737</v>
       </c>
       <c r="J98" t="n">
-        <v>9.000641633837835</v>
+        <v>9.580762290217397</v>
       </c>
       <c r="K98" t="n">
-        <v>79.37874376346088</v>
+        <v>0.002394520695474966</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>22.06568277670215</v>
       </c>
       <c r="M98" t="n">
-        <v>0.9895527337646914</v>
+        <v>2.468804360944432e-06</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>0.9749099612236023</v>
+        <v>0.9869179129600525</v>
       </c>
       <c r="P98" t="n">
-        <v>0.000605639535933733</v>
+        <v>0.0008679009624756873</v>
       </c>
       <c r="Q98" t="n">
-        <v>930.1923421324998</v>
+        <v>832.0222165005507</v>
       </c>
       <c r="R98" t="n">
-        <v>198.5222939748784</v>
+        <v>161.5672315109592</v>
       </c>
       <c r="S98" t="n">
-        <v>9.000641677059376</v>
+        <v>9.468221611477116</v>
       </c>
       <c r="T98" t="n">
-        <v>76.52577050987952</v>
+        <v>114.0537502978676</v>
       </c>
       <c r="U98" t="n">
-        <v>0.753142707726937</v>
+        <v>7.459658040287707</v>
       </c>
       <c r="V98" t="n">
-        <v>0.9895527769862316</v>
+        <v>0.1125431475446419</v>
       </c>
       <c r="W98" t="b">
         <v>1</v>
@@ -7624,64 +7624,64 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>807.6692789674012</v>
+        <v>886.7320035318303</v>
       </c>
       <c r="D99" t="n">
-        <v>8.29204520892505</v>
+        <v>7.067811158178888</v>
       </c>
       <c r="E99" t="n">
-        <v>207.8843195352499</v>
+        <v>201.0474114737337</v>
       </c>
       <c r="F99" t="n">
-        <v>0.8163442015647888</v>
+        <v>0.8871044516563416</v>
       </c>
       <c r="G99" t="n">
-        <v>0.004001171793788671</v>
+        <v>0.0004035303718410432</v>
       </c>
       <c r="H99" t="n">
-        <v>916.4024450851115</v>
+        <v>940.8700912480335</v>
       </c>
       <c r="I99" t="n">
-        <v>207.8843195352526</v>
+        <v>201.0474114737297</v>
       </c>
       <c r="J99" t="n">
-        <v>9.000623852342402</v>
+        <v>9.000641570597013</v>
       </c>
       <c r="K99" t="n">
-        <v>108.7331661177103</v>
+        <v>54.13808771620324</v>
       </c>
       <c r="L99" t="n">
-        <v>2.756905814749189e-12</v>
+        <v>3.950617610826157e-12</v>
       </c>
       <c r="M99" t="n">
-        <v>0.7085786434173524</v>
+        <v>1.932830412418125</v>
       </c>
       <c r="N99" t="b">
         <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>0.9572621583938599</v>
+        <v>0.9502797722816467</v>
       </c>
       <c r="P99" t="n">
-        <v>0.001039233291521668</v>
+        <v>0.0004196920490358025</v>
       </c>
       <c r="Q99" t="n">
-        <v>926.6671077541839</v>
+        <v>936.602498644831</v>
       </c>
       <c r="R99" t="n">
-        <v>207.3958812301202</v>
+        <v>201.7020376581893</v>
       </c>
       <c r="S99" t="n">
-        <v>9.000641698294629</v>
+        <v>9.000640537698938</v>
       </c>
       <c r="T99" t="n">
-        <v>118.9978287867827</v>
+        <v>49.87049511300074</v>
       </c>
       <c r="U99" t="n">
-        <v>0.4884383051296766</v>
+        <v>0.6546261844556511</v>
       </c>
       <c r="V99" t="n">
-        <v>0.7085964893695795</v>
+        <v>1.932829379520051</v>
       </c>
       <c r="W99" t="b">
         <v>1</v>
@@ -7693,68 +7693,68 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Pastry</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>943.8134301445141</v>
+        <v>1021.424404903021</v>
       </c>
       <c r="D100" t="n">
-        <v>10.5416950744846</v>
+        <v>8.912397178232448</v>
       </c>
       <c r="E100" t="n">
-        <v>143.1611992120024</v>
+        <v>202.0729792371364</v>
       </c>
       <c r="F100" t="n">
-        <v>0.9065549969673157</v>
+        <v>0.7210264205932617</v>
       </c>
       <c r="G100" t="n">
-        <v>0.001030104584060609</v>
+        <v>0.0001128785734181292</v>
       </c>
       <c r="H100" t="n">
-        <v>943.8137819908089</v>
+        <v>985.8937766144934</v>
       </c>
       <c r="I100" t="n">
-        <v>176.1299334757794</v>
+        <v>202.0729167839633</v>
       </c>
       <c r="J100" t="n">
-        <v>10.54169094731249</v>
+        <v>9.000641527014711</v>
       </c>
       <c r="K100" t="n">
-        <v>0.0003518462948477463</v>
+        <v>35.53062828852728</v>
       </c>
       <c r="L100" t="n">
-        <v>32.96873426377692</v>
+        <v>6.245317308639642e-05</v>
       </c>
       <c r="M100" t="n">
-        <v>4.127172115175881e-06</v>
+        <v>0.08824434878226306</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>0.9992758631706238</v>
+        <v>0.6351427435874939</v>
       </c>
       <c r="P100" t="n">
-        <v>0.004649315495043993</v>
+        <v>0.0002099389093928039</v>
       </c>
       <c r="Q100" t="n">
-        <v>800.0002135690013</v>
+        <v>971.8709134238034</v>
       </c>
       <c r="R100" t="n">
-        <v>158.7902180698048</v>
+        <v>201.3920574043729</v>
       </c>
       <c r="S100" t="n">
-        <v>10.07105028681568</v>
+        <v>9.000641559805413</v>
       </c>
       <c r="T100" t="n">
-        <v>143.8132165755128</v>
+        <v>49.55349147921731</v>
       </c>
       <c r="U100" t="n">
-        <v>15.62901885780232</v>
+        <v>0.6809218327634596</v>
       </c>
       <c r="V100" t="n">
-        <v>0.4706447876689204</v>
+        <v>0.08824438157296477</v>
       </c>
       <c r="W100" t="b">
         <v>1</v>
@@ -7766,68 +7766,68 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>866.0466215846022</v>
+        <v>938.5879772302337</v>
       </c>
       <c r="D101" t="n">
-        <v>8.883345110211364</v>
+        <v>11.08767417115766</v>
       </c>
       <c r="E101" t="n">
-        <v>206.4366122184509</v>
+        <v>139.5517799663994</v>
       </c>
       <c r="F101" t="n">
-        <v>0.7579154968261719</v>
+        <v>0.9841193556785583</v>
       </c>
       <c r="G101" t="n">
-        <v>0.002170027466490865</v>
+        <v>0.0001908497797558084</v>
       </c>
       <c r="H101" t="n">
-        <v>919.4300916867811</v>
+        <v>938.5798568635637</v>
       </c>
       <c r="I101" t="n">
-        <v>206.436563578844</v>
+        <v>176.1735528344169</v>
       </c>
       <c r="J101" t="n">
-        <v>9.328898478925602</v>
+        <v>11.08656396636439</v>
       </c>
       <c r="K101" t="n">
-        <v>53.38347010217888</v>
+        <v>0.008120366670027579</v>
       </c>
       <c r="L101" t="n">
-        <v>4.863960694478919e-05</v>
+        <v>36.62177286801753</v>
       </c>
       <c r="M101" t="n">
-        <v>0.4455533687142381</v>
+        <v>0.001110204793274505</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>0.8912108540534973</v>
+        <v>0.9999825954437256</v>
       </c>
       <c r="P101" t="n">
-        <v>0.0005053678178228438</v>
+        <v>0.00169484899379313</v>
       </c>
       <c r="Q101" t="n">
-        <v>930.7552569684668</v>
+        <v>800.0000678345394</v>
       </c>
       <c r="R101" t="n">
-        <v>206.2174158124488</v>
+        <v>150.2904852533921</v>
       </c>
       <c r="S101" t="n">
-        <v>9.000641822762658</v>
+        <v>10.89822481162234</v>
       </c>
       <c r="T101" t="n">
-        <v>64.70863538386459</v>
+        <v>138.5879093956943</v>
       </c>
       <c r="U101" t="n">
-        <v>0.2191964060021121</v>
+        <v>10.73870528699274</v>
       </c>
       <c r="V101" t="n">
-        <v>0.117296712551294</v>
+        <v>0.1894493595353168</v>
       </c>
       <c r="W101" t="b">
         <v>1</v>

--- a/export_dati/06_Step6_Simulazione_Massiva_100.xlsx
+++ b/export_dati/06_Step6_Simulazione_Massiva_100.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W101"/>
+  <dimension ref="A1:Y101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,85 +449,95 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Tempo_Esecuzione_XGBoost</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Prob_Finale_XGBoost</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Temp_Finale_XGBoost</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Press_Finale_XGBoost</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Vel_Finale_XGBoost</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Delta_Temp_XGBoost</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Delta_Press_XGBoost</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Delta_Vel_XGBoost</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Successo_XGBoost</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Prob_Iniziale_TensorFlow</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Tempo_Esecuzione_TensorFlow</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>Prob_Finale_TensorFlow</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Temp_Finale_TensorFlow</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Press_Finale_TensorFlow</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Vel_Finale_TensorFlow</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Delta_Temp_TensorFlow</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Delta_Press_TensorFlow</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Delta_Vel_TensorFlow</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Successo_TensorFlow</t>
         </is>
@@ -555,54 +565,60 @@
         <v>0.6594186425209045</v>
       </c>
       <c r="G2" t="n">
+        <v>0.1148099000565708</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.0008911140612326562</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>920.0548507071468</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>201.2411827932042</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>9.711011639075149</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>73.7001180975368</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.01106637899650309</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>0.03300140236935256</v>
       </c>
-      <c r="N2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.7613406181335449</v>
+      <c r="O2" t="b">
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0005433859187178314</v>
+        <v>0.7568662166595459</v>
       </c>
       <c r="Q2" t="n">
-        <v>922.8714624173679</v>
+        <v>0.4123388000298291</v>
       </c>
       <c r="R2" t="n">
-        <v>199.9695216718602</v>
+        <v>0.0005708818789571524</v>
       </c>
       <c r="S2" t="n">
-        <v>9.740446104148106</v>
+        <v>922.2980210297865</v>
       </c>
       <c r="T2" t="n">
-        <v>76.51672980775788</v>
+        <v>201.5339916121708</v>
       </c>
       <c r="U2" t="n">
-        <v>1.260594742347479</v>
+        <v>9.790420239017783</v>
       </c>
       <c r="V2" t="n">
-        <v>0.06243586744230889</v>
-      </c>
-      <c r="W2" t="b">
+        <v>75.94328842017649</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.3038751979631797</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.1124100023119858</v>
+      </c>
+      <c r="Y2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -628,54 +644,60 @@
         <v>0.6184679865837097</v>
       </c>
       <c r="G3" t="n">
+        <v>0.1300379000604153</v>
+      </c>
+      <c r="H3" t="n">
         <v>9.742625115904957e-05</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>985.8937770676032</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>195.7838875835934</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>10.96782296594122</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>53.68790795291193</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>3.55041252078081e-05</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.9861426949501038</v>
+      <c r="O3" t="b">
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0002667448716238141</v>
+        <v>0.9643027782440186</v>
       </c>
       <c r="Q3" t="n">
-        <v>975.3683586632568</v>
+        <v>0.4306553001515567</v>
       </c>
       <c r="R3" t="n">
-        <v>195.3094626140189</v>
+        <v>0.0002911596384365112</v>
       </c>
       <c r="S3" t="n">
-        <v>10.967173305267</v>
+        <v>974.6592620854868</v>
       </c>
       <c r="T3" t="n">
-        <v>64.21332635725832</v>
+        <v>195.8000885688702</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4743894654492919</v>
+        <v>10.94245247530181</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0006496606742132371</v>
-      </c>
-      <c r="W3" t="b">
+        <v>64.92242293502829</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.01623648940193334</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.02537049063940522</v>
+      </c>
+      <c r="Y3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -701,54 +723,60 @@
         <v>0.9324119091033936</v>
       </c>
       <c r="G4" t="n">
+        <v>0.05062859994359314</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.000253947131568566</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>966.3537262610907</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>191.0819217970763</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>3.410605131648481e-13</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>3.611175761276333</v>
       </c>
-      <c r="N4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.9593839645385742</v>
+      <c r="O4" t="b">
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0001522877864772454</v>
+        <v>0.95229572057724</v>
       </c>
       <c r="Q4" t="n">
-        <v>957.9046369489666</v>
+        <v>0.195089700166136</v>
       </c>
       <c r="R4" t="n">
-        <v>191.5366588035811</v>
+        <v>0.0001709491480141878</v>
       </c>
       <c r="S4" t="n">
+        <v>961.5250387179119</v>
+      </c>
+      <c r="T4" t="n">
+        <v>191.5713759598443</v>
+      </c>
+      <c r="U4" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T4" t="n">
-        <v>8.449089312124443</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.45473700650507</v>
-      </c>
       <c r="V4" t="n">
+        <v>4.828687543179171</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.4894541627682543</v>
+      </c>
+      <c r="X4" t="n">
         <v>3.611175761276333</v>
       </c>
-      <c r="W4" t="b">
+      <c r="Y4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -774,54 +802,60 @@
         <v>0.9806832075119019</v>
       </c>
       <c r="G5" t="n">
+        <v>0.2745032000821084</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.01705425418913364</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>970.2248744616279</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>166.3955239495973</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>10.2422937265863</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>25.15067731380395</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>58.12705737421825</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>0.07334958114606671</v>
       </c>
-      <c r="N5" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
+      <c r="O5" t="b">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001186170382425189</v>
+        <v>0.9999994039535522</v>
       </c>
       <c r="Q5" t="n">
-        <v>801.5323704320843</v>
+        <v>0.9226595000363886</v>
       </c>
       <c r="R5" t="n">
-        <v>150.0005523686477</v>
+        <v>0.02252509817481041</v>
       </c>
       <c r="S5" t="n">
-        <v>10.19476330015607</v>
+        <v>800.0000002337264</v>
       </c>
       <c r="T5" t="n">
-        <v>143.5418267157396</v>
+        <v>156.5149942513265</v>
       </c>
       <c r="U5" t="n">
-        <v>41.73208579326865</v>
+        <v>9.183113562909172</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1208800075763001</v>
-      </c>
-      <c r="W5" t="b">
+        <v>145.0741969140976</v>
+      </c>
+      <c r="W5" t="n">
+        <v>48.24652767594745</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.132529744823193</v>
+      </c>
+      <c r="Y5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -847,54 +881,60 @@
         <v>0.9835739135742188</v>
       </c>
       <c r="G6" t="n">
+        <v>0.2413848000578582</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.001278240233659744</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>857.2976406733651</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>176.1732637380991</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>9.740868471732181</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>79.6128258805611</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>48.66839488187156</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>0.1562558594210888</v>
       </c>
-      <c r="N6" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.9999996423721313</v>
+      <c r="O6" t="b">
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001099389512091875</v>
+        <v>0.9999877214431763</v>
       </c>
       <c r="Q6" t="n">
-        <v>806.1222020152608</v>
+        <v>0.8820146000944078</v>
       </c>
       <c r="R6" t="n">
-        <v>150.0005523521421</v>
+        <v>0.01039397343993187</v>
       </c>
       <c r="S6" t="n">
-        <v>9.484521859520243</v>
+        <v>800.0000220735074</v>
       </c>
       <c r="T6" t="n">
-        <v>130.7882645386654</v>
+        <v>160.6200746000245</v>
       </c>
       <c r="U6" t="n">
-        <v>22.49568349591453</v>
+        <v>9.213440495759903</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1000907527908499</v>
-      </c>
-      <c r="W6" t="b">
+        <v>136.9104444804188</v>
+      </c>
+      <c r="W6" t="n">
+        <v>33.11520574379702</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.3711721165511896</v>
+      </c>
+      <c r="Y6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -920,54 +960,60 @@
         <v>0.6979028582572937</v>
       </c>
       <c r="G7" t="n">
+        <v>0.1536425999365747</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.001823191996663809</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>920.0234447258514</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>176.6771407193691</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>9.438119575974012</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>53.73875471781514</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>2.842170943040401e-14</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>0.4428588193845897</v>
       </c>
-      <c r="N7" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.9147205948829651</v>
+      <c r="O7" t="b">
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0008118203841149807</v>
+        <v>0.8673694133758545</v>
       </c>
       <c r="Q7" t="n">
-        <v>937.3181585469058</v>
+        <v>0.4963392000645399</v>
       </c>
       <c r="R7" t="n">
-        <v>177.9227023451915</v>
+        <v>0.0006938831647858024</v>
       </c>
       <c r="S7" t="n">
-        <v>9.124220769798955</v>
+        <v>941.0793728588742</v>
       </c>
       <c r="T7" t="n">
-        <v>71.03346853886956</v>
+        <v>179.247224021337</v>
       </c>
       <c r="U7" t="n">
-        <v>1.245561625822319</v>
+        <v>9.106679146139149</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1289600132095323</v>
-      </c>
-      <c r="W7" t="b">
+        <v>74.79468285083794</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.570083301967827</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.1114183895497263</v>
+      </c>
+      <c r="Y7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -993,54 +1039,60 @@
         <v>0.9655842781066895</v>
       </c>
       <c r="G8" t="n">
+        <v>0.03577279997989535</v>
+      </c>
+      <c r="H8" t="n">
         <v>0.0002531284117139876</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>940.869883521915</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>206.5003175015104</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>0.3664940941380337</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>4.774847184307873e-12</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>3.170588788582752</v>
       </c>
-      <c r="N8" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.8467274308204651</v>
+      <c r="O8" t="b">
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>9.20423335628584e-05</v>
+        <v>0.8306910991668701</v>
       </c>
       <c r="Q8" t="n">
-        <v>940.1738274090035</v>
+        <v>0.2052114999387413</v>
       </c>
       <c r="R8" t="n">
-        <v>206.2006449566969</v>
+        <v>8.185818296624348e-05</v>
       </c>
       <c r="S8" t="n">
+        <v>942.1007516985072</v>
+      </c>
+      <c r="T8" t="n">
+        <v>206.4526096379934</v>
+      </c>
+      <c r="U8" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T8" t="n">
-        <v>1.062550207049526</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.2996725448087147</v>
-      </c>
       <c r="V8" t="n">
+        <v>0.8643740824542192</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.04770786351221545</v>
+      </c>
+      <c r="X8" t="n">
         <v>3.170588788582752</v>
       </c>
-      <c r="W8" t="b">
+      <c r="Y8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1066,54 +1118,60 @@
         <v>0.8222670555114746</v>
       </c>
       <c r="G9" t="n">
+        <v>0.1128199999220669</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.001392161007970572</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>925.9037157961071</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>190.8029197760437</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>9.000540538610286</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>48.81022171673828</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>2.842170943040401e-14</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>0.4932362220224942</v>
       </c>
-      <c r="N9" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.905357301235199</v>
+      <c r="O9" t="b">
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0004600656393449754</v>
+        <v>0.8811309337615967</v>
       </c>
       <c r="Q9" t="n">
-        <v>937.4510330395266</v>
+        <v>0.4324777000583708</v>
       </c>
       <c r="R9" t="n">
-        <v>191.4340264013696</v>
+        <v>0.0004764958284795284</v>
       </c>
       <c r="S9" t="n">
-        <v>9.000641659469542</v>
+        <v>936.5260359180689</v>
       </c>
       <c r="T9" t="n">
-        <v>60.35753896015774</v>
+        <v>192.1167233077616</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6311066253259412</v>
+        <v>9.000641305933799</v>
       </c>
       <c r="V9" t="n">
-        <v>0.49333734288175</v>
-      </c>
-      <c r="W9" t="b">
+        <v>59.4325418387001</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.313803531717923</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.4933369893460071</v>
+      </c>
+      <c r="Y9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1139,54 +1197,60 @@
         <v>0.9792359471321106</v>
       </c>
       <c r="G10" t="n">
+        <v>0.1166550000198185</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.0004074503376614302</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>940.8703895322254</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>183.8016390686678</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>9.00074240025527</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>79.57627933645506</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>2.75370003066655e-05</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>1.543898024957448</v>
       </c>
-      <c r="N10" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.9938086867332458</v>
+      <c r="O10" t="b">
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0008139526471495628</v>
+        <v>0.9812757968902588</v>
       </c>
       <c r="Q10" t="n">
-        <v>935.8644288209084</v>
+        <v>0.4082530001178384</v>
       </c>
       <c r="R10" t="n">
-        <v>185.4695796277663</v>
+        <v>0.0006709850276820362</v>
       </c>
       <c r="S10" t="n">
-        <v>9.000641158624035</v>
+        <v>937.7940921391931</v>
       </c>
       <c r="T10" t="n">
-        <v>74.57031862513804</v>
+        <v>186.014746591795</v>
       </c>
       <c r="U10" t="n">
-        <v>1.667913022098162</v>
+        <v>9.000640575937489</v>
       </c>
       <c r="V10" t="n">
-        <v>1.543796783326213</v>
-      </c>
-      <c r="W10" t="b">
+        <v>76.49998194342277</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.213079986126957</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.543796200639667</v>
+      </c>
+      <c r="Y10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1212,54 +1276,60 @@
         <v>0.9629010558128357</v>
       </c>
       <c r="G11" t="n">
+        <v>0.09964590007439256</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.001197295030578971</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>925.9037179955458</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>204.2353346863231</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>9.14054197930473</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>82.03226147657404</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>8.526512829121202e-14</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>0.2267078691045157</v>
       </c>
-      <c r="N11" t="b">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.9316202998161316</v>
+      <c r="O11" t="b">
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0008104241569526494</v>
+        <v>0.9127441644668579</v>
       </c>
       <c r="Q11" t="n">
-        <v>931.1274538887245</v>
+        <v>0.4021340999752283</v>
       </c>
       <c r="R11" t="n">
-        <v>202.86571498608</v>
+        <v>0.0006975957076065242</v>
       </c>
       <c r="S11" t="n">
-        <v>9.057323664140805</v>
+        <v>930.5358388212916</v>
       </c>
       <c r="T11" t="n">
-        <v>87.25599736975278</v>
+        <v>204.4391400831735</v>
       </c>
       <c r="U11" t="n">
-        <v>1.369619700243135</v>
+        <v>9.044953600465856</v>
       </c>
       <c r="V11" t="n">
-        <v>0.14348955394059</v>
-      </c>
-      <c r="W11" t="b">
+        <v>86.66438230231984</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.2038053968503846</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.1311194902656414</v>
+      </c>
+      <c r="Y11" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1285,54 +1355,60 @@
         <v>0.9834682941436768</v>
       </c>
       <c r="G12" t="n">
+        <v>0.1714788000099361</v>
+      </c>
+      <c r="H12" t="n">
         <v>0.0002063950814772397</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>956.2139859828969</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>176.1732562784816</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>9.609087940925981</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>0.02841828036298466</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>55.37751677818477</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>5.164538625024306e-05</v>
       </c>
-      <c r="N12" t="b">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="O12" t="b">
         <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>0.001205819193273783</v>
+        <v>0.9999974966049194</v>
       </c>
       <c r="Q12" t="n">
-        <v>806.7000349875539</v>
+        <v>0.5958890998736024</v>
       </c>
       <c r="R12" t="n">
-        <v>150.0005524239352</v>
+        <v>0.01383373141288757</v>
       </c>
       <c r="S12" t="n">
-        <v>9.49864303421038</v>
+        <v>800.0000431862165</v>
       </c>
       <c r="T12" t="n">
-        <v>149.4855327149801</v>
+        <v>158.7743226305047</v>
       </c>
       <c r="U12" t="n">
-        <v>29.20481292363843</v>
+        <v>9.036969910669169</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1103932613293512</v>
-      </c>
-      <c r="W12" t="b">
+        <v>156.1855245163174</v>
+      </c>
+      <c r="W12" t="n">
+        <v>37.97858313020794</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.5720663848705616</v>
+      </c>
+      <c r="Y12" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1358,54 +1434,60 @@
         <v>0.9216844439506531</v>
       </c>
       <c r="G13" t="n">
+        <v>0.1425656999927014</v>
+      </c>
+      <c r="H13" t="n">
         <v>0.00115188374184072</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>925.903722391216</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>179.3816766502316</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>9.000641767919562</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>42.97983564816525</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>0.6097961259710019</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>1.609114422948815</v>
       </c>
-      <c r="N13" t="b">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.9591795206069946</v>
+      <c r="O13" t="b">
+        <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0005985167226754129</v>
+        <v>0.9197916984558105</v>
       </c>
       <c r="Q13" t="n">
-        <v>940.4709368943387</v>
+        <v>0.420236499980092</v>
       </c>
       <c r="R13" t="n">
-        <v>181.1667405124898</v>
+        <v>0.0005262662889435887</v>
       </c>
       <c r="S13" t="n">
-        <v>9.000641401718326</v>
+        <v>942.3892829258076</v>
       </c>
       <c r="T13" t="n">
-        <v>57.54705015128798</v>
+        <v>181.8904781820779</v>
       </c>
       <c r="U13" t="n">
-        <v>1.175267736287225</v>
+        <v>9.000639799986432</v>
       </c>
       <c r="V13" t="n">
-        <v>1.609114056747579</v>
-      </c>
-      <c r="W13" t="b">
+        <v>59.46539618275688</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.899005405875243</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.609112455015685</v>
+      </c>
+      <c r="Y13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1431,54 +1513,60 @@
         <v>0.6788570880889893</v>
       </c>
       <c r="G14" t="n">
+        <v>0.09052939992398024</v>
+      </c>
+      <c r="H14" t="n">
         <v>0.0009468119242228568</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>920.0548587821094</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>198.2654474321198</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>9.977749373670072</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>71.34124015366922</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>3.126388037344441e-13</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="b">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.6402310729026794</v>
+      <c r="O14" t="b">
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0005777662736363709</v>
+        <v>0.6549311280250549</v>
       </c>
       <c r="Q14" t="n">
-        <v>918.9948686969481</v>
+        <v>0.3376397998072207</v>
       </c>
       <c r="R14" t="n">
-        <v>198.4618634645798</v>
+        <v>0.0005301035125739872</v>
       </c>
       <c r="S14" t="n">
-        <v>10.08806581593034</v>
+        <v>919.6533529534845</v>
       </c>
       <c r="T14" t="n">
-        <v>70.28125006850792</v>
+        <v>198.8376977159488</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1964160324597231</v>
+        <v>10.0826193860212</v>
       </c>
       <c r="V14" t="n">
-        <v>0.110316442260272</v>
-      </c>
-      <c r="W14" t="b">
+        <v>70.93973432504436</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.5722502838287369</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.1048700123511246</v>
+      </c>
+      <c r="Y14" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1504,54 +1592,60 @@
         <v>0.7952963709831238</v>
       </c>
       <c r="G15" t="n">
+        <v>0.03968399995937943</v>
+      </c>
+      <c r="H15" t="n">
         <v>0.000253947131568566</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>961.8072441622284</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>202.8315364014029</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>7.059952622512355e-11</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>7.105427357601002e-13</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>3.224221448792141</v>
       </c>
-      <c r="N15" t="b">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.8996849656105042</v>
+      <c r="O15" t="b">
+        <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>9.912327368510887e-05</v>
+        <v>0.8876581192016602</v>
       </c>
       <c r="Q15" t="n">
-        <v>955.5901352049857</v>
+        <v>0.1741335999686271</v>
       </c>
       <c r="R15" t="n">
-        <v>202.3649107996706</v>
+        <v>9.255448094336316e-05</v>
       </c>
       <c r="S15" t="n">
+        <v>959.5128314202112</v>
+      </c>
+      <c r="T15" t="n">
+        <v>202.882371458895</v>
+      </c>
+      <c r="U15" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T15" t="n">
-        <v>6.217108957313258</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.4666256017315504</v>
-      </c>
       <c r="V15" t="n">
+        <v>2.294412742087729</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.05083505749280448</v>
+      </c>
+      <c r="X15" t="n">
         <v>3.224221448792141</v>
       </c>
-      <c r="W15" t="b">
+      <c r="Y15" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1577,54 +1671,60 @@
         <v>0.9842979311943054</v>
       </c>
       <c r="G16" t="n">
+        <v>0.1039881999604404</v>
+      </c>
+      <c r="H16" t="n">
         <v>0.001060195965692401</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>937.9053910882772</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>220.1042600299626</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>9.000645620321198</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>117.6325336741903</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>0.6827293580660694</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>1.673586958005852</v>
       </c>
-      <c r="N16" t="b">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.996921181678772</v>
+      <c r="O16" t="b">
+        <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>0.001144251204095781</v>
+        <v>0.9843368530273438</v>
       </c>
       <c r="Q16" t="n">
-        <v>934.1263414437773</v>
+        <v>0.4257890000008047</v>
       </c>
       <c r="R16" t="n">
-        <v>218.1800748214364</v>
+        <v>0.001031925203278661</v>
       </c>
       <c r="S16" t="n">
-        <v>9.00064143614474</v>
+        <v>931.1041740569792</v>
       </c>
       <c r="T16" t="n">
-        <v>113.8534840296904</v>
+        <v>217.7102106437499</v>
       </c>
       <c r="U16" t="n">
-        <v>2.606914566592252</v>
+        <v>9.000641320074816</v>
       </c>
       <c r="V16" t="n">
-        <v>1.673582773829394</v>
-      </c>
-      <c r="W16" t="b">
+        <v>110.8313166428924</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.076778744278755</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.673582657759471</v>
+      </c>
+      <c r="Y16" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1650,54 +1750,60 @@
         <v>0.8579790592193604</v>
       </c>
       <c r="G17" t="n">
+        <v>0.1073563999962062</v>
+      </c>
+      <c r="H17" t="n">
         <v>0.0004035303718410432</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>940.8711338869272</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>192.5125193001732</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>9.000641706318349</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>55.70494701237078</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>1.932676241267473e-12</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>0.760414908182355</v>
       </c>
-      <c r="N17" t="b">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.8316174745559692</v>
+      <c r="O17" t="b">
+        <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0003955218999180943</v>
+        <v>0.8278878331184387</v>
       </c>
       <c r="Q17" t="n">
-        <v>937.9754251215503</v>
+        <v>0.4214375999290496</v>
       </c>
       <c r="R17" t="n">
-        <v>193.0669831017955</v>
+        <v>0.0004051265132147819</v>
       </c>
       <c r="S17" t="n">
-        <v>9.000641840584759</v>
+        <v>936.8748371100689</v>
       </c>
       <c r="T17" t="n">
-        <v>52.80923824699391</v>
+        <v>193.5584827886359</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5544638016204146</v>
+        <v>9.000641453245866</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7604150424487646</v>
-      </c>
-      <c r="W17" t="b">
+        <v>51.70865023551255</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.045963488460785</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.7604146551098712</v>
+      </c>
+      <c r="Y17" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1723,54 +1829,60 @@
         <v>0.6072345972061157</v>
       </c>
       <c r="G18" t="n">
+        <v>0.0391332998406142</v>
+      </c>
+      <c r="H18" t="n">
         <v>0.00027896897518076</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>923.5689299805319</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>210.8644338795117</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>0.193329750674593</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>4.205322696293479e-05</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>2.408916369189187</v>
       </c>
-      <c r="N18" t="b">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.2149681448936462</v>
+      <c r="O18" t="b">
+        <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>0.0001078279528883286</v>
+        <v>0.2370161265134811</v>
       </c>
       <c r="Q18" t="n">
-        <v>926.7729900152885</v>
+        <v>0.1791290000546724</v>
       </c>
       <c r="R18" t="n">
-        <v>211.0144049665592</v>
+        <v>0.0001314371329499409</v>
       </c>
       <c r="S18" t="n">
+        <v>927.5675701103778</v>
+      </c>
+      <c r="T18" t="n">
+        <v>210.6658734136567</v>
+      </c>
+      <c r="U18" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T18" t="n">
-        <v>3.397389785431187</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.1500131402744671</v>
-      </c>
       <c r="V18" t="n">
+        <v>4.191969880520446</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.198518412628033</v>
+      </c>
+      <c r="X18" t="n">
         <v>2.408916369189187</v>
       </c>
-      <c r="W18" t="b">
+      <c r="Y18" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1796,54 +1908,60 @@
         <v>0.9723821878433228</v>
       </c>
       <c r="G19" t="n">
+        <v>0.2418418999295682</v>
+      </c>
+      <c r="H19" t="n">
         <v>0.001777262426912785</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>980.6562466243272</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>173.8994571341418</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>10.39192679211197</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>2.269421047352353</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>51.00351739425815</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>7.042105814036859e-07</v>
       </c>
-      <c r="N19" t="b">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.9999998807907104</v>
+      <c r="O19" t="b">
+        <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>0.001379667315632105</v>
+        <v>0.9999909400939941</v>
       </c>
       <c r="Q19" t="n">
-        <v>802.2463404644901</v>
+        <v>1.240526499925181</v>
       </c>
       <c r="R19" t="n">
-        <v>150.0005522524178</v>
+        <v>0.0116626163944602</v>
       </c>
       <c r="S19" t="n">
-        <v>10.251242020522</v>
+        <v>800.0000484147823</v>
       </c>
       <c r="T19" t="n">
-        <v>180.6793272071894</v>
+        <v>161.2813116596394</v>
       </c>
       <c r="U19" t="n">
-        <v>27.10461251253409</v>
+        <v>10.06601636648029</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1406854758005522</v>
-      </c>
-      <c r="W19" t="b">
+        <v>182.9256192568972</v>
+      </c>
+      <c r="W19" t="n">
+        <v>38.38537191975567</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.3259111298422628</v>
+      </c>
+      <c r="Y19" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1869,54 +1987,60 @@
         <v>0.9851580262184143</v>
       </c>
       <c r="G20" t="n">
+        <v>0.03048730012960732</v>
+      </c>
+      <c r="H20" t="n">
         <v>0.0002752725849859416</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>928.7700471761835</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>206.8596956383719</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>3.072955223615281e-10</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>2.080469130305573e-11</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>4.010025352909084</v>
       </c>
-      <c r="N20" t="b">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.9745203852653503</v>
+      <c r="O20" t="b">
+        <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>9.672575833974406e-05</v>
+        <v>0.9262952208518982</v>
       </c>
       <c r="Q20" t="n">
-        <v>931.5014521472814</v>
+        <v>0.2043945998884737</v>
       </c>
       <c r="R20" t="n">
-        <v>206.8819205344054</v>
+        <v>0.0001038869668263942</v>
       </c>
       <c r="S20" t="n">
+        <v>931.6526519599557</v>
+      </c>
+      <c r="T20" t="n">
+        <v>206.7985988204536</v>
+      </c>
+      <c r="U20" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T20" t="n">
-        <v>2.731404971405141</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.0222248960126592</v>
-      </c>
       <c r="V20" t="n">
+        <v>2.88260478407949</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.06109681793907384</v>
+      </c>
+      <c r="X20" t="n">
         <v>4.010025352909084</v>
       </c>
-      <c r="W20" t="b">
+      <c r="Y20" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1942,54 +2066,60 @@
         <v>0.7952963709831238</v>
       </c>
       <c r="G21" t="n">
+        <v>0.04120999993756413</v>
+      </c>
+      <c r="H21" t="n">
         <v>0.0002481373958289623</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>957.5953327879187</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>201.840116699303</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>2.454661134667163</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>4.263256414560601e-13</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>2.803715452595798</v>
       </c>
-      <c r="N21" t="b">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.7199969887733459</v>
+      <c r="O21" t="b">
+        <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>9.093464177567512e-05</v>
+        <v>0.718028724193573</v>
       </c>
       <c r="Q21" t="n">
-        <v>955.6526061024898</v>
+        <v>0.1968372000847012</v>
       </c>
       <c r="R21" t="n">
-        <v>201.5062186996885</v>
+        <v>9.068239160114899e-05</v>
       </c>
       <c r="S21" t="n">
+        <v>958.0650875109833</v>
+      </c>
+      <c r="T21" t="n">
+        <v>201.91308266588</v>
+      </c>
+      <c r="U21" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T21" t="n">
-        <v>4.397387820096014</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.3338979996140665</v>
-      </c>
       <c r="V21" t="n">
+        <v>1.984906411602537</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.07296596657735677</v>
+      </c>
+      <c r="X21" t="n">
         <v>2.803715452595798</v>
       </c>
-      <c r="W21" t="b">
+      <c r="Y21" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2015,54 +2145,60 @@
         <v>0.7019981145858765</v>
       </c>
       <c r="G22" t="n">
+        <v>0.09814969985745847</v>
+      </c>
+      <c r="H22" t="n">
         <v>0.000411912944400683</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>940.8700915289151</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>207.9615602408907</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>9.000641655378949</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>52.66450649690034</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>0.9259025795035605</v>
       </c>
-      <c r="N22" t="b">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.7525087594985962</v>
+      <c r="O22" t="b">
+        <v>1</v>
       </c>
       <c r="P22" t="n">
-        <v>0.0003843112499453127</v>
+        <v>0.8021401166915894</v>
       </c>
       <c r="Q22" t="n">
-        <v>938.665155213009</v>
+        <v>0.4709292000625283</v>
       </c>
       <c r="R22" t="n">
-        <v>206.93691963733</v>
+        <v>0.000357930432073772</v>
       </c>
       <c r="S22" t="n">
-        <v>9.000641479829829</v>
+        <v>935.1249652165901</v>
       </c>
       <c r="T22" t="n">
-        <v>50.45957018099432</v>
+        <v>207.7440228019852</v>
       </c>
       <c r="U22" t="n">
-        <v>1.024640603560641</v>
+        <v>9.000641754909143</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9259024039544403</v>
-      </c>
-      <c r="W22" t="b">
+        <v>46.9193801845754</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.2175374389054809</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.9259026790337543</v>
+      </c>
+      <c r="Y22" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2088,54 +2224,60 @@
         <v>0.9158090949058533</v>
       </c>
       <c r="G23" t="n">
+        <v>0.1064828000962734</v>
+      </c>
+      <c r="H23" t="n">
         <v>0.001327915932051837</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>925.9037229340205</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>198.6980166651561</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>9.140537946887919</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>96.60345804089025</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>4.007461029686965e-12</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>0.01447296966421341</v>
       </c>
-      <c r="N23" t="b">
-        <v>1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.9185240268707275</v>
+      <c r="O23" t="b">
+        <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>0.0008830088190734386</v>
+        <v>0.8835404515266418</v>
       </c>
       <c r="Q23" t="n">
-        <v>925.7961345245654</v>
+        <v>0.5368796000257134</v>
       </c>
       <c r="R23" t="n">
-        <v>199.984272134458</v>
+        <v>0.0007934897439554334</v>
       </c>
       <c r="S23" t="n">
-        <v>9.328020855699309</v>
+        <v>927.1026932959888</v>
       </c>
       <c r="T23" t="n">
-        <v>96.4958696314352</v>
+        <v>199.6700237159809</v>
       </c>
       <c r="U23" t="n">
-        <v>1.286255469305871</v>
+        <v>9.281360722020638</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2019558784756033</v>
-      </c>
-      <c r="W23" t="b">
+        <v>97.8024284028586</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.9720070508287506</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.1552957447969323</v>
+      </c>
+      <c r="Y23" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2161,54 +2303,60 @@
         <v>0.578937828540802</v>
       </c>
       <c r="G24" t="n">
+        <v>0.03562650014646351</v>
+      </c>
+      <c r="H24" t="n">
         <v>0.000253947131568566</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>962.1201990269394</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>202.6234247915654</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>2.660272002685815e-11</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>2.410916221782254</v>
       </c>
-      <c r="N24" t="b">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.384284108877182</v>
+      <c r="O24" t="b">
+        <v>1</v>
       </c>
       <c r="P24" t="n">
-        <v>9.885372128337622e-05</v>
+        <v>0.4307235479354858</v>
       </c>
       <c r="Q24" t="n">
-        <v>955.9111106197507</v>
+        <v>0.1834670999087393</v>
       </c>
       <c r="R24" t="n">
-        <v>202.1605808544388</v>
+        <v>9.343211422674358e-05</v>
       </c>
       <c r="S24" t="n">
+        <v>959.7582605048731</v>
+      </c>
+      <c r="T24" t="n">
+        <v>202.6784910013182</v>
+      </c>
+      <c r="U24" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T24" t="n">
-        <v>6.209088407162085</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.4628439371263937</v>
-      </c>
       <c r="V24" t="n">
+        <v>2.361938522039736</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.05506620975296528</v>
+      </c>
+      <c r="X24" t="n">
         <v>2.410916221782254</v>
       </c>
-      <c r="W24" t="b">
+      <c r="Y24" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2234,54 +2382,60 @@
         <v>0.9558945894241333</v>
       </c>
       <c r="G25" t="n">
+        <v>0.2576979000587016</v>
+      </c>
+      <c r="H25" t="n">
         <v>0.000221210895688273</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>963.1849133869182</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>176.1732576611711</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>9.00000171320859</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>1.82700432560523e-08</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>39.20804205391184</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>1.209080765696037</v>
       </c>
-      <c r="N25" t="b">
-        <v>1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.9999759197235107</v>
+      <c r="O25" t="b">
+        <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>0.001095251413062215</v>
+        <v>0.9996470212936401</v>
       </c>
       <c r="Q25" t="n">
-        <v>809.9402019035333</v>
+        <v>0.6005369999911636</v>
       </c>
       <c r="R25" t="n">
-        <v>150.0005525357284</v>
+        <v>0.006656422279775143</v>
       </c>
       <c r="S25" t="n">
-        <v>9.000641702659145</v>
+        <v>800.0000345629662</v>
       </c>
       <c r="T25" t="n">
-        <v>153.2447114651148</v>
+        <v>162.4130274132106</v>
       </c>
       <c r="U25" t="n">
-        <v>13.03533692846915</v>
+        <v>9.000642020576061</v>
       </c>
       <c r="V25" t="n">
-        <v>1.209720755146591</v>
-      </c>
-      <c r="W25" t="b">
+        <v>163.1848788056819</v>
+      </c>
+      <c r="W25" t="n">
+        <v>25.44781180595129</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.209721073063507</v>
+      </c>
+      <c r="Y25" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2307,54 +2461,60 @@
         <v>0.9593200087547302</v>
       </c>
       <c r="G26" t="n">
+        <v>0.03573119989596307</v>
+      </c>
+      <c r="H26" t="n">
         <v>0.0002819020883180201</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>921.5473306165907</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>197.3268466222976</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>8.787992555880919e-10</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>4.223102223477326e-08</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>7.420886976429525</v>
       </c>
-      <c r="N26" t="b">
-        <v>1</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0.999847412109375</v>
+      <c r="O26" t="b">
+        <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0001655499800108373</v>
+        <v>0.9911040067672729</v>
       </c>
       <c r="Q26" t="n">
-        <v>929.307332401006</v>
+        <v>0.1863694000057876</v>
       </c>
       <c r="R26" t="n">
-        <v>197.8663378519999</v>
+        <v>0.0001417156890965998</v>
       </c>
       <c r="S26" t="n">
+        <v>926.140012342643</v>
+      </c>
+      <c r="T26" t="n">
+        <v>197.521136696433</v>
+      </c>
+      <c r="U26" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T26" t="n">
-        <v>7.760001785294094</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0.5394912719333433</v>
-      </c>
       <c r="V26" t="n">
+        <v>4.592681726931119</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.1942901163664317</v>
+      </c>
+      <c r="X26" t="n">
         <v>7.420886976429525</v>
       </c>
-      <c r="W26" t="b">
+      <c r="Y26" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2380,54 +2540,60 @@
         <v>0.9209200143814087</v>
       </c>
       <c r="G27" t="n">
+        <v>0.04966160003095865</v>
+      </c>
+      <c r="H27" t="n">
         <v>0.000253947131568566</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>979.6651776971187</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>191.5825472588183</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>1.318767317570746e-11</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>3.803787981821364</v>
       </c>
-      <c r="N27" t="b">
-        <v>1</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0.9783687591552734</v>
+      <c r="O27" t="b">
+        <v>1</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0002305722155142576</v>
+        <v>0.9677569270133972</v>
       </c>
       <c r="Q27" t="n">
-        <v>966.2149183878104</v>
+        <v>0.2118361999746412</v>
       </c>
       <c r="R27" t="n">
-        <v>192.2770742262953</v>
+        <v>0.0002242007903987542</v>
       </c>
       <c r="S27" t="n">
+        <v>970.224955262712</v>
+      </c>
+      <c r="T27" t="n">
+        <v>192.1561491681835</v>
+      </c>
+      <c r="U27" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T27" t="n">
-        <v>13.4502593093215</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0.6945269674767474</v>
-      </c>
       <c r="V27" t="n">
+        <v>9.440222434419866</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.5736019093649816</v>
+      </c>
+      <c r="X27" t="n">
         <v>3.803787981821364</v>
       </c>
-      <c r="W27" t="b">
+      <c r="Y27" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2453,54 +2619,60 @@
         <v>0.7058996558189392</v>
       </c>
       <c r="G28" t="n">
+        <v>0.110088599845767</v>
+      </c>
+      <c r="H28" t="n">
         <v>0.0001050807259161957</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>985.8937780007902</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>195.5914779393746</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>9.458810875340344</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>24.20510144911805</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>7.394100262558823e-05</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>6.427194124469793e-06</v>
       </c>
-      <c r="N28" t="b">
-        <v>1</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0.2233198583126068</v>
+      <c r="O28" t="b">
+        <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>0.0001602740812813863</v>
+        <v>0.2003501355648041</v>
       </c>
       <c r="Q28" t="n">
-        <v>973.0537009867018</v>
+        <v>0.3602583000902086</v>
       </c>
       <c r="R28" t="n">
-        <v>194.946216007718</v>
+        <v>0.0001663559232838452</v>
       </c>
       <c r="S28" t="n">
-        <v>9.458934504884526</v>
+        <v>974.1580303117572</v>
       </c>
       <c r="T28" t="n">
-        <v>37.04517846320653</v>
+        <v>195.8041666487806</v>
       </c>
       <c r="U28" t="n">
-        <v>0.6453358726593024</v>
+        <v>9.460563031550096</v>
       </c>
       <c r="V28" t="n">
-        <v>0.0001172023500579655</v>
-      </c>
-      <c r="W28" t="b">
+        <v>35.94084913815107</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.2126147684033413</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.001745729015627973</v>
+      </c>
+      <c r="Y28" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2526,54 +2698,60 @@
         <v>0.7772117853164673</v>
       </c>
       <c r="G29" t="n">
+        <v>0.08481939998455346</v>
+      </c>
+      <c r="H29" t="n">
         <v>0.001392161007970572</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>925.9044564923068</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>188.5912253305267</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>9.000458133074735</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>45.15509963916452</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>6.536993168992922e-13</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>0.3170035245811587</v>
       </c>
-      <c r="N29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0.8484960794448853</v>
+      <c r="O29" t="b">
+        <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>0.0004724953614640981</v>
+        <v>0.8065098524093628</v>
       </c>
       <c r="Q29" t="n">
-        <v>937.580897911713</v>
+        <v>0.4070402001962066</v>
       </c>
       <c r="R29" t="n">
-        <v>190.1407925270615</v>
+        <v>0.0004629315226338804</v>
       </c>
       <c r="S29" t="n">
-        <v>9.000641777042683</v>
+        <v>937.77789113753</v>
       </c>
       <c r="T29" t="n">
-        <v>56.83154105857068</v>
+        <v>190.0055498328339</v>
       </c>
       <c r="U29" t="n">
-        <v>1.549567196535492</v>
+        <v>9.000641286190351</v>
       </c>
       <c r="V29" t="n">
-        <v>0.3171871685491059</v>
-      </c>
-      <c r="W29" t="b">
+        <v>57.02853428438766</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.414324502307863</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.3171866776967747</v>
+      </c>
+      <c r="Y29" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2599,54 +2777,60 @@
         <v>0.9804819226264954</v>
       </c>
       <c r="G30" t="n">
+        <v>0.129959600046277</v>
+      </c>
+      <c r="H30" t="n">
         <v>0.001278901007026434</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>920.066988000005</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>187.3611277202333</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>9.000398779892071</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>89.14279338990298</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>0.3975683165048167</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>0.4698464309210024</v>
       </c>
-      <c r="N30" t="b">
-        <v>1</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0.9746896624565125</v>
+      <c r="O30" t="b">
+        <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>0.0008967292378656566</v>
+        <v>0.9539496898651123</v>
       </c>
       <c r="Q30" t="n">
-        <v>934.0741017748486</v>
+        <v>0.4369451999664307</v>
       </c>
       <c r="R30" t="n">
-        <v>189.0181080717882</v>
+        <v>0.0009118904708884656</v>
       </c>
       <c r="S30" t="n">
-        <v>9.000641782501154</v>
+        <v>933.4183443953783</v>
       </c>
       <c r="T30" t="n">
-        <v>103.1499071647465</v>
+        <v>190.2866497262488</v>
       </c>
       <c r="U30" t="n">
-        <v>1.259412035050019</v>
+        <v>9.000641043542675</v>
       </c>
       <c r="V30" t="n">
-        <v>0.4700894335300845</v>
-      </c>
-      <c r="W30" t="b">
+        <v>102.4941497852762</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.527953689510639</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.4700886945716061</v>
+      </c>
+      <c r="Y30" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2672,54 +2856,60 @@
         <v>0.9357121586799622</v>
       </c>
       <c r="G31" t="n">
+        <v>0.03220909996889532</v>
+      </c>
+      <c r="H31" t="n">
         <v>0.0002481373958289623</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>948.4170994745834</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>189.5951259527817</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>5.684341886080801e-13</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>1.4210854715202e-13</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>2.684728284674931</v>
       </c>
-      <c r="N31" t="b">
-        <v>1</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0.5973597168922424</v>
+      <c r="O31" t="b">
+        <v>1</v>
       </c>
       <c r="P31" t="n">
-        <v>0.000136012036819011</v>
+        <v>0.6217303276062012</v>
       </c>
       <c r="Q31" t="n">
-        <v>949.1320697827482</v>
+        <v>0.1601867999415845</v>
       </c>
       <c r="R31" t="n">
-        <v>190.3090014250181</v>
+        <v>0.0001532512833364308</v>
       </c>
       <c r="S31" t="n">
+        <v>947.7505152783879</v>
+      </c>
+      <c r="T31" t="n">
+        <v>190.0674318579549</v>
+      </c>
+      <c r="U31" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T31" t="n">
-        <v>0.7149703081641974</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0.7138754722365377</v>
-      </c>
       <c r="V31" t="n">
+        <v>0.6665841961961405</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.4723059051732719</v>
+      </c>
+      <c r="X31" t="n">
         <v>2.684728284674931</v>
       </c>
-      <c r="W31" t="b">
+      <c r="Y31" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2745,54 +2935,60 @@
         <v>0.9438311457633972</v>
       </c>
       <c r="G32" t="n">
+        <v>0.1825534000527114</v>
+      </c>
+      <c r="H32" t="n">
         <v>0.0007830621325410903</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>857.2842430817823</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>176.1732571575571</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>9.181216882346309</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>75.71823841586968</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>34.85752379430758</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>4.648185189637388e-05</v>
       </c>
-      <c r="N32" t="b">
-        <v>1</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.9999220371246338</v>
+      <c r="O32" t="b">
+        <v>1</v>
       </c>
       <c r="P32" t="n">
-        <v>0.0009473156533204019</v>
+        <v>0.9996411800384521</v>
       </c>
       <c r="Q32" t="n">
-        <v>808.3780025139052</v>
+        <v>0.5782287002075464</v>
       </c>
       <c r="R32" t="n">
-        <v>150.000552462468</v>
+        <v>0.005348614417016506</v>
       </c>
       <c r="S32" t="n">
-        <v>9.060269515117977</v>
+        <v>800.0002277231252</v>
       </c>
       <c r="T32" t="n">
-        <v>124.6244789837467</v>
+        <v>163.4818743007253</v>
       </c>
       <c r="U32" t="n">
-        <v>8.684819099218458</v>
+        <v>9.00053848542133</v>
       </c>
       <c r="V32" t="n">
-        <v>0.120900885376436</v>
-      </c>
-      <c r="W32" t="b">
+        <v>133.0022537745267</v>
+      </c>
+      <c r="W32" t="n">
+        <v>22.16614093747577</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.1806319150730822</v>
+      </c>
+      <c r="Y32" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2818,54 +3014,60 @@
         <v>0.985556423664093</v>
       </c>
       <c r="G33" t="n">
+        <v>0.09795870003290474</v>
+      </c>
+      <c r="H33" t="n">
         <v>0.000411912944400683</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>940.8724259033206</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>209.7582135058447</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>9.000792066771698</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>71.25859576572986</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>4.559254057312501e-05</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>2.14915384471342</v>
       </c>
-      <c r="N33" t="b">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0.9940339922904968</v>
+      <c r="O33" t="b">
+        <v>1</v>
       </c>
       <c r="P33" t="n">
-        <v>0.0005393409519456327</v>
+        <v>0.9838081002235413</v>
       </c>
       <c r="Q33" t="n">
-        <v>937.231212664414</v>
+        <v>0.4712052999529988</v>
       </c>
       <c r="R33" t="n">
-        <v>209.3073512554583</v>
+        <v>0.0005023063858971</v>
       </c>
       <c r="S33" t="n">
-        <v>9.000641839176451</v>
+        <v>933.264643307288</v>
       </c>
       <c r="T33" t="n">
-        <v>67.61738252682323</v>
+        <v>209.2747428184135</v>
       </c>
       <c r="U33" t="n">
-        <v>0.450907842926938</v>
+        <v>9.000641898956975</v>
       </c>
       <c r="V33" t="n">
-        <v>2.149003617118173</v>
-      </c>
-      <c r="W33" t="b">
+        <v>63.65081316969724</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.4835162799717239</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.149003676898697</v>
+      </c>
+      <c r="Y33" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2891,54 +3093,60 @@
         <v>0.6023518443107605</v>
       </c>
       <c r="G34" t="n">
+        <v>0.1382859998848289</v>
+      </c>
+      <c r="H34" t="n">
         <v>0.0004035303718410432</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>940.8700877632323</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>195.4663604418713</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>9.00064169072197</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>30.86981896943814</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>0.0001075287231344646</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>2.490947005769868</v>
       </c>
-      <c r="N34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0.7095156908035278</v>
+      <c r="O34" t="b">
+        <v>1</v>
       </c>
       <c r="P34" t="n">
-        <v>0.0002230912650702521</v>
+        <v>0.6133726835250854</v>
       </c>
       <c r="Q34" t="n">
-        <v>940.9225514289294</v>
+        <v>0.4593996000476182</v>
       </c>
       <c r="R34" t="n">
-        <v>195.5942420968957</v>
+        <v>0.0002281493070768192</v>
       </c>
       <c r="S34" t="n">
-        <v>9.000641738451689</v>
+        <v>939.4492613408485</v>
       </c>
       <c r="T34" t="n">
-        <v>30.92228263513528</v>
+        <v>195.9748062809168</v>
       </c>
       <c r="U34" t="n">
-        <v>0.1279891837475304</v>
+        <v>9.000641563843633</v>
       </c>
       <c r="V34" t="n">
-        <v>2.490947053499587</v>
-      </c>
-      <c r="W34" t="b">
+        <v>29.44899254705433</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.5085533677685987</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.490946878891531</v>
+      </c>
+      <c r="Y34" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2964,54 +3172,60 @@
         <v>0.5389013886451721</v>
       </c>
       <c r="G35" t="n">
+        <v>0.02640870003961027</v>
+      </c>
+      <c r="H35" t="n">
         <v>0.000253292266279459</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>944.2477137625023</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>202.9110208185284</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>7.958078640513122e-13</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>6.338041202980094e-12</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>2.286850850919654</v>
       </c>
-      <c r="N35" t="b">
-        <v>1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0.2857986986637115</v>
+      <c r="O35" t="b">
+        <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>6.801854760851711e-05</v>
+        <v>0.3045288920402527</v>
       </c>
       <c r="Q35" t="n">
-        <v>944.2045204081038</v>
+        <v>0.2004813998937607</v>
       </c>
       <c r="R35" t="n">
-        <v>202.6210047121934</v>
+        <v>7.947607809910551e-05</v>
       </c>
       <c r="S35" t="n">
+        <v>944.6974977412119</v>
+      </c>
+      <c r="T35" t="n">
+        <v>202.9457082362748</v>
+      </c>
+      <c r="U35" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T35" t="n">
-        <v>0.04319335439765837</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0.2900161063413123</v>
-      </c>
       <c r="V35" t="n">
+        <v>0.4497839787104567</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.03468741774014461</v>
+      </c>
+      <c r="X35" t="n">
         <v>2.286850850919654</v>
       </c>
-      <c r="W35" t="b">
+      <c r="Y35" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3037,54 +3251,60 @@
         <v>0.5939324498176575</v>
       </c>
       <c r="G36" t="n">
+        <v>0.04045010008849204</v>
+      </c>
+      <c r="H36" t="n">
         <v>0.000253947131568566</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>960.7595512215461</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>194.5526131976409</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>0.585050756947453</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>6.650680006714538e-12</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>2.08124050703609</v>
       </c>
-      <c r="N36" t="b">
-        <v>1</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0.2214724123477936</v>
+      <c r="O36" t="b">
+        <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>9.755695646163076e-05</v>
+        <v>0.2360904663801193</v>
       </c>
       <c r="Q36" t="n">
-        <v>954.8750935505767</v>
+        <v>0.2080049000214785</v>
       </c>
       <c r="R36" t="n">
-        <v>194.8541510484343</v>
+        <v>0.0001215048323501833</v>
       </c>
       <c r="S36" t="n">
+        <v>957.5335662314053</v>
+      </c>
+      <c r="T36" t="n">
+        <v>194.851063974719</v>
+      </c>
+      <c r="U36" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T36" t="n">
-        <v>5.299406914021915</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0.3015378507867013</v>
-      </c>
       <c r="V36" t="n">
+        <v>2.64093423319332</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.2984507770714231</v>
+      </c>
+      <c r="X36" t="n">
         <v>2.08124050703609</v>
       </c>
-      <c r="W36" t="b">
+      <c r="Y36" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3110,54 +3330,60 @@
         <v>0.8210803866386414</v>
       </c>
       <c r="G37" t="n">
+        <v>0.09326590015552938</v>
+      </c>
+      <c r="H37" t="n">
         <v>0.0004035303718410432</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>940.8700875246753</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>198.2877898279416</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>9.00064177013282</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>49.02855814581994</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>5.115907697472721e-12</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>1.448022623495367</v>
       </c>
-      <c r="N37" t="b">
-        <v>1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0.8353708982467651</v>
+      <c r="O37" t="b">
+        <v>1</v>
       </c>
       <c r="P37" t="n">
-        <v>0.0003396867250557989</v>
+        <v>0.8381036520004272</v>
       </c>
       <c r="Q37" t="n">
-        <v>938.2394138496758</v>
+        <v>0.4105590998660773</v>
       </c>
       <c r="R37" t="n">
-        <v>198.4891410057571</v>
+        <v>0.000336482422426343</v>
       </c>
       <c r="S37" t="n">
-        <v>9.000641792512026</v>
+        <v>936.2168014995145</v>
       </c>
       <c r="T37" t="n">
-        <v>46.39788447082037</v>
+        <v>198.8294999909633</v>
       </c>
       <c r="U37" t="n">
-        <v>0.2013511778206407</v>
+        <v>9.000641738259615</v>
       </c>
       <c r="V37" t="n">
-        <v>1.448022645874573</v>
-      </c>
-      <c r="W37" t="b">
+        <v>44.37527212065913</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.5417101630268348</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.448022591622163</v>
+      </c>
+      <c r="Y37" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3183,54 +3409,60 @@
         <v>0.8523421287536621</v>
       </c>
       <c r="G38" t="n">
+        <v>0.1240206998772919</v>
+      </c>
+      <c r="H38" t="n">
         <v>0.0009401811985298991</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>933.5317547573583</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>212.085043933552</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>9.140517219559058</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>62.96321286494447</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>4.831690603168681e-13</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>0.1681872685028711</v>
       </c>
-      <c r="N38" t="b">
-        <v>1</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0.8625028729438782</v>
+      <c r="O38" t="b">
+        <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>0.0005280999466776848</v>
+        <v>0.8575426936149597</v>
       </c>
       <c r="Q38" t="n">
-        <v>937.2163987752673</v>
+        <v>0.3820386999286711</v>
       </c>
       <c r="R38" t="n">
-        <v>211.6371636356351</v>
+        <v>0.0004938316997140646</v>
       </c>
       <c r="S38" t="n">
-        <v>9.041741678188288</v>
+        <v>932.952213117459</v>
       </c>
       <c r="T38" t="n">
-        <v>66.64785688285349</v>
+        <v>211.3056254021631</v>
       </c>
       <c r="U38" t="n">
-        <v>0.4478802979164698</v>
+        <v>9.057761658836251</v>
       </c>
       <c r="V38" t="n">
-        <v>0.06941172713210086</v>
-      </c>
-      <c r="W38" t="b">
+        <v>62.38367122504519</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.7794185313884725</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.0854317077800637</v>
+      </c>
+      <c r="Y38" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3256,54 +3488,60 @@
         <v>0.9430859684944153</v>
       </c>
       <c r="G39" t="n">
+        <v>0.03830570005811751</v>
+      </c>
+      <c r="H39" t="n">
         <v>0.0002567658957559615</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>983.8468877335921</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>194.8632000756561</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>3.914317091324392</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>2.077342742268229e-10</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>3.320403384713055</v>
       </c>
-      <c r="N39" t="b">
-        <v>1</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0.9402955770492554</v>
+      <c r="O39" t="b">
+        <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>0.0002447155711706728</v>
+        <v>0.9140621423721313</v>
       </c>
       <c r="Q39" t="n">
-        <v>970.4327363135158</v>
+        <v>0.1820610999129713</v>
       </c>
       <c r="R39" t="n">
-        <v>195.4047599117028</v>
+        <v>0.000236918858718127</v>
       </c>
       <c r="S39" t="n">
+        <v>975.537449388029</v>
+      </c>
+      <c r="T39" t="n">
+        <v>195.3430547812418</v>
+      </c>
+      <c r="U39" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T39" t="n">
-        <v>17.32846851140073</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0.5415598362544074</v>
-      </c>
       <c r="V39" t="n">
+        <v>12.22375543688747</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.4798547057934286</v>
+      </c>
+      <c r="X39" t="n">
         <v>3.320403384713055</v>
       </c>
-      <c r="W39" t="b">
+      <c r="Y39" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3329,54 +3567,60 @@
         <v>0.9287258982658386</v>
       </c>
       <c r="G40" t="n">
+        <v>0.1636351998895407</v>
+      </c>
+      <c r="H40" t="n">
         <v>0.001690759556367993</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>944.2003722545508</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>193.0366390264005</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>12.2293513262616</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>17.42526130415797</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>0.02229335758994466</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>2.47040345395717</v>
       </c>
-      <c r="N40" t="b">
-        <v>1</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0.9976328611373901</v>
+      <c r="O40" t="b">
+        <v>1</v>
       </c>
       <c r="P40" t="n">
-        <v>0.003201540093868971</v>
+        <v>0.9971678853034973</v>
       </c>
       <c r="Q40" t="n">
-        <v>942.6131840930096</v>
+        <v>0.888255099998787</v>
       </c>
       <c r="R40" t="n">
-        <v>195.2798984007391</v>
+        <v>0.004683330655097961</v>
       </c>
       <c r="S40" t="n">
-        <v>11.86594435661859</v>
+        <v>800.0002201244063</v>
       </c>
       <c r="T40" t="n">
-        <v>15.83807314261685</v>
+        <v>200.3216208356956</v>
       </c>
       <c r="U40" t="n">
-        <v>2.265552731928551</v>
+        <v>13.00764143304811</v>
       </c>
       <c r="V40" t="n">
-        <v>2.833810423600179</v>
-      </c>
-      <c r="W40" t="b">
+        <v>126.7748908259865</v>
+      </c>
+      <c r="W40" t="n">
+        <v>7.307275166885034</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.692113347170665</v>
+      </c>
+      <c r="Y40" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3402,54 +3646,60 @@
         <v>0.9571895003318787</v>
       </c>
       <c r="G41" t="n">
+        <v>0.1993780001066625</v>
+      </c>
+      <c r="H41" t="n">
         <v>0.001836215727962554</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>957.5903888236588</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>193.1433285014407</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>12.60945375558594</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>10.13343494803712</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>0.0002268543694015079</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>4.357316220184797</v>
       </c>
-      <c r="N41" t="b">
-        <v>1</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0.9999992847442627</v>
+      <c r="O41" t="b">
+        <v>1</v>
       </c>
       <c r="P41" t="n">
-        <v>0.006113273091614246</v>
+        <v>0.9999898672103882</v>
       </c>
       <c r="Q41" t="n">
-        <v>997.6463614792851</v>
+        <v>1.339986899867654</v>
       </c>
       <c r="R41" t="n">
-        <v>202.3419907418982</v>
+        <v>0.00730981444939971</v>
       </c>
       <c r="S41" t="n">
-        <v>12.39254106358857</v>
+        <v>800.0000284926539</v>
       </c>
       <c r="T41" t="n">
-        <v>29.92253770758919</v>
+        <v>203.669020157672</v>
       </c>
       <c r="U41" t="n">
-        <v>9.198889094826882</v>
+        <v>13.35077891675294</v>
       </c>
       <c r="V41" t="n">
-        <v>4.574228912182168</v>
-      </c>
-      <c r="W41" t="b">
+        <v>167.7237952790421</v>
+      </c>
+      <c r="W41" t="n">
+        <v>10.5259185106006</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3.6159910590178</v>
+      </c>
+      <c r="Y41" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3475,54 +3725,60 @@
         <v>0.8681793212890625</v>
       </c>
       <c r="G42" t="n">
+        <v>0.0932088999543339</v>
+      </c>
+      <c r="H42" t="n">
         <v>0.0009456591797061265</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>933.529305815971</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>201.2938789870477</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>9.221556844223198</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>62.34144131299468</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>1.4210854715202e-13</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>1.865174681370263e-13</v>
       </c>
-      <c r="N42" t="b">
-        <v>1</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0.7932679653167725</v>
+      <c r="O42" t="b">
+        <v>1</v>
       </c>
       <c r="P42" t="n">
-        <v>0.000482002884382382</v>
+        <v>0.7997660040855408</v>
       </c>
       <c r="Q42" t="n">
-        <v>929.4627165375941</v>
+        <v>0.3653216999955475</v>
       </c>
       <c r="R42" t="n">
-        <v>201.2974331655836</v>
+        <v>0.0004361179016996175</v>
       </c>
       <c r="S42" t="n">
-        <v>9.3355220125991</v>
+        <v>929.8362148659014</v>
       </c>
       <c r="T42" t="n">
-        <v>58.27485203461777</v>
+        <v>201.6343154739984</v>
       </c>
       <c r="U42" t="n">
-        <v>0.003554178536091968</v>
+        <v>9.307300075872964</v>
       </c>
       <c r="V42" t="n">
-        <v>0.1139651683760885</v>
-      </c>
-      <c r="W42" t="b">
+        <v>58.64835036292504</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.3404364869508925</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.08574323164995334</v>
+      </c>
+      <c r="Y42" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3548,54 +3804,60 @@
         <v>0.5367275476455688</v>
       </c>
       <c r="G43" t="n">
+        <v>0.09967649984173477</v>
+      </c>
+      <c r="H43" t="n">
         <v>0.0004035303718410432</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>940.8700882102418</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>191.4686898763189</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>9.000641570011767</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>30.12260204369329</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>1.688249540165998e-11</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2.084106363180322</v>
       </c>
-      <c r="N43" t="b">
-        <v>1</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0.6276092529296875</v>
+      <c r="O43" t="b">
+        <v>1</v>
       </c>
       <c r="P43" t="n">
-        <v>0.0002688669483177364</v>
+        <v>0.5337762832641602</v>
       </c>
       <c r="Q43" t="n">
-        <v>940.7493143942288</v>
+        <v>0.4129649000242352</v>
       </c>
       <c r="R43" t="n">
-        <v>192.0537798779237</v>
+        <v>0.0002367529814364389</v>
       </c>
       <c r="S43" t="n">
-        <v>9.000641489598474</v>
+        <v>940.8814856144299</v>
       </c>
       <c r="T43" t="n">
-        <v>30.00182822768033</v>
+        <v>192.1604870641244</v>
       </c>
       <c r="U43" t="n">
-        <v>0.5850900016217224</v>
+        <v>9.000641435401073</v>
       </c>
       <c r="V43" t="n">
-        <v>2.084106282767029</v>
-      </c>
-      <c r="W43" t="b">
+        <v>30.13399944788148</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.6917971878223739</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.084106228569628</v>
+      </c>
+      <c r="Y43" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3621,54 +3883,60 @@
         <v>0.5986339449882507</v>
       </c>
       <c r="G44" t="n">
+        <v>0.09465189999900758</v>
+      </c>
+      <c r="H44" t="n">
         <v>0.000411912944400683</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>940.8700876071158</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>205.3223585507395</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>9.000641771151603</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>46.18937051134981</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>2.842170943040401e-14</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>0.946334907059672</v>
       </c>
-      <c r="N44" t="b">
-        <v>1</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0.574456512928009</v>
+      <c r="O44" t="b">
+        <v>1</v>
       </c>
       <c r="P44" t="n">
-        <v>0.0003302170371171087</v>
+        <v>0.6484922766685486</v>
       </c>
       <c r="Q44" t="n">
-        <v>938.6620247693616</v>
+        <v>0.4573738998733461</v>
       </c>
       <c r="R44" t="n">
-        <v>204.4655777312656</v>
+        <v>0.0003097565786447376</v>
       </c>
       <c r="S44" t="n">
-        <v>9.000641545257663</v>
+        <v>935.8940877360927</v>
       </c>
       <c r="T44" t="n">
-        <v>43.98130767359555</v>
+        <v>205.3299235620032</v>
       </c>
       <c r="U44" t="n">
-        <v>0.8567808194738404</v>
+        <v>9.000641794909864</v>
       </c>
       <c r="V44" t="n">
-        <v>0.9463346811657321</v>
-      </c>
-      <c r="W44" t="b">
+        <v>41.21337064032673</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.007565011263693577</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.9463349308179332</v>
+      </c>
+      <c r="Y44" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3694,54 +3962,60 @@
         <v>0.9862354397773743</v>
       </c>
       <c r="G45" t="n">
+        <v>0.05248289997689426</v>
+      </c>
+      <c r="H45" t="n">
         <v>0.000275987054919824</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>935.8914960217039</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>198.357638409793</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>0.2809437084627007</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>2.310684976691846e-11</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>5.01752155194014</v>
       </c>
-      <c r="N45" t="b">
-        <v>1</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0.9986103773117065</v>
+      <c r="O45" t="b">
+        <v>1</v>
       </c>
       <c r="P45" t="n">
-        <v>8.306914241984487e-05</v>
+        <v>0.9840670824050903</v>
       </c>
       <c r="Q45" t="n">
-        <v>940.1894910089754</v>
+        <v>0.1879743000026792</v>
       </c>
       <c r="R45" t="n">
-        <v>198.5975637538426</v>
+        <v>9.787471935851499e-05</v>
       </c>
       <c r="S45" t="n">
+        <v>937.3600994753324</v>
+      </c>
+      <c r="T45" t="n">
+        <v>198.5015766118829</v>
+      </c>
+      <c r="U45" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T45" t="n">
-        <v>4.578938695734223</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0.2399253440265454</v>
-      </c>
       <c r="V45" t="n">
+        <v>1.749547162091176</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.1439382020668347</v>
+      </c>
+      <c r="X45" t="n">
         <v>5.01752155194014</v>
       </c>
-      <c r="W45" t="b">
+      <c r="Y45" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3767,54 +4041,60 @@
         <v>0.9871838092803955</v>
       </c>
       <c r="G46" t="n">
+        <v>0.08853010018356144</v>
+      </c>
+      <c r="H46" t="n">
         <v>0.001659385743550956</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>925.9037138259948</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>193.3079578136815</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>9.000641664806555</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>105.7527651555272</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>0.0001506232214865122</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>1.180885603381993</v>
       </c>
-      <c r="N46" t="b">
-        <v>1</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0.9938814640045166</v>
+      <c r="O46" t="b">
+        <v>1</v>
       </c>
       <c r="P46" t="n">
-        <v>0.0009672881569713354</v>
+        <v>0.9815143942832947</v>
       </c>
       <c r="Q46" t="n">
-        <v>932.5852889144468</v>
+        <v>0.4564521999564022</v>
       </c>
       <c r="R46" t="n">
-        <v>193.8467371367263</v>
+        <v>0.0009679677314125001</v>
       </c>
       <c r="S46" t="n">
-        <v>9.00064181636632</v>
+        <v>930.9860663106579</v>
       </c>
       <c r="T46" t="n">
-        <v>112.4343402439791</v>
+        <v>195.3302766870889</v>
       </c>
       <c r="U46" t="n">
-        <v>0.5386286998232777</v>
+        <v>9.000641477307619</v>
       </c>
       <c r="V46" t="n">
-        <v>1.180885754941759</v>
-      </c>
-      <c r="W46" t="b">
+        <v>110.8351176401902</v>
+      </c>
+      <c r="W46" t="n">
+        <v>2.022168250185899</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.180885415883058</v>
+      </c>
+      <c r="Y46" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3840,54 +4120,60 @@
         <v>0.7437790036201477</v>
       </c>
       <c r="G47" t="n">
+        <v>0.1021233999636024</v>
+      </c>
+      <c r="H47" t="n">
         <v>0.000411912944400683</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>940.8726226535753</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>210.507934973459</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>9.000565823278913</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>59.43579317790068</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>3.126388037344441e-13</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>0.3166821046588044</v>
       </c>
-      <c r="N47" t="b">
-        <v>1</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0.7713530659675598</v>
+      <c r="O47" t="b">
+        <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>0.0004413022543303668</v>
+        <v>0.7974120378494263</v>
       </c>
       <c r="Q47" t="n">
-        <v>938.5293567094973</v>
+        <v>0.4211554999928921</v>
       </c>
       <c r="R47" t="n">
-        <v>210.1331971044325</v>
+        <v>0.0004132960748393089</v>
       </c>
       <c r="S47" t="n">
-        <v>9.000641817535367</v>
+        <v>934.541737117346</v>
       </c>
       <c r="T47" t="n">
-        <v>57.09252723382269</v>
+        <v>210.0103203519259</v>
       </c>
       <c r="U47" t="n">
-        <v>0.374737869026859</v>
+        <v>9.000641644275618</v>
       </c>
       <c r="V47" t="n">
-        <v>0.3167580989152583</v>
-      </c>
-      <c r="W47" t="b">
+        <v>53.10490764167139</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.4976146215335007</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.3167579256555086</v>
+      </c>
+      <c r="Y47" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3913,54 +4199,60 @@
         <v>0.9884505271911621</v>
       </c>
       <c r="G48" t="n">
+        <v>0.1680437000468373</v>
+      </c>
+      <c r="H48" t="n">
         <v>0.001565012848004699</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>925.904175032681</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>206.4751248904578</v>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>9.000641775249187</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>87.40834290626822</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
         <v>0.5694505241451964</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>2.576074828285974</v>
       </c>
-      <c r="N48" t="b">
-        <v>1</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0.9993426203727722</v>
+      <c r="O48" t="b">
+        <v>1</v>
       </c>
       <c r="P48" t="n">
-        <v>0.0008612173842266202</v>
+        <v>0.9956574440002441</v>
       </c>
       <c r="Q48" t="n">
-        <v>931.7496615487512</v>
+        <v>0.4644058998674154</v>
       </c>
       <c r="R48" t="n">
-        <v>203.1123440504731</v>
+        <v>0.0007579441298730671</v>
       </c>
       <c r="S48" t="n">
-        <v>9.000641776003501</v>
+        <v>930.640624929596</v>
       </c>
       <c r="T48" t="n">
-        <v>93.25382942233841</v>
+        <v>205.890373325238</v>
       </c>
       <c r="U48" t="n">
-        <v>2.793330315839455</v>
+        <v>9.000641825775205</v>
       </c>
       <c r="V48" t="n">
-        <v>2.576074829040288</v>
-      </c>
-      <c r="W48" t="b">
+        <v>92.14479280318324</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0.01530104107459351</v>
+      </c>
+      <c r="X48" t="n">
+        <v>2.576074878811991</v>
+      </c>
+      <c r="Y48" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3986,54 +4278,60 @@
         <v>0.9624367356300354</v>
       </c>
       <c r="G49" t="n">
+        <v>0.1341595000121742</v>
+      </c>
+      <c r="H49" t="n">
         <v>0.00113704486284405</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>933.5293046828175</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>202.0291270286342</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>9.000641646246294</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>65.044079171416</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>0.9301339407832927</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>0.7079495635160065</v>
       </c>
-      <c r="N49" t="b">
-        <v>1</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0.9565010666847229</v>
+      <c r="O49" t="b">
+        <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>0.0005720136105082929</v>
+        <v>0.9446417689323425</v>
       </c>
       <c r="Q49" t="n">
-        <v>934.3204597322963</v>
+        <v>0.4727296999190003</v>
       </c>
       <c r="R49" t="n">
-        <v>202.8428408865294</v>
+        <v>0.0005008716252632439</v>
       </c>
       <c r="S49" t="n">
-        <v>9.000641793594395</v>
+        <v>933.1467706639318</v>
       </c>
       <c r="T49" t="n">
-        <v>65.83523422089479</v>
+        <v>203.2542928508576</v>
       </c>
       <c r="U49" t="n">
-        <v>0.116420082888169</v>
+        <v>9.000641849400719</v>
       </c>
       <c r="V49" t="n">
-        <v>0.7079497108641082</v>
-      </c>
-      <c r="W49" t="b">
+        <v>64.66154515253027</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.2950318814400248</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0.7079497666704313</v>
+      </c>
+      <c r="Y49" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4059,54 +4357,60 @@
         <v>0.9600974917411804</v>
       </c>
       <c r="G50" t="n">
+        <v>0.0292609001044184</v>
+      </c>
+      <c r="H50" t="n">
         <v>0.000253947131568566</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>979.1832198837656</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>209.913731913648</v>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>8.29913915367797e-12</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>3.410605131648481e-13</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>2.959625702918892</v>
       </c>
-      <c r="N50" t="b">
-        <v>1</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0.6635180711746216</v>
+      <c r="O50" t="b">
+        <v>1</v>
       </c>
       <c r="P50" t="n">
-        <v>0.0002802814706228673</v>
+        <v>0.74163419008255</v>
       </c>
       <c r="Q50" t="n">
-        <v>962.2228492949848</v>
+        <v>0.1970645999535918</v>
       </c>
       <c r="R50" t="n">
-        <v>209.0336145198863</v>
+        <v>0.0001582434924785048</v>
       </c>
       <c r="S50" t="n">
+        <v>972.0490611198499</v>
+      </c>
+      <c r="T50" t="n">
+        <v>209.7024953339797</v>
+      </c>
+      <c r="U50" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T50" t="n">
-        <v>16.96037058878903</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0.8801173937620206</v>
-      </c>
       <c r="V50" t="n">
+        <v>7.134158763924006</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.2112365796685935</v>
+      </c>
+      <c r="X50" t="n">
         <v>2.959625702918892</v>
       </c>
-      <c r="W50" t="b">
+      <c r="Y50" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4132,54 +4436,60 @@
         <v>0.9850831031799316</v>
       </c>
       <c r="G51" t="n">
+        <v>0.03760640020482242</v>
+      </c>
+      <c r="H51" t="n">
         <v>0.000253947131568566</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>976.2856368605152</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>200.1675935669443</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>7.526068657170981e-11</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
         <v>1.534772309241816e-11</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>5.392436175342905</v>
       </c>
-      <c r="N51" t="b">
-        <v>1</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0.9998348951339722</v>
+      <c r="O51" t="b">
+        <v>1</v>
       </c>
       <c r="P51" t="n">
-        <v>0.0001455066521884874</v>
+        <v>0.9971093535423279</v>
       </c>
       <c r="Q51" t="n">
-        <v>966.6650389299334</v>
+        <v>0.2056935001164675</v>
       </c>
       <c r="R51" t="n">
-        <v>199.5008290252252</v>
+        <v>0.0001439207553630695</v>
       </c>
       <c r="S51" t="n">
+        <v>969.8804372788995</v>
+      </c>
+      <c r="T51" t="n">
+        <v>200.3478326256698</v>
+      </c>
+      <c r="U51" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T51" t="n">
-        <v>9.620597930657027</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0.6667645417344659</v>
-      </c>
       <c r="V51" t="n">
+        <v>6.405199581690908</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0.1802390587101286</v>
+      </c>
+      <c r="X51" t="n">
         <v>5.392436175342905</v>
       </c>
-      <c r="W51" t="b">
+      <c r="Y51" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4205,54 +4515,60 @@
         <v>0.947009265422821</v>
       </c>
       <c r="G52" t="n">
+        <v>0.09620709996670485</v>
+      </c>
+      <c r="H52" t="n">
         <v>0.000411912944400683</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>940.8731615347237</v>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>204.2154180932891</v>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>9.000819739421681</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
         <v>61.30329765647537</v>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
         <v>3.126388037344441e-13</v>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
         <v>1.481763026454068</v>
       </c>
-      <c r="N52" t="b">
-        <v>1</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0.9585382342338562</v>
+      <c r="O52" t="b">
+        <v>1</v>
       </c>
       <c r="P52" t="n">
-        <v>0.0004808686499018222</v>
+        <v>0.9488450288772583</v>
       </c>
       <c r="Q52" t="n">
-        <v>935.4956827664361</v>
+        <v>0.4507665999699384</v>
       </c>
       <c r="R52" t="n">
-        <v>202.8839473154934</v>
+        <v>0.000417387462221086</v>
       </c>
       <c r="S52" t="n">
-        <v>9.000641085506452</v>
+        <v>934.1464328812875</v>
       </c>
       <c r="T52" t="n">
-        <v>55.92581888818768</v>
+        <v>204.345254477297</v>
       </c>
       <c r="U52" t="n">
-        <v>1.331470777795431</v>
+        <v>9.000641739095107</v>
       </c>
       <c r="V52" t="n">
-        <v>1.481584372538839</v>
-      </c>
-      <c r="W52" t="b">
+        <v>54.57656900303914</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.1298363840082288</v>
+      </c>
+      <c r="X52" t="n">
+        <v>1.481585026127494</v>
+      </c>
+      <c r="Y52" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4278,54 +4594,60 @@
         <v>0.9875456690788269</v>
       </c>
       <c r="G53" t="n">
+        <v>0.102502099936828</v>
+      </c>
+      <c r="H53" t="n">
         <v>0.001542833168059587</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>925.9037154494032</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>201.315813711462</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>9.000641710553122</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>80.63936698153111</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>2.543742994021159e-11</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>2.519554879297776</v>
       </c>
-      <c r="N53" t="b">
-        <v>1</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0.9990785121917725</v>
+      <c r="O53" t="b">
+        <v>1</v>
       </c>
       <c r="P53" t="n">
-        <v>0.0007722207228653133</v>
+        <v>0.9952842593193054</v>
       </c>
       <c r="Q53" t="n">
-        <v>932.4366476622735</v>
+        <v>0.4609359998721629</v>
       </c>
       <c r="R53" t="n">
-        <v>202.3069924400194</v>
+        <v>0.0006976982112973928</v>
       </c>
       <c r="S53" t="n">
-        <v>9.000641766265922</v>
+        <v>931.3627951638401</v>
       </c>
       <c r="T53" t="n">
-        <v>87.17229919440138</v>
+        <v>201.9354166860134</v>
       </c>
       <c r="U53" t="n">
-        <v>0.9911787285828098</v>
+        <v>9.00064169824771</v>
       </c>
       <c r="V53" t="n">
-        <v>2.519554935010576</v>
-      </c>
-      <c r="W53" t="b">
+        <v>86.09844669596805</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.6196029745768215</v>
+      </c>
+      <c r="X53" t="n">
+        <v>2.519554866992364</v>
+      </c>
+      <c r="Y53" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4351,54 +4673,60 @@
         <v>0.9508481621742249</v>
       </c>
       <c r="G54" t="n">
+        <v>0.109625699929893</v>
+      </c>
+      <c r="H54" t="n">
         <v>0.000411912944400683</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>940.8711689760428</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>211.0666041718132</v>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>9.000790958495239</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
         <v>71.66344011740989</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
         <v>1.392663762089796e-12</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>0.8442183601889521</v>
       </c>
-      <c r="N54" t="b">
-        <v>1</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0.9606555700302124</v>
+      <c r="O54" t="b">
+        <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>0.0005422459216788411</v>
+        <v>0.9481151700019836</v>
       </c>
       <c r="Q54" t="n">
-        <v>937.3466056090383</v>
+        <v>0.4499967000447214</v>
       </c>
       <c r="R54" t="n">
-        <v>210.6104757333097</v>
+        <v>0.0005092869978398085</v>
       </c>
       <c r="S54" t="n">
-        <v>9.000641828255763</v>
+        <v>933.3542961488367</v>
       </c>
       <c r="T54" t="n">
-        <v>68.13887675040542</v>
+        <v>210.4210290306728</v>
       </c>
       <c r="U54" t="n">
-        <v>0.4561284385048907</v>
+        <v>9.000641818799471</v>
       </c>
       <c r="V54" t="n">
-        <v>0.8440692299494756</v>
-      </c>
-      <c r="W54" t="b">
+        <v>64.14656729020385</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0.6455751411417907</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0.8440692204931839</v>
+      </c>
+      <c r="Y54" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4424,54 +4752,60 @@
         <v>0.9797565340995789</v>
       </c>
       <c r="G55" t="n">
+        <v>0.1500470999162644</v>
+      </c>
+      <c r="H55" t="n">
         <v>0.003873131237924099</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>934.2940845470123</v>
       </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
         <v>207.3980148487063</v>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>12.60851163809747</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>19.80402322683813</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>8.526512829121202e-14</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>1.004885601283739</v>
       </c>
-      <c r="N55" t="b">
-        <v>1</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0.7573673129081726</v>
+      <c r="O55" t="b">
+        <v>1</v>
       </c>
       <c r="P55" t="n">
-        <v>0.003130298340693116</v>
+        <v>0.8356514573097229</v>
       </c>
       <c r="Q55" t="n">
-        <v>991.18655346703</v>
+        <v>0.7901467999909073</v>
       </c>
       <c r="R55" t="n">
-        <v>211.8481165997178</v>
+        <v>0.00290088402107358</v>
       </c>
       <c r="S55" t="n">
-        <v>12.27486805864158</v>
+        <v>817.3886717370838</v>
       </c>
       <c r="T55" t="n">
-        <v>37.08844569317955</v>
+        <v>212.0985549420784</v>
       </c>
       <c r="U55" t="n">
-        <v>4.450101751011402</v>
+        <v>12.54391379621714</v>
       </c>
       <c r="V55" t="n">
-        <v>1.338529180739631</v>
-      </c>
-      <c r="W55" t="b">
+        <v>136.7094360367666</v>
+      </c>
+      <c r="W55" t="n">
+        <v>4.700540093371984</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1.069483443164074</v>
+      </c>
+      <c r="Y55" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4497,54 +4831,60 @@
         <v>0.9017484784126282</v>
       </c>
       <c r="G56" t="n">
+        <v>0.2738896999508142</v>
+      </c>
+      <c r="H56" t="n">
         <v>0.006988451816141605</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>963.2227555194617</v>
       </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
         <v>168.5515212074577</v>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
         <v>12.31551705382621</v>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" t="n">
         <v>31.49192711210605</v>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
         <v>28.0725871093203</v>
       </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
         <v>0.09755748729765834</v>
       </c>
-      <c r="N56" t="b">
-        <v>1</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0.9999312162399292</v>
+      <c r="O56" t="b">
+        <v>1</v>
       </c>
       <c r="P56" t="n">
-        <v>0.001832844573073089</v>
+        <v>0.9996423721313477</v>
       </c>
       <c r="Q56" t="n">
-        <v>800.0000091408048</v>
+        <v>0.8811459001153708</v>
       </c>
       <c r="R56" t="n">
-        <v>152.9628440298373</v>
+        <v>0.004668192472308874</v>
       </c>
       <c r="S56" t="n">
-        <v>11.98061332445481</v>
+        <v>800.0026144488385</v>
       </c>
       <c r="T56" t="n">
-        <v>131.7308192665508</v>
+        <v>163.8678534604791</v>
       </c>
       <c r="U56" t="n">
-        <v>12.48390993169988</v>
+        <v>12.5217953236076</v>
       </c>
       <c r="V56" t="n">
-        <v>0.2373462420737376</v>
-      </c>
-      <c r="W56" t="b">
+        <v>131.7282139585171</v>
+      </c>
+      <c r="W56" t="n">
+        <v>23.38891936234174</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0.3038357570790513</v>
+      </c>
+      <c r="Y56" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4570,54 +4910,60 @@
         <v>0.9745776653289795</v>
       </c>
       <c r="G57" t="n">
+        <v>0.1248651000205427</v>
+      </c>
+      <c r="H57" t="n">
         <v>0.0004035303718410432</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>940.8751706479679</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>188.766031281211</v>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>9.000712603548521</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>83.57572259989661</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>0.1860447587924625</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>0.7900141725393404</v>
       </c>
-      <c r="N57" t="b">
-        <v>1</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0.9783176183700562</v>
+      <c r="O57" t="b">
+        <v>1</v>
       </c>
       <c r="P57" t="n">
-        <v>0.0006282278918661177</v>
+        <v>0.9656620621681213</v>
       </c>
       <c r="Q57" t="n">
-        <v>935.9869932756089</v>
+        <v>0.4027561000548303</v>
       </c>
       <c r="R57" t="n">
-        <v>189.7997976671825</v>
+        <v>0.0006545205833390355</v>
       </c>
       <c r="S57" t="n">
-        <v>9.000641716806388</v>
+        <v>935.2017420516025</v>
       </c>
       <c r="T57" t="n">
-        <v>78.68754522753761</v>
+        <v>190.8081041314765</v>
       </c>
       <c r="U57" t="n">
-        <v>0.8477216271789985</v>
+        <v>9.00064112700305</v>
       </c>
       <c r="V57" t="n">
-        <v>0.7899432857972073</v>
-      </c>
-      <c r="W57" t="b">
+        <v>77.90229400353121</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.856028091473064</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0.7899426959938687</v>
+      </c>
+      <c r="Y57" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4643,54 +4989,60 @@
         <v>0.7210264205932617</v>
       </c>
       <c r="G58" t="n">
+        <v>0.09566040011122823</v>
+      </c>
+      <c r="H58" t="n">
         <v>0.0001128785734181292</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>985.893777989925</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>202.610868033151</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>9.017888444486854</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>24.38208766443495</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>5.442845755965209e-05</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>0</v>
       </c>
-      <c r="N58" t="b">
-        <v>1</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0.2172415405511856</v>
+      <c r="O58" t="b">
+        <v>1</v>
       </c>
       <c r="P58" t="n">
-        <v>0.0001713034143904224</v>
+        <v>0.2366334348917007</v>
       </c>
       <c r="Q58" t="n">
-        <v>970.7350899870861</v>
+        <v>0.4110938000958413</v>
       </c>
       <c r="R58" t="n">
-        <v>202.0518413661979</v>
+        <v>0.0001672586222412065</v>
       </c>
       <c r="S58" t="n">
-        <v>9.016835065698935</v>
+        <v>974.440838332911</v>
       </c>
       <c r="T58" t="n">
-        <v>39.54077566727381</v>
+        <v>202.6419329655097</v>
       </c>
       <c r="U58" t="n">
-        <v>0.5590810954106757</v>
+        <v>9.021850999825135</v>
       </c>
       <c r="V58" t="n">
-        <v>0.001053378787919002</v>
-      </c>
-      <c r="W58" t="b">
+        <v>35.83502732144893</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0.03101050390111482</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0.003962555338281604</v>
+      </c>
+      <c r="Y58" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4716,54 +5068,60 @@
         <v>0.858593761920929</v>
       </c>
       <c r="G59" t="n">
+        <v>0.07592890015803277</v>
+      </c>
+      <c r="H59" t="n">
         <v>0.0002920783299487084</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>992.206710447728</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>206.6120925773116</v>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
         <v>15.1613506656073</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
         <v>8.810729923425242e-13</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>3.142187227191671</v>
       </c>
-      <c r="N59" t="b">
-        <v>1</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0.8841882944107056</v>
+      <c r="O59" t="b">
+        <v>1</v>
       </c>
       <c r="P59" t="n">
-        <v>0.000573034689296037</v>
+        <v>0.8498181104660034</v>
       </c>
       <c r="Q59" t="n">
-        <v>980.9178434157742</v>
+        <v>0.3698599999770522</v>
       </c>
       <c r="R59" t="n">
-        <v>204.8738046546223</v>
+        <v>0.0003315290668979287</v>
       </c>
       <c r="S59" t="n">
-        <v>9.000628038949028</v>
+        <v>986.0960167255304</v>
       </c>
       <c r="T59" t="n">
-        <v>26.45021769756113</v>
+        <v>206.5822911850829</v>
       </c>
       <c r="U59" t="n">
-        <v>1.738287922690148</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V59" t="n">
-        <v>3.142173486278536</v>
-      </c>
-      <c r="W59" t="b">
+        <v>21.27204438780495</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0.02980139222955813</v>
+      </c>
+      <c r="X59" t="n">
+        <v>3.142187227191671</v>
+      </c>
+      <c r="Y59" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4789,54 +5147,60 @@
         <v>0.8984211683273315</v>
       </c>
       <c r="G60" t="n">
+        <v>0.03001679992303252</v>
+      </c>
+      <c r="H60" t="n">
         <v>0.0002481373958289623</v>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>952.8683526134881</v>
       </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
         <v>193.0425995540116</v>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>1.414264261256903e-10</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
         <v>7.986500349943526e-12</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>3.210234609064206</v>
       </c>
-      <c r="N60" t="b">
-        <v>1</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0.8999966979026794</v>
+      <c r="O60" t="b">
+        <v>1</v>
       </c>
       <c r="P60" t="n">
-        <v>9.054003749042749e-05</v>
+        <v>0.8788536787033081</v>
       </c>
       <c r="Q60" t="n">
-        <v>951.3724997507622</v>
+        <v>0.1619484999682754</v>
       </c>
       <c r="R60" t="n">
-        <v>193.3197302100868</v>
+        <v>0.0001215683951159008</v>
       </c>
       <c r="S60" t="n">
+        <v>951.6040102210409</v>
+      </c>
+      <c r="T60" t="n">
+        <v>193.3690622465273</v>
+      </c>
+      <c r="U60" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T60" t="n">
-        <v>1.495852862867309</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0.2771306560672144</v>
-      </c>
       <c r="V60" t="n">
+        <v>1.264342392588674</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0.3264626925076755</v>
+      </c>
+      <c r="X60" t="n">
         <v>3.210234609064206</v>
       </c>
-      <c r="W60" t="b">
+      <c r="Y60" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4862,54 +5226,60 @@
         <v>0.7833482623100281</v>
       </c>
       <c r="G61" t="n">
+        <v>0.03666280000470579</v>
+      </c>
+      <c r="H61" t="n">
         <v>0.0002815423358697444</v>
       </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
         <v>924.8299017867786</v>
       </c>
-      <c r="I61" t="n">
+      <c r="J61" t="n">
         <v>195.1662686173202</v>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K61" t="n">
+      <c r="L61" t="n">
         <v>2.852402758435346e-10</v>
       </c>
-      <c r="L61" t="n">
+      <c r="M61" t="n">
         <v>3.021227712451946e-11</v>
       </c>
-      <c r="M61" t="n">
+      <c r="N61" t="n">
         <v>3.46624564339104</v>
       </c>
-      <c r="N61" t="b">
-        <v>1</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0.8357070088386536</v>
+      <c r="O61" t="b">
+        <v>1</v>
       </c>
       <c r="P61" t="n">
-        <v>0.0001572461769683287</v>
+        <v>0.7623541355133057</v>
       </c>
       <c r="Q61" t="n">
-        <v>933.4096860014398</v>
+        <v>0.1922165001742542</v>
       </c>
       <c r="R61" t="n">
-        <v>195.6067456782189</v>
+        <v>0.0001406157243764028</v>
       </c>
       <c r="S61" t="n">
+        <v>928.8007711442121</v>
+      </c>
+      <c r="T61" t="n">
+        <v>195.4196728769813</v>
+      </c>
+      <c r="U61" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T61" t="n">
-        <v>8.579784214946471</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0.4404770608684885</v>
-      </c>
       <c r="V61" t="n">
+        <v>3.970869357718811</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0.2534042596309689</v>
+      </c>
+      <c r="X61" t="n">
         <v>3.46624564339104</v>
       </c>
-      <c r="W61" t="b">
+      <c r="Y61" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4935,54 +5305,60 @@
         <v>0.8887342810630798</v>
       </c>
       <c r="G62" t="n">
+        <v>0.02656169980764389</v>
+      </c>
+      <c r="H62" t="n">
         <v>0.0002782602678053081</v>
       </c>
-      <c r="H62" t="n">
+      <c r="I62" t="n">
         <v>930.7910609201529</v>
       </c>
-      <c r="I62" t="n">
+      <c r="J62" t="n">
         <v>196.7342250164554</v>
       </c>
-      <c r="J62" t="n">
+      <c r="K62" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K62" t="n">
+      <c r="L62" t="n">
         <v>1.695070750429295e-10</v>
       </c>
-      <c r="L62" t="n">
+      <c r="M62" t="n">
         <v>3.100748699580436e-06</v>
       </c>
-      <c r="M62" t="n">
+      <c r="N62" t="n">
         <v>3.419179935513551</v>
       </c>
-      <c r="N62" t="b">
-        <v>1</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0.8975760936737061</v>
+      <c r="O62" t="b">
+        <v>1</v>
       </c>
       <c r="P62" t="n">
-        <v>0.0001132614415837452</v>
+        <v>0.8324795961380005</v>
       </c>
       <c r="Q62" t="n">
-        <v>937.0014956331149</v>
+        <v>0.1943131000734866</v>
       </c>
       <c r="R62" t="n">
-        <v>197.0572972587113</v>
+        <v>0.0001143808767665178</v>
       </c>
       <c r="S62" t="n">
+        <v>933.4396689896248</v>
+      </c>
+      <c r="T62" t="n">
+        <v>196.9257671723956</v>
+      </c>
+      <c r="U62" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T62" t="n">
-        <v>6.210434712792562</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0.323069141507176</v>
-      </c>
       <c r="V62" t="n">
+        <v>2.648608069302441</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0.1915390551914413</v>
+      </c>
+      <c r="X62" t="n">
         <v>3.419179935513551</v>
       </c>
-      <c r="W62" t="b">
+      <c r="Y62" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5008,54 +5384,60 @@
         <v>0.9867919683456421</v>
       </c>
       <c r="G63" t="n">
+        <v>0.1151899001561105</v>
+      </c>
+      <c r="H63" t="n">
         <v>0.0004035303718410432</v>
       </c>
-      <c r="H63" t="n">
+      <c r="I63" t="n">
         <v>940.870088731476</v>
       </c>
-      <c r="I63" t="n">
+      <c r="J63" t="n">
         <v>191.7940433259601</v>
       </c>
-      <c r="J63" t="n">
+      <c r="K63" t="n">
         <v>9.000790976912986</v>
       </c>
-      <c r="K63" t="n">
+      <c r="L63" t="n">
         <v>79.33711413934179</v>
       </c>
-      <c r="L63" t="n">
+      <c r="M63" t="n">
         <v>3.581135388230905e-12</v>
       </c>
-      <c r="M63" t="n">
+      <c r="N63" t="n">
         <v>1.790258050540842</v>
       </c>
-      <c r="N63" t="b">
-        <v>1</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0.9944410920143127</v>
+      <c r="O63" t="b">
+        <v>1</v>
       </c>
       <c r="P63" t="n">
-        <v>0.0005870770546607673</v>
+        <v>0.9867004752159119</v>
       </c>
       <c r="Q63" t="n">
-        <v>935.7631255584643</v>
+        <v>0.454731100006029</v>
       </c>
       <c r="R63" t="n">
-        <v>192.6067966181187</v>
+        <v>0.0005976100801490247</v>
       </c>
       <c r="S63" t="n">
-        <v>9.000641753231061</v>
+        <v>934.6160318650626</v>
       </c>
       <c r="T63" t="n">
-        <v>74.23015096633003</v>
+        <v>193.3036917354937</v>
       </c>
       <c r="U63" t="n">
-        <v>0.8127532921621707</v>
+        <v>9.000641490074365</v>
       </c>
       <c r="V63" t="n">
-        <v>1.790108826858917</v>
-      </c>
-      <c r="W63" t="b">
+        <v>73.08305727292839</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1.509648409537249</v>
+      </c>
+      <c r="X63" t="n">
+        <v>1.790108563702221</v>
+      </c>
+      <c r="Y63" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5081,54 +5463,60 @@
         <v>0.941252589225769</v>
       </c>
       <c r="G64" t="n">
+        <v>0.09081290010362864</v>
+      </c>
+      <c r="H64" t="n">
         <v>0.001797718345187604</v>
       </c>
-      <c r="H64" t="n">
+      <c r="I64" t="n">
         <v>920.0676024229934</v>
       </c>
-      <c r="I64" t="n">
+      <c r="J64" t="n">
         <v>199.9840388767092</v>
       </c>
-      <c r="J64" t="n">
+      <c r="K64" t="n">
         <v>9.438070172352452</v>
       </c>
-      <c r="K64" t="n">
+      <c r="L64" t="n">
         <v>107.1377914461879</v>
       </c>
-      <c r="L64" t="n">
+      <c r="M64" t="n">
         <v>1.70530256582424e-13</v>
       </c>
-      <c r="M64" t="n">
+      <c r="N64" t="n">
         <v>0.5107308676982996</v>
       </c>
-      <c r="N64" t="b">
-        <v>1</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0.951556921005249</v>
+      <c r="O64" t="b">
+        <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>0.001087722019292414</v>
+        <v>0.9043301343917847</v>
       </c>
       <c r="Q64" t="n">
-        <v>927.3972624839309</v>
+        <v>0.3562833999749273</v>
       </c>
       <c r="R64" t="n">
-        <v>200.88141034478</v>
+        <v>0.0009822093416005373</v>
       </c>
       <c r="S64" t="n">
-        <v>9.163684741342754</v>
+        <v>928.0534310903639</v>
       </c>
       <c r="T64" t="n">
-        <v>114.4674515071254</v>
+        <v>200.9851248252849</v>
       </c>
       <c r="U64" t="n">
-        <v>0.8973714680705882</v>
+        <v>9.107304461060796</v>
       </c>
       <c r="V64" t="n">
-        <v>0.2363454366886018</v>
-      </c>
-      <c r="W64" t="b">
+        <v>115.1236201135583</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.001085948575508</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0.1799651564066433</v>
+      </c>
+      <c r="Y64" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5154,54 +5542,60 @@
         <v>0.9844457507133484</v>
       </c>
       <c r="G65" t="n">
+        <v>0.2207776999566704</v>
+      </c>
+      <c r="H65" t="n">
         <v>0.0001908497797558084</v>
       </c>
-      <c r="H65" t="n">
+      <c r="I65" t="n">
         <v>937.9052154350181</v>
       </c>
-      <c r="I65" t="n">
+      <c r="J65" t="n">
         <v>176.1734342559908</v>
       </c>
-      <c r="J65" t="n">
+      <c r="K65" t="n">
         <v>10.79917135648461</v>
       </c>
-      <c r="K65" t="n">
+      <c r="L65" t="n">
         <v>1.104295697950079</v>
       </c>
-      <c r="L65" t="n">
+      <c r="M65" t="n">
         <v>45.72864170994379</v>
       </c>
-      <c r="M65" t="n">
+      <c r="N65" t="n">
         <v>0.001164051527615229</v>
       </c>
-      <c r="N65" t="b">
-        <v>1</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0.9999996423721313</v>
+      <c r="O65" t="b">
+        <v>1</v>
       </c>
       <c r="P65" t="n">
-        <v>0.001466728397645056</v>
+        <v>0.9999833106994629</v>
       </c>
       <c r="Q65" t="n">
-        <v>800.0001507079837</v>
+        <v>1.201422299956903</v>
       </c>
       <c r="R65" t="n">
-        <v>150.000552917753</v>
+        <v>0.008305249735713005</v>
       </c>
       <c r="S65" t="n">
-        <v>10.63746911898502</v>
+        <v>800.0000302218374</v>
       </c>
       <c r="T65" t="n">
-        <v>136.8007690290843</v>
+        <v>163.1370545410572</v>
       </c>
       <c r="U65" t="n">
-        <v>19.55576037170599</v>
+        <v>10.80419083586322</v>
       </c>
       <c r="V65" t="n">
-        <v>0.160538185971971</v>
-      </c>
-      <c r="W65" t="b">
+        <v>136.8008895152307</v>
+      </c>
+      <c r="W65" t="n">
+        <v>32.6922619950102</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0.006183530906222146</v>
+      </c>
+      <c r="Y65" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5227,54 +5621,60 @@
         <v>0.9790980815887451</v>
       </c>
       <c r="G66" t="n">
+        <v>0.1146622998639941</v>
+      </c>
+      <c r="H66" t="n">
         <v>0.0009753215708769858</v>
       </c>
-      <c r="H66" t="n">
+      <c r="I66" t="n">
         <v>933.5301576108425</v>
       </c>
-      <c r="I66" t="n">
+      <c r="J66" t="n">
         <v>180.7271785998349</v>
       </c>
-      <c r="J66" t="n">
+      <c r="K66" t="n">
         <v>9.000678720989361</v>
       </c>
-      <c r="K66" t="n">
+      <c r="L66" t="n">
         <v>69.38425521866998</v>
       </c>
-      <c r="L66" t="n">
+      <c r="M66" t="n">
         <v>1.149667071002938</v>
       </c>
-      <c r="M66" t="n">
+      <c r="N66" t="n">
         <v>1.785612877677009</v>
       </c>
-      <c r="N66" t="b">
-        <v>1</v>
-      </c>
-      <c r="O66" t="n">
-        <v>0.9942413568496704</v>
+      <c r="O66" t="b">
+        <v>1</v>
       </c>
       <c r="P66" t="n">
-        <v>0.000791300437413156</v>
+        <v>0.9812487363815308</v>
       </c>
       <c r="Q66" t="n">
-        <v>937.0812140315644</v>
+        <v>0.3726045999210328</v>
       </c>
       <c r="R66" t="n">
-        <v>183.4696252299289</v>
+        <v>0.0006683568353764713</v>
       </c>
       <c r="S66" t="n">
-        <v>9.000641277380145</v>
+        <v>939.0754473547565</v>
       </c>
       <c r="T66" t="n">
-        <v>72.9353116393919</v>
+        <v>184.1626625328815</v>
       </c>
       <c r="U66" t="n">
-        <v>1.592779559091099</v>
+        <v>9.000640205630994</v>
       </c>
       <c r="V66" t="n">
-        <v>1.785575434067793</v>
-      </c>
-      <c r="W66" t="b">
+        <v>74.92954496258403</v>
+      </c>
+      <c r="W66" t="n">
+        <v>2.285816862043731</v>
+      </c>
+      <c r="X66" t="n">
+        <v>1.785574362318641</v>
+      </c>
+      <c r="Y66" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5300,54 +5700,60 @@
         <v>0.7356811761856079</v>
       </c>
       <c r="G67" t="n">
+        <v>0.06387319997884333</v>
+      </c>
+      <c r="H67" t="n">
         <v>9.742625115904957e-05</v>
       </c>
-      <c r="H67" t="n">
+      <c r="I67" t="n">
         <v>985.8937770003619</v>
       </c>
-      <c r="I67" t="n">
+      <c r="J67" t="n">
         <v>212.6385535812693</v>
       </c>
-      <c r="J67" t="n">
+      <c r="K67" t="n">
         <v>10.83054006389804</v>
       </c>
-      <c r="K67" t="n">
+      <c r="L67" t="n">
         <v>43.33478425794772</v>
       </c>
-      <c r="L67" t="n">
+      <c r="M67" t="n">
         <v>0</v>
       </c>
-      <c r="M67" t="n">
+      <c r="N67" t="n">
         <v>0.0001471996507493856</v>
       </c>
-      <c r="N67" t="b">
-        <v>1</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0.923780620098114</v>
+      <c r="O67" t="b">
+        <v>1</v>
       </c>
       <c r="P67" t="n">
-        <v>0.0002607010246720165</v>
+        <v>0.9455968141555786</v>
       </c>
       <c r="Q67" t="n">
-        <v>971.1219136847757</v>
+        <v>0.321779299993068</v>
       </c>
       <c r="R67" t="n">
-        <v>212.1368848941592</v>
+        <v>0.0002416250354144722</v>
       </c>
       <c r="S67" t="n">
-        <v>10.82596850169796</v>
+        <v>972.8524376748964</v>
       </c>
       <c r="T67" t="n">
-        <v>58.10664757353391</v>
+        <v>212.0616648362186</v>
       </c>
       <c r="U67" t="n">
-        <v>0.5016686871101683</v>
+        <v>10.80826273369459</v>
       </c>
       <c r="V67" t="n">
-        <v>0.004424362549332983</v>
-      </c>
-      <c r="W67" t="b">
+        <v>56.37612358341323</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0.5768887450507236</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0.02213013055270174</v>
+      </c>
+      <c r="Y67" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5373,54 +5779,60 @@
         <v>0.7658896446228027</v>
       </c>
       <c r="G68" t="n">
+        <v>0.2388488999567926</v>
+      </c>
+      <c r="H68" t="n">
         <v>0.0007880357443355024</v>
       </c>
-      <c r="H68" t="n">
+      <c r="I68" t="n">
         <v>925.9052788979586</v>
       </c>
-      <c r="I68" t="n">
+      <c r="J68" t="n">
         <v>220.1083942025494</v>
       </c>
-      <c r="J68" t="n">
+      <c r="K68" t="n">
         <v>10.01016271697617</v>
       </c>
-      <c r="K68" t="n">
+      <c r="L68" t="n">
         <v>56.11871570970993</v>
       </c>
-      <c r="L68" t="n">
+      <c r="M68" t="n">
         <v>0.5116539195075518</v>
       </c>
-      <c r="M68" t="n">
+      <c r="N68" t="n">
         <v>3.552713678800501e-15</v>
       </c>
-      <c r="N68" t="b">
-        <v>1</v>
-      </c>
-      <c r="O68" t="n">
-        <v>0.6383228898048401</v>
+      <c r="O68" t="b">
+        <v>1</v>
       </c>
       <c r="P68" t="n">
-        <v>0.0004742451419588178</v>
+        <v>0.600747287273407</v>
       </c>
       <c r="Q68" t="n">
-        <v>929.3630438185602</v>
+        <v>0.3567796000279486</v>
       </c>
       <c r="R68" t="n">
-        <v>218.7516846822802</v>
+        <v>0.0004555316991172731</v>
       </c>
       <c r="S68" t="n">
-        <v>10.04089007789262</v>
+        <v>924.6907360838259</v>
       </c>
       <c r="T68" t="n">
-        <v>59.57648063031149</v>
+        <v>218.5495471907728</v>
       </c>
       <c r="U68" t="n">
-        <v>1.868363439776772</v>
+        <v>10.08125713643015</v>
       </c>
       <c r="V68" t="n">
-        <v>0.03072736091645822</v>
-      </c>
-      <c r="W68" t="b">
+        <v>54.90417289557718</v>
+      </c>
+      <c r="W68" t="n">
+        <v>2.070500931284244</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0.07109441945398665</v>
+      </c>
+      <c r="Y68" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5446,54 +5858,60 @@
         <v>0.9864906072616577</v>
       </c>
       <c r="G69" t="n">
+        <v>0.1515601000282913</v>
+      </c>
+      <c r="H69" t="n">
         <v>0.001153156976215541</v>
       </c>
-      <c r="H69" t="n">
+      <c r="I69" t="n">
         <v>933.5293079644696</v>
       </c>
-      <c r="I69" t="n">
+      <c r="J69" t="n">
         <v>203.9794727730373</v>
       </c>
-      <c r="J69" t="n">
+      <c r="K69" t="n">
         <v>9.000641612788701</v>
       </c>
-      <c r="K69" t="n">
+      <c r="L69" t="n">
         <v>81.14153793350795</v>
       </c>
-      <c r="L69" t="n">
+      <c r="M69" t="n">
         <v>2.870592652470805e-12</v>
       </c>
-      <c r="M69" t="n">
+      <c r="N69" t="n">
         <v>1.295050693937339</v>
       </c>
-      <c r="N69" t="b">
-        <v>1</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0.9914131164550781</v>
+      <c r="O69" t="b">
+        <v>1</v>
       </c>
       <c r="P69" t="n">
-        <v>0.0007015690789557993</v>
+        <v>0.9819844365119934</v>
       </c>
       <c r="Q69" t="n">
-        <v>933.0378740011065</v>
+        <v>0.4285587999038398</v>
       </c>
       <c r="R69" t="n">
-        <v>202.9771593752459</v>
+        <v>0.0006326048169285059</v>
       </c>
       <c r="S69" t="n">
-        <v>9.00064178893847</v>
+        <v>931.7249762808516</v>
       </c>
       <c r="T69" t="n">
-        <v>80.65010397014487</v>
+        <v>204.2126425873483</v>
       </c>
       <c r="U69" t="n">
-        <v>1.002313397794325</v>
+        <v>9.000641738316181</v>
       </c>
       <c r="V69" t="n">
-        <v>1.295050870087107</v>
-      </c>
-      <c r="W69" t="b">
+        <v>79.33720624988996</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0.23316981430807</v>
+      </c>
+      <c r="X69" t="n">
+        <v>1.295050819464818</v>
+      </c>
+      <c r="Y69" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5519,54 +5937,60 @@
         <v>0.9526134133338928</v>
       </c>
       <c r="G70" t="n">
+        <v>0.14387740008533</v>
+      </c>
+      <c r="H70" t="n">
         <v>0.001392161007970572</v>
       </c>
-      <c r="H70" t="n">
+      <c r="I70" t="n">
         <v>925.9037133508269</v>
       </c>
-      <c r="I70" t="n">
+      <c r="J70" t="n">
         <v>189.6956515728363</v>
       </c>
-      <c r="J70" t="n">
+      <c r="K70" t="n">
         <v>9.000641718221598</v>
       </c>
-      <c r="K70" t="n">
+      <c r="L70" t="n">
         <v>50.72030729955566</v>
       </c>
-      <c r="L70" t="n">
+      <c r="M70" t="n">
         <v>1.70530256582424e-13</v>
       </c>
-      <c r="M70" t="n">
+      <c r="N70" t="n">
         <v>2.557919049661384</v>
       </c>
-      <c r="N70" t="b">
-        <v>1</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0.9910576343536377</v>
+      <c r="O70" t="b">
+        <v>1</v>
       </c>
       <c r="P70" t="n">
-        <v>0.000479795562569052</v>
+        <v>0.9780243635177612</v>
       </c>
       <c r="Q70" t="n">
-        <v>937.4447875887574</v>
+        <v>0.388588699977845</v>
       </c>
       <c r="R70" t="n">
-        <v>190.3498873846831</v>
+        <v>0.0005021069664508104</v>
       </c>
       <c r="S70" t="n">
-        <v>9.000641991304178</v>
+        <v>936.6759064940979</v>
       </c>
       <c r="T70" t="n">
-        <v>62.26138153748616</v>
+        <v>191.1415944281951</v>
       </c>
       <c r="U70" t="n">
-        <v>0.6542358118469167</v>
+        <v>9.000641201147461</v>
       </c>
       <c r="V70" t="n">
-        <v>2.557919322743965</v>
-      </c>
-      <c r="W70" t="b">
+        <v>61.49250044282667</v>
+      </c>
+      <c r="W70" t="n">
+        <v>1.445942855358936</v>
+      </c>
+      <c r="X70" t="n">
+        <v>2.557918532587248</v>
+      </c>
+      <c r="Y70" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5592,54 +6016,60 @@
         <v>0.7990202307701111</v>
       </c>
       <c r="G71" t="n">
+        <v>0.08183700009249151</v>
+      </c>
+      <c r="H71" t="n">
         <v>0.0004035303718410432</v>
       </c>
-      <c r="H71" t="n">
+      <c r="I71" t="n">
         <v>940.870098875969</v>
       </c>
-      <c r="I71" t="n">
+      <c r="J71" t="n">
         <v>193.6028206897864</v>
       </c>
-      <c r="J71" t="n">
+      <c r="K71" t="n">
         <v>9.000641549284468</v>
       </c>
-      <c r="K71" t="n">
+      <c r="L71" t="n">
         <v>61.37204487654276</v>
       </c>
-      <c r="L71" t="n">
+      <c r="M71" t="n">
         <v>5.115907697472721e-13</v>
       </c>
-      <c r="M71" t="n">
+      <c r="N71" t="n">
         <v>0.261734928876642</v>
       </c>
-      <c r="N71" t="b">
-        <v>1</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0.8270676136016846</v>
+      <c r="O71" t="b">
+        <v>1</v>
       </c>
       <c r="P71" t="n">
-        <v>0.000432800967246294</v>
+        <v>0.8146300911903381</v>
       </c>
       <c r="Q71" t="n">
-        <v>937.2173254955171</v>
+        <v>0.4636518999468535</v>
       </c>
       <c r="R71" t="n">
-        <v>194.1086399025454</v>
+        <v>0.0004418827011249959</v>
       </c>
       <c r="S71" t="n">
-        <v>9.000641752862078</v>
+        <v>935.8991490715102</v>
       </c>
       <c r="T71" t="n">
-        <v>57.71927149609087</v>
+        <v>194.6556681321374</v>
       </c>
       <c r="U71" t="n">
-        <v>0.5058192127584391</v>
+        <v>9.00064162075174</v>
       </c>
       <c r="V71" t="n">
-        <v>0.2617351324542518</v>
-      </c>
-      <c r="W71" t="b">
+        <v>56.40109507208399</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1.052847442350441</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0.2617350003439132</v>
+      </c>
+      <c r="Y71" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5665,54 +6095,60 @@
         <v>0.9320546984672546</v>
       </c>
       <c r="G72" t="n">
+        <v>0.2572891998570412</v>
+      </c>
+      <c r="H72" t="n">
         <v>0.001686847768723965</v>
       </c>
-      <c r="H72" t="n">
+      <c r="I72" t="n">
         <v>918.4376755048595</v>
       </c>
-      <c r="I72" t="n">
+      <c r="J72" t="n">
         <v>206.285132575113</v>
       </c>
-      <c r="J72" t="n">
+      <c r="K72" t="n">
         <v>12.22541010675307</v>
       </c>
-      <c r="K72" t="n">
+      <c r="L72" t="n">
         <v>29.60300985320544</v>
       </c>
-      <c r="L72" t="n">
+      <c r="M72" t="n">
         <v>2.133117065708404</v>
       </c>
-      <c r="M72" t="n">
+      <c r="N72" t="n">
         <v>1.534360355370373</v>
       </c>
-      <c r="N72" t="b">
-        <v>1</v>
-      </c>
-      <c r="O72" t="n">
-        <v>0.8628045916557312</v>
+      <c r="O72" t="b">
+        <v>1</v>
       </c>
       <c r="P72" t="n">
-        <v>0.003511777613312006</v>
+        <v>0.9115007519721985</v>
       </c>
       <c r="Q72" t="n">
-        <v>992.3112875783348</v>
+        <v>1.002238299930468</v>
       </c>
       <c r="R72" t="n">
-        <v>208.9912806387586</v>
+        <v>0.003087344346567988</v>
       </c>
       <c r="S72" t="n">
-        <v>12.27949167529618</v>
+        <v>811.8959212735638</v>
       </c>
       <c r="T72" t="n">
-        <v>44.27060222026989</v>
+        <v>209.3014566461669</v>
       </c>
       <c r="U72" t="n">
-        <v>4.839265129353976</v>
+        <v>12.6635532280411</v>
       </c>
       <c r="V72" t="n">
-        <v>1.480278786827265</v>
-      </c>
-      <c r="W72" t="b">
+        <v>136.1447640845012</v>
+      </c>
+      <c r="W72" t="n">
+        <v>5.149441136762221</v>
+      </c>
+      <c r="X72" t="n">
+        <v>1.096217234082349</v>
+      </c>
+      <c r="Y72" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5738,54 +6174,60 @@
         <v>0.961039125919342</v>
       </c>
       <c r="G73" t="n">
+        <v>0.1905967998318374</v>
+      </c>
+      <c r="H73" t="n">
         <v>0.0005593529785983264</v>
       </c>
-      <c r="H73" t="n">
+      <c r="I73" t="n">
         <v>944.1999543755353</v>
       </c>
-      <c r="I73" t="n">
+      <c r="J73" t="n">
         <v>211.3862036764079</v>
       </c>
-      <c r="J73" t="n">
+      <c r="K73" t="n">
         <v>12.24328301386874</v>
       </c>
-      <c r="K73" t="n">
+      <c r="L73" t="n">
         <v>22.20601311464395</v>
       </c>
-      <c r="L73" t="n">
+      <c r="M73" t="n">
         <v>5.754319062134527e-06</v>
       </c>
-      <c r="M73" t="n">
+      <c r="N73" t="n">
         <v>2.934417254490297</v>
       </c>
-      <c r="N73" t="b">
-        <v>1</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0.999210000038147</v>
+      <c r="O73" t="b">
+        <v>1</v>
       </c>
       <c r="P73" t="n">
-        <v>0.003619997529312968</v>
+        <v>0.9992827773094177</v>
       </c>
       <c r="Q73" t="n">
-        <v>994.819259883107</v>
+        <v>1.100516099948436</v>
       </c>
       <c r="R73" t="n">
-        <v>223.6151777573764</v>
+        <v>0.004422673955559731</v>
       </c>
       <c r="S73" t="n">
-        <v>12.56653644760171</v>
+        <v>800.0000306840237</v>
       </c>
       <c r="T73" t="n">
-        <v>28.4132923929277</v>
+        <v>217.0231904763192</v>
       </c>
       <c r="U73" t="n">
-        <v>12.22897983528759</v>
+        <v>13.32489516558742</v>
       </c>
       <c r="V73" t="n">
-        <v>2.611163820757326</v>
-      </c>
-      <c r="W73" t="b">
+        <v>166.4059368061555</v>
+      </c>
+      <c r="W73" t="n">
+        <v>5.636992554230375</v>
+      </c>
+      <c r="X73" t="n">
+        <v>1.852805102771617</v>
+      </c>
+      <c r="Y73" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5811,54 +6253,60 @@
         <v>0.8671261668205261</v>
       </c>
       <c r="G74" t="n">
+        <v>0.1682114999275655</v>
+      </c>
+      <c r="H74" t="n">
         <v>0.0004035303718410432</v>
       </c>
-      <c r="H74" t="n">
+      <c r="I74" t="n">
         <v>940.871427355211</v>
       </c>
-      <c r="I74" t="n">
+      <c r="J74" t="n">
         <v>189.061086313599</v>
       </c>
-      <c r="J74" t="n">
+      <c r="K74" t="n">
         <v>9.000641667410143</v>
       </c>
-      <c r="K74" t="n">
+      <c r="L74" t="n">
         <v>47.62278882649525</v>
       </c>
-      <c r="L74" t="n">
+      <c r="M74" t="n">
         <v>9.407585821463726e-12</v>
       </c>
-      <c r="M74" t="n">
+      <c r="N74" t="n">
         <v>2.405357348876813</v>
       </c>
-      <c r="N74" t="b">
-        <v>1</v>
-      </c>
-      <c r="O74" t="n">
-        <v>0.9443646669387817</v>
+      <c r="O74" t="b">
+        <v>1</v>
       </c>
       <c r="P74" t="n">
-        <v>0.0004216879606246948</v>
+        <v>0.8970097303390503</v>
       </c>
       <c r="Q74" t="n">
-        <v>938.221775418859</v>
+        <v>0.6279978998936713</v>
       </c>
       <c r="R74" t="n">
-        <v>190.3461218253021</v>
+        <v>0.0003695680352393538</v>
       </c>
       <c r="S74" t="n">
-        <v>9.000641768627496</v>
+        <v>939.0922863223436</v>
       </c>
       <c r="T74" t="n">
-        <v>44.97313689014322</v>
+        <v>190.2044761468036</v>
       </c>
       <c r="U74" t="n">
-        <v>1.285035511693735</v>
+        <v>9.000641170323545</v>
       </c>
       <c r="V74" t="n">
-        <v>2.405357450094166</v>
-      </c>
-      <c r="W74" t="b">
+        <v>45.84364779362784</v>
+      </c>
+      <c r="W74" t="n">
+        <v>1.143389833195215</v>
+      </c>
+      <c r="X74" t="n">
+        <v>2.405356851790216</v>
+      </c>
+      <c r="Y74" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5884,54 +6332,60 @@
         <v>0.974799633026123</v>
       </c>
       <c r="G75" t="n">
+        <v>0.1061207999009639</v>
+      </c>
+      <c r="H75" t="n">
         <v>0.001176272286102176</v>
       </c>
-      <c r="H75" t="n">
+      <c r="I75" t="n">
         <v>933.5293019251812</v>
       </c>
-      <c r="I75" t="n">
+      <c r="J75" t="n">
         <v>199.8737532158483</v>
       </c>
-      <c r="J75" t="n">
+      <c r="K75" t="n">
         <v>9.000641734796444</v>
       </c>
-      <c r="K75" t="n">
+      <c r="L75" t="n">
         <v>63.11520694789237</v>
       </c>
-      <c r="L75" t="n">
+      <c r="M75" t="n">
         <v>2.188471626141109e-12</v>
       </c>
-      <c r="M75" t="n">
+      <c r="N75" t="n">
         <v>1.047649111165825</v>
       </c>
-      <c r="N75" t="b">
-        <v>1</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0.9719758033752441</v>
+      <c r="O75" t="b">
+        <v>1</v>
       </c>
       <c r="P75" t="n">
-        <v>0.0005613354151137173</v>
+        <v>0.959416925907135</v>
       </c>
       <c r="Q75" t="n">
-        <v>934.9361922073288</v>
+        <v>0.4656754999887198</v>
       </c>
       <c r="R75" t="n">
-        <v>200.7485020133153</v>
+        <v>0.0004905613022856414</v>
       </c>
       <c r="S75" t="n">
-        <v>9.000641471498632</v>
+        <v>933.634536905446</v>
       </c>
       <c r="T75" t="n">
-        <v>64.52209723003989</v>
+        <v>200.4744968783431</v>
       </c>
       <c r="U75" t="n">
-        <v>0.8747487974692092</v>
+        <v>9.000641704903027</v>
       </c>
       <c r="V75" t="n">
-        <v>1.047648847868013</v>
-      </c>
-      <c r="W75" t="b">
+        <v>63.22044192815713</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6007436624970239</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.047649081272407</v>
+      </c>
+      <c r="Y75" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5957,54 +6411,60 @@
         <v>0.9152489304542542</v>
       </c>
       <c r="G76" t="n">
+        <v>0.2399756999220699</v>
+      </c>
+      <c r="H76" t="n">
         <v>0.0006277773063629866</v>
       </c>
-      <c r="H76" t="n">
+      <c r="I76" t="n">
         <v>857.2992001435658</v>
       </c>
-      <c r="I76" t="n">
+      <c r="J76" t="n">
         <v>176.1732571670742</v>
       </c>
-      <c r="J76" t="n">
+      <c r="K76" t="n">
         <v>9.000001070377479</v>
       </c>
-      <c r="K76" t="n">
+      <c r="L76" t="n">
         <v>97.83518331234893</v>
       </c>
-      <c r="L76" t="n">
+      <c r="M76" t="n">
         <v>26.67567403540298</v>
       </c>
-      <c r="M76" t="n">
+      <c r="N76" t="n">
         <v>0.0223027121325412</v>
       </c>
-      <c r="N76" t="b">
-        <v>1</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0.9978660941123962</v>
+      <c r="O76" t="b">
+        <v>1</v>
       </c>
       <c r="P76" t="n">
-        <v>0.0009542824700474739</v>
+        <v>0.995904266834259</v>
       </c>
       <c r="Q76" t="n">
-        <v>825.7593186655516</v>
+        <v>1.3503657002002</v>
       </c>
       <c r="R76" t="n">
-        <v>156.9450891358731</v>
+        <v>0.002736728172749281</v>
       </c>
       <c r="S76" t="n">
-        <v>9.000641898947027</v>
+        <v>968.5475989499128</v>
       </c>
       <c r="T76" t="n">
-        <v>129.3750647903631</v>
+        <v>177.0944569984135</v>
       </c>
       <c r="U76" t="n">
-        <v>7.447506004201841</v>
+        <v>9.129396163131487</v>
       </c>
       <c r="V76" t="n">
-        <v>0.02294354070208904</v>
-      </c>
-      <c r="W76" t="b">
+        <v>13.413215493998</v>
+      </c>
+      <c r="W76" t="n">
+        <v>27.59687386674224</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0.1516978048865489</v>
+      </c>
+      <c r="Y76" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6030,54 +6490,60 @@
         <v>0.9866198301315308</v>
       </c>
       <c r="G77" t="n">
+        <v>0.1218620000872761</v>
+      </c>
+      <c r="H77" t="n">
         <v>0.002527530770748854</v>
       </c>
-      <c r="H77" t="n">
+      <c r="I77" t="n">
         <v>920.0590705958026</v>
       </c>
-      <c r="I77" t="n">
+      <c r="J77" t="n">
         <v>204.0722128093243</v>
       </c>
-      <c r="J77" t="n">
+      <c r="K77" t="n">
         <v>9.000595810886647</v>
       </c>
-      <c r="K77" t="n">
+      <c r="L77" t="n">
         <v>68.48454361916254</v>
       </c>
-      <c r="L77" t="n">
+      <c r="M77" t="n">
         <v>0.7052747660477507</v>
       </c>
-      <c r="M77" t="n">
+      <c r="N77" t="n">
         <v>1.55097274748058</v>
       </c>
-      <c r="N77" t="b">
-        <v>1</v>
-      </c>
-      <c r="O77" t="n">
-        <v>0.9947485327720642</v>
+      <c r="O77" t="b">
+        <v>1</v>
       </c>
       <c r="P77" t="n">
-        <v>0.0007225964218378067</v>
+        <v>0.9868501424789429</v>
       </c>
       <c r="Q77" t="n">
-        <v>932.8523372106046</v>
+        <v>0.4591127999592572</v>
       </c>
       <c r="R77" t="n">
-        <v>202.9966871986997</v>
+        <v>0.0006404300802387297</v>
       </c>
       <c r="S77" t="n">
-        <v>9.000641779210863</v>
+        <v>931.6855047847178</v>
       </c>
       <c r="T77" t="n">
-        <v>81.27781023396449</v>
+        <v>203.6868514977849</v>
       </c>
       <c r="U77" t="n">
-        <v>0.370250844576816</v>
+        <v>9.000641852425925</v>
       </c>
       <c r="V77" t="n">
-        <v>1.551018715804796</v>
-      </c>
-      <c r="W77" t="b">
+        <v>80.11097780807768</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0.3199134545083666</v>
+      </c>
+      <c r="X77" t="n">
+        <v>1.551018789019858</v>
+      </c>
+      <c r="Y77" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6103,54 +6569,60 @@
         <v>0.7411229610443115</v>
       </c>
       <c r="G78" t="n">
+        <v>0.2532765998039395</v>
+      </c>
+      <c r="H78" t="n">
         <v>0.001695083919912577</v>
       </c>
-      <c r="H78" t="n">
+      <c r="I78" t="n">
         <v>980.651521949164</v>
       </c>
-      <c r="I78" t="n">
+      <c r="J78" t="n">
         <v>173.9057564547762</v>
       </c>
-      <c r="J78" t="n">
+      <c r="K78" t="n">
         <v>10.90223005966835</v>
       </c>
-      <c r="K78" t="n">
+      <c r="L78" t="n">
         <v>3.258794435833124</v>
       </c>
-      <c r="L78" t="n">
+      <c r="M78" t="n">
         <v>16.22206716760144</v>
       </c>
-      <c r="M78" t="n">
+      <c r="N78" t="n">
         <v>0.09280878392869596</v>
       </c>
-      <c r="N78" t="b">
-        <v>1</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0.8478268384933472</v>
+      <c r="O78" t="b">
+        <v>1</v>
       </c>
       <c r="P78" t="n">
-        <v>0.001091392943635583</v>
+        <v>0.8012228608131409</v>
       </c>
       <c r="Q78" t="n">
-        <v>838.1733811423935</v>
+        <v>0.7927646001335233</v>
       </c>
       <c r="R78" t="n">
-        <v>166.8817318252682</v>
+        <v>0.002592191798612475</v>
       </c>
       <c r="S78" t="n">
-        <v>10.70126787999254</v>
+        <v>838.8451283938605</v>
       </c>
       <c r="T78" t="n">
-        <v>145.7369352426036</v>
+        <v>176.3374337876815</v>
       </c>
       <c r="U78" t="n">
-        <v>9.198042538093432</v>
+        <v>10.79179876111648</v>
       </c>
       <c r="V78" t="n">
-        <v>0.1081533957471077</v>
-      </c>
-      <c r="W78" t="b">
+        <v>145.0651879911367</v>
+      </c>
+      <c r="W78" t="n">
+        <v>18.65374450050678</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0.01762251462316833</v>
+      </c>
+      <c r="Y78" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6176,54 +6648,60 @@
         <v>0.9748581051826477</v>
       </c>
       <c r="G79" t="n">
+        <v>0.3449452000204474</v>
+      </c>
+      <c r="H79" t="n">
         <v>0.6460902690887451</v>
       </c>
-      <c r="H79" t="n">
+      <c r="I79" t="n">
         <v>945.6722747289361</v>
       </c>
-      <c r="I79" t="n">
+      <c r="J79" t="n">
         <v>158.2367514784902</v>
       </c>
-      <c r="J79" t="n">
+      <c r="K79" t="n">
         <v>10.22185835107431</v>
       </c>
-      <c r="K79" t="n">
+      <c r="L79" t="n">
         <v>48.1368377872634</v>
       </c>
-      <c r="L79" t="n">
+      <c r="M79" t="n">
         <v>31.81449335571106</v>
       </c>
-      <c r="M79" t="n">
+      <c r="N79" t="n">
         <v>0.2069575365274687</v>
       </c>
-      <c r="N79" t="b">
-        <v>1</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0.9999992847442627</v>
+      <c r="O79" t="b">
+        <v>1</v>
       </c>
       <c r="P79" t="n">
-        <v>0.001430986099876463</v>
+        <v>0.9999610185623169</v>
       </c>
       <c r="Q79" t="n">
-        <v>802.3016053467004</v>
+        <v>1.183981499867514</v>
       </c>
       <c r="R79" t="n">
-        <v>150.000552308477</v>
+        <v>0.01020536478608847</v>
       </c>
       <c r="S79" t="n">
-        <v>10.28149806424723</v>
+        <v>800.0000560979408</v>
       </c>
       <c r="T79" t="n">
-        <v>191.5075071694991</v>
+        <v>162.0675053733594</v>
       </c>
       <c r="U79" t="n">
-        <v>23.57829418569789</v>
+        <v>10.28129265562665</v>
       </c>
       <c r="V79" t="n">
-        <v>0.1473178233545536</v>
-      </c>
-      <c r="W79" t="b">
+        <v>193.8090564182587</v>
+      </c>
+      <c r="W79" t="n">
+        <v>35.64524725058025</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0.1475232319751356</v>
+      </c>
+      <c r="Y79" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6249,54 +6727,60 @@
         <v>0.8736257553100586</v>
       </c>
       <c r="G80" t="n">
+        <v>0.2273296001367271</v>
+      </c>
+      <c r="H80" t="n">
         <v>0.0001908630947582424</v>
       </c>
-      <c r="H80" t="n">
+      <c r="I80" t="n">
         <v>957.0934828425404</v>
       </c>
-      <c r="I80" t="n">
+      <c r="J80" t="n">
         <v>176.173305591252</v>
       </c>
-      <c r="J80" t="n">
+      <c r="K80" t="n">
         <v>10.45735275974209</v>
       </c>
-      <c r="K80" t="n">
+      <c r="L80" t="n">
         <v>0.002879521027466581</v>
       </c>
-      <c r="L80" t="n">
+      <c r="M80" t="n">
         <v>30.02945565869624</v>
       </c>
-      <c r="M80" t="n">
+      <c r="N80" t="n">
         <v>0.5118177118683747</v>
       </c>
-      <c r="N80" t="b">
-        <v>1</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0.9993975162506104</v>
+      <c r="O80" t="b">
+        <v>1</v>
       </c>
       <c r="P80" t="n">
-        <v>0.001149837160483003</v>
+        <v>0.9989305138587952</v>
       </c>
       <c r="Q80" t="n">
-        <v>813.6166645695683</v>
+        <v>0.767661799909547</v>
       </c>
       <c r="R80" t="n">
-        <v>154.0988370143027</v>
+        <v>0.004141734447330236</v>
       </c>
       <c r="S80" t="n">
-        <v>9.835380076011546</v>
+        <v>800.0013987224835</v>
       </c>
       <c r="T80" t="n">
-        <v>143.4796977939995</v>
+        <v>165.8646354403891</v>
       </c>
       <c r="U80" t="n">
-        <v>7.954987081746964</v>
+        <v>9.873318941401386</v>
       </c>
       <c r="V80" t="n">
-        <v>0.1101549718621673</v>
-      </c>
-      <c r="W80" t="b">
+        <v>157.0949636410844</v>
+      </c>
+      <c r="W80" t="n">
+        <v>19.72078550783331</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0.07221610647232701</v>
+      </c>
+      <c r="Y80" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6322,54 +6806,60 @@
         <v>0.9823979735374451</v>
       </c>
       <c r="G81" t="n">
+        <v>0.2217566000763327</v>
+      </c>
+      <c r="H81" t="n">
         <v>0.0006277773063629866</v>
       </c>
-      <c r="H81" t="n">
+      <c r="I81" t="n">
         <v>857.2856615298629</v>
       </c>
-      <c r="I81" t="n">
+      <c r="J81" t="n">
         <v>176.1732577477451</v>
       </c>
-      <c r="J81" t="n">
+      <c r="K81" t="n">
         <v>9.000001253609373</v>
       </c>
-      <c r="K81" t="n">
+      <c r="L81" t="n">
         <v>103.6195081306595</v>
       </c>
-      <c r="L81" t="n">
+      <c r="M81" t="n">
         <v>45.67836518388796</v>
       </c>
-      <c r="M81" t="n">
+      <c r="N81" t="n">
         <v>0.1620437560287762</v>
       </c>
-      <c r="N81" t="b">
-        <v>1</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0.9999986886978149</v>
+      <c r="O81" t="b">
+        <v>1</v>
       </c>
       <c r="P81" t="n">
-        <v>0.001082598813809454</v>
+        <v>0.9999749660491943</v>
       </c>
       <c r="Q81" t="n">
-        <v>809.8632596390128</v>
+        <v>0.5748632000759244</v>
       </c>
       <c r="R81" t="n">
-        <v>150.0005525771487</v>
+        <v>0.008983481675386429</v>
       </c>
       <c r="S81" t="n">
-        <v>9.000641750763702</v>
+        <v>800.0000395550629</v>
       </c>
       <c r="T81" t="n">
-        <v>151.0419100215096</v>
+        <v>160.9161272312666</v>
       </c>
       <c r="U81" t="n">
-        <v>19.50566001329153</v>
+        <v>9.000642171565886</v>
       </c>
       <c r="V81" t="n">
-        <v>0.1626842531831052</v>
-      </c>
-      <c r="W81" t="b">
+        <v>160.9051301054594</v>
+      </c>
+      <c r="W81" t="n">
+        <v>30.42123466740952</v>
+      </c>
+      <c r="X81" t="n">
+        <v>0.1626846739852894</v>
+      </c>
+      <c r="Y81" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6395,54 +6885,60 @@
         <v>0.9816255569458008</v>
       </c>
       <c r="G82" t="n">
+        <v>0.3144268000032753</v>
+      </c>
+      <c r="H82" t="n">
         <v>0.002671804977580905</v>
       </c>
-      <c r="H82" t="n">
+      <c r="I82" t="n">
         <v>963.2195815735341</v>
       </c>
-      <c r="I82" t="n">
+      <c r="J82" t="n">
         <v>173.947135934415</v>
       </c>
-      <c r="J82" t="n">
+      <c r="K82" t="n">
         <v>10.51127185358748</v>
       </c>
-      <c r="K82" t="n">
+      <c r="L82" t="n">
         <v>7.817893346578899</v>
       </c>
-      <c r="L82" t="n">
+      <c r="M82" t="n">
         <v>50.78650448870104</v>
       </c>
-      <c r="M82" t="n">
+      <c r="N82" t="n">
         <v>0.8219191230331671</v>
       </c>
-      <c r="N82" t="b">
-        <v>1</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0.9999998807907104</v>
+      <c r="O82" t="b">
+        <v>1</v>
       </c>
       <c r="P82" t="n">
-        <v>0.001205563778057694</v>
+        <v>0.9999963045120239</v>
       </c>
       <c r="Q82" t="n">
-        <v>806.1187487135985</v>
+        <v>0.8854722001124173</v>
       </c>
       <c r="R82" t="n">
-        <v>150.0005523809073</v>
+        <v>0.01242727413773537</v>
       </c>
       <c r="S82" t="n">
-        <v>9.577554091634845</v>
+        <v>800.0000001712805</v>
       </c>
       <c r="T82" t="n">
-        <v>149.2829395133567</v>
+        <v>159.6918072561193</v>
       </c>
       <c r="U82" t="n">
-        <v>26.83992093519339</v>
+        <v>9.202218281272526</v>
       </c>
       <c r="V82" t="n">
-        <v>0.1117986389194634</v>
-      </c>
-      <c r="W82" t="b">
+        <v>155.4016880556748</v>
+      </c>
+      <c r="W82" t="n">
+        <v>36.53117581040533</v>
+      </c>
+      <c r="X82" t="n">
+        <v>0.4871344492817826</v>
+      </c>
+      <c r="Y82" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6468,54 +6964,60 @@
         <v>0.8763126730918884</v>
       </c>
       <c r="G83" t="n">
+        <v>0.2024073000065982</v>
+      </c>
+      <c r="H83" t="n">
         <v>0.0001908630947582424</v>
       </c>
-      <c r="H83" t="n">
+      <c r="I83" t="n">
         <v>957.595351926822</v>
       </c>
-      <c r="I83" t="n">
+      <c r="J83" t="n">
         <v>176.1732562427629</v>
       </c>
-      <c r="J83" t="n">
+      <c r="K83" t="n">
         <v>10.6453756697237</v>
       </c>
-      <c r="K83" t="n">
+      <c r="L83" t="n">
         <v>1.666575388025194</v>
       </c>
-      <c r="L83" t="n">
+      <c r="M83" t="n">
         <v>28.7807522866452</v>
       </c>
-      <c r="M83" t="n">
+      <c r="N83" t="n">
         <v>5.61519539825639e-05</v>
       </c>
-      <c r="N83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0.9990686774253845</v>
+      <c r="O83" t="b">
+        <v>1</v>
       </c>
       <c r="P83" t="n">
-        <v>0.00116412085480988</v>
+        <v>0.9980813264846802</v>
       </c>
       <c r="Q83" t="n">
-        <v>812.8254762022008</v>
+        <v>0.8478394001722336</v>
       </c>
       <c r="R83" t="n">
-        <v>155.7319196026767</v>
+        <v>0.003741910448297858</v>
       </c>
       <c r="S83" t="n">
-        <v>10.52625283050107</v>
+        <v>800.0024596149598</v>
       </c>
       <c r="T83" t="n">
-        <v>146.4364511126464</v>
+        <v>166.5618089233324</v>
       </c>
       <c r="U83" t="n">
-        <v>8.339415646559019</v>
+        <v>10.65838411008192</v>
       </c>
       <c r="V83" t="n">
-        <v>0.1191789911766161</v>
-      </c>
-      <c r="W83" t="b">
+        <v>159.2594676998874</v>
+      </c>
+      <c r="W83" t="n">
+        <v>19.16930496721477</v>
+      </c>
+      <c r="X83" t="n">
+        <v>0.0129522884042359</v>
+      </c>
+      <c r="Y83" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6541,54 +7043,60 @@
         <v>0.9779818654060364</v>
       </c>
       <c r="G84" t="n">
+        <v>0.2301713000051677</v>
+      </c>
+      <c r="H84" t="n">
         <v>0.00139266811311245</v>
       </c>
-      <c r="H84" t="n">
+      <c r="I84" t="n">
         <v>925.9037221576409</v>
       </c>
-      <c r="I84" t="n">
+      <c r="J84" t="n">
         <v>191.0020853883559</v>
       </c>
-      <c r="J84" t="n">
+      <c r="K84" t="n">
         <v>9.000723577019036</v>
       </c>
-      <c r="K84" t="n">
+      <c r="L84" t="n">
         <v>81.76499804687649</v>
       </c>
-      <c r="L84" t="n">
+      <c r="M84" t="n">
         <v>11.83918130052203</v>
       </c>
-      <c r="M84" t="n">
+      <c r="N84" t="n">
         <v>0.6409166829542894</v>
       </c>
-      <c r="N84" t="b">
-        <v>1</v>
-      </c>
-      <c r="O84" t="n">
-        <v>0.9751982092857361</v>
+      <c r="O84" t="b">
+        <v>1</v>
       </c>
       <c r="P84" t="n">
-        <v>0.000778059649746865</v>
+        <v>0.9603607654571533</v>
       </c>
       <c r="Q84" t="n">
-        <v>932.3881242143485</v>
+        <v>0.4283501000609249</v>
       </c>
       <c r="R84" t="n">
-        <v>202.852877928763</v>
+        <v>0.0007038408075459301</v>
       </c>
       <c r="S84" t="n">
-        <v>9.000641815761385</v>
+        <v>931.1727695277716</v>
       </c>
       <c r="T84" t="n">
-        <v>88.24940010358409</v>
+        <v>203.2623278007789</v>
       </c>
       <c r="U84" t="n">
-        <v>0.01161123988509871</v>
+        <v>9.000641872699958</v>
       </c>
       <c r="V84" t="n">
-        <v>0.6408349216966389</v>
-      </c>
-      <c r="W84" t="b">
+        <v>87.03404541700718</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0.4210611119009684</v>
+      </c>
+      <c r="X84" t="n">
+        <v>0.6408349786352119</v>
+      </c>
+      <c r="Y84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6614,54 +7122,60 @@
         <v>0.9806914329528809</v>
       </c>
       <c r="G85" t="n">
+        <v>0.1396172000095248</v>
+      </c>
+      <c r="H85" t="n">
         <v>0.0009205389069393277</v>
       </c>
-      <c r="H85" t="n">
+      <c r="I85" t="n">
         <v>933.5316326486537</v>
       </c>
-      <c r="I85" t="n">
+      <c r="J85" t="n">
         <v>185.8717530899106</v>
       </c>
-      <c r="J85" t="n">
+      <c r="K85" t="n">
         <v>9.000778900824686</v>
       </c>
-      <c r="K85" t="n">
+      <c r="L85" t="n">
         <v>63.06700468986287</v>
       </c>
-      <c r="L85" t="n">
+      <c r="M85" t="n">
         <v>1.948590102902415</v>
       </c>
-      <c r="M85" t="n">
+      <c r="N85" t="n">
         <v>1.733697642840978</v>
       </c>
-      <c r="N85" t="b">
-        <v>1</v>
-      </c>
-      <c r="O85" t="n">
-        <v>0.9893494844436646</v>
+      <c r="O85" t="b">
+        <v>1</v>
       </c>
       <c r="P85" t="n">
-        <v>0.0007114786421880126</v>
+        <v>0.9739370942115784</v>
       </c>
       <c r="Q85" t="n">
-        <v>936.9937504318341</v>
+        <v>0.4169599001761526</v>
       </c>
       <c r="R85" t="n">
-        <v>185.3831038268206</v>
+        <v>0.0005893245688639581</v>
       </c>
       <c r="S85" t="n">
-        <v>9.000641188679623</v>
+        <v>938.711898903316</v>
       </c>
       <c r="T85" t="n">
-        <v>66.52912247304323</v>
+        <v>185.9048202019186</v>
       </c>
       <c r="U85" t="n">
-        <v>1.45994083981239</v>
+        <v>9.000640579272725</v>
       </c>
       <c r="V85" t="n">
-        <v>1.733559930695915</v>
-      </c>
-      <c r="W85" t="b">
+        <v>68.2472709445251</v>
+      </c>
+      <c r="W85" t="n">
+        <v>1.981657214910399</v>
+      </c>
+      <c r="X85" t="n">
+        <v>1.733559321289016</v>
+      </c>
+      <c r="Y85" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6687,54 +7201,60 @@
         <v>0.9742845892906189</v>
       </c>
       <c r="G86" t="n">
+        <v>0.1737034001853317</v>
+      </c>
+      <c r="H86" t="n">
         <v>0.0009308591834269464</v>
       </c>
-      <c r="H86" t="n">
+      <c r="I86" t="n">
         <v>920.0548465954727</v>
       </c>
-      <c r="I86" t="n">
+      <c r="J86" t="n">
         <v>192.9091882371536</v>
       </c>
-      <c r="J86" t="n">
+      <c r="K86" t="n">
         <v>9.710948091122503</v>
       </c>
-      <c r="K86" t="n">
+      <c r="L86" t="n">
         <v>68.74404244758807</v>
       </c>
-      <c r="L86" t="n">
+      <c r="M86" t="n">
         <v>8.526512829121202e-14</v>
       </c>
-      <c r="M86" t="n">
+      <c r="N86" t="n">
         <v>0.2454532452458942</v>
       </c>
-      <c r="N86" t="b">
-        <v>1</v>
-      </c>
-      <c r="O86" t="n">
-        <v>0.8256574869155884</v>
+      <c r="O86" t="b">
+        <v>1</v>
       </c>
       <c r="P86" t="n">
-        <v>0.000521176727488637</v>
+        <v>0.8187144994735718</v>
       </c>
       <c r="Q86" t="n">
-        <v>925.9549669497503</v>
+        <v>0.3864044998772442</v>
       </c>
       <c r="R86" t="n">
-        <v>193.2005295497968</v>
+        <v>0.0005837970529682934</v>
       </c>
       <c r="S86" t="n">
-        <v>9.576079516169717</v>
+        <v>926.3021142192191</v>
       </c>
       <c r="T86" t="n">
-        <v>74.64416280186572</v>
+        <v>194.2403647875714</v>
       </c>
       <c r="U86" t="n">
-        <v>0.2913413126433113</v>
+        <v>9.579142492131494</v>
       </c>
       <c r="V86" t="n">
-        <v>0.1105846702931075</v>
-      </c>
-      <c r="W86" t="b">
+        <v>74.99131007133451</v>
+      </c>
+      <c r="W86" t="n">
+        <v>1.331176550417894</v>
+      </c>
+      <c r="X86" t="n">
+        <v>0.1136476462548845</v>
+      </c>
+      <c r="Y86" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6760,54 +7280,60 @@
         <v>0.9742164015769958</v>
       </c>
       <c r="G87" t="n">
+        <v>0.1976201001089066</v>
+      </c>
+      <c r="H87" t="n">
         <v>0.002779936417937279</v>
       </c>
-      <c r="H87" t="n">
+      <c r="I87" t="n">
         <v>828.025278046671</v>
       </c>
-      <c r="I87" t="n">
+      <c r="J87" t="n">
         <v>176.1732562382385</v>
       </c>
-      <c r="J87" t="n">
+      <c r="K87" t="n">
         <v>10.52896040961697</v>
       </c>
-      <c r="K87" t="n">
+      <c r="L87" t="n">
         <v>107.5864469633052</v>
       </c>
-      <c r="L87" t="n">
+      <c r="M87" t="n">
         <v>55.70643434808989</v>
       </c>
-      <c r="M87" t="n">
+      <c r="N87" t="n">
         <v>2.431984622362041</v>
       </c>
-      <c r="N87" t="b">
-        <v>1</v>
-      </c>
-      <c r="O87" t="n">
+      <c r="O87" t="b">
         <v>1</v>
       </c>
       <c r="P87" t="n">
-        <v>0.0009585798834450543</v>
+        <v>0.999982476234436</v>
       </c>
       <c r="Q87" t="n">
-        <v>809.0576498480506</v>
+        <v>0.5885926000773907</v>
       </c>
       <c r="R87" t="n">
-        <v>150.0005526172212</v>
+        <v>0.01384405326098204</v>
       </c>
       <c r="S87" t="n">
-        <v>9.000641797303111</v>
+        <v>800.0000235560657</v>
       </c>
       <c r="T87" t="n">
-        <v>126.5540751619257</v>
+        <v>158.6847531624352</v>
       </c>
       <c r="U87" t="n">
-        <v>29.53373072707259</v>
+        <v>9.000641996954409</v>
       </c>
       <c r="V87" t="n">
-        <v>0.9036660100481821</v>
-      </c>
-      <c r="W87" t="b">
+        <v>135.6117014539105</v>
+      </c>
+      <c r="W87" t="n">
+        <v>38.21793127228659</v>
+      </c>
+      <c r="X87" t="n">
+        <v>0.9036662096994803</v>
+      </c>
+      <c r="Y87" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6833,54 +7359,60 @@
         <v>0.966529905796051</v>
       </c>
       <c r="G88" t="n">
+        <v>0.02561299991793931</v>
+      </c>
+      <c r="H88" t="n">
         <v>0.0002481373958289623</v>
       </c>
-      <c r="H88" t="n">
+      <c r="I88" t="n">
         <v>941.4647434232262</v>
       </c>
-      <c r="I88" t="n">
+      <c r="J88" t="n">
         <v>197.0383130866234</v>
       </c>
-      <c r="J88" t="n">
+      <c r="K88" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K88" t="n">
+      <c r="L88" t="n">
         <v>2.387423592153937e-12</v>
       </c>
-      <c r="L88" t="n">
+      <c r="M88" t="n">
         <v>7.986500349943526e-12</v>
       </c>
-      <c r="M88" t="n">
+      <c r="N88" t="n">
         <v>3.309793536225845</v>
       </c>
-      <c r="N88" t="b">
-        <v>1</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0.9168035984039307</v>
+      <c r="O88" t="b">
+        <v>1</v>
       </c>
       <c r="P88" t="n">
-        <v>7.379243470495567e-05</v>
+        <v>0.877874493598938</v>
       </c>
       <c r="Q88" t="n">
-        <v>944.1741116076072</v>
+        <v>0.1810258999466896</v>
       </c>
       <c r="R88" t="n">
-        <v>197.2879143069717</v>
+        <v>9.585031511960551e-05</v>
       </c>
       <c r="S88" t="n">
+        <v>942.3031976462509</v>
+      </c>
+      <c r="T88" t="n">
+        <v>197.2130476809959</v>
+      </c>
+      <c r="U88" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T88" t="n">
-        <v>2.709368184378604</v>
-      </c>
-      <c r="U88" t="n">
-        <v>0.2496012203562259</v>
-      </c>
       <c r="V88" t="n">
+        <v>0.8384542230222678</v>
+      </c>
+      <c r="W88" t="n">
+        <v>0.1747345943804532</v>
+      </c>
+      <c r="X88" t="n">
         <v>3.309793536225845</v>
       </c>
-      <c r="W88" t="b">
+      <c r="Y88" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6906,54 +7438,60 @@
         <v>0.9555602073669434</v>
       </c>
       <c r="G89" t="n">
+        <v>0.02918379986658692</v>
+      </c>
+      <c r="H89" t="n">
         <v>0.000253947131568566</v>
       </c>
-      <c r="H89" t="n">
+      <c r="I89" t="n">
         <v>970.7952457920951</v>
       </c>
-      <c r="I89" t="n">
+      <c r="J89" t="n">
         <v>209.4559736232624</v>
       </c>
-      <c r="J89" t="n">
+      <c r="K89" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K89" t="n">
+      <c r="L89" t="n">
         <v>5.684341886080801e-13</v>
       </c>
-      <c r="L89" t="n">
+      <c r="M89" t="n">
         <v>4.405364961712621e-12</v>
       </c>
-      <c r="M89" t="n">
+      <c r="N89" t="n">
         <v>2.97740221465285</v>
       </c>
-      <c r="N89" t="b">
-        <v>1</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0.6877107620239258</v>
+      <c r="O89" t="b">
+        <v>1</v>
       </c>
       <c r="P89" t="n">
-        <v>0.0002129104541381821</v>
+        <v>0.7576003670692444</v>
       </c>
       <c r="Q89" t="n">
-        <v>958.1342269951343</v>
+        <v>0.1798985998611897</v>
       </c>
       <c r="R89" t="n">
-        <v>208.7891453574638</v>
+        <v>0.0001228055189130828</v>
       </c>
       <c r="S89" t="n">
+        <v>966.3777074088998</v>
+      </c>
+      <c r="T89" t="n">
+        <v>209.2888752562138</v>
+      </c>
+      <c r="U89" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T89" t="n">
-        <v>12.66101879696134</v>
-      </c>
-      <c r="U89" t="n">
-        <v>0.6668282657941518</v>
-      </c>
       <c r="V89" t="n">
+        <v>4.417538383195847</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0.1670983670441331</v>
+      </c>
+      <c r="X89" t="n">
         <v>2.97740221465285</v>
       </c>
-      <c r="W89" t="b">
+      <c r="Y89" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6979,54 +7517,60 @@
         <v>0.573319137096405</v>
       </c>
       <c r="G90" t="n">
+        <v>0.1531768999993801</v>
+      </c>
+      <c r="H90" t="n">
         <v>0.0009827348403632641</v>
       </c>
-      <c r="H90" t="n">
+      <c r="I90" t="n">
         <v>920.0581520444725</v>
       </c>
-      <c r="I90" t="n">
+      <c r="J90" t="n">
         <v>209.1236725574585</v>
       </c>
-      <c r="J90" t="n">
+      <c r="K90" t="n">
         <v>9.697405842036328</v>
       </c>
-      <c r="K90" t="n">
+      <c r="L90" t="n">
         <v>26.83972523418106</v>
       </c>
-      <c r="L90" t="n">
+      <c r="M90" t="n">
         <v>0.0001144867273126238</v>
       </c>
-      <c r="M90" t="n">
+      <c r="N90" t="n">
         <v>0.0806204707386744</v>
       </c>
-      <c r="N90" t="b">
-        <v>1</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0.1592088490724564</v>
+      <c r="O90" t="b">
+        <v>1</v>
       </c>
       <c r="P90" t="n">
-        <v>0.0003098166198469698</v>
+        <v>0.1536517739295959</v>
       </c>
       <c r="Q90" t="n">
-        <v>930.5117822941343</v>
+        <v>0.3575754999183118</v>
       </c>
       <c r="R90" t="n">
-        <v>208.030578759704</v>
+        <v>0.0002543953305575997</v>
       </c>
       <c r="S90" t="n">
-        <v>9.682177542113363</v>
+        <v>928.6878374183932</v>
       </c>
       <c r="T90" t="n">
-        <v>37.29335548384279</v>
+        <v>208.7213811975867</v>
       </c>
       <c r="U90" t="n">
-        <v>1.09320828448179</v>
+        <v>9.664924274177128</v>
       </c>
       <c r="V90" t="n">
-        <v>0.06539217081570925</v>
-      </c>
-      <c r="W90" t="b">
+        <v>35.46941060810173</v>
+      </c>
+      <c r="W90" t="n">
+        <v>0.4024058465991516</v>
+      </c>
+      <c r="X90" t="n">
+        <v>0.04813890287947409</v>
+      </c>
+      <c r="Y90" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7052,54 +7596,60 @@
         <v>0.9806832075119019</v>
       </c>
       <c r="G91" t="n">
+        <v>0.2558557000011206</v>
+      </c>
+      <c r="H91" t="n">
         <v>0.0001908630947582424</v>
       </c>
-      <c r="H91" t="n">
+      <c r="I91" t="n">
         <v>946.6770800594492</v>
       </c>
-      <c r="I91" t="n">
+      <c r="J91" t="n">
         <v>176.1732562382421</v>
       </c>
-      <c r="J91" t="n">
+      <c r="K91" t="n">
         <v>10.82079502788056</v>
       </c>
-      <c r="K91" t="n">
+      <c r="L91" t="n">
         <v>0.003421258042862974</v>
       </c>
-      <c r="L91" t="n">
+      <c r="M91" t="n">
         <v>46.08897562419628</v>
       </c>
-      <c r="M91" t="n">
+      <c r="N91" t="n">
         <v>0.0004894396944052914</v>
       </c>
-      <c r="N91" t="b">
-        <v>1</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0.9999995231628418</v>
+      <c r="O91" t="b">
+        <v>1</v>
       </c>
       <c r="P91" t="n">
-        <v>0.001492185285314918</v>
+        <v>0.9999833106994629</v>
       </c>
       <c r="Q91" t="n">
-        <v>800.0000772633028</v>
+        <v>1.192420999985188</v>
       </c>
       <c r="R91" t="n">
-        <v>150.0005529414757</v>
+        <v>0.008410211652517319</v>
       </c>
       <c r="S91" t="n">
-        <v>10.65599292394612</v>
+        <v>800.0000534489454</v>
       </c>
       <c r="T91" t="n">
-        <v>146.6735815381035</v>
+        <v>163.0817421923393</v>
       </c>
       <c r="U91" t="n">
-        <v>19.91627232742982</v>
+        <v>10.8316126588835</v>
       </c>
       <c r="V91" t="n">
-        <v>0.1643126642400361</v>
-      </c>
-      <c r="W91" t="b">
+        <v>146.6736053524609</v>
+      </c>
+      <c r="W91" t="n">
+        <v>32.9974615782935</v>
+      </c>
+      <c r="X91" t="n">
+        <v>0.01130707069734882</v>
+      </c>
+      <c r="Y91" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7125,54 +7675,60 @@
         <v>0.961887001991272</v>
       </c>
       <c r="G92" t="n">
+        <v>0.1523321999702603</v>
+      </c>
+      <c r="H92" t="n">
         <v>0.01351658906787634</v>
       </c>
-      <c r="H92" t="n">
+      <c r="I92" t="n">
         <v>952.7864045000421</v>
       </c>
-      <c r="I92" t="n">
+      <c r="J92" t="n">
         <v>196.3535407277273</v>
       </c>
-      <c r="J92" t="n">
+      <c r="K92" t="n">
         <v>12.67378394915221</v>
       </c>
-      <c r="K92" t="n">
+      <c r="L92" t="n">
         <v>32.31526761518865</v>
       </c>
-      <c r="L92" t="n">
+      <c r="M92" t="n">
         <v>1.110551192560678</v>
       </c>
-      <c r="M92" t="n">
+      <c r="N92" t="n">
         <v>1.64926669890075</v>
       </c>
-      <c r="N92" t="b">
-        <v>1</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0.978660523891449</v>
+      <c r="O92" t="b">
+        <v>1</v>
       </c>
       <c r="P92" t="n">
-        <v>0.003753010649234056</v>
+        <v>0.9725342988967896</v>
       </c>
       <c r="Q92" t="n">
-        <v>993.074366447731</v>
+        <v>0.4839137999806553</v>
       </c>
       <c r="R92" t="n">
-        <v>202.397504154491</v>
+        <v>0.004093831405043602</v>
       </c>
       <c r="S92" t="n">
-        <v>12.22133803359736</v>
+        <v>802.8295922222691</v>
       </c>
       <c r="T92" t="n">
-        <v>7.972694332500282</v>
+        <v>201.7163677825116</v>
       </c>
       <c r="U92" t="n">
-        <v>7.154514619324431</v>
+        <v>12.88618694878027</v>
       </c>
       <c r="V92" t="n">
-        <v>2.101712614455593</v>
-      </c>
-      <c r="W92" t="b">
+        <v>182.2720798929616</v>
+      </c>
+      <c r="W92" t="n">
+        <v>6.473378247344982</v>
+      </c>
+      <c r="X92" t="n">
+        <v>1.436863699272692</v>
+      </c>
+      <c r="Y92" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7198,54 +7754,60 @@
         <v>0.920503556728363</v>
       </c>
       <c r="G93" t="n">
+        <v>0.04467609990388155</v>
+      </c>
+      <c r="H93" t="n">
         <v>0.0002785818069241941</v>
       </c>
-      <c r="H93" t="n">
+      <c r="I93" t="n">
         <v>920.0551572371252</v>
       </c>
-      <c r="I93" t="n">
+      <c r="J93" t="n">
         <v>201.6262289489925</v>
       </c>
-      <c r="J93" t="n">
+      <c r="K93" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="K93" t="n">
+      <c r="L93" t="n">
         <v>0.16646093901727</v>
       </c>
-      <c r="L93" t="n">
+      <c r="M93" t="n">
         <v>1.171542862721253e-10</v>
       </c>
-      <c r="M93" t="n">
+      <c r="N93" t="n">
         <v>5.747329405109182</v>
       </c>
-      <c r="N93" t="b">
-        <v>1</v>
-      </c>
-      <c r="O93" t="n">
-        <v>0.9969003200531006</v>
+      <c r="O93" t="b">
+        <v>1</v>
       </c>
       <c r="P93" t="n">
-        <v>0.0001354460546281189</v>
+        <v>0.9725978970527649</v>
       </c>
       <c r="Q93" t="n">
-        <v>925.8859438848896</v>
+        <v>0.1982468001078814</v>
       </c>
       <c r="R93" t="n">
-        <v>202.1825667962769</v>
+        <v>0.0001353306142846122</v>
       </c>
       <c r="S93" t="n">
+        <v>924.7180807076431</v>
+      </c>
+      <c r="T93" t="n">
+        <v>201.7033937900675</v>
+      </c>
+      <c r="U93" t="n">
         <v>9.000641779862162</v>
       </c>
-      <c r="T93" t="n">
-        <v>5.997247586781668</v>
-      </c>
-      <c r="U93" t="n">
-        <v>0.5563378474015224</v>
-      </c>
       <c r="V93" t="n">
+        <v>4.829384409535237</v>
+      </c>
+      <c r="W93" t="n">
+        <v>0.07716484119205802</v>
+      </c>
+      <c r="X93" t="n">
         <v>5.747329405109182</v>
       </c>
-      <c r="W93" t="b">
+      <c r="Y93" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7271,54 +7833,60 @@
         <v>0.9808417558670044</v>
       </c>
       <c r="G94" t="n">
+        <v>0.1685287998989224</v>
+      </c>
+      <c r="H94" t="n">
         <v>0.01346223335713148</v>
       </c>
-      <c r="H94" t="n">
+      <c r="I94" t="n">
         <v>983.8469288560883</v>
       </c>
-      <c r="I94" t="n">
+      <c r="J94" t="n">
         <v>169.4477859692686</v>
       </c>
-      <c r="J94" t="n">
+      <c r="K94" t="n">
         <v>10.73647508767043</v>
       </c>
-      <c r="K94" t="n">
+      <c r="L94" t="n">
         <v>17.92072719901762</v>
       </c>
-      <c r="L94" t="n">
+      <c r="M94" t="n">
         <v>34.49083817515299</v>
       </c>
-      <c r="M94" t="n">
+      <c r="N94" t="n">
         <v>0.3875007081851596</v>
       </c>
-      <c r="N94" t="b">
-        <v>1</v>
-      </c>
-      <c r="O94" t="n">
-        <v>0.9999947547912598</v>
+      <c r="O94" t="b">
+        <v>1</v>
       </c>
       <c r="P94" t="n">
-        <v>0.001884272904135287</v>
+        <v>0.9998940229415894</v>
       </c>
       <c r="Q94" t="n">
-        <v>800.0000381085832</v>
+        <v>1.038731900043786</v>
       </c>
       <c r="R94" t="n">
-        <v>150.0005529163256</v>
+        <v>0.006613067351281643</v>
       </c>
       <c r="S94" t="n">
-        <v>10.91074169056781</v>
+        <v>800.0005344035815</v>
       </c>
       <c r="T94" t="n">
-        <v>165.9261635484875</v>
+        <v>163.9775272807305</v>
       </c>
       <c r="U94" t="n">
-        <v>15.04360512220995</v>
+        <v>11.23081233430889</v>
       </c>
       <c r="V94" t="n">
-        <v>0.2132341052877766</v>
-      </c>
-      <c r="W94" t="b">
+        <v>165.9256672534892</v>
+      </c>
+      <c r="W94" t="n">
+        <v>29.02057948661482</v>
+      </c>
+      <c r="X94" t="n">
+        <v>0.106836538453301</v>
+      </c>
+      <c r="Y94" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7344,54 +7912,60 @@
         <v>0.5065088272094727</v>
       </c>
       <c r="G95" t="n">
+        <v>0.09160050004720688</v>
+      </c>
+      <c r="H95" t="n">
         <v>9.540664177620783e-05</v>
       </c>
-      <c r="H95" t="n">
+      <c r="I95" t="n">
         <v>985.8937768399126</v>
       </c>
-      <c r="I95" t="n">
+      <c r="J95" t="n">
         <v>201.8109792519376</v>
       </c>
-      <c r="J95" t="n">
+      <c r="K95" t="n">
         <v>9.980027350415719</v>
       </c>
-      <c r="K95" t="n">
+      <c r="L95" t="n">
         <v>26.91468136213223</v>
       </c>
-      <c r="L95" t="n">
+      <c r="M95" t="n">
         <v>0</v>
       </c>
-      <c r="M95" t="n">
+      <c r="N95" t="n">
         <v>5.136362856816845e-06</v>
       </c>
-      <c r="N95" t="b">
-        <v>1</v>
-      </c>
-      <c r="O95" t="n">
-        <v>0.3398919999599457</v>
+      <c r="O95" t="b">
+        <v>1</v>
       </c>
       <c r="P95" t="n">
-        <v>0.0001813282287912443</v>
+        <v>0.3840338587760925</v>
       </c>
       <c r="Q95" t="n">
-        <v>971.9395462658636</v>
+        <v>0.4083006998989731</v>
       </c>
       <c r="R95" t="n">
-        <v>201.2533652131466</v>
+        <v>0.0001658270630287006</v>
       </c>
       <c r="S95" t="n">
-        <v>9.984604753091288</v>
+        <v>974.4586037303105</v>
       </c>
       <c r="T95" t="n">
-        <v>40.86891193618123</v>
+        <v>201.8189530715663</v>
       </c>
       <c r="U95" t="n">
-        <v>0.5576140387909732</v>
+        <v>9.975546426040461</v>
       </c>
       <c r="V95" t="n">
-        <v>0.004582539038425537</v>
-      </c>
-      <c r="W95" t="b">
+        <v>38.34985447173426</v>
+      </c>
+      <c r="W95" t="n">
+        <v>0.007973819628688261</v>
+      </c>
+      <c r="X95" t="n">
+        <v>0.004475788012401338</v>
+      </c>
+      <c r="Y95" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7417,54 +7991,60 @@
         <v>0.7313722372055054</v>
       </c>
       <c r="G96" t="n">
+        <v>0.1030800000298768</v>
+      </c>
+      <c r="H96" t="n">
         <v>9.798719838727266e-05</v>
       </c>
-      <c r="H96" t="n">
+      <c r="I96" t="n">
         <v>985.8937777479543</v>
       </c>
-      <c r="I96" t="n">
+      <c r="J96" t="n">
         <v>213.22179032479</v>
       </c>
-      <c r="J96" t="n">
+      <c r="K96" t="n">
         <v>11.87590853111443</v>
       </c>
-      <c r="K96" t="n">
+      <c r="L96" t="n">
         <v>22.68487255716286</v>
       </c>
-      <c r="L96" t="n">
+      <c r="M96" t="n">
         <v>0</v>
       </c>
-      <c r="M96" t="n">
+      <c r="N96" t="n">
         <v>2.191476799140446e-06</v>
       </c>
-      <c r="N96" t="b">
-        <v>1</v>
-      </c>
-      <c r="O96" t="n">
-        <v>0.3155722618103027</v>
+      <c r="O96" t="b">
+        <v>1</v>
       </c>
       <c r="P96" t="n">
-        <v>0.0001751119416439906</v>
+        <v>0.4573763906955719</v>
       </c>
       <c r="Q96" t="n">
-        <v>968.8324358270991</v>
+        <v>0.3547569999936968</v>
       </c>
       <c r="R96" t="n">
-        <v>212.8675182768862</v>
+        <v>0.000205824282602407</v>
       </c>
       <c r="S96" t="n">
-        <v>11.88075236671716</v>
+        <v>966.6731971241541</v>
       </c>
       <c r="T96" t="n">
-        <v>39.74621447801815</v>
+        <v>212.826067720395</v>
       </c>
       <c r="U96" t="n">
-        <v>0.3542720479038053</v>
+        <v>11.83692133085207</v>
       </c>
       <c r="V96" t="n">
-        <v>0.004841644125933797</v>
-      </c>
-      <c r="W96" t="b">
+        <v>41.90545318096315</v>
+      </c>
+      <c r="W96" t="n">
+        <v>0.3957226043949618</v>
+      </c>
+      <c r="X96" t="n">
+        <v>0.03898939173915927</v>
+      </c>
+      <c r="Y96" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7490,54 +8070,60 @@
         <v>0.8587307333946228</v>
       </c>
       <c r="G97" t="n">
+        <v>0.1767973999958485</v>
+      </c>
+      <c r="H97" t="n">
         <v>0.000411912944400683</v>
       </c>
-      <c r="H97" t="n">
+      <c r="I97" t="n">
         <v>940.8700876040477</v>
       </c>
-      <c r="I97" t="n">
+      <c r="J97" t="n">
         <v>203.6379405791603</v>
       </c>
-      <c r="J97" t="n">
+      <c r="K97" t="n">
         <v>9.000641764910846</v>
       </c>
-      <c r="K97" t="n">
+      <c r="L97" t="n">
         <v>43.4610780618325</v>
       </c>
-      <c r="L97" t="n">
+      <c r="M97" t="n">
         <v>1.989519660128281e-13</v>
       </c>
-      <c r="M97" t="n">
+      <c r="N97" t="n">
         <v>2.936136536507306</v>
       </c>
-      <c r="N97" t="b">
-        <v>1</v>
-      </c>
-      <c r="O97" t="n">
-        <v>0.9261912107467651</v>
+      <c r="O97" t="b">
+        <v>1</v>
       </c>
       <c r="P97" t="n">
-        <v>0.0003565092920325696</v>
+        <v>0.8571485877037048</v>
       </c>
       <c r="Q97" t="n">
-        <v>937.6236143402366</v>
+        <v>0.435849699890241</v>
       </c>
       <c r="R97" t="n">
-        <v>203.0320182731289</v>
+        <v>0.0002964336017612368</v>
       </c>
       <c r="S97" t="n">
-        <v>9.000635566424766</v>
+        <v>936.2095851385541</v>
       </c>
       <c r="T97" t="n">
-        <v>40.21460479802136</v>
+        <v>203.7658399572401</v>
       </c>
       <c r="U97" t="n">
-        <v>0.6059223060311751</v>
+        <v>9.00064178209551</v>
       </c>
       <c r="V97" t="n">
-        <v>2.936130338021226</v>
-      </c>
-      <c r="W97" t="b">
+        <v>38.80057559633883</v>
+      </c>
+      <c r="W97" t="n">
+        <v>0.1278993780800022</v>
+      </c>
+      <c r="X97" t="n">
+        <v>2.93613655369197</v>
+      </c>
+      <c r="Y97" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7563,54 +8149,60 @@
         <v>0.8382338285446167</v>
       </c>
       <c r="G98" t="n">
+        <v>0.2463492001406848</v>
+      </c>
+      <c r="H98" t="n">
         <v>0.0002063950814772397</v>
       </c>
-      <c r="H98" t="n">
+      <c r="I98" t="n">
         <v>946.0783613191138</v>
       </c>
-      <c r="I98" t="n">
+      <c r="J98" t="n">
         <v>176.1732562473737</v>
       </c>
-      <c r="J98" t="n">
+      <c r="K98" t="n">
         <v>9.580762290217397</v>
       </c>
-      <c r="K98" t="n">
+      <c r="L98" t="n">
         <v>0.002394520695474966</v>
       </c>
-      <c r="L98" t="n">
+      <c r="M98" t="n">
         <v>22.06568277670215</v>
       </c>
-      <c r="M98" t="n">
+      <c r="N98" t="n">
         <v>2.468804360944432e-06</v>
       </c>
-      <c r="N98" t="b">
-        <v>1</v>
-      </c>
-      <c r="O98" t="n">
-        <v>0.9869179129600525</v>
+      <c r="O98" t="b">
+        <v>1</v>
       </c>
       <c r="P98" t="n">
-        <v>0.0008679009624756873</v>
+        <v>0.9876689314842224</v>
       </c>
       <c r="Q98" t="n">
-        <v>832.0222165005507</v>
+        <v>1.156852800166234</v>
       </c>
       <c r="R98" t="n">
-        <v>161.5672315109592</v>
+        <v>0.002921792678534985</v>
       </c>
       <c r="S98" t="n">
-        <v>9.468221611477116</v>
+        <v>824.1142362082983</v>
       </c>
       <c r="T98" t="n">
-        <v>114.0537502978676</v>
+        <v>171.6034038574118</v>
       </c>
       <c r="U98" t="n">
-        <v>7.459658040287707</v>
+        <v>9.45856370747596</v>
       </c>
       <c r="V98" t="n">
-        <v>0.1125431475446419</v>
-      </c>
-      <c r="W98" t="b">
+        <v>121.9617305901201</v>
+      </c>
+      <c r="W98" t="n">
+        <v>17.49583038674027</v>
+      </c>
+      <c r="X98" t="n">
+        <v>0.1222010515457974</v>
+      </c>
+      <c r="Y98" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7636,54 +8228,60 @@
         <v>0.8871044516563416</v>
       </c>
       <c r="G99" t="n">
+        <v>0.09269850002601743</v>
+      </c>
+      <c r="H99" t="n">
         <v>0.0004035303718410432</v>
       </c>
-      <c r="H99" t="n">
+      <c r="I99" t="n">
         <v>940.8700912480335</v>
       </c>
-      <c r="I99" t="n">
+      <c r="J99" t="n">
         <v>201.0474114737297</v>
       </c>
-      <c r="J99" t="n">
+      <c r="K99" t="n">
         <v>9.000641570597013</v>
       </c>
-      <c r="K99" t="n">
+      <c r="L99" t="n">
         <v>54.13808771620324</v>
       </c>
-      <c r="L99" t="n">
+      <c r="M99" t="n">
         <v>3.950617610826157e-12</v>
       </c>
-      <c r="M99" t="n">
+      <c r="N99" t="n">
         <v>1.932830412418125</v>
       </c>
-      <c r="N99" t="b">
-        <v>1</v>
-      </c>
-      <c r="O99" t="n">
-        <v>0.9502797722816467</v>
+      <c r="O99" t="b">
+        <v>1</v>
       </c>
       <c r="P99" t="n">
-        <v>0.0004196920490358025</v>
+        <v>0.9332478046417236</v>
       </c>
       <c r="Q99" t="n">
-        <v>936.602498644831</v>
+        <v>0.4653634999413043</v>
       </c>
       <c r="R99" t="n">
-        <v>201.7020376581893</v>
+        <v>0.0003679298970382661</v>
       </c>
       <c r="S99" t="n">
-        <v>9.000640537698938</v>
+        <v>935.1732513708779</v>
       </c>
       <c r="T99" t="n">
-        <v>49.87049511300074</v>
+        <v>201.422463848071</v>
       </c>
       <c r="U99" t="n">
-        <v>0.6546261844556511</v>
+        <v>9.000641856381241</v>
       </c>
       <c r="V99" t="n">
-        <v>1.932829379520051</v>
-      </c>
-      <c r="W99" t="b">
+        <v>48.44124783904761</v>
+      </c>
+      <c r="W99" t="n">
+        <v>0.3750523743373151</v>
+      </c>
+      <c r="X99" t="n">
+        <v>1.932830698202354</v>
+      </c>
+      <c r="Y99" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7709,54 +8307,60 @@
         <v>0.7210264205932617</v>
       </c>
       <c r="G100" t="n">
+        <v>0.09544899989850819</v>
+      </c>
+      <c r="H100" t="n">
         <v>0.0001128785734181292</v>
       </c>
-      <c r="H100" t="n">
+      <c r="I100" t="n">
         <v>985.8937766144934</v>
       </c>
-      <c r="I100" t="n">
+      <c r="J100" t="n">
         <v>202.0729167839633</v>
       </c>
-      <c r="J100" t="n">
+      <c r="K100" t="n">
         <v>9.000641527014711</v>
       </c>
-      <c r="K100" t="n">
+      <c r="L100" t="n">
         <v>35.53062828852728</v>
       </c>
-      <c r="L100" t="n">
+      <c r="M100" t="n">
         <v>6.245317308639642e-05</v>
       </c>
-      <c r="M100" t="n">
+      <c r="N100" t="n">
         <v>0.08824434878226306</v>
       </c>
-      <c r="N100" t="b">
-        <v>1</v>
-      </c>
-      <c r="O100" t="n">
-        <v>0.6351427435874939</v>
+      <c r="O100" t="b">
+        <v>1</v>
       </c>
       <c r="P100" t="n">
-        <v>0.0002099389093928039</v>
+        <v>0.676930844783783</v>
       </c>
       <c r="Q100" t="n">
-        <v>971.8709134238034</v>
+        <v>0.5007621999830008</v>
       </c>
       <c r="R100" t="n">
-        <v>201.3920574043729</v>
+        <v>0.0002089121553581208</v>
       </c>
       <c r="S100" t="n">
-        <v>9.000641559805413</v>
+        <v>975.4527167065283</v>
       </c>
       <c r="T100" t="n">
-        <v>49.55349147921731</v>
+        <v>202.1394580752661</v>
       </c>
       <c r="U100" t="n">
-        <v>0.6809218327634596</v>
+        <v>9.000641556267123</v>
       </c>
       <c r="V100" t="n">
-        <v>0.08824438157296477</v>
-      </c>
-      <c r="W100" t="b">
+        <v>45.97168819649232</v>
+      </c>
+      <c r="W100" t="n">
+        <v>0.06647883812968303</v>
+      </c>
+      <c r="X100" t="n">
+        <v>0.08824437803467511</v>
+      </c>
+      <c r="Y100" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7782,54 +8386,60 @@
         <v>0.9841193556785583</v>
       </c>
       <c r="G101" t="n">
+        <v>0.1911677001044154</v>
+      </c>
+      <c r="H101" t="n">
         <v>0.0001908497797558084</v>
       </c>
-      <c r="H101" t="n">
+      <c r="I101" t="n">
         <v>938.5798568635637</v>
       </c>
-      <c r="I101" t="n">
+      <c r="J101" t="n">
         <v>176.1735528344169</v>
       </c>
-      <c r="J101" t="n">
+      <c r="K101" t="n">
         <v>11.08656396636439</v>
       </c>
-      <c r="K101" t="n">
+      <c r="L101" t="n">
         <v>0.008120366670027579</v>
       </c>
-      <c r="L101" t="n">
+      <c r="M101" t="n">
         <v>36.62177286801753</v>
       </c>
-      <c r="M101" t="n">
+      <c r="N101" t="n">
         <v>0.001110204793274505</v>
       </c>
-      <c r="N101" t="b">
-        <v>1</v>
-      </c>
-      <c r="O101" t="n">
-        <v>0.9999825954437256</v>
+      <c r="O101" t="b">
+        <v>1</v>
       </c>
       <c r="P101" t="n">
-        <v>0.00169484899379313</v>
+        <v>0.9998763799667358</v>
       </c>
       <c r="Q101" t="n">
-        <v>800.0000678345394</v>
+        <v>0.9469119999557734</v>
       </c>
       <c r="R101" t="n">
-        <v>150.2904852533921</v>
+        <v>0.005378850270062685</v>
       </c>
       <c r="S101" t="n">
-        <v>10.89822481162234</v>
+        <v>800.0017159111572</v>
       </c>
       <c r="T101" t="n">
-        <v>138.5879093956943</v>
+        <v>164.8636861873947</v>
       </c>
       <c r="U101" t="n">
-        <v>10.73870528699274</v>
+        <v>11.17490305718081</v>
       </c>
       <c r="V101" t="n">
-        <v>0.1894493595353168</v>
-      </c>
-      <c r="W101" t="b">
+        <v>138.5862613190765</v>
+      </c>
+      <c r="W101" t="n">
+        <v>25.31190622099527</v>
+      </c>
+      <c r="X101" t="n">
+        <v>0.08722888602315138</v>
+      </c>
+      <c r="Y101" t="b">
         <v>1</v>
       </c>
     </row>

--- a/export_dati/06_Step6_Simulazione_Massiva_100.xlsx
+++ b/export_dati/06_Step6_Simulazione_Massiva_100.xlsx
@@ -553,70 +553,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>846.35473260961</v>
+        <v>863.4770745195466</v>
       </c>
       <c r="D2" t="n">
-        <v>9.678010236705797</v>
+        <v>6.756043538619733</v>
       </c>
       <c r="E2" t="n">
-        <v>201.2301164142077</v>
+        <v>206.036686911038</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6594186425209045</v>
+        <v>0.8507716059684753</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1148099000565708</v>
+        <v>0.22394990012981</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008911140612326562</v>
+        <v>0.001641420414671302</v>
       </c>
       <c r="I2" t="n">
-        <v>920.0548507071468</v>
+        <v>929.0271678735249</v>
       </c>
       <c r="J2" t="n">
-        <v>201.2411827932042</v>
+        <v>206.0366900492533</v>
       </c>
       <c r="K2" t="n">
-        <v>9.711011639075149</v>
+        <v>9.000682447809323</v>
       </c>
       <c r="L2" t="n">
-        <v>73.7001180975368</v>
+        <v>65.55009335397835</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01106637899650309</v>
+        <v>3.138215333819971e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03300140236935256</v>
+        <v>2.24463890918959</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7568662166595459</v>
+        <v>0.9937140345573425</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4123388000298291</v>
+        <v>1.364118500147015</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0005708818789571524</v>
+        <v>0.0004225433804094791</v>
       </c>
       <c r="S2" t="n">
-        <v>922.2980210297865</v>
+        <v>926.6309168893274</v>
       </c>
       <c r="T2" t="n">
-        <v>201.5339916121708</v>
+        <v>205.1592652049273</v>
       </c>
       <c r="U2" t="n">
-        <v>9.790420239017783</v>
+        <v>9.000641744472151</v>
       </c>
       <c r="V2" t="n">
-        <v>75.94328842017649</v>
+        <v>63.15384236978082</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3038751979631797</v>
+        <v>0.8774217061107095</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1124100023119858</v>
+        <v>2.244598205852419</v>
       </c>
       <c r="Y2" t="b">
         <v>1</v>
@@ -628,74 +628,74 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1039.581685020515</v>
+        <v>964.2254725998696</v>
       </c>
       <c r="D3" t="n">
-        <v>10.96782296594122</v>
+        <v>6.100727872701607</v>
       </c>
       <c r="E3" t="n">
-        <v>195.7838520794682</v>
+        <v>191.825603674138</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6184679865837097</v>
+        <v>0.7307463884353638</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1300379000604153</v>
+        <v>0.06619199994020164</v>
       </c>
       <c r="H3" t="n">
-        <v>9.742625115904957e-05</v>
+        <v>0.001032155007123947</v>
       </c>
       <c r="I3" t="n">
-        <v>985.8937770676032</v>
+        <v>964.2254725998694</v>
       </c>
       <c r="J3" t="n">
-        <v>195.7838875835934</v>
+        <v>191.825603674138</v>
       </c>
       <c r="K3" t="n">
-        <v>10.96782296594122</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L3" t="n">
-        <v>53.68790795291193</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55041252078081e-05</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.899913907160555</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9643027782440186</v>
+        <v>0.8290861845016479</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4306553001515567</v>
+        <v>0.5464034001342952</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0002911596384365112</v>
+        <v>7.189831376308575e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>974.6592620854868</v>
+        <v>961.775985358845</v>
       </c>
       <c r="T3" t="n">
-        <v>195.8000885688702</v>
+        <v>191.9618184856335</v>
       </c>
       <c r="U3" t="n">
-        <v>10.94245247530181</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V3" t="n">
-        <v>64.92242293502829</v>
+        <v>2.449487241024599</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01623648940193334</v>
+        <v>0.1362148114954493</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02537049063940522</v>
+        <v>2.899913907160555</v>
       </c>
       <c r="Y3" t="b">
         <v>1</v>
@@ -711,70 +711,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>966.3537262610911</v>
+        <v>978.6619930305176</v>
       </c>
       <c r="D4" t="n">
-        <v>5.389466018585829</v>
+        <v>5.1903593055076</v>
       </c>
       <c r="E4" t="n">
-        <v>191.0819217970761</v>
+        <v>202.24996343845</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9324119091033936</v>
+        <v>0.7307463884353638</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05062859994359314</v>
+        <v>0.06858119997195899</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000253947131568566</v>
+        <v>0.001032155007123947</v>
       </c>
       <c r="I4" t="n">
-        <v>966.3537262610907</v>
+        <v>978.6619930305287</v>
       </c>
       <c r="J4" t="n">
-        <v>191.0819217970763</v>
+        <v>202.2499634384501</v>
       </c>
       <c r="K4" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="L4" t="n">
-        <v>3.410605131648481e-13</v>
+        <v>1.114131009671837e-11</v>
       </c>
       <c r="M4" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="N4" t="n">
-        <v>3.611175761276333</v>
+        <v>3.810282474354562</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0.95229572057724</v>
+        <v>0.977730929851532</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.195089700166136</v>
+        <v>0.4984098998829722</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0001709491480141878</v>
+        <v>0.0001072272643796168</v>
       </c>
       <c r="S4" t="n">
-        <v>961.5250387179119</v>
+        <v>972.6628751651358</v>
       </c>
       <c r="T4" t="n">
-        <v>191.5713759598443</v>
+        <v>202.153442427246</v>
       </c>
       <c r="U4" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V4" t="n">
-        <v>4.828687543179171</v>
+        <v>5.999117865381777</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4894541627682543</v>
+        <v>0.0965210112039756</v>
       </c>
       <c r="X4" t="n">
-        <v>3.611175761276333</v>
+        <v>3.810282474354562</v>
       </c>
       <c r="Y4" t="b">
         <v>1</v>
@@ -786,74 +786,74 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>945.074197147824</v>
+        <v>868.2168670683342</v>
       </c>
       <c r="D5" t="n">
-        <v>10.31564330773237</v>
+        <v>7.82025280204405</v>
       </c>
       <c r="E5" t="n">
-        <v>108.2684665753791</v>
+        <v>203.7268990784758</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9806832075119019</v>
+        <v>0.8485633730888367</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2745032000821084</v>
+        <v>0.2313975000288337</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01705425418913364</v>
+        <v>0.001641420414671302</v>
       </c>
       <c r="I5" t="n">
-        <v>970.2248744616279</v>
+        <v>929.0269671066073</v>
       </c>
       <c r="J5" t="n">
-        <v>166.3955239495973</v>
+        <v>203.7268990784758</v>
       </c>
       <c r="K5" t="n">
-        <v>10.2422937265863</v>
+        <v>9.000641693387658</v>
       </c>
       <c r="L5" t="n">
-        <v>25.15067731380395</v>
+        <v>60.81010003827316</v>
       </c>
       <c r="M5" t="n">
-        <v>58.12705737421825</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07334958114606671</v>
+        <v>1.180388891343608</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9999994039535522</v>
+        <v>0.9792587757110596</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9226595000363886</v>
+        <v>1.334037600085139</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02252509817481041</v>
+        <v>0.0003816164389718324</v>
       </c>
       <c r="S5" t="n">
-        <v>800.0000002337264</v>
+        <v>926.6965405481463</v>
       </c>
       <c r="T5" t="n">
-        <v>156.5149942513265</v>
+        <v>203.1251695256903</v>
       </c>
       <c r="U5" t="n">
-        <v>9.183113562909172</v>
+        <v>9.000641658335425</v>
       </c>
       <c r="V5" t="n">
-        <v>145.0741969140976</v>
+        <v>58.47967347981216</v>
       </c>
       <c r="W5" t="n">
-        <v>48.24652767594745</v>
+        <v>0.6017295527854856</v>
       </c>
       <c r="X5" t="n">
-        <v>1.132529744823193</v>
+        <v>1.180388856291375</v>
       </c>
       <c r="Y5" t="b">
         <v>1</v>
@@ -869,70 +869,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>936.9104665539262</v>
+        <v>964.1300016773724</v>
       </c>
       <c r="D6" t="n">
-        <v>9.584612612311092</v>
+        <v>8.075113912420624</v>
       </c>
       <c r="E6" t="n">
-        <v>127.5048688562275</v>
+        <v>144.2625365949665</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9835739135742188</v>
+        <v>0.6357733607292175</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2413848000578582</v>
+        <v>0.4911432000808418</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001278240233659744</v>
+        <v>0.0008352872682735324</v>
       </c>
       <c r="I6" t="n">
-        <v>857.2976406733651</v>
+        <v>964.1300016070304</v>
       </c>
       <c r="J6" t="n">
-        <v>176.1732637380991</v>
+        <v>173.7371835006011</v>
       </c>
       <c r="K6" t="n">
-        <v>9.740868471732181</v>
+        <v>9.000641779985012</v>
       </c>
       <c r="L6" t="n">
-        <v>79.6128258805611</v>
+        <v>7.034202553768409e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>48.66839488187156</v>
+        <v>29.47464690563459</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1562558594210888</v>
+        <v>0.9255278675643872</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9999877214431763</v>
+        <v>0.9953216910362244</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8820146000944078</v>
+        <v>1.81189849996008</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01039397343993187</v>
+        <v>0.001653288374654949</v>
       </c>
       <c r="S6" t="n">
-        <v>800.0000220735074</v>
+        <v>817.9451949149911</v>
       </c>
       <c r="T6" t="n">
-        <v>160.6200746000245</v>
+        <v>150.6928710290704</v>
       </c>
       <c r="U6" t="n">
-        <v>9.213440495759903</v>
+        <v>9.000639696119682</v>
       </c>
       <c r="V6" t="n">
-        <v>136.9104444804188</v>
+        <v>146.1848067623813</v>
       </c>
       <c r="W6" t="n">
-        <v>33.11520574379702</v>
+        <v>6.430334434103827</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3711721165511896</v>
+        <v>0.925525783699058</v>
       </c>
       <c r="Y6" t="b">
         <v>1</v>
@@ -944,74 +944,74 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>866.2846900080363</v>
+        <v>920.55495001203</v>
       </c>
       <c r="D7" t="n">
-        <v>8.995260756589422</v>
+        <v>10.89601601904119</v>
       </c>
       <c r="E7" t="n">
-        <v>176.6771407193691</v>
+        <v>131.9176933424709</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6979028582572937</v>
+        <v>0.7186955213546753</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1536425999365747</v>
+        <v>0.4821589000057429</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001823191996663809</v>
+        <v>0.000834758160635829</v>
       </c>
       <c r="I7" t="n">
-        <v>920.0234447258514</v>
+        <v>920.5577682708407</v>
       </c>
       <c r="J7" t="n">
-        <v>176.6771407193691</v>
+        <v>173.7376566381731</v>
       </c>
       <c r="K7" t="n">
-        <v>9.438119575974012</v>
+        <v>10.89610858497909</v>
       </c>
       <c r="L7" t="n">
-        <v>53.73875471781514</v>
+        <v>0.002818258810748375</v>
       </c>
       <c r="M7" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>41.81996329570225</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4428588193845897</v>
+        <v>9.256593790318846e-05</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8673694133758545</v>
+        <v>0.9997448325157166</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4963392000645399</v>
+        <v>1.996571299852803</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0006938831647858024</v>
+        <v>0.001581317279487848</v>
       </c>
       <c r="S7" t="n">
-        <v>941.0793728588742</v>
+        <v>802.0274998333349</v>
       </c>
       <c r="T7" t="n">
-        <v>179.247224021337</v>
+        <v>150.0005519897055</v>
       </c>
       <c r="U7" t="n">
-        <v>9.106679146139149</v>
+        <v>10.74201411224709</v>
       </c>
       <c r="V7" t="n">
-        <v>74.79468285083794</v>
+        <v>118.5274501786951</v>
       </c>
       <c r="W7" t="n">
-        <v>2.570083301967827</v>
+        <v>18.08285864723459</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1114183895497263</v>
+        <v>0.1540019067941003</v>
       </c>
       <c r="Y7" t="b">
         <v>1</v>
@@ -1023,74 +1023,74 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>941.236377616053</v>
+        <v>929.6487242872754</v>
       </c>
       <c r="D8" t="n">
-        <v>5.830052991279411</v>
+        <v>12.66081088891495</v>
       </c>
       <c r="E8" t="n">
-        <v>206.5003175015056</v>
+        <v>162.271849181696</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9655842781066895</v>
+        <v>0.6700266003608704</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03577279997989535</v>
+        <v>0.4825254001189023</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0002531284117139876</v>
+        <v>0.0008368453127332032</v>
       </c>
       <c r="I8" t="n">
-        <v>940.869883521915</v>
+        <v>929.6487255194605</v>
       </c>
       <c r="J8" t="n">
-        <v>206.5003175015104</v>
+        <v>173.7371843695789</v>
       </c>
       <c r="K8" t="n">
-        <v>9.000641779862162</v>
+        <v>12.66081088366578</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3664940941380337</v>
+        <v>1.232185127264529e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>4.774847184307873e-12</v>
+        <v>11.46533518788294</v>
       </c>
       <c r="N8" t="n">
-        <v>3.170588788582752</v>
+        <v>5.249162882137171e-09</v>
       </c>
       <c r="O8" t="b">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8306910991668701</v>
+        <v>0.2854719460010529</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2052114999387413</v>
+        <v>3.038330900017172</v>
       </c>
       <c r="R8" t="n">
-        <v>8.185818296624348e-05</v>
+        <v>0.001569393207319081</v>
       </c>
       <c r="S8" t="n">
-        <v>942.1007516985072</v>
+        <v>826.4950908113385</v>
       </c>
       <c r="T8" t="n">
-        <v>206.4526096379934</v>
+        <v>169.5830814489993</v>
       </c>
       <c r="U8" t="n">
-        <v>9.000641779862162</v>
+        <v>12.43293157320231</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8643740824542192</v>
+        <v>103.1536334759369</v>
       </c>
       <c r="W8" t="n">
-        <v>0.04770786351221545</v>
+        <v>7.311232267303296</v>
       </c>
       <c r="X8" t="n">
-        <v>3.170588788582752</v>
+        <v>0.2278793157126344</v>
       </c>
       <c r="Y8" t="b">
         <v>1</v>
@@ -1102,74 +1102,74 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>877.0934940793688</v>
+        <v>961.8165393036306</v>
       </c>
       <c r="D9" t="n">
-        <v>8.507304316587792</v>
+        <v>10.17705382690166</v>
       </c>
       <c r="E9" t="n">
-        <v>190.8029197760436</v>
+        <v>146.7127562677171</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8222670555114746</v>
+        <v>0.6767300963401794</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1128199999220669</v>
+        <v>0.4964979998767376</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001392161007970572</v>
+        <v>0.0008354719611816108</v>
       </c>
       <c r="I9" t="n">
-        <v>925.9037157961071</v>
+        <v>961.8195199358701</v>
       </c>
       <c r="J9" t="n">
-        <v>190.8029197760437</v>
+        <v>173.737503088327</v>
       </c>
       <c r="K9" t="n">
-        <v>9.000540538610286</v>
+        <v>10.1771914922531</v>
       </c>
       <c r="L9" t="n">
-        <v>48.81022171673828</v>
+        <v>0.002980632239427905</v>
       </c>
       <c r="M9" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>27.02474682060992</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4932362220224942</v>
+        <v>0.0001376653514491011</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8811309337615967</v>
+        <v>0.9950148463249207</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4324777000583708</v>
+        <v>3.22749359998852</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0004764958284795284</v>
+        <v>0.001672614947892725</v>
       </c>
       <c r="S9" t="n">
-        <v>936.5260359180689</v>
+        <v>816.7245196361405</v>
       </c>
       <c r="T9" t="n">
-        <v>192.1167233077616</v>
+        <v>153.8091321446313</v>
       </c>
       <c r="U9" t="n">
-        <v>9.000641305933799</v>
+        <v>10.04717325624213</v>
       </c>
       <c r="V9" t="n">
-        <v>59.4325418387001</v>
+        <v>145.0920196674901</v>
       </c>
       <c r="W9" t="n">
-        <v>1.313803531717923</v>
+        <v>7.096375876914152</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4933369893460071</v>
+        <v>0.1298805706595285</v>
       </c>
       <c r="Y9" t="b">
         <v>1</v>
@@ -1185,70 +1185,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>861.2941101957704</v>
+        <v>874.0869389934916</v>
       </c>
       <c r="D10" t="n">
-        <v>7.456844375297822</v>
+        <v>8.903517098889219</v>
       </c>
       <c r="E10" t="n">
-        <v>183.8016666056681</v>
+        <v>212.1431163763257</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9792359471321106</v>
+        <v>0.7533094882965088</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1166550000198185</v>
+        <v>0.3362185000441968</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0004074503376614302</v>
+        <v>0.001640764763578773</v>
       </c>
       <c r="I10" t="n">
-        <v>940.8703895322254</v>
+        <v>929.0269669700332</v>
       </c>
       <c r="J10" t="n">
-        <v>183.8016390686678</v>
+        <v>212.1431803900632</v>
       </c>
       <c r="K10" t="n">
-        <v>9.00074240025527</v>
+        <v>9.000641667451532</v>
       </c>
       <c r="L10" t="n">
-        <v>79.57627933645506</v>
+        <v>54.94002797654161</v>
       </c>
       <c r="M10" t="n">
-        <v>2.75370003066655e-05</v>
+        <v>6.401373752851214e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>1.543898024957448</v>
+        <v>0.09712456856231277</v>
       </c>
       <c r="O10" t="b">
         <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9812757968902588</v>
+        <v>0.9000845551490784</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4082530001178384</v>
+        <v>0.9040955000091344</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0006709850276820362</v>
+        <v>0.00038534463965334</v>
       </c>
       <c r="S10" t="n">
-        <v>937.7940921391931</v>
+        <v>928.9880637667362</v>
       </c>
       <c r="T10" t="n">
-        <v>186.014746591795</v>
+        <v>210.68593686549</v>
       </c>
       <c r="U10" t="n">
-        <v>9.000640575937489</v>
+        <v>9.000641506884289</v>
       </c>
       <c r="V10" t="n">
-        <v>76.49998194342277</v>
+        <v>54.90112477324465</v>
       </c>
       <c r="W10" t="n">
-        <v>2.213079986126957</v>
+        <v>1.457179510835687</v>
       </c>
       <c r="X10" t="n">
-        <v>1.543796200639667</v>
+        <v>0.09712440799506972</v>
       </c>
       <c r="Y10" t="b">
         <v>1</v>
@@ -1260,74 +1260,74 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>843.8714565189717</v>
+        <v>966.3702073861947</v>
       </c>
       <c r="D11" t="n">
-        <v>8.913834110200215</v>
+        <v>11.89632430453699</v>
       </c>
       <c r="E11" t="n">
-        <v>204.2353346863231</v>
+        <v>129.2772934821159</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9629010558128357</v>
+        <v>0.5425188541412354</v>
       </c>
       <c r="G11" t="n">
-        <v>0.09964590007439256</v>
+        <v>0.6344544000457972</v>
       </c>
       <c r="H11" t="n">
-        <v>0.001197295030578971</v>
+        <v>0.01433388702571392</v>
       </c>
       <c r="I11" t="n">
-        <v>925.9037179955458</v>
+        <v>964.8039689291198</v>
       </c>
       <c r="J11" t="n">
-        <v>204.2353346863231</v>
+        <v>167.3097805342292</v>
       </c>
       <c r="K11" t="n">
-        <v>9.14054197930473</v>
+        <v>11.8963242893919</v>
       </c>
       <c r="L11" t="n">
-        <v>82.03226147657404</v>
+        <v>1.56623845707486</v>
       </c>
       <c r="M11" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>38.0324870521134</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2267078691045157</v>
+        <v>1.514508873867726e-08</v>
       </c>
       <c r="O11" t="b">
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9127441644668579</v>
+        <v>0.9994769692420959</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4021340999752283</v>
+        <v>1.510406700195745</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0006975957076065242</v>
+        <v>0.002670569578185678</v>
       </c>
       <c r="S11" t="n">
-        <v>930.5358388212916</v>
+        <v>800.0000420883573</v>
       </c>
       <c r="T11" t="n">
-        <v>204.4391400831735</v>
+        <v>150.0005529423611</v>
       </c>
       <c r="U11" t="n">
-        <v>9.044953600465856</v>
+        <v>11.53846191938536</v>
       </c>
       <c r="V11" t="n">
-        <v>86.66438230231984</v>
+        <v>166.3701652978374</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2038053968503846</v>
+        <v>20.72325946024526</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1311194902656414</v>
+        <v>0.3578623851516269</v>
       </c>
       <c r="Y11" t="b">
         <v>1</v>
@@ -1343,70 +1343,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>956.1855677025339</v>
+        <v>956.5626946838948</v>
       </c>
       <c r="D12" t="n">
-        <v>9.609036295539731</v>
+        <v>9.307627823649433</v>
       </c>
       <c r="E12" t="n">
-        <v>120.7957395002968</v>
+        <v>120.9567867658997</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9834682941436768</v>
+        <v>0.6767300963401794</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1714788000099361</v>
+        <v>0.3193496000021696</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0002063950814772397</v>
+        <v>0.02174675464630127</v>
       </c>
       <c r="I12" t="n">
-        <v>956.2139859828969</v>
+        <v>956.5626926228375</v>
       </c>
       <c r="J12" t="n">
-        <v>176.1732562784816</v>
+        <v>167.3097816079831</v>
       </c>
       <c r="K12" t="n">
-        <v>9.609087940925981</v>
+        <v>9.307627821158924</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02841828036298466</v>
+        <v>2.061057330138283e-06</v>
       </c>
       <c r="M12" t="n">
-        <v>55.37751677818477</v>
+        <v>46.35299484208342</v>
       </c>
       <c r="N12" t="n">
-        <v>5.164538625024306e-05</v>
+        <v>2.490509132258012e-09</v>
       </c>
       <c r="O12" t="b">
         <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9999974966049194</v>
+        <v>0.9999653100967407</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5958890998736024</v>
+        <v>0.8663240000605583</v>
       </c>
       <c r="R12" t="n">
-        <v>0.01383373141288757</v>
+        <v>0.001635634689591825</v>
       </c>
       <c r="S12" t="n">
-        <v>800.0000431862165</v>
+        <v>814.8955627568181</v>
       </c>
       <c r="T12" t="n">
-        <v>158.7743226305047</v>
+        <v>150.0005525287171</v>
       </c>
       <c r="U12" t="n">
-        <v>9.036969910669169</v>
+        <v>9.210541250526582</v>
       </c>
       <c r="V12" t="n">
-        <v>156.1855245163174</v>
+        <v>141.6671319270768</v>
       </c>
       <c r="W12" t="n">
-        <v>37.97858313020794</v>
+        <v>29.04376576281744</v>
       </c>
       <c r="X12" t="n">
-        <v>0.5720663848705616</v>
+        <v>0.09708657312285141</v>
       </c>
       <c r="Y12" t="b">
         <v>1</v>
@@ -1418,74 +1418,74 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>882.9238867430507</v>
+        <v>957.9007298454952</v>
       </c>
       <c r="D13" t="n">
-        <v>7.391527344970747</v>
+        <v>4.104445614920706</v>
       </c>
       <c r="E13" t="n">
-        <v>179.9914727762026</v>
+        <v>178.1293633295699</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9216844439506531</v>
+        <v>0.7250093221664429</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1425656999927014</v>
+        <v>0.07744869985617697</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00115188374184072</v>
+        <v>0.001032155007123947</v>
       </c>
       <c r="I13" t="n">
-        <v>925.903722391216</v>
+        <v>957.9007298454983</v>
       </c>
       <c r="J13" t="n">
-        <v>179.3816766502316</v>
+        <v>178.1293633295694</v>
       </c>
       <c r="K13" t="n">
-        <v>9.000641767919562</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L13" t="n">
-        <v>42.97983564816525</v>
+        <v>3.069544618483633e-12</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6097961259710019</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="N13" t="n">
-        <v>1.609114422948815</v>
+        <v>4.896196164941456</v>
       </c>
       <c r="O13" t="b">
         <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9197916984558105</v>
+        <v>0.9952362179756165</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.420236499980092</v>
+        <v>0.2965941000729799</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0005262662889435887</v>
+        <v>0.0002002094261115417</v>
       </c>
       <c r="S13" t="n">
-        <v>942.3892829258076</v>
+        <v>954.1891138489104</v>
       </c>
       <c r="T13" t="n">
-        <v>181.8904781820779</v>
+        <v>178.9364447615191</v>
       </c>
       <c r="U13" t="n">
-        <v>9.000639799986432</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V13" t="n">
-        <v>59.46539618275688</v>
+        <v>3.711615996584783</v>
       </c>
       <c r="W13" t="n">
-        <v>1.899005405875243</v>
+        <v>0.8070814319492285</v>
       </c>
       <c r="X13" t="n">
-        <v>1.609112455015685</v>
+        <v>4.896196164941456</v>
       </c>
       <c r="Y13" t="b">
         <v>1</v>
@@ -1497,74 +1497,74 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>848.7136186284401</v>
+        <v>925.0400309044297</v>
       </c>
       <c r="D14" t="n">
-        <v>9.977749373670072</v>
+        <v>10.06704279456354</v>
       </c>
       <c r="E14" t="n">
-        <v>198.2654474321201</v>
+        <v>125.0040432603061</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6788570880889893</v>
+        <v>0.720072865486145</v>
       </c>
       <c r="G14" t="n">
-        <v>0.09052939992398024</v>
+        <v>0.1753734999801964</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0009468119242228568</v>
+        <v>0.02472542598843575</v>
       </c>
       <c r="I14" t="n">
-        <v>920.0548587821094</v>
+        <v>925.0400309045317</v>
       </c>
       <c r="J14" t="n">
-        <v>198.2654474321198</v>
+        <v>167.3098316411032</v>
       </c>
       <c r="K14" t="n">
-        <v>9.977749373670072</v>
+        <v>10.06716860078033</v>
       </c>
       <c r="L14" t="n">
-        <v>71.34124015366922</v>
+        <v>1.019770934362896e-10</v>
       </c>
       <c r="M14" t="n">
-        <v>3.126388037344441e-13</v>
+        <v>42.30578838079711</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>0.0001258062167845964</v>
       </c>
       <c r="O14" t="b">
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6549311280250549</v>
+        <v>0.9999381303787231</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3376397998072207</v>
+        <v>1.8865934999194</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0005301035125739872</v>
+        <v>0.001486682798713446</v>
       </c>
       <c r="S14" t="n">
-        <v>919.6533529534845</v>
+        <v>808.1776303749591</v>
       </c>
       <c r="T14" t="n">
-        <v>198.8376977159488</v>
+        <v>150.000552399261</v>
       </c>
       <c r="U14" t="n">
-        <v>10.0826193860212</v>
+        <v>9.955716204328713</v>
       </c>
       <c r="V14" t="n">
-        <v>70.93973432504436</v>
+        <v>116.8624005294706</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5722502838287369</v>
+        <v>24.99650913895488</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1048700123511246</v>
+        <v>0.1113265902348282</v>
       </c>
       <c r="Y14" t="b">
         <v>1</v>
@@ -1576,74 +1576,74 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>961.807244162299</v>
+        <v>848.8299954072052</v>
       </c>
       <c r="D15" t="n">
-        <v>5.776420331070021</v>
+        <v>7.740394859456654</v>
       </c>
       <c r="E15" t="n">
-        <v>202.8315364014022</v>
+        <v>216.9791780068796</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7952963709831238</v>
+        <v>0.847973108291626</v>
       </c>
       <c r="G15" t="n">
-        <v>0.03968399995937943</v>
+        <v>0.9275811999104917</v>
       </c>
       <c r="H15" t="n">
-        <v>0.000253947131568566</v>
+        <v>0.001640737871639431</v>
       </c>
       <c r="I15" t="n">
-        <v>961.8072441622284</v>
+        <v>929.0294788076374</v>
       </c>
       <c r="J15" t="n">
-        <v>202.8315364014029</v>
+        <v>216.9792101479127</v>
       </c>
       <c r="K15" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641777326312</v>
       </c>
       <c r="L15" t="n">
-        <v>7.059952622512355e-11</v>
+        <v>80.1994834004322</v>
       </c>
       <c r="M15" t="n">
-        <v>7.105427357601002e-13</v>
+        <v>3.214103307414007e-05</v>
       </c>
       <c r="N15" t="n">
-        <v>3.224221448792141</v>
+        <v>1.260246917869658</v>
       </c>
       <c r="O15" t="b">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8876581192016602</v>
+        <v>0.9912964105606079</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1741335999686271</v>
+        <v>1.488595700124279</v>
       </c>
       <c r="R15" t="n">
-        <v>9.255448094336316e-05</v>
+        <v>0.0006200964562594891</v>
       </c>
       <c r="S15" t="n">
-        <v>959.5128314202112</v>
+        <v>928.1261874460239</v>
       </c>
       <c r="T15" t="n">
-        <v>202.882371458895</v>
+        <v>214.1363174280627</v>
       </c>
       <c r="U15" t="n">
-        <v>9.000641779862162</v>
+        <v>9.00064061091858</v>
       </c>
       <c r="V15" t="n">
-        <v>2.294412742087729</v>
+        <v>79.29619203881873</v>
       </c>
       <c r="W15" t="n">
-        <v>0.05083505749280448</v>
+        <v>2.842860578816897</v>
       </c>
       <c r="X15" t="n">
-        <v>3.224221448792141</v>
+        <v>1.260245751461927</v>
       </c>
       <c r="Y15" t="b">
         <v>1</v>
@@ -1659,70 +1659,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>820.2728574140868</v>
+        <v>850.8279531763469</v>
       </c>
       <c r="D16" t="n">
-        <v>7.327058662315346</v>
+        <v>6.285781981063937</v>
       </c>
       <c r="E16" t="n">
-        <v>220.7869893880287</v>
+        <v>189.182542092788</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9842979311943054</v>
+        <v>0.7904574275016785</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1039881999604404</v>
+        <v>0.2245128999929875</v>
       </c>
       <c r="H16" t="n">
-        <v>0.001060195965692401</v>
+        <v>0.002008212730288506</v>
       </c>
       <c r="I16" t="n">
-        <v>937.9053910882772</v>
+        <v>924.8608245568929</v>
       </c>
       <c r="J16" t="n">
-        <v>220.1042600299626</v>
+        <v>189.1825415942864</v>
       </c>
       <c r="K16" t="n">
-        <v>9.000645620321198</v>
+        <v>9.000605602113362</v>
       </c>
       <c r="L16" t="n">
-        <v>117.6325336741903</v>
+        <v>74.032871380546</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6827293580660694</v>
+        <v>4.985016062164505e-07</v>
       </c>
       <c r="N16" t="n">
-        <v>1.673586958005852</v>
+        <v>2.714823621049425</v>
       </c>
       <c r="O16" t="b">
         <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9843368530273438</v>
+        <v>0.9950404763221741</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.4257890000008047</v>
+        <v>1.488969000056386</v>
       </c>
       <c r="R16" t="n">
-        <v>0.001031925203278661</v>
+        <v>0.000529961776919663</v>
       </c>
       <c r="S16" t="n">
-        <v>931.1041740569792</v>
+        <v>924.7858239123844</v>
       </c>
       <c r="T16" t="n">
-        <v>217.7102106437499</v>
+        <v>189.6656384544455</v>
       </c>
       <c r="U16" t="n">
-        <v>9.000641320074816</v>
+        <v>9.000641858741639</v>
       </c>
       <c r="V16" t="n">
-        <v>110.8313166428924</v>
+        <v>73.95787073603753</v>
       </c>
       <c r="W16" t="n">
-        <v>3.076778744278755</v>
+        <v>0.4830963616574877</v>
       </c>
       <c r="X16" t="n">
-        <v>1.673582657759471</v>
+        <v>2.714859877677703</v>
       </c>
       <c r="Y16" t="b">
         <v>1</v>
@@ -1738,70 +1738,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>885.1661868745564</v>
+        <v>864.8903470003072</v>
       </c>
       <c r="D17" t="n">
-        <v>8.240226798135994</v>
+        <v>7.455783838301119</v>
       </c>
       <c r="E17" t="n">
-        <v>192.5125193001751</v>
+        <v>195.8393717611224</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8579790592193604</v>
+        <v>0.8514803051948547</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1073563999962062</v>
+        <v>0.2699425001628697</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0004035303718410432</v>
+        <v>0.002008181530982256</v>
       </c>
       <c r="I17" t="n">
-        <v>940.8711338869272</v>
+        <v>924.8602892878602</v>
       </c>
       <c r="J17" t="n">
-        <v>192.5125193001732</v>
+        <v>195.8394232750141</v>
       </c>
       <c r="K17" t="n">
-        <v>9.000641706318349</v>
+        <v>9.000641720596469</v>
       </c>
       <c r="L17" t="n">
-        <v>55.70494701237078</v>
+        <v>59.96994228755295</v>
       </c>
       <c r="M17" t="n">
-        <v>1.932676241267473e-12</v>
+        <v>5.151389169100185e-05</v>
       </c>
       <c r="N17" t="n">
-        <v>0.760414908182355</v>
+        <v>1.544857882295351</v>
       </c>
       <c r="O17" t="b">
         <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8278878331184387</v>
+        <v>0.9830912947654724</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4214375999290496</v>
+        <v>1.499527600128204</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0004051265132147819</v>
+        <v>0.0003996603772975504</v>
       </c>
       <c r="S17" t="n">
-        <v>936.8748371100689</v>
+        <v>925.8026640705901</v>
       </c>
       <c r="T17" t="n">
-        <v>193.5584827886359</v>
+        <v>195.8309883935017</v>
       </c>
       <c r="U17" t="n">
-        <v>9.000641453245866</v>
+        <v>9.000641779916164</v>
       </c>
       <c r="V17" t="n">
-        <v>51.70865023551255</v>
+        <v>60.91231707028294</v>
       </c>
       <c r="W17" t="n">
-        <v>1.045963488460785</v>
+        <v>0.008383367620695026</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7604146551098712</v>
+        <v>1.544857941615045</v>
       </c>
       <c r="Y17" t="b">
         <v>1</v>
@@ -1813,74 +1813,74 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>923.3756002298574</v>
+        <v>853.8047045219632</v>
       </c>
       <c r="D18" t="n">
-        <v>6.591725410672975</v>
+        <v>7.040943394308916</v>
       </c>
       <c r="E18" t="n">
-        <v>210.8643918262847</v>
+        <v>205.3484099415133</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6072345972061157</v>
+        <v>0.8507716059684753</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0391332998406142</v>
+        <v>0.2301232998725027</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00027896897518076</v>
+        <v>0.001641420414671302</v>
       </c>
       <c r="I18" t="n">
-        <v>923.5689299805319</v>
+        <v>929.0271662019918</v>
       </c>
       <c r="J18" t="n">
-        <v>210.8644338795117</v>
+        <v>205.3484099407056</v>
       </c>
       <c r="K18" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641674809065</v>
       </c>
       <c r="L18" t="n">
-        <v>0.193329750674593</v>
+        <v>75.22246168002857</v>
       </c>
       <c r="M18" t="n">
-        <v>4.205322696293479e-05</v>
+        <v>8.077449820120819e-10</v>
       </c>
       <c r="N18" t="n">
-        <v>2.408916369189187</v>
+        <v>1.95969828050015</v>
       </c>
       <c r="O18" t="b">
         <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2370161265134811</v>
+        <v>0.994712233543396</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1791290000546724</v>
+        <v>1.380338499788195</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0001314371329499409</v>
+        <v>0.0004857330932281911</v>
       </c>
       <c r="S18" t="n">
-        <v>927.5675701103778</v>
+        <v>925.7808976450618</v>
       </c>
       <c r="T18" t="n">
-        <v>210.6658734136567</v>
+        <v>204.4490907202137</v>
       </c>
       <c r="U18" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641730153157</v>
       </c>
       <c r="V18" t="n">
-        <v>4.191969880520446</v>
+        <v>71.9761931230986</v>
       </c>
       <c r="W18" t="n">
-        <v>0.198518412628033</v>
+        <v>0.899319221299578</v>
       </c>
       <c r="X18" t="n">
-        <v>2.408916369189187</v>
+        <v>1.959698335844242</v>
       </c>
       <c r="Y18" t="b">
         <v>1</v>
@@ -1892,74 +1892,74 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>982.9256676716795</v>
+        <v>949.638777990016</v>
       </c>
       <c r="D19" t="n">
-        <v>10.39192749632255</v>
+        <v>6.351698191204475</v>
       </c>
       <c r="E19" t="n">
-        <v>122.8959397398837</v>
+        <v>183.3875941831551</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9723821878433228</v>
+        <v>0.7250093221664429</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2418418999295682</v>
+        <v>0.1004166000057012</v>
       </c>
       <c r="H19" t="n">
-        <v>0.001777262426912785</v>
+        <v>0.001032155007123947</v>
       </c>
       <c r="I19" t="n">
-        <v>980.6562466243272</v>
+        <v>951.9834356291486</v>
       </c>
       <c r="J19" t="n">
-        <v>173.8994571341418</v>
+        <v>183.3875941831551</v>
       </c>
       <c r="K19" t="n">
-        <v>10.39192679211197</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L19" t="n">
-        <v>2.269421047352353</v>
+        <v>2.344657639132606</v>
       </c>
       <c r="M19" t="n">
-        <v>51.00351739425815</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N19" t="n">
-        <v>7.042105814036859e-07</v>
+        <v>2.648943588657687</v>
       </c>
       <c r="O19" t="b">
         <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9999909400939941</v>
+        <v>0.5054143071174622</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.240526499925181</v>
+        <v>0.6173115000128746</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0116626163944602</v>
+        <v>0.0001054428284987807</v>
       </c>
       <c r="S19" t="n">
-        <v>800.0000484147823</v>
+        <v>948.7269515704596</v>
       </c>
       <c r="T19" t="n">
-        <v>161.2813116596394</v>
+        <v>183.7607544473893</v>
       </c>
       <c r="U19" t="n">
-        <v>10.06601636648029</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V19" t="n">
-        <v>182.9256192568972</v>
+        <v>0.9118264195564052</v>
       </c>
       <c r="W19" t="n">
-        <v>38.38537191975567</v>
+        <v>0.3731602642342295</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3259111298422628</v>
+        <v>2.648943588657687</v>
       </c>
       <c r="Y19" t="b">
         <v>1</v>
@@ -1971,74 +1971,74 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>928.7700471758762</v>
+        <v>924.0020384589923</v>
       </c>
       <c r="D20" t="n">
-        <v>4.990616426953078</v>
+        <v>10.02226642460204</v>
       </c>
       <c r="E20" t="n">
-        <v>206.8596956383927</v>
+        <v>142.297378885927</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9851580262184143</v>
+        <v>0.7188459038734436</v>
       </c>
       <c r="G20" t="n">
-        <v>0.03048730012960732</v>
+        <v>0.4127406000625342</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0002752725849859416</v>
+        <v>0.0008347913390025496</v>
       </c>
       <c r="I20" t="n">
-        <v>928.7700471761835</v>
+        <v>923.9776698975705</v>
       </c>
       <c r="J20" t="n">
-        <v>206.8596956383719</v>
+        <v>173.7390696194847</v>
       </c>
       <c r="K20" t="n">
-        <v>9.000641779862162</v>
+        <v>10.02200304591045</v>
       </c>
       <c r="L20" t="n">
-        <v>3.072955223615281e-10</v>
+        <v>0.02436856142173838</v>
       </c>
       <c r="M20" t="n">
-        <v>2.080469130305573e-11</v>
+        <v>31.44169073355769</v>
       </c>
       <c r="N20" t="n">
-        <v>4.010025352909084</v>
+        <v>0.0002633786915922087</v>
       </c>
       <c r="O20" t="b">
         <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9262952208518982</v>
+        <v>0.9985077977180481</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.2043945998884737</v>
+        <v>1.874344800133258</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0001038869668263942</v>
+        <v>0.001473016222007573</v>
       </c>
       <c r="S20" t="n">
-        <v>931.6526519599557</v>
+        <v>808.414634159449</v>
       </c>
       <c r="T20" t="n">
-        <v>206.7985988204536</v>
+        <v>150.0005522964133</v>
       </c>
       <c r="U20" t="n">
-        <v>9.000641779862162</v>
+        <v>9.913870488173094</v>
       </c>
       <c r="V20" t="n">
-        <v>2.88260478407949</v>
+        <v>115.5874042995433</v>
       </c>
       <c r="W20" t="n">
-        <v>0.06109681793907384</v>
+        <v>7.703173410486272</v>
       </c>
       <c r="X20" t="n">
-        <v>4.010025352909084</v>
+        <v>0.1083959364289466</v>
       </c>
       <c r="Y20" t="b">
         <v>1</v>
@@ -2050,74 +2050,74 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>960.0499939225858</v>
+        <v>883.9955445799355</v>
       </c>
       <c r="D21" t="n">
-        <v>6.196926327266365</v>
+        <v>6.575576983758507</v>
       </c>
       <c r="E21" t="n">
-        <v>201.8401166993026</v>
+        <v>210.0947048817987</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7952963709831238</v>
+        <v>0.7930038571357727</v>
       </c>
       <c r="G21" t="n">
-        <v>0.04120999993756413</v>
+        <v>0.9353830001782626</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0002481373958289623</v>
+        <v>0.001640764763578773</v>
       </c>
       <c r="I21" t="n">
-        <v>957.5953327879187</v>
+        <v>929.0269662343837</v>
       </c>
       <c r="J21" t="n">
-        <v>201.840116699303</v>
+        <v>210.0945493926517</v>
       </c>
       <c r="K21" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641741080626</v>
       </c>
       <c r="L21" t="n">
-        <v>2.454661134667163</v>
+        <v>45.0314216544482</v>
       </c>
       <c r="M21" t="n">
-        <v>4.263256414560601e-13</v>
+        <v>0.0001554891469197628</v>
       </c>
       <c r="N21" t="n">
-        <v>2.803715452595798</v>
+        <v>2.425064757322119</v>
       </c>
       <c r="O21" t="b">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>0.718028724193573</v>
+        <v>0.9643447995185852</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1968372000847012</v>
+        <v>1.54735629982315</v>
       </c>
       <c r="R21" t="n">
-        <v>9.068239160114899e-05</v>
+        <v>0.0003112194535788149</v>
       </c>
       <c r="S21" t="n">
-        <v>958.0650875109833</v>
+        <v>929.426661036791</v>
       </c>
       <c r="T21" t="n">
-        <v>201.91308266588</v>
+        <v>209.0522040162957</v>
       </c>
       <c r="U21" t="n">
-        <v>9.000641779862162</v>
+        <v>9.00064148646385</v>
       </c>
       <c r="V21" t="n">
-        <v>1.984906411602537</v>
+        <v>45.43111645685542</v>
       </c>
       <c r="W21" t="n">
-        <v>0.07296596657735677</v>
+        <v>1.042500865502916</v>
       </c>
       <c r="X21" t="n">
-        <v>2.803715452595798</v>
+        <v>2.425064502705343</v>
       </c>
       <c r="Y21" t="b">
         <v>1</v>
@@ -2133,70 +2133,70 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>888.2055850320147</v>
+        <v>847.1119345863104</v>
       </c>
       <c r="D22" t="n">
-        <v>8.074739075875389</v>
+        <v>7.358725573590418</v>
       </c>
       <c r="E22" t="n">
-        <v>207.9615602408907</v>
+        <v>209.8626167603591</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7019981145858765</v>
+        <v>0.8492217063903809</v>
       </c>
       <c r="G22" t="n">
-        <v>0.09814969985745847</v>
+        <v>0.3054285000544041</v>
       </c>
       <c r="H22" t="n">
-        <v>0.000411912944400683</v>
+        <v>0.00200738525018096</v>
       </c>
       <c r="I22" t="n">
-        <v>940.8700915289151</v>
+        <v>924.8594728554535</v>
       </c>
       <c r="J22" t="n">
-        <v>207.9615602408907</v>
+        <v>209.8626167603493</v>
       </c>
       <c r="K22" t="n">
-        <v>9.000641655378949</v>
+        <v>9.000641739788913</v>
       </c>
       <c r="L22" t="n">
-        <v>52.66450649690034</v>
+        <v>77.74753826914309</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>9.748646334628575e-12</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9259025795035605</v>
+        <v>1.641916166198495</v>
       </c>
       <c r="O22" t="b">
         <v>1</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8021401166915894</v>
+        <v>0.9938475489616394</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.4709292000625283</v>
+        <v>1.583922100020573</v>
       </c>
       <c r="R22" t="n">
-        <v>0.000357930432073772</v>
+        <v>0.0005598661373369396</v>
       </c>
       <c r="S22" t="n">
-        <v>935.1249652165901</v>
+        <v>926.1093666579063</v>
       </c>
       <c r="T22" t="n">
-        <v>207.7440228019852</v>
+        <v>208.2787262051803</v>
       </c>
       <c r="U22" t="n">
-        <v>9.000641754909143</v>
+        <v>9.000641597593463</v>
       </c>
       <c r="V22" t="n">
-        <v>46.9193801845754</v>
+        <v>78.99743207159588</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2175374389054809</v>
+        <v>1.583890555178783</v>
       </c>
       <c r="X22" t="n">
-        <v>0.9259026790337543</v>
+        <v>1.641916024003045</v>
       </c>
       <c r="Y22" t="b">
         <v>1</v>
@@ -2208,74 +2208,74 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>829.3002648931302</v>
+        <v>953.0379410721091</v>
       </c>
       <c r="D23" t="n">
-        <v>9.126064977223706</v>
+        <v>12.0888957163943</v>
       </c>
       <c r="E23" t="n">
-        <v>198.6980166651521</v>
+        <v>165.4040158925322</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9158090949058533</v>
+        <v>0.5629615783691406</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1064828000962734</v>
+        <v>0.3659905001986772</v>
       </c>
       <c r="H23" t="n">
-        <v>0.001327915932051837</v>
+        <v>0.0008342087967321277</v>
       </c>
       <c r="I23" t="n">
-        <v>925.9037229340205</v>
+        <v>953.0379694204754</v>
       </c>
       <c r="J23" t="n">
-        <v>198.6980166651561</v>
+        <v>173.7371836578429</v>
       </c>
       <c r="K23" t="n">
-        <v>9.140537946887919</v>
+        <v>12.08889289016804</v>
       </c>
       <c r="L23" t="n">
-        <v>96.60345804089025</v>
+        <v>2.834836629972415e-05</v>
       </c>
       <c r="M23" t="n">
-        <v>4.007461029686965e-12</v>
+        <v>8.333167765310634</v>
       </c>
       <c r="N23" t="n">
-        <v>0.01447296966421341</v>
+        <v>2.826226266350318e-06</v>
       </c>
       <c r="O23" t="b">
         <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>0.8835404515266418</v>
+        <v>0.08879907429218292</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.5368796000257134</v>
+        <v>2.371637500124052</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0007934897439554334</v>
+        <v>0.001580131705850363</v>
       </c>
       <c r="S23" t="n">
-        <v>927.1026932959888</v>
+        <v>841.5043704677315</v>
       </c>
       <c r="T23" t="n">
-        <v>199.6700237159809</v>
+        <v>173.4045301262063</v>
       </c>
       <c r="U23" t="n">
-        <v>9.281360722020638</v>
+        <v>11.90309091828418</v>
       </c>
       <c r="V23" t="n">
-        <v>97.8024284028586</v>
+        <v>111.5335706043776</v>
       </c>
       <c r="W23" t="n">
-        <v>0.9720070508287506</v>
+        <v>8.000514233674011</v>
       </c>
       <c r="X23" t="n">
-        <v>0.1552957447969323</v>
+        <v>0.185804798110123</v>
       </c>
       <c r="Y23" t="b">
         <v>1</v>
@@ -2291,70 +2291,70 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>962.1201990269128</v>
+        <v>974.1268048590981</v>
       </c>
       <c r="D24" t="n">
-        <v>6.589725558079908</v>
+        <v>6.113105295328706</v>
       </c>
       <c r="E24" t="n">
-        <v>202.6234247915652</v>
+        <v>204.6480532053325</v>
       </c>
       <c r="F24" t="n">
-        <v>0.578937828540802</v>
+        <v>0.7307463884353638</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03562650014646351</v>
+        <v>0.07482959982007742</v>
       </c>
       <c r="H24" t="n">
-        <v>0.000253947131568566</v>
+        <v>0.001032155007123947</v>
       </c>
       <c r="I24" t="n">
-        <v>962.1201990269394</v>
+        <v>974.1268048591006</v>
       </c>
       <c r="J24" t="n">
-        <v>202.6234247915654</v>
+        <v>204.6480532053326</v>
       </c>
       <c r="K24" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="L24" t="n">
-        <v>2.660272002685815e-11</v>
+        <v>2.501110429875553e-12</v>
       </c>
       <c r="M24" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="N24" t="n">
-        <v>2.410916221782254</v>
+        <v>2.887536484533457</v>
       </c>
       <c r="O24" t="b">
         <v>1</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4307235479354858</v>
+        <v>0.7626535296440125</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1834670999087393</v>
+        <v>0.562657400034368</v>
       </c>
       <c r="R24" t="n">
-        <v>9.343211422674358e-05</v>
+        <v>9.675252658780664e-05</v>
       </c>
       <c r="S24" t="n">
-        <v>959.7582605048731</v>
+        <v>969.463372641931</v>
       </c>
       <c r="T24" t="n">
-        <v>202.6784910013182</v>
+        <v>204.483247817329</v>
       </c>
       <c r="U24" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V24" t="n">
-        <v>2.361938522039736</v>
+        <v>4.663432217167156</v>
       </c>
       <c r="W24" t="n">
-        <v>0.05506620975296528</v>
+        <v>0.164805388003515</v>
       </c>
       <c r="X24" t="n">
-        <v>2.410916221782254</v>
+        <v>2.887536484533457</v>
       </c>
       <c r="Y24" t="b">
         <v>1</v>
@@ -2366,74 +2366,74 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>963.1849133686482</v>
+        <v>867.2734201196864</v>
       </c>
       <c r="D25" t="n">
-        <v>7.790920947512554</v>
+        <v>7.079763259912518</v>
       </c>
       <c r="E25" t="n">
-        <v>136.9652156072593</v>
+        <v>218.4079355201941</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9558945894241333</v>
+        <v>0.8525735139846802</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2576979000587016</v>
+        <v>0.3070523000787944</v>
       </c>
       <c r="H25" t="n">
-        <v>0.000221210895688273</v>
+        <v>0.001640737871639431</v>
       </c>
       <c r="I25" t="n">
-        <v>963.1849133869182</v>
+        <v>929.0273665148541</v>
       </c>
       <c r="J25" t="n">
-        <v>176.1732576611711</v>
+        <v>218.4079640796471</v>
       </c>
       <c r="K25" t="n">
-        <v>9.00000171320859</v>
+        <v>9.000641469297328</v>
       </c>
       <c r="L25" t="n">
-        <v>1.82700432560523e-08</v>
+        <v>61.75394639516765</v>
       </c>
       <c r="M25" t="n">
-        <v>39.20804205391184</v>
+        <v>2.855945299984342e-05</v>
       </c>
       <c r="N25" t="n">
-        <v>1.209080765696037</v>
+        <v>1.92087820938481</v>
       </c>
       <c r="O25" t="b">
         <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9996470212936401</v>
+        <v>0.990874171257019</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.6005369999911636</v>
+        <v>1.572764700045809</v>
       </c>
       <c r="R25" t="n">
-        <v>0.006656422279775143</v>
+        <v>0.0004998066578991711</v>
       </c>
       <c r="S25" t="n">
-        <v>800.0000345629662</v>
+        <v>930.3724720389766</v>
       </c>
       <c r="T25" t="n">
-        <v>162.4130274132106</v>
+        <v>215.7429727727841</v>
       </c>
       <c r="U25" t="n">
-        <v>9.000642020576061</v>
+        <v>9.00063985353014</v>
       </c>
       <c r="V25" t="n">
-        <v>163.1848788056819</v>
+        <v>63.09905191929022</v>
       </c>
       <c r="W25" t="n">
-        <v>25.44781180595129</v>
+        <v>2.664962747409959</v>
       </c>
       <c r="X25" t="n">
-        <v>1.209721073063507</v>
+        <v>1.920876593617622</v>
       </c>
       <c r="Y25" t="b">
         <v>1</v>
@@ -2445,74 +2445,74 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>921.5473306157119</v>
+        <v>956.2207419740964</v>
       </c>
       <c r="D26" t="n">
-        <v>1.579754803432637</v>
+        <v>10.6314366474908</v>
       </c>
       <c r="E26" t="n">
-        <v>197.3268465800665</v>
+        <v>151.5456832369129</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9593200087547302</v>
+        <v>0.6767300963401794</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03573119989596307</v>
+        <v>0.3592511999886483</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0002819020883180201</v>
+        <v>0.0008354719611816108</v>
       </c>
       <c r="I26" t="n">
-        <v>921.5473306165907</v>
+        <v>956.220743406441</v>
       </c>
       <c r="J26" t="n">
-        <v>197.3268466222976</v>
+        <v>173.7371852347398</v>
       </c>
       <c r="K26" t="n">
-        <v>9.000641779862162</v>
+        <v>10.63133882250647</v>
       </c>
       <c r="L26" t="n">
-        <v>8.787992555880919e-10</v>
+        <v>1.432344561180798e-06</v>
       </c>
       <c r="M26" t="n">
-        <v>4.223102223477326e-08</v>
+        <v>22.19150199782698</v>
       </c>
       <c r="N26" t="n">
-        <v>7.420886976429525</v>
+        <v>9.7824984329975e-05</v>
       </c>
       <c r="O26" t="b">
         <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9911040067672729</v>
+        <v>0.9782317280769348</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1863694000057876</v>
+        <v>2.454094799933955</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0001417156890965998</v>
+        <v>0.001589211286045611</v>
       </c>
       <c r="S26" t="n">
-        <v>926.140012342643</v>
+        <v>822.66524694979</v>
       </c>
       <c r="T26" t="n">
-        <v>197.521136696433</v>
+        <v>158.6370014526266</v>
       </c>
       <c r="U26" t="n">
-        <v>9.000641779862162</v>
+        <v>10.49156314359158</v>
       </c>
       <c r="V26" t="n">
-        <v>4.592681726931119</v>
+        <v>133.5554950243064</v>
       </c>
       <c r="W26" t="n">
-        <v>0.1942901163664317</v>
+        <v>7.091318215713784</v>
       </c>
       <c r="X26" t="n">
-        <v>7.420886976429525</v>
+        <v>0.1398735038992189</v>
       </c>
       <c r="Y26" t="b">
         <v>1</v>
@@ -2524,74 +2524,74 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>979.6651776971319</v>
+        <v>871.6973506981192</v>
       </c>
       <c r="D27" t="n">
-        <v>5.196853798040799</v>
+        <v>7.567281293393127</v>
       </c>
       <c r="E27" t="n">
-        <v>191.5825472588185</v>
+        <v>200.6666113793854</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9209200143814087</v>
+        <v>0.8491541743278503</v>
       </c>
       <c r="G27" t="n">
-        <v>0.04966160003095865</v>
+        <v>0.2276772998739034</v>
       </c>
       <c r="H27" t="n">
-        <v>0.000253947131568566</v>
+        <v>0.001641420414671302</v>
       </c>
       <c r="I27" t="n">
-        <v>979.6651776971187</v>
+        <v>929.0287776888827</v>
       </c>
       <c r="J27" t="n">
-        <v>191.5825472588183</v>
+        <v>200.6666113793854</v>
       </c>
       <c r="K27" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641625199611</v>
       </c>
       <c r="L27" t="n">
-        <v>1.318767317570746e-11</v>
+        <v>57.33142699076348</v>
       </c>
       <c r="M27" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.803787981821364</v>
+        <v>1.433360331806484</v>
       </c>
       <c r="O27" t="b">
         <v>1</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9677569270133972</v>
+        <v>0.9760347604751587</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.2118361999746412</v>
+        <v>1.294846800155938</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0002242007903987542</v>
+        <v>0.0003537610464263707</v>
       </c>
       <c r="S27" t="n">
-        <v>970.224955262712</v>
+        <v>926.6508397436913</v>
       </c>
       <c r="T27" t="n">
-        <v>192.1561491681835</v>
+        <v>200.3387851681008</v>
       </c>
       <c r="U27" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641675461011</v>
       </c>
       <c r="V27" t="n">
-        <v>9.440222434419866</v>
+        <v>54.95348904557216</v>
       </c>
       <c r="W27" t="n">
-        <v>0.5736019093649816</v>
+        <v>0.3278262112845596</v>
       </c>
       <c r="X27" t="n">
-        <v>3.803787981821364</v>
+        <v>1.433360382067884</v>
       </c>
       <c r="Y27" t="b">
         <v>1</v>
@@ -2603,74 +2603,74 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1010.098879449908</v>
+        <v>856.1193233431169</v>
       </c>
       <c r="D28" t="n">
-        <v>9.458817302534468</v>
+        <v>8.192890169186759</v>
       </c>
       <c r="E28" t="n">
-        <v>195.5915518803773</v>
+        <v>200.8093246378927</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7058996558189392</v>
+        <v>0.8441774249076843</v>
       </c>
       <c r="G28" t="n">
-        <v>0.110088599845767</v>
+        <v>0.2411728999577463</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0001050807259161957</v>
+        <v>0.001641420414671302</v>
       </c>
       <c r="I28" t="n">
-        <v>985.8937780007902</v>
+        <v>929.0283605503008</v>
       </c>
       <c r="J28" t="n">
-        <v>195.5914779393746</v>
+        <v>200.8093246343892</v>
       </c>
       <c r="K28" t="n">
-        <v>9.458810875340344</v>
+        <v>9.000641667905569</v>
       </c>
       <c r="L28" t="n">
-        <v>24.20510144911805</v>
+        <v>72.90903720718393</v>
       </c>
       <c r="M28" t="n">
-        <v>7.394100262558823e-05</v>
+        <v>3.503487278067041e-09</v>
       </c>
       <c r="N28" t="n">
-        <v>6.427194124469793e-06</v>
+        <v>0.8077514987188099</v>
       </c>
       <c r="O28" t="b">
         <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>0.2003501355648041</v>
+        <v>0.9799456596374512</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.3602583000902086</v>
+        <v>1.436776600079611</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0001663559232838452</v>
+        <v>0.0004570444580167532</v>
       </c>
       <c r="S28" t="n">
-        <v>974.1580303117572</v>
+        <v>925.4132921352116</v>
       </c>
       <c r="T28" t="n">
-        <v>195.8041666487806</v>
+        <v>200.383579558851</v>
       </c>
       <c r="U28" t="n">
-        <v>9.460563031550096</v>
+        <v>9.000641787377026</v>
       </c>
       <c r="V28" t="n">
-        <v>35.94084913815107</v>
+        <v>69.29396879209469</v>
       </c>
       <c r="W28" t="n">
-        <v>0.2126147684033413</v>
+        <v>0.4257450790417181</v>
       </c>
       <c r="X28" t="n">
-        <v>0.001745729015627973</v>
+        <v>0.8077516181902666</v>
       </c>
       <c r="Y28" t="b">
         <v>1</v>
@@ -2682,74 +2682,74 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>880.7493568531423</v>
+        <v>938.3180514967125</v>
       </c>
       <c r="D29" t="n">
-        <v>8.683454608493577</v>
+        <v>9.247788728967553</v>
       </c>
       <c r="E29" t="n">
-        <v>188.591225330526</v>
+        <v>115.9945698135512</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7772117853164673</v>
+        <v>0.7147024869918823</v>
       </c>
       <c r="G29" t="n">
-        <v>0.08481939998455346</v>
+        <v>0.3243708000518382</v>
       </c>
       <c r="H29" t="n">
-        <v>0.001392161007970572</v>
+        <v>0.0008354719611816108</v>
       </c>
       <c r="I29" t="n">
-        <v>925.9044564923068</v>
+        <v>938.3180514967514</v>
       </c>
       <c r="J29" t="n">
-        <v>188.5912253305267</v>
+        <v>173.7371904753844</v>
       </c>
       <c r="K29" t="n">
-        <v>9.000458133074735</v>
+        <v>9.247788728967549</v>
       </c>
       <c r="L29" t="n">
-        <v>45.15509963916452</v>
+        <v>3.888089850079268e-11</v>
       </c>
       <c r="M29" t="n">
-        <v>6.536993168992922e-13</v>
+        <v>57.74262066183314</v>
       </c>
       <c r="N29" t="n">
-        <v>0.3170035245811587</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="O29" t="b">
         <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>0.8065098524093628</v>
+        <v>0.9999799728393555</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.4070402001962066</v>
+        <v>1.491667099995539</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0004629315226338804</v>
+        <v>0.001502027967944741</v>
       </c>
       <c r="S29" t="n">
-        <v>937.77789113753</v>
+        <v>814.3477327313718</v>
       </c>
       <c r="T29" t="n">
-        <v>190.0055498328339</v>
+        <v>150.0005523891731</v>
       </c>
       <c r="U29" t="n">
-        <v>9.000641286190351</v>
+        <v>9.161314395198012</v>
       </c>
       <c r="V29" t="n">
-        <v>57.02853428438766</v>
+        <v>123.9703187653407</v>
       </c>
       <c r="W29" t="n">
-        <v>1.414324502307863</v>
+        <v>34.00598257562189</v>
       </c>
       <c r="X29" t="n">
-        <v>0.3171866776967747</v>
+        <v>0.08647433376954083</v>
       </c>
       <c r="Y29" t="b">
         <v>1</v>
@@ -2761,74 +2761,74 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>830.9241946101021</v>
+        <v>931.6918825194863</v>
       </c>
       <c r="D30" t="n">
-        <v>8.530552348971069</v>
+        <v>11.10716329475271</v>
       </c>
       <c r="E30" t="n">
-        <v>187.7586960367381</v>
+        <v>138.6039614468914</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9804819226264954</v>
+        <v>0.7219393849372864</v>
       </c>
       <c r="G30" t="n">
-        <v>0.129959600046277</v>
+        <v>0.4584415000863373</v>
       </c>
       <c r="H30" t="n">
-        <v>0.001278901007026434</v>
+        <v>0.0008354719611816108</v>
       </c>
       <c r="I30" t="n">
-        <v>920.066988000005</v>
+        <v>931.6913626663281</v>
       </c>
       <c r="J30" t="n">
-        <v>187.3611277202333</v>
+        <v>173.73968632214</v>
       </c>
       <c r="K30" t="n">
-        <v>9.000398779892071</v>
+        <v>11.10710732832323</v>
       </c>
       <c r="L30" t="n">
-        <v>89.14279338990298</v>
+        <v>0.0005198531581527277</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3975683165048167</v>
+        <v>35.13572487524866</v>
       </c>
       <c r="N30" t="n">
-        <v>0.4698464309210024</v>
+        <v>5.596642948013653e-05</v>
       </c>
       <c r="O30" t="b">
         <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>0.9539496898651123</v>
+        <v>0.9992604851722717</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.4369451999664307</v>
+        <v>1.501021299976856</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0009118904708884656</v>
+        <v>0.001708808937110007</v>
       </c>
       <c r="S30" t="n">
-        <v>933.4183443953783</v>
+        <v>801.1154357846618</v>
       </c>
       <c r="T30" t="n">
-        <v>190.2866497262488</v>
+        <v>150.0005520116362</v>
       </c>
       <c r="U30" t="n">
-        <v>9.000641043542675</v>
+        <v>10.92984022282149</v>
       </c>
       <c r="V30" t="n">
-        <v>102.4941497852762</v>
+        <v>130.5764467348245</v>
       </c>
       <c r="W30" t="n">
-        <v>2.527953689510639</v>
+        <v>11.39659056474483</v>
       </c>
       <c r="X30" t="n">
-        <v>0.4700886945716061</v>
+        <v>0.177323071931216</v>
       </c>
       <c r="Y30" t="b">
         <v>1</v>
@@ -2840,74 +2840,74 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>948.417099474584</v>
+        <v>957.0510297320667</v>
       </c>
       <c r="D31" t="n">
-        <v>6.315913495187232</v>
+        <v>7.500469853186457</v>
       </c>
       <c r="E31" t="n">
-        <v>189.5951259527816</v>
+        <v>151.0090387900675</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9357121586799622</v>
+        <v>0.616788387298584</v>
       </c>
       <c r="G31" t="n">
-        <v>0.03220909996889532</v>
+        <v>0.4436089000664651</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0002481373958289623</v>
+        <v>0.0008352872682735324</v>
       </c>
       <c r="I31" t="n">
-        <v>948.4170994745834</v>
+        <v>957.0510304368813</v>
       </c>
       <c r="J31" t="n">
-        <v>189.5951259527817</v>
+        <v>173.7371849751884</v>
       </c>
       <c r="K31" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641779854396</v>
       </c>
       <c r="L31" t="n">
-        <v>5.684341886080801e-13</v>
+        <v>7.048146244414966e-07</v>
       </c>
       <c r="M31" t="n">
-        <v>1.4210854715202e-13</v>
+        <v>22.72814618512086</v>
       </c>
       <c r="N31" t="n">
-        <v>2.684728284674931</v>
+        <v>1.500171926667939</v>
       </c>
       <c r="O31" t="b">
         <v>1</v>
       </c>
       <c r="P31" t="n">
-        <v>0.6217303276062012</v>
+        <v>0.9552946090698242</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1601867999415845</v>
+        <v>3.305520500056446</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0001532512833364308</v>
+        <v>0.001459878636524081</v>
       </c>
       <c r="S31" t="n">
-        <v>947.7505152783879</v>
+        <v>830.7455740596424</v>
       </c>
       <c r="T31" t="n">
-        <v>190.0674318579549</v>
+        <v>157.5179537893604</v>
       </c>
       <c r="U31" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641819476746</v>
       </c>
       <c r="V31" t="n">
-        <v>0.6665841961961405</v>
+        <v>126.3054556724243</v>
       </c>
       <c r="W31" t="n">
-        <v>0.4723059051732719</v>
+        <v>6.50891499929287</v>
       </c>
       <c r="X31" t="n">
-        <v>2.684728284674931</v>
+        <v>1.500171966290289</v>
       </c>
       <c r="Y31" t="b">
         <v>1</v>
@@ -2919,74 +2919,74 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>933.002481497652</v>
+        <v>856.9336195049942</v>
       </c>
       <c r="D32" t="n">
-        <v>9.181170400494413</v>
+        <v>9.056245506034927</v>
       </c>
       <c r="E32" t="n">
-        <v>141.3157333632496</v>
+        <v>211.1414902169284</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9438311457633972</v>
+        <v>0.7370278239250183</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1825534000527114</v>
+        <v>0.2066501001827419</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0007830621325410903</v>
+        <v>0.001641824259422719</v>
       </c>
       <c r="I32" t="n">
-        <v>857.2842430817823</v>
+        <v>929.0269723606521</v>
       </c>
       <c r="J32" t="n">
-        <v>176.1732571575571</v>
+        <v>211.1414902169284</v>
       </c>
       <c r="K32" t="n">
-        <v>9.181216882346309</v>
+        <v>9.056245506034921</v>
       </c>
       <c r="L32" t="n">
-        <v>75.71823841586968</v>
+        <v>72.09335285565783</v>
       </c>
       <c r="M32" t="n">
-        <v>34.85752379430758</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.648185189637388e-05</v>
+        <v>5.329070518200751e-15</v>
       </c>
       <c r="O32" t="b">
         <v>1</v>
       </c>
       <c r="P32" t="n">
-        <v>0.9996411800384521</v>
+        <v>0.9530578851699829</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.5782287002075464</v>
+        <v>1.204095900058746</v>
       </c>
       <c r="R32" t="n">
-        <v>0.005348614417016506</v>
+        <v>0.0004797768779098988</v>
       </c>
       <c r="S32" t="n">
-        <v>800.0002277231252</v>
+        <v>925.8347288752615</v>
       </c>
       <c r="T32" t="n">
-        <v>163.4818743007253</v>
+        <v>209.6000366118565</v>
       </c>
       <c r="U32" t="n">
-        <v>9.00053848542133</v>
+        <v>9.137626293535936</v>
       </c>
       <c r="V32" t="n">
-        <v>133.0022537745267</v>
+        <v>68.90110937026725</v>
       </c>
       <c r="W32" t="n">
-        <v>22.16614093747577</v>
+        <v>1.541453605071865</v>
       </c>
       <c r="X32" t="n">
-        <v>0.1806319150730822</v>
+        <v>0.08138078750100952</v>
       </c>
       <c r="Y32" t="b">
         <v>1</v>
@@ -3002,70 +3002,70 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>869.6138301375908</v>
+        <v>846.2242419961858</v>
       </c>
       <c r="D33" t="n">
-        <v>6.851638222058278</v>
+        <v>7.246049245449091</v>
       </c>
       <c r="E33" t="n">
-        <v>209.7582590983853</v>
+        <v>201.3124706733739</v>
       </c>
       <c r="F33" t="n">
-        <v>0.985556423664093</v>
+        <v>0.8491541743278503</v>
       </c>
       <c r="G33" t="n">
-        <v>0.09795870003290474</v>
+        <v>0.2348328998778015</v>
       </c>
       <c r="H33" t="n">
-        <v>0.000411912944400683</v>
+        <v>0.00200818688608706</v>
       </c>
       <c r="I33" t="n">
-        <v>940.8724259033206</v>
+        <v>924.8594836812757</v>
       </c>
       <c r="J33" t="n">
-        <v>209.7582135058447</v>
+        <v>201.3124887052236</v>
       </c>
       <c r="K33" t="n">
-        <v>9.000792066771698</v>
+        <v>9.00064160515956</v>
       </c>
       <c r="L33" t="n">
-        <v>71.25859576572986</v>
+        <v>78.63524168508991</v>
       </c>
       <c r="M33" t="n">
-        <v>4.559254057312501e-05</v>
+        <v>1.803184974846772e-05</v>
       </c>
       <c r="N33" t="n">
-        <v>2.14915384471342</v>
+        <v>1.754592359710468</v>
       </c>
       <c r="O33" t="b">
         <v>1</v>
       </c>
       <c r="P33" t="n">
-        <v>0.9838081002235413</v>
+        <v>0.9936483502388</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.4712052999529988</v>
+        <v>1.218184900004417</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0005023063858971</v>
+        <v>0.0005289252148941159</v>
       </c>
       <c r="S33" t="n">
-        <v>933.264643307288</v>
+        <v>924.7547011731529</v>
       </c>
       <c r="T33" t="n">
-        <v>209.2747428184135</v>
+        <v>200.7749869898945</v>
       </c>
       <c r="U33" t="n">
-        <v>9.000641898956975</v>
+        <v>9.000641818943469</v>
       </c>
       <c r="V33" t="n">
-        <v>63.65081316969724</v>
+        <v>78.53045917696704</v>
       </c>
       <c r="W33" t="n">
-        <v>0.4835162799717239</v>
+        <v>0.5374836834793655</v>
       </c>
       <c r="X33" t="n">
-        <v>2.149003676898697</v>
+        <v>1.754592573494378</v>
       </c>
       <c r="Y33" t="b">
         <v>1</v>
@@ -3081,70 +3081,70 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>910.0002687937941</v>
+        <v>863.546214833475</v>
       </c>
       <c r="D34" t="n">
-        <v>6.509694684952102</v>
+        <v>5.947375873056869</v>
       </c>
       <c r="E34" t="n">
-        <v>195.4662529131482</v>
+        <v>208.9049188863797</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6023518443107605</v>
+        <v>0.8488157987594604</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1382859998848289</v>
+        <v>0.2683546000625938</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0004035303718410432</v>
+        <v>0.001641420414671302</v>
       </c>
       <c r="I34" t="n">
-        <v>940.8700877632323</v>
+        <v>929.0275243199916</v>
       </c>
       <c r="J34" t="n">
-        <v>195.4663604418713</v>
+        <v>208.8716131547437</v>
       </c>
       <c r="K34" t="n">
-        <v>9.00064169072197</v>
+        <v>9.000686037987416</v>
       </c>
       <c r="L34" t="n">
-        <v>30.86981896943814</v>
+        <v>65.48130948651658</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0001075287231344646</v>
+        <v>0.03330573163600548</v>
       </c>
       <c r="N34" t="n">
-        <v>2.490947005769868</v>
+        <v>3.053310164930547</v>
       </c>
       <c r="O34" t="b">
         <v>1</v>
       </c>
       <c r="P34" t="n">
-        <v>0.6133726835250854</v>
+        <v>0.9939314126968384</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.4593996000476182</v>
+        <v>1.419169700006023</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0002281493070768192</v>
+        <v>0.000438923278125003</v>
       </c>
       <c r="S34" t="n">
-        <v>939.4492613408485</v>
+        <v>927.1547647746088</v>
       </c>
       <c r="T34" t="n">
-        <v>195.9748062809168</v>
+        <v>207.6914918759447</v>
       </c>
       <c r="U34" t="n">
-        <v>9.000641563843633</v>
+        <v>9.000641596926251</v>
       </c>
       <c r="V34" t="n">
-        <v>29.44899254705433</v>
+        <v>63.60854994113379</v>
       </c>
       <c r="W34" t="n">
-        <v>0.5085533677685987</v>
+        <v>1.213427010435026</v>
       </c>
       <c r="X34" t="n">
-        <v>2.490946878891531</v>
+        <v>3.053265723869382</v>
       </c>
       <c r="Y34" t="b">
         <v>1</v>
@@ -3156,74 +3156,74 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>944.2477137625015</v>
+        <v>893.6457020487852</v>
       </c>
       <c r="D35" t="n">
-        <v>6.713790928942508</v>
+        <v>8.130160659592907</v>
       </c>
       <c r="E35" t="n">
-        <v>202.9110208185347</v>
+        <v>215.7724493702983</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5389013886451721</v>
+        <v>0.5715892314910889</v>
       </c>
       <c r="G35" t="n">
-        <v>0.02640870003961027</v>
+        <v>0.2498170998878777</v>
       </c>
       <c r="H35" t="n">
-        <v>0.000253292266279459</v>
+        <v>0.001640764763578773</v>
       </c>
       <c r="I35" t="n">
-        <v>944.2477137625023</v>
+        <v>929.0269691926703</v>
       </c>
       <c r="J35" t="n">
-        <v>202.9110208185284</v>
+        <v>215.7724852584124</v>
       </c>
       <c r="K35" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641541958043</v>
       </c>
       <c r="L35" t="n">
-        <v>7.958078640513122e-13</v>
+        <v>35.38126714388511</v>
       </c>
       <c r="M35" t="n">
-        <v>6.338041202980094e-12</v>
+        <v>3.588811409827031e-05</v>
       </c>
       <c r="N35" t="n">
-        <v>2.286850850919654</v>
+        <v>0.8704808823651362</v>
       </c>
       <c r="O35" t="b">
         <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>0.3045288920402527</v>
+        <v>0.6592084765434265</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.2004813998937607</v>
+        <v>1.510465499944985</v>
       </c>
       <c r="R35" t="n">
-        <v>7.947607809910551e-05</v>
+        <v>0.0002893247292377055</v>
       </c>
       <c r="S35" t="n">
-        <v>944.6974977412119</v>
+        <v>932.5896998936623</v>
       </c>
       <c r="T35" t="n">
-        <v>202.9457082362748</v>
+        <v>214.2460471336375</v>
       </c>
       <c r="U35" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000640651001168</v>
       </c>
       <c r="V35" t="n">
-        <v>0.4497839787104567</v>
+        <v>38.94399784487712</v>
       </c>
       <c r="W35" t="n">
-        <v>0.03468741774014461</v>
+        <v>1.526402236660743</v>
       </c>
       <c r="X35" t="n">
-        <v>2.286850850919654</v>
+        <v>0.8704799914082617</v>
       </c>
       <c r="Y35" t="b">
         <v>1</v>
@@ -3239,70 +3239,70 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>960.1745004645986</v>
+        <v>933.2877293780917</v>
       </c>
       <c r="D36" t="n">
-        <v>6.919401272826073</v>
+        <v>4.427490388850389</v>
       </c>
       <c r="E36" t="n">
-        <v>194.5526131976476</v>
+        <v>193.6613243102345</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5939324498176575</v>
+        <v>0.7307463884353638</v>
       </c>
       <c r="G36" t="n">
-        <v>0.04045010008849204</v>
+        <v>0.0837842000182718</v>
       </c>
       <c r="H36" t="n">
-        <v>0.000253947131568566</v>
+        <v>0.001059164758771658</v>
       </c>
       <c r="I36" t="n">
-        <v>960.7595512215461</v>
+        <v>933.2877293781787</v>
       </c>
       <c r="J36" t="n">
-        <v>194.5526131976409</v>
+        <v>193.6613243102344</v>
       </c>
       <c r="K36" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="L36" t="n">
-        <v>0.585050756947453</v>
+        <v>8.697043085703626e-11</v>
       </c>
       <c r="M36" t="n">
-        <v>6.650680006714538e-12</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="N36" t="n">
-        <v>2.08124050703609</v>
+        <v>4.573151391011773</v>
       </c>
       <c r="O36" t="b">
         <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>0.2360904663801193</v>
+        <v>0.9862813353538513</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.2080049000214785</v>
+        <v>0.5624810999725014</v>
       </c>
       <c r="R36" t="n">
-        <v>0.0001215048323501833</v>
+        <v>5.997930566081777e-05</v>
       </c>
       <c r="S36" t="n">
-        <v>957.5335662314053</v>
+        <v>934.7711182797447</v>
       </c>
       <c r="T36" t="n">
-        <v>194.851063974719</v>
+        <v>193.7260050156243</v>
       </c>
       <c r="U36" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V36" t="n">
-        <v>2.64093423319332</v>
+        <v>1.483388901652916</v>
       </c>
       <c r="W36" t="n">
-        <v>0.2984507770714231</v>
+        <v>0.06468070538986126</v>
       </c>
       <c r="X36" t="n">
-        <v>2.08124050703609</v>
+        <v>4.573151391011773</v>
       </c>
       <c r="Y36" t="b">
         <v>1</v>
@@ -3318,70 +3318,70 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>891.8415293788554</v>
+        <v>865.8087676085786</v>
       </c>
       <c r="D37" t="n">
-        <v>7.552619146637452</v>
+        <v>8.144551773257559</v>
       </c>
       <c r="E37" t="n">
-        <v>198.2877898279365</v>
+        <v>205.8424484230689</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8210803866386414</v>
+        <v>0.8443735241889954</v>
       </c>
       <c r="G37" t="n">
-        <v>0.09326590015552938</v>
+        <v>0.2306583998724818</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0004035303718410432</v>
+        <v>0.00200818688608706</v>
       </c>
       <c r="I37" t="n">
-        <v>940.8700875246753</v>
+        <v>924.8600710147941</v>
       </c>
       <c r="J37" t="n">
-        <v>198.2877898279416</v>
+        <v>205.8424520582051</v>
       </c>
       <c r="K37" t="n">
-        <v>9.00064177013282</v>
+        <v>9.000641491698769</v>
       </c>
       <c r="L37" t="n">
-        <v>49.02855814581994</v>
+        <v>59.05130340621554</v>
       </c>
       <c r="M37" t="n">
-        <v>5.115907697472721e-12</v>
+        <v>3.635136181401322e-06</v>
       </c>
       <c r="N37" t="n">
-        <v>1.448022623495367</v>
+        <v>0.8560897184412095</v>
       </c>
       <c r="O37" t="b">
         <v>1</v>
       </c>
       <c r="P37" t="n">
-        <v>0.8381036520004272</v>
+        <v>0.9761877655982971</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.4105590998660773</v>
+        <v>1.690500900149345</v>
       </c>
       <c r="R37" t="n">
-        <v>0.000336482422426343</v>
+        <v>0.0004043198132421821</v>
       </c>
       <c r="S37" t="n">
-        <v>936.2168014995145</v>
+        <v>926.8131487107878</v>
       </c>
       <c r="T37" t="n">
-        <v>198.8294999909633</v>
+        <v>205.0086439078982</v>
       </c>
       <c r="U37" t="n">
-        <v>9.000641738259615</v>
+        <v>9.000641788049258</v>
       </c>
       <c r="V37" t="n">
-        <v>44.37527212065913</v>
+        <v>61.00438110220921</v>
       </c>
       <c r="W37" t="n">
-        <v>0.5417101630268348</v>
+        <v>0.8338045151707263</v>
       </c>
       <c r="X37" t="n">
-        <v>1.448022591622163</v>
+        <v>0.8560900147916986</v>
       </c>
       <c r="Y37" t="b">
         <v>1</v>
@@ -3393,74 +3393,74 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>870.5685418924138</v>
+        <v>926.9163097633106</v>
       </c>
       <c r="D38" t="n">
-        <v>8.972329951056187</v>
+        <v>9.536587457411368</v>
       </c>
       <c r="E38" t="n">
-        <v>212.0850439335515</v>
+        <v>166.8619071037921</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8523421287536621</v>
+        <v>0.7198591232299805</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1240206998772919</v>
+        <v>0.3856684998609126</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0009401811985298991</v>
+        <v>0.0008350148564204574</v>
       </c>
       <c r="I38" t="n">
-        <v>933.5317547573583</v>
+        <v>926.9205254159402</v>
       </c>
       <c r="J38" t="n">
-        <v>212.085043933552</v>
+        <v>173.7376823977106</v>
       </c>
       <c r="K38" t="n">
-        <v>9.140517219559058</v>
+        <v>9.536465768679115</v>
       </c>
       <c r="L38" t="n">
-        <v>62.96321286494447</v>
+        <v>0.004215652629682154</v>
       </c>
       <c r="M38" t="n">
-        <v>4.831690603168681e-13</v>
+        <v>6.875775293918508</v>
       </c>
       <c r="N38" t="n">
-        <v>0.1681872685028711</v>
+        <v>0.0001216887322534888</v>
       </c>
       <c r="O38" t="b">
         <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>0.8575426936149597</v>
+        <v>0.1352208703756332</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.3820386999286711</v>
+        <v>2.328645600005984</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0004938316997140646</v>
+        <v>0.0009825332090258598</v>
       </c>
       <c r="S38" t="n">
-        <v>932.952213117459</v>
+        <v>853.5935942041882</v>
       </c>
       <c r="T38" t="n">
-        <v>211.3056254021631</v>
+        <v>172.0228094604772</v>
       </c>
       <c r="U38" t="n">
-        <v>9.057761658836251</v>
+        <v>9.480453882640152</v>
       </c>
       <c r="V38" t="n">
-        <v>62.38367122504519</v>
+        <v>73.32271555912234</v>
       </c>
       <c r="W38" t="n">
-        <v>0.7794185313884725</v>
+        <v>5.160902356685057</v>
       </c>
       <c r="X38" t="n">
-        <v>0.0854317077800637</v>
+        <v>0.05613357477121639</v>
       </c>
       <c r="Y38" t="b">
         <v>1</v>
@@ -3472,74 +3472,74 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>987.7612048249165</v>
+        <v>875.4128117083939</v>
       </c>
       <c r="D39" t="n">
-        <v>5.680238395149107</v>
+        <v>6.906295241792681</v>
       </c>
       <c r="E39" t="n">
-        <v>194.8632000754484</v>
+        <v>214.0973115201308</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9430859684944153</v>
+        <v>0.7958791851997375</v>
       </c>
       <c r="G39" t="n">
-        <v>0.03830570005811751</v>
+        <v>0.2402254999615252</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0002567658957559615</v>
+        <v>0.001640764763578773</v>
       </c>
       <c r="I39" t="n">
-        <v>983.8468877335921</v>
+        <v>929.0269681711083</v>
       </c>
       <c r="J39" t="n">
-        <v>194.8632000756561</v>
+        <v>214.0973589214042</v>
       </c>
       <c r="K39" t="n">
-        <v>9.000641779862162</v>
+        <v>9.00064166651547</v>
       </c>
       <c r="L39" t="n">
-        <v>3.914317091324392</v>
+        <v>53.61415646271439</v>
       </c>
       <c r="M39" t="n">
-        <v>2.077342742268229e-10</v>
+        <v>4.740127337754529e-05</v>
       </c>
       <c r="N39" t="n">
-        <v>3.320403384713055</v>
+        <v>2.094346424722789</v>
       </c>
       <c r="O39" t="b">
         <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>0.9140621423721313</v>
+        <v>0.9842520356178284</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.1820610999129713</v>
+        <v>1.465094399871305</v>
       </c>
       <c r="R39" t="n">
-        <v>0.000236918858718127</v>
+        <v>0.0003955659631174058</v>
       </c>
       <c r="S39" t="n">
-        <v>975.537449388029</v>
+        <v>929.6760480653995</v>
       </c>
       <c r="T39" t="n">
-        <v>195.3430547812418</v>
+        <v>212.3783946047745</v>
       </c>
       <c r="U39" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641068420588</v>
       </c>
       <c r="V39" t="n">
-        <v>12.22375543688747</v>
+        <v>54.26323635700567</v>
       </c>
       <c r="W39" t="n">
-        <v>0.4798547057934286</v>
+        <v>1.71891691535626</v>
       </c>
       <c r="X39" t="n">
-        <v>3.320403384713055</v>
+        <v>2.094345826627907</v>
       </c>
       <c r="Y39" t="b">
         <v>1</v>
@@ -3551,74 +3551,74 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>926.7751109503928</v>
+        <v>969.1019806515382</v>
       </c>
       <c r="D40" t="n">
-        <v>14.69975478021877</v>
+        <v>5.53307287589563</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0143456688106</v>
+        <v>198.6194214414134</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9287258982658386</v>
+        <v>0.7307463884353638</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1636351998895407</v>
+        <v>0.07510599982924759</v>
       </c>
       <c r="H40" t="n">
-        <v>0.001690759556367993</v>
+        <v>0.001032155007123947</v>
       </c>
       <c r="I40" t="n">
-        <v>944.2003722545508</v>
+        <v>969.1019806515377</v>
       </c>
       <c r="J40" t="n">
-        <v>193.0366390264005</v>
+        <v>198.6194214414133</v>
       </c>
       <c r="K40" t="n">
-        <v>12.2293513262616</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L40" t="n">
-        <v>17.42526130415797</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="M40" t="n">
-        <v>0.02229335758994466</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N40" t="n">
-        <v>2.47040345395717</v>
+        <v>3.467568903966532</v>
       </c>
       <c r="O40" t="b">
         <v>1</v>
       </c>
       <c r="P40" t="n">
-        <v>0.9971678853034973</v>
+        <v>0.9627785682678223</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.888255099998787</v>
+        <v>0.5498942998237908</v>
       </c>
       <c r="R40" t="n">
-        <v>0.004683330655097961</v>
+        <v>7.20190437277779e-05</v>
       </c>
       <c r="S40" t="n">
-        <v>800.0002201244063</v>
+        <v>965.9210437148083</v>
       </c>
       <c r="T40" t="n">
-        <v>200.3216208356956</v>
+        <v>198.6200186514636</v>
       </c>
       <c r="U40" t="n">
-        <v>13.00764143304811</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V40" t="n">
-        <v>126.7748908259865</v>
+        <v>3.180936936729836</v>
       </c>
       <c r="W40" t="n">
-        <v>7.307275166885034</v>
+        <v>0.0005972100502731337</v>
       </c>
       <c r="X40" t="n">
-        <v>1.692113347170665</v>
+        <v>3.467568903966532</v>
       </c>
       <c r="Y40" t="b">
         <v>1</v>
@@ -3630,74 +3630,74 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>967.7238237716959</v>
+        <v>879.6736162586592</v>
       </c>
       <c r="D41" t="n">
-        <v>16.96676997577074</v>
+        <v>8.301725031905841</v>
       </c>
       <c r="E41" t="n">
-        <v>193.1431016470713</v>
+        <v>186.3342508131452</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9571895003318787</v>
+        <v>0.5084219574928284</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1993780001066625</v>
+        <v>0.2431669998914003</v>
       </c>
       <c r="H41" t="n">
-        <v>0.001836215727962554</v>
+        <v>0.001641420414671302</v>
       </c>
       <c r="I41" t="n">
-        <v>957.5903888236588</v>
+        <v>929.0269703472128</v>
       </c>
       <c r="J41" t="n">
-        <v>193.1433285014407</v>
+        <v>186.3342508131451</v>
       </c>
       <c r="K41" t="n">
-        <v>12.60945375558594</v>
+        <v>9.000641568709835</v>
       </c>
       <c r="L41" t="n">
-        <v>10.13343494803712</v>
+        <v>49.3533540885536</v>
       </c>
       <c r="M41" t="n">
-        <v>0.0002268543694015079</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N41" t="n">
-        <v>4.357316220184797</v>
+        <v>0.6989165368039938</v>
       </c>
       <c r="O41" t="b">
         <v>1</v>
       </c>
       <c r="P41" t="n">
-        <v>0.9999898672103882</v>
+        <v>0.7495420575141907</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.339986899867654</v>
+        <v>1.43965580011718</v>
       </c>
       <c r="R41" t="n">
-        <v>0.00730981444939971</v>
+        <v>0.0003389256889931858</v>
       </c>
       <c r="S41" t="n">
-        <v>800.0000284926539</v>
+        <v>927.670505952938</v>
       </c>
       <c r="T41" t="n">
-        <v>203.669020157672</v>
+        <v>186.8597361454417</v>
       </c>
       <c r="U41" t="n">
-        <v>13.35077891675294</v>
+        <v>9.00064171220026</v>
       </c>
       <c r="V41" t="n">
-        <v>167.7237952790421</v>
+        <v>47.99688969427882</v>
       </c>
       <c r="W41" t="n">
-        <v>10.5259185106006</v>
+        <v>0.5254853322965687</v>
       </c>
       <c r="X41" t="n">
-        <v>3.6159910590178</v>
+        <v>0.6989166802944187</v>
       </c>
       <c r="Y41" t="b">
         <v>1</v>
@@ -3709,74 +3709,74 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>871.1878645029764</v>
+        <v>943.7726220608309</v>
       </c>
       <c r="D42" t="n">
-        <v>9.221556844223011</v>
+        <v>10.40442627614036</v>
       </c>
       <c r="E42" t="n">
-        <v>201.2938789870475</v>
+        <v>160.2382276536959</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8681793212890625</v>
+        <v>0.6767300963401794</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0932088999543339</v>
+        <v>0.2904225001111627</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0009456591797061265</v>
+        <v>0.0008354719611816108</v>
       </c>
       <c r="I42" t="n">
-        <v>933.529305815971</v>
+        <v>943.7697611833348</v>
       </c>
       <c r="J42" t="n">
-        <v>201.2938789870477</v>
+        <v>173.7387993527583</v>
       </c>
       <c r="K42" t="n">
-        <v>9.221556844223198</v>
+        <v>10.40439847328815</v>
       </c>
       <c r="L42" t="n">
-        <v>62.34144131299468</v>
+        <v>0.002860877496118519</v>
       </c>
       <c r="M42" t="n">
-        <v>1.4210854715202e-13</v>
+        <v>13.50057169906242</v>
       </c>
       <c r="N42" t="n">
-        <v>1.865174681370263e-13</v>
+        <v>2.780285221604117e-05</v>
       </c>
       <c r="O42" t="b">
         <v>1</v>
       </c>
       <c r="P42" t="n">
-        <v>0.7997660040855408</v>
+        <v>0.7561230659484863</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.3653216999955475</v>
+        <v>2.181232600007206</v>
       </c>
       <c r="R42" t="n">
-        <v>0.0004361179016996175</v>
+        <v>0.001305108773522079</v>
       </c>
       <c r="S42" t="n">
-        <v>929.8362148659014</v>
+        <v>839.0401325734077</v>
       </c>
       <c r="T42" t="n">
-        <v>201.6343154739984</v>
+        <v>166.6531764880535</v>
       </c>
       <c r="U42" t="n">
-        <v>9.307300075872964</v>
+        <v>10.30140624744792</v>
       </c>
       <c r="V42" t="n">
-        <v>58.64835036292504</v>
+        <v>104.7324894874232</v>
       </c>
       <c r="W42" t="n">
-        <v>0.3404364869508925</v>
+        <v>6.414948834357574</v>
       </c>
       <c r="X42" t="n">
-        <v>0.08574323164995334</v>
+        <v>0.1030200286924448</v>
       </c>
       <c r="Y42" t="b">
         <v>1</v>
@@ -3788,74 +3788,74 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>910.7474861665485</v>
+        <v>965.2011952530343</v>
       </c>
       <c r="D43" t="n">
-        <v>6.916535206831445</v>
+        <v>9.763368787822451</v>
       </c>
       <c r="E43" t="n">
-        <v>191.468689876302</v>
+        <v>112.0461826509299</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5367275476455688</v>
+        <v>0.6767300963401794</v>
       </c>
       <c r="G43" t="n">
-        <v>0.09967649984173477</v>
+        <v>0.4437258001416922</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0004035303718410432</v>
+        <v>0.0008354719611816108</v>
       </c>
       <c r="I43" t="n">
-        <v>940.8700882102418</v>
+        <v>965.2011927346382</v>
       </c>
       <c r="J43" t="n">
-        <v>191.4686898763189</v>
+        <v>173.7371848408262</v>
       </c>
       <c r="K43" t="n">
-        <v>9.000641570011767</v>
+        <v>9.763253716228888</v>
       </c>
       <c r="L43" t="n">
-        <v>30.12260204369329</v>
+        <v>2.518396058803773e-06</v>
       </c>
       <c r="M43" t="n">
-        <v>1.688249540165998e-11</v>
+        <v>61.69100218989627</v>
       </c>
       <c r="N43" t="n">
-        <v>2.084106363180322</v>
+        <v>0.000115071593562277</v>
       </c>
       <c r="O43" t="b">
         <v>1</v>
       </c>
       <c r="P43" t="n">
-        <v>0.5337762832641602</v>
+        <v>0.9999816417694092</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.4129649000242352</v>
+        <v>1.459018799941987</v>
       </c>
       <c r="R43" t="n">
-        <v>0.0002367529814364389</v>
+        <v>0.00173470878507942</v>
       </c>
       <c r="S43" t="n">
-        <v>940.8814856144299</v>
+        <v>812.2869164598184</v>
       </c>
       <c r="T43" t="n">
-        <v>192.1604870641244</v>
+        <v>150.0005524264441</v>
       </c>
       <c r="U43" t="n">
-        <v>9.000641435401073</v>
+        <v>9.643740983973773</v>
       </c>
       <c r="V43" t="n">
-        <v>30.13399944788148</v>
+        <v>152.9142787932159</v>
       </c>
       <c r="W43" t="n">
-        <v>0.6917971878223739</v>
+        <v>37.95436977551421</v>
       </c>
       <c r="X43" t="n">
-        <v>2.084106228569628</v>
+        <v>0.1196278038486778</v>
       </c>
       <c r="Y43" t="b">
         <v>1</v>
@@ -3867,74 +3867,74 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>894.680717095766</v>
+        <v>964.5739433906937</v>
       </c>
       <c r="D44" t="n">
-        <v>8.054306864091931</v>
+        <v>6.487327250518685</v>
       </c>
       <c r="E44" t="n">
-        <v>205.3223585507395</v>
+        <v>212.2483806212175</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5986339449882507</v>
+        <v>0.7307463884353638</v>
       </c>
       <c r="G44" t="n">
-        <v>0.09465189999900758</v>
+        <v>0.06732219993136823</v>
       </c>
       <c r="H44" t="n">
-        <v>0.000411912944400683</v>
+        <v>0.0008134524687193334</v>
       </c>
       <c r="I44" t="n">
-        <v>940.8700876071158</v>
+        <v>964.573943390694</v>
       </c>
       <c r="J44" t="n">
-        <v>205.3223585507395</v>
+        <v>212.2483806212174</v>
       </c>
       <c r="K44" t="n">
-        <v>9.000641771151603</v>
+        <v>9.022256386191025</v>
       </c>
       <c r="L44" t="n">
-        <v>46.18937051134981</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="M44" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="N44" t="n">
-        <v>0.946334907059672</v>
+        <v>2.534929135672339</v>
       </c>
       <c r="O44" t="b">
         <v>1</v>
       </c>
       <c r="P44" t="n">
-        <v>0.6484922766685486</v>
+        <v>0.4742973446846008</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.4573738998733461</v>
+        <v>0.5007862998172641</v>
       </c>
       <c r="R44" t="n">
-        <v>0.0003097565786447376</v>
+        <v>0.000117031297122594</v>
       </c>
       <c r="S44" t="n">
-        <v>935.8940877360927</v>
+        <v>961.5325657551296</v>
       </c>
       <c r="T44" t="n">
-        <v>205.3299235620032</v>
+        <v>211.7357198120444</v>
       </c>
       <c r="U44" t="n">
-        <v>9.000641794909864</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V44" t="n">
-        <v>41.21337064032673</v>
+        <v>3.041377635564118</v>
       </c>
       <c r="W44" t="n">
-        <v>0.007565011263693577</v>
+        <v>0.5126608091731839</v>
       </c>
       <c r="X44" t="n">
-        <v>0.9463349308179332</v>
+        <v>2.513314529343477</v>
       </c>
       <c r="Y44" t="b">
         <v>1</v>
@@ -3946,74 +3946,74 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>935.6105523132412</v>
+        <v>889.5980895494844</v>
       </c>
       <c r="D45" t="n">
-        <v>3.983120227922022</v>
+        <v>7.610245508005957</v>
       </c>
       <c r="E45" t="n">
-        <v>198.3576384098161</v>
+        <v>193.5441101137055</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9862354397773743</v>
+        <v>0.7952448129653931</v>
       </c>
       <c r="G45" t="n">
-        <v>0.05248289997689426</v>
+        <v>0.2625043999869376</v>
       </c>
       <c r="H45" t="n">
-        <v>0.000275987054919824</v>
+        <v>0.001641420414671302</v>
       </c>
       <c r="I45" t="n">
-        <v>935.8914960217039</v>
+        <v>929.0269664561034</v>
       </c>
       <c r="J45" t="n">
-        <v>198.357638409793</v>
+        <v>193.5441101137055</v>
       </c>
       <c r="K45" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641686075078</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2809437084627007</v>
+        <v>39.42887690661905</v>
       </c>
       <c r="M45" t="n">
-        <v>2.310684976691846e-11</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>5.01752155194014</v>
+        <v>1.39039617806912</v>
       </c>
       <c r="O45" t="b">
         <v>1</v>
       </c>
       <c r="P45" t="n">
-        <v>0.9840670824050903</v>
+        <v>0.7567412853240967</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.1879743000026792</v>
+        <v>1.322271100012586</v>
       </c>
       <c r="R45" t="n">
-        <v>9.787471935851499e-05</v>
+        <v>0.0002485042787156999</v>
       </c>
       <c r="S45" t="n">
-        <v>937.3600994753324</v>
+        <v>928.2332327864444</v>
       </c>
       <c r="T45" t="n">
-        <v>198.5015766118829</v>
+        <v>193.6683808320113</v>
       </c>
       <c r="U45" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641846928602</v>
       </c>
       <c r="V45" t="n">
-        <v>1.749547162091176</v>
+        <v>38.63514323696006</v>
       </c>
       <c r="W45" t="n">
-        <v>0.1439382020668347</v>
+        <v>0.1242707183057803</v>
       </c>
       <c r="X45" t="n">
-        <v>5.01752155194014</v>
+        <v>1.390396338922645</v>
       </c>
       <c r="Y45" t="b">
         <v>1</v>
@@ -4029,70 +4029,70 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>820.1509486704676</v>
+        <v>870.0541739306535</v>
       </c>
       <c r="D46" t="n">
-        <v>7.819756061424561</v>
+        <v>6.453242891746804</v>
       </c>
       <c r="E46" t="n">
-        <v>193.308108436903</v>
+        <v>192.4539211513667</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9871838092803955</v>
+        <v>0.8037148118019104</v>
       </c>
       <c r="G46" t="n">
-        <v>0.08853010018356144</v>
+        <v>0.2283703999128193</v>
       </c>
       <c r="H46" t="n">
-        <v>0.001659385743550956</v>
+        <v>0.001641420414671302</v>
       </c>
       <c r="I46" t="n">
-        <v>925.9037138259948</v>
+        <v>929.0276320766679</v>
       </c>
       <c r="J46" t="n">
-        <v>193.3079578136815</v>
+        <v>192.4540282010211</v>
       </c>
       <c r="K46" t="n">
-        <v>9.000641664806555</v>
+        <v>9.000691620665208</v>
       </c>
       <c r="L46" t="n">
-        <v>105.7527651555272</v>
+        <v>58.97345814601442</v>
       </c>
       <c r="M46" t="n">
-        <v>0.0001506232214865122</v>
+        <v>0.0001070496543320587</v>
       </c>
       <c r="N46" t="n">
-        <v>1.180885603381993</v>
+        <v>2.547448728918404</v>
       </c>
       <c r="O46" t="b">
         <v>1</v>
       </c>
       <c r="P46" t="n">
-        <v>0.9815143942832947</v>
+        <v>0.986186146736145</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.4564521999564022</v>
+        <v>1.240937200142071</v>
       </c>
       <c r="R46" t="n">
-        <v>0.0009679677314125001</v>
+        <v>0.0003761979751288891</v>
       </c>
       <c r="S46" t="n">
-        <v>930.9860663106579</v>
+        <v>926.2176622459165</v>
       </c>
       <c r="T46" t="n">
-        <v>195.3302766870889</v>
+        <v>192.6654862792646</v>
       </c>
       <c r="U46" t="n">
-        <v>9.000641477307619</v>
+        <v>9.000641745792718</v>
       </c>
       <c r="V46" t="n">
-        <v>110.8351176401902</v>
+        <v>56.16348831526295</v>
       </c>
       <c r="W46" t="n">
-        <v>2.022168250185899</v>
+        <v>0.2115651278978703</v>
       </c>
       <c r="X46" t="n">
-        <v>1.180885415883058</v>
+        <v>2.547398854045914</v>
       </c>
       <c r="Y46" t="b">
         <v>1</v>
@@ -4104,74 +4104,74 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>881.4368294756746</v>
+        <v>973.8930806056156</v>
       </c>
       <c r="D47" t="n">
-        <v>8.683883718620109</v>
+        <v>6.453513634429815</v>
       </c>
       <c r="E47" t="n">
-        <v>210.5079349734594</v>
+        <v>204.1455548798793</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7437790036201477</v>
+        <v>0.7307463884353638</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1021233999636024</v>
+        <v>0.07137780007906258</v>
       </c>
       <c r="H47" t="n">
-        <v>0.000411912944400683</v>
+        <v>0.001032155007123947</v>
       </c>
       <c r="I47" t="n">
-        <v>940.8726226535753</v>
+        <v>973.8930806056087</v>
       </c>
       <c r="J47" t="n">
-        <v>210.507934973459</v>
+        <v>204.1455548798793</v>
       </c>
       <c r="K47" t="n">
-        <v>9.000565823278913</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L47" t="n">
-        <v>59.43579317790068</v>
+        <v>6.934897101018578e-12</v>
       </c>
       <c r="M47" t="n">
-        <v>3.126388037344441e-13</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N47" t="n">
-        <v>0.3166821046588044</v>
+        <v>2.547128145432348</v>
       </c>
       <c r="O47" t="b">
         <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>0.7974120378494263</v>
+        <v>0.5181303024291992</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.4211554999928921</v>
+        <v>0.5293264999054372</v>
       </c>
       <c r="R47" t="n">
-        <v>0.0004132960748393089</v>
+        <v>9.4331189757213e-05</v>
       </c>
       <c r="S47" t="n">
-        <v>934.541737117346</v>
+        <v>969.3308537476071</v>
       </c>
       <c r="T47" t="n">
-        <v>210.0103203519259</v>
+        <v>203.9992432142571</v>
       </c>
       <c r="U47" t="n">
-        <v>9.000641644275618</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V47" t="n">
-        <v>53.10490764167139</v>
+        <v>4.562226858008557</v>
       </c>
       <c r="W47" t="n">
-        <v>0.4976146215335007</v>
+        <v>0.1463116656222212</v>
       </c>
       <c r="X47" t="n">
-        <v>0.3167579256555086</v>
+        <v>2.547128145432348</v>
       </c>
       <c r="Y47" t="b">
         <v>1</v>
@@ -4183,74 +4183,74 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>838.4958321264128</v>
+        <v>935.9882360664233</v>
       </c>
       <c r="D48" t="n">
-        <v>6.424566946963213</v>
+        <v>4.394966240331074</v>
       </c>
       <c r="E48" t="n">
-        <v>205.9056743663126</v>
+        <v>196.2689669060536</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9884505271911621</v>
+        <v>0.7307463884353638</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1680437000468373</v>
+        <v>0.06914420006796718</v>
       </c>
       <c r="H48" t="n">
-        <v>0.001565012848004699</v>
+        <v>0.001059164758771658</v>
       </c>
       <c r="I48" t="n">
-        <v>925.904175032681</v>
+        <v>935.9882360664794</v>
       </c>
       <c r="J48" t="n">
-        <v>206.4751248904578</v>
+        <v>196.2689669060535</v>
       </c>
       <c r="K48" t="n">
-        <v>9.000641775249187</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L48" t="n">
-        <v>87.40834290626822</v>
+        <v>5.616129783447832e-11</v>
       </c>
       <c r="M48" t="n">
-        <v>0.5694505241451964</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="N48" t="n">
-        <v>2.576074828285974</v>
+        <v>4.605675539531088</v>
       </c>
       <c r="O48" t="b">
         <v>1</v>
       </c>
       <c r="P48" t="n">
-        <v>0.9956574440002441</v>
+        <v>0.989998996257782</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.4644058998674154</v>
+        <v>0.4476663998793811</v>
       </c>
       <c r="R48" t="n">
-        <v>0.0007579441298730671</v>
+        <v>5.330352723831311e-05</v>
       </c>
       <c r="S48" t="n">
-        <v>930.640624929596</v>
+        <v>937.1649486686674</v>
       </c>
       <c r="T48" t="n">
-        <v>205.890373325238</v>
+        <v>196.2946006948045</v>
       </c>
       <c r="U48" t="n">
-        <v>9.000641825775205</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V48" t="n">
-        <v>92.14479280318324</v>
+        <v>1.176712602244152</v>
       </c>
       <c r="W48" t="n">
-        <v>0.01530104107459351</v>
+        <v>0.02563378875095168</v>
       </c>
       <c r="X48" t="n">
-        <v>2.576074878811991</v>
+        <v>4.605675539531088</v>
       </c>
       <c r="Y48" t="b">
         <v>1</v>
@@ -4266,70 +4266,70 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>868.4852255114015</v>
+        <v>825.9598769695076</v>
       </c>
       <c r="D49" t="n">
-        <v>8.292692082730287</v>
+        <v>7.876612341413422</v>
       </c>
       <c r="E49" t="n">
-        <v>202.9592609694175</v>
+        <v>205.6284077315138</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9624367356300354</v>
+        <v>0.8487548828125</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1341595000121742</v>
+        <v>0.4133754000067711</v>
       </c>
       <c r="H49" t="n">
-        <v>0.00113704486284405</v>
+        <v>0.00200818688608706</v>
       </c>
       <c r="I49" t="n">
-        <v>933.5293046828175</v>
+        <v>924.8594723894713</v>
       </c>
       <c r="J49" t="n">
-        <v>202.0291270286342</v>
+        <v>205.6284119221718</v>
       </c>
       <c r="K49" t="n">
-        <v>9.000641646246294</v>
+        <v>9.000641792519545</v>
       </c>
       <c r="L49" t="n">
-        <v>65.044079171416</v>
+        <v>98.8995954199637</v>
       </c>
       <c r="M49" t="n">
-        <v>0.9301339407832927</v>
+        <v>4.190657989511237e-06</v>
       </c>
       <c r="N49" t="n">
-        <v>0.7079495635160065</v>
+        <v>1.124029451106123</v>
       </c>
       <c r="O49" t="b">
         <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>0.9446417689323425</v>
+        <v>0.9876496195793152</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.4727296999190003</v>
+        <v>1.286408900050446</v>
       </c>
       <c r="R49" t="n">
-        <v>0.0005008716252632439</v>
+        <v>0.0006963856867514551</v>
       </c>
       <c r="S49" t="n">
-        <v>933.1467706639318</v>
+        <v>924.0139778317182</v>
       </c>
       <c r="T49" t="n">
-        <v>203.2542928508576</v>
+        <v>204.3942468561218</v>
       </c>
       <c r="U49" t="n">
-        <v>9.000641849400719</v>
+        <v>9.000641865030756</v>
       </c>
       <c r="V49" t="n">
-        <v>64.66154515253027</v>
+        <v>98.05410086221059</v>
       </c>
       <c r="W49" t="n">
-        <v>0.2950318814400248</v>
+        <v>1.234160875392064</v>
       </c>
       <c r="X49" t="n">
-        <v>0.7079497666704313</v>
+        <v>1.124029523617335</v>
       </c>
       <c r="Y49" t="b">
         <v>1</v>
@@ -4341,74 +4341,74 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>979.1832198837739</v>
+        <v>846.5847665177828</v>
       </c>
       <c r="D50" t="n">
-        <v>6.04101607694327</v>
+        <v>8.992942659853101</v>
       </c>
       <c r="E50" t="n">
-        <v>209.9137319136483</v>
+        <v>194.7162467658121</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9600974917411804</v>
+        <v>0.7379212975502014</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0292609001044184</v>
+        <v>0.2435905998572707</v>
       </c>
       <c r="H50" t="n">
-        <v>0.000253947131568566</v>
+        <v>0.002008181530982256</v>
       </c>
       <c r="I50" t="n">
-        <v>979.1832198837656</v>
+        <v>924.8600527357677</v>
       </c>
       <c r="J50" t="n">
-        <v>209.913731913648</v>
+        <v>194.7163129705346</v>
       </c>
       <c r="K50" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641723451468</v>
       </c>
       <c r="L50" t="n">
-        <v>8.29913915367797e-12</v>
+        <v>78.2752862179849</v>
       </c>
       <c r="M50" t="n">
-        <v>3.410605131648481e-13</v>
+        <v>6.62047225432616e-05</v>
       </c>
       <c r="N50" t="n">
-        <v>2.959625702918892</v>
+        <v>0.007699063598366251</v>
       </c>
       <c r="O50" t="b">
         <v>1</v>
       </c>
       <c r="P50" t="n">
-        <v>0.74163419008255</v>
+        <v>0.9524005651473999</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.1970645999535918</v>
+        <v>1.089561200002208</v>
       </c>
       <c r="R50" t="n">
-        <v>0.0001582434924785048</v>
+        <v>0.0005211347597651184</v>
       </c>
       <c r="S50" t="n">
-        <v>972.0490611198499</v>
+        <v>923.7636643492689</v>
       </c>
       <c r="T50" t="n">
-        <v>209.7024953339797</v>
+        <v>194.7939687646141</v>
       </c>
       <c r="U50" t="n">
-        <v>9.000641779862162</v>
+        <v>9.076154394691741</v>
       </c>
       <c r="V50" t="n">
-        <v>7.134158763924006</v>
+        <v>77.1788978314861</v>
       </c>
       <c r="W50" t="n">
-        <v>0.2112365796685935</v>
+        <v>0.07772199880204766</v>
       </c>
       <c r="X50" t="n">
-        <v>2.959625702918892</v>
+        <v>0.08321173483864008</v>
       </c>
       <c r="Y50" t="b">
         <v>1</v>
@@ -4420,74 +4420,74 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>976.2856368605904</v>
+        <v>850.5687900251156</v>
       </c>
       <c r="D51" t="n">
-        <v>3.608205604519258</v>
+        <v>8.790001779809423</v>
       </c>
       <c r="E51" t="n">
-        <v>200.1675935669597</v>
+        <v>189.1670865725537</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9850831031799316</v>
+        <v>0.6824439167976379</v>
       </c>
       <c r="G51" t="n">
-        <v>0.03760640020482242</v>
+        <v>0.3560074998531491</v>
       </c>
       <c r="H51" t="n">
-        <v>0.000253947131568566</v>
+        <v>0.003652139566838741</v>
       </c>
       <c r="I51" t="n">
-        <v>976.2856368605152</v>
+        <v>912.9378550648254</v>
       </c>
       <c r="J51" t="n">
-        <v>200.1675935669443</v>
+        <v>189.228464265379</v>
       </c>
       <c r="K51" t="n">
-        <v>9.000641779862162</v>
+        <v>9.238522435180684</v>
       </c>
       <c r="L51" t="n">
-        <v>7.526068657170981e-11</v>
+        <v>62.36906503970977</v>
       </c>
       <c r="M51" t="n">
-        <v>1.534772309241816e-11</v>
+        <v>0.06137769282534578</v>
       </c>
       <c r="N51" t="n">
-        <v>5.392436175342905</v>
+        <v>0.4485206553712615</v>
       </c>
       <c r="O51" t="b">
         <v>1</v>
       </c>
       <c r="P51" t="n">
-        <v>0.9971093535423279</v>
+        <v>0.951898455619812</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.2056935001164675</v>
+        <v>1.374096399871632</v>
       </c>
       <c r="R51" t="n">
-        <v>0.0001439207553630695</v>
+        <v>0.0005295484443195164</v>
       </c>
       <c r="S51" t="n">
-        <v>969.8804372788995</v>
+        <v>924.7924058723705</v>
       </c>
       <c r="T51" t="n">
-        <v>200.3478326256698</v>
+        <v>189.6459634920217</v>
       </c>
       <c r="U51" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641783293537</v>
       </c>
       <c r="V51" t="n">
-        <v>6.405199581690908</v>
+        <v>74.22361584725491</v>
       </c>
       <c r="W51" t="n">
-        <v>0.1802390587101286</v>
+        <v>0.4788769194680071</v>
       </c>
       <c r="X51" t="n">
-        <v>5.392436175342905</v>
+        <v>0.210640003484114</v>
       </c>
       <c r="Y51" t="b">
         <v>1</v>
@@ -4503,70 +4503,70 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>879.5698638782484</v>
+        <v>874.5961786984</v>
       </c>
       <c r="D52" t="n">
-        <v>7.519056712967613</v>
+        <v>7.283575034765953</v>
       </c>
       <c r="E52" t="n">
-        <v>204.2154180932888</v>
+        <v>211.7301351302594</v>
       </c>
       <c r="F52" t="n">
-        <v>0.947009265422821</v>
+        <v>0.8511509895324707</v>
       </c>
       <c r="G52" t="n">
-        <v>0.09620709996670485</v>
+        <v>0.2580041999462992</v>
       </c>
       <c r="H52" t="n">
-        <v>0.000411912944400683</v>
+        <v>0.001640764763578773</v>
       </c>
       <c r="I52" t="n">
-        <v>940.8731615347237</v>
+        <v>929.0269664546263</v>
       </c>
       <c r="J52" t="n">
-        <v>204.2154180932891</v>
+        <v>211.7302100659202</v>
       </c>
       <c r="K52" t="n">
-        <v>9.000819739421681</v>
+        <v>9.000641703588617</v>
       </c>
       <c r="L52" t="n">
-        <v>61.30329765647537</v>
+        <v>54.43078775622632</v>
       </c>
       <c r="M52" t="n">
-        <v>3.126388037344441e-13</v>
+        <v>7.493566079119773e-05</v>
       </c>
       <c r="N52" t="n">
-        <v>1.481763026454068</v>
+        <v>1.717066668822664</v>
       </c>
       <c r="O52" t="b">
         <v>1</v>
       </c>
       <c r="P52" t="n">
-        <v>0.9488450288772583</v>
+        <v>0.9825460910797119</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.4507665999699384</v>
+        <v>1.240952600026503</v>
       </c>
       <c r="R52" t="n">
-        <v>0.000417387462221086</v>
+        <v>0.0003806603199336678</v>
       </c>
       <c r="S52" t="n">
-        <v>934.1464328812875</v>
+        <v>928.8975963937371</v>
       </c>
       <c r="T52" t="n">
-        <v>204.345254477297</v>
+        <v>210.3360803781563</v>
       </c>
       <c r="U52" t="n">
-        <v>9.000641739095107</v>
+        <v>9.000641346934142</v>
       </c>
       <c r="V52" t="n">
-        <v>54.57656900303914</v>
+        <v>54.30141769533714</v>
       </c>
       <c r="W52" t="n">
-        <v>0.1298363840082288</v>
+        <v>1.394054752103131</v>
       </c>
       <c r="X52" t="n">
-        <v>1.481585026127494</v>
+        <v>1.717066312168189</v>
       </c>
       <c r="Y52" t="b">
         <v>1</v>
@@ -4578,74 +4578,74 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>845.2643484678721</v>
+        <v>945.8083921095481</v>
       </c>
       <c r="D53" t="n">
-        <v>6.481086831255346</v>
+        <v>10.48900916292622</v>
       </c>
       <c r="E53" t="n">
-        <v>201.3158137114366</v>
+        <v>133.9114797784555</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9875456690788269</v>
+        <v>0.6767300963401794</v>
       </c>
       <c r="G53" t="n">
-        <v>0.102502099936828</v>
+        <v>0.3351312000304461</v>
       </c>
       <c r="H53" t="n">
-        <v>0.001542833168059587</v>
+        <v>0.02174675464630127</v>
       </c>
       <c r="I53" t="n">
-        <v>925.9037154494032</v>
+        <v>945.8088833208609</v>
       </c>
       <c r="J53" t="n">
-        <v>201.315813711462</v>
+        <v>167.3116498091097</v>
       </c>
       <c r="K53" t="n">
-        <v>9.000641710553122</v>
+        <v>10.48902223459781</v>
       </c>
       <c r="L53" t="n">
-        <v>80.63936698153111</v>
+        <v>0.0004912113128057172</v>
       </c>
       <c r="M53" t="n">
-        <v>2.543742994021159e-11</v>
+        <v>33.40017003065418</v>
       </c>
       <c r="N53" t="n">
-        <v>2.519554879297776</v>
+        <v>1.30716715887047e-05</v>
       </c>
       <c r="O53" t="b">
         <v>1</v>
       </c>
       <c r="P53" t="n">
-        <v>0.9952842593193054</v>
+        <v>0.9998112320899963</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.4609359998721629</v>
+        <v>1.38329379982315</v>
       </c>
       <c r="R53" t="n">
-        <v>0.0006976982112973928</v>
+        <v>0.001698347390629351</v>
       </c>
       <c r="S53" t="n">
-        <v>931.3627951638401</v>
+        <v>806.3955977542981</v>
       </c>
       <c r="T53" t="n">
-        <v>201.9354166860134</v>
+        <v>150.0005522499343</v>
       </c>
       <c r="U53" t="n">
-        <v>9.00064169824771</v>
+        <v>10.34333313012497</v>
       </c>
       <c r="V53" t="n">
-        <v>86.09844669596805</v>
+        <v>139.41279435525</v>
       </c>
       <c r="W53" t="n">
-        <v>0.6196029745768215</v>
+        <v>16.08907247147877</v>
       </c>
       <c r="X53" t="n">
-        <v>2.519554866992364</v>
+        <v>0.1456760328012514</v>
       </c>
       <c r="Y53" t="b">
         <v>1</v>
@@ -4661,70 +4661,70 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>869.2077288586329</v>
+        <v>863.7740009755142</v>
       </c>
       <c r="D54" t="n">
-        <v>8.156572598306287</v>
+        <v>9.208810364877245</v>
       </c>
       <c r="E54" t="n">
-        <v>211.0666041718146</v>
+        <v>209.8926924406994</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9508481621742249</v>
+        <v>0.7265956997871399</v>
       </c>
       <c r="G54" t="n">
-        <v>0.109625699929893</v>
+        <v>0.2010147999972105</v>
       </c>
       <c r="H54" t="n">
-        <v>0.000411912944400683</v>
+        <v>0.002424679230898619</v>
       </c>
       <c r="I54" t="n">
-        <v>940.8711689760428</v>
+        <v>923.5243482490237</v>
       </c>
       <c r="J54" t="n">
-        <v>211.0666041718132</v>
+        <v>210.02871986632</v>
       </c>
       <c r="K54" t="n">
-        <v>9.000790958495239</v>
+        <v>9.208818082389881</v>
       </c>
       <c r="L54" t="n">
-        <v>71.66344011740989</v>
+        <v>59.75034727350942</v>
       </c>
       <c r="M54" t="n">
-        <v>1.392663762089796e-12</v>
+        <v>0.1360274256205116</v>
       </c>
       <c r="N54" t="n">
-        <v>0.8442183601889521</v>
+        <v>7.717512636062906e-06</v>
       </c>
       <c r="O54" t="b">
         <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>0.9481151700019836</v>
+        <v>0.9266018271446228</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.4499967000447214</v>
+        <v>0.9905840000137687</v>
       </c>
       <c r="R54" t="n">
-        <v>0.0005092869978398085</v>
+        <v>0.0004086036933586001</v>
       </c>
       <c r="S54" t="n">
-        <v>933.3542961488367</v>
+        <v>924.8452961757986</v>
       </c>
       <c r="T54" t="n">
-        <v>210.4210290306728</v>
+        <v>208.6921049532858</v>
       </c>
       <c r="U54" t="n">
-        <v>9.000641818799471</v>
+        <v>9.27818194364529</v>
       </c>
       <c r="V54" t="n">
-        <v>64.14656729020385</v>
+        <v>61.07129520028434</v>
       </c>
       <c r="W54" t="n">
-        <v>0.6455751411417907</v>
+        <v>1.200587487413685</v>
       </c>
       <c r="X54" t="n">
-        <v>0.8440692204931839</v>
+        <v>0.06937157876804534</v>
       </c>
       <c r="Y54" t="b">
         <v>1</v>
@@ -4736,74 +4736,74 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>954.0981077738504</v>
+        <v>955.4030319393862</v>
       </c>
       <c r="D55" t="n">
-        <v>13.61339723938121</v>
+        <v>8.545170262957331</v>
       </c>
       <c r="E55" t="n">
-        <v>207.3980148487064</v>
+        <v>105.7874903676893</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9797565340995789</v>
+        <v>0.7475630044937134</v>
       </c>
       <c r="G55" t="n">
-        <v>0.1500470999162644</v>
+        <v>0.3329115000087768</v>
       </c>
       <c r="H55" t="n">
-        <v>0.003873131237924099</v>
+        <v>0.02173936180770397</v>
       </c>
       <c r="I55" t="n">
-        <v>934.2940845470123</v>
+        <v>955.4030319393745</v>
       </c>
       <c r="J55" t="n">
-        <v>207.3980148487063</v>
+        <v>167.3099722083214</v>
       </c>
       <c r="K55" t="n">
-        <v>12.60851163809747</v>
+        <v>9.000405959832324</v>
       </c>
       <c r="L55" t="n">
-        <v>19.80402322683813</v>
+        <v>1.170974428532645e-11</v>
       </c>
       <c r="M55" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>61.52248184063211</v>
       </c>
       <c r="N55" t="n">
-        <v>1.004885601283739</v>
+        <v>0.4552356968749933</v>
       </c>
       <c r="O55" t="b">
         <v>1</v>
       </c>
       <c r="P55" t="n">
-        <v>0.8356514573097229</v>
+        <v>0.999987006187439</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.7901467999909073</v>
+        <v>2.008653699886054</v>
       </c>
       <c r="R55" t="n">
-        <v>0.00290088402107358</v>
+        <v>0.001610016566701233</v>
       </c>
       <c r="S55" t="n">
-        <v>817.3886717370838</v>
+        <v>816.2340796663143</v>
       </c>
       <c r="T55" t="n">
-        <v>212.0985549420784</v>
+        <v>150.0005525229262</v>
       </c>
       <c r="U55" t="n">
-        <v>12.54391379621714</v>
+        <v>9.000652532053421</v>
       </c>
       <c r="V55" t="n">
-        <v>136.7094360367666</v>
+        <v>139.1689522730719</v>
       </c>
       <c r="W55" t="n">
-        <v>4.700540093371984</v>
+        <v>44.21306215523688</v>
       </c>
       <c r="X55" t="n">
-        <v>1.069483443164074</v>
+        <v>0.4554822690960894</v>
       </c>
       <c r="Y55" t="b">
         <v>1</v>
@@ -4819,70 +4819,70 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>931.7308284073556</v>
+        <v>927.9779130066328</v>
       </c>
       <c r="D56" t="n">
-        <v>12.21795956652855</v>
+        <v>10.22557489068757</v>
       </c>
       <c r="E56" t="n">
-        <v>140.4789340981374</v>
+        <v>138.2664482202784</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9017484784126282</v>
+        <v>0.7199835777282715</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2738896999508142</v>
+        <v>0.4943528999574482</v>
       </c>
       <c r="H56" t="n">
-        <v>0.006988451816141605</v>
+        <v>0.0008350422140210867</v>
       </c>
       <c r="I56" t="n">
-        <v>963.2227555194617</v>
+        <v>927.9519047968892</v>
       </c>
       <c r="J56" t="n">
-        <v>168.5515212074577</v>
+        <v>173.73995228162</v>
       </c>
       <c r="K56" t="n">
-        <v>12.31551705382621</v>
+        <v>10.22516022653331</v>
       </c>
       <c r="L56" t="n">
-        <v>31.49192711210605</v>
+        <v>0.0260082097436225</v>
       </c>
       <c r="M56" t="n">
-        <v>28.0725871093203</v>
+        <v>35.47350406134157</v>
       </c>
       <c r="N56" t="n">
-        <v>0.09755748729765834</v>
+        <v>0.0004146641542526197</v>
       </c>
       <c r="O56" t="b">
         <v>1</v>
       </c>
       <c r="P56" t="n">
-        <v>0.9996423721313477</v>
+        <v>0.9994863271713257</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.8811459001153708</v>
+        <v>1.756716700037941</v>
       </c>
       <c r="R56" t="n">
-        <v>0.004668192472308874</v>
+        <v>0.001529441098682582</v>
       </c>
       <c r="S56" t="n">
-        <v>800.0026144488385</v>
+        <v>807.2642104770206</v>
       </c>
       <c r="T56" t="n">
-        <v>163.8678534604791</v>
+        <v>150.0005523363333</v>
       </c>
       <c r="U56" t="n">
-        <v>12.5217953236076</v>
+        <v>10.10500626146617</v>
       </c>
       <c r="V56" t="n">
-        <v>131.7282139585171</v>
+        <v>120.7137025296122</v>
       </c>
       <c r="W56" t="n">
-        <v>23.38891936234174</v>
+        <v>11.73410411605488</v>
       </c>
       <c r="X56" t="n">
-        <v>0.3038357570790513</v>
+        <v>0.1205686292213954</v>
       </c>
       <c r="Y56" t="b">
         <v>1</v>
@@ -4894,74 +4894,74 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>857.2994480480713</v>
+        <v>977.4682948805337</v>
       </c>
       <c r="D57" t="n">
-        <v>8.210698431009181</v>
+        <v>11.15997726407362</v>
       </c>
       <c r="E57" t="n">
-        <v>188.9520760400035</v>
+        <v>142.5083483932059</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9745776653289795</v>
+        <v>0.6767300963401794</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1248651000205427</v>
+        <v>0.7258266001008451</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0004035303718410432</v>
+        <v>0.0008354719611816108</v>
       </c>
       <c r="I57" t="n">
-        <v>940.8751706479679</v>
+        <v>956.163597253803</v>
       </c>
       <c r="J57" t="n">
-        <v>188.766031281211</v>
+        <v>173.7379051441053</v>
       </c>
       <c r="K57" t="n">
-        <v>9.000712603548521</v>
+        <v>11.16012525609531</v>
       </c>
       <c r="L57" t="n">
-        <v>83.57572259989661</v>
+        <v>21.30469762673067</v>
       </c>
       <c r="M57" t="n">
-        <v>0.1860447587924625</v>
+        <v>31.22955675089935</v>
       </c>
       <c r="N57" t="n">
-        <v>0.7900141725393404</v>
+        <v>0.0001479920216862496</v>
       </c>
       <c r="O57" t="b">
         <v>1</v>
       </c>
       <c r="P57" t="n">
-        <v>0.9656620621681213</v>
+        <v>0.9886354207992554</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.4027561000548303</v>
+        <v>1.77789010014385</v>
       </c>
       <c r="R57" t="n">
-        <v>0.0006545205833390355</v>
+        <v>0.002027305774390697</v>
       </c>
       <c r="S57" t="n">
-        <v>935.2017420516025</v>
+        <v>803.1866695009609</v>
       </c>
       <c r="T57" t="n">
-        <v>190.8081041314765</v>
+        <v>150.1741456937212</v>
       </c>
       <c r="U57" t="n">
-        <v>9.00064112700305</v>
+        <v>10.95282112333738</v>
       </c>
       <c r="V57" t="n">
-        <v>77.90229400353121</v>
+        <v>174.2816253795728</v>
       </c>
       <c r="W57" t="n">
-        <v>1.856028091473064</v>
+        <v>7.665797300515237</v>
       </c>
       <c r="X57" t="n">
-        <v>0.7899426959938687</v>
+        <v>0.2071561407362434</v>
       </c>
       <c r="Y57" t="b">
         <v>1</v>
@@ -4973,74 +4973,74 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1010.27586565436</v>
+        <v>972.2967900359994</v>
       </c>
       <c r="D58" t="n">
-        <v>9.017888444486854</v>
+        <v>9.863881551845235</v>
       </c>
       <c r="E58" t="n">
-        <v>202.6109224616086</v>
+        <v>120.4338779820945</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7210264205932617</v>
+        <v>0.6767300963401794</v>
       </c>
       <c r="G58" t="n">
-        <v>0.09566040011122823</v>
+        <v>0.6126461999956518</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0001128785734181292</v>
+        <v>0.02174675464630127</v>
       </c>
       <c r="I58" t="n">
-        <v>985.893777989925</v>
+        <v>972.2967920041988</v>
       </c>
       <c r="J58" t="n">
-        <v>202.610868033151</v>
+        <v>167.3097806153223</v>
       </c>
       <c r="K58" t="n">
-        <v>9.017888444486854</v>
+        <v>9.863881568612399</v>
       </c>
       <c r="L58" t="n">
-        <v>24.38208766443495</v>
+        <v>1.968199399016157e-06</v>
       </c>
       <c r="M58" t="n">
-        <v>5.442845755965209e-05</v>
+        <v>46.87590263322784</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.676716365750508e-08</v>
       </c>
       <c r="O58" t="b">
         <v>1</v>
       </c>
       <c r="P58" t="n">
-        <v>0.2366334348917007</v>
+        <v>0.9999473094940186</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.4110938000958413</v>
+        <v>1.874648400116712</v>
       </c>
       <c r="R58" t="n">
-        <v>0.0001672586222412065</v>
+        <v>0.001792471506632864</v>
       </c>
       <c r="S58" t="n">
-        <v>974.440838332911</v>
+        <v>811.9116277227274</v>
       </c>
       <c r="T58" t="n">
-        <v>202.6419329655097</v>
+        <v>150.0005523202645</v>
       </c>
       <c r="U58" t="n">
-        <v>9.021850999825135</v>
+        <v>9.737284547400694</v>
       </c>
       <c r="V58" t="n">
-        <v>35.83502732144893</v>
+        <v>160.385162313272</v>
       </c>
       <c r="W58" t="n">
-        <v>0.03101050390111482</v>
+        <v>29.56667433817003</v>
       </c>
       <c r="X58" t="n">
-        <v>0.003962555338281604</v>
+        <v>0.126597004444541</v>
       </c>
       <c r="Y58" t="b">
         <v>1</v>
@@ -5052,74 +5052,74 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1007.368061113335</v>
+        <v>938.8775425384561</v>
       </c>
       <c r="D59" t="n">
-        <v>5.858454552670492</v>
+        <v>10.00173040385492</v>
       </c>
       <c r="E59" t="n">
-        <v>206.6120925773124</v>
+        <v>124.1093492680039</v>
       </c>
       <c r="F59" t="n">
-        <v>0.858593761920929</v>
+        <v>0.7147024869918823</v>
       </c>
       <c r="G59" t="n">
-        <v>0.07592890015803277</v>
+        <v>0.4218063000589609</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0002920783299487084</v>
+        <v>0.02474404126405716</v>
       </c>
       <c r="I59" t="n">
-        <v>992.206710447728</v>
+        <v>938.8775425384785</v>
       </c>
       <c r="J59" t="n">
-        <v>206.6120925773116</v>
+        <v>167.3100111322507</v>
       </c>
       <c r="K59" t="n">
-        <v>9.000641779862162</v>
+        <v>10.00178769917164</v>
       </c>
       <c r="L59" t="n">
-        <v>15.1613506656073</v>
+        <v>2.239630703115836e-11</v>
       </c>
       <c r="M59" t="n">
-        <v>8.810729923425242e-13</v>
+        <v>43.20066186424678</v>
       </c>
       <c r="N59" t="n">
-        <v>3.142187227191671</v>
+        <v>5.729531671505583e-05</v>
       </c>
       <c r="O59" t="b">
         <v>1</v>
       </c>
       <c r="P59" t="n">
-        <v>0.8498181104660034</v>
+        <v>0.9999579191207886</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.3698599999770522</v>
+        <v>1.584052300080657</v>
       </c>
       <c r="R59" t="n">
-        <v>0.0003315290668979287</v>
+        <v>0.001582584227435291</v>
       </c>
       <c r="S59" t="n">
-        <v>986.0960167255304</v>
+        <v>809.4219024214792</v>
       </c>
       <c r="T59" t="n">
-        <v>206.5822911850829</v>
+        <v>150.0005523474917</v>
       </c>
       <c r="U59" t="n">
-        <v>9.000641779862162</v>
+        <v>9.885096296915709</v>
       </c>
       <c r="V59" t="n">
-        <v>21.27204438780495</v>
+        <v>129.4556401169768</v>
       </c>
       <c r="W59" t="n">
-        <v>0.02980139222955813</v>
+        <v>25.89120307948779</v>
       </c>
       <c r="X59" t="n">
-        <v>3.142187227191671</v>
+        <v>0.1166341069392125</v>
       </c>
       <c r="Y59" t="b">
         <v>1</v>
@@ -5131,74 +5131,74 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>952.8683526136296</v>
+        <v>851.9132717869732</v>
       </c>
       <c r="D60" t="n">
-        <v>5.790407170797956</v>
+        <v>6.991764341026262</v>
       </c>
       <c r="E60" t="n">
-        <v>193.0425995540196</v>
+        <v>201.9060442549379</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8984211683273315</v>
+        <v>0.8506406545639038</v>
       </c>
       <c r="G60" t="n">
-        <v>0.03001679992303252</v>
+        <v>0.5302205998450518</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0002481373958289623</v>
+        <v>0.00200818688608706</v>
       </c>
       <c r="I60" t="n">
-        <v>952.8683526134881</v>
+        <v>924.8785694554992</v>
       </c>
       <c r="J60" t="n">
-        <v>193.0425995540116</v>
+        <v>201.9057690386109</v>
       </c>
       <c r="K60" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000000222407492</v>
       </c>
       <c r="L60" t="n">
-        <v>1.414264261256903e-10</v>
+        <v>72.96529766852609</v>
       </c>
       <c r="M60" t="n">
-        <v>7.986500349943526e-12</v>
+        <v>0.0002752163269974517</v>
       </c>
       <c r="N60" t="n">
-        <v>3.210234609064206</v>
+        <v>2.008235881381229</v>
       </c>
       <c r="O60" t="b">
         <v>1</v>
       </c>
       <c r="P60" t="n">
-        <v>0.8788536787033081</v>
+        <v>0.9947133660316467</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.1619484999682754</v>
+        <v>1.434768300037831</v>
       </c>
       <c r="R60" t="n">
-        <v>0.0001215683951159008</v>
+        <v>0.0004895073943771422</v>
       </c>
       <c r="S60" t="n">
-        <v>951.6040102210409</v>
+        <v>925.2011591175732</v>
       </c>
       <c r="T60" t="n">
-        <v>193.3690622465273</v>
+        <v>201.3482566309344</v>
       </c>
       <c r="U60" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641820358487</v>
       </c>
       <c r="V60" t="n">
-        <v>1.264342392588674</v>
+        <v>73.28788733060003</v>
       </c>
       <c r="W60" t="n">
-        <v>0.3264626925076755</v>
+        <v>0.557787624003538</v>
       </c>
       <c r="X60" t="n">
-        <v>3.210234609064206</v>
+        <v>2.008877479332225</v>
       </c>
       <c r="Y60" t="b">
         <v>1</v>
@@ -5210,74 +5210,74 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>924.8299017864933</v>
+        <v>842.2455954311095</v>
       </c>
       <c r="D61" t="n">
-        <v>5.534396136471122</v>
+        <v>8.773947996961862</v>
       </c>
       <c r="E61" t="n">
-        <v>195.1662686173504</v>
+        <v>213.7771672924718</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7833482623100281</v>
+        <v>0.7533094882965088</v>
       </c>
       <c r="G61" t="n">
-        <v>0.03666280000470579</v>
+        <v>0.2620055000297725</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0002815423358697444</v>
+        <v>0.002007473492994905</v>
       </c>
       <c r="I61" t="n">
-        <v>924.8299017867786</v>
+        <v>924.8595228610391</v>
       </c>
       <c r="J61" t="n">
-        <v>195.1662686173202</v>
+        <v>213.7772241672464</v>
       </c>
       <c r="K61" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641623842233</v>
       </c>
       <c r="L61" t="n">
-        <v>2.852402758435346e-10</v>
+        <v>82.61392742992962</v>
       </c>
       <c r="M61" t="n">
-        <v>3.021227712451946e-11</v>
+        <v>5.687477460014634e-05</v>
       </c>
       <c r="N61" t="n">
-        <v>3.46624564339104</v>
+        <v>0.2266936268803708</v>
       </c>
       <c r="O61" t="b">
         <v>1</v>
       </c>
       <c r="P61" t="n">
-        <v>0.7623541355133057</v>
+        <v>0.973253607749939</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.1922165001742542</v>
+        <v>1.554880700074136</v>
       </c>
       <c r="R61" t="n">
-        <v>0.0001406157243764028</v>
+        <v>0.0006326495786197484</v>
       </c>
       <c r="S61" t="n">
-        <v>928.8007711442121</v>
+        <v>926.6769293286666</v>
       </c>
       <c r="T61" t="n">
-        <v>195.4196728769813</v>
+        <v>211.440351500992</v>
       </c>
       <c r="U61" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641109442343</v>
       </c>
       <c r="V61" t="n">
-        <v>3.970869357718811</v>
+        <v>84.43133389755712</v>
       </c>
       <c r="W61" t="n">
-        <v>0.2534042596309689</v>
+        <v>2.336815791479808</v>
       </c>
       <c r="X61" t="n">
-        <v>3.46624564339104</v>
+        <v>0.226693112480481</v>
       </c>
       <c r="Y61" t="b">
         <v>1</v>
@@ -5289,74 +5289,74 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>930.7910609203224</v>
+        <v>956.1273760116578</v>
       </c>
       <c r="D62" t="n">
-        <v>5.581461844348611</v>
+        <v>8.942136767004067</v>
       </c>
       <c r="E62" t="n">
-        <v>196.7342281172041</v>
+        <v>153.3117825201578</v>
       </c>
       <c r="F62" t="n">
-        <v>0.8887342810630798</v>
+        <v>0.6758859157562256</v>
       </c>
       <c r="G62" t="n">
-        <v>0.02656169980764389</v>
+        <v>0.4123972000088543</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0002782602678053081</v>
+        <v>0.0008352872682735324</v>
       </c>
       <c r="I62" t="n">
-        <v>930.7910609201529</v>
+        <v>956.1273736338767</v>
       </c>
       <c r="J62" t="n">
-        <v>196.7342250164554</v>
+        <v>173.7371842984149</v>
       </c>
       <c r="K62" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641784596473</v>
       </c>
       <c r="L62" t="n">
-        <v>1.695070750429295e-10</v>
+        <v>2.37778112932574e-06</v>
       </c>
       <c r="M62" t="n">
-        <v>3.100748699580436e-06</v>
+        <v>20.42540177825708</v>
       </c>
       <c r="N62" t="n">
-        <v>3.419179935513551</v>
+        <v>0.05850501759240601</v>
       </c>
       <c r="O62" t="b">
         <v>1</v>
       </c>
       <c r="P62" t="n">
-        <v>0.8324795961380005</v>
+        <v>0.9701135754585266</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.1943131000734866</v>
+        <v>2.454364400124177</v>
       </c>
       <c r="R62" t="n">
-        <v>0.0001143808767665178</v>
+        <v>0.001407187082804739</v>
       </c>
       <c r="S62" t="n">
-        <v>933.4396689896248</v>
+        <v>835.0184271843821</v>
       </c>
       <c r="T62" t="n">
-        <v>196.9257671723956</v>
+        <v>159.7677679547213</v>
       </c>
       <c r="U62" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000561324843234</v>
       </c>
       <c r="V62" t="n">
-        <v>2.648608069302441</v>
+        <v>121.1089488272758</v>
       </c>
       <c r="W62" t="n">
-        <v>0.1915390551914413</v>
+        <v>6.455985434563416</v>
       </c>
       <c r="X62" t="n">
-        <v>3.419179935513551</v>
+        <v>0.05842455783916733</v>
       </c>
       <c r="Y62" t="b">
         <v>1</v>
@@ -5372,70 +5372,70 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>861.5329745921342</v>
+        <v>895.6931956810989</v>
       </c>
       <c r="D63" t="n">
-        <v>7.210532926372144</v>
+        <v>7.456793908548683</v>
       </c>
       <c r="E63" t="n">
-        <v>191.7940433259565</v>
+        <v>203.9415293593273</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9867919683456421</v>
+        <v>0.6574357151985168</v>
       </c>
       <c r="G63" t="n">
-        <v>0.1151899001561105</v>
+        <v>0.2579375000204891</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0004035303718410432</v>
+        <v>0.001641420414671302</v>
       </c>
       <c r="I63" t="n">
-        <v>940.870088731476</v>
+        <v>929.0269687770967</v>
       </c>
       <c r="J63" t="n">
-        <v>191.7940433259601</v>
+        <v>203.9415293593273</v>
       </c>
       <c r="K63" t="n">
-        <v>9.000790976912986</v>
+        <v>9.000641547887318</v>
       </c>
       <c r="L63" t="n">
-        <v>79.33711413934179</v>
+        <v>33.3337730959978</v>
       </c>
       <c r="M63" t="n">
-        <v>3.581135388230905e-12</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>1.790258050540842</v>
+        <v>1.543847639338635</v>
       </c>
       <c r="O63" t="b">
         <v>1</v>
       </c>
       <c r="P63" t="n">
-        <v>0.9867004752159119</v>
+        <v>0.7420944571495056</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.454731100006029</v>
+        <v>1.242139499867335</v>
       </c>
       <c r="R63" t="n">
-        <v>0.0005976100801490247</v>
+        <v>0.0002156924601877108</v>
       </c>
       <c r="S63" t="n">
-        <v>934.6160318650626</v>
+        <v>929.6199216030675</v>
       </c>
       <c r="T63" t="n">
-        <v>193.3036917354937</v>
+        <v>203.5559540361875</v>
       </c>
       <c r="U63" t="n">
-        <v>9.000641490074365</v>
+        <v>9.000641672509747</v>
       </c>
       <c r="V63" t="n">
-        <v>73.08305727292839</v>
+        <v>33.92672592196857</v>
       </c>
       <c r="W63" t="n">
-        <v>1.509648409537249</v>
+        <v>0.3855753231397614</v>
       </c>
       <c r="X63" t="n">
-        <v>1.790108563702221</v>
+        <v>1.543847763961065</v>
       </c>
       <c r="Y63" t="b">
         <v>1</v>
@@ -5447,74 +5447,74 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>812.9298109768056</v>
+        <v>997.5384536262509</v>
       </c>
       <c r="D64" t="n">
-        <v>8.927339304654152</v>
+        <v>6.217061970224169</v>
       </c>
       <c r="E64" t="n">
-        <v>199.9840388767094</v>
+        <v>217.1075412767862</v>
       </c>
       <c r="F64" t="n">
-        <v>0.941252589225769</v>
+        <v>0.7226564288139343</v>
       </c>
       <c r="G64" t="n">
-        <v>0.09081290010362864</v>
+        <v>0.1043100999668241</v>
       </c>
       <c r="H64" t="n">
-        <v>0.001797718345187604</v>
+        <v>0.001416410086676478</v>
       </c>
       <c r="I64" t="n">
-        <v>920.0676024229934</v>
+        <v>997.5384536258931</v>
       </c>
       <c r="J64" t="n">
-        <v>199.9840388767092</v>
+        <v>217.0942252206817</v>
       </c>
       <c r="K64" t="n">
-        <v>9.438070172352452</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L64" t="n">
-        <v>107.1377914461879</v>
+        <v>3.577724783099256e-10</v>
       </c>
       <c r="M64" t="n">
-        <v>1.70530256582424e-13</v>
+        <v>0.01331605610440079</v>
       </c>
       <c r="N64" t="n">
-        <v>0.5107308676982996</v>
+        <v>2.783579809637994</v>
       </c>
       <c r="O64" t="b">
         <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>0.9043301343917847</v>
+        <v>0.2949511706829071</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.3562833999749273</v>
+        <v>1.082346899900585</v>
       </c>
       <c r="R64" t="n">
-        <v>0.0009822093416005373</v>
+        <v>0.000362639082595706</v>
       </c>
       <c r="S64" t="n">
-        <v>928.0534310903639</v>
+        <v>982.2066752914056</v>
       </c>
       <c r="T64" t="n">
-        <v>200.9851248252849</v>
+        <v>215.8887087749304</v>
       </c>
       <c r="U64" t="n">
-        <v>9.107304461060796</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V64" t="n">
-        <v>115.1236201135583</v>
+        <v>15.33177833484524</v>
       </c>
       <c r="W64" t="n">
-        <v>1.001085948575508</v>
+        <v>1.218832501855786</v>
       </c>
       <c r="X64" t="n">
-        <v>0.1799651564066433</v>
+        <v>2.783579809637994</v>
       </c>
       <c r="Y64" t="b">
         <v>1</v>
@@ -5526,74 +5526,74 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>936.8009197370681</v>
+        <v>945.8067125336677</v>
       </c>
       <c r="D65" t="n">
-        <v>10.79800730495699</v>
+        <v>5.345714920075298</v>
       </c>
       <c r="E65" t="n">
-        <v>130.444792546047</v>
+        <v>202.7598332826755</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9844457507133484</v>
+        <v>0.7307463884353638</v>
       </c>
       <c r="G65" t="n">
-        <v>0.2207776999566704</v>
+        <v>0.09948670002631843</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0001908497797558084</v>
+        <v>0.001032155007123947</v>
       </c>
       <c r="I65" t="n">
-        <v>937.9052154350181</v>
+        <v>951.9836653266326</v>
       </c>
       <c r="J65" t="n">
-        <v>176.1734342559908</v>
+        <v>202.7598332826754</v>
       </c>
       <c r="K65" t="n">
-        <v>10.79917135648461</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L65" t="n">
-        <v>1.104295697950079</v>
+        <v>6.176952792964926</v>
       </c>
       <c r="M65" t="n">
-        <v>45.72864170994379</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="N65" t="n">
-        <v>0.001164051527615229</v>
+        <v>3.654926859786864</v>
       </c>
       <c r="O65" t="b">
         <v>1</v>
       </c>
       <c r="P65" t="n">
-        <v>0.9999833106994629</v>
+        <v>0.9771674275398254</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.201422299956903</v>
+        <v>0.4680579998530447</v>
       </c>
       <c r="R65" t="n">
-        <v>0.008305249735713005</v>
+        <v>5.001795943826437e-05</v>
       </c>
       <c r="S65" t="n">
-        <v>800.0000302218374</v>
+        <v>945.994120295074</v>
       </c>
       <c r="T65" t="n">
-        <v>163.1370545410572</v>
+        <v>202.6844961224853</v>
       </c>
       <c r="U65" t="n">
-        <v>10.80419083586322</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V65" t="n">
-        <v>136.8008895152307</v>
+        <v>0.1874077614063481</v>
       </c>
       <c r="W65" t="n">
-        <v>32.6922619950102</v>
+        <v>0.07533716019014491</v>
       </c>
       <c r="X65" t="n">
-        <v>0.006183530906222146</v>
+        <v>3.654926859786864</v>
       </c>
       <c r="Y65" t="b">
         <v>1</v>
@@ -5605,74 +5605,74 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>864.1459023921725</v>
+        <v>967.0058881332455</v>
       </c>
       <c r="D66" t="n">
-        <v>7.215065843312352</v>
+        <v>5.670345033041892</v>
       </c>
       <c r="E66" t="n">
-        <v>181.8768456708378</v>
+        <v>206.7896898427944</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9790980815887451</v>
+        <v>0.7307463884353638</v>
       </c>
       <c r="G66" t="n">
-        <v>0.1146622998639941</v>
+        <v>0.08572329999879003</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0009753215708769858</v>
+        <v>0.001032155007123947</v>
       </c>
       <c r="I66" t="n">
-        <v>933.5301576108425</v>
+        <v>967.0058881332461</v>
       </c>
       <c r="J66" t="n">
-        <v>180.7271785998349</v>
+        <v>206.7896898427958</v>
       </c>
       <c r="K66" t="n">
-        <v>9.000678720989361</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L66" t="n">
-        <v>69.38425521866998</v>
+        <v>5.684341886080801e-13</v>
       </c>
       <c r="M66" t="n">
-        <v>1.149667071002938</v>
+        <v>1.4210854715202e-12</v>
       </c>
       <c r="N66" t="n">
-        <v>1.785612877677009</v>
+        <v>3.33029674682027</v>
       </c>
       <c r="O66" t="b">
         <v>1</v>
       </c>
       <c r="P66" t="n">
-        <v>0.9812487363815308</v>
+        <v>0.9361515641212463</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.3726045999210328</v>
+        <v>0.4489954998716712</v>
       </c>
       <c r="R66" t="n">
-        <v>0.0006683568353764713</v>
+        <v>8.43124435050413e-05</v>
       </c>
       <c r="S66" t="n">
-        <v>939.0754473547565</v>
+        <v>963.9930065074412</v>
       </c>
       <c r="T66" t="n">
-        <v>184.1626625328815</v>
+        <v>206.5721421579277</v>
       </c>
       <c r="U66" t="n">
-        <v>9.000640205630994</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V66" t="n">
-        <v>74.92954496258403</v>
+        <v>3.012881625804312</v>
       </c>
       <c r="W66" t="n">
-        <v>2.285816862043731</v>
+        <v>0.2175476848667017</v>
       </c>
       <c r="X66" t="n">
-        <v>1.785574362318641</v>
+        <v>3.33029674682027</v>
       </c>
       <c r="Y66" t="b">
         <v>1</v>
@@ -5684,74 +5684,74 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1029.22856125831</v>
+        <v>862.5811093112261</v>
       </c>
       <c r="D67" t="n">
-        <v>10.83039286424729</v>
+        <v>7.068694089761317</v>
       </c>
       <c r="E67" t="n">
-        <v>212.6385535812693</v>
+        <v>198.7895470824437</v>
       </c>
       <c r="F67" t="n">
-        <v>0.7356811761856079</v>
+        <v>0.8506406545639038</v>
       </c>
       <c r="G67" t="n">
-        <v>0.06387319997884333</v>
+        <v>0.2488955999724567</v>
       </c>
       <c r="H67" t="n">
-        <v>9.742625115904957e-05</v>
+        <v>0.001641420414671302</v>
       </c>
       <c r="I67" t="n">
-        <v>985.8937770003619</v>
+        <v>929.0277995067916</v>
       </c>
       <c r="J67" t="n">
-        <v>212.6385535812693</v>
+        <v>198.7895676922058</v>
       </c>
       <c r="K67" t="n">
-        <v>10.83054006389804</v>
+        <v>9.000681979472796</v>
       </c>
       <c r="L67" t="n">
-        <v>43.33478425794772</v>
+        <v>66.44669019556545</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>2.060976214579568e-05</v>
       </c>
       <c r="N67" t="n">
-        <v>0.0001471996507493856</v>
+        <v>1.931987889711479</v>
       </c>
       <c r="O67" t="b">
         <v>1</v>
       </c>
       <c r="P67" t="n">
-        <v>0.9455968141555786</v>
+        <v>0.9907901287078857</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.321779299993068</v>
+        <v>1.380273799877614</v>
       </c>
       <c r="R67" t="n">
-        <v>0.0002416250354144722</v>
+        <v>0.0004132807371206582</v>
       </c>
       <c r="S67" t="n">
-        <v>972.8524376748964</v>
+        <v>925.7358474703134</v>
       </c>
       <c r="T67" t="n">
-        <v>212.0616648362186</v>
+        <v>198.5602942725729</v>
       </c>
       <c r="U67" t="n">
-        <v>10.80826273369459</v>
+        <v>9.000641818505011</v>
       </c>
       <c r="V67" t="n">
-        <v>56.37612358341323</v>
+        <v>63.15473815908729</v>
       </c>
       <c r="W67" t="n">
-        <v>0.5768887450507236</v>
+        <v>0.2292528098708431</v>
       </c>
       <c r="X67" t="n">
-        <v>0.02213013055270174</v>
+        <v>1.931947728743694</v>
       </c>
       <c r="Y67" t="b">
         <v>1</v>
@@ -5763,74 +5763,74 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>869.7865631882487</v>
+        <v>945.8972918235561</v>
       </c>
       <c r="D68" t="n">
-        <v>10.01016271697617</v>
+        <v>11.51762446884641</v>
       </c>
       <c r="E68" t="n">
-        <v>220.620048122057</v>
+        <v>148.010106484674</v>
       </c>
       <c r="F68" t="n">
-        <v>0.7658896446228027</v>
+        <v>0.6555349826812744</v>
       </c>
       <c r="G68" t="n">
-        <v>0.2388488999567926</v>
+        <v>0.3526365000288934</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0007880357443355024</v>
+        <v>0.0008354719611816108</v>
       </c>
       <c r="I68" t="n">
-        <v>925.9052788979586</v>
+        <v>945.8972875523858</v>
       </c>
       <c r="J68" t="n">
-        <v>220.1083942025494</v>
+        <v>173.7371880071923</v>
       </c>
       <c r="K68" t="n">
-        <v>10.01016271697617</v>
+        <v>11.51756544029782</v>
       </c>
       <c r="L68" t="n">
-        <v>56.11871570970993</v>
+        <v>4.271170269021241e-06</v>
       </c>
       <c r="M68" t="n">
-        <v>0.5116539195075518</v>
+        <v>25.72708152251832</v>
       </c>
       <c r="N68" t="n">
-        <v>3.552713678800501e-15</v>
+        <v>5.902854859485274e-05</v>
       </c>
       <c r="O68" t="b">
         <v>1</v>
       </c>
       <c r="P68" t="n">
-        <v>0.600747287273407</v>
+        <v>0.9875911474227905</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.3567796000279486</v>
+        <v>2.621496599866077</v>
       </c>
       <c r="R68" t="n">
-        <v>0.0004555316991172731</v>
+        <v>0.001751977950334549</v>
       </c>
       <c r="S68" t="n">
-        <v>924.6907360838259</v>
+        <v>808.8191597698816</v>
       </c>
       <c r="T68" t="n">
-        <v>218.5495471907728</v>
+        <v>155.2320504368665</v>
       </c>
       <c r="U68" t="n">
-        <v>10.08125713643015</v>
+        <v>11.31141396413199</v>
       </c>
       <c r="V68" t="n">
-        <v>54.90417289557718</v>
+        <v>137.0781320536745</v>
       </c>
       <c r="W68" t="n">
-        <v>2.070500931284244</v>
+        <v>7.221943952192532</v>
       </c>
       <c r="X68" t="n">
-        <v>0.07109441945398665</v>
+        <v>0.2062105047144218</v>
       </c>
       <c r="Y68" t="b">
         <v>1</v>
@@ -5842,74 +5842,74 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>852.3877700309616</v>
+        <v>947.4829902238973</v>
       </c>
       <c r="D69" t="n">
-        <v>7.705590918851363</v>
+        <v>10.66889407103901</v>
       </c>
       <c r="E69" t="n">
-        <v>203.9794727730402</v>
+        <v>120.4383965880583</v>
       </c>
       <c r="F69" t="n">
-        <v>0.9864906072616577</v>
+        <v>0.6767300963401794</v>
       </c>
       <c r="G69" t="n">
-        <v>0.1515601000282913</v>
+        <v>0.316197499865666</v>
       </c>
       <c r="H69" t="n">
-        <v>0.001153156976215541</v>
+        <v>0.0008354719611816108</v>
       </c>
       <c r="I69" t="n">
-        <v>933.5293079644696</v>
+        <v>935.5381755079873</v>
       </c>
       <c r="J69" t="n">
-        <v>203.9794727730373</v>
+        <v>173.7378496309283</v>
       </c>
       <c r="K69" t="n">
-        <v>9.000641612788701</v>
+        <v>10.76515973796006</v>
       </c>
       <c r="L69" t="n">
-        <v>81.14153793350795</v>
+        <v>11.94481471591007</v>
       </c>
       <c r="M69" t="n">
-        <v>2.870592652470805e-12</v>
+        <v>53.29945304287</v>
       </c>
       <c r="N69" t="n">
-        <v>1.295050693937339</v>
+        <v>0.0962656669210542</v>
       </c>
       <c r="O69" t="b">
         <v>1</v>
       </c>
       <c r="P69" t="n">
-        <v>0.9819844365119934</v>
+        <v>0.9999669790267944</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.4285587999038398</v>
+        <v>1.750522200018167</v>
       </c>
       <c r="R69" t="n">
-        <v>0.0006326048169285059</v>
+        <v>0.001739119994454086</v>
       </c>
       <c r="S69" t="n">
-        <v>931.7249762808516</v>
+        <v>805.1886734035901</v>
       </c>
       <c r="T69" t="n">
-        <v>204.2126425873483</v>
+        <v>150.0005521274128</v>
       </c>
       <c r="U69" t="n">
-        <v>9.000641738316181</v>
+        <v>10.51138908210346</v>
       </c>
       <c r="V69" t="n">
-        <v>79.33720624988996</v>
+        <v>142.2943168203072</v>
       </c>
       <c r="W69" t="n">
-        <v>0.23316981430807</v>
+        <v>29.56215553935448</v>
       </c>
       <c r="X69" t="n">
-        <v>1.295050819464818</v>
+        <v>0.1575049889355444</v>
       </c>
       <c r="Y69" t="b">
         <v>1</v>
@@ -5921,74 +5921,74 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>875.1834060512713</v>
+        <v>944.4980539404664</v>
       </c>
       <c r="D70" t="n">
-        <v>6.442722668560213</v>
+        <v>6.246501148709108</v>
       </c>
       <c r="E70" t="n">
-        <v>189.6956515728362</v>
+        <v>199.1020091497184</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9526134133338928</v>
+        <v>0.7307463884353638</v>
       </c>
       <c r="G70" t="n">
-        <v>0.14387740008533</v>
+        <v>0.0795182001311332</v>
       </c>
       <c r="H70" t="n">
-        <v>0.001392161007970572</v>
+        <v>0.001059164758771658</v>
       </c>
       <c r="I70" t="n">
-        <v>925.9037133508269</v>
+        <v>944.49805394046</v>
       </c>
       <c r="J70" t="n">
-        <v>189.6956515728363</v>
+        <v>199.1020091497184</v>
       </c>
       <c r="K70" t="n">
-        <v>9.000641718221598</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L70" t="n">
-        <v>50.72030729955566</v>
+        <v>6.480149750132114e-12</v>
       </c>
       <c r="M70" t="n">
-        <v>1.70530256582424e-13</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N70" t="n">
-        <v>2.557919049661384</v>
+        <v>2.754140631153055</v>
       </c>
       <c r="O70" t="b">
         <v>1</v>
       </c>
       <c r="P70" t="n">
-        <v>0.9780243635177612</v>
+        <v>0.738786518573761</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.388588699977845</v>
+        <v>0.6165701998397708</v>
       </c>
       <c r="R70" t="n">
-        <v>0.0005021069664508104</v>
+        <v>4.660089325625449e-05</v>
       </c>
       <c r="S70" t="n">
-        <v>936.6759064940979</v>
+        <v>944.7935491651274</v>
       </c>
       <c r="T70" t="n">
-        <v>191.1415944281951</v>
+        <v>199.0912042849029</v>
       </c>
       <c r="U70" t="n">
-        <v>9.000641201147461</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V70" t="n">
-        <v>61.49250044282667</v>
+        <v>0.2954952246609537</v>
       </c>
       <c r="W70" t="n">
-        <v>1.445942855358936</v>
+        <v>0.01080486481544085</v>
       </c>
       <c r="X70" t="n">
-        <v>2.557918532587248</v>
+        <v>2.754140631153055</v>
       </c>
       <c r="Y70" t="b">
         <v>1</v>
@@ -6000,74 +6000,74 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>879.4980539994262</v>
+        <v>907.2141165346436</v>
       </c>
       <c r="D71" t="n">
-        <v>8.738906620407827</v>
+        <v>11.4538571561289</v>
       </c>
       <c r="E71" t="n">
-        <v>193.6028206897869</v>
+        <v>140.7149458954127</v>
       </c>
       <c r="F71" t="n">
-        <v>0.7990202307701111</v>
+        <v>0.6217793226242065</v>
       </c>
       <c r="G71" t="n">
-        <v>0.08183700009249151</v>
+        <v>0.4370387999806553</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0004035303718410432</v>
+        <v>0.0008331580320373178</v>
       </c>
       <c r="I71" t="n">
-        <v>940.870098875969</v>
+        <v>910.6221367311381</v>
       </c>
       <c r="J71" t="n">
-        <v>193.6028206897864</v>
+        <v>173.7371839394637</v>
       </c>
       <c r="K71" t="n">
-        <v>9.000641549284468</v>
+        <v>11.45371597580618</v>
       </c>
       <c r="L71" t="n">
-        <v>61.37204487654276</v>
+        <v>3.408020196494476</v>
       </c>
       <c r="M71" t="n">
-        <v>5.115907697472721e-13</v>
+        <v>33.02223804405099</v>
       </c>
       <c r="N71" t="n">
-        <v>0.261734928876642</v>
+        <v>0.0001411803227231445</v>
       </c>
       <c r="O71" t="b">
         <v>1</v>
       </c>
       <c r="P71" t="n">
-        <v>0.8146300911903381</v>
+        <v>0.9966008067131042</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.4636518999468535</v>
+        <v>2.115213300101459</v>
       </c>
       <c r="R71" t="n">
-        <v>0.0004418827011249959</v>
+        <v>0.001994211226701736</v>
       </c>
       <c r="S71" t="n">
-        <v>935.8991490715102</v>
+        <v>800.0000229883224</v>
       </c>
       <c r="T71" t="n">
-        <v>194.6556681321374</v>
+        <v>150.0005528821134</v>
       </c>
       <c r="U71" t="n">
-        <v>9.00064162075174</v>
+        <v>11.2189462543591</v>
       </c>
       <c r="V71" t="n">
-        <v>56.40109507208399</v>
+        <v>107.2140935463212</v>
       </c>
       <c r="W71" t="n">
-        <v>1.052847442350441</v>
+        <v>9.285606986700714</v>
       </c>
       <c r="X71" t="n">
-        <v>0.2617350003439132</v>
+        <v>0.2349109017698012</v>
       </c>
       <c r="Y71" t="b">
         <v>1</v>
@@ -6079,74 +6079,74 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>948.0406853580649</v>
+        <v>831.4542015270936</v>
       </c>
       <c r="D72" t="n">
-        <v>13.75977046212345</v>
+        <v>6.817806106316048</v>
       </c>
       <c r="E72" t="n">
-        <v>204.1520155094046</v>
+        <v>185.0178315093528</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9320546984672546</v>
+        <v>0.7725018262863159</v>
       </c>
       <c r="G72" t="n">
-        <v>0.2572891998570412</v>
+        <v>0.2325774999335408</v>
       </c>
       <c r="H72" t="n">
-        <v>0.001686847768723965</v>
+        <v>0.002008212730288506</v>
       </c>
       <c r="I72" t="n">
-        <v>918.4376755048595</v>
+        <v>924.8605801276852</v>
       </c>
       <c r="J72" t="n">
-        <v>206.285132575113</v>
+        <v>185.0178314596837</v>
       </c>
       <c r="K72" t="n">
-        <v>12.22541010675307</v>
+        <v>9.000690749593387</v>
       </c>
       <c r="L72" t="n">
-        <v>29.60300985320544</v>
+        <v>93.40637860059167</v>
       </c>
       <c r="M72" t="n">
-        <v>2.133117065708404</v>
+        <v>4.966906885783828e-08</v>
       </c>
       <c r="N72" t="n">
-        <v>1.534360355370373</v>
+        <v>2.182884643277339</v>
       </c>
       <c r="O72" t="b">
         <v>1</v>
       </c>
       <c r="P72" t="n">
-        <v>0.9115007519721985</v>
+        <v>0.9936195015907288</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.002238299930468</v>
+        <v>1.584618499968201</v>
       </c>
       <c r="R72" t="n">
-        <v>0.003087344346567988</v>
+        <v>0.0007275063544511795</v>
       </c>
       <c r="S72" t="n">
-        <v>811.8959212735638</v>
+        <v>923.7235066213619</v>
       </c>
       <c r="T72" t="n">
-        <v>209.3014566461669</v>
+        <v>185.9190082622438</v>
       </c>
       <c r="U72" t="n">
-        <v>12.6635532280411</v>
+        <v>9.00064174870929</v>
       </c>
       <c r="V72" t="n">
-        <v>136.1447640845012</v>
+        <v>92.26930509426836</v>
       </c>
       <c r="W72" t="n">
-        <v>5.149441136762221</v>
+        <v>0.90117675289099</v>
       </c>
       <c r="X72" t="n">
-        <v>1.096217234082349</v>
+        <v>2.182835642393242</v>
       </c>
       <c r="Y72" t="b">
         <v>1</v>
@@ -6158,74 +6158,74 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>966.4059674901793</v>
+        <v>931.7308002100249</v>
       </c>
       <c r="D73" t="n">
-        <v>15.17770026835904</v>
+        <v>4.965118508521456</v>
       </c>
       <c r="E73" t="n">
-        <v>211.3861979220888</v>
+        <v>187.2320079581123</v>
       </c>
       <c r="F73" t="n">
-        <v>0.961039125919342</v>
+        <v>0.6949499249458313</v>
       </c>
       <c r="G73" t="n">
-        <v>0.1905967998318374</v>
+        <v>0.1139036999084055</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0005593529785983264</v>
+        <v>0.001059164758771658</v>
       </c>
       <c r="I73" t="n">
-        <v>944.1999543755353</v>
+        <v>931.7308002101901</v>
       </c>
       <c r="J73" t="n">
-        <v>211.3862036764079</v>
+        <v>187.2320079581115</v>
       </c>
       <c r="K73" t="n">
-        <v>12.24328301386874</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L73" t="n">
-        <v>22.20601311464395</v>
+        <v>1.651869752095081e-10</v>
       </c>
       <c r="M73" t="n">
-        <v>5.754319062134527e-06</v>
+        <v>8.242295734817162e-13</v>
       </c>
       <c r="N73" t="n">
-        <v>2.934417254490297</v>
+        <v>4.035523271340707</v>
       </c>
       <c r="O73" t="b">
         <v>1</v>
       </c>
       <c r="P73" t="n">
-        <v>0.9992827773094177</v>
+        <v>0.9562298059463501</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.100516099948436</v>
+        <v>0.5066314998548478</v>
       </c>
       <c r="R73" t="n">
-        <v>0.004422673955559731</v>
+        <v>8.435447671217844e-05</v>
       </c>
       <c r="S73" t="n">
-        <v>800.0000306840237</v>
+        <v>933.3777122287474</v>
       </c>
       <c r="T73" t="n">
-        <v>217.0231904763192</v>
+        <v>187.4302782474072</v>
       </c>
       <c r="U73" t="n">
-        <v>13.32489516558742</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V73" t="n">
-        <v>166.4059368061555</v>
+        <v>1.64691201872256</v>
       </c>
       <c r="W73" t="n">
-        <v>5.636992554230375</v>
+        <v>0.198270289294868</v>
       </c>
       <c r="X73" t="n">
-        <v>1.852805102771617</v>
+        <v>4.035523271340707</v>
       </c>
       <c r="Y73" t="b">
         <v>1</v>
@@ -6241,70 +6241,70 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>893.2486385287158</v>
+        <v>887.8886139952617</v>
       </c>
       <c r="D74" t="n">
-        <v>6.59528431853333</v>
+        <v>6.776869402268809</v>
       </c>
       <c r="E74" t="n">
-        <v>189.0610863136084</v>
+        <v>189.111925958194</v>
       </c>
       <c r="F74" t="n">
-        <v>0.8671261668205261</v>
+        <v>0.7249653935432434</v>
       </c>
       <c r="G74" t="n">
-        <v>0.1682114999275655</v>
+        <v>0.2437248001806438</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0004035303718410432</v>
+        <v>0.001641420414671302</v>
       </c>
       <c r="I74" t="n">
-        <v>940.871427355211</v>
+        <v>929.026967757634</v>
       </c>
       <c r="J74" t="n">
-        <v>189.061086313599</v>
+        <v>189.111925958194</v>
       </c>
       <c r="K74" t="n">
-        <v>9.000641667410143</v>
+        <v>9.000641636641358</v>
       </c>
       <c r="L74" t="n">
-        <v>47.62278882649525</v>
+        <v>41.13835376237228</v>
       </c>
       <c r="M74" t="n">
-        <v>9.407585821463726e-12</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.405357348876813</v>
+        <v>2.223772234372549</v>
       </c>
       <c r="O74" t="b">
         <v>1</v>
       </c>
       <c r="P74" t="n">
-        <v>0.8970097303390503</v>
+        <v>0.8822795152664185</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.6279978998936713</v>
+        <v>1.606696299975738</v>
       </c>
       <c r="R74" t="n">
-        <v>0.0003695680352393538</v>
+        <v>0.0002743584918789566</v>
       </c>
       <c r="S74" t="n">
-        <v>939.0922863223436</v>
+        <v>928.2509341161606</v>
       </c>
       <c r="T74" t="n">
-        <v>190.2044761468036</v>
+        <v>189.451085303586</v>
       </c>
       <c r="U74" t="n">
-        <v>9.000641170323545</v>
+        <v>9.000641767290265</v>
       </c>
       <c r="V74" t="n">
-        <v>45.84364779362784</v>
+        <v>40.36232012089886</v>
       </c>
       <c r="W74" t="n">
-        <v>1.143389833195215</v>
+        <v>0.3391593453920052</v>
       </c>
       <c r="X74" t="n">
-        <v>2.405356851790216</v>
+        <v>2.223772365021456</v>
       </c>
       <c r="Y74" t="b">
         <v>1</v>
@@ -6316,74 +6316,74 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>870.4140949772889</v>
+        <v>959.4257991206367</v>
       </c>
       <c r="D75" t="n">
-        <v>7.952992623630619</v>
+        <v>6.331033396665713</v>
       </c>
       <c r="E75" t="n">
-        <v>199.8737532158461</v>
+        <v>189.5268645747033</v>
       </c>
       <c r="F75" t="n">
-        <v>0.974799633026123</v>
+        <v>0.7307463884353638</v>
       </c>
       <c r="G75" t="n">
-        <v>0.1061207999009639</v>
+        <v>0.112019999884069</v>
       </c>
       <c r="H75" t="n">
-        <v>0.001176272286102176</v>
+        <v>0.001032155007123947</v>
       </c>
       <c r="I75" t="n">
-        <v>933.5293019251812</v>
+        <v>959.4257991206371</v>
       </c>
       <c r="J75" t="n">
-        <v>199.8737532158483</v>
+        <v>189.5268645747033</v>
       </c>
       <c r="K75" t="n">
-        <v>9.000641734796444</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L75" t="n">
-        <v>63.11520694789237</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="M75" t="n">
-        <v>2.188471626141109e-12</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>1.047649111165825</v>
+        <v>2.669608383196449</v>
       </c>
       <c r="O75" t="b">
         <v>1</v>
       </c>
       <c r="P75" t="n">
-        <v>0.959416925907135</v>
+        <v>0.6686036586761475</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.4656754999887198</v>
+        <v>0.5333283999934793</v>
       </c>
       <c r="R75" t="n">
-        <v>0.0004905613022856414</v>
+        <v>7.241316052386537e-05</v>
       </c>
       <c r="S75" t="n">
-        <v>933.634536905446</v>
+        <v>957.6483882696963</v>
       </c>
       <c r="T75" t="n">
-        <v>200.4744968783431</v>
+        <v>189.7069072562254</v>
       </c>
       <c r="U75" t="n">
-        <v>9.000641704903027</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V75" t="n">
-        <v>63.22044192815713</v>
+        <v>1.777410850940441</v>
       </c>
       <c r="W75" t="n">
-        <v>0.6007436624970239</v>
+        <v>0.1800426815220817</v>
       </c>
       <c r="X75" t="n">
-        <v>1.047649081272407</v>
+        <v>2.669608383196449</v>
       </c>
       <c r="Y75" t="b">
         <v>1</v>
@@ -6395,74 +6395,74 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>955.1343834559148</v>
+        <v>872.7046428715975</v>
       </c>
       <c r="D76" t="n">
-        <v>8.977698358244938</v>
+        <v>6.7207164120645</v>
       </c>
       <c r="E76" t="n">
-        <v>149.4975831316712</v>
+        <v>212.4005522397584</v>
       </c>
       <c r="F76" t="n">
-        <v>0.9152489304542542</v>
+        <v>0.8526367545127869</v>
       </c>
       <c r="G76" t="n">
-        <v>0.2399756999220699</v>
+        <v>0.2491564000956714</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0006277773063629866</v>
+        <v>0.001640764763578773</v>
       </c>
       <c r="I76" t="n">
-        <v>857.2992001435658</v>
+        <v>929.0269678100341</v>
       </c>
       <c r="J76" t="n">
-        <v>176.1732571670742</v>
+        <v>212.4006107348139</v>
       </c>
       <c r="K76" t="n">
-        <v>9.000001070377479</v>
+        <v>9.000641549142101</v>
       </c>
       <c r="L76" t="n">
-        <v>97.83518331234893</v>
+        <v>56.32232493843662</v>
       </c>
       <c r="M76" t="n">
-        <v>26.67567403540298</v>
+        <v>5.849505541277722e-05</v>
       </c>
       <c r="N76" t="n">
-        <v>0.0223027121325412</v>
+        <v>2.2799251370776</v>
       </c>
       <c r="O76" t="b">
         <v>1</v>
       </c>
       <c r="P76" t="n">
-        <v>0.995904266834259</v>
+        <v>0.988240122795105</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.3503657002002</v>
+        <v>1.5745353999082</v>
       </c>
       <c r="R76" t="n">
-        <v>0.002736728172749281</v>
+        <v>0.0003997681487817317</v>
       </c>
       <c r="S76" t="n">
-        <v>968.5475989499128</v>
+        <v>928.878551611837</v>
       </c>
       <c r="T76" t="n">
-        <v>177.0944569984135</v>
+        <v>210.8789315253923</v>
       </c>
       <c r="U76" t="n">
-        <v>9.129396163131487</v>
+        <v>9.0006411952403</v>
       </c>
       <c r="V76" t="n">
-        <v>13.413215493998</v>
+        <v>56.17390874023954</v>
       </c>
       <c r="W76" t="n">
-        <v>27.59687386674224</v>
+        <v>1.521620714366122</v>
       </c>
       <c r="X76" t="n">
-        <v>0.1516978048865489</v>
+        <v>2.2799247831758</v>
       </c>
       <c r="Y76" t="b">
         <v>1</v>
@@ -6478,70 +6478,70 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>851.5745269766401</v>
+        <v>847.1931358488914</v>
       </c>
       <c r="D77" t="n">
-        <v>7.449623063406067</v>
+        <v>8.499112741453565</v>
       </c>
       <c r="E77" t="n">
-        <v>203.3669380432765</v>
+        <v>214.2980575220417</v>
       </c>
       <c r="F77" t="n">
-        <v>0.9866198301315308</v>
+        <v>0.7607967853546143</v>
       </c>
       <c r="G77" t="n">
-        <v>0.1218620000872761</v>
+        <v>0.2742709999438375</v>
       </c>
       <c r="H77" t="n">
-        <v>0.002527530770748854</v>
+        <v>0.002007473492994905</v>
       </c>
       <c r="I77" t="n">
-        <v>920.0590705958026</v>
+        <v>924.8594770251983</v>
       </c>
       <c r="J77" t="n">
-        <v>204.0722128093243</v>
+        <v>214.2981243889143</v>
       </c>
       <c r="K77" t="n">
-        <v>9.000595810886647</v>
+        <v>9.000641607794503</v>
       </c>
       <c r="L77" t="n">
-        <v>68.48454361916254</v>
+        <v>77.6663411763069</v>
       </c>
       <c r="M77" t="n">
-        <v>0.7052747660477507</v>
+        <v>6.686687265755609e-05</v>
       </c>
       <c r="N77" t="n">
-        <v>1.55097274748058</v>
+        <v>0.5015288663409372</v>
       </c>
       <c r="O77" t="b">
         <v>1</v>
       </c>
       <c r="P77" t="n">
-        <v>0.9868501424789429</v>
+        <v>0.9796766638755798</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.4591127999592572</v>
+        <v>1.59867179999128</v>
       </c>
       <c r="R77" t="n">
-        <v>0.0006404300802387297</v>
+        <v>0.0005997993866913021</v>
       </c>
       <c r="S77" t="n">
-        <v>931.6855047847178</v>
+        <v>927.1962550936013</v>
       </c>
       <c r="T77" t="n">
-        <v>203.6868514977849</v>
+        <v>211.9615461255205</v>
       </c>
       <c r="U77" t="n">
-        <v>9.000641852425925</v>
+        <v>9.000641043423281</v>
       </c>
       <c r="V77" t="n">
-        <v>80.11097780807768</v>
+        <v>80.00311924470986</v>
       </c>
       <c r="W77" t="n">
-        <v>0.3199134545083666</v>
+        <v>2.336511396521132</v>
       </c>
       <c r="X77" t="n">
-        <v>1.551018789019858</v>
+        <v>0.5015283019697154</v>
       </c>
       <c r="Y77" t="b">
         <v>1</v>
@@ -6553,74 +6553,74 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>983.9103163849971</v>
+        <v>859.7074679282812</v>
       </c>
       <c r="D78" t="n">
-        <v>10.80942127573965</v>
+        <v>6.821419512121432</v>
       </c>
       <c r="E78" t="n">
-        <v>157.6836892871747</v>
+        <v>203.3974169651172</v>
       </c>
       <c r="F78" t="n">
-        <v>0.7411229610443115</v>
+        <v>0.8506406545639038</v>
       </c>
       <c r="G78" t="n">
-        <v>0.2532765998039395</v>
+        <v>0.2243352001532912</v>
       </c>
       <c r="H78" t="n">
-        <v>0.001695083919912577</v>
+        <v>0.00200818688608706</v>
       </c>
       <c r="I78" t="n">
-        <v>980.651521949164</v>
+        <v>924.8604949812226</v>
       </c>
       <c r="J78" t="n">
-        <v>173.9057564547762</v>
+        <v>203.3974162844619</v>
       </c>
       <c r="K78" t="n">
-        <v>10.90223005966835</v>
+        <v>9.000600720611482</v>
       </c>
       <c r="L78" t="n">
-        <v>3.258794435833124</v>
+        <v>65.15302705294141</v>
       </c>
       <c r="M78" t="n">
-        <v>16.22206716760144</v>
+        <v>6.80655233509242e-07</v>
       </c>
       <c r="N78" t="n">
-        <v>0.09280878392869596</v>
+        <v>2.17918120849005</v>
       </c>
       <c r="O78" t="b">
         <v>1</v>
       </c>
       <c r="P78" t="n">
-        <v>0.8012228608131409</v>
+        <v>0.9942852854728699</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.7927646001335233</v>
+        <v>1.619586500106379</v>
       </c>
       <c r="R78" t="n">
-        <v>0.002592191798612475</v>
+        <v>0.0004391717084217817</v>
       </c>
       <c r="S78" t="n">
-        <v>838.8451283938605</v>
+        <v>925.9430029616933</v>
       </c>
       <c r="T78" t="n">
-        <v>176.3374337876815</v>
+        <v>202.7527942851561</v>
       </c>
       <c r="U78" t="n">
-        <v>10.79179876111648</v>
+        <v>9.000641617595038</v>
       </c>
       <c r="V78" t="n">
-        <v>145.0651879911367</v>
+        <v>66.23553503341213</v>
       </c>
       <c r="W78" t="n">
-        <v>18.65374450050678</v>
+        <v>0.6446226799610599</v>
       </c>
       <c r="X78" t="n">
-        <v>0.01762251462316833</v>
+        <v>2.179222105473606</v>
       </c>
       <c r="Y78" t="b">
         <v>1</v>
@@ -6632,74 +6632,74 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>993.8091125161995</v>
+        <v>838.7925819789939</v>
       </c>
       <c r="D79" t="n">
-        <v>10.42881588760178</v>
+        <v>7.235527935875294</v>
       </c>
       <c r="E79" t="n">
-        <v>126.4222581227791</v>
+        <v>196.4741261679814</v>
       </c>
       <c r="F79" t="n">
-        <v>0.9748581051826477</v>
+        <v>0.8509666323661804</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3449452000204474</v>
+        <v>0.2566208001226187</v>
       </c>
       <c r="H79" t="n">
-        <v>0.6460902690887451</v>
+        <v>0.001641420414671302</v>
       </c>
       <c r="I79" t="n">
-        <v>945.6722747289361</v>
+        <v>929.0275965722744</v>
       </c>
       <c r="J79" t="n">
-        <v>158.2367514784902</v>
+        <v>196.4741288774167</v>
       </c>
       <c r="K79" t="n">
-        <v>10.22185835107431</v>
+        <v>9.000682785503855</v>
       </c>
       <c r="L79" t="n">
-        <v>48.1368377872634</v>
+        <v>90.23501459328054</v>
       </c>
       <c r="M79" t="n">
-        <v>31.81449335571106</v>
+        <v>2.70943527880263e-06</v>
       </c>
       <c r="N79" t="n">
-        <v>0.2069575365274687</v>
+        <v>1.765154849628561</v>
       </c>
       <c r="O79" t="b">
         <v>1</v>
       </c>
       <c r="P79" t="n">
-        <v>0.9999610185623169</v>
+        <v>0.9930439591407776</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.183981499867514</v>
+        <v>1.675785699859262</v>
       </c>
       <c r="R79" t="n">
-        <v>0.01020536478608847</v>
+        <v>0.0005860047531314194</v>
       </c>
       <c r="S79" t="n">
-        <v>800.0000560979408</v>
+        <v>923.9479840287044</v>
       </c>
       <c r="T79" t="n">
-        <v>162.0675053733594</v>
+        <v>196.3653760364051</v>
       </c>
       <c r="U79" t="n">
-        <v>10.28129265562665</v>
+        <v>9.000641793966926</v>
       </c>
       <c r="V79" t="n">
-        <v>193.8090564182587</v>
+        <v>85.15540204971046</v>
       </c>
       <c r="W79" t="n">
-        <v>35.64524725058025</v>
+        <v>0.1087501315762438</v>
       </c>
       <c r="X79" t="n">
-        <v>0.1475232319751356</v>
+        <v>1.765113858091632</v>
       </c>
       <c r="Y79" t="b">
         <v>1</v>
@@ -6711,74 +6711,74 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>957.0963623635679</v>
+        <v>934.0645962626772</v>
       </c>
       <c r="D80" t="n">
-        <v>9.945535047873713</v>
+        <v>6.569227270143569</v>
       </c>
       <c r="E80" t="n">
-        <v>146.1438499325558</v>
+        <v>200.9181426360591</v>
       </c>
       <c r="F80" t="n">
-        <v>0.8736257553100586</v>
+        <v>0.7307463884353638</v>
       </c>
       <c r="G80" t="n">
-        <v>0.2273296001367271</v>
+        <v>0.1003854000009596</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0001908630947582424</v>
+        <v>0.001059164758771658</v>
       </c>
       <c r="I80" t="n">
-        <v>957.0934828425404</v>
+        <v>934.0645962626883</v>
       </c>
       <c r="J80" t="n">
-        <v>176.173305591252</v>
+        <v>200.9181426360591</v>
       </c>
       <c r="K80" t="n">
-        <v>10.45735275974209</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L80" t="n">
-        <v>0.002879521027466581</v>
+        <v>1.102762325899675e-11</v>
       </c>
       <c r="M80" t="n">
-        <v>30.02945565869624</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N80" t="n">
-        <v>0.5118177118683747</v>
+        <v>2.431414509718594</v>
       </c>
       <c r="O80" t="b">
         <v>1</v>
       </c>
       <c r="P80" t="n">
-        <v>0.9989305138587952</v>
+        <v>0.4573295116424561</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.767661799909547</v>
+        <v>0.5052175999153405</v>
       </c>
       <c r="R80" t="n">
-        <v>0.004141734447330236</v>
+        <v>5.69809417356737e-05</v>
       </c>
       <c r="S80" t="n">
-        <v>800.0013987224835</v>
+        <v>935.5858265671992</v>
       </c>
       <c r="T80" t="n">
-        <v>165.8646354403891</v>
+        <v>200.8673151076025</v>
       </c>
       <c r="U80" t="n">
-        <v>9.873318941401386</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V80" t="n">
-        <v>157.0949636410844</v>
+        <v>1.521230304521964</v>
       </c>
       <c r="W80" t="n">
-        <v>19.72078550783331</v>
+        <v>0.05082752845663663</v>
       </c>
       <c r="X80" t="n">
-        <v>0.07221610647232701</v>
+        <v>2.431414509718594</v>
       </c>
       <c r="Y80" t="b">
         <v>1</v>
@@ -6794,70 +6794,70 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>960.9051696605223</v>
+        <v>1000.530798651601</v>
       </c>
       <c r="D81" t="n">
-        <v>8.837957497580597</v>
+        <v>10.80129278338204</v>
       </c>
       <c r="E81" t="n">
-        <v>130.4948925638571</v>
+        <v>157.8993784828023</v>
       </c>
       <c r="F81" t="n">
-        <v>0.9823979735374451</v>
+        <v>0.6631425023078918</v>
       </c>
       <c r="G81" t="n">
-        <v>0.2217566000763327</v>
+        <v>0.5334628999698907</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0006277773063629866</v>
+        <v>0.0008324514492414892</v>
       </c>
       <c r="I81" t="n">
-        <v>857.2856615298629</v>
+        <v>999.9999806378897</v>
       </c>
       <c r="J81" t="n">
-        <v>176.1732577477451</v>
+        <v>173.7371866221566</v>
       </c>
       <c r="K81" t="n">
-        <v>9.000001253609373</v>
+        <v>10.80139311912626</v>
       </c>
       <c r="L81" t="n">
-        <v>103.6195081306595</v>
+        <v>0.5308180137116096</v>
       </c>
       <c r="M81" t="n">
-        <v>45.67836518388796</v>
+        <v>15.83780813935428</v>
       </c>
       <c r="N81" t="n">
-        <v>0.1620437560287762</v>
+        <v>0.0001003357442197483</v>
       </c>
       <c r="O81" t="b">
         <v>1</v>
       </c>
       <c r="P81" t="n">
-        <v>0.9999749660491943</v>
+        <v>0.1600920110940933</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.5748632000759244</v>
+        <v>2.787225500214845</v>
       </c>
       <c r="R81" t="n">
-        <v>0.008983481675386429</v>
+        <v>0.001763349748216569</v>
       </c>
       <c r="S81" t="n">
-        <v>800.0000395550629</v>
+        <v>839.2586338246971</v>
       </c>
       <c r="T81" t="n">
-        <v>160.9161272312666</v>
+        <v>166.5247036060972</v>
       </c>
       <c r="U81" t="n">
-        <v>9.000642171565886</v>
+        <v>10.64395722779983</v>
       </c>
       <c r="V81" t="n">
-        <v>160.9051301054594</v>
+        <v>161.2721648269043</v>
       </c>
       <c r="W81" t="n">
-        <v>30.42123466740952</v>
+        <v>8.625325123294886</v>
       </c>
       <c r="X81" t="n">
-        <v>0.1626846739852894</v>
+        <v>0.1573355555822094</v>
       </c>
       <c r="Y81" t="b">
         <v>1</v>
@@ -6869,74 +6869,74 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>955.4016882269552</v>
+        <v>916.9964215899955</v>
       </c>
       <c r="D82" t="n">
-        <v>9.689352730554308</v>
+        <v>4.061906490210131</v>
       </c>
       <c r="E82" t="n">
-        <v>123.1606314457139</v>
+        <v>202.4842632135048</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9816255569458008</v>
+        <v>0.5444756150245667</v>
       </c>
       <c r="G82" t="n">
-        <v>0.3144268000032753</v>
+        <v>0.1345057999715209</v>
       </c>
       <c r="H82" t="n">
-        <v>0.002671804977580905</v>
+        <v>0.001054888241924345</v>
       </c>
       <c r="I82" t="n">
-        <v>963.2195815735341</v>
+        <v>915.9952042607318</v>
       </c>
       <c r="J82" t="n">
-        <v>173.947135934415</v>
+        <v>202.4841960292941</v>
       </c>
       <c r="K82" t="n">
-        <v>10.51127185358748</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L82" t="n">
-        <v>7.817893346578899</v>
+        <v>1.001217329263682</v>
       </c>
       <c r="M82" t="n">
-        <v>50.78650448870104</v>
+        <v>6.718421073514946e-05</v>
       </c>
       <c r="N82" t="n">
-        <v>0.8219191230331671</v>
+        <v>4.938735289652032</v>
       </c>
       <c r="O82" t="b">
         <v>1</v>
       </c>
       <c r="P82" t="n">
-        <v>0.9999963045120239</v>
+        <v>0.9490045309066772</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.8854722001124173</v>
+        <v>0.6504508000798523</v>
       </c>
       <c r="R82" t="n">
-        <v>0.01242727413773537</v>
+        <v>0.0001079364228644408</v>
       </c>
       <c r="S82" t="n">
-        <v>800.0000001712805</v>
+        <v>922.1735183840758</v>
       </c>
       <c r="T82" t="n">
-        <v>159.6918072561193</v>
+        <v>202.3424349450505</v>
       </c>
       <c r="U82" t="n">
-        <v>9.202218281272526</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V82" t="n">
-        <v>155.4016880556748</v>
+        <v>5.177096794080285</v>
       </c>
       <c r="W82" t="n">
-        <v>36.53117581040533</v>
+        <v>0.1418282684543328</v>
       </c>
       <c r="X82" t="n">
-        <v>0.4871344492817826</v>
+        <v>4.938735289652032</v>
       </c>
       <c r="Y82" t="b">
         <v>1</v>
@@ -6952,70 +6952,70 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>959.2619273148472</v>
+        <v>926.7147831503679</v>
       </c>
       <c r="D83" t="n">
-        <v>10.64543182167768</v>
+        <v>11.10188954260576</v>
       </c>
       <c r="E83" t="n">
-        <v>147.3925039561177</v>
+        <v>118.639878759105</v>
       </c>
       <c r="F83" t="n">
-        <v>0.8763126730918884</v>
+        <v>0.7199835777282715</v>
       </c>
       <c r="G83" t="n">
-        <v>0.2024073000065982</v>
+        <v>0.5737242000177503</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0001908630947582424</v>
+        <v>0.004656502045691013</v>
       </c>
       <c r="I83" t="n">
-        <v>957.595351926822</v>
+        <v>891.6673146525425</v>
       </c>
       <c r="J83" t="n">
-        <v>176.1732562427629</v>
+        <v>173.7371835569596</v>
       </c>
       <c r="K83" t="n">
-        <v>10.6453756697237</v>
+        <v>11.10171871541859</v>
       </c>
       <c r="L83" t="n">
-        <v>1.666575388025194</v>
+        <v>35.04746849782543</v>
       </c>
       <c r="M83" t="n">
-        <v>28.7807522866452</v>
+        <v>55.0973047978546</v>
       </c>
       <c r="N83" t="n">
-        <v>5.61519539825639e-05</v>
+        <v>0.0001708271871692091</v>
       </c>
       <c r="O83" t="b">
         <v>1</v>
       </c>
       <c r="P83" t="n">
-        <v>0.9980813264846802</v>
+        <v>0.9999591112136841</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.8478394001722336</v>
+        <v>1.554130600066856</v>
       </c>
       <c r="R83" t="n">
-        <v>0.003741910448297858</v>
+        <v>0.001670715282671154</v>
       </c>
       <c r="S83" t="n">
-        <v>800.0024596149598</v>
+        <v>800.8793300296152</v>
       </c>
       <c r="T83" t="n">
-        <v>166.5618089233324</v>
+        <v>150.0005521801378</v>
       </c>
       <c r="U83" t="n">
-        <v>10.65838411008192</v>
+        <v>10.92773995668466</v>
       </c>
       <c r="V83" t="n">
-        <v>159.2594676998874</v>
+        <v>125.8354531207527</v>
       </c>
       <c r="W83" t="n">
-        <v>19.16930496721477</v>
+        <v>31.36067342103277</v>
       </c>
       <c r="X83" t="n">
-        <v>0.0129522884042359</v>
+        <v>0.1741495859211035</v>
       </c>
       <c r="Y83" t="b">
         <v>1</v>
@@ -7031,70 +7031,70 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>844.1387241107644</v>
+        <v>876.7511479722946</v>
       </c>
       <c r="D84" t="n">
-        <v>8.359806894064747</v>
+        <v>8.046191324537496</v>
       </c>
       <c r="E84" t="n">
-        <v>202.8412666888779</v>
+        <v>207.9055936817364</v>
       </c>
       <c r="F84" t="n">
-        <v>0.9779818654060364</v>
+        <v>0.6946394443511963</v>
       </c>
       <c r="G84" t="n">
-        <v>0.2301713000051677</v>
+        <v>0.2366309999488294</v>
       </c>
       <c r="H84" t="n">
-        <v>0.00139266811311245</v>
+        <v>0.001641420414671302</v>
       </c>
       <c r="I84" t="n">
-        <v>925.9037221576409</v>
+        <v>929.026971484157</v>
       </c>
       <c r="J84" t="n">
-        <v>191.0020853883559</v>
+        <v>207.9055936817364</v>
       </c>
       <c r="K84" t="n">
-        <v>9.000723577019036</v>
+        <v>9.000641551537415</v>
       </c>
       <c r="L84" t="n">
-        <v>81.76499804687649</v>
+        <v>52.27582351186243</v>
       </c>
       <c r="M84" t="n">
-        <v>11.83918130052203</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N84" t="n">
-        <v>0.6409166829542894</v>
+        <v>0.9544502269999189</v>
       </c>
       <c r="O84" t="b">
         <v>1</v>
       </c>
       <c r="P84" t="n">
-        <v>0.9603607654571533</v>
+        <v>0.9524722695350647</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.4283501000609249</v>
+        <v>1.287052900064737</v>
       </c>
       <c r="R84" t="n">
-        <v>0.0007038408075459301</v>
+        <v>0.000342210492817685</v>
       </c>
       <c r="S84" t="n">
-        <v>931.1727695277716</v>
+        <v>928.1992610690543</v>
       </c>
       <c r="T84" t="n">
-        <v>203.2623278007789</v>
+        <v>206.992105275543</v>
       </c>
       <c r="U84" t="n">
-        <v>9.000641872699958</v>
+        <v>9.000641635179212</v>
       </c>
       <c r="V84" t="n">
-        <v>87.03404541700718</v>
+        <v>51.4481130967597</v>
       </c>
       <c r="W84" t="n">
-        <v>0.4210611119009684</v>
+        <v>0.9134884061933803</v>
       </c>
       <c r="X84" t="n">
-        <v>0.6408349786352119</v>
+        <v>0.9544503106417164</v>
       </c>
       <c r="Y84" t="b">
         <v>1</v>
@@ -7106,74 +7106,74 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>870.4646279587909</v>
+        <v>945.8233754351328</v>
       </c>
       <c r="D85" t="n">
-        <v>7.267081257983708</v>
+        <v>9.351547350593361</v>
       </c>
       <c r="E85" t="n">
-        <v>183.9231629870082</v>
+        <v>150.2474638719561</v>
       </c>
       <c r="F85" t="n">
-        <v>0.9806914329528809</v>
+        <v>0.6767300963401794</v>
       </c>
       <c r="G85" t="n">
-        <v>0.1396172000095248</v>
+        <v>0.369642399949953</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0009205389069393277</v>
+        <v>0.0008354719611816108</v>
       </c>
       <c r="I85" t="n">
-        <v>933.5316326486537</v>
+        <v>945.8233782282691</v>
       </c>
       <c r="J85" t="n">
-        <v>185.8717530899106</v>
+        <v>173.7371834327885</v>
       </c>
       <c r="K85" t="n">
-        <v>9.000778900824686</v>
+        <v>9.351635653297663</v>
       </c>
       <c r="L85" t="n">
-        <v>63.06700468986287</v>
+        <v>2.793136332002177e-06</v>
       </c>
       <c r="M85" t="n">
-        <v>1.948590102902415</v>
+        <v>23.48971956083238</v>
       </c>
       <c r="N85" t="n">
-        <v>1.733697642840978</v>
+        <v>8.830270430237874e-05</v>
       </c>
       <c r="O85" t="b">
         <v>1</v>
       </c>
       <c r="P85" t="n">
-        <v>0.9739370942115784</v>
+        <v>0.9909306168556213</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.4169599001761526</v>
+        <v>2.247947700088844</v>
       </c>
       <c r="R85" t="n">
-        <v>0.0005893245688639581</v>
+        <v>0.001419720472767949</v>
       </c>
       <c r="S85" t="n">
-        <v>938.711898903316</v>
+        <v>826.4695559391522</v>
       </c>
       <c r="T85" t="n">
-        <v>185.9048202019186</v>
+        <v>156.5000052247234</v>
       </c>
       <c r="U85" t="n">
-        <v>9.000640579272725</v>
+        <v>9.26869916384992</v>
       </c>
       <c r="V85" t="n">
-        <v>68.2472709445251</v>
+        <v>119.3538194959806</v>
       </c>
       <c r="W85" t="n">
-        <v>1.981657214910399</v>
+        <v>6.252541352767281</v>
       </c>
       <c r="X85" t="n">
-        <v>1.733559321289016</v>
+        <v>0.08284818674344052</v>
       </c>
       <c r="Y85" t="b">
         <v>1</v>
@@ -7185,74 +7185,74 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>851.3108041478846</v>
+        <v>946.9959803049074</v>
       </c>
       <c r="D86" t="n">
-        <v>9.465494845876609</v>
+        <v>10.69043681472218</v>
       </c>
       <c r="E86" t="n">
-        <v>192.9091882371535</v>
+        <v>122.5622611924395</v>
       </c>
       <c r="F86" t="n">
-        <v>0.9742845892906189</v>
+        <v>0.6767300963401794</v>
       </c>
       <c r="G86" t="n">
-        <v>0.1737034001853317</v>
+        <v>0.341127400053665</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0009308591834269464</v>
+        <v>0.0008354719611816108</v>
       </c>
       <c r="I86" t="n">
-        <v>920.0548465954727</v>
+        <v>938.8344453378912</v>
       </c>
       <c r="J86" t="n">
-        <v>192.9091882371536</v>
+        <v>173.7382322432709</v>
       </c>
       <c r="K86" t="n">
-        <v>9.710948091122503</v>
+        <v>10.7543009236818</v>
       </c>
       <c r="L86" t="n">
-        <v>68.74404244758807</v>
+        <v>8.161534967016223</v>
       </c>
       <c r="M86" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>51.17597105083134</v>
       </c>
       <c r="N86" t="n">
-        <v>0.2454532452458942</v>
+        <v>0.0638641089596188</v>
       </c>
       <c r="O86" t="b">
         <v>1</v>
       </c>
       <c r="P86" t="n">
-        <v>0.8187144994735718</v>
+        <v>0.9999586343765259</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.3864044998772442</v>
+        <v>1.425939799984917</v>
       </c>
       <c r="R86" t="n">
-        <v>0.0005837970529682934</v>
+        <v>0.0017396459588781</v>
       </c>
       <c r="S86" t="n">
-        <v>926.3021142192191</v>
+        <v>805.0111637170454</v>
       </c>
       <c r="T86" t="n">
-        <v>194.2403647875714</v>
+        <v>150.0005521349353</v>
       </c>
       <c r="U86" t="n">
-        <v>9.579142492131494</v>
+        <v>10.53175419089168</v>
       </c>
       <c r="V86" t="n">
-        <v>74.99131007133451</v>
+        <v>141.984816587862</v>
       </c>
       <c r="W86" t="n">
-        <v>1.331176550417894</v>
+        <v>27.43829094249575</v>
       </c>
       <c r="X86" t="n">
-        <v>0.1136476462548845</v>
+        <v>0.1586826238304972</v>
       </c>
       <c r="Y86" t="b">
         <v>1</v>
@@ -7264,74 +7264,74 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>935.6117250099762</v>
+        <v>853.2445715938389</v>
       </c>
       <c r="D87" t="n">
-        <v>8.096975787254928</v>
+        <v>8.889361698892458</v>
       </c>
       <c r="E87" t="n">
-        <v>120.4668218901487</v>
+        <v>201.7835415270264</v>
       </c>
       <c r="F87" t="n">
-        <v>0.9742164015769958</v>
+        <v>0.7346910834312439</v>
       </c>
       <c r="G87" t="n">
-        <v>0.1976201001089066</v>
+        <v>0.219273499911651</v>
       </c>
       <c r="H87" t="n">
-        <v>0.002779936417937279</v>
+        <v>0.001641420414671302</v>
       </c>
       <c r="I87" t="n">
-        <v>828.025278046671</v>
+        <v>929.0283708884666</v>
       </c>
       <c r="J87" t="n">
-        <v>176.1732562382385</v>
+        <v>201.783541519616</v>
       </c>
       <c r="K87" t="n">
-        <v>10.52896040961697</v>
+        <v>9.000641486686645</v>
       </c>
       <c r="L87" t="n">
-        <v>107.5864469633052</v>
+        <v>75.78379929462767</v>
       </c>
       <c r="M87" t="n">
-        <v>55.70643434808989</v>
+        <v>7.410420721498667e-09</v>
       </c>
       <c r="N87" t="n">
-        <v>2.431984622362041</v>
+        <v>0.1112797877941869</v>
       </c>
       <c r="O87" t="b">
         <v>1</v>
       </c>
       <c r="P87" t="n">
-        <v>0.999982476234436</v>
+        <v>0.9593555927276611</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.5885926000773907</v>
+        <v>1.309527900069952</v>
       </c>
       <c r="R87" t="n">
-        <v>0.01384405326098204</v>
+        <v>0.0004781610623467714</v>
       </c>
       <c r="S87" t="n">
-        <v>800.0000235560657</v>
+        <v>925.3009666335253</v>
       </c>
       <c r="T87" t="n">
-        <v>158.6847531624352</v>
+        <v>201.247803666124</v>
       </c>
       <c r="U87" t="n">
-        <v>9.000641996954409</v>
+        <v>9.000641746968371</v>
       </c>
       <c r="V87" t="n">
-        <v>135.6117014539105</v>
+        <v>72.05639503968632</v>
       </c>
       <c r="W87" t="n">
-        <v>38.21793127228659</v>
+        <v>0.5357378609024011</v>
       </c>
       <c r="X87" t="n">
-        <v>0.9036662096994803</v>
+        <v>0.1112800480759137</v>
       </c>
       <c r="Y87" t="b">
         <v>1</v>
@@ -7343,74 +7343,74 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>941.4647434232286</v>
+        <v>837.2414016303974</v>
       </c>
       <c r="D88" t="n">
-        <v>5.690848243636317</v>
+        <v>8.017493072487792</v>
       </c>
       <c r="E88" t="n">
-        <v>197.0383130866155</v>
+        <v>194.9453487487005</v>
       </c>
       <c r="F88" t="n">
-        <v>0.966529905796051</v>
+        <v>0.8449464440345764</v>
       </c>
       <c r="G88" t="n">
-        <v>0.02561299991793931</v>
+        <v>0.2241438999772072</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0002481373958289623</v>
+        <v>0.0023431780282408</v>
       </c>
       <c r="I88" t="n">
-        <v>941.4647434232262</v>
+        <v>923.5221648716871</v>
       </c>
       <c r="J88" t="n">
-        <v>197.0383130866234</v>
+        <v>194.9454117449691</v>
       </c>
       <c r="K88" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000631800358006</v>
       </c>
       <c r="L88" t="n">
-        <v>2.387423592153937e-12</v>
+        <v>86.28076324128972</v>
       </c>
       <c r="M88" t="n">
-        <v>7.986500349943526e-12</v>
+        <v>6.299626866734798e-05</v>
       </c>
       <c r="N88" t="n">
-        <v>3.309793536225845</v>
+        <v>0.9831387278702142</v>
       </c>
       <c r="O88" t="b">
         <v>1</v>
       </c>
       <c r="P88" t="n">
-        <v>0.877874493598938</v>
+        <v>0.9837929606437683</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.1810258999466896</v>
+        <v>1.399755100021139</v>
       </c>
       <c r="R88" t="n">
-        <v>9.585031511960551e-05</v>
+        <v>0.0006017276318743825</v>
       </c>
       <c r="S88" t="n">
-        <v>942.3031976462509</v>
+        <v>923.8059292009133</v>
       </c>
       <c r="T88" t="n">
-        <v>197.2130476809959</v>
+        <v>194.9666147729972</v>
       </c>
       <c r="U88" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641858720295</v>
       </c>
       <c r="V88" t="n">
-        <v>0.8384542230222678</v>
+        <v>86.56452757051591</v>
       </c>
       <c r="W88" t="n">
-        <v>0.1747345943804532</v>
+        <v>0.0212660242967786</v>
       </c>
       <c r="X88" t="n">
-        <v>3.309793536225845</v>
+        <v>0.983148786232503</v>
       </c>
       <c r="Y88" t="b">
         <v>1</v>
@@ -7426,70 +7426,70 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>970.7952457920957</v>
+        <v>938.7719152961016</v>
       </c>
       <c r="D89" t="n">
-        <v>6.023239565209312</v>
+        <v>6.342125500575403</v>
       </c>
       <c r="E89" t="n">
-        <v>209.455973623258</v>
+        <v>204.4031534074724</v>
       </c>
       <c r="F89" t="n">
-        <v>0.9555602073669434</v>
+        <v>0.7307463884353638</v>
       </c>
       <c r="G89" t="n">
-        <v>0.02918379986658692</v>
+        <v>0.09846289991401136</v>
       </c>
       <c r="H89" t="n">
-        <v>0.000253947131568566</v>
+        <v>0.001059164758771658</v>
       </c>
       <c r="I89" t="n">
-        <v>970.7952457920951</v>
+        <v>938.7719152956544</v>
       </c>
       <c r="J89" t="n">
-        <v>209.4559736232624</v>
+        <v>204.4031534074724</v>
       </c>
       <c r="K89" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="L89" t="n">
-        <v>5.684341886080801e-13</v>
+        <v>4.472440195968375e-10</v>
       </c>
       <c r="M89" t="n">
-        <v>4.405364961712621e-12</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="N89" t="n">
-        <v>2.97740221465285</v>
+        <v>2.65851627928676</v>
       </c>
       <c r="O89" t="b">
         <v>1</v>
       </c>
       <c r="P89" t="n">
-        <v>0.7576003670692444</v>
+        <v>0.692533552646637</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.1798985998611897</v>
+        <v>0.5875717999879271</v>
       </c>
       <c r="R89" t="n">
-        <v>0.0001228055189130828</v>
+        <v>5.778055492555723e-05</v>
       </c>
       <c r="S89" t="n">
-        <v>966.3777074088998</v>
+        <v>939.7902360443297</v>
       </c>
       <c r="T89" t="n">
-        <v>209.2888752562138</v>
+        <v>204.2856349967401</v>
       </c>
       <c r="U89" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V89" t="n">
-        <v>4.417538383195847</v>
+        <v>1.01832074822812</v>
       </c>
       <c r="W89" t="n">
-        <v>0.1670983670441331</v>
+        <v>0.1175184107323162</v>
       </c>
       <c r="X89" t="n">
-        <v>2.97740221465285</v>
+        <v>2.65851627928676</v>
       </c>
       <c r="Y89" t="b">
         <v>1</v>
@@ -7501,74 +7501,74 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>893.2184268102915</v>
+        <v>959.5049599256882</v>
       </c>
       <c r="D90" t="n">
-        <v>9.616785371297654</v>
+        <v>11.64064096072369</v>
       </c>
       <c r="E90" t="n">
-        <v>209.1237870441858</v>
+        <v>133.5682807777723</v>
       </c>
       <c r="F90" t="n">
-        <v>0.573319137096405</v>
+        <v>0.5675098896026611</v>
       </c>
       <c r="G90" t="n">
-        <v>0.1531768999993801</v>
+        <v>0.5393866000231355</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0009827348403632641</v>
+        <v>0.01439552940428257</v>
       </c>
       <c r="I90" t="n">
-        <v>920.0581520444725</v>
+        <v>962.2663924347563</v>
       </c>
       <c r="J90" t="n">
-        <v>209.1236725574585</v>
+        <v>167.3097803804677</v>
       </c>
       <c r="K90" t="n">
-        <v>9.697405842036328</v>
+        <v>11.64064326039687</v>
       </c>
       <c r="L90" t="n">
-        <v>26.83972523418106</v>
+        <v>2.761432509068072</v>
       </c>
       <c r="M90" t="n">
-        <v>0.0001144867273126238</v>
+        <v>33.74149960269543</v>
       </c>
       <c r="N90" t="n">
-        <v>0.0806204707386744</v>
+        <v>2.299673184325002e-06</v>
       </c>
       <c r="O90" t="b">
         <v>1</v>
       </c>
       <c r="P90" t="n">
-        <v>0.1536517739295959</v>
+        <v>0.9993539452552795</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.3575754999183118</v>
+        <v>1.783423600019887</v>
       </c>
       <c r="R90" t="n">
-        <v>0.0002543953305575997</v>
+        <v>0.002262635622173548</v>
       </c>
       <c r="S90" t="n">
-        <v>928.6878374183932</v>
+        <v>800.0000546562968</v>
       </c>
       <c r="T90" t="n">
-        <v>208.7213811975867</v>
+        <v>150.0005529130447</v>
       </c>
       <c r="U90" t="n">
-        <v>9.664924274177128</v>
+        <v>11.35894252851554</v>
       </c>
       <c r="V90" t="n">
-        <v>35.46941060810173</v>
+        <v>159.5049052693914</v>
       </c>
       <c r="W90" t="n">
-        <v>0.4024058465991516</v>
+        <v>16.4322721352724</v>
       </c>
       <c r="X90" t="n">
-        <v>0.04813890287947409</v>
+        <v>0.2816984322081471</v>
       </c>
       <c r="Y90" t="b">
         <v>1</v>
@@ -7580,74 +7580,74 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>946.6736588014063</v>
+        <v>876.4757668973676</v>
       </c>
       <c r="D91" t="n">
-        <v>10.82030558818615</v>
+        <v>6.605769645544348</v>
       </c>
       <c r="E91" t="n">
-        <v>130.0842806140458</v>
+        <v>205.7483966820732</v>
       </c>
       <c r="F91" t="n">
-        <v>0.9806832075119019</v>
+        <v>0.7930442690849304</v>
       </c>
       <c r="G91" t="n">
-        <v>0.2558557000011206</v>
+        <v>0.4156311999540776</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0001908630947582424</v>
+        <v>0.001641420414671302</v>
       </c>
       <c r="I91" t="n">
-        <v>946.6770800594492</v>
+        <v>929.0272838051541</v>
       </c>
       <c r="J91" t="n">
-        <v>176.1732562382421</v>
+        <v>205.7483476948057</v>
       </c>
       <c r="K91" t="n">
-        <v>10.82079502788056</v>
+        <v>9.000000239654062</v>
       </c>
       <c r="L91" t="n">
-        <v>0.003421258042862974</v>
+        <v>52.55151690778644</v>
       </c>
       <c r="M91" t="n">
-        <v>46.08897562419628</v>
+        <v>4.898726749047455e-05</v>
       </c>
       <c r="N91" t="n">
-        <v>0.0004894396944052914</v>
+        <v>2.394230594109714</v>
       </c>
       <c r="O91" t="b">
         <v>1</v>
       </c>
       <c r="P91" t="n">
-        <v>0.9999833106994629</v>
+        <v>0.9835144281387329</v>
       </c>
       <c r="Q91" t="n">
-        <v>1.192420999985188</v>
+        <v>1.484753199853003</v>
       </c>
       <c r="R91" t="n">
-        <v>0.008410211652517319</v>
+        <v>0.0003369417681824416</v>
       </c>
       <c r="S91" t="n">
-        <v>800.0000534489454</v>
+        <v>927.7284964280966</v>
       </c>
       <c r="T91" t="n">
-        <v>163.0817421923393</v>
+        <v>205.039928614542</v>
       </c>
       <c r="U91" t="n">
-        <v>10.8316126588835</v>
+        <v>9.000641655518043</v>
       </c>
       <c r="V91" t="n">
-        <v>146.6736053524609</v>
+        <v>51.25272953072897</v>
       </c>
       <c r="W91" t="n">
-        <v>32.9974615782935</v>
+        <v>0.7084680675312711</v>
       </c>
       <c r="X91" t="n">
-        <v>0.01130707069734882</v>
+        <v>2.394872009973695</v>
       </c>
       <c r="Y91" t="b">
         <v>1</v>
@@ -7659,74 +7659,74 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>985.1016721152307</v>
+        <v>883.4868469274719</v>
       </c>
       <c r="D92" t="n">
-        <v>14.32305064805296</v>
+        <v>7.496374588215676</v>
       </c>
       <c r="E92" t="n">
-        <v>195.2429895351666</v>
+        <v>216.8016449596609</v>
       </c>
       <c r="F92" t="n">
-        <v>0.961887001991272</v>
+        <v>0.7943462133407593</v>
       </c>
       <c r="G92" t="n">
-        <v>0.1523321999702603</v>
+        <v>0.2410278001334518</v>
       </c>
       <c r="H92" t="n">
-        <v>0.01351658906787634</v>
+        <v>0.001640737871639431</v>
       </c>
       <c r="I92" t="n">
-        <v>952.7864045000421</v>
+        <v>929.0269663015033</v>
       </c>
       <c r="J92" t="n">
-        <v>196.3535407277273</v>
+        <v>216.8016777577037</v>
       </c>
       <c r="K92" t="n">
-        <v>12.67378394915221</v>
+        <v>9.000641714754583</v>
       </c>
       <c r="L92" t="n">
-        <v>32.31526761518865</v>
+        <v>45.54011937403141</v>
       </c>
       <c r="M92" t="n">
-        <v>1.110551192560678</v>
+        <v>3.279804280964527e-05</v>
       </c>
       <c r="N92" t="n">
-        <v>1.64926669890075</v>
+        <v>1.504267126538907</v>
       </c>
       <c r="O92" t="b">
         <v>1</v>
       </c>
       <c r="P92" t="n">
-        <v>0.9725342988967896</v>
+        <v>0.9485679864883423</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.4839137999806553</v>
+        <v>1.26100270007737</v>
       </c>
       <c r="R92" t="n">
-        <v>0.004093831405043602</v>
+        <v>0.0003664910909719765</v>
       </c>
       <c r="S92" t="n">
-        <v>802.8295922222691</v>
+        <v>931.6067796999025</v>
       </c>
       <c r="T92" t="n">
-        <v>201.7163677825116</v>
+        <v>214.8575322181752</v>
       </c>
       <c r="U92" t="n">
-        <v>12.88618694878027</v>
+        <v>9.000640342871806</v>
       </c>
       <c r="V92" t="n">
-        <v>182.2720798929616</v>
+        <v>48.11993277243062</v>
       </c>
       <c r="W92" t="n">
-        <v>6.473378247344982</v>
+        <v>1.944112741485753</v>
       </c>
       <c r="X92" t="n">
-        <v>1.436863699272692</v>
+        <v>1.504265754656131</v>
       </c>
       <c r="Y92" t="b">
         <v>1</v>
@@ -7738,74 +7738,74 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>919.8886962981079</v>
+        <v>882.5883669668395</v>
       </c>
       <c r="D93" t="n">
-        <v>3.25331237475298</v>
+        <v>7.586598678500282</v>
       </c>
       <c r="E93" t="n">
-        <v>201.6262289488754</v>
+        <v>179.8249621550254</v>
       </c>
       <c r="F93" t="n">
-        <v>0.920503556728363</v>
+        <v>0.7243368029594421</v>
       </c>
       <c r="G93" t="n">
-        <v>0.04467609990388155</v>
+        <v>0.2347736998926848</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0002785818069241941</v>
+        <v>0.002008212730288506</v>
       </c>
       <c r="I93" t="n">
-        <v>920.0551572371252</v>
+        <v>924.8594728992016</v>
       </c>
       <c r="J93" t="n">
-        <v>201.6262289489925</v>
+        <v>179.8249544693294</v>
       </c>
       <c r="K93" t="n">
-        <v>9.000641779862162</v>
+        <v>9.00064157126331</v>
       </c>
       <c r="L93" t="n">
-        <v>0.16646093901727</v>
+        <v>42.27110593236205</v>
       </c>
       <c r="M93" t="n">
-        <v>1.171542862721253e-10</v>
+        <v>7.685696004955389e-06</v>
       </c>
       <c r="N93" t="n">
-        <v>5.747329405109182</v>
+        <v>1.414042892763028</v>
       </c>
       <c r="O93" t="b">
         <v>1</v>
       </c>
       <c r="P93" t="n">
-        <v>0.9725978970527649</v>
+        <v>0.7135631442070007</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.1982468001078814</v>
+        <v>1.318423099815845</v>
       </c>
       <c r="R93" t="n">
-        <v>0.0001353306142846122</v>
+        <v>0.0003714924387168139</v>
       </c>
       <c r="S93" t="n">
-        <v>924.7180807076431</v>
+        <v>929.2491630418084</v>
       </c>
       <c r="T93" t="n">
-        <v>201.7033937900675</v>
+        <v>180.7034969697479</v>
       </c>
       <c r="U93" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641708525187</v>
       </c>
       <c r="V93" t="n">
-        <v>4.829384409535237</v>
+        <v>46.66079607496886</v>
       </c>
       <c r="W93" t="n">
-        <v>0.07716484119205802</v>
+        <v>0.8785348147224568</v>
       </c>
       <c r="X93" t="n">
-        <v>5.747329405109182</v>
+        <v>1.414043030024905</v>
       </c>
       <c r="Y93" t="b">
         <v>1</v>
@@ -7817,74 +7817,74 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>965.9262016570707</v>
+        <v>930.7810504699386</v>
       </c>
       <c r="D94" t="n">
-        <v>11.12397579585559</v>
+        <v>4.167404912785494</v>
       </c>
       <c r="E94" t="n">
-        <v>134.9569477941156</v>
+        <v>191.3971014722671</v>
       </c>
       <c r="F94" t="n">
-        <v>0.9808417558670044</v>
+        <v>0.6949499249458313</v>
       </c>
       <c r="G94" t="n">
-        <v>0.1685287998989224</v>
+        <v>0.08335580001585186</v>
       </c>
       <c r="H94" t="n">
-        <v>0.01346223335713148</v>
+        <v>0.001059164758771658</v>
       </c>
       <c r="I94" t="n">
-        <v>983.8469288560883</v>
+        <v>930.7810504703618</v>
       </c>
       <c r="J94" t="n">
-        <v>169.4477859692686</v>
+        <v>191.3971014722673</v>
       </c>
       <c r="K94" t="n">
-        <v>10.73647508767043</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L94" t="n">
-        <v>17.92072719901762</v>
+        <v>4.232560968375765e-10</v>
       </c>
       <c r="M94" t="n">
-        <v>34.49083817515299</v>
+        <v>2.842170943040401e-13</v>
       </c>
       <c r="N94" t="n">
-        <v>0.3875007081851596</v>
+        <v>4.833236867076669</v>
       </c>
       <c r="O94" t="b">
         <v>1</v>
       </c>
       <c r="P94" t="n">
-        <v>0.9998940229415894</v>
+        <v>0.9864331483840942</v>
       </c>
       <c r="Q94" t="n">
-        <v>1.038731900043786</v>
+        <v>0.5066314002033323</v>
       </c>
       <c r="R94" t="n">
-        <v>0.006613067351281643</v>
+        <v>6.914245750522241e-05</v>
       </c>
       <c r="S94" t="n">
-        <v>800.0005344035815</v>
+        <v>932.5906830912296</v>
       </c>
       <c r="T94" t="n">
-        <v>163.9775272807305</v>
+        <v>191.4998723057442</v>
       </c>
       <c r="U94" t="n">
-        <v>11.23081233430889</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V94" t="n">
-        <v>165.9256672534892</v>
+        <v>1.80963262129103</v>
       </c>
       <c r="W94" t="n">
-        <v>29.02057948661482</v>
+        <v>0.1027708334771944</v>
       </c>
       <c r="X94" t="n">
-        <v>0.106836538453301</v>
+        <v>4.833236867076669</v>
       </c>
       <c r="Y94" t="b">
         <v>1</v>
@@ -7896,74 +7896,74 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1012.808458202045</v>
+        <v>890.3054586948058</v>
       </c>
       <c r="D95" t="n">
-        <v>9.980022214052862</v>
+        <v>6.576401178182833</v>
       </c>
       <c r="E95" t="n">
-        <v>201.8109792519376</v>
+        <v>199.2832620237663</v>
       </c>
       <c r="F95" t="n">
-        <v>0.5065088272094727</v>
+        <v>0.7929344177246094</v>
       </c>
       <c r="G95" t="n">
-        <v>0.09160050004720688</v>
+        <v>0.2437549999449402</v>
       </c>
       <c r="H95" t="n">
-        <v>9.540664177620783e-05</v>
+        <v>0.001641420414671302</v>
       </c>
       <c r="I95" t="n">
-        <v>985.8937768399126</v>
+        <v>929.0269673295993</v>
       </c>
       <c r="J95" t="n">
-        <v>201.8109792519376</v>
+        <v>199.2832620237663</v>
       </c>
       <c r="K95" t="n">
-        <v>9.980027350415719</v>
+        <v>9.000641674599413</v>
       </c>
       <c r="L95" t="n">
-        <v>26.91468136213223</v>
+        <v>38.72150863479351</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>5.136362856816845e-06</v>
+        <v>2.42424049641658</v>
       </c>
       <c r="O95" t="b">
         <v>1</v>
       </c>
       <c r="P95" t="n">
-        <v>0.3840338587760925</v>
+        <v>0.9206873774528503</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.4083006998989731</v>
+        <v>1.3052161000669</v>
       </c>
       <c r="R95" t="n">
-        <v>0.0001658270630287006</v>
+        <v>0.0002421541576040909</v>
       </c>
       <c r="S95" t="n">
-        <v>974.4586037303105</v>
+        <v>928.3925216671081</v>
       </c>
       <c r="T95" t="n">
-        <v>201.8189530715663</v>
+        <v>199.1260555224414</v>
       </c>
       <c r="U95" t="n">
-        <v>9.975546426040461</v>
+        <v>9.000641743964731</v>
       </c>
       <c r="V95" t="n">
-        <v>38.34985447173426</v>
+        <v>38.08706297230231</v>
       </c>
       <c r="W95" t="n">
-        <v>0.007973819628688261</v>
+        <v>0.1572065013249073</v>
       </c>
       <c r="X95" t="n">
-        <v>0.004475788012401338</v>
+        <v>2.424240565781899</v>
       </c>
       <c r="Y95" t="b">
         <v>1</v>
@@ -7975,74 +7975,74 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1008.578650305117</v>
+        <v>876.7461009023923</v>
       </c>
       <c r="D96" t="n">
-        <v>11.87591072259123</v>
+        <v>5.53099689378211</v>
       </c>
       <c r="E96" t="n">
-        <v>213.22179032479</v>
+        <v>199.7216912713952</v>
       </c>
       <c r="F96" t="n">
-        <v>0.7313722372055054</v>
+        <v>0.7929344177246094</v>
       </c>
       <c r="G96" t="n">
-        <v>0.1030800000298768</v>
+        <v>0.2202717999462038</v>
       </c>
       <c r="H96" t="n">
-        <v>9.798719838727266e-05</v>
+        <v>0.001641420414671302</v>
       </c>
       <c r="I96" t="n">
-        <v>985.8937777479543</v>
+        <v>929.0269667989231</v>
       </c>
       <c r="J96" t="n">
-        <v>213.22179032479</v>
+        <v>199.7216912713952</v>
       </c>
       <c r="K96" t="n">
-        <v>11.87590853111443</v>
+        <v>9.000641430228491</v>
       </c>
       <c r="L96" t="n">
-        <v>22.68487255716286</v>
+        <v>52.28086589653083</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N96" t="n">
-        <v>2.191476799140446e-06</v>
+        <v>3.469644536446381</v>
       </c>
       <c r="O96" t="b">
         <v>1</v>
       </c>
       <c r="P96" t="n">
-        <v>0.4573763906955719</v>
+        <v>0.9775899052619934</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.3547569999936968</v>
+        <v>1.293022199999541</v>
       </c>
       <c r="R96" t="n">
-        <v>0.000205824282602407</v>
+        <v>0.0003258523647673428</v>
       </c>
       <c r="S96" t="n">
-        <v>966.6731971241541</v>
+        <v>926.9645372481081</v>
       </c>
       <c r="T96" t="n">
-        <v>212.826067720395</v>
+        <v>199.4796145558719</v>
       </c>
       <c r="U96" t="n">
-        <v>11.83692133085207</v>
+        <v>9.000641840458128</v>
       </c>
       <c r="V96" t="n">
-        <v>41.90545318096315</v>
+        <v>50.21843634571576</v>
       </c>
       <c r="W96" t="n">
-        <v>0.3957226043949618</v>
+        <v>0.2420767155232966</v>
       </c>
       <c r="X96" t="n">
-        <v>0.03898939173915927</v>
+        <v>3.469644946676018</v>
       </c>
       <c r="Y96" t="b">
         <v>1</v>
@@ -8058,70 +8058,70 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>897.4090095422152</v>
+        <v>876.9410955441447</v>
       </c>
       <c r="D97" t="n">
-        <v>6.06450522840354</v>
+        <v>5.922903181947195</v>
       </c>
       <c r="E97" t="n">
-        <v>203.6379405791601</v>
+        <v>196.2076374337506</v>
       </c>
       <c r="F97" t="n">
-        <v>0.8587307333946228</v>
+        <v>0.7929344177246094</v>
       </c>
       <c r="G97" t="n">
-        <v>0.1767973999958485</v>
+        <v>0.2276775001082569</v>
       </c>
       <c r="H97" t="n">
-        <v>0.000411912944400683</v>
+        <v>0.001641420414671302</v>
       </c>
       <c r="I97" t="n">
-        <v>940.8700876040477</v>
+        <v>929.0269718751144</v>
       </c>
       <c r="J97" t="n">
-        <v>203.6379405791603</v>
+        <v>196.2076374337506</v>
       </c>
       <c r="K97" t="n">
-        <v>9.000641764910846</v>
+        <v>9.000641548764357</v>
       </c>
       <c r="L97" t="n">
-        <v>43.4610780618325</v>
+        <v>52.08587633096977</v>
       </c>
       <c r="M97" t="n">
-        <v>1.989519660128281e-13</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.936136536507306</v>
+        <v>3.077738366817162</v>
       </c>
       <c r="O97" t="b">
         <v>1</v>
       </c>
       <c r="P97" t="n">
-        <v>0.8571485877037048</v>
+        <v>0.9807537198066711</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.435849699890241</v>
+        <v>1.290139100048691</v>
       </c>
       <c r="R97" t="n">
-        <v>0.0002964336017612368</v>
+        <v>0.0003247980203013867</v>
       </c>
       <c r="S97" t="n">
-        <v>936.2095851385541</v>
+        <v>926.8226288536933</v>
       </c>
       <c r="T97" t="n">
-        <v>203.7658399572401</v>
+        <v>196.1935193988279</v>
       </c>
       <c r="U97" t="n">
-        <v>9.00064178209551</v>
+        <v>9.000641799019057</v>
       </c>
       <c r="V97" t="n">
-        <v>38.80057559633883</v>
+        <v>49.88153330954867</v>
       </c>
       <c r="W97" t="n">
-        <v>0.1278993780800022</v>
+        <v>0.01411803492271702</v>
       </c>
       <c r="X97" t="n">
-        <v>2.93613655369197</v>
+        <v>3.077738617071862</v>
       </c>
       <c r="Y97" t="b">
         <v>1</v>
@@ -8133,74 +8133,74 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>946.0759667984183</v>
+        <v>868.6870572887069</v>
       </c>
       <c r="D98" t="n">
-        <v>9.580764759021758</v>
+        <v>7.650520726875163</v>
       </c>
       <c r="E98" t="n">
-        <v>154.1075734706715</v>
+        <v>189.1050907213636</v>
       </c>
       <c r="F98" t="n">
-        <v>0.8382338285446167</v>
+        <v>0.7926901578903198</v>
       </c>
       <c r="G98" t="n">
-        <v>0.2463492001406848</v>
+        <v>0.3864965999964625</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0002063950814772397</v>
+        <v>0.001641420414671302</v>
       </c>
       <c r="I98" t="n">
-        <v>946.0783613191138</v>
+        <v>929.0269665662559</v>
       </c>
       <c r="J98" t="n">
-        <v>176.1732562473737</v>
+        <v>189.1050907216019</v>
       </c>
       <c r="K98" t="n">
-        <v>9.580762290217397</v>
+        <v>9.000641781085085</v>
       </c>
       <c r="L98" t="n">
-        <v>0.002394520695474966</v>
+        <v>60.33990927754894</v>
       </c>
       <c r="M98" t="n">
-        <v>22.06568277670215</v>
+        <v>2.383728769927984e-10</v>
       </c>
       <c r="N98" t="n">
-        <v>2.468804360944432e-06</v>
+        <v>1.350121054209922</v>
       </c>
       <c r="O98" t="b">
         <v>1</v>
       </c>
       <c r="P98" t="n">
-        <v>0.9876689314842224</v>
+        <v>0.9589347839355469</v>
       </c>
       <c r="Q98" t="n">
-        <v>1.156852800166234</v>
+        <v>1.34539039991796</v>
       </c>
       <c r="R98" t="n">
-        <v>0.002921792678534985</v>
+        <v>0.000398824515286833</v>
       </c>
       <c r="S98" t="n">
-        <v>824.1142362082983</v>
+        <v>926.2784830298667</v>
       </c>
       <c r="T98" t="n">
-        <v>171.6034038574118</v>
+        <v>189.5258600009328</v>
       </c>
       <c r="U98" t="n">
-        <v>9.45856370747596</v>
+        <v>9.000641663846006</v>
       </c>
       <c r="V98" t="n">
-        <v>121.9617305901201</v>
+        <v>57.59142574115981</v>
       </c>
       <c r="W98" t="n">
-        <v>17.49583038674027</v>
+        <v>0.4207692795692708</v>
       </c>
       <c r="X98" t="n">
-        <v>0.1222010515457974</v>
+        <v>1.350120936970843</v>
       </c>
       <c r="Y98" t="b">
         <v>1</v>
@@ -8216,70 +8216,70 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>886.7320035318303</v>
+        <v>836.7768189575141</v>
       </c>
       <c r="D99" t="n">
-        <v>7.067811158178888</v>
+        <v>9.083962981284996</v>
       </c>
       <c r="E99" t="n">
-        <v>201.0474114737337</v>
+        <v>182.2619562966848</v>
       </c>
       <c r="F99" t="n">
-        <v>0.8871044516563416</v>
+        <v>0.6594071388244629</v>
       </c>
       <c r="G99" t="n">
-        <v>0.09269850002601743</v>
+        <v>0.2006121999584138</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0004035303718410432</v>
+        <v>0.002008706564083695</v>
       </c>
       <c r="I99" t="n">
-        <v>940.8700912480335</v>
+        <v>924.8594837494456</v>
       </c>
       <c r="J99" t="n">
-        <v>201.0474114737297</v>
+        <v>182.2619513903775</v>
       </c>
       <c r="K99" t="n">
-        <v>9.000641570597013</v>
+        <v>9.084046458499142</v>
       </c>
       <c r="L99" t="n">
-        <v>54.13808771620324</v>
+        <v>88.08266479193151</v>
       </c>
       <c r="M99" t="n">
-        <v>3.950617610826157e-12</v>
+        <v>4.906307253804698e-06</v>
       </c>
       <c r="N99" t="n">
-        <v>1.932830412418125</v>
+        <v>8.347721414558862e-05</v>
       </c>
       <c r="O99" t="b">
         <v>1</v>
       </c>
       <c r="P99" t="n">
-        <v>0.9332478046417236</v>
+        <v>0.9372252225875854</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.4653634999413043</v>
+        <v>1.214148200117052</v>
       </c>
       <c r="R99" t="n">
-        <v>0.0003679298970382661</v>
+        <v>0.0006909906514920294</v>
       </c>
       <c r="S99" t="n">
-        <v>935.1732513708779</v>
+        <v>923.1722923446655</v>
       </c>
       <c r="T99" t="n">
-        <v>201.422463848071</v>
+        <v>183.4249786551319</v>
       </c>
       <c r="U99" t="n">
-        <v>9.000641856381241</v>
+        <v>9.166767869666685</v>
       </c>
       <c r="V99" t="n">
-        <v>48.44124783904761</v>
+        <v>86.39547338715136</v>
       </c>
       <c r="W99" t="n">
-        <v>0.3750523743373151</v>
+        <v>1.163022358447108</v>
       </c>
       <c r="X99" t="n">
-        <v>1.932830698202354</v>
+        <v>0.08280488838168942</v>
       </c>
       <c r="Y99" t="b">
         <v>1</v>
@@ -8291,74 +8291,74 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Pastry</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1021.424404903021</v>
+        <v>951.0286877103533</v>
       </c>
       <c r="D100" t="n">
-        <v>8.912397178232448</v>
+        <v>9.617151377680672</v>
       </c>
       <c r="E100" t="n">
-        <v>202.0729792371364</v>
+        <v>134.2322609952119</v>
       </c>
       <c r="F100" t="n">
-        <v>0.7210264205932617</v>
+        <v>0.6767300963401794</v>
       </c>
       <c r="G100" t="n">
-        <v>0.09544899989850819</v>
+        <v>0.3618227001279593</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0001128785734181292</v>
+        <v>0.0008354719611816108</v>
       </c>
       <c r="I100" t="n">
-        <v>985.8937766144934</v>
+        <v>951.0286874786497</v>
       </c>
       <c r="J100" t="n">
-        <v>202.0729167839633</v>
+        <v>173.7371840447312</v>
       </c>
       <c r="K100" t="n">
-        <v>9.000641527014711</v>
+        <v>9.616994643252752</v>
       </c>
       <c r="L100" t="n">
-        <v>35.53062828852728</v>
+        <v>2.317036660315352e-07</v>
       </c>
       <c r="M100" t="n">
-        <v>6.245317308639642e-05</v>
+        <v>39.50492304951931</v>
       </c>
       <c r="N100" t="n">
-        <v>0.08824434878226306</v>
+        <v>0.0001567344279198579</v>
       </c>
       <c r="O100" t="b">
         <v>1</v>
       </c>
       <c r="P100" t="n">
-        <v>0.676930844783783</v>
+        <v>0.9998160004615784</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.5007621999830008</v>
+        <v>1.51004229998216</v>
       </c>
       <c r="R100" t="n">
-        <v>0.0002089121553581208</v>
+        <v>0.001625560456886888</v>
       </c>
       <c r="S100" t="n">
-        <v>975.4527167065283</v>
+        <v>812.6109556366022</v>
       </c>
       <c r="T100" t="n">
-        <v>202.1394580752661</v>
+        <v>150.0005524288247</v>
       </c>
       <c r="U100" t="n">
-        <v>9.000641556267123</v>
+        <v>9.510559577515583</v>
       </c>
       <c r="V100" t="n">
-        <v>45.97168819649232</v>
+        <v>138.4177320737512</v>
       </c>
       <c r="W100" t="n">
-        <v>0.06647883812968303</v>
+        <v>15.76829143361283</v>
       </c>
       <c r="X100" t="n">
-        <v>0.08824437803467511</v>
+        <v>0.1065918001650896</v>
       </c>
       <c r="Y100" t="b">
         <v>1</v>
@@ -8370,74 +8370,74 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>938.5879772302337</v>
+        <v>948.9005492473864</v>
       </c>
       <c r="D101" t="n">
-        <v>11.08767417115766</v>
+        <v>3.594222788425768</v>
       </c>
       <c r="E101" t="n">
-        <v>139.5517799663994</v>
+        <v>199.4674332195344</v>
       </c>
       <c r="F101" t="n">
-        <v>0.9841193556785583</v>
+        <v>0.7307463884353638</v>
       </c>
       <c r="G101" t="n">
-        <v>0.1911677001044154</v>
+        <v>0.1444097999483347</v>
       </c>
       <c r="H101" t="n">
-        <v>0.0001908497797558084</v>
+        <v>0.001032155007123947</v>
       </c>
       <c r="I101" t="n">
-        <v>938.5798568635637</v>
+        <v>951.9834703382377</v>
       </c>
       <c r="J101" t="n">
-        <v>176.1735528344169</v>
+        <v>199.4674332195348</v>
       </c>
       <c r="K101" t="n">
-        <v>11.08656396636439</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L101" t="n">
-        <v>0.008120366670027579</v>
+        <v>3.082921090851301</v>
       </c>
       <c r="M101" t="n">
-        <v>36.62177286801753</v>
+        <v>4.263256414560601e-13</v>
       </c>
       <c r="N101" t="n">
-        <v>0.001110204793274505</v>
+        <v>5.406418991436395</v>
       </c>
       <c r="O101" t="b">
         <v>1</v>
       </c>
       <c r="P101" t="n">
-        <v>0.9998763799667358</v>
+        <v>0.9980429410934448</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.9469119999557734</v>
+        <v>0.593808599980548</v>
       </c>
       <c r="R101" t="n">
-        <v>0.005378850270062685</v>
+        <v>4.639910548576154e-05</v>
       </c>
       <c r="S101" t="n">
-        <v>800.0017159111572</v>
+        <v>948.7586446397174</v>
       </c>
       <c r="T101" t="n">
-        <v>164.8636861873947</v>
+        <v>199.4521902447854</v>
       </c>
       <c r="U101" t="n">
-        <v>11.17490305718081</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V101" t="n">
-        <v>138.5862613190765</v>
+        <v>0.1419046076689483</v>
       </c>
       <c r="W101" t="n">
-        <v>25.31190622099527</v>
+        <v>0.01524297474898617</v>
       </c>
       <c r="X101" t="n">
-        <v>0.08722888602315138</v>
+        <v>5.406418991436395</v>
       </c>
       <c r="Y101" t="b">
         <v>1</v>

--- a/export_dati/06_Step6_Simulazione_Massiva_100.xlsx
+++ b/export_dati/06_Step6_Simulazione_Massiva_100.xlsx
@@ -444,12 +444,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Prob_Iniziale_XGBoost</t>
+          <t>Probabilità iniziale_XGBoost</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Tempo_Esecuzione_XGBoost</t>
+          <t>Tempo di esecuzione_XGBoost</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -494,12 +494,12 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Prob_Iniziale_TensorFlow</t>
+          <t>Probabilità iniziale_TensorFlow</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Tempo_Esecuzione_TensorFlow</t>
+          <t>Tempo di esecuzione_TensorFlow</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
@@ -549,74 +549,74 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>863.4770745195466</v>
+        <v>973.3556412331961</v>
       </c>
       <c r="D2" t="n">
-        <v>6.756043538619733</v>
+        <v>3.964780873045247</v>
       </c>
       <c r="E2" t="n">
-        <v>206.036686911038</v>
+        <v>193.4837471974598</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8507716059684753</v>
+        <v>0.8107597231864929</v>
       </c>
       <c r="G2" t="n">
-        <v>0.22394990012981</v>
+        <v>0.03084179999859771</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001641420414671302</v>
+        <v>0.0006575194420292974</v>
       </c>
       <c r="I2" t="n">
-        <v>929.0271678735249</v>
+        <v>973.3555828200604</v>
       </c>
       <c r="J2" t="n">
-        <v>206.0366900492533</v>
+        <v>193.4837913689334</v>
       </c>
       <c r="K2" t="n">
-        <v>9.000682447809323</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L2" t="n">
-        <v>65.55009335397835</v>
+        <v>5.841313577548135e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.138215333819971e-06</v>
+        <v>4.417147357571594e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.24463890918959</v>
+        <v>5.035860906816915</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9937140345573425</v>
+        <v>0.9988646507263184</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.364118500147015</v>
+        <v>0.2011913999995159</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0004225433804094791</v>
+        <v>0.0001356776192551479</v>
       </c>
       <c r="S2" t="n">
-        <v>926.6309168893274</v>
+        <v>974.0311834527407</v>
       </c>
       <c r="T2" t="n">
-        <v>205.1592652049273</v>
+        <v>193.5505771872832</v>
       </c>
       <c r="U2" t="n">
-        <v>9.000641744472151</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V2" t="n">
-        <v>63.15384236978082</v>
+        <v>0.6755422195445817</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8774217061107095</v>
+        <v>0.0668299898233613</v>
       </c>
       <c r="X2" t="n">
-        <v>2.244598205852419</v>
+        <v>5.035860906816915</v>
       </c>
       <c r="Y2" t="b">
         <v>1</v>
@@ -628,74 +628,74 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>964.2254725998696</v>
+        <v>968.297355961957</v>
       </c>
       <c r="D3" t="n">
-        <v>6.100727872701607</v>
+        <v>13.26575829067173</v>
       </c>
       <c r="E3" t="n">
-        <v>191.825603674138</v>
+        <v>206.5498194286949</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7307463884353638</v>
+        <v>0.5131295919418335</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06619199994020164</v>
+        <v>0.1471380000002682</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001032155007123947</v>
+        <v>0.00620739022269845</v>
       </c>
       <c r="I3" t="n">
-        <v>964.2254725998694</v>
+        <v>924.0466802114934</v>
       </c>
       <c r="J3" t="n">
-        <v>191.825603674138</v>
+        <v>207.0847207401031</v>
       </c>
       <c r="K3" t="n">
-        <v>9.000641779862162</v>
+        <v>12.35660419996731</v>
       </c>
       <c r="L3" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>44.25067575046364</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.534901311408106</v>
       </c>
       <c r="N3" t="n">
-        <v>2.899913907160555</v>
+        <v>0.9091540907044227</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8290861845016479</v>
+        <v>0.4018758833408356</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5464034001342952</v>
+        <v>0.7152002999991964</v>
       </c>
       <c r="R3" t="n">
-        <v>7.189831376308575e-05</v>
+        <v>0.001132149482145905</v>
       </c>
       <c r="S3" t="n">
-        <v>961.775985358845</v>
+        <v>838.2430729640236</v>
       </c>
       <c r="T3" t="n">
-        <v>191.9618184856335</v>
+        <v>205.6382135512308</v>
       </c>
       <c r="U3" t="n">
-        <v>9.000641779862162</v>
+        <v>12.46484487716202</v>
       </c>
       <c r="V3" t="n">
-        <v>2.449487241024599</v>
+        <v>130.0542829979335</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1362148114954493</v>
+        <v>0.9116058774641829</v>
       </c>
       <c r="X3" t="n">
-        <v>2.899913907160555</v>
+        <v>0.8009134135097167</v>
       </c>
       <c r="Y3" t="b">
         <v>1</v>
@@ -707,74 +707,74 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>978.6619930305176</v>
+        <v>928.5196805722064</v>
       </c>
       <c r="D4" t="n">
-        <v>5.1903593055076</v>
+        <v>10.69634413899631</v>
       </c>
       <c r="E4" t="n">
-        <v>202.24996343845</v>
+        <v>157.9807758931487</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7307463884353638</v>
+        <v>0.8342413306236267</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06858119997195899</v>
+        <v>0.1829912000011973</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001032155007123947</v>
+        <v>0.0186562966555357</v>
       </c>
       <c r="I4" t="n">
-        <v>978.6619930305287</v>
+        <v>933.9714700163664</v>
       </c>
       <c r="J4" t="n">
-        <v>202.2499634384501</v>
+        <v>163.0059038864132</v>
       </c>
       <c r="K4" t="n">
-        <v>9.000641779862162</v>
+        <v>11.94947639600404</v>
       </c>
       <c r="L4" t="n">
-        <v>1.114131009671837e-11</v>
+        <v>5.451789444159999</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>5.025127993264476</v>
       </c>
       <c r="N4" t="n">
-        <v>3.810282474354562</v>
+        <v>1.253132257007728</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0.977730929851532</v>
+        <v>0.7840512990951538</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4984098998829722</v>
+        <v>0.8656842000000324</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0001072272643796168</v>
+        <v>0.0008841350208967924</v>
       </c>
       <c r="S4" t="n">
-        <v>972.6628751651358</v>
+        <v>835.3667781137857</v>
       </c>
       <c r="T4" t="n">
-        <v>202.153442427246</v>
+        <v>166.1793825708943</v>
       </c>
       <c r="U4" t="n">
-        <v>9.000641779862162</v>
+        <v>10.60719706035339</v>
       </c>
       <c r="V4" t="n">
-        <v>5.999117865381777</v>
+        <v>93.15290245842073</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0965210112039756</v>
+        <v>8.198606677745545</v>
       </c>
       <c r="X4" t="n">
-        <v>3.810282474354562</v>
+        <v>0.08914707864291316</v>
       </c>
       <c r="Y4" t="b">
         <v>1</v>
@@ -786,74 +786,74 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>868.2168670683342</v>
+        <v>948.4574824509183</v>
       </c>
       <c r="D5" t="n">
-        <v>7.82025280204405</v>
+        <v>4.234818532952462</v>
       </c>
       <c r="E5" t="n">
-        <v>203.7268990784758</v>
+        <v>183.7958103216791</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8485633730888367</v>
+        <v>0.7809576988220215</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2313975000288337</v>
+        <v>0.0341496000000916</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001641420414671302</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I5" t="n">
-        <v>929.0269671066073</v>
+        <v>948.457482451174</v>
       </c>
       <c r="J5" t="n">
-        <v>203.7268990784758</v>
+        <v>183.7958103216795</v>
       </c>
       <c r="K5" t="n">
-        <v>9.000641693387658</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L5" t="n">
-        <v>60.81010003827316</v>
+        <v>2.556816980359145e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.979039320256561e-13</v>
       </c>
       <c r="N5" t="n">
-        <v>1.180388891343608</v>
+        <v>4.7658232469097</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9792587757110596</v>
+        <v>0.9951609969139099</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.334037600085139</v>
+        <v>0.2276376000008895</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0003816164389718324</v>
+        <v>0.0001758132420945913</v>
       </c>
       <c r="S5" t="n">
-        <v>926.6965405481463</v>
+        <v>949.6254232223604</v>
       </c>
       <c r="T5" t="n">
-        <v>203.1251695256903</v>
+        <v>183.8764653880124</v>
       </c>
       <c r="U5" t="n">
-        <v>9.000641658335425</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V5" t="n">
-        <v>58.47967347981216</v>
+        <v>1.16794077144209</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6017295527854856</v>
+        <v>0.08065506633334962</v>
       </c>
       <c r="X5" t="n">
-        <v>1.180388856291375</v>
+        <v>4.7658232469097</v>
       </c>
       <c r="Y5" t="b">
         <v>1</v>
@@ -869,70 +869,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>964.1300016773724</v>
+        <v>933.0546011156074</v>
       </c>
       <c r="D6" t="n">
-        <v>8.075113912420624</v>
+        <v>9.253343152804804</v>
       </c>
       <c r="E6" t="n">
-        <v>144.2625365949665</v>
+        <v>155.4723444527573</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6357733607292175</v>
+        <v>0.8342413306236267</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4911432000808418</v>
+        <v>0.2194755000000441</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0008352872682735324</v>
+        <v>0.000942692335229367</v>
       </c>
       <c r="I6" t="n">
-        <v>964.1300016070304</v>
+        <v>944.9210204485925</v>
       </c>
       <c r="J6" t="n">
-        <v>173.7371835006011</v>
+        <v>173.1928082986053</v>
       </c>
       <c r="K6" t="n">
-        <v>9.000641779985012</v>
+        <v>9.258998707891159</v>
       </c>
       <c r="L6" t="n">
-        <v>7.034202553768409e-08</v>
+        <v>11.86641933298506</v>
       </c>
       <c r="M6" t="n">
-        <v>29.47464690563459</v>
+        <v>17.72046384584795</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9255278675643872</v>
+        <v>0.005655555086354624</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9953216910362244</v>
+        <v>0.9279007911682129</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.81189849996008</v>
+        <v>0.7336667999989004</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001653288374654949</v>
+        <v>0.0008793186862021685</v>
       </c>
       <c r="S6" t="n">
-        <v>817.9451949149911</v>
+        <v>837.3071007408083</v>
       </c>
       <c r="T6" t="n">
-        <v>150.6928710290704</v>
+        <v>163.1958458270779</v>
       </c>
       <c r="U6" t="n">
-        <v>9.000639696119682</v>
+        <v>9.175959497258631</v>
       </c>
       <c r="V6" t="n">
-        <v>146.1848067623813</v>
+        <v>95.74750037479907</v>
       </c>
       <c r="W6" t="n">
-        <v>6.430334434103827</v>
+        <v>7.723501374320563</v>
       </c>
       <c r="X6" t="n">
-        <v>0.925525783699058</v>
+        <v>0.0773836555461731</v>
       </c>
       <c r="Y6" t="b">
         <v>1</v>
@@ -944,74 +944,74 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>920.55495001203</v>
+        <v>932.6854511500906</v>
       </c>
       <c r="D7" t="n">
-        <v>10.89601601904119</v>
+        <v>4.822039544966751</v>
       </c>
       <c r="E7" t="n">
-        <v>131.9176933424709</v>
+        <v>203.85972612514</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7186955213546753</v>
+        <v>0.786822497844696</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4821589000057429</v>
+        <v>0.03984810000110883</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000834758160635829</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I7" t="n">
-        <v>920.5577682708407</v>
+        <v>932.6854511501308</v>
       </c>
       <c r="J7" t="n">
-        <v>173.7376566381731</v>
+        <v>203.85972612514</v>
       </c>
       <c r="K7" t="n">
-        <v>10.89610858497909</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002818258810748375</v>
+        <v>4.024514055345207e-11</v>
       </c>
       <c r="M7" t="n">
-        <v>41.81996329570225</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N7" t="n">
-        <v>9.256593790318846e-05</v>
+        <v>4.178602234895411</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9997448325157166</v>
+        <v>0.935815155506134</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.996571299852803</v>
+        <v>0.2396212999992713</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001581317279487848</v>
+        <v>0.0001350106322206557</v>
       </c>
       <c r="S7" t="n">
-        <v>802.0274998333349</v>
+        <v>933.4779040509108</v>
       </c>
       <c r="T7" t="n">
-        <v>150.0005519897055</v>
+        <v>203.9801834042082</v>
       </c>
       <c r="U7" t="n">
-        <v>10.74201411224709</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V7" t="n">
-        <v>118.5274501786951</v>
+        <v>0.7924529008201944</v>
       </c>
       <c r="W7" t="n">
-        <v>18.08285864723459</v>
+        <v>0.1204572790681766</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1540019067941003</v>
+        <v>4.178602234895411</v>
       </c>
       <c r="Y7" t="b">
         <v>1</v>
@@ -1027,70 +1027,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>929.6487242872754</v>
+        <v>942.0783206784146</v>
       </c>
       <c r="D8" t="n">
-        <v>12.66081088891495</v>
+        <v>8.782888865165532</v>
       </c>
       <c r="E8" t="n">
-        <v>162.271849181696</v>
+        <v>110.5384742595066</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6700266003608704</v>
+        <v>0.8342413306236267</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4825254001189023</v>
+        <v>0.240936000000147</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0008368453127332032</v>
+        <v>0.01939161494374275</v>
       </c>
       <c r="I8" t="n">
-        <v>929.6487255194605</v>
+        <v>929.47063563396</v>
       </c>
       <c r="J8" t="n">
-        <v>173.7371843695789</v>
+        <v>163.0203411533257</v>
       </c>
       <c r="K8" t="n">
-        <v>12.66081088366578</v>
+        <v>10.02671661219607</v>
       </c>
       <c r="L8" t="n">
-        <v>1.232185127264529e-06</v>
+        <v>12.60768504445457</v>
       </c>
       <c r="M8" t="n">
-        <v>11.46533518788294</v>
+        <v>52.48186689381903</v>
       </c>
       <c r="N8" t="n">
-        <v>5.249162882137171e-09</v>
+        <v>1.243827747030538</v>
       </c>
       <c r="O8" t="b">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2854719460010529</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.038330900017172</v>
+        <v>0.5688343000001623</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001569393207319081</v>
+        <v>0.001183155691251159</v>
       </c>
       <c r="S8" t="n">
-        <v>826.4950908113385</v>
+        <v>806.0673663088908</v>
       </c>
       <c r="T8" t="n">
-        <v>169.5830814489993</v>
+        <v>150.0005526757936</v>
       </c>
       <c r="U8" t="n">
-        <v>12.43293157320231</v>
+        <v>9.000447461072532</v>
       </c>
       <c r="V8" t="n">
-        <v>103.1536334759369</v>
+        <v>136.0109543695238</v>
       </c>
       <c r="W8" t="n">
-        <v>7.311232267303296</v>
+        <v>39.46207841628696</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2278793157126344</v>
+        <v>0.2175585959070006</v>
       </c>
       <c r="Y8" t="b">
         <v>1</v>
@@ -1102,74 +1102,74 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>961.8165393036306</v>
+        <v>947.3537016694139</v>
       </c>
       <c r="D9" t="n">
-        <v>10.17705382690166</v>
+        <v>5.640381666124846</v>
       </c>
       <c r="E9" t="n">
-        <v>146.7127562677171</v>
+        <v>187.6566987571223</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6767300963401794</v>
+        <v>0.8132951259613037</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4964979998767376</v>
+        <v>0.03370399999948859</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0008354719611816108</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I9" t="n">
-        <v>961.8195199358701</v>
+        <v>947.353701669413</v>
       </c>
       <c r="J9" t="n">
-        <v>173.737503088327</v>
+        <v>187.6566987571223</v>
       </c>
       <c r="K9" t="n">
-        <v>10.1771914922531</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002980632239427905</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="M9" t="n">
-        <v>27.02474682060992</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0001376653514491011</v>
+        <v>3.360260113737317</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9950148463249207</v>
+        <v>0.8469259142875671</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.22749359998852</v>
+        <v>0.1958651000004465</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001672614947892725</v>
+        <v>0.0001682467700447887</v>
       </c>
       <c r="S9" t="n">
-        <v>816.7245196361405</v>
+        <v>948.4655697655137</v>
       </c>
       <c r="T9" t="n">
-        <v>153.8091321446313</v>
+        <v>187.7375329164716</v>
       </c>
       <c r="U9" t="n">
-        <v>10.04717325624213</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V9" t="n">
-        <v>145.0920196674901</v>
+        <v>1.111868096099784</v>
       </c>
       <c r="W9" t="n">
-        <v>7.096375876914152</v>
+        <v>0.080834159349223</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1298805706595285</v>
+        <v>3.360260113737317</v>
       </c>
       <c r="Y9" t="b">
         <v>1</v>
@@ -1185,70 +1185,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>874.0869389934916</v>
+        <v>872.5361624196954</v>
       </c>
       <c r="D10" t="n">
-        <v>8.903517098889219</v>
+        <v>7.40157731907105</v>
       </c>
       <c r="E10" t="n">
-        <v>212.1431163763257</v>
+        <v>188.23047414045</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7533094882965088</v>
+        <v>0.6951717734336853</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3362185000441968</v>
+        <v>0.1259501000004093</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001640764763578773</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I10" t="n">
-        <v>929.0269669700332</v>
+        <v>924.4806758069504</v>
       </c>
       <c r="J10" t="n">
-        <v>212.1431803900632</v>
+        <v>188.23047414045</v>
       </c>
       <c r="K10" t="n">
-        <v>9.000641667451532</v>
+        <v>9.000641579120586</v>
       </c>
       <c r="L10" t="n">
-        <v>54.94002797654161</v>
+        <v>51.94451338725503</v>
       </c>
       <c r="M10" t="n">
-        <v>6.401373752851214e-05</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N10" t="n">
-        <v>0.09712456856231277</v>
+        <v>1.599064260049536</v>
       </c>
       <c r="O10" t="b">
         <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9000845551490784</v>
+        <v>0.9762711524963379</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9040955000091344</v>
+        <v>0.3480361000001722</v>
       </c>
       <c r="R10" t="n">
-        <v>0.00038534463965334</v>
+        <v>0.0005839144578203559</v>
       </c>
       <c r="S10" t="n">
-        <v>928.9880637667362</v>
+        <v>936.2163907322051</v>
       </c>
       <c r="T10" t="n">
-        <v>210.68593686549</v>
+        <v>188.6839099378621</v>
       </c>
       <c r="U10" t="n">
-        <v>9.000641506884289</v>
+        <v>9.000641731833941</v>
       </c>
       <c r="V10" t="n">
-        <v>54.90112477324465</v>
+        <v>63.68022831250971</v>
       </c>
       <c r="W10" t="n">
-        <v>1.457179510835687</v>
+        <v>0.4534357974121122</v>
       </c>
       <c r="X10" t="n">
-        <v>0.09712440799506972</v>
+        <v>1.599064412762891</v>
       </c>
       <c r="Y10" t="b">
         <v>1</v>
@@ -1260,74 +1260,74 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>966.3702073861947</v>
+        <v>920.2162385330984</v>
       </c>
       <c r="D11" t="n">
-        <v>11.89632430453699</v>
+        <v>2.853205011335399</v>
       </c>
       <c r="E11" t="n">
-        <v>129.2772934821159</v>
+        <v>205.8182749431537</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5425188541412354</v>
+        <v>0.8053354620933533</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6344544000457972</v>
+        <v>0.07242620000033639</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01433388702571392</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I11" t="n">
-        <v>964.8039689291198</v>
+        <v>924.4808457871983</v>
       </c>
       <c r="J11" t="n">
-        <v>167.3097805342292</v>
+        <v>205.8182749431532</v>
       </c>
       <c r="K11" t="n">
-        <v>11.8963242893919</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L11" t="n">
-        <v>1.56623845707486</v>
+        <v>4.264607254099928</v>
       </c>
       <c r="M11" t="n">
-        <v>38.0324870521134</v>
+        <v>5.684341886080801e-13</v>
       </c>
       <c r="N11" t="n">
-        <v>1.514508873867726e-08</v>
+        <v>6.147436768526763</v>
       </c>
       <c r="O11" t="b">
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9994769692420959</v>
+        <v>0.9837148785591125</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.510406700195745</v>
+        <v>0.1928910999995423</v>
       </c>
       <c r="R11" t="n">
-        <v>0.002670569578185678</v>
+        <v>0.0001402409543516114</v>
       </c>
       <c r="S11" t="n">
-        <v>800.0000420883573</v>
+        <v>920.9436515999181</v>
       </c>
       <c r="T11" t="n">
-        <v>150.0005529423611</v>
+        <v>205.9480643316476</v>
       </c>
       <c r="U11" t="n">
-        <v>11.53846191938536</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V11" t="n">
-        <v>166.3701652978374</v>
+        <v>0.7274130668197358</v>
       </c>
       <c r="W11" t="n">
-        <v>20.72325946024526</v>
+        <v>0.1297893884938333</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3578623851516269</v>
+        <v>6.147436768526763</v>
       </c>
       <c r="Y11" t="b">
         <v>1</v>
@@ -1339,74 +1339,74 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>956.5626946838948</v>
+        <v>842.1697898062494</v>
       </c>
       <c r="D12" t="n">
-        <v>9.307627823649433</v>
+        <v>8.285643848494162</v>
       </c>
       <c r="E12" t="n">
-        <v>120.9567867658997</v>
+        <v>195.9351771870371</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6767300963401794</v>
+        <v>0.7797855734825134</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3193496000021696</v>
+        <v>0.1026173999998719</v>
       </c>
       <c r="H12" t="n">
-        <v>0.02174675464630127</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I12" t="n">
-        <v>956.5626926228375</v>
+        <v>924.4807996458985</v>
       </c>
       <c r="J12" t="n">
-        <v>167.3097816079831</v>
+        <v>195.9351771870371</v>
       </c>
       <c r="K12" t="n">
-        <v>9.307627821158924</v>
+        <v>9.000641609028916</v>
       </c>
       <c r="L12" t="n">
-        <v>2.061057330138283e-06</v>
+        <v>82.31100983964916</v>
       </c>
       <c r="M12" t="n">
-        <v>46.35299484208342</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.490509132258012e-09</v>
+        <v>0.7149977605347537</v>
       </c>
       <c r="O12" t="b">
         <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9999653100967407</v>
+        <v>0.9096106886863708</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8663240000605583</v>
+        <v>0.5481517000007443</v>
       </c>
       <c r="R12" t="n">
-        <v>0.001635634689591825</v>
+        <v>0.0008831974118947983</v>
       </c>
       <c r="S12" t="n">
-        <v>814.8955627568181</v>
+        <v>932.0890579696306</v>
       </c>
       <c r="T12" t="n">
-        <v>150.0005525287171</v>
+        <v>196.7342501696838</v>
       </c>
       <c r="U12" t="n">
-        <v>9.210541250526582</v>
+        <v>9.000641805801305</v>
       </c>
       <c r="V12" t="n">
-        <v>141.6671319270768</v>
+        <v>89.91926816338128</v>
       </c>
       <c r="W12" t="n">
-        <v>29.04376576281744</v>
+        <v>0.7990729826467202</v>
       </c>
       <c r="X12" t="n">
-        <v>0.09708657312285141</v>
+        <v>0.7149979573071423</v>
       </c>
       <c r="Y12" t="b">
         <v>1</v>
@@ -1418,74 +1418,74 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>957.9007298454952</v>
+        <v>955.7354822476517</v>
       </c>
       <c r="D13" t="n">
-        <v>4.104445614920706</v>
+        <v>13.812537298508</v>
       </c>
       <c r="E13" t="n">
-        <v>178.1293633295699</v>
+        <v>216.0857256505867</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7250093221664429</v>
+        <v>0.527676522731781</v>
       </c>
       <c r="G13" t="n">
-        <v>0.07744869985617697</v>
+        <v>0.1596759999993083</v>
       </c>
       <c r="H13" t="n">
-        <v>0.001032155007123947</v>
+        <v>0.003476700745522976</v>
       </c>
       <c r="I13" t="n">
-        <v>957.9007298454983</v>
+        <v>891.8547026711234</v>
       </c>
       <c r="J13" t="n">
-        <v>178.1293633295694</v>
+        <v>216.085725650587</v>
       </c>
       <c r="K13" t="n">
-        <v>9.000641779862162</v>
+        <v>12.31824070222429</v>
       </c>
       <c r="L13" t="n">
-        <v>3.069544618483633e-12</v>
+        <v>63.88077957652831</v>
       </c>
       <c r="M13" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>2.842170943040401e-13</v>
       </c>
       <c r="N13" t="n">
-        <v>4.896196164941456</v>
+        <v>1.494296596283716</v>
       </c>
       <c r="O13" t="b">
         <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9952362179756165</v>
+        <v>0.9450944066047668</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2965941000729799</v>
+        <v>0.866138299999875</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0002002094261115417</v>
+        <v>0.001127222087234259</v>
       </c>
       <c r="S13" t="n">
-        <v>954.1891138489104</v>
+        <v>821.8058372243822</v>
       </c>
       <c r="T13" t="n">
-        <v>178.9364447615191</v>
+        <v>215.1732523174193</v>
       </c>
       <c r="U13" t="n">
-        <v>9.000641779862162</v>
+        <v>12.93542711549076</v>
       </c>
       <c r="V13" t="n">
-        <v>3.711615996584783</v>
+        <v>133.9296450232695</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8070814319492285</v>
+        <v>0.9124733331674122</v>
       </c>
       <c r="X13" t="n">
-        <v>4.896196164941456</v>
+        <v>0.8771101830172441</v>
       </c>
       <c r="Y13" t="b">
         <v>1</v>
@@ -1501,70 +1501,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>925.0400309044297</v>
+        <v>968.5770249210045</v>
       </c>
       <c r="D14" t="n">
-        <v>10.06704279456354</v>
+        <v>10.38388828828963</v>
       </c>
       <c r="E14" t="n">
-        <v>125.0040432603061</v>
+        <v>149.1615787620191</v>
       </c>
       <c r="F14" t="n">
-        <v>0.720072865486145</v>
+        <v>0.8338657021522522</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1753734999801964</v>
+        <v>0.2432939000009355</v>
       </c>
       <c r="H14" t="n">
-        <v>0.02472542598843575</v>
+        <v>0.01935457438230515</v>
       </c>
       <c r="I14" t="n">
-        <v>925.0400309045317</v>
+        <v>939.7160895250917</v>
       </c>
       <c r="J14" t="n">
-        <v>167.3098316411032</v>
+        <v>163.532100866892</v>
       </c>
       <c r="K14" t="n">
-        <v>10.06716860078033</v>
+        <v>11.83244120368154</v>
       </c>
       <c r="L14" t="n">
-        <v>1.019770934362896e-10</v>
+        <v>28.86093539591286</v>
       </c>
       <c r="M14" t="n">
-        <v>42.30578838079711</v>
+        <v>14.37052210487289</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0001258062167845964</v>
+        <v>1.448552915391909</v>
       </c>
       <c r="O14" t="b">
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9999381303787231</v>
+        <v>0.984896183013916</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8865934999194</v>
+        <v>1.020322599999417</v>
       </c>
       <c r="R14" t="n">
-        <v>0.001486682798713446</v>
+        <v>0.001203607534989715</v>
       </c>
       <c r="S14" t="n">
-        <v>808.1776303749591</v>
+        <v>816.8633303455302</v>
       </c>
       <c r="T14" t="n">
-        <v>150.000552399261</v>
+        <v>158.0496142034982</v>
       </c>
       <c r="U14" t="n">
-        <v>9.955716204328713</v>
+        <v>10.26640937474792</v>
       </c>
       <c r="V14" t="n">
-        <v>116.8624005294706</v>
+        <v>151.7136945754743</v>
       </c>
       <c r="W14" t="n">
-        <v>24.99650913895488</v>
+        <v>8.888035441479019</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1113265902348282</v>
+        <v>0.1174789135417118</v>
       </c>
       <c r="Y14" t="b">
         <v>1</v>
@@ -1580,70 +1580,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>848.8299954072052</v>
+        <v>870.1725279466541</v>
       </c>
       <c r="D15" t="n">
-        <v>7.740394859456654</v>
+        <v>8.444930492758932</v>
       </c>
       <c r="E15" t="n">
-        <v>216.9791780068796</v>
+        <v>207.6879680120539</v>
       </c>
       <c r="F15" t="n">
-        <v>0.847973108291626</v>
+        <v>0.8276062607765198</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9275811999104917</v>
+        <v>0.1272275999999692</v>
       </c>
       <c r="H15" t="n">
-        <v>0.001640737871639431</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I15" t="n">
-        <v>929.0294788076374</v>
+        <v>924.4813581768642</v>
       </c>
       <c r="J15" t="n">
-        <v>216.9792101479127</v>
+        <v>207.6879680120543</v>
       </c>
       <c r="K15" t="n">
-        <v>9.000641777326312</v>
+        <v>9.000641723741971</v>
       </c>
       <c r="L15" t="n">
-        <v>80.1994834004322</v>
+        <v>54.30883023021011</v>
       </c>
       <c r="M15" t="n">
-        <v>3.214103307414007e-05</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="N15" t="n">
-        <v>1.260246917869658</v>
+        <v>0.5557112309830394</v>
       </c>
       <c r="O15" t="b">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9912964105606079</v>
+        <v>0.8443998694419861</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.488595700124279</v>
+        <v>0.6010490999997273</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0006200964562594891</v>
+        <v>0.0005889525054953992</v>
       </c>
       <c r="S15" t="n">
-        <v>928.1261874460239</v>
+        <v>933.9087944432212</v>
       </c>
       <c r="T15" t="n">
-        <v>214.1363174280627</v>
+        <v>207.877314114899</v>
       </c>
       <c r="U15" t="n">
-        <v>9.00064061091858</v>
+        <v>9.000641873708618</v>
       </c>
       <c r="V15" t="n">
-        <v>79.29619203881873</v>
+        <v>63.73626649656705</v>
       </c>
       <c r="W15" t="n">
-        <v>2.842860578816897</v>
+        <v>0.1893461028451213</v>
       </c>
       <c r="X15" t="n">
-        <v>1.260245751461927</v>
+        <v>0.5557113809496865</v>
       </c>
       <c r="Y15" t="b">
         <v>1</v>
@@ -1655,74 +1655,74 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>850.8279531763469</v>
+        <v>956.6903877099024</v>
       </c>
       <c r="D16" t="n">
-        <v>6.285781981063937</v>
+        <v>5.802309338563953</v>
       </c>
       <c r="E16" t="n">
-        <v>189.182542092788</v>
+        <v>209.2168315742735</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7904574275016785</v>
+        <v>0.8140485286712646</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2245128999929875</v>
+        <v>0.05658439999933762</v>
       </c>
       <c r="H16" t="n">
-        <v>0.002008212730288506</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I16" t="n">
-        <v>924.8608245568929</v>
+        <v>956.6903877099055</v>
       </c>
       <c r="J16" t="n">
-        <v>189.1825415942864</v>
+        <v>209.2168315742733</v>
       </c>
       <c r="K16" t="n">
-        <v>9.000605602113362</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L16" t="n">
-        <v>74.032871380546</v>
+        <v>3.069544618483633e-12</v>
       </c>
       <c r="M16" t="n">
-        <v>4.985016062164505e-07</v>
+        <v>1.70530256582424e-13</v>
       </c>
       <c r="N16" t="n">
-        <v>2.714823621049425</v>
+        <v>3.198332441298209</v>
       </c>
       <c r="O16" t="b">
         <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9950404763221741</v>
+        <v>0.7027662992477417</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.488969000056386</v>
+        <v>0.2314889999997831</v>
       </c>
       <c r="R16" t="n">
-        <v>0.000529961776919663</v>
+        <v>9.874146780930459e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>924.7858239123844</v>
+        <v>957.801214310937</v>
       </c>
       <c r="T16" t="n">
-        <v>189.6656384544455</v>
+        <v>209.3596744846091</v>
       </c>
       <c r="U16" t="n">
-        <v>9.000641858741639</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V16" t="n">
-        <v>73.95787073603753</v>
+        <v>1.110826601034546</v>
       </c>
       <c r="W16" t="n">
-        <v>0.4830963616574877</v>
+        <v>0.1428429103355597</v>
       </c>
       <c r="X16" t="n">
-        <v>2.714859877677703</v>
+        <v>3.198332441298209</v>
       </c>
       <c r="Y16" t="b">
         <v>1</v>
@@ -1734,74 +1734,74 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>864.8903470003072</v>
+        <v>934.5775048631689</v>
       </c>
       <c r="D17" t="n">
-        <v>7.455783838301119</v>
+        <v>7.914524483267093</v>
       </c>
       <c r="E17" t="n">
-        <v>195.8393717611224</v>
+        <v>117.89617775543</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8514803051948547</v>
+        <v>0.6712142825126648</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2699425001628697</v>
+        <v>0.3859142000001157</v>
       </c>
       <c r="H17" t="n">
-        <v>0.002008181530982256</v>
+        <v>0.001524175517261028</v>
       </c>
       <c r="I17" t="n">
-        <v>924.8602892878602</v>
+        <v>910.8501730697529</v>
       </c>
       <c r="J17" t="n">
-        <v>195.8394232750141</v>
+        <v>173.1915857150382</v>
       </c>
       <c r="K17" t="n">
-        <v>9.000641720596469</v>
+        <v>10.24288475891473</v>
       </c>
       <c r="L17" t="n">
-        <v>59.96994228755295</v>
+        <v>23.72733179341594</v>
       </c>
       <c r="M17" t="n">
-        <v>5.151389169100185e-05</v>
+        <v>55.29540795960823</v>
       </c>
       <c r="N17" t="n">
-        <v>1.544857882295351</v>
+        <v>2.328360275647639</v>
       </c>
       <c r="O17" t="b">
         <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9830912947654724</v>
+        <v>0.9999998807907104</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.499527600128204</v>
+        <v>0.6403121000003011</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0003996603772975504</v>
+        <v>0.001139359083026648</v>
       </c>
       <c r="S17" t="n">
-        <v>925.8026640705901</v>
+        <v>805.7752470501516</v>
       </c>
       <c r="T17" t="n">
-        <v>195.8309883935017</v>
+        <v>150.0005526461474</v>
       </c>
       <c r="U17" t="n">
-        <v>9.000641779916164</v>
+        <v>9.000542663875235</v>
       </c>
       <c r="V17" t="n">
-        <v>60.91231707028294</v>
+        <v>128.8022578130173</v>
       </c>
       <c r="W17" t="n">
-        <v>0.008383367620695026</v>
+        <v>32.10437489071744</v>
       </c>
       <c r="X17" t="n">
-        <v>1.544857941615045</v>
+        <v>1.086018180608142</v>
       </c>
       <c r="Y17" t="b">
         <v>1</v>
@@ -1813,74 +1813,74 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>853.8047045219632</v>
+        <v>936.6538078905809</v>
       </c>
       <c r="D18" t="n">
-        <v>7.040943394308916</v>
+        <v>8.503736900599202</v>
       </c>
       <c r="E18" t="n">
-        <v>205.3484099415133</v>
+        <v>132.2452147401917</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8507716059684753</v>
+        <v>0.8141006827354431</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2301232998725027</v>
+        <v>0.318269400000645</v>
       </c>
       <c r="H18" t="n">
-        <v>0.001641420414671302</v>
+        <v>0.001156819984316826</v>
       </c>
       <c r="I18" t="n">
-        <v>929.0271662019918</v>
+        <v>949.9796645045041</v>
       </c>
       <c r="J18" t="n">
-        <v>205.3484099407056</v>
+        <v>173.1939764038761</v>
       </c>
       <c r="K18" t="n">
-        <v>9.000641674809065</v>
+        <v>9.122331467672074</v>
       </c>
       <c r="L18" t="n">
-        <v>75.22246168002857</v>
+        <v>13.32585661392318</v>
       </c>
       <c r="M18" t="n">
-        <v>8.077449820120819e-10</v>
+        <v>40.94876166368439</v>
       </c>
       <c r="N18" t="n">
-        <v>1.95969828050015</v>
+        <v>0.6185945670728721</v>
       </c>
       <c r="O18" t="b">
         <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>0.994712233543396</v>
+        <v>0.99998939037323</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.380338499788195</v>
+        <v>0.9917552999995678</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0004857330932281911</v>
+        <v>0.0011518340324983</v>
       </c>
       <c r="S18" t="n">
-        <v>925.7808976450618</v>
+        <v>805.8606740553065</v>
       </c>
       <c r="T18" t="n">
-        <v>204.4490907202137</v>
+        <v>150.0005526374236</v>
       </c>
       <c r="U18" t="n">
-        <v>9.000641730153157</v>
+        <v>9.00037640753019</v>
       </c>
       <c r="V18" t="n">
-        <v>71.9761931230986</v>
+        <v>130.7931338352744</v>
       </c>
       <c r="W18" t="n">
-        <v>0.899319221299578</v>
+        <v>17.7553378972319</v>
       </c>
       <c r="X18" t="n">
-        <v>1.959698335844242</v>
+        <v>0.4966395069309879</v>
       </c>
       <c r="Y18" t="b">
         <v>1</v>
@@ -1892,74 +1892,74 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>949.638777990016</v>
+        <v>939.8622530026555</v>
       </c>
       <c r="D19" t="n">
-        <v>6.351698191204475</v>
+        <v>8.270832149839636</v>
       </c>
       <c r="E19" t="n">
-        <v>183.3875941831551</v>
+        <v>118.198925961433</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7250093221664429</v>
+        <v>0.6280300617218018</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1004166000057012</v>
+        <v>0.1854825999998866</v>
       </c>
       <c r="H19" t="n">
-        <v>0.001032155007123947</v>
+        <v>0.01939161494374275</v>
       </c>
       <c r="I19" t="n">
-        <v>951.9834356291486</v>
+        <v>929.4714824948228</v>
       </c>
       <c r="J19" t="n">
-        <v>183.3875941831551</v>
+        <v>163.0132626987895</v>
       </c>
       <c r="K19" t="n">
-        <v>9.000641779862162</v>
+        <v>10.02689024954314</v>
       </c>
       <c r="L19" t="n">
-        <v>2.344657639132606</v>
+        <v>10.39077050783271</v>
       </c>
       <c r="M19" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>44.81433673735646</v>
       </c>
       <c r="N19" t="n">
-        <v>2.648943588657687</v>
+        <v>1.756058099703504</v>
       </c>
       <c r="O19" t="b">
         <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5054143071174622</v>
+        <v>0.9999998807907104</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.6173115000128746</v>
+        <v>0.5587272000011581</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0001054428284987807</v>
+        <v>0.001170899602584541</v>
       </c>
       <c r="S19" t="n">
-        <v>948.7269515704596</v>
+        <v>805.9853378010438</v>
       </c>
       <c r="T19" t="n">
-        <v>183.7607544473893</v>
+        <v>150.0005526554787</v>
       </c>
       <c r="U19" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000651050526621</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9118264195564052</v>
+        <v>133.8769152016117</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3731602642342295</v>
+        <v>31.80162669404572</v>
       </c>
       <c r="X19" t="n">
-        <v>2.648943588657687</v>
+        <v>0.7298189006869844</v>
       </c>
       <c r="Y19" t="b">
         <v>1</v>
@@ -1971,74 +1971,74 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>924.0020384589923</v>
+        <v>868.926638772415</v>
       </c>
       <c r="D20" t="n">
-        <v>10.02226642460204</v>
+        <v>8.696047358868302</v>
       </c>
       <c r="E20" t="n">
-        <v>142.297378885927</v>
+        <v>208.0304100682312</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7188459038734436</v>
+        <v>0.8221606016159058</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4127406000625342</v>
+        <v>0.1029772000001685</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0008347913390025496</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I20" t="n">
-        <v>923.9776698975705</v>
+        <v>924.4806708797444</v>
       </c>
       <c r="J20" t="n">
-        <v>173.7390696194847</v>
+        <v>208.0304100682312</v>
       </c>
       <c r="K20" t="n">
-        <v>10.02200304591045</v>
+        <v>9.000641674887545</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02436856142173838</v>
+        <v>55.55403210732936</v>
       </c>
       <c r="M20" t="n">
-        <v>31.44169073355769</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0002633786915922087</v>
+        <v>0.3045943160192426</v>
       </c>
       <c r="O20" t="b">
         <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9985077977180481</v>
+        <v>0.7836688160896301</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.874344800133258</v>
+        <v>0.4802214000010281</v>
       </c>
       <c r="R20" t="n">
-        <v>0.001473016222007573</v>
+        <v>0.0006003818125464022</v>
       </c>
       <c r="S20" t="n">
-        <v>808.414634159449</v>
+        <v>933.7561770506289</v>
       </c>
       <c r="T20" t="n">
-        <v>150.0005522964133</v>
+        <v>208.2252571417574</v>
       </c>
       <c r="U20" t="n">
-        <v>9.913870488173094</v>
+        <v>9.000641910067984</v>
       </c>
       <c r="V20" t="n">
-        <v>115.5874042995433</v>
+        <v>64.82953827821393</v>
       </c>
       <c r="W20" t="n">
-        <v>7.703173410486272</v>
+        <v>0.1948470735261481</v>
       </c>
       <c r="X20" t="n">
-        <v>0.1083959364289466</v>
+        <v>0.3045945511996813</v>
       </c>
       <c r="Y20" t="b">
         <v>1</v>
@@ -2050,74 +2050,74 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>883.9955445799355</v>
+        <v>964.2438355600153</v>
       </c>
       <c r="D21" t="n">
-        <v>6.575576983758507</v>
+        <v>11.28084661540241</v>
       </c>
       <c r="E21" t="n">
-        <v>210.0947048817987</v>
+        <v>162.6883530273284</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7930038571357727</v>
+        <v>0.8342413306236267</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9353830001782626</v>
+        <v>0.1876532999995106</v>
       </c>
       <c r="H21" t="n">
-        <v>0.001640764763578773</v>
+        <v>0.01565238833427429</v>
       </c>
       <c r="I21" t="n">
-        <v>929.0269662343837</v>
+        <v>939.7149737679706</v>
       </c>
       <c r="J21" t="n">
-        <v>210.0945493926517</v>
+        <v>166.3423312252067</v>
       </c>
       <c r="K21" t="n">
-        <v>9.000641741080626</v>
+        <v>12.31845272855687</v>
       </c>
       <c r="L21" t="n">
-        <v>45.0314216544482</v>
+        <v>24.52886179204472</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0001554891469197628</v>
+        <v>3.653978197878217</v>
       </c>
       <c r="N21" t="n">
-        <v>2.425064757322119</v>
+        <v>1.03760611315446</v>
       </c>
       <c r="O21" t="b">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9643447995185852</v>
+        <v>0.2471821308135986</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.54735629982315</v>
+        <v>1.000615999999354</v>
       </c>
       <c r="R21" t="n">
-        <v>0.0003112194535788149</v>
+        <v>0.000967298517934978</v>
       </c>
       <c r="S21" t="n">
-        <v>929.426661036791</v>
+        <v>846.9686650678743</v>
       </c>
       <c r="T21" t="n">
-        <v>209.0522040162957</v>
+        <v>171.4171044825447</v>
       </c>
       <c r="U21" t="n">
-        <v>9.00064148646385</v>
+        <v>11.1130684919404</v>
       </c>
       <c r="V21" t="n">
-        <v>45.43111645685542</v>
+        <v>117.275170492141</v>
       </c>
       <c r="W21" t="n">
-        <v>1.042500865502916</v>
+        <v>8.728751455216269</v>
       </c>
       <c r="X21" t="n">
-        <v>2.425064502705343</v>
+        <v>0.1677781234620088</v>
       </c>
       <c r="Y21" t="b">
         <v>1</v>
@@ -2129,74 +2129,74 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>847.1119345863104</v>
+        <v>915.1064995175359</v>
       </c>
       <c r="D22" t="n">
-        <v>7.358725573590418</v>
+        <v>5.136058296964662</v>
       </c>
       <c r="E22" t="n">
-        <v>209.8626167603591</v>
+        <v>212.8896076452998</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8492217063903809</v>
+        <v>0.7656013369560242</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3054285000544041</v>
+        <v>0.1357451999992918</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00200738525018096</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I22" t="n">
-        <v>924.8594728554535</v>
+        <v>924.4806678907321</v>
       </c>
       <c r="J22" t="n">
-        <v>209.8626167603493</v>
+        <v>212.8896076453</v>
       </c>
       <c r="K22" t="n">
-        <v>9.000641739788913</v>
+        <v>9.000641564512286</v>
       </c>
       <c r="L22" t="n">
-        <v>77.74753826914309</v>
+        <v>9.374168373196198</v>
       </c>
       <c r="M22" t="n">
-        <v>9.748646334628575e-12</v>
+        <v>1.70530256582424e-13</v>
       </c>
       <c r="N22" t="n">
-        <v>1.641916166198495</v>
+        <v>3.864583267547624</v>
       </c>
       <c r="O22" t="b">
         <v>1</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9938475489616394</v>
+        <v>0.5002244710922241</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.583922100020573</v>
+        <v>0.2098779999996623</v>
       </c>
       <c r="R22" t="n">
-        <v>0.0005598661373369396</v>
+        <v>0.0001237623946508393</v>
       </c>
       <c r="S22" t="n">
-        <v>926.1093666579063</v>
+        <v>915.6495976114203</v>
       </c>
       <c r="T22" t="n">
-        <v>208.2787262051803</v>
+        <v>213.0142939911524</v>
       </c>
       <c r="U22" t="n">
-        <v>9.000641597593463</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V22" t="n">
-        <v>78.99743207159588</v>
+        <v>0.5430980938843959</v>
       </c>
       <c r="W22" t="n">
-        <v>1.583890555178783</v>
+        <v>0.124686345852524</v>
       </c>
       <c r="X22" t="n">
-        <v>1.641916024003045</v>
+        <v>3.8645834828975</v>
       </c>
       <c r="Y22" t="b">
         <v>1</v>
@@ -2208,74 +2208,74 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>953.0379410721091</v>
+        <v>918.6608125766529</v>
       </c>
       <c r="D23" t="n">
-        <v>12.0888957163943</v>
+        <v>13.0057444259856</v>
       </c>
       <c r="E23" t="n">
-        <v>165.4040158925322</v>
+        <v>189.6928737188748</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5629615783691406</v>
+        <v>0.6327797174453735</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3659905001986772</v>
+        <v>0.1335053000002517</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0008342087967321277</v>
+        <v>0.001114324550144374</v>
       </c>
       <c r="I23" t="n">
-        <v>953.0379694204754</v>
+        <v>891.8760989702231</v>
       </c>
       <c r="J23" t="n">
-        <v>173.7371836578429</v>
+        <v>189.6928737188764</v>
       </c>
       <c r="K23" t="n">
-        <v>12.08889289016804</v>
+        <v>11.69500114517549</v>
       </c>
       <c r="L23" t="n">
-        <v>2.834836629972415e-05</v>
+        <v>26.78471360642982</v>
       </c>
       <c r="M23" t="n">
-        <v>8.333167765310634</v>
+        <v>1.591615728102624e-12</v>
       </c>
       <c r="N23" t="n">
-        <v>2.826226266350318e-06</v>
+        <v>1.310743280810108</v>
       </c>
       <c r="O23" t="b">
         <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>0.08879907429218292</v>
+        <v>0.1018594428896904</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.371637500124052</v>
+        <v>1.094349099999818</v>
       </c>
       <c r="R23" t="n">
-        <v>0.001580131705850363</v>
+        <v>0.001309116254560649</v>
       </c>
       <c r="S23" t="n">
-        <v>841.5043704677315</v>
+        <v>951.1066187313785</v>
       </c>
       <c r="T23" t="n">
-        <v>173.4045301262063</v>
+        <v>185.0358251663455</v>
       </c>
       <c r="U23" t="n">
-        <v>11.90309091828418</v>
+        <v>12.16920300061558</v>
       </c>
       <c r="V23" t="n">
-        <v>111.5335706043776</v>
+        <v>32.44580615472557</v>
       </c>
       <c r="W23" t="n">
-        <v>8.000514233674011</v>
+        <v>4.65704855252929</v>
       </c>
       <c r="X23" t="n">
-        <v>0.185804798110123</v>
+        <v>0.8365414253700258</v>
       </c>
       <c r="Y23" t="b">
         <v>1</v>
@@ -2287,74 +2287,74 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>974.1268048590981</v>
+        <v>962.4592655014204</v>
       </c>
       <c r="D24" t="n">
-        <v>6.113105295328706</v>
+        <v>10.81607633529812</v>
       </c>
       <c r="E24" t="n">
-        <v>204.6480532053325</v>
+        <v>138.4444598484636</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7307463884353638</v>
+        <v>0.8342413306236267</v>
       </c>
       <c r="G24" t="n">
-        <v>0.07482959982007742</v>
+        <v>0.2111710000008316</v>
       </c>
       <c r="H24" t="n">
-        <v>0.001032155007123947</v>
+        <v>0.0008712398703210056</v>
       </c>
       <c r="I24" t="n">
-        <v>974.1268048591006</v>
+        <v>962.459276802575</v>
       </c>
       <c r="J24" t="n">
-        <v>204.6480532053326</v>
+        <v>173.1913501718469</v>
       </c>
       <c r="K24" t="n">
-        <v>9.000641779862162</v>
+        <v>10.81607600685761</v>
       </c>
       <c r="L24" t="n">
-        <v>2.501110429875553e-12</v>
+        <v>1.130115458636283e-05</v>
       </c>
       <c r="M24" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>34.74689032338324</v>
       </c>
       <c r="N24" t="n">
-        <v>2.887536484533457</v>
+        <v>3.284405156733783e-07</v>
       </c>
       <c r="O24" t="b">
         <v>1</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7626535296440125</v>
+        <v>0.9996767044067383</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.562657400034368</v>
+        <v>0.5083945999995194</v>
       </c>
       <c r="R24" t="n">
-        <v>9.675252658780664e-05</v>
+        <v>0.002355154370889068</v>
       </c>
       <c r="S24" t="n">
-        <v>969.463372641931</v>
+        <v>800.0001033883907</v>
       </c>
       <c r="T24" t="n">
-        <v>204.483247817329</v>
+        <v>150.6460123542645</v>
       </c>
       <c r="U24" t="n">
-        <v>9.000641779862162</v>
+        <v>10.39925094392139</v>
       </c>
       <c r="V24" t="n">
-        <v>4.663432217167156</v>
+        <v>162.4591621130297</v>
       </c>
       <c r="W24" t="n">
-        <v>0.164805388003515</v>
+        <v>12.20155250580089</v>
       </c>
       <c r="X24" t="n">
-        <v>2.887536484533457</v>
+        <v>0.4168253913767348</v>
       </c>
       <c r="Y24" t="b">
         <v>1</v>
@@ -2370,70 +2370,70 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>867.2734201196864</v>
+        <v>867.2993295782069</v>
       </c>
       <c r="D25" t="n">
-        <v>7.079763259912518</v>
+        <v>6.407002093161154</v>
       </c>
       <c r="E25" t="n">
-        <v>218.4079355201941</v>
+        <v>198.9489646310919</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8525735139846802</v>
+        <v>0.8415312170982361</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3070523000787944</v>
+        <v>0.1013672000008228</v>
       </c>
       <c r="H25" t="n">
-        <v>0.001640737871639431</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I25" t="n">
-        <v>929.0273665148541</v>
+        <v>924.4806722595536</v>
       </c>
       <c r="J25" t="n">
-        <v>218.4079640796471</v>
+        <v>198.9489646310918</v>
       </c>
       <c r="K25" t="n">
-        <v>9.000641469297328</v>
+        <v>9.000641606286587</v>
       </c>
       <c r="L25" t="n">
-        <v>61.75394639516765</v>
+        <v>57.18134268134668</v>
       </c>
       <c r="M25" t="n">
-        <v>2.855945299984342e-05</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N25" t="n">
-        <v>1.92087820938481</v>
+        <v>2.593639513125433</v>
       </c>
       <c r="O25" t="b">
         <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>0.990874171257019</v>
+        <v>0.9919732809066772</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.572764700045809</v>
+        <v>0.4867912999998225</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0004998066578991711</v>
+        <v>0.0006223596865311265</v>
       </c>
       <c r="S25" t="n">
-        <v>930.3724720389766</v>
+        <v>934.0690005105253</v>
       </c>
       <c r="T25" t="n">
-        <v>215.7429727727841</v>
+        <v>199.5267464002485</v>
       </c>
       <c r="U25" t="n">
-        <v>9.00063985353014</v>
+        <v>9.000641778849703</v>
       </c>
       <c r="V25" t="n">
-        <v>63.09905191929022</v>
+        <v>66.76967093231838</v>
       </c>
       <c r="W25" t="n">
-        <v>2.664962747409959</v>
+        <v>0.5777817691566156</v>
       </c>
       <c r="X25" t="n">
-        <v>1.920876593617622</v>
+        <v>2.593639685688549</v>
       </c>
       <c r="Y25" t="b">
         <v>1</v>
@@ -2449,70 +2449,70 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>956.2207419740964</v>
+        <v>951.9562658618662</v>
       </c>
       <c r="D26" t="n">
-        <v>10.6314366474908</v>
+        <v>11.22672540610299</v>
       </c>
       <c r="E26" t="n">
-        <v>151.5456832369129</v>
+        <v>115.4908264912468</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6767300963401794</v>
+        <v>0.8342413306236267</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3592511999886483</v>
+        <v>0.2025833999996394</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0008354719611816108</v>
+        <v>0.01565238833427429</v>
       </c>
       <c r="I26" t="n">
-        <v>956.220743406441</v>
+        <v>939.7162882422027</v>
       </c>
       <c r="J26" t="n">
-        <v>173.7371852347398</v>
+        <v>163.0146506522758</v>
       </c>
       <c r="K26" t="n">
-        <v>10.63133882250647</v>
+        <v>12.31841773728678</v>
       </c>
       <c r="L26" t="n">
-        <v>1.432344561180798e-06</v>
+        <v>12.23997761966348</v>
       </c>
       <c r="M26" t="n">
-        <v>22.19150199782698</v>
+        <v>47.52382416102897</v>
       </c>
       <c r="N26" t="n">
-        <v>9.7824984329975e-05</v>
+        <v>1.091692331183785</v>
       </c>
       <c r="O26" t="b">
         <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9782317280769348</v>
+        <v>0.9999998807907104</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.454094799933955</v>
+        <v>0.5500197999990633</v>
       </c>
       <c r="R26" t="n">
-        <v>0.001589211286045611</v>
+        <v>0.003563979174941778</v>
       </c>
       <c r="S26" t="n">
-        <v>822.66524694979</v>
+        <v>800.000032276658</v>
       </c>
       <c r="T26" t="n">
-        <v>158.6370014526266</v>
+        <v>150.0005529051632</v>
       </c>
       <c r="U26" t="n">
-        <v>10.49156314359158</v>
+        <v>10.55151298835904</v>
       </c>
       <c r="V26" t="n">
-        <v>133.5554950243064</v>
+        <v>151.9562335852082</v>
       </c>
       <c r="W26" t="n">
-        <v>7.091318215713784</v>
+        <v>34.50972641391637</v>
       </c>
       <c r="X26" t="n">
-        <v>0.1398735038992189</v>
+        <v>0.6752124177439569</v>
       </c>
       <c r="Y26" t="b">
         <v>1</v>
@@ -2528,70 +2528,70 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>871.6973506981192</v>
+        <v>891.0725068260823</v>
       </c>
       <c r="D27" t="n">
-        <v>7.567281293393127</v>
+        <v>6.329903495610772</v>
       </c>
       <c r="E27" t="n">
-        <v>200.6666113793854</v>
+        <v>212.3937396458292</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8491541743278503</v>
+        <v>0.8062700033187866</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2276772998739034</v>
+        <v>0.1235274000009667</v>
       </c>
       <c r="H27" t="n">
-        <v>0.001641420414671302</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I27" t="n">
-        <v>929.0287776888827</v>
+        <v>924.480668220032</v>
       </c>
       <c r="J27" t="n">
-        <v>200.6666113793854</v>
+        <v>212.3937396458292</v>
       </c>
       <c r="K27" t="n">
-        <v>9.000641625199611</v>
+        <v>9.000641647637073</v>
       </c>
       <c r="L27" t="n">
-        <v>57.33142699076348</v>
+        <v>33.40816139394974</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="N27" t="n">
-        <v>1.433360331806484</v>
+        <v>2.670738152026301</v>
       </c>
       <c r="O27" t="b">
         <v>1</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9760347604751587</v>
+        <v>0.9695480465888977</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.294846800155938</v>
+        <v>0.375311600000714</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0003537610464263707</v>
+        <v>0.0004044155066367239</v>
       </c>
       <c r="S27" t="n">
-        <v>926.6508397436913</v>
+        <v>936.2941706744315</v>
       </c>
       <c r="T27" t="n">
-        <v>200.3387851681008</v>
+        <v>212.5300074365715</v>
       </c>
       <c r="U27" t="n">
-        <v>9.000641675461011</v>
+        <v>9.000641743714763</v>
       </c>
       <c r="V27" t="n">
-        <v>54.95348904557216</v>
+        <v>45.22166384834918</v>
       </c>
       <c r="W27" t="n">
-        <v>0.3278262112845596</v>
+        <v>0.1362677907423802</v>
       </c>
       <c r="X27" t="n">
-        <v>1.433360382067884</v>
+        <v>2.670738248103991</v>
       </c>
       <c r="Y27" t="b">
         <v>1</v>
@@ -2603,74 +2603,74 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>856.1193233431169</v>
+        <v>937.2035501383766</v>
       </c>
       <c r="D28" t="n">
-        <v>8.192890169186759</v>
+        <v>15.33543121419699</v>
       </c>
       <c r="E28" t="n">
-        <v>200.8093246378927</v>
+        <v>197.5726330513037</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8441774249076843</v>
+        <v>0.5688954591751099</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2411728999577463</v>
+        <v>0.163131200000862</v>
       </c>
       <c r="H28" t="n">
-        <v>0.001641420414671302</v>
+        <v>0.002681383397430182</v>
       </c>
       <c r="I28" t="n">
-        <v>929.0283605503008</v>
+        <v>891.8549263762808</v>
       </c>
       <c r="J28" t="n">
-        <v>200.8093246343892</v>
+        <v>203.1418454673367</v>
       </c>
       <c r="K28" t="n">
-        <v>9.000641667905569</v>
+        <v>12.31792562758323</v>
       </c>
       <c r="L28" t="n">
-        <v>72.90903720718393</v>
+        <v>45.34862376209583</v>
       </c>
       <c r="M28" t="n">
-        <v>3.503487278067041e-09</v>
+        <v>5.569212416032968</v>
       </c>
       <c r="N28" t="n">
-        <v>0.8077514987188099</v>
+        <v>3.017505586613755</v>
       </c>
       <c r="O28" t="b">
         <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>0.9799456596374512</v>
+        <v>0.99819415807724</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.436776600079611</v>
+        <v>0.4532982999990054</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0004570444580167532</v>
+        <v>0.001568982377648354</v>
       </c>
       <c r="S28" t="n">
-        <v>925.4132921352116</v>
+        <v>800.000040246188</v>
       </c>
       <c r="T28" t="n">
-        <v>200.383579558851</v>
+        <v>196.5024719743436</v>
       </c>
       <c r="U28" t="n">
-        <v>9.000641787377026</v>
+        <v>13.79522426934381</v>
       </c>
       <c r="V28" t="n">
-        <v>69.29396879209469</v>
+        <v>137.2035098921887</v>
       </c>
       <c r="W28" t="n">
-        <v>0.4257450790417181</v>
+        <v>1.07016107696009</v>
       </c>
       <c r="X28" t="n">
-        <v>0.8077516181902666</v>
+        <v>1.540206944853184</v>
       </c>
       <c r="Y28" t="b">
         <v>1</v>
@@ -2682,74 +2682,74 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>938.3180514967125</v>
+        <v>842.7758475776127</v>
       </c>
       <c r="D29" t="n">
-        <v>9.247788728967553</v>
+        <v>8.005908950111959</v>
       </c>
       <c r="E29" t="n">
-        <v>115.9945698135512</v>
+        <v>210.5470878388263</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7147024869918823</v>
+        <v>0.8184717893600464</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3243708000518382</v>
+        <v>0.09438690000024508</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0008354719611816108</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I29" t="n">
-        <v>938.3180514967514</v>
+        <v>924.4809262433802</v>
       </c>
       <c r="J29" t="n">
-        <v>173.7371904753844</v>
+        <v>210.5470878388263</v>
       </c>
       <c r="K29" t="n">
-        <v>9.247788728967549</v>
+        <v>9.000641531991317</v>
       </c>
       <c r="L29" t="n">
-        <v>3.888089850079268e-11</v>
+        <v>81.70507866576747</v>
       </c>
       <c r="M29" t="n">
-        <v>57.74262066183314</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.552713678800501e-15</v>
+        <v>0.994732581879358</v>
       </c>
       <c r="O29" t="b">
         <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>0.9999799728393555</v>
+        <v>0.898146390914917</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.491667099995539</v>
+        <v>0.4205766999984917</v>
       </c>
       <c r="R29" t="n">
-        <v>0.001502027967944741</v>
+        <v>0.0008703551138751209</v>
       </c>
       <c r="S29" t="n">
-        <v>814.3477327313718</v>
+        <v>931.022166984422</v>
       </c>
       <c r="T29" t="n">
-        <v>150.0005523891731</v>
+        <v>210.8336785592793</v>
       </c>
       <c r="U29" t="n">
-        <v>9.161314395198012</v>
+        <v>9.000641858603196</v>
       </c>
       <c r="V29" t="n">
-        <v>123.9703187653407</v>
+        <v>88.24631940680933</v>
       </c>
       <c r="W29" t="n">
-        <v>34.00598257562189</v>
+        <v>0.286590720453006</v>
       </c>
       <c r="X29" t="n">
-        <v>0.08647433376954083</v>
+        <v>0.9947329084912369</v>
       </c>
       <c r="Y29" t="b">
         <v>1</v>
@@ -2761,74 +2761,74 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>931.6918825194863</v>
+        <v>977.4020370722075</v>
       </c>
       <c r="D30" t="n">
-        <v>11.10716329475271</v>
+        <v>5.524665656531412</v>
       </c>
       <c r="E30" t="n">
-        <v>138.6039614468914</v>
+        <v>204.7693296104794</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7219393849372864</v>
+        <v>0.8122895956039429</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4584415000863373</v>
+        <v>0.03380620000098133</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0008354719611816108</v>
+        <v>0.0006574049475602806</v>
       </c>
       <c r="I30" t="n">
-        <v>931.6913626663281</v>
+        <v>977.4021474280188</v>
       </c>
       <c r="J30" t="n">
-        <v>173.73968632214</v>
+        <v>204.769249955451</v>
       </c>
       <c r="K30" t="n">
-        <v>11.10710732832323</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0005198531581527277</v>
+        <v>0.0001103558113300096</v>
       </c>
       <c r="M30" t="n">
-        <v>35.13572487524866</v>
+        <v>7.965502842921524e-05</v>
       </c>
       <c r="N30" t="n">
-        <v>5.596642948013653e-05</v>
+        <v>3.47597612333075</v>
       </c>
       <c r="O30" t="b">
         <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>0.9992604851722717</v>
+        <v>0.8491940498352051</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.501021299976856</v>
+        <v>0.1607930999998644</v>
       </c>
       <c r="R30" t="n">
-        <v>0.001708808937110007</v>
+        <v>8.892534970073029e-05</v>
       </c>
       <c r="S30" t="n">
-        <v>801.1154357846618</v>
+        <v>978.4543271177363</v>
       </c>
       <c r="T30" t="n">
-        <v>150.0005520116362</v>
+        <v>204.891726295927</v>
       </c>
       <c r="U30" t="n">
-        <v>10.92984022282149</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V30" t="n">
-        <v>130.5764467348245</v>
+        <v>1.052290045528821</v>
       </c>
       <c r="W30" t="n">
-        <v>11.39659056474483</v>
+        <v>0.1223966854475691</v>
       </c>
       <c r="X30" t="n">
-        <v>0.177323071931216</v>
+        <v>3.47597612333075</v>
       </c>
       <c r="Y30" t="b">
         <v>1</v>
@@ -2840,74 +2840,74 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>957.0510297320667</v>
+        <v>882.8955330312515</v>
       </c>
       <c r="D31" t="n">
-        <v>7.500469853186457</v>
+        <v>8.380686905239088</v>
       </c>
       <c r="E31" t="n">
-        <v>151.0090387900675</v>
+        <v>205.836830216832</v>
       </c>
       <c r="F31" t="n">
-        <v>0.616788387298584</v>
+        <v>0.5772911310195923</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4436089000664651</v>
+        <v>0.1368141999992076</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0008352872682735324</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I31" t="n">
-        <v>957.0510304368813</v>
+        <v>924.4806701329694</v>
       </c>
       <c r="J31" t="n">
-        <v>173.7371849751884</v>
+        <v>205.836830216832</v>
       </c>
       <c r="K31" t="n">
-        <v>9.000641779854396</v>
+        <v>9.000641616808313</v>
       </c>
       <c r="L31" t="n">
-        <v>7.048146244414966e-07</v>
+        <v>41.58513710171792</v>
       </c>
       <c r="M31" t="n">
-        <v>22.72814618512086</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.500171926667939</v>
+        <v>0.6199547115692248</v>
       </c>
       <c r="O31" t="b">
         <v>1</v>
       </c>
       <c r="P31" t="n">
-        <v>0.9552946090698242</v>
+        <v>0.7053912878036499</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.305520500056446</v>
+        <v>0.4051727000005485</v>
       </c>
       <c r="R31" t="n">
-        <v>0.001459878636524081</v>
+        <v>0.0004726394254248589</v>
       </c>
       <c r="S31" t="n">
-        <v>830.7455740596424</v>
+        <v>935.5461732586581</v>
       </c>
       <c r="T31" t="n">
-        <v>157.5179537893604</v>
+        <v>205.987548388324</v>
       </c>
       <c r="U31" t="n">
-        <v>9.000641819476746</v>
+        <v>9.000641897143414</v>
       </c>
       <c r="V31" t="n">
-        <v>126.3054556724243</v>
+        <v>52.6506402274066</v>
       </c>
       <c r="W31" t="n">
-        <v>6.50891499929287</v>
+        <v>0.1507181714919454</v>
       </c>
       <c r="X31" t="n">
-        <v>1.500171966290289</v>
+        <v>0.6199549919043257</v>
       </c>
       <c r="Y31" t="b">
         <v>1</v>
@@ -2923,70 +2923,70 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>856.9336195049942</v>
+        <v>884.5688467109494</v>
       </c>
       <c r="D32" t="n">
-        <v>9.056245506034927</v>
+        <v>7.965092399768455</v>
       </c>
       <c r="E32" t="n">
-        <v>211.1414902169284</v>
+        <v>208.8988801593934</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7370278239250183</v>
+        <v>0.7613494992256165</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2066501001827419</v>
+        <v>0.1263880999995308</v>
       </c>
       <c r="H32" t="n">
-        <v>0.001641824259422719</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I32" t="n">
-        <v>929.0269723606521</v>
+        <v>924.4806673284035</v>
       </c>
       <c r="J32" t="n">
-        <v>211.1414902169284</v>
+        <v>208.8988801593934</v>
       </c>
       <c r="K32" t="n">
-        <v>9.056245506034921</v>
+        <v>9.000641767669954</v>
       </c>
       <c r="L32" t="n">
-        <v>72.09335285565783</v>
+        <v>39.91182061745405</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>5.329070518200751e-15</v>
+        <v>1.035549367901499</v>
       </c>
       <c r="O32" t="b">
         <v>1</v>
       </c>
       <c r="P32" t="n">
-        <v>0.9530578851699829</v>
+        <v>0.8096842169761658</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.204095900058746</v>
+        <v>0.4382589000015287</v>
       </c>
       <c r="R32" t="n">
-        <v>0.0004797768779098988</v>
+        <v>0.0004578556690830737</v>
       </c>
       <c r="S32" t="n">
-        <v>925.8347288752615</v>
+        <v>935.6086459184327</v>
       </c>
       <c r="T32" t="n">
-        <v>209.6000366118565</v>
+        <v>209.0434748535456</v>
       </c>
       <c r="U32" t="n">
-        <v>9.137626293535936</v>
+        <v>9.000641611981488</v>
       </c>
       <c r="V32" t="n">
-        <v>68.90110937026725</v>
+        <v>51.03979920748327</v>
       </c>
       <c r="W32" t="n">
-        <v>1.541453605071865</v>
+        <v>0.1445946941522323</v>
       </c>
       <c r="X32" t="n">
-        <v>0.08138078750100952</v>
+        <v>1.035549212213033</v>
       </c>
       <c r="Y32" t="b">
         <v>1</v>
@@ -3002,70 +3002,70 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>846.2242419961858</v>
+        <v>866.0481149643638</v>
       </c>
       <c r="D33" t="n">
-        <v>7.246049245449091</v>
+        <v>8.396102050098845</v>
       </c>
       <c r="E33" t="n">
-        <v>201.3124706733739</v>
+        <v>204.4913804540041</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8491541743278503</v>
+        <v>0.8276007771492004</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2348328998778015</v>
+        <v>0.1399230000006355</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00200818688608706</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I33" t="n">
-        <v>924.8594836812757</v>
+        <v>924.4806702136211</v>
       </c>
       <c r="J33" t="n">
-        <v>201.3124887052236</v>
+        <v>204.4913804540041</v>
       </c>
       <c r="K33" t="n">
-        <v>9.00064160515956</v>
+        <v>9.000641674596414</v>
       </c>
       <c r="L33" t="n">
-        <v>78.63524168508991</v>
+        <v>58.43255524925735</v>
       </c>
       <c r="M33" t="n">
-        <v>1.803184974846772e-05</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.754592359710468</v>
+        <v>0.6045396244975692</v>
       </c>
       <c r="O33" t="b">
         <v>1</v>
       </c>
       <c r="P33" t="n">
-        <v>0.9936483502388</v>
+        <v>0.8861083388328552</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.218184900004417</v>
+        <v>0.4247175000000425</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0005289252148941159</v>
+        <v>0.0006306460127234459</v>
       </c>
       <c r="S33" t="n">
-        <v>924.7547011731529</v>
+        <v>933.5971456417242</v>
       </c>
       <c r="T33" t="n">
-        <v>200.7749869898945</v>
+        <v>204.6880896479087</v>
       </c>
       <c r="U33" t="n">
-        <v>9.000641818943469</v>
+        <v>9.000641798935765</v>
       </c>
       <c r="V33" t="n">
-        <v>78.53045917696704</v>
+        <v>67.54903067736041</v>
       </c>
       <c r="W33" t="n">
-        <v>0.5374836834793655</v>
+        <v>0.1967091939046384</v>
       </c>
       <c r="X33" t="n">
-        <v>1.754592573494378</v>
+        <v>0.6045397488369204</v>
       </c>
       <c r="Y33" t="b">
         <v>1</v>
@@ -3077,74 +3077,74 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>863.546214833475</v>
+        <v>959.224565229976</v>
       </c>
       <c r="D34" t="n">
-        <v>5.947375873056869</v>
+        <v>9.94751973559673</v>
       </c>
       <c r="E34" t="n">
-        <v>208.9049188863797</v>
+        <v>162.2570436523471</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8488157987594604</v>
+        <v>0.8342413306236267</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2683546000625938</v>
+        <v>0.2493610000001354</v>
       </c>
       <c r="H34" t="n">
-        <v>0.001641420414671302</v>
+        <v>0.01395832654088736</v>
       </c>
       <c r="I34" t="n">
-        <v>929.0275243199916</v>
+        <v>939.6998724026978</v>
       </c>
       <c r="J34" t="n">
-        <v>208.8716131547437</v>
+        <v>167.0988485136219</v>
       </c>
       <c r="K34" t="n">
-        <v>9.000686037987416</v>
+        <v>10.39476371594618</v>
       </c>
       <c r="L34" t="n">
-        <v>65.48130948651658</v>
+        <v>19.52469282727816</v>
       </c>
       <c r="M34" t="n">
-        <v>0.03330573163600548</v>
+        <v>4.841804861274852</v>
       </c>
       <c r="N34" t="n">
-        <v>3.053310164930547</v>
+        <v>0.4472439803494481</v>
       </c>
       <c r="O34" t="b">
         <v>1</v>
       </c>
       <c r="P34" t="n">
-        <v>0.9939314126968384</v>
+        <v>0.4192837476730347</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.419169700006023</v>
+        <v>0.7170040999990306</v>
       </c>
       <c r="R34" t="n">
-        <v>0.000438923278125003</v>
+        <v>0.0009151280391961336</v>
       </c>
       <c r="S34" t="n">
-        <v>927.1547647746088</v>
+        <v>852.644515937266</v>
       </c>
       <c r="T34" t="n">
-        <v>207.6914918759447</v>
+        <v>170.1972405686948</v>
       </c>
       <c r="U34" t="n">
-        <v>9.000641596926251</v>
+        <v>9.86373623666578</v>
       </c>
       <c r="V34" t="n">
-        <v>63.60854994113379</v>
+        <v>106.58004929271</v>
       </c>
       <c r="W34" t="n">
-        <v>1.213427010435026</v>
+        <v>7.940196916347787</v>
       </c>
       <c r="X34" t="n">
-        <v>3.053265723869382</v>
+        <v>0.08378349893095027</v>
       </c>
       <c r="Y34" t="b">
         <v>1</v>
@@ -3156,74 +3156,74 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>893.6457020487852</v>
+        <v>941.6997239640687</v>
       </c>
       <c r="D35" t="n">
-        <v>8.130160659592907</v>
+        <v>5.744317367295932</v>
       </c>
       <c r="E35" t="n">
-        <v>215.7724493702983</v>
+        <v>217.4297844451559</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5715892314910889</v>
+        <v>0.737879753112793</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2498170998878777</v>
+        <v>0.03715459999875748</v>
       </c>
       <c r="H35" t="n">
-        <v>0.001640764763578773</v>
+        <v>0.0006575155421160161</v>
       </c>
       <c r="I35" t="n">
-        <v>929.0269691926703</v>
+        <v>941.6997239640593</v>
       </c>
       <c r="J35" t="n">
-        <v>215.7724852584124</v>
+        <v>217.4297790300862</v>
       </c>
       <c r="K35" t="n">
-        <v>9.000641541958043</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L35" t="n">
-        <v>35.38126714388511</v>
+        <v>9.322320693172514e-12</v>
       </c>
       <c r="M35" t="n">
-        <v>3.588811409827031e-05</v>
+        <v>5.415069637138004e-06</v>
       </c>
       <c r="N35" t="n">
-        <v>0.8704808823651362</v>
+        <v>3.25632441256623</v>
       </c>
       <c r="O35" t="b">
         <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>0.6592084765434265</v>
+        <v>0.7000265717506409</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.510465499944985</v>
+        <v>0.1668485999998666</v>
       </c>
       <c r="R35" t="n">
-        <v>0.0002893247292377055</v>
+        <v>9.137560846284032e-05</v>
       </c>
       <c r="S35" t="n">
-        <v>932.5896998936623</v>
+        <v>942.8702160535091</v>
       </c>
       <c r="T35" t="n">
-        <v>214.2460471336375</v>
+        <v>217.5713724849467</v>
       </c>
       <c r="U35" t="n">
-        <v>9.000640651001168</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V35" t="n">
-        <v>38.94399784487712</v>
+        <v>1.170492089440472</v>
       </c>
       <c r="W35" t="n">
-        <v>1.526402236660743</v>
+        <v>0.1415880397908609</v>
       </c>
       <c r="X35" t="n">
-        <v>0.8704799914082617</v>
+        <v>3.25632441256623</v>
       </c>
       <c r="Y35" t="b">
         <v>1</v>
@@ -3239,70 +3239,70 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>933.2877293780917</v>
+        <v>956.1809367004807</v>
       </c>
       <c r="D36" t="n">
-        <v>4.427490388850389</v>
+        <v>5.779851383891266</v>
       </c>
       <c r="E36" t="n">
-        <v>193.6613243102345</v>
+        <v>202.9369456856241</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7307463884353638</v>
+        <v>0.7933008670806885</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0837842000182718</v>
+        <v>0.0266274000005069</v>
       </c>
       <c r="H36" t="n">
-        <v>0.001059164758771658</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I36" t="n">
-        <v>933.2877293781787</v>
+        <v>956.1809367004672</v>
       </c>
       <c r="J36" t="n">
-        <v>193.6613243102344</v>
+        <v>202.9369456856243</v>
       </c>
       <c r="K36" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="L36" t="n">
-        <v>8.697043085703626e-11</v>
+        <v>1.352873368887231e-11</v>
       </c>
       <c r="M36" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>1.989519660128281e-13</v>
       </c>
       <c r="N36" t="n">
-        <v>4.573151391011773</v>
+        <v>3.220790395970896</v>
       </c>
       <c r="O36" t="b">
         <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>0.9862813353538513</v>
+        <v>0.7445645332336426</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.5624810999725014</v>
+        <v>0.2055216999997356</v>
       </c>
       <c r="R36" t="n">
-        <v>5.997930566081777e-05</v>
+        <v>0.0001196384328068234</v>
       </c>
       <c r="S36" t="n">
-        <v>934.7711182797447</v>
+        <v>956.6888191898864</v>
       </c>
       <c r="T36" t="n">
-        <v>193.7260050156243</v>
+        <v>203.0434600025148</v>
       </c>
       <c r="U36" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V36" t="n">
-        <v>1.483388901652916</v>
+        <v>0.5078824894056879</v>
       </c>
       <c r="W36" t="n">
-        <v>0.06468070538986126</v>
+        <v>0.1065143168906957</v>
       </c>
       <c r="X36" t="n">
-        <v>4.573151391011773</v>
+        <v>3.220790395970896</v>
       </c>
       <c r="Y36" t="b">
         <v>1</v>
@@ -3314,74 +3314,74 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>865.8087676085786</v>
+        <v>932.0227942400774</v>
       </c>
       <c r="D37" t="n">
-        <v>8.144551773257559</v>
+        <v>3.279709688528632</v>
       </c>
       <c r="E37" t="n">
-        <v>205.8424484230689</v>
+        <v>206.0283507747026</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8443735241889954</v>
+        <v>0.8071516752243042</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2306583998724818</v>
+        <v>0.03051049999885436</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00200818688608706</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I37" t="n">
-        <v>924.8600710147941</v>
+        <v>932.0227942401589</v>
       </c>
       <c r="J37" t="n">
-        <v>205.8424520582051</v>
+        <v>206.0283507747002</v>
       </c>
       <c r="K37" t="n">
-        <v>9.000641491698769</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L37" t="n">
-        <v>59.05130340621554</v>
+        <v>8.151346264639869e-11</v>
       </c>
       <c r="M37" t="n">
-        <v>3.635136181401322e-06</v>
+        <v>2.387423592153937e-12</v>
       </c>
       <c r="N37" t="n">
-        <v>0.8560897184412095</v>
+        <v>5.72093209133353</v>
       </c>
       <c r="O37" t="b">
         <v>1</v>
       </c>
       <c r="P37" t="n">
-        <v>0.9761877655982971</v>
+        <v>0.9904733300209045</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.690500900149345</v>
+        <v>0.1997496999993018</v>
       </c>
       <c r="R37" t="n">
-        <v>0.0004043198132421821</v>
+        <v>0.0001293522509513423</v>
       </c>
       <c r="S37" t="n">
-        <v>926.8131487107878</v>
+        <v>932.7675535106589</v>
       </c>
       <c r="T37" t="n">
-        <v>205.0086439078982</v>
+        <v>206.1446709805294</v>
       </c>
       <c r="U37" t="n">
-        <v>9.000641788049258</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V37" t="n">
-        <v>61.00438110220921</v>
+        <v>0.7447592705815396</v>
       </c>
       <c r="W37" t="n">
-        <v>0.8338045151707263</v>
+        <v>0.1163202058267814</v>
       </c>
       <c r="X37" t="n">
-        <v>0.8560900147916986</v>
+        <v>5.72093209133353</v>
       </c>
       <c r="Y37" t="b">
         <v>1</v>
@@ -3393,74 +3393,74 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>926.9163097633106</v>
+        <v>894.058597332233</v>
       </c>
       <c r="D38" t="n">
-        <v>9.536587457411368</v>
+        <v>7.10729215437061</v>
       </c>
       <c r="E38" t="n">
-        <v>166.8619071037921</v>
+        <v>206.5638010411286</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7198591232299805</v>
+        <v>0.7774769067764282</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3856684998609126</v>
+        <v>0.1009745000010298</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0008350148564204574</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I38" t="n">
-        <v>926.9205254159402</v>
+        <v>924.4806678336713</v>
       </c>
       <c r="J38" t="n">
-        <v>173.7376823977106</v>
+        <v>206.5638010411287</v>
       </c>
       <c r="K38" t="n">
-        <v>9.536465768679115</v>
+        <v>9.000641635118944</v>
       </c>
       <c r="L38" t="n">
-        <v>0.004215652629682154</v>
+        <v>30.42207050143827</v>
       </c>
       <c r="M38" t="n">
-        <v>6.875775293918508</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="N38" t="n">
-        <v>0.0001216887322534888</v>
+        <v>1.893349480748334</v>
       </c>
       <c r="O38" t="b">
         <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>0.1352208703756332</v>
+        <v>0.8802700042724609</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.328645600005984</v>
+        <v>0.3668240000006335</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0009825332090258598</v>
+        <v>0.0003797303361352533</v>
       </c>
       <c r="S38" t="n">
-        <v>853.5935942041882</v>
+        <v>937.0401347756589</v>
       </c>
       <c r="T38" t="n">
-        <v>172.0228094604772</v>
+        <v>206.6848070899788</v>
       </c>
       <c r="U38" t="n">
-        <v>9.480453882640152</v>
+        <v>9.000641834226704</v>
       </c>
       <c r="V38" t="n">
-        <v>73.32271555912234</v>
+        <v>42.98153744342585</v>
       </c>
       <c r="W38" t="n">
-        <v>5.160902356685057</v>
+        <v>0.121006048850262</v>
       </c>
       <c r="X38" t="n">
-        <v>0.05613357477121639</v>
+        <v>1.893349679856094</v>
       </c>
       <c r="Y38" t="b">
         <v>1</v>
@@ -3472,74 +3472,74 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>875.4128117083939</v>
+        <v>915.9628707257309</v>
       </c>
       <c r="D39" t="n">
-        <v>6.906295241792681</v>
+        <v>11.2926756758084</v>
       </c>
       <c r="E39" t="n">
-        <v>214.0973115201308</v>
+        <v>145.5897009610678</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7958791851997375</v>
+        <v>0.8310216665267944</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2402254999615252</v>
+        <v>0.2477748000001156</v>
       </c>
       <c r="H39" t="n">
-        <v>0.001640764763578773</v>
+        <v>0.004034198820590973</v>
       </c>
       <c r="I39" t="n">
-        <v>929.0269681711083</v>
+        <v>898.3641717137543</v>
       </c>
       <c r="J39" t="n">
-        <v>214.0973589214042</v>
+        <v>173.1996341318766</v>
       </c>
       <c r="K39" t="n">
-        <v>9.00064166651547</v>
+        <v>11.25044915722544</v>
       </c>
       <c r="L39" t="n">
-        <v>53.61415646271439</v>
+        <v>17.59869901197658</v>
       </c>
       <c r="M39" t="n">
-        <v>4.740127337754529e-05</v>
+        <v>27.60993317080889</v>
       </c>
       <c r="N39" t="n">
-        <v>2.094346424722789</v>
+        <v>0.04222651858296622</v>
       </c>
       <c r="O39" t="b">
         <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>0.9842520356178284</v>
+        <v>0.9962121248245239</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.465094399871305</v>
+        <v>0.9162108000000444</v>
       </c>
       <c r="R39" t="n">
-        <v>0.0003955659631174058</v>
+        <v>0.001545119215734303</v>
       </c>
       <c r="S39" t="n">
-        <v>929.6760480653995</v>
+        <v>800.0007183078104</v>
       </c>
       <c r="T39" t="n">
-        <v>212.3783946047745</v>
+        <v>155.1810930980546</v>
       </c>
       <c r="U39" t="n">
-        <v>9.000641068420588</v>
+        <v>11.01362970766526</v>
       </c>
       <c r="V39" t="n">
-        <v>54.26323635700567</v>
+        <v>115.9621524179205</v>
       </c>
       <c r="W39" t="n">
-        <v>1.71891691535626</v>
+        <v>9.591392136986855</v>
       </c>
       <c r="X39" t="n">
-        <v>2.094345826627907</v>
+        <v>0.2790459681431372</v>
       </c>
       <c r="Y39" t="b">
         <v>1</v>
@@ -3551,74 +3551,74 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>969.1019806515382</v>
+        <v>914.9356469254265</v>
       </c>
       <c r="D40" t="n">
-        <v>5.53307287589563</v>
+        <v>13.57521521596934</v>
       </c>
       <c r="E40" t="n">
-        <v>198.6194214414134</v>
+        <v>197.9143229760539</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7307463884353638</v>
+        <v>0.7837685346603394</v>
       </c>
       <c r="G40" t="n">
-        <v>0.07510599982924759</v>
+        <v>0.1604312999988906</v>
       </c>
       <c r="H40" t="n">
-        <v>0.001032155007123947</v>
+        <v>0.0008012968464754522</v>
       </c>
       <c r="I40" t="n">
-        <v>969.1019806515377</v>
+        <v>891.8630123780105</v>
       </c>
       <c r="J40" t="n">
-        <v>198.6194214414133</v>
+        <v>200.1620275358584</v>
       </c>
       <c r="K40" t="n">
-        <v>9.000641779862162</v>
+        <v>11.69492063924486</v>
       </c>
       <c r="L40" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>23.07263454741599</v>
       </c>
       <c r="M40" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>2.247704559804561</v>
       </c>
       <c r="N40" t="n">
-        <v>3.467568903966532</v>
+        <v>1.880294576724477</v>
       </c>
       <c r="O40" t="b">
         <v>1</v>
       </c>
       <c r="P40" t="n">
-        <v>0.9627785682678223</v>
+        <v>0.5898296236991882</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.5498942998237908</v>
+        <v>0.7043693000014173</v>
       </c>
       <c r="R40" t="n">
-        <v>7.20190437277779e-05</v>
+        <v>0.0008531625499017537</v>
       </c>
       <c r="S40" t="n">
-        <v>965.9210437148083</v>
+        <v>822.3079642785661</v>
       </c>
       <c r="T40" t="n">
-        <v>198.6200186514636</v>
+        <v>197.2936607689693</v>
       </c>
       <c r="U40" t="n">
-        <v>9.000641779862162</v>
+        <v>12.93004360977719</v>
       </c>
       <c r="V40" t="n">
-        <v>3.180936936729836</v>
+        <v>92.62768264686031</v>
       </c>
       <c r="W40" t="n">
-        <v>0.0005972100502731337</v>
+        <v>0.620662207084564</v>
       </c>
       <c r="X40" t="n">
-        <v>3.467568903966532</v>
+        <v>0.6451716061921466</v>
       </c>
       <c r="Y40" t="b">
         <v>1</v>
@@ -3630,74 +3630,74 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>879.6736162586592</v>
+        <v>934.2994599959595</v>
       </c>
       <c r="D41" t="n">
-        <v>8.301725031905841</v>
+        <v>13.29227209175094</v>
       </c>
       <c r="E41" t="n">
-        <v>186.3342508131452</v>
+        <v>191.4696694458699</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5084219574928284</v>
+        <v>0.5390264391899109</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2431669998914003</v>
+        <v>0.1476729000005435</v>
       </c>
       <c r="H41" t="n">
-        <v>0.001641420414671302</v>
+        <v>0.001172499847598374</v>
       </c>
       <c r="I41" t="n">
-        <v>929.0269703472128</v>
+        <v>891.8621679710011</v>
       </c>
       <c r="J41" t="n">
-        <v>186.3342508131451</v>
+        <v>191.0703474696069</v>
       </c>
       <c r="K41" t="n">
-        <v>9.000641568709835</v>
+        <v>11.69500109083224</v>
       </c>
       <c r="L41" t="n">
-        <v>49.3533540885536</v>
+        <v>42.43729202495842</v>
       </c>
       <c r="M41" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0.3993219762630531</v>
       </c>
       <c r="N41" t="n">
-        <v>0.6989165368039938</v>
+        <v>1.597271000918694</v>
       </c>
       <c r="O41" t="b">
         <v>1</v>
       </c>
       <c r="P41" t="n">
-        <v>0.7495420575141907</v>
+        <v>0.191131979227066</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.43965580011718</v>
+        <v>1.120314299998427</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0003389256889931858</v>
+        <v>0.00158974074292928</v>
       </c>
       <c r="S41" t="n">
-        <v>927.670505952938</v>
+        <v>954.2061645314308</v>
       </c>
       <c r="T41" t="n">
-        <v>186.8597361454417</v>
+        <v>184.8518429435482</v>
       </c>
       <c r="U41" t="n">
-        <v>9.00064171220026</v>
+        <v>12.2383612793745</v>
       </c>
       <c r="V41" t="n">
-        <v>47.99688969427882</v>
+        <v>19.90670453547125</v>
       </c>
       <c r="W41" t="n">
-        <v>0.5254853322965687</v>
+        <v>6.617826502321719</v>
       </c>
       <c r="X41" t="n">
-        <v>0.6989166802944187</v>
+        <v>1.053910812376442</v>
       </c>
       <c r="Y41" t="b">
         <v>1</v>
@@ -3713,70 +3713,70 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>943.7726220608309</v>
+        <v>923.2970677667828</v>
       </c>
       <c r="D42" t="n">
-        <v>10.40442627614036</v>
+        <v>12.15593215202897</v>
       </c>
       <c r="E42" t="n">
-        <v>160.2382276536959</v>
+        <v>148.2154659732632</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6767300963401794</v>
+        <v>0.8265721797943115</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2904225001111627</v>
+        <v>0.1940635000009934</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0008354719611816108</v>
+        <v>0.001362329348921776</v>
       </c>
       <c r="I42" t="n">
-        <v>943.7697611833348</v>
+        <v>924.479116666373</v>
       </c>
       <c r="J42" t="n">
-        <v>173.7387993527583</v>
+        <v>173.193227843581</v>
       </c>
       <c r="K42" t="n">
-        <v>10.40439847328815</v>
+        <v>12.15597198149028</v>
       </c>
       <c r="L42" t="n">
-        <v>0.002860877496118519</v>
+        <v>1.1820488995902</v>
       </c>
       <c r="M42" t="n">
-        <v>13.50057169906242</v>
+        <v>24.97776187031778</v>
       </c>
       <c r="N42" t="n">
-        <v>2.780285221604117e-05</v>
+        <v>3.982946130953735e-05</v>
       </c>
       <c r="O42" t="b">
         <v>1</v>
       </c>
       <c r="P42" t="n">
-        <v>0.7561230659484863</v>
+        <v>0.9862338304519653</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.181232600007206</v>
+        <v>0.8101370000003953</v>
       </c>
       <c r="R42" t="n">
-        <v>0.001305108773522079</v>
+        <v>0.001609932980500162</v>
       </c>
       <c r="S42" t="n">
-        <v>839.0401325734077</v>
+        <v>800.0016377621449</v>
       </c>
       <c r="T42" t="n">
-        <v>166.6531764880535</v>
+        <v>158.8516153374016</v>
       </c>
       <c r="U42" t="n">
-        <v>10.30140624744792</v>
+        <v>11.85658951288739</v>
       </c>
       <c r="V42" t="n">
-        <v>104.7324894874232</v>
+        <v>123.2954300046379</v>
       </c>
       <c r="W42" t="n">
-        <v>6.414948834357574</v>
+        <v>10.63614936413836</v>
       </c>
       <c r="X42" t="n">
-        <v>0.1030200286924448</v>
+        <v>0.2993426391415852</v>
       </c>
       <c r="Y42" t="b">
         <v>1</v>
@@ -3788,74 +3788,74 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>965.2011952530343</v>
+        <v>957.8461883377502</v>
       </c>
       <c r="D43" t="n">
-        <v>9.763368787822451</v>
+        <v>5.40731851194075</v>
       </c>
       <c r="E43" t="n">
-        <v>112.0461826509299</v>
+        <v>203.2139416671867</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6767300963401794</v>
+        <v>0.7943711876869202</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4437258001416922</v>
+        <v>0.02722840000024007</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0008354719611816108</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I43" t="n">
-        <v>965.2011927346382</v>
+        <v>957.8461883377539</v>
       </c>
       <c r="J43" t="n">
-        <v>173.7371848408262</v>
+        <v>203.2139416671866</v>
       </c>
       <c r="K43" t="n">
-        <v>9.763253716228888</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L43" t="n">
-        <v>2.518396058803773e-06</v>
+        <v>3.751665644813329e-12</v>
       </c>
       <c r="M43" t="n">
-        <v>61.69100218989627</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="N43" t="n">
-        <v>0.000115071593562277</v>
+        <v>3.593323267921412</v>
       </c>
       <c r="O43" t="b">
         <v>1</v>
       </c>
       <c r="P43" t="n">
-        <v>0.9999816417694092</v>
+        <v>0.901283323764801</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.459018799941987</v>
+        <v>0.1719758999988699</v>
       </c>
       <c r="R43" t="n">
-        <v>0.00173470878507942</v>
+        <v>0.0001180368708446622</v>
       </c>
       <c r="S43" t="n">
-        <v>812.2869164598184</v>
+        <v>958.3371593473358</v>
       </c>
       <c r="T43" t="n">
-        <v>150.0005524264441</v>
+        <v>203.3174290775349</v>
       </c>
       <c r="U43" t="n">
-        <v>9.643740983973773</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V43" t="n">
-        <v>152.9142787932159</v>
+        <v>0.4909710095856781</v>
       </c>
       <c r="W43" t="n">
-        <v>37.95436977551421</v>
+        <v>0.1034874103481229</v>
       </c>
       <c r="X43" t="n">
-        <v>0.1196278038486778</v>
+        <v>3.593323267921412</v>
       </c>
       <c r="Y43" t="b">
         <v>1</v>
@@ -3871,70 +3871,70 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>964.5739433906937</v>
+        <v>919.8850439887167</v>
       </c>
       <c r="D44" t="n">
-        <v>6.487327250518685</v>
+        <v>6.987860270816064</v>
       </c>
       <c r="E44" t="n">
-        <v>212.2483806212175</v>
+        <v>213.1441079328948</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7307463884353638</v>
+        <v>0.5113658905029297</v>
       </c>
       <c r="G44" t="n">
-        <v>0.06732219993136823</v>
+        <v>0.1324557999996614</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0008134524687193334</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I44" t="n">
-        <v>964.573943390694</v>
+        <v>924.4806673134666</v>
       </c>
       <c r="J44" t="n">
-        <v>212.2483806212174</v>
+        <v>213.1441079328948</v>
       </c>
       <c r="K44" t="n">
-        <v>9.022256386191025</v>
+        <v>9.000641728722</v>
       </c>
       <c r="L44" t="n">
-        <v>3.410605131648481e-13</v>
+        <v>4.595623324749909</v>
       </c>
       <c r="M44" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N44" t="n">
-        <v>2.534929135672339</v>
+        <v>2.012781457905936</v>
       </c>
       <c r="O44" t="b">
         <v>1</v>
       </c>
       <c r="P44" t="n">
-        <v>0.4742973446846008</v>
+        <v>0.05108459293842316</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.5007862998172641</v>
+        <v>0.171445699999822</v>
       </c>
       <c r="R44" t="n">
-        <v>0.000117031297122594</v>
+        <v>0.0001197151141241193</v>
       </c>
       <c r="S44" t="n">
-        <v>961.5325657551296</v>
+        <v>920.4992377971934</v>
       </c>
       <c r="T44" t="n">
-        <v>211.7357198120444</v>
+        <v>213.2658062653188</v>
       </c>
       <c r="U44" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V44" t="n">
-        <v>3.041377635564118</v>
+        <v>0.6141938084766707</v>
       </c>
       <c r="W44" t="n">
-        <v>0.5126608091731839</v>
+        <v>0.1216983324239322</v>
       </c>
       <c r="X44" t="n">
-        <v>2.513314529343477</v>
+        <v>2.012781509046098</v>
       </c>
       <c r="Y44" t="b">
         <v>1</v>
@@ -3950,70 +3950,70 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>889.5980895494844</v>
+        <v>856.1319878890793</v>
       </c>
       <c r="D45" t="n">
-        <v>7.610245508005957</v>
+        <v>7.047902626896689</v>
       </c>
       <c r="E45" t="n">
-        <v>193.5441101137055</v>
+        <v>194.8680250367964</v>
       </c>
       <c r="F45" t="n">
-        <v>0.7952448129653931</v>
+        <v>0.8388520479202271</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2625043999869376</v>
+        <v>0.1332616999989114</v>
       </c>
       <c r="H45" t="n">
-        <v>0.001641420414671302</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I45" t="n">
-        <v>929.0269664561034</v>
+        <v>924.4806679704964</v>
       </c>
       <c r="J45" t="n">
-        <v>193.5441101137055</v>
+        <v>194.8680250367964</v>
       </c>
       <c r="K45" t="n">
-        <v>9.000641686075078</v>
+        <v>9.000641506820683</v>
       </c>
       <c r="L45" t="n">
-        <v>39.42887690661905</v>
+        <v>68.34868008141711</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1.39039617806912</v>
+        <v>1.952738879923994</v>
       </c>
       <c r="O45" t="b">
         <v>1</v>
       </c>
       <c r="P45" t="n">
-        <v>0.7567412853240967</v>
+        <v>0.9849173426628113</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.322271100012586</v>
+        <v>0.4248204000014084</v>
       </c>
       <c r="R45" t="n">
-        <v>0.0002485042787156999</v>
+        <v>0.0007378043956123292</v>
       </c>
       <c r="S45" t="n">
-        <v>928.2332327864444</v>
+        <v>933.5397006458571</v>
       </c>
       <c r="T45" t="n">
-        <v>193.6683808320113</v>
+        <v>195.5236715079213</v>
       </c>
       <c r="U45" t="n">
-        <v>9.000641846928602</v>
+        <v>9.000641727137973</v>
       </c>
       <c r="V45" t="n">
-        <v>38.63514323696006</v>
+        <v>77.40771275677787</v>
       </c>
       <c r="W45" t="n">
-        <v>0.1242707183057803</v>
+        <v>0.6556464711248395</v>
       </c>
       <c r="X45" t="n">
-        <v>1.390396338922645</v>
+        <v>1.952739100241284</v>
       </c>
       <c r="Y45" t="b">
         <v>1</v>
@@ -4029,70 +4029,70 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>870.0541739306535</v>
+        <v>891.8267851103899</v>
       </c>
       <c r="D46" t="n">
-        <v>6.453242891746804</v>
+        <v>8.90862009710092</v>
       </c>
       <c r="E46" t="n">
-        <v>192.4539211513667</v>
+        <v>214.6839444567854</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8037148118019104</v>
+        <v>0.59441739320755</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2283703999128193</v>
+        <v>0.1268964999999298</v>
       </c>
       <c r="H46" t="n">
-        <v>0.001641420414671302</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I46" t="n">
-        <v>929.0276320766679</v>
+        <v>924.4806687804495</v>
       </c>
       <c r="J46" t="n">
-        <v>192.4540282010211</v>
+        <v>214.6839444567854</v>
       </c>
       <c r="K46" t="n">
-        <v>9.000691620665208</v>
+        <v>9.000641455627086</v>
       </c>
       <c r="L46" t="n">
-        <v>58.97345814601442</v>
+        <v>32.6538836700596</v>
       </c>
       <c r="M46" t="n">
-        <v>0.0001070496543320587</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N46" t="n">
-        <v>2.547448728918404</v>
+        <v>0.092021358526166</v>
       </c>
       <c r="O46" t="b">
         <v>1</v>
       </c>
       <c r="P46" t="n">
-        <v>0.986186146736145</v>
+        <v>0.2020948678255081</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.240937200142071</v>
+        <v>0.4259170000004815</v>
       </c>
       <c r="R46" t="n">
-        <v>0.0003761979751288891</v>
+        <v>0.0003919356386177242</v>
       </c>
       <c r="S46" t="n">
-        <v>926.2176622459165</v>
+        <v>936.3935700046733</v>
       </c>
       <c r="T46" t="n">
-        <v>192.6654862792646</v>
+        <v>214.8188408813083</v>
       </c>
       <c r="U46" t="n">
-        <v>9.000641745792718</v>
+        <v>9.000641643679471</v>
       </c>
       <c r="V46" t="n">
-        <v>56.16348831526295</v>
+        <v>44.56678489428339</v>
       </c>
       <c r="W46" t="n">
-        <v>0.2115651278978703</v>
+        <v>0.1348964245229638</v>
       </c>
       <c r="X46" t="n">
-        <v>2.547398854045914</v>
+        <v>0.09202154657855033</v>
       </c>
       <c r="Y46" t="b">
         <v>1</v>
@@ -4108,70 +4108,70 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>973.8930806056156</v>
+        <v>937.8430346825069</v>
       </c>
       <c r="D47" t="n">
-        <v>6.453513634429815</v>
+        <v>4.714656273080053</v>
       </c>
       <c r="E47" t="n">
-        <v>204.1455548798793</v>
+        <v>184.6784915092103</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7307463884353638</v>
+        <v>0.7805690169334412</v>
       </c>
       <c r="G47" t="n">
-        <v>0.07137780007906258</v>
+        <v>0.03655149999940477</v>
       </c>
       <c r="H47" t="n">
-        <v>0.001032155007123947</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I47" t="n">
-        <v>973.8930806056087</v>
+        <v>937.843034682439</v>
       </c>
       <c r="J47" t="n">
-        <v>204.1455548798793</v>
+        <v>184.6784915092109</v>
       </c>
       <c r="K47" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="L47" t="n">
-        <v>6.934897101018578e-12</v>
+        <v>6.787104211980477e-11</v>
       </c>
       <c r="M47" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>5.400124791776761e-13</v>
       </c>
       <c r="N47" t="n">
-        <v>2.547128145432348</v>
+        <v>4.28598550678211</v>
       </c>
       <c r="O47" t="b">
         <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>0.5181303024291992</v>
+        <v>0.9717041254043579</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.5293264999054372</v>
+        <v>0.1672189000000799</v>
       </c>
       <c r="R47" t="n">
-        <v>9.4331189757213e-05</v>
+        <v>0.0001876782043837011</v>
       </c>
       <c r="S47" t="n">
-        <v>969.3308537476071</v>
+        <v>939.0506026082115</v>
       </c>
       <c r="T47" t="n">
-        <v>203.9992432142571</v>
+        <v>184.7635664641608</v>
       </c>
       <c r="U47" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V47" t="n">
-        <v>4.562226858008557</v>
+        <v>1.207567925704666</v>
       </c>
       <c r="W47" t="n">
-        <v>0.1463116656222212</v>
+        <v>0.08507495495049966</v>
       </c>
       <c r="X47" t="n">
-        <v>2.547128145432348</v>
+        <v>4.28598550678211</v>
       </c>
       <c r="Y47" t="b">
         <v>1</v>
@@ -4183,74 +4183,74 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>935.9882360664233</v>
+        <v>852.2007345185287</v>
       </c>
       <c r="D48" t="n">
-        <v>4.394966240331074</v>
+        <v>8.234111512734437</v>
       </c>
       <c r="E48" t="n">
-        <v>196.2689669060536</v>
+        <v>201.4532764955338</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7307463884353638</v>
+        <v>0.7837687730789185</v>
       </c>
       <c r="G48" t="n">
-        <v>0.06914420006796718</v>
+        <v>0.1266963999987638</v>
       </c>
       <c r="H48" t="n">
-        <v>0.001059164758771658</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I48" t="n">
-        <v>935.9882360664794</v>
+        <v>924.4806727501011</v>
       </c>
       <c r="J48" t="n">
-        <v>196.2689669060535</v>
+        <v>201.4532764955338</v>
       </c>
       <c r="K48" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641520526491</v>
       </c>
       <c r="L48" t="n">
-        <v>5.616129783447832e-11</v>
+        <v>72.27993823157237</v>
       </c>
       <c r="M48" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4.605675539531088</v>
+        <v>0.7665300077920545</v>
       </c>
       <c r="O48" t="b">
         <v>1</v>
       </c>
       <c r="P48" t="n">
-        <v>0.989998996257782</v>
+        <v>0.9181942343711853</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.4476663998793811</v>
+        <v>0.4532667999992555</v>
       </c>
       <c r="R48" t="n">
-        <v>5.330352723831311e-05</v>
+        <v>0.0007723270100541413</v>
       </c>
       <c r="S48" t="n">
-        <v>937.1649486686674</v>
+        <v>932.3364803414411</v>
       </c>
       <c r="T48" t="n">
-        <v>196.2946006948045</v>
+        <v>201.6872895414843</v>
       </c>
       <c r="U48" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641734287282</v>
       </c>
       <c r="V48" t="n">
-        <v>1.176712602244152</v>
+        <v>80.13574582291233</v>
       </c>
       <c r="W48" t="n">
-        <v>0.02563378875095168</v>
+        <v>0.234013045950519</v>
       </c>
       <c r="X48" t="n">
-        <v>4.605675539531088</v>
+        <v>0.7665302215528449</v>
       </c>
       <c r="Y48" t="b">
         <v>1</v>
@@ -4266,70 +4266,70 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>825.9598769695076</v>
+        <v>900.7263175218887</v>
       </c>
       <c r="D49" t="n">
-        <v>7.876612341413422</v>
+        <v>6.573016988322543</v>
       </c>
       <c r="E49" t="n">
-        <v>205.6284077315138</v>
+        <v>199.1010662715858</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8487548828125</v>
+        <v>0.7352117896080017</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4133754000067711</v>
+        <v>0.1115269999991142</v>
       </c>
       <c r="H49" t="n">
-        <v>0.00200818688608706</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I49" t="n">
-        <v>924.8594723894713</v>
+        <v>924.4806673727901</v>
       </c>
       <c r="J49" t="n">
-        <v>205.6284119221718</v>
+        <v>199.1010662715858</v>
       </c>
       <c r="K49" t="n">
-        <v>9.000641792519545</v>
+        <v>9.000641768960563</v>
       </c>
       <c r="L49" t="n">
-        <v>98.8995954199637</v>
+        <v>23.75434985090135</v>
       </c>
       <c r="M49" t="n">
-        <v>4.190657989511237e-06</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>1.124029451106123</v>
+        <v>2.42762478063802</v>
       </c>
       <c r="O49" t="b">
         <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>0.9876496195793152</v>
+        <v>0.8801118135452271</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.286408900050446</v>
+        <v>0.4399883999994927</v>
       </c>
       <c r="R49" t="n">
-        <v>0.0006963856867514551</v>
+        <v>0.0003305335994809866</v>
       </c>
       <c r="S49" t="n">
-        <v>924.0139778317182</v>
+        <v>938.4927500622725</v>
       </c>
       <c r="T49" t="n">
-        <v>204.3942468561218</v>
+        <v>199.409682446859</v>
       </c>
       <c r="U49" t="n">
-        <v>9.000641865030756</v>
+        <v>9.000641750264094</v>
       </c>
       <c r="V49" t="n">
-        <v>98.05410086221059</v>
+        <v>37.76643254038379</v>
       </c>
       <c r="W49" t="n">
-        <v>1.234160875392064</v>
+        <v>0.3086161752732437</v>
       </c>
       <c r="X49" t="n">
-        <v>1.124029523617335</v>
+        <v>2.427624761941551</v>
       </c>
       <c r="Y49" t="b">
         <v>1</v>
@@ -4341,74 +4341,74 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>846.5847665177828</v>
+        <v>971.6542106706307</v>
       </c>
       <c r="D50" t="n">
-        <v>8.992942659853101</v>
+        <v>9.679699438752699</v>
       </c>
       <c r="E50" t="n">
-        <v>194.7162467658121</v>
+        <v>149.4314563953131</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7379212975502014</v>
+        <v>0.8341188430786133</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2435905998572707</v>
+        <v>0.1928124999994907</v>
       </c>
       <c r="H50" t="n">
-        <v>0.002008181530982256</v>
+        <v>0.0009419303387403488</v>
       </c>
       <c r="I50" t="n">
-        <v>924.8600527357677</v>
+        <v>971.6542173536892</v>
       </c>
       <c r="J50" t="n">
-        <v>194.7163129705346</v>
+        <v>173.1913506201487</v>
       </c>
       <c r="K50" t="n">
-        <v>9.000641723451468</v>
+        <v>9.679851116437586</v>
       </c>
       <c r="L50" t="n">
-        <v>78.2752862179849</v>
+        <v>6.683058472845005e-06</v>
       </c>
       <c r="M50" t="n">
-        <v>6.62047225432616e-05</v>
+        <v>23.75989422483565</v>
       </c>
       <c r="N50" t="n">
-        <v>0.007699063598366251</v>
+        <v>0.0001516776848866641</v>
       </c>
       <c r="O50" t="b">
         <v>1</v>
       </c>
       <c r="P50" t="n">
-        <v>0.9524005651473999</v>
+        <v>0.9869421720504761</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.089561200002208</v>
+        <v>0.8412749999988591</v>
       </c>
       <c r="R50" t="n">
-        <v>0.0005211347597651184</v>
+        <v>0.001226867316290736</v>
       </c>
       <c r="S50" t="n">
-        <v>923.7636643492689</v>
+        <v>825.8411199005631</v>
       </c>
       <c r="T50" t="n">
-        <v>194.7939687646141</v>
+        <v>159.4115488371688</v>
       </c>
       <c r="U50" t="n">
-        <v>9.076154394691741</v>
+        <v>9.563628437061322</v>
       </c>
       <c r="V50" t="n">
-        <v>77.1788978314861</v>
+        <v>145.8130907700677</v>
       </c>
       <c r="W50" t="n">
-        <v>0.07772199880204766</v>
+        <v>9.98009244185576</v>
       </c>
       <c r="X50" t="n">
-        <v>0.08321173483864008</v>
+        <v>0.1160710016913775</v>
       </c>
       <c r="Y50" t="b">
         <v>1</v>
@@ -4424,70 +4424,70 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>850.5687900251156</v>
+        <v>887.1501231880142</v>
       </c>
       <c r="D51" t="n">
-        <v>8.790001779809423</v>
+        <v>6.582303349592957</v>
       </c>
       <c r="E51" t="n">
-        <v>189.1670865725537</v>
+        <v>211.3566360846236</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6824439167976379</v>
+        <v>0.8435402512550354</v>
       </c>
       <c r="G51" t="n">
-        <v>0.3560074998531491</v>
+        <v>0.1009933999994246</v>
       </c>
       <c r="H51" t="n">
-        <v>0.003652139566838741</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I51" t="n">
-        <v>912.9378550648254</v>
+        <v>924.4811060678609</v>
       </c>
       <c r="J51" t="n">
-        <v>189.228464265379</v>
+        <v>211.3566360846236</v>
       </c>
       <c r="K51" t="n">
-        <v>9.238522435180684</v>
+        <v>9.000641660549674</v>
       </c>
       <c r="L51" t="n">
-        <v>62.36906503970977</v>
+        <v>37.33098287984672</v>
       </c>
       <c r="M51" t="n">
-        <v>0.06137769282534578</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N51" t="n">
-        <v>0.4485206553712615</v>
+        <v>2.418338310956717</v>
       </c>
       <c r="O51" t="b">
         <v>1</v>
       </c>
       <c r="P51" t="n">
-        <v>0.951898455619812</v>
+        <v>0.9739328026771545</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.374096399871632</v>
+        <v>0.4533549999996467</v>
       </c>
       <c r="R51" t="n">
-        <v>0.0005295484443195164</v>
+        <v>0.0004376955330371857</v>
       </c>
       <c r="S51" t="n">
-        <v>924.7924058723705</v>
+        <v>935.7949612346154</v>
       </c>
       <c r="T51" t="n">
-        <v>189.6459634920217</v>
+        <v>211.502268654002</v>
       </c>
       <c r="U51" t="n">
-        <v>9.000641783293537</v>
+        <v>9.000641561005152</v>
       </c>
       <c r="V51" t="n">
-        <v>74.22361584725491</v>
+        <v>48.64483804660119</v>
       </c>
       <c r="W51" t="n">
-        <v>0.4788769194680071</v>
+        <v>0.1456325693783924</v>
       </c>
       <c r="X51" t="n">
-        <v>0.210640003484114</v>
+        <v>2.418338211412195</v>
       </c>
       <c r="Y51" t="b">
         <v>1</v>
@@ -4499,74 +4499,74 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>874.5961786984</v>
+        <v>926.6726500100951</v>
       </c>
       <c r="D52" t="n">
-        <v>7.283575034765953</v>
+        <v>5.834740604668191</v>
       </c>
       <c r="E52" t="n">
-        <v>211.7301351302594</v>
+        <v>199.6577601407073</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8511509895324707</v>
+        <v>0.8077849149703979</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2580041999462992</v>
+        <v>0.03049370000007912</v>
       </c>
       <c r="H52" t="n">
-        <v>0.001640764763578773</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I52" t="n">
-        <v>929.0269664546263</v>
+        <v>926.6726500100767</v>
       </c>
       <c r="J52" t="n">
-        <v>211.7302100659202</v>
+        <v>199.6577601407072</v>
       </c>
       <c r="K52" t="n">
-        <v>9.000641703588617</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L52" t="n">
-        <v>54.43078775622632</v>
+        <v>1.84172677109018e-11</v>
       </c>
       <c r="M52" t="n">
-        <v>7.493566079119773e-05</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N52" t="n">
-        <v>1.717066668822664</v>
+        <v>3.165901175193971</v>
       </c>
       <c r="O52" t="b">
         <v>1</v>
       </c>
       <c r="P52" t="n">
-        <v>0.9825460910797119</v>
+        <v>0.6036913990974426</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.240952600026503</v>
+        <v>0.188606500001697</v>
       </c>
       <c r="R52" t="n">
-        <v>0.0003806603199336678</v>
+        <v>0.0001547730207676068</v>
       </c>
       <c r="S52" t="n">
-        <v>928.8975963937371</v>
+        <v>927.5787766706371</v>
       </c>
       <c r="T52" t="n">
-        <v>210.3360803781563</v>
+        <v>199.8324506352653</v>
       </c>
       <c r="U52" t="n">
-        <v>9.000641346934142</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V52" t="n">
-        <v>54.30141769533714</v>
+        <v>0.906126660541986</v>
       </c>
       <c r="W52" t="n">
-        <v>1.394054752103131</v>
+        <v>0.1746904945580638</v>
       </c>
       <c r="X52" t="n">
-        <v>1.717066312168189</v>
+        <v>3.165901175193971</v>
       </c>
       <c r="Y52" t="b">
         <v>1</v>
@@ -4578,74 +4578,74 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>945.8083921095481</v>
+        <v>928.0424742349063</v>
       </c>
       <c r="D53" t="n">
-        <v>10.48900916292622</v>
+        <v>14.39454277695739</v>
       </c>
       <c r="E53" t="n">
-        <v>133.9114797784555</v>
+        <v>204.9006277479043</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6767300963401794</v>
+        <v>0.6630008816719055</v>
       </c>
       <c r="G53" t="n">
-        <v>0.3351312000304461</v>
+        <v>0.1416719000008015</v>
       </c>
       <c r="H53" t="n">
-        <v>0.02174675464630127</v>
+        <v>0.002421969082206488</v>
       </c>
       <c r="I53" t="n">
-        <v>945.8088833208609</v>
+        <v>891.853858463534</v>
       </c>
       <c r="J53" t="n">
-        <v>167.3116498091097</v>
+        <v>205.0749302699842</v>
       </c>
       <c r="K53" t="n">
-        <v>10.48902223459781</v>
+        <v>12.31813765676279</v>
       </c>
       <c r="L53" t="n">
-        <v>0.0004912113128057172</v>
+        <v>36.18861577137227</v>
       </c>
       <c r="M53" t="n">
-        <v>33.40017003065418</v>
+        <v>0.1743025220798984</v>
       </c>
       <c r="N53" t="n">
-        <v>1.30716715887047e-05</v>
+        <v>2.076405120194599</v>
       </c>
       <c r="O53" t="b">
         <v>1</v>
       </c>
       <c r="P53" t="n">
-        <v>0.9998112320899963</v>
+        <v>0.9753878712654114</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.38329379982315</v>
+        <v>0.8403077999992092</v>
       </c>
       <c r="R53" t="n">
-        <v>0.001698347390629351</v>
+        <v>0.00107042258605361</v>
       </c>
       <c r="S53" t="n">
-        <v>806.3955977542981</v>
+        <v>805.8293929216601</v>
       </c>
       <c r="T53" t="n">
-        <v>150.0005522499343</v>
+        <v>204.1218710905988</v>
       </c>
       <c r="U53" t="n">
-        <v>10.34333313012497</v>
+        <v>13.48221061413342</v>
       </c>
       <c r="V53" t="n">
-        <v>139.41279435525</v>
+        <v>122.2130813132462</v>
       </c>
       <c r="W53" t="n">
-        <v>16.08907247147877</v>
+        <v>0.7787566573054789</v>
       </c>
       <c r="X53" t="n">
-        <v>0.1456760328012514</v>
+        <v>0.9123321628239722</v>
       </c>
       <c r="Y53" t="b">
         <v>1</v>
@@ -4657,74 +4657,74 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>863.7740009755142</v>
+        <v>920.190680118923</v>
       </c>
       <c r="D54" t="n">
-        <v>9.208810364877245</v>
+        <v>12.92564418956117</v>
       </c>
       <c r="E54" t="n">
-        <v>209.8926924406994</v>
+        <v>196.9481724590098</v>
       </c>
       <c r="F54" t="n">
-        <v>0.7265956997871399</v>
+        <v>0.5190762281417847</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2010147999972105</v>
+        <v>0.2818693999997777</v>
       </c>
       <c r="H54" t="n">
-        <v>0.002424679230898619</v>
+        <v>0.0009203365771099925</v>
       </c>
       <c r="I54" t="n">
-        <v>923.5243482490237</v>
+        <v>891.8717779954161</v>
       </c>
       <c r="J54" t="n">
-        <v>210.02871986632</v>
+        <v>197.3407795222889</v>
       </c>
       <c r="K54" t="n">
-        <v>9.208818082389881</v>
+        <v>11.69500117267008</v>
       </c>
       <c r="L54" t="n">
-        <v>59.75034727350942</v>
+        <v>28.31890212350686</v>
       </c>
       <c r="M54" t="n">
-        <v>0.1360274256205116</v>
+        <v>0.3926070632790868</v>
       </c>
       <c r="N54" t="n">
-        <v>7.717512636062906e-06</v>
+        <v>1.230643016891094</v>
       </c>
       <c r="O54" t="b">
         <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>0.9266018271446228</v>
+        <v>0.1265840530395508</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.9905840000137687</v>
+        <v>0.7444093999984034</v>
       </c>
       <c r="R54" t="n">
-        <v>0.0004086036933586001</v>
+        <v>0.0007879638578742743</v>
       </c>
       <c r="S54" t="n">
-        <v>924.8452961757986</v>
+        <v>839.0766433309378</v>
       </c>
       <c r="T54" t="n">
-        <v>208.6921049532858</v>
+        <v>196.3377956742819</v>
       </c>
       <c r="U54" t="n">
-        <v>9.27818194364529</v>
+        <v>12.39525267170594</v>
       </c>
       <c r="V54" t="n">
-        <v>61.07129520028434</v>
+        <v>81.11403678798513</v>
       </c>
       <c r="W54" t="n">
-        <v>1.200587487413685</v>
+        <v>0.6103767847279187</v>
       </c>
       <c r="X54" t="n">
-        <v>0.06937157876804534</v>
+        <v>0.5303915178552288</v>
       </c>
       <c r="Y54" t="b">
         <v>1</v>
@@ -4736,74 +4736,74 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>955.4030319393862</v>
+        <v>904.7260228175338</v>
       </c>
       <c r="D55" t="n">
-        <v>8.545170262957331</v>
+        <v>6.513873947704546</v>
       </c>
       <c r="E55" t="n">
-        <v>105.7874903676893</v>
+        <v>194.1900640139415</v>
       </c>
       <c r="F55" t="n">
-        <v>0.7475630044937134</v>
+        <v>0.5757224559783936</v>
       </c>
       <c r="G55" t="n">
-        <v>0.3329115000087768</v>
+        <v>0.1071010999985447</v>
       </c>
       <c r="H55" t="n">
-        <v>0.02173936180770397</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I55" t="n">
-        <v>955.4030319393745</v>
+        <v>924.4806679266952</v>
       </c>
       <c r="J55" t="n">
-        <v>167.3099722083214</v>
+        <v>194.1900640139415</v>
       </c>
       <c r="K55" t="n">
-        <v>9.000405959832324</v>
+        <v>9.000641660370865</v>
       </c>
       <c r="L55" t="n">
-        <v>1.170974428532645e-11</v>
+        <v>19.7546451091614</v>
       </c>
       <c r="M55" t="n">
-        <v>61.52248184063211</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>0.4552356968749933</v>
+        <v>2.486767712666319</v>
       </c>
       <c r="O55" t="b">
         <v>1</v>
       </c>
       <c r="P55" t="n">
-        <v>0.999987006187439</v>
+        <v>0.8196242451667786</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.008653699886054</v>
+        <v>0.3965094000013778</v>
       </c>
       <c r="R55" t="n">
-        <v>0.001610016566701233</v>
+        <v>0.0003062655450776219</v>
       </c>
       <c r="S55" t="n">
-        <v>816.2340796663143</v>
+        <v>939.8257292647016</v>
       </c>
       <c r="T55" t="n">
-        <v>150.0005525229262</v>
+        <v>194.4442288392474</v>
       </c>
       <c r="U55" t="n">
-        <v>9.000652532053421</v>
+        <v>9.000641568461951</v>
       </c>
       <c r="V55" t="n">
-        <v>139.1689522730719</v>
+        <v>35.09970644716782</v>
       </c>
       <c r="W55" t="n">
-        <v>44.21306215523688</v>
+        <v>0.2541648253059066</v>
       </c>
       <c r="X55" t="n">
-        <v>0.4554822690960894</v>
+        <v>2.486767620757405</v>
       </c>
       <c r="Y55" t="b">
         <v>1</v>
@@ -4815,74 +4815,74 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>927.9779130066328</v>
+        <v>953.6799627409868</v>
       </c>
       <c r="D56" t="n">
-        <v>10.22557489068757</v>
+        <v>5.695247330655505</v>
       </c>
       <c r="E56" t="n">
-        <v>138.2664482202784</v>
+        <v>211.4400709604765</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7199835777282715</v>
+        <v>0.8140485286712646</v>
       </c>
       <c r="G56" t="n">
-        <v>0.4943528999574482</v>
+        <v>0.03059759999996459</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0008350422140210867</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I56" t="n">
-        <v>927.9519047968892</v>
+        <v>953.679962740982</v>
       </c>
       <c r="J56" t="n">
-        <v>173.73995228162</v>
+        <v>211.4400709604764</v>
       </c>
       <c r="K56" t="n">
-        <v>10.22516022653331</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L56" t="n">
-        <v>0.0260082097436225</v>
+        <v>4.774847184307873e-12</v>
       </c>
       <c r="M56" t="n">
-        <v>35.47350406134157</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="N56" t="n">
-        <v>0.0004146641542526197</v>
+        <v>3.305394449206657</v>
       </c>
       <c r="O56" t="b">
         <v>1</v>
       </c>
       <c r="P56" t="n">
-        <v>0.9994863271713257</v>
+        <v>0.7604827284812927</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.756716700037941</v>
+        <v>0.1889549999996234</v>
       </c>
       <c r="R56" t="n">
-        <v>0.001529441098682582</v>
+        <v>9.524988126941025e-05</v>
       </c>
       <c r="S56" t="n">
-        <v>807.2642104770206</v>
+        <v>954.7453234484341</v>
       </c>
       <c r="T56" t="n">
-        <v>150.0005523363333</v>
+        <v>211.5806574209546</v>
       </c>
       <c r="U56" t="n">
-        <v>10.10500626146617</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V56" t="n">
-        <v>120.7137025296122</v>
+        <v>1.065360707447326</v>
       </c>
       <c r="W56" t="n">
-        <v>11.73410411605488</v>
+        <v>0.1405864604781186</v>
       </c>
       <c r="X56" t="n">
-        <v>0.1205686292213954</v>
+        <v>3.305394449206657</v>
       </c>
       <c r="Y56" t="b">
         <v>1</v>
@@ -4894,74 +4894,74 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>977.4682948805337</v>
+        <v>878.7244280711647</v>
       </c>
       <c r="D57" t="n">
-        <v>11.15997726407362</v>
+        <v>7.496107712312081</v>
       </c>
       <c r="E57" t="n">
-        <v>142.5083483932059</v>
+        <v>215.4862590673856</v>
       </c>
       <c r="F57" t="n">
-        <v>0.6767300963401794</v>
+        <v>0.8227301239967346</v>
       </c>
       <c r="G57" t="n">
-        <v>0.7258266001008451</v>
+        <v>0.1355751999999484</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0008354719611816108</v>
+        <v>0.001030344516038895</v>
       </c>
       <c r="I57" t="n">
-        <v>956.163597253803</v>
+        <v>924.4806673224532</v>
       </c>
       <c r="J57" t="n">
-        <v>173.7379051441053</v>
+        <v>215.486259067386</v>
       </c>
       <c r="K57" t="n">
-        <v>11.16012525609531</v>
+        <v>9.000641605265576</v>
       </c>
       <c r="L57" t="n">
-        <v>21.30469762673067</v>
+        <v>45.75623925128855</v>
       </c>
       <c r="M57" t="n">
-        <v>31.22955675089935</v>
+        <v>3.979039320256561e-13</v>
       </c>
       <c r="N57" t="n">
-        <v>0.0001479920216862496</v>
+        <v>1.504533892953495</v>
       </c>
       <c r="O57" t="b">
         <v>1</v>
       </c>
       <c r="P57" t="n">
-        <v>0.9886354207992554</v>
+        <v>0.93586266040802</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.77789010014385</v>
+        <v>0.4178374000002805</v>
       </c>
       <c r="R57" t="n">
-        <v>0.002027305774390697</v>
+        <v>0.0005075081717222929</v>
       </c>
       <c r="S57" t="n">
-        <v>803.1866695009609</v>
+        <v>934.5424221097506</v>
       </c>
       <c r="T57" t="n">
-        <v>150.1741456937212</v>
+        <v>215.660281100011</v>
       </c>
       <c r="U57" t="n">
-        <v>10.95282112333738</v>
+        <v>9.000641882373063</v>
       </c>
       <c r="V57" t="n">
-        <v>174.2816253795728</v>
+        <v>55.81799403858599</v>
       </c>
       <c r="W57" t="n">
-        <v>7.665797300515237</v>
+        <v>0.1740220326254018</v>
       </c>
       <c r="X57" t="n">
-        <v>0.2071561407362434</v>
+        <v>1.504534170060983</v>
       </c>
       <c r="Y57" t="b">
         <v>1</v>
@@ -4977,70 +4977,70 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>972.2967900359994</v>
+        <v>959.4549444551382</v>
       </c>
       <c r="D58" t="n">
-        <v>9.863881551845235</v>
+        <v>9.61145559527602</v>
       </c>
       <c r="E58" t="n">
-        <v>120.4338779820945</v>
+        <v>154.1556131362414</v>
       </c>
       <c r="F58" t="n">
-        <v>0.6767300963401794</v>
+        <v>0.8342413306236267</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6126461999956518</v>
+        <v>0.1542993999992177</v>
       </c>
       <c r="H58" t="n">
-        <v>0.02174675464630127</v>
+        <v>0.0009383680298924446</v>
       </c>
       <c r="I58" t="n">
-        <v>972.2967920041988</v>
+        <v>960.4299786405732</v>
       </c>
       <c r="J58" t="n">
-        <v>167.3097806153223</v>
+        <v>173.1914970857922</v>
       </c>
       <c r="K58" t="n">
-        <v>9.863881568612399</v>
+        <v>9.609333334284983</v>
       </c>
       <c r="L58" t="n">
-        <v>1.968199399016157e-06</v>
+        <v>0.9750341854349927</v>
       </c>
       <c r="M58" t="n">
-        <v>46.87590263322784</v>
+        <v>19.03588394955085</v>
       </c>
       <c r="N58" t="n">
-        <v>1.676716365750508e-08</v>
+        <v>0.00212226099103674</v>
       </c>
       <c r="O58" t="b">
         <v>1</v>
       </c>
       <c r="P58" t="n">
-        <v>0.9999473094940186</v>
+        <v>0.9423930644989014</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.874648400116712</v>
+        <v>0.7485969999997906</v>
       </c>
       <c r="R58" t="n">
-        <v>0.001792471506632864</v>
+        <v>0.001064009964466095</v>
       </c>
       <c r="S58" t="n">
-        <v>811.9116277227274</v>
+        <v>836.5903342080511</v>
       </c>
       <c r="T58" t="n">
-        <v>150.0005523202645</v>
+        <v>163.3670525900826</v>
       </c>
       <c r="U58" t="n">
-        <v>9.737284547400694</v>
+        <v>9.512552945100481</v>
       </c>
       <c r="V58" t="n">
-        <v>160.385162313272</v>
+        <v>122.8646102470871</v>
       </c>
       <c r="W58" t="n">
-        <v>29.56667433817003</v>
+        <v>9.211439453841223</v>
       </c>
       <c r="X58" t="n">
-        <v>0.126597004444541</v>
+        <v>0.09890265017553901</v>
       </c>
       <c r="Y58" t="b">
         <v>1</v>
@@ -5052,74 +5052,74 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>938.8775425384561</v>
+        <v>965.4668338928942</v>
       </c>
       <c r="D59" t="n">
-        <v>10.00173040385492</v>
+        <v>5.628955132374228</v>
       </c>
       <c r="E59" t="n">
-        <v>124.1093492680039</v>
+        <v>215.9415361021917</v>
       </c>
       <c r="F59" t="n">
-        <v>0.7147024869918823</v>
+        <v>0.7377122640609741</v>
       </c>
       <c r="G59" t="n">
-        <v>0.4218063000589609</v>
+        <v>0.03172099999937927</v>
       </c>
       <c r="H59" t="n">
-        <v>0.02474404126405716</v>
+        <v>0.0006574971484951675</v>
       </c>
       <c r="I59" t="n">
-        <v>938.8775425384785</v>
+        <v>965.4668338884472</v>
       </c>
       <c r="J59" t="n">
-        <v>167.3100111322507</v>
+        <v>215.941518819786</v>
       </c>
       <c r="K59" t="n">
-        <v>10.00178769917164</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L59" t="n">
-        <v>2.239630703115836e-11</v>
+        <v>4.446974344318733e-09</v>
       </c>
       <c r="M59" t="n">
-        <v>43.20066186424678</v>
+        <v>1.728240576426288e-05</v>
       </c>
       <c r="N59" t="n">
-        <v>5.729531671505583e-05</v>
+        <v>3.371686647487935</v>
       </c>
       <c r="O59" t="b">
         <v>1</v>
       </c>
       <c r="P59" t="n">
-        <v>0.9999579191207886</v>
+        <v>0.7703380584716797</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.584052300080657</v>
+        <v>0.1675304000000324</v>
       </c>
       <c r="R59" t="n">
-        <v>0.001582584227435291</v>
+        <v>7.142432150430977e-05</v>
       </c>
       <c r="S59" t="n">
-        <v>809.4219024214792</v>
+        <v>966.2791013759787</v>
       </c>
       <c r="T59" t="n">
-        <v>150.0005523474917</v>
+        <v>216.0516758296297</v>
       </c>
       <c r="U59" t="n">
-        <v>9.885096296915709</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V59" t="n">
-        <v>129.4556401169768</v>
+        <v>0.8122674830844971</v>
       </c>
       <c r="W59" t="n">
-        <v>25.89120307948779</v>
+        <v>0.1101397274379678</v>
       </c>
       <c r="X59" t="n">
-        <v>0.1166341069392125</v>
+        <v>3.371686647487935</v>
       </c>
       <c r="Y59" t="b">
         <v>1</v>
@@ -5131,74 +5131,74 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>851.9132717869732</v>
+        <v>914.4277433020131</v>
       </c>
       <c r="D60" t="n">
-        <v>6.991764341026262</v>
+        <v>6.127249242883064</v>
       </c>
       <c r="E60" t="n">
-        <v>201.9060442549379</v>
+        <v>190.5813030830286</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8506406545639038</v>
+        <v>0.7621703743934631</v>
       </c>
       <c r="G60" t="n">
-        <v>0.5302205998450518</v>
+        <v>0.1463242999998329</v>
       </c>
       <c r="H60" t="n">
-        <v>0.00200818688608706</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I60" t="n">
-        <v>924.8785694554992</v>
+        <v>924.4806674329564</v>
       </c>
       <c r="J60" t="n">
-        <v>201.9057690386109</v>
+        <v>190.5813030830286</v>
       </c>
       <c r="K60" t="n">
-        <v>9.000000222407492</v>
+        <v>9.000641694793952</v>
       </c>
       <c r="L60" t="n">
-        <v>72.96529766852609</v>
+        <v>10.05292413094321</v>
       </c>
       <c r="M60" t="n">
-        <v>0.0002752163269974517</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.008235881381229</v>
+        <v>2.873392451910888</v>
       </c>
       <c r="O60" t="b">
         <v>1</v>
       </c>
       <c r="P60" t="n">
-        <v>0.9947133660316467</v>
+        <v>0.2493027597665787</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.434768300037831</v>
+        <v>0.1995973000011873</v>
       </c>
       <c r="R60" t="n">
-        <v>0.0004895073943771422</v>
+        <v>0.0002035595534835011</v>
       </c>
       <c r="S60" t="n">
-        <v>925.2011591175732</v>
+        <v>915.3829504453581</v>
       </c>
       <c r="T60" t="n">
-        <v>201.3482566309344</v>
+        <v>190.6834606943153</v>
       </c>
       <c r="U60" t="n">
-        <v>9.000641820358487</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V60" t="n">
-        <v>73.28788733060003</v>
+        <v>0.9552071433449782</v>
       </c>
       <c r="W60" t="n">
-        <v>0.557787624003538</v>
+        <v>0.1021576112866853</v>
       </c>
       <c r="X60" t="n">
-        <v>2.008877479332225</v>
+        <v>2.873392536979098</v>
       </c>
       <c r="Y60" t="b">
         <v>1</v>
@@ -5210,74 +5210,74 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>842.2455954311095</v>
+        <v>954.3218973270541</v>
       </c>
       <c r="D61" t="n">
-        <v>8.773947996961862</v>
+        <v>4.267466985438978</v>
       </c>
       <c r="E61" t="n">
-        <v>213.7771672924718</v>
+        <v>214.7086949110996</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7533094882965088</v>
+        <v>0.8140485286712646</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2620055000297725</v>
+        <v>0.03699129999949946</v>
       </c>
       <c r="H61" t="n">
-        <v>0.002007473492994905</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I61" t="n">
-        <v>924.8595228610391</v>
+        <v>954.3218973271643</v>
       </c>
       <c r="J61" t="n">
-        <v>213.7772241672464</v>
+        <v>214.708694911107</v>
       </c>
       <c r="K61" t="n">
-        <v>9.000641623842233</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L61" t="n">
-        <v>82.61392742992962</v>
+        <v>1.101625457522459e-10</v>
       </c>
       <c r="M61" t="n">
-        <v>5.687477460014634e-05</v>
+        <v>7.332801033044234e-12</v>
       </c>
       <c r="N61" t="n">
-        <v>0.2266936268803708</v>
+        <v>4.733174794423184</v>
       </c>
       <c r="O61" t="b">
         <v>1</v>
       </c>
       <c r="P61" t="n">
-        <v>0.973253607749939</v>
+        <v>0.9945182204246521</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.554880700074136</v>
+        <v>0.1928062000006321</v>
       </c>
       <c r="R61" t="n">
-        <v>0.0006326495786197484</v>
+        <v>8.501165575580671e-05</v>
       </c>
       <c r="S61" t="n">
-        <v>926.6769293286666</v>
+        <v>955.269006075916</v>
       </c>
       <c r="T61" t="n">
-        <v>211.440351500992</v>
+        <v>214.8373939506008</v>
       </c>
       <c r="U61" t="n">
-        <v>9.000641109442343</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V61" t="n">
-        <v>84.43133389755712</v>
+        <v>0.947108748861865</v>
       </c>
       <c r="W61" t="n">
-        <v>2.336815791479808</v>
+        <v>0.1286990395011287</v>
       </c>
       <c r="X61" t="n">
-        <v>0.226693112480481</v>
+        <v>4.733174794423184</v>
       </c>
       <c r="Y61" t="b">
         <v>1</v>
@@ -5293,70 +5293,70 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>956.1273760116578</v>
+        <v>964.7328412473059</v>
       </c>
       <c r="D62" t="n">
-        <v>8.942136767004067</v>
+        <v>11.95522054844252</v>
       </c>
       <c r="E62" t="n">
-        <v>153.3117825201578</v>
+        <v>158.0495834532315</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6758859157562256</v>
+        <v>0.8333476185798645</v>
       </c>
       <c r="G62" t="n">
-        <v>0.4123972000088543</v>
+        <v>0.2319010000010167</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0008352872682735324</v>
+        <v>0.0009662620141170919</v>
       </c>
       <c r="I62" t="n">
-        <v>956.1273736338767</v>
+        <v>964.7328512355643</v>
       </c>
       <c r="J62" t="n">
-        <v>173.7371842984149</v>
+        <v>173.1913502113057</v>
       </c>
       <c r="K62" t="n">
-        <v>9.000641784596473</v>
+        <v>11.95531632114984</v>
       </c>
       <c r="L62" t="n">
-        <v>2.37778112932574e-06</v>
+        <v>9.988258398152539e-06</v>
       </c>
       <c r="M62" t="n">
-        <v>20.42540177825708</v>
+        <v>15.1417667580742</v>
       </c>
       <c r="N62" t="n">
-        <v>0.05850501759240601</v>
+        <v>9.577270731853105e-05</v>
       </c>
       <c r="O62" t="b">
         <v>1</v>
       </c>
       <c r="P62" t="n">
-        <v>0.9701135754585266</v>
+        <v>0.57620769739151</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.454364400124177</v>
+        <v>1.19765660000121</v>
       </c>
       <c r="R62" t="n">
-        <v>0.001407187082804739</v>
+        <v>0.001437750761397183</v>
       </c>
       <c r="S62" t="n">
-        <v>835.0184271843821</v>
+        <v>838.7820905439297</v>
       </c>
       <c r="T62" t="n">
-        <v>159.7677679547213</v>
+        <v>170.2021753806105</v>
       </c>
       <c r="U62" t="n">
-        <v>9.000561324843234</v>
+        <v>11.68553061984703</v>
       </c>
       <c r="V62" t="n">
-        <v>121.1089488272758</v>
+        <v>125.9507507033762</v>
       </c>
       <c r="W62" t="n">
-        <v>6.455985434563416</v>
+        <v>12.15259192737892</v>
       </c>
       <c r="X62" t="n">
-        <v>0.05842455783916733</v>
+        <v>0.2696899285954935</v>
       </c>
       <c r="Y62" t="b">
         <v>1</v>
@@ -5368,74 +5368,74 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>895.6931956810989</v>
+        <v>927.2347573008381</v>
       </c>
       <c r="D63" t="n">
-        <v>7.456793908548683</v>
+        <v>9.738030885550424</v>
       </c>
       <c r="E63" t="n">
-        <v>203.9415293593273</v>
+        <v>158.9384212940965</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6574357151985168</v>
+        <v>0.8342413306236267</v>
       </c>
       <c r="G63" t="n">
-        <v>0.2579375000204891</v>
+        <v>0.1955748999989737</v>
       </c>
       <c r="H63" t="n">
-        <v>0.001641420414671302</v>
+        <v>0.01450293231755495</v>
       </c>
       <c r="I63" t="n">
-        <v>929.0269687770967</v>
+        <v>933.9691992068756</v>
       </c>
       <c r="J63" t="n">
-        <v>203.9415293593273</v>
+        <v>163.2351149768217</v>
       </c>
       <c r="K63" t="n">
-        <v>9.000641547887318</v>
+        <v>10.39423143519245</v>
       </c>
       <c r="L63" t="n">
-        <v>33.3337730959978</v>
+        <v>6.734441906037546</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>4.296693682725248</v>
       </c>
       <c r="N63" t="n">
-        <v>1.543847639338635</v>
+        <v>0.6562005496420245</v>
       </c>
       <c r="O63" t="b">
         <v>1</v>
       </c>
       <c r="P63" t="n">
-        <v>0.7420944571495056</v>
+        <v>0.7622626423835754</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.242139499867335</v>
+        <v>0.6658169999991514</v>
       </c>
       <c r="R63" t="n">
-        <v>0.0002156924601877108</v>
+        <v>0.000796763168182224</v>
       </c>
       <c r="S63" t="n">
-        <v>929.6199216030675</v>
+        <v>841.5427863056591</v>
       </c>
       <c r="T63" t="n">
-        <v>203.5559540361875</v>
+        <v>166.2797083721771</v>
       </c>
       <c r="U63" t="n">
-        <v>9.000641672509747</v>
+        <v>9.664999892662786</v>
       </c>
       <c r="V63" t="n">
-        <v>33.92672592196857</v>
+        <v>85.69197099517896</v>
       </c>
       <c r="W63" t="n">
-        <v>0.3855753231397614</v>
+        <v>7.341287078080626</v>
       </c>
       <c r="X63" t="n">
-        <v>1.543847763961065</v>
+        <v>0.07303099288763804</v>
       </c>
       <c r="Y63" t="b">
         <v>1</v>
@@ -5451,70 +5451,70 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>997.5384536262509</v>
+        <v>938.6987905289761</v>
       </c>
       <c r="D64" t="n">
-        <v>6.217061970224169</v>
+        <v>4.094369333927407</v>
       </c>
       <c r="E64" t="n">
-        <v>217.1075412767862</v>
+        <v>200.7026873771016</v>
       </c>
       <c r="F64" t="n">
-        <v>0.7226564288139343</v>
+        <v>0.8001946806907654</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1043100999668241</v>
+        <v>0.0424299999995128</v>
       </c>
       <c r="H64" t="n">
-        <v>0.001416410086676478</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I64" t="n">
-        <v>997.5384536258931</v>
+        <v>938.69879052898</v>
       </c>
       <c r="J64" t="n">
-        <v>217.0942252206817</v>
+        <v>200.7026873771017</v>
       </c>
       <c r="K64" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="L64" t="n">
-        <v>3.577724783099256e-10</v>
+        <v>3.865352482534945e-12</v>
       </c>
       <c r="M64" t="n">
-        <v>0.01331605610440079</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="N64" t="n">
-        <v>2.783579809637994</v>
+        <v>4.906272445934755</v>
       </c>
       <c r="O64" t="b">
         <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>0.2949511706829071</v>
+        <v>0.9884545803070068</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.082346899900585</v>
+        <v>0.2067377999992459</v>
       </c>
       <c r="R64" t="n">
-        <v>0.000362639082595706</v>
+        <v>0.0001389217213727534</v>
       </c>
       <c r="S64" t="n">
-        <v>982.2066752914056</v>
+        <v>939.5303449365394</v>
       </c>
       <c r="T64" t="n">
-        <v>215.8887087749304</v>
+        <v>200.8275160107046</v>
       </c>
       <c r="U64" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V64" t="n">
-        <v>15.33177833484524</v>
+        <v>0.831554407563317</v>
       </c>
       <c r="W64" t="n">
-        <v>1.218832501855786</v>
+        <v>0.1248286336029878</v>
       </c>
       <c r="X64" t="n">
-        <v>2.783579809637994</v>
+        <v>4.906272445934755</v>
       </c>
       <c r="Y64" t="b">
         <v>1</v>
@@ -5526,74 +5526,74 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>945.8067125336677</v>
+        <v>854.5975405822235</v>
       </c>
       <c r="D65" t="n">
-        <v>5.345714920075298</v>
+        <v>8.545119477592145</v>
       </c>
       <c r="E65" t="n">
-        <v>202.7598332826755</v>
+        <v>210.8389043747138</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7307463884353638</v>
+        <v>0.8276062607765198</v>
       </c>
       <c r="G65" t="n">
-        <v>0.09948670002631843</v>
+        <v>0.1225571000013588</v>
       </c>
       <c r="H65" t="n">
-        <v>0.001032155007123947</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I65" t="n">
-        <v>951.9836653266326</v>
+        <v>924.4806723075287</v>
       </c>
       <c r="J65" t="n">
-        <v>202.7598332826754</v>
+        <v>210.8389043747138</v>
       </c>
       <c r="K65" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641649022834</v>
       </c>
       <c r="L65" t="n">
-        <v>6.176952792964926</v>
+        <v>69.88313172530525</v>
       </c>
       <c r="M65" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3.654926859786864</v>
+        <v>0.4555221714306885</v>
       </c>
       <c r="O65" t="b">
         <v>1</v>
       </c>
       <c r="P65" t="n">
-        <v>0.9771674275398254</v>
+        <v>0.8437613844871521</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.4680579998530447</v>
+        <v>0.4663670000009006</v>
       </c>
       <c r="R65" t="n">
-        <v>5.001795943826437e-05</v>
+        <v>0.0007422577473334968</v>
       </c>
       <c r="S65" t="n">
-        <v>945.994120295074</v>
+        <v>932.1227581002694</v>
       </c>
       <c r="T65" t="n">
-        <v>202.6844961224853</v>
+        <v>211.0860069107594</v>
       </c>
       <c r="U65" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641863904157</v>
       </c>
       <c r="V65" t="n">
-        <v>0.1874077614063481</v>
+        <v>77.52521751804591</v>
       </c>
       <c r="W65" t="n">
-        <v>0.07533716019014491</v>
+        <v>0.2471025360456736</v>
       </c>
       <c r="X65" t="n">
-        <v>3.654926859786864</v>
+        <v>0.4555223863120119</v>
       </c>
       <c r="Y65" t="b">
         <v>1</v>
@@ -5605,74 +5605,74 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>967.0058881332455</v>
+        <v>940.0682196056371</v>
       </c>
       <c r="D66" t="n">
-        <v>5.670345033041892</v>
+        <v>9.807608135251126</v>
       </c>
       <c r="E66" t="n">
-        <v>206.7896898427944</v>
+        <v>133.164629856318</v>
       </c>
       <c r="F66" t="n">
-        <v>0.7307463884353638</v>
+        <v>0.8342413306236267</v>
       </c>
       <c r="G66" t="n">
-        <v>0.08572329999879003</v>
+        <v>0.2527258999998594</v>
       </c>
       <c r="H66" t="n">
-        <v>0.001032155007123947</v>
+        <v>0.01395832654088736</v>
       </c>
       <c r="I66" t="n">
-        <v>967.0058881332461</v>
+        <v>939.7143323962179</v>
       </c>
       <c r="J66" t="n">
-        <v>206.7896898427958</v>
+        <v>163.0211355440055</v>
       </c>
       <c r="K66" t="n">
-        <v>9.000641779862162</v>
+        <v>10.39414075505328</v>
       </c>
       <c r="L66" t="n">
-        <v>5.684341886080801e-13</v>
+        <v>0.3538872094192129</v>
       </c>
       <c r="M66" t="n">
-        <v>1.4210854715202e-12</v>
+        <v>29.85650568768756</v>
       </c>
       <c r="N66" t="n">
-        <v>3.33029674682027</v>
+        <v>0.5865326198021563</v>
       </c>
       <c r="O66" t="b">
         <v>1</v>
       </c>
       <c r="P66" t="n">
-        <v>0.9361515641212463</v>
+        <v>0.9999763965606689</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.4489954998716712</v>
+        <v>0.4801877999998396</v>
       </c>
       <c r="R66" t="n">
-        <v>8.43124435050413e-05</v>
+        <v>0.001211823429912329</v>
       </c>
       <c r="S66" t="n">
-        <v>963.9930065074412</v>
+        <v>800.9001713402897</v>
       </c>
       <c r="T66" t="n">
-        <v>206.5721421579277</v>
+        <v>150.0005523879942</v>
       </c>
       <c r="U66" t="n">
-        <v>9.000641779862162</v>
+        <v>9.694933437081053</v>
       </c>
       <c r="V66" t="n">
-        <v>3.012881625804312</v>
+        <v>139.1680482653474</v>
       </c>
       <c r="W66" t="n">
-        <v>0.2175476848667017</v>
+        <v>16.83592253167623</v>
       </c>
       <c r="X66" t="n">
-        <v>3.33029674682027</v>
+        <v>0.112674698170073</v>
       </c>
       <c r="Y66" t="b">
         <v>1</v>
@@ -5688,70 +5688,70 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>862.5811093112261</v>
+        <v>898.5499725581047</v>
       </c>
       <c r="D67" t="n">
-        <v>7.068694089761317</v>
+        <v>6.853027509410801</v>
       </c>
       <c r="E67" t="n">
-        <v>198.7895470824437</v>
+        <v>188.198430366255</v>
       </c>
       <c r="F67" t="n">
-        <v>0.8506406545639038</v>
+        <v>0.6342471837997437</v>
       </c>
       <c r="G67" t="n">
-        <v>0.2488955999724567</v>
+        <v>0.1258354000001418</v>
       </c>
       <c r="H67" t="n">
-        <v>0.001641420414671302</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I67" t="n">
-        <v>929.0277995067916</v>
+        <v>924.4806673446582</v>
       </c>
       <c r="J67" t="n">
-        <v>198.7895676922058</v>
+        <v>188.1984303662551</v>
       </c>
       <c r="K67" t="n">
-        <v>9.000681979472796</v>
+        <v>9.000641761690584</v>
       </c>
       <c r="L67" t="n">
-        <v>66.44669019556545</v>
+        <v>25.93069478655343</v>
       </c>
       <c r="M67" t="n">
-        <v>2.060976214579568e-05</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N67" t="n">
-        <v>1.931987889711479</v>
+        <v>2.147614252279784</v>
       </c>
       <c r="O67" t="b">
         <v>1</v>
       </c>
       <c r="P67" t="n">
-        <v>0.9907901287078857</v>
+        <v>0.8768274188041687</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.380273799877614</v>
+        <v>0.3985108999986551</v>
       </c>
       <c r="R67" t="n">
-        <v>0.0004132807371206582</v>
+        <v>0.0003588769177440554</v>
       </c>
       <c r="S67" t="n">
-        <v>925.7358474703134</v>
+        <v>939.6358230472654</v>
       </c>
       <c r="T67" t="n">
-        <v>198.5602942725729</v>
+        <v>188.4741893158343</v>
       </c>
       <c r="U67" t="n">
-        <v>9.000641818505011</v>
+        <v>9.000641871806357</v>
       </c>
       <c r="V67" t="n">
-        <v>63.15473815908729</v>
+        <v>41.08585048916063</v>
       </c>
       <c r="W67" t="n">
-        <v>0.2292528098708431</v>
+        <v>0.2757589495792274</v>
       </c>
       <c r="X67" t="n">
-        <v>1.931947728743694</v>
+        <v>2.147614362395556</v>
       </c>
       <c r="Y67" t="b">
         <v>1</v>
@@ -5763,74 +5763,74 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>945.8972918235561</v>
+        <v>953.4399911766055</v>
       </c>
       <c r="D68" t="n">
-        <v>11.51762446884641</v>
+        <v>3.692187777550672</v>
       </c>
       <c r="E68" t="n">
-        <v>148.010106484674</v>
+        <v>202.1025006005814</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6555349826812744</v>
+        <v>0.8173863291740417</v>
       </c>
       <c r="G68" t="n">
-        <v>0.3526365000288934</v>
+        <v>0.02904699999999139</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0008354719611816108</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I68" t="n">
-        <v>945.8972875523858</v>
+        <v>953.439991176548</v>
       </c>
       <c r="J68" t="n">
-        <v>173.7371880071923</v>
+        <v>202.1025006005814</v>
       </c>
       <c r="K68" t="n">
-        <v>11.51756544029782</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L68" t="n">
-        <v>4.271170269021241e-06</v>
+        <v>5.752553988713771e-11</v>
       </c>
       <c r="M68" t="n">
-        <v>25.72708152251832</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N68" t="n">
-        <v>5.902854859485274e-05</v>
+        <v>5.30845400231149</v>
       </c>
       <c r="O68" t="b">
         <v>1</v>
       </c>
       <c r="P68" t="n">
-        <v>0.9875911474227905</v>
+        <v>0.9986415505409241</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.621496599866077</v>
+        <v>0.1630648999998812</v>
       </c>
       <c r="R68" t="n">
-        <v>0.001751977950334549</v>
+        <v>0.0001233608345501125</v>
       </c>
       <c r="S68" t="n">
-        <v>808.8191597698816</v>
+        <v>953.952865041337</v>
       </c>
       <c r="T68" t="n">
-        <v>155.2320504368665</v>
+        <v>202.2075706657974</v>
       </c>
       <c r="U68" t="n">
-        <v>11.31141396413199</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V68" t="n">
-        <v>137.0781320536745</v>
+        <v>0.5128738647314321</v>
       </c>
       <c r="W68" t="n">
-        <v>7.221943952192532</v>
+        <v>0.1050700652159549</v>
       </c>
       <c r="X68" t="n">
-        <v>0.2062105047144218</v>
+        <v>5.30845400231149</v>
       </c>
       <c r="Y68" t="b">
         <v>1</v>
@@ -5842,74 +5842,74 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>947.4829902238973</v>
+        <v>893.6151260554346</v>
       </c>
       <c r="D69" t="n">
-        <v>10.66889407103901</v>
+        <v>6.063577599875421</v>
       </c>
       <c r="E69" t="n">
-        <v>120.4383965880583</v>
+        <v>195.5242698740448</v>
       </c>
       <c r="F69" t="n">
-        <v>0.6767300963401794</v>
+        <v>0.6838685870170593</v>
       </c>
       <c r="G69" t="n">
-        <v>0.316197499865666</v>
+        <v>0.1367686999983562</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0008354719611816108</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I69" t="n">
-        <v>935.5381755079873</v>
+        <v>924.4806673313456</v>
       </c>
       <c r="J69" t="n">
-        <v>173.7378496309283</v>
+        <v>195.5242698740448</v>
       </c>
       <c r="K69" t="n">
-        <v>10.76515973796006</v>
+        <v>9.000641722785351</v>
       </c>
       <c r="L69" t="n">
-        <v>11.94481471591007</v>
+        <v>30.86554127591091</v>
       </c>
       <c r="M69" t="n">
-        <v>53.29945304287</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>0.0962656669210542</v>
+        <v>2.937064122909931</v>
       </c>
       <c r="O69" t="b">
         <v>1</v>
       </c>
       <c r="P69" t="n">
-        <v>0.9999669790267944</v>
+        <v>0.9543607831001282</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.750522200018167</v>
+        <v>0.3802390000000742</v>
       </c>
       <c r="R69" t="n">
-        <v>0.001739119994454086</v>
+        <v>0.0003933592233806849</v>
       </c>
       <c r="S69" t="n">
-        <v>805.1886734035901</v>
+        <v>937.8599054555471</v>
       </c>
       <c r="T69" t="n">
-        <v>150.0005521274128</v>
+        <v>195.8775230933143</v>
       </c>
       <c r="U69" t="n">
-        <v>10.51138908210346</v>
+        <v>9.000641849397857</v>
       </c>
       <c r="V69" t="n">
-        <v>142.2943168203072</v>
+        <v>44.24477940011241</v>
       </c>
       <c r="W69" t="n">
-        <v>29.56215553935448</v>
+        <v>0.3532532192695612</v>
       </c>
       <c r="X69" t="n">
-        <v>0.1575049889355444</v>
+        <v>2.937064249522436</v>
       </c>
       <c r="Y69" t="b">
         <v>1</v>
@@ -5921,74 +5921,74 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>944.4980539404664</v>
+        <v>833.1191433149253</v>
       </c>
       <c r="D70" t="n">
-        <v>6.246501148709108</v>
+        <v>7.630198787376239</v>
       </c>
       <c r="E70" t="n">
-        <v>199.1020091497184</v>
+        <v>201.5815297457368</v>
       </c>
       <c r="F70" t="n">
-        <v>0.7307463884353638</v>
+        <v>0.8120322227478027</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0795182001311332</v>
+        <v>0.1316437000004953</v>
       </c>
       <c r="H70" t="n">
-        <v>0.001059164758771658</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I70" t="n">
-        <v>944.49805394046</v>
+        <v>924.4806711702983</v>
       </c>
       <c r="J70" t="n">
-        <v>199.1020091497184</v>
+        <v>201.5815297457368</v>
       </c>
       <c r="K70" t="n">
-        <v>9.000641779862162</v>
+        <v>9.00064165804284</v>
       </c>
       <c r="L70" t="n">
-        <v>6.480149750132114e-12</v>
+        <v>91.36152785537297</v>
       </c>
       <c r="M70" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.754140631153055</v>
+        <v>1.370442870666601</v>
       </c>
       <c r="O70" t="b">
         <v>1</v>
       </c>
       <c r="P70" t="n">
-        <v>0.738786518573761</v>
+        <v>0.9377415180206299</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.6165701998397708</v>
+        <v>0.468416800000341</v>
       </c>
       <c r="R70" t="n">
-        <v>4.660089325625449e-05</v>
+        <v>0.0009844875894486904</v>
       </c>
       <c r="S70" t="n">
-        <v>944.7935491651274</v>
+        <v>930.6286171338442</v>
       </c>
       <c r="T70" t="n">
-        <v>199.0912042849029</v>
+        <v>201.8757595409537</v>
       </c>
       <c r="U70" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641816894808</v>
       </c>
       <c r="V70" t="n">
-        <v>0.2954952246609537</v>
+        <v>97.50947381891888</v>
       </c>
       <c r="W70" t="n">
-        <v>0.01080486481544085</v>
+        <v>0.294229795216836</v>
       </c>
       <c r="X70" t="n">
-        <v>2.754140631153055</v>
+        <v>1.370443029518569</v>
       </c>
       <c r="Y70" t="b">
         <v>1</v>
@@ -6000,74 +6000,74 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>907.2141165346436</v>
+        <v>939.3143389700824</v>
       </c>
       <c r="D71" t="n">
-        <v>11.4538571561289</v>
+        <v>6.00391592587845</v>
       </c>
       <c r="E71" t="n">
-        <v>140.7149458954127</v>
+        <v>212.8995855811849</v>
       </c>
       <c r="F71" t="n">
-        <v>0.6217793226242065</v>
+        <v>0.8140485286712646</v>
       </c>
       <c r="G71" t="n">
-        <v>0.4370387999806553</v>
+        <v>0.03057059999991907</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0008331580320373178</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I71" t="n">
-        <v>910.6221367311381</v>
+        <v>939.3143389700804</v>
       </c>
       <c r="J71" t="n">
-        <v>173.7371839394637</v>
+        <v>212.8995855811851</v>
       </c>
       <c r="K71" t="n">
-        <v>11.45371597580618</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L71" t="n">
-        <v>3.408020196494476</v>
+        <v>2.046363078989089e-12</v>
       </c>
       <c r="M71" t="n">
-        <v>33.02223804405099</v>
+        <v>2.557953848736361e-13</v>
       </c>
       <c r="N71" t="n">
-        <v>0.0001411803227231445</v>
+        <v>2.996725853983713</v>
       </c>
       <c r="O71" t="b">
         <v>1</v>
       </c>
       <c r="P71" t="n">
-        <v>0.9966008067131042</v>
+        <v>0.5411326289176941</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.115213300101459</v>
+        <v>0.2038587000006373</v>
       </c>
       <c r="R71" t="n">
-        <v>0.001994211226701736</v>
+        <v>0.0001060059221345</v>
       </c>
       <c r="S71" t="n">
-        <v>800.0000229883224</v>
+        <v>939.9490512839977</v>
       </c>
       <c r="T71" t="n">
-        <v>150.0005528821134</v>
+        <v>213.0054460729478</v>
       </c>
       <c r="U71" t="n">
-        <v>11.2189462543591</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V71" t="n">
-        <v>107.2140935463212</v>
+        <v>0.6347123139153155</v>
       </c>
       <c r="W71" t="n">
-        <v>9.285606986700714</v>
+        <v>0.1058604917629111</v>
       </c>
       <c r="X71" t="n">
-        <v>0.2349109017698012</v>
+        <v>2.996725853983713</v>
       </c>
       <c r="Y71" t="b">
         <v>1</v>
@@ -6083,70 +6083,70 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>831.4542015270936</v>
+        <v>884.0525024462436</v>
       </c>
       <c r="D72" t="n">
-        <v>6.817806106316048</v>
+        <v>6.714681683110493</v>
       </c>
       <c r="E72" t="n">
-        <v>185.0178315093528</v>
+        <v>188.9420095987055</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7725018262863159</v>
+        <v>0.7708748579025269</v>
       </c>
       <c r="G72" t="n">
-        <v>0.2325774999335408</v>
+        <v>0.118660699999964</v>
       </c>
       <c r="H72" t="n">
-        <v>0.002008212730288506</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I72" t="n">
-        <v>924.8605801276852</v>
+        <v>924.480668200554</v>
       </c>
       <c r="J72" t="n">
-        <v>185.0178314596837</v>
+        <v>188.9420095987055</v>
       </c>
       <c r="K72" t="n">
-        <v>9.000690749593387</v>
+        <v>9.000641717438157</v>
       </c>
       <c r="L72" t="n">
-        <v>93.40637860059167</v>
+        <v>40.42816575431038</v>
       </c>
       <c r="M72" t="n">
-        <v>4.966906885783828e-08</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N72" t="n">
-        <v>2.182884643277339</v>
+        <v>2.285960034327664</v>
       </c>
       <c r="O72" t="b">
         <v>1</v>
       </c>
       <c r="P72" t="n">
-        <v>0.9936195015907288</v>
+        <v>0.9761733412742615</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.584618499968201</v>
+        <v>0.4292052999990119</v>
       </c>
       <c r="R72" t="n">
-        <v>0.0007275063544511795</v>
+        <v>0.0004801404429599643</v>
       </c>
       <c r="S72" t="n">
-        <v>923.7235066213619</v>
+        <v>937.4819987153314</v>
       </c>
       <c r="T72" t="n">
-        <v>185.9190082622438</v>
+        <v>189.3129014786839</v>
       </c>
       <c r="U72" t="n">
-        <v>9.00064174870929</v>
+        <v>9.00064180984058</v>
       </c>
       <c r="V72" t="n">
-        <v>92.26930509426836</v>
+        <v>53.42949626908785</v>
       </c>
       <c r="W72" t="n">
-        <v>0.90117675289099</v>
+        <v>0.3708918799784158</v>
       </c>
       <c r="X72" t="n">
-        <v>2.182835642393242</v>
+        <v>2.285960126730087</v>
       </c>
       <c r="Y72" t="b">
         <v>1</v>
@@ -6158,74 +6158,74 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>931.7308002100249</v>
+        <v>929.2087438988716</v>
       </c>
       <c r="D73" t="n">
-        <v>4.965118508521456</v>
+        <v>12.27835645211013</v>
       </c>
       <c r="E73" t="n">
-        <v>187.2320079581123</v>
+        <v>153.010881866181</v>
       </c>
       <c r="F73" t="n">
-        <v>0.6949499249458313</v>
+        <v>0.8265721797943115</v>
       </c>
       <c r="G73" t="n">
-        <v>0.1139036999084055</v>
+        <v>0.1944313999993028</v>
       </c>
       <c r="H73" t="n">
-        <v>0.001059164758771658</v>
+        <v>0.001156892394647002</v>
       </c>
       <c r="I73" t="n">
-        <v>931.7308002101901</v>
+        <v>929.2087435860079</v>
       </c>
       <c r="J73" t="n">
-        <v>187.2320079581115</v>
+        <v>173.1913510493296</v>
       </c>
       <c r="K73" t="n">
-        <v>9.000641779862162</v>
+        <v>12.27835645704801</v>
       </c>
       <c r="L73" t="n">
-        <v>1.651869752095081e-10</v>
+        <v>3.128636762994574e-07</v>
       </c>
       <c r="M73" t="n">
-        <v>8.242295734817162e-13</v>
+        <v>20.18046918314857</v>
       </c>
       <c r="N73" t="n">
-        <v>4.035523271340707</v>
+        <v>4.937881215028028e-09</v>
       </c>
       <c r="O73" t="b">
         <v>1</v>
       </c>
       <c r="P73" t="n">
-        <v>0.9562298059463501</v>
+        <v>0.9238184690475464</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.5066314998548478</v>
+        <v>1.052046400000108</v>
       </c>
       <c r="R73" t="n">
-        <v>8.435447671217844e-05</v>
+        <v>0.00141736795194447</v>
       </c>
       <c r="S73" t="n">
-        <v>933.3777122287474</v>
+        <v>807.6890648975353</v>
       </c>
       <c r="T73" t="n">
-        <v>187.4302782474072</v>
+        <v>162.6786125842324</v>
       </c>
       <c r="U73" t="n">
-        <v>9.000641779862162</v>
+        <v>12.09898410985965</v>
       </c>
       <c r="V73" t="n">
-        <v>1.64691201872256</v>
+        <v>121.5196790013363</v>
       </c>
       <c r="W73" t="n">
-        <v>0.198270289294868</v>
+        <v>9.667730718051388</v>
       </c>
       <c r="X73" t="n">
-        <v>4.035523271340707</v>
+        <v>0.179372342250474</v>
       </c>
       <c r="Y73" t="b">
         <v>1</v>
@@ -6237,74 +6237,74 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>887.8886139952617</v>
+        <v>971.2530929094758</v>
       </c>
       <c r="D74" t="n">
-        <v>6.776869402268809</v>
+        <v>10.70422964915671</v>
       </c>
       <c r="E74" t="n">
-        <v>189.111925958194</v>
+        <v>127.2548136260511</v>
       </c>
       <c r="F74" t="n">
-        <v>0.7249653935432434</v>
+        <v>0.8341188430786133</v>
       </c>
       <c r="G74" t="n">
-        <v>0.2437248001806438</v>
+        <v>0.318491100000756</v>
       </c>
       <c r="H74" t="n">
-        <v>0.001641420414671302</v>
+        <v>0.01866349019110203</v>
       </c>
       <c r="I74" t="n">
-        <v>929.026967757634</v>
+        <v>939.7170909050923</v>
       </c>
       <c r="J74" t="n">
-        <v>189.111925958194</v>
+        <v>163.0038996273458</v>
       </c>
       <c r="K74" t="n">
-        <v>9.000641636641358</v>
+        <v>11.94922366345705</v>
       </c>
       <c r="L74" t="n">
-        <v>41.13835376237228</v>
+        <v>31.53600200438348</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>35.74908600129469</v>
       </c>
       <c r="N74" t="n">
-        <v>2.223772234372549</v>
+        <v>1.244994014300339</v>
       </c>
       <c r="O74" t="b">
         <v>1</v>
       </c>
       <c r="P74" t="n">
-        <v>0.8822795152664185</v>
+        <v>0.9999942779541016</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.606696299975738</v>
+        <v>0.5378185999998095</v>
       </c>
       <c r="R74" t="n">
-        <v>0.0002743584918789566</v>
+        <v>0.002393670147284865</v>
       </c>
       <c r="S74" t="n">
-        <v>928.2509341161606</v>
+        <v>800.0000604110494</v>
       </c>
       <c r="T74" t="n">
-        <v>189.451085303586</v>
+        <v>150.000552831106</v>
       </c>
       <c r="U74" t="n">
-        <v>9.000641767290265</v>
+        <v>10.28638617194319</v>
       </c>
       <c r="V74" t="n">
-        <v>40.36232012089886</v>
+        <v>171.2530324984264</v>
       </c>
       <c r="W74" t="n">
-        <v>0.3391593453920052</v>
+        <v>22.7457392050549</v>
       </c>
       <c r="X74" t="n">
-        <v>2.223772365021456</v>
+        <v>0.4178434772135144</v>
       </c>
       <c r="Y74" t="b">
         <v>1</v>
@@ -6316,74 +6316,74 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>959.4257991206367</v>
+        <v>882.9168039349611</v>
       </c>
       <c r="D75" t="n">
-        <v>6.331033396665713</v>
+        <v>8.944751373635901</v>
       </c>
       <c r="E75" t="n">
-        <v>189.5268645747033</v>
+        <v>208.2526466964262</v>
       </c>
       <c r="F75" t="n">
-        <v>0.7307463884353638</v>
+        <v>0.5638843178749084</v>
       </c>
       <c r="G75" t="n">
-        <v>0.112019999884069</v>
+        <v>0.1079219999992347</v>
       </c>
       <c r="H75" t="n">
-        <v>0.001032155007123947</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I75" t="n">
-        <v>959.4257991206371</v>
+        <v>924.4806681515233</v>
       </c>
       <c r="J75" t="n">
-        <v>189.5268645747033</v>
+        <v>208.2526466964262</v>
       </c>
       <c r="K75" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641618845385</v>
       </c>
       <c r="L75" t="n">
-        <v>3.410605131648481e-13</v>
+        <v>41.56386421656225</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.669608383196449</v>
+        <v>0.05589024520948449</v>
       </c>
       <c r="O75" t="b">
         <v>1</v>
       </c>
       <c r="P75" t="n">
-        <v>0.6686036586761475</v>
+        <v>0.4321063160896301</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.5333283999934793</v>
+        <v>0.3643185000000813</v>
       </c>
       <c r="R75" t="n">
-        <v>7.241316052386537e-05</v>
+        <v>0.0004688234766945243</v>
       </c>
       <c r="S75" t="n">
-        <v>957.6483882696963</v>
+        <v>935.1813922688189</v>
       </c>
       <c r="T75" t="n">
-        <v>189.7069072562254</v>
+        <v>208.40787806084</v>
       </c>
       <c r="U75" t="n">
-        <v>9.000641779862162</v>
+        <v>9.021256659829975</v>
       </c>
       <c r="V75" t="n">
-        <v>1.777410850940441</v>
+        <v>52.26458833385777</v>
       </c>
       <c r="W75" t="n">
-        <v>0.1800426815220817</v>
+        <v>0.1552313644138223</v>
       </c>
       <c r="X75" t="n">
-        <v>2.669608383196449</v>
+        <v>0.07650528619407382</v>
       </c>
       <c r="Y75" t="b">
         <v>1</v>
@@ -6399,70 +6399,70 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>872.7046428715975</v>
+        <v>877.3692237215081</v>
       </c>
       <c r="D76" t="n">
-        <v>6.7207164120645</v>
+        <v>9.000114999317264</v>
       </c>
       <c r="E76" t="n">
-        <v>212.4005522397584</v>
+        <v>193.2959101989771</v>
       </c>
       <c r="F76" t="n">
-        <v>0.8526367545127869</v>
+        <v>0.5507853031158447</v>
       </c>
       <c r="G76" t="n">
-        <v>0.2491564000956714</v>
+        <v>0.1162901999996393</v>
       </c>
       <c r="H76" t="n">
-        <v>0.001640764763578773</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I76" t="n">
-        <v>929.0269678100341</v>
+        <v>924.4806716588629</v>
       </c>
       <c r="J76" t="n">
-        <v>212.4006107348139</v>
+        <v>193.2959101989771</v>
       </c>
       <c r="K76" t="n">
-        <v>9.000641549142101</v>
+        <v>9.000641614529927</v>
       </c>
       <c r="L76" t="n">
-        <v>56.32232493843662</v>
+        <v>47.1114479373548</v>
       </c>
       <c r="M76" t="n">
-        <v>5.849505541277722e-05</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.2799251370776</v>
+        <v>0.000526615212663728</v>
       </c>
       <c r="O76" t="b">
         <v>1</v>
       </c>
       <c r="P76" t="n">
-        <v>0.988240122795105</v>
+        <v>0.6445889472961426</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.5745353999082</v>
+        <v>0.3655375999987882</v>
       </c>
       <c r="R76" t="n">
-        <v>0.0003997681487817317</v>
+        <v>0.0005228730733506382</v>
       </c>
       <c r="S76" t="n">
-        <v>928.878551611837</v>
+        <v>935.2168060001291</v>
       </c>
       <c r="T76" t="n">
-        <v>210.8789315253923</v>
+        <v>193.7231703718294</v>
       </c>
       <c r="U76" t="n">
-        <v>9.0006411952403</v>
+        <v>9.077597820249409</v>
       </c>
       <c r="V76" t="n">
-        <v>56.17390874023954</v>
+        <v>57.84758227862096</v>
       </c>
       <c r="W76" t="n">
-        <v>1.521620714366122</v>
+        <v>0.4272601728523</v>
       </c>
       <c r="X76" t="n">
-        <v>2.2799247831758</v>
+        <v>0.0774828209321452</v>
       </c>
       <c r="Y76" t="b">
         <v>1</v>
@@ -6474,74 +6474,74 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>847.1931358488914</v>
+        <v>939.0208991743779</v>
       </c>
       <c r="D77" t="n">
-        <v>8.499112741453565</v>
+        <v>10.68189274023577</v>
       </c>
       <c r="E77" t="n">
-        <v>214.2980575220417</v>
+        <v>136.4872994500552</v>
       </c>
       <c r="F77" t="n">
-        <v>0.7607967853546143</v>
+        <v>0.8342413306236267</v>
       </c>
       <c r="G77" t="n">
-        <v>0.2742709999438375</v>
+        <v>0.1276684000004025</v>
       </c>
       <c r="H77" t="n">
-        <v>0.002007473492994905</v>
+        <v>0.002018802100792527</v>
       </c>
       <c r="I77" t="n">
-        <v>924.8594770251983</v>
+        <v>917.7887190746554</v>
       </c>
       <c r="J77" t="n">
-        <v>214.2981243889143</v>
+        <v>173.1945262499984</v>
       </c>
       <c r="K77" t="n">
-        <v>9.000641607794503</v>
+        <v>12.75145686751307</v>
       </c>
       <c r="L77" t="n">
-        <v>77.6663411763069</v>
+        <v>21.23218009972243</v>
       </c>
       <c r="M77" t="n">
-        <v>6.686687265755609e-05</v>
+        <v>36.70722679994313</v>
       </c>
       <c r="N77" t="n">
-        <v>0.5015288663409372</v>
+        <v>2.069564127277294</v>
       </c>
       <c r="O77" t="b">
         <v>1</v>
       </c>
       <c r="P77" t="n">
-        <v>0.9796766638755798</v>
+        <v>0.9998886585235596</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.59867179999128</v>
+        <v>0.5982686999996076</v>
       </c>
       <c r="R77" t="n">
-        <v>0.0005997993866913021</v>
+        <v>0.002344639506191015</v>
       </c>
       <c r="S77" t="n">
-        <v>927.1962550936013</v>
+        <v>800.0000435648012</v>
       </c>
       <c r="T77" t="n">
-        <v>211.9615461255205</v>
+        <v>150.0005529379655</v>
       </c>
       <c r="U77" t="n">
-        <v>9.000641043423281</v>
+        <v>10.27270873411296</v>
       </c>
       <c r="V77" t="n">
-        <v>80.00311924470986</v>
+        <v>139.0208556095766</v>
       </c>
       <c r="W77" t="n">
-        <v>2.336511396521132</v>
+        <v>13.51325348791022</v>
       </c>
       <c r="X77" t="n">
-        <v>0.5015283019697154</v>
+        <v>0.4091840061228105</v>
       </c>
       <c r="Y77" t="b">
         <v>1</v>
@@ -6557,70 +6557,70 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>859.7074679282812</v>
+        <v>884.6688868673981</v>
       </c>
       <c r="D78" t="n">
-        <v>6.821419512121432</v>
+        <v>6.943234626599951</v>
       </c>
       <c r="E78" t="n">
-        <v>203.3974169651172</v>
+        <v>204.6900831043484</v>
       </c>
       <c r="F78" t="n">
-        <v>0.8506406545639038</v>
+        <v>0.8440181612968445</v>
       </c>
       <c r="G78" t="n">
-        <v>0.2243352001532912</v>
+        <v>0.09701029999996535</v>
       </c>
       <c r="H78" t="n">
-        <v>0.00200818688608706</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I78" t="n">
-        <v>924.8604949812226</v>
+        <v>924.4809565202777</v>
       </c>
       <c r="J78" t="n">
-        <v>203.3974162844619</v>
+        <v>204.6900831043484</v>
       </c>
       <c r="K78" t="n">
-        <v>9.000600720611482</v>
+        <v>9.000641544526271</v>
       </c>
       <c r="L78" t="n">
-        <v>65.15302705294141</v>
+        <v>39.81206965287959</v>
       </c>
       <c r="M78" t="n">
-        <v>6.80655233509242e-07</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="N78" t="n">
-        <v>2.17918120849005</v>
+        <v>2.05740691792632</v>
       </c>
       <c r="O78" t="b">
         <v>1</v>
       </c>
       <c r="P78" t="n">
-        <v>0.9942852854728699</v>
+        <v>0.968358039855957</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.619586500106379</v>
+        <v>0.4506753999994544</v>
       </c>
       <c r="R78" t="n">
-        <v>0.0004391717084217817</v>
+        <v>0.000460146926343441</v>
       </c>
       <c r="S78" t="n">
-        <v>925.9430029616933</v>
+        <v>935.7938081251889</v>
       </c>
       <c r="T78" t="n">
-        <v>202.7527942851561</v>
+        <v>204.833273231664</v>
       </c>
       <c r="U78" t="n">
-        <v>9.000641617595038</v>
+        <v>9.000641713436492</v>
       </c>
       <c r="V78" t="n">
-        <v>66.23553503341213</v>
+        <v>51.12492125779079</v>
       </c>
       <c r="W78" t="n">
-        <v>0.6446226799610599</v>
+        <v>0.1431901273155916</v>
       </c>
       <c r="X78" t="n">
-        <v>2.179222105473606</v>
+        <v>2.057407086836541</v>
       </c>
       <c r="Y78" t="b">
         <v>1</v>
@@ -6632,74 +6632,74 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Z_Scratch</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>838.7925819789939</v>
+        <v>932.2204333806808</v>
       </c>
       <c r="D79" t="n">
-        <v>7.235527935875294</v>
+        <v>13.03981855565778</v>
       </c>
       <c r="E79" t="n">
-        <v>196.4741261679814</v>
+        <v>191.1558959956488</v>
       </c>
       <c r="F79" t="n">
-        <v>0.8509666323661804</v>
+        <v>0.6110718250274658</v>
       </c>
       <c r="G79" t="n">
-        <v>0.2566208001226187</v>
+        <v>0.1527317000000039</v>
       </c>
       <c r="H79" t="n">
-        <v>0.001641420414671302</v>
+        <v>0.002067800611257553</v>
       </c>
       <c r="I79" t="n">
-        <v>929.0275965722744</v>
+        <v>924.0382220847861</v>
       </c>
       <c r="J79" t="n">
-        <v>196.4741288774167</v>
+        <v>187.1332932452968</v>
       </c>
       <c r="K79" t="n">
-        <v>9.000682785503855</v>
+        <v>12.50750790625518</v>
       </c>
       <c r="L79" t="n">
-        <v>90.23501459328054</v>
+        <v>8.182211295894717</v>
       </c>
       <c r="M79" t="n">
-        <v>2.70943527880263e-06</v>
+        <v>4.022602750352064</v>
       </c>
       <c r="N79" t="n">
-        <v>1.765154849628561</v>
+        <v>0.5323106494025964</v>
       </c>
       <c r="O79" t="b">
         <v>1</v>
       </c>
       <c r="P79" t="n">
-        <v>0.9930439591407776</v>
+        <v>0.08337151259183884</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.675785699859262</v>
+        <v>1.100767100000667</v>
       </c>
       <c r="R79" t="n">
-        <v>0.0005860047531314194</v>
+        <v>0.001358153065666556</v>
       </c>
       <c r="S79" t="n">
-        <v>923.9479840287044</v>
+        <v>950.6380545289414</v>
       </c>
       <c r="T79" t="n">
-        <v>196.3653760364051</v>
+        <v>185.1892156924482</v>
       </c>
       <c r="U79" t="n">
-        <v>9.000641793966926</v>
+        <v>12.17256584643809</v>
       </c>
       <c r="V79" t="n">
-        <v>85.15540204971046</v>
+        <v>18.41762114826065</v>
       </c>
       <c r="W79" t="n">
-        <v>0.1087501315762438</v>
+        <v>5.966680303200633</v>
       </c>
       <c r="X79" t="n">
-        <v>1.765113858091632</v>
+        <v>0.8672527092196862</v>
       </c>
       <c r="Y79" t="b">
         <v>1</v>
@@ -6711,74 +6711,74 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>934.0645962626772</v>
+        <v>972.4393547485565</v>
       </c>
       <c r="D80" t="n">
-        <v>6.569227270143569</v>
+        <v>10.29519839564596</v>
       </c>
       <c r="E80" t="n">
-        <v>200.9181426360591</v>
+        <v>151.529578268895</v>
       </c>
       <c r="F80" t="n">
-        <v>0.7307463884353638</v>
+        <v>0.8341188430786133</v>
       </c>
       <c r="G80" t="n">
-        <v>0.1003854000009596</v>
+        <v>0.2394552000005206</v>
       </c>
       <c r="H80" t="n">
-        <v>0.001059164758771658</v>
+        <v>0.0008777803741395473</v>
       </c>
       <c r="I80" t="n">
-        <v>934.0645962626883</v>
+        <v>972.4548319337069</v>
       </c>
       <c r="J80" t="n">
-        <v>200.9181426360591</v>
+        <v>173.1947969893786</v>
       </c>
       <c r="K80" t="n">
-        <v>9.000641779862162</v>
+        <v>10.29533756016274</v>
       </c>
       <c r="L80" t="n">
-        <v>1.102762325899675e-11</v>
+        <v>0.01547718515041652</v>
       </c>
       <c r="M80" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>21.66521872048358</v>
       </c>
       <c r="N80" t="n">
-        <v>2.431414509718594</v>
+        <v>0.000139164516779644</v>
       </c>
       <c r="O80" t="b">
         <v>1</v>
       </c>
       <c r="P80" t="n">
-        <v>0.4573295116424561</v>
+        <v>0.9639032483100891</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.5052175999153405</v>
+        <v>0.8599228999992192</v>
       </c>
       <c r="R80" t="n">
-        <v>5.69809417356737e-05</v>
+        <v>0.00126209924928844</v>
       </c>
       <c r="S80" t="n">
-        <v>935.5858265671992</v>
+        <v>829.1770962181605</v>
       </c>
       <c r="T80" t="n">
-        <v>200.8673151076025</v>
+        <v>162.0995596863681</v>
       </c>
       <c r="U80" t="n">
-        <v>9.000641779862162</v>
+        <v>10.16698584857551</v>
       </c>
       <c r="V80" t="n">
-        <v>1.521230304521964</v>
+        <v>143.262258530396</v>
       </c>
       <c r="W80" t="n">
-        <v>0.05082752845663663</v>
+        <v>10.56998141747312</v>
       </c>
       <c r="X80" t="n">
-        <v>2.431414509718594</v>
+        <v>0.1282125470704507</v>
       </c>
       <c r="Y80" t="b">
         <v>1</v>
@@ -6790,74 +6790,74 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1000.530798651601</v>
+        <v>858.9869051172776</v>
       </c>
       <c r="D81" t="n">
-        <v>10.80129278338204</v>
+        <v>6.821027048326163</v>
       </c>
       <c r="E81" t="n">
-        <v>157.8993784828023</v>
+        <v>185.9448383803137</v>
       </c>
       <c r="F81" t="n">
-        <v>0.6631425023078918</v>
+        <v>0.839372456073761</v>
       </c>
       <c r="G81" t="n">
-        <v>0.5334628999698907</v>
+        <v>0.1136040000001231</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0008324514492414892</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I81" t="n">
-        <v>999.9999806378897</v>
+        <v>924.4806705751859</v>
       </c>
       <c r="J81" t="n">
-        <v>173.7371866221566</v>
+        <v>185.9448383803138</v>
       </c>
       <c r="K81" t="n">
-        <v>10.80139311912626</v>
+        <v>9.000641641022909</v>
       </c>
       <c r="L81" t="n">
-        <v>0.5308180137116096</v>
+        <v>65.49376545790824</v>
       </c>
       <c r="M81" t="n">
-        <v>15.83780813935428</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="N81" t="n">
-        <v>0.0001003357442197483</v>
+        <v>2.179614592696746</v>
       </c>
       <c r="O81" t="b">
         <v>1</v>
       </c>
       <c r="P81" t="n">
-        <v>0.1600920110940933</v>
+        <v>0.9914631247520447</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.787225500214845</v>
+        <v>0.3739974000000075</v>
       </c>
       <c r="R81" t="n">
-        <v>0.001763349748216569</v>
+        <v>0.0007205067668110132</v>
       </c>
       <c r="S81" t="n">
-        <v>839.2586338246971</v>
+        <v>935.08827386296</v>
       </c>
       <c r="T81" t="n">
-        <v>166.5247036060972</v>
+        <v>186.4921710164753</v>
       </c>
       <c r="U81" t="n">
-        <v>10.64395722779983</v>
+        <v>9.000641864383589</v>
       </c>
       <c r="V81" t="n">
-        <v>161.2721648269043</v>
+        <v>76.10136874568241</v>
       </c>
       <c r="W81" t="n">
-        <v>8.625325123294886</v>
+        <v>0.5473326361615989</v>
       </c>
       <c r="X81" t="n">
-        <v>0.1573355555822094</v>
+        <v>2.179614816057425</v>
       </c>
       <c r="Y81" t="b">
         <v>1</v>
@@ -6873,70 +6873,70 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>916.9964215899955</v>
+        <v>964.3146848234168</v>
       </c>
       <c r="D82" t="n">
-        <v>4.061906490210131</v>
+        <v>4.070486283664396</v>
       </c>
       <c r="E82" t="n">
-        <v>202.4842632135048</v>
+        <v>206.7471843876719</v>
       </c>
       <c r="F82" t="n">
-        <v>0.5444756150245667</v>
+        <v>0.81343674659729</v>
       </c>
       <c r="G82" t="n">
-        <v>0.1345057999715209</v>
+        <v>0.048921400000836</v>
       </c>
       <c r="H82" t="n">
-        <v>0.001054888241924345</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I82" t="n">
-        <v>915.9952042607318</v>
+        <v>964.314684894108</v>
       </c>
       <c r="J82" t="n">
-        <v>202.4841960292941</v>
+        <v>206.7471843876693</v>
       </c>
       <c r="K82" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="L82" t="n">
-        <v>1.001217329263682</v>
+        <v>7.06912715031649e-08</v>
       </c>
       <c r="M82" t="n">
-        <v>6.718421073514946e-05</v>
+        <v>2.643218977027573e-12</v>
       </c>
       <c r="N82" t="n">
-        <v>4.938735289652032</v>
+        <v>4.930155496197766</v>
       </c>
       <c r="O82" t="b">
         <v>1</v>
       </c>
       <c r="P82" t="n">
-        <v>0.9490045309066772</v>
+        <v>0.9978795051574707</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.6504508000798523</v>
+        <v>0.1667718000007881</v>
       </c>
       <c r="R82" t="n">
-        <v>0.0001079364228644408</v>
+        <v>9.763384150573984e-05</v>
       </c>
       <c r="S82" t="n">
-        <v>922.1735183840758</v>
+        <v>965.4285214294903</v>
       </c>
       <c r="T82" t="n">
-        <v>202.3424349450505</v>
+        <v>206.8835627551345</v>
       </c>
       <c r="U82" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V82" t="n">
-        <v>5.177096794080285</v>
+        <v>1.113836606073505</v>
       </c>
       <c r="W82" t="n">
-        <v>0.1418282684543328</v>
+        <v>0.136378367462612</v>
       </c>
       <c r="X82" t="n">
-        <v>4.938735289652032</v>
+        <v>4.930155496197766</v>
       </c>
       <c r="Y82" t="b">
         <v>1</v>
@@ -6948,74 +6948,74 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>926.7147831503679</v>
+        <v>839.9126042606035</v>
       </c>
       <c r="D83" t="n">
-        <v>11.10188954260576</v>
+        <v>8.907747838441404</v>
       </c>
       <c r="E83" t="n">
-        <v>118.639878759105</v>
+        <v>221.1927624072788</v>
       </c>
       <c r="F83" t="n">
-        <v>0.7199835777282715</v>
+        <v>0.8026584386825562</v>
       </c>
       <c r="G83" t="n">
-        <v>0.5737242000177503</v>
+        <v>0.1588515999992524</v>
       </c>
       <c r="H83" t="n">
-        <v>0.004656502045691013</v>
+        <v>0.00147869111970067</v>
       </c>
       <c r="I83" t="n">
-        <v>891.6673146525425</v>
+        <v>923.1727218297198</v>
       </c>
       <c r="J83" t="n">
-        <v>173.7371835569596</v>
+        <v>221.1927448638558</v>
       </c>
       <c r="K83" t="n">
-        <v>11.10171871541859</v>
+        <v>9.000536995142108</v>
       </c>
       <c r="L83" t="n">
-        <v>35.04746849782543</v>
+        <v>83.26011756911623</v>
       </c>
       <c r="M83" t="n">
-        <v>55.0973047978546</v>
+        <v>1.754342295612332e-05</v>
       </c>
       <c r="N83" t="n">
-        <v>0.0001708271871692091</v>
+        <v>0.09278915670070376</v>
       </c>
       <c r="O83" t="b">
         <v>1</v>
       </c>
       <c r="P83" t="n">
-        <v>0.9999591112136841</v>
+        <v>0.7315876483917236</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.554130600066856</v>
+        <v>0.384424099998796</v>
       </c>
       <c r="R83" t="n">
-        <v>0.001670715282671154</v>
+        <v>0.0008903037523850799</v>
       </c>
       <c r="S83" t="n">
-        <v>800.8793300296152</v>
+        <v>929.5986465121015</v>
       </c>
       <c r="T83" t="n">
-        <v>150.0005521801378</v>
+        <v>221.5202664062019</v>
       </c>
       <c r="U83" t="n">
-        <v>10.92773995668466</v>
+        <v>9.049795252340969</v>
       </c>
       <c r="V83" t="n">
-        <v>125.8354531207527</v>
+        <v>89.68604225149795</v>
       </c>
       <c r="W83" t="n">
-        <v>31.36067342103277</v>
+        <v>0.3275039989231061</v>
       </c>
       <c r="X83" t="n">
-        <v>0.1741495859211035</v>
+        <v>0.1420474138995651</v>
       </c>
       <c r="Y83" t="b">
         <v>1</v>
@@ -7031,70 +7031,70 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>876.7511479722946</v>
+        <v>855.3309995817704</v>
       </c>
       <c r="D84" t="n">
-        <v>8.046191324537496</v>
+        <v>8.772997773417615</v>
       </c>
       <c r="E84" t="n">
-        <v>207.9055936817364</v>
+        <v>187.5215368940038</v>
       </c>
       <c r="F84" t="n">
-        <v>0.6946394443511963</v>
+        <v>0.783454954624176</v>
       </c>
       <c r="G84" t="n">
-        <v>0.2366309999488294</v>
+        <v>0.1168059999999969</v>
       </c>
       <c r="H84" t="n">
-        <v>0.001641420414671302</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I84" t="n">
-        <v>929.026971484157</v>
+        <v>924.4806741762613</v>
       </c>
       <c r="J84" t="n">
-        <v>207.9055936817364</v>
+        <v>187.5215368940038</v>
       </c>
       <c r="K84" t="n">
-        <v>9.000641551537415</v>
+        <v>9.00064139435195</v>
       </c>
       <c r="L84" t="n">
-        <v>52.27582351186243</v>
+        <v>69.14967459449099</v>
       </c>
       <c r="M84" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>0.9544502269999189</v>
+        <v>0.2276436209343355</v>
       </c>
       <c r="O84" t="b">
         <v>1</v>
       </c>
       <c r="P84" t="n">
-        <v>0.9524722695350647</v>
+        <v>0.9085878133773804</v>
       </c>
       <c r="Q84" t="n">
-        <v>1.287052900064737</v>
+        <v>0.4086628000004566</v>
       </c>
       <c r="R84" t="n">
-        <v>0.000342210492817685</v>
+        <v>0.0007539137732237577</v>
       </c>
       <c r="S84" t="n">
-        <v>928.1992610690543</v>
+        <v>934.5265725426169</v>
       </c>
       <c r="T84" t="n">
-        <v>206.992105275543</v>
+        <v>188.103494595004</v>
       </c>
       <c r="U84" t="n">
-        <v>9.000641635179212</v>
+        <v>9.00064190066119</v>
       </c>
       <c r="V84" t="n">
-        <v>51.4481130967597</v>
+        <v>79.19557296084656</v>
       </c>
       <c r="W84" t="n">
-        <v>0.9134884061933803</v>
+        <v>0.5819577010001353</v>
       </c>
       <c r="X84" t="n">
-        <v>0.9544503106417164</v>
+        <v>0.2276441272435754</v>
       </c>
       <c r="Y84" t="b">
         <v>1</v>
@@ -7106,74 +7106,74 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>945.8233754351328</v>
+        <v>847.863121084725</v>
       </c>
       <c r="D85" t="n">
-        <v>9.351547350593361</v>
+        <v>8.55256397682507</v>
       </c>
       <c r="E85" t="n">
-        <v>150.2474638719561</v>
+        <v>201.3666153914067</v>
       </c>
       <c r="F85" t="n">
-        <v>0.6767300963401794</v>
+        <v>0.833712637424469</v>
       </c>
       <c r="G85" t="n">
-        <v>0.369642399949953</v>
+        <v>0.1276875000003201</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0008354719611816108</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I85" t="n">
-        <v>945.8233782282691</v>
+        <v>924.480683723165</v>
       </c>
       <c r="J85" t="n">
-        <v>173.7371834327885</v>
+        <v>201.3666153914067</v>
       </c>
       <c r="K85" t="n">
-        <v>9.351635653297663</v>
+        <v>9.000641446570471</v>
       </c>
       <c r="L85" t="n">
-        <v>2.793136332002177e-06</v>
+        <v>76.61756263844006</v>
       </c>
       <c r="M85" t="n">
-        <v>23.48971956083238</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>8.830270430237874e-05</v>
+        <v>0.4480774697454013</v>
       </c>
       <c r="O85" t="b">
         <v>1</v>
       </c>
       <c r="P85" t="n">
-        <v>0.9909306168556213</v>
+        <v>0.8725757598876953</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.247947700088844</v>
+        <v>0.4364466999995784</v>
       </c>
       <c r="R85" t="n">
-        <v>0.001419720472767949</v>
+        <v>0.000818071304820478</v>
       </c>
       <c r="S85" t="n">
-        <v>826.4695559391522</v>
+        <v>931.9377649361013</v>
       </c>
       <c r="T85" t="n">
-        <v>156.5000052247234</v>
+        <v>201.6146280114612</v>
       </c>
       <c r="U85" t="n">
-        <v>9.26869916384992</v>
+        <v>9.000641696564838</v>
       </c>
       <c r="V85" t="n">
-        <v>119.3538194959806</v>
+        <v>84.07464385137632</v>
       </c>
       <c r="W85" t="n">
-        <v>6.252541352767281</v>
+        <v>0.2480126200544532</v>
       </c>
       <c r="X85" t="n">
-        <v>0.08284818674344052</v>
+        <v>0.4480777197397678</v>
       </c>
       <c r="Y85" t="b">
         <v>1</v>
@@ -7189,70 +7189,70 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>946.9959803049074</v>
+        <v>939.9969463757054</v>
       </c>
       <c r="D86" t="n">
-        <v>10.69043681472218</v>
+        <v>9.754555634461923</v>
       </c>
       <c r="E86" t="n">
-        <v>122.5622611924395</v>
+        <v>125.3672234885963</v>
       </c>
       <c r="F86" t="n">
-        <v>0.6767300963401794</v>
+        <v>0.8342413306236267</v>
       </c>
       <c r="G86" t="n">
-        <v>0.341127400053665</v>
+        <v>0.236075400000118</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0008354719611816108</v>
+        <v>0.01395832654088736</v>
       </c>
       <c r="I86" t="n">
-        <v>938.8344453378912</v>
+        <v>939.7084528955079</v>
       </c>
       <c r="J86" t="n">
-        <v>173.7382322432709</v>
+        <v>163.0337470339863</v>
       </c>
       <c r="K86" t="n">
-        <v>10.7543009236818</v>
+        <v>10.39441374192302</v>
       </c>
       <c r="L86" t="n">
-        <v>8.161534967016223</v>
+        <v>0.2884934801975305</v>
       </c>
       <c r="M86" t="n">
-        <v>51.17597105083134</v>
+        <v>37.66652354538999</v>
       </c>
       <c r="N86" t="n">
-        <v>0.0638641089596188</v>
+        <v>0.6398581074610927</v>
       </c>
       <c r="O86" t="b">
         <v>1</v>
       </c>
       <c r="P86" t="n">
-        <v>0.9999586343765259</v>
+        <v>0.9999986886978149</v>
       </c>
       <c r="Q86" t="n">
-        <v>1.425939799984917</v>
+        <v>0.4828793999986374</v>
       </c>
       <c r="R86" t="n">
-        <v>0.0017396459588781</v>
+        <v>0.001209896989166737</v>
       </c>
       <c r="S86" t="n">
-        <v>805.0111637170454</v>
+        <v>801.2785318567885</v>
       </c>
       <c r="T86" t="n">
-        <v>150.0005521349353</v>
+        <v>150.0005523520783</v>
       </c>
       <c r="U86" t="n">
-        <v>10.53175419089168</v>
+        <v>9.643008740573507</v>
       </c>
       <c r="V86" t="n">
-        <v>141.984816587862</v>
+        <v>138.7184145189169</v>
       </c>
       <c r="W86" t="n">
-        <v>27.43829094249575</v>
+        <v>24.63332886348203</v>
       </c>
       <c r="X86" t="n">
-        <v>0.1586826238304972</v>
+        <v>0.1115468938884163</v>
       </c>
       <c r="Y86" t="b">
         <v>1</v>
@@ -7264,74 +7264,74 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>853.2445715938389</v>
+        <v>919.0539202212327</v>
       </c>
       <c r="D87" t="n">
-        <v>8.889361698892458</v>
+        <v>10.63748294760498</v>
       </c>
       <c r="E87" t="n">
-        <v>201.7835415270264</v>
+        <v>148.5639561828438</v>
       </c>
       <c r="F87" t="n">
-        <v>0.7346910834312439</v>
+        <v>0.8329695463180542</v>
       </c>
       <c r="G87" t="n">
-        <v>0.219273499911651</v>
+        <v>0.2104945000010048</v>
       </c>
       <c r="H87" t="n">
-        <v>0.001641420414671302</v>
+        <v>0.0193394273519516</v>
       </c>
       <c r="I87" t="n">
-        <v>929.0283708884666</v>
+        <v>933.4884744948813</v>
       </c>
       <c r="J87" t="n">
-        <v>201.783541519616</v>
+        <v>163.0071440884688</v>
       </c>
       <c r="K87" t="n">
-        <v>9.000641486686645</v>
+        <v>11.83249054207861</v>
       </c>
       <c r="L87" t="n">
-        <v>75.78379929462767</v>
+        <v>14.43455427364859</v>
       </c>
       <c r="M87" t="n">
-        <v>7.410420721498667e-09</v>
+        <v>14.44318790562505</v>
       </c>
       <c r="N87" t="n">
-        <v>0.1112797877941869</v>
+        <v>1.19500759447363</v>
       </c>
       <c r="O87" t="b">
         <v>1</v>
       </c>
       <c r="P87" t="n">
-        <v>0.9593555927276611</v>
+        <v>0.9923118948936462</v>
       </c>
       <c r="Q87" t="n">
-        <v>1.309527900069952</v>
+        <v>0.9211178999994445</v>
       </c>
       <c r="R87" t="n">
-        <v>0.0004781610623467714</v>
+        <v>0.001253631198778749</v>
       </c>
       <c r="S87" t="n">
-        <v>925.3009666335253</v>
+        <v>811.4174586751725</v>
       </c>
       <c r="T87" t="n">
-        <v>201.247803666124</v>
+        <v>156.8457142618649</v>
       </c>
       <c r="U87" t="n">
-        <v>9.000641746968371</v>
+        <v>10.43301672576839</v>
       </c>
       <c r="V87" t="n">
-        <v>72.05639503968632</v>
+        <v>107.6364615460602</v>
       </c>
       <c r="W87" t="n">
-        <v>0.5357378609024011</v>
+        <v>8.281758079021131</v>
       </c>
       <c r="X87" t="n">
-        <v>0.1112800480759137</v>
+        <v>0.2044662218365936</v>
       </c>
       <c r="Y87" t="b">
         <v>1</v>
@@ -7347,70 +7347,70 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>837.2414016303974</v>
+        <v>852.897604864306</v>
       </c>
       <c r="D88" t="n">
-        <v>8.017493072487792</v>
+        <v>7.909474033516901</v>
       </c>
       <c r="E88" t="n">
-        <v>194.9453487487005</v>
+        <v>202.305244416779</v>
       </c>
       <c r="F88" t="n">
-        <v>0.8449464440345764</v>
+        <v>0.827983558177948</v>
       </c>
       <c r="G88" t="n">
-        <v>0.2241438999772072</v>
+        <v>0.1131361999996443</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0023431780282408</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I88" t="n">
-        <v>923.5221648716871</v>
+        <v>924.4806718453683</v>
       </c>
       <c r="J88" t="n">
-        <v>194.9454117449691</v>
+        <v>202.305244416779</v>
       </c>
       <c r="K88" t="n">
-        <v>9.000631800358006</v>
+        <v>9.000641699974473</v>
       </c>
       <c r="L88" t="n">
-        <v>86.28076324128972</v>
+        <v>71.5830669810623</v>
       </c>
       <c r="M88" t="n">
-        <v>6.299626866734798e-05</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>0.9831387278702142</v>
+        <v>1.091167666457572</v>
       </c>
       <c r="O88" t="b">
         <v>1</v>
       </c>
       <c r="P88" t="n">
-        <v>0.9837929606437683</v>
+        <v>0.943444550037384</v>
       </c>
       <c r="Q88" t="n">
-        <v>1.399755100021139</v>
+        <v>0.4648555000003398</v>
       </c>
       <c r="R88" t="n">
-        <v>0.0006017276318743825</v>
+        <v>0.0007648080354556441</v>
       </c>
       <c r="S88" t="n">
-        <v>923.8059292009133</v>
+        <v>932.3605990368237</v>
       </c>
       <c r="T88" t="n">
-        <v>194.9666147729972</v>
+        <v>202.535035362852</v>
       </c>
       <c r="U88" t="n">
-        <v>9.000641858720295</v>
+        <v>9.000641887834918</v>
       </c>
       <c r="V88" t="n">
-        <v>86.56452757051591</v>
+        <v>79.46299417251771</v>
       </c>
       <c r="W88" t="n">
-        <v>0.0212660242967786</v>
+        <v>0.2297909460729954</v>
       </c>
       <c r="X88" t="n">
-        <v>0.983148786232503</v>
+        <v>1.091167854318018</v>
       </c>
       <c r="Y88" t="b">
         <v>1</v>
@@ -7422,74 +7422,74 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>938.7719152961016</v>
+        <v>895.8486861265578</v>
       </c>
       <c r="D89" t="n">
-        <v>6.342125500575403</v>
+        <v>7.439542226029475</v>
       </c>
       <c r="E89" t="n">
-        <v>204.4031534074724</v>
+        <v>189.9192228340302</v>
       </c>
       <c r="F89" t="n">
-        <v>0.7307463884353638</v>
+        <v>0.5483524203300476</v>
       </c>
       <c r="G89" t="n">
-        <v>0.09846289991401136</v>
+        <v>0.1160435000001598</v>
       </c>
       <c r="H89" t="n">
-        <v>0.001059164758771658</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I89" t="n">
-        <v>938.7719152956544</v>
+        <v>924.4806684564029</v>
       </c>
       <c r="J89" t="n">
-        <v>204.4031534074724</v>
+        <v>189.9192228340302</v>
       </c>
       <c r="K89" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641622948679</v>
       </c>
       <c r="L89" t="n">
-        <v>4.472440195968375e-10</v>
+        <v>28.63198232984507</v>
       </c>
       <c r="M89" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.65851627928676</v>
+        <v>1.561099396919204</v>
       </c>
       <c r="O89" t="b">
         <v>1</v>
       </c>
       <c r="P89" t="n">
-        <v>0.692533552646637</v>
+        <v>0.780864953994751</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.5875717999879271</v>
+        <v>0.4067883000006987</v>
       </c>
       <c r="R89" t="n">
-        <v>5.778055492555723e-05</v>
+        <v>0.0003769493196159601</v>
       </c>
       <c r="S89" t="n">
-        <v>939.7902360443297</v>
+        <v>939.0272607680729</v>
       </c>
       <c r="T89" t="n">
-        <v>204.2856349967401</v>
+        <v>190.2184969052683</v>
       </c>
       <c r="U89" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641774509734</v>
       </c>
       <c r="V89" t="n">
-        <v>1.01832074822812</v>
+        <v>43.17857464151507</v>
       </c>
       <c r="W89" t="n">
-        <v>0.1175184107323162</v>
+        <v>0.2992740712380737</v>
       </c>
       <c r="X89" t="n">
-        <v>2.65851627928676</v>
+        <v>1.561099548480259</v>
       </c>
       <c r="Y89" t="b">
         <v>1</v>
@@ -7501,74 +7501,74 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>959.5049599256882</v>
+        <v>981.7689435248022</v>
       </c>
       <c r="D90" t="n">
-        <v>11.64064096072369</v>
+        <v>5.627043921572811</v>
       </c>
       <c r="E90" t="n">
-        <v>133.5682807777723</v>
+        <v>188.4837153950874</v>
       </c>
       <c r="F90" t="n">
-        <v>0.5675098896026611</v>
+        <v>0.6692194938659668</v>
       </c>
       <c r="G90" t="n">
-        <v>0.5393866000231355</v>
+        <v>0.03070329999900423</v>
       </c>
       <c r="H90" t="n">
-        <v>0.01439552940428257</v>
+        <v>0.0006574757280759513</v>
       </c>
       <c r="I90" t="n">
-        <v>962.2663924347563</v>
+        <v>981.7689466259225</v>
       </c>
       <c r="J90" t="n">
-        <v>167.3097803804677</v>
+        <v>188.4835529933779</v>
       </c>
       <c r="K90" t="n">
-        <v>11.64064326039687</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L90" t="n">
-        <v>2.761432509068072</v>
+        <v>3.10112022816611e-06</v>
       </c>
       <c r="M90" t="n">
-        <v>33.74149960269543</v>
+        <v>0.0001624017095025465</v>
       </c>
       <c r="N90" t="n">
-        <v>2.299673184325002e-06</v>
+        <v>3.373597858289351</v>
       </c>
       <c r="O90" t="b">
         <v>1</v>
       </c>
       <c r="P90" t="n">
-        <v>0.9993539452552795</v>
+        <v>0.8354538083076477</v>
       </c>
       <c r="Q90" t="n">
-        <v>1.783423600019887</v>
+        <v>0.1854237999996258</v>
       </c>
       <c r="R90" t="n">
-        <v>0.002262635622173548</v>
+        <v>0.000136482049128972</v>
       </c>
       <c r="S90" t="n">
-        <v>800.0000546562968</v>
+        <v>983.4635094091665</v>
       </c>
       <c r="T90" t="n">
-        <v>150.0005529130447</v>
+        <v>188.6015786164005</v>
       </c>
       <c r="U90" t="n">
-        <v>11.35894252851554</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V90" t="n">
-        <v>159.5049052693914</v>
+        <v>1.694565884364238</v>
       </c>
       <c r="W90" t="n">
-        <v>16.4322721352724</v>
+        <v>0.1178632213130868</v>
       </c>
       <c r="X90" t="n">
-        <v>0.2816984322081471</v>
+        <v>3.373597858289351</v>
       </c>
       <c r="Y90" t="b">
         <v>1</v>
@@ -7580,74 +7580,74 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>876.4757668973676</v>
+        <v>962.7382604486442</v>
       </c>
       <c r="D91" t="n">
-        <v>6.605769645544348</v>
+        <v>11.37501727749736</v>
       </c>
       <c r="E91" t="n">
-        <v>205.7483966820732</v>
+        <v>121.3048178851563</v>
       </c>
       <c r="F91" t="n">
-        <v>0.7930442690849304</v>
+        <v>0.8342413306236267</v>
       </c>
       <c r="G91" t="n">
-        <v>0.4156311999540776</v>
+        <v>0.2951578000011068</v>
       </c>
       <c r="H91" t="n">
-        <v>0.001641420414671302</v>
+        <v>0.01565238833427429</v>
       </c>
       <c r="I91" t="n">
-        <v>929.0272838051541</v>
+        <v>939.7170960890315</v>
       </c>
       <c r="J91" t="n">
-        <v>205.7483476948057</v>
+        <v>163.0038989774016</v>
       </c>
       <c r="K91" t="n">
-        <v>9.000000239654062</v>
+        <v>12.31880557481792</v>
       </c>
       <c r="L91" t="n">
-        <v>52.55151690778644</v>
+        <v>23.02116435961261</v>
       </c>
       <c r="M91" t="n">
-        <v>4.898726749047455e-05</v>
+        <v>41.69908109224531</v>
       </c>
       <c r="N91" t="n">
-        <v>2.394230594109714</v>
+        <v>0.9437882973205607</v>
       </c>
       <c r="O91" t="b">
         <v>1</v>
       </c>
       <c r="P91" t="n">
-        <v>0.9835144281387329</v>
+        <v>0.9999992847442627</v>
       </c>
       <c r="Q91" t="n">
-        <v>1.484753199853003</v>
+        <v>0.5967092999999295</v>
       </c>
       <c r="R91" t="n">
-        <v>0.0003369417681824416</v>
+        <v>0.003925133962184191</v>
       </c>
       <c r="S91" t="n">
-        <v>927.7284964280966</v>
+        <v>800.0000309649686</v>
       </c>
       <c r="T91" t="n">
-        <v>205.039928614542</v>
+        <v>150.0005528369569</v>
       </c>
       <c r="U91" t="n">
-        <v>9.000641655518043</v>
+        <v>10.61645059904456</v>
       </c>
       <c r="V91" t="n">
-        <v>51.25272953072897</v>
+        <v>162.7382294836756</v>
       </c>
       <c r="W91" t="n">
-        <v>0.7084680675312711</v>
+        <v>28.6957349518006</v>
       </c>
       <c r="X91" t="n">
-        <v>2.394872009973695</v>
+        <v>0.7585666784528051</v>
       </c>
       <c r="Y91" t="b">
         <v>1</v>
@@ -7663,70 +7663,70 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>883.4868469274719</v>
+        <v>876.5930409073219</v>
       </c>
       <c r="D92" t="n">
-        <v>7.496374588215676</v>
+        <v>7.501724386319491</v>
       </c>
       <c r="E92" t="n">
-        <v>216.8016449596609</v>
+        <v>210.6284858802542</v>
       </c>
       <c r="F92" t="n">
-        <v>0.7943462133407593</v>
+        <v>0.8236976861953735</v>
       </c>
       <c r="G92" t="n">
-        <v>0.2410278001334518</v>
+        <v>0.1186863999992056</v>
       </c>
       <c r="H92" t="n">
-        <v>0.001640737871639431</v>
+        <v>0.001478823600336909</v>
       </c>
       <c r="I92" t="n">
-        <v>929.0269663015033</v>
+        <v>923.1727125466235</v>
       </c>
       <c r="J92" t="n">
-        <v>216.8016777577037</v>
+        <v>210.6284858802542</v>
       </c>
       <c r="K92" t="n">
-        <v>9.000641714754583</v>
+        <v>9.000641745576274</v>
       </c>
       <c r="L92" t="n">
-        <v>45.54011937403141</v>
+        <v>46.57967163930164</v>
       </c>
       <c r="M92" t="n">
-        <v>3.279804280964527e-05</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N92" t="n">
-        <v>1.504267126538907</v>
+        <v>1.498917359256783</v>
       </c>
       <c r="O92" t="b">
         <v>1</v>
       </c>
       <c r="P92" t="n">
-        <v>0.9485679864883423</v>
+        <v>0.9502381086349487</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.26100270007737</v>
+        <v>0.4128682999999</v>
       </c>
       <c r="R92" t="n">
-        <v>0.0003664910909719765</v>
+        <v>0.0005291284760460258</v>
       </c>
       <c r="S92" t="n">
-        <v>931.6067796999025</v>
+        <v>934.504851282891</v>
       </c>
       <c r="T92" t="n">
-        <v>214.8575322181752</v>
+        <v>210.8040990174519</v>
       </c>
       <c r="U92" t="n">
-        <v>9.000640342871806</v>
+        <v>9.000641736337943</v>
       </c>
       <c r="V92" t="n">
-        <v>48.11993277243062</v>
+        <v>57.91181037556908</v>
       </c>
       <c r="W92" t="n">
-        <v>1.944112741485753</v>
+        <v>0.1756131371977006</v>
       </c>
       <c r="X92" t="n">
-        <v>1.504265754656131</v>
+        <v>1.498917350018452</v>
       </c>
       <c r="Y92" t="b">
         <v>1</v>
@@ -7738,74 +7738,74 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>882.5883669668395</v>
+        <v>927.4869006439883</v>
       </c>
       <c r="D93" t="n">
-        <v>7.586598678500282</v>
+        <v>5.690886471949463</v>
       </c>
       <c r="E93" t="n">
-        <v>179.8249621550254</v>
+        <v>197.0422059273024</v>
       </c>
       <c r="F93" t="n">
-        <v>0.7243368029594421</v>
+        <v>0.7905915975570679</v>
       </c>
       <c r="G93" t="n">
-        <v>0.2347736998926848</v>
+        <v>0.03258359999927052</v>
       </c>
       <c r="H93" t="n">
-        <v>0.002008212730288506</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I93" t="n">
-        <v>924.8594728992016</v>
+        <v>927.4869006439819</v>
       </c>
       <c r="J93" t="n">
-        <v>179.8249544693294</v>
+        <v>197.0422059273024</v>
       </c>
       <c r="K93" t="n">
-        <v>9.00064157126331</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L93" t="n">
-        <v>42.27110593236205</v>
+        <v>6.366462912410498e-12</v>
       </c>
       <c r="M93" t="n">
-        <v>7.685696004955389e-06</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>1.414042892763028</v>
+        <v>3.309755307912699</v>
       </c>
       <c r="O93" t="b">
         <v>1</v>
       </c>
       <c r="P93" t="n">
-        <v>0.7135631442070007</v>
+        <v>0.6931074857711792</v>
       </c>
       <c r="Q93" t="n">
-        <v>1.318423099815845</v>
+        <v>0.1693536000002496</v>
       </c>
       <c r="R93" t="n">
-        <v>0.0003714924387168139</v>
+        <v>0.0001658303226577118</v>
       </c>
       <c r="S93" t="n">
-        <v>929.2491630418084</v>
+        <v>928.4618835007274</v>
       </c>
       <c r="T93" t="n">
-        <v>180.7034969697479</v>
+        <v>197.2279539590416</v>
       </c>
       <c r="U93" t="n">
-        <v>9.000641708525187</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V93" t="n">
-        <v>46.66079607496886</v>
+        <v>0.974982856739075</v>
       </c>
       <c r="W93" t="n">
-        <v>0.8785348147224568</v>
+        <v>0.1857480317391378</v>
       </c>
       <c r="X93" t="n">
-        <v>1.414043030024905</v>
+        <v>3.309755307912699</v>
       </c>
       <c r="Y93" t="b">
         <v>1</v>
@@ -7817,74 +7817,74 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>930.7810504699386</v>
+        <v>997.9875441341283</v>
       </c>
       <c r="D94" t="n">
-        <v>4.167404912785494</v>
+        <v>11.16705915943403</v>
       </c>
       <c r="E94" t="n">
-        <v>191.3971014722671</v>
+        <v>106.0591878524666</v>
       </c>
       <c r="F94" t="n">
-        <v>0.6949499249458313</v>
+        <v>0.8300918936729431</v>
       </c>
       <c r="G94" t="n">
-        <v>0.08335580001585186</v>
+        <v>0.2997752999999648</v>
       </c>
       <c r="H94" t="n">
-        <v>0.001059164758771658</v>
+        <v>0.01565238833427429</v>
       </c>
       <c r="I94" t="n">
-        <v>930.7810504703618</v>
+        <v>939.7170952372755</v>
       </c>
       <c r="J94" t="n">
-        <v>191.3971014722673</v>
+        <v>163.0038982941061</v>
       </c>
       <c r="K94" t="n">
-        <v>9.000641779862162</v>
+        <v>12.31880748258491</v>
       </c>
       <c r="L94" t="n">
-        <v>4.232560968375765e-10</v>
+        <v>58.27044889685271</v>
       </c>
       <c r="M94" t="n">
-        <v>2.842170943040401e-13</v>
+        <v>56.94471044163944</v>
       </c>
       <c r="N94" t="n">
-        <v>4.833236867076669</v>
+        <v>1.151748323150883</v>
       </c>
       <c r="O94" t="b">
         <v>1</v>
       </c>
       <c r="P94" t="n">
-        <v>0.9864331483840942</v>
+        <v>1</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.5066314002033323</v>
+        <v>0.5442158000005293</v>
       </c>
       <c r="R94" t="n">
-        <v>6.914245750522241e-05</v>
+        <v>0.003423250513151288</v>
       </c>
       <c r="S94" t="n">
-        <v>932.5906830912296</v>
+        <v>800.0000410764735</v>
       </c>
       <c r="T94" t="n">
-        <v>191.4998723057442</v>
+        <v>150.0005528601709</v>
       </c>
       <c r="U94" t="n">
-        <v>9.000641779862162</v>
+        <v>10.52448764956129</v>
       </c>
       <c r="V94" t="n">
-        <v>1.80963262129103</v>
+        <v>197.9875030576547</v>
       </c>
       <c r="W94" t="n">
-        <v>0.1027708334771944</v>
+        <v>43.94136500770426</v>
       </c>
       <c r="X94" t="n">
-        <v>4.833236867076669</v>
+        <v>0.6425715098727327</v>
       </c>
       <c r="Y94" t="b">
         <v>1</v>
@@ -7896,74 +7896,74 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>890.3054586948058</v>
+        <v>947.578491352189</v>
       </c>
       <c r="D95" t="n">
-        <v>6.576401178182833</v>
+        <v>5.654812820737789</v>
       </c>
       <c r="E95" t="n">
-        <v>199.2832620237663</v>
+        <v>200.2528700668194</v>
       </c>
       <c r="F95" t="n">
-        <v>0.7929344177246094</v>
+        <v>0.8132951259613037</v>
       </c>
       <c r="G95" t="n">
-        <v>0.2437549999449402</v>
+        <v>0.0366212999997515</v>
       </c>
       <c r="H95" t="n">
-        <v>0.001641420414671302</v>
+        <v>0.000657533819321543</v>
       </c>
       <c r="I95" t="n">
-        <v>929.0269673295993</v>
+        <v>947.5784913521876</v>
       </c>
       <c r="J95" t="n">
-        <v>199.2832620237663</v>
+        <v>200.2528700668194</v>
       </c>
       <c r="K95" t="n">
-        <v>9.000641674599413</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L95" t="n">
-        <v>38.72150863479351</v>
+        <v>1.364242052659392e-12</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N95" t="n">
-        <v>2.42424049641658</v>
+        <v>3.345828959124374</v>
       </c>
       <c r="O95" t="b">
         <v>1</v>
       </c>
       <c r="P95" t="n">
-        <v>0.9206873774528503</v>
+        <v>0.8203698992729187</v>
       </c>
       <c r="Q95" t="n">
-        <v>1.3052161000669</v>
+        <v>0.1727991000007023</v>
       </c>
       <c r="R95" t="n">
-        <v>0.0002421541576040909</v>
+        <v>0.0001321505842497572</v>
       </c>
       <c r="S95" t="n">
-        <v>928.3925216671081</v>
+        <v>948.3934127082003</v>
       </c>
       <c r="T95" t="n">
-        <v>199.1260555224414</v>
+        <v>200.3686448796067</v>
       </c>
       <c r="U95" t="n">
-        <v>9.000641743964731</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V95" t="n">
-        <v>38.08706297230231</v>
+        <v>0.8149213560113822</v>
       </c>
       <c r="W95" t="n">
-        <v>0.1572065013249073</v>
+        <v>0.1157748127873219</v>
       </c>
       <c r="X95" t="n">
-        <v>2.424240565781899</v>
+        <v>3.345828959124374</v>
       </c>
       <c r="Y95" t="b">
         <v>1</v>
@@ -7979,70 +7979,70 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>876.7461009023923</v>
+        <v>853.9855462443677</v>
       </c>
       <c r="D96" t="n">
-        <v>5.53099689378211</v>
+        <v>7.987659714746035</v>
       </c>
       <c r="E96" t="n">
-        <v>199.7216912713952</v>
+        <v>197.5842788078801</v>
       </c>
       <c r="F96" t="n">
-        <v>0.7929344177246094</v>
+        <v>0.8169287443161011</v>
       </c>
       <c r="G96" t="n">
-        <v>0.2202717999462038</v>
+        <v>0.1164031000007526</v>
       </c>
       <c r="H96" t="n">
-        <v>0.001641420414671302</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I96" t="n">
-        <v>929.0269667989231</v>
+        <v>924.4806694830611</v>
       </c>
       <c r="J96" t="n">
-        <v>199.7216912713952</v>
+        <v>197.5842788078801</v>
       </c>
       <c r="K96" t="n">
-        <v>9.000641430228491</v>
+        <v>9.0006414939416</v>
       </c>
       <c r="L96" t="n">
-        <v>52.28086589653083</v>
+        <v>70.4951232386934</v>
       </c>
       <c r="M96" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3.469644536446381</v>
+        <v>1.012981779195566</v>
       </c>
       <c r="O96" t="b">
         <v>1</v>
       </c>
       <c r="P96" t="n">
-        <v>0.9775899052619934</v>
+        <v>0.9471377730369568</v>
       </c>
       <c r="Q96" t="n">
-        <v>1.293022199999541</v>
+        <v>0.4517273000001296</v>
       </c>
       <c r="R96" t="n">
-        <v>0.0003258523647673428</v>
+        <v>0.0007548374123871326</v>
       </c>
       <c r="S96" t="n">
-        <v>926.9645372481081</v>
+        <v>932.930602752039</v>
       </c>
       <c r="T96" t="n">
-        <v>199.4796145558719</v>
+        <v>198.273461216431</v>
       </c>
       <c r="U96" t="n">
-        <v>9.000641840458128</v>
+        <v>9.000641648912826</v>
       </c>
       <c r="V96" t="n">
-        <v>50.21843634571576</v>
+        <v>78.94505650767132</v>
       </c>
       <c r="W96" t="n">
-        <v>0.2420767155232966</v>
+        <v>0.6891824085509484</v>
       </c>
       <c r="X96" t="n">
-        <v>3.469644946676018</v>
+        <v>1.012981934166791</v>
       </c>
       <c r="Y96" t="b">
         <v>1</v>
@@ -8054,74 +8054,74 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>876.9410955441447</v>
+        <v>947.4469580674147</v>
       </c>
       <c r="D97" t="n">
-        <v>5.922903181947195</v>
+        <v>10.57432112273982</v>
       </c>
       <c r="E97" t="n">
-        <v>196.2076374337506</v>
+        <v>136.2270958374783</v>
       </c>
       <c r="F97" t="n">
-        <v>0.7929344177246094</v>
+        <v>0.8342413306236267</v>
       </c>
       <c r="G97" t="n">
-        <v>0.2276775001082569</v>
+        <v>0.1354125999987446</v>
       </c>
       <c r="H97" t="n">
-        <v>0.001641420414671302</v>
+        <v>0.02069370076060295</v>
       </c>
       <c r="I97" t="n">
-        <v>929.0269718751144</v>
+        <v>929.472093863953</v>
       </c>
       <c r="J97" t="n">
-        <v>196.2076374337506</v>
+        <v>167.2837065127374</v>
       </c>
       <c r="K97" t="n">
-        <v>9.000641548764357</v>
+        <v>12.25531054993708</v>
       </c>
       <c r="L97" t="n">
-        <v>52.08587633096977</v>
+        <v>17.97486420346172</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>31.05661067525915</v>
       </c>
       <c r="N97" t="n">
-        <v>3.077738366817162</v>
+        <v>1.680989427197259</v>
       </c>
       <c r="O97" t="b">
         <v>1</v>
       </c>
       <c r="P97" t="n">
-        <v>0.9807537198066711</v>
+        <v>0.9998952150344849</v>
       </c>
       <c r="Q97" t="n">
-        <v>1.290139100048691</v>
+        <v>0.6606907999994291</v>
       </c>
       <c r="R97" t="n">
-        <v>0.0003247980203013867</v>
+        <v>0.002132153138518333</v>
       </c>
       <c r="S97" t="n">
-        <v>926.8226288536933</v>
+        <v>800.0002613231311</v>
       </c>
       <c r="T97" t="n">
-        <v>196.1935193988279</v>
+        <v>150.0005528276915</v>
       </c>
       <c r="U97" t="n">
-        <v>9.000641799019057</v>
+        <v>10.21003052987741</v>
       </c>
       <c r="V97" t="n">
-        <v>49.88153330954867</v>
+        <v>147.4466967442836</v>
       </c>
       <c r="W97" t="n">
-        <v>0.01411803492271702</v>
+        <v>13.77345699021319</v>
       </c>
       <c r="X97" t="n">
-        <v>3.077738617071862</v>
+        <v>0.3642905928624138</v>
       </c>
       <c r="Y97" t="b">
         <v>1</v>
@@ -8133,74 +8133,74 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>868.6870572887069</v>
+        <v>963.056306834058</v>
       </c>
       <c r="D98" t="n">
-        <v>7.650520726875163</v>
+        <v>11.03750141426828</v>
       </c>
       <c r="E98" t="n">
-        <v>189.1050907213636</v>
+        <v>141.0446898309199</v>
       </c>
       <c r="F98" t="n">
-        <v>0.7926901578903198</v>
+        <v>0.8342413306236267</v>
       </c>
       <c r="G98" t="n">
-        <v>0.3864965999964625</v>
+        <v>0.2435194000008778</v>
       </c>
       <c r="H98" t="n">
-        <v>0.001641420414671302</v>
+        <v>0.0008712398703210056</v>
       </c>
       <c r="I98" t="n">
-        <v>929.0269665662559</v>
+        <v>963.0563078508883</v>
       </c>
       <c r="J98" t="n">
-        <v>189.1050907216019</v>
+        <v>173.1913500386705</v>
       </c>
       <c r="K98" t="n">
-        <v>9.000641781085085</v>
+        <v>11.03750138812716</v>
       </c>
       <c r="L98" t="n">
-        <v>60.33990927754894</v>
+        <v>1.016830310618388e-06</v>
       </c>
       <c r="M98" t="n">
-        <v>2.383728769927984e-10</v>
+        <v>32.14666020775059</v>
       </c>
       <c r="N98" t="n">
-        <v>1.350121054209922</v>
+        <v>2.614111949128528e-08</v>
       </c>
       <c r="O98" t="b">
         <v>1</v>
       </c>
       <c r="P98" t="n">
-        <v>0.9589347839355469</v>
+        <v>0.9990684390068054</v>
       </c>
       <c r="Q98" t="n">
-        <v>1.34539039991796</v>
+        <v>1.079687499999636</v>
       </c>
       <c r="R98" t="n">
-        <v>0.000398824515286833</v>
+        <v>0.002004957292228937</v>
       </c>
       <c r="S98" t="n">
-        <v>926.2784830298667</v>
+        <v>800.0002832195379</v>
       </c>
       <c r="T98" t="n">
-        <v>189.5258600009328</v>
+        <v>152.6355579613555</v>
       </c>
       <c r="U98" t="n">
-        <v>9.000641663846006</v>
+        <v>10.67905302638131</v>
       </c>
       <c r="V98" t="n">
-        <v>57.59142574115981</v>
+        <v>163.0560236145201</v>
       </c>
       <c r="W98" t="n">
-        <v>0.4207692795692708</v>
+        <v>11.59086813043558</v>
       </c>
       <c r="X98" t="n">
-        <v>1.350120936970843</v>
+        <v>0.3584483878869733</v>
       </c>
       <c r="Y98" t="b">
         <v>1</v>
@@ -8212,74 +8212,74 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>836.7768189575141</v>
+        <v>936.611796449889</v>
       </c>
       <c r="D99" t="n">
-        <v>9.083962981284996</v>
+        <v>11.28067789888034</v>
       </c>
       <c r="E99" t="n">
-        <v>182.2619562966848</v>
+        <v>109.4019196015007</v>
       </c>
       <c r="F99" t="n">
-        <v>0.6594071388244629</v>
+        <v>0.8342413306236267</v>
       </c>
       <c r="G99" t="n">
-        <v>0.2006121999584138</v>
+        <v>0.2654767999993055</v>
       </c>
       <c r="H99" t="n">
-        <v>0.002008706564083695</v>
+        <v>0.01562827080488205</v>
       </c>
       <c r="I99" t="n">
-        <v>924.8594837494456</v>
+        <v>932.6390745258095</v>
       </c>
       <c r="J99" t="n">
-        <v>182.2619513903775</v>
+        <v>163.00389845341</v>
       </c>
       <c r="K99" t="n">
-        <v>9.084046458499142</v>
+        <v>12.31844659227882</v>
       </c>
       <c r="L99" t="n">
-        <v>88.08266479193151</v>
+        <v>3.972721924079451</v>
       </c>
       <c r="M99" t="n">
-        <v>4.906307253804698e-06</v>
+        <v>53.60197885190929</v>
       </c>
       <c r="N99" t="n">
-        <v>8.347721414558862e-05</v>
+        <v>1.037768693398473</v>
       </c>
       <c r="O99" t="b">
         <v>1</v>
       </c>
       <c r="P99" t="n">
-        <v>0.9372252225875854</v>
+        <v>1</v>
       </c>
       <c r="Q99" t="n">
-        <v>1.214148200117052</v>
+        <v>0.5423943999994663</v>
       </c>
       <c r="R99" t="n">
-        <v>0.0006909906514920294</v>
+        <v>0.003696478437632322</v>
       </c>
       <c r="S99" t="n">
-        <v>923.1722923446655</v>
+        <v>800.0000280230023</v>
       </c>
       <c r="T99" t="n">
-        <v>183.4249786551319</v>
+        <v>150.0005528483752</v>
       </c>
       <c r="U99" t="n">
-        <v>9.166767869666685</v>
+        <v>10.57603918760459</v>
       </c>
       <c r="V99" t="n">
-        <v>86.39547338715136</v>
+        <v>136.6117684268867</v>
       </c>
       <c r="W99" t="n">
-        <v>1.163022358447108</v>
+        <v>40.59863324687451</v>
       </c>
       <c r="X99" t="n">
-        <v>0.08280488838168942</v>
+        <v>0.7046387112757539</v>
       </c>
       <c r="Y99" t="b">
         <v>1</v>
@@ -8291,74 +8291,74 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>951.0286877103533</v>
+        <v>870.8980293109241</v>
       </c>
       <c r="D100" t="n">
-        <v>9.617151377680672</v>
+        <v>7.87401015685547</v>
       </c>
       <c r="E100" t="n">
-        <v>134.2322609952119</v>
+        <v>201.0372975914116</v>
       </c>
       <c r="F100" t="n">
-        <v>0.6767300963401794</v>
+        <v>0.827983558177948</v>
       </c>
       <c r="G100" t="n">
-        <v>0.3618227001279593</v>
+        <v>0.1249941999994917</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0008354719611816108</v>
+        <v>0.001030373154208064</v>
       </c>
       <c r="I100" t="n">
-        <v>951.0286874786497</v>
+        <v>924.4806707539068</v>
       </c>
       <c r="J100" t="n">
-        <v>173.7371840447312</v>
+        <v>201.0372975914116</v>
       </c>
       <c r="K100" t="n">
-        <v>9.616994643252752</v>
+        <v>9.000641624012538</v>
       </c>
       <c r="L100" t="n">
-        <v>2.317036660315352e-07</v>
+        <v>53.58264144298266</v>
       </c>
       <c r="M100" t="n">
-        <v>39.50492304951931</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>0.0001567344279198579</v>
+        <v>1.126631467157067</v>
       </c>
       <c r="O100" t="b">
         <v>1</v>
       </c>
       <c r="P100" t="n">
-        <v>0.9998160004615784</v>
+        <v>0.9480962753295898</v>
       </c>
       <c r="Q100" t="n">
-        <v>1.51004229998216</v>
+        <v>0.39643100000103</v>
       </c>
       <c r="R100" t="n">
-        <v>0.001625560456886888</v>
+        <v>0.0005860305391252041</v>
       </c>
       <c r="S100" t="n">
-        <v>812.6109556366022</v>
+        <v>934.2920009514331</v>
       </c>
       <c r="T100" t="n">
-        <v>150.0005524288247</v>
+        <v>201.2114210869627</v>
       </c>
       <c r="U100" t="n">
-        <v>9.510559577515583</v>
+        <v>9.000641814034209</v>
       </c>
       <c r="V100" t="n">
-        <v>138.4177320737512</v>
+        <v>63.39397164050899</v>
       </c>
       <c r="W100" t="n">
-        <v>15.76829143361283</v>
+        <v>0.1741234955511004</v>
       </c>
       <c r="X100" t="n">
-        <v>0.1065918001650896</v>
+        <v>1.126631657178739</v>
       </c>
       <c r="Y100" t="b">
         <v>1</v>
@@ -8370,74 +8370,74 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>948.9005492473864</v>
+        <v>970.7561388305421</v>
       </c>
       <c r="D101" t="n">
-        <v>3.594222788425768</v>
+        <v>10.37399377702127</v>
       </c>
       <c r="E101" t="n">
-        <v>199.4674332195344</v>
+        <v>139.4368561057225</v>
       </c>
       <c r="F101" t="n">
-        <v>0.7307463884353638</v>
+        <v>0.8341188430786133</v>
       </c>
       <c r="G101" t="n">
-        <v>0.1444097999483347</v>
+        <v>0.1997789000015473</v>
       </c>
       <c r="H101" t="n">
-        <v>0.001032155007123947</v>
+        <v>0.01935457438230515</v>
       </c>
       <c r="I101" t="n">
-        <v>951.9834703382377</v>
+        <v>939.7124554799866</v>
       </c>
       <c r="J101" t="n">
-        <v>199.4674332195348</v>
+        <v>163.5756111462861</v>
       </c>
       <c r="K101" t="n">
-        <v>9.000641779862162</v>
+        <v>11.83268195040376</v>
       </c>
       <c r="L101" t="n">
-        <v>3.082921090851301</v>
+        <v>31.04368335055551</v>
       </c>
       <c r="M101" t="n">
-        <v>4.263256414560601e-13</v>
+        <v>24.13875504056361</v>
       </c>
       <c r="N101" t="n">
-        <v>5.406418991436395</v>
+        <v>1.458688173382491</v>
       </c>
       <c r="O101" t="b">
         <v>1</v>
       </c>
       <c r="P101" t="n">
-        <v>0.9980429410934448</v>
+        <v>0.9995613694190979</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.593808599980548</v>
+        <v>0.5014737000001332</v>
       </c>
       <c r="R101" t="n">
-        <v>4.639910548576154e-05</v>
+        <v>0.00184032297693193</v>
       </c>
       <c r="S101" t="n">
-        <v>948.7586446397174</v>
+        <v>800.5723188615206</v>
       </c>
       <c r="T101" t="n">
-        <v>199.4521902447854</v>
+        <v>150.0005521281755</v>
       </c>
       <c r="U101" t="n">
-        <v>9.000641779862162</v>
+        <v>10.07653342538259</v>
       </c>
       <c r="V101" t="n">
-        <v>0.1419046076689483</v>
+        <v>170.1838199690216</v>
       </c>
       <c r="W101" t="n">
-        <v>0.01524297474898617</v>
+        <v>10.56369602245303</v>
       </c>
       <c r="X101" t="n">
-        <v>5.406418991436395</v>
+        <v>0.2974603516386836</v>
       </c>
       <c r="Y101" t="b">
         <v>1</v>

--- a/export_dati/06_Step6_Simulazione_Massiva_100.xlsx
+++ b/export_dati/06_Step6_Simulazione_Massiva_100.xlsx
@@ -444,12 +444,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Probabilità iniziale_XGBoost</t>
+          <t>Probabilità_Iniziale_XGBoost</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Tempo di esecuzione_XGBoost</t>
+          <t>Tempo_Esecuzione_XGBoost</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -494,12 +494,12 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Probabilità iniziale_TensorFlow</t>
+          <t>Probabilità_Iniziale_TensorFlow</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Tempo di esecuzione_TensorFlow</t>
+          <t>Tempo_Esecuzione_TensorFlow</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
@@ -549,74 +549,74 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>973.3556412331961</v>
+        <v>886.0462648034497</v>
       </c>
       <c r="D2" t="n">
-        <v>3.964780873045247</v>
+        <v>7.312567912603805</v>
       </c>
       <c r="E2" t="n">
-        <v>193.4837471974598</v>
+        <v>217.0438265160413</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8107597231864929</v>
+        <v>0.8036846518516541</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03084179999859771</v>
+        <v>0.3044505999932881</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0006575194420292974</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I2" t="n">
-        <v>973.3555828200604</v>
+        <v>922.205825825996</v>
       </c>
       <c r="J2" t="n">
-        <v>193.4837913689334</v>
+        <v>217.043826516037</v>
       </c>
       <c r="K2" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641573235685</v>
       </c>
       <c r="L2" t="n">
-        <v>5.841313577548135e-05</v>
+        <v>36.15956102254631</v>
       </c>
       <c r="M2" t="n">
-        <v>4.417147357571594e-05</v>
+        <v>4.320099833421409e-12</v>
       </c>
       <c r="N2" t="n">
-        <v>5.035860906816915</v>
+        <v>1.688073660631879</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9988646507263184</v>
+        <v>0.9577955603599548</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2011913999995159</v>
+        <v>1.437959099996078</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0001356776192551479</v>
+        <v>0.0003539097378961742</v>
       </c>
       <c r="S2" t="n">
-        <v>974.0311834527407</v>
+        <v>932.3014585363629</v>
       </c>
       <c r="T2" t="n">
-        <v>193.5505771872832</v>
+        <v>215.174222047529</v>
       </c>
       <c r="U2" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641774231712</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6755422195445817</v>
+        <v>46.2551937329132</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0668299898233613</v>
+        <v>1.869604468512392</v>
       </c>
       <c r="X2" t="n">
-        <v>5.035860906816915</v>
+        <v>1.688073861627906</v>
       </c>
       <c r="Y2" t="b">
         <v>1</v>
@@ -628,74 +628,74 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>968.297355961957</v>
+        <v>901.4802941863005</v>
       </c>
       <c r="D3" t="n">
-        <v>13.26575829067173</v>
+        <v>6.374007667835555</v>
       </c>
       <c r="E3" t="n">
-        <v>206.5498194286949</v>
+        <v>196.7796843806025</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5131295919418335</v>
+        <v>0.5276130437850952</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1471380000002682</v>
+        <v>0.2740455000021029</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00620739022269845</v>
+        <v>0.0008494904031977057</v>
       </c>
       <c r="I3" t="n">
-        <v>924.0466802114934</v>
+        <v>909.3976957334251</v>
       </c>
       <c r="J3" t="n">
-        <v>207.0847207401031</v>
+        <v>196.7795944057828</v>
       </c>
       <c r="K3" t="n">
-        <v>12.35660419996731</v>
+        <v>9.000641489611244</v>
       </c>
       <c r="L3" t="n">
-        <v>44.25067575046364</v>
+        <v>7.917401547124541</v>
       </c>
       <c r="M3" t="n">
-        <v>0.534901311408106</v>
+        <v>8.997481970141052e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9091540907044227</v>
+        <v>2.626633821775689</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4018758833408356</v>
+        <v>0.3084385693073273</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7152002999991964</v>
+        <v>0.5243454000010388</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001132149482145905</v>
+        <v>0.0002449585299473256</v>
       </c>
       <c r="S3" t="n">
-        <v>838.2430729640236</v>
+        <v>908.8647429048053</v>
       </c>
       <c r="T3" t="n">
-        <v>205.6382135512308</v>
+        <v>196.7616894136254</v>
       </c>
       <c r="U3" t="n">
-        <v>12.46484487716202</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V3" t="n">
-        <v>130.0542829979335</v>
+        <v>7.384448718504814</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9116058774641829</v>
+        <v>0.01799496697708491</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8009134135097167</v>
+        <v>2.626634112026608</v>
       </c>
       <c r="Y3" t="b">
         <v>1</v>
@@ -707,74 +707,74 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>928.5196805722064</v>
+        <v>964.3575052005159</v>
       </c>
       <c r="D4" t="n">
-        <v>10.69634413899631</v>
+        <v>6.616285434079799</v>
       </c>
       <c r="E4" t="n">
-        <v>157.9807758931487</v>
+        <v>183.684291259932</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8342413306236267</v>
+        <v>0.6916452050209045</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1829912000011973</v>
+        <v>0.06195659999502823</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0186562966555357</v>
+        <v>0.0008420366793870926</v>
       </c>
       <c r="I4" t="n">
-        <v>933.9714700163664</v>
+        <v>964.3575052005151</v>
       </c>
       <c r="J4" t="n">
-        <v>163.0059038864132</v>
+        <v>183.684291259932</v>
       </c>
       <c r="K4" t="n">
-        <v>11.94947639600404</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L4" t="n">
-        <v>5.451789444159999</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="M4" t="n">
-        <v>5.025127993264476</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.253132257007728</v>
+        <v>2.384356345782363</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7840512990951538</v>
+        <v>0.4316332936286926</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8656842000000324</v>
+        <v>0.6007677000015974</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0008841350208967924</v>
+        <v>0.0001229960907949135</v>
       </c>
       <c r="S4" t="n">
-        <v>835.3667781137857</v>
+        <v>964.075134523684</v>
       </c>
       <c r="T4" t="n">
-        <v>166.1793825708943</v>
+        <v>184.5057664063757</v>
       </c>
       <c r="U4" t="n">
-        <v>10.60719706035339</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V4" t="n">
-        <v>93.15290245842073</v>
+        <v>0.2823706768318743</v>
       </c>
       <c r="W4" t="n">
-        <v>8.198606677745545</v>
+        <v>0.8214751464437029</v>
       </c>
       <c r="X4" t="n">
-        <v>0.08914707864291316</v>
+        <v>2.384356345782363</v>
       </c>
       <c r="Y4" t="b">
         <v>1</v>
@@ -786,74 +786,74 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>948.4574824509183</v>
+        <v>959.3798922287798</v>
       </c>
       <c r="D5" t="n">
-        <v>4.234818532952462</v>
+        <v>8.418357444447395</v>
       </c>
       <c r="E5" t="n">
-        <v>183.7958103216791</v>
+        <v>120.1312505294391</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7809576988220215</v>
+        <v>0.752820611000061</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0341496000000916</v>
+        <v>0.4440901000052691</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.01405216194689274</v>
       </c>
       <c r="I5" t="n">
-        <v>948.457482451174</v>
+        <v>950.6938634465636</v>
       </c>
       <c r="J5" t="n">
-        <v>183.7958103216795</v>
+        <v>165.1588098492162</v>
       </c>
       <c r="K5" t="n">
-        <v>9.000641779862162</v>
+        <v>9.893564800181833</v>
       </c>
       <c r="L5" t="n">
-        <v>2.556816980359145e-10</v>
+        <v>8.686028782216226</v>
       </c>
       <c r="M5" t="n">
-        <v>3.979039320256561e-13</v>
+        <v>45.02755931977711</v>
       </c>
       <c r="N5" t="n">
-        <v>4.7658232469097</v>
+        <v>1.475207355734439</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9951609969139099</v>
+        <v>0.9999998807907104</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2276376000008895</v>
+        <v>1.674420800001826</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0001758132420945913</v>
+        <v>0.000846900453325361</v>
       </c>
       <c r="S5" t="n">
-        <v>949.6254232223604</v>
+        <v>846.4083647864366</v>
       </c>
       <c r="T5" t="n">
-        <v>183.8764653880124</v>
+        <v>150.0005527206193</v>
       </c>
       <c r="U5" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641917387313</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16794077144209</v>
+        <v>112.9715274423432</v>
       </c>
       <c r="W5" t="n">
-        <v>0.08065506633334962</v>
+        <v>29.86930219118022</v>
       </c>
       <c r="X5" t="n">
-        <v>4.7658232469097</v>
+        <v>0.5822844729399179</v>
       </c>
       <c r="Y5" t="b">
         <v>1</v>
@@ -865,74 +865,74 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>933.0546011156074</v>
+        <v>886.4304481775114</v>
       </c>
       <c r="D6" t="n">
-        <v>9.253343152804804</v>
+        <v>8.037285146351248</v>
       </c>
       <c r="E6" t="n">
-        <v>155.4723444527573</v>
+        <v>212.2585366535716</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8342413306236267</v>
+        <v>0.8063374757766724</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2194755000000441</v>
+        <v>0.2451428999993368</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000942692335229367</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I6" t="n">
-        <v>944.9210204485925</v>
+        <v>922.2058289561362</v>
       </c>
       <c r="J6" t="n">
-        <v>173.1928082986053</v>
+        <v>212.2585366535716</v>
       </c>
       <c r="K6" t="n">
-        <v>9.258998707891159</v>
+        <v>9.000641601038879</v>
       </c>
       <c r="L6" t="n">
-        <v>11.86641933298506</v>
+        <v>35.77538077862482</v>
       </c>
       <c r="M6" t="n">
-        <v>17.72046384584795</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.005655555086354624</v>
+        <v>0.9633564546876308</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9279007911682129</v>
+        <v>0.8857000470161438</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7336667999989004</v>
+        <v>1.258999499994388</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0008793186862021685</v>
+        <v>0.0003069405793212354</v>
       </c>
       <c r="S6" t="n">
-        <v>837.3071007408083</v>
+        <v>931.8350500170983</v>
       </c>
       <c r="T6" t="n">
-        <v>163.1958458270779</v>
+        <v>211.4120515081246</v>
       </c>
       <c r="U6" t="n">
-        <v>9.175959497258631</v>
+        <v>9.000641707566652</v>
       </c>
       <c r="V6" t="n">
-        <v>95.74750037479907</v>
+        <v>45.40460183958692</v>
       </c>
       <c r="W6" t="n">
-        <v>7.723501374320563</v>
+        <v>0.8464851454469624</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0773836555461731</v>
+        <v>0.963356561215404</v>
       </c>
       <c r="Y6" t="b">
         <v>1</v>
@@ -944,74 +944,74 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>932.6854511500906</v>
+        <v>835.5161025640529</v>
       </c>
       <c r="D7" t="n">
-        <v>4.822039544966751</v>
+        <v>7.043614946763783</v>
       </c>
       <c r="E7" t="n">
-        <v>203.85972612514</v>
+        <v>196.6896824256995</v>
       </c>
       <c r="F7" t="n">
-        <v>0.786822497844696</v>
+        <v>0.8492916226387024</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03984810000110883</v>
+        <v>0.2754987000007532</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I7" t="n">
-        <v>932.6854511501308</v>
+        <v>922.2058264394848</v>
       </c>
       <c r="J7" t="n">
-        <v>203.85972612514</v>
+        <v>196.6896824256995</v>
       </c>
       <c r="K7" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641759402784</v>
       </c>
       <c r="L7" t="n">
-        <v>4.024514055345207e-11</v>
+        <v>86.68972387543192</v>
       </c>
       <c r="M7" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.178602234895411</v>
+        <v>1.957026812639001</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>0.935815155506134</v>
+        <v>0.9969677329063416</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2396212999992713</v>
+        <v>1.345960799997556</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001350106322206557</v>
+        <v>0.0006575367297045887</v>
       </c>
       <c r="S7" t="n">
-        <v>933.4779040509108</v>
+        <v>924.9419803076114</v>
       </c>
       <c r="T7" t="n">
-        <v>203.9801834042082</v>
+        <v>197.0898382314952</v>
       </c>
       <c r="U7" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641789604858</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7924529008201944</v>
+        <v>89.42587774355854</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1204572790681766</v>
+        <v>0.4001558057956913</v>
       </c>
       <c r="X7" t="n">
-        <v>4.178602234895411</v>
+        <v>1.957026842841075</v>
       </c>
       <c r="Y7" t="b">
         <v>1</v>
@@ -1027,70 +1027,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>942.0783206784146</v>
+        <v>924.0772648008368</v>
       </c>
       <c r="D8" t="n">
-        <v>8.782888865165532</v>
+        <v>8.611482052016722</v>
       </c>
       <c r="E8" t="n">
-        <v>110.5384742595066</v>
+        <v>163.930789383622</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8342413306236267</v>
+        <v>0.7553641796112061</v>
       </c>
       <c r="G8" t="n">
-        <v>0.240936000000147</v>
+        <v>0.6406617000029655</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01939161494374275</v>
+        <v>0.001092163613066077</v>
       </c>
       <c r="I8" t="n">
-        <v>929.47063563396</v>
+        <v>924.077269138559</v>
       </c>
       <c r="J8" t="n">
-        <v>163.0203411533257</v>
+        <v>173.3836257832929</v>
       </c>
       <c r="K8" t="n">
-        <v>10.02671661219607</v>
+        <v>9.000000000081432</v>
       </c>
       <c r="L8" t="n">
-        <v>12.60768504445457</v>
+        <v>4.337722202762961e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>52.48186689381903</v>
+        <v>9.4528363996709</v>
       </c>
       <c r="N8" t="n">
-        <v>1.243827747030538</v>
+        <v>0.3885179480647096</v>
       </c>
       <c r="O8" t="b">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0.1949854791164398</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5688343000001623</v>
+        <v>1.816701000003377</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001183155691251159</v>
+        <v>0.0004794154083356261</v>
       </c>
       <c r="S8" t="n">
-        <v>806.0673663088908</v>
+        <v>864.9493507998546</v>
       </c>
       <c r="T8" t="n">
-        <v>150.0005526757936</v>
+        <v>166.3996631716699</v>
       </c>
       <c r="U8" t="n">
-        <v>9.000447461072532</v>
+        <v>9.000639485801056</v>
       </c>
       <c r="V8" t="n">
-        <v>136.0109543695238</v>
+        <v>59.12791400098217</v>
       </c>
       <c r="W8" t="n">
-        <v>39.46207841628696</v>
+        <v>2.468873788047972</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2175585959070006</v>
+        <v>0.3891574337843338</v>
       </c>
       <c r="Y8" t="b">
         <v>1</v>
@@ -1102,74 +1102,74 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>947.3537016694139</v>
+        <v>964.0515090933636</v>
       </c>
       <c r="D9" t="n">
-        <v>5.640381666124846</v>
+        <v>10.45024595140237</v>
       </c>
       <c r="E9" t="n">
-        <v>187.6566987571223</v>
+        <v>148.0832106138096</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8132951259613037</v>
+        <v>0.7394377589225769</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03370399999948859</v>
+        <v>0.3882597000047099</v>
       </c>
       <c r="H9" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.001092163613066077</v>
       </c>
       <c r="I9" t="n">
-        <v>947.353701669413</v>
+        <v>959.9604824860373</v>
       </c>
       <c r="J9" t="n">
-        <v>187.6566987571223</v>
+        <v>173.3836503845424</v>
       </c>
       <c r="K9" t="n">
-        <v>9.000641779862162</v>
+        <v>10.45024595140236</v>
       </c>
       <c r="L9" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>4.091026607326285</v>
       </c>
       <c r="M9" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>25.30043977073279</v>
       </c>
       <c r="N9" t="n">
-        <v>3.360260113737317</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8469259142875671</v>
+        <v>0.998335063457489</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1958651000004465</v>
+        <v>2.13017409999884</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0001682467700447887</v>
+        <v>0.000895558565389365</v>
       </c>
       <c r="S9" t="n">
-        <v>948.4655697655137</v>
+        <v>836.305643766047</v>
       </c>
       <c r="T9" t="n">
-        <v>187.7375329164716</v>
+        <v>152.7009777792938</v>
       </c>
       <c r="U9" t="n">
-        <v>9.000641779862162</v>
+        <v>10.32898335331059</v>
       </c>
       <c r="V9" t="n">
-        <v>1.111868096099784</v>
+        <v>127.7458653273167</v>
       </c>
       <c r="W9" t="n">
-        <v>0.080834159349223</v>
+        <v>4.617767165484139</v>
       </c>
       <c r="X9" t="n">
-        <v>3.360260113737317</v>
+        <v>0.1212625980917856</v>
       </c>
       <c r="Y9" t="b">
         <v>1</v>
@@ -1185,70 +1185,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>872.5361624196954</v>
+        <v>839.0963997956384</v>
       </c>
       <c r="D10" t="n">
-        <v>7.40157731907105</v>
+        <v>8.745637729024736</v>
       </c>
       <c r="E10" t="n">
-        <v>188.23047414045</v>
+        <v>207.7873942146539</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6951717734336853</v>
+        <v>0.8152469396591187</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1259501000004093</v>
+        <v>0.2232014000037452</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.002021597931161523</v>
       </c>
       <c r="I10" t="n">
-        <v>924.4806758069504</v>
+        <v>918.0450005179725</v>
       </c>
       <c r="J10" t="n">
-        <v>188.23047414045</v>
+        <v>207.7873942146539</v>
       </c>
       <c r="K10" t="n">
-        <v>9.000641579120586</v>
+        <v>9.000641513366228</v>
       </c>
       <c r="L10" t="n">
-        <v>51.94451338725503</v>
+        <v>78.94860072233416</v>
       </c>
       <c r="M10" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.599064260049536</v>
+        <v>0.2550037843414916</v>
       </c>
       <c r="O10" t="b">
         <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9762711524963379</v>
+        <v>0.9024824500083923</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3480361000001722</v>
+        <v>1.328955899996799</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0005839144578203559</v>
+        <v>0.000640415062662214</v>
       </c>
       <c r="S10" t="n">
-        <v>936.2163907322051</v>
+        <v>926.3685641401298</v>
       </c>
       <c r="T10" t="n">
-        <v>188.6839099378621</v>
+        <v>206.624483893216</v>
       </c>
       <c r="U10" t="n">
-        <v>9.000641731833941</v>
+        <v>9.000641685490871</v>
       </c>
       <c r="V10" t="n">
-        <v>63.68022831250971</v>
+        <v>87.27216434449144</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4534357974121122</v>
+        <v>1.162910321437948</v>
       </c>
       <c r="X10" t="n">
-        <v>1.599064412762891</v>
+        <v>0.2550039564661351</v>
       </c>
       <c r="Y10" t="b">
         <v>1</v>
@@ -1260,74 +1260,74 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>920.2162385330984</v>
+        <v>891.5370024825149</v>
       </c>
       <c r="D11" t="n">
-        <v>2.853205011335399</v>
+        <v>8.580225963721533</v>
       </c>
       <c r="E11" t="n">
-        <v>205.8182749431537</v>
+        <v>186.4931274131962</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8053354620933533</v>
+        <v>0.7312969565391541</v>
       </c>
       <c r="G11" t="n">
-        <v>0.07242620000033639</v>
+        <v>0.3294923000066774</v>
       </c>
       <c r="H11" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I11" t="n">
-        <v>924.4808457871983</v>
+        <v>922.2058257862417</v>
       </c>
       <c r="J11" t="n">
-        <v>205.8182749431532</v>
+        <v>186.4931274131962</v>
       </c>
       <c r="K11" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641777946276</v>
       </c>
       <c r="L11" t="n">
-        <v>4.264607254099928</v>
+        <v>30.66882330372675</v>
       </c>
       <c r="M11" t="n">
-        <v>5.684341886080801e-13</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>6.147436768526763</v>
+        <v>0.4204158142247429</v>
       </c>
       <c r="O11" t="b">
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9837148785591125</v>
+        <v>0.4762341380119324</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1928910999995423</v>
+        <v>1.322598399994604</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0001402409543516114</v>
+        <v>0.0002403802936896682</v>
       </c>
       <c r="S11" t="n">
-        <v>920.9436515999181</v>
+        <v>932.0457000915492</v>
       </c>
       <c r="T11" t="n">
-        <v>205.9480643316476</v>
+        <v>187.2500503227766</v>
       </c>
       <c r="U11" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641568320809</v>
       </c>
       <c r="V11" t="n">
-        <v>0.7274130668197358</v>
+        <v>40.50869760903424</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1297893884938333</v>
+        <v>0.7569229095803962</v>
       </c>
       <c r="X11" t="n">
-        <v>6.147436768526763</v>
+        <v>0.4204156045992757</v>
       </c>
       <c r="Y11" t="b">
         <v>1</v>
@@ -1339,74 +1339,74 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>842.1697898062494</v>
+        <v>951.8538140072274</v>
       </c>
       <c r="D12" t="n">
-        <v>8.285643848494162</v>
+        <v>9.693092562379064</v>
       </c>
       <c r="E12" t="n">
-        <v>195.9351771870371</v>
+        <v>163.0976055708734</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7797855734825134</v>
+        <v>0.7431839108467102</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1026173999998719</v>
+        <v>0.3517162999996799</v>
       </c>
       <c r="H12" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.001092163613066077</v>
       </c>
       <c r="I12" t="n">
-        <v>924.4807996458985</v>
+        <v>951.8538137347042</v>
       </c>
       <c r="J12" t="n">
-        <v>195.9351771870371</v>
+        <v>173.3840716653759</v>
       </c>
       <c r="K12" t="n">
-        <v>9.000641609028916</v>
+        <v>9.693093112460648</v>
       </c>
       <c r="L12" t="n">
-        <v>82.31100983964916</v>
+        <v>2.725231524891569e-07</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>10.28646609450249</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7149977605347537</v>
+        <v>5.500815838388462e-07</v>
       </c>
       <c r="O12" t="b">
         <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9096106886863708</v>
+        <v>0.5247876048088074</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5481517000007443</v>
+        <v>1.976943699999538</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0008831974118947983</v>
+        <v>0.0006861446890980005</v>
       </c>
       <c r="S12" t="n">
-        <v>932.0890579696306</v>
+        <v>861.8910928896213</v>
       </c>
       <c r="T12" t="n">
-        <v>196.7342501696838</v>
+        <v>166.9344270417922</v>
       </c>
       <c r="U12" t="n">
-        <v>9.000641805801305</v>
+        <v>9.606198203416927</v>
       </c>
       <c r="V12" t="n">
-        <v>89.91926816338128</v>
+        <v>89.96272111760607</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7990729826467202</v>
+        <v>3.83682147091875</v>
       </c>
       <c r="X12" t="n">
-        <v>0.7149979573071423</v>
+        <v>0.08689435896213737</v>
       </c>
       <c r="Y12" t="b">
         <v>1</v>
@@ -1418,74 +1418,74 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>955.7354822476517</v>
+        <v>972.2930207955989</v>
       </c>
       <c r="D13" t="n">
-        <v>13.812537298508</v>
+        <v>11.16436097658171</v>
       </c>
       <c r="E13" t="n">
-        <v>216.0857256505867</v>
+        <v>124.4958804142084</v>
       </c>
       <c r="F13" t="n">
-        <v>0.527676522731781</v>
+        <v>0.7440423965454102</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1596759999993083</v>
+        <v>0.365613800000574</v>
       </c>
       <c r="H13" t="n">
-        <v>0.003476700745522976</v>
+        <v>0.02071010880172253</v>
       </c>
       <c r="I13" t="n">
-        <v>891.8547026711234</v>
+        <v>848.8203180763823</v>
       </c>
       <c r="J13" t="n">
-        <v>216.085725650587</v>
+        <v>173.3835554328514</v>
       </c>
       <c r="K13" t="n">
-        <v>12.31824070222429</v>
+        <v>12.15242357642767</v>
       </c>
       <c r="L13" t="n">
-        <v>63.88077957652831</v>
+        <v>123.4727027192166</v>
       </c>
       <c r="M13" t="n">
-        <v>2.842170943040401e-13</v>
+        <v>48.88767501864302</v>
       </c>
       <c r="N13" t="n">
-        <v>1.494296596283716</v>
+        <v>0.9880625998459607</v>
       </c>
       <c r="O13" t="b">
         <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9450944066047668</v>
+        <v>0.9999998807907104</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.866138299999875</v>
+        <v>1.253005099999427</v>
       </c>
       <c r="R13" t="n">
-        <v>0.001127222087234259</v>
+        <v>0.001006041071377695</v>
       </c>
       <c r="S13" t="n">
-        <v>821.8058372243822</v>
+        <v>827.9536504745266</v>
       </c>
       <c r="T13" t="n">
-        <v>215.1732523174193</v>
+        <v>150.0005525189106</v>
       </c>
       <c r="U13" t="n">
-        <v>12.93542711549076</v>
+        <v>11.06324441835485</v>
       </c>
       <c r="V13" t="n">
-        <v>133.9296450232695</v>
+        <v>144.3393703210722</v>
       </c>
       <c r="W13" t="n">
-        <v>0.9124733331674122</v>
+        <v>25.50467210470219</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8771101830172441</v>
+        <v>0.1011165582268596</v>
       </c>
       <c r="Y13" t="b">
         <v>1</v>
@@ -1497,74 +1497,74 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>968.5770249210045</v>
+        <v>847.9817992634456</v>
       </c>
       <c r="D14" t="n">
-        <v>10.38388828828963</v>
+        <v>8.344559994233892</v>
       </c>
       <c r="E14" t="n">
-        <v>149.1615787620191</v>
+        <v>200.5512507437769</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8338657021522522</v>
+        <v>0.8313014507293701</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2432939000009355</v>
+        <v>0.2404978999984451</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01935457438230515</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I14" t="n">
-        <v>939.7160895250917</v>
+        <v>922.2060078739363</v>
       </c>
       <c r="J14" t="n">
-        <v>163.532100866892</v>
+        <v>200.5512507437768</v>
       </c>
       <c r="K14" t="n">
-        <v>11.83244120368154</v>
+        <v>9.000677688111637</v>
       </c>
       <c r="L14" t="n">
-        <v>28.86093539591286</v>
+        <v>74.22420861049068</v>
       </c>
       <c r="M14" t="n">
-        <v>14.37052210487289</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N14" t="n">
-        <v>1.448552915391909</v>
+        <v>0.6561176938777447</v>
       </c>
       <c r="O14" t="b">
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>0.984896183013916</v>
+        <v>0.9585037231445312</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.020322599999417</v>
+        <v>1.332565700002306</v>
       </c>
       <c r="R14" t="n">
-        <v>0.001203607534989715</v>
+        <v>0.0005724549409933388</v>
       </c>
       <c r="S14" t="n">
-        <v>816.8633303455302</v>
+        <v>925.7968598894247</v>
       </c>
       <c r="T14" t="n">
-        <v>158.0496142034982</v>
+        <v>199.82815021681</v>
       </c>
       <c r="U14" t="n">
-        <v>10.26640937474792</v>
+        <v>9.000641788958129</v>
       </c>
       <c r="V14" t="n">
-        <v>151.7136945754743</v>
+        <v>77.81506062597907</v>
       </c>
       <c r="W14" t="n">
-        <v>8.888035441479019</v>
+        <v>0.7231005269669026</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1174789135417118</v>
+        <v>0.656081794724237</v>
       </c>
       <c r="Y14" t="b">
         <v>1</v>
@@ -1576,74 +1576,74 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>870.1725279466541</v>
+        <v>935.9336484809282</v>
       </c>
       <c r="D15" t="n">
-        <v>8.444930492758932</v>
+        <v>9.521344162431488</v>
       </c>
       <c r="E15" t="n">
-        <v>207.6879680120539</v>
+        <v>120.6485878985782</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8276062607765198</v>
+        <v>0.7431839108467102</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1272275999999692</v>
+        <v>0.485958599994774</v>
       </c>
       <c r="H15" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.2544034421443939</v>
       </c>
       <c r="I15" t="n">
-        <v>924.4813581768642</v>
+        <v>891.4454468153482</v>
       </c>
       <c r="J15" t="n">
-        <v>207.6879680120543</v>
+        <v>165.1584996706972</v>
       </c>
       <c r="K15" t="n">
-        <v>9.000641723741971</v>
+        <v>12.26858390659553</v>
       </c>
       <c r="L15" t="n">
-        <v>54.30883023021011</v>
+        <v>44.48820166558005</v>
       </c>
       <c r="M15" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>44.50991177211904</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5557112309830394</v>
+        <v>2.747239744164046</v>
       </c>
       <c r="O15" t="b">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8443998694419861</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6010490999997273</v>
+        <v>1.447910799994133</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0005889525054953992</v>
+        <v>0.0007126907585188746</v>
       </c>
       <c r="S15" t="n">
-        <v>933.9087944432212</v>
+        <v>840.3806130664761</v>
       </c>
       <c r="T15" t="n">
-        <v>207.877314114899</v>
+        <v>150.0005514832273</v>
       </c>
       <c r="U15" t="n">
-        <v>9.000641873708618</v>
+        <v>9.404473062098202</v>
       </c>
       <c r="V15" t="n">
-        <v>63.73626649656705</v>
+        <v>95.5530354144521</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1893461028451213</v>
+        <v>29.35196358464907</v>
       </c>
       <c r="X15" t="n">
-        <v>0.5557113809496865</v>
+        <v>0.1168711003332863</v>
       </c>
       <c r="Y15" t="b">
         <v>1</v>
@@ -1655,74 +1655,74 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>956.6903877099024</v>
+        <v>962.3982561420007</v>
       </c>
       <c r="D16" t="n">
-        <v>5.802309338563953</v>
+        <v>11.1925117093596</v>
       </c>
       <c r="E16" t="n">
-        <v>209.2168315742735</v>
+        <v>155.7149330005663</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8140485286712646</v>
+        <v>0.7394377589225769</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05658439999933762</v>
+        <v>0.4060150000004796</v>
       </c>
       <c r="H16" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.001615169807337224</v>
       </c>
       <c r="I16" t="n">
-        <v>956.6903877099055</v>
+        <v>924.887864151394</v>
       </c>
       <c r="J16" t="n">
-        <v>209.2168315742733</v>
+        <v>173.384028678165</v>
       </c>
       <c r="K16" t="n">
-        <v>9.000641779862162</v>
+        <v>11.19251995325138</v>
       </c>
       <c r="L16" t="n">
-        <v>3.069544618483633e-12</v>
+        <v>37.51039199060676</v>
       </c>
       <c r="M16" t="n">
-        <v>1.70530256582424e-13</v>
+        <v>17.6690956775987</v>
       </c>
       <c r="N16" t="n">
-        <v>3.198332441298209</v>
+        <v>8.24389178788465e-06</v>
       </c>
       <c r="O16" t="b">
         <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7027662992477417</v>
+        <v>0.9308580756187439</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2314889999997831</v>
+        <v>1.873916500000632</v>
       </c>
       <c r="R16" t="n">
-        <v>9.874146780930459e-05</v>
+        <v>0.0008479378884658217</v>
       </c>
       <c r="S16" t="n">
-        <v>957.801214310937</v>
+        <v>843.2795809991143</v>
       </c>
       <c r="T16" t="n">
-        <v>209.3596744846091</v>
+        <v>160.632657255986</v>
       </c>
       <c r="U16" t="n">
-        <v>9.000641779862162</v>
+        <v>11.11650258745972</v>
       </c>
       <c r="V16" t="n">
-        <v>1.110826601034546</v>
+        <v>119.1186751428864</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1428429103355597</v>
+        <v>4.917724255419671</v>
       </c>
       <c r="X16" t="n">
-        <v>3.198332441298209</v>
+        <v>0.07600912189987241</v>
       </c>
       <c r="Y16" t="b">
         <v>1</v>
@@ -1734,74 +1734,74 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>934.5775048631689</v>
+        <v>817.2041417244839</v>
       </c>
       <c r="D17" t="n">
-        <v>7.914524483267093</v>
+        <v>7.824402416484763</v>
       </c>
       <c r="E17" t="n">
-        <v>117.89617775543</v>
+        <v>196.8825697422384</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6712142825126648</v>
+        <v>0.8500553369522095</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3859142000001157</v>
+        <v>0.4162807000029716</v>
       </c>
       <c r="H17" t="n">
-        <v>0.001524175517261028</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I17" t="n">
-        <v>910.8501730697529</v>
+        <v>922.2075900409461</v>
       </c>
       <c r="J17" t="n">
-        <v>173.1915857150382</v>
+        <v>196.882569742238</v>
       </c>
       <c r="K17" t="n">
-        <v>10.24288475891473</v>
+        <v>9.000668275672897</v>
       </c>
       <c r="L17" t="n">
-        <v>23.72733179341594</v>
+        <v>105.0034483164623</v>
       </c>
       <c r="M17" t="n">
-        <v>55.29540795960823</v>
+        <v>3.979039320256561e-13</v>
       </c>
       <c r="N17" t="n">
-        <v>2.328360275647639</v>
+        <v>1.176265859188134</v>
       </c>
       <c r="O17" t="b">
         <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9999998807907104</v>
+        <v>0.9848967790603638</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.6403121000003011</v>
+        <v>1.235699799995928</v>
       </c>
       <c r="R17" t="n">
-        <v>0.001139359083026648</v>
+        <v>0.0008181274752132595</v>
       </c>
       <c r="S17" t="n">
-        <v>805.7752470501516</v>
+        <v>923.7990498220126</v>
       </c>
       <c r="T17" t="n">
-        <v>150.0005526461474</v>
+        <v>197.3817425209418</v>
       </c>
       <c r="U17" t="n">
-        <v>9.000542663875235</v>
+        <v>9.000641793414523</v>
       </c>
       <c r="V17" t="n">
-        <v>128.8022578130173</v>
+        <v>106.5949080975288</v>
       </c>
       <c r="W17" t="n">
-        <v>32.10437489071744</v>
+        <v>0.4991727787034108</v>
       </c>
       <c r="X17" t="n">
-        <v>1.086018180608142</v>
+        <v>1.17623937692976</v>
       </c>
       <c r="Y17" t="b">
         <v>1</v>
@@ -1817,70 +1817,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>936.6538078905809</v>
+        <v>936.4826269507254</v>
       </c>
       <c r="D18" t="n">
-        <v>8.503736900599202</v>
+        <v>10.76011747898417</v>
       </c>
       <c r="E18" t="n">
-        <v>132.2452147401917</v>
+        <v>153.3598906632496</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8141006827354431</v>
+        <v>0.7394377589225769</v>
       </c>
       <c r="G18" t="n">
-        <v>0.318269400000645</v>
+        <v>0.4538985999970464</v>
       </c>
       <c r="H18" t="n">
-        <v>0.001156819984316826</v>
+        <v>0.001188212772831321</v>
       </c>
       <c r="I18" t="n">
-        <v>949.9796645045041</v>
+        <v>909.3882357558507</v>
       </c>
       <c r="J18" t="n">
-        <v>173.1939764038761</v>
+        <v>173.3837824921653</v>
       </c>
       <c r="K18" t="n">
-        <v>9.122331467672074</v>
+        <v>10.59486606830883</v>
       </c>
       <c r="L18" t="n">
-        <v>13.32585661392318</v>
+        <v>27.09439119487467</v>
       </c>
       <c r="M18" t="n">
-        <v>40.94876166368439</v>
+        <v>20.02389182891571</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6185945670728721</v>
+        <v>0.1652514106753458</v>
       </c>
       <c r="O18" t="b">
         <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>0.99998939037323</v>
+        <v>0.9735525846481323</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9917552999995678</v>
+        <v>2.024149200005922</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0011518340324983</v>
+        <v>0.0007249211193993688</v>
       </c>
       <c r="S18" t="n">
-        <v>805.8606740553065</v>
+        <v>839.613517430681</v>
       </c>
       <c r="T18" t="n">
-        <v>150.0005526374236</v>
+        <v>157.3960818469052</v>
       </c>
       <c r="U18" t="n">
-        <v>9.00037640753019</v>
+        <v>10.67762527762256</v>
       </c>
       <c r="V18" t="n">
-        <v>130.7931338352744</v>
+        <v>96.86910952004439</v>
       </c>
       <c r="W18" t="n">
-        <v>17.7553378972319</v>
+        <v>4.036191183655603</v>
       </c>
       <c r="X18" t="n">
-        <v>0.4966395069309879</v>
+        <v>0.08249220136161206</v>
       </c>
       <c r="Y18" t="b">
         <v>1</v>
@@ -1892,74 +1892,74 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>939.8622530026555</v>
+        <v>943.6326863954179</v>
       </c>
       <c r="D19" t="n">
-        <v>8.270832149839636</v>
+        <v>4.869314538243593</v>
       </c>
       <c r="E19" t="n">
-        <v>118.198925961433</v>
+        <v>177.0200181795361</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6280300617218018</v>
+        <v>0.6927988529205322</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1854825999998866</v>
+        <v>0.07825569999840809</v>
       </c>
       <c r="H19" t="n">
-        <v>0.01939161494374275</v>
+        <v>0.0009034593240357935</v>
       </c>
       <c r="I19" t="n">
-        <v>929.4714824948228</v>
+        <v>943.6326863954175</v>
       </c>
       <c r="J19" t="n">
-        <v>163.0132626987895</v>
+        <v>177.0200181796648</v>
       </c>
       <c r="K19" t="n">
-        <v>10.02689024954314</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L19" t="n">
-        <v>10.39077050783271</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="M19" t="n">
-        <v>44.81433673735646</v>
+        <v>1.286650785914389e-10</v>
       </c>
       <c r="N19" t="n">
-        <v>1.756058099703504</v>
+        <v>4.131327241618569</v>
       </c>
       <c r="O19" t="b">
         <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9999998807907104</v>
+        <v>0.9963584542274475</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.5587272000011581</v>
+        <v>0.6011625999963144</v>
       </c>
       <c r="R19" t="n">
-        <v>0.001170899602584541</v>
+        <v>0.0003446523915044963</v>
       </c>
       <c r="S19" t="n">
-        <v>805.9853378010438</v>
+        <v>949.6456948639936</v>
       </c>
       <c r="T19" t="n">
-        <v>150.0005526554787</v>
+        <v>178.7337284714598</v>
       </c>
       <c r="U19" t="n">
-        <v>9.000651050526621</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V19" t="n">
-        <v>133.8769152016117</v>
+        <v>6.013008468575777</v>
       </c>
       <c r="W19" t="n">
-        <v>31.80162669404572</v>
+        <v>1.713710291923746</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7298189006869844</v>
+        <v>4.131327241618569</v>
       </c>
       <c r="Y19" t="b">
         <v>1</v>
@@ -1975,70 +1975,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>868.926638772415</v>
+        <v>874.9579323382688</v>
       </c>
       <c r="D20" t="n">
-        <v>8.696047358868302</v>
+        <v>7.029400784356617</v>
       </c>
       <c r="E20" t="n">
-        <v>208.0304100682312</v>
+        <v>189.9770764073022</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8221606016159058</v>
+        <v>0.8036876320838928</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1029772000001685</v>
+        <v>0.2581949999948847</v>
       </c>
       <c r="H20" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I20" t="n">
-        <v>924.4806708797444</v>
+        <v>922.205828906969</v>
       </c>
       <c r="J20" t="n">
-        <v>208.0304100682312</v>
+        <v>189.9770764073022</v>
       </c>
       <c r="K20" t="n">
-        <v>9.000641674887545</v>
+        <v>9.000641557103457</v>
       </c>
       <c r="L20" t="n">
-        <v>55.55403210732936</v>
+        <v>47.24789656870018</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3045943160192426</v>
+        <v>1.97124077274684</v>
       </c>
       <c r="O20" t="b">
         <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7836688160896301</v>
+        <v>0.9935641884803772</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.4802214000010281</v>
+        <v>1.172792100005609</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0006003818125464022</v>
+        <v>0.0003398375702090561</v>
       </c>
       <c r="S20" t="n">
-        <v>933.7561770506289</v>
+        <v>929.102794511669</v>
       </c>
       <c r="T20" t="n">
-        <v>208.2252571417574</v>
+        <v>190.8634976096435</v>
       </c>
       <c r="U20" t="n">
-        <v>9.000641910067984</v>
+        <v>9.000641563284724</v>
       </c>
       <c r="V20" t="n">
-        <v>64.82953827821393</v>
+        <v>54.14486217340016</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1948470735261481</v>
+        <v>0.8864212023412392</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3045945511996813</v>
+        <v>1.971240778928107</v>
       </c>
       <c r="Y20" t="b">
         <v>1</v>
@@ -2054,70 +2054,70 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>964.2438355600153</v>
+        <v>926.5635058127848</v>
       </c>
       <c r="D21" t="n">
-        <v>11.28084661540241</v>
+        <v>10.63843987747379</v>
       </c>
       <c r="E21" t="n">
-        <v>162.6883530273284</v>
+        <v>139.0715076585351</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8342413306236267</v>
+        <v>0.7394377589225769</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1876532999995106</v>
+        <v>0.5248902000021189</v>
       </c>
       <c r="H21" t="n">
-        <v>0.01565238833427429</v>
+        <v>0.01950404606759548</v>
       </c>
       <c r="I21" t="n">
-        <v>939.7149737679706</v>
+        <v>892.2543321903079</v>
       </c>
       <c r="J21" t="n">
-        <v>166.3423312252067</v>
+        <v>165.1586350385763</v>
       </c>
       <c r="K21" t="n">
-        <v>12.31845272855687</v>
+        <v>10.63842400271545</v>
       </c>
       <c r="L21" t="n">
-        <v>24.52886179204472</v>
+        <v>34.30917362247692</v>
       </c>
       <c r="M21" t="n">
-        <v>3.653978197878217</v>
+        <v>26.08712738004115</v>
       </c>
       <c r="N21" t="n">
-        <v>1.03760611315446</v>
+        <v>1.587475833630947e-05</v>
       </c>
       <c r="O21" t="b">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2471821308135986</v>
+        <v>0.9999071359634399</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.000615999999354</v>
+        <v>1.379199899995001</v>
       </c>
       <c r="R21" t="n">
-        <v>0.000967298517934978</v>
+        <v>0.0007441879715770483</v>
       </c>
       <c r="S21" t="n">
-        <v>846.9686650678743</v>
+        <v>829.2742070300852</v>
       </c>
       <c r="T21" t="n">
-        <v>171.4171044825447</v>
+        <v>150.0005523093434</v>
       </c>
       <c r="U21" t="n">
-        <v>11.1130684919404</v>
+        <v>10.54367341280924</v>
       </c>
       <c r="V21" t="n">
-        <v>117.275170492141</v>
+        <v>97.28929878269957</v>
       </c>
       <c r="W21" t="n">
-        <v>8.728751455216269</v>
+        <v>10.92904465080832</v>
       </c>
       <c r="X21" t="n">
-        <v>0.1677781234620088</v>
+        <v>0.09476646466454852</v>
       </c>
       <c r="Y21" t="b">
         <v>1</v>
@@ -2129,74 +2129,74 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>915.1064995175359</v>
+        <v>966.9696635119175</v>
       </c>
       <c r="D22" t="n">
-        <v>5.136058296964662</v>
+        <v>8.777587584971407</v>
       </c>
       <c r="E22" t="n">
-        <v>212.8896076452998</v>
+        <v>131.5979617419729</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7656013369560242</v>
+        <v>0.7539470195770264</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1357451999992918</v>
+        <v>0.5124885000041104</v>
       </c>
       <c r="H22" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.01405216194689274</v>
       </c>
       <c r="I22" t="n">
-        <v>924.4806678907321</v>
+        <v>950.6929209130627</v>
       </c>
       <c r="J22" t="n">
-        <v>212.8896076453</v>
+        <v>172.079418211541</v>
       </c>
       <c r="K22" t="n">
-        <v>9.000641564512286</v>
+        <v>9.977346525009901</v>
       </c>
       <c r="L22" t="n">
-        <v>9.374168373196198</v>
+        <v>16.27674259885475</v>
       </c>
       <c r="M22" t="n">
-        <v>1.70530256582424e-13</v>
+        <v>40.48145646956812</v>
       </c>
       <c r="N22" t="n">
-        <v>3.864583267547624</v>
+        <v>1.199758940038494</v>
       </c>
       <c r="O22" t="b">
         <v>1</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5002244710922241</v>
+        <v>0.9999967813491821</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.2098779999996623</v>
+        <v>1.522029399995517</v>
       </c>
       <c r="R22" t="n">
-        <v>0.0001237623946508393</v>
+        <v>0.0008885128190740943</v>
       </c>
       <c r="S22" t="n">
-        <v>915.6495976114203</v>
+        <v>846.7393640978421</v>
       </c>
       <c r="T22" t="n">
-        <v>213.0142939911524</v>
+        <v>150.0005525151687</v>
       </c>
       <c r="U22" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641678781566</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5430980938843959</v>
+        <v>120.2302994140754</v>
       </c>
       <c r="W22" t="n">
-        <v>0.124686345852524</v>
+        <v>18.40259077319578</v>
       </c>
       <c r="X22" t="n">
-        <v>3.8645834828975</v>
+        <v>0.2230540938101591</v>
       </c>
       <c r="Y22" t="b">
         <v>1</v>
@@ -2208,74 +2208,74 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>918.6608125766529</v>
+        <v>940.8319683457532</v>
       </c>
       <c r="D23" t="n">
-        <v>13.0057444259856</v>
+        <v>9.77003585630926</v>
       </c>
       <c r="E23" t="n">
-        <v>189.6928737188748</v>
+        <v>138.1800630880161</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6327797174453735</v>
+        <v>0.7431839108467102</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1335053000002517</v>
+        <v>0.4792442999969353</v>
       </c>
       <c r="H23" t="n">
-        <v>0.001114324550144374</v>
+        <v>0.0137840760871768</v>
       </c>
       <c r="I23" t="n">
-        <v>891.8760989702231</v>
+        <v>940.8480978120622</v>
       </c>
       <c r="J23" t="n">
-        <v>189.6928737188764</v>
+        <v>165.1588553016968</v>
       </c>
       <c r="K23" t="n">
-        <v>11.69500114517549</v>
+        <v>10.04028612056689</v>
       </c>
       <c r="L23" t="n">
-        <v>26.78471360642982</v>
+        <v>0.0161294663089393</v>
       </c>
       <c r="M23" t="n">
-        <v>1.591615728102624e-12</v>
+        <v>26.97879221368075</v>
       </c>
       <c r="N23" t="n">
-        <v>1.310743280810108</v>
+        <v>0.2702502642576334</v>
       </c>
       <c r="O23" t="b">
         <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1018594428896904</v>
+        <v>0.9999563694000244</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.094349099999818</v>
+        <v>1.302425599998969</v>
       </c>
       <c r="R23" t="n">
-        <v>0.001309116254560649</v>
+        <v>0.0007549930014647543</v>
       </c>
       <c r="S23" t="n">
-        <v>951.1066187313785</v>
+        <v>837.9046021103494</v>
       </c>
       <c r="T23" t="n">
-        <v>185.0358251663455</v>
+        <v>150.0005515760341</v>
       </c>
       <c r="U23" t="n">
-        <v>12.16920300061558</v>
+        <v>9.648040810611135</v>
       </c>
       <c r="V23" t="n">
-        <v>32.44580615472557</v>
+        <v>102.9273662354038</v>
       </c>
       <c r="W23" t="n">
-        <v>4.65704855252929</v>
+        <v>11.82048848801801</v>
       </c>
       <c r="X23" t="n">
-        <v>0.8365414253700258</v>
+        <v>0.1219950456981245</v>
       </c>
       <c r="Y23" t="b">
         <v>1</v>
@@ -2287,74 +2287,74 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>962.4592655014204</v>
+        <v>969.2701716322383</v>
       </c>
       <c r="D24" t="n">
-        <v>10.81607633529812</v>
+        <v>6.547893863015358</v>
       </c>
       <c r="E24" t="n">
-        <v>138.4444598484636</v>
+        <v>206.2024201963596</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8342413306236267</v>
+        <v>0.7118977904319763</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2111710000008316</v>
+        <v>0.0707683000000543</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0008712398703210056</v>
+        <v>0.0008416271884925663</v>
       </c>
       <c r="I24" t="n">
-        <v>962.459276802575</v>
+        <v>969.2701716327872</v>
       </c>
       <c r="J24" t="n">
-        <v>173.1913501718469</v>
+        <v>206.2024300514465</v>
       </c>
       <c r="K24" t="n">
-        <v>10.81607600685761</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L24" t="n">
-        <v>1.130115458636283e-05</v>
+        <v>5.488800525199622e-10</v>
       </c>
       <c r="M24" t="n">
-        <v>34.74689032338324</v>
+        <v>9.855086830157234e-06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.284405156733783e-07</v>
+        <v>2.452747916846804</v>
       </c>
       <c r="O24" t="b">
         <v>1</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9996767044067383</v>
+        <v>0.4435377717018127</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.5083945999995194</v>
+        <v>0.4324574999991455</v>
       </c>
       <c r="R24" t="n">
-        <v>0.002355154370889068</v>
+        <v>3.048932194360532e-05</v>
       </c>
       <c r="S24" t="n">
-        <v>800.0001033883907</v>
+        <v>967.433215288818</v>
       </c>
       <c r="T24" t="n">
-        <v>150.6460123542645</v>
+        <v>206.1015408176048</v>
       </c>
       <c r="U24" t="n">
-        <v>10.39925094392139</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V24" t="n">
-        <v>162.4591621130297</v>
+        <v>1.836956343420297</v>
       </c>
       <c r="W24" t="n">
-        <v>12.20155250580089</v>
+        <v>0.1008793787548257</v>
       </c>
       <c r="X24" t="n">
-        <v>0.4168253913767348</v>
+        <v>2.452747916846804</v>
       </c>
       <c r="Y24" t="b">
         <v>1</v>
@@ -2370,70 +2370,70 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>867.2993295782069</v>
+        <v>874.6214748419038</v>
       </c>
       <c r="D25" t="n">
-        <v>6.407002093161154</v>
+        <v>8.270712484139578</v>
       </c>
       <c r="E25" t="n">
-        <v>198.9489646310919</v>
+        <v>198.0061817033346</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8415312170982361</v>
+        <v>0.78890460729599</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1013672000008228</v>
+        <v>0.2701446999999462</v>
       </c>
       <c r="H25" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I25" t="n">
-        <v>924.4806722595536</v>
+        <v>922.2058285563212</v>
       </c>
       <c r="J25" t="n">
-        <v>198.9489646310918</v>
+        <v>198.0061817033346</v>
       </c>
       <c r="K25" t="n">
-        <v>9.000641606286587</v>
+        <v>9.000641671372222</v>
       </c>
       <c r="L25" t="n">
-        <v>57.18134268134668</v>
+        <v>47.58435371441738</v>
       </c>
       <c r="M25" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.593639513125433</v>
+        <v>0.7299291872326439</v>
       </c>
       <c r="O25" t="b">
         <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9919732809066772</v>
+        <v>0.9414178133010864</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.4867912999998225</v>
+        <v>1.466110900000785</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0006223596865311265</v>
+        <v>0.0003356573870405555</v>
       </c>
       <c r="S25" t="n">
-        <v>934.0690005105253</v>
+        <v>928.2175262741487</v>
       </c>
       <c r="T25" t="n">
-        <v>199.5267464002485</v>
+        <v>198.0060002752699</v>
       </c>
       <c r="U25" t="n">
-        <v>9.000641778849703</v>
+        <v>9.00064177836744</v>
       </c>
       <c r="V25" t="n">
-        <v>66.76967093231838</v>
+        <v>53.59605143224485</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5777817691566156</v>
+        <v>0.000181428064706779</v>
       </c>
       <c r="X25" t="n">
-        <v>2.593639685688549</v>
+        <v>0.7299292942278619</v>
       </c>
       <c r="Y25" t="b">
         <v>1</v>
@@ -2445,74 +2445,74 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>951.9562658618662</v>
+        <v>872.1838157186767</v>
       </c>
       <c r="D26" t="n">
-        <v>11.22672540610299</v>
+        <v>8.730761291996881</v>
       </c>
       <c r="E26" t="n">
-        <v>115.4908264912468</v>
+        <v>192.1902398812833</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8342413306236267</v>
+        <v>0.8152469396591187</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2025833999996394</v>
+        <v>0.2707813000015449</v>
       </c>
       <c r="H26" t="n">
-        <v>0.01565238833427429</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I26" t="n">
-        <v>939.7162882422027</v>
+        <v>922.2058270341867</v>
       </c>
       <c r="J26" t="n">
-        <v>163.0146506522758</v>
+        <v>192.1902398812833</v>
       </c>
       <c r="K26" t="n">
-        <v>12.31841773728678</v>
+        <v>9.000641581954957</v>
       </c>
       <c r="L26" t="n">
-        <v>12.23997761966348</v>
+        <v>50.02201131550999</v>
       </c>
       <c r="M26" t="n">
-        <v>47.52382416102897</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.091692331183785</v>
+        <v>0.2698802899580759</v>
       </c>
       <c r="O26" t="b">
         <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9999998807907104</v>
+        <v>0.8771054148674011</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.5500197999990633</v>
+        <v>1.26866959999461</v>
       </c>
       <c r="R26" t="n">
-        <v>0.003563979174941778</v>
+        <v>0.0003488020156510174</v>
       </c>
       <c r="S26" t="n">
-        <v>800.000032276658</v>
+        <v>928.3880205548303</v>
       </c>
       <c r="T26" t="n">
-        <v>150.0005529051632</v>
+        <v>192.5650689080193</v>
       </c>
       <c r="U26" t="n">
-        <v>10.55151298835904</v>
+        <v>9.000641519877467</v>
       </c>
       <c r="V26" t="n">
-        <v>151.9562335852082</v>
+        <v>56.20420483615362</v>
       </c>
       <c r="W26" t="n">
-        <v>34.50972641391637</v>
+        <v>0.3748290267360233</v>
       </c>
       <c r="X26" t="n">
-        <v>0.6752124177439569</v>
+        <v>0.2698802278805861</v>
       </c>
       <c r="Y26" t="b">
         <v>1</v>
@@ -2528,70 +2528,70 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>891.0725068260823</v>
+        <v>865.4255032833089</v>
       </c>
       <c r="D27" t="n">
-        <v>6.329903495610772</v>
+        <v>8.322304625737797</v>
       </c>
       <c r="E27" t="n">
-        <v>212.3937396458292</v>
+        <v>212.3803957552401</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8062700033187866</v>
+        <v>0.8276203870773315</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1235274000009667</v>
+        <v>0.2622172000046703</v>
       </c>
       <c r="H27" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I27" t="n">
-        <v>924.480668220032</v>
+        <v>922.2058346073445</v>
       </c>
       <c r="J27" t="n">
-        <v>212.3937396458292</v>
+        <v>212.3803957552401</v>
       </c>
       <c r="K27" t="n">
-        <v>9.000641647637073</v>
+        <v>9.000641524610058</v>
       </c>
       <c r="L27" t="n">
-        <v>33.40816139394974</v>
+        <v>56.78033132403561</v>
       </c>
       <c r="M27" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.670738152026301</v>
+        <v>0.6783368988722618</v>
       </c>
       <c r="O27" t="b">
         <v>1</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9695480465888977</v>
+        <v>0.9516874551773071</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.375311600000714</v>
+        <v>1.183657100002165</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0004044155066367239</v>
+        <v>0.0004550183948595077</v>
       </c>
       <c r="S27" t="n">
-        <v>936.2941706744315</v>
+        <v>929.6605480721981</v>
       </c>
       <c r="T27" t="n">
-        <v>212.5300074365715</v>
+        <v>211.135083321386</v>
       </c>
       <c r="U27" t="n">
-        <v>9.000641743714763</v>
+        <v>9.000641392099171</v>
       </c>
       <c r="V27" t="n">
-        <v>45.22166384834918</v>
+        <v>64.23504478888924</v>
       </c>
       <c r="W27" t="n">
-        <v>0.1362677907423802</v>
+        <v>1.24531243385411</v>
       </c>
       <c r="X27" t="n">
-        <v>2.670738248103991</v>
+        <v>0.6783367663613742</v>
       </c>
       <c r="Y27" t="b">
         <v>1</v>
@@ -2603,74 +2603,74 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>937.2035501383766</v>
+        <v>964.2581785076476</v>
       </c>
       <c r="D28" t="n">
-        <v>15.33543121419699</v>
+        <v>4.770179906475832</v>
       </c>
       <c r="E28" t="n">
-        <v>197.5726330513037</v>
+        <v>181.4013806326738</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5688954591751099</v>
+        <v>0.6903558969497681</v>
       </c>
       <c r="G28" t="n">
-        <v>0.163131200000862</v>
+        <v>0.1478638999979012</v>
       </c>
       <c r="H28" t="n">
-        <v>0.002681383397430182</v>
+        <v>0.0008412539027631283</v>
       </c>
       <c r="I28" t="n">
-        <v>891.8549263762808</v>
+        <v>964.2581785076388</v>
       </c>
       <c r="J28" t="n">
-        <v>203.1418454673367</v>
+        <v>181.4123329323168</v>
       </c>
       <c r="K28" t="n">
-        <v>12.31792562758323</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L28" t="n">
-        <v>45.34862376209583</v>
+        <v>8.753886504564434e-12</v>
       </c>
       <c r="M28" t="n">
-        <v>5.569212416032968</v>
+        <v>0.0109522996430087</v>
       </c>
       <c r="N28" t="n">
-        <v>3.017505586613755</v>
+        <v>4.23046187338633</v>
       </c>
       <c r="O28" t="b">
         <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>0.99819415807724</v>
+        <v>0.9971801042556763</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.4532982999990054</v>
+        <v>0.5750000000043656</v>
       </c>
       <c r="R28" t="n">
-        <v>0.001568982377648354</v>
+        <v>0.0001858387549873441</v>
       </c>
       <c r="S28" t="n">
-        <v>800.000040246188</v>
+        <v>964.4114647860148</v>
       </c>
       <c r="T28" t="n">
-        <v>196.5024719743436</v>
+        <v>182.3873961829869</v>
       </c>
       <c r="U28" t="n">
-        <v>13.79522426934381</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V28" t="n">
-        <v>137.2035098921887</v>
+        <v>0.1532862783672044</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07016107696009</v>
+        <v>0.9860155503130557</v>
       </c>
       <c r="X28" t="n">
-        <v>1.540206944853184</v>
+        <v>4.23046187338633</v>
       </c>
       <c r="Y28" t="b">
         <v>1</v>
@@ -2682,74 +2682,74 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>842.7758475776127</v>
+        <v>940.0087588505779</v>
       </c>
       <c r="D29" t="n">
-        <v>8.005908950111959</v>
+        <v>4.952363154887061</v>
       </c>
       <c r="E29" t="n">
-        <v>210.5470878388263</v>
+        <v>205.9263920869823</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8184717893600464</v>
+        <v>0.7136481404304504</v>
       </c>
       <c r="G29" t="n">
-        <v>0.09438690000024508</v>
+        <v>0.0826221000024816</v>
       </c>
       <c r="H29" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.0008420366793870926</v>
       </c>
       <c r="I29" t="n">
-        <v>924.4809262433802</v>
+        <v>940.0087588505777</v>
       </c>
       <c r="J29" t="n">
-        <v>210.5470878388263</v>
+        <v>205.9263920869818</v>
       </c>
       <c r="K29" t="n">
-        <v>9.000641531991317</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L29" t="n">
-        <v>81.70507866576747</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>5.400124791776761e-13</v>
       </c>
       <c r="N29" t="n">
-        <v>0.994732581879358</v>
+        <v>4.048278624975101</v>
       </c>
       <c r="O29" t="b">
         <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>0.898146390914917</v>
+        <v>0.9962222576141357</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.4205766999984917</v>
+        <v>0.5086211999951047</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0008703551138751209</v>
+        <v>4.604656714946032e-05</v>
       </c>
       <c r="S29" t="n">
-        <v>931.022166984422</v>
+        <v>942.370111593135</v>
       </c>
       <c r="T29" t="n">
-        <v>210.8336785592793</v>
+        <v>205.677488734921</v>
       </c>
       <c r="U29" t="n">
-        <v>9.000641858603196</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V29" t="n">
-        <v>88.24631940680933</v>
+        <v>2.361352742557074</v>
       </c>
       <c r="W29" t="n">
-        <v>0.286590720453006</v>
+        <v>0.2489033520612907</v>
       </c>
       <c r="X29" t="n">
-        <v>0.9947329084912369</v>
+        <v>4.048278624975101</v>
       </c>
       <c r="Y29" t="b">
         <v>1</v>
@@ -2765,70 +2765,70 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>977.4020370722075</v>
+        <v>990.9456609016629</v>
       </c>
       <c r="D30" t="n">
-        <v>5.524665656531412</v>
+        <v>4.084392595623243</v>
       </c>
       <c r="E30" t="n">
-        <v>204.7693296104794</v>
+        <v>187.1081648616498</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8122895956039429</v>
+        <v>0.6832804679870605</v>
       </c>
       <c r="G30" t="n">
-        <v>0.03380620000098133</v>
+        <v>0.08865830000286223</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0006574049475602806</v>
+        <v>0.0008359886123798788</v>
       </c>
       <c r="I30" t="n">
-        <v>977.4021474280188</v>
+        <v>990.9456609019934</v>
       </c>
       <c r="J30" t="n">
-        <v>204.769249955451</v>
+        <v>187.1082677671345</v>
       </c>
       <c r="K30" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0001103558113300096</v>
+        <v>3.304876372567378e-10</v>
       </c>
       <c r="M30" t="n">
-        <v>7.965502842921524e-05</v>
+        <v>0.000102905484737903</v>
       </c>
       <c r="N30" t="n">
-        <v>3.47597612333075</v>
+        <v>4.916249184238919</v>
       </c>
       <c r="O30" t="b">
         <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>0.8491940498352051</v>
+        <v>0.9993795156478882</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.1607930999998644</v>
+        <v>0.4492645999998786</v>
       </c>
       <c r="R30" t="n">
-        <v>8.892534970073029e-05</v>
+        <v>0.0001446526584913954</v>
       </c>
       <c r="S30" t="n">
-        <v>978.4543271177363</v>
+        <v>988.7245600284743</v>
       </c>
       <c r="T30" t="n">
-        <v>204.891726295927</v>
+        <v>187.8034768565056</v>
       </c>
       <c r="U30" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V30" t="n">
-        <v>1.052290045528821</v>
+        <v>2.221100873188561</v>
       </c>
       <c r="W30" t="n">
-        <v>0.1223966854475691</v>
+        <v>0.6953119948558708</v>
       </c>
       <c r="X30" t="n">
-        <v>3.47597612333075</v>
+        <v>4.916249184238919</v>
       </c>
       <c r="Y30" t="b">
         <v>1</v>
@@ -2844,70 +2844,70 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>882.8955330312515</v>
+        <v>863.2390053591722</v>
       </c>
       <c r="D31" t="n">
-        <v>8.380686905239088</v>
+        <v>8.474556643405082</v>
       </c>
       <c r="E31" t="n">
-        <v>205.836830216832</v>
+        <v>206.9437995896181</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5772911310195923</v>
+        <v>0.8125014901161194</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1368141999992076</v>
+        <v>0.2753408999997191</v>
       </c>
       <c r="H31" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I31" t="n">
-        <v>924.4806701329694</v>
+        <v>922.2058295565251</v>
       </c>
       <c r="J31" t="n">
-        <v>205.836830216832</v>
+        <v>206.9437995896182</v>
       </c>
       <c r="K31" t="n">
-        <v>9.000641616808313</v>
+        <v>9.000641689441041</v>
       </c>
       <c r="L31" t="n">
-        <v>41.58513710171792</v>
+        <v>58.96682419735293</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="N31" t="n">
-        <v>0.6199547115692248</v>
+        <v>0.5260850460359592</v>
       </c>
       <c r="O31" t="b">
         <v>1</v>
       </c>
       <c r="P31" t="n">
-        <v>0.7053912878036499</v>
+        <v>0.936190664768219</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.4051727000005485</v>
+        <v>1.38021110000409</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0004726394254248589</v>
+        <v>0.0004545041883829981</v>
       </c>
       <c r="S31" t="n">
-        <v>935.5461732586581</v>
+        <v>928.0212263047378</v>
       </c>
       <c r="T31" t="n">
-        <v>205.987548388324</v>
+        <v>206.0854384359355</v>
       </c>
       <c r="U31" t="n">
-        <v>9.000641897143414</v>
+        <v>9.000641774578158</v>
       </c>
       <c r="V31" t="n">
-        <v>52.6506402274066</v>
+        <v>64.78222094556554</v>
       </c>
       <c r="W31" t="n">
-        <v>0.1507181714919454</v>
+        <v>0.8583611536825515</v>
       </c>
       <c r="X31" t="n">
-        <v>0.6199549919043257</v>
+        <v>0.5260851311730761</v>
       </c>
       <c r="Y31" t="b">
         <v>1</v>
@@ -2923,70 +2923,70 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>884.5688467109494</v>
+        <v>878.2112344083204</v>
       </c>
       <c r="D32" t="n">
-        <v>7.965092399768455</v>
+        <v>7.997508119704239</v>
       </c>
       <c r="E32" t="n">
-        <v>208.8988801593934</v>
+        <v>182.8284980190639</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7613494992256165</v>
+        <v>0.8058133721351624</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1263880999995308</v>
+        <v>0.2681568999978481</v>
       </c>
       <c r="H32" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I32" t="n">
-        <v>924.4806673284035</v>
+        <v>922.2058259969646</v>
       </c>
       <c r="J32" t="n">
-        <v>208.8988801593934</v>
+        <v>182.8284980190639</v>
       </c>
       <c r="K32" t="n">
-        <v>9.000641767669954</v>
+        <v>9.000641681016079</v>
       </c>
       <c r="L32" t="n">
-        <v>39.91182061745405</v>
+        <v>43.9945915886442</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.035549367901499</v>
+        <v>1.00313356131184</v>
       </c>
       <c r="O32" t="b">
         <v>1</v>
       </c>
       <c r="P32" t="n">
-        <v>0.8096842169761658</v>
+        <v>0.9538737535476685</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.4382589000015287</v>
+        <v>1.263430400002107</v>
       </c>
       <c r="R32" t="n">
-        <v>0.0004578556690830737</v>
+        <v>0.0003632345178630203</v>
       </c>
       <c r="S32" t="n">
-        <v>935.6086459184327</v>
+        <v>931.5006680066516</v>
       </c>
       <c r="T32" t="n">
-        <v>209.0434748535456</v>
+        <v>184.0351737861193</v>
       </c>
       <c r="U32" t="n">
-        <v>9.000641611981488</v>
+        <v>9.00064114801344</v>
       </c>
       <c r="V32" t="n">
-        <v>51.03979920748327</v>
+        <v>53.28943359833124</v>
       </c>
       <c r="W32" t="n">
-        <v>0.1445946941522323</v>
+        <v>1.206675767055401</v>
       </c>
       <c r="X32" t="n">
-        <v>1.035549212213033</v>
+        <v>1.0031330283092</v>
       </c>
       <c r="Y32" t="b">
         <v>1</v>
@@ -3002,70 +3002,70 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>866.0481149643638</v>
+        <v>861.9132022656921</v>
       </c>
       <c r="D33" t="n">
-        <v>8.396102050098845</v>
+        <v>6.713454922337743</v>
       </c>
       <c r="E33" t="n">
-        <v>204.4913804540041</v>
+        <v>202.6647057415086</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8276007771492004</v>
+        <v>0.8501506447792053</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1399230000006355</v>
+        <v>0.4451698999982909</v>
       </c>
       <c r="H33" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I33" t="n">
-        <v>924.4806702136211</v>
+        <v>922.2058257867878</v>
       </c>
       <c r="J33" t="n">
-        <v>204.4913804540041</v>
+        <v>202.6647057415086</v>
       </c>
       <c r="K33" t="n">
-        <v>9.000641674596414</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L33" t="n">
-        <v>58.43255524925735</v>
+        <v>60.29262352109572</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N33" t="n">
-        <v>0.6045396244975692</v>
+        <v>2.28718685752442</v>
       </c>
       <c r="O33" t="b">
         <v>1</v>
       </c>
       <c r="P33" t="n">
-        <v>0.8861083388328552</v>
+        <v>0.9970473647117615</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.4247175000000425</v>
+        <v>1.216746699996293</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0006306460127234459</v>
+        <v>0.0004207211313769221</v>
       </c>
       <c r="S33" t="n">
-        <v>933.5971456417242</v>
+        <v>927.7660168999032</v>
       </c>
       <c r="T33" t="n">
-        <v>204.6880896479087</v>
+        <v>202.0996573202283</v>
       </c>
       <c r="U33" t="n">
-        <v>9.000641798935765</v>
+        <v>9.000641748286604</v>
       </c>
       <c r="V33" t="n">
-        <v>67.54903067736041</v>
+        <v>65.85281463421109</v>
       </c>
       <c r="W33" t="n">
-        <v>0.1967091939046384</v>
+        <v>0.5650484212802951</v>
       </c>
       <c r="X33" t="n">
-        <v>0.6045397488369204</v>
+        <v>2.287186825948861</v>
       </c>
       <c r="Y33" t="b">
         <v>1</v>
@@ -3077,74 +3077,74 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>959.224565229976</v>
+        <v>956.510440951339</v>
       </c>
       <c r="D34" t="n">
-        <v>9.94751973559673</v>
+        <v>4.650758313629222</v>
       </c>
       <c r="E34" t="n">
-        <v>162.2570436523471</v>
+        <v>207.7859355032038</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8342413306236267</v>
+        <v>0.7136481404304504</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2493610000001354</v>
+        <v>0.06434140000055777</v>
       </c>
       <c r="H34" t="n">
-        <v>0.01395832654088736</v>
+        <v>0.0008420366793870926</v>
       </c>
       <c r="I34" t="n">
-        <v>939.6998724026978</v>
+        <v>956.5104409513438</v>
       </c>
       <c r="J34" t="n">
-        <v>167.0988485136219</v>
+        <v>207.785935503202</v>
       </c>
       <c r="K34" t="n">
-        <v>10.39476371594618</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L34" t="n">
-        <v>19.52469282727816</v>
+        <v>4.774847184307873e-12</v>
       </c>
       <c r="M34" t="n">
-        <v>4.841804861274852</v>
+        <v>1.762145984685048e-12</v>
       </c>
       <c r="N34" t="n">
-        <v>0.4472439803494481</v>
+        <v>4.34988346623294</v>
       </c>
       <c r="O34" t="b">
         <v>1</v>
       </c>
       <c r="P34" t="n">
-        <v>0.4192837476730347</v>
+        <v>0.9990326166152954</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.7170040999990306</v>
+        <v>0.4300718000013148</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0009151280391961336</v>
+        <v>2.834846782207023e-05</v>
       </c>
       <c r="S34" t="n">
-        <v>852.644515937266</v>
+        <v>957.1921877673193</v>
       </c>
       <c r="T34" t="n">
-        <v>170.1972405686948</v>
+        <v>207.558136724187</v>
       </c>
       <c r="U34" t="n">
-        <v>9.86373623666578</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V34" t="n">
-        <v>106.58004929271</v>
+        <v>0.6817468159803184</v>
       </c>
       <c r="W34" t="n">
-        <v>7.940196916347787</v>
+        <v>0.2277987790167515</v>
       </c>
       <c r="X34" t="n">
-        <v>0.08378349893095027</v>
+        <v>4.34988346623294</v>
       </c>
       <c r="Y34" t="b">
         <v>1</v>
@@ -3156,74 +3156,74 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>941.6997239640687</v>
+        <v>848.0334203853446</v>
       </c>
       <c r="D35" t="n">
-        <v>5.744317367295932</v>
+        <v>8.468464203971727</v>
       </c>
       <c r="E35" t="n">
-        <v>217.4297844451559</v>
+        <v>205.9985645582225</v>
       </c>
       <c r="F35" t="n">
-        <v>0.737879753112793</v>
+        <v>0.8125014901161194</v>
       </c>
       <c r="G35" t="n">
-        <v>0.03715459999875748</v>
+        <v>0.2332601000016439</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0006575155421160161</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I35" t="n">
-        <v>941.6997239640593</v>
+        <v>922.206068765507</v>
       </c>
       <c r="J35" t="n">
-        <v>217.4297790300862</v>
+        <v>205.9985645582225</v>
       </c>
       <c r="K35" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000677525123407</v>
       </c>
       <c r="L35" t="n">
-        <v>9.322320693172514e-12</v>
+        <v>74.1726483801624</v>
       </c>
       <c r="M35" t="n">
-        <v>5.415069637138004e-06</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="N35" t="n">
-        <v>3.25632441256623</v>
+        <v>0.53221332115168</v>
       </c>
       <c r="O35" t="b">
         <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>0.7000265717506409</v>
+        <v>0.9413420557975769</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.1668485999998666</v>
+        <v>1.429021599993575</v>
       </c>
       <c r="R35" t="n">
-        <v>9.137560846284032e-05</v>
+        <v>0.0005645690835081041</v>
       </c>
       <c r="S35" t="n">
-        <v>942.8702160535091</v>
+        <v>926.7654413279303</v>
       </c>
       <c r="T35" t="n">
-        <v>217.5713724849467</v>
+        <v>205.2604266893572</v>
       </c>
       <c r="U35" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641734006866</v>
       </c>
       <c r="V35" t="n">
-        <v>1.170492089440472</v>
+        <v>78.73202094258568</v>
       </c>
       <c r="W35" t="n">
-        <v>0.1415880397908609</v>
+        <v>0.738137868865266</v>
       </c>
       <c r="X35" t="n">
-        <v>3.25632441256623</v>
+        <v>0.5321775300351383</v>
       </c>
       <c r="Y35" t="b">
         <v>1</v>
@@ -3235,74 +3235,74 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>956.1809367004807</v>
+        <v>867.5896228550795</v>
       </c>
       <c r="D36" t="n">
-        <v>5.779851383891266</v>
+        <v>7.005396616061271</v>
       </c>
       <c r="E36" t="n">
-        <v>202.9369456856241</v>
+        <v>204.0796698151825</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7933008670806885</v>
+        <v>0.8501506447792053</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0266274000005069</v>
+        <v>0.3625288999974146</v>
       </c>
       <c r="H36" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.002021597931161523</v>
       </c>
       <c r="I36" t="n">
-        <v>956.1809367004672</v>
+        <v>918.0461846495624</v>
       </c>
       <c r="J36" t="n">
-        <v>202.9369456856243</v>
+        <v>204.0796698151825</v>
       </c>
       <c r="K36" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000592901281946</v>
       </c>
       <c r="L36" t="n">
-        <v>1.352873368887231e-11</v>
+        <v>50.45656179448292</v>
       </c>
       <c r="M36" t="n">
-        <v>1.989519660128281e-13</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N36" t="n">
-        <v>3.220790395970896</v>
+        <v>1.995196285220675</v>
       </c>
       <c r="O36" t="b">
         <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>0.7445645332336426</v>
+        <v>0.9946594834327698</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.2055216999997356</v>
+        <v>1.249669999997423</v>
       </c>
       <c r="R36" t="n">
-        <v>0.0001196384328068234</v>
+        <v>0.0003833578084595501</v>
       </c>
       <c r="S36" t="n">
-        <v>956.6888191898864</v>
+        <v>928.4306687339489</v>
       </c>
       <c r="T36" t="n">
-        <v>203.0434600025148</v>
+        <v>203.5531517355269</v>
       </c>
       <c r="U36" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641875277887</v>
       </c>
       <c r="V36" t="n">
-        <v>0.5078824894056879</v>
+        <v>60.84104587886941</v>
       </c>
       <c r="W36" t="n">
-        <v>0.1065143168906957</v>
+        <v>0.526518079655574</v>
       </c>
       <c r="X36" t="n">
-        <v>3.220790395970896</v>
+        <v>1.995245259216617</v>
       </c>
       <c r="Y36" t="b">
         <v>1</v>
@@ -3314,74 +3314,74 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>932.0227942400774</v>
+        <v>946.5896832555172</v>
       </c>
       <c r="D37" t="n">
-        <v>3.279709688528632</v>
+        <v>10.09461692154121</v>
       </c>
       <c r="E37" t="n">
-        <v>206.0283507747026</v>
+        <v>144.1745818847029</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8071516752243042</v>
+        <v>0.7394377589225769</v>
       </c>
       <c r="G37" t="n">
-        <v>0.03051049999885436</v>
+        <v>0.6693073000060394</v>
       </c>
       <c r="H37" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.004407444968819618</v>
       </c>
       <c r="I37" t="n">
-        <v>932.0227942401589</v>
+        <v>880.3856173432486</v>
       </c>
       <c r="J37" t="n">
-        <v>206.0283507747002</v>
+        <v>177.0234147187984</v>
       </c>
       <c r="K37" t="n">
-        <v>9.000641779862162</v>
+        <v>9.223667054151539</v>
       </c>
       <c r="L37" t="n">
-        <v>8.151346264639869e-11</v>
+        <v>66.20406591226867</v>
       </c>
       <c r="M37" t="n">
-        <v>2.387423592153937e-12</v>
+        <v>32.84883283409556</v>
       </c>
       <c r="N37" t="n">
-        <v>5.72093209133353</v>
+        <v>0.8709498673896743</v>
       </c>
       <c r="O37" t="b">
         <v>1</v>
       </c>
       <c r="P37" t="n">
-        <v>0.9904733300209045</v>
+        <v>0.9996563196182251</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.1997496999993018</v>
+        <v>1.217217199999141</v>
       </c>
       <c r="R37" t="n">
-        <v>0.0001293522509513423</v>
+        <v>0.0008111563511192799</v>
       </c>
       <c r="S37" t="n">
-        <v>932.7675535106589</v>
+        <v>834.9053416279284</v>
       </c>
       <c r="T37" t="n">
-        <v>206.1446709805294</v>
+        <v>150.0005516934538</v>
       </c>
       <c r="U37" t="n">
-        <v>9.000641779862162</v>
+        <v>9.965421967097869</v>
       </c>
       <c r="V37" t="n">
-        <v>0.7447592705815396</v>
+        <v>111.6843416275889</v>
       </c>
       <c r="W37" t="n">
-        <v>0.1163202058267814</v>
+        <v>5.825969808750898</v>
       </c>
       <c r="X37" t="n">
-        <v>5.72093209133353</v>
+        <v>0.1291949544433439</v>
       </c>
       <c r="Y37" t="b">
         <v>1</v>
@@ -3397,70 +3397,70 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>894.058597332233</v>
+        <v>868.1032238620171</v>
       </c>
       <c r="D38" t="n">
-        <v>7.10729215437061</v>
+        <v>8.762971541934927</v>
       </c>
       <c r="E38" t="n">
-        <v>206.5638010411286</v>
+        <v>194.6890313803294</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7774769067764282</v>
+        <v>0.8152469396591187</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1009745000010298</v>
+        <v>0.2891786999971373</v>
       </c>
       <c r="H38" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I38" t="n">
-        <v>924.4806678336713</v>
+        <v>922.2058273809587</v>
       </c>
       <c r="J38" t="n">
-        <v>206.5638010411287</v>
+        <v>194.6890313803294</v>
       </c>
       <c r="K38" t="n">
-        <v>9.000641635118944</v>
+        <v>9.000641428610697</v>
       </c>
       <c r="L38" t="n">
-        <v>30.42207050143827</v>
+        <v>54.10260351894158</v>
       </c>
       <c r="M38" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.893349480748334</v>
+        <v>0.2376698866757696</v>
       </c>
       <c r="O38" t="b">
         <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>0.8802700042724609</v>
+        <v>0.8948182463645935</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.3668240000006335</v>
+        <v>1.229596500001207</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0003797303361352533</v>
+        <v>0.0003732691402547061</v>
       </c>
       <c r="S38" t="n">
-        <v>937.0401347756589</v>
+        <v>927.9202013827087</v>
       </c>
       <c r="T38" t="n">
-        <v>206.6848070899788</v>
+        <v>194.8829643752386</v>
       </c>
       <c r="U38" t="n">
-        <v>9.000641834226704</v>
+        <v>9.00064177925432</v>
       </c>
       <c r="V38" t="n">
-        <v>42.98153744342585</v>
+        <v>59.81697752069158</v>
       </c>
       <c r="W38" t="n">
-        <v>0.121006048850262</v>
+        <v>0.193932994909261</v>
       </c>
       <c r="X38" t="n">
-        <v>1.893349679856094</v>
+        <v>0.2376702373193922</v>
       </c>
       <c r="Y38" t="b">
         <v>1</v>
@@ -3472,74 +3472,74 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>915.9628707257309</v>
+        <v>852.9891149027849</v>
       </c>
       <c r="D39" t="n">
-        <v>11.2926756758084</v>
+        <v>7.39793391564124</v>
       </c>
       <c r="E39" t="n">
-        <v>145.5897009610678</v>
+        <v>176.7987090245322</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8310216665267944</v>
+        <v>0.8463224768638611</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2477748000001156</v>
+        <v>0.2853286000026856</v>
       </c>
       <c r="H39" t="n">
-        <v>0.004034198820590973</v>
+        <v>0.001724448404274881</v>
       </c>
       <c r="I39" t="n">
-        <v>898.3641717137543</v>
+        <v>922.2058331709978</v>
       </c>
       <c r="J39" t="n">
-        <v>173.1996341318766</v>
+        <v>176.7987090245297</v>
       </c>
       <c r="K39" t="n">
-        <v>11.25044915722544</v>
+        <v>9.000641612817498</v>
       </c>
       <c r="L39" t="n">
-        <v>17.59869901197658</v>
+        <v>69.21671826821296</v>
       </c>
       <c r="M39" t="n">
-        <v>27.60993317080889</v>
+        <v>2.501110429875553e-12</v>
       </c>
       <c r="N39" t="n">
-        <v>0.04222651858296622</v>
+        <v>1.602707697176258</v>
       </c>
       <c r="O39" t="b">
         <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>0.9962121248245239</v>
+        <v>0.9930249452590942</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.9162108000000444</v>
+        <v>1.298404399996798</v>
       </c>
       <c r="R39" t="n">
-        <v>0.001545119215734303</v>
+        <v>0.0005793051095679402</v>
       </c>
       <c r="S39" t="n">
-        <v>800.0007183078104</v>
+        <v>931.7527753097147</v>
       </c>
       <c r="T39" t="n">
-        <v>155.1810930980546</v>
+        <v>178.4805916897221</v>
       </c>
       <c r="U39" t="n">
-        <v>11.01362970766526</v>
+        <v>9.000641079673978</v>
       </c>
       <c r="V39" t="n">
-        <v>115.9621524179205</v>
+        <v>78.76366040692983</v>
       </c>
       <c r="W39" t="n">
-        <v>9.591392136986855</v>
+        <v>1.681882665189903</v>
       </c>
       <c r="X39" t="n">
-        <v>0.2790459681431372</v>
+        <v>1.602707164032737</v>
       </c>
       <c r="Y39" t="b">
         <v>1</v>
@@ -3551,74 +3551,74 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>914.9356469254265</v>
+        <v>948.4924456995418</v>
       </c>
       <c r="D40" t="n">
-        <v>13.57521521596934</v>
+        <v>6.055042849744302</v>
       </c>
       <c r="E40" t="n">
-        <v>197.9143229760539</v>
+        <v>199.2025722440827</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7837685346603394</v>
+        <v>0.6916452050209045</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1604312999988906</v>
+        <v>0.06864929999574088</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0008012968464754522</v>
+        <v>0.0008420366793870926</v>
       </c>
       <c r="I40" t="n">
-        <v>891.8630123780105</v>
+        <v>948.492445699542</v>
       </c>
       <c r="J40" t="n">
-        <v>200.1620275358584</v>
+        <v>199.2025722440827</v>
       </c>
       <c r="K40" t="n">
-        <v>11.69492063924486</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L40" t="n">
-        <v>23.07263454741599</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="M40" t="n">
-        <v>2.247704559804561</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N40" t="n">
-        <v>1.880294576724477</v>
+        <v>2.94559893011786</v>
       </c>
       <c r="O40" t="b">
         <v>1</v>
       </c>
       <c r="P40" t="n">
-        <v>0.5898296236991882</v>
+        <v>0.8830639719963074</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.7043693000014173</v>
+        <v>0.4526412000050186</v>
       </c>
       <c r="R40" t="n">
-        <v>0.0008531625499017537</v>
+        <v>1.903056181618012e-05</v>
       </c>
       <c r="S40" t="n">
-        <v>822.3079642785661</v>
+        <v>949.4658506170199</v>
       </c>
       <c r="T40" t="n">
-        <v>197.2936607689693</v>
+        <v>199.1558707592875</v>
       </c>
       <c r="U40" t="n">
-        <v>12.93004360977719</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V40" t="n">
-        <v>92.62768264686031</v>
+        <v>0.9734049174780921</v>
       </c>
       <c r="W40" t="n">
-        <v>0.620662207084564</v>
+        <v>0.04670148479519298</v>
       </c>
       <c r="X40" t="n">
-        <v>0.6451716061921466</v>
+        <v>2.94559893011786</v>
       </c>
       <c r="Y40" t="b">
         <v>1</v>
@@ -3630,74 +3630,74 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>934.2994599959595</v>
+        <v>929.3276580842945</v>
       </c>
       <c r="D41" t="n">
-        <v>13.29227209175094</v>
+        <v>9.554939797636102</v>
       </c>
       <c r="E41" t="n">
-        <v>191.4696694458699</v>
+        <v>126.519321320786</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5390264391899109</v>
+        <v>0.7431839108467102</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1476729000005435</v>
+        <v>0.3878465999951004</v>
       </c>
       <c r="H41" t="n">
-        <v>0.001172499847598374</v>
+        <v>0.01405216194689274</v>
       </c>
       <c r="I41" t="n">
-        <v>891.8621679710011</v>
+        <v>929.3276580842988</v>
       </c>
       <c r="J41" t="n">
-        <v>191.0703474696069</v>
+        <v>165.1588583137162</v>
       </c>
       <c r="K41" t="n">
-        <v>11.69500109083224</v>
+        <v>9.893629746653792</v>
       </c>
       <c r="L41" t="n">
-        <v>42.43729202495842</v>
+        <v>4.320099833421409e-12</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3993219762630531</v>
+        <v>38.63953699293018</v>
       </c>
       <c r="N41" t="n">
-        <v>1.597271000918694</v>
+        <v>0.3386899490176898</v>
       </c>
       <c r="O41" t="b">
         <v>1</v>
       </c>
       <c r="P41" t="n">
-        <v>0.191131979227066</v>
+        <v>0.9999992847442627</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.120314299998427</v>
+        <v>1.199550699995598</v>
       </c>
       <c r="R41" t="n">
-        <v>0.00158974074292928</v>
+        <v>0.0006795671069994569</v>
       </c>
       <c r="S41" t="n">
-        <v>954.2061645314308</v>
+        <v>839.5920246361242</v>
       </c>
       <c r="T41" t="n">
-        <v>184.8518429435482</v>
+        <v>150.0005513451833</v>
       </c>
       <c r="U41" t="n">
-        <v>12.2383612793745</v>
+        <v>9.443604844038036</v>
       </c>
       <c r="V41" t="n">
-        <v>19.90670453547125</v>
+        <v>89.73563344817035</v>
       </c>
       <c r="W41" t="n">
-        <v>6.617826502321719</v>
+        <v>23.48123002439726</v>
       </c>
       <c r="X41" t="n">
-        <v>1.053910812376442</v>
+        <v>0.1113349535980657</v>
       </c>
       <c r="Y41" t="b">
         <v>1</v>
@@ -3709,74 +3709,74 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>923.2970677667828</v>
+        <v>943.1977020468481</v>
       </c>
       <c r="D42" t="n">
-        <v>12.15593215202897</v>
+        <v>4.184199159468379</v>
       </c>
       <c r="E42" t="n">
-        <v>148.2154659732632</v>
+        <v>208.4536711562265</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8265721797943115</v>
+        <v>0.7136481404304504</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1940635000009934</v>
+        <v>0.1079536000033841</v>
       </c>
       <c r="H42" t="n">
-        <v>0.001362329348921776</v>
+        <v>0.0008420366793870926</v>
       </c>
       <c r="I42" t="n">
-        <v>924.479116666373</v>
+        <v>943.1977020468519</v>
       </c>
       <c r="J42" t="n">
-        <v>173.193227843581</v>
+        <v>208.453671156226</v>
       </c>
       <c r="K42" t="n">
-        <v>12.15597198149028</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L42" t="n">
-        <v>1.1820488995902</v>
+        <v>3.751665644813329e-12</v>
       </c>
       <c r="M42" t="n">
-        <v>24.97776187031778</v>
+        <v>4.831690603168681e-13</v>
       </c>
       <c r="N42" t="n">
-        <v>3.982946130953735e-05</v>
+        <v>4.816442620393784</v>
       </c>
       <c r="O42" t="b">
         <v>1</v>
       </c>
       <c r="P42" t="n">
-        <v>0.9862338304519653</v>
+        <v>0.9996654987335205</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.8101370000003953</v>
+        <v>0.5065219000025536</v>
       </c>
       <c r="R42" t="n">
-        <v>0.001609932980500162</v>
+        <v>5.189417061046697e-05</v>
       </c>
       <c r="S42" t="n">
-        <v>800.0016377621449</v>
+        <v>945.8915862948336</v>
       </c>
       <c r="T42" t="n">
-        <v>158.8516153374016</v>
+        <v>208.1659279607368</v>
       </c>
       <c r="U42" t="n">
-        <v>11.85658951288739</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V42" t="n">
-        <v>123.2954300046379</v>
+        <v>2.693884247985466</v>
       </c>
       <c r="W42" t="n">
-        <v>10.63614936413836</v>
+        <v>0.2877431954897247</v>
       </c>
       <c r="X42" t="n">
-        <v>0.2993426391415852</v>
+        <v>4.816442620393784</v>
       </c>
       <c r="Y42" t="b">
         <v>1</v>
@@ -3792,70 +3792,70 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>957.8461883377502</v>
+        <v>951.9914692102243</v>
       </c>
       <c r="D43" t="n">
-        <v>5.40731851194075</v>
+        <v>4.993058825068983</v>
       </c>
       <c r="E43" t="n">
-        <v>203.2139416671867</v>
+        <v>202.4337247027007</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7943711876869202</v>
+        <v>0.6916452050209045</v>
       </c>
       <c r="G43" t="n">
-        <v>0.02722840000024007</v>
+        <v>0.07154459999583196</v>
       </c>
       <c r="H43" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.0008420366793870926</v>
       </c>
       <c r="I43" t="n">
-        <v>957.8461883377539</v>
+        <v>951.9914692102287</v>
       </c>
       <c r="J43" t="n">
-        <v>203.2139416671866</v>
+        <v>202.4337247027007</v>
       </c>
       <c r="K43" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="L43" t="n">
-        <v>3.751665644813329e-12</v>
+        <v>4.433786671143025e-12</v>
       </c>
       <c r="M43" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.593323267921412</v>
+        <v>4.007582954793179</v>
       </c>
       <c r="O43" t="b">
         <v>1</v>
       </c>
       <c r="P43" t="n">
-        <v>0.901283323764801</v>
+        <v>0.9966591596603394</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.1719758999988699</v>
+        <v>0.4647676999957184</v>
       </c>
       <c r="R43" t="n">
-        <v>0.0001180368708446622</v>
+        <v>1.905684985104017e-05</v>
       </c>
       <c r="S43" t="n">
-        <v>958.3371593473358</v>
+        <v>952.9749566177765</v>
       </c>
       <c r="T43" t="n">
-        <v>203.3174290775349</v>
+        <v>202.3850950609859</v>
       </c>
       <c r="U43" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V43" t="n">
-        <v>0.4909710095856781</v>
+        <v>0.9834874075521611</v>
       </c>
       <c r="W43" t="n">
-        <v>0.1034874103481229</v>
+        <v>0.04862964171482531</v>
       </c>
       <c r="X43" t="n">
-        <v>3.593323267921412</v>
+        <v>4.007582954793179</v>
       </c>
       <c r="Y43" t="b">
         <v>1</v>
@@ -3867,74 +3867,74 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>919.8850439887167</v>
+        <v>944.5017580958511</v>
       </c>
       <c r="D44" t="n">
-        <v>6.987860270816064</v>
+        <v>10.38117004774009</v>
       </c>
       <c r="E44" t="n">
-        <v>213.1441079328948</v>
+        <v>163.6103805496427</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5113658905029297</v>
+        <v>0.7394377589225769</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1324557999996614</v>
+        <v>0.3583410999999614</v>
       </c>
       <c r="H44" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.001092163613066077</v>
       </c>
       <c r="I44" t="n">
-        <v>924.4806673134666</v>
+        <v>944.5090206506209</v>
       </c>
       <c r="J44" t="n">
-        <v>213.1441079328948</v>
+        <v>173.3841004429623</v>
       </c>
       <c r="K44" t="n">
-        <v>9.000641728722</v>
+        <v>10.38119474432181</v>
       </c>
       <c r="L44" t="n">
-        <v>4.595623324749909</v>
+        <v>0.007262554769795315</v>
       </c>
       <c r="M44" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>9.773719893319594</v>
       </c>
       <c r="N44" t="n">
-        <v>2.012781457905936</v>
+        <v>2.469658171655453e-05</v>
       </c>
       <c r="O44" t="b">
         <v>1</v>
       </c>
       <c r="P44" t="n">
-        <v>0.05108459293842316</v>
+        <v>0.3692962825298309</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.171445699999822</v>
+        <v>1.888097500006552</v>
       </c>
       <c r="R44" t="n">
-        <v>0.0001197151141241193</v>
+        <v>0.0006770239560864866</v>
       </c>
       <c r="S44" t="n">
-        <v>920.4992377971934</v>
+        <v>857.1191728028257</v>
       </c>
       <c r="T44" t="n">
-        <v>213.2658062653188</v>
+        <v>167.5146474812732</v>
       </c>
       <c r="U44" t="n">
-        <v>9.000641779862162</v>
+        <v>10.31417131531367</v>
       </c>
       <c r="V44" t="n">
-        <v>0.6141938084766707</v>
+        <v>87.38258529302539</v>
       </c>
       <c r="W44" t="n">
-        <v>0.1216983324239322</v>
+        <v>3.904266931630502</v>
       </c>
       <c r="X44" t="n">
-        <v>2.012781509046098</v>
+        <v>0.06699873242642518</v>
       </c>
       <c r="Y44" t="b">
         <v>1</v>
@@ -3946,74 +3946,74 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>856.1319878890793</v>
+        <v>969.0217240256204</v>
       </c>
       <c r="D45" t="n">
-        <v>7.047902626896689</v>
+        <v>5.863660710669682</v>
       </c>
       <c r="E45" t="n">
-        <v>194.8680250367964</v>
+        <v>204.3078919752531</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8388520479202271</v>
+        <v>0.7118977904319763</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1332616999989114</v>
+        <v>0.09406180000223685</v>
       </c>
       <c r="H45" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.0008416271884925663</v>
       </c>
       <c r="I45" t="n">
-        <v>924.4806679704964</v>
+        <v>969.0217240258403</v>
       </c>
       <c r="J45" t="n">
-        <v>194.8680250367964</v>
+        <v>204.3079209294194</v>
       </c>
       <c r="K45" t="n">
-        <v>9.000641506820683</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L45" t="n">
-        <v>68.34868008141711</v>
+        <v>2.198703441536054e-10</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.895416622550329e-05</v>
       </c>
       <c r="N45" t="n">
-        <v>1.952738879923994</v>
+        <v>3.136981069192481</v>
       </c>
       <c r="O45" t="b">
         <v>1</v>
       </c>
       <c r="P45" t="n">
-        <v>0.9849173426628113</v>
+        <v>0.9110298752784729</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.4248204000014084</v>
+        <v>0.4503598000010243</v>
       </c>
       <c r="R45" t="n">
-        <v>0.0007378043956123292</v>
+        <v>2.678244891285431e-05</v>
       </c>
       <c r="S45" t="n">
-        <v>933.5397006458571</v>
+        <v>967.4616528201619</v>
       </c>
       <c r="T45" t="n">
-        <v>195.5236715079213</v>
+        <v>204.2693296858247</v>
       </c>
       <c r="U45" t="n">
-        <v>9.000641727137973</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V45" t="n">
-        <v>77.40771275677787</v>
+        <v>1.560071205458485</v>
       </c>
       <c r="W45" t="n">
-        <v>0.6556464711248395</v>
+        <v>0.03856228942842677</v>
       </c>
       <c r="X45" t="n">
-        <v>1.952739100241284</v>
+        <v>3.136981069192481</v>
       </c>
       <c r="Y45" t="b">
         <v>1</v>
@@ -4029,70 +4029,70 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>891.8267851103899</v>
+        <v>880.3940965666376</v>
       </c>
       <c r="D46" t="n">
-        <v>8.90862009710092</v>
+        <v>7.828670423142086</v>
       </c>
       <c r="E46" t="n">
-        <v>214.6839444567854</v>
+        <v>195.5862138254634</v>
       </c>
       <c r="F46" t="n">
-        <v>0.59441739320755</v>
+        <v>0.8040255308151245</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1268964999999298</v>
+        <v>0.2764700999978231</v>
       </c>
       <c r="H46" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I46" t="n">
-        <v>924.4806687804495</v>
+        <v>922.2058259371253</v>
       </c>
       <c r="J46" t="n">
-        <v>214.6839444567854</v>
+        <v>195.5862138254634</v>
       </c>
       <c r="K46" t="n">
-        <v>9.000641455627086</v>
+        <v>9.000641628834696</v>
       </c>
       <c r="L46" t="n">
-        <v>32.6538836700596</v>
+        <v>41.81172937048768</v>
       </c>
       <c r="M46" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0.092021358526166</v>
+        <v>1.171971205692611</v>
       </c>
       <c r="O46" t="b">
         <v>1</v>
       </c>
       <c r="P46" t="n">
-        <v>0.2020948678255081</v>
+        <v>0.9587864875793457</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.4259170000004815</v>
+        <v>1.199286300005042</v>
       </c>
       <c r="R46" t="n">
-        <v>0.0003919356386177242</v>
+        <v>0.0002955686359200627</v>
       </c>
       <c r="S46" t="n">
-        <v>936.3935700046733</v>
+        <v>928.9606913521658</v>
       </c>
       <c r="T46" t="n">
-        <v>214.8188408813083</v>
+        <v>195.7427030768381</v>
       </c>
       <c r="U46" t="n">
-        <v>9.000641643679471</v>
+        <v>9.000641751337811</v>
       </c>
       <c r="V46" t="n">
-        <v>44.56678489428339</v>
+        <v>48.5665947855282</v>
       </c>
       <c r="W46" t="n">
-        <v>0.1348964245229638</v>
+        <v>0.156489251374694</v>
       </c>
       <c r="X46" t="n">
-        <v>0.09202154657855033</v>
+        <v>1.171971328195726</v>
       </c>
       <c r="Y46" t="b">
         <v>1</v>
@@ -4108,70 +4108,70 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>937.8430346825069</v>
+        <v>913.8532508199647</v>
       </c>
       <c r="D47" t="n">
-        <v>4.714656273080053</v>
+        <v>6.564262266985383</v>
       </c>
       <c r="E47" t="n">
-        <v>184.6784915092103</v>
+        <v>212.8119881922711</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7805690169334412</v>
+        <v>0.6761674284934998</v>
       </c>
       <c r="G47" t="n">
-        <v>0.03655149999940477</v>
+        <v>0.09717950000049314</v>
       </c>
       <c r="H47" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.0008399065118283033</v>
       </c>
       <c r="I47" t="n">
-        <v>937.843034682439</v>
+        <v>913.8532508199625</v>
       </c>
       <c r="J47" t="n">
-        <v>184.6784915092109</v>
+        <v>212.8120094273573</v>
       </c>
       <c r="K47" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="L47" t="n">
-        <v>6.787104211980477e-11</v>
+        <v>2.273736754432321e-12</v>
       </c>
       <c r="M47" t="n">
-        <v>5.400124791776761e-13</v>
+        <v>2.123508619433778e-05</v>
       </c>
       <c r="N47" t="n">
-        <v>4.28598550678211</v>
+        <v>2.43637951287678</v>
       </c>
       <c r="O47" t="b">
         <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>0.9717041254043579</v>
+        <v>0.7316827178001404</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.1672189000000799</v>
+        <v>0.5385124999957043</v>
       </c>
       <c r="R47" t="n">
-        <v>0.0001876782043837011</v>
+        <v>0.0002641877217683941</v>
       </c>
       <c r="S47" t="n">
-        <v>939.0506026082115</v>
+        <v>923.2404200024794</v>
       </c>
       <c r="T47" t="n">
-        <v>184.7635664641608</v>
+        <v>211.6649160440006</v>
       </c>
       <c r="U47" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V47" t="n">
-        <v>1.207567925704666</v>
+        <v>9.38716918251464</v>
       </c>
       <c r="W47" t="n">
-        <v>0.08507495495049966</v>
+        <v>1.147072148270496</v>
       </c>
       <c r="X47" t="n">
-        <v>4.28598550678211</v>
+        <v>2.43637951287678</v>
       </c>
       <c r="Y47" t="b">
         <v>1</v>
@@ -4187,70 +4187,70 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>852.2007345185287</v>
+        <v>888.507701038656</v>
       </c>
       <c r="D48" t="n">
-        <v>8.234111512734437</v>
+        <v>5.247358479825308</v>
       </c>
       <c r="E48" t="n">
-        <v>201.4532764955338</v>
+        <v>226.2567744185995</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7837687730789185</v>
+        <v>0.7591444849967957</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1266963999987638</v>
+        <v>0.264119399995252</v>
       </c>
       <c r="H48" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.001604381715878844</v>
       </c>
       <c r="I48" t="n">
-        <v>924.4806727501011</v>
+        <v>922.2058288997894</v>
       </c>
       <c r="J48" t="n">
-        <v>201.4532764955338</v>
+        <v>226.2567744185216</v>
       </c>
       <c r="K48" t="n">
-        <v>9.000641520526491</v>
+        <v>9.00064153207826</v>
       </c>
       <c r="L48" t="n">
-        <v>72.27993823157237</v>
+        <v>33.69812786113334</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>7.790390554873738e-11</v>
       </c>
       <c r="N48" t="n">
-        <v>0.7665300077920545</v>
+        <v>3.753283052252953</v>
       </c>
       <c r="O48" t="b">
         <v>1</v>
       </c>
       <c r="P48" t="n">
-        <v>0.9181942343711853</v>
+        <v>0.3652864694595337</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.4532667999992555</v>
+        <v>1.116640799999004</v>
       </c>
       <c r="R48" t="n">
-        <v>0.0007723270100541413</v>
+        <v>0.0005885112332180142</v>
       </c>
       <c r="S48" t="n">
-        <v>932.3364803414411</v>
+        <v>935.7230952232256</v>
       </c>
       <c r="T48" t="n">
-        <v>201.6872895414843</v>
+        <v>222.3186654042264</v>
       </c>
       <c r="U48" t="n">
-        <v>9.000641734287282</v>
+        <v>9.000637418355975</v>
       </c>
       <c r="V48" t="n">
-        <v>80.13574582291233</v>
+        <v>47.21539418456962</v>
       </c>
       <c r="W48" t="n">
-        <v>0.234013045950519</v>
+        <v>3.938109014373083</v>
       </c>
       <c r="X48" t="n">
-        <v>0.7665302215528449</v>
+        <v>3.753278938530667</v>
       </c>
       <c r="Y48" t="b">
         <v>1</v>
@@ -4266,70 +4266,70 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>900.7263175218887</v>
+        <v>881.8077175927488</v>
       </c>
       <c r="D49" t="n">
-        <v>6.573016988322543</v>
+        <v>7.630990200237124</v>
       </c>
       <c r="E49" t="n">
-        <v>199.1010662715858</v>
+        <v>204.8174626499961</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7352117896080017</v>
+        <v>0.8041542172431946</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1115269999991142</v>
+        <v>0.2661947000015061</v>
       </c>
       <c r="H49" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I49" t="n">
-        <v>924.4806673727901</v>
+        <v>922.2058258740703</v>
       </c>
       <c r="J49" t="n">
-        <v>199.1010662715858</v>
+        <v>204.8174626499961</v>
       </c>
       <c r="K49" t="n">
-        <v>9.000641768960563</v>
+        <v>9.000641767923808</v>
       </c>
       <c r="L49" t="n">
-        <v>23.75434985090135</v>
+        <v>40.39810828132158</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.42762478063802</v>
+        <v>1.369651567686684</v>
       </c>
       <c r="O49" t="b">
         <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>0.8801118135452271</v>
+        <v>0.9618977308273315</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.4399883999994927</v>
+        <v>1.529994600001373</v>
       </c>
       <c r="R49" t="n">
-        <v>0.0003305335994809866</v>
+        <v>0.0003134294820483774</v>
       </c>
       <c r="S49" t="n">
-        <v>938.4927500622725</v>
+        <v>929.4760403942433</v>
       </c>
       <c r="T49" t="n">
-        <v>199.409682446859</v>
+        <v>204.1631038490684</v>
       </c>
       <c r="U49" t="n">
-        <v>9.000641750264094</v>
+        <v>9.000641688740028</v>
       </c>
       <c r="V49" t="n">
-        <v>37.76643254038379</v>
+        <v>47.66832280149458</v>
       </c>
       <c r="W49" t="n">
-        <v>0.3086161752732437</v>
+        <v>0.6543588009276391</v>
       </c>
       <c r="X49" t="n">
-        <v>2.427624761941551</v>
+        <v>1.369651488502904</v>
       </c>
       <c r="Y49" t="b">
         <v>1</v>
@@ -4341,74 +4341,74 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>971.6542106706307</v>
+        <v>878.2946391566084</v>
       </c>
       <c r="D50" t="n">
-        <v>9.679699438752699</v>
+        <v>6.604873147224154</v>
       </c>
       <c r="E50" t="n">
-        <v>149.4314563953131</v>
+        <v>195.3563523850261</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8341188430786133</v>
+        <v>0.7959065437316895</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1928124999994907</v>
+        <v>0.2584471000009216</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0009419303387403488</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I50" t="n">
-        <v>971.6542173536892</v>
+        <v>922.2058266159781</v>
       </c>
       <c r="J50" t="n">
-        <v>173.1913506201487</v>
+        <v>195.3563523850261</v>
       </c>
       <c r="K50" t="n">
-        <v>9.679851116437586</v>
+        <v>9.000641598788686</v>
       </c>
       <c r="L50" t="n">
-        <v>6.683058472845005e-06</v>
+        <v>43.91118745936978</v>
       </c>
       <c r="M50" t="n">
-        <v>23.75989422483565</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0.0001516776848866641</v>
+        <v>2.395768451564532</v>
       </c>
       <c r="O50" t="b">
         <v>1</v>
       </c>
       <c r="P50" t="n">
-        <v>0.9869421720504761</v>
+        <v>0.9901665449142456</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.8412749999988591</v>
+        <v>1.227842499996768</v>
       </c>
       <c r="R50" t="n">
-        <v>0.001226867316290736</v>
+        <v>0.000310430972604081</v>
       </c>
       <c r="S50" t="n">
-        <v>825.8411199005631</v>
+        <v>928.7446065262505</v>
       </c>
       <c r="T50" t="n">
-        <v>159.4115488371688</v>
+        <v>195.5214045915932</v>
       </c>
       <c r="U50" t="n">
-        <v>9.563628437061322</v>
+        <v>9.00064180754033</v>
       </c>
       <c r="V50" t="n">
-        <v>145.8130907700677</v>
+        <v>50.4499673696422</v>
       </c>
       <c r="W50" t="n">
-        <v>9.98009244185576</v>
+        <v>0.1650522065670543</v>
       </c>
       <c r="X50" t="n">
-        <v>0.1160710016913775</v>
+        <v>2.395768660316175</v>
       </c>
       <c r="Y50" t="b">
         <v>1</v>
@@ -4420,74 +4420,74 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>887.1501231880142</v>
+        <v>968.1549719963527</v>
       </c>
       <c r="D51" t="n">
-        <v>6.582303349592957</v>
+        <v>8.695575030253764</v>
       </c>
       <c r="E51" t="n">
-        <v>211.3566360846236</v>
+        <v>121.2536082708588</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8435402512550354</v>
+        <v>0.7599234580993652</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1009933999994246</v>
+        <v>0.4327330999949481</v>
       </c>
       <c r="H51" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.01405216194689274</v>
       </c>
       <c r="I51" t="n">
-        <v>924.4811060678609</v>
+        <v>950.6936783434352</v>
       </c>
       <c r="J51" t="n">
-        <v>211.3566360846236</v>
+        <v>165.1587146657744</v>
       </c>
       <c r="K51" t="n">
-        <v>9.000641660549674</v>
+        <v>9.893533624064606</v>
       </c>
       <c r="L51" t="n">
-        <v>37.33098287984672</v>
+        <v>17.46129365291756</v>
       </c>
       <c r="M51" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>43.90510639491552</v>
       </c>
       <c r="N51" t="n">
-        <v>2.418338310956717</v>
+        <v>1.197958593810842</v>
       </c>
       <c r="O51" t="b">
         <v>1</v>
       </c>
       <c r="P51" t="n">
-        <v>0.9739328026771545</v>
+        <v>0.9999998807907104</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.4533549999996467</v>
+        <v>1.50650279999536</v>
       </c>
       <c r="R51" t="n">
-        <v>0.0004376955330371857</v>
+        <v>0.0008941132109612226</v>
       </c>
       <c r="S51" t="n">
-        <v>935.7949612346154</v>
+        <v>846.7827145854616</v>
       </c>
       <c r="T51" t="n">
-        <v>211.502268654002</v>
+        <v>150.0005525377416</v>
       </c>
       <c r="U51" t="n">
-        <v>9.000641561005152</v>
+        <v>9.000641704997239</v>
       </c>
       <c r="V51" t="n">
-        <v>48.64483804660119</v>
+        <v>121.3722574108912</v>
       </c>
       <c r="W51" t="n">
-        <v>0.1456325693783924</v>
+        <v>28.74694426688276</v>
       </c>
       <c r="X51" t="n">
-        <v>2.418338211412195</v>
+        <v>0.3050666747434754</v>
       </c>
       <c r="Y51" t="b">
         <v>1</v>
@@ -4499,74 +4499,74 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>926.6726500100951</v>
+        <v>938.6079709221476</v>
       </c>
       <c r="D52" t="n">
-        <v>5.834740604668191</v>
+        <v>11.16659435783242</v>
       </c>
       <c r="E52" t="n">
-        <v>199.6577601407073</v>
+        <v>141.72176577615</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8077849149703979</v>
+        <v>0.7394377589225769</v>
       </c>
       <c r="G52" t="n">
-        <v>0.03049370000007912</v>
+        <v>0.5601841000025161</v>
       </c>
       <c r="H52" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.02069401741027832</v>
       </c>
       <c r="I52" t="n">
-        <v>926.6726500100767</v>
+        <v>840.277289824849</v>
       </c>
       <c r="J52" t="n">
-        <v>199.6577601407072</v>
+        <v>173.4960416798492</v>
       </c>
       <c r="K52" t="n">
-        <v>9.000641779862162</v>
+        <v>10.60684878768247</v>
       </c>
       <c r="L52" t="n">
-        <v>1.84172677109018e-11</v>
+        <v>98.33068109729857</v>
       </c>
       <c r="M52" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>31.77427590369928</v>
       </c>
       <c r="N52" t="n">
-        <v>3.165901175193971</v>
+        <v>0.5597455701499463</v>
       </c>
       <c r="O52" t="b">
         <v>1</v>
       </c>
       <c r="P52" t="n">
-        <v>0.6036913990974426</v>
+        <v>0.9997976422309875</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.188606500001697</v>
+        <v>1.31335019999824</v>
       </c>
       <c r="R52" t="n">
-        <v>0.0001547730207676068</v>
+        <v>0.0008404589025303721</v>
       </c>
       <c r="S52" t="n">
-        <v>927.5787766706371</v>
+        <v>826.6649636867384</v>
       </c>
       <c r="T52" t="n">
-        <v>199.8324506352653</v>
+        <v>150.0005525335621</v>
       </c>
       <c r="U52" t="n">
-        <v>9.000641779862162</v>
+        <v>11.08256768908223</v>
       </c>
       <c r="V52" t="n">
-        <v>0.906126660541986</v>
+        <v>111.9430072354093</v>
       </c>
       <c r="W52" t="n">
-        <v>0.1746904945580638</v>
+        <v>8.278786757412121</v>
       </c>
       <c r="X52" t="n">
-        <v>3.165901175193971</v>
+        <v>0.08402666875018916</v>
       </c>
       <c r="Y52" t="b">
         <v>1</v>
@@ -4578,74 +4578,74 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>928.0424742349063</v>
+        <v>875.4632379859565</v>
       </c>
       <c r="D53" t="n">
-        <v>14.39454277695739</v>
+        <v>6.86564083170728</v>
       </c>
       <c r="E53" t="n">
-        <v>204.9006277479043</v>
+        <v>207.7290680842257</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6630008816719055</v>
+        <v>0.8041200637817383</v>
       </c>
       <c r="G53" t="n">
-        <v>0.1416719000008015</v>
+        <v>0.2437291999958688</v>
       </c>
       <c r="H53" t="n">
-        <v>0.002421969082206488</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I53" t="n">
-        <v>891.853858463534</v>
+        <v>922.2058276599912</v>
       </c>
       <c r="J53" t="n">
-        <v>205.0749302699842</v>
+        <v>207.7290680842257</v>
       </c>
       <c r="K53" t="n">
-        <v>12.31813765676279</v>
+        <v>9.000641440682417</v>
       </c>
       <c r="L53" t="n">
-        <v>36.18861577137227</v>
+        <v>46.74258967403466</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1743025220798984</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="N53" t="n">
-        <v>2.076405120194599</v>
+        <v>2.135000608975137</v>
       </c>
       <c r="O53" t="b">
         <v>1</v>
       </c>
       <c r="P53" t="n">
-        <v>0.9753878712654114</v>
+        <v>0.9897705316543579</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.8403077999992092</v>
+        <v>1.296600900001067</v>
       </c>
       <c r="R53" t="n">
-        <v>0.00107042258605361</v>
+        <v>0.0003744474670384079</v>
       </c>
       <c r="S53" t="n">
-        <v>805.8293929216601</v>
+        <v>929.2656573742784</v>
       </c>
       <c r="T53" t="n">
-        <v>204.1218710905988</v>
+        <v>206.7390007582378</v>
       </c>
       <c r="U53" t="n">
-        <v>13.48221061413342</v>
+        <v>9.000641525423552</v>
       </c>
       <c r="V53" t="n">
-        <v>122.2130813132462</v>
+        <v>53.80241938832182</v>
       </c>
       <c r="W53" t="n">
-        <v>0.7787566573054789</v>
+        <v>0.9900673259879511</v>
       </c>
       <c r="X53" t="n">
-        <v>0.9123321628239722</v>
+        <v>2.135000693716272</v>
       </c>
       <c r="Y53" t="b">
         <v>1</v>
@@ -4657,74 +4657,74 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>920.190680118923</v>
+        <v>960.2392442225636</v>
       </c>
       <c r="D54" t="n">
-        <v>12.92564418956117</v>
+        <v>5.77224334439606</v>
       </c>
       <c r="E54" t="n">
-        <v>196.9481724590098</v>
+        <v>207.0077893507324</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5190762281417847</v>
+        <v>0.7136481404304504</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2818693999997777</v>
+        <v>0.07957509999687318</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0009203365771099925</v>
+        <v>0.0008420366793870926</v>
       </c>
       <c r="I54" t="n">
-        <v>891.8717779954161</v>
+        <v>960.2392442225597</v>
       </c>
       <c r="J54" t="n">
-        <v>197.3407795222889</v>
+        <v>207.007789350732</v>
       </c>
       <c r="K54" t="n">
-        <v>11.69500117267008</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L54" t="n">
-        <v>28.31890212350686</v>
+        <v>3.865352482534945e-12</v>
       </c>
       <c r="M54" t="n">
-        <v>0.3926070632790868</v>
+        <v>3.979039320256561e-13</v>
       </c>
       <c r="N54" t="n">
-        <v>1.230643016891094</v>
+        <v>3.228398435466103</v>
       </c>
       <c r="O54" t="b">
         <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>0.1265840530395508</v>
+        <v>0.9495652914047241</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.7444093999984034</v>
+        <v>0.5692853000000468</v>
       </c>
       <c r="R54" t="n">
-        <v>0.0007879638578742743</v>
+        <v>2.303709152329247e-05</v>
       </c>
       <c r="S54" t="n">
-        <v>839.0766433309378</v>
+        <v>959.9687462346609</v>
       </c>
       <c r="T54" t="n">
-        <v>196.3377956742819</v>
+        <v>206.9179120232771</v>
       </c>
       <c r="U54" t="n">
-        <v>12.39525267170594</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V54" t="n">
-        <v>81.11403678798513</v>
+        <v>0.2704979879026723</v>
       </c>
       <c r="W54" t="n">
-        <v>0.6103767847279187</v>
+        <v>0.08987732745526955</v>
       </c>
       <c r="X54" t="n">
-        <v>0.5303915178552288</v>
+        <v>3.228398435466103</v>
       </c>
       <c r="Y54" t="b">
         <v>1</v>
@@ -4740,70 +4740,70 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>904.7260228175338</v>
+        <v>861.0830515064821</v>
       </c>
       <c r="D55" t="n">
-        <v>6.513873947704546</v>
+        <v>8.645064780297236</v>
       </c>
       <c r="E55" t="n">
-        <v>194.1900640139415</v>
+        <v>199.3531760598806</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5757224559783936</v>
+        <v>0.8152469396591187</v>
       </c>
       <c r="G55" t="n">
-        <v>0.1071010999985447</v>
+        <v>0.4454246999957832</v>
       </c>
       <c r="H55" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I55" t="n">
-        <v>924.4806679266952</v>
+        <v>922.205826495489</v>
       </c>
       <c r="J55" t="n">
-        <v>194.1900640139415</v>
+        <v>199.3531760598806</v>
       </c>
       <c r="K55" t="n">
-        <v>9.000641660370865</v>
+        <v>9.000641796213429</v>
       </c>
       <c r="L55" t="n">
-        <v>19.7546451091614</v>
+        <v>61.12277498900687</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.486767712666319</v>
+        <v>0.3555770159161931</v>
       </c>
       <c r="O55" t="b">
         <v>1</v>
       </c>
       <c r="P55" t="n">
-        <v>0.8196242451667786</v>
+        <v>0.9244984984397888</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.3965094000013778</v>
+        <v>1.220590699995228</v>
       </c>
       <c r="R55" t="n">
-        <v>0.0003062655450776219</v>
+        <v>0.0004675545205827802</v>
       </c>
       <c r="S55" t="n">
-        <v>939.8257292647016</v>
+        <v>926.6899473672918</v>
       </c>
       <c r="T55" t="n">
-        <v>194.4442288392474</v>
+        <v>198.765854024484</v>
       </c>
       <c r="U55" t="n">
-        <v>9.000641568461951</v>
+        <v>9.000641756911103</v>
       </c>
       <c r="V55" t="n">
-        <v>35.09970644716782</v>
+        <v>65.60689586080969</v>
       </c>
       <c r="W55" t="n">
-        <v>0.2541648253059066</v>
+        <v>0.5873220353965678</v>
       </c>
       <c r="X55" t="n">
-        <v>2.486767620757405</v>
+        <v>0.3555769766138663</v>
       </c>
       <c r="Y55" t="b">
         <v>1</v>
@@ -4815,74 +4815,74 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>953.6799627409868</v>
+        <v>856.3683046909155</v>
       </c>
       <c r="D56" t="n">
-        <v>5.695247330655505</v>
+        <v>8.347014394014183</v>
       </c>
       <c r="E56" t="n">
-        <v>211.4400709604765</v>
+        <v>184.5598449981941</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8140485286712646</v>
+        <v>0.8306360840797424</v>
       </c>
       <c r="G56" t="n">
-        <v>0.03059759999996459</v>
+        <v>0.2652698000019882</v>
       </c>
       <c r="H56" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I56" t="n">
-        <v>953.679962740982</v>
+        <v>922.2058285003015</v>
       </c>
       <c r="J56" t="n">
-        <v>211.4400709604764</v>
+        <v>184.5598449981941</v>
       </c>
       <c r="K56" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641548158409</v>
       </c>
       <c r="L56" t="n">
-        <v>4.774847184307873e-12</v>
+        <v>65.83752380938608</v>
       </c>
       <c r="M56" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N56" t="n">
-        <v>3.305394449206657</v>
+        <v>0.6536271541442265</v>
       </c>
       <c r="O56" t="b">
         <v>1</v>
       </c>
       <c r="P56" t="n">
-        <v>0.7604827284812927</v>
+        <v>0.9553053379058838</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.1889549999996234</v>
+        <v>1.241435900003125</v>
       </c>
       <c r="R56" t="n">
-        <v>9.524988126941025e-05</v>
+        <v>0.0004869443364441395</v>
       </c>
       <c r="S56" t="n">
-        <v>954.7453234484341</v>
+        <v>929.232772858305</v>
       </c>
       <c r="T56" t="n">
-        <v>211.5806574209546</v>
+        <v>185.9174363753475</v>
       </c>
       <c r="U56" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641345490003</v>
       </c>
       <c r="V56" t="n">
-        <v>1.065360707447326</v>
+        <v>72.86446816738953</v>
       </c>
       <c r="W56" t="n">
-        <v>0.1405864604781186</v>
+        <v>1.357591377153398</v>
       </c>
       <c r="X56" t="n">
-        <v>3.305394449206657</v>
+        <v>0.65362695147582</v>
       </c>
       <c r="Y56" t="b">
         <v>1</v>
@@ -4894,74 +4894,74 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>878.7244280711647</v>
+        <v>952.1760960157819</v>
       </c>
       <c r="D57" t="n">
-        <v>7.496107712312081</v>
+        <v>5.768600426339933</v>
       </c>
       <c r="E57" t="n">
-        <v>215.4862590673856</v>
+        <v>170.3411856075121</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8227301239967346</v>
+        <v>0.5854483246803284</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1355751999999484</v>
+        <v>0.08755499999824679</v>
       </c>
       <c r="H57" t="n">
-        <v>0.001030344516038895</v>
+        <v>0.002010466996580362</v>
       </c>
       <c r="I57" t="n">
-        <v>924.4806673224532</v>
+        <v>952.1760960158495</v>
       </c>
       <c r="J57" t="n">
-        <v>215.486259067386</v>
+        <v>170.3411856075115</v>
       </c>
       <c r="K57" t="n">
-        <v>9.000641605265576</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L57" t="n">
-        <v>45.75623925128855</v>
+        <v>6.752998160663992e-11</v>
       </c>
       <c r="M57" t="n">
-        <v>3.979039320256561e-13</v>
+        <v>5.968558980384842e-13</v>
       </c>
       <c r="N57" t="n">
-        <v>1.504533892953495</v>
+        <v>3.232041353522229</v>
       </c>
       <c r="O57" t="b">
         <v>1</v>
       </c>
       <c r="P57" t="n">
-        <v>0.93586266040802</v>
+        <v>0.9249246716499329</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.4178374000002805</v>
+        <v>1.082642600005784</v>
       </c>
       <c r="R57" t="n">
-        <v>0.0005075081717222929</v>
+        <v>0.0007656744564883411</v>
       </c>
       <c r="S57" t="n">
-        <v>934.5424221097506</v>
+        <v>947.9854923616515</v>
       </c>
       <c r="T57" t="n">
-        <v>215.660281100011</v>
+        <v>173.8604224924369</v>
       </c>
       <c r="U57" t="n">
-        <v>9.000641882373063</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V57" t="n">
-        <v>55.81799403858599</v>
+        <v>4.190603654130427</v>
       </c>
       <c r="W57" t="n">
-        <v>0.1740220326254018</v>
+        <v>3.519236884924823</v>
       </c>
       <c r="X57" t="n">
-        <v>1.504534170060983</v>
+        <v>3.232041353522229</v>
       </c>
       <c r="Y57" t="b">
         <v>1</v>
@@ -4977,70 +4977,70 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>959.4549444551382</v>
+        <v>971.9323726605396</v>
       </c>
       <c r="D58" t="n">
-        <v>9.61145559527602</v>
+        <v>11.38331986296445</v>
       </c>
       <c r="E58" t="n">
-        <v>154.1556131362414</v>
+        <v>163.6228451961527</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8342413306236267</v>
+        <v>0.6532474756240845</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1542993999992177</v>
+        <v>0.4673800000018673</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0009383680298924446</v>
+        <v>0.01299904845654964</v>
       </c>
       <c r="I58" t="n">
-        <v>960.4299786405732</v>
+        <v>950.6927588536137</v>
       </c>
       <c r="J58" t="n">
-        <v>173.1914970857922</v>
+        <v>173.3833204676627</v>
       </c>
       <c r="K58" t="n">
-        <v>9.609333334284983</v>
+        <v>11.5617182178689</v>
       </c>
       <c r="L58" t="n">
-        <v>0.9750341854349927</v>
+        <v>21.23961380692595</v>
       </c>
       <c r="M58" t="n">
-        <v>19.03588394955085</v>
+        <v>9.760475271510046</v>
       </c>
       <c r="N58" t="n">
-        <v>0.00212226099103674</v>
+        <v>0.1783983549044486</v>
       </c>
       <c r="O58" t="b">
         <v>1</v>
       </c>
       <c r="P58" t="n">
-        <v>0.9423930644989014</v>
+        <v>0.3177532553672791</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.7485969999997906</v>
+        <v>1.972996000004059</v>
       </c>
       <c r="R58" t="n">
-        <v>0.001064009964466095</v>
+        <v>0.0008190005901269615</v>
       </c>
       <c r="S58" t="n">
-        <v>836.5903342080511</v>
+        <v>855.4944084283692</v>
       </c>
       <c r="T58" t="n">
-        <v>163.3670525900826</v>
+        <v>168.9675787393436</v>
       </c>
       <c r="U58" t="n">
-        <v>9.512552945100481</v>
+        <v>11.32283305963921</v>
       </c>
       <c r="V58" t="n">
-        <v>122.8646102470871</v>
+        <v>116.4379642321704</v>
       </c>
       <c r="W58" t="n">
-        <v>9.211439453841223</v>
+        <v>5.344733543190898</v>
       </c>
       <c r="X58" t="n">
-        <v>0.09890265017553901</v>
+        <v>0.06048680332523837</v>
       </c>
       <c r="Y58" t="b">
         <v>1</v>
@@ -5052,74 +5052,74 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>965.4668338928942</v>
+        <v>879.7078327036852</v>
       </c>
       <c r="D59" t="n">
-        <v>5.628955132374228</v>
+        <v>6.753868342719074</v>
       </c>
       <c r="E59" t="n">
-        <v>215.9415361021917</v>
+        <v>188.4352889703314</v>
       </c>
       <c r="F59" t="n">
-        <v>0.7377122640609741</v>
+        <v>0.8036876320838928</v>
       </c>
       <c r="G59" t="n">
-        <v>0.03172099999937927</v>
+        <v>0.2466894000026514</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0006574971484951675</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I59" t="n">
-        <v>965.4668338884472</v>
+        <v>922.2058301653756</v>
       </c>
       <c r="J59" t="n">
-        <v>215.941518819786</v>
+        <v>188.4352889703314</v>
       </c>
       <c r="K59" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641532258104</v>
       </c>
       <c r="L59" t="n">
-        <v>4.446974344318733e-09</v>
+        <v>42.49799746169037</v>
       </c>
       <c r="M59" t="n">
-        <v>1.728240576426288e-05</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.371686647487935</v>
+        <v>2.24677318953903</v>
       </c>
       <c r="O59" t="b">
         <v>1</v>
       </c>
       <c r="P59" t="n">
-        <v>0.7703380584716797</v>
+        <v>0.9910854697227478</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.1675304000000324</v>
+        <v>1.102226399998472</v>
       </c>
       <c r="R59" t="n">
-        <v>7.142432150430977e-05</v>
+        <v>0.0003135894949082285</v>
       </c>
       <c r="S59" t="n">
-        <v>966.2791013759787</v>
+        <v>930.0498938375127</v>
       </c>
       <c r="T59" t="n">
-        <v>216.0516758296297</v>
+        <v>189.2416970678907</v>
       </c>
       <c r="U59" t="n">
-        <v>9.000641779862162</v>
+        <v>9.000641557658593</v>
       </c>
       <c r="V59" t="n">
-        <v>0.8122674830844971</v>
+        <v>50.34206113382754</v>
       </c>
       <c r="W59" t="n">
-        <v>0.1101397274379678</v>
+        <v>0.8064080975592844</v>
       </c>
       <c r="X59" t="n">
-        <v>3.371686647487935</v>
+        <v>2.246773214939519</v>
       </c>
       <c r="Y59" t="b">
         <v>1</v>
@@ -5131,74 +5131,74 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>914.4277433020131</v>
+        <v>865.6685175307517</v>
       </c>
       <c r="D60" t="n">
-        <v>6.127249242883064</v>
+        <v>8.438458625979363</v>
       </c>
       <c r="E60" t="n">
-        <v>190.5813030830286</v>
+        <v>194.684084868373</v>
       </c>
       <c r="F60" t="n">
-        <v>0.7621703743934631</v>
+        <v>0.8096859455108643</v>
       </c>
       <c r="G60" t="n">
-        <v>0.1463242999998329</v>
+        <v>0.2580949999974109</v>
       </c>
       <c r="H60" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I60" t="n">
-        <v>924.4806674329564</v>
+        <v>922.2058273493387</v>
       </c>
       <c r="J60" t="n">
-        <v>190.5813030830286</v>
+        <v>194.684084868373</v>
       </c>
       <c r="K60" t="n">
-        <v>9.000641694793952</v>
+        <v>9.000641699154775</v>
       </c>
       <c r="L60" t="n">
-        <v>10.05292413094321</v>
+        <v>56.537309818587</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.873392451910888</v>
+        <v>0.5621830731754116</v>
       </c>
       <c r="O60" t="b">
         <v>1</v>
       </c>
       <c r="P60" t="n">
-        <v>0.2493027597665787</v>
+        <v>0.9487231373786926</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.1995973000011873</v>
+        <v>1.250352100003511</v>
       </c>
       <c r="R60" t="n">
-        <v>0.0002035595534835011</v>
+        <v>0.0003891636442858726</v>
       </c>
       <c r="S60" t="n">
-        <v>915.3829504453581</v>
+        <v>927.7241604923164</v>
       </c>
       <c r="T60" t="n">
-        <v>190.6834606943153</v>
+        <v>194.8864741156494</v>
       </c>
       <c r="U60" t="n">
-        <v>9.000641779862162</v>
+        <v>9.00064174923315</v>
       </c>
       <c r="V60" t="n">
-        <v>0.9552071433449782</v>
+        <v>62.05564296156467</v>
       </c>
       <c r="W60" t="n">
-        <v>0.1021576112866853</v>
+        <v>0.2023892472763862</v>
       </c>
       <c r="X60" t="n">
-        <v>2.873392536979098</v>
+        <v>0.5621831232537868</v>
       </c>
       <c r="Y60" t="b">
         <v>1</v>
@@ -5210,74 +5210,74 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>954.3218973270541</v>
+        <v>988.7733876329025</v>
       </c>
       <c r="D61" t="n">
-        <v>4.267466985438978</v>
+        <v>9.629504688193911</v>
       </c>
       <c r="E61" t="n">
-        <v>214.7086949110996</v>
+        <v>151.4781551745641</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8140485286712646</v>
+        <v>0.7426249384880066</v>
       </c>
       <c r="G61" t="n">
-        <v>0.03699129999949946</v>
+        <v>0.424492599995574</v>
       </c>
       <c r="H61" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.001212719012983143</v>
       </c>
       <c r="I61" t="n">
-        <v>954.3218973271643</v>
+        <v>988.7797656467599</v>
       </c>
       <c r="J61" t="n">
-        <v>214.708694911107</v>
+        <v>173.3837353722952</v>
       </c>
       <c r="K61" t="n">
-        <v>9.000641779862162</v>
+        <v>9.628521256100942</v>
       </c>
       <c r="L61" t="n">
-        <v>1.101625457522459e-10</v>
+        <v>0.006378013857329279</v>
       </c>
       <c r="M61" t="n">
-        <v>7.332801033044234e-12</v>
+        <v>21.90558019773107</v>
       </c>
       <c r="N61" t="n">
-        <v>4.733174794423184</v>
+        <v>0.0009834320929691387</v>
       </c>
       <c r="O61" t="b">
         <v>1</v>
       </c>
       <c r="P61" t="n">
-        <v>0.9945182204246521</v>
+        <v>0.9939936995506287</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.1928062000006321</v>
+        <v>2.077964200005226</v>
       </c>
       <c r="R61" t="n">
-        <v>8.501165575580671e-05</v>
+        <v>0.0009684700053185225</v>
       </c>
       <c r="S61" t="n">
-        <v>955.269006075916</v>
+        <v>849.8559731438171</v>
       </c>
       <c r="T61" t="n">
-        <v>214.8373939506008</v>
+        <v>155.9793855659326</v>
       </c>
       <c r="U61" t="n">
-        <v>9.000641779862162</v>
+        <v>9.486339917866889</v>
       </c>
       <c r="V61" t="n">
-        <v>0.947108748861865</v>
+        <v>138.9174144890854</v>
       </c>
       <c r="W61" t="n">
-        <v>0.1286990395011287</v>
+        <v>4.501230391368466</v>
       </c>
       <c r="X61" t="n">
-        <v>4.733174794423184</v>
+        <v>0.1431647703270222</v>
       </c>
       <c r="Y61" t="b">
         <v>1</v>
@@ -5289,74 +5289,74 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>964.7328412473059</v>
+        <v>983.6887118717664</v>
       </c>
       <c r="D62" t="n">
-        <v>11.95522054844252</v>
+        <v>5.390577709287466</v>
       </c>
       <c r="E62" t="n">
-        <v>158.0495834532315</v>
+        <v>185.7832902829906</v>
       </c>
       <c r="F62" t="n">
-        <v>0.8333476185798645</v>
+        <v>0.6900404095649719</v>
       </c>
       <c r="G62" t="n">
-        <v>0.2319010000010167</v>
+        <v>0.09115519999613753</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0009662620141170919</v>
+        <v>0.0008416784112341702</v>
       </c>
       <c r="I62" t="n">
-        <v>964.7328512355643</v>
+        <v>983.6887118718071</v>
       </c>
       <c r="J62" t="n">
-        <v>173.1913502113057</v>
+        <v>185.7832931429506</v>
       </c>
       <c r="K62" t="n">
-        <v>11.95531632114984</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L62" t="n">
-        <v>9.988258398152539e-06</v>
+        <v>4.069988790433854e-11</v>
       </c>
       <c r="M62" t="n">
-        <v>15.1417667580742</v>
+        <v>2.859959920442634e-06</v>
       </c>
       <c r="N62" t="n">
-        <v>9.577270731853105e-05</v>
+        <v>3.610064070574697</v>
       </c>
       <c r="O62" t="b">
         <v>1</v>
       </c>
       <c r="P62" t="n">
-        <v>0.57620769739151</v>
+        <v>0.9637253880500793</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.19765660000121</v>
+        <v>0.5179513000039151</v>
       </c>
       <c r="R62" t="n">
-        <v>0.001437750761397183</v>
+        <v>0.0001541051897220314</v>
       </c>
       <c r="S62" t="n">
-        <v>838.7820905439297</v>
+        <v>981.1400271259154</v>
       </c>
       <c r="T62" t="n">
-        <v>170.2021753806105</v>
+        <v>186.5172419413266</v>
       </c>
       <c r="U62" t="n">
-        <v>11.68553061984703</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V62" t="n">
-        <v>125.9507507033762</v>
+        <v>2.548684745851006</v>
       </c>
       <c r="W62" t="n">
-        <v>12.15259192737892</v>
+        <v>0.7339516583359682</v>
       </c>
       <c r="X62" t="n">
-        <v>0.2696899285954935</v>
+        <v>3.610064070574697</v>
       </c>
       <c r="Y62" t="b">
         <v>1</v>
@@ -5368,74 +5368,74 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>927.2347573008381</v>
+        <v>888.1834963461654</v>
       </c>
       <c r="D63" t="n">
-        <v>9.738030885550424</v>
+        <v>7.292302755980059</v>
       </c>
       <c r="E63" t="n">
-        <v>158.9384212940965</v>
+        <v>190.945487020255</v>
       </c>
       <c r="F63" t="n">
-        <v>0.8342413306236267</v>
+        <v>0.8026574850082397</v>
       </c>
       <c r="G63" t="n">
-        <v>0.1955748999989737</v>
+        <v>0.2448476999998093</v>
       </c>
       <c r="H63" t="n">
-        <v>0.01450293231755495</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I63" t="n">
-        <v>933.9691992068756</v>
+        <v>922.2058293061137</v>
       </c>
       <c r="J63" t="n">
-        <v>163.2351149768217</v>
+        <v>190.945487020255</v>
       </c>
       <c r="K63" t="n">
-        <v>10.39423143519245</v>
+        <v>9.000641559358268</v>
       </c>
       <c r="L63" t="n">
-        <v>6.734441906037546</v>
+        <v>34.02233295994836</v>
       </c>
       <c r="M63" t="n">
-        <v>4.296693682725248</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0.6562005496420245</v>
+        <v>1.708338803378209</v>
       </c>
       <c r="O63" t="b">
         <v>1</v>
       </c>
       <c r="P63" t="n">
-        <v>0.7622626423835754</v>
+        <v>0.9516106843948364</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.6658169999991514</v>
+        <v>1.146246500000416</v>
       </c>
       <c r="R63" t="n">
-        <v>0.000796763168182224</v>
+        <v>0.0002567590854596347</v>
       </c>
       <c r="S63" t="n">
-        <v>841.5427863056591</v>
+        <v>930.1775447252965</v>
       </c>
       <c r="T63" t="n">
-        <v>166.2797083721771</v>
+        <v>191.6244779880829</v>
       </c>
       <c r="U63" t="n">
-        <v>9.664999892662786</v>
+        <v>9.000641589183269</v>
       </c>
       <c r="V63" t="n">
-        <v>85.69197099517896</v>
+        <v>41.99404837913107</v>
       </c>
       <c r="W63" t="n">
-        <v>7.341287078080626</v>
+        <v>0.6789909678278718</v>
       </c>
       <c r="X63" t="n">
-        <v>0.07303099288763804</v>
+        <v>1.70833883320321</v>
       </c>
       <c r="Y63" t="b">
         <v>1</v>
@@ -5447,74 +5447,74 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>938.6987905289761</v>
+        <v>948.0380557917572</v>
       </c>
       <c r="D64" t="n">
-        <v>4.094369333927407</v>
+        <v>11.49331049301696</v>
       </c>
       <c r="E64" t="n">
-        <v>200.7026873771016</v>
+        <v>139.4305598667262</v>
       </c>
       <c r="F64" t="n">
-        <v>0.8001946806907654</v>
+        <v>0.6444942355155945</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0424299999995128</v>
+        <v>0.4537392999991425</v>
       </c>
       <c r="H64" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.01256675831973553</v>
       </c>
       <c r="I64" t="n">
-        <v>938.69879052898</v>
+        <v>892.263393229351</v>
       </c>
       <c r="J64" t="n">
-        <v>200.7026873771017</v>
+        <v>165.1586349537145</v>
       </c>
       <c r="K64" t="n">
-        <v>9.000641779862162</v>
+        <v>11.49329741700601</v>
       </c>
       <c r="L64" t="n">
-        <v>3.865352482534945e-12</v>
+        <v>55.77466256240621</v>
       </c>
       <c r="M64" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>25.7280750869883</v>
       </c>
       <c r="N64" t="n">
-        <v>4.906272445934755</v>
+        <v>1.307601095135169e-05</v>
       </c>
       <c r="O64" t="b">
         <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>0.9884545803070068</v>
+        <v>0.9999234676361084</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.2067377999992459</v>
+        <v>1.289429900003597</v>
       </c>
       <c r="R64" t="n">
-        <v>0.0001389217213727534</v>
+        <v>0.0009414580999873579</v>
       </c>
       <c r="S64" t="n">
-        <v>939.5303449365394</v>
+        <v>825.7263989720077</v>
       </c>
       <c r="T64" t="n">
-        <v>200.8275160107046</v>
+        <v>150.000552456347</v>
       </c>
       <c r="U64" t="n">
-        <v>9.000641779862162</v>
+        <v>11.40711341161041</v>
       </c>
       <c r="V64" t="n">
-        <v>0.831554407563317</v>
+        <v>122.3116568197495</v>
       </c>
       <c r="W64" t="n">
-        <v>0.1248286336029878</v>
+        <v>10.56999258962077</v>
       </c>
       <c r="X64" t="n">
-        <v>4.906272445934755</v>
+        <v>0.08619708140655113</v>
       </c>
       <c r="Y64" t="b">
         <v>1</v>
@@ -5530,70 +5530,70 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>854.5975405822235</v>
+        <v>893.1249473592206</v>
       </c>
       <c r="D65" t="n">
-        <v>8.545119477592145</v>
+        <v>7.717089651771773</v>
       </c>
       <c r="E65" t="n">
-        <v>210.8389043747138</v>
+        <v>179.1941913944448</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8276062607765198</v>
+        <v>0.5936911106109619</v>
       </c>
       <c r="G65" t="n">
-        <v>0.1225571000013588</v>
+        <v>0.2529091999967932</v>
       </c>
       <c r="H65" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.001724448404274881</v>
       </c>
       <c r="I65" t="n">
-        <v>924.4806723075287</v>
+        <v>922.205826139241</v>
       </c>
       <c r="J65" t="n">
-        <v>210.8389043747138</v>
+        <v>179.1941913944434</v>
       </c>
       <c r="K65" t="n">
-        <v>9.000641649022834</v>
+        <v>9.000641590709408</v>
       </c>
       <c r="L65" t="n">
-        <v>69.88313172530525</v>
+        <v>29.08087878002038</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>1.392663762089796e-12</v>
       </c>
       <c r="N65" t="n">
-        <v>0.4555221714306885</v>
+        <v>1.283551938937635</v>
       </c>
       <c r="O65" t="b">
         <v>1</v>
       </c>
       <c r="P65" t="n">
-        <v>0.8437613844871521</v>
+        <v>0.7811267375946045</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.4663670000009006</v>
+        <v>1.150375000004715</v>
       </c>
       <c r="R65" t="n">
-        <v>0.0007422577473334968</v>
+        <v>0.0002758514310698956</v>
       </c>
       <c r="S65" t="n">
-        <v>932.1227581002694</v>
+        <v>934.9810124556619</v>
       </c>
       <c r="T65" t="n">
-        <v>211.0860069107594</v>
+        <v>179.9349405702163</v>
       </c>
       <c r="U65" t="n">
-        <v>9.000641863904157</v>
+        <v>9.000642110353626</v>
       </c>
       <c r="V65" t="n">
-        <v>77.52521751804591</v>
+        <v>41.85606509644128</v>
       </c>
       <c r="W65" t="n">
-        <v>0.2471025360456736</v>
+        <v>0.7407491757714695</v>
       </c>
       <c r="X65" t="n">
-        <v>0.4555223863120119</v>
+        <v>1.283552458581853</v>
       </c>
       <c r="Y65" t="b">
         <v>1</v>
@@ -5605,74 +5605,74 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>940.0682196056371</v>
+        <v>921.0496129967865</v>
       </c>
       <c r="D66" t="n">
-        <v>9.807608135251126</v>
+        <v>5.469884301326367</v>
       </c>
       <c r="E66" t="n">
-        <v>133.164629856318</v>
+        <v>213.7835095603872</v>
       </c>
       <c r="F66" t="n">
-        <v>0.8342413306236267</v>
+        <v>0.7021283507347107</v>
       </c>
       <c r="G66" t="n">
-        <v>0.2527258999998594</v>
+        <v>0.0932226000004448</v>
       </c>
       <c r="H66" t="n">
-        <v>0.01395832654088736</v>
+        <v>0.0008416872005909681</v>
       </c>
       <c r="I66" t="n">
-        <v>939.7143323962179</v>
+        <v>921.0496129967853</v>
       </c>
       <c r="J66" t="n">
-        <v>163.0211355440055</v>
+        <v>213.7835095603847</v>
       </c>
       <c r="K66" t="n">
-        <v>10.39414075505328</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L66" t="n">
-        <v>0.3538872094192129</v>
+        <v>1.250555214937776e-12</v>
       </c>
       <c r="M66" t="n">
-        <v>29.85650568768756</v>
+        <v>2.501110429875553e-12</v>
       </c>
       <c r="N66" t="n">
-        <v>0.5865326198021563</v>
+        <v>3.530757478535795</v>
       </c>
       <c r="O66" t="b">
         <v>1</v>
       </c>
       <c r="P66" t="n">
-        <v>0.9999763965606689</v>
+        <v>0.9821173548698425</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.4801877999998396</v>
+        <v>0.5183016000009957</v>
       </c>
       <c r="R66" t="n">
-        <v>0.001211823429912329</v>
+        <v>0.0001922985975397751</v>
       </c>
       <c r="S66" t="n">
-        <v>800.9001713402897</v>
+        <v>932.3766867131628</v>
       </c>
       <c r="T66" t="n">
-        <v>150.0005523879942</v>
+        <v>212.9077556532865</v>
       </c>
       <c r="U66" t="n">
-        <v>9.694933437081053</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V66" t="n">
-        <v>139.1680482653474</v>
+        <v>11.32707371637628</v>
       </c>
       <c r="W66" t="n">
-        <v>16.83592253167623</v>
+        <v>0.8757539071007443</v>
       </c>
       <c r="X66" t="n">
-        <v>0.112674698170073</v>
+        <v>3.530757478535795</v>
       </c>
       <c r="Y66" t="b">
         <v>1</v>
@@ -5688,70 +5688,70 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>898.5499725581047</v>
+        <v>880.8422945584357</v>
       </c>
       <c r="D67" t="n">
-        <v>6.853027509410801</v>
+        <v>5.923619001789338</v>
       </c>
       <c r="E67" t="n">
-        <v>188.198430366255</v>
+        <v>199.5229307489909</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6342471837997437</v>
+        <v>0.7963674068450928</v>
       </c>
       <c r="G67" t="n">
-        <v>0.1258354000001418</v>
+        <v>0.2732383999973536</v>
       </c>
       <c r="H67" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I67" t="n">
-        <v>924.4806673446582</v>
+        <v>922.2058289072628</v>
       </c>
       <c r="J67" t="n">
-        <v>188.1984303662551</v>
+        <v>199.5229307489909</v>
       </c>
       <c r="K67" t="n">
-        <v>9.000641761690584</v>
+        <v>9.000641603253946</v>
       </c>
       <c r="L67" t="n">
-        <v>25.93069478655343</v>
+        <v>41.3635343488271</v>
       </c>
       <c r="M67" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.147614252279784</v>
+        <v>3.077022601464608</v>
       </c>
       <c r="O67" t="b">
         <v>1</v>
       </c>
       <c r="P67" t="n">
-        <v>0.8768274188041687</v>
+        <v>0.9546601176261902</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.3985108999986551</v>
+        <v>1.162950500001898</v>
       </c>
       <c r="R67" t="n">
-        <v>0.0003588769177440554</v>
+        <v>0.0003047188802156597</v>
       </c>
       <c r="S67" t="n">
-        <v>939.6358230472654</v>
+        <v>928.8641353711305</v>
       </c>
       <c r="T67" t="n">
-        <v>188.4741893158343</v>
+        <v>199.115470387669</v>
       </c>
       <c r="U67" t="n">
-        <v>9.000641871806357</v>
+        <v>9.00064162954418</v>
       </c>
       <c r="V67" t="n">
-        <v>41.08585048916063</v>
+        <v>48.02184081269479</v>
       </c>
       <c r="W67" t="n">
-        <v>0.2757589495792274</v>
+        <v>0.4074603613218528</v>
       </c>
       <c r="X67" t="n">
-        <v>2.147614362395556</v>
+        <v>3.077022627754842</v>
       </c>
       <c r="Y67" t="b">
         <v>1</v>
@@ -5767,70 +5767,70 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>953.4399911766055</v>
+        <v>978.530894094716</v>
       </c>
       <c r="D68" t="n">
-        <v>3.692187777550672</v>
+        <v>6.071580970314155</v>
       </c>
       <c r="E68" t="n">
-        <v>202.1025006005814</v>
+        <v>186.1547233149043</v>
       </c>
       <c r="F68" t="n">
-        <v>0.8173863291740417</v>
+        <v>0.6900404095649719</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02904699999999139</v>
+        <v>0.1060820999991847</v>
       </c>
       <c r="H68" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.0008416784112341702</v>
       </c>
       <c r="I68" t="n">
-        <v>953.439991176548</v>
+        <v>978.5308940948452</v>
       </c>
       <c r="J68" t="n">
-        <v>202.1025006005814</v>
+        <v>186.1547290925585</v>
       </c>
       <c r="K68" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="L68" t="n">
-        <v>5.752553988713771e-11</v>
+        <v>1.291482476517558e-10</v>
       </c>
       <c r="M68" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>5.777654166649882e-06</v>
       </c>
       <c r="N68" t="n">
-        <v>5.30845400231149</v>
+        <v>2.929060809548007</v>
       </c>
       <c r="O68" t="b">
         <v>1</v>
       </c>
       <c r="P68" t="n">
-        <v>0.9986415505409241</v>
+        <v>0.7608194351196289</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.1630648999998812</v>
+        <v>0.5899174999940442</v>
       </c>
       <c r="R68" t="n">
-        <v>0.0001233608345501125</v>
+        <v>0.0001180428225779906</v>
       </c>
       <c r="S68" t="n">
-        <v>953.952865041337</v>
+        <v>973.3548711246297</v>
       </c>
       <c r="T68" t="n">
-        <v>202.2075706657974</v>
+        <v>186.7124538019537</v>
       </c>
       <c r="U68" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V68" t="n">
-        <v>0.5128738647314321</v>
+        <v>5.176022970086365</v>
       </c>
       <c r="W68" t="n">
-        <v>0.1050700652159549</v>
+        <v>0.5577304870493833</v>
       </c>
       <c r="X68" t="n">
-        <v>5.30845400231149</v>
+        <v>2.929060809548007</v>
       </c>
       <c r="Y68" t="b">
         <v>1</v>
@@ -5842,74 +5842,74 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>893.6151260554346</v>
+        <v>939.5196707482213</v>
       </c>
       <c r="D69" t="n">
-        <v>6.063577599875421</v>
+        <v>9.510200513016633</v>
       </c>
       <c r="E69" t="n">
-        <v>195.5242698740448</v>
+        <v>148.3966678154006</v>
       </c>
       <c r="F69" t="n">
-        <v>0.6838685870170593</v>
+        <v>0.7431839108467102</v>
       </c>
       <c r="G69" t="n">
-        <v>0.1367686999983562</v>
+        <v>0.3322971000015968</v>
       </c>
       <c r="H69" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.001092163613066077</v>
       </c>
       <c r="I69" t="n">
-        <v>924.4806673313456</v>
+        <v>939.5128295108293</v>
       </c>
       <c r="J69" t="n">
-        <v>195.5242698740448</v>
+        <v>173.3837605668239</v>
       </c>
       <c r="K69" t="n">
-        <v>9.000641722785351</v>
+        <v>9.510176681074078</v>
       </c>
       <c r="L69" t="n">
-        <v>30.86554127591091</v>
+        <v>0.006841237391995492</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>24.98709275142335</v>
       </c>
       <c r="N69" t="n">
-        <v>2.937064122909931</v>
+        <v>2.38319425545086e-05</v>
       </c>
       <c r="O69" t="b">
         <v>1</v>
       </c>
       <c r="P69" t="n">
-        <v>0.9543607831001282</v>
+        <v>0.9972988963127136</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.3802390000000742</v>
+        <v>1.674686099999235</v>
       </c>
       <c r="R69" t="n">
-        <v>0.0003933592233806849</v>
+        <v>0.0007537179044447839</v>
       </c>
       <c r="S69" t="n">
-        <v>937.8599054555471</v>
+        <v>842.9025348007971</v>
       </c>
       <c r="T69" t="n">
-        <v>195.8775230933143</v>
+        <v>151.5237625662782</v>
       </c>
       <c r="U69" t="n">
-        <v>9.000641849397857</v>
+        <v>9.405994870203534</v>
       </c>
       <c r="V69" t="n">
-        <v>44.24477940011241</v>
+        <v>96.61713594742423</v>
       </c>
       <c r="W69" t="n">
-        <v>0.3532532192695612</v>
+        <v>3.127094750877632</v>
       </c>
       <c r="X69" t="n">
-        <v>2.937064249522436</v>
+        <v>0.1042056428130991</v>
       </c>
       <c r="Y69" t="b">
         <v>1</v>
@@ -5921,74 +5921,74 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>833.1191433149253</v>
+        <v>949.0275749593204</v>
       </c>
       <c r="D70" t="n">
-        <v>7.630198787376239</v>
+        <v>6.605347132292355</v>
       </c>
       <c r="E70" t="n">
-        <v>201.5815297457368</v>
+        <v>200.7727103628514</v>
       </c>
       <c r="F70" t="n">
-        <v>0.8120322227478027</v>
+        <v>0.6916452050209045</v>
       </c>
       <c r="G70" t="n">
-        <v>0.1316437000004953</v>
+        <v>0.08395589999418007</v>
       </c>
       <c r="H70" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.0008420366793870926</v>
       </c>
       <c r="I70" t="n">
-        <v>924.4806711702983</v>
+        <v>949.0275749593194</v>
       </c>
       <c r="J70" t="n">
-        <v>201.5815297457368</v>
+        <v>200.7727103628514</v>
       </c>
       <c r="K70" t="n">
-        <v>9.00064165804284</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L70" t="n">
-        <v>91.36152785537297</v>
+        <v>1.023181539494544e-12</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>1.370442870666601</v>
+        <v>2.395294647569807</v>
       </c>
       <c r="O70" t="b">
         <v>1</v>
       </c>
       <c r="P70" t="n">
-        <v>0.9377415180206299</v>
+        <v>0.4882946908473969</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.468416800000341</v>
+        <v>0.5183206000001519</v>
       </c>
       <c r="R70" t="n">
-        <v>0.0009844875894486904</v>
+        <v>2.026511720032431e-05</v>
       </c>
       <c r="S70" t="n">
-        <v>930.6286171338442</v>
+        <v>950.0684250469041</v>
       </c>
       <c r="T70" t="n">
-        <v>201.8757595409537</v>
+        <v>200.7225079698721</v>
       </c>
       <c r="U70" t="n">
-        <v>9.000641816894808</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V70" t="n">
-        <v>97.50947381891888</v>
+        <v>1.040850087583635</v>
       </c>
       <c r="W70" t="n">
-        <v>0.294229795216836</v>
+        <v>0.05020239297931539</v>
       </c>
       <c r="X70" t="n">
-        <v>1.370443029518569</v>
+        <v>2.395294647569807</v>
       </c>
       <c r="Y70" t="b">
         <v>1</v>
@@ -6004,70 +6004,70 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>939.3143389700824</v>
+        <v>947.246106486715</v>
       </c>
       <c r="D71" t="n">
-        <v>6.00391592587845</v>
+        <v>5.710804380280239</v>
       </c>
       <c r="E71" t="n">
-        <v>212.8995855811849</v>
+        <v>214.4264247137572</v>
       </c>
       <c r="F71" t="n">
-        <v>0.8140485286712646</v>
+        <v>0.7136481404304504</v>
       </c>
       <c r="G71" t="n">
-        <v>0.03057059999991907</v>
+        <v>0.08069960000284482</v>
       </c>
       <c r="H71" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.0008420366793870926</v>
       </c>
       <c r="I71" t="n">
-        <v>939.3143389700804</v>
+        <v>947.2461064867159</v>
       </c>
       <c r="J71" t="n">
-        <v>212.8995855811851</v>
+        <v>214.4264247137436</v>
       </c>
       <c r="K71" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="L71" t="n">
-        <v>2.046363078989089e-12</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="M71" t="n">
-        <v>2.557953848736361e-13</v>
+        <v>1.364242052659392e-11</v>
       </c>
       <c r="N71" t="n">
-        <v>2.996725853983713</v>
+        <v>3.289837399581923</v>
       </c>
       <c r="O71" t="b">
         <v>1</v>
       </c>
       <c r="P71" t="n">
-        <v>0.5411326289176941</v>
+        <v>0.9583125710487366</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.2038587000006373</v>
+        <v>0.4464440000010654</v>
       </c>
       <c r="R71" t="n">
-        <v>0.0001060059221345</v>
+        <v>0.0001035949680954218</v>
       </c>
       <c r="S71" t="n">
-        <v>939.9490512839977</v>
+        <v>949.993406728825</v>
       </c>
       <c r="T71" t="n">
-        <v>213.0054460729478</v>
+        <v>213.5384241110025</v>
       </c>
       <c r="U71" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V71" t="n">
-        <v>0.6347123139153155</v>
+        <v>2.747300242109986</v>
       </c>
       <c r="W71" t="n">
-        <v>0.1058604917629111</v>
+        <v>0.8880006027547722</v>
       </c>
       <c r="X71" t="n">
-        <v>2.996725853983713</v>
+        <v>3.289837399581923</v>
       </c>
       <c r="Y71" t="b">
         <v>1</v>
@@ -6079,74 +6079,74 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>884.0525024462436</v>
+        <v>934.0364866687535</v>
       </c>
       <c r="D72" t="n">
-        <v>6.714681683110493</v>
+        <v>3.663800279555868</v>
       </c>
       <c r="E72" t="n">
-        <v>188.9420095987055</v>
+        <v>213.5496562965097</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7708748579025269</v>
+        <v>0.7086822986602783</v>
       </c>
       <c r="G72" t="n">
-        <v>0.118660699999964</v>
+        <v>0.1069246000042767</v>
       </c>
       <c r="H72" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.0008420366793870926</v>
       </c>
       <c r="I72" t="n">
-        <v>924.480668200554</v>
+        <v>934.0364866687496</v>
       </c>
       <c r="J72" t="n">
-        <v>188.9420095987055</v>
+        <v>213.5496562965104</v>
       </c>
       <c r="K72" t="n">
-        <v>9.000641717438157</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L72" t="n">
-        <v>40.42816575431038</v>
+        <v>3.865352482534945e-12</v>
       </c>
       <c r="M72" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>6.252776074688882e-13</v>
       </c>
       <c r="N72" t="n">
-        <v>2.285960034327664</v>
+        <v>5.336841500306295</v>
       </c>
       <c r="O72" t="b">
         <v>1</v>
       </c>
       <c r="P72" t="n">
-        <v>0.9761733412742615</v>
+        <v>0.999675989151001</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.4292052999990119</v>
+        <v>0.4928064000050654</v>
       </c>
       <c r="R72" t="n">
-        <v>0.0004801404429599643</v>
+        <v>0.000125186110381037</v>
       </c>
       <c r="S72" t="n">
-        <v>937.4819987153314</v>
+        <v>940.779101576279</v>
       </c>
       <c r="T72" t="n">
-        <v>189.3129014786839</v>
+        <v>212.8220117272085</v>
       </c>
       <c r="U72" t="n">
-        <v>9.00064180984058</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V72" t="n">
-        <v>53.42949626908785</v>
+        <v>6.742614907525535</v>
       </c>
       <c r="W72" t="n">
-        <v>0.3708918799784158</v>
+        <v>0.7276445693012477</v>
       </c>
       <c r="X72" t="n">
-        <v>2.285960126730087</v>
+        <v>5.336841500306295</v>
       </c>
       <c r="Y72" t="b">
         <v>1</v>
@@ -6158,74 +6158,74 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>929.2087438988716</v>
+        <v>839.0334151815869</v>
       </c>
       <c r="D73" t="n">
-        <v>12.27835645211013</v>
+        <v>8.030760253486523</v>
       </c>
       <c r="E73" t="n">
-        <v>153.010881866181</v>
+        <v>188.5626192910129</v>
       </c>
       <c r="F73" t="n">
-        <v>0.8265721797943115</v>
+        <v>0.8515658974647522</v>
       </c>
       <c r="G73" t="n">
-        <v>0.1944313999993028</v>
+        <v>0.2682053000025917</v>
       </c>
       <c r="H73" t="n">
-        <v>0.001156892394647002</v>
+        <v>0.002021597931161523</v>
       </c>
       <c r="I73" t="n">
-        <v>929.2087435860079</v>
+        <v>918.0458240077306</v>
       </c>
       <c r="J73" t="n">
-        <v>173.1913510493296</v>
+        <v>188.5626192910132</v>
       </c>
       <c r="K73" t="n">
-        <v>12.27835645704801</v>
+        <v>9.000641556048571</v>
       </c>
       <c r="L73" t="n">
-        <v>3.128636762994574e-07</v>
+        <v>79.01240882614377</v>
       </c>
       <c r="M73" t="n">
-        <v>20.18046918314857</v>
+        <v>2.557953848736361e-13</v>
       </c>
       <c r="N73" t="n">
-        <v>4.937881215028028e-09</v>
+        <v>0.9698813025620474</v>
       </c>
       <c r="O73" t="b">
         <v>1</v>
       </c>
       <c r="P73" t="n">
-        <v>0.9238184690475464</v>
+        <v>0.9786239862442017</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.052046400000108</v>
+        <v>1.31790689999616</v>
       </c>
       <c r="R73" t="n">
-        <v>0.00141736795194447</v>
+        <v>0.0006177912000566721</v>
       </c>
       <c r="S73" t="n">
-        <v>807.6890648975353</v>
+        <v>926.5458054966806</v>
       </c>
       <c r="T73" t="n">
-        <v>162.6786125842324</v>
+        <v>189.9888157123912</v>
       </c>
       <c r="U73" t="n">
-        <v>12.09898410985965</v>
+        <v>9.000641905542803</v>
       </c>
       <c r="V73" t="n">
-        <v>121.5196790013363</v>
+        <v>87.51239031509374</v>
       </c>
       <c r="W73" t="n">
-        <v>9.667730718051388</v>
+        <v>1.426196421378307</v>
       </c>
       <c r="X73" t="n">
-        <v>0.179372342250474</v>
+        <v>0.9698816520562801</v>
       </c>
       <c r="Y73" t="b">
         <v>1</v>
@@ -6237,74 +6237,74 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>971.2530929094758</v>
+        <v>945.0613792652688</v>
       </c>
       <c r="D74" t="n">
-        <v>10.70422964915671</v>
+        <v>4.264814151631617</v>
       </c>
       <c r="E74" t="n">
-        <v>127.2548136260511</v>
+        <v>199.996314381239</v>
       </c>
       <c r="F74" t="n">
-        <v>0.8341188430786133</v>
+        <v>0.6916452050209045</v>
       </c>
       <c r="G74" t="n">
-        <v>0.318491100000756</v>
+        <v>0.0991241000010632</v>
       </c>
       <c r="H74" t="n">
-        <v>0.01866349019110203</v>
+        <v>0.0008420366793870926</v>
       </c>
       <c r="I74" t="n">
-        <v>939.7170909050923</v>
+        <v>945.0613792652647</v>
       </c>
       <c r="J74" t="n">
-        <v>163.0038996273458</v>
+        <v>199.996314381239</v>
       </c>
       <c r="K74" t="n">
-        <v>11.94922366345705</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L74" t="n">
-        <v>31.53600200438348</v>
+        <v>4.092726157978177e-12</v>
       </c>
       <c r="M74" t="n">
-        <v>35.74908600129469</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="N74" t="n">
-        <v>1.244994014300339</v>
+        <v>4.735827628230545</v>
       </c>
       <c r="O74" t="b">
         <v>1</v>
       </c>
       <c r="P74" t="n">
-        <v>0.9999942779541016</v>
+        <v>0.9995777010917664</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.5378185999998095</v>
+        <v>0.5011131000064779</v>
       </c>
       <c r="R74" t="n">
-        <v>0.002393670147284865</v>
+        <v>2.393891736574005e-05</v>
       </c>
       <c r="S74" t="n">
-        <v>800.0000604110494</v>
+        <v>946.9089807681223</v>
       </c>
       <c r="T74" t="n">
-        <v>150.000552831106</v>
+        <v>199.9660676609036</v>
       </c>
       <c r="U74" t="n">
-        <v>10.28638617194319</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V74" t="n">
-        <v>171.2530324984264</v>
+        <v>1.847601502853536</v>
       </c>
       <c r="W74" t="n">
-        <v>22.7457392050549</v>
+        <v>0.03024672033541265</v>
       </c>
       <c r="X74" t="n">
-        <v>0.4178434772135144</v>
+        <v>4.735827628230545</v>
       </c>
       <c r="Y74" t="b">
         <v>1</v>
@@ -6320,70 +6320,70 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>882.9168039349611</v>
+        <v>877.5317534081569</v>
       </c>
       <c r="D75" t="n">
-        <v>8.944751373635901</v>
+        <v>6.80807667478205</v>
       </c>
       <c r="E75" t="n">
-        <v>208.2526466964262</v>
+        <v>194.0252297873003</v>
       </c>
       <c r="F75" t="n">
-        <v>0.5638843178749084</v>
+        <v>0.8031570315361023</v>
       </c>
       <c r="G75" t="n">
-        <v>0.1079219999992347</v>
+        <v>0.2529292999970494</v>
       </c>
       <c r="H75" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I75" t="n">
-        <v>924.4806681515233</v>
+        <v>922.2058290655435</v>
       </c>
       <c r="J75" t="n">
-        <v>208.2526466964262</v>
+        <v>194.0252297873003</v>
       </c>
       <c r="K75" t="n">
-        <v>9.000641618845385</v>
+        <v>9.000641657386829</v>
       </c>
       <c r="L75" t="n">
-        <v>41.56386421656225</v>
+        <v>44.67407565738665</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>0.05589024520948449</v>
+        <v>2.19256498260478</v>
       </c>
       <c r="O75" t="b">
         <v>1</v>
       </c>
       <c r="P75" t="n">
-        <v>0.4321063160896301</v>
+        <v>0.9918712377548218</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.3643185000000813</v>
+        <v>1.257818600002793</v>
       </c>
       <c r="R75" t="n">
-        <v>0.0004688234766945243</v>
+        <v>0.0003151548153255135</v>
       </c>
       <c r="S75" t="n">
-        <v>935.1813922688189</v>
+        <v>928.7595576686881</v>
       </c>
       <c r="T75" t="n">
-        <v>208.40787806084</v>
+        <v>194.1898478802496</v>
       </c>
       <c r="U75" t="n">
-        <v>9.021256659829975</v>
+        <v>9.000641744780634</v>
       </c>
       <c r="V75" t="n">
-        <v>52.26458833385777</v>
+        <v>51.22780426053123</v>
       </c>
       <c r="W75" t="n">
-        <v>0.1552313644138223</v>
+        <v>0.1646180929492687</v>
       </c>
       <c r="X75" t="n">
-        <v>0.07650528619407382</v>
+        <v>2.192565069998584</v>
       </c>
       <c r="Y75" t="b">
         <v>1</v>
@@ -6395,74 +6395,74 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>877.3692237215081</v>
+        <v>942.989724643875</v>
       </c>
       <c r="D76" t="n">
-        <v>9.000114999317264</v>
+        <v>11.71596944962758</v>
       </c>
       <c r="E76" t="n">
-        <v>193.2959101989771</v>
+        <v>127.4889293428171</v>
       </c>
       <c r="F76" t="n">
-        <v>0.5507853031158447</v>
+        <v>0.6464095115661621</v>
       </c>
       <c r="G76" t="n">
-        <v>0.1162901999996393</v>
+        <v>0.7961703999972087</v>
       </c>
       <c r="H76" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.0130509315058589</v>
       </c>
       <c r="I76" t="n">
-        <v>924.4806716588629</v>
+        <v>919.7665887827184</v>
       </c>
       <c r="J76" t="n">
-        <v>193.2959101989771</v>
+        <v>165.1586384024819</v>
       </c>
       <c r="K76" t="n">
-        <v>9.000641614529927</v>
+        <v>11.71593515260261</v>
       </c>
       <c r="L76" t="n">
-        <v>47.1114479373548</v>
+        <v>23.22313586115661</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>37.6697090596648</v>
       </c>
       <c r="N76" t="n">
-        <v>0.000526615212663728</v>
+        <v>3.429702497292908e-05</v>
       </c>
       <c r="O76" t="b">
         <v>1</v>
       </c>
       <c r="P76" t="n">
-        <v>0.6445889472961426</v>
+        <v>0.9999994039535522</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.3655375999987882</v>
+        <v>1.295689300000959</v>
       </c>
       <c r="R76" t="n">
-        <v>0.0005228730733506382</v>
+        <v>0.0009203584049828351</v>
       </c>
       <c r="S76" t="n">
-        <v>935.2168060001291</v>
+        <v>824.5286449040241</v>
       </c>
       <c r="T76" t="n">
-        <v>193.7231703718294</v>
+        <v>150.0005524902014</v>
       </c>
       <c r="U76" t="n">
-        <v>9.077597820249409</v>
+        <v>11.6395414748954</v>
       </c>
       <c r="V76" t="n">
-        <v>57.84758227862096</v>
+        <v>118.4610797398509</v>
       </c>
       <c r="W76" t="n">
-        <v>0.4272601728523</v>
+        <v>22.51162314738437</v>
       </c>
       <c r="X76" t="n">
-        <v>0.0774828209321452</v>
+        <v>0.07642797473218366</v>
       </c>
       <c r="Y76" t="b">
         <v>1</v>
@@ -6478,70 +6478,70 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>939.0208991743779</v>
+        <v>947.9151831652808</v>
       </c>
       <c r="D77" t="n">
-        <v>10.68189274023577</v>
+        <v>9.193474878346382</v>
       </c>
       <c r="E77" t="n">
-        <v>136.4872994500552</v>
+        <v>108.2672046072037</v>
       </c>
       <c r="F77" t="n">
-        <v>0.8342413306236267</v>
+        <v>0.7431839108467102</v>
       </c>
       <c r="G77" t="n">
-        <v>0.1276684000004025</v>
+        <v>0.3487988999986555</v>
       </c>
       <c r="H77" t="n">
-        <v>0.002018802100792527</v>
+        <v>0.01405216194689274</v>
       </c>
       <c r="I77" t="n">
-        <v>917.7887190746554</v>
+        <v>947.9151831652086</v>
       </c>
       <c r="J77" t="n">
-        <v>173.1945262499984</v>
+        <v>165.1587225588535</v>
       </c>
       <c r="K77" t="n">
-        <v>12.75145686751307</v>
+        <v>9.893435480395592</v>
       </c>
       <c r="L77" t="n">
-        <v>21.23218009972243</v>
+        <v>7.219114195322618e-11</v>
       </c>
       <c r="M77" t="n">
-        <v>36.70722679994313</v>
+        <v>56.8915179516498</v>
       </c>
       <c r="N77" t="n">
-        <v>2.069564127277294</v>
+        <v>0.6999606020492095</v>
       </c>
       <c r="O77" t="b">
         <v>1</v>
       </c>
       <c r="P77" t="n">
-        <v>0.9998886585235596</v>
+        <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.5982686999996076</v>
+        <v>1.363378499998362</v>
       </c>
       <c r="R77" t="n">
-        <v>0.002344639506191015</v>
+        <v>0.0007889397675171494</v>
       </c>
       <c r="S77" t="n">
-        <v>800.0000435648012</v>
+        <v>844.962329412985</v>
       </c>
       <c r="T77" t="n">
-        <v>150.0005529379655</v>
+        <v>150.0005516881647</v>
       </c>
       <c r="U77" t="n">
-        <v>10.27270873411296</v>
+        <v>9.079481405399065</v>
       </c>
       <c r="V77" t="n">
-        <v>139.0208556095766</v>
+        <v>102.9528537522958</v>
       </c>
       <c r="W77" t="n">
-        <v>13.51325348791022</v>
+        <v>41.73334708096101</v>
       </c>
       <c r="X77" t="n">
-        <v>0.4091840061228105</v>
+        <v>0.1139934729473175</v>
       </c>
       <c r="Y77" t="b">
         <v>1</v>
@@ -6557,70 +6557,70 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>884.6688868673981</v>
+        <v>871.8854560109301</v>
       </c>
       <c r="D78" t="n">
-        <v>6.943234626599951</v>
+        <v>6.916476008336256</v>
       </c>
       <c r="E78" t="n">
-        <v>204.6900831043484</v>
+        <v>222.9065255520293</v>
       </c>
       <c r="F78" t="n">
-        <v>0.8440181612968445</v>
+        <v>0.8457565307617188</v>
       </c>
       <c r="G78" t="n">
-        <v>0.09701029999996535</v>
+        <v>0.2762287000005017</v>
       </c>
       <c r="H78" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.001605496276170015</v>
       </c>
       <c r="I78" t="n">
-        <v>924.4809565202777</v>
+        <v>922.2058285651951</v>
       </c>
       <c r="J78" t="n">
-        <v>204.6900831043484</v>
+        <v>222.9065792769907</v>
       </c>
       <c r="K78" t="n">
-        <v>9.000641544526271</v>
+        <v>9.00064164675794</v>
       </c>
       <c r="L78" t="n">
-        <v>39.81206965287959</v>
+        <v>50.32037255426508</v>
       </c>
       <c r="M78" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>5.372496138988936e-05</v>
       </c>
       <c r="N78" t="n">
-        <v>2.05740691792632</v>
+        <v>2.084165638421683</v>
       </c>
       <c r="O78" t="b">
         <v>1</v>
       </c>
       <c r="P78" t="n">
-        <v>0.968358039855957</v>
+        <v>0.9884188771247864</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.4506753999994544</v>
+        <v>1.433672499995737</v>
       </c>
       <c r="R78" t="n">
-        <v>0.000460146926343441</v>
+        <v>0.0007008083630353212</v>
       </c>
       <c r="S78" t="n">
-        <v>935.7938081251889</v>
+        <v>930.6355386761165</v>
       </c>
       <c r="T78" t="n">
-        <v>204.833273231664</v>
+        <v>219.7155954593306</v>
       </c>
       <c r="U78" t="n">
-        <v>9.000641713436492</v>
+        <v>9.000641777830067</v>
       </c>
       <c r="V78" t="n">
-        <v>51.12492125779079</v>
+        <v>58.75008266518648</v>
       </c>
       <c r="W78" t="n">
-        <v>0.1431901273155916</v>
+        <v>3.190930092698721</v>
       </c>
       <c r="X78" t="n">
-        <v>2.057407086836541</v>
+        <v>2.08416576949381</v>
       </c>
       <c r="Y78" t="b">
         <v>1</v>
@@ -6632,74 +6632,74 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Z_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>932.2204333806808</v>
+        <v>826.3062461094183</v>
       </c>
       <c r="D79" t="n">
-        <v>13.03981855565778</v>
+        <v>8.706141572777794</v>
       </c>
       <c r="E79" t="n">
-        <v>191.1558959956488</v>
+        <v>208.0898692070231</v>
       </c>
       <c r="F79" t="n">
-        <v>0.6110718250274658</v>
+        <v>0.8152469396591187</v>
       </c>
       <c r="G79" t="n">
-        <v>0.1527317000000039</v>
+        <v>0.230747399997199</v>
       </c>
       <c r="H79" t="n">
-        <v>0.002067800611257553</v>
+        <v>0.002684350591152906</v>
       </c>
       <c r="I79" t="n">
-        <v>924.0382220847861</v>
+        <v>913.993437831081</v>
       </c>
       <c r="J79" t="n">
-        <v>187.1332932452968</v>
+        <v>208.0898692070232</v>
       </c>
       <c r="K79" t="n">
-        <v>12.50750790625518</v>
+        <v>9.000641580237213</v>
       </c>
       <c r="L79" t="n">
-        <v>8.182211295894717</v>
+        <v>87.68719172166266</v>
       </c>
       <c r="M79" t="n">
-        <v>4.022602750352064</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N79" t="n">
-        <v>0.5323106494025964</v>
+        <v>0.2945000074594191</v>
       </c>
       <c r="O79" t="b">
         <v>1</v>
       </c>
       <c r="P79" t="n">
-        <v>0.08337151259183884</v>
+        <v>0.9105802774429321</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.100767100000667</v>
+        <v>1.309967499997583</v>
       </c>
       <c r="R79" t="n">
-        <v>0.001358153065666556</v>
+        <v>0.0007506557158194482</v>
       </c>
       <c r="S79" t="n">
-        <v>950.6380545289414</v>
+        <v>925.5691786833794</v>
       </c>
       <c r="T79" t="n">
-        <v>185.1892156924482</v>
+        <v>206.7193667956829</v>
       </c>
       <c r="U79" t="n">
-        <v>12.17256584643809</v>
+        <v>9.000641645094834</v>
       </c>
       <c r="V79" t="n">
-        <v>18.41762114826065</v>
+        <v>99.26293257396105</v>
       </c>
       <c r="W79" t="n">
-        <v>5.966680303200633</v>
+        <v>1.370502411340198</v>
       </c>
       <c r="X79" t="n">
-        <v>0.8672527092196862</v>
+        <v>0.2945000723170406</v>
       </c>
       <c r="Y79" t="b">
         <v>1</v>
@@ -6711,74 +6711,74 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>972.4393547485565</v>
+        <v>870.6556061291161</v>
       </c>
       <c r="D80" t="n">
-        <v>10.29519839564596</v>
+        <v>8.070185334123567</v>
       </c>
       <c r="E80" t="n">
-        <v>151.529578268895</v>
+        <v>195.4632670450195</v>
       </c>
       <c r="F80" t="n">
-        <v>0.8341188430786133</v>
+        <v>0.8498510122299194</v>
       </c>
       <c r="G80" t="n">
-        <v>0.2394552000005206</v>
+        <v>0.2674407999948016</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0008777803741395473</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I80" t="n">
-        <v>972.4548319337069</v>
+        <v>922.2058283074825</v>
       </c>
       <c r="J80" t="n">
-        <v>173.1947969893786</v>
+        <v>195.4632670450195</v>
       </c>
       <c r="K80" t="n">
-        <v>10.29533756016274</v>
+        <v>9.000641600409805</v>
       </c>
       <c r="L80" t="n">
-        <v>0.01547718515041652</v>
+        <v>51.55022217836643</v>
       </c>
       <c r="M80" t="n">
-        <v>21.66521872048358</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>0.000139164516779644</v>
+        <v>0.9304562662862388</v>
       </c>
       <c r="O80" t="b">
         <v>1</v>
       </c>
       <c r="P80" t="n">
-        <v>0.9639032483100891</v>
+        <v>0.9699541926383972</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.8599228999992192</v>
+        <v>1.167383100000734</v>
       </c>
       <c r="R80" t="n">
-        <v>0.00126209924928844</v>
+        <v>0.0003561023331712931</v>
       </c>
       <c r="S80" t="n">
-        <v>829.1770962181605</v>
+        <v>928.0917450773708</v>
       </c>
       <c r="T80" t="n">
-        <v>162.0995596863681</v>
+        <v>195.6511246398176</v>
       </c>
       <c r="U80" t="n">
-        <v>10.16698584857551</v>
+        <v>9.000641923253797</v>
       </c>
       <c r="V80" t="n">
-        <v>143.262258530396</v>
+        <v>57.43613894825467</v>
       </c>
       <c r="W80" t="n">
-        <v>10.56998141747312</v>
+        <v>0.1878575947980892</v>
       </c>
       <c r="X80" t="n">
-        <v>0.1282125470704507</v>
+        <v>0.9304565891302303</v>
       </c>
       <c r="Y80" t="b">
         <v>1</v>
@@ -6794,70 +6794,70 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>858.9869051172776</v>
+        <v>835.2771892783403</v>
       </c>
       <c r="D81" t="n">
-        <v>6.821027048326163</v>
+        <v>7.571486103960769</v>
       </c>
       <c r="E81" t="n">
-        <v>185.9448383803137</v>
+        <v>206.9009492437244</v>
       </c>
       <c r="F81" t="n">
-        <v>0.839372456073761</v>
+        <v>0.8501850366592407</v>
       </c>
       <c r="G81" t="n">
-        <v>0.1136040000001231</v>
+        <v>0.2620736999961082</v>
       </c>
       <c r="H81" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I81" t="n">
-        <v>924.4806705751859</v>
+        <v>922.2058319161893</v>
       </c>
       <c r="J81" t="n">
-        <v>185.9448383803138</v>
+        <v>206.9009492437245</v>
       </c>
       <c r="K81" t="n">
-        <v>9.000641641022909</v>
+        <v>9.000641612962443</v>
       </c>
       <c r="L81" t="n">
-        <v>65.49376545790824</v>
+        <v>86.92864263784895</v>
       </c>
       <c r="M81" t="n">
         <v>8.526512829121202e-14</v>
       </c>
       <c r="N81" t="n">
-        <v>2.179614592696746</v>
+        <v>1.429155509001674</v>
       </c>
       <c r="O81" t="b">
         <v>1</v>
       </c>
       <c r="P81" t="n">
-        <v>0.9914631247520447</v>
+        <v>0.9894846081733704</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.3739974000000075</v>
+        <v>1.268750100003672</v>
       </c>
       <c r="R81" t="n">
-        <v>0.0007205067668110132</v>
+        <v>0.0006708495202474296</v>
       </c>
       <c r="S81" t="n">
-        <v>935.08827386296</v>
+        <v>925.9962250398866</v>
       </c>
       <c r="T81" t="n">
-        <v>186.4921710164753</v>
+        <v>206.0110994611994</v>
       </c>
       <c r="U81" t="n">
-        <v>9.000641864383589</v>
+        <v>9.000641832031047</v>
       </c>
       <c r="V81" t="n">
-        <v>76.10136874568241</v>
+        <v>90.71903576154625</v>
       </c>
       <c r="W81" t="n">
-        <v>0.5473326361615989</v>
+        <v>0.8898497825249763</v>
       </c>
       <c r="X81" t="n">
-        <v>2.179614816057425</v>
+        <v>1.429155728070278</v>
       </c>
       <c r="Y81" t="b">
         <v>1</v>
@@ -6869,74 +6869,74 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>964.3146848234168</v>
+        <v>931.6909483615435</v>
       </c>
       <c r="D82" t="n">
-        <v>4.070486283664396</v>
+        <v>11.93276300546589</v>
       </c>
       <c r="E82" t="n">
-        <v>206.7471843876719</v>
+        <v>164.4810752764879</v>
       </c>
       <c r="F82" t="n">
-        <v>0.81343674659729</v>
+        <v>0.6464095115661621</v>
       </c>
       <c r="G82" t="n">
-        <v>0.048921400000836</v>
+        <v>0.4053917000055662</v>
       </c>
       <c r="H82" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.001615169807337224</v>
       </c>
       <c r="I82" t="n">
-        <v>964.314684894108</v>
+        <v>928.6808325093019</v>
       </c>
       <c r="J82" t="n">
-        <v>206.7471843876693</v>
+        <v>173.3835757657632</v>
       </c>
       <c r="K82" t="n">
-        <v>9.000641779862162</v>
+        <v>11.93276302174899</v>
       </c>
       <c r="L82" t="n">
-        <v>7.06912715031649e-08</v>
+        <v>3.010115852241597</v>
       </c>
       <c r="M82" t="n">
-        <v>2.643218977027573e-12</v>
+        <v>8.902500489275326</v>
       </c>
       <c r="N82" t="n">
-        <v>4.930155496197766</v>
+        <v>1.628309931334115e-08</v>
       </c>
       <c r="O82" t="b">
         <v>1</v>
       </c>
       <c r="P82" t="n">
-        <v>0.9978795051574707</v>
+        <v>0.1096323281526566</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.1667718000007881</v>
+        <v>1.973546300003363</v>
       </c>
       <c r="R82" t="n">
-        <v>9.763384150573984e-05</v>
+        <v>0.0006425203173421323</v>
       </c>
       <c r="S82" t="n">
-        <v>965.4285214294903</v>
+        <v>851.1349822534781</v>
       </c>
       <c r="T82" t="n">
-        <v>206.8835627551345</v>
+        <v>168.581733539082</v>
       </c>
       <c r="U82" t="n">
-        <v>9.000641779862162</v>
+        <v>11.88955180145306</v>
       </c>
       <c r="V82" t="n">
-        <v>1.113836606073505</v>
+        <v>80.55596610806538</v>
       </c>
       <c r="W82" t="n">
-        <v>0.136378367462612</v>
+        <v>4.100658262594067</v>
       </c>
       <c r="X82" t="n">
-        <v>4.930155496197766</v>
+        <v>0.04321120401282208</v>
       </c>
       <c r="Y82" t="b">
         <v>1</v>
@@ -6952,70 +6952,70 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>839.9126042606035</v>
+        <v>878.3331401650551</v>
       </c>
       <c r="D83" t="n">
-        <v>8.907747838441404</v>
+        <v>8.618580890887042</v>
       </c>
       <c r="E83" t="n">
-        <v>221.1927624072788</v>
+        <v>195.2322602506398</v>
       </c>
       <c r="F83" t="n">
-        <v>0.8026584386825562</v>
+        <v>0.728635311126709</v>
       </c>
       <c r="G83" t="n">
-        <v>0.1588515999992524</v>
+        <v>0.2451749999963795</v>
       </c>
       <c r="H83" t="n">
-        <v>0.00147869111970067</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I83" t="n">
-        <v>923.1727218297198</v>
+        <v>922.2058289389695</v>
       </c>
       <c r="J83" t="n">
-        <v>221.1927448638558</v>
+        <v>195.2322602506398</v>
       </c>
       <c r="K83" t="n">
-        <v>9.000536995142108</v>
+        <v>9.000641622055827</v>
       </c>
       <c r="L83" t="n">
-        <v>83.26011756911623</v>
+        <v>43.87268877391443</v>
       </c>
       <c r="M83" t="n">
-        <v>1.754342295612332e-05</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>0.09278915670070376</v>
+        <v>0.3820607311687851</v>
       </c>
       <c r="O83" t="b">
         <v>1</v>
       </c>
       <c r="P83" t="n">
-        <v>0.7315876483917236</v>
+        <v>0.8391749262809753</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.384424099998796</v>
+        <v>1.214337799996429</v>
       </c>
       <c r="R83" t="n">
-        <v>0.0008903037523850799</v>
+        <v>0.0003075041749980301</v>
       </c>
       <c r="S83" t="n">
-        <v>929.5986465121015</v>
+        <v>928.797279320914</v>
       </c>
       <c r="T83" t="n">
-        <v>221.5202664062019</v>
+        <v>195.3943361095741</v>
       </c>
       <c r="U83" t="n">
-        <v>9.049795252340969</v>
+        <v>9.000641821257469</v>
       </c>
       <c r="V83" t="n">
-        <v>89.68604225149795</v>
+        <v>50.4641391558589</v>
       </c>
       <c r="W83" t="n">
-        <v>0.3275039989231061</v>
+        <v>0.162075858934287</v>
       </c>
       <c r="X83" t="n">
-        <v>0.1420474138995651</v>
+        <v>0.382060930370427</v>
       </c>
       <c r="Y83" t="b">
         <v>1</v>
@@ -7031,70 +7031,70 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>855.3309995817704</v>
+        <v>820.9664621707288</v>
       </c>
       <c r="D84" t="n">
-        <v>8.772997773417615</v>
+        <v>6.465457077017227</v>
       </c>
       <c r="E84" t="n">
-        <v>187.5215368940038</v>
+        <v>163.4304930582331</v>
       </c>
       <c r="F84" t="n">
-        <v>0.783454954624176</v>
+        <v>0.5216308236122131</v>
       </c>
       <c r="G84" t="n">
-        <v>0.1168059999999969</v>
+        <v>0.3704686000055517</v>
       </c>
       <c r="H84" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.003862845944240689</v>
       </c>
       <c r="I84" t="n">
-        <v>924.4806741762613</v>
+        <v>922.2340479745938</v>
       </c>
       <c r="J84" t="n">
-        <v>187.5215368940038</v>
+        <v>165.1586350810926</v>
       </c>
       <c r="K84" t="n">
-        <v>9.00064139435195</v>
+        <v>9.000641732869223</v>
       </c>
       <c r="L84" t="n">
-        <v>69.14967459449099</v>
+        <v>101.2675858038649</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>1.728142022859487</v>
       </c>
       <c r="N84" t="n">
-        <v>0.2276436209343355</v>
+        <v>2.535184655851996</v>
       </c>
       <c r="O84" t="b">
         <v>1</v>
       </c>
       <c r="P84" t="n">
-        <v>0.9085878133773804</v>
+        <v>0.9986388087272644</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.4086628000004566</v>
+        <v>1.244851199997356</v>
       </c>
       <c r="R84" t="n">
-        <v>0.0007539137732237577</v>
+        <v>0.000745869823731482</v>
       </c>
       <c r="S84" t="n">
-        <v>934.5265725426169</v>
+        <v>932.6437580501572</v>
       </c>
       <c r="T84" t="n">
-        <v>188.103494595004</v>
+        <v>159.7241293340472</v>
       </c>
       <c r="U84" t="n">
-        <v>9.00064190066119</v>
+        <v>9.000637721007102</v>
       </c>
       <c r="V84" t="n">
-        <v>79.19557296084656</v>
+        <v>111.6772958794284</v>
       </c>
       <c r="W84" t="n">
-        <v>0.5819577010001353</v>
+        <v>3.706363724185962</v>
       </c>
       <c r="X84" t="n">
-        <v>0.2276441272435754</v>
+        <v>2.535180643989875</v>
       </c>
       <c r="Y84" t="b">
         <v>1</v>
@@ -7110,70 +7110,70 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>847.863121084725</v>
+        <v>817.6875585172629</v>
       </c>
       <c r="D85" t="n">
-        <v>8.55256397682507</v>
+        <v>7.315800083460689</v>
       </c>
       <c r="E85" t="n">
-        <v>201.3666153914067</v>
+        <v>213.922824918435</v>
       </c>
       <c r="F85" t="n">
-        <v>0.833712637424469</v>
+        <v>0.8495083451271057</v>
       </c>
       <c r="G85" t="n">
-        <v>0.1276875000003201</v>
+        <v>0.2583872999966843</v>
       </c>
       <c r="H85" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.002021597931161523</v>
       </c>
       <c r="I85" t="n">
-        <v>924.480683723165</v>
+        <v>918.0444487935658</v>
       </c>
       <c r="J85" t="n">
-        <v>201.3666153914067</v>
+        <v>213.9228249184349</v>
       </c>
       <c r="K85" t="n">
-        <v>9.000641446570471</v>
+        <v>9.000641635552942</v>
       </c>
       <c r="L85" t="n">
-        <v>76.61756263844006</v>
+        <v>100.3568902763029</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="N85" t="n">
-        <v>0.4480774697454013</v>
+        <v>1.684841552092252</v>
       </c>
       <c r="O85" t="b">
         <v>1</v>
       </c>
       <c r="P85" t="n">
-        <v>0.8725757598876953</v>
+        <v>0.9921920895576477</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.4364466999995784</v>
+        <v>1.150991499998781</v>
       </c>
       <c r="R85" t="n">
-        <v>0.000818071304820478</v>
+        <v>0.0009434610838070512</v>
       </c>
       <c r="S85" t="n">
-        <v>931.9377649361013</v>
+        <v>925.5988735877182</v>
       </c>
       <c r="T85" t="n">
-        <v>201.6146280114612</v>
+        <v>211.4131859447005</v>
       </c>
       <c r="U85" t="n">
-        <v>9.000641696564838</v>
+        <v>9.000641166854022</v>
       </c>
       <c r="V85" t="n">
-        <v>84.07464385137632</v>
+        <v>107.9113150704553</v>
       </c>
       <c r="W85" t="n">
-        <v>0.2480126200544532</v>
+        <v>2.509638973734468</v>
       </c>
       <c r="X85" t="n">
-        <v>0.4480777197397678</v>
+        <v>1.684841083393333</v>
       </c>
       <c r="Y85" t="b">
         <v>1</v>
@@ -7185,74 +7185,74 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>939.9969463757054</v>
+        <v>933.4535566835518</v>
       </c>
       <c r="D86" t="n">
-        <v>9.754555634461923</v>
+        <v>4.221359047912894</v>
       </c>
       <c r="E86" t="n">
-        <v>125.3672234885963</v>
+        <v>211.7951508707739</v>
       </c>
       <c r="F86" t="n">
-        <v>0.8342413306236267</v>
+        <v>0.7086822986602783</v>
       </c>
       <c r="G86" t="n">
-        <v>0.236075400000118</v>
+        <v>0.08129899999767076</v>
       </c>
       <c r="H86" t="n">
-        <v>0.01395832654088736</v>
+        <v>0.0008420366793870926</v>
       </c>
       <c r="I86" t="n">
-        <v>939.7084528955079</v>
+        <v>933.4535566835502</v>
       </c>
       <c r="J86" t="n">
-        <v>163.0337470339863</v>
+        <v>211.7951508707737</v>
       </c>
       <c r="K86" t="n">
-        <v>10.39441374192302</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L86" t="n">
-        <v>0.2884934801975305</v>
+        <v>1.591615728102624e-12</v>
       </c>
       <c r="M86" t="n">
-        <v>37.66652354538999</v>
+        <v>1.4210854715202e-13</v>
       </c>
       <c r="N86" t="n">
-        <v>0.6398581074610927</v>
+        <v>4.779282731949269</v>
       </c>
       <c r="O86" t="b">
         <v>1</v>
       </c>
       <c r="P86" t="n">
-        <v>0.9999986886978149</v>
+        <v>0.9990314245223999</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.4828793999986374</v>
+        <v>0.503407199998037</v>
       </c>
       <c r="R86" t="n">
-        <v>0.001209896989166737</v>
+        <v>0.0001100934969144873</v>
       </c>
       <c r="S86" t="n">
-        <v>801.2785318567885</v>
+        <v>939.305723163325</v>
       </c>
       <c r="T86" t="n">
-        <v>150.0005523520783</v>
+        <v>211.1651433660745</v>
       </c>
       <c r="U86" t="n">
-        <v>9.643008740573507</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V86" t="n">
-        <v>138.7184145189169</v>
+        <v>5.852166479773132</v>
       </c>
       <c r="W86" t="n">
-        <v>24.63332886348203</v>
+        <v>0.6300075046993072</v>
       </c>
       <c r="X86" t="n">
-        <v>0.1115468938884163</v>
+        <v>4.779282731949269</v>
       </c>
       <c r="Y86" t="b">
         <v>1</v>
@@ -7264,74 +7264,74 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>919.0539202212327</v>
+        <v>889.3165426512867</v>
       </c>
       <c r="D87" t="n">
-        <v>10.63748294760498</v>
+        <v>5.962924279928853</v>
       </c>
       <c r="E87" t="n">
-        <v>148.5639561828438</v>
+        <v>203.9871174177678</v>
       </c>
       <c r="F87" t="n">
-        <v>0.8329695463180542</v>
+        <v>0.7963674068450928</v>
       </c>
       <c r="G87" t="n">
-        <v>0.2104945000010048</v>
+        <v>0.2583885999993072</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0193394273519516</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I87" t="n">
-        <v>933.4884744948813</v>
+        <v>922.205827464233</v>
       </c>
       <c r="J87" t="n">
-        <v>163.0071440884688</v>
+        <v>203.9871174177679</v>
       </c>
       <c r="K87" t="n">
-        <v>11.83249054207861</v>
+        <v>9.000641707596483</v>
       </c>
       <c r="L87" t="n">
-        <v>14.43455427364859</v>
+        <v>32.88928481294636</v>
       </c>
       <c r="M87" t="n">
-        <v>14.44318790562505</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="N87" t="n">
-        <v>1.19500759447363</v>
+        <v>3.03771742766763</v>
       </c>
       <c r="O87" t="b">
         <v>1</v>
       </c>
       <c r="P87" t="n">
-        <v>0.9923118948936462</v>
+        <v>0.799266517162323</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.9211178999994445</v>
+        <v>1.451706100000592</v>
       </c>
       <c r="R87" t="n">
-        <v>0.001253631198778749</v>
+        <v>0.0002720451739151031</v>
       </c>
       <c r="S87" t="n">
-        <v>811.4174586751725</v>
+        <v>930.0307000080733</v>
       </c>
       <c r="T87" t="n">
-        <v>156.8457142618649</v>
+        <v>203.4300663688255</v>
       </c>
       <c r="U87" t="n">
-        <v>10.43301672576839</v>
+        <v>9.000641779353819</v>
       </c>
       <c r="V87" t="n">
-        <v>107.6364615460602</v>
+        <v>40.71415735678659</v>
       </c>
       <c r="W87" t="n">
-        <v>8.281758079021131</v>
+        <v>0.5570510489422986</v>
       </c>
       <c r="X87" t="n">
-        <v>0.2044662218365936</v>
+        <v>3.037717499424966</v>
       </c>
       <c r="Y87" t="b">
         <v>1</v>
@@ -7343,74 +7343,74 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>K_Scratch</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>852.897604864306</v>
+        <v>975.1752385215719</v>
       </c>
       <c r="D88" t="n">
-        <v>7.909474033516901</v>
+        <v>4.60669126748069</v>
       </c>
       <c r="E88" t="n">
-        <v>202.305244416779</v>
+        <v>193.459614792617</v>
       </c>
       <c r="F88" t="n">
-        <v>0.827983558177948</v>
+        <v>0.6900404095649719</v>
       </c>
       <c r="G88" t="n">
-        <v>0.1131361999996443</v>
+        <v>0.07906250000087311</v>
       </c>
       <c r="H88" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.0008416784112341702</v>
       </c>
       <c r="I88" t="n">
-        <v>924.4806718453683</v>
+        <v>975.1752385205574</v>
       </c>
       <c r="J88" t="n">
-        <v>202.305244416779</v>
+        <v>193.4597170263514</v>
       </c>
       <c r="K88" t="n">
-        <v>9.000641699974473</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="L88" t="n">
-        <v>71.5830669810623</v>
+        <v>1.014541339827701e-09</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>0.0001022337344238622</v>
       </c>
       <c r="N88" t="n">
-        <v>1.091167666457572</v>
+        <v>4.393950512381473</v>
       </c>
       <c r="O88" t="b">
         <v>1</v>
       </c>
       <c r="P88" t="n">
-        <v>0.943444550037384</v>
+        <v>0.9980594515800476</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.4648555000003398</v>
+        <v>0.5522415000014007</v>
       </c>
       <c r="R88" t="n">
-        <v>0.0007648080354556441</v>
+        <v>4.615699435817078e-05</v>
       </c>
       <c r="S88" t="n">
-        <v>932.3605990368237</v>
+        <v>973.2340010449933</v>
       </c>
       <c r="T88" t="n">
-        <v>202.535035362852</v>
+        <v>193.6489032466731</v>
       </c>
       <c r="U88" t="n">
-        <v>9.000641887834918</v>
+        <v>9.000641779862162</v>
       </c>
       <c r="V88" t="n">
-        <v>79.46299417251771</v>
+        <v>1.941237476578635</v>
       </c>
       <c r="W88" t="n">
-        <v>0.2297909460729954</v>
+        <v>0.1892884540561397</v>
       </c>
       <c r="X88" t="n">
-        <v>1.091167854318018</v>
+        <v>4.393950512381473</v>
       </c>
       <c r="Y88" t="b">
         <v>1</v>
@@ -7422,74 +7422,74 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>895.8486861265578</v>
+        <v>987.8986731236233</v>
       </c>
       <c r="D89" t="n">
-        <v>7.439542226029475</v>
+        <v>8.757448023630989</v>
       </c>
       <c r="E89" t="n">
-        <v>189.9192228340302</v>
+        <v>147.4382369061982</v>
       </c>
       <c r="F89" t="n">
-        <v>0.5483524203300476</v>
+        <v>0.7420690655708313</v>
       </c>
       <c r="G89" t="n">
-        <v>0.1160435000001598</v>
+        <v>0.4633738999982597</v>
       </c>
       <c r="H89" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.001206731772981584</v>
       </c>
       <c r="I89" t="n">
-        <v>924.4806684564029</v>
+        <v>988.8306914635974</v>
       </c>
       <c r="J89" t="n">
-        <v>189.9192228340302</v>
+        <v>173.3839470318653</v>
       </c>
       <c r="K89" t="n">
-        <v>9.000641622948679</v>
+        <v>9.000000252491583</v>
       </c>
       <c r="L89" t="n">
-        <v>28.63198232984507</v>
+        <v>0.9320183399740927</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>25.94571012566709</v>
       </c>
       <c r="N89" t="n">
-        <v>1.561099396919204</v>
+        <v>0.2425522288605944</v>
       </c>
       <c r="O89" t="b">
         <v>1</v>
       </c>
       <c r="P89" t="n">
-        <v>0.780864953994751</v>
+        <v>0.99887615442276</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.4067883000006987</v>
+        <v>1.199405799998203</v>
       </c>
       <c r="R89" t="n">
-        <v>0.0003769493196159601</v>
+        <v>0.0009798330720514059</v>
       </c>
       <c r="S89" t="n">
-        <v>939.0272607680729</v>
+        <v>849.2579581130085</v>
       </c>
       <c r="T89" t="n">
-        <v>190.2184969052683</v>
+        <v>151.3485072351411</v>
       </c>
       <c r="U89" t="n">
-        <v>9.000641774509734</v>
+        <v>9.000639418445283</v>
       </c>
       <c r="V89" t="n">
-        <v>43.17857464151507</v>
+        <v>138.6407150106148</v>
       </c>
       <c r="W89" t="n">
-        <v>0.2992740712380737</v>
+        <v>3.910270328942914</v>
       </c>
       <c r="X89" t="n">
-        <v>1.561099548480259</v>
+        <v>0.2431913948142945</v>
       </c>
       <c r="Y89" t="b">
         <v>1</v>
@@ -7505,70 +7505,70 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>981.7689435248022</v>
+        <v>912.3400664953293</v>
       </c>
       <c r="D90" t="n">
-        <v>5.627043921572811</v>
+        <v>5.022960347220912</v>
       </c>
       <c r="E90" t="n">
-        <v>188.4837153950874</v>
+        <v>187.3929016489362</v>
       </c>
       <c r="F90" t="n">
-        <v>0.6692194938659668</v>
+        <v>0.6025776267051697</v>
       </c>
       <c r="G90" t="n">
-        <v>0.03070329999900423</v>
+        <v>0.1066102000040701</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0006574757280759513</v>
+        <v>0.0008405398693867028</v>
       </c>
       <c r="I90" t="n">
-        <v>981.7689466259225</v>
+        <v>913.0476062281323</v>
       </c>
       <c r="J90" t="n">
-        <v>188.4835529933779</v>
+        <v>187.3929069158127</v>
       </c>
       <c r="K90" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="L90" t="n">
-        <v>3.10112022816611e-06</v>
+        <v>0.7075397328029567</v>
       </c>
       <c r="M90" t="n">
-        <v>0.0001624017095025465</v>
+        <v>5.266876456744285e-06</v>
       </c>
       <c r="N90" t="n">
-        <v>3.373597858289351</v>
+        <v>3.97768143264125</v>
       </c>
       <c r="O90" t="b">
         <v>1</v>
       </c>
       <c r="P90" t="n">
-        <v>0.8354538083076477</v>
+        <v>0.9375208020210266</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.1854237999996258</v>
+        <v>0.4198659000030602</v>
       </c>
       <c r="R90" t="n">
-        <v>0.000136482049128972</v>
+        <v>0.0002133646485162899</v>
       </c>
       <c r="S90" t="n">
-        <v>983.4635094091665</v>
+        <v>919.0785081861868</v>
       </c>
       <c r="T90" t="n">
-        <v>188.6015786164005</v>
+        <v>187.9084769588527</v>
       </c>
       <c r="U90" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V90" t="n">
-        <v>1.694565884364238</v>
+        <v>6.738441690857485</v>
       </c>
       <c r="W90" t="n">
-        <v>0.1178632213130868</v>
+        <v>0.5155753099164997</v>
       </c>
       <c r="X90" t="n">
-        <v>3.373597858289351</v>
+        <v>3.97768143264125</v>
       </c>
       <c r="Y90" t="b">
         <v>1</v>
@@ -7584,70 +7584,70 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>962.7382604486442</v>
+        <v>933.1064295128662</v>
       </c>
       <c r="D91" t="n">
-        <v>11.37501727749736</v>
+        <v>9.554910832118011</v>
       </c>
       <c r="E91" t="n">
-        <v>121.3048178851563</v>
+        <v>142.9612581551121</v>
       </c>
       <c r="F91" t="n">
-        <v>0.8342413306236267</v>
+        <v>0.7431839108467102</v>
       </c>
       <c r="G91" t="n">
-        <v>0.2951578000011068</v>
+        <v>0.4775217000060366</v>
       </c>
       <c r="H91" t="n">
-        <v>0.01565238833427429</v>
+        <v>0.2544034421443939</v>
       </c>
       <c r="I91" t="n">
-        <v>939.7170960890315</v>
+        <v>888.6169680194448</v>
       </c>
       <c r="J91" t="n">
-        <v>163.0038989774016</v>
+        <v>165.1582069430503</v>
       </c>
       <c r="K91" t="n">
-        <v>12.31880557481792</v>
+        <v>12.26858369454161</v>
       </c>
       <c r="L91" t="n">
-        <v>23.02116435961261</v>
+        <v>44.48946149342135</v>
       </c>
       <c r="M91" t="n">
-        <v>41.69908109224531</v>
+        <v>22.19694878793817</v>
       </c>
       <c r="N91" t="n">
-        <v>0.9437882973205607</v>
+        <v>2.7136728624236</v>
       </c>
       <c r="O91" t="b">
         <v>1</v>
       </c>
       <c r="P91" t="n">
-        <v>0.9999992847442627</v>
+        <v>0.9996021389961243</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.5967092999999295</v>
+        <v>1.235980299999937</v>
       </c>
       <c r="R91" t="n">
-        <v>0.003925133962184191</v>
+        <v>0.0006997841992415488</v>
       </c>
       <c r="S91" t="n">
-        <v>800.0000309649686</v>
+        <v>839.8255874486603</v>
       </c>
       <c r="T91" t="n">
-        <v>150.0005528369569</v>
+        <v>150.0005513851656</v>
       </c>
       <c r="U91" t="n">
-        <v>10.61645059904456</v>
+        <v>9.440159193134548</v>
       </c>
       <c r="V91" t="n">
-        <v>162.7382294836756</v>
+        <v>93.2808420642059</v>
       </c>
       <c r="W91" t="n">
-        <v>28.6957349518006</v>
+        <v>7.03929323005346</v>
       </c>
       <c r="X91" t="n">
-        <v>0.7585666784528051</v>
+        <v>0.1147516389834635</v>
       </c>
       <c r="Y91" t="b">
         <v>1</v>
@@ -7659,74 +7659,74 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>876.5930409073219</v>
+        <v>918.1002206880542</v>
       </c>
       <c r="D92" t="n">
-        <v>7.501724386319491</v>
+        <v>9.942869950779015</v>
       </c>
       <c r="E92" t="n">
-        <v>210.6284858802542</v>
+        <v>151.2685438491009</v>
       </c>
       <c r="F92" t="n">
-        <v>0.8236976861953735</v>
+        <v>0.7367280721664429</v>
       </c>
       <c r="G92" t="n">
-        <v>0.1186863999992056</v>
+        <v>0.4316671999986283</v>
       </c>
       <c r="H92" t="n">
-        <v>0.001478823600336909</v>
+        <v>0.001086266012862325</v>
       </c>
       <c r="I92" t="n">
-        <v>923.1727125466235</v>
+        <v>917.281074132129</v>
       </c>
       <c r="J92" t="n">
-        <v>210.6284858802542</v>
+        <v>173.3838101001208</v>
       </c>
       <c r="K92" t="n">
-        <v>9.000641745576274</v>
+        <v>9.943692127073531</v>
       </c>
       <c r="L92" t="n">
-        <v>46.57967163930164</v>
+        <v>0.8191465559251583</v>
       </c>
       <c r="M92" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>22.11526625101993</v>
       </c>
       <c r="N92" t="n">
-        <v>1.498917359256783</v>
+        <v>0.000822176294516197</v>
       </c>
       <c r="O92" t="b">
         <v>1</v>
       </c>
       <c r="P92" t="n">
-        <v>0.9502381086349487</v>
+        <v>0.9821063280105591</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.4128682999999</v>
+        <v>2.114820899994811</v>
       </c>
       <c r="R92" t="n">
-        <v>0.0005291284760460258</v>
+        <v>0.0005982475122436881</v>
       </c>
       <c r="S92" t="n">
-        <v>934.504851282891</v>
+        <v>840.5957458612838</v>
       </c>
       <c r="T92" t="n">
-        <v>210.8040990174519</v>
+        <v>154.4422509884995</v>
       </c>
       <c r="U92" t="n">
-        <v>9.000641736337943</v>
+        <v>9.854159987425994</v>
       </c>
       <c r="V92" t="n">
-        <v>57.91181037556908</v>
+        <v>77.50447482677032</v>
       </c>
       <c r="W92" t="n">
-        <v>0.1756131371977006</v>
+        <v>3.173707139398601</v>
       </c>
       <c r="X92" t="n">
-        <v>1.498917350018452</v>
+        <v>0.08870996335302017</v>
       </c>
       <c r="Y92" t="b">
         <v>1</v>
@@ -7738,74 +7738,74 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>927.4869006439883</v>
+        <v>866.6374836681871</v>
       </c>
       <c r="D93" t="n">
-        <v>5.690886471949463</v>
+        <v>9.048755549115382</v>
       </c>
       <c r="E93" t="n">
-        <v>197.0422059273024</v>
+        <v>191.4794582777003</v>
       </c>
       <c r="F93" t="n">
-        <v>0.7905915975570679</v>
+        <v>0.6970879435539246</v>
       </c>
       <c r="G93" t="n">
-        <v>0.03258359999927052</v>
+        <v>0.243559099995764</v>
       </c>
       <c r="H93" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I93" t="n">
-        <v>927.4869006439819</v>
+        <v>922.2058315696462</v>
       </c>
       <c r="J93" t="n">
-        <v>197.0422059273024</v>
+        <v>191.4794582777003</v>
       </c>
       <c r="K93" t="n">
-        <v>9.000641779862162</v>
+        <v>9.048755549115377</v>
       </c>
       <c r="L93" t="n">
-        <v>6.366462912410498e-12</v>
+        <v>55.56834790145911</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>3.309755307912699</v>
+        <v>5.329070518200751e-15</v>
       </c>
       <c r="O93" t="b">
         <v>1</v>
       </c>
       <c r="P93" t="n">
-        <v>0.6931074857711792</v>
+        <v>0.8159929513931274</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.1693536000002496</v>
+        <v>0.9750493000028655</v>
       </c>
       <c r="R93" t="n">
-        <v>0.0001658303226577118</v>
+        <v>0.0003841823781840503</v>
       </c>
       <c r="S93" t="n">
-        <v>928.4618835007274</v>
+        <v>927.058003867287</v>
       </c>
       <c r="T93" t="n">
-        <v>197.2279539590416</v>
+        <v>192.4911374463842</v>
       </c>
       <c r="U93" t="n">
-        <v>9.000641779862162</v>
+        <v>9.104462944294269</v>
       </c>
       <c r="V93" t="n">
-        <v>0.974982856739075</v>
+        <v>60.42052019909988</v>
       </c>
       <c r="W93" t="n">
-        <v>0.1857480317391378</v>
+        <v>1.011679168683855</v>
       </c>
       <c r="X93" t="n">
-        <v>3.309755307912699</v>
+        <v>0.0557073951788869</v>
       </c>
       <c r="Y93" t="b">
         <v>1</v>
@@ -7817,74 +7817,74 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>997.9875441341283</v>
+        <v>888.8746840878158</v>
       </c>
       <c r="D94" t="n">
-        <v>11.16705915943403</v>
+        <v>6.785040231385346</v>
       </c>
       <c r="E94" t="n">
-        <v>106.0591878524666</v>
+        <v>203.9010598594718</v>
       </c>
       <c r="F94" t="n">
-        <v>0.8300918936729431</v>
+        <v>0.8041200637817383</v>
       </c>
       <c r="G94" t="n">
-        <v>0.2997752999999648</v>
+        <v>0.2417024999958812</v>
       </c>
       <c r="H94" t="n">
-        <v>0.01565238833427429</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I94" t="n">
-        <v>939.7170952372755</v>
+        <v>922.205828536554</v>
       </c>
       <c r="J94" t="n">
-        <v>163.0038982941061</v>
+        <v>203.9010598594718</v>
       </c>
       <c r="K94" t="n">
-        <v>12.31880748258491</v>
+        <v>9.000641516308777</v>
       </c>
       <c r="L94" t="n">
-        <v>58.27044889685271</v>
+        <v>33.3311444487382</v>
       </c>
       <c r="M94" t="n">
-        <v>56.94471044163944</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>1.151748323150883</v>
+        <v>2.215601284923431</v>
       </c>
       <c r="O94" t="b">
         <v>1</v>
       </c>
       <c r="P94" t="n">
-        <v>1</v>
+        <v>0.9355366230010986</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.5442158000005293</v>
+        <v>1.626289699997869</v>
       </c>
       <c r="R94" t="n">
-        <v>0.003423250513151288</v>
+        <v>0.0002682387712411582</v>
       </c>
       <c r="S94" t="n">
-        <v>800.0000410764735</v>
+        <v>930.0859546327538</v>
       </c>
       <c r="T94" t="n">
-        <v>150.0005528601709</v>
+        <v>203.3573762956004</v>
       </c>
       <c r="U94" t="n">
-        <v>10.52448764956129</v>
+        <v>9.000641786033791</v>
       </c>
       <c r="V94" t="n">
-        <v>197.9875030576547</v>
+        <v>41.21127054493797</v>
       </c>
       <c r="W94" t="n">
-        <v>43.94136500770426</v>
+        <v>0.5436835638714399</v>
       </c>
       <c r="X94" t="n">
-        <v>0.6425715098727327</v>
+        <v>2.215601554648445</v>
       </c>
       <c r="Y94" t="b">
         <v>1</v>
@@ -7896,74 +7896,74 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>K_Scratch</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>947.578491352189</v>
+        <v>917.0224402344937</v>
       </c>
       <c r="D95" t="n">
-        <v>5.654812820737789</v>
+        <v>10.66791308942049</v>
       </c>
       <c r="E95" t="n">
-        <v>200.2528700668194</v>
+        <v>135.5846194631318</v>
       </c>
       <c r="F95" t="n">
-        <v>0.8132951259613037</v>
+        <v>0.7230772376060486</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0366212999997515</v>
+        <v>0.4971211999945808</v>
       </c>
       <c r="H95" t="n">
-        <v>0.000657533819321543</v>
+        <v>0.01950404606759548</v>
       </c>
       <c r="I95" t="n">
-        <v>947.5784913521876</v>
+        <v>892.2584318049006</v>
       </c>
       <c r="J95" t="n">
-        <v>200.2528700668194</v>
+        <v>165.158635040148</v>
       </c>
       <c r="K95" t="n">
-        <v>9.000641779862162</v>
+        <v>10.66790246600142</v>
       </c>
       <c r="L95" t="n">
-        <v>1.364242052659392e-12</v>
+        <v>24.7640084295931</v>
       </c>
       <c r="M95" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>29.57401557701618</v>
       </c>
       <c r="N95" t="n">
-        <v>3.345828959124374</v>
+        <v>1.062341906710174e-05</v>
       </c>
       <c r="O95" t="b">
         <v>1</v>
       </c>
       <c r="P95" t="n">
-        <v>0.8203698992729187</v>
+        <v>0.9999618530273438</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.1727991000007023</v>
+        <v>1.222156999996514</v>
       </c>
       <c r="R95" t="n">
-        <v>0.0001321505842497572</v>
+        <v>0.0006905795307829976</v>
       </c>
       <c r="S95" t="n">
-        <v>948.3934127082003</v>
+        <v>828.5053794873593</v>
       </c>
       <c r="T95" t="n">
-        <v>200.3686448796067</v>
+        <v>150.0005523101303</v>
       </c>
       <c r="U95" t="n">
-        <v>9.000641779862162</v>
+        <v>10.58156846354765</v>
       </c>
       <c r="V95" t="n">
-        <v>0.8149213560113822</v>
+        <v>88.51706074713445</v>
       </c>
       <c r="W95" t="n">
-        <v>0.1157748127873219</v>
+        <v>14.41593284699852</v>
       </c>
       <c r="X95" t="n">
-        <v>3.345828959124374</v>
+        <v>0.08634462587284197</v>
       </c>
       <c r="Y95" t="b">
         <v>1</v>
@@ -7979,70 +7979,70 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>853.9855462443677</v>
+        <v>882.5854480486973</v>
       </c>
       <c r="D96" t="n">
-        <v>7.987659714746035</v>
+        <v>8.348573319451948</v>
       </c>
       <c r="E96" t="n">
-        <v>197.5842788078801</v>
+        <v>196.3073874372661</v>
       </c>
       <c r="F96" t="n">
-        <v>0.8169287443161011</v>
+        <v>0.7805430889129639</v>
       </c>
       <c r="G96" t="n">
-        <v>0.1164031000007526</v>
+        <v>0.23951169999782</v>
       </c>
       <c r="H96" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I96" t="n">
-        <v>924.4806694830611</v>
+        <v>922.2058281277565</v>
       </c>
       <c r="J96" t="n">
-        <v>197.5842788078801</v>
+        <v>196.3072777926082</v>
       </c>
       <c r="K96" t="n">
-        <v>9.0006414939416</v>
+        <v>9.000641621937302</v>
       </c>
       <c r="L96" t="n">
-        <v>70.4951232386934</v>
+        <v>39.62038007905915</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>0.000109644657896979</v>
       </c>
       <c r="N96" t="n">
-        <v>1.012981779195566</v>
+        <v>0.652068302485354</v>
       </c>
       <c r="O96" t="b">
         <v>1</v>
       </c>
       <c r="P96" t="n">
-        <v>0.9471377730369568</v>
+        <v>0.8481296896934509</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.4517273000001296</v>
+        <v>1.176249100004497</v>
       </c>
       <c r="R96" t="n">
-        <v>0.0007548374123871326</v>
+        <v>0.0002812418097164482</v>
       </c>
       <c r="S96" t="n">
-        <v>932.930602752039</v>
+        <v>929.1477061965609</v>
       </c>
       <c r="T96" t="n">
-        <v>198.273461216431</v>
+        <v>196.4602181286574</v>
       </c>
       <c r="U96" t="n">
-        <v>9.000641648912826</v>
+        <v>9.000641846036745</v>
       </c>
       <c r="V96" t="n">
-        <v>78.94505650767132</v>
+        <v>46.56225814786353</v>
       </c>
       <c r="W96" t="n">
-        <v>0.6891824085509484</v>
+        <v>0.1528306913912729</v>
       </c>
       <c r="X96" t="n">
-        <v>1.012981934166791</v>
+        <v>0.652068526584797</v>
       </c>
       <c r="Y96" t="b">
         <v>1</v>
@@ -8058,70 +8058,70 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>947.4469580674147</v>
+        <v>955.4719570090319</v>
       </c>
       <c r="D97" t="n">
-        <v>10.57432112273982</v>
+        <v>10.02842232849754</v>
       </c>
       <c r="E97" t="n">
-        <v>136.2270958374783</v>
+        <v>127.6714609512611</v>
       </c>
       <c r="F97" t="n">
-        <v>0.8342413306236267</v>
+        <v>0.7431839108467102</v>
       </c>
       <c r="G97" t="n">
-        <v>0.1354125999987446</v>
+        <v>0.305734499997925</v>
       </c>
       <c r="H97" t="n">
-        <v>0.02069370076060295</v>
+        <v>0.02071113511919975</v>
       </c>
       <c r="I97" t="n">
-        <v>929.472093863953</v>
+        <v>857.9460852572724</v>
       </c>
       <c r="J97" t="n">
-        <v>167.2837065127374</v>
+        <v>173.3835541483931</v>
       </c>
       <c r="K97" t="n">
-        <v>12.25531054993708</v>
+        <v>11.52556910352204</v>
       </c>
       <c r="L97" t="n">
-        <v>17.97486420346172</v>
+        <v>97.5258717517595</v>
       </c>
       <c r="M97" t="n">
-        <v>31.05661067525915</v>
+        <v>45.71209319713196</v>
       </c>
       <c r="N97" t="n">
-        <v>1.680989427197259</v>
+        <v>1.4971467750245</v>
       </c>
       <c r="O97" t="b">
         <v>1</v>
       </c>
       <c r="P97" t="n">
-        <v>0.9998952150344849</v>
+        <v>0.9999996423721313</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.6606907999994291</v>
+        <v>1.188494699999865</v>
       </c>
       <c r="R97" t="n">
-        <v>0.002132153138518333</v>
+        <v>0.0008521150448359549</v>
       </c>
       <c r="S97" t="n">
-        <v>800.0002613231311</v>
+        <v>835.9987652350135</v>
       </c>
       <c r="T97" t="n">
-        <v>150.0005528276915</v>
+        <v>150.0005516122743</v>
       </c>
       <c r="U97" t="n">
-        <v>10.21003052987741</v>
+        <v>9.892447954494457</v>
       </c>
       <c r="V97" t="n">
-        <v>147.4466967442836</v>
+        <v>119.4731917740185</v>
       </c>
       <c r="W97" t="n">
-        <v>13.77345699021319</v>
+        <v>22.32909066101323</v>
       </c>
       <c r="X97" t="n">
-        <v>0.3642905928624138</v>
+        <v>0.1359743740030819</v>
       </c>
       <c r="Y97" t="b">
         <v>1</v>
@@ -8133,74 +8133,74 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>963.056306834058</v>
+        <v>845.2523265905591</v>
       </c>
       <c r="D98" t="n">
-        <v>11.03750141426828</v>
+        <v>7.942229626313777</v>
       </c>
       <c r="E98" t="n">
-        <v>141.0446898309199</v>
+        <v>185.3201572991623</v>
       </c>
       <c r="F98" t="n">
-        <v>0.8342413306236267</v>
+        <v>0.8515315055847168</v>
       </c>
       <c r="G98" t="n">
-        <v>0.2435194000008778</v>
+        <v>0.2564698999995016</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0008712398703210056</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I98" t="n">
-        <v>963.0563078508883</v>
+        <v>922.2058290727135</v>
       </c>
       <c r="J98" t="n">
-        <v>173.1913500386705</v>
+        <v>185.3201572991622</v>
       </c>
       <c r="K98" t="n">
-        <v>11.03750138812716</v>
+        <v>9.000641698506609</v>
       </c>
       <c r="L98" t="n">
-        <v>1.016830310618388e-06</v>
+        <v>76.95350248215448</v>
       </c>
       <c r="M98" t="n">
-        <v>32.14666020775059</v>
+        <v>1.70530256582424e-13</v>
       </c>
       <c r="N98" t="n">
-        <v>2.614111949128528e-08</v>
+        <v>1.058412072192832</v>
       </c>
       <c r="O98" t="b">
         <v>1</v>
       </c>
       <c r="P98" t="n">
-        <v>0.9990684390068054</v>
+        <v>0.9820444583892822</v>
       </c>
       <c r="Q98" t="n">
-        <v>1.079687499999636</v>
+        <v>1.211572100000922</v>
       </c>
       <c r="R98" t="n">
-        <v>0.002004957292228937</v>
+        <v>0.0005680100293830037</v>
       </c>
       <c r="S98" t="n">
-        <v>800.0002832195379</v>
+        <v>928.0741389920637</v>
       </c>
       <c r="T98" t="n">
-        <v>152.6355579613555</v>
+        <v>186.9164879509091</v>
       </c>
       <c r="U98" t="n">
-        <v>10.67905302638131</v>
+        <v>9.000641326646431</v>
       </c>
       <c r="V98" t="n">
-        <v>163.0560236145201</v>
+        <v>82.82181240150464</v>
       </c>
       <c r="W98" t="n">
-        <v>11.59086813043558</v>
+        <v>1.596330651746769</v>
       </c>
       <c r="X98" t="n">
-        <v>0.3584483878869733</v>
+        <v>1.058411700332654</v>
       </c>
       <c r="Y98" t="b">
         <v>1</v>
@@ -8212,74 +8212,74 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Bumps</t>
+          <t>Other_Faults</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>936.611796449889</v>
+        <v>892.1221014058799</v>
       </c>
       <c r="D99" t="n">
-        <v>11.28067789888034</v>
+        <v>8.287189905343608</v>
       </c>
       <c r="E99" t="n">
-        <v>109.4019196015007</v>
+        <v>190.8519852575191</v>
       </c>
       <c r="F99" t="n">
-        <v>0.8342413306236267</v>
+        <v>0.7828472852706909</v>
       </c>
       <c r="G99" t="n">
-        <v>0.2654767999993055</v>
+        <v>0.2668154999992112</v>
       </c>
       <c r="H99" t="n">
-        <v>0.01562827080488205</v>
+        <v>0.00160721002612263</v>
       </c>
       <c r="I99" t="n">
-        <v>932.6390745258095</v>
+        <v>922.2058271391193</v>
       </c>
       <c r="J99" t="n">
-        <v>163.00389845341</v>
+        <v>190.8519852575191</v>
       </c>
       <c r="K99" t="n">
-        <v>12.31844659227882</v>
+        <v>9.000641628336743</v>
       </c>
       <c r="L99" t="n">
-        <v>3.972721924079451</v>
+        <v>30.08372573323936</v>
       </c>
       <c r="M99" t="n">
-        <v>53.60197885190929</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>1.037768693398473</v>
+        <v>0.7134517229931348</v>
       </c>
       <c r="O99" t="b">
         <v>1</v>
       </c>
       <c r="P99" t="n">
-        <v>1</v>
+        <v>0.6039832830429077</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.5423943999994663</v>
+        <v>1.171101200001431</v>
       </c>
       <c r="R99" t="n">
-        <v>0.003696478437632322</v>
+        <v>0.0002322361251572147</v>
       </c>
       <c r="S99" t="n">
-        <v>800.0000280230023</v>
+        <v>930.7118235940761</v>
       </c>
       <c r="T99" t="n">
-        <v>150.0005528483752</v>
+        <v>191.4665743905766</v>
       </c>
       <c r="U99" t="n">
-        <v>10.57603918760459</v>
+        <v>9.000641728498216</v>
       </c>
       <c r="V99" t="n">
-        <v>136.6117684268867</v>
+        <v>38.58972218819622</v>
       </c>
       <c r="W99" t="n">
-        <v>40.59863324687451</v>
+        <v>0.6145891330574784</v>
       </c>
       <c r="X99" t="n">
-        <v>0.7046387112757539</v>
+        <v>0.7134518231546085</v>
       </c>
       <c r="Y99" t="b">
         <v>1</v>
@@ -8291,74 +8291,74 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Other_Faults</t>
+          <t>Bumps</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>870.8980293109241</v>
+        <v>956.494142587789</v>
       </c>
       <c r="D100" t="n">
-        <v>7.87401015685547</v>
+        <v>9.900900899575108</v>
       </c>
       <c r="E100" t="n">
-        <v>201.0372975914116</v>
+        <v>128.7849147927062</v>
       </c>
       <c r="F100" t="n">
-        <v>0.827983558177948</v>
+        <v>0.7431839108467102</v>
       </c>
       <c r="G100" t="n">
-        <v>0.1249941999994917</v>
+        <v>0.5291274999981397</v>
       </c>
       <c r="H100" t="n">
-        <v>0.001030373154208064</v>
+        <v>0.2209932953119278</v>
       </c>
       <c r="I100" t="n">
-        <v>924.4806707539068</v>
+        <v>892.258337302456</v>
       </c>
       <c r="J100" t="n">
-        <v>201.0372975914116</v>
+        <v>156.1173403660189</v>
       </c>
       <c r="K100" t="n">
-        <v>9.000641624012538</v>
+        <v>13.73072678714508</v>
       </c>
       <c r="L100" t="n">
-        <v>53.58264144298266</v>
+        <v>64.23580528533307</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>27.33242557331263</v>
       </c>
       <c r="N100" t="n">
-        <v>1.126631467157067</v>
+        <v>3.829825887569969</v>
       </c>
       <c r="O100" t="b">
         <v>1</v>
       </c>
       <c r="P100" t="n">
-        <v>0.9480962753295898</v>
+        <v>0.9999992847442627</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.39643100000103</v>
+        <v>1.181638699999894</v>
       </c>
       <c r="R100" t="n">
-        <v>0.0005860305391252041</v>
+        <v>0.0008464037673547864</v>
       </c>
       <c r="S100" t="n">
-        <v>934.2920009514331</v>
+        <v>837.34005279289</v>
       </c>
       <c r="T100" t="n">
-        <v>201.2114210869627</v>
+        <v>150.0005515823589</v>
       </c>
       <c r="U100" t="n">
-        <v>9.000641814034209</v>
+        <v>9.764982911729982</v>
       </c>
       <c r="V100" t="n">
-        <v>63.39397164050899</v>
+        <v>119.1540897948991</v>
       </c>
       <c r="W100" t="n">
-        <v>0.1741234955511004</v>
+        <v>21.21563678965271</v>
       </c>
       <c r="X100" t="n">
-        <v>1.126631657178739</v>
+        <v>0.1359179878451258</v>
       </c>
       <c r="Y100" t="b">
         <v>1</v>
@@ -8374,70 +8374,70 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>970.7561388305421</v>
+        <v>990.0677017479472</v>
       </c>
       <c r="D101" t="n">
-        <v>10.37399377702127</v>
+        <v>9.871682505805071</v>
       </c>
       <c r="E101" t="n">
-        <v>139.4368561057225</v>
+        <v>106.6717533813656</v>
       </c>
       <c r="F101" t="n">
-        <v>0.8341188430786133</v>
+        <v>0.7401382923126221</v>
       </c>
       <c r="G101" t="n">
-        <v>0.1997789000015473</v>
+        <v>0.396209499995166</v>
       </c>
       <c r="H101" t="n">
-        <v>0.01935457438230515</v>
+        <v>0.01405216194689274</v>
       </c>
       <c r="I101" t="n">
-        <v>939.7124554799866</v>
+        <v>950.6938303740087</v>
       </c>
       <c r="J101" t="n">
-        <v>163.5756111462861</v>
+        <v>165.1587973834407</v>
       </c>
       <c r="K101" t="n">
-        <v>11.83268195040376</v>
+        <v>9.893687263355231</v>
       </c>
       <c r="L101" t="n">
-        <v>31.04368335055551</v>
+        <v>39.37387137393853</v>
       </c>
       <c r="M101" t="n">
-        <v>24.13875504056361</v>
+        <v>58.48704400207518</v>
       </c>
       <c r="N101" t="n">
-        <v>1.458688173382491</v>
+        <v>0.02200475755016029</v>
       </c>
       <c r="O101" t="b">
         <v>1</v>
       </c>
       <c r="P101" t="n">
-        <v>0.9995613694190979</v>
+        <v>1</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.5014737000001332</v>
+        <v>1.221128799996222</v>
       </c>
       <c r="R101" t="n">
-        <v>0.00184032297693193</v>
+        <v>0.001001108787022531</v>
       </c>
       <c r="S101" t="n">
-        <v>800.5723188615206</v>
+        <v>839.0228430384873</v>
       </c>
       <c r="T101" t="n">
-        <v>150.0005521281755</v>
+        <v>150.0005515234239</v>
       </c>
       <c r="U101" t="n">
-        <v>10.07653342538259</v>
+        <v>9.71167652079051</v>
       </c>
       <c r="V101" t="n">
-        <v>170.1838199690216</v>
+        <v>151.04485870946</v>
       </c>
       <c r="W101" t="n">
-        <v>10.56369602245303</v>
+        <v>43.32879814205833</v>
       </c>
       <c r="X101" t="n">
-        <v>0.2974603516386836</v>
+        <v>0.1600059850145605</v>
       </c>
       <c r="Y101" t="b">
         <v>1</v>

--- a/export_dati/06_Step6_Simulazione_Massiva_100.xlsx
+++ b/export_dati/06_Step6_Simulazione_Massiva_100.xlsx
@@ -565,7 +565,7 @@
         <v>0.8036846518516541</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3044505999932881</v>
+        <v>0.1404709999915212</v>
       </c>
       <c r="H2" t="n">
         <v>0.00160721002612263</v>
@@ -592,31 +592,31 @@
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9577955603599548</v>
+        <v>0.9563551545143127</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.437959099996078</v>
+        <v>0.5805505999596789</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0003539097378961742</v>
+        <v>0.0004639677936211228</v>
       </c>
       <c r="S2" t="n">
-        <v>932.3014585363629</v>
+        <v>932.4076964787682</v>
       </c>
       <c r="T2" t="n">
-        <v>215.174222047529</v>
+        <v>214.7894747167909</v>
       </c>
       <c r="U2" t="n">
-        <v>9.000641774231712</v>
+        <v>9.000640201858566</v>
       </c>
       <c r="V2" t="n">
-        <v>46.2551937329132</v>
+        <v>46.3614316753185</v>
       </c>
       <c r="W2" t="n">
-        <v>1.869604468512392</v>
+        <v>2.254351799250429</v>
       </c>
       <c r="X2" t="n">
-        <v>1.688073861627906</v>
+        <v>1.688072289254761</v>
       </c>
       <c r="Y2" t="b">
         <v>1</v>
@@ -644,7 +644,7 @@
         <v>0.5276130437850952</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2740455000021029</v>
+        <v>0.1128971999860369</v>
       </c>
       <c r="H3" t="n">
         <v>0.0008494904031977057</v>
@@ -671,28 +671,28 @@
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3084385693073273</v>
+        <v>0.4894337058067322</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5243454000010388</v>
+        <v>0.2551483999704942</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0002449585299473256</v>
+        <v>0.0001733063108986244</v>
       </c>
       <c r="S3" t="n">
-        <v>908.8647429048053</v>
+        <v>896.9371645137774</v>
       </c>
       <c r="T3" t="n">
-        <v>196.7616894136254</v>
+        <v>196.8169647425804</v>
       </c>
       <c r="U3" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V3" t="n">
-        <v>7.384448718504814</v>
+        <v>4.54312967252315</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01799496697708491</v>
+        <v>0.03728036197784945</v>
       </c>
       <c r="X3" t="n">
         <v>2.626634112026608</v>
@@ -723,7 +723,7 @@
         <v>0.6916452050209045</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06195659999502823</v>
+        <v>0.02723760000662878</v>
       </c>
       <c r="H4" t="n">
         <v>0.0008420366793870926</v>
@@ -750,28 +750,28 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4316332936286926</v>
+        <v>0.3820589482784271</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6007677000015974</v>
+        <v>0.2057245000032708</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0001229960907949135</v>
+        <v>0.0001040293936966918</v>
       </c>
       <c r="S4" t="n">
-        <v>964.075134523684</v>
+        <v>965.8201462119036</v>
       </c>
       <c r="T4" t="n">
-        <v>184.5057664063757</v>
+        <v>183.8207472838451</v>
       </c>
       <c r="U4" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2823706768318743</v>
+        <v>1.462641011387745</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8214751464437029</v>
+        <v>0.1364560239130981</v>
       </c>
       <c r="X4" t="n">
         <v>2.384356345782363</v>
@@ -802,7 +802,7 @@
         <v>0.752820611000061</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4440901000052691</v>
+        <v>0.2012873000348918</v>
       </c>
       <c r="H5" t="n">
         <v>0.01405216194689274</v>
@@ -832,28 +832,28 @@
         <v>0.9999998807907104</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.674420800001826</v>
+        <v>0.4965764000080526</v>
       </c>
       <c r="R5" t="n">
-        <v>0.000846900453325361</v>
+        <v>0.0005800288636237383</v>
       </c>
       <c r="S5" t="n">
-        <v>846.4083647864366</v>
+        <v>839.4288795320416</v>
       </c>
       <c r="T5" t="n">
-        <v>150.0005527206193</v>
+        <v>150.0005526656765</v>
       </c>
       <c r="U5" t="n">
-        <v>9.000641917387313</v>
+        <v>9.000641853577985</v>
       </c>
       <c r="V5" t="n">
-        <v>112.9715274423432</v>
+        <v>119.9510126967382</v>
       </c>
       <c r="W5" t="n">
-        <v>29.86930219118022</v>
+        <v>29.86930213623742</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5822844729399179</v>
+        <v>0.5822844091305903</v>
       </c>
       <c r="Y5" t="b">
         <v>1</v>
@@ -881,7 +881,7 @@
         <v>0.8063374757766724</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2451428999993368</v>
+        <v>0.09734900004696101</v>
       </c>
       <c r="H6" t="n">
         <v>0.00160721002612263</v>
@@ -908,31 +908,31 @@
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8857000470161438</v>
+        <v>0.8532194495201111</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.258999499994388</v>
+        <v>0.6575662000104785</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0003069405793212354</v>
+        <v>0.000423809775384143</v>
       </c>
       <c r="S6" t="n">
-        <v>931.8350500170983</v>
+        <v>930.7696463106088</v>
       </c>
       <c r="T6" t="n">
-        <v>211.4120515081246</v>
+        <v>211.9257766496321</v>
       </c>
       <c r="U6" t="n">
-        <v>9.000641707566652</v>
+        <v>9.000641798844926</v>
       </c>
       <c r="V6" t="n">
-        <v>45.40460183958692</v>
+        <v>44.3391981330974</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8464851454469624</v>
+        <v>0.3327600039394838</v>
       </c>
       <c r="X6" t="n">
-        <v>0.963356561215404</v>
+        <v>0.9633566524936779</v>
       </c>
       <c r="Y6" t="b">
         <v>1</v>
@@ -960,7 +960,7 @@
         <v>0.8492916226387024</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2754987000007532</v>
+        <v>0.1154087000177242</v>
       </c>
       <c r="H7" t="n">
         <v>0.00160721002612263</v>
@@ -987,31 +987,31 @@
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9969677329063416</v>
+        <v>0.9980788230895996</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.345960799997556</v>
+        <v>0.5828228000318632</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0006575367297045887</v>
+        <v>0.0007912979344837368</v>
       </c>
       <c r="S7" t="n">
-        <v>924.9419803076114</v>
+        <v>927.1622941698568</v>
       </c>
       <c r="T7" t="n">
-        <v>197.0898382314952</v>
+        <v>196.6785622987539</v>
       </c>
       <c r="U7" t="n">
-        <v>9.000641789604858</v>
+        <v>9.000641784506007</v>
       </c>
       <c r="V7" t="n">
-        <v>89.42587774355854</v>
+        <v>91.64619160580389</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4001558057956913</v>
+        <v>0.01112012694562736</v>
       </c>
       <c r="X7" t="n">
-        <v>1.957026842841075</v>
+        <v>1.957026837742224</v>
       </c>
       <c r="Y7" t="b">
         <v>1</v>
@@ -1039,7 +1039,7 @@
         <v>0.7553641796112061</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6406617000029655</v>
+        <v>0.2501609000028111</v>
       </c>
       <c r="H8" t="n">
         <v>0.001092163613066077</v>
@@ -1066,31 +1066,31 @@
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1949854791164398</v>
+        <v>0.3148050308227539</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.816701000003377</v>
+        <v>0.8436365999514237</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0004794154083356261</v>
+        <v>0.0003144613874610513</v>
       </c>
       <c r="S8" t="n">
-        <v>864.9493507998546</v>
+        <v>866.4623731200975</v>
       </c>
       <c r="T8" t="n">
-        <v>166.3996631716699</v>
+        <v>167.1795952388061</v>
       </c>
       <c r="U8" t="n">
-        <v>9.000639485801056</v>
+        <v>9.000641788984801</v>
       </c>
       <c r="V8" t="n">
-        <v>59.12791400098217</v>
+        <v>57.61489168073933</v>
       </c>
       <c r="W8" t="n">
-        <v>2.468873788047972</v>
+        <v>3.248805855184116</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3891574337843338</v>
+        <v>0.3891597369680788</v>
       </c>
       <c r="Y8" t="b">
         <v>1</v>
@@ -1118,7 +1118,7 @@
         <v>0.7394377589225769</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3882597000047099</v>
+        <v>0.1481004999950528</v>
       </c>
       <c r="H9" t="n">
         <v>0.001092163613066077</v>
@@ -1145,31 +1145,31 @@
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>0.998335063457489</v>
+        <v>0.9975793957710266</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.13017409999884</v>
+        <v>0.6337984999991022</v>
       </c>
       <c r="R9" t="n">
-        <v>0.000895558565389365</v>
+        <v>0.0006291447789408267</v>
       </c>
       <c r="S9" t="n">
-        <v>836.305643766047</v>
+        <v>839.6209912452707</v>
       </c>
       <c r="T9" t="n">
-        <v>152.7009777792938</v>
+        <v>153.1772580498455</v>
       </c>
       <c r="U9" t="n">
-        <v>10.32898335331059</v>
+        <v>10.42062910438047</v>
       </c>
       <c r="V9" t="n">
-        <v>127.7458653273167</v>
+        <v>124.4305178480929</v>
       </c>
       <c r="W9" t="n">
-        <v>4.617767165484139</v>
+        <v>5.094047436035851</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1212625980917856</v>
+        <v>0.02961684702190404</v>
       </c>
       <c r="Y9" t="b">
         <v>1</v>
@@ -1197,7 +1197,7 @@
         <v>0.8152469396591187</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2232014000037452</v>
+        <v>0.09170670004095882</v>
       </c>
       <c r="H10" t="n">
         <v>0.002021597931161523</v>
@@ -1224,31 +1224,31 @@
         <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9024824500083923</v>
+        <v>0.9133782982826233</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.328955899996799</v>
+        <v>0.4404870999860577</v>
       </c>
       <c r="R10" t="n">
-        <v>0.000640415062662214</v>
+        <v>0.0006568343960680068</v>
       </c>
       <c r="S10" t="n">
-        <v>926.3685641401298</v>
+        <v>927.9116894572181</v>
       </c>
       <c r="T10" t="n">
-        <v>206.624483893216</v>
+        <v>207.1907605647461</v>
       </c>
       <c r="U10" t="n">
-        <v>9.000641685490871</v>
+        <v>9.000641832451</v>
       </c>
       <c r="V10" t="n">
-        <v>87.27216434449144</v>
+        <v>88.81528966157975</v>
       </c>
       <c r="W10" t="n">
-        <v>1.162910321437948</v>
+        <v>0.5966336499078295</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2550039564661351</v>
+        <v>0.2550041034262645</v>
       </c>
       <c r="Y10" t="b">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>0.7312969565391541</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3294923000066774</v>
+        <v>0.1103067999938503</v>
       </c>
       <c r="H11" t="n">
         <v>0.00160721002612263</v>
@@ -1303,31 +1303,31 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4762341380119324</v>
+        <v>0.4486678838729858</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.322598399994604</v>
+        <v>0.5267644000123255</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0002403802936896682</v>
+        <v>0.0003348806931171566</v>
       </c>
       <c r="S11" t="n">
-        <v>932.0457000915492</v>
+        <v>933.383814049633</v>
       </c>
       <c r="T11" t="n">
-        <v>187.2500503227766</v>
+        <v>186.6340612098391</v>
       </c>
       <c r="U11" t="n">
-        <v>9.000641568320809</v>
+        <v>9.000641673881157</v>
       </c>
       <c r="V11" t="n">
-        <v>40.50869760903424</v>
+        <v>41.84681156711804</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7569229095803962</v>
+        <v>0.1409337966429405</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4204156045992757</v>
+        <v>0.4204157101596238</v>
       </c>
       <c r="Y11" t="b">
         <v>1</v>
@@ -1355,7 +1355,7 @@
         <v>0.7431839108467102</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3517162999996799</v>
+        <v>0.1643245999584906</v>
       </c>
       <c r="H12" t="n">
         <v>0.001092163613066077</v>
@@ -1382,31 +1382,31 @@
         <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5247876048088074</v>
+        <v>0.6073025465011597</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.976943699999538</v>
+        <v>0.7779117000172846</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0006861446890980005</v>
+        <v>0.0004632817581295967</v>
       </c>
       <c r="S12" t="n">
-        <v>861.8910928896213</v>
+        <v>866.2189184323736</v>
       </c>
       <c r="T12" t="n">
-        <v>166.9344270417922</v>
+        <v>167.7859724468038</v>
       </c>
       <c r="U12" t="n">
-        <v>9.606198203416927</v>
+        <v>9.654860115208166</v>
       </c>
       <c r="V12" t="n">
-        <v>89.96272111760607</v>
+        <v>85.63489557485377</v>
       </c>
       <c r="W12" t="n">
-        <v>3.83682147091875</v>
+        <v>4.688366875930427</v>
       </c>
       <c r="X12" t="n">
-        <v>0.08689435896213737</v>
+        <v>0.03823244717089835</v>
       </c>
       <c r="Y12" t="b">
         <v>1</v>
@@ -1434,7 +1434,7 @@
         <v>0.7440423965454102</v>
       </c>
       <c r="G13" t="n">
-        <v>0.365613800000574</v>
+        <v>0.1596298000076786</v>
       </c>
       <c r="H13" t="n">
         <v>0.02071010880172253</v>
@@ -1461,31 +1461,31 @@
         <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9999998807907104</v>
+        <v>0.9999991655349731</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.253005099999427</v>
+        <v>0.4419611999765038</v>
       </c>
       <c r="R13" t="n">
-        <v>0.001006041071377695</v>
+        <v>0.0007437951862812042</v>
       </c>
       <c r="S13" t="n">
-        <v>827.9536504745266</v>
+        <v>834.0271367606601</v>
       </c>
       <c r="T13" t="n">
-        <v>150.0005525189106</v>
+        <v>150.0005525783772</v>
       </c>
       <c r="U13" t="n">
-        <v>11.06324441835485</v>
+        <v>11.09946755081671</v>
       </c>
       <c r="V13" t="n">
-        <v>144.3393703210722</v>
+        <v>138.2658840349387</v>
       </c>
       <c r="W13" t="n">
-        <v>25.50467210470219</v>
+        <v>25.50467216416877</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1011165582268596</v>
+        <v>0.06489342576500512</v>
       </c>
       <c r="Y13" t="b">
         <v>1</v>
@@ -1513,7 +1513,7 @@
         <v>0.8313014507293701</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2404978999984451</v>
+        <v>0.08708670001942664</v>
       </c>
       <c r="H14" t="n">
         <v>0.00160721002612263</v>
@@ -1540,31 +1540,31 @@
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9585037231445312</v>
+        <v>0.9622455239295959</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.332565700002306</v>
+        <v>0.4591340000042692</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0005724549409933388</v>
+        <v>0.0005727298557758331</v>
       </c>
       <c r="S14" t="n">
-        <v>925.7968598894247</v>
+        <v>928.7343825331521</v>
       </c>
       <c r="T14" t="n">
-        <v>199.82815021681</v>
+        <v>201.0845483203647</v>
       </c>
       <c r="U14" t="n">
-        <v>9.000641788958129</v>
+        <v>9.000641733392783</v>
       </c>
       <c r="V14" t="n">
-        <v>77.81506062597907</v>
+        <v>80.75258326970652</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7231005269669026</v>
+        <v>0.5332975765878416</v>
       </c>
       <c r="X14" t="n">
-        <v>0.656081794724237</v>
+        <v>0.6560817391588909</v>
       </c>
       <c r="Y14" t="b">
         <v>1</v>
@@ -1592,7 +1592,7 @@
         <v>0.7431839108467102</v>
       </c>
       <c r="G15" t="n">
-        <v>0.485958599994774</v>
+        <v>0.2032650000182912</v>
       </c>
       <c r="H15" t="n">
         <v>0.2544034421443939</v>
@@ -1619,31 +1619,31 @@
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0.9999997615814209</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.447910799994133</v>
+        <v>0.4328661999898031</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0007126907585188746</v>
+        <v>0.0005092268111184239</v>
       </c>
       <c r="S15" t="n">
-        <v>840.3806130664761</v>
+        <v>836.6051926700869</v>
       </c>
       <c r="T15" t="n">
-        <v>150.0005514832273</v>
+        <v>150.0005525368144</v>
       </c>
       <c r="U15" t="n">
-        <v>9.404473062098202</v>
+        <v>9.475216883620348</v>
       </c>
       <c r="V15" t="n">
-        <v>95.5530354144521</v>
+        <v>99.32845581084132</v>
       </c>
       <c r="W15" t="n">
-        <v>29.35196358464907</v>
+        <v>29.35196463823618</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1168711003332863</v>
+        <v>0.04612727881113976</v>
       </c>
       <c r="Y15" t="b">
         <v>1</v>
@@ -1671,7 +1671,7 @@
         <v>0.7394377589225769</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4060150000004796</v>
+        <v>0.1443563999491744</v>
       </c>
       <c r="H16" t="n">
         <v>0.001615169807337224</v>
@@ -1698,31 +1698,31 @@
         <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9308580756187439</v>
+        <v>0.9290319681167603</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.873916500000632</v>
+        <v>0.6387000000104308</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0008479378884658217</v>
+        <v>0.000651575333904475</v>
       </c>
       <c r="S16" t="n">
-        <v>843.2795809991143</v>
+        <v>851.7938841828567</v>
       </c>
       <c r="T16" t="n">
-        <v>160.632657255986</v>
+        <v>160.8895431865145</v>
       </c>
       <c r="U16" t="n">
-        <v>11.11650258745972</v>
+        <v>11.15500832172363</v>
       </c>
       <c r="V16" t="n">
-        <v>119.1186751428864</v>
+        <v>110.604371959144</v>
       </c>
       <c r="W16" t="n">
-        <v>4.917724255419671</v>
+        <v>5.174610185948183</v>
       </c>
       <c r="X16" t="n">
-        <v>0.07600912189987241</v>
+        <v>0.03750338763596872</v>
       </c>
       <c r="Y16" t="b">
         <v>1</v>
@@ -1750,7 +1750,7 @@
         <v>0.8500553369522095</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4162807000029716</v>
+        <v>0.1687268000096083</v>
       </c>
       <c r="H17" t="n">
         <v>0.00160721002612263</v>
@@ -1777,31 +1777,31 @@
         <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9848967790603638</v>
+        <v>0.9894110560417175</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.235699799995928</v>
+        <v>0.4450003000092693</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0008181274752132595</v>
+        <v>0.0009250477887690067</v>
       </c>
       <c r="S17" t="n">
-        <v>923.7990498220126</v>
+        <v>926.2792646015755</v>
       </c>
       <c r="T17" t="n">
-        <v>197.3817425209418</v>
+        <v>196.8438650496468</v>
       </c>
       <c r="U17" t="n">
-        <v>9.000641793414523</v>
+        <v>9.00064172042959</v>
       </c>
       <c r="V17" t="n">
-        <v>106.5949080975288</v>
+        <v>109.0751228770916</v>
       </c>
       <c r="W17" t="n">
-        <v>0.4991727787034108</v>
+        <v>0.03870469259163656</v>
       </c>
       <c r="X17" t="n">
-        <v>1.17623937692976</v>
+        <v>1.176239303944826</v>
       </c>
       <c r="Y17" t="b">
         <v>1</v>
@@ -1829,7 +1829,7 @@
         <v>0.7394377589225769</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4538985999970464</v>
+        <v>0.1778085000114515</v>
       </c>
       <c r="H18" t="n">
         <v>0.001188212772831321</v>
@@ -1856,31 +1856,31 @@
         <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9735525846481323</v>
+        <v>0.965168297290802</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.024149200005922</v>
+        <v>0.7018846999853849</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0007249211193993688</v>
+        <v>0.0005028856103308499</v>
       </c>
       <c r="S18" t="n">
-        <v>839.613517430681</v>
+        <v>846.0574457872673</v>
       </c>
       <c r="T18" t="n">
-        <v>157.3960818469052</v>
+        <v>157.6944568662727</v>
       </c>
       <c r="U18" t="n">
-        <v>10.67762527762256</v>
+        <v>10.75329360562319</v>
       </c>
       <c r="V18" t="n">
-        <v>96.86910952004439</v>
+        <v>90.42518116345809</v>
       </c>
       <c r="W18" t="n">
-        <v>4.036191183655603</v>
+        <v>4.334566203023115</v>
       </c>
       <c r="X18" t="n">
-        <v>0.08249220136161206</v>
+        <v>0.006823873360987776</v>
       </c>
       <c r="Y18" t="b">
         <v>1</v>
@@ -1908,7 +1908,7 @@
         <v>0.6927988529205322</v>
       </c>
       <c r="G19" t="n">
-        <v>0.07825569999840809</v>
+        <v>0.02879050001502037</v>
       </c>
       <c r="H19" t="n">
         <v>0.0009034593240357935</v>
@@ -1935,28 +1935,28 @@
         <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9963584542274475</v>
+        <v>0.9971601963043213</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.6011625999963144</v>
+        <v>0.1929084999719635</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0003446523915044963</v>
+        <v>0.0001310585648752749</v>
       </c>
       <c r="S19" t="n">
-        <v>949.6456948639936</v>
+        <v>944.9859765803026</v>
       </c>
       <c r="T19" t="n">
-        <v>178.7337284714598</v>
+        <v>177.0546064824467</v>
       </c>
       <c r="U19" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V19" t="n">
-        <v>6.013008468575777</v>
+        <v>1.353290184884713</v>
       </c>
       <c r="W19" t="n">
-        <v>1.713710291923746</v>
+        <v>0.03458830291060622</v>
       </c>
       <c r="X19" t="n">
         <v>4.131327241618569</v>
@@ -1987,7 +1987,7 @@
         <v>0.8036876320838928</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2581949999948847</v>
+        <v>0.1015832000412047</v>
       </c>
       <c r="H20" t="n">
         <v>0.00160721002612263</v>
@@ -2014,31 +2014,31 @@
         <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9935641884803772</v>
+        <v>0.9896934628486633</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.172792100005609</v>
+        <v>0.3985322999651544</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0003398375702090561</v>
+        <v>0.0004673315852414817</v>
       </c>
       <c r="S20" t="n">
-        <v>929.102794511669</v>
+        <v>930.9937499493019</v>
       </c>
       <c r="T20" t="n">
-        <v>190.8634976096435</v>
+        <v>190.1789024878047</v>
       </c>
       <c r="U20" t="n">
-        <v>9.000641563284724</v>
+        <v>9.000641864130865</v>
       </c>
       <c r="V20" t="n">
-        <v>54.14486217340016</v>
+        <v>56.03581761103305</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8864212023412392</v>
+        <v>0.2018260805025136</v>
       </c>
       <c r="X20" t="n">
-        <v>1.971240778928107</v>
+        <v>1.971241079774248</v>
       </c>
       <c r="Y20" t="b">
         <v>1</v>
@@ -2066,7 +2066,7 @@
         <v>0.7394377589225769</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5248902000021189</v>
+        <v>0.1808062000200152</v>
       </c>
       <c r="H21" t="n">
         <v>0.01950404606759548</v>
@@ -2093,31 +2093,31 @@
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9999071359634399</v>
+        <v>0.9997584223747253</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.379199899995001</v>
+        <v>0.4171488999854773</v>
       </c>
       <c r="R21" t="n">
-        <v>0.0007441879715770483</v>
+        <v>0.0005148017080500722</v>
       </c>
       <c r="S21" t="n">
-        <v>829.2742070300852</v>
+        <v>832.7981029778227</v>
       </c>
       <c r="T21" t="n">
-        <v>150.0005523093434</v>
+        <v>150.0005525379823</v>
       </c>
       <c r="U21" t="n">
-        <v>10.54367341280924</v>
+        <v>10.61802640725526</v>
       </c>
       <c r="V21" t="n">
-        <v>97.28929878269957</v>
+        <v>93.76540283496206</v>
       </c>
       <c r="W21" t="n">
-        <v>10.92904465080832</v>
+        <v>10.92904487944722</v>
       </c>
       <c r="X21" t="n">
-        <v>0.09476646466454852</v>
+        <v>0.02041347021853213</v>
       </c>
       <c r="Y21" t="b">
         <v>1</v>
@@ -2145,7 +2145,7 @@
         <v>0.7539470195770264</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5124885000041104</v>
+        <v>0.1672733000013977</v>
       </c>
       <c r="H22" t="n">
         <v>0.01405216194689274</v>
@@ -2172,31 +2172,31 @@
         <v>1</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9999967813491821</v>
+        <v>0.9999943971633911</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.522029399995517</v>
+        <v>0.6998504999792203</v>
       </c>
       <c r="R22" t="n">
-        <v>0.0008885128190740943</v>
+        <v>0.0006055525736883283</v>
       </c>
       <c r="S22" t="n">
-        <v>846.7393640978421</v>
+        <v>839.6204867502371</v>
       </c>
       <c r="T22" t="n">
-        <v>150.0005525151687</v>
+        <v>150.0005526030472</v>
       </c>
       <c r="U22" t="n">
-        <v>9.000641678781566</v>
+        <v>9.000641780841656</v>
       </c>
       <c r="V22" t="n">
-        <v>120.2302994140754</v>
+        <v>127.3491767616804</v>
       </c>
       <c r="W22" t="n">
-        <v>18.40259077319578</v>
+        <v>18.40259086107426</v>
       </c>
       <c r="X22" t="n">
-        <v>0.2230540938101591</v>
+        <v>0.2230541958702492</v>
       </c>
       <c r="Y22" t="b">
         <v>1</v>
@@ -2224,7 +2224,7 @@
         <v>0.7431839108467102</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4792442999969353</v>
+        <v>0.2355058999964967</v>
       </c>
       <c r="H23" t="n">
         <v>0.0137840760871768</v>
@@ -2251,31 +2251,31 @@
         <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9999563694000244</v>
+        <v>0.9999099969863892</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.302425599998969</v>
+        <v>0.4654005999909714</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0007549930014647543</v>
+        <v>0.000536194012966007</v>
       </c>
       <c r="S23" t="n">
-        <v>837.9046021103494</v>
+        <v>835.7576483253357</v>
       </c>
       <c r="T23" t="n">
-        <v>150.0005515760341</v>
+        <v>150.0005526521587</v>
       </c>
       <c r="U23" t="n">
-        <v>9.648040810611135</v>
+        <v>9.722145860990249</v>
       </c>
       <c r="V23" t="n">
-        <v>102.9273662354038</v>
+        <v>105.0743200204175</v>
       </c>
       <c r="W23" t="n">
-        <v>11.82048848801801</v>
+        <v>11.8204895641426</v>
       </c>
       <c r="X23" t="n">
-        <v>0.1219950456981245</v>
+        <v>0.04788999531901084</v>
       </c>
       <c r="Y23" t="b">
         <v>1</v>
@@ -2303,7 +2303,7 @@
         <v>0.7118977904319763</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0707683000000543</v>
+        <v>0.03560339997056872</v>
       </c>
       <c r="H24" t="n">
         <v>0.0008416271884925663</v>
@@ -2330,28 +2330,28 @@
         <v>1</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4435377717018127</v>
+        <v>0.471419483423233</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.4324574999991455</v>
+        <v>0.2063532000174746</v>
       </c>
       <c r="R24" t="n">
-        <v>3.048932194360532e-05</v>
+        <v>0.0001400195033056661</v>
       </c>
       <c r="S24" t="n">
-        <v>967.433215288818</v>
+        <v>967.6625023618475</v>
       </c>
       <c r="T24" t="n">
-        <v>206.1015408176048</v>
+        <v>205.928584431484</v>
       </c>
       <c r="U24" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V24" t="n">
-        <v>1.836956343420297</v>
+        <v>1.607669270390829</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1008793787548257</v>
+        <v>0.2738357648756278</v>
       </c>
       <c r="X24" t="n">
         <v>2.452747916846804</v>
@@ -2382,7 +2382,7 @@
         <v>0.78890460729599</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2701446999999462</v>
+        <v>0.09828129998641089</v>
       </c>
       <c r="H25" t="n">
         <v>0.00160721002612263</v>
@@ -2409,31 +2409,31 @@
         <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9414178133010864</v>
+        <v>0.9293907880783081</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.466110900000785</v>
+        <v>0.4292687000124715</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0003356573870405555</v>
+        <v>0.0004638182872440666</v>
       </c>
       <c r="S25" t="n">
-        <v>928.2175262741487</v>
+        <v>930.4356768440496</v>
       </c>
       <c r="T25" t="n">
-        <v>198.0060002752699</v>
+        <v>198.2234771458207</v>
       </c>
       <c r="U25" t="n">
-        <v>9.00064177836744</v>
+        <v>9.000641740286104</v>
       </c>
       <c r="V25" t="n">
-        <v>53.59605143224485</v>
+        <v>55.81420200214575</v>
       </c>
       <c r="W25" t="n">
-        <v>0.000181428064706779</v>
+        <v>0.2172954424860905</v>
       </c>
       <c r="X25" t="n">
-        <v>0.7299292942278619</v>
+        <v>0.7299292561465265</v>
       </c>
       <c r="Y25" t="b">
         <v>1</v>
@@ -2461,7 +2461,7 @@
         <v>0.8152469396591187</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2707813000015449</v>
+        <v>0.102812500030268</v>
       </c>
       <c r="H26" t="n">
         <v>0.00160721002612263</v>
@@ -2488,31 +2488,31 @@
         <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>0.8771054148674011</v>
+        <v>0.8558262586593628</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.26866959999461</v>
+        <v>0.4349098000093363</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0003488020156510174</v>
+        <v>0.0004871543205808848</v>
       </c>
       <c r="S26" t="n">
-        <v>928.3880205548303</v>
+        <v>930.5626884062148</v>
       </c>
       <c r="T26" t="n">
-        <v>192.5650689080193</v>
+        <v>192.4029066600849</v>
       </c>
       <c r="U26" t="n">
-        <v>9.000641519877467</v>
+        <v>9.000641715993032</v>
       </c>
       <c r="V26" t="n">
-        <v>56.20420483615362</v>
+        <v>58.37887268753809</v>
       </c>
       <c r="W26" t="n">
-        <v>0.3748290267360233</v>
+        <v>0.2126667788016334</v>
       </c>
       <c r="X26" t="n">
-        <v>0.2698802278805861</v>
+        <v>0.2698804239961508</v>
       </c>
       <c r="Y26" t="b">
         <v>1</v>
@@ -2540,7 +2540,7 @@
         <v>0.8276203870773315</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2622172000046703</v>
+        <v>0.1094410000368953</v>
       </c>
       <c r="H27" t="n">
         <v>0.00160721002612263</v>
@@ -2567,31 +2567,31 @@
         <v>1</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9516874551773071</v>
+        <v>0.9556170105934143</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.183657100002165</v>
+        <v>0.4815266999648884</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0004550183948595077</v>
+        <v>0.0004584174894262105</v>
       </c>
       <c r="S27" t="n">
-        <v>929.6605480721981</v>
+        <v>930.3684759121219</v>
       </c>
       <c r="T27" t="n">
-        <v>211.135083321386</v>
+        <v>212.121949352405</v>
       </c>
       <c r="U27" t="n">
-        <v>9.000641392099171</v>
+        <v>9.000641791448791</v>
       </c>
       <c r="V27" t="n">
-        <v>64.23504478888924</v>
+        <v>64.94297262881298</v>
       </c>
       <c r="W27" t="n">
-        <v>1.24531243385411</v>
+        <v>0.2584464028350908</v>
       </c>
       <c r="X27" t="n">
-        <v>0.6783367663613742</v>
+        <v>0.6783371657109942</v>
       </c>
       <c r="Y27" t="b">
         <v>1</v>
@@ -2619,7 +2619,7 @@
         <v>0.6903558969497681</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1478638999979012</v>
+        <v>0.04639929998666048</v>
       </c>
       <c r="H28" t="n">
         <v>0.0008412539027631283</v>
@@ -2646,28 +2646,28 @@
         <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>0.9971801042556763</v>
+        <v>0.9973803162574768</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.5750000000043656</v>
+        <v>0.2649373999447562</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0001858387549873441</v>
+        <v>0.000113287016574759</v>
       </c>
       <c r="S28" t="n">
-        <v>964.4114647860148</v>
+        <v>964.4514433395517</v>
       </c>
       <c r="T28" t="n">
-        <v>182.3873961829869</v>
+        <v>181.4438808600451</v>
       </c>
       <c r="U28" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V28" t="n">
-        <v>0.1532862783672044</v>
+        <v>0.1932648319041164</v>
       </c>
       <c r="W28" t="n">
-        <v>0.9860155503130557</v>
+        <v>0.04250022737124937</v>
       </c>
       <c r="X28" t="n">
         <v>4.23046187338633</v>
@@ -2698,7 +2698,7 @@
         <v>0.7136481404304504</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0826221000024816</v>
+        <v>0.02956100000301376</v>
       </c>
       <c r="H29" t="n">
         <v>0.0008420366793870926</v>
@@ -2725,28 +2725,28 @@
         <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>0.9962222576141357</v>
+        <v>0.9982007741928101</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.5086211999951047</v>
+        <v>0.233598200022243</v>
       </c>
       <c r="R29" t="n">
-        <v>4.604656714946032e-05</v>
+        <v>0.0001184867942356504</v>
       </c>
       <c r="S29" t="n">
-        <v>942.370111593135</v>
+        <v>939.8322474398553</v>
       </c>
       <c r="T29" t="n">
-        <v>205.677488734921</v>
+        <v>205.9181135721143</v>
       </c>
       <c r="U29" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V29" t="n">
-        <v>2.361352742557074</v>
+        <v>0.1765114107225827</v>
       </c>
       <c r="W29" t="n">
-        <v>0.2489033520612907</v>
+        <v>0.008278514867981812</v>
       </c>
       <c r="X29" t="n">
         <v>4.048278624975101</v>
@@ -2777,7 +2777,7 @@
         <v>0.6832804679870605</v>
       </c>
       <c r="G30" t="n">
-        <v>0.08865830000286223</v>
+        <v>0.028903900005389</v>
       </c>
       <c r="H30" t="n">
         <v>0.0008359886123798788</v>
@@ -2804,28 +2804,28 @@
         <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>0.9993795156478882</v>
+        <v>0.9995225667953491</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.4492645999998786</v>
+        <v>0.1719118999899365</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0001446526584913954</v>
+        <v>8.578052802477032e-05</v>
       </c>
       <c r="S30" t="n">
-        <v>988.7245600284743</v>
+        <v>991.442869157067</v>
       </c>
       <c r="T30" t="n">
-        <v>187.8034768565056</v>
+        <v>187.0956204691894</v>
       </c>
       <c r="U30" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V30" t="n">
-        <v>2.221100873188561</v>
+        <v>0.4972082554040753</v>
       </c>
       <c r="W30" t="n">
-        <v>0.6953119948558708</v>
+        <v>0.01254439246031325</v>
       </c>
       <c r="X30" t="n">
         <v>4.916249184238919</v>
@@ -2856,7 +2856,7 @@
         <v>0.8125014901161194</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2753408999997191</v>
+        <v>0.1174386999919079</v>
       </c>
       <c r="H31" t="n">
         <v>0.00160721002612263</v>
@@ -2883,31 +2883,31 @@
         <v>1</v>
       </c>
       <c r="P31" t="n">
-        <v>0.936190664768219</v>
+        <v>0.9365798830986023</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.38021110000409</v>
+        <v>0.4212844000430778</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0004545041883829981</v>
+        <v>0.0004640481492970139</v>
       </c>
       <c r="S31" t="n">
-        <v>928.0212263047378</v>
+        <v>929.6465388077906</v>
       </c>
       <c r="T31" t="n">
-        <v>206.0854384359355</v>
+        <v>206.5242194878257</v>
       </c>
       <c r="U31" t="n">
-        <v>9.000641774578158</v>
+        <v>9.000641802677629</v>
       </c>
       <c r="V31" t="n">
-        <v>64.78222094556554</v>
+        <v>66.40753344861844</v>
       </c>
       <c r="W31" t="n">
-        <v>0.8583611536825515</v>
+        <v>0.419580101792377</v>
       </c>
       <c r="X31" t="n">
-        <v>0.5260851311730761</v>
+        <v>0.5260851592725473</v>
       </c>
       <c r="Y31" t="b">
         <v>1</v>
@@ -2935,7 +2935,7 @@
         <v>0.8058133721351624</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2681568999978481</v>
+        <v>0.1235893000266515</v>
       </c>
       <c r="H32" t="n">
         <v>0.00160721002612263</v>
@@ -2962,31 +2962,31 @@
         <v>1</v>
       </c>
       <c r="P32" t="n">
-        <v>0.9538737535476685</v>
+        <v>0.9428529739379883</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.263430400002107</v>
+        <v>0.5365784000023268</v>
       </c>
       <c r="R32" t="n">
-        <v>0.0003632345178630203</v>
+        <v>0.0004439284966792911</v>
       </c>
       <c r="S32" t="n">
-        <v>931.5006680066516</v>
+        <v>931.9264439773585</v>
       </c>
       <c r="T32" t="n">
-        <v>184.0351737861193</v>
+        <v>183.0512013726503</v>
       </c>
       <c r="U32" t="n">
-        <v>9.00064114801344</v>
+        <v>9.000641849495713</v>
       </c>
       <c r="V32" t="n">
-        <v>53.28943359833124</v>
+        <v>53.71520956903817</v>
       </c>
       <c r="W32" t="n">
-        <v>1.206675767055401</v>
+        <v>0.2227033535864109</v>
       </c>
       <c r="X32" t="n">
-        <v>1.0031330283092</v>
+        <v>1.003133729791474</v>
       </c>
       <c r="Y32" t="b">
         <v>1</v>
@@ -3014,7 +3014,7 @@
         <v>0.8501506447792053</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4451698999982909</v>
+        <v>0.1931440000189468</v>
       </c>
       <c r="H33" t="n">
         <v>0.00160721002612263</v>
@@ -3041,31 +3041,31 @@
         <v>1</v>
       </c>
       <c r="P33" t="n">
-        <v>0.9970473647117615</v>
+        <v>0.9976477026939392</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.216746699996293</v>
+        <v>0.4122283000033349</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0004207211313769221</v>
+        <v>0.000466840632725507</v>
       </c>
       <c r="S33" t="n">
-        <v>927.7660168999032</v>
+        <v>929.537710502282</v>
       </c>
       <c r="T33" t="n">
-        <v>202.0996573202283</v>
+        <v>203.1093946925668</v>
       </c>
       <c r="U33" t="n">
-        <v>9.000641748286604</v>
+        <v>9.000641802333529</v>
       </c>
       <c r="V33" t="n">
-        <v>65.85281463421109</v>
+        <v>67.62450823658992</v>
       </c>
       <c r="W33" t="n">
-        <v>0.5650484212802951</v>
+        <v>0.4446889510581968</v>
       </c>
       <c r="X33" t="n">
-        <v>2.287186825948861</v>
+        <v>2.287186879995787</v>
       </c>
       <c r="Y33" t="b">
         <v>1</v>
@@ -3093,7 +3093,7 @@
         <v>0.7136481404304504</v>
       </c>
       <c r="G34" t="n">
-        <v>0.06434140000055777</v>
+        <v>0.0248583999928087</v>
       </c>
       <c r="H34" t="n">
         <v>0.0008420366793870926</v>
@@ -3120,28 +3120,28 @@
         <v>1</v>
       </c>
       <c r="P34" t="n">
-        <v>0.9990326166152954</v>
+        <v>0.999090313911438</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.4300718000013148</v>
+        <v>0.2020485000102781</v>
       </c>
       <c r="R34" t="n">
-        <v>2.834846782207023e-05</v>
+        <v>0.0001375649590045214</v>
       </c>
       <c r="S34" t="n">
-        <v>957.1921877673193</v>
+        <v>955.8848434046689</v>
       </c>
       <c r="T34" t="n">
-        <v>207.558136724187</v>
+        <v>207.5047844854833</v>
       </c>
       <c r="U34" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V34" t="n">
-        <v>0.6817468159803184</v>
+        <v>0.6255975466700647</v>
       </c>
       <c r="W34" t="n">
-        <v>0.2277987790167515</v>
+        <v>0.2811510177204468</v>
       </c>
       <c r="X34" t="n">
         <v>4.34988346623294</v>
@@ -3172,7 +3172,7 @@
         <v>0.8125014901161194</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2332601000016439</v>
+        <v>0.1588341000024229</v>
       </c>
       <c r="H35" t="n">
         <v>0.00160721002612263</v>
@@ -3199,31 +3199,31 @@
         <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>0.9413420557975769</v>
+        <v>0.949138879776001</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.429021599993575</v>
+        <v>0.6240945000317879</v>
       </c>
       <c r="R35" t="n">
-        <v>0.0005645690835081041</v>
+        <v>0.0005808307905681431</v>
       </c>
       <c r="S35" t="n">
-        <v>926.7654413279303</v>
+        <v>928.3634621519225</v>
       </c>
       <c r="T35" t="n">
-        <v>205.2604266893572</v>
+        <v>205.4745756897852</v>
       </c>
       <c r="U35" t="n">
-        <v>9.000641734006866</v>
+        <v>9.000641886999249</v>
       </c>
       <c r="V35" t="n">
-        <v>78.73202094258568</v>
+        <v>80.33004176657789</v>
       </c>
       <c r="W35" t="n">
-        <v>0.738137868865266</v>
+        <v>0.5239888684372715</v>
       </c>
       <c r="X35" t="n">
-        <v>0.5321775300351383</v>
+        <v>0.5321776830275216</v>
       </c>
       <c r="Y35" t="b">
         <v>1</v>
@@ -3251,7 +3251,7 @@
         <v>0.8501506447792053</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3625288999974146</v>
+        <v>0.1497793999733403</v>
       </c>
       <c r="H36" t="n">
         <v>0.002021597931161523</v>
@@ -3278,31 +3278,31 @@
         <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>0.9946594834327698</v>
+        <v>0.9955601692199707</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.249669999997423</v>
+        <v>0.5615559000289068</v>
       </c>
       <c r="R36" t="n">
-        <v>0.0003833578084595501</v>
+        <v>0.0004256375541444868</v>
       </c>
       <c r="S36" t="n">
-        <v>928.4306687339489</v>
+        <v>929.8600001682789</v>
       </c>
       <c r="T36" t="n">
-        <v>203.5531517355269</v>
+        <v>204.368864520937</v>
       </c>
       <c r="U36" t="n">
-        <v>9.000641875277887</v>
+        <v>9.00064166714113</v>
       </c>
       <c r="V36" t="n">
-        <v>60.84104587886941</v>
+        <v>62.27037731319945</v>
       </c>
       <c r="W36" t="n">
-        <v>0.526518079655574</v>
+        <v>0.289194705754511</v>
       </c>
       <c r="X36" t="n">
-        <v>1.995245259216617</v>
+        <v>1.995245051079859</v>
       </c>
       <c r="Y36" t="b">
         <v>1</v>
@@ -3330,7 +3330,7 @@
         <v>0.7394377589225769</v>
       </c>
       <c r="G37" t="n">
-        <v>0.6693073000060394</v>
+        <v>0.2861473999801092</v>
       </c>
       <c r="H37" t="n">
         <v>0.004407444968819618</v>
@@ -3357,31 +3357,31 @@
         <v>1</v>
       </c>
       <c r="P37" t="n">
-        <v>0.9996563196182251</v>
+        <v>0.9993112087249756</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.217217199999141</v>
+        <v>0.475135600019712</v>
       </c>
       <c r="R37" t="n">
-        <v>0.0008111563511192799</v>
+        <v>0.0005713824066333473</v>
       </c>
       <c r="S37" t="n">
-        <v>834.9053416279284</v>
+        <v>834.7437859089091</v>
       </c>
       <c r="T37" t="n">
-        <v>150.0005516934538</v>
+        <v>150.0005525822948</v>
       </c>
       <c r="U37" t="n">
-        <v>9.965421967097869</v>
+        <v>10.05304877605965</v>
       </c>
       <c r="V37" t="n">
-        <v>111.6843416275889</v>
+        <v>111.8458973466081</v>
       </c>
       <c r="W37" t="n">
-        <v>5.825969808750898</v>
+        <v>5.825970697591941</v>
       </c>
       <c r="X37" t="n">
-        <v>0.1291949544433439</v>
+        <v>0.04156814548156262</v>
       </c>
       <c r="Y37" t="b">
         <v>1</v>
@@ -3409,7 +3409,7 @@
         <v>0.8152469396591187</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2891786999971373</v>
+        <v>0.09680699999444187</v>
       </c>
       <c r="H38" t="n">
         <v>0.00160721002612263</v>
@@ -3436,31 +3436,31 @@
         <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>0.8948182463645935</v>
+        <v>0.8727958798408508</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.229596500001207</v>
+        <v>0.5320647000335157</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0003732691402547061</v>
+        <v>0.0005206417408771813</v>
       </c>
       <c r="S38" t="n">
-        <v>927.9202013827087</v>
+        <v>929.9511534120666</v>
       </c>
       <c r="T38" t="n">
-        <v>194.8829643752386</v>
+        <v>194.9216625769731</v>
       </c>
       <c r="U38" t="n">
-        <v>9.00064177925432</v>
+        <v>9.000641801932311</v>
       </c>
       <c r="V38" t="n">
-        <v>59.81697752069158</v>
+        <v>61.84792955004946</v>
       </c>
       <c r="W38" t="n">
-        <v>0.193932994909261</v>
+        <v>0.2326311966437515</v>
       </c>
       <c r="X38" t="n">
-        <v>0.2376702373193922</v>
+        <v>0.2376702599973832</v>
       </c>
       <c r="Y38" t="b">
         <v>1</v>
@@ -3488,7 +3488,7 @@
         <v>0.8463224768638611</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2853286000026856</v>
+        <v>0.1031957000377588</v>
       </c>
       <c r="H39" t="n">
         <v>0.001724448404274881</v>
@@ -3515,31 +3515,31 @@
         <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>0.9930249452590942</v>
+        <v>0.995142936706543</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.298404399996798</v>
+        <v>0.6111965000163764</v>
       </c>
       <c r="R39" t="n">
-        <v>0.0005793051095679402</v>
+        <v>0.0006729615270160139</v>
       </c>
       <c r="S39" t="n">
-        <v>931.7527753097147</v>
+        <v>929.8304277945801</v>
       </c>
       <c r="T39" t="n">
-        <v>178.4805916897221</v>
+        <v>177.0923438096627</v>
       </c>
       <c r="U39" t="n">
-        <v>9.000641079673978</v>
+        <v>9.000641820193088</v>
       </c>
       <c r="V39" t="n">
-        <v>78.76366040692983</v>
+        <v>76.84131289179527</v>
       </c>
       <c r="W39" t="n">
-        <v>1.681882665189903</v>
+        <v>0.2936347851305356</v>
       </c>
       <c r="X39" t="n">
-        <v>1.602707164032737</v>
+        <v>1.602707904551848</v>
       </c>
       <c r="Y39" t="b">
         <v>1</v>
@@ -3567,7 +3567,7 @@
         <v>0.6916452050209045</v>
       </c>
       <c r="G40" t="n">
-        <v>0.06864929999574088</v>
+        <v>0.04405669996049255</v>
       </c>
       <c r="H40" t="n">
         <v>0.0008420366793870926</v>
@@ -3594,28 +3594,28 @@
         <v>1</v>
       </c>
       <c r="P40" t="n">
-        <v>0.8830639719963074</v>
+        <v>0.9025447368621826</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.4526412000050186</v>
+        <v>0.2014755000127479</v>
       </c>
       <c r="R40" t="n">
-        <v>1.903056181618012e-05</v>
+        <v>9.525340283289552e-05</v>
       </c>
       <c r="S40" t="n">
-        <v>949.4658506170199</v>
+        <v>949.9830341641443</v>
       </c>
       <c r="T40" t="n">
-        <v>199.1558707592875</v>
+        <v>199.1989220009441</v>
       </c>
       <c r="U40" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V40" t="n">
-        <v>0.9734049174780921</v>
+        <v>1.490588464602524</v>
       </c>
       <c r="W40" t="n">
-        <v>0.04670148479519298</v>
+        <v>0.003650243138594078</v>
       </c>
       <c r="X40" t="n">
         <v>2.94559893011786</v>
@@ -3646,7 +3646,7 @@
         <v>0.7431839108467102</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3878465999951004</v>
+        <v>0.1572997000184841</v>
       </c>
       <c r="H41" t="n">
         <v>0.01405216194689274</v>
@@ -3673,31 +3673,31 @@
         <v>1</v>
       </c>
       <c r="P41" t="n">
-        <v>0.9999992847442627</v>
+        <v>0.999997615814209</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.199550699995598</v>
+        <v>0.4425220999983139</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0006795671069994569</v>
+        <v>0.0004844892828259617</v>
       </c>
       <c r="S41" t="n">
-        <v>839.5920246361242</v>
+        <v>836.2219170079234</v>
       </c>
       <c r="T41" t="n">
-        <v>150.0005513451833</v>
+        <v>150.0005525645221</v>
       </c>
       <c r="U41" t="n">
-        <v>9.443604844038036</v>
+        <v>9.510703011436711</v>
       </c>
       <c r="V41" t="n">
-        <v>89.73563344817035</v>
+        <v>93.10574107637115</v>
       </c>
       <c r="W41" t="n">
-        <v>23.48123002439726</v>
+        <v>23.48123124373606</v>
       </c>
       <c r="X41" t="n">
-        <v>0.1113349535980657</v>
+        <v>0.04423678619939153</v>
       </c>
       <c r="Y41" t="b">
         <v>1</v>
@@ -3725,7 +3725,7 @@
         <v>0.7136481404304504</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1079536000033841</v>
+        <v>0.03786080004647374</v>
       </c>
       <c r="H42" t="n">
         <v>0.0008420366793870926</v>
@@ -3752,28 +3752,28 @@
         <v>1</v>
       </c>
       <c r="P42" t="n">
-        <v>0.9996654987335205</v>
+        <v>0.9997630715370178</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.5065219000025536</v>
+        <v>0.2070302999927662</v>
       </c>
       <c r="R42" t="n">
-        <v>5.189417061046697e-05</v>
+        <v>0.0001330657105427235</v>
       </c>
       <c r="S42" t="n">
-        <v>945.8915862948336</v>
+        <v>942.6069340955289</v>
       </c>
       <c r="T42" t="n">
-        <v>208.1659279607368</v>
+        <v>208.1771944759077</v>
       </c>
       <c r="U42" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V42" t="n">
-        <v>2.693884247985466</v>
+        <v>0.5907679513192079</v>
       </c>
       <c r="W42" t="n">
-        <v>0.2877431954897247</v>
+        <v>0.2764766803188365</v>
       </c>
       <c r="X42" t="n">
         <v>4.816442620393784</v>
@@ -3804,7 +3804,7 @@
         <v>0.6916452050209045</v>
       </c>
       <c r="G43" t="n">
-        <v>0.07154459999583196</v>
+        <v>0.02646480000112206</v>
       </c>
       <c r="H43" t="n">
         <v>0.0008420366793870926</v>
@@ -3831,28 +3831,28 @@
         <v>1</v>
       </c>
       <c r="P43" t="n">
-        <v>0.9966591596603394</v>
+        <v>0.9974554181098938</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.4647676999957184</v>
+        <v>0.2211002000258304</v>
       </c>
       <c r="R43" t="n">
-        <v>1.905684985104017e-05</v>
+        <v>0.0001060117574525066</v>
       </c>
       <c r="S43" t="n">
-        <v>952.9749566177765</v>
+        <v>951.7990226459926</v>
       </c>
       <c r="T43" t="n">
-        <v>202.3850950609859</v>
+        <v>202.2884702352036</v>
       </c>
       <c r="U43" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V43" t="n">
-        <v>0.9834874075521611</v>
+        <v>0.1924465642316591</v>
       </c>
       <c r="W43" t="n">
-        <v>0.04862964171482531</v>
+        <v>0.1452544674971534</v>
       </c>
       <c r="X43" t="n">
         <v>4.007582954793179</v>
@@ -3883,7 +3883,7 @@
         <v>0.7394377589225769</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3583410999999614</v>
+        <v>0.1337932000169531</v>
       </c>
       <c r="H44" t="n">
         <v>0.001092163613066077</v>
@@ -3910,31 +3910,31 @@
         <v>1</v>
       </c>
       <c r="P44" t="n">
-        <v>0.3692962825298309</v>
+        <v>0.4349760115146637</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.888097500006552</v>
+        <v>0.6829667999991216</v>
       </c>
       <c r="R44" t="n">
-        <v>0.0006770239560864866</v>
+        <v>0.0004785683413501829</v>
       </c>
       <c r="S44" t="n">
-        <v>857.1191728028257</v>
+        <v>865.9191356195907</v>
       </c>
       <c r="T44" t="n">
-        <v>167.5146474812732</v>
+        <v>168.4265327411502</v>
       </c>
       <c r="U44" t="n">
-        <v>10.31417131531367</v>
+        <v>10.37459700684043</v>
       </c>
       <c r="V44" t="n">
-        <v>87.38258529302539</v>
+        <v>78.58262247626033</v>
       </c>
       <c r="W44" t="n">
-        <v>3.904266931630502</v>
+        <v>4.816152191507484</v>
       </c>
       <c r="X44" t="n">
-        <v>0.06699873242642518</v>
+        <v>0.006573040899665372</v>
       </c>
       <c r="Y44" t="b">
         <v>1</v>
@@ -3962,7 +3962,7 @@
         <v>0.7118977904319763</v>
       </c>
       <c r="G45" t="n">
-        <v>0.09406180000223685</v>
+        <v>0.02786869998089969</v>
       </c>
       <c r="H45" t="n">
         <v>0.0008416271884925663</v>
@@ -3989,28 +3989,28 @@
         <v>1</v>
       </c>
       <c r="P45" t="n">
-        <v>0.9110298752784729</v>
+        <v>0.9031394124031067</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.4503598000010243</v>
+        <v>0.1949147999985144</v>
       </c>
       <c r="R45" t="n">
-        <v>2.678244891285431e-05</v>
+        <v>0.0001280892320210114</v>
       </c>
       <c r="S45" t="n">
-        <v>967.4616528201619</v>
+        <v>967.4698278760336</v>
       </c>
       <c r="T45" t="n">
-        <v>204.2693296858247</v>
+        <v>204.0471489232342</v>
       </c>
       <c r="U45" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V45" t="n">
-        <v>1.560071205458485</v>
+        <v>1.55189614958681</v>
       </c>
       <c r="W45" t="n">
-        <v>0.03856228942842677</v>
+        <v>0.2607430520189098</v>
       </c>
       <c r="X45" t="n">
         <v>3.136981069192481</v>
@@ -4041,7 +4041,7 @@
         <v>0.8040255308151245</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2764700999978231</v>
+        <v>0.1247542999917641</v>
       </c>
       <c r="H46" t="n">
         <v>0.00160721002612263</v>
@@ -4068,31 +4068,31 @@
         <v>1</v>
       </c>
       <c r="P46" t="n">
-        <v>0.9587864875793457</v>
+        <v>0.9431642889976501</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.199286300005042</v>
+        <v>0.5709519000374712</v>
       </c>
       <c r="R46" t="n">
-        <v>0.0002955686359200627</v>
+        <v>0.0004181688709650189</v>
       </c>
       <c r="S46" t="n">
-        <v>928.9606913521658</v>
+        <v>931.2774011137517</v>
       </c>
       <c r="T46" t="n">
-        <v>195.7427030768381</v>
+        <v>195.7760038956704</v>
       </c>
       <c r="U46" t="n">
-        <v>9.000641751337811</v>
+        <v>9.000641780952636</v>
       </c>
       <c r="V46" t="n">
-        <v>48.5665947855282</v>
+        <v>50.88330454711411</v>
       </c>
       <c r="W46" t="n">
-        <v>0.156489251374694</v>
+        <v>0.1897900702069819</v>
       </c>
       <c r="X46" t="n">
-        <v>1.171971328195726</v>
+        <v>1.17197135781055</v>
       </c>
       <c r="Y46" t="b">
         <v>1</v>
@@ -4120,7 +4120,7 @@
         <v>0.6761674284934998</v>
       </c>
       <c r="G47" t="n">
-        <v>0.09717950000049314</v>
+        <v>0.03480419999687001</v>
       </c>
       <c r="H47" t="n">
         <v>0.0008399065118283033</v>
@@ -4147,28 +4147,28 @@
         <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>0.7316827178001404</v>
+        <v>0.7036243081092834</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.5385124999957043</v>
+        <v>0.2270114999846555</v>
       </c>
       <c r="R47" t="n">
-        <v>0.0002641877217683941</v>
+        <v>0.0002129056229023263</v>
       </c>
       <c r="S47" t="n">
-        <v>923.2404200024794</v>
+        <v>920.2317621930941</v>
       </c>
       <c r="T47" t="n">
-        <v>211.6649160440006</v>
+        <v>212.329426659325</v>
       </c>
       <c r="U47" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V47" t="n">
-        <v>9.38716918251464</v>
+        <v>6.378511373129413</v>
       </c>
       <c r="W47" t="n">
-        <v>1.147072148270496</v>
+        <v>0.4825615329461641</v>
       </c>
       <c r="X47" t="n">
         <v>2.43637951287678</v>
@@ -4199,7 +4199,7 @@
         <v>0.7591444849967957</v>
       </c>
       <c r="G48" t="n">
-        <v>0.264119399995252</v>
+        <v>0.11431650002487</v>
       </c>
       <c r="H48" t="n">
         <v>0.001604381715878844</v>
@@ -4226,31 +4226,31 @@
         <v>1</v>
       </c>
       <c r="P48" t="n">
-        <v>0.3652864694595337</v>
+        <v>0.4181808829307556</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.116640799999004</v>
+        <v>0.4163732000160962</v>
       </c>
       <c r="R48" t="n">
-        <v>0.0005885112332180142</v>
+        <v>0.0005324264639057219</v>
       </c>
       <c r="S48" t="n">
-        <v>935.7230952232256</v>
+        <v>938.5330520078613</v>
       </c>
       <c r="T48" t="n">
-        <v>222.3186654042264</v>
+        <v>224.2186397567366</v>
       </c>
       <c r="U48" t="n">
-        <v>9.000637418355975</v>
+        <v>9.000639703030775</v>
       </c>
       <c r="V48" t="n">
-        <v>47.21539418456962</v>
+        <v>50.02535096920531</v>
       </c>
       <c r="W48" t="n">
-        <v>3.938109014373083</v>
+        <v>2.038134661862927</v>
       </c>
       <c r="X48" t="n">
-        <v>3.753278938530667</v>
+        <v>3.753281223205467</v>
       </c>
       <c r="Y48" t="b">
         <v>1</v>
@@ -4278,7 +4278,7 @@
         <v>0.8041542172431946</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2661947000015061</v>
+        <v>0.1046506999991834</v>
       </c>
       <c r="H49" t="n">
         <v>0.00160721002612263</v>
@@ -4305,31 +4305,31 @@
         <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>0.9618977308273315</v>
+        <v>0.9526969194412231</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.529994600001373</v>
+        <v>0.4265130999847315</v>
       </c>
       <c r="R49" t="n">
-        <v>0.0003134294820483774</v>
+        <v>0.0003317652444820851</v>
       </c>
       <c r="S49" t="n">
-        <v>929.4760403942433</v>
+        <v>931.1731436360317</v>
       </c>
       <c r="T49" t="n">
-        <v>204.1631038490684</v>
+        <v>204.5258074682216</v>
       </c>
       <c r="U49" t="n">
-        <v>9.000641688740028</v>
+        <v>9.000641768657816</v>
       </c>
       <c r="V49" t="n">
-        <v>47.66832280149458</v>
+        <v>49.36542604328292</v>
       </c>
       <c r="W49" t="n">
-        <v>0.6543588009276391</v>
+        <v>0.2916551817744164</v>
       </c>
       <c r="X49" t="n">
-        <v>1.369651488502904</v>
+        <v>1.369651568420692</v>
       </c>
       <c r="Y49" t="b">
         <v>1</v>
@@ -4357,7 +4357,7 @@
         <v>0.7959065437316895</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2584471000009216</v>
+        <v>0.09488410002086312</v>
       </c>
       <c r="H50" t="n">
         <v>0.00160721002612263</v>
@@ -4384,31 +4384,31 @@
         <v>1</v>
       </c>
       <c r="P50" t="n">
-        <v>0.9901665449142456</v>
+        <v>0.9758033752441406</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.227842499996768</v>
+        <v>0.4082495999755338</v>
       </c>
       <c r="R50" t="n">
-        <v>0.000310430972604081</v>
+        <v>0.00043777099926956</v>
       </c>
       <c r="S50" t="n">
-        <v>928.7446065262505</v>
+        <v>931.0034440997713</v>
       </c>
       <c r="T50" t="n">
-        <v>195.5214045915932</v>
+        <v>195.5545635562019</v>
       </c>
       <c r="U50" t="n">
-        <v>9.00064180754033</v>
+        <v>9.000641735098666</v>
       </c>
       <c r="V50" t="n">
-        <v>50.4499673696422</v>
+        <v>52.70880494316293</v>
       </c>
       <c r="W50" t="n">
-        <v>0.1650522065670543</v>
+        <v>0.1982111711757852</v>
       </c>
       <c r="X50" t="n">
-        <v>2.395768660316175</v>
+        <v>2.395768587874512</v>
       </c>
       <c r="Y50" t="b">
         <v>1</v>
@@ -4436,7 +4436,7 @@
         <v>0.7599234580993652</v>
       </c>
       <c r="G51" t="n">
-        <v>0.4327330999949481</v>
+        <v>0.1620672999997623</v>
       </c>
       <c r="H51" t="n">
         <v>0.01405216194689274</v>
@@ -4466,28 +4466,28 @@
         <v>0.9999998807907104</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.50650279999536</v>
+        <v>0.4539263000478968</v>
       </c>
       <c r="R51" t="n">
-        <v>0.0008941132109612226</v>
+        <v>0.0006105663487687707</v>
       </c>
       <c r="S51" t="n">
-        <v>846.7827145854616</v>
+        <v>839.6571754980539</v>
       </c>
       <c r="T51" t="n">
-        <v>150.0005525377416</v>
+        <v>150.0005525849829</v>
       </c>
       <c r="U51" t="n">
-        <v>9.000641704997239</v>
+        <v>9.000641759862207</v>
       </c>
       <c r="V51" t="n">
-        <v>121.3722574108912</v>
+        <v>128.4977964982988</v>
       </c>
       <c r="W51" t="n">
-        <v>28.74694426688276</v>
+        <v>28.74694431412405</v>
       </c>
       <c r="X51" t="n">
-        <v>0.3050666747434754</v>
+        <v>0.3050667296084431</v>
       </c>
       <c r="Y51" t="b">
         <v>1</v>
@@ -4515,7 +4515,7 @@
         <v>0.7394377589225769</v>
       </c>
       <c r="G52" t="n">
-        <v>0.5601841000025161</v>
+        <v>0.2390685999998823</v>
       </c>
       <c r="H52" t="n">
         <v>0.02069401741027832</v>
@@ -4542,31 +4542,31 @@
         <v>1</v>
       </c>
       <c r="P52" t="n">
-        <v>0.9997976422309875</v>
+        <v>0.9994592070579529</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.31335019999824</v>
+        <v>0.5505838000099175</v>
       </c>
       <c r="R52" t="n">
-        <v>0.0008404589025303721</v>
+        <v>0.0006080094026401639</v>
       </c>
       <c r="S52" t="n">
-        <v>826.6649636867384</v>
+        <v>832.9548358118973</v>
       </c>
       <c r="T52" t="n">
-        <v>150.0005525335621</v>
+        <v>150.000552568158</v>
       </c>
       <c r="U52" t="n">
-        <v>11.08256768908223</v>
+        <v>11.11321792827218</v>
       </c>
       <c r="V52" t="n">
-        <v>111.9430072354093</v>
+        <v>105.6531351102503</v>
       </c>
       <c r="W52" t="n">
-        <v>8.278786757412121</v>
+        <v>8.278786792007992</v>
       </c>
       <c r="X52" t="n">
-        <v>0.08402666875018916</v>
+        <v>0.05337642956023991</v>
       </c>
       <c r="Y52" t="b">
         <v>1</v>
@@ -4594,7 +4594,7 @@
         <v>0.8041200637817383</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2437291999958688</v>
+        <v>0.1043762999470346</v>
       </c>
       <c r="H53" t="n">
         <v>0.00160721002612263</v>
@@ -4621,31 +4621,31 @@
         <v>1</v>
       </c>
       <c r="P53" t="n">
-        <v>0.9897705316543579</v>
+        <v>0.9886653423309326</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.296600900001067</v>
+        <v>0.4673085999675095</v>
       </c>
       <c r="R53" t="n">
-        <v>0.0003744474670384079</v>
+        <v>0.0003781947598326951</v>
       </c>
       <c r="S53" t="n">
-        <v>929.2656573742784</v>
+        <v>930.8052859169306</v>
       </c>
       <c r="T53" t="n">
-        <v>206.7390007582378</v>
+        <v>207.3852599733199</v>
       </c>
       <c r="U53" t="n">
-        <v>9.000641525423552</v>
+        <v>9.000641711753751</v>
       </c>
       <c r="V53" t="n">
-        <v>53.80241938832182</v>
+        <v>55.3420479309741</v>
       </c>
       <c r="W53" t="n">
-        <v>0.9900673259879511</v>
+        <v>0.3438081109057975</v>
       </c>
       <c r="X53" t="n">
-        <v>2.135000693716272</v>
+        <v>2.135000880046471</v>
       </c>
       <c r="Y53" t="b">
         <v>1</v>
@@ -4673,7 +4673,7 @@
         <v>0.7136481404304504</v>
       </c>
       <c r="G54" t="n">
-        <v>0.07957509999687318</v>
+        <v>0.0265967000159435</v>
       </c>
       <c r="H54" t="n">
         <v>0.0008420366793870926</v>
@@ -4700,28 +4700,28 @@
         <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>0.9495652914047241</v>
+        <v>0.9477619528770447</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.5692853000000468</v>
+        <v>0.1612867999938317</v>
       </c>
       <c r="R54" t="n">
-        <v>2.303709152329247e-05</v>
+        <v>0.0001350645325146616</v>
       </c>
       <c r="S54" t="n">
-        <v>959.9687462346609</v>
+        <v>959.6167280212775</v>
       </c>
       <c r="T54" t="n">
-        <v>206.9179120232771</v>
+        <v>206.7329868208328</v>
       </c>
       <c r="U54" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V54" t="n">
-        <v>0.2704979879026723</v>
+        <v>0.6225162012860892</v>
       </c>
       <c r="W54" t="n">
-        <v>0.08987732745526955</v>
+        <v>0.2748025298995742</v>
       </c>
       <c r="X54" t="n">
         <v>3.228398435466103</v>
@@ -4752,7 +4752,7 @@
         <v>0.8152469396591187</v>
       </c>
       <c r="G55" t="n">
-        <v>0.4454246999957832</v>
+        <v>0.1608525000046939</v>
       </c>
       <c r="H55" t="n">
         <v>0.00160721002612263</v>
@@ -4779,31 +4779,31 @@
         <v>1</v>
       </c>
       <c r="P55" t="n">
-        <v>0.9244984984397888</v>
+        <v>0.9163233637809753</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.220590699995228</v>
+        <v>0.5402483000070788</v>
       </c>
       <c r="R55" t="n">
-        <v>0.0004675545205827802</v>
+        <v>0.0005096686654724181</v>
       </c>
       <c r="S55" t="n">
-        <v>926.6899473672918</v>
+        <v>929.4486746483415</v>
       </c>
       <c r="T55" t="n">
-        <v>198.765854024484</v>
+        <v>200.0797792406213</v>
       </c>
       <c r="U55" t="n">
-        <v>9.000641756911103</v>
+        <v>9.000641638419866</v>
       </c>
       <c r="V55" t="n">
-        <v>65.60689586080969</v>
+        <v>68.36562314185937</v>
       </c>
       <c r="W55" t="n">
-        <v>0.5873220353965678</v>
+        <v>0.7266031807407387</v>
       </c>
       <c r="X55" t="n">
-        <v>0.3555769766138663</v>
+        <v>0.35557685812263</v>
       </c>
       <c r="Y55" t="b">
         <v>1</v>
@@ -4831,7 +4831,7 @@
         <v>0.8306360840797424</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2652698000019882</v>
+        <v>0.1015162999974564</v>
       </c>
       <c r="H56" t="n">
         <v>0.00160721002612263</v>
@@ -4858,31 +4858,31 @@
         <v>1</v>
       </c>
       <c r="P56" t="n">
-        <v>0.9553053379058838</v>
+        <v>0.9608390331268311</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.241435900003125</v>
+        <v>0.4306281000026502</v>
       </c>
       <c r="R56" t="n">
-        <v>0.0004869443364441395</v>
+        <v>0.0006343166460283101</v>
       </c>
       <c r="S56" t="n">
-        <v>929.232772858305</v>
+        <v>929.4841693611487</v>
       </c>
       <c r="T56" t="n">
-        <v>185.9174363753475</v>
+        <v>184.8825345888584</v>
       </c>
       <c r="U56" t="n">
-        <v>9.000641345490003</v>
+        <v>9.000641786702143</v>
       </c>
       <c r="V56" t="n">
-        <v>72.86446816738953</v>
+        <v>73.11586467023324</v>
       </c>
       <c r="W56" t="n">
-        <v>1.357591377153398</v>
+        <v>0.3226895906643392</v>
       </c>
       <c r="X56" t="n">
-        <v>0.65362695147582</v>
+        <v>0.6536273926879606</v>
       </c>
       <c r="Y56" t="b">
         <v>1</v>
@@ -4910,7 +4910,7 @@
         <v>0.5854483246803284</v>
       </c>
       <c r="G57" t="n">
-        <v>0.08755499999824679</v>
+        <v>0.03032320004422218</v>
       </c>
       <c r="H57" t="n">
         <v>0.002010466996580362</v>
@@ -4937,28 +4937,28 @@
         <v>1</v>
       </c>
       <c r="P57" t="n">
-        <v>0.9249246716499329</v>
+        <v>0.9215929508209229</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.082642600005784</v>
+        <v>0.2074997000163421</v>
       </c>
       <c r="R57" t="n">
-        <v>0.0007656744564883411</v>
+        <v>0.0001241768768522888</v>
       </c>
       <c r="S57" t="n">
-        <v>947.9854923616515</v>
+        <v>952.9452786214741</v>
       </c>
       <c r="T57" t="n">
-        <v>173.8604224924369</v>
+        <v>170.2671734068721</v>
       </c>
       <c r="U57" t="n">
         <v>9.000641779862162</v>
       </c>
       <c r="V57" t="n">
-        <v>4.190603654130427</v>
+        <v>0.7691826056922082</v>
       </c>
       <c r="W57" t="n">
-        <v>3.519236884924823</v>
+        <v>0.07401220063994174</v>
       </c>
       <c r="X57" t="n">
         <v>3.232041353522229</v>
@@ -4989,7 +4989,7 @@
         <v>0.6532474756240845</v>
       </c>
       <c r="G58" t="n">
-        <v>0.4673800000018673</v>
+        <v>0.1780314999632537</v>
       </c>
       <c r="H58" t="n">
         <v>0.01299904845654964</v>
@@ -5016,31 +5016,31 @@
         <v>1</v>
       </c>
       <c r="P58" t="n">
-        <v>0.3177532553672791</v>
+        <v>0.315390557050705</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.972996000004059</v>
+        <v>0.8235337000223808</v>
       </c>
       <c r="R58" t="n">
-        <v>0.0008190005901269615</v>
+        <v>0.0008319269400089979</v>
       </c>
       <c r="S58" t="n">
-        <v>855.4944084283692</v>
+        <v>874.9578204842621</v>
       </c>
       <c r="T58" t="n">
-        <v>168.9675787393436</v>
+        <v>171.1498702235159</v>
       </c>
       <c r="U58" t="n">
-        <v>11.32283305963921</v>
+        <v>11.41113156683861</v>
       </c>
       <c r="V58" t="n">
-        <v>116.4379642321704</v>
+        <v>96.97455217627748</v>
       </c>
       <c r="W58" t="n">
-        <v>5.344733543190898</v>
+        <v>7.52702502736318</v>
       </c>
       <c r="X58" t="n">
-        <v>0.06048680332523837</v>
+        <v>0.02781170387416232</v>
       </c>
       <c r="Y58" t="b">
         <v>1</v>
@@ -5068,7 +5068,7 @@
         <v>0.8036876320838928</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2466894000026514</v>
+        <v>0.1404349000076763</v>
       </c>
       <c r="H59" t="n">
         <v>0.00160721002612263</v>
@@ -5095,31 +5095,31 @@
         <v>1</v>
       </c>
       <c r="P59" t="n">
-        <v>0.9910854697227478</v>
+        <v>0.9760629534721375</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.102226399998472</v>
+        <v>0.5851866000448354</v>
       </c>
       <c r="R59" t="n">
-        <v>0.0003135894949082285</v>
+        <v>0.0004298822896089405</v>
       </c>
       <c r="S59" t="n">
-        <v>930.0498938375127</v>
+        <v>931.6412686597633</v>
       </c>
       <c r="T59" t="n">
-        <v>189.2416970678907</v>
+        <v>188.6173827335263</v>
       </c>
       <c r="U59" t="n">
-        <v>9.000641557658593</v>
+        <v>9.000641757205976</v>
       </c>
       <c r="V5